--- a/database/HAPV3.xlsx
+++ b/database/HAPV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2084"/>
+  <dimension ref="A1:F2085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>43217</v>
       </c>
       <c r="B3" t="n">
-        <v>82.00556945800781</v>
+        <v>82.00554656982422</v>
       </c>
       <c r="C3" t="n">
-        <v>83.90926719826945</v>
+        <v>83.90924377875386</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54118428911481</v>
+        <v>80.54116180964878</v>
       </c>
       <c r="E3" t="n">
-        <v>81.97628294634966</v>
+        <v>81.97626006634007</v>
       </c>
       <c r="F3" t="n">
         <v>932166</v>
@@ -492,16 +492,16 @@
         <v>43220</v>
       </c>
       <c r="B4" t="n">
-        <v>80.98047637939453</v>
+        <v>80.98049163818359</v>
       </c>
       <c r="C4" t="n">
-        <v>82.00554871766383</v>
+        <v>82.00556416960269</v>
       </c>
       <c r="D4" t="n">
-        <v>80.68760388863633</v>
+        <v>80.68761909224075</v>
       </c>
       <c r="E4" t="n">
-        <v>81.56622880915717</v>
+        <v>81.56624417831694</v>
       </c>
       <c r="F4" t="n">
         <v>370366</v>
@@ -512,16 +512,16 @@
         <v>43222</v>
       </c>
       <c r="B5" t="n">
-        <v>79.98471832275391</v>
+        <v>79.98471069335938</v>
       </c>
       <c r="C5" t="n">
-        <v>81.85912955369824</v>
+        <v>81.85912174551177</v>
       </c>
       <c r="D5" t="n">
-        <v>79.07679921897648</v>
+        <v>79.0767916761844</v>
       </c>
       <c r="E5" t="n">
-        <v>79.07679921897648</v>
+        <v>79.0767916761844</v>
       </c>
       <c r="F5" t="n">
         <v>428333</v>
@@ -532,16 +532,16 @@
         <v>43223</v>
       </c>
       <c r="B6" t="n">
-        <v>80.51187896728516</v>
+        <v>80.51188659667969</v>
       </c>
       <c r="C6" t="n">
-        <v>81.71267035421486</v>
+        <v>81.71267809739771</v>
       </c>
       <c r="D6" t="n">
-        <v>78.49102820427865</v>
+        <v>78.49103564217513</v>
       </c>
       <c r="E6" t="n">
-        <v>79.39894709480311</v>
+        <v>79.39895461873498</v>
       </c>
       <c r="F6" t="n">
         <v>790600</v>
@@ -652,16 +652,16 @@
         <v>43231</v>
       </c>
       <c r="B12" t="n">
-        <v>80.83403015136719</v>
+        <v>80.83406066894531</v>
       </c>
       <c r="C12" t="n">
-        <v>82.59129475284621</v>
+        <v>82.59132593385111</v>
       </c>
       <c r="D12" t="n">
-        <v>80.48258467931706</v>
+        <v>80.48261506421264</v>
       </c>
       <c r="E12" t="n">
-        <v>80.51187118130076</v>
+        <v>80.51190157725298</v>
       </c>
       <c r="F12" t="n">
         <v>586000</v>
@@ -692,16 +692,16 @@
         <v>43235</v>
       </c>
       <c r="B14" t="n">
-        <v>84.78787231445312</v>
+        <v>84.78789520263672</v>
       </c>
       <c r="C14" t="n">
-        <v>85.22718474346625</v>
+        <v>85.22720775024067</v>
       </c>
       <c r="D14" t="n">
-        <v>82.00554288479667</v>
+        <v>82.00556502190037</v>
       </c>
       <c r="E14" t="n">
-        <v>82.29841535472352</v>
+        <v>82.29843757088707</v>
       </c>
       <c r="F14" t="n">
         <v>900866</v>
@@ -732,16 +732,16 @@
         <v>43237</v>
       </c>
       <c r="B16" t="n">
-        <v>88.74173736572266</v>
+        <v>88.74172973632812</v>
       </c>
       <c r="C16" t="n">
-        <v>90.7333019689424</v>
+        <v>90.73329416832706</v>
       </c>
       <c r="D16" t="n">
-        <v>87.86310482779517</v>
+        <v>87.86309727393932</v>
       </c>
       <c r="E16" t="n">
-        <v>87.86310482779517</v>
+        <v>87.86309727393932</v>
       </c>
       <c r="F16" t="n">
         <v>520533</v>
@@ -752,16 +752,16 @@
         <v>43238</v>
       </c>
       <c r="B17" t="n">
-        <v>86.69158935546875</v>
+        <v>86.69159698486328</v>
       </c>
       <c r="C17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74174216703163</v>
       </c>
       <c r="D17" t="n">
-        <v>85.60795128505117</v>
+        <v>85.60795881907887</v>
       </c>
       <c r="E17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74174216703163</v>
       </c>
       <c r="F17" t="n">
         <v>980066</v>
@@ -792,16 +792,16 @@
         <v>43242</v>
       </c>
       <c r="B19" t="n">
-        <v>95.91720581054688</v>
+        <v>95.91722106933594</v>
       </c>
       <c r="C19" t="n">
-        <v>96.06364578234965</v>
+        <v>96.06366106443481</v>
       </c>
       <c r="D19" t="n">
-        <v>90.20610649620939</v>
+        <v>90.2061208464601</v>
       </c>
       <c r="E19" t="n">
-        <v>90.20610649620939</v>
+        <v>90.2061208464601</v>
       </c>
       <c r="F19" t="n">
         <v>462766</v>
@@ -812,16 +812,16 @@
         <v>43243</v>
       </c>
       <c r="B20" t="n">
-        <v>95.74148559570312</v>
+        <v>95.74147796630859</v>
       </c>
       <c r="C20" t="n">
-        <v>95.91721208371003</v>
+        <v>95.9172044403123</v>
       </c>
       <c r="D20" t="n">
-        <v>90.79186487313009</v>
+        <v>90.79185763815821</v>
       </c>
       <c r="E20" t="n">
-        <v>95.91721208371003</v>
+        <v>95.9172044403123</v>
       </c>
       <c r="F20" t="n">
         <v>487666</v>
@@ -832,16 +832,16 @@
         <v>43244</v>
       </c>
       <c r="B21" t="n">
-        <v>89.32748413085938</v>
+        <v>89.32749938964844</v>
       </c>
       <c r="C21" t="n">
-        <v>93.77921210410572</v>
+        <v>93.77922812333239</v>
       </c>
       <c r="D21" t="n">
-        <v>89.09318461864831</v>
+        <v>89.09319983741467</v>
       </c>
       <c r="E21" t="n">
-        <v>93.13488658346348</v>
+        <v>93.1349024926274</v>
       </c>
       <c r="F21" t="n">
         <v>822100</v>
@@ -852,16 +852,16 @@
         <v>43245</v>
       </c>
       <c r="B22" t="n">
-        <v>90.76258087158203</v>
+        <v>90.7625732421875</v>
       </c>
       <c r="C22" t="n">
-        <v>90.879726901322</v>
+        <v>90.87971926208031</v>
       </c>
       <c r="D22" t="n">
-        <v>87.95095698586984</v>
+        <v>87.95094959281705</v>
       </c>
       <c r="E22" t="n">
-        <v>88.77101643528491</v>
+        <v>88.77100897329892</v>
       </c>
       <c r="F22" t="n">
         <v>562433</v>
@@ -892,16 +892,16 @@
         <v>43249</v>
       </c>
       <c r="B24" t="n">
-        <v>87.16019439697266</v>
+        <v>87.16018676757812</v>
       </c>
       <c r="C24" t="n">
-        <v>88.88816542744976</v>
+        <v>88.88815764680072</v>
       </c>
       <c r="D24" t="n">
-        <v>84.49501040785843</v>
+        <v>84.49500301175549</v>
       </c>
       <c r="E24" t="n">
-        <v>87.27734787886412</v>
+        <v>87.27734023921479</v>
       </c>
       <c r="F24" t="n">
         <v>175300</v>
@@ -932,16 +932,16 @@
         <v>43252</v>
       </c>
       <c r="B26" t="n">
-        <v>87.54095458984375</v>
+        <v>87.54093170166016</v>
       </c>
       <c r="C26" t="n">
-        <v>90.76260534482641</v>
+        <v>90.76258161432011</v>
       </c>
       <c r="D26" t="n">
-        <v>84.90506393449363</v>
+        <v>84.90504173548175</v>
       </c>
       <c r="E26" t="n">
-        <v>89.70824610338673</v>
+        <v>89.70822264854989</v>
       </c>
       <c r="F26" t="n">
         <v>391033</v>
@@ -952,16 +952,16 @@
         <v>43255</v>
       </c>
       <c r="B27" t="n">
-        <v>88.74173736572266</v>
+        <v>88.74172973632812</v>
       </c>
       <c r="C27" t="n">
-        <v>90.2061224461859</v>
+        <v>90.20611469089378</v>
       </c>
       <c r="D27" t="n">
-        <v>86.72088625261327</v>
+        <v>86.72087879695741</v>
       </c>
       <c r="E27" t="n">
-        <v>88.44885737033093</v>
+        <v>88.44884976611618</v>
       </c>
       <c r="F27" t="n">
         <v>304000</v>
@@ -992,16 +992,16 @@
         <v>43257</v>
       </c>
       <c r="B29" t="n">
-        <v>83.411376953125</v>
+        <v>83.41136932373047</v>
       </c>
       <c r="C29" t="n">
-        <v>85.46151458562363</v>
+        <v>85.46150676870901</v>
       </c>
       <c r="D29" t="n">
-        <v>81.71268488917815</v>
+        <v>81.71267741515801</v>
       </c>
       <c r="E29" t="n">
-        <v>84.99290808047505</v>
+        <v>84.9929003064225</v>
       </c>
       <c r="F29" t="n">
         <v>443766</v>
@@ -1012,16 +1012,16 @@
         <v>43258</v>
       </c>
       <c r="B30" t="n">
-        <v>80.83403015136719</v>
+        <v>80.83406066894531</v>
       </c>
       <c r="C30" t="n">
-        <v>83.41135404961831</v>
+        <v>83.41138554022331</v>
       </c>
       <c r="D30" t="n">
-        <v>78.63745312364125</v>
+        <v>78.63748281193732</v>
       </c>
       <c r="E30" t="n">
-        <v>83.41135404961831</v>
+        <v>83.41138554022331</v>
       </c>
       <c r="F30" t="n">
         <v>547066</v>
@@ -1032,16 +1032,16 @@
         <v>43259</v>
       </c>
       <c r="B31" t="n">
-        <v>80.98047637939453</v>
+        <v>80.98049163818359</v>
       </c>
       <c r="C31" t="n">
-        <v>83.1477670729379</v>
+        <v>83.14778274009986</v>
       </c>
       <c r="D31" t="n">
-        <v>79.0767791206044</v>
+        <v>79.07679402068831</v>
       </c>
       <c r="E31" t="n">
-        <v>79.75039851136687</v>
+        <v>79.75041353837787</v>
       </c>
       <c r="F31" t="n">
         <v>443000</v>
@@ -1072,16 +1072,16 @@
         <v>43263</v>
       </c>
       <c r="B33" t="n">
-        <v>82.23986053466797</v>
+        <v>82.23985290527344</v>
       </c>
       <c r="C33" t="n">
-        <v>83.38207906125773</v>
+        <v>83.38207132589955</v>
       </c>
       <c r="D33" t="n">
-        <v>80.07256951606338</v>
+        <v>80.0725620877285</v>
       </c>
       <c r="E33" t="n">
-        <v>81.419808499654</v>
+        <v>81.41980094633571</v>
       </c>
       <c r="F33" t="n">
         <v>203566</v>
@@ -1112,16 +1112,16 @@
         <v>43265</v>
       </c>
       <c r="B35" t="n">
-        <v>79.13536834716797</v>
+        <v>79.13535308837891</v>
       </c>
       <c r="C35" t="n">
-        <v>80.21901391602279</v>
+        <v>80.21899844828646</v>
       </c>
       <c r="D35" t="n">
-        <v>77.90528277879942</v>
+        <v>77.90526775719401</v>
       </c>
       <c r="E35" t="n">
-        <v>78.19816277782689</v>
+        <v>78.19814769974872</v>
       </c>
       <c r="F35" t="n">
         <v>536566</v>
@@ -1152,16 +1152,16 @@
         <v>43269</v>
       </c>
       <c r="B37" t="n">
-        <v>77.26097106933594</v>
+        <v>77.26094818115234</v>
       </c>
       <c r="C37" t="n">
-        <v>79.07680951327856</v>
+        <v>79.07678608716174</v>
       </c>
       <c r="D37" t="n">
-        <v>76.73379144545751</v>
+        <v>76.7337687134483</v>
       </c>
       <c r="E37" t="n">
-        <v>79.07680951327856</v>
+        <v>79.07678608716174</v>
       </c>
       <c r="F37" t="n">
         <v>465333</v>
@@ -1172,16 +1172,16 @@
         <v>43270</v>
       </c>
       <c r="B38" t="n">
-        <v>81.56624603271484</v>
+        <v>81.56623077392578</v>
       </c>
       <c r="C38" t="n">
-        <v>83.14778463045384</v>
+        <v>83.14776907580264</v>
       </c>
       <c r="D38" t="n">
-        <v>77.02665815728874</v>
+        <v>77.02664374773103</v>
       </c>
       <c r="E38" t="n">
-        <v>77.84671024246967</v>
+        <v>77.8466956795029</v>
       </c>
       <c r="F38" t="n">
         <v>159600</v>
@@ -1212,16 +1212,16 @@
         <v>43272</v>
       </c>
       <c r="B40" t="n">
-        <v>82.62059783935547</v>
+        <v>82.62061309814453</v>
       </c>
       <c r="C40" t="n">
-        <v>85.46150827396475</v>
+        <v>85.4615240574275</v>
       </c>
       <c r="D40" t="n">
-        <v>80.10185388772712</v>
+        <v>80.10186868134184</v>
       </c>
       <c r="E40" t="n">
-        <v>83.46994380860144</v>
+        <v>83.46995922425201</v>
       </c>
       <c r="F40" t="n">
         <v>246900</v>
@@ -1232,16 +1232,16 @@
         <v>43273</v>
       </c>
       <c r="B41" t="n">
-        <v>84.93433380126953</v>
+        <v>84.93434906005859</v>
       </c>
       <c r="C41" t="n">
-        <v>85.52008633783566</v>
+        <v>85.52010170185748</v>
       </c>
       <c r="D41" t="n">
-        <v>81.21479811823937</v>
+        <v>81.21481270879913</v>
       </c>
       <c r="E41" t="n">
-        <v>82.03485017978244</v>
+        <v>82.03486491766779</v>
       </c>
       <c r="F41" t="n">
         <v>298800</v>
@@ -1272,16 +1272,16 @@
         <v>43277</v>
       </c>
       <c r="B43" t="n">
-        <v>86.75016784667969</v>
+        <v>86.75018310546875</v>
       </c>
       <c r="C43" t="n">
-        <v>87.86309984890605</v>
+        <v>87.86311530345259</v>
       </c>
       <c r="D43" t="n">
-        <v>85.08076984334015</v>
+        <v>85.08078480849298</v>
       </c>
       <c r="E43" t="n">
-        <v>86.60372785728207</v>
+        <v>86.60374309031327</v>
       </c>
       <c r="F43" t="n">
         <v>153233</v>
@@ -1312,16 +1312,16 @@
         <v>43279</v>
       </c>
       <c r="B45" t="n">
-        <v>88.68315887451172</v>
+        <v>88.68314361572266</v>
       </c>
       <c r="C45" t="n">
-        <v>88.68315887451172</v>
+        <v>88.68314361572266</v>
       </c>
       <c r="D45" t="n">
-        <v>85.37364911475306</v>
+        <v>85.37363442539693</v>
       </c>
       <c r="E45" t="n">
-        <v>87.8631067863316</v>
+        <v>87.86309166864037</v>
       </c>
       <c r="F45" t="n">
         <v>922066</v>
@@ -1332,16 +1332,16 @@
         <v>43280</v>
       </c>
       <c r="B46" t="n">
-        <v>87.54095458984375</v>
+        <v>87.54093170166016</v>
       </c>
       <c r="C46" t="n">
-        <v>89.41536605357047</v>
+        <v>89.41534267530913</v>
       </c>
       <c r="D46" t="n">
-        <v>85.37366307630077</v>
+        <v>85.37364075477042</v>
       </c>
       <c r="E46" t="n">
-        <v>87.45309504384831</v>
+        <v>87.45307217863621</v>
       </c>
       <c r="F46" t="n">
         <v>492266</v>
@@ -1352,16 +1352,16 @@
         <v>43283</v>
       </c>
       <c r="B47" t="n">
-        <v>86.10584259033203</v>
+        <v>86.1058349609375</v>
       </c>
       <c r="C47" t="n">
-        <v>86.95518864636772</v>
+        <v>86.95518094171702</v>
       </c>
       <c r="D47" t="n">
-        <v>85.87154305524381</v>
+        <v>85.87153544660936</v>
       </c>
       <c r="E47" t="n">
-        <v>86.04726956862196</v>
+        <v>86.04726194441729</v>
       </c>
       <c r="F47" t="n">
         <v>88033</v>
@@ -1372,16 +1372,16 @@
         <v>43284</v>
       </c>
       <c r="B48" t="n">
-        <v>85.52008819580078</v>
+        <v>85.52008056640625</v>
       </c>
       <c r="C48" t="n">
-        <v>87.21877282322158</v>
+        <v>87.21876504228447</v>
       </c>
       <c r="D48" t="n">
-        <v>83.93854960928969</v>
+        <v>83.93854212098695</v>
       </c>
       <c r="E48" t="n">
-        <v>86.72088725285975</v>
+        <v>86.72087951633988</v>
       </c>
       <c r="F48" t="n">
         <v>142500</v>
@@ -1392,16 +1392,16 @@
         <v>43285</v>
       </c>
       <c r="B49" t="n">
-        <v>85.78368377685547</v>
+        <v>85.78366851806641</v>
       </c>
       <c r="C49" t="n">
-        <v>87.07234239603083</v>
+        <v>87.07232690802138</v>
       </c>
       <c r="D49" t="n">
-        <v>84.14357212988246</v>
+        <v>84.14355716282856</v>
       </c>
       <c r="E49" t="n">
-        <v>86.66230889810163</v>
+        <v>86.66229348302694</v>
       </c>
       <c r="F49" t="n">
         <v>320933</v>
@@ -1412,16 +1412,16 @@
         <v>43286</v>
       </c>
       <c r="B50" t="n">
-        <v>85.52008819580078</v>
+        <v>85.52008056640625</v>
       </c>
       <c r="C50" t="n">
-        <v>86.31085376493245</v>
+        <v>86.31084606499235</v>
       </c>
       <c r="D50" t="n">
-        <v>84.29000262851439</v>
+        <v>84.28999510885791</v>
       </c>
       <c r="E50" t="n">
-        <v>85.78368168434318</v>
+        <v>85.78367403143302</v>
       </c>
       <c r="F50" t="n">
         <v>391100</v>
@@ -1432,16 +1432,16 @@
         <v>43287</v>
       </c>
       <c r="B51" t="n">
-        <v>83.61638641357422</v>
+        <v>83.61637878417969</v>
       </c>
       <c r="C51" t="n">
-        <v>85.57865698425219</v>
+        <v>85.57864917581456</v>
       </c>
       <c r="D51" t="n">
-        <v>83.61638641357422</v>
+        <v>83.61637878417969</v>
       </c>
       <c r="E51" t="n">
-        <v>85.52008396669386</v>
+        <v>85.52007616360061</v>
       </c>
       <c r="F51" t="n">
         <v>769100</v>
@@ -1452,16 +1452,16 @@
         <v>43291</v>
       </c>
       <c r="B52" t="n">
-        <v>84.23142242431641</v>
+        <v>84.23143768310547</v>
       </c>
       <c r="C52" t="n">
-        <v>86.07654689375923</v>
+        <v>86.07656248679844</v>
       </c>
       <c r="D52" t="n">
-        <v>83.17706345656418</v>
+        <v>83.17707852435278</v>
       </c>
       <c r="E52" t="n">
-        <v>84.14356290112728</v>
+        <v>84.14357814400032</v>
       </c>
       <c r="F52" t="n">
         <v>281266</v>
@@ -1472,16 +1472,16 @@
         <v>43292</v>
       </c>
       <c r="B53" t="n">
-        <v>84.08497619628906</v>
+        <v>84.08499145507812</v>
       </c>
       <c r="C53" t="n">
-        <v>86.25226698638772</v>
+        <v>86.25228263847217</v>
       </c>
       <c r="D53" t="n">
-        <v>82.64987783807528</v>
+        <v>82.64989283643895</v>
       </c>
       <c r="E53" t="n">
-        <v>83.79210369248307</v>
+        <v>83.79211889812494</v>
       </c>
       <c r="F53" t="n">
         <v>271833</v>
@@ -1512,16 +1512,16 @@
         <v>43294</v>
       </c>
       <c r="B55" t="n">
-        <v>84.40714263916016</v>
+        <v>84.40715789794922</v>
       </c>
       <c r="C55" t="n">
-        <v>87.57021185884146</v>
+        <v>87.57022768943764</v>
       </c>
       <c r="D55" t="n">
-        <v>83.96783015940457</v>
+        <v>83.96784533877647</v>
       </c>
       <c r="E55" t="n">
-        <v>87.10161287353505</v>
+        <v>87.10162861941977</v>
       </c>
       <c r="F55" t="n">
         <v>222900</v>
@@ -1552,16 +1552,16 @@
         <v>43298</v>
       </c>
       <c r="B57" t="n">
-        <v>83.08921051025391</v>
+        <v>83.08919525146484</v>
       </c>
       <c r="C57" t="n">
-        <v>84.58288210867671</v>
+        <v>84.58286657558465</v>
       </c>
       <c r="D57" t="n">
-        <v>82.35701796606644</v>
+        <v>82.35700284173974</v>
       </c>
       <c r="E57" t="n">
-        <v>84.11427560316773</v>
+        <v>84.11426015613218</v>
       </c>
       <c r="F57" t="n">
         <v>152666</v>
@@ -1572,16 +1572,16 @@
         <v>43299</v>
       </c>
       <c r="B58" t="n">
-        <v>85.90081024169922</v>
+        <v>85.90081787109375</v>
       </c>
       <c r="C58" t="n">
-        <v>85.90081024169922</v>
+        <v>85.90081787109375</v>
       </c>
       <c r="D58" t="n">
-        <v>82.73774116071021</v>
+        <v>82.73774850917258</v>
       </c>
       <c r="E58" t="n">
-        <v>82.91346763455662</v>
+        <v>82.91347499862636</v>
       </c>
       <c r="F58" t="n">
         <v>444433</v>
@@ -1592,16 +1592,16 @@
         <v>43300</v>
       </c>
       <c r="B59" t="n">
-        <v>85.19790649414062</v>
+        <v>85.19791412353516</v>
       </c>
       <c r="C59" t="n">
-        <v>86.54514531034216</v>
+        <v>86.5451530603807</v>
       </c>
       <c r="D59" t="n">
-        <v>83.6163756378991</v>
+        <v>83.61638312566897</v>
       </c>
       <c r="E59" t="n">
-        <v>85.52007294568851</v>
+        <v>85.52008060393275</v>
       </c>
       <c r="F59" t="n">
         <v>169366</v>
@@ -1632,16 +1632,16 @@
         <v>43304</v>
       </c>
       <c r="B61" t="n">
-        <v>87.6580810546875</v>
+        <v>87.65808868408203</v>
       </c>
       <c r="C61" t="n">
-        <v>89.26890593519866</v>
+        <v>89.26891370479268</v>
       </c>
       <c r="D61" t="n">
-        <v>86.7208756119757</v>
+        <v>86.72088315979977</v>
       </c>
       <c r="E61" t="n">
-        <v>89.00531248203944</v>
+        <v>89.00532022869139</v>
       </c>
       <c r="F61" t="n">
         <v>145300</v>
@@ -1672,16 +1672,16 @@
         <v>43306</v>
       </c>
       <c r="B63" t="n">
-        <v>83.99710845947266</v>
+        <v>83.99713134765625</v>
       </c>
       <c r="C63" t="n">
-        <v>89.91322034669925</v>
+        <v>89.9132448469509</v>
       </c>
       <c r="D63" t="n">
-        <v>83.99710845947266</v>
+        <v>83.99713134765625</v>
       </c>
       <c r="E63" t="n">
-        <v>88.77100205231812</v>
+        <v>88.77102624132928</v>
       </c>
       <c r="F63" t="n">
         <v>653300</v>
@@ -1692,16 +1692,16 @@
         <v>43307</v>
       </c>
       <c r="B64" t="n">
-        <v>80.57046508789062</v>
+        <v>80.57045745849609</v>
       </c>
       <c r="C64" t="n">
-        <v>84.84646679649717</v>
+        <v>84.84645876219862</v>
       </c>
       <c r="D64" t="n">
-        <v>79.9554260419345</v>
+        <v>79.95541847077936</v>
       </c>
       <c r="E64" t="n">
-        <v>84.14356822179629</v>
+        <v>84.14356025405675</v>
       </c>
       <c r="F64" t="n">
         <v>454233</v>
@@ -1712,16 +1712,16 @@
         <v>43308</v>
       </c>
       <c r="B65" t="n">
-        <v>82.62059783935547</v>
+        <v>82.62061309814453</v>
       </c>
       <c r="C65" t="n">
-        <v>82.62059783935547</v>
+        <v>82.62061309814453</v>
       </c>
       <c r="D65" t="n">
-        <v>80.04328087200228</v>
+        <v>80.04329565479944</v>
       </c>
       <c r="E65" t="n">
-        <v>81.24407983209161</v>
+        <v>81.24409483665839</v>
       </c>
       <c r="F65" t="n">
         <v>199833</v>
@@ -1732,16 +1732,16 @@
         <v>43311</v>
       </c>
       <c r="B66" t="n">
-        <v>80.39473724365234</v>
+        <v>80.39472198486328</v>
       </c>
       <c r="C66" t="n">
-        <v>82.59131480467153</v>
+        <v>82.59129912897563</v>
       </c>
       <c r="D66" t="n">
-        <v>79.80898471703006</v>
+        <v>79.80896956941586</v>
       </c>
       <c r="E66" t="n">
-        <v>82.53274178648354</v>
+        <v>82.53272612190472</v>
       </c>
       <c r="F66" t="n">
         <v>306800</v>
@@ -1752,16 +1752,16 @@
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>82.47415924072266</v>
+        <v>82.47416687011719</v>
       </c>
       <c r="C67" t="n">
-        <v>82.56202621403682</v>
+        <v>82.56203385155962</v>
       </c>
       <c r="D67" t="n">
-        <v>79.3696627348224</v>
+        <v>79.36967007703086</v>
       </c>
       <c r="E67" t="n">
-        <v>81.24408120030263</v>
+        <v>81.24408871590697</v>
       </c>
       <c r="F67" t="n">
         <v>430700</v>
@@ -1792,16 +1792,16 @@
         <v>43314</v>
       </c>
       <c r="B69" t="n">
-        <v>84.75860595703125</v>
+        <v>84.75859069824219</v>
       </c>
       <c r="C69" t="n">
-        <v>84.75860595703125</v>
+        <v>84.75859069824219</v>
       </c>
       <c r="D69" t="n">
-        <v>83.2356478963592</v>
+        <v>83.23563291174283</v>
       </c>
       <c r="E69" t="n">
-        <v>83.2356478963592</v>
+        <v>83.23563291174283</v>
       </c>
       <c r="F69" t="n">
         <v>63600</v>
@@ -1852,16 +1852,16 @@
         <v>43319</v>
       </c>
       <c r="B72" t="n">
-        <v>79.13536834716797</v>
+        <v>79.13535308837891</v>
       </c>
       <c r="C72" t="n">
-        <v>81.41981297413815</v>
+        <v>81.41979727486515</v>
       </c>
       <c r="D72" t="n">
-        <v>79.13536834716797</v>
+        <v>79.13535308837891</v>
       </c>
       <c r="E72" t="n">
-        <v>81.27337297462441</v>
+        <v>81.27335730358779</v>
       </c>
       <c r="F72" t="n">
         <v>212866</v>
@@ -1912,16 +1912,16 @@
         <v>43322</v>
       </c>
       <c r="B75" t="n">
-        <v>78.87178039550781</v>
+        <v>78.87176513671875</v>
       </c>
       <c r="C75" t="n">
-        <v>80.36545196820988</v>
+        <v>80.36543642045031</v>
       </c>
       <c r="D75" t="n">
-        <v>78.16887437347211</v>
+        <v>78.16885925066951</v>
       </c>
       <c r="E75" t="n">
-        <v>79.13536642964741</v>
+        <v>79.13535111986414</v>
       </c>
       <c r="F75" t="n">
         <v>176700</v>
@@ -1972,16 +1972,16 @@
         <v>43327</v>
       </c>
       <c r="B78" t="n">
-        <v>76.14802551269531</v>
+        <v>76.14801788330078</v>
       </c>
       <c r="C78" t="n">
-        <v>77.67098363950991</v>
+        <v>77.67097585752774</v>
       </c>
       <c r="D78" t="n">
-        <v>76.14802551269531</v>
+        <v>76.14801788330078</v>
       </c>
       <c r="E78" t="n">
-        <v>77.0266580659529</v>
+        <v>77.02665034852674</v>
       </c>
       <c r="F78" t="n">
         <v>702366</v>
@@ -1992,16 +1992,16 @@
         <v>43328</v>
       </c>
       <c r="B79" t="n">
-        <v>73.51211547851562</v>
+        <v>73.51213073730469</v>
       </c>
       <c r="C79" t="n">
-        <v>76.64590563232663</v>
+        <v>76.64592154159136</v>
       </c>
       <c r="D79" t="n">
-        <v>72.69206353234769</v>
+        <v>72.69207862091992</v>
       </c>
       <c r="E79" t="n">
-        <v>76.32373917565498</v>
+        <v>76.32375501804815</v>
       </c>
       <c r="F79" t="n">
         <v>1651000</v>
@@ -2012,16 +2012,16 @@
         <v>43329</v>
       </c>
       <c r="B80" t="n">
-        <v>71.46198272705078</v>
+        <v>71.46199798583984</v>
       </c>
       <c r="C80" t="n">
-        <v>72.95565418739019</v>
+        <v>72.95566976511273</v>
       </c>
       <c r="D80" t="n">
-        <v>70.29047774395042</v>
+        <v>70.29049275259602</v>
       </c>
       <c r="E80" t="n">
-        <v>72.95565418739019</v>
+        <v>72.95566976511273</v>
       </c>
       <c r="F80" t="n">
         <v>2138466</v>
@@ -2032,16 +2032,16 @@
         <v>43332</v>
       </c>
       <c r="B81" t="n">
-        <v>72.34062194824219</v>
+        <v>72.34062957763672</v>
       </c>
       <c r="C81" t="n">
-        <v>73.01424147300597</v>
+        <v>73.01424917344369</v>
       </c>
       <c r="D81" t="n">
-        <v>71.75486940195739</v>
+        <v>71.75487696957561</v>
       </c>
       <c r="E81" t="n">
-        <v>71.95988242074468</v>
+        <v>71.95989000998456</v>
       </c>
       <c r="F81" t="n">
         <v>425766</v>
@@ -2052,16 +2052,16 @@
         <v>43333</v>
       </c>
       <c r="B82" t="n">
-        <v>71.60842132568359</v>
+        <v>71.60843658447266</v>
       </c>
       <c r="C82" t="n">
-        <v>72.57491329044277</v>
+        <v>72.57492875517822</v>
       </c>
       <c r="D82" t="n">
-        <v>70.31976288992242</v>
+        <v>70.31977787411573</v>
       </c>
       <c r="E82" t="n">
-        <v>71.63770783245707</v>
+        <v>71.63772309748668</v>
       </c>
       <c r="F82" t="n">
         <v>1384333</v>
@@ -2072,16 +2072,16 @@
         <v>43334</v>
       </c>
       <c r="B83" t="n">
-        <v>73.51211547851562</v>
+        <v>73.51213073730469</v>
       </c>
       <c r="C83" t="n">
-        <v>73.68784195958683</v>
+        <v>73.68785725485115</v>
       </c>
       <c r="D83" t="n">
-        <v>70.96409267535293</v>
+        <v>70.96410740525307</v>
       </c>
       <c r="E83" t="n">
-        <v>70.96409267535293</v>
+        <v>70.96410740525307</v>
       </c>
       <c r="F83" t="n">
         <v>518466</v>
@@ -2092,16 +2092,16 @@
         <v>43335</v>
       </c>
       <c r="B84" t="n">
-        <v>73.36568450927734</v>
+        <v>73.36569976806641</v>
       </c>
       <c r="C84" t="n">
-        <v>74.33217645157174</v>
+        <v>74.33219191137435</v>
       </c>
       <c r="D84" t="n">
-        <v>71.901299618666</v>
+        <v>71.90131457288842</v>
       </c>
       <c r="E84" t="n">
-        <v>72.57491160353946</v>
+        <v>72.57492669786147</v>
       </c>
       <c r="F84" t="n">
         <v>126566</v>
@@ -2132,16 +2132,16 @@
         <v>43339</v>
       </c>
       <c r="B86" t="n">
-        <v>76.03086090087891</v>
+        <v>76.03087615966797</v>
       </c>
       <c r="C86" t="n">
-        <v>76.44088688300364</v>
+        <v>76.44090222408167</v>
       </c>
       <c r="D86" t="n">
-        <v>73.6585570782333</v>
+        <v>73.65857186091985</v>
       </c>
       <c r="E86" t="n">
-        <v>75.29866845497898</v>
+        <v>75.29868356682285</v>
       </c>
       <c r="F86" t="n">
         <v>318500</v>
@@ -2152,16 +2152,16 @@
         <v>43340</v>
       </c>
       <c r="B87" t="n">
-        <v>75.24009704589844</v>
+        <v>75.2401123046875</v>
       </c>
       <c r="C87" t="n">
-        <v>76.14801599608937</v>
+        <v>76.14803143900558</v>
       </c>
       <c r="D87" t="n">
-        <v>73.89286559810573</v>
+        <v>73.89288058367451</v>
       </c>
       <c r="E87" t="n">
-        <v>75.91371649391823</v>
+        <v>75.91373188931819</v>
       </c>
       <c r="F87" t="n">
         <v>298400</v>
@@ -2172,16 +2172,16 @@
         <v>43341</v>
       </c>
       <c r="B88" t="n">
-        <v>74.4200439453125</v>
+        <v>74.42005157470703</v>
       </c>
       <c r="C88" t="n">
-        <v>76.14802247243639</v>
+        <v>76.14803027897985</v>
       </c>
       <c r="D88" t="n">
-        <v>73.45355189944088</v>
+        <v>73.45355942975257</v>
       </c>
       <c r="E88" t="n">
-        <v>75.6794159799925</v>
+        <v>75.67942373849533</v>
       </c>
       <c r="F88" t="n">
         <v>162200</v>
@@ -2232,16 +2232,16 @@
         <v>43346</v>
       </c>
       <c r="B91" t="n">
-        <v>74.65435028076172</v>
+        <v>74.65434265136719</v>
       </c>
       <c r="C91" t="n">
-        <v>76.06015484964274</v>
+        <v>76.06014707658026</v>
       </c>
       <c r="D91" t="n">
-        <v>73.98073078117974</v>
+        <v>73.9807232206266</v>
       </c>
       <c r="E91" t="n">
-        <v>75.76728231157261</v>
+        <v>75.76727456844061</v>
       </c>
       <c r="F91" t="n">
         <v>159200</v>
@@ -2252,16 +2252,16 @@
         <v>43347</v>
       </c>
       <c r="B92" t="n">
-        <v>73.04352569580078</v>
+        <v>73.04351043701172</v>
       </c>
       <c r="C92" t="n">
-        <v>74.42004376405343</v>
+        <v>74.42002821770981</v>
       </c>
       <c r="D92" t="n">
-        <v>71.87202063991565</v>
+        <v>71.87200562585394</v>
       </c>
       <c r="E92" t="n">
-        <v>74.39075725489343</v>
+        <v>74.39074171466777</v>
       </c>
       <c r="F92" t="n">
         <v>196200</v>
@@ -2292,16 +2292,16 @@
         <v>43349</v>
       </c>
       <c r="B94" t="n">
-        <v>74.21503448486328</v>
+        <v>74.21504211425781</v>
       </c>
       <c r="C94" t="n">
-        <v>76.52876565210674</v>
+        <v>76.52877351935561</v>
       </c>
       <c r="D94" t="n">
-        <v>71.4619907616264</v>
+        <v>71.46199810800472</v>
       </c>
       <c r="E94" t="n">
-        <v>74.15646146359693</v>
+        <v>74.15646908697008</v>
       </c>
       <c r="F94" t="n">
         <v>139100</v>
@@ -2372,16 +2372,16 @@
         <v>43356</v>
       </c>
       <c r="B98" t="n">
-        <v>71.60842132568359</v>
+        <v>71.60843658447266</v>
       </c>
       <c r="C98" t="n">
-        <v>73.86357172620396</v>
+        <v>73.86358746553515</v>
       </c>
       <c r="D98" t="n">
-        <v>70.4369163652632</v>
+        <v>70.43693137442035</v>
       </c>
       <c r="E98" t="n">
-        <v>73.77571220588352</v>
+        <v>73.77572792649305</v>
       </c>
       <c r="F98" t="n">
         <v>250366</v>
@@ -2392,16 +2392,16 @@
         <v>43357</v>
       </c>
       <c r="B99" t="n">
-        <v>69.79257965087891</v>
+        <v>69.79258728027344</v>
       </c>
       <c r="C99" t="n">
-        <v>72.28203686752244</v>
+        <v>72.28204476905265</v>
       </c>
       <c r="D99" t="n">
-        <v>69.7047201353074</v>
+        <v>69.70472775509755</v>
       </c>
       <c r="E99" t="n">
-        <v>70.96409199622441</v>
+        <v>70.96409975368313</v>
       </c>
       <c r="F99" t="n">
         <v>269466</v>
@@ -2412,16 +2412,16 @@
         <v>43360</v>
       </c>
       <c r="B100" t="n">
-        <v>73.48281860351562</v>
+        <v>73.48284149169922</v>
       </c>
       <c r="C100" t="n">
-        <v>74.06857842325786</v>
+        <v>74.06860149389196</v>
       </c>
       <c r="D100" t="n">
-        <v>69.79257047001622</v>
+        <v>69.79259220877361</v>
       </c>
       <c r="E100" t="n">
-        <v>70.02686992896581</v>
+        <v>70.02689174070201</v>
       </c>
       <c r="F100" t="n">
         <v>114333</v>
@@ -2432,16 +2432,16 @@
         <v>43361</v>
       </c>
       <c r="B101" t="n">
-        <v>74.50789642333984</v>
+        <v>74.50790405273438</v>
       </c>
       <c r="C101" t="n">
-        <v>75.35724226701849</v>
+        <v>75.35724998338361</v>
       </c>
       <c r="D101" t="n">
-        <v>73.62926407612848</v>
+        <v>73.62927161555359</v>
       </c>
       <c r="E101" t="n">
-        <v>74.56646943040525</v>
+        <v>74.56647706579749</v>
       </c>
       <c r="F101" t="n">
         <v>194766</v>
@@ -2452,16 +2452,16 @@
         <v>43362</v>
       </c>
       <c r="B102" t="n">
-        <v>68.76750946044922</v>
+        <v>68.76752471923828</v>
       </c>
       <c r="C102" t="n">
-        <v>74.68362139964943</v>
+        <v>74.68363797116167</v>
       </c>
       <c r="D102" t="n">
-        <v>68.76750946044922</v>
+        <v>68.76752471923828</v>
       </c>
       <c r="E102" t="n">
-        <v>73.57068959818099</v>
+        <v>73.57070592274535</v>
       </c>
       <c r="F102" t="n">
         <v>510266</v>
@@ -2472,16 +2472,16 @@
         <v>43363</v>
       </c>
       <c r="B103" t="n">
-        <v>68.24034118652344</v>
+        <v>68.24034881591797</v>
       </c>
       <c r="C103" t="n">
-        <v>69.58757267942752</v>
+        <v>69.58758045944499</v>
       </c>
       <c r="D103" t="n">
-        <v>65.63373027563168</v>
+        <v>65.63373761360235</v>
       </c>
       <c r="E103" t="n">
-        <v>69.41184618485332</v>
+        <v>69.41185394522425</v>
       </c>
       <c r="F103" t="n">
         <v>1256966</v>
@@ -2492,16 +2492,16 @@
         <v>43364</v>
       </c>
       <c r="B104" t="n">
-        <v>69.353271484375</v>
+        <v>69.35326385498047</v>
       </c>
       <c r="C104" t="n">
-        <v>71.16910940144096</v>
+        <v>71.16910157229026</v>
       </c>
       <c r="D104" t="n">
-        <v>67.88888654791837</v>
+        <v>67.88887907961748</v>
       </c>
       <c r="E104" t="n">
-        <v>67.94745956193762</v>
+        <v>67.94745208719324</v>
       </c>
       <c r="F104" t="n">
         <v>293166</v>
@@ -2512,16 +2512,16 @@
         <v>43367</v>
       </c>
       <c r="B105" t="n">
-        <v>65.45800018310547</v>
+        <v>65.45801544189453</v>
       </c>
       <c r="C105" t="n">
-        <v>69.49970933615616</v>
+        <v>69.4997255371003</v>
       </c>
       <c r="D105" t="n">
-        <v>65.37014066477121</v>
+        <v>65.37015590307951</v>
       </c>
       <c r="E105" t="n">
-        <v>69.35326935735233</v>
+        <v>69.35328552416013</v>
       </c>
       <c r="F105" t="n">
         <v>831466</v>
@@ -2532,16 +2532,16 @@
         <v>43368</v>
       </c>
       <c r="B106" t="n">
-        <v>63.90575408935547</v>
+        <v>63.90575790405273</v>
       </c>
       <c r="C106" t="n">
-        <v>67.21526326118382</v>
+        <v>67.21526727343412</v>
       </c>
       <c r="D106" t="n">
-        <v>61.62131356977399</v>
+        <v>61.62131724810718</v>
       </c>
       <c r="E106" t="n">
-        <v>64.46222003555015</v>
+        <v>64.46222388346429</v>
       </c>
       <c r="F106" t="n">
         <v>629433</v>
@@ -2552,16 +2552,16 @@
         <v>43369</v>
       </c>
       <c r="B107" t="n">
-        <v>65.01868438720703</v>
+        <v>65.01869964599609</v>
       </c>
       <c r="C107" t="n">
-        <v>66.48306920425335</v>
+        <v>66.48308480670883</v>
       </c>
       <c r="D107" t="n">
-        <v>63.14427360896688</v>
+        <v>63.14428842786333</v>
       </c>
       <c r="E107" t="n">
-        <v>63.93503902673306</v>
+        <v>63.93505403120882</v>
       </c>
       <c r="F107" t="n">
         <v>469400</v>
@@ -2572,16 +2572,16 @@
         <v>43370</v>
       </c>
       <c r="B108" t="n">
-        <v>68.59178924560547</v>
+        <v>68.591796875</v>
       </c>
       <c r="C108" t="n">
-        <v>69.85115367658149</v>
+        <v>69.85116144605384</v>
       </c>
       <c r="D108" t="n">
-        <v>65.07725960672998</v>
+        <v>65.07726684520698</v>
       </c>
       <c r="E108" t="n">
-        <v>65.48729303009652</v>
+        <v>65.48730031418111</v>
       </c>
       <c r="F108" t="n">
         <v>605400</v>
@@ -2592,16 +2592,16 @@
         <v>43371</v>
       </c>
       <c r="B109" t="n">
-        <v>70.29048919677734</v>
+        <v>70.29046630859375</v>
       </c>
       <c r="C109" t="n">
-        <v>71.34484832230859</v>
+        <v>71.34482509080165</v>
       </c>
       <c r="D109" t="n">
-        <v>67.33243230146601</v>
+        <v>67.3324103764931</v>
       </c>
       <c r="E109" t="n">
-        <v>68.5918044600314</v>
+        <v>68.59178212497824</v>
       </c>
       <c r="F109" t="n">
         <v>612400</v>
@@ -2652,16 +2652,16 @@
         <v>43376</v>
       </c>
       <c r="B112" t="n">
-        <v>70.43692779541016</v>
+        <v>70.43691253662109</v>
       </c>
       <c r="C112" t="n">
-        <v>73.59999766042965</v>
+        <v>73.59998171642307</v>
       </c>
       <c r="D112" t="n">
-        <v>69.08968867923201</v>
+        <v>69.08967371229606</v>
       </c>
       <c r="E112" t="n">
-        <v>70.58336035303988</v>
+        <v>70.58334506252905</v>
       </c>
       <c r="F112" t="n">
         <v>463466</v>
@@ -2672,16 +2672,16 @@
         <v>43377</v>
       </c>
       <c r="B113" t="n">
-        <v>70.29048919677734</v>
+        <v>70.29046630859375</v>
       </c>
       <c r="C113" t="n">
-        <v>72.1356139423329</v>
+        <v>72.13559045333467</v>
       </c>
       <c r="D113" t="n">
-        <v>67.71317185542203</v>
+        <v>67.71314980647165</v>
       </c>
       <c r="E113" t="n">
-        <v>70.55407525403604</v>
+        <v>70.55405228002282</v>
       </c>
       <c r="F113" t="n">
         <v>201700</v>
@@ -2692,16 +2692,16 @@
         <v>43378</v>
       </c>
       <c r="B114" t="n">
-        <v>68.26963043212891</v>
+        <v>68.26964569091797</v>
       </c>
       <c r="C114" t="n">
-        <v>71.60842651469054</v>
+        <v>71.60844251972628</v>
       </c>
       <c r="D114" t="n">
-        <v>67.36171141512558</v>
+        <v>67.36172647098773</v>
       </c>
       <c r="E114" t="n">
-        <v>71.60842651469054</v>
+        <v>71.60844251972628</v>
       </c>
       <c r="F114" t="n">
         <v>364566</v>
@@ -2712,16 +2712,16 @@
         <v>43381</v>
       </c>
       <c r="B115" t="n">
-        <v>69.55828094482422</v>
+        <v>69.55828857421875</v>
       </c>
       <c r="C115" t="n">
-        <v>70.90551233649205</v>
+        <v>70.90552011365561</v>
       </c>
       <c r="D115" t="n">
-        <v>68.85537501934654</v>
+        <v>68.8553825716439</v>
       </c>
       <c r="E115" t="n">
-        <v>68.85537501934654</v>
+        <v>68.8553825716439</v>
       </c>
       <c r="F115" t="n">
         <v>697200</v>
@@ -2732,16 +2732,16 @@
         <v>43382</v>
       </c>
       <c r="B116" t="n">
-        <v>68.26963043212891</v>
+        <v>68.26964569091797</v>
       </c>
       <c r="C116" t="n">
-        <v>71.75486650741638</v>
+        <v>71.7548825451826</v>
       </c>
       <c r="D116" t="n">
-        <v>68.26963043212891</v>
+        <v>68.26964569091797</v>
       </c>
       <c r="E116" t="n">
-        <v>69.9683149823054</v>
+        <v>69.96833062076357</v>
       </c>
       <c r="F116" t="n">
         <v>433600</v>
@@ -2772,16 +2772,16 @@
         <v>43384</v>
       </c>
       <c r="B118" t="n">
-        <v>70.87622833251953</v>
+        <v>70.87624359130859</v>
       </c>
       <c r="C118" t="n">
-        <v>71.63770729591425</v>
+        <v>71.63772271864046</v>
       </c>
       <c r="D118" t="n">
-        <v>68.62107794888951</v>
+        <v>68.62109272217215</v>
       </c>
       <c r="E118" t="n">
-        <v>69.08967695024926</v>
+        <v>69.08969182441557</v>
       </c>
       <c r="F118" t="n">
         <v>258833</v>
@@ -2792,16 +2792,16 @@
         <v>43388</v>
       </c>
       <c r="B119" t="n">
-        <v>72.0477294921875</v>
+        <v>72.04773712158203</v>
       </c>
       <c r="C119" t="n">
-        <v>72.89707537878911</v>
+        <v>72.89708309812396</v>
       </c>
       <c r="D119" t="n">
-        <v>66.77595003899427</v>
+        <v>66.77595711014101</v>
       </c>
       <c r="E119" t="n">
-        <v>71.5791305154908</v>
+        <v>71.5791380952637</v>
       </c>
       <c r="F119" t="n">
         <v>520433</v>
@@ -2812,16 +2812,16 @@
         <v>43389</v>
       </c>
       <c r="B120" t="n">
-        <v>73.83429718017578</v>
+        <v>73.83428955078125</v>
       </c>
       <c r="C120" t="n">
-        <v>75.85514840562809</v>
+        <v>75.85514056741636</v>
       </c>
       <c r="D120" t="n">
-        <v>71.34484687394362</v>
+        <v>71.34483950178725</v>
       </c>
       <c r="E120" t="n">
-        <v>71.98917247207794</v>
+        <v>71.98916503334256</v>
       </c>
       <c r="F120" t="n">
         <v>484533</v>
@@ -2832,16 +2832,16 @@
         <v>43390</v>
       </c>
       <c r="B121" t="n">
-        <v>74.91793823242188</v>
+        <v>74.91793060302734</v>
       </c>
       <c r="C121" t="n">
-        <v>75.88443029487647</v>
+        <v>75.88442256705758</v>
       </c>
       <c r="D121" t="n">
-        <v>73.27782665309864</v>
+        <v>73.27781919072763</v>
       </c>
       <c r="E121" t="n">
-        <v>73.27782665309864</v>
+        <v>73.27781919072763</v>
       </c>
       <c r="F121" t="n">
         <v>520600</v>
@@ -2852,16 +2852,16 @@
         <v>43391</v>
       </c>
       <c r="B122" t="n">
-        <v>75.56228637695312</v>
+        <v>75.56227111816406</v>
       </c>
       <c r="C122" t="n">
-        <v>76.79236472168148</v>
+        <v>76.79234921449461</v>
       </c>
       <c r="D122" t="n">
-        <v>74.88866672513822</v>
+        <v>74.88865160237759</v>
       </c>
       <c r="E122" t="n">
-        <v>74.91795324073902</v>
+        <v>74.91793811206438</v>
       </c>
       <c r="F122" t="n">
         <v>252733</v>
@@ -2892,16 +2892,16 @@
         <v>43395</v>
       </c>
       <c r="B124" t="n">
-        <v>74.65435028076172</v>
+        <v>74.65434265136719</v>
       </c>
       <c r="C124" t="n">
-        <v>76.55804784708366</v>
+        <v>76.55804002313839</v>
       </c>
       <c r="D124" t="n">
-        <v>74.3907568034264</v>
+        <v>74.39074920097013</v>
       </c>
       <c r="E124" t="n">
-        <v>74.53719679658519</v>
+        <v>74.53718917916331</v>
       </c>
       <c r="F124" t="n">
         <v>312766</v>
@@ -2912,16 +2912,16 @@
         <v>43396</v>
       </c>
       <c r="B125" t="n">
-        <v>75.44511413574219</v>
+        <v>75.44510650634766</v>
       </c>
       <c r="C125" t="n">
-        <v>76.14802012864928</v>
+        <v>76.14801242817332</v>
       </c>
       <c r="D125" t="n">
-        <v>74.15645563149494</v>
+        <v>74.15644813241612</v>
       </c>
       <c r="E125" t="n">
-        <v>74.80078860774221</v>
+        <v>74.80078104350515</v>
       </c>
       <c r="F125" t="n">
         <v>244366</v>
@@ -2932,16 +2932,16 @@
         <v>43397</v>
       </c>
       <c r="B126" t="n">
-        <v>74.39076232910156</v>
+        <v>74.39076995849609</v>
       </c>
       <c r="C126" t="n">
-        <v>75.26939490507085</v>
+        <v>75.2694026245765</v>
       </c>
       <c r="D126" t="n">
-        <v>74.24432232506534</v>
+        <v>74.24432993944123</v>
       </c>
       <c r="E126" t="n">
-        <v>75.26939490507085</v>
+        <v>75.2694026245765</v>
       </c>
       <c r="F126" t="n">
         <v>414300</v>
@@ -2952,16 +2952,16 @@
         <v>43398</v>
       </c>
       <c r="B127" t="n">
-        <v>76.00157165527344</v>
+        <v>76.0015869140625</v>
       </c>
       <c r="C127" t="n">
-        <v>76.00157165527344</v>
+        <v>76.0015869140625</v>
       </c>
       <c r="D127" t="n">
-        <v>73.10208848230262</v>
+        <v>73.10210315896421</v>
       </c>
       <c r="E127" t="n">
-        <v>74.56647332131847</v>
+        <v>74.56648829198372</v>
       </c>
       <c r="F127" t="n">
         <v>495966</v>
@@ -2972,16 +2972,16 @@
         <v>43399</v>
       </c>
       <c r="B128" t="n">
-        <v>74.97650909423828</v>
+        <v>74.97651672363281</v>
       </c>
       <c r="C128" t="n">
-        <v>78.02243263911183</v>
+        <v>78.02244057845078</v>
       </c>
       <c r="D128" t="n">
-        <v>73.36569151925214</v>
+        <v>73.36569898473449</v>
       </c>
       <c r="E128" t="n">
-        <v>76.1187350787205</v>
+        <v>76.11874282434466</v>
       </c>
       <c r="F128" t="n">
         <v>546200</v>
@@ -3012,16 +3012,16 @@
         <v>43403</v>
       </c>
       <c r="B130" t="n">
-        <v>74.56647491455078</v>
+        <v>74.56649017333984</v>
       </c>
       <c r="C130" t="n">
-        <v>76.14801325584872</v>
+        <v>76.14802883827332</v>
       </c>
       <c r="D130" t="n">
-        <v>73.65855599703195</v>
+        <v>73.6585710700305</v>
       </c>
       <c r="E130" t="n">
-        <v>75.65012031443605</v>
+        <v>75.65013579497513</v>
       </c>
       <c r="F130" t="n">
         <v>1306966</v>
@@ -3032,16 +3032,16 @@
         <v>43404</v>
       </c>
       <c r="B131" t="n">
-        <v>74.62506103515625</v>
+        <v>74.62505340576172</v>
       </c>
       <c r="C131" t="n">
-        <v>76.61661805539134</v>
+        <v>76.61661022238727</v>
       </c>
       <c r="D131" t="n">
-        <v>73.86357458830497</v>
+        <v>73.86356703676205</v>
       </c>
       <c r="E131" t="n">
-        <v>75.67941256109036</v>
+        <v>75.67940482390277</v>
       </c>
       <c r="F131" t="n">
         <v>863500</v>
@@ -3052,16 +3052,16 @@
         <v>43405</v>
       </c>
       <c r="B132" t="n">
-        <v>75.35724639892578</v>
+        <v>75.35723876953125</v>
       </c>
       <c r="C132" t="n">
-        <v>78.08099565225757</v>
+        <v>78.08098774710245</v>
       </c>
       <c r="D132" t="n">
-        <v>74.15644755052168</v>
+        <v>74.15644004269964</v>
       </c>
       <c r="E132" t="n">
-        <v>75.65011889855732</v>
+        <v>75.6501112395115</v>
       </c>
       <c r="F132" t="n">
         <v>289433</v>
@@ -3072,16 +3072,16 @@
         <v>43409</v>
       </c>
       <c r="B133" t="n">
-        <v>76.38230895996094</v>
+        <v>76.38231658935547</v>
       </c>
       <c r="C133" t="n">
-        <v>76.85091537243757</v>
+        <v>76.85092304863853</v>
       </c>
       <c r="D133" t="n">
-        <v>73.98071878560305</v>
+        <v>73.98072617511639</v>
       </c>
       <c r="E133" t="n">
-        <v>75.82584303478345</v>
+        <v>75.82585060859577</v>
       </c>
       <c r="F133" t="n">
         <v>315933</v>
@@ -3092,16 +3092,16 @@
         <v>43410</v>
       </c>
       <c r="B134" t="n">
-        <v>75.12294769287109</v>
+        <v>75.12295532226562</v>
       </c>
       <c r="C134" t="n">
-        <v>76.96807220124005</v>
+        <v>76.96808001802316</v>
       </c>
       <c r="D134" t="n">
-        <v>74.12716916781773</v>
+        <v>74.12717669608222</v>
       </c>
       <c r="E134" t="n">
-        <v>76.17730668286687</v>
+        <v>76.1773144193408</v>
       </c>
       <c r="F134" t="n">
         <v>244033</v>
@@ -3112,16 +3112,16 @@
         <v>43411</v>
       </c>
       <c r="B135" t="n">
-        <v>77.31953430175781</v>
+        <v>77.31951904296875</v>
       </c>
       <c r="C135" t="n">
-        <v>79.04751298019434</v>
+        <v>79.04749738039364</v>
       </c>
       <c r="D135" t="n">
-        <v>75.56227655977359</v>
+        <v>75.56226164777432</v>
       </c>
       <c r="E135" t="n">
-        <v>75.56227655977359</v>
+        <v>75.56226164777432</v>
       </c>
       <c r="F135" t="n">
         <v>375833</v>
@@ -3132,16 +3132,16 @@
         <v>43412</v>
       </c>
       <c r="B136" t="n">
-        <v>77.31953430175781</v>
+        <v>77.31951904296875</v>
       </c>
       <c r="C136" t="n">
-        <v>79.25252601101343</v>
+        <v>79.25251037075398</v>
       </c>
       <c r="D136" t="n">
-        <v>76.148029140435</v>
+        <v>76.14801411283914</v>
       </c>
       <c r="E136" t="n">
-        <v>77.29024778996197</v>
+        <v>77.29023253695252</v>
       </c>
       <c r="F136" t="n">
         <v>245533</v>
@@ -3152,16 +3152,16 @@
         <v>43413</v>
       </c>
       <c r="B137" t="n">
-        <v>76.73377227783203</v>
+        <v>76.73377990722656</v>
       </c>
       <c r="C137" t="n">
-        <v>79.07678976038169</v>
+        <v>79.07679762273497</v>
       </c>
       <c r="D137" t="n">
-        <v>75.21081426588603</v>
+        <v>75.21082174385769</v>
       </c>
       <c r="E137" t="n">
-        <v>77.31952478640763</v>
+        <v>77.31953247404167</v>
       </c>
       <c r="F137" t="n">
         <v>423466</v>
@@ -3192,16 +3192,16 @@
         <v>43417</v>
       </c>
       <c r="B139" t="n">
-        <v>75.26937103271484</v>
+        <v>75.26938629150391</v>
       </c>
       <c r="C139" t="n">
-        <v>77.84668747264041</v>
+        <v>77.84670325390931</v>
       </c>
       <c r="D139" t="n">
-        <v>74.91791811379356</v>
+        <v>74.91793330133525</v>
       </c>
       <c r="E139" t="n">
-        <v>77.26093509052018</v>
+        <v>77.26095075304393</v>
       </c>
       <c r="F139" t="n">
         <v>637900</v>
@@ -3212,16 +3212,16 @@
         <v>43418</v>
       </c>
       <c r="B140" t="n">
-        <v>79.36965942382812</v>
+        <v>79.36966705322266</v>
       </c>
       <c r="C140" t="n">
-        <v>80.33615884872891</v>
+        <v>80.33616657102803</v>
       </c>
       <c r="D140" t="n">
-        <v>71.02266971955076</v>
+        <v>71.02267654659238</v>
       </c>
       <c r="E140" t="n">
-        <v>75.03508505832947</v>
+        <v>75.0350922710638</v>
       </c>
       <c r="F140" t="n">
         <v>1608700</v>
@@ -3232,16 +3232,16 @@
         <v>43420</v>
       </c>
       <c r="B141" t="n">
-        <v>81.09764099121094</v>
+        <v>81.09762573242188</v>
       </c>
       <c r="C141" t="n">
-        <v>83.46994498882317</v>
+        <v>83.46992928367727</v>
       </c>
       <c r="D141" t="n">
-        <v>78.81319651842826</v>
+        <v>78.81318168946497</v>
       </c>
       <c r="E141" t="n">
-        <v>78.81319651842826</v>
+        <v>78.81318168946497</v>
       </c>
       <c r="F141" t="n">
         <v>652300</v>
@@ -3332,16 +3332,16 @@
         <v>43430</v>
       </c>
       <c r="B146" t="n">
-        <v>78.75460815429688</v>
+        <v>78.75463104248047</v>
       </c>
       <c r="C146" t="n">
-        <v>80.33614632724637</v>
+        <v>80.33616967506701</v>
       </c>
       <c r="D146" t="n">
-        <v>76.23586465790369</v>
+        <v>76.23588681407345</v>
       </c>
       <c r="E146" t="n">
-        <v>80.27756587386213</v>
+        <v>80.27758920465774</v>
       </c>
       <c r="F146" t="n">
         <v>252366</v>
@@ -3352,16 +3352,16 @@
         <v>43431</v>
       </c>
       <c r="B147" t="n">
-        <v>81.59553527832031</v>
+        <v>81.59555816650391</v>
       </c>
       <c r="C147" t="n">
-        <v>82.5913138168435</v>
+        <v>82.59133698435073</v>
       </c>
       <c r="D147" t="n">
-        <v>76.32374770527765</v>
+        <v>76.32376911468376</v>
       </c>
       <c r="E147" t="n">
-        <v>78.28602572182773</v>
+        <v>78.28604768166809</v>
       </c>
       <c r="F147" t="n">
         <v>436400</v>
@@ -3392,16 +3392,16 @@
         <v>43433</v>
       </c>
       <c r="B149" t="n">
-        <v>84.1728515625</v>
+        <v>84.17285919189453</v>
       </c>
       <c r="C149" t="n">
-        <v>85.69580958938813</v>
+        <v>85.69581735682299</v>
       </c>
       <c r="D149" t="n">
-        <v>83.2942190668925</v>
+        <v>83.29422661664812</v>
       </c>
       <c r="E149" t="n">
-        <v>84.31929155314248</v>
+        <v>84.31929919581027</v>
       </c>
       <c r="F149" t="n">
         <v>232033</v>
@@ -3412,16 +3412,16 @@
         <v>43434</v>
       </c>
       <c r="B150" t="n">
-        <v>82.91346740722656</v>
+        <v>82.91347503662109</v>
       </c>
       <c r="C150" t="n">
-        <v>84.26069873752434</v>
+        <v>84.26070649088619</v>
       </c>
       <c r="D150" t="n">
-        <v>82.32771497875997</v>
+        <v>82.32772255425571</v>
       </c>
       <c r="E150" t="n">
-        <v>84.23141223333795</v>
+        <v>84.23141998400496</v>
       </c>
       <c r="F150" t="n">
         <v>464600</v>
@@ -3432,16 +3432,16 @@
         <v>43437</v>
       </c>
       <c r="B151" t="n">
-        <v>84.49500274658203</v>
+        <v>84.49501800537109</v>
       </c>
       <c r="C151" t="n">
-        <v>85.2857756432162</v>
+        <v>85.2857910448094</v>
       </c>
       <c r="D151" t="n">
-        <v>82.79631837853798</v>
+        <v>82.79633333056491</v>
       </c>
       <c r="E151" t="n">
-        <v>83.29421132112294</v>
+        <v>83.2942263630634</v>
       </c>
       <c r="F151" t="n">
         <v>313866</v>
@@ -3472,16 +3472,16 @@
         <v>43439</v>
       </c>
       <c r="B153" t="n">
-        <v>86.10584259033203</v>
+        <v>86.1058349609375</v>
       </c>
       <c r="C153" t="n">
-        <v>86.39872259537825</v>
+        <v>86.39871494003313</v>
       </c>
       <c r="D153" t="n">
-        <v>83.11849931115151</v>
+        <v>83.11849194645005</v>
       </c>
       <c r="E153" t="n">
-        <v>83.82140536466409</v>
+        <v>83.82139793768175</v>
       </c>
       <c r="F153" t="n">
         <v>198233</v>
@@ -3492,16 +3492,16 @@
         <v>43440</v>
       </c>
       <c r="B154" t="n">
-        <v>84.93433380126953</v>
+        <v>84.93434906005859</v>
       </c>
       <c r="C154" t="n">
-        <v>85.46151331865333</v>
+        <v>85.46152867215227</v>
       </c>
       <c r="D154" t="n">
-        <v>83.87997476650193</v>
+        <v>83.87998983587121</v>
       </c>
       <c r="E154" t="n">
-        <v>85.25650030326756</v>
+        <v>85.25651561993512</v>
       </c>
       <c r="F154" t="n">
         <v>270866</v>
@@ -3512,16 +3512,16 @@
         <v>43441</v>
       </c>
       <c r="B155" t="n">
-        <v>84.26071166992188</v>
+        <v>84.26071929931641</v>
       </c>
       <c r="C155" t="n">
-        <v>86.10583619931816</v>
+        <v>86.10584399577968</v>
       </c>
       <c r="D155" t="n">
-        <v>82.18128762282772</v>
+        <v>82.1812950639406</v>
       </c>
       <c r="E155" t="n">
-        <v>85.57865669831246</v>
+        <v>85.57866444704045</v>
       </c>
       <c r="F155" t="n">
         <v>485833</v>
@@ -3552,16 +3552,16 @@
         <v>43445</v>
       </c>
       <c r="B157" t="n">
-        <v>83.87998199462891</v>
+        <v>83.87995910644531</v>
       </c>
       <c r="C157" t="n">
-        <v>84.37787504532611</v>
+        <v>84.37785202128332</v>
       </c>
       <c r="D157" t="n">
-        <v>83.14778939876466</v>
+        <v>83.14776671037318</v>
       </c>
       <c r="E157" t="n">
-        <v>83.4699559285245</v>
+        <v>83.46993315222402</v>
       </c>
       <c r="F157" t="n">
         <v>276533</v>
@@ -3572,16 +3572,16 @@
         <v>43446</v>
       </c>
       <c r="B158" t="n">
-        <v>85.60794067382812</v>
+        <v>85.60794830322266</v>
       </c>
       <c r="C158" t="n">
-        <v>86.28155263970095</v>
+        <v>86.2815603291279</v>
       </c>
       <c r="D158" t="n">
-        <v>84.37785531490263</v>
+        <v>84.37786283467175</v>
       </c>
       <c r="E158" t="n">
-        <v>84.55358179474914</v>
+        <v>84.55358933017901</v>
       </c>
       <c r="F158" t="n">
         <v>243466</v>
@@ -3592,16 +3592,16 @@
         <v>43447</v>
       </c>
       <c r="B159" t="n">
-        <v>86.77945709228516</v>
+        <v>86.77944183349609</v>
       </c>
       <c r="C159" t="n">
-        <v>88.77102164547205</v>
+        <v>88.77100603649799</v>
       </c>
       <c r="D159" t="n">
-        <v>84.99290555142299</v>
+        <v>84.99289060677064</v>
       </c>
       <c r="E159" t="n">
-        <v>85.78367853981547</v>
+        <v>85.78366345611825</v>
       </c>
       <c r="F159" t="n">
         <v>486800</v>
@@ -3632,16 +3632,16 @@
         <v>43451</v>
       </c>
       <c r="B161" t="n">
-        <v>84.93784332275391</v>
+        <v>84.9378662109375</v>
       </c>
       <c r="C161" t="n">
-        <v>86.47037662854606</v>
+        <v>86.47039992970112</v>
       </c>
       <c r="D161" t="n">
-        <v>84.28945923487161</v>
+        <v>84.28948194833528</v>
       </c>
       <c r="E161" t="n">
-        <v>86.44090598729262</v>
+        <v>86.44092928050621</v>
       </c>
       <c r="F161" t="n">
         <v>205700</v>
@@ -3672,16 +3672,16 @@
         <v>43453</v>
       </c>
       <c r="B163" t="n">
-        <v>89.68283081054688</v>
+        <v>89.68282318115234</v>
       </c>
       <c r="C163" t="n">
-        <v>90.56698771453594</v>
+        <v>90.56698000992543</v>
       </c>
       <c r="D163" t="n">
-        <v>86.29356392776849</v>
+        <v>86.29355658670175</v>
       </c>
       <c r="E163" t="n">
-        <v>86.52934409888439</v>
+        <v>86.52933673775965</v>
       </c>
       <c r="F163" t="n">
         <v>384866</v>
@@ -3692,16 +3692,16 @@
         <v>43454</v>
       </c>
       <c r="B164" t="n">
-        <v>89.00497436523438</v>
+        <v>89.00496673583984</v>
       </c>
       <c r="C164" t="n">
-        <v>93.07208855677598</v>
+        <v>93.07208057875353</v>
       </c>
       <c r="D164" t="n">
-        <v>87.20718994134303</v>
+        <v>87.20718246605232</v>
       </c>
       <c r="E164" t="n">
-        <v>89.27022517929211</v>
+        <v>89.2702175271606</v>
       </c>
       <c r="F164" t="n">
         <v>975500</v>
@@ -3712,16 +3712,16 @@
         <v>43455</v>
       </c>
       <c r="B165" t="n">
-        <v>88.00293731689453</v>
+        <v>88.0029296875</v>
       </c>
       <c r="C165" t="n">
-        <v>90.18384770834878</v>
+        <v>90.18383988988073</v>
       </c>
       <c r="D165" t="n">
-        <v>86.08726275666103</v>
+        <v>86.08725529334548</v>
       </c>
       <c r="E165" t="n">
-        <v>90.18384770834878</v>
+        <v>90.18383988988073</v>
       </c>
       <c r="F165" t="n">
         <v>2053700</v>
@@ -3732,16 +3732,16 @@
         <v>43460</v>
       </c>
       <c r="B166" t="n">
-        <v>90.59645080566406</v>
+        <v>90.59645843505859</v>
       </c>
       <c r="C166" t="n">
-        <v>92.68894905800803</v>
+        <v>92.68895686361802</v>
       </c>
       <c r="D166" t="n">
-        <v>86.38197616073666</v>
+        <v>86.38198343521785</v>
       </c>
       <c r="E166" t="n">
-        <v>87.88503902461112</v>
+        <v>87.88504642566966</v>
       </c>
       <c r="F166" t="n">
         <v>396300</v>
@@ -3752,16 +3752,16 @@
         <v>43461</v>
       </c>
       <c r="B167" t="n">
-        <v>90.62592315673828</v>
+        <v>90.62593078613281</v>
       </c>
       <c r="C167" t="n">
-        <v>91.3627192799638</v>
+        <v>91.36272697138592</v>
       </c>
       <c r="D167" t="n">
-        <v>89.35863292538107</v>
+        <v>89.35864044808805</v>
       </c>
       <c r="E167" t="n">
-        <v>91.3627192799638</v>
+        <v>91.36272697138592</v>
       </c>
       <c r="F167" t="n">
         <v>343866</v>
@@ -3772,16 +3772,16 @@
         <v>43462</v>
       </c>
       <c r="B168" t="n">
-        <v>91.9521484375</v>
+        <v>91.95216369628906</v>
       </c>
       <c r="C168" t="n">
-        <v>92.09950915115729</v>
+        <v>92.0995244343998</v>
       </c>
       <c r="D168" t="n">
-        <v>89.97753286267756</v>
+        <v>89.97754779379356</v>
       </c>
       <c r="E168" t="n">
-        <v>91.33324243423203</v>
+        <v>91.33325759031815</v>
       </c>
       <c r="F168" t="n">
         <v>582800</v>
@@ -3792,16 +3792,16 @@
         <v>43467</v>
       </c>
       <c r="B169" t="n">
-        <v>91.65743255615234</v>
+        <v>91.65742492675781</v>
       </c>
       <c r="C169" t="n">
-        <v>94.192013000172</v>
+        <v>94.19200515980368</v>
       </c>
       <c r="D169" t="n">
-        <v>90.3017303976449</v>
+        <v>90.3017228810965</v>
       </c>
       <c r="E169" t="n">
-        <v>92.21740480094809</v>
+        <v>92.21739712494251</v>
       </c>
       <c r="F169" t="n">
         <v>431033</v>
@@ -3812,16 +3812,16 @@
         <v>43468</v>
       </c>
       <c r="B170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494140625</v>
       </c>
       <c r="C170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.53955725766548</v>
       </c>
       <c r="D170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494140625</v>
       </c>
       <c r="E170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.53955725766548</v>
       </c>
       <c r="F170" t="n">
         <v>308333</v>
@@ -3852,16 +3852,16 @@
         <v>43472</v>
       </c>
       <c r="B172" t="n">
-        <v>91.24482727050781</v>
+        <v>91.24484252929688</v>
       </c>
       <c r="C172" t="n">
-        <v>91.65743129196125</v>
+        <v>91.65744661974971</v>
       </c>
       <c r="D172" t="n">
-        <v>89.88912513069897</v>
+        <v>89.88914016277521</v>
       </c>
       <c r="E172" t="n">
-        <v>89.88912513069897</v>
+        <v>89.88914016277521</v>
       </c>
       <c r="F172" t="n">
         <v>470133</v>
@@ -3892,16 +3892,16 @@
         <v>43474</v>
       </c>
       <c r="B174" t="n">
-        <v>91.36272430419922</v>
+        <v>91.36271667480469</v>
       </c>
       <c r="C174" t="n">
-        <v>91.92268908884118</v>
+        <v>91.92268141268588</v>
       </c>
       <c r="D174" t="n">
-        <v>89.71230059761056</v>
+        <v>89.71229310603738</v>
       </c>
       <c r="E174" t="n">
-        <v>89.71230059761056</v>
+        <v>89.71229310603738</v>
       </c>
       <c r="F174" t="n">
         <v>225833</v>
@@ -3932,16 +3932,16 @@
         <v>43476</v>
       </c>
       <c r="B176" t="n">
-        <v>92.36475372314453</v>
+        <v>92.36476898193359</v>
       </c>
       <c r="C176" t="n">
-        <v>93.04260851834098</v>
+        <v>93.04262388911262</v>
       </c>
       <c r="D176" t="n">
-        <v>90.861690912124</v>
+        <v>90.86170592260495</v>
       </c>
       <c r="E176" t="n">
-        <v>92.39422436727006</v>
+        <v>92.39423963092771</v>
       </c>
       <c r="F176" t="n">
         <v>283133</v>
@@ -3972,16 +3972,16 @@
         <v>43480</v>
       </c>
       <c r="B178" t="n">
-        <v>93.42575073242188</v>
+        <v>93.42575836181641</v>
       </c>
       <c r="C178" t="n">
-        <v>99.26117866454547</v>
+        <v>99.26118677047653</v>
       </c>
       <c r="D178" t="n">
-        <v>92.7478958730117</v>
+        <v>92.74790344705082</v>
       </c>
       <c r="E178" t="n">
-        <v>94.69304101541225</v>
+        <v>94.69304874829707</v>
       </c>
       <c r="F178" t="n">
         <v>736266</v>
@@ -4012,16 +4012,16 @@
         <v>43482</v>
       </c>
       <c r="B180" t="n">
-        <v>99.26117706298828</v>
+        <v>99.26116943359375</v>
       </c>
       <c r="C180" t="n">
-        <v>100.0274438507868</v>
+        <v>100.0274361624956</v>
       </c>
       <c r="D180" t="n">
-        <v>97.90546736604202</v>
+        <v>97.90545984084979</v>
       </c>
       <c r="E180" t="n">
-        <v>98.78962423468569</v>
+        <v>98.78961664153556</v>
       </c>
       <c r="F180" t="n">
         <v>313600</v>
@@ -4032,16 +4032,16 @@
         <v>43483</v>
       </c>
       <c r="B181" t="n">
-        <v>100.7937164306641</v>
+        <v>100.7937088012695</v>
       </c>
       <c r="C181" t="n">
-        <v>102.267308798057</v>
+        <v>102.2673010571217</v>
       </c>
       <c r="D181" t="n">
-        <v>98.73068861532957</v>
+        <v>98.73068114209212</v>
       </c>
       <c r="E181" t="n">
-        <v>99.67378683105167</v>
+        <v>99.67377928642814</v>
       </c>
       <c r="F181" t="n">
         <v>475600</v>
@@ -4052,16 +4052,16 @@
         <v>43486</v>
       </c>
       <c r="B182" t="n">
-        <v>101.3831329345703</v>
+        <v>101.3831481933594</v>
       </c>
       <c r="C182" t="n">
-        <v>102.3557091117745</v>
+        <v>102.3557245169423</v>
       </c>
       <c r="D182" t="n">
-        <v>98.22964675700621</v>
+        <v>98.22966154117607</v>
       </c>
       <c r="E182" t="n">
-        <v>100.7936975967683</v>
+        <v>100.7937127668437</v>
       </c>
       <c r="F182" t="n">
         <v>260300</v>
@@ -4092,16 +4092,16 @@
         <v>43488</v>
       </c>
       <c r="B184" t="n">
-        <v>99.23171997070312</v>
+        <v>99.23169708251953</v>
       </c>
       <c r="C184" t="n">
-        <v>101.0589752504606</v>
+        <v>101.0589519408135</v>
       </c>
       <c r="D184" t="n">
-        <v>98.17073158340929</v>
+        <v>98.17070893994681</v>
       </c>
       <c r="E184" t="n">
-        <v>99.58538276646773</v>
+        <v>99.58535979671043</v>
       </c>
       <c r="F184" t="n">
         <v>240366</v>
@@ -4112,16 +4112,16 @@
         <v>43489</v>
       </c>
       <c r="B185" t="n">
-        <v>98.22965240478516</v>
+        <v>98.22966003417969</v>
       </c>
       <c r="C185" t="n">
-        <v>100.9705347529844</v>
+        <v>100.9705425952604</v>
       </c>
       <c r="D185" t="n">
-        <v>97.05078166140109</v>
+        <v>97.05078919923396</v>
       </c>
       <c r="E185" t="n">
-        <v>99.23169928223126</v>
+        <v>99.23170698945374</v>
       </c>
       <c r="F185" t="n">
         <v>372266</v>
@@ -4132,16 +4132,16 @@
         <v>43493</v>
       </c>
       <c r="B186" t="n">
-        <v>97.257080078125</v>
+        <v>97.25707244873047</v>
       </c>
       <c r="C186" t="n">
-        <v>98.05281742579406</v>
+        <v>98.05280973397741</v>
       </c>
       <c r="D186" t="n">
-        <v>95.96031931021975</v>
+        <v>95.96031178255046</v>
       </c>
       <c r="E186" t="n">
-        <v>98.05281742579406</v>
+        <v>98.05280973397741</v>
       </c>
       <c r="F186" t="n">
         <v>263933</v>
@@ -4152,16 +4152,16 @@
         <v>43494</v>
       </c>
       <c r="B187" t="n">
-        <v>97.31602478027344</v>
+        <v>97.3160400390625</v>
       </c>
       <c r="C187" t="n">
-        <v>97.9938795787921</v>
+        <v>97.99389494386627</v>
       </c>
       <c r="D187" t="n">
-        <v>96.72658940964205</v>
+        <v>96.72660457600985</v>
       </c>
       <c r="E187" t="n">
-        <v>97.4928561409706</v>
+        <v>97.49287142748615</v>
       </c>
       <c r="F187" t="n">
         <v>185333</v>
@@ -4192,16 +4192,16 @@
         <v>43496</v>
       </c>
       <c r="B189" t="n">
-        <v>100.9115905761719</v>
+        <v>100.9115982055664</v>
       </c>
       <c r="C189" t="n">
-        <v>104.566100269176</v>
+        <v>104.5661081748688</v>
       </c>
       <c r="D189" t="n">
-        <v>99.2022183035879</v>
+        <v>99.20222580374578</v>
       </c>
       <c r="E189" t="n">
-        <v>99.79166115348703</v>
+        <v>99.79166869820958</v>
       </c>
       <c r="F189" t="n">
         <v>504800</v>
@@ -4272,16 +4272,16 @@
         <v>43502</v>
       </c>
       <c r="B193" t="n">
-        <v>97.46340179443359</v>
+        <v>97.46340942382812</v>
       </c>
       <c r="C193" t="n">
-        <v>99.55590033335764</v>
+        <v>99.5559081265521</v>
       </c>
       <c r="D193" t="n">
-        <v>96.07822132149781</v>
+        <v>96.07822884246099</v>
       </c>
       <c r="E193" t="n">
-        <v>98.43597069336126</v>
+        <v>98.43597839888808</v>
       </c>
       <c r="F193" t="n">
         <v>594200</v>
@@ -4312,16 +4312,16 @@
         <v>43504</v>
       </c>
       <c r="B195" t="n">
-        <v>97.16866302490234</v>
+        <v>97.16867065429688</v>
       </c>
       <c r="C195" t="n">
-        <v>98.52437260744419</v>
+        <v>98.524380343285</v>
       </c>
       <c r="D195" t="n">
-        <v>95.78349029348294</v>
+        <v>95.78349781411782</v>
       </c>
       <c r="E195" t="n">
-        <v>96.84447844632162</v>
+        <v>96.84448605026213</v>
       </c>
       <c r="F195" t="n">
         <v>210500</v>
@@ -4352,16 +4352,16 @@
         <v>43508</v>
       </c>
       <c r="B197" t="n">
-        <v>97.55181121826172</v>
+        <v>97.55180358886719</v>
       </c>
       <c r="C197" t="n">
-        <v>99.64431719812912</v>
+        <v>99.64430940508254</v>
       </c>
       <c r="D197" t="n">
-        <v>96.7855443786229</v>
+        <v>96.78553680915705</v>
       </c>
       <c r="E197" t="n">
-        <v>98.20019546415823</v>
+        <v>98.20018778405444</v>
       </c>
       <c r="F197" t="n">
         <v>301900</v>
@@ -4472,16 +4472,16 @@
         <v>43516</v>
       </c>
       <c r="B203" t="n">
-        <v>97.257080078125</v>
+        <v>97.25707244873047</v>
       </c>
       <c r="C203" t="n">
-        <v>99.17274683920873</v>
+        <v>99.17273905953849</v>
       </c>
       <c r="D203" t="n">
-        <v>95.51823717645472</v>
+        <v>95.51822968346485</v>
       </c>
       <c r="E203" t="n">
-        <v>98.87803291177583</v>
+        <v>98.87802515522462</v>
       </c>
       <c r="F203" t="n">
         <v>616733</v>
@@ -4492,16 +4492,16 @@
         <v>43517</v>
       </c>
       <c r="B204" t="n">
-        <v>95.78349304199219</v>
+        <v>95.78350067138672</v>
       </c>
       <c r="C204" t="n">
-        <v>97.61074797039947</v>
+        <v>97.61075574533942</v>
       </c>
       <c r="D204" t="n">
-        <v>95.04669694166917</v>
+        <v>95.04670451237605</v>
       </c>
       <c r="E204" t="n">
-        <v>97.28655588743874</v>
+        <v>97.28656363655598</v>
       </c>
       <c r="F204" t="n">
         <v>542100</v>
@@ -4512,16 +4512,16 @@
         <v>43518</v>
       </c>
       <c r="B205" t="n">
-        <v>92.86579132080078</v>
+        <v>92.86577606201172</v>
       </c>
       <c r="C205" t="n">
-        <v>95.87191740128438</v>
+        <v>95.87190164855839</v>
       </c>
       <c r="D205" t="n">
-        <v>92.86579132080078</v>
+        <v>92.86577606201172</v>
       </c>
       <c r="E205" t="n">
-        <v>95.8424467526645</v>
+        <v>95.84243100478083</v>
       </c>
       <c r="F205" t="n">
         <v>514866</v>
@@ -4552,16 +4552,16 @@
         <v>43522</v>
       </c>
       <c r="B207" t="n">
-        <v>95.13511657714844</v>
+        <v>95.13510894775391</v>
       </c>
       <c r="C207" t="n">
-        <v>97.25709311548748</v>
+        <v>97.25708531592029</v>
       </c>
       <c r="D207" t="n">
-        <v>93.36681029027736</v>
+        <v>93.36680280269279</v>
       </c>
       <c r="E207" t="n">
-        <v>95.5771987701748</v>
+        <v>95.57719110532733</v>
       </c>
       <c r="F207" t="n">
         <v>332133</v>
@@ -4572,16 +4572,16 @@
         <v>43523</v>
       </c>
       <c r="B208" t="n">
-        <v>95.69506072998047</v>
+        <v>95.69508361816406</v>
       </c>
       <c r="C208" t="n">
-        <v>96.63816620710067</v>
+        <v>96.63818932085464</v>
       </c>
       <c r="D208" t="n">
-        <v>94.45724884452868</v>
+        <v>94.45727143665449</v>
       </c>
       <c r="E208" t="n">
-        <v>95.13509606892089</v>
+        <v>95.13511882317307</v>
       </c>
       <c r="F208" t="n">
         <v>447266</v>
@@ -4592,16 +4592,16 @@
         <v>43524</v>
       </c>
       <c r="B209" t="n">
-        <v>96.04873657226562</v>
+        <v>96.04875183105469</v>
       </c>
       <c r="C209" t="n">
-        <v>96.46134808570203</v>
+        <v>96.46136341004065</v>
       </c>
       <c r="D209" t="n">
-        <v>94.75197573236808</v>
+        <v>94.75199078514714</v>
       </c>
       <c r="E209" t="n">
-        <v>95.69507384365015</v>
+        <v>95.69508904625457</v>
       </c>
       <c r="F209" t="n">
         <v>596166</v>
@@ -4612,16 +4612,16 @@
         <v>43525</v>
       </c>
       <c r="B210" t="n">
-        <v>95.42984008789062</v>
+        <v>95.42982482910156</v>
       </c>
       <c r="C210" t="n">
-        <v>96.66765976182906</v>
+        <v>96.66764430511837</v>
       </c>
       <c r="D210" t="n">
-        <v>94.60462447357224</v>
+        <v>94.60460934673134</v>
       </c>
       <c r="E210" t="n">
-        <v>95.28247935371824</v>
+        <v>95.28246411849148</v>
       </c>
       <c r="F210" t="n">
         <v>326633</v>
@@ -4652,16 +4652,16 @@
         <v>43531</v>
       </c>
       <c r="B212" t="n">
-        <v>96.10768127441406</v>
+        <v>96.10769653320312</v>
       </c>
       <c r="C212" t="n">
-        <v>96.22556384889319</v>
+        <v>96.22557912639819</v>
       </c>
       <c r="D212" t="n">
-        <v>94.89933242046251</v>
+        <v>94.89934748740488</v>
       </c>
       <c r="E212" t="n">
-        <v>95.72454791720247</v>
+        <v>95.72456311516235</v>
       </c>
       <c r="F212" t="n">
         <v>372100</v>
@@ -4672,16 +4672,16 @@
         <v>43532</v>
       </c>
       <c r="B213" t="n">
-        <v>96.63819122314453</v>
+        <v>96.63817596435547</v>
       </c>
       <c r="C213" t="n">
-        <v>96.75607381699261</v>
+        <v>96.75605853959034</v>
       </c>
       <c r="D213" t="n">
-        <v>95.63614420496521</v>
+        <v>95.63612910439541</v>
       </c>
       <c r="E213" t="n">
-        <v>95.69508550188925</v>
+        <v>95.69507039201285</v>
       </c>
       <c r="F213" t="n">
         <v>212466</v>
@@ -4692,16 +4692,16 @@
         <v>43535</v>
       </c>
       <c r="B214" t="n">
-        <v>97.31602478027344</v>
+        <v>97.3160400390625</v>
       </c>
       <c r="C214" t="n">
-        <v>97.52232678524055</v>
+        <v>97.522342076377</v>
       </c>
       <c r="D214" t="n">
-        <v>96.19609532755058</v>
+        <v>96.19611041073888</v>
       </c>
       <c r="E214" t="n">
-        <v>97.25708349173351</v>
+        <v>97.2570987412808</v>
       </c>
       <c r="F214" t="n">
         <v>533833</v>
@@ -4712,16 +4712,16 @@
         <v>43536</v>
       </c>
       <c r="B215" t="n">
-        <v>97.257080078125</v>
+        <v>97.25707244873047</v>
       </c>
       <c r="C215" t="n">
-        <v>98.49489955955909</v>
+        <v>98.49489183306302</v>
       </c>
       <c r="D215" t="n">
-        <v>95.34140582196414</v>
+        <v>95.34139834284592</v>
       </c>
       <c r="E215" t="n">
-        <v>96.84447608267267</v>
+        <v>96.84446848564514</v>
       </c>
       <c r="F215" t="n">
         <v>275666</v>
@@ -4732,16 +4732,16 @@
         <v>43537</v>
       </c>
       <c r="B216" t="n">
-        <v>95.78349304199219</v>
+        <v>95.78350067138672</v>
       </c>
       <c r="C216" t="n">
-        <v>97.58127732559895</v>
+        <v>97.58128509819149</v>
       </c>
       <c r="D216" t="n">
-        <v>95.40035966943042</v>
+        <v>95.40036726830742</v>
       </c>
       <c r="E216" t="n">
-        <v>97.43391660651884</v>
+        <v>97.43392436737373</v>
       </c>
       <c r="F216" t="n">
         <v>425833</v>
@@ -4752,16 +4752,16 @@
         <v>43538</v>
       </c>
       <c r="B217" t="n">
-        <v>91.0679931640625</v>
+        <v>91.06800842285156</v>
       </c>
       <c r="C217" t="n">
-        <v>94.86986366323212</v>
+        <v>94.86987955903906</v>
       </c>
       <c r="D217" t="n">
-        <v>90.62591851082115</v>
+        <v>90.62593369553892</v>
       </c>
       <c r="E217" t="n">
-        <v>94.86986366323212</v>
+        <v>94.86987955903906</v>
       </c>
       <c r="F217" t="n">
         <v>2325333</v>
@@ -4772,16 +4772,16 @@
         <v>43539</v>
       </c>
       <c r="B218" t="n">
-        <v>89.29969787597656</v>
+        <v>89.29969024658203</v>
       </c>
       <c r="C218" t="n">
-        <v>92.15846313647816</v>
+        <v>92.15845526284264</v>
       </c>
       <c r="D218" t="n">
-        <v>88.91656446472457</v>
+        <v>88.91655686806337</v>
       </c>
       <c r="E218" t="n">
-        <v>91.06800419827536</v>
+        <v>91.0679964178041</v>
       </c>
       <c r="F218" t="n">
         <v>927800</v>
@@ -4832,16 +4832,16 @@
         <v>43544</v>
       </c>
       <c r="B221" t="n">
-        <v>88.65130615234375</v>
+        <v>88.65131378173828</v>
       </c>
       <c r="C221" t="n">
-        <v>89.948067010467</v>
+        <v>89.94807475146169</v>
       </c>
       <c r="D221" t="n">
-        <v>87.88503939459969</v>
+        <v>87.88504695804876</v>
       </c>
       <c r="E221" t="n">
-        <v>89.948067010467</v>
+        <v>89.94807475146169</v>
       </c>
       <c r="F221" t="n">
         <v>1179966</v>
@@ -4872,16 +4872,16 @@
         <v>43546</v>
       </c>
       <c r="B223" t="n">
-        <v>87.82609558105469</v>
+        <v>87.82608795166016</v>
       </c>
       <c r="C223" t="n">
-        <v>87.9439781588119</v>
+        <v>87.94397051917699</v>
       </c>
       <c r="D223" t="n">
-        <v>86.55880540462269</v>
+        <v>86.55879788531681</v>
       </c>
       <c r="E223" t="n">
-        <v>87.9439781588119</v>
+        <v>87.94397051917699</v>
       </c>
       <c r="F223" t="n">
         <v>257266</v>
@@ -4912,16 +4912,16 @@
         <v>43550</v>
       </c>
       <c r="B225" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494140625</v>
       </c>
       <c r="C225" t="n">
-        <v>89.62387506752287</v>
+        <v>89.62388270193819</v>
       </c>
       <c r="D225" t="n">
-        <v>86.76511004398911</v>
+        <v>86.76511743488673</v>
       </c>
       <c r="E225" t="n">
-        <v>88.20923162596166</v>
+        <v>88.20923913987366</v>
       </c>
       <c r="F225" t="n">
         <v>883933</v>
@@ -4992,16 +4992,16 @@
         <v>43556</v>
       </c>
       <c r="B229" t="n">
-        <v>90.89117431640625</v>
+        <v>90.89116668701172</v>
       </c>
       <c r="C229" t="n">
-        <v>91.62797050329212</v>
+        <v>91.62796281205101</v>
       </c>
       <c r="D229" t="n">
-        <v>89.91860544833887</v>
+        <v>89.91859790058164</v>
       </c>
       <c r="E229" t="n">
-        <v>91.12695449266617</v>
+        <v>91.12694684348028</v>
       </c>
       <c r="F229" t="n">
         <v>342733</v>
@@ -5012,16 +5012,16 @@
         <v>43557</v>
       </c>
       <c r="B230" t="n">
-        <v>91.68691253662109</v>
+        <v>91.6868896484375</v>
       </c>
       <c r="C230" t="n">
-        <v>91.92268520042373</v>
+        <v>91.92266225338324</v>
       </c>
       <c r="D230" t="n">
-        <v>89.88912817431608</v>
+        <v>89.88910573492085</v>
       </c>
       <c r="E230" t="n">
-        <v>91.65743439545264</v>
+        <v>91.65741151462781</v>
       </c>
       <c r="F230" t="n">
         <v>264800</v>
@@ -5032,16 +5032,16 @@
         <v>43558</v>
       </c>
       <c r="B231" t="n">
-        <v>88.88707733154297</v>
+        <v>88.88706970214844</v>
       </c>
       <c r="C231" t="n">
-        <v>92.777367336296</v>
+        <v>92.77735937298839</v>
       </c>
       <c r="D231" t="n">
-        <v>88.88707733154297</v>
+        <v>88.88706970214844</v>
       </c>
       <c r="E231" t="n">
-        <v>92.71841855162685</v>
+        <v>92.71841059337896</v>
       </c>
       <c r="F231" t="n">
         <v>371500</v>
@@ -5072,16 +5072,16 @@
         <v>43560</v>
       </c>
       <c r="B233" t="n">
-        <v>84.73155975341797</v>
+        <v>84.73155212402344</v>
       </c>
       <c r="C233" t="n">
-        <v>87.94398776449573</v>
+        <v>87.94397984584793</v>
       </c>
       <c r="D233" t="n">
-        <v>84.43683828667913</v>
+        <v>84.4368306838219</v>
       </c>
       <c r="E233" t="n">
-        <v>87.08930900209394</v>
+        <v>87.08930116040308</v>
       </c>
       <c r="F233" t="n">
         <v>673866</v>
@@ -5132,16 +5132,16 @@
         <v>43565</v>
       </c>
       <c r="B236" t="n">
-        <v>83.40531158447266</v>
+        <v>83.40531921386719</v>
       </c>
       <c r="C236" t="n">
-        <v>84.2305195353845</v>
+        <v>84.23052724026388</v>
       </c>
       <c r="D236" t="n">
-        <v>81.60752748345887</v>
+        <v>81.60753494840338</v>
       </c>
       <c r="E236" t="n">
-        <v>83.64108421400793</v>
+        <v>83.64109186496947</v>
       </c>
       <c r="F236" t="n">
         <v>456233</v>
@@ -5152,16 +5152,16 @@
         <v>43566</v>
       </c>
       <c r="B237" t="n">
-        <v>84.34843444824219</v>
+        <v>84.34842681884766</v>
       </c>
       <c r="C237" t="n">
-        <v>84.61367779773019</v>
+        <v>84.61367014434416</v>
       </c>
       <c r="D237" t="n">
-        <v>82.40328907004057</v>
+        <v>82.40328161658626</v>
       </c>
       <c r="E237" t="n">
-        <v>83.78846960369731</v>
+        <v>83.78846202495211</v>
       </c>
       <c r="F237" t="n">
         <v>403133</v>
@@ -5192,16 +5192,16 @@
         <v>43570</v>
       </c>
       <c r="B239" t="n">
-        <v>83.96528625488281</v>
+        <v>83.96529388427734</v>
       </c>
       <c r="C239" t="n">
-        <v>84.37789027943356</v>
+        <v>84.37789794631881</v>
       </c>
       <c r="D239" t="n">
-        <v>82.58010596450545</v>
+        <v>82.58011346803741</v>
       </c>
       <c r="E239" t="n">
-        <v>82.81587862209479</v>
+        <v>82.81588614704992</v>
       </c>
       <c r="F239" t="n">
         <v>210900</v>
@@ -5212,16 +5212,16 @@
         <v>43571</v>
       </c>
       <c r="B240" t="n">
-        <v>83.58213806152344</v>
+        <v>83.58214569091797</v>
       </c>
       <c r="C240" t="n">
-        <v>84.40734596436485</v>
+        <v>84.40735366908453</v>
       </c>
       <c r="D240" t="n">
-        <v>82.58009132798593</v>
+        <v>82.58009886591343</v>
       </c>
       <c r="E240" t="n">
-        <v>83.11058533484525</v>
+        <v>83.11059292119636</v>
       </c>
       <c r="F240" t="n">
         <v>215300</v>
@@ -5232,16 +5232,16 @@
         <v>43572</v>
       </c>
       <c r="B241" t="n">
-        <v>82.66853332519531</v>
+        <v>82.66852569580078</v>
       </c>
       <c r="C241" t="n">
-        <v>84.23053763728586</v>
+        <v>84.23052986373555</v>
       </c>
       <c r="D241" t="n">
-        <v>81.460184285873</v>
+        <v>81.46017676799576</v>
       </c>
       <c r="E241" t="n">
-        <v>84.20106698914505</v>
+        <v>84.20105921831454</v>
       </c>
       <c r="F241" t="n">
         <v>289766</v>
@@ -5252,16 +5252,16 @@
         <v>43573</v>
       </c>
       <c r="B242" t="n">
-        <v>83.99476623535156</v>
+        <v>83.99475860595703</v>
       </c>
       <c r="C242" t="n">
-        <v>84.43684095434833</v>
+        <v>84.43683328479936</v>
       </c>
       <c r="D242" t="n">
-        <v>81.69595820936428</v>
+        <v>81.6959507887746</v>
       </c>
       <c r="E242" t="n">
-        <v>82.19698172061818</v>
+        <v>82.19697425451963</v>
       </c>
       <c r="F242" t="n">
         <v>318766</v>
@@ -5332,16 +5332,16 @@
         <v>43580</v>
       </c>
       <c r="B246" t="n">
-        <v>87.90399169921875</v>
+        <v>87.90398406982422</v>
       </c>
       <c r="C246" t="n">
-        <v>88.55513600257547</v>
+        <v>88.5551283166666</v>
       </c>
       <c r="D246" t="n">
-        <v>84.88506908870511</v>
+        <v>84.88506172132999</v>
       </c>
       <c r="E246" t="n">
-        <v>87.01607107054306</v>
+        <v>87.01606351821326</v>
       </c>
       <c r="F246" t="n">
         <v>486633</v>
@@ -5372,16 +5372,16 @@
         <v>43584</v>
       </c>
       <c r="B248" t="n">
-        <v>87.60800170898438</v>
+        <v>87.60800933837891</v>
       </c>
       <c r="C248" t="n">
-        <v>88.910290108505</v>
+        <v>88.91029785131008</v>
       </c>
       <c r="D248" t="n">
-        <v>86.66088903140958</v>
+        <v>86.66089657832424</v>
       </c>
       <c r="E248" t="n">
-        <v>87.87438161869812</v>
+        <v>87.87438927129051</v>
       </c>
       <c r="F248" t="n">
         <v>356166</v>
@@ -5392,16 +5392,16 @@
         <v>43585</v>
       </c>
       <c r="B249" t="n">
-        <v>89.56143188476562</v>
+        <v>89.56143951416016</v>
       </c>
       <c r="C249" t="n">
-        <v>90.27176831516947</v>
+        <v>90.27177600507484</v>
       </c>
       <c r="D249" t="n">
-        <v>86.77928588367251</v>
+        <v>86.77929327606671</v>
       </c>
       <c r="E249" t="n">
-        <v>86.77928588367251</v>
+        <v>86.77929327606671</v>
       </c>
       <c r="F249" t="n">
         <v>318366</v>
@@ -5412,16 +5412,16 @@
         <v>43587</v>
       </c>
       <c r="B250" t="n">
-        <v>89.82781982421875</v>
+        <v>89.82780456542969</v>
       </c>
       <c r="C250" t="n">
-        <v>90.41977196996037</v>
+        <v>90.41975661061814</v>
       </c>
       <c r="D250" t="n">
-        <v>88.6439305867039</v>
+        <v>88.64391552901864</v>
       </c>
       <c r="E250" t="n">
-        <v>88.6439305867039</v>
+        <v>88.64391552901864</v>
       </c>
       <c r="F250" t="n">
         <v>415166</v>
@@ -5432,16 +5432,16 @@
         <v>43588</v>
       </c>
       <c r="B251" t="n">
-        <v>90.21257781982422</v>
+        <v>90.21257019042969</v>
       </c>
       <c r="C251" t="n">
-        <v>90.89331063928984</v>
+        <v>90.89330295232486</v>
       </c>
       <c r="D251" t="n">
-        <v>88.91029684856353</v>
+        <v>88.91028932930459</v>
       </c>
       <c r="E251" t="n">
-        <v>88.91029684856353</v>
+        <v>88.91028932930459</v>
       </c>
       <c r="F251" t="n">
         <v>248400</v>
@@ -5452,16 +5452,16 @@
         <v>43591</v>
       </c>
       <c r="B252" t="n">
-        <v>90.53814697265625</v>
+        <v>90.53813934326172</v>
       </c>
       <c r="C252" t="n">
-        <v>91.10049543110814</v>
+        <v>91.1004877543261</v>
       </c>
       <c r="D252" t="n">
-        <v>88.19996484240103</v>
+        <v>88.19995741003851</v>
       </c>
       <c r="E252" t="n">
-        <v>88.64392137860601</v>
+        <v>88.64391390883252</v>
       </c>
       <c r="F252" t="n">
         <v>206566</v>
@@ -5472,16 +5472,16 @@
         <v>43592</v>
       </c>
       <c r="B253" t="n">
-        <v>96.93115997314453</v>
+        <v>96.93116760253906</v>
       </c>
       <c r="C253" t="n">
-        <v>97.64149639558559</v>
+        <v>97.64150408089029</v>
       </c>
       <c r="D253" t="n">
-        <v>89.47264259147906</v>
+        <v>89.47264963381808</v>
       </c>
       <c r="E253" t="n">
-        <v>90.83411571650254</v>
+        <v>90.8341228660023</v>
       </c>
       <c r="F253" t="n">
         <v>3210933</v>
@@ -5512,16 +5512,16 @@
         <v>43594</v>
       </c>
       <c r="B255" t="n">
-        <v>105.2183990478516</v>
+        <v>105.2184219360352</v>
       </c>
       <c r="C255" t="n">
-        <v>106.3726918979597</v>
+        <v>106.3727150372369</v>
       </c>
       <c r="D255" t="n">
-        <v>99.7724918375764</v>
+        <v>99.7725135411105</v>
       </c>
       <c r="E255" t="n">
-        <v>101.4891405924361</v>
+        <v>101.4891626693933</v>
       </c>
       <c r="F255" t="n">
         <v>781533</v>
@@ -5532,16 +5532,16 @@
         <v>43595</v>
       </c>
       <c r="B256" t="n">
-        <v>103.5905532836914</v>
+        <v>103.5905456542969</v>
       </c>
       <c r="C256" t="n">
-        <v>105.2184063406888</v>
+        <v>105.2183985914037</v>
       </c>
       <c r="D256" t="n">
-        <v>101.3411596167057</v>
+        <v>101.3411521529779</v>
       </c>
       <c r="E256" t="n">
-        <v>105.2184063406888</v>
+        <v>105.2183985914037</v>
       </c>
       <c r="F256" t="n">
         <v>440400</v>
@@ -5552,16 +5552,16 @@
         <v>43598</v>
       </c>
       <c r="B257" t="n">
-        <v>102.9986114501953</v>
+        <v>102.9986038208008</v>
       </c>
       <c r="C257" t="n">
-        <v>102.9986114501953</v>
+        <v>102.9986038208008</v>
       </c>
       <c r="D257" t="n">
-        <v>100.6900180029186</v>
+        <v>100.6900105445281</v>
       </c>
       <c r="E257" t="n">
-        <v>102.3770632970524</v>
+        <v>102.3770557136976</v>
       </c>
       <c r="F257" t="n">
         <v>256966</v>
@@ -5592,16 +5592,16 @@
         <v>43600</v>
       </c>
       <c r="B259" t="n">
-        <v>103.5905532836914</v>
+        <v>103.5905456542969</v>
       </c>
       <c r="C259" t="n">
-        <v>104.3304858071463</v>
+        <v>104.3304781232561</v>
       </c>
       <c r="D259" t="n">
-        <v>100.9267916830639</v>
+        <v>100.9267842498542</v>
       </c>
       <c r="E259" t="n">
-        <v>101.607532013277</v>
+        <v>101.607524529931</v>
       </c>
       <c r="F259" t="n">
         <v>328866</v>
@@ -5612,16 +5612,16 @@
         <v>43601</v>
       </c>
       <c r="B260" t="n">
-        <v>102.5842361450195</v>
+        <v>102.5842437744141</v>
       </c>
       <c r="C260" t="n">
-        <v>103.6793368318073</v>
+        <v>103.6793445426467</v>
       </c>
       <c r="D260" t="n">
-        <v>102.5842361450195</v>
+        <v>102.5842437744141</v>
       </c>
       <c r="E260" t="n">
-        <v>103.5905485460052</v>
+        <v>103.5905562502412</v>
       </c>
       <c r="F260" t="n">
         <v>583833</v>
@@ -5632,16 +5632,16 @@
         <v>43602</v>
       </c>
       <c r="B261" t="n">
-        <v>102.9690246582031</v>
+        <v>102.9690093994141</v>
       </c>
       <c r="C261" t="n">
-        <v>103.5609692404666</v>
+        <v>103.5609538939583</v>
       </c>
       <c r="D261" t="n">
-        <v>101.5483516391839</v>
+        <v>101.5483365909217</v>
       </c>
       <c r="E261" t="n">
-        <v>102.9394210311538</v>
+        <v>102.9394057767516</v>
       </c>
       <c r="F261" t="n">
         <v>361233</v>
@@ -5672,16 +5672,16 @@
         <v>43606</v>
       </c>
       <c r="B263" t="n">
-        <v>108.355712890625</v>
+        <v>108.3557281494141</v>
       </c>
       <c r="C263" t="n">
-        <v>109.8355778330471</v>
+        <v>109.8355933002327</v>
       </c>
       <c r="D263" t="n">
-        <v>105.8103433831832</v>
+        <v>105.8103582835301</v>
       </c>
       <c r="E263" t="n">
-        <v>105.8103433831832</v>
+        <v>105.8103582835301</v>
       </c>
       <c r="F263" t="n">
         <v>554800</v>
@@ -5692,16 +5692,16 @@
         <v>43607</v>
       </c>
       <c r="B264" t="n">
-        <v>109.4508361816406</v>
+        <v>109.4508285522461</v>
       </c>
       <c r="C264" t="n">
-        <v>110.3091532084535</v>
+        <v>110.309145519229</v>
       </c>
       <c r="D264" t="n">
-        <v>107.8821751042858</v>
+        <v>107.8821675842365</v>
       </c>
       <c r="E264" t="n">
-        <v>108.3261316680177</v>
+        <v>108.3261241170219</v>
       </c>
       <c r="F264" t="n">
         <v>582066</v>
@@ -5732,16 +5732,16 @@
         <v>43609</v>
       </c>
       <c r="B266" t="n">
-        <v>110.3979339599609</v>
+        <v>110.3979263305664</v>
       </c>
       <c r="C266" t="n">
-        <v>111.9073951028777</v>
+        <v>111.9073873691671</v>
       </c>
       <c r="D266" t="n">
-        <v>109.9539699298789</v>
+        <v>109.9539623311659</v>
       </c>
       <c r="E266" t="n">
-        <v>111.1970586763327</v>
+        <v>111.1970509917121</v>
       </c>
       <c r="F266" t="n">
         <v>294000</v>
@@ -5772,16 +5772,16 @@
         <v>43613</v>
       </c>
       <c r="B268" t="n">
-        <v>109.302848815918</v>
+        <v>109.3028335571289</v>
       </c>
       <c r="C268" t="n">
-        <v>111.0786826086257</v>
+        <v>111.0786671019285</v>
       </c>
       <c r="D268" t="n">
-        <v>107.0830509297953</v>
+        <v>107.0830359808923</v>
       </c>
       <c r="E268" t="n">
-        <v>110.575533840533</v>
+        <v>110.5755184040759</v>
       </c>
       <c r="F268" t="n">
         <v>402233</v>
@@ -5792,16 +5792,16 @@
         <v>43614</v>
       </c>
       <c r="B269" t="n">
-        <v>109.9243927001953</v>
+        <v>109.9243774414062</v>
       </c>
       <c r="C269" t="n">
-        <v>110.1019768373113</v>
+        <v>110.1019615538715</v>
       </c>
       <c r="D269" t="n">
-        <v>108.3557390948242</v>
+        <v>108.3557240537826</v>
       </c>
       <c r="E269" t="n">
-        <v>109.2732558820928</v>
+        <v>109.2732407136891</v>
       </c>
       <c r="F269" t="n">
         <v>725533</v>
@@ -5832,16 +5832,16 @@
         <v>43616</v>
       </c>
       <c r="B271" t="n">
-        <v>108.8588714599609</v>
+        <v>108.8588790893555</v>
       </c>
       <c r="C271" t="n">
-        <v>110.4275323557388</v>
+        <v>110.4275400950732</v>
       </c>
       <c r="D271" t="n">
-        <v>106.8462540518404</v>
+        <v>106.8462615401803</v>
       </c>
       <c r="E271" t="n">
-        <v>107.4086100070495</v>
+        <v>107.4086175348022</v>
       </c>
       <c r="F271" t="n">
         <v>504400</v>
@@ -5892,16 +5892,16 @@
         <v>43621</v>
       </c>
       <c r="B274" t="n">
-        <v>108.8884811401367</v>
+        <v>108.8884735107422</v>
       </c>
       <c r="C274" t="n">
-        <v>109.8355939389301</v>
+        <v>109.835586243175</v>
       </c>
       <c r="D274" t="n">
-        <v>106.4023034571936</v>
+        <v>106.4022960019959</v>
       </c>
       <c r="E274" t="n">
-        <v>106.6390797751461</v>
+        <v>106.6390723033584</v>
       </c>
       <c r="F274" t="n">
         <v>231033</v>
@@ -5932,16 +5932,16 @@
         <v>43623</v>
       </c>
       <c r="B276" t="n">
-        <v>110.6051177978516</v>
+        <v>110.6051254272461</v>
       </c>
       <c r="C276" t="n">
-        <v>110.6643099930145</v>
+        <v>110.664317626492</v>
       </c>
       <c r="D276" t="n">
-        <v>108.9180724928598</v>
+        <v>108.9180800058842</v>
       </c>
       <c r="E276" t="n">
-        <v>109.2140409956576</v>
+        <v>109.2140485290975</v>
       </c>
       <c r="F276" t="n">
         <v>204266</v>
@@ -5992,16 +5992,16 @@
         <v>43628</v>
       </c>
       <c r="B279" t="n">
-        <v>108.9180679321289</v>
+        <v>108.9180755615234</v>
       </c>
       <c r="C279" t="n">
-        <v>111.7594060857212</v>
+        <v>111.7594139141432</v>
       </c>
       <c r="D279" t="n">
-        <v>108.7996760197774</v>
+        <v>108.7996836408789</v>
       </c>
       <c r="E279" t="n">
-        <v>111.7594060857212</v>
+        <v>111.7594139141432</v>
       </c>
       <c r="F279" t="n">
         <v>382266</v>
@@ -6012,16 +6012,16 @@
         <v>43629</v>
       </c>
       <c r="B280" t="n">
-        <v>113.8608169555664</v>
+        <v>113.8608093261719</v>
       </c>
       <c r="C280" t="n">
-        <v>114.9855138301545</v>
+        <v>114.9855061253982</v>
       </c>
       <c r="D280" t="n">
-        <v>108.9180729377125</v>
+        <v>108.9180656395131</v>
       </c>
       <c r="E280" t="n">
-        <v>108.9180729377125</v>
+        <v>108.9180656395131</v>
       </c>
       <c r="F280" t="n">
         <v>845300</v>
@@ -6032,16 +6032,16 @@
         <v>43630</v>
       </c>
       <c r="B281" t="n">
-        <v>111.9370040893555</v>
+        <v>111.9369964599609</v>
       </c>
       <c r="C281" t="n">
-        <v>114.1568019144333</v>
+        <v>114.156794133742</v>
       </c>
       <c r="D281" t="n">
-        <v>110.7531149267741</v>
+        <v>110.753107378071</v>
       </c>
       <c r="E281" t="n">
-        <v>113.3576771060401</v>
+        <v>113.3576693798154</v>
       </c>
       <c r="F281" t="n">
         <v>560666</v>
@@ -6052,16 +6052,16 @@
         <v>43633</v>
       </c>
       <c r="B282" t="n">
-        <v>110.0723648071289</v>
+        <v>110.0723571777344</v>
       </c>
       <c r="C282" t="n">
-        <v>113.1504868960452</v>
+        <v>113.1504790532982</v>
       </c>
       <c r="D282" t="n">
-        <v>109.066052333433</v>
+        <v>109.0660447737885</v>
       </c>
       <c r="E282" t="n">
-        <v>113.1504868960452</v>
+        <v>113.1504790532982</v>
       </c>
       <c r="F282" t="n">
         <v>481366</v>
@@ -6072,16 +6072,16 @@
         <v>43634</v>
       </c>
       <c r="B283" t="n">
-        <v>112.4697418212891</v>
+        <v>112.4697494506836</v>
       </c>
       <c r="C283" t="n">
-        <v>113.1800782371092</v>
+        <v>113.1800859146894</v>
       </c>
       <c r="D283" t="n">
-        <v>110.0131679890634</v>
+        <v>110.0131754518161</v>
       </c>
       <c r="E283" t="n">
-        <v>110.9602807011627</v>
+        <v>110.9602882281628</v>
       </c>
       <c r="F283" t="n">
         <v>583133</v>
@@ -6152,16 +6152,16 @@
         <v>43641</v>
       </c>
       <c r="B287" t="n">
-        <v>114.4823684692383</v>
+        <v>114.4823760986328</v>
       </c>
       <c r="C287" t="n">
-        <v>117.1165266196842</v>
+        <v>117.1165344246257</v>
       </c>
       <c r="D287" t="n">
-        <v>113.8312241927775</v>
+        <v>113.8312317787781</v>
       </c>
       <c r="E287" t="n">
-        <v>116.5837742644845</v>
+        <v>116.583782033922</v>
       </c>
       <c r="F287" t="n">
         <v>481433</v>
@@ -6172,16 +6172,16 @@
         <v>43642</v>
       </c>
       <c r="B288" t="n">
-        <v>113.1208801269531</v>
+        <v>113.1208877563477</v>
       </c>
       <c r="C288" t="n">
-        <v>115.7254420040218</v>
+        <v>115.72544980908</v>
       </c>
       <c r="D288" t="n">
-        <v>112.6769236242416</v>
+        <v>112.6769312236937</v>
       </c>
       <c r="E288" t="n">
-        <v>115.7254420040218</v>
+        <v>115.72544980908</v>
       </c>
       <c r="F288" t="n">
         <v>335833</v>
@@ -6192,16 +6192,16 @@
         <v>43643</v>
       </c>
       <c r="B289" t="n">
-        <v>115.281494140625</v>
+        <v>115.2814865112305</v>
       </c>
       <c r="C289" t="n">
-        <v>115.281494140625</v>
+        <v>115.2814865112305</v>
       </c>
       <c r="D289" t="n">
-        <v>112.9137083857593</v>
+        <v>112.9137009130662</v>
       </c>
       <c r="E289" t="n">
-        <v>113.3872685475258</v>
+        <v>113.3872610434922</v>
       </c>
       <c r="F289" t="n">
         <v>276700</v>
@@ -6252,16 +6252,16 @@
         <v>43648</v>
       </c>
       <c r="B292" t="n">
-        <v>110.1315536499023</v>
+        <v>110.1315612792969</v>
       </c>
       <c r="C292" t="n">
-        <v>115.1334971877844</v>
+        <v>115.1335051636899</v>
       </c>
       <c r="D292" t="n">
-        <v>110.1315536499023</v>
+        <v>110.1315612792969</v>
       </c>
       <c r="E292" t="n">
-        <v>113.9792042621922</v>
+        <v>113.9792121581339</v>
       </c>
       <c r="F292" t="n">
         <v>537533</v>
@@ -6272,16 +6272,16 @@
         <v>43649</v>
       </c>
       <c r="B293" t="n">
-        <v>109.9691543579102</v>
+        <v>109.9691619873047</v>
       </c>
       <c r="C293" t="n">
-        <v>110.8607976617096</v>
+        <v>110.8608053529641</v>
       </c>
       <c r="D293" t="n">
-        <v>107.3239521887562</v>
+        <v>107.323959634633</v>
       </c>
       <c r="E293" t="n">
-        <v>110.7121891846528</v>
+        <v>110.7121968655973</v>
       </c>
       <c r="F293" t="n">
         <v>1690900</v>
@@ -6292,16 +6292,16 @@
         <v>43650</v>
       </c>
       <c r="B294" t="n">
-        <v>114.1004333496094</v>
+        <v>114.1004409790039</v>
       </c>
       <c r="C294" t="n">
-        <v>114.1004333496094</v>
+        <v>114.1004409790039</v>
       </c>
       <c r="D294" t="n">
-        <v>109.4044550659338</v>
+        <v>109.4044623813289</v>
       </c>
       <c r="E294" t="n">
-        <v>109.9691612673977</v>
+        <v>109.9691686205522</v>
       </c>
       <c r="F294" t="n">
         <v>412866</v>
@@ -6312,16 +6312,16 @@
         <v>43651</v>
       </c>
       <c r="B295" t="n">
-        <v>117.5184097290039</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="C295" t="n">
-        <v>117.5184097290039</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="D295" t="n">
-        <v>112.9115915541116</v>
+        <v>112.9115768934796</v>
       </c>
       <c r="E295" t="n">
-        <v>114.0707242553141</v>
+        <v>114.0707094441784</v>
       </c>
       <c r="F295" t="n">
         <v>288866</v>
@@ -6332,16 +6332,16 @@
         <v>43654</v>
       </c>
       <c r="B296" t="n">
-        <v>121.9171600341797</v>
+        <v>121.9171676635742</v>
       </c>
       <c r="C296" t="n">
-        <v>122.8682437684256</v>
+        <v>122.8682514573375</v>
       </c>
       <c r="D296" t="n">
-        <v>115.4081748228237</v>
+        <v>115.4081820448956</v>
       </c>
       <c r="E296" t="n">
-        <v>117.4886709638954</v>
+        <v>117.4886783161617</v>
       </c>
       <c r="F296" t="n">
         <v>420600</v>
@@ -6352,16 +6352,16 @@
         <v>43656</v>
       </c>
       <c r="B297" t="n">
-        <v>128.0397796630859</v>
+        <v>128.0398101806641</v>
       </c>
       <c r="C297" t="n">
-        <v>128.0397796630859</v>
+        <v>128.0398101806641</v>
       </c>
       <c r="D297" t="n">
-        <v>121.9171642141075</v>
+        <v>121.9171932723939</v>
       </c>
       <c r="E297" t="n">
-        <v>121.9171642141075</v>
+        <v>121.9171932723939</v>
       </c>
       <c r="F297" t="n">
         <v>529166</v>
@@ -6372,16 +6372,16 @@
         <v>43657</v>
       </c>
       <c r="B298" t="n">
-        <v>123.1654663085938</v>
+        <v>123.1654586791992</v>
       </c>
       <c r="C298" t="n">
-        <v>130.1797101104775</v>
+        <v>130.1797020465908</v>
       </c>
       <c r="D298" t="n">
-        <v>123.1060259345613</v>
+        <v>123.1060183088487</v>
       </c>
       <c r="E298" t="n">
-        <v>130.1797101104775</v>
+        <v>130.1797020465908</v>
       </c>
       <c r="F298" t="n">
         <v>660700</v>
@@ -6392,16 +6392,16 @@
         <v>43658</v>
       </c>
       <c r="B299" t="n">
-        <v>124.8001403808594</v>
+        <v>124.8001327514648</v>
       </c>
       <c r="C299" t="n">
-        <v>125.8701048697979</v>
+        <v>125.8700971749934</v>
       </c>
       <c r="D299" t="n">
-        <v>122.7196442164533</v>
+        <v>122.7196367142455</v>
       </c>
       <c r="E299" t="n">
-        <v>124.2057139851064</v>
+        <v>124.2057063920509</v>
       </c>
       <c r="F299" t="n">
         <v>362933</v>
@@ -6412,16 +6412,16 @@
         <v>43661</v>
       </c>
       <c r="B300" t="n">
-        <v>121.5605087280273</v>
+        <v>121.5605010986328</v>
       </c>
       <c r="C300" t="n">
-        <v>126.7320329312208</v>
+        <v>126.7320249772505</v>
       </c>
       <c r="D300" t="n">
-        <v>118.5289287021037</v>
+        <v>118.5289212629776</v>
       </c>
       <c r="E300" t="n">
-        <v>124.9784738625208</v>
+        <v>124.9784660186075</v>
       </c>
       <c r="F300" t="n">
         <v>1110366</v>
@@ -6452,16 +6452,16 @@
         <v>43663</v>
       </c>
       <c r="B302" t="n">
-        <v>126.6131439208984</v>
+        <v>126.6131362915039</v>
       </c>
       <c r="C302" t="n">
-        <v>127.9506052449931</v>
+        <v>127.9505975350065</v>
       </c>
       <c r="D302" t="n">
-        <v>122.7493684420787</v>
+        <v>122.7493610455057</v>
       </c>
       <c r="E302" t="n">
-        <v>123.9679414596935</v>
+        <v>123.9679339896924</v>
       </c>
       <c r="F302" t="n">
         <v>443966</v>
@@ -6492,16 +6492,16 @@
         <v>43665</v>
       </c>
       <c r="B304" t="n">
-        <v>126.9995346069336</v>
+        <v>126.9995193481445</v>
       </c>
       <c r="C304" t="n">
-        <v>132.3791003266432</v>
+        <v>132.379084421508</v>
       </c>
       <c r="D304" t="n">
-        <v>126.9995346069336</v>
+        <v>126.9995193481445</v>
       </c>
       <c r="E304" t="n">
-        <v>129.9419541843396</v>
+        <v>129.9419385720236</v>
       </c>
       <c r="F304" t="n">
         <v>683033</v>
@@ -6512,16 +6512,16 @@
         <v>43668</v>
       </c>
       <c r="B305" t="n">
-        <v>127.4453506469727</v>
+        <v>127.4453582763672</v>
       </c>
       <c r="C305" t="n">
-        <v>129.0800214468836</v>
+        <v>129.0800291741361</v>
       </c>
       <c r="D305" t="n">
-        <v>126.078169096225</v>
+        <v>126.0781766437745</v>
       </c>
       <c r="E305" t="n">
-        <v>126.3456583453883</v>
+        <v>126.3456659089508</v>
       </c>
       <c r="F305" t="n">
         <v>163233</v>
@@ -6532,16 +6532,16 @@
         <v>43669</v>
       </c>
       <c r="B306" t="n">
-        <v>125.067626953125</v>
+        <v>125.0676422119141</v>
       </c>
       <c r="C306" t="n">
-        <v>127.8019973856753</v>
+        <v>127.8020129780693</v>
       </c>
       <c r="D306" t="n">
-        <v>123.6409975868307</v>
+        <v>123.6410126715648</v>
       </c>
       <c r="E306" t="n">
-        <v>127.4750602294759</v>
+        <v>127.4750757819822</v>
       </c>
       <c r="F306" t="n">
         <v>528700</v>
@@ -6552,16 +6552,16 @@
         <v>43670</v>
       </c>
       <c r="B307" t="n">
-        <v>128.8719635009766</v>
+        <v>128.8719787597656</v>
       </c>
       <c r="C307" t="n">
-        <v>131.8441028387747</v>
+        <v>131.8441184494731</v>
       </c>
       <c r="D307" t="n">
-        <v>124.948740482108</v>
+        <v>124.9487552763768</v>
       </c>
       <c r="E307" t="n">
-        <v>124.948740482108</v>
+        <v>124.9487552763768</v>
       </c>
       <c r="F307" t="n">
         <v>788600</v>
@@ -6612,16 +6612,16 @@
         <v>43675</v>
       </c>
       <c r="B310" t="n">
-        <v>126.0187225341797</v>
+        <v>126.0187149047852</v>
       </c>
       <c r="C310" t="n">
-        <v>126.8806382252905</v>
+        <v>126.8806305437141</v>
       </c>
       <c r="D310" t="n">
-        <v>125.0081983436745</v>
+        <v>125.0081907754589</v>
       </c>
       <c r="E310" t="n">
-        <v>126.6131489732146</v>
+        <v>126.6131413078325</v>
       </c>
       <c r="F310" t="n">
         <v>708133</v>
@@ -6632,16 +6632,16 @@
         <v>43676</v>
       </c>
       <c r="B311" t="n">
-        <v>124.3840408325195</v>
+        <v>124.384033203125</v>
       </c>
       <c r="C311" t="n">
-        <v>126.3753765306633</v>
+        <v>126.3753687791254</v>
       </c>
       <c r="D311" t="n">
-        <v>124.294880270392</v>
+        <v>124.2948726464664</v>
       </c>
       <c r="E311" t="n">
-        <v>126.2267680352421</v>
+        <v>126.2267602928194</v>
       </c>
       <c r="F311" t="n">
         <v>1065500</v>
@@ -6652,16 +6652,16 @@
         <v>43677</v>
       </c>
       <c r="B312" t="n">
-        <v>124.2354431152344</v>
+        <v>124.2354354858398</v>
       </c>
       <c r="C312" t="n">
-        <v>126.1673309301498</v>
+        <v>126.1673231821166</v>
       </c>
       <c r="D312" t="n">
-        <v>121.1444150528274</v>
+        <v>121.1444076132553</v>
       </c>
       <c r="E312" t="n">
-        <v>125.5729044916022</v>
+        <v>125.5728967800731</v>
       </c>
       <c r="F312" t="n">
         <v>1188566</v>
@@ -6672,16 +6672,16 @@
         <v>43678</v>
       </c>
       <c r="B313" t="n">
-        <v>122.6601943969727</v>
+        <v>122.6601867675781</v>
       </c>
       <c r="C313" t="n">
-        <v>126.5834176187757</v>
+        <v>126.5834097453589</v>
       </c>
       <c r="D313" t="n">
-        <v>121.7982787818937</v>
+        <v>121.7982712061099</v>
       </c>
       <c r="E313" t="n">
-        <v>124.6515299726937</v>
+        <v>124.6515222194392</v>
       </c>
       <c r="F313" t="n">
         <v>895666</v>
@@ -6732,16 +6732,16 @@
         <v>43683</v>
       </c>
       <c r="B316" t="n">
-        <v>126.6131439208984</v>
+        <v>126.6131362915039</v>
       </c>
       <c r="C316" t="n">
-        <v>127.1778501492292</v>
+        <v>127.1778424858068</v>
       </c>
       <c r="D316" t="n">
-        <v>123.1357459899607</v>
+        <v>123.1357385701055</v>
       </c>
       <c r="E316" t="n">
-        <v>123.1951863639296</v>
+        <v>123.1951789404927</v>
       </c>
       <c r="F316" t="n">
         <v>466533</v>
@@ -6752,16 +6752,16 @@
         <v>43684</v>
       </c>
       <c r="B317" t="n">
-        <v>128.5153045654297</v>
+        <v>128.5153198242188</v>
       </c>
       <c r="C317" t="n">
-        <v>129.2583393905688</v>
+        <v>129.2583547375794</v>
       </c>
       <c r="D317" t="n">
-        <v>124.740682513915</v>
+        <v>124.7406973245383</v>
       </c>
       <c r="E317" t="n">
-        <v>126.6131296685823</v>
+        <v>126.6131447015237</v>
       </c>
       <c r="F317" t="n">
         <v>506366</v>
@@ -6772,16 +6772,16 @@
         <v>43685</v>
       </c>
       <c r="B318" t="n">
-        <v>131.903564453125</v>
+        <v>131.9035491943359</v>
       </c>
       <c r="C318" t="n">
-        <v>133.5679554941837</v>
+        <v>133.5679400428555</v>
       </c>
       <c r="D318" t="n">
-        <v>129.2880820192579</v>
+        <v>129.2880670630315</v>
       </c>
       <c r="E318" t="n">
-        <v>129.2880820192579</v>
+        <v>129.2880670630315</v>
       </c>
       <c r="F318" t="n">
         <v>971500</v>
@@ -6792,16 +6792,16 @@
         <v>43686</v>
       </c>
       <c r="B319" t="n">
-        <v>131.5171661376953</v>
+        <v>131.5171966552734</v>
       </c>
       <c r="C319" t="n">
-        <v>134.8756829959633</v>
+        <v>134.8757142928603</v>
       </c>
       <c r="D319" t="n">
-        <v>129.4069423633303</v>
+        <v>129.4069723912467</v>
       </c>
       <c r="E319" t="n">
-        <v>134.8756829959633</v>
+        <v>134.8757142928603</v>
       </c>
       <c r="F319" t="n">
         <v>371566</v>
@@ -6812,16 +6812,16 @@
         <v>43689</v>
       </c>
       <c r="B320" t="n">
-        <v>131.1902313232422</v>
+        <v>131.1902465820312</v>
       </c>
       <c r="C320" t="n">
-        <v>131.487448286707</v>
+        <v>131.4874635800655</v>
       </c>
       <c r="D320" t="n">
-        <v>128.8422460343276</v>
+        <v>128.8422610200215</v>
       </c>
       <c r="E320" t="n">
-        <v>131.487448286707</v>
+        <v>131.4874635800655</v>
       </c>
       <c r="F320" t="n">
         <v>372500</v>
@@ -6832,16 +6832,16 @@
         <v>43690</v>
       </c>
       <c r="B321" t="n">
-        <v>131.0713348388672</v>
+        <v>131.0713806152344</v>
       </c>
       <c r="C321" t="n">
-        <v>133.7759771356097</v>
+        <v>133.7760238565671</v>
       </c>
       <c r="D321" t="n">
-        <v>128.8125103752236</v>
+        <v>128.8125553627015</v>
       </c>
       <c r="E321" t="n">
-        <v>133.6570964113382</v>
+        <v>133.6571430907768</v>
       </c>
       <c r="F321" t="n">
         <v>614133</v>
@@ -6852,16 +6852,16 @@
         <v>43691</v>
       </c>
       <c r="B322" t="n">
-        <v>137.0156555175781</v>
+        <v>137.0156707763672</v>
       </c>
       <c r="C322" t="n">
-        <v>140.9685919991994</v>
+        <v>140.9686076982084</v>
       </c>
       <c r="D322" t="n">
-        <v>135.2323685137598</v>
+        <v>135.2323835739525</v>
       </c>
       <c r="E322" t="n">
-        <v>139.6905784647628</v>
+        <v>139.6905940214455</v>
       </c>
       <c r="F322" t="n">
         <v>1453733</v>
@@ -6952,16 +6952,16 @@
         <v>43698</v>
       </c>
       <c r="B327" t="n">
-        <v>148.5772399902344</v>
+        <v>148.5772857666016</v>
       </c>
       <c r="C327" t="n">
-        <v>148.7258409035746</v>
+        <v>148.7258867257254</v>
       </c>
       <c r="D327" t="n">
-        <v>143.4057165668508</v>
+        <v>143.4057607498814</v>
       </c>
       <c r="E327" t="n">
-        <v>146.8236736274112</v>
+        <v>146.8237188635079</v>
       </c>
       <c r="F327" t="n">
         <v>558733</v>
@@ -6972,16 +6972,16 @@
         <v>43699</v>
       </c>
       <c r="B328" t="n">
-        <v>148.5475463867188</v>
+        <v>148.5475158691406</v>
       </c>
       <c r="C328" t="n">
-        <v>151.3116296889876</v>
+        <v>151.3115986035568</v>
       </c>
       <c r="D328" t="n">
-        <v>146.8236998981212</v>
+        <v>146.8236697346897</v>
       </c>
       <c r="E328" t="n">
-        <v>148.5772665747045</v>
+        <v>148.5772360510207</v>
       </c>
       <c r="F328" t="n">
         <v>509000</v>
@@ -7012,16 +7012,16 @@
         <v>43703</v>
       </c>
       <c r="B330" t="n">
-        <v>143.5543365478516</v>
+        <v>143.5543212890625</v>
       </c>
       <c r="C330" t="n">
-        <v>146.2292742799288</v>
+        <v>146.2292587368132</v>
       </c>
       <c r="D330" t="n">
-        <v>141.2063511027138</v>
+        <v>141.2063360934986</v>
       </c>
       <c r="E330" t="n">
-        <v>143.3165750549265</v>
+        <v>143.3165598214097</v>
       </c>
       <c r="F330" t="n">
         <v>278200</v>
@@ -7072,16 +7072,16 @@
         <v>43706</v>
       </c>
       <c r="B333" t="n">
-        <v>150.0930633544922</v>
+        <v>150.0930328369141</v>
       </c>
       <c r="C333" t="n">
-        <v>151.103595142534</v>
+        <v>151.1035644194901</v>
       </c>
       <c r="D333" t="n">
-        <v>145.9617907514584</v>
+        <v>145.9617610738686</v>
       </c>
       <c r="E333" t="n">
-        <v>146.5264894655712</v>
+        <v>146.5264596731645</v>
       </c>
       <c r="F333" t="n">
         <v>1067466</v>
@@ -7092,16 +7092,16 @@
         <v>43707</v>
       </c>
       <c r="B334" t="n">
-        <v>153.6893310546875</v>
+        <v>153.6893463134766</v>
       </c>
       <c r="C334" t="n">
-        <v>153.6893310546875</v>
+        <v>153.6893463134766</v>
       </c>
       <c r="D334" t="n">
-        <v>149.8849811870925</v>
+        <v>149.884996068173</v>
       </c>
       <c r="E334" t="n">
-        <v>150.9846733543434</v>
+        <v>150.984688344605</v>
       </c>
       <c r="F334" t="n">
         <v>973933</v>
@@ -7132,16 +7132,16 @@
         <v>43711</v>
       </c>
       <c r="B336" t="n">
-        <v>154.5512847900391</v>
+        <v>154.5512542724609</v>
       </c>
       <c r="C336" t="n">
-        <v>157.1073270833093</v>
+        <v>157.107296061017</v>
       </c>
       <c r="D336" t="n">
-        <v>153.2138157017523</v>
+        <v>153.2137854482698</v>
       </c>
       <c r="E336" t="n">
-        <v>154.2540677574102</v>
+        <v>154.2540372985203</v>
       </c>
       <c r="F336" t="n">
         <v>578066</v>
@@ -7152,16 +7152,16 @@
         <v>43712</v>
       </c>
       <c r="B337" t="n">
-        <v>149.4689025878906</v>
+        <v>149.4689178466797</v>
       </c>
       <c r="C337" t="n">
-        <v>156.185937186464</v>
+        <v>156.185953130973</v>
       </c>
       <c r="D337" t="n">
-        <v>147.9828327188773</v>
+        <v>147.9828478259584</v>
       </c>
       <c r="E337" t="n">
-        <v>155.9778958703694</v>
+        <v>155.9779117936402</v>
       </c>
       <c r="F337" t="n">
         <v>865766</v>
@@ -7192,16 +7192,16 @@
         <v>43714</v>
       </c>
       <c r="B339" t="n">
-        <v>146.2292785644531</v>
+        <v>146.2292633056641</v>
       </c>
       <c r="C339" t="n">
-        <v>150.5091518504265</v>
+        <v>150.5091361450396</v>
       </c>
       <c r="D339" t="n">
-        <v>145.4862436431238</v>
+        <v>145.4862284618692</v>
       </c>
       <c r="E339" t="n">
-        <v>150.0633339210457</v>
+        <v>150.0633182621792</v>
       </c>
       <c r="F339" t="n">
         <v>678033</v>
@@ -7212,16 +7212,16 @@
         <v>43717</v>
       </c>
       <c r="B340" t="n">
-        <v>142.9004821777344</v>
+        <v>142.9004974365234</v>
       </c>
       <c r="C340" t="n">
-        <v>146.734537552183</v>
+        <v>146.7345532203692</v>
       </c>
       <c r="D340" t="n">
-        <v>139.7202860481167</v>
+        <v>139.7203009673272</v>
       </c>
       <c r="E340" t="n">
-        <v>146.734537552183</v>
+        <v>146.7345532203692</v>
       </c>
       <c r="F340" t="n">
         <v>1841333</v>
@@ -7232,16 +7232,16 @@
         <v>43718</v>
       </c>
       <c r="B341" t="n">
-        <v>146.4075927734375</v>
+        <v>146.4075775146484</v>
       </c>
       <c r="C341" t="n">
-        <v>146.4967533316851</v>
+        <v>146.4967380636036</v>
       </c>
       <c r="D341" t="n">
-        <v>140.6416348000909</v>
+        <v>140.6416201422374</v>
       </c>
       <c r="E341" t="n">
-        <v>142.0385440143037</v>
+        <v>142.0385292108626</v>
       </c>
       <c r="F341" t="n">
         <v>1022600</v>
@@ -7252,16 +7252,16 @@
         <v>43719</v>
       </c>
       <c r="B342" t="n">
-        <v>152.5302124023438</v>
+        <v>152.5301971435547</v>
       </c>
       <c r="C342" t="n">
-        <v>152.5302124023438</v>
+        <v>152.5301971435547</v>
       </c>
       <c r="D342" t="n">
-        <v>146.7048284321351</v>
+        <v>146.7048137561047</v>
       </c>
       <c r="E342" t="n">
-        <v>148.5772759791817</v>
+        <v>148.5772611158358</v>
       </c>
       <c r="F342" t="n">
         <v>523500</v>
@@ -7272,16 +7272,16 @@
         <v>43720</v>
       </c>
       <c r="B343" t="n">
-        <v>148.3691864013672</v>
+        <v>148.3692016601562</v>
       </c>
       <c r="C343" t="n">
-        <v>154.4918011372027</v>
+        <v>154.4918170256621</v>
       </c>
       <c r="D343" t="n">
-        <v>148.3394662181369</v>
+        <v>148.3394814738694</v>
       </c>
       <c r="E343" t="n">
-        <v>153.9568076048933</v>
+        <v>153.9568234383322</v>
       </c>
       <c r="F343" t="n">
         <v>700866</v>
@@ -7292,16 +7292,16 @@
         <v>43721</v>
       </c>
       <c r="B344" t="n">
-        <v>149.2013854980469</v>
+        <v>149.2014007568359</v>
       </c>
       <c r="C344" t="n">
-        <v>150.4793986306752</v>
+        <v>150.4794140201663</v>
       </c>
       <c r="D344" t="n">
-        <v>145.6348126117433</v>
+        <v>145.6348275057798</v>
       </c>
       <c r="E344" t="n">
-        <v>148.606951644636</v>
+        <v>148.6069668426325</v>
       </c>
       <c r="F344" t="n">
         <v>622000</v>
@@ -7312,16 +7312,16 @@
         <v>43724</v>
       </c>
       <c r="B345" t="n">
-        <v>149.9444274902344</v>
+        <v>149.9444427490234</v>
       </c>
       <c r="C345" t="n">
-        <v>151.2521608669158</v>
+        <v>151.2521762587837</v>
       </c>
       <c r="D345" t="n">
-        <v>146.5264553438454</v>
+        <v>146.5264702548115</v>
       </c>
       <c r="E345" t="n">
-        <v>149.4985945201269</v>
+        <v>149.4986097335467</v>
       </c>
       <c r="F345" t="n">
         <v>541366</v>
@@ -7372,16 +7372,16 @@
         <v>43727</v>
       </c>
       <c r="B348" t="n">
-        <v>153.0354614257812</v>
+        <v>153.0354461669922</v>
       </c>
       <c r="C348" t="n">
-        <v>155.3834467528314</v>
+        <v>155.3834312599305</v>
       </c>
       <c r="D348" t="n">
-        <v>151.5493917014036</v>
+        <v>151.5493765907869</v>
       </c>
       <c r="E348" t="n">
-        <v>154.4026504096753</v>
+        <v>154.4026350145672</v>
       </c>
       <c r="F348" t="n">
         <v>446666</v>
@@ -7472,16 +7472,16 @@
         <v>43734</v>
       </c>
       <c r="B353" t="n">
-        <v>157.3748016357422</v>
+        <v>157.3747863769531</v>
       </c>
       <c r="C353" t="n">
-        <v>159.4255701479717</v>
+        <v>159.4255546903437</v>
       </c>
       <c r="D353" t="n">
-        <v>154.9970808285488</v>
+        <v>154.9970658002995</v>
       </c>
       <c r="E353" t="n">
-        <v>155.4726189431538</v>
+        <v>155.4726038687971</v>
       </c>
       <c r="F353" t="n">
         <v>815966</v>
@@ -7492,16 +7492,16 @@
         <v>43735</v>
       </c>
       <c r="B354" t="n">
-        <v>158.1178131103516</v>
+        <v>158.1178283691406</v>
       </c>
       <c r="C354" t="n">
-        <v>158.8013924350218</v>
+        <v>158.8014077597781</v>
       </c>
       <c r="D354" t="n">
-        <v>156.2453508827271</v>
+        <v>156.2453659608186</v>
       </c>
       <c r="E354" t="n">
-        <v>157.3747783027223</v>
+        <v>157.3747934898065</v>
       </c>
       <c r="F354" t="n">
         <v>505200</v>
@@ -7532,16 +7532,16 @@
         <v>43739</v>
       </c>
       <c r="B356" t="n">
-        <v>158.1178131103516</v>
+        <v>158.1178283691406</v>
       </c>
       <c r="C356" t="n">
-        <v>159.4849868767739</v>
+        <v>159.4850022674988</v>
       </c>
       <c r="D356" t="n">
-        <v>156.8992251415405</v>
+        <v>156.8992402827326</v>
       </c>
       <c r="E356" t="n">
-        <v>159.3066657791421</v>
+        <v>159.3066811526586</v>
       </c>
       <c r="F356" t="n">
         <v>759100</v>
@@ -7552,16 +7552,16 @@
         <v>43740</v>
       </c>
       <c r="B357" t="n">
-        <v>156.0373229980469</v>
+        <v>156.0373382568359</v>
       </c>
       <c r="C357" t="n">
-        <v>159.0689028547042</v>
+        <v>159.0689184099495</v>
       </c>
       <c r="D357" t="n">
-        <v>154.4323725132479</v>
+        <v>154.4323876150899</v>
       </c>
       <c r="E357" t="n">
-        <v>156.5723014539522</v>
+        <v>156.5723167650564</v>
       </c>
       <c r="F357" t="n">
         <v>1285800</v>
@@ -7572,16 +7572,16 @@
         <v>43741</v>
       </c>
       <c r="B358" t="n">
-        <v>160.4955444335938</v>
+        <v>160.4955291748047</v>
       </c>
       <c r="C358" t="n">
-        <v>160.4955444335938</v>
+        <v>160.4955291748047</v>
       </c>
       <c r="D358" t="n">
-        <v>154.2243278277865</v>
+        <v>154.2243131652207</v>
       </c>
       <c r="E358" t="n">
-        <v>155.7401178714037</v>
+        <v>155.7401030647272</v>
       </c>
       <c r="F358" t="n">
         <v>638566</v>
@@ -7592,16 +7592,16 @@
         <v>43742</v>
       </c>
       <c r="B359" t="n">
-        <v>160.4955444335938</v>
+        <v>160.4955291748047</v>
       </c>
       <c r="C359" t="n">
-        <v>161.624956919369</v>
+        <v>161.6249415532033</v>
       </c>
       <c r="D359" t="n">
-        <v>158.2961598375444</v>
+        <v>158.2961447878574</v>
       </c>
       <c r="E359" t="n">
-        <v>160.3766636825914</v>
+        <v>160.3766484351047</v>
       </c>
       <c r="F359" t="n">
         <v>752266</v>
@@ -7612,16 +7612,16 @@
         <v>43745</v>
       </c>
       <c r="B360" t="n">
-        <v>161.4168701171875</v>
+        <v>161.4168853759766</v>
       </c>
       <c r="C360" t="n">
-        <v>163.7054299629767</v>
+        <v>163.7054454381041</v>
       </c>
       <c r="D360" t="n">
-        <v>159.6335987193404</v>
+        <v>159.6336138095562</v>
       </c>
       <c r="E360" t="n">
-        <v>161.6249265093798</v>
+        <v>161.6249417878365</v>
       </c>
       <c r="F360" t="n">
         <v>812666</v>
@@ -7732,16 +7732,16 @@
         <v>43753</v>
       </c>
       <c r="B366" t="n">
-        <v>167.3314666748047</v>
+        <v>167.3314514160156</v>
       </c>
       <c r="C366" t="n">
-        <v>169.2039141662959</v>
+        <v>169.2038987367602</v>
       </c>
       <c r="D366" t="n">
-        <v>167.1828657298788</v>
+        <v>167.1828504846405</v>
       </c>
       <c r="E366" t="n">
-        <v>167.3017464858195</v>
+        <v>167.3017312297406</v>
       </c>
       <c r="F366" t="n">
         <v>550533</v>
@@ -7752,16 +7752,16 @@
         <v>43754</v>
       </c>
       <c r="B367" t="n">
-        <v>170.7791290283203</v>
+        <v>170.7791442871094</v>
       </c>
       <c r="C367" t="n">
-        <v>172.8001771009563</v>
+        <v>172.8001925403221</v>
       </c>
       <c r="D367" t="n">
-        <v>167.301716372126</v>
+        <v>167.3017313202149</v>
       </c>
       <c r="E367" t="n">
-        <v>168.7580658386021</v>
+        <v>168.7580809168131</v>
       </c>
       <c r="F367" t="n">
         <v>599666</v>
@@ -7772,16 +7772,16 @@
         <v>43755</v>
       </c>
       <c r="B368" t="n">
-        <v>169.7686157226562</v>
+        <v>169.7686309814453</v>
       </c>
       <c r="C368" t="n">
-        <v>172.9785319548521</v>
+        <v>172.9785475021482</v>
       </c>
       <c r="D368" t="n">
-        <v>168.8769647662821</v>
+        <v>168.8769799449297</v>
       </c>
       <c r="E368" t="n">
-        <v>171.2546855328626</v>
+        <v>171.2547009252195</v>
       </c>
       <c r="F368" t="n">
         <v>460533</v>
@@ -7792,16 +7792,16 @@
         <v>43756</v>
       </c>
       <c r="B369" t="n">
-        <v>170.9574584960938</v>
+        <v>170.9574737548828</v>
       </c>
       <c r="C369" t="n">
-        <v>171.0466190513639</v>
+        <v>171.046634318111</v>
       </c>
       <c r="D369" t="n">
-        <v>169.1444516201863</v>
+        <v>169.1444667171556</v>
       </c>
       <c r="E369" t="n">
-        <v>170.3333043750369</v>
+        <v>170.3333195781172</v>
       </c>
       <c r="F369" t="n">
         <v>657533</v>
@@ -7832,16 +7832,16 @@
         <v>43760</v>
       </c>
       <c r="B371" t="n">
-        <v>166.8856506347656</v>
+        <v>166.8856201171875</v>
       </c>
       <c r="C371" t="n">
-        <v>169.8875106933376</v>
+        <v>169.8874796268238</v>
       </c>
       <c r="D371" t="n">
-        <v>165.3401403214911</v>
+        <v>165.3401100865331</v>
       </c>
       <c r="E371" t="n">
-        <v>169.6497491787324</v>
+        <v>169.6497181556968</v>
       </c>
       <c r="F371" t="n">
         <v>630100</v>
@@ -7912,16 +7912,16 @@
         <v>43766</v>
       </c>
       <c r="B375" t="n">
-        <v>170.0063781738281</v>
+        <v>170.0063934326172</v>
       </c>
       <c r="C375" t="n">
-        <v>170.5710767937866</v>
+        <v>170.5710921032597</v>
       </c>
       <c r="D375" t="n">
-        <v>167.6880979740227</v>
+        <v>167.6881130247363</v>
       </c>
       <c r="E375" t="n">
-        <v>169.3525038837014</v>
+        <v>169.3525190838025</v>
       </c>
       <c r="F375" t="n">
         <v>598700</v>
@@ -7972,16 +7972,16 @@
         <v>43769</v>
       </c>
       <c r="B378" t="n">
-        <v>167.3314666748047</v>
+        <v>167.3314514160156</v>
       </c>
       <c r="C378" t="n">
-        <v>168.5203347025518</v>
+        <v>168.520319335351</v>
       </c>
       <c r="D378" t="n">
-        <v>166.1426137641425</v>
+        <v>166.1425986137638</v>
       </c>
       <c r="E378" t="n">
-        <v>167.5989634927563</v>
+        <v>167.5989482095744</v>
       </c>
       <c r="F378" t="n">
         <v>595400</v>
@@ -7992,16 +7992,16 @@
         <v>43770</v>
       </c>
       <c r="B379" t="n">
-        <v>168.6689300537109</v>
+        <v>168.6689453125</v>
       </c>
       <c r="C379" t="n">
-        <v>168.8769713697077</v>
+        <v>168.8769866473174</v>
       </c>
       <c r="D379" t="n">
-        <v>166.9748037523151</v>
+        <v>166.9748188578435</v>
       </c>
       <c r="E379" t="n">
-        <v>167.331461125394</v>
+        <v>167.3314762631877</v>
       </c>
       <c r="F379" t="n">
         <v>1063666</v>
@@ -8012,16 +8012,16 @@
         <v>43773</v>
       </c>
       <c r="B380" t="n">
-        <v>165.9939880371094</v>
+        <v>165.9940032958984</v>
       </c>
       <c r="C380" t="n">
-        <v>168.5203095432768</v>
+        <v>168.5203250342948</v>
       </c>
       <c r="D380" t="n">
-        <v>163.9729247853423</v>
+        <v>163.9729398583477</v>
       </c>
       <c r="E380" t="n">
-        <v>168.5203095432768</v>
+        <v>168.5203250342948</v>
       </c>
       <c r="F380" t="n">
         <v>963600</v>
@@ -8032,16 +8032,16 @@
         <v>43774</v>
       </c>
       <c r="B381" t="n">
-        <v>161.5357513427734</v>
+        <v>161.5357971191406</v>
       </c>
       <c r="C381" t="n">
-        <v>166.8855952862789</v>
+        <v>166.885642578697</v>
       </c>
       <c r="D381" t="n">
-        <v>160.971037698706</v>
+        <v>160.9710833150434</v>
       </c>
       <c r="E381" t="n">
-        <v>166.8855952862789</v>
+        <v>166.885642578697</v>
       </c>
       <c r="F381" t="n">
         <v>956400</v>
@@ -8112,16 +8112,16 @@
         <v>43780</v>
       </c>
       <c r="B385" t="n">
-        <v>170.8385620117188</v>
+        <v>170.8385772705078</v>
       </c>
       <c r="C385" t="n">
-        <v>170.8385620117188</v>
+        <v>170.8385772705078</v>
       </c>
       <c r="D385" t="n">
-        <v>164.9834442152444</v>
+        <v>164.9834589510719</v>
       </c>
       <c r="E385" t="n">
-        <v>165.9642555840758</v>
+        <v>165.9642704075064</v>
       </c>
       <c r="F385" t="n">
         <v>906700</v>
@@ -8152,16 +8152,16 @@
         <v>43782</v>
       </c>
       <c r="B387" t="n">
-        <v>167.8961639404297</v>
+        <v>167.8961791992188</v>
       </c>
       <c r="C387" t="n">
-        <v>170.2738695272456</v>
+        <v>170.273885002126</v>
       </c>
       <c r="D387" t="n">
-        <v>164.9834647704759</v>
+        <v>164.9834797645522</v>
       </c>
       <c r="E387" t="n">
-        <v>168.2528212901604</v>
+        <v>168.2528365813633</v>
       </c>
       <c r="F387" t="n">
         <v>1028933</v>
@@ -8172,16 +8172,16 @@
         <v>43783</v>
       </c>
       <c r="B388" t="n">
-        <v>161.5060882568359</v>
+        <v>161.5060729980469</v>
       </c>
       <c r="C388" t="n">
-        <v>167.4800883151972</v>
+        <v>167.4800724919959</v>
       </c>
       <c r="D388" t="n">
-        <v>160.9710946031133</v>
+        <v>160.9710793948695</v>
       </c>
       <c r="E388" t="n">
-        <v>165.1023672975915</v>
+        <v>165.1023516990328</v>
       </c>
       <c r="F388" t="n">
         <v>1805133</v>
@@ -8192,16 +8192,16 @@
         <v>43787</v>
       </c>
       <c r="B389" t="n">
-        <v>161.6249389648438</v>
+        <v>161.6249694824219</v>
       </c>
       <c r="C389" t="n">
-        <v>163.0218481022793</v>
+        <v>163.021878883618</v>
       </c>
       <c r="D389" t="n">
-        <v>158.8311206899726</v>
+        <v>158.8311506800296</v>
       </c>
       <c r="E389" t="n">
-        <v>161.5952187803947</v>
+        <v>161.5952492923612</v>
       </c>
       <c r="F389" t="n">
         <v>1204133</v>
@@ -8212,16 +8212,16 @@
         <v>43788</v>
       </c>
       <c r="B390" t="n">
-        <v>159.5741577148438</v>
+        <v>159.5741882324219</v>
       </c>
       <c r="C390" t="n">
-        <v>162.7840737329255</v>
+        <v>162.7841048643803</v>
       </c>
       <c r="D390" t="n">
-        <v>158.5339210107543</v>
+        <v>158.5339513293935</v>
       </c>
       <c r="E390" t="n">
-        <v>162.6354728086507</v>
+        <v>162.6355039116865</v>
       </c>
       <c r="F390" t="n">
         <v>1296633</v>
@@ -8252,16 +8252,16 @@
         <v>43791</v>
       </c>
       <c r="B392" t="n">
-        <v>169.9766693115234</v>
+        <v>169.9766387939453</v>
       </c>
       <c r="C392" t="n">
-        <v>169.9766693115234</v>
+        <v>169.9766387939453</v>
       </c>
       <c r="D392" t="n">
-        <v>164.2404460811953</v>
+        <v>164.2404165934975</v>
       </c>
       <c r="E392" t="n">
-        <v>165.1023617959225</v>
+        <v>165.1023321534766</v>
       </c>
       <c r="F392" t="n">
         <v>1134300</v>
@@ -8272,16 +8272,16 @@
         <v>43794</v>
       </c>
       <c r="B393" t="n">
-        <v>171.7599487304688</v>
+        <v>171.7599334716797</v>
       </c>
       <c r="C393" t="n">
-        <v>172.2652221552997</v>
+        <v>172.2652068516232</v>
       </c>
       <c r="D393" t="n">
-        <v>167.9556135358149</v>
+        <v>167.9555986149949</v>
       </c>
       <c r="E393" t="n">
-        <v>169.2039067698807</v>
+        <v>169.203891738165</v>
       </c>
       <c r="F393" t="n">
         <v>1287433</v>
@@ -8292,16 +8292,16 @@
         <v>43795</v>
       </c>
       <c r="B394" t="n">
-        <v>169.4119567871094</v>
+        <v>169.4119720458984</v>
       </c>
       <c r="C394" t="n">
-        <v>172.5029771261092</v>
+        <v>172.5029926633038</v>
       </c>
       <c r="D394" t="n">
-        <v>167.4800690752345</v>
+        <v>167.4800841600201</v>
       </c>
       <c r="E394" t="n">
-        <v>170.9574669566093</v>
+        <v>170.9574823546011</v>
       </c>
       <c r="F394" t="n">
         <v>9961800</v>
@@ -8332,16 +8332,16 @@
         <v>43797</v>
       </c>
       <c r="B396" t="n">
-        <v>163.6162719726562</v>
+        <v>163.6162872314453</v>
       </c>
       <c r="C396" t="n">
-        <v>168.490578895245</v>
+        <v>168.49059460861</v>
       </c>
       <c r="D396" t="n">
-        <v>163.2893348165146</v>
+        <v>163.2893500448137</v>
       </c>
       <c r="E396" t="n">
-        <v>166.4695307047406</v>
+        <v>166.4695462296235</v>
       </c>
       <c r="F396" t="n">
         <v>574533</v>
@@ -8352,16 +8352,16 @@
         <v>43798</v>
       </c>
       <c r="B397" t="n">
-        <v>165.5481872558594</v>
+        <v>165.5481567382812</v>
       </c>
       <c r="C397" t="n">
-        <v>166.0831657500806</v>
+        <v>166.0831351338832</v>
       </c>
       <c r="D397" t="n">
-        <v>161.08997770804</v>
+        <v>161.0899480122997</v>
       </c>
       <c r="E397" t="n">
-        <v>163.6460045457557</v>
+        <v>163.6459743788308</v>
       </c>
       <c r="F397" t="n">
         <v>703133</v>
@@ -8372,16 +8372,16 @@
         <v>43801</v>
       </c>
       <c r="B398" t="n">
-        <v>167.1828308105469</v>
+        <v>167.182861328125</v>
       </c>
       <c r="C398" t="n">
-        <v>167.3017115416571</v>
+        <v>167.3017420809357</v>
       </c>
       <c r="D398" t="n">
-        <v>162.9623985682345</v>
+        <v>162.9624283154143</v>
       </c>
       <c r="E398" t="n">
-        <v>165.6373208377869</v>
+        <v>165.6373510732474</v>
       </c>
       <c r="F398" t="n">
         <v>805633</v>
@@ -8392,16 +8392,16 @@
         <v>43802</v>
       </c>
       <c r="B399" t="n">
-        <v>169.8280639648438</v>
+        <v>169.8280487060547</v>
       </c>
       <c r="C399" t="n">
-        <v>170.4522181515157</v>
+        <v>170.4522028366473</v>
       </c>
       <c r="D399" t="n">
-        <v>165.8453924561812</v>
+        <v>165.845377555229</v>
       </c>
       <c r="E399" t="n">
-        <v>167.3314623352405</v>
+        <v>167.3314473007672</v>
       </c>
       <c r="F399" t="n">
         <v>915133</v>
@@ -8412,16 +8412,16 @@
         <v>43803</v>
       </c>
       <c r="B400" t="n">
-        <v>172.4435272216797</v>
+        <v>172.4435577392578</v>
       </c>
       <c r="C400" t="n">
-        <v>173.7215556414925</v>
+        <v>173.7215863852452</v>
       </c>
       <c r="D400" t="n">
-        <v>170.8980171376033</v>
+        <v>170.8980473816703</v>
       </c>
       <c r="E400" t="n">
-        <v>170.8980171376033</v>
+        <v>170.8980473816703</v>
       </c>
       <c r="F400" t="n">
         <v>662400</v>
@@ -8432,16 +8432,16 @@
         <v>43804</v>
       </c>
       <c r="B401" t="n">
-        <v>172.3543701171875</v>
+        <v>172.3543853759766</v>
       </c>
       <c r="C401" t="n">
-        <v>174.7617958462494</v>
+        <v>174.7618113181715</v>
       </c>
       <c r="D401" t="n">
-        <v>169.1147338425086</v>
+        <v>169.1147488144879</v>
       </c>
       <c r="E401" t="n">
-        <v>172.7110274604281</v>
+        <v>172.7110427507926</v>
       </c>
       <c r="F401" t="n">
         <v>632400</v>
@@ -8452,16 +8452,16 @@
         <v>43805</v>
       </c>
       <c r="B402" t="n">
-        <v>171.7302398681641</v>
+        <v>171.7302093505859</v>
       </c>
       <c r="C402" t="n">
-        <v>173.4243662634142</v>
+        <v>173.4243354447788</v>
       </c>
       <c r="D402" t="n">
-        <v>167.9556246122654</v>
+        <v>167.9555947654609</v>
       </c>
       <c r="E402" t="n">
-        <v>173.4243662634142</v>
+        <v>173.4243354447788</v>
       </c>
       <c r="F402" t="n">
         <v>837700</v>
@@ -8512,16 +8512,16 @@
         <v>43810</v>
       </c>
       <c r="B405" t="n">
-        <v>167.0936737060547</v>
+        <v>167.0936889648438</v>
       </c>
       <c r="C405" t="n">
-        <v>167.0936737060547</v>
+        <v>167.0936889648438</v>
       </c>
       <c r="D405" t="n">
-        <v>161.9815905238091</v>
+        <v>161.981605315769</v>
       </c>
       <c r="E405" t="n">
-        <v>162.7840657095058</v>
+        <v>162.7840805747468</v>
       </c>
       <c r="F405" t="n">
         <v>789933</v>
@@ -8532,16 +8532,16 @@
         <v>43811</v>
       </c>
       <c r="B406" t="n">
-        <v>170.0063781738281</v>
+        <v>170.0063934326172</v>
       </c>
       <c r="C406" t="n">
-        <v>170.2144194643613</v>
+        <v>170.214434741823</v>
       </c>
       <c r="D406" t="n">
-        <v>167.1233993540642</v>
+        <v>167.1234143540938</v>
       </c>
       <c r="E406" t="n">
-        <v>169.0850071073618</v>
+        <v>169.085022283454</v>
       </c>
       <c r="F406" t="n">
         <v>578333</v>
@@ -8552,16 +8552,16 @@
         <v>43812</v>
       </c>
       <c r="B407" t="n">
-        <v>166.9747924804688</v>
+        <v>166.9748077392578</v>
       </c>
       <c r="C407" t="n">
-        <v>171.3141210404826</v>
+        <v>171.3141366958159</v>
       </c>
       <c r="D407" t="n">
-        <v>166.2020374104777</v>
+        <v>166.2020525986495</v>
       </c>
       <c r="E407" t="n">
-        <v>170.8088627615141</v>
+        <v>170.808878370675</v>
       </c>
       <c r="F407" t="n">
         <v>591766</v>
@@ -8592,16 +8592,16 @@
         <v>43816</v>
       </c>
       <c r="B409" t="n">
-        <v>173.1568603515625</v>
+        <v>173.1568450927734</v>
       </c>
       <c r="C409" t="n">
-        <v>175.2373642201033</v>
+        <v>175.2373487779778</v>
       </c>
       <c r="D409" t="n">
-        <v>171.4032936690544</v>
+        <v>171.4032785647917</v>
       </c>
       <c r="E409" t="n">
-        <v>173.4243571614228</v>
+        <v>173.4243418790616</v>
       </c>
       <c r="F409" t="n">
         <v>614666</v>
@@ -8612,16 +8612,16 @@
         <v>43817</v>
       </c>
       <c r="B410" t="n">
-        <v>180.4683074951172</v>
+        <v>180.4683380126953</v>
       </c>
       <c r="C410" t="n">
-        <v>180.4683074951172</v>
+        <v>180.4683380126953</v>
       </c>
       <c r="D410" t="n">
-        <v>171.6410498735219</v>
+        <v>171.6410788983919</v>
       </c>
       <c r="E410" t="n">
-        <v>171.6410498735219</v>
+        <v>171.6410788983919</v>
       </c>
       <c r="F410" t="n">
         <v>804400</v>
@@ -8632,16 +8632,16 @@
         <v>43818</v>
       </c>
       <c r="B411" t="n">
-        <v>184.7481994628906</v>
+        <v>184.7481842041016</v>
       </c>
       <c r="C411" t="n">
-        <v>185.7587311933661</v>
+        <v>185.7587158511149</v>
       </c>
       <c r="D411" t="n">
-        <v>178.922815932284</v>
+        <v>178.922801154627</v>
       </c>
       <c r="E411" t="n">
-        <v>181.3005216447253</v>
+        <v>181.3005066706881</v>
       </c>
       <c r="F411" t="n">
         <v>904966</v>
@@ -8652,16 +8652,16 @@
         <v>43819</v>
       </c>
       <c r="B412" t="n">
-        <v>190.068359375</v>
+        <v>190.0683288574219</v>
       </c>
       <c r="C412" t="n">
-        <v>190.068359375</v>
+        <v>190.0683288574219</v>
       </c>
       <c r="D412" t="n">
-        <v>182.9352112690155</v>
+        <v>182.9351818967433</v>
       </c>
       <c r="E412" t="n">
-        <v>185.8479108927782</v>
+        <v>185.8478810528398</v>
       </c>
       <c r="F412" t="n">
         <v>984100</v>
@@ -8672,16 +8672,16 @@
         <v>43822</v>
       </c>
       <c r="B413" t="n">
-        <v>187.8392181396484</v>
+        <v>187.8392333984375</v>
       </c>
       <c r="C413" t="n">
-        <v>190.4547002349917</v>
+        <v>190.4547157062448</v>
       </c>
       <c r="D413" t="n">
-        <v>186.1748121969302</v>
+        <v>186.1748273205142</v>
       </c>
       <c r="E413" t="n">
-        <v>190.216923638294</v>
+        <v>190.2169390902317</v>
       </c>
       <c r="F413" t="n">
         <v>629966</v>
@@ -8692,16 +8692,16 @@
         <v>43825</v>
       </c>
       <c r="B414" t="n">
-        <v>191.4057769775391</v>
+        <v>191.4057922363281</v>
       </c>
       <c r="C414" t="n">
-        <v>191.6435535749696</v>
+        <v>191.6435688527141</v>
       </c>
       <c r="D414" t="n">
-        <v>187.3636655237174</v>
+        <v>187.363680460271</v>
       </c>
       <c r="E414" t="n">
-        <v>188.7902948741348</v>
+        <v>188.7903099244187</v>
       </c>
       <c r="F414" t="n">
         <v>400133</v>
@@ -8732,16 +8732,16 @@
         <v>43829</v>
       </c>
       <c r="B416" t="n">
-        <v>189.9197235107422</v>
+        <v>189.9197082519531</v>
       </c>
       <c r="C416" t="n">
-        <v>193.3376811370011</v>
+        <v>193.3376656036019</v>
       </c>
       <c r="D416" t="n">
-        <v>188.0472761073423</v>
+        <v>188.047260998992</v>
       </c>
       <c r="E416" t="n">
-        <v>190.6627584345848</v>
+        <v>190.6627431160977</v>
       </c>
       <c r="F416" t="n">
         <v>1069533</v>
@@ -8792,16 +8792,16 @@
         <v>43836</v>
       </c>
       <c r="B419" t="n">
-        <v>199.4744720458984</v>
+        <v>199.4744415283203</v>
       </c>
       <c r="C419" t="n">
-        <v>205.1941645753199</v>
+        <v>205.1941331826866</v>
       </c>
       <c r="D419" t="n">
-        <v>196.346503119601</v>
+        <v>196.3464730805705</v>
       </c>
       <c r="E419" t="n">
-        <v>203.4663336878787</v>
+        <v>203.4663025595861</v>
       </c>
       <c r="F419" t="n">
         <v>735666</v>
@@ -8812,16 +8812,16 @@
         <v>43837</v>
       </c>
       <c r="B420" t="n">
-        <v>193.9930572509766</v>
+        <v>193.9930877685547</v>
       </c>
       <c r="C420" t="n">
-        <v>200.1894011243377</v>
+        <v>200.1894326166796</v>
       </c>
       <c r="D420" t="n">
-        <v>193.9334794981979</v>
+        <v>193.9335100064037</v>
       </c>
       <c r="E420" t="n">
-        <v>198.401992780866</v>
+        <v>198.4020239920258</v>
       </c>
       <c r="F420" t="n">
         <v>612400</v>
@@ -8852,16 +8852,16 @@
         <v>43839</v>
       </c>
       <c r="B422" t="n">
-        <v>188.8691558837891</v>
+        <v>188.8691711425781</v>
       </c>
       <c r="C422" t="n">
-        <v>191.5204719115027</v>
+        <v>191.5204873844923</v>
       </c>
       <c r="D422" t="n">
-        <v>187.2009182199783</v>
+        <v>187.20093334399</v>
       </c>
       <c r="E422" t="n">
-        <v>190.0011786276671</v>
+        <v>190.0011939779125</v>
       </c>
       <c r="F422" t="n">
         <v>950500</v>
@@ -8872,16 +8872,16 @@
         <v>43840</v>
       </c>
       <c r="B423" t="n">
-        <v>184.8475036621094</v>
+        <v>184.8475189208984</v>
       </c>
       <c r="C423" t="n">
-        <v>190.6267884348786</v>
+        <v>190.6268041707359</v>
       </c>
       <c r="D423" t="n">
-        <v>182.3153581162909</v>
+        <v>182.3153731660564</v>
       </c>
       <c r="E423" t="n">
-        <v>190.6267884348786</v>
+        <v>190.6268041707359</v>
       </c>
       <c r="F423" t="n">
         <v>656333</v>
@@ -8892,16 +8892,16 @@
         <v>43843</v>
       </c>
       <c r="B424" t="n">
-        <v>185.8603820800781</v>
+        <v>185.8603668212891</v>
       </c>
       <c r="C424" t="n">
-        <v>186.6945010191898</v>
+        <v>186.6944856919212</v>
       </c>
       <c r="D424" t="n">
-        <v>183.6559140609799</v>
+        <v>183.6558989831735</v>
       </c>
       <c r="E424" t="n">
-        <v>184.6985703108816</v>
+        <v>184.6985551474751</v>
       </c>
       <c r="F424" t="n">
         <v>736233</v>
@@ -8972,16 +8972,16 @@
         <v>43847</v>
       </c>
       <c r="B428" t="n">
-        <v>187.6775970458984</v>
+        <v>187.6775665283203</v>
       </c>
       <c r="C428" t="n">
-        <v>191.58009218769</v>
+        <v>191.5800610355412</v>
       </c>
       <c r="D428" t="n">
-        <v>185.3539732903878</v>
+        <v>185.3539431506457</v>
       </c>
       <c r="E428" t="n">
-        <v>189.1968906669651</v>
+        <v>189.1968599023401</v>
       </c>
       <c r="F428" t="n">
         <v>852600</v>
@@ -8992,16 +8992,16 @@
         <v>43850</v>
       </c>
       <c r="B429" t="n">
-        <v>188.1244354248047</v>
+        <v>188.1244201660156</v>
       </c>
       <c r="C429" t="n">
-        <v>189.4947845599039</v>
+        <v>189.4947691899657</v>
       </c>
       <c r="D429" t="n">
-        <v>185.9497561980689</v>
+        <v>185.9497411156683</v>
       </c>
       <c r="E429" t="n">
-        <v>189.4649956788822</v>
+        <v>189.4649803113602</v>
       </c>
       <c r="F429" t="n">
         <v>883800</v>
@@ -9032,16 +9032,16 @@
         <v>43852</v>
       </c>
       <c r="B431" t="n">
-        <v>190.5672302246094</v>
+        <v>190.5672149658203</v>
       </c>
       <c r="C431" t="n">
-        <v>193.2781244687579</v>
+        <v>193.2781089929065</v>
       </c>
       <c r="D431" t="n">
-        <v>189.4947850489844</v>
+        <v>189.4947698760664</v>
       </c>
       <c r="E431" t="n">
-        <v>191.4013491994205</v>
+        <v>191.4013338738432</v>
       </c>
       <c r="F431" t="n">
         <v>460300</v>
@@ -9052,16 +9052,16 @@
         <v>43853</v>
       </c>
       <c r="B432" t="n">
-        <v>191.5503082275391</v>
+        <v>191.55029296875</v>
       </c>
       <c r="C432" t="n">
-        <v>191.5503082275391</v>
+        <v>191.55029296875</v>
       </c>
       <c r="D432" t="n">
-        <v>186.5157899612223</v>
+        <v>186.5157751034802</v>
       </c>
       <c r="E432" t="n">
-        <v>189.8224923838211</v>
+        <v>189.8224772626689</v>
       </c>
       <c r="F432" t="n">
         <v>1068366</v>
@@ -9072,16 +9072,16 @@
         <v>43854</v>
       </c>
       <c r="B433" t="n">
-        <v>192.1460876464844</v>
+        <v>192.1461029052734</v>
       </c>
       <c r="C433" t="n">
-        <v>193.1887438656685</v>
+        <v>193.1887592072574</v>
       </c>
       <c r="D433" t="n">
-        <v>190.0607752081161</v>
+        <v>190.0607903013054</v>
       </c>
       <c r="E433" t="n">
-        <v>191.8481837049998</v>
+        <v>191.8481989401316</v>
       </c>
       <c r="F433" t="n">
         <v>639666</v>
@@ -9132,16 +9132,16 @@
         <v>43859</v>
       </c>
       <c r="B436" t="n">
-        <v>182.6132659912109</v>
+        <v>182.6132354736328</v>
       </c>
       <c r="C436" t="n">
-        <v>187.5286435106423</v>
+        <v>187.5286121716265</v>
       </c>
       <c r="D436" t="n">
-        <v>181.1237613252075</v>
+        <v>181.1237310565493</v>
       </c>
       <c r="E436" t="n">
-        <v>186.9328355834309</v>
+        <v>186.9328043439841</v>
       </c>
       <c r="F436" t="n">
         <v>838300</v>
@@ -9152,16 +9152,16 @@
         <v>43860</v>
       </c>
       <c r="B437" t="n">
-        <v>179.0682373046875</v>
+        <v>179.0682220458984</v>
       </c>
       <c r="C437" t="n">
-        <v>182.523883588893</v>
+        <v>182.5238680356409</v>
       </c>
       <c r="D437" t="n">
-        <v>174.8678387517811</v>
+        <v>174.867823850917</v>
       </c>
       <c r="E437" t="n">
-        <v>182.523883588893</v>
+        <v>182.5238680356409</v>
       </c>
       <c r="F437" t="n">
         <v>937800</v>
@@ -9172,16 +9172,16 @@
         <v>43861</v>
       </c>
       <c r="B438" t="n">
-        <v>178.9490661621094</v>
+        <v>178.9490814208984</v>
       </c>
       <c r="C438" t="n">
-        <v>179.8725668518933</v>
+        <v>179.8725821894282</v>
       </c>
       <c r="D438" t="n">
-        <v>175.3742643730724</v>
+        <v>175.374279327042</v>
       </c>
       <c r="E438" t="n">
-        <v>177.3701949931508</v>
+        <v>177.3702101173112</v>
       </c>
       <c r="F438" t="n">
         <v>886766</v>
@@ -9192,16 +9192,16 @@
         <v>43864</v>
       </c>
       <c r="B439" t="n">
-        <v>184.1027679443359</v>
+        <v>184.1027526855469</v>
       </c>
       <c r="C439" t="n">
-        <v>186.1582916261031</v>
+        <v>186.1582761969483</v>
       </c>
       <c r="D439" t="n">
-        <v>178.7405572865494</v>
+        <v>178.7405424721906</v>
       </c>
       <c r="E439" t="n">
-        <v>179.0384612457652</v>
+        <v>179.0384464067156</v>
       </c>
       <c r="F439" t="n">
         <v>700100</v>
@@ -9212,16 +9212,16 @@
         <v>43865</v>
       </c>
       <c r="B440" t="n">
-        <v>182.7622222900391</v>
+        <v>182.7621917724609</v>
       </c>
       <c r="C440" t="n">
-        <v>186.5753505305267</v>
+        <v>186.5753193762337</v>
       </c>
       <c r="D440" t="n">
-        <v>182.5238960929993</v>
+        <v>182.5238656152168</v>
       </c>
       <c r="E440" t="n">
-        <v>186.3668132141139</v>
+        <v>186.3667820946423</v>
       </c>
       <c r="F440" t="n">
         <v>732700</v>
@@ -9232,16 +9232,16 @@
         <v>43866</v>
       </c>
       <c r="B441" t="n">
-        <v>173.91455078125</v>
+        <v>173.9145660400391</v>
       </c>
       <c r="C441" t="n">
-        <v>185.2049904299985</v>
+        <v>185.2050066793799</v>
       </c>
       <c r="D441" t="n">
-        <v>171.85902722775</v>
+        <v>171.859042306193</v>
       </c>
       <c r="E441" t="n">
-        <v>184.6985643373504</v>
+        <v>184.6985805422995</v>
       </c>
       <c r="F441" t="n">
         <v>2347200</v>
@@ -9252,16 +9252,16 @@
         <v>43867</v>
       </c>
       <c r="B442" t="n">
-        <v>174.8678436279297</v>
+        <v>174.8678283691406</v>
       </c>
       <c r="C442" t="n">
-        <v>179.3363573647385</v>
+        <v>179.3363417160315</v>
       </c>
       <c r="D442" t="n">
-        <v>174.0634984276038</v>
+        <v>174.0634832390011</v>
       </c>
       <c r="E442" t="n">
-        <v>174.8678436279297</v>
+        <v>174.8678283691406</v>
       </c>
       <c r="F442" t="n">
         <v>1198833</v>
@@ -9272,16 +9272,16 @@
         <v>43868</v>
       </c>
       <c r="B443" t="n">
-        <v>171.6802825927734</v>
+        <v>171.6802978515625</v>
       </c>
       <c r="C443" t="n">
-        <v>180.8556354750996</v>
+        <v>180.8556515493858</v>
       </c>
       <c r="D443" t="n">
-        <v>171.4419564256401</v>
+        <v>171.4419716632469</v>
       </c>
       <c r="E443" t="n">
-        <v>172.961249755061</v>
+        <v>172.9612651277013</v>
       </c>
       <c r="F443" t="n">
         <v>1239533</v>
@@ -9292,16 +9292,16 @@
         <v>43871</v>
       </c>
       <c r="B444" t="n">
-        <v>166.1095428466797</v>
+        <v>166.1095733642578</v>
       </c>
       <c r="C444" t="n">
-        <v>172.7527354297412</v>
+        <v>172.752767167804</v>
       </c>
       <c r="D444" t="n">
-        <v>164.083823366511</v>
+        <v>164.0838535119248</v>
       </c>
       <c r="E444" t="n">
-        <v>171.6505014789369</v>
+        <v>171.6505330144978</v>
       </c>
       <c r="F444" t="n">
         <v>872966</v>
@@ -9332,16 +9332,16 @@
         <v>43873</v>
       </c>
       <c r="B446" t="n">
-        <v>174.9571990966797</v>
+        <v>174.9572143554688</v>
       </c>
       <c r="C446" t="n">
-        <v>176.3275329184407</v>
+        <v>176.3275482967427</v>
       </c>
       <c r="D446" t="n">
-        <v>171.412171152159</v>
+        <v>171.4121861017706</v>
       </c>
       <c r="E446" t="n">
-        <v>173.4974834903504</v>
+        <v>173.4974986218312</v>
       </c>
       <c r="F446" t="n">
         <v>872333</v>
@@ -9352,16 +9352,16 @@
         <v>43874</v>
       </c>
       <c r="B447" t="n">
-        <v>174.8678436279297</v>
+        <v>174.8678283691406</v>
       </c>
       <c r="C447" t="n">
-        <v>175.9700624703994</v>
+        <v>175.9700471154318</v>
       </c>
       <c r="D447" t="n">
-        <v>171.7696638003658</v>
+        <v>171.7696488119207</v>
       </c>
       <c r="E447" t="n">
-        <v>174.2720357355455</v>
+        <v>174.2720205287461</v>
       </c>
       <c r="F447" t="n">
         <v>404433</v>
@@ -9372,16 +9372,16 @@
         <v>43875</v>
       </c>
       <c r="B448" t="n">
-        <v>174.2422332763672</v>
+        <v>174.2422485351562</v>
       </c>
       <c r="C448" t="n">
-        <v>175.9998527850967</v>
+        <v>175.9998681978045</v>
       </c>
       <c r="D448" t="n">
-        <v>172.9910398302784</v>
+        <v>172.9910549794976</v>
       </c>
       <c r="E448" t="n">
-        <v>175.7913154934076</v>
+        <v>175.7913308878533</v>
       </c>
       <c r="F448" t="n">
         <v>468100</v>
@@ -9412,16 +9412,16 @@
         <v>43879</v>
       </c>
       <c r="B450" t="n">
-        <v>175.7019348144531</v>
+        <v>175.7019653320312</v>
       </c>
       <c r="C450" t="n">
-        <v>177.519131932085</v>
+        <v>177.5191627652912</v>
       </c>
       <c r="D450" t="n">
-        <v>172.7825038763567</v>
+        <v>172.7825338868604</v>
       </c>
       <c r="E450" t="n">
-        <v>177.519131932085</v>
+        <v>177.5191627652912</v>
       </c>
       <c r="F450" t="n">
         <v>669733</v>
@@ -9432,16 +9432,16 @@
         <v>43880</v>
       </c>
       <c r="B451" t="n">
-        <v>177.3702087402344</v>
+        <v>177.3701934814453</v>
       </c>
       <c r="C451" t="n">
-        <v>178.3234983824099</v>
+        <v>178.3234830416113</v>
       </c>
       <c r="D451" t="n">
-        <v>173.1995987537694</v>
+        <v>173.1995838537692</v>
       </c>
       <c r="E451" t="n">
-        <v>174.9870073628329</v>
+        <v>174.9869923090657</v>
       </c>
       <c r="F451" t="n">
         <v>740433</v>
@@ -9452,16 +9452,16 @@
         <v>43881</v>
       </c>
       <c r="B452" t="n">
-        <v>172.1569366455078</v>
+        <v>172.1569213867188</v>
       </c>
       <c r="C452" t="n">
-        <v>177.0722987901394</v>
+        <v>177.072283095687</v>
       </c>
       <c r="D452" t="n">
-        <v>171.3228177068359</v>
+        <v>171.3228025219774</v>
       </c>
       <c r="E452" t="n">
-        <v>175.7019648628997</v>
+        <v>175.7019492899041</v>
       </c>
       <c r="F452" t="n">
         <v>757533</v>
@@ -9472,16 +9472,16 @@
         <v>43882</v>
       </c>
       <c r="B453" t="n">
-        <v>166.8245239257812</v>
+        <v>166.8245086669922</v>
       </c>
       <c r="C453" t="n">
-        <v>171.2334601967152</v>
+        <v>171.2334445346579</v>
       </c>
       <c r="D453" t="n">
-        <v>165.5435414176457</v>
+        <v>165.543526276023</v>
       </c>
       <c r="E453" t="n">
-        <v>169.8333221629949</v>
+        <v>169.8333066290028</v>
       </c>
       <c r="F453" t="n">
         <v>990066</v>
@@ -9552,16 +9552,16 @@
         <v>43892</v>
       </c>
       <c r="B457" t="n">
-        <v>162.5347442626953</v>
+        <v>162.5347290039062</v>
       </c>
       <c r="C457" t="n">
-        <v>165.9308282847228</v>
+        <v>165.9308127071088</v>
       </c>
       <c r="D457" t="n">
-        <v>159.079097629504</v>
+        <v>159.0790826951317</v>
       </c>
       <c r="E457" t="n">
-        <v>164.7392124128411</v>
+        <v>164.7391969470962</v>
       </c>
       <c r="F457" t="n">
         <v>1544166</v>
@@ -9572,16 +9572,16 @@
         <v>43893</v>
       </c>
       <c r="B458" t="n">
-        <v>165.0966949462891</v>
+        <v>165.0966796875</v>
       </c>
       <c r="C458" t="n">
-        <v>168.6417233935162</v>
+        <v>168.6417078070837</v>
       </c>
       <c r="D458" t="n">
-        <v>161.0154514757296</v>
+        <v>161.0154365941427</v>
       </c>
       <c r="E458" t="n">
-        <v>161.1644110364513</v>
+        <v>161.1643961410971</v>
       </c>
       <c r="F458" t="n">
         <v>1281800</v>
@@ -9592,16 +9592,16 @@
         <v>43894</v>
       </c>
       <c r="B459" t="n">
-        <v>159.4663543701172</v>
+        <v>159.4663391113281</v>
       </c>
       <c r="C459" t="n">
-        <v>169.7439418828748</v>
+        <v>169.7439256406586</v>
       </c>
       <c r="D459" t="n">
-        <v>159.0790837910523</v>
+        <v>159.0790685693198</v>
       </c>
       <c r="E459" t="n">
-        <v>167.5692628035011</v>
+        <v>167.5692467693725</v>
       </c>
       <c r="F459" t="n">
         <v>1186600</v>
@@ -9632,16 +9632,16 @@
         <v>43896</v>
       </c>
       <c r="B461" t="n">
-        <v>148.9802398681641</v>
+        <v>148.9802703857422</v>
       </c>
       <c r="C461" t="n">
-        <v>152.8231566550619</v>
+        <v>152.8231879598351</v>
       </c>
       <c r="D461" t="n">
-        <v>147.8780059247562</v>
+        <v>147.8780362165492</v>
       </c>
       <c r="E461" t="n">
-        <v>151.9294600099305</v>
+        <v>151.9294911316361</v>
       </c>
       <c r="F461" t="n">
         <v>1046833</v>
@@ -9672,16 +9672,16 @@
         <v>43900</v>
       </c>
       <c r="B463" t="n">
-        <v>145.6437683105469</v>
+        <v>145.6437530517578</v>
       </c>
       <c r="C463" t="n">
-        <v>147.3715992239526</v>
+        <v>147.3715837841424</v>
       </c>
       <c r="D463" t="n">
-        <v>136.9152774017098</v>
+        <v>136.9152630573862</v>
       </c>
       <c r="E463" t="n">
-        <v>142.4562215733386</v>
+        <v>142.456206648502</v>
       </c>
       <c r="F463" t="n">
         <v>1718533</v>
@@ -9712,16 +9712,16 @@
         <v>43902</v>
       </c>
       <c r="B465" t="n">
-        <v>116.0622024536133</v>
+        <v>116.0621948242188</v>
       </c>
       <c r="C465" t="n">
-        <v>124.8204897078642</v>
+        <v>124.8204815027402</v>
       </c>
       <c r="D465" t="n">
-        <v>107.3635005385155</v>
+        <v>107.3634934809335</v>
       </c>
       <c r="E465" t="n">
-        <v>111.206417781332</v>
+        <v>111.2064104711344</v>
       </c>
       <c r="F465" t="n">
         <v>1010966</v>
@@ -9732,16 +9732,16 @@
         <v>43903</v>
       </c>
       <c r="B466" t="n">
-        <v>129.9145965576172</v>
+        <v>129.9145660400391</v>
       </c>
       <c r="C466" t="n">
-        <v>137.0344269206882</v>
+        <v>137.0343947306269</v>
       </c>
       <c r="D466" t="n">
-        <v>118.713515297641</v>
+        <v>118.713487411252</v>
       </c>
       <c r="E466" t="n">
-        <v>136.9450602787476</v>
+        <v>136.945028109679</v>
       </c>
       <c r="F466" t="n">
         <v>2459466</v>
@@ -9752,16 +9752,16 @@
         <v>43906</v>
       </c>
       <c r="B467" t="n">
-        <v>110.2233276367188</v>
+        <v>110.2233352661133</v>
       </c>
       <c r="C467" t="n">
-        <v>120.67964750577</v>
+        <v>120.6796558589259</v>
       </c>
       <c r="D467" t="n">
-        <v>106.3208257335674</v>
+        <v>106.3208330928401</v>
       </c>
       <c r="E467" t="n">
-        <v>109.7466828864663</v>
+        <v>109.7466904828687</v>
       </c>
       <c r="F467" t="n">
         <v>2066566</v>
@@ -9792,16 +9792,16 @@
         <v>43908</v>
       </c>
       <c r="B469" t="n">
-        <v>94.49417114257812</v>
+        <v>94.49417877197266</v>
       </c>
       <c r="C469" t="n">
-        <v>104.8611259403486</v>
+        <v>104.861134406764</v>
       </c>
       <c r="D469" t="n">
-        <v>85.43798771097393</v>
+        <v>85.43799460917843</v>
       </c>
       <c r="E469" t="n">
-        <v>103.6695252496678</v>
+        <v>103.6695336198741</v>
       </c>
       <c r="F469" t="n">
         <v>1809666</v>
@@ -9832,16 +9832,16 @@
         <v>43910</v>
       </c>
       <c r="B471" t="n">
-        <v>116.1813583374023</v>
+        <v>116.1813507080078</v>
       </c>
       <c r="C471" t="n">
-        <v>120.9477684928167</v>
+        <v>120.9477605504217</v>
       </c>
       <c r="D471" t="n">
-        <v>108.1976128040696</v>
+        <v>108.1976056989515</v>
       </c>
       <c r="E471" t="n">
-        <v>113.9471014462984</v>
+        <v>113.947093963623</v>
       </c>
       <c r="F471" t="n">
         <v>2114800</v>
@@ -9852,16 +9852,16 @@
         <v>43913</v>
       </c>
       <c r="B472" t="n">
-        <v>113.7981491088867</v>
+        <v>113.7981414794922</v>
       </c>
       <c r="C472" t="n">
-        <v>119.6072154920344</v>
+        <v>119.6072074731813</v>
       </c>
       <c r="D472" t="n">
-        <v>108.4657199517548</v>
+        <v>108.4657126798635</v>
       </c>
       <c r="E472" t="n">
-        <v>118.9518374122596</v>
+        <v>118.9518294373453</v>
       </c>
       <c r="F472" t="n">
         <v>1372400</v>
@@ -9892,16 +9892,16 @@
         <v>43915</v>
       </c>
       <c r="B474" t="n">
-        <v>135.2469940185547</v>
+        <v>135.2470245361328</v>
       </c>
       <c r="C474" t="n">
-        <v>138.3749622926183</v>
+        <v>138.3749935160015</v>
       </c>
       <c r="D474" t="n">
-        <v>119.8455242586765</v>
+        <v>119.8455513010161</v>
       </c>
       <c r="E474" t="n">
-        <v>123.8969703948857</v>
+        <v>123.8969983514071</v>
       </c>
       <c r="F474" t="n">
         <v>1102933</v>
@@ -9932,16 +9932,16 @@
         <v>43917</v>
       </c>
       <c r="B476" t="n">
-        <v>135.544921875</v>
+        <v>135.5449066162109</v>
       </c>
       <c r="C476" t="n">
-        <v>143.9457195368442</v>
+        <v>143.9457033323465</v>
       </c>
       <c r="D476" t="n">
-        <v>133.7277244008504</v>
+        <v>133.72770934663</v>
       </c>
       <c r="E476" t="n">
-        <v>141.3837848967248</v>
+        <v>141.3837689806335</v>
       </c>
       <c r="F476" t="n">
         <v>773066</v>
@@ -9972,16 +9972,16 @@
         <v>43921</v>
       </c>
       <c r="B478" t="n">
-        <v>126.3099899291992</v>
+        <v>126.3099822998047</v>
       </c>
       <c r="C478" t="n">
-        <v>138.5239309580564</v>
+        <v>138.5239225909137</v>
       </c>
       <c r="D478" t="n">
-        <v>125.1183892524381</v>
+        <v>125.1183816950188</v>
       </c>
       <c r="E478" t="n">
-        <v>134.1447836977352</v>
+        <v>134.1447755951023</v>
       </c>
       <c r="F478" t="n">
         <v>993633</v>
@@ -9992,16 +9992,16 @@
         <v>43922</v>
       </c>
       <c r="B479" t="n">
-        <v>119.398681640625</v>
+        <v>119.3986968994141</v>
       </c>
       <c r="C479" t="n">
-        <v>125.6248148518141</v>
+        <v>125.6248309062841</v>
       </c>
       <c r="D479" t="n">
-        <v>115.7344980529492</v>
+        <v>115.7345128434667</v>
       </c>
       <c r="E479" t="n">
-        <v>120.6498675737846</v>
+        <v>120.6498829924714</v>
       </c>
       <c r="F479" t="n">
         <v>1115733</v>
@@ -10012,16 +10012,16 @@
         <v>43923</v>
       </c>
       <c r="B480" t="n">
-        <v>121.573371887207</v>
+        <v>121.5733642578125</v>
       </c>
       <c r="C480" t="n">
-        <v>124.3438514920716</v>
+        <v>124.3438436888143</v>
       </c>
       <c r="D480" t="n">
-        <v>116.4792610496121</v>
+        <v>116.4792537399009</v>
       </c>
       <c r="E480" t="n">
-        <v>118.4156216728895</v>
+        <v>118.415614241661</v>
       </c>
       <c r="F480" t="n">
         <v>765700</v>
@@ -10032,16 +10032,16 @@
         <v>43924</v>
       </c>
       <c r="B481" t="n">
-        <v>112.4575881958008</v>
+        <v>112.4575958251953</v>
       </c>
       <c r="C481" t="n">
-        <v>121.3946150722883</v>
+        <v>121.3946233079923</v>
       </c>
       <c r="D481" t="n">
-        <v>109.1508864332576</v>
+        <v>109.1508938383175</v>
       </c>
       <c r="E481" t="n">
-        <v>121.2456631091445</v>
+        <v>121.2456713347432</v>
       </c>
       <c r="F481" t="n">
         <v>1289233</v>
@@ -10052,16 +10052,16 @@
         <v>43927</v>
       </c>
       <c r="B482" t="n">
-        <v>128.097412109375</v>
+        <v>128.0973815917969</v>
       </c>
       <c r="C482" t="n">
-        <v>135.6343027202543</v>
+        <v>135.6342704071079</v>
       </c>
       <c r="D482" t="n">
-        <v>118.2368900834965</v>
+        <v>118.2368619150623</v>
       </c>
       <c r="E482" t="n">
-        <v>119.1603833575581</v>
+        <v>119.1603549691134</v>
       </c>
       <c r="F482" t="n">
         <v>1479633</v>
@@ -10072,16 +10072,16 @@
         <v>43928</v>
       </c>
       <c r="B483" t="n">
-        <v>143.8861389160156</v>
+        <v>143.8861236572266</v>
       </c>
       <c r="C483" t="n">
-        <v>154.908479064077</v>
+        <v>154.9084626363945</v>
       </c>
       <c r="D483" t="n">
-        <v>138.0175022823959</v>
+        <v>138.017487645962</v>
       </c>
       <c r="E483" t="n">
-        <v>145.1969102426065</v>
+        <v>145.1968948448132</v>
       </c>
       <c r="F483" t="n">
         <v>1844300</v>
@@ -10092,16 +10092,16 @@
         <v>43929</v>
       </c>
       <c r="B484" t="n">
-        <v>148.920654296875</v>
+        <v>148.9206848144531</v>
       </c>
       <c r="C484" t="n">
-        <v>152.5252598703173</v>
+        <v>152.5252911265695</v>
       </c>
       <c r="D484" t="n">
-        <v>142.0987288481829</v>
+        <v>142.0987579677773</v>
       </c>
       <c r="E484" t="n">
-        <v>144.3329854957831</v>
+        <v>144.3330150732328</v>
       </c>
       <c r="F484" t="n">
         <v>859700</v>
@@ -10152,16 +10152,16 @@
         <v>43935</v>
       </c>
       <c r="B487" t="n">
-        <v>157.8577117919922</v>
+        <v>157.8576965332031</v>
       </c>
       <c r="C487" t="n">
-        <v>161.5814736003482</v>
+        <v>161.5814579816142</v>
       </c>
       <c r="D487" t="n">
-        <v>150.0824953179016</v>
+        <v>150.082480810678</v>
       </c>
       <c r="E487" t="n">
-        <v>150.1718619648161</v>
+        <v>150.171847448954</v>
       </c>
       <c r="F487" t="n">
         <v>964366</v>
@@ -10172,16 +10172,16 @@
         <v>43936</v>
       </c>
       <c r="B488" t="n">
-        <v>155.0574340820312</v>
+        <v>155.0574188232422</v>
       </c>
       <c r="C488" t="n">
-        <v>160.8069307415302</v>
+        <v>160.8069149169485</v>
       </c>
       <c r="D488" t="n">
-        <v>148.0865629562494</v>
+        <v>148.0865483834452</v>
       </c>
       <c r="E488" t="n">
-        <v>154.6105856999209</v>
+        <v>154.610570485105</v>
       </c>
       <c r="F488" t="n">
         <v>821233</v>
@@ -10192,16 +10192,16 @@
         <v>43937</v>
       </c>
       <c r="B489" t="n">
-        <v>154.7893218994141</v>
+        <v>154.789306640625</v>
       </c>
       <c r="C489" t="n">
-        <v>158.4832944961593</v>
+        <v>158.4832788732266</v>
       </c>
       <c r="D489" t="n">
-        <v>151.5719865290805</v>
+        <v>151.5719715874492</v>
       </c>
       <c r="E489" t="n">
-        <v>155.5638630743422</v>
+        <v>155.5638477392006</v>
       </c>
       <c r="F489" t="n">
         <v>851733</v>
@@ -10212,16 +10212,16 @@
         <v>43938</v>
       </c>
       <c r="B490" t="n">
-        <v>156.1000671386719</v>
+        <v>156.1000823974609</v>
       </c>
       <c r="C490" t="n">
-        <v>159.6450950891468</v>
+        <v>159.6451106944625</v>
       </c>
       <c r="D490" t="n">
-        <v>151.8400909746121</v>
+        <v>151.8401058169883</v>
       </c>
       <c r="E490" t="n">
-        <v>159.6450950891468</v>
+        <v>159.6451106944625</v>
       </c>
       <c r="F490" t="n">
         <v>607466</v>
@@ -10252,16 +10252,16 @@
         <v>43943</v>
       </c>
       <c r="B492" t="n">
-        <v>158.8109588623047</v>
+        <v>158.8109741210938</v>
       </c>
       <c r="C492" t="n">
-        <v>166.8245001608599</v>
+        <v>166.8245161896017</v>
       </c>
       <c r="D492" t="n">
-        <v>157.6193583201317</v>
+        <v>157.6193734644301</v>
       </c>
       <c r="E492" t="n">
-        <v>166.8245001608599</v>
+        <v>166.8245161896017</v>
       </c>
       <c r="F492" t="n">
         <v>2119233</v>
@@ -10272,16 +10272,16 @@
         <v>43944</v>
       </c>
       <c r="B493" t="n">
-        <v>151.8401184082031</v>
+        <v>151.8401031494141</v>
       </c>
       <c r="C493" t="n">
-        <v>160.8665135898119</v>
+        <v>160.8664974239381</v>
       </c>
       <c r="D493" t="n">
-        <v>144.809654144183</v>
+        <v>144.8096395919027</v>
       </c>
       <c r="E493" t="n">
-        <v>159.8238572305839</v>
+        <v>159.8238411694891</v>
       </c>
       <c r="F493" t="n">
         <v>1242300</v>
@@ -10292,16 +10292,16 @@
         <v>43945</v>
       </c>
       <c r="B494" t="n">
-        <v>148.9504699707031</v>
+        <v>148.950439453125</v>
       </c>
       <c r="C494" t="n">
-        <v>152.0188460156135</v>
+        <v>152.018814869374</v>
       </c>
       <c r="D494" t="n">
-        <v>136.1109315801753</v>
+        <v>136.1109036932141</v>
       </c>
       <c r="E494" t="n">
-        <v>146.9545391278248</v>
+        <v>146.9545090191811</v>
       </c>
       <c r="F494" t="n">
         <v>1301233</v>
@@ -10312,16 +10312,16 @@
         <v>43948</v>
       </c>
       <c r="B495" t="n">
-        <v>156.9640045166016</v>
+        <v>156.9639892578125</v>
       </c>
       <c r="C495" t="n">
-        <v>157.9172942346718</v>
+        <v>157.9172788832115</v>
       </c>
       <c r="D495" t="n">
-        <v>152.8231830812869</v>
+        <v>152.8231682250355</v>
       </c>
       <c r="E495" t="n">
-        <v>153.8658394489189</v>
+        <v>153.8658244913087</v>
       </c>
       <c r="F495" t="n">
         <v>935633</v>
@@ -10332,16 +10332,16 @@
         <v>43949</v>
       </c>
       <c r="B496" t="n">
-        <v>159.1386566162109</v>
+        <v>159.1386413574219</v>
       </c>
       <c r="C496" t="n">
-        <v>166.1989086095649</v>
+        <v>166.1988926738134</v>
       </c>
       <c r="D496" t="n">
-        <v>157.8874782807897</v>
+        <v>157.8874631419682</v>
       </c>
       <c r="E496" t="n">
-        <v>157.8874782807897</v>
+        <v>157.8874631419682</v>
       </c>
       <c r="F496" t="n">
         <v>787066</v>
@@ -10372,16 +10372,16 @@
         <v>43951</v>
       </c>
       <c r="B498" t="n">
-        <v>156.2674407958984</v>
+        <v>156.2674560546875</v>
       </c>
       <c r="C498" t="n">
-        <v>162.1081054364251</v>
+        <v>162.108121265528</v>
       </c>
       <c r="D498" t="n">
-        <v>155.4926606076694</v>
+        <v>155.4926757908048</v>
       </c>
       <c r="E498" t="n">
-        <v>159.0983788998354</v>
+        <v>159.0983944350523</v>
       </c>
       <c r="F498" t="n">
         <v>826166</v>
@@ -10392,16 +10392,16 @@
         <v>43955</v>
       </c>
       <c r="B499" t="n">
-        <v>152.4531555175781</v>
+        <v>152.4531402587891</v>
       </c>
       <c r="C499" t="n">
-        <v>152.8107475853664</v>
+        <v>152.8107322907865</v>
       </c>
       <c r="D499" t="n">
-        <v>147.5660740289393</v>
+        <v>147.5660592592903</v>
       </c>
       <c r="E499" t="n">
-        <v>148.5494560045326</v>
+        <v>148.5494411364585</v>
       </c>
       <c r="F499" t="n">
         <v>865433</v>
@@ -10412,16 +10412,16 @@
         <v>43956</v>
       </c>
       <c r="B500" t="n">
-        <v>154.6582794189453</v>
+        <v>154.6582946777344</v>
       </c>
       <c r="C500" t="n">
-        <v>157.6382077898564</v>
+        <v>157.6382233426491</v>
       </c>
       <c r="D500" t="n">
-        <v>151.4101532507764</v>
+        <v>151.4101681891011</v>
       </c>
       <c r="E500" t="n">
-        <v>153.6153014577865</v>
+        <v>153.615316613674</v>
       </c>
       <c r="F500" t="n">
         <v>670733</v>
@@ -10432,16 +10432,16 @@
         <v>43957</v>
       </c>
       <c r="B501" t="n">
-        <v>155.5820617675781</v>
+        <v>155.5820770263672</v>
       </c>
       <c r="C501" t="n">
-        <v>160.2009445810146</v>
+        <v>160.2009602928029</v>
       </c>
       <c r="D501" t="n">
-        <v>150.3075759322569</v>
+        <v>150.3075906737481</v>
       </c>
       <c r="E501" t="n">
-        <v>155.2840659055211</v>
+        <v>155.2840811350841</v>
       </c>
       <c r="F501" t="n">
         <v>746233</v>
@@ -10552,16 +10552,16 @@
         <v>43965</v>
       </c>
       <c r="B507" t="n">
-        <v>141.2784271240234</v>
+        <v>141.2784118652344</v>
       </c>
       <c r="C507" t="n">
-        <v>147.5064828667171</v>
+        <v>147.5064669352663</v>
       </c>
       <c r="D507" t="n">
-        <v>138.3580943310847</v>
+        <v>138.3580793877065</v>
       </c>
       <c r="E507" t="n">
-        <v>145.6589263134315</v>
+        <v>145.6589105815262</v>
       </c>
       <c r="F507" t="n">
         <v>844800</v>
@@ -10592,16 +10592,16 @@
         <v>43969</v>
       </c>
       <c r="B509" t="n">
-        <v>147.6256561279297</v>
+        <v>147.6256713867188</v>
       </c>
       <c r="C509" t="n">
-        <v>148.3408401954261</v>
+        <v>148.3408555281376</v>
       </c>
       <c r="D509" t="n">
-        <v>142.4405792169308</v>
+        <v>142.4405939397833</v>
       </c>
       <c r="E509" t="n">
-        <v>144.4967372001582</v>
+        <v>144.4967521355379</v>
       </c>
       <c r="F509" t="n">
         <v>822866</v>
@@ -10612,16 +10612,16 @@
         <v>43970</v>
       </c>
       <c r="B510" t="n">
-        <v>150.1586151123047</v>
+        <v>150.1585998535156</v>
       </c>
       <c r="C510" t="n">
-        <v>154.9563024492492</v>
+        <v>154.9562867029296</v>
       </c>
       <c r="D510" t="n">
-        <v>145.807914078008</v>
+        <v>145.8078992613276</v>
       </c>
       <c r="E510" t="n">
-        <v>148.2216643630295</v>
+        <v>148.2216493010691</v>
       </c>
       <c r="F510" t="n">
         <v>591566</v>
@@ -10732,16 +10732,16 @@
         <v>43978</v>
       </c>
       <c r="B516" t="n">
-        <v>163.8960876464844</v>
+        <v>163.8960571289062</v>
       </c>
       <c r="C516" t="n">
-        <v>165.982043915575</v>
+        <v>165.9820130095902</v>
       </c>
       <c r="D516" t="n">
-        <v>160.3201669442439</v>
+        <v>160.320137092505</v>
       </c>
       <c r="E516" t="n">
-        <v>165.5350424602684</v>
+        <v>165.5350116375157</v>
       </c>
       <c r="F516" t="n">
         <v>627900</v>
@@ -10752,16 +10752,16 @@
         <v>43979</v>
       </c>
       <c r="B517" t="n">
-        <v>163.9258728027344</v>
+        <v>163.9258880615234</v>
       </c>
       <c r="C517" t="n">
-        <v>168.0679717816257</v>
+        <v>168.0679874259757</v>
       </c>
       <c r="D517" t="n">
-        <v>161.3333342871174</v>
+        <v>161.333349304584</v>
       </c>
       <c r="E517" t="n">
-        <v>163.4490884655809</v>
+        <v>163.4491036799892</v>
       </c>
       <c r="F517" t="n">
         <v>560100</v>
@@ -10772,16 +10772,16 @@
         <v>43980</v>
       </c>
       <c r="B518" t="n">
-        <v>163.4788970947266</v>
+        <v>163.4789123535156</v>
       </c>
       <c r="C518" t="n">
-        <v>165.0582557337539</v>
+        <v>165.0582711399571</v>
       </c>
       <c r="D518" t="n">
-        <v>157.9958238149825</v>
+        <v>157.9958385619926</v>
       </c>
       <c r="E518" t="n">
-        <v>163.9556814626646</v>
+        <v>163.9556967659558</v>
       </c>
       <c r="F518" t="n">
         <v>1761600</v>
@@ -10812,16 +10812,16 @@
         <v>43984</v>
       </c>
       <c r="B520" t="n">
-        <v>162.5849151611328</v>
+        <v>162.5848999023438</v>
       </c>
       <c r="C520" t="n">
-        <v>164.1642890132777</v>
+        <v>164.1642736062624</v>
       </c>
       <c r="D520" t="n">
-        <v>159.7241936946168</v>
+        <v>159.7241787043098</v>
       </c>
       <c r="E520" t="n">
-        <v>163.8662930889087</v>
+        <v>163.8662777098608</v>
       </c>
       <c r="F520" t="n">
         <v>917300</v>
@@ -10852,16 +10852,16 @@
         <v>43986</v>
       </c>
       <c r="B522" t="n">
-        <v>174.8025970458984</v>
+        <v>174.8026123046875</v>
       </c>
       <c r="C522" t="n">
-        <v>176.977947219718</v>
+        <v>176.9779626683967</v>
       </c>
       <c r="D522" t="n">
-        <v>169.7963239643039</v>
+        <v>169.7963387860876</v>
       </c>
       <c r="E522" t="n">
-        <v>174.6238086157378</v>
+        <v>174.6238238589201</v>
       </c>
       <c r="F522" t="n">
         <v>1106633</v>
@@ -10872,16 +10872,16 @@
         <v>43987</v>
       </c>
       <c r="B523" t="n">
-        <v>177.4547576904297</v>
+        <v>177.4547424316406</v>
       </c>
       <c r="C523" t="n">
-        <v>182.3716524386734</v>
+        <v>182.3716367570957</v>
       </c>
       <c r="D523" t="n">
-        <v>175.1006187393156</v>
+        <v>175.1006036829517</v>
       </c>
       <c r="E523" t="n">
-        <v>178.7957317411692</v>
+        <v>178.7957163670739</v>
       </c>
       <c r="F523" t="n">
         <v>929700</v>
@@ -10912,16 +10912,16 @@
         <v>43991</v>
       </c>
       <c r="B525" t="n">
-        <v>179.0639038085938</v>
+        <v>179.0639190673828</v>
       </c>
       <c r="C525" t="n">
-        <v>181.8352305827343</v>
+        <v>181.8352460776798</v>
       </c>
       <c r="D525" t="n">
-        <v>173.7000235344026</v>
+        <v>173.7000383361128</v>
       </c>
       <c r="E525" t="n">
-        <v>178.1699161845453</v>
+        <v>178.1699313671539</v>
       </c>
       <c r="F525" t="n">
         <v>591500</v>
@@ -10932,16 +10932,16 @@
         <v>43992</v>
       </c>
       <c r="B526" t="n">
-        <v>180.8518676757812</v>
+        <v>180.8518829345703</v>
       </c>
       <c r="C526" t="n">
-        <v>183.5636137469044</v>
+        <v>183.5636292344882</v>
       </c>
       <c r="D526" t="n">
-        <v>178.4977288170735</v>
+        <v>178.4977438772397</v>
       </c>
       <c r="E526" t="n">
-        <v>181.4180614126206</v>
+        <v>181.4180767191804</v>
       </c>
       <c r="F526" t="n">
         <v>715466</v>
@@ -10952,16 +10952,16 @@
         <v>43994</v>
       </c>
       <c r="B527" t="n">
-        <v>177.9315643310547</v>
+        <v>177.9315338134766</v>
       </c>
       <c r="C527" t="n">
-        <v>180.2261072216798</v>
+        <v>180.2260763105577</v>
       </c>
       <c r="D527" t="n">
-        <v>171.763104670555</v>
+        <v>171.763075210948</v>
       </c>
       <c r="E527" t="n">
-        <v>174.0874456384582</v>
+        <v>174.0874157801964</v>
       </c>
       <c r="F527" t="n">
         <v>1048900</v>
@@ -10972,16 +10972,16 @@
         <v>43997</v>
       </c>
       <c r="B528" t="n">
-        <v>180.3750457763672</v>
+        <v>180.3750915527344</v>
       </c>
       <c r="C528" t="n">
-        <v>182.8781896453499</v>
+        <v>182.8782360569759</v>
       </c>
       <c r="D528" t="n">
-        <v>173.521217151253</v>
+        <v>173.5212611882256</v>
       </c>
       <c r="E528" t="n">
-        <v>175.7859613138141</v>
+        <v>175.7860059255433</v>
       </c>
       <c r="F528" t="n">
         <v>826966</v>
@@ -11012,16 +11012,16 @@
         <v>43999</v>
       </c>
       <c r="B530" t="n">
-        <v>181.2392578125</v>
+        <v>181.2392425537109</v>
       </c>
       <c r="C530" t="n">
-        <v>186.0667429864499</v>
+        <v>186.066727321228</v>
       </c>
       <c r="D530" t="n">
-        <v>180.6134830825056</v>
+        <v>180.6134678764014</v>
       </c>
       <c r="E530" t="n">
-        <v>182.0438513054095</v>
+        <v>182.0438359788805</v>
       </c>
       <c r="F530" t="n">
         <v>934766</v>
@@ -11032,16 +11032,16 @@
         <v>44000</v>
       </c>
       <c r="B531" t="n">
-        <v>179.689697265625</v>
+        <v>179.6896820068359</v>
       </c>
       <c r="C531" t="n">
-        <v>182.9080257667236</v>
+        <v>182.9080102346423</v>
       </c>
       <c r="D531" t="n">
-        <v>178.438132649104</v>
+        <v>178.4381174965946</v>
       </c>
       <c r="E531" t="n">
-        <v>181.7756534498614</v>
+        <v>181.7756380139382</v>
       </c>
       <c r="F531" t="n">
         <v>656233</v>
@@ -11052,16 +11052,16 @@
         <v>44001</v>
       </c>
       <c r="B532" t="n">
-        <v>187.1693115234375</v>
+        <v>187.1692962646484</v>
       </c>
       <c r="C532" t="n">
-        <v>190.1194421040784</v>
+        <v>190.119426604783</v>
       </c>
       <c r="D532" t="n">
-        <v>181.0306657700721</v>
+        <v>181.0306510117299</v>
       </c>
       <c r="E532" t="n">
-        <v>181.7756479337349</v>
+        <v>181.7756331146588</v>
       </c>
       <c r="F532" t="n">
         <v>2381566</v>
@@ -11152,16 +11152,16 @@
         <v>44008</v>
       </c>
       <c r="B537" t="n">
-        <v>182.7292022705078</v>
+        <v>182.7292175292969</v>
       </c>
       <c r="C537" t="n">
-        <v>187.1692968299095</v>
+        <v>187.1693124594684</v>
       </c>
       <c r="D537" t="n">
-        <v>182.6696061271655</v>
+        <v>182.669621380978</v>
       </c>
       <c r="E537" t="n">
-        <v>182.6994041988366</v>
+        <v>182.6994194551374</v>
       </c>
       <c r="F537" t="n">
         <v>565500</v>
@@ -11192,16 +11192,16 @@
         <v>44012</v>
       </c>
       <c r="B539" t="n">
-        <v>185.2621765136719</v>
+        <v>185.2621612548828</v>
       </c>
       <c r="C539" t="n">
-        <v>190.7154519235229</v>
+        <v>190.7154362155846</v>
       </c>
       <c r="D539" t="n">
-        <v>184.3980019722882</v>
+        <v>184.3979867846753</v>
       </c>
       <c r="E539" t="n">
-        <v>186.9309445994879</v>
+        <v>186.9309292032538</v>
       </c>
       <c r="F539" t="n">
         <v>688100</v>
@@ -11212,16 +11212,16 @@
         <v>44013</v>
       </c>
       <c r="B540" t="n">
-        <v>187.7056884765625</v>
+        <v>187.7057037353516</v>
       </c>
       <c r="C540" t="n">
-        <v>189.9108366739434</v>
+        <v>189.9108521119912</v>
       </c>
       <c r="D540" t="n">
-        <v>185.232342483095</v>
+        <v>185.2323575408232</v>
       </c>
       <c r="E540" t="n">
-        <v>185.7985361463114</v>
+        <v>185.7985512500661</v>
       </c>
       <c r="F540" t="n">
         <v>601100</v>
@@ -11232,16 +11232,16 @@
         <v>44014</v>
       </c>
       <c r="B541" t="n">
-        <v>180.9710845947266</v>
+        <v>180.9710540771484</v>
       </c>
       <c r="C541" t="n">
-        <v>190.5366460610093</v>
+        <v>190.5366139303682</v>
       </c>
       <c r="D541" t="n">
-        <v>179.987702600919</v>
+        <v>179.9876722491709</v>
       </c>
       <c r="E541" t="n">
-        <v>190.1492559101219</v>
+        <v>190.1492238448073</v>
       </c>
       <c r="F541" t="n">
         <v>782133</v>
@@ -11252,16 +11252,16 @@
         <v>44015</v>
       </c>
       <c r="B542" t="n">
-        <v>181.5074615478516</v>
+        <v>181.5074462890625</v>
       </c>
       <c r="C542" t="n">
-        <v>184.4575923143823</v>
+        <v>184.4575768075846</v>
       </c>
       <c r="D542" t="n">
-        <v>178.0805464104103</v>
+        <v>178.0805314397118</v>
       </c>
       <c r="E542" t="n">
-        <v>179.3917223762915</v>
+        <v>179.3917072953663</v>
       </c>
       <c r="F542" t="n">
         <v>277066</v>
@@ -11292,16 +11292,16 @@
         <v>44019</v>
       </c>
       <c r="B544" t="n">
-        <v>178.6467437744141</v>
+        <v>178.646728515625</v>
       </c>
       <c r="C544" t="n">
-        <v>182.8186412067338</v>
+        <v>182.8186255916096</v>
       </c>
       <c r="D544" t="n">
-        <v>177.8421502390783</v>
+        <v>177.8421350490122</v>
       </c>
       <c r="E544" t="n">
-        <v>178.7957341568639</v>
+        <v>178.7957188853491</v>
       </c>
       <c r="F544" t="n">
         <v>1026966</v>
@@ -11312,16 +11312,16 @@
         <v>44020</v>
       </c>
       <c r="B545" t="n">
-        <v>180.9412689208984</v>
+        <v>180.9412994384766</v>
       </c>
       <c r="C545" t="n">
-        <v>183.5040093454935</v>
+        <v>183.5040402953038</v>
       </c>
       <c r="D545" t="n">
-        <v>177.1567620095117</v>
+        <v>177.1567918887944</v>
       </c>
       <c r="E545" t="n">
-        <v>180.4346713566746</v>
+        <v>180.4347017888099</v>
       </c>
       <c r="F545" t="n">
         <v>677066</v>
@@ -11352,16 +11352,16 @@
         <v>44022</v>
       </c>
       <c r="B547" t="n">
-        <v>180.1962738037109</v>
+        <v>180.1963043212891</v>
       </c>
       <c r="C547" t="n">
-        <v>181.0604481886947</v>
+        <v>181.0604788526272</v>
       </c>
       <c r="D547" t="n">
-        <v>177.931529434533</v>
+        <v>177.9315595685599</v>
       </c>
       <c r="E547" t="n">
-        <v>178.8255018909508</v>
+        <v>178.8255321763785</v>
       </c>
       <c r="F547" t="n">
         <v>618666</v>
@@ -11372,16 +11372,16 @@
         <v>44025</v>
       </c>
       <c r="B548" t="n">
-        <v>175.6965942382812</v>
+        <v>175.6966094970703</v>
       </c>
       <c r="C548" t="n">
-        <v>181.2690612990238</v>
+        <v>181.269077041767</v>
       </c>
       <c r="D548" t="n">
-        <v>175.6369829349472</v>
+        <v>175.6369981885591</v>
       </c>
       <c r="E548" t="n">
-        <v>180.1366890428852</v>
+        <v>180.1367046872849</v>
       </c>
       <c r="F548" t="n">
         <v>495033</v>
@@ -11392,16 +11392,16 @@
         <v>44026</v>
       </c>
       <c r="B549" t="n">
-        <v>178.4679412841797</v>
+        <v>178.4679107666016</v>
       </c>
       <c r="C549" t="n">
-        <v>179.2129235145311</v>
+        <v>179.2128928695628</v>
       </c>
       <c r="D549" t="n">
-        <v>173.2828637483977</v>
+        <v>173.282834117455</v>
       </c>
       <c r="E549" t="n">
-        <v>175.0708241325815</v>
+        <v>175.0707941959021</v>
       </c>
       <c r="F549" t="n">
         <v>493066</v>
@@ -11452,16 +11452,16 @@
         <v>44029</v>
       </c>
       <c r="B552" t="n">
-        <v>190.1492462158203</v>
+        <v>190.1492614746094</v>
       </c>
       <c r="C552" t="n">
-        <v>190.1492462158203</v>
+        <v>190.1492614746094</v>
       </c>
       <c r="D552" t="n">
-        <v>181.3882635744458</v>
+        <v>181.3882781301977</v>
       </c>
       <c r="E552" t="n">
-        <v>181.3882635744458</v>
+        <v>181.3882781301977</v>
       </c>
       <c r="F552" t="n">
         <v>595900</v>
@@ -11472,16 +11472,16 @@
         <v>44032</v>
       </c>
       <c r="B553" t="n">
-        <v>196.0197143554688</v>
+        <v>196.0196990966797</v>
       </c>
       <c r="C553" t="n">
-        <v>197.77787660506</v>
+        <v>197.7778612094101</v>
       </c>
       <c r="D553" t="n">
-        <v>189.1956822003815</v>
+        <v>189.1956674727965</v>
       </c>
       <c r="E553" t="n">
-        <v>190.7154446877005</v>
+        <v>190.7154298418124</v>
       </c>
       <c r="F553" t="n">
         <v>643066</v>
@@ -11492,16 +11492,16 @@
         <v>44033</v>
       </c>
       <c r="B554" t="n">
-        <v>195.1853179931641</v>
+        <v>195.1853332519531</v>
       </c>
       <c r="C554" t="n">
-        <v>198.5824346859968</v>
+        <v>198.5824502103585</v>
       </c>
       <c r="D554" t="n">
-        <v>190.506823549418</v>
+        <v>190.5068384424615</v>
       </c>
       <c r="E554" t="n">
-        <v>196.0494924135241</v>
+        <v>196.0495077398707</v>
       </c>
       <c r="F554" t="n">
         <v>627900</v>
@@ -11512,16 +11512,16 @@
         <v>44034</v>
       </c>
       <c r="B555" t="n">
-        <v>193.9933471679688</v>
+        <v>193.9933624267578</v>
       </c>
       <c r="C555" t="n">
-        <v>197.9268442756138</v>
+        <v>197.926859843797</v>
       </c>
       <c r="D555" t="n">
-        <v>191.4306068551939</v>
+        <v>191.4306219124074</v>
       </c>
       <c r="E555" t="n">
-        <v>195.2151136014509</v>
+        <v>195.2151289563396</v>
       </c>
       <c r="F555" t="n">
         <v>664000</v>
@@ -11532,16 +11532,16 @@
         <v>44035</v>
       </c>
       <c r="B556" t="n">
-        <v>191.6392059326172</v>
+        <v>191.6391906738281</v>
       </c>
       <c r="C556" t="n">
-        <v>196.6752926716999</v>
+        <v>196.6752770119251</v>
       </c>
       <c r="D556" t="n">
-        <v>190.0002512230334</v>
+        <v>190.000236094742</v>
       </c>
       <c r="E556" t="n">
-        <v>194.8277362857887</v>
+        <v>194.8277207731209</v>
       </c>
       <c r="F556" t="n">
         <v>517766</v>
@@ -11552,16 +11552,16 @@
         <v>44036</v>
       </c>
       <c r="B557" t="n">
-        <v>195.7515258789062</v>
+        <v>195.7514953613281</v>
       </c>
       <c r="C557" t="n">
-        <v>196.0793198839435</v>
+        <v>196.0792893152624</v>
       </c>
       <c r="D557" t="n">
-        <v>188.0335207704287</v>
+        <v>188.0334914560843</v>
       </c>
       <c r="E557" t="n">
-        <v>192.7120007589094</v>
+        <v>192.7119707151919</v>
       </c>
       <c r="F557" t="n">
         <v>615366</v>
@@ -11592,16 +11592,16 @@
         <v>44040</v>
       </c>
       <c r="B559" t="n">
-        <v>194.2317352294922</v>
+        <v>194.2317657470703</v>
       </c>
       <c r="C559" t="n">
-        <v>195.9005030904659</v>
+        <v>195.9005338702399</v>
       </c>
       <c r="D559" t="n">
-        <v>188.7188795654674</v>
+        <v>188.7189092168689</v>
       </c>
       <c r="E559" t="n">
-        <v>190.7154262273731</v>
+        <v>190.7154561924708</v>
       </c>
       <c r="F559" t="n">
         <v>415300</v>
@@ -11612,16 +11612,16 @@
         <v>44041</v>
       </c>
       <c r="B560" t="n">
-        <v>195.1853179931641</v>
+        <v>195.1853332519531</v>
       </c>
       <c r="C560" t="n">
-        <v>196.6752822526539</v>
+        <v>196.6752976279222</v>
       </c>
       <c r="D560" t="n">
-        <v>193.3973578504363</v>
+        <v>193.3973729694499</v>
       </c>
       <c r="E560" t="n">
-        <v>195.4535158037483</v>
+        <v>195.4535310835039</v>
       </c>
       <c r="F560" t="n">
         <v>374733</v>
@@ -11672,16 +11672,16 @@
         <v>44046</v>
       </c>
       <c r="B563" t="n">
-        <v>194.3211364746094</v>
+        <v>194.3211517333984</v>
       </c>
       <c r="C563" t="n">
-        <v>196.7646692831627</v>
+        <v>196.7646847338267</v>
       </c>
       <c r="D563" t="n">
-        <v>190.1790226466353</v>
+        <v>190.1790375801708</v>
       </c>
       <c r="E563" t="n">
-        <v>196.049485252196</v>
+        <v>196.0495006467012</v>
       </c>
       <c r="F563" t="n">
         <v>823000</v>
@@ -11692,16 +11692,16 @@
         <v>44047</v>
       </c>
       <c r="B564" t="n">
-        <v>191.1922302246094</v>
+        <v>191.1922149658203</v>
       </c>
       <c r="C564" t="n">
-        <v>194.7979489729283</v>
+        <v>194.7979334263718</v>
       </c>
       <c r="D564" t="n">
-        <v>188.8976874417525</v>
+        <v>188.8976723660878</v>
       </c>
       <c r="E564" t="n">
-        <v>193.4271768557092</v>
+        <v>193.4271614185521</v>
       </c>
       <c r="F564" t="n">
         <v>411633</v>
@@ -11712,16 +11712,16 @@
         <v>44048</v>
       </c>
       <c r="B565" t="n">
-        <v>194.4999389648438</v>
+        <v>194.4999694824219</v>
       </c>
       <c r="C565" t="n">
-        <v>198.075859378189</v>
+        <v>198.0758904568389</v>
       </c>
       <c r="D565" t="n">
-        <v>193.0993688732251</v>
+        <v>193.09939917105</v>
       </c>
       <c r="E565" t="n">
-        <v>193.3675666934012</v>
+        <v>193.367597033307</v>
       </c>
       <c r="F565" t="n">
         <v>503800</v>
@@ -11772,16 +11772,16 @@
         <v>44053</v>
       </c>
       <c r="B568" t="n">
-        <v>191.9074096679688</v>
+        <v>191.9073791503906</v>
       </c>
       <c r="C568" t="n">
-        <v>197.0030927124582</v>
+        <v>197.0030613845523</v>
       </c>
       <c r="D568" t="n">
-        <v>191.0432351752126</v>
+        <v>191.0432047950576</v>
       </c>
       <c r="E568" t="n">
-        <v>195.3641227956948</v>
+        <v>195.3640917284218</v>
       </c>
       <c r="F568" t="n">
         <v>446333</v>
@@ -11832,16 +11832,16 @@
         <v>44056</v>
       </c>
       <c r="B571" t="n">
-        <v>186.5733337402344</v>
+        <v>186.5733489990234</v>
       </c>
       <c r="C571" t="n">
-        <v>190.9240192427385</v>
+        <v>190.9240348573458</v>
       </c>
       <c r="D571" t="n">
-        <v>184.6363831579516</v>
+        <v>184.6363982583284</v>
       </c>
       <c r="E571" t="n">
-        <v>184.8449696747432</v>
+        <v>184.844984792179</v>
       </c>
       <c r="F571" t="n">
         <v>646800</v>
@@ -11872,16 +11872,16 @@
         <v>44060</v>
       </c>
       <c r="B573" t="n">
-        <v>186.0965423583984</v>
+        <v>186.0965576171875</v>
       </c>
       <c r="C573" t="n">
-        <v>193.0397661179825</v>
+        <v>193.0397819460739</v>
       </c>
       <c r="D573" t="n">
-        <v>183.0272044600494</v>
+        <v>183.0272194671714</v>
       </c>
       <c r="E573" t="n">
-        <v>191.877595812602</v>
+        <v>191.8776115454024</v>
       </c>
       <c r="F573" t="n">
         <v>389400</v>
@@ -11912,16 +11912,16 @@
         <v>44062</v>
       </c>
       <c r="B575" t="n">
-        <v>184.6959533691406</v>
+        <v>184.6959991455078</v>
       </c>
       <c r="C575" t="n">
-        <v>188.3612675022022</v>
+        <v>188.3613141870071</v>
       </c>
       <c r="D575" t="n">
-        <v>183.7721677401152</v>
+        <v>183.7722132875247</v>
       </c>
       <c r="E575" t="n">
-        <v>187.7354777263042</v>
+        <v>187.7355242560089</v>
       </c>
       <c r="F575" t="n">
         <v>275166</v>
@@ -11932,16 +11932,16 @@
         <v>44063</v>
       </c>
       <c r="B576" t="n">
-        <v>185.1429595947266</v>
+        <v>185.1429748535156</v>
       </c>
       <c r="C576" t="n">
-        <v>189.3744526653612</v>
+        <v>189.374468272894</v>
       </c>
       <c r="D576" t="n">
-        <v>180.0174788680197</v>
+        <v>180.0174937043858</v>
       </c>
       <c r="E576" t="n">
-        <v>180.5240764201374</v>
+        <v>180.5240912982554</v>
       </c>
       <c r="F576" t="n">
         <v>586600</v>
@@ -11952,16 +11952,16 @@
         <v>44064</v>
       </c>
       <c r="B577" t="n">
-        <v>186.5733337402344</v>
+        <v>186.5733489990234</v>
       </c>
       <c r="C577" t="n">
-        <v>188.1228942060606</v>
+        <v>188.1229095915795</v>
       </c>
       <c r="D577" t="n">
-        <v>182.9080190924604</v>
+        <v>182.908034051484</v>
       </c>
       <c r="E577" t="n">
-        <v>184.7555754532611</v>
+        <v>184.7555905633859</v>
       </c>
       <c r="F577" t="n">
         <v>431666</v>
@@ -11992,16 +11992,16 @@
         <v>44068</v>
       </c>
       <c r="B579" t="n">
-        <v>186.2455596923828</v>
+        <v>186.2455444335938</v>
       </c>
       <c r="C579" t="n">
-        <v>189.046685028671</v>
+        <v>189.0466695403904</v>
       </c>
       <c r="D579" t="n">
-        <v>184.4575992879955</v>
+        <v>184.457584175691</v>
       </c>
       <c r="E579" t="n">
-        <v>186.5137575422165</v>
+        <v>186.5137422614545</v>
       </c>
       <c r="F579" t="n">
         <v>543433</v>
@@ -12012,16 +12012,16 @@
         <v>44069</v>
       </c>
       <c r="B580" t="n">
-        <v>186.0369567871094</v>
+        <v>186.0369415283203</v>
       </c>
       <c r="C580" t="n">
-        <v>191.0134478100261</v>
+        <v>191.0134321430643</v>
       </c>
       <c r="D580" t="n">
-        <v>182.5206473119266</v>
+        <v>182.520632341546</v>
       </c>
       <c r="E580" t="n">
-        <v>186.6627467137522</v>
+        <v>186.6627314036357</v>
       </c>
       <c r="F580" t="n">
         <v>788933</v>
@@ -12052,16 +12052,16 @@
         <v>44071</v>
       </c>
       <c r="B582" t="n">
-        <v>192.1458129882812</v>
+        <v>192.1457977294922</v>
       </c>
       <c r="C582" t="n">
-        <v>192.1458129882812</v>
+        <v>192.1457977294922</v>
       </c>
       <c r="D582" t="n">
-        <v>187.1991202278299</v>
+        <v>187.1991053618704</v>
       </c>
       <c r="E582" t="n">
-        <v>188.9274844020878</v>
+        <v>188.9274693988745</v>
       </c>
       <c r="F582" t="n">
         <v>688066</v>
@@ -12072,16 +12072,16 @@
         <v>44074</v>
       </c>
       <c r="B583" t="n">
-        <v>192.8907928466797</v>
+        <v>192.8907775878906</v>
       </c>
       <c r="C583" t="n">
-        <v>194.8873396779618</v>
+        <v>194.8873242612342</v>
       </c>
       <c r="D583" t="n">
-        <v>189.0466744041134</v>
+        <v>189.0466594494166</v>
       </c>
       <c r="E583" t="n">
-        <v>191.9968051163775</v>
+        <v>191.9967899283081</v>
       </c>
       <c r="F583" t="n">
         <v>944966</v>
@@ -12132,16 +12132,16 @@
         <v>44077</v>
       </c>
       <c r="B586" t="n">
-        <v>199.3572235107422</v>
+        <v>199.3572082519531</v>
       </c>
       <c r="C586" t="n">
-        <v>204.6018967184463</v>
+        <v>204.6018810582302</v>
       </c>
       <c r="D586" t="n">
-        <v>196.5858965371773</v>
+        <v>196.5858814905054</v>
       </c>
       <c r="E586" t="n">
-        <v>202.0391562624793</v>
+        <v>202.0391407984153</v>
       </c>
       <c r="F586" t="n">
         <v>527733</v>
@@ -12152,16 +12152,16 @@
         <v>44078</v>
       </c>
       <c r="B587" t="n">
-        <v>197.8970642089844</v>
+        <v>197.8970794677734</v>
       </c>
       <c r="C587" t="n">
-        <v>203.1417376008307</v>
+        <v>203.1417532640086</v>
       </c>
       <c r="D587" t="n">
-        <v>194.6489376248939</v>
+        <v>194.6489526332372</v>
       </c>
       <c r="E587" t="n">
-        <v>200.2512182300084</v>
+        <v>200.2512336703138</v>
       </c>
       <c r="F587" t="n">
         <v>642700</v>
@@ -12172,16 +12172,16 @@
         <v>44082</v>
       </c>
       <c r="B588" t="n">
-        <v>200.6684112548828</v>
+        <v>200.6683959960938</v>
       </c>
       <c r="C588" t="n">
-        <v>207.7904393255396</v>
+        <v>207.7904235251929</v>
       </c>
       <c r="D588" t="n">
-        <v>198.3142571773322</v>
+        <v>198.3142420975526</v>
       </c>
       <c r="E588" t="n">
-        <v>198.4632627125554</v>
+        <v>198.4632476214454</v>
       </c>
       <c r="F588" t="n">
         <v>1005833</v>
@@ -12212,16 +12212,16 @@
         <v>44084</v>
       </c>
       <c r="B590" t="n">
-        <v>195.1853179931641</v>
+        <v>195.1853332519531</v>
       </c>
       <c r="C590" t="n">
-        <v>205.7938562455153</v>
+        <v>205.7938723336365</v>
       </c>
       <c r="D590" t="n">
-        <v>193.7549498789818</v>
+        <v>193.7549650259506</v>
       </c>
       <c r="E590" t="n">
-        <v>205.6746639549002</v>
+        <v>205.6746800337034</v>
       </c>
       <c r="F590" t="n">
         <v>559966</v>
@@ -12272,16 +12272,16 @@
         <v>44089</v>
       </c>
       <c r="B593" t="n">
-        <v>197.2733154296875</v>
+        <v>197.2733001708984</v>
       </c>
       <c r="C593" t="n">
-        <v>199.0653546966144</v>
+        <v>199.0653392992138</v>
       </c>
       <c r="D593" t="n">
-        <v>191.8076146546597</v>
+        <v>191.8075998186343</v>
       </c>
       <c r="E593" t="n">
-        <v>199.0056225862634</v>
+        <v>199.005607193483</v>
       </c>
       <c r="F593" t="n">
         <v>591666</v>
@@ -12292,16 +12292,16 @@
         <v>44090</v>
       </c>
       <c r="B594" t="n">
-        <v>197.8407745361328</v>
+        <v>197.8408050537109</v>
       </c>
       <c r="C594" t="n">
-        <v>202.7688704709959</v>
+        <v>202.7689017487487</v>
       </c>
       <c r="D594" t="n">
-        <v>196.7954171702461</v>
+        <v>196.7954475265745</v>
       </c>
       <c r="E594" t="n">
-        <v>198.9458640044226</v>
+        <v>198.9458946924643</v>
       </c>
       <c r="F594" t="n">
         <v>602300</v>
@@ -12332,16 +12332,16 @@
         <v>44092</v>
       </c>
       <c r="B596" t="n">
-        <v>187.3872375488281</v>
+        <v>187.3872528076172</v>
       </c>
       <c r="C596" t="n">
-        <v>192.9724171801275</v>
+        <v>192.9724328937132</v>
       </c>
       <c r="D596" t="n">
-        <v>185.4757342513885</v>
+        <v>185.4757493545254</v>
       </c>
       <c r="E596" t="n">
-        <v>192.225735492474</v>
+        <v>192.225751145258</v>
       </c>
       <c r="F596" t="n">
         <v>571800</v>
@@ -12352,16 +12352,16 @@
         <v>44095</v>
       </c>
       <c r="B597" t="n">
-        <v>187.8949890136719</v>
+        <v>187.8949737548828</v>
       </c>
       <c r="C597" t="n">
-        <v>188.1936647482672</v>
+        <v>188.193649465223</v>
       </c>
       <c r="D597" t="n">
-        <v>182.847428344998</v>
+        <v>182.847413496117</v>
       </c>
       <c r="E597" t="n">
-        <v>186.0432176887153</v>
+        <v>186.043202580307</v>
       </c>
       <c r="F597" t="n">
         <v>424066</v>
@@ -12412,16 +12412,16 @@
         <v>44098</v>
       </c>
       <c r="B600" t="n">
-        <v>187.2677764892578</v>
+        <v>187.2677917480469</v>
       </c>
       <c r="C600" t="n">
-        <v>190.7921074300882</v>
+        <v>190.7921229760437</v>
       </c>
       <c r="D600" t="n">
-        <v>185.5354694759098</v>
+        <v>185.5354845935485</v>
       </c>
       <c r="E600" t="n">
-        <v>187.6560503657161</v>
+        <v>187.6560656561421</v>
       </c>
       <c r="F600" t="n">
         <v>378566</v>
@@ -12432,16 +12432,16 @@
         <v>44099</v>
       </c>
       <c r="B601" t="n">
-        <v>187.8352508544922</v>
+        <v>187.8352661132812</v>
       </c>
       <c r="C601" t="n">
-        <v>188.1339265794667</v>
+        <v>188.1339418625186</v>
       </c>
       <c r="D601" t="n">
-        <v>182.9967527219967</v>
+        <v>182.9967675877305</v>
       </c>
       <c r="E601" t="n">
-        <v>186.6704291992423</v>
+        <v>186.6704443634071</v>
       </c>
       <c r="F601" t="n">
         <v>316200</v>
@@ -12452,16 +12452,16 @@
         <v>44102</v>
       </c>
       <c r="B602" t="n">
-        <v>180.6372222900391</v>
+        <v>180.6372375488281</v>
       </c>
       <c r="C602" t="n">
-        <v>189.5078036968999</v>
+        <v>189.5078197050047</v>
       </c>
       <c r="D602" t="n">
-        <v>179.352921379823</v>
+        <v>179.3529365301246</v>
       </c>
       <c r="E602" t="n">
-        <v>188.9403183665075</v>
+        <v>188.9403343266758</v>
       </c>
       <c r="F602" t="n">
         <v>595500</v>
@@ -12472,16 +12472,16 @@
         <v>44103</v>
       </c>
       <c r="B603" t="n">
-        <v>180.9359283447266</v>
+        <v>180.9359130859375</v>
       </c>
       <c r="C603" t="n">
-        <v>183.5045002136614</v>
+        <v>183.5044847382582</v>
       </c>
       <c r="D603" t="n">
-        <v>178.6062697236995</v>
+        <v>178.6062546613765</v>
       </c>
       <c r="E603" t="n">
-        <v>181.2644549486086</v>
+        <v>181.2644396621141</v>
       </c>
       <c r="F603" t="n">
         <v>676133</v>
@@ -12512,16 +12512,16 @@
         <v>44105</v>
       </c>
       <c r="B605" t="n">
-        <v>188.1638031005859</v>
+        <v>188.1637878417969</v>
       </c>
       <c r="C605" t="n">
-        <v>191.1803961889597</v>
+        <v>191.1803806855457</v>
       </c>
       <c r="D605" t="n">
-        <v>183.2954386438886</v>
+        <v>183.2954237798904</v>
       </c>
       <c r="E605" t="n">
-        <v>185.923757825579</v>
+        <v>185.9237427484422</v>
       </c>
       <c r="F605" t="n">
         <v>698566</v>
@@ -12592,16 +12592,16 @@
         <v>44111</v>
       </c>
       <c r="B609" t="n">
-        <v>187.4171142578125</v>
+        <v>187.4170989990234</v>
       </c>
       <c r="C609" t="n">
-        <v>190.1648975557599</v>
+        <v>190.1648820732568</v>
       </c>
       <c r="D609" t="n">
-        <v>183.6837056072585</v>
+        <v>183.6836906524294</v>
       </c>
       <c r="E609" t="n">
-        <v>186.7600306894081</v>
+        <v>186.7600154841163</v>
       </c>
       <c r="F609" t="n">
         <v>573633</v>
@@ -12612,16 +12612,16 @@
         <v>44112</v>
       </c>
       <c r="B610" t="n">
-        <v>194.2268371582031</v>
+        <v>194.2268524169922</v>
       </c>
       <c r="C610" t="n">
-        <v>195.481272117246</v>
+        <v>195.4812874745856</v>
       </c>
       <c r="D610" t="n">
-        <v>187.4469698575246</v>
+        <v>187.4469845836759</v>
       </c>
       <c r="E610" t="n">
-        <v>188.1637854937555</v>
+        <v>188.1638002762209</v>
       </c>
       <c r="F610" t="n">
         <v>582633</v>
@@ -12632,16 +12632,16 @@
         <v>44113</v>
       </c>
       <c r="B611" t="n">
-        <v>192.8230743408203</v>
+        <v>192.8230895996094</v>
       </c>
       <c r="C611" t="n">
-        <v>196.5564828296802</v>
+        <v>196.5564983839074</v>
       </c>
       <c r="D611" t="n">
-        <v>190.4336989844612</v>
+        <v>190.4337140541703</v>
       </c>
       <c r="E611" t="n">
-        <v>194.1372414207124</v>
+        <v>194.1372567834963</v>
       </c>
       <c r="F611" t="n">
         <v>718800</v>
@@ -12692,16 +12692,16 @@
         <v>44119</v>
       </c>
       <c r="B614" t="n">
-        <v>198.4978637695312</v>
+        <v>198.4978790283203</v>
       </c>
       <c r="C614" t="n">
-        <v>201.4547244539764</v>
+        <v>201.4547399400632</v>
       </c>
       <c r="D614" t="n">
-        <v>196.9148870538109</v>
+        <v>196.9149021909145</v>
       </c>
       <c r="E614" t="n">
-        <v>199.6029532696903</v>
+        <v>199.6029686134291</v>
       </c>
       <c r="F614" t="n">
         <v>599566</v>
@@ -12712,16 +12712,16 @@
         <v>44120</v>
       </c>
       <c r="B615" t="n">
-        <v>193.1814727783203</v>
+        <v>193.1814880371094</v>
       </c>
       <c r="C615" t="n">
-        <v>198.8562655587187</v>
+        <v>198.8562812657416</v>
       </c>
       <c r="D615" t="n">
-        <v>190.0155498253865</v>
+        <v>190.0155648341094</v>
       </c>
       <c r="E615" t="n">
-        <v>198.6770540604953</v>
+        <v>198.6770697533628</v>
       </c>
       <c r="F615" t="n">
         <v>665566</v>
@@ -12752,16 +12752,16 @@
         <v>44124</v>
       </c>
       <c r="B617" t="n">
-        <v>194.2268371582031</v>
+        <v>194.2268524169922</v>
       </c>
       <c r="C617" t="n">
-        <v>195.8396647440835</v>
+        <v>195.8396801295791</v>
       </c>
       <c r="D617" t="n">
-        <v>190.6128929248125</v>
+        <v>190.612907899684</v>
       </c>
       <c r="E617" t="n">
-        <v>193.032149494911</v>
+        <v>193.0321646598434</v>
       </c>
       <c r="F617" t="n">
         <v>555666</v>
@@ -12812,16 +12812,16 @@
         <v>44127</v>
       </c>
       <c r="B620" t="n">
-        <v>190.3441162109375</v>
+        <v>190.3440856933594</v>
       </c>
       <c r="C620" t="n">
-        <v>195.242346721261</v>
+        <v>195.2423154183572</v>
       </c>
       <c r="D620" t="n">
-        <v>188.940350859762</v>
+        <v>188.9403205672475</v>
       </c>
       <c r="E620" t="n">
-        <v>194.1671231666126</v>
+        <v>194.1670920360976</v>
       </c>
       <c r="F620" t="n">
         <v>403166</v>
@@ -12852,16 +12852,16 @@
         <v>44131</v>
       </c>
       <c r="B622" t="n">
-        <v>198.3186492919922</v>
+        <v>198.3186645507812</v>
       </c>
       <c r="C622" t="n">
-        <v>204.710242589321</v>
+        <v>204.7102583398841</v>
       </c>
       <c r="D622" t="n">
-        <v>195.7500625141592</v>
+        <v>195.7500775753192</v>
       </c>
       <c r="E622" t="n">
-        <v>196.2876818257843</v>
+        <v>196.2876969283092</v>
       </c>
       <c r="F622" t="n">
         <v>606666</v>
@@ -12892,16 +12892,16 @@
         <v>44133</v>
       </c>
       <c r="B624" t="n">
-        <v>199.2743988037109</v>
+        <v>199.2744140625</v>
       </c>
       <c r="C624" t="n">
-        <v>199.8717349981709</v>
+        <v>199.871750302699</v>
       </c>
       <c r="D624" t="n">
-        <v>189.5376714786287</v>
+        <v>189.5376859918596</v>
       </c>
       <c r="E624" t="n">
-        <v>192.8529245765097</v>
+        <v>192.8529393435952</v>
       </c>
       <c r="F624" t="n">
         <v>707700</v>
@@ -12912,16 +12912,16 @@
         <v>44134</v>
       </c>
       <c r="B625" t="n">
-        <v>192.2555999755859</v>
+        <v>192.255615234375</v>
       </c>
       <c r="C625" t="n">
-        <v>199.8120149470612</v>
+        <v>199.8120308055818</v>
       </c>
       <c r="D625" t="n">
-        <v>192.2555999755859</v>
+        <v>192.255615234375</v>
       </c>
       <c r="E625" t="n">
-        <v>198.6471933467818</v>
+        <v>198.6472091128537</v>
       </c>
       <c r="F625" t="n">
         <v>632900</v>
@@ -12952,16 +12952,16 @@
         <v>44139</v>
       </c>
       <c r="B627" t="n">
-        <v>205.3076019287109</v>
+        <v>205.3076171875</v>
       </c>
       <c r="C627" t="n">
-        <v>208.0553851222939</v>
+        <v>208.0554005853026</v>
       </c>
       <c r="D627" t="n">
-        <v>195.9591476304417</v>
+        <v>195.9591621944386</v>
       </c>
       <c r="E627" t="n">
-        <v>196.5564838770755</v>
+        <v>196.5564984854674</v>
       </c>
       <c r="F627" t="n">
         <v>937700</v>
@@ -12972,16 +12972,16 @@
         <v>44140</v>
       </c>
       <c r="B628" t="n">
-        <v>207.9956359863281</v>
+        <v>207.9956512451172</v>
       </c>
       <c r="C628" t="n">
-        <v>214.8949822450603</v>
+        <v>214.894998009993</v>
       </c>
       <c r="D628" t="n">
-        <v>206.4425406044565</v>
+        <v>206.4425557493087</v>
       </c>
       <c r="E628" t="n">
-        <v>206.9801447015363</v>
+        <v>206.9801598858278</v>
       </c>
       <c r="F628" t="n">
         <v>801700</v>
@@ -12992,16 +12992,16 @@
         <v>44141</v>
       </c>
       <c r="B629" t="n">
-        <v>213.5509490966797</v>
+        <v>213.5509643554688</v>
       </c>
       <c r="C629" t="n">
-        <v>214.2378986362663</v>
+        <v>214.2379139441398</v>
       </c>
       <c r="D629" t="n">
-        <v>205.1881208029708</v>
+        <v>205.1881354642133</v>
       </c>
       <c r="E629" t="n">
-        <v>206.8308143348961</v>
+        <v>206.8308291135134</v>
       </c>
       <c r="F629" t="n">
         <v>849833</v>
@@ -13012,16 +13012,16 @@
         <v>44144</v>
       </c>
       <c r="B630" t="n">
-        <v>208.5332641601562</v>
+        <v>208.5332489013672</v>
       </c>
       <c r="C630" t="n">
-        <v>226.0653517136236</v>
+        <v>226.0653351719772</v>
       </c>
       <c r="D630" t="n">
-        <v>207.7865824333327</v>
+        <v>207.7865672291798</v>
       </c>
       <c r="E630" t="n">
-        <v>221.0177911397615</v>
+        <v>221.0177749674551</v>
       </c>
       <c r="F630" t="n">
         <v>887833</v>
@@ -13052,16 +13052,16 @@
         <v>44146</v>
       </c>
       <c r="B632" t="n">
-        <v>204.5907897949219</v>
+        <v>204.5908050537109</v>
       </c>
       <c r="C632" t="n">
-        <v>206.5620252678551</v>
+        <v>206.5620406736629</v>
       </c>
       <c r="D632" t="n">
-        <v>200.7379170088981</v>
+        <v>200.7379319803322</v>
       </c>
       <c r="E632" t="n">
-        <v>202.9779621526382</v>
+        <v>202.9779772911393</v>
       </c>
       <c r="F632" t="n">
         <v>574366</v>
@@ -13092,16 +13092,16 @@
         <v>44148</v>
       </c>
       <c r="B634" t="n">
-        <v>218.897216796875</v>
+        <v>218.8972015380859</v>
       </c>
       <c r="C634" t="n">
-        <v>220.6593899790492</v>
+        <v>220.6593745974234</v>
       </c>
       <c r="D634" t="n">
-        <v>209.9370358039121</v>
+        <v>209.9370211697153</v>
       </c>
       <c r="E634" t="n">
-        <v>209.9370358039121</v>
+        <v>209.9370211697153</v>
       </c>
       <c r="F634" t="n">
         <v>872100</v>
@@ -13152,16 +13152,16 @@
         <v>44153</v>
       </c>
       <c r="B637" t="n">
-        <v>213.1029510498047</v>
+        <v>213.1029663085938</v>
       </c>
       <c r="C637" t="n">
-        <v>217.4336956087137</v>
+        <v>217.4337111775966</v>
       </c>
       <c r="D637" t="n">
-        <v>213.1029510498047</v>
+        <v>213.1029663085938</v>
       </c>
       <c r="E637" t="n">
-        <v>216.8662254405929</v>
+        <v>216.8662409688433</v>
       </c>
       <c r="F637" t="n">
         <v>504433</v>
@@ -13172,16 +13172,16 @@
         <v>44154</v>
       </c>
       <c r="B638" t="n">
-        <v>213.1626892089844</v>
+        <v>213.1627044677734</v>
       </c>
       <c r="C638" t="n">
-        <v>215.4326003285149</v>
+        <v>215.4326157497906</v>
       </c>
       <c r="D638" t="n">
-        <v>209.9668848955181</v>
+        <v>209.9668999255425</v>
       </c>
       <c r="E638" t="n">
-        <v>213.81977274129</v>
+        <v>213.819788047115</v>
       </c>
       <c r="F638" t="n">
         <v>672366</v>
@@ -13192,16 +13192,16 @@
         <v>44158</v>
       </c>
       <c r="B639" t="n">
-        <v>215.3430023193359</v>
+        <v>215.3429870605469</v>
       </c>
       <c r="C639" t="n">
-        <v>217.9115891545185</v>
+        <v>217.9115737137244</v>
       </c>
       <c r="D639" t="n">
-        <v>212.326409508648</v>
+        <v>212.3263944636089</v>
       </c>
       <c r="E639" t="n">
-        <v>213.5509632260367</v>
+        <v>213.5509480942281</v>
       </c>
       <c r="F639" t="n">
         <v>541300</v>
@@ -13212,16 +13212,16 @@
         <v>44159</v>
       </c>
       <c r="B640" t="n">
-        <v>214.8053894042969</v>
+        <v>214.8053741455078</v>
       </c>
       <c r="C640" t="n">
-        <v>216.477964338369</v>
+        <v>216.4779489607679</v>
       </c>
       <c r="D640" t="n">
-        <v>212.2965497901061</v>
+        <v>212.2965347095335</v>
       </c>
       <c r="E640" t="n">
-        <v>214.2379192027341</v>
+        <v>214.2379039842555</v>
       </c>
       <c r="F640" t="n">
         <v>404100</v>
@@ -13232,16 +13232,16 @@
         <v>44160</v>
       </c>
       <c r="B641" t="n">
-        <v>216.8363800048828</v>
+        <v>216.8363647460938</v>
       </c>
       <c r="C641" t="n">
-        <v>220.4204432366713</v>
+        <v>220.4204277256715</v>
       </c>
       <c r="D641" t="n">
-        <v>214.745665059547</v>
+        <v>214.7456499478817</v>
       </c>
       <c r="E641" t="n">
-        <v>215.0443407933491</v>
+        <v>215.044325660666</v>
       </c>
       <c r="F641" t="n">
         <v>311466</v>
@@ -13252,16 +13252,16 @@
         <v>44161</v>
       </c>
       <c r="B642" t="n">
-        <v>212.8042907714844</v>
+        <v>212.8043060302734</v>
       </c>
       <c r="C642" t="n">
-        <v>218.6284142796364</v>
+        <v>218.6284299560349</v>
       </c>
       <c r="D642" t="n">
-        <v>210.265569878411</v>
+        <v>210.2655849551651</v>
       </c>
       <c r="E642" t="n">
-        <v>216.3883691136208</v>
+        <v>216.3883846294004</v>
       </c>
       <c r="F642" t="n">
         <v>253146</v>
@@ -13292,16 +13292,16 @@
         <v>44165</v>
       </c>
       <c r="B644" t="n">
-        <v>215.3430023193359</v>
+        <v>215.3429870605469</v>
       </c>
       <c r="C644" t="n">
-        <v>217.5830473881405</v>
+        <v>217.5830319706262</v>
       </c>
       <c r="D644" t="n">
-        <v>209.9668850394382</v>
+        <v>209.9668701615904</v>
       </c>
       <c r="E644" t="n">
-        <v>214.2976449156382</v>
+        <v>214.2976297309212</v>
       </c>
       <c r="F644" t="n">
         <v>990433</v>
@@ -13312,16 +13312,16 @@
         <v>44166</v>
       </c>
       <c r="B645" t="n">
-        <v>215.3430023193359</v>
+        <v>215.3429870605469</v>
       </c>
       <c r="C645" t="n">
-        <v>219.8230924569451</v>
+        <v>219.8230768807055</v>
       </c>
       <c r="D645" t="n">
-        <v>212.8042815364352</v>
+        <v>212.804266457535</v>
       </c>
       <c r="E645" t="n">
-        <v>216.2390142703466</v>
+        <v>216.2389989480679</v>
       </c>
       <c r="F645" t="n">
         <v>896293</v>
@@ -13352,16 +13352,16 @@
         <v>44168</v>
       </c>
       <c r="B647" t="n">
-        <v>226.3938903808594</v>
+        <v>226.3938751220703</v>
       </c>
       <c r="C647" t="n">
-        <v>229.8286384300032</v>
+        <v>229.8286229397145</v>
       </c>
       <c r="D647" t="n">
-        <v>219.9724306568018</v>
+        <v>219.9724158308146</v>
       </c>
       <c r="E647" t="n">
-        <v>219.9724306568018</v>
+        <v>219.9724158308146</v>
       </c>
       <c r="F647" t="n">
         <v>476626</v>
@@ -13432,16 +13432,16 @@
         <v>44174</v>
       </c>
       <c r="B651" t="n">
-        <v>225.4978637695312</v>
+        <v>225.4978790283203</v>
       </c>
       <c r="C651" t="n">
-        <v>232.0686685254193</v>
+        <v>232.0686842288357</v>
       </c>
       <c r="D651" t="n">
-        <v>222.6604673541984</v>
+        <v>222.660482420989</v>
       </c>
       <c r="E651" t="n">
-        <v>229.9779537781974</v>
+        <v>229.9779693401412</v>
       </c>
       <c r="F651" t="n">
         <v>560820</v>
@@ -13452,16 +13452,16 @@
         <v>44175</v>
       </c>
       <c r="B652" t="n">
-        <v>227.8872680664062</v>
+        <v>227.8872528076172</v>
       </c>
       <c r="C652" t="n">
-        <v>233.4127161526883</v>
+        <v>233.4127005239284</v>
       </c>
       <c r="D652" t="n">
-        <v>225.6472227766659</v>
+        <v>225.6472076678649</v>
       </c>
       <c r="E652" t="n">
-        <v>226.6925802834673</v>
+        <v>226.6925651046716</v>
       </c>
       <c r="F652" t="n">
         <v>713620</v>
@@ -13532,16 +13532,16 @@
         <v>44181</v>
       </c>
       <c r="B656" t="n">
-        <v>230.4259490966797</v>
+        <v>230.4259796142578</v>
       </c>
       <c r="C656" t="n">
-        <v>232.9646696892409</v>
+        <v>232.9647005430468</v>
       </c>
       <c r="D656" t="n">
-        <v>225.1991776613442</v>
+        <v>225.1992074866895</v>
       </c>
       <c r="E656" t="n">
-        <v>227.2898923119891</v>
+        <v>227.2899224142283</v>
       </c>
       <c r="F656" t="n">
         <v>398466</v>
@@ -13652,16 +13652,16 @@
         <v>44193</v>
       </c>
       <c r="B662" t="n">
-        <v>226.3938903808594</v>
+        <v>226.3938751220703</v>
       </c>
       <c r="C662" t="n">
-        <v>227.588593280359</v>
+        <v>227.5885779410478</v>
       </c>
       <c r="D662" t="n">
-        <v>222.8098272561957</v>
+        <v>222.80981223897</v>
       </c>
       <c r="E662" t="n">
-        <v>225.3485481307148</v>
+        <v>225.3485329423811</v>
       </c>
       <c r="F662" t="n">
         <v>229633</v>
@@ -13692,16 +13692,16 @@
         <v>44195</v>
       </c>
       <c r="B664" t="n">
-        <v>227.8872680664062</v>
+        <v>227.8872528076172</v>
       </c>
       <c r="C664" t="n">
-        <v>235.6527614424286</v>
+        <v>235.6527456636806</v>
       </c>
       <c r="D664" t="n">
-        <v>225.9458985202205</v>
+        <v>225.9458833914209</v>
       </c>
       <c r="E664" t="n">
-        <v>234.1593979159351</v>
+        <v>234.1593822371791</v>
       </c>
       <c r="F664" t="n">
         <v>659613</v>
@@ -13712,16 +13712,16 @@
         <v>44200</v>
       </c>
       <c r="B665" t="n">
-        <v>224.6018524169922</v>
+        <v>224.6018676757812</v>
       </c>
       <c r="C665" t="n">
-        <v>231.6206479621102</v>
+        <v>231.6206636977356</v>
       </c>
       <c r="D665" t="n">
-        <v>220.4204229118868</v>
+        <v>220.4204378866018</v>
       </c>
       <c r="E665" t="n">
-        <v>230.1272846220805</v>
+        <v>230.1273002562511</v>
       </c>
       <c r="F665" t="n">
         <v>564553</v>
@@ -13732,16 +13732,16 @@
         <v>44201</v>
       </c>
       <c r="B666" t="n">
-        <v>218.7777404785156</v>
+        <v>218.7777252197266</v>
       </c>
       <c r="C666" t="n">
-        <v>225.6472061166881</v>
+        <v>225.6471903787839</v>
       </c>
       <c r="D666" t="n">
-        <v>218.1803890355101</v>
+        <v>218.1803738183837</v>
       </c>
       <c r="E666" t="n">
-        <v>224.9005244085703</v>
+        <v>224.9005087227439</v>
       </c>
       <c r="F666" t="n">
         <v>585466</v>
@@ -13772,16 +13772,16 @@
         <v>44203</v>
       </c>
       <c r="B668" t="n">
-        <v>213.2522888183594</v>
+        <v>213.2523040771484</v>
       </c>
       <c r="C668" t="n">
-        <v>217.2843730051644</v>
+        <v>217.2843885524602</v>
       </c>
       <c r="D668" t="n">
-        <v>207.1295050026288</v>
+        <v>207.1295198233158</v>
       </c>
       <c r="E668" t="n">
-        <v>211.4602497140818</v>
+        <v>211.4602648446455</v>
       </c>
       <c r="F668" t="n">
         <v>485820</v>
@@ -42092,19 +42092,39 @@
         <v>46279</v>
       </c>
       <c r="B2084" t="n">
-        <v>6.72</v>
+        <v>6.71999979019165</v>
       </c>
       <c r="C2084" t="n">
-        <v>6.83</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="D2084" t="n">
         <v>6.5</v>
       </c>
       <c r="E2084" t="n">
-        <v>6.62</v>
+        <v>6.619999885559082</v>
       </c>
       <c r="F2084" t="n">
         <v>7714500</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2085" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>8419600</v>
       </c>
     </row>
   </sheetData>

--- a/database/HAPV3.xlsx
+++ b/database/HAPV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2085"/>
+  <dimension ref="A1:F2086"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43216</v>
       </c>
       <c r="B2" t="n">
-        <v>81.53694152832031</v>
+        <v>81.53695678710938</v>
       </c>
       <c r="C2" t="n">
-        <v>85.66650989807103</v>
+        <v>85.66652592966578</v>
       </c>
       <c r="D2" t="n">
-        <v>79.57467127971712</v>
+        <v>79.57468617128777</v>
       </c>
       <c r="E2" t="n">
-        <v>84.93431750577982</v>
+        <v>84.9343334003524</v>
       </c>
       <c r="F2" t="n">
         <v>1956933</v>
@@ -472,16 +472,16 @@
         <v>43217</v>
       </c>
       <c r="B3" t="n">
-        <v>82.00554656982422</v>
+        <v>82.00556182861328</v>
       </c>
       <c r="C3" t="n">
-        <v>83.90924377875386</v>
+        <v>83.90925939176427</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54116180964878</v>
+        <v>80.54117679595947</v>
       </c>
       <c r="E3" t="n">
-        <v>81.97626006634007</v>
+        <v>81.9762753196798</v>
       </c>
       <c r="F3" t="n">
         <v>932166</v>
@@ -492,16 +492,16 @@
         <v>43220</v>
       </c>
       <c r="B4" t="n">
-        <v>80.98049163818359</v>
+        <v>80.98048400878906</v>
       </c>
       <c r="C4" t="n">
-        <v>82.00556416960269</v>
+        <v>82.00555644363325</v>
       </c>
       <c r="D4" t="n">
-        <v>80.68761909224075</v>
+        <v>80.68761149043854</v>
       </c>
       <c r="E4" t="n">
-        <v>81.56624417831694</v>
+        <v>81.56623649373705</v>
       </c>
       <c r="F4" t="n">
         <v>370366</v>
@@ -532,16 +532,16 @@
         <v>43223</v>
       </c>
       <c r="B6" t="n">
-        <v>80.51188659667969</v>
+        <v>80.51187896728516</v>
       </c>
       <c r="C6" t="n">
-        <v>81.71267809739771</v>
+        <v>81.71267035421486</v>
       </c>
       <c r="D6" t="n">
-        <v>78.49103564217513</v>
+        <v>78.49102820427865</v>
       </c>
       <c r="E6" t="n">
-        <v>79.39895461873498</v>
+        <v>79.39894709480311</v>
       </c>
       <c r="F6" t="n">
         <v>790600</v>
@@ -552,16 +552,16 @@
         <v>43224</v>
       </c>
       <c r="B7" t="n">
-        <v>78.3446044921875</v>
+        <v>78.34459686279297</v>
       </c>
       <c r="C7" t="n">
-        <v>81.0390752181759</v>
+        <v>81.03906732638703</v>
       </c>
       <c r="D7" t="n">
-        <v>77.31953192140176</v>
+        <v>77.31952439183137</v>
       </c>
       <c r="E7" t="n">
-        <v>81.0390752181759</v>
+        <v>81.03906732638703</v>
       </c>
       <c r="F7" t="n">
         <v>632800</v>
@@ -572,16 +572,16 @@
         <v>43227</v>
       </c>
       <c r="B8" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C8" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="D8" t="n">
-        <v>77.90527738914264</v>
+        <v>77.90526987277661</v>
       </c>
       <c r="E8" t="n">
-        <v>78.05171737852535</v>
+        <v>78.05170984803067</v>
       </c>
       <c r="F8" t="n">
         <v>375200</v>
@@ -592,16 +592,16 @@
         <v>43228</v>
       </c>
       <c r="B9" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C9" t="n">
-        <v>79.95542234400601</v>
+        <v>79.95541462984029</v>
       </c>
       <c r="D9" t="n">
-        <v>78.49103734667347</v>
+        <v>78.49102977379283</v>
       </c>
       <c r="E9" t="n">
-        <v>79.51610237585788</v>
+        <v>79.51609470407813</v>
       </c>
       <c r="F9" t="n">
         <v>315733</v>
@@ -652,16 +652,16 @@
         <v>43231</v>
       </c>
       <c r="B12" t="n">
-        <v>80.83406066894531</v>
+        <v>80.83404541015625</v>
       </c>
       <c r="C12" t="n">
-        <v>82.59132593385111</v>
+        <v>82.59131034334867</v>
       </c>
       <c r="D12" t="n">
-        <v>80.48261506421264</v>
+        <v>80.48259987176485</v>
       </c>
       <c r="E12" t="n">
-        <v>80.51190157725298</v>
+        <v>80.51188637927687</v>
       </c>
       <c r="F12" t="n">
         <v>586000</v>
@@ -672,16 +672,16 @@
         <v>43234</v>
       </c>
       <c r="B13" t="n">
-        <v>80.01399993896484</v>
+        <v>80.01399230957031</v>
       </c>
       <c r="C13" t="n">
-        <v>81.82983803542157</v>
+        <v>81.82983023288553</v>
       </c>
       <c r="D13" t="n">
-        <v>80.01399993896484</v>
+        <v>80.01399230957031</v>
       </c>
       <c r="E13" t="n">
-        <v>81.68339803765939</v>
+        <v>81.6833902490865</v>
       </c>
       <c r="F13" t="n">
         <v>350433</v>
@@ -772,16 +772,16 @@
         <v>43241</v>
       </c>
       <c r="B18" t="n">
-        <v>90.20611572265625</v>
+        <v>90.20610809326172</v>
       </c>
       <c r="C18" t="n">
-        <v>91.05545423914081</v>
+        <v>91.05544653791148</v>
       </c>
       <c r="D18" t="n">
-        <v>84.93432833627266</v>
+        <v>84.93432115275195</v>
       </c>
       <c r="E18" t="n">
-        <v>86.9844658064643</v>
+        <v>86.98445844954838</v>
       </c>
       <c r="F18" t="n">
         <v>633933</v>
@@ -792,16 +792,16 @@
         <v>43242</v>
       </c>
       <c r="B19" t="n">
-        <v>95.91722106933594</v>
+        <v>95.91720581054688</v>
       </c>
       <c r="C19" t="n">
-        <v>96.06366106443481</v>
+        <v>96.06364578234965</v>
       </c>
       <c r="D19" t="n">
-        <v>90.2061208464601</v>
+        <v>90.20610649620939</v>
       </c>
       <c r="E19" t="n">
-        <v>90.2061208464601</v>
+        <v>90.20610649620939</v>
       </c>
       <c r="F19" t="n">
         <v>462766</v>
@@ -812,16 +812,16 @@
         <v>43243</v>
       </c>
       <c r="B20" t="n">
-        <v>95.74147796630859</v>
+        <v>95.74149322509766</v>
       </c>
       <c r="C20" t="n">
-        <v>95.9172044403123</v>
+        <v>95.91721972710775</v>
       </c>
       <c r="D20" t="n">
-        <v>90.79185763815821</v>
+        <v>90.79187210810198</v>
       </c>
       <c r="E20" t="n">
-        <v>95.9172044403123</v>
+        <v>95.91721972710775</v>
       </c>
       <c r="F20" t="n">
         <v>487666</v>
@@ -832,16 +832,16 @@
         <v>43244</v>
       </c>
       <c r="B21" t="n">
-        <v>89.32749938964844</v>
+        <v>89.32748413085938</v>
       </c>
       <c r="C21" t="n">
-        <v>93.77922812333239</v>
+        <v>93.77921210410572</v>
       </c>
       <c r="D21" t="n">
-        <v>89.09319983741467</v>
+        <v>89.09318461864831</v>
       </c>
       <c r="E21" t="n">
-        <v>93.1349024926274</v>
+        <v>93.13488658346348</v>
       </c>
       <c r="F21" t="n">
         <v>822100</v>
@@ -852,16 +852,16 @@
         <v>43245</v>
       </c>
       <c r="B22" t="n">
-        <v>90.7625732421875</v>
+        <v>90.76258087158203</v>
       </c>
       <c r="C22" t="n">
-        <v>90.87971926208031</v>
+        <v>90.879726901322</v>
       </c>
       <c r="D22" t="n">
-        <v>87.95094959281705</v>
+        <v>87.95095698586984</v>
       </c>
       <c r="E22" t="n">
-        <v>88.77100897329892</v>
+        <v>88.77101643528491</v>
       </c>
       <c r="F22" t="n">
         <v>562433</v>
@@ -972,16 +972,16 @@
         <v>43256</v>
       </c>
       <c r="B28" t="n">
-        <v>85.72509765625</v>
+        <v>85.72509002685547</v>
       </c>
       <c r="C28" t="n">
-        <v>88.15597473141518</v>
+        <v>88.15596688567655</v>
       </c>
       <c r="D28" t="n">
-        <v>84.34857959498085</v>
+        <v>84.34857208809417</v>
       </c>
       <c r="E28" t="n">
-        <v>88.15597473141518</v>
+        <v>88.15596688567655</v>
       </c>
       <c r="F28" t="n">
         <v>239700</v>
@@ -1012,16 +1012,16 @@
         <v>43258</v>
       </c>
       <c r="B30" t="n">
-        <v>80.83406066894531</v>
+        <v>80.83404541015625</v>
       </c>
       <c r="C30" t="n">
-        <v>83.41138554022331</v>
+        <v>83.41136979492082</v>
       </c>
       <c r="D30" t="n">
-        <v>78.63748281193732</v>
+        <v>78.63746796778928</v>
       </c>
       <c r="E30" t="n">
-        <v>83.41138554022331</v>
+        <v>83.41136979492082</v>
       </c>
       <c r="F30" t="n">
         <v>547066</v>
@@ -1032,16 +1032,16 @@
         <v>43259</v>
       </c>
       <c r="B31" t="n">
-        <v>80.98049163818359</v>
+        <v>80.98048400878906</v>
       </c>
       <c r="C31" t="n">
-        <v>83.14778274009986</v>
+        <v>83.14777490651888</v>
       </c>
       <c r="D31" t="n">
-        <v>79.07679402068831</v>
+        <v>79.07678657064635</v>
       </c>
       <c r="E31" t="n">
-        <v>79.75041353837787</v>
+        <v>79.75040602487236</v>
       </c>
       <c r="F31" t="n">
         <v>443000</v>
@@ -1052,16 +1052,16 @@
         <v>43262</v>
       </c>
       <c r="B32" t="n">
-        <v>81.41980743408203</v>
+        <v>81.41979217529297</v>
       </c>
       <c r="C32" t="n">
-        <v>82.73775244353311</v>
+        <v>82.73773693774955</v>
       </c>
       <c r="D32" t="n">
-        <v>78.93034995648213</v>
+        <v>78.93033516423932</v>
       </c>
       <c r="E32" t="n">
-        <v>81.47838045060293</v>
+        <v>81.47836518083678</v>
       </c>
       <c r="F32" t="n">
         <v>202266</v>
@@ -1072,16 +1072,16 @@
         <v>43263</v>
       </c>
       <c r="B33" t="n">
-        <v>82.23985290527344</v>
+        <v>82.2398681640625</v>
       </c>
       <c r="C33" t="n">
-        <v>83.38207132589955</v>
+        <v>83.38208679661591</v>
       </c>
       <c r="D33" t="n">
-        <v>80.0725620877285</v>
+        <v>80.07257694439825</v>
       </c>
       <c r="E33" t="n">
-        <v>81.41980094633571</v>
+        <v>81.41981605297228</v>
       </c>
       <c r="F33" t="n">
         <v>203566</v>
@@ -1092,16 +1092,16 @@
         <v>43264</v>
       </c>
       <c r="B34" t="n">
-        <v>78.31531524658203</v>
+        <v>78.3153076171875</v>
       </c>
       <c r="C34" t="n">
-        <v>82.32773096043591</v>
+        <v>82.32772294015612</v>
       </c>
       <c r="D34" t="n">
-        <v>77.70026874628836</v>
+        <v>77.70026117681101</v>
       </c>
       <c r="E34" t="n">
-        <v>82.32773096043591</v>
+        <v>82.32772294015612</v>
       </c>
       <c r="F34" t="n">
         <v>786033</v>
@@ -1112,16 +1112,16 @@
         <v>43265</v>
       </c>
       <c r="B35" t="n">
-        <v>79.13535308837891</v>
+        <v>79.13536071777344</v>
       </c>
       <c r="C35" t="n">
-        <v>80.21899844828646</v>
+        <v>80.21900618215462</v>
       </c>
       <c r="D35" t="n">
-        <v>77.90526775719401</v>
+        <v>77.90527526799671</v>
       </c>
       <c r="E35" t="n">
-        <v>78.19814769974872</v>
+        <v>78.19815523878781</v>
       </c>
       <c r="F35" t="n">
         <v>536566</v>
@@ -1132,16 +1132,16 @@
         <v>43266</v>
       </c>
       <c r="B36" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C36" t="n">
-        <v>79.22322984533973</v>
+        <v>79.22322220181655</v>
       </c>
       <c r="D36" t="n">
-        <v>75.12294738386028</v>
+        <v>75.12294013593576</v>
       </c>
       <c r="E36" t="n">
-        <v>79.13536287241121</v>
+        <v>79.1353552373655</v>
       </c>
       <c r="F36" t="n">
         <v>389566</v>
@@ -1152,16 +1152,16 @@
         <v>43269</v>
       </c>
       <c r="B37" t="n">
-        <v>77.26094818115234</v>
+        <v>77.26095581054688</v>
       </c>
       <c r="C37" t="n">
-        <v>79.07678608716174</v>
+        <v>79.07679389586734</v>
       </c>
       <c r="D37" t="n">
-        <v>76.7337687134483</v>
+        <v>76.7337762907847</v>
       </c>
       <c r="E37" t="n">
-        <v>79.07678608716174</v>
+        <v>79.07679389586734</v>
       </c>
       <c r="F37" t="n">
         <v>465333</v>
@@ -1172,16 +1172,16 @@
         <v>43270</v>
       </c>
       <c r="B38" t="n">
-        <v>81.56623077392578</v>
+        <v>81.56623840332031</v>
       </c>
       <c r="C38" t="n">
-        <v>83.14776907580264</v>
+        <v>83.14777685312824</v>
       </c>
       <c r="D38" t="n">
-        <v>77.02664374773103</v>
+        <v>77.02665095250988</v>
       </c>
       <c r="E38" t="n">
-        <v>77.8466956795029</v>
+        <v>77.84670296098628</v>
       </c>
       <c r="F38" t="n">
         <v>159600</v>
@@ -1192,16 +1192,16 @@
         <v>43271</v>
       </c>
       <c r="B39" t="n">
-        <v>84.34857940673828</v>
+        <v>84.34859466552734</v>
       </c>
       <c r="C39" t="n">
-        <v>85.52008445406554</v>
+        <v>85.52009992478168</v>
       </c>
       <c r="D39" t="n">
-        <v>81.71268187788078</v>
+        <v>81.71269665983189</v>
       </c>
       <c r="E39" t="n">
-        <v>82.03484837278239</v>
+        <v>82.03486321301391</v>
       </c>
       <c r="F39" t="n">
         <v>141600</v>
@@ -1232,16 +1232,16 @@
         <v>43273</v>
       </c>
       <c r="B41" t="n">
-        <v>84.93434906005859</v>
+        <v>84.93433380126953</v>
       </c>
       <c r="C41" t="n">
-        <v>85.52010170185748</v>
+        <v>85.52008633783566</v>
       </c>
       <c r="D41" t="n">
-        <v>81.21481270879913</v>
+        <v>81.21479811823937</v>
       </c>
       <c r="E41" t="n">
-        <v>82.03486491766779</v>
+        <v>82.03485017978244</v>
       </c>
       <c r="F41" t="n">
         <v>298800</v>
@@ -1272,16 +1272,16 @@
         <v>43277</v>
       </c>
       <c r="B43" t="n">
-        <v>86.75018310546875</v>
+        <v>86.75016784667969</v>
       </c>
       <c r="C43" t="n">
-        <v>87.86311530345259</v>
+        <v>87.86309984890605</v>
       </c>
       <c r="D43" t="n">
-        <v>85.08078480849298</v>
+        <v>85.08076984334015</v>
       </c>
       <c r="E43" t="n">
-        <v>86.60374309031327</v>
+        <v>86.60372785728207</v>
       </c>
       <c r="F43" t="n">
         <v>153233</v>
@@ -1312,16 +1312,16 @@
         <v>43279</v>
       </c>
       <c r="B45" t="n">
-        <v>88.68314361572266</v>
+        <v>88.68315124511719</v>
       </c>
       <c r="C45" t="n">
-        <v>88.68314361572266</v>
+        <v>88.68315124511719</v>
       </c>
       <c r="D45" t="n">
-        <v>85.37363442539693</v>
+        <v>85.373641770075</v>
       </c>
       <c r="E45" t="n">
-        <v>87.86309166864037</v>
+        <v>87.86309922748598</v>
       </c>
       <c r="F45" t="n">
         <v>922066</v>
@@ -1352,16 +1352,16 @@
         <v>43283</v>
       </c>
       <c r="B47" t="n">
-        <v>86.1058349609375</v>
+        <v>86.10584259033203</v>
       </c>
       <c r="C47" t="n">
-        <v>86.95518094171702</v>
+        <v>86.95518864636772</v>
       </c>
       <c r="D47" t="n">
-        <v>85.87153544660936</v>
+        <v>85.87154305524381</v>
       </c>
       <c r="E47" t="n">
-        <v>86.04726194441729</v>
+        <v>86.04726956862196</v>
       </c>
       <c r="F47" t="n">
         <v>88033</v>
@@ -1372,16 +1372,16 @@
         <v>43284</v>
       </c>
       <c r="B48" t="n">
-        <v>85.52008056640625</v>
+        <v>85.52008819580078</v>
       </c>
       <c r="C48" t="n">
-        <v>87.21876504228447</v>
+        <v>87.21877282322158</v>
       </c>
       <c r="D48" t="n">
-        <v>83.93854212098695</v>
+        <v>83.93854960928969</v>
       </c>
       <c r="E48" t="n">
-        <v>86.72087951633988</v>
+        <v>86.72088725285975</v>
       </c>
       <c r="F48" t="n">
         <v>142500</v>
@@ -1392,16 +1392,16 @@
         <v>43285</v>
       </c>
       <c r="B49" t="n">
-        <v>85.78366851806641</v>
+        <v>85.78367614746094</v>
       </c>
       <c r="C49" t="n">
-        <v>87.07232690802138</v>
+        <v>87.07233465202611</v>
       </c>
       <c r="D49" t="n">
-        <v>84.14355716282856</v>
+        <v>84.14356464635551</v>
       </c>
       <c r="E49" t="n">
-        <v>86.66229348302694</v>
+        <v>86.66230119056429</v>
       </c>
       <c r="F49" t="n">
         <v>320933</v>
@@ -1412,16 +1412,16 @@
         <v>43286</v>
       </c>
       <c r="B50" t="n">
-        <v>85.52008056640625</v>
+        <v>85.52008819580078</v>
       </c>
       <c r="C50" t="n">
-        <v>86.31084606499235</v>
+        <v>86.31085376493245</v>
       </c>
       <c r="D50" t="n">
-        <v>84.28999510885791</v>
+        <v>84.29000262851439</v>
       </c>
       <c r="E50" t="n">
-        <v>85.78367403143302</v>
+        <v>85.78368168434318</v>
       </c>
       <c r="F50" t="n">
         <v>391100</v>
@@ -1432,16 +1432,16 @@
         <v>43287</v>
       </c>
       <c r="B51" t="n">
-        <v>83.61637878417969</v>
+        <v>83.61638641357422</v>
       </c>
       <c r="C51" t="n">
-        <v>85.57864917581456</v>
+        <v>85.57865698425219</v>
       </c>
       <c r="D51" t="n">
-        <v>83.61637878417969</v>
+        <v>83.61638641357422</v>
       </c>
       <c r="E51" t="n">
-        <v>85.52007616360061</v>
+        <v>85.52008396669386</v>
       </c>
       <c r="F51" t="n">
         <v>769100</v>
@@ -1472,16 +1472,16 @@
         <v>43292</v>
       </c>
       <c r="B53" t="n">
-        <v>84.08499145507812</v>
+        <v>84.08497619628906</v>
       </c>
       <c r="C53" t="n">
-        <v>86.25228263847217</v>
+        <v>86.25226698638772</v>
       </c>
       <c r="D53" t="n">
-        <v>82.64989283643895</v>
+        <v>82.64987783807528</v>
       </c>
       <c r="E53" t="n">
-        <v>83.79211889812494</v>
+        <v>83.79210369248307</v>
       </c>
       <c r="F53" t="n">
         <v>271833</v>
@@ -1512,16 +1512,16 @@
         <v>43294</v>
       </c>
       <c r="B55" t="n">
-        <v>84.40715789794922</v>
+        <v>84.40715026855469</v>
       </c>
       <c r="C55" t="n">
-        <v>87.57022768943764</v>
+        <v>87.57021977413956</v>
       </c>
       <c r="D55" t="n">
-        <v>83.96784533877647</v>
+        <v>83.96783774909052</v>
       </c>
       <c r="E55" t="n">
-        <v>87.10162861941977</v>
+        <v>87.10162074647741</v>
       </c>
       <c r="F55" t="n">
         <v>222900</v>
@@ -1552,16 +1552,16 @@
         <v>43298</v>
       </c>
       <c r="B57" t="n">
-        <v>83.08919525146484</v>
+        <v>83.08921813964844</v>
       </c>
       <c r="C57" t="n">
-        <v>84.58286657558465</v>
+        <v>84.58288987522275</v>
       </c>
       <c r="D57" t="n">
-        <v>82.35700284173974</v>
+        <v>82.35702552822978</v>
       </c>
       <c r="E57" t="n">
-        <v>84.11426015613218</v>
+        <v>84.11428332668551</v>
       </c>
       <c r="F57" t="n">
         <v>152666</v>
@@ -1632,16 +1632,16 @@
         <v>43304</v>
       </c>
       <c r="B61" t="n">
-        <v>87.65808868408203</v>
+        <v>87.65807342529297</v>
       </c>
       <c r="C61" t="n">
-        <v>89.26891370479268</v>
+        <v>89.26889816560464</v>
       </c>
       <c r="D61" t="n">
-        <v>86.72088315979977</v>
+        <v>86.72086806415163</v>
       </c>
       <c r="E61" t="n">
-        <v>89.00532022869139</v>
+        <v>89.0053047353875</v>
       </c>
       <c r="F61" t="n">
         <v>145300</v>
@@ -1652,16 +1652,16 @@
         <v>43305</v>
       </c>
       <c r="B62" t="n">
-        <v>88.15598297119141</v>
+        <v>88.15597534179688</v>
       </c>
       <c r="C62" t="n">
-        <v>88.71245648741085</v>
+        <v>88.71244880985672</v>
       </c>
       <c r="D62" t="n">
-        <v>87.10163130699453</v>
+        <v>87.1016237688481</v>
       </c>
       <c r="E62" t="n">
-        <v>88.18527693118834</v>
+        <v>88.18526929925858</v>
       </c>
       <c r="F62" t="n">
         <v>140566</v>
@@ -1672,16 +1672,16 @@
         <v>43306</v>
       </c>
       <c r="B63" t="n">
-        <v>83.99713134765625</v>
+        <v>83.99711608886719</v>
       </c>
       <c r="C63" t="n">
-        <v>89.9132448469509</v>
+        <v>89.91322851344979</v>
       </c>
       <c r="D63" t="n">
-        <v>83.99713134765625</v>
+        <v>83.99711608886719</v>
       </c>
       <c r="E63" t="n">
-        <v>88.77102624132928</v>
+        <v>88.77101011532184</v>
       </c>
       <c r="F63" t="n">
         <v>653300</v>
@@ -1732,16 +1732,16 @@
         <v>43311</v>
       </c>
       <c r="B66" t="n">
-        <v>80.39472198486328</v>
+        <v>80.39475250244141</v>
       </c>
       <c r="C66" t="n">
-        <v>82.59129912897563</v>
+        <v>82.5913304803674</v>
       </c>
       <c r="D66" t="n">
-        <v>79.80896956941586</v>
+        <v>79.80899986464426</v>
       </c>
       <c r="E66" t="n">
-        <v>82.53272612190472</v>
+        <v>82.53275745106235</v>
       </c>
       <c r="F66" t="n">
         <v>306800</v>
@@ -1792,16 +1792,16 @@
         <v>43314</v>
       </c>
       <c r="B69" t="n">
-        <v>84.75859069824219</v>
+        <v>84.75860595703125</v>
       </c>
       <c r="C69" t="n">
-        <v>84.75859069824219</v>
+        <v>84.75860595703125</v>
       </c>
       <c r="D69" t="n">
-        <v>83.23563291174283</v>
+        <v>83.2356478963592</v>
       </c>
       <c r="E69" t="n">
-        <v>83.23563291174283</v>
+        <v>83.2356478963592</v>
       </c>
       <c r="F69" t="n">
         <v>63600</v>
@@ -1812,16 +1812,16 @@
         <v>43315</v>
       </c>
       <c r="B70" t="n">
-        <v>83.90925598144531</v>
+        <v>83.90926361083984</v>
       </c>
       <c r="C70" t="n">
-        <v>84.75860194723369</v>
+        <v>84.75860965385445</v>
       </c>
       <c r="D70" t="n">
-        <v>83.52851648428948</v>
+        <v>83.52852407906553</v>
       </c>
       <c r="E70" t="n">
-        <v>84.75860194723369</v>
+        <v>84.75860965385445</v>
       </c>
       <c r="F70" t="n">
         <v>171233</v>
@@ -1832,16 +1832,16 @@
         <v>43318</v>
       </c>
       <c r="B71" t="n">
-        <v>81.33193206787109</v>
+        <v>81.33193969726562</v>
       </c>
       <c r="C71" t="n">
-        <v>83.55779584493075</v>
+        <v>83.55780368312388</v>
       </c>
       <c r="D71" t="n">
-        <v>81.12691908295734</v>
+        <v>81.1269266931205</v>
       </c>
       <c r="E71" t="n">
-        <v>83.38206936525518</v>
+        <v>83.38207718696417</v>
       </c>
       <c r="F71" t="n">
         <v>242633</v>
@@ -1852,16 +1852,16 @@
         <v>43319</v>
       </c>
       <c r="B72" t="n">
-        <v>79.13535308837891</v>
+        <v>79.13536071777344</v>
       </c>
       <c r="C72" t="n">
-        <v>81.41979727486515</v>
+        <v>81.41980512450165</v>
       </c>
       <c r="D72" t="n">
-        <v>79.13535308837891</v>
+        <v>79.13536071777344</v>
       </c>
       <c r="E72" t="n">
-        <v>81.27335730358779</v>
+        <v>81.2733651391061</v>
       </c>
       <c r="F72" t="n">
         <v>212866</v>
@@ -1892,16 +1892,16 @@
         <v>43321</v>
       </c>
       <c r="B74" t="n">
-        <v>78.95963287353516</v>
+        <v>78.95962524414062</v>
       </c>
       <c r="C74" t="n">
-        <v>79.1353593633528</v>
+        <v>79.13535171697887</v>
       </c>
       <c r="D74" t="n">
-        <v>76.85092244397033</v>
+        <v>76.85091501832781</v>
       </c>
       <c r="E74" t="n">
-        <v>78.19815390040766</v>
+        <v>78.19814634459027</v>
       </c>
       <c r="F74" t="n">
         <v>546266</v>
@@ -1912,16 +1912,16 @@
         <v>43322</v>
       </c>
       <c r="B75" t="n">
-        <v>78.87176513671875</v>
+        <v>78.87178039550781</v>
       </c>
       <c r="C75" t="n">
-        <v>80.36543642045031</v>
+        <v>80.36545196820988</v>
       </c>
       <c r="D75" t="n">
-        <v>78.16885925066951</v>
+        <v>78.16887437347211</v>
       </c>
       <c r="E75" t="n">
-        <v>79.13535111986414</v>
+        <v>79.13536642964741</v>
       </c>
       <c r="F75" t="n">
         <v>176700</v>
@@ -1932,16 +1932,16 @@
         <v>43325</v>
       </c>
       <c r="B76" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C76" t="n">
-        <v>80.10185488514145</v>
+        <v>80.1018471568478</v>
       </c>
       <c r="D76" t="n">
-        <v>77.7588448480072</v>
+        <v>77.75883734576911</v>
       </c>
       <c r="E76" t="n">
-        <v>78.93034986657432</v>
+        <v>78.93034225130845</v>
       </c>
       <c r="F76" t="n">
         <v>160400</v>
@@ -1952,16 +1952,16 @@
         <v>43326</v>
       </c>
       <c r="B77" t="n">
-        <v>77.46596527099609</v>
+        <v>77.46595764160156</v>
       </c>
       <c r="C77" t="n">
-        <v>78.46175124536504</v>
+        <v>78.46174351789847</v>
       </c>
       <c r="D77" t="n">
-        <v>74.4493357360049</v>
+        <v>74.44932840370932</v>
       </c>
       <c r="E77" t="n">
-        <v>78.46175124536504</v>
+        <v>78.46174351789847</v>
       </c>
       <c r="F77" t="n">
         <v>524933</v>
@@ -1972,16 +1972,16 @@
         <v>43327</v>
       </c>
       <c r="B78" t="n">
-        <v>76.14801788330078</v>
+        <v>76.14802551269531</v>
       </c>
       <c r="C78" t="n">
-        <v>77.67097585752774</v>
+        <v>77.67098363950991</v>
       </c>
       <c r="D78" t="n">
-        <v>76.14801788330078</v>
+        <v>76.14802551269531</v>
       </c>
       <c r="E78" t="n">
-        <v>77.02665034852674</v>
+        <v>77.0266580659529</v>
       </c>
       <c r="F78" t="n">
         <v>702366</v>
@@ -1992,16 +1992,16 @@
         <v>43328</v>
       </c>
       <c r="B79" t="n">
-        <v>73.51213073730469</v>
+        <v>73.51212310791016</v>
       </c>
       <c r="C79" t="n">
-        <v>76.64592154159136</v>
+        <v>76.645913586959</v>
       </c>
       <c r="D79" t="n">
-        <v>72.69207862091992</v>
+        <v>72.69207107663379</v>
       </c>
       <c r="E79" t="n">
-        <v>76.32375501804815</v>
+        <v>76.32374709685156</v>
       </c>
       <c r="F79" t="n">
         <v>1651000</v>
@@ -2012,16 +2012,16 @@
         <v>43329</v>
       </c>
       <c r="B80" t="n">
-        <v>71.46199798583984</v>
+        <v>71.46196746826172</v>
       </c>
       <c r="C80" t="n">
-        <v>72.95566976511273</v>
+        <v>72.95563860966767</v>
       </c>
       <c r="D80" t="n">
-        <v>70.29049275259602</v>
+        <v>70.29046273530481</v>
       </c>
       <c r="E80" t="n">
-        <v>72.95566976511273</v>
+        <v>72.95563860966767</v>
       </c>
       <c r="F80" t="n">
         <v>2138466</v>
@@ -2032,16 +2032,16 @@
         <v>43332</v>
       </c>
       <c r="B81" t="n">
-        <v>72.34062957763672</v>
+        <v>72.34061431884766</v>
       </c>
       <c r="C81" t="n">
-        <v>73.01424917344369</v>
+        <v>73.01423377256823</v>
       </c>
       <c r="D81" t="n">
-        <v>71.75487696957561</v>
+        <v>71.75486183433918</v>
       </c>
       <c r="E81" t="n">
-        <v>71.95989000998456</v>
+        <v>71.95987483150479</v>
       </c>
       <c r="F81" t="n">
         <v>425766</v>
@@ -2052,16 +2052,16 @@
         <v>43333</v>
       </c>
       <c r="B82" t="n">
-        <v>71.60843658447266</v>
+        <v>71.60842895507812</v>
       </c>
       <c r="C82" t="n">
-        <v>72.57492875517822</v>
+        <v>72.5749210228105</v>
       </c>
       <c r="D82" t="n">
-        <v>70.31977787411573</v>
+        <v>70.31977038201907</v>
       </c>
       <c r="E82" t="n">
-        <v>71.63772309748668</v>
+        <v>71.63771546497189</v>
       </c>
       <c r="F82" t="n">
         <v>1384333</v>
@@ -2072,16 +2072,16 @@
         <v>43334</v>
       </c>
       <c r="B83" t="n">
-        <v>73.51213073730469</v>
+        <v>73.51212310791016</v>
       </c>
       <c r="C83" t="n">
-        <v>73.68785725485115</v>
+        <v>73.68784960721899</v>
       </c>
       <c r="D83" t="n">
-        <v>70.96410740525307</v>
+        <v>70.96410004030301</v>
       </c>
       <c r="E83" t="n">
-        <v>70.96410740525307</v>
+        <v>70.96410004030301</v>
       </c>
       <c r="F83" t="n">
         <v>518466</v>
@@ -2092,16 +2092,16 @@
         <v>43335</v>
       </c>
       <c r="B84" t="n">
-        <v>73.36569976806641</v>
+        <v>73.36570739746094</v>
       </c>
       <c r="C84" t="n">
-        <v>74.33219191137435</v>
+        <v>74.33219964127566</v>
       </c>
       <c r="D84" t="n">
-        <v>71.90131457288842</v>
+        <v>71.90132204999964</v>
       </c>
       <c r="E84" t="n">
-        <v>72.57492669786147</v>
+        <v>72.57493424502249</v>
       </c>
       <c r="F84" t="n">
         <v>126566</v>
@@ -2152,16 +2152,16 @@
         <v>43340</v>
       </c>
       <c r="B87" t="n">
-        <v>75.2401123046875</v>
+        <v>75.24009704589844</v>
       </c>
       <c r="C87" t="n">
-        <v>76.14803143900558</v>
+        <v>76.14801599608937</v>
       </c>
       <c r="D87" t="n">
-        <v>73.89288058367451</v>
+        <v>73.89286559810573</v>
       </c>
       <c r="E87" t="n">
-        <v>75.91373188931819</v>
+        <v>75.91371649391823</v>
       </c>
       <c r="F87" t="n">
         <v>298400</v>
@@ -2172,16 +2172,16 @@
         <v>43341</v>
       </c>
       <c r="B88" t="n">
-        <v>74.42005157470703</v>
+        <v>74.4200439453125</v>
       </c>
       <c r="C88" t="n">
-        <v>76.14803027897985</v>
+        <v>76.14802247243639</v>
       </c>
       <c r="D88" t="n">
-        <v>73.45355942975257</v>
+        <v>73.45355189944088</v>
       </c>
       <c r="E88" t="n">
-        <v>75.67942373849533</v>
+        <v>75.6794159799925</v>
       </c>
       <c r="F88" t="n">
         <v>162200</v>
@@ -2192,16 +2192,16 @@
         <v>43342</v>
       </c>
       <c r="B89" t="n">
-        <v>75.85514068603516</v>
+        <v>75.85513305664062</v>
       </c>
       <c r="C89" t="n">
-        <v>75.85514068603516</v>
+        <v>75.85513305664062</v>
       </c>
       <c r="D89" t="n">
-        <v>73.39497714168559</v>
+        <v>73.39496975973056</v>
       </c>
       <c r="E89" t="n">
-        <v>74.18574266518235</v>
+        <v>74.18573520369333</v>
       </c>
       <c r="F89" t="n">
         <v>206466</v>
@@ -2252,16 +2252,16 @@
         <v>43347</v>
       </c>
       <c r="B92" t="n">
-        <v>73.04351043701172</v>
+        <v>73.04352569580078</v>
       </c>
       <c r="C92" t="n">
-        <v>74.42002821770981</v>
+        <v>74.42004376405343</v>
       </c>
       <c r="D92" t="n">
-        <v>71.87200562585394</v>
+        <v>71.87202063991565</v>
       </c>
       <c r="E92" t="n">
-        <v>74.39074171466777</v>
+        <v>74.39075725489343</v>
       </c>
       <c r="F92" t="n">
         <v>196200</v>
@@ -2292,16 +2292,16 @@
         <v>43349</v>
       </c>
       <c r="B94" t="n">
-        <v>74.21504211425781</v>
+        <v>74.21503448486328</v>
       </c>
       <c r="C94" t="n">
-        <v>76.52877351935561</v>
+        <v>76.52876565210674</v>
       </c>
       <c r="D94" t="n">
-        <v>71.46199810800472</v>
+        <v>71.4619907616264</v>
       </c>
       <c r="E94" t="n">
-        <v>74.15646908697008</v>
+        <v>74.15646146359693</v>
       </c>
       <c r="F94" t="n">
         <v>139100</v>
@@ -2352,16 +2352,16 @@
         <v>43355</v>
       </c>
       <c r="B97" t="n">
-        <v>72.95565032958984</v>
+        <v>72.95565795898438</v>
       </c>
       <c r="C97" t="n">
-        <v>74.65434214798188</v>
+        <v>74.65434995501845</v>
       </c>
       <c r="D97" t="n">
-        <v>71.34483292506654</v>
+        <v>71.34484038600858</v>
       </c>
       <c r="E97" t="n">
-        <v>73.21924377820952</v>
+        <v>73.21925143516954</v>
       </c>
       <c r="F97" t="n">
         <v>133333</v>
@@ -2372,16 +2372,16 @@
         <v>43356</v>
       </c>
       <c r="B98" t="n">
-        <v>71.60843658447266</v>
+        <v>71.60842895507812</v>
       </c>
       <c r="C98" t="n">
-        <v>73.86358746553515</v>
+        <v>73.86357959586955</v>
       </c>
       <c r="D98" t="n">
-        <v>70.43693137442035</v>
+        <v>70.43692386984178</v>
       </c>
       <c r="E98" t="n">
-        <v>73.77572792649305</v>
+        <v>73.77572006618828</v>
       </c>
       <c r="F98" t="n">
         <v>250366</v>
@@ -2412,16 +2412,16 @@
         <v>43360</v>
       </c>
       <c r="B100" t="n">
-        <v>73.48284149169922</v>
+        <v>73.48284912109375</v>
       </c>
       <c r="C100" t="n">
-        <v>74.06860149389196</v>
+        <v>74.06860918410334</v>
       </c>
       <c r="D100" t="n">
-        <v>69.79259220877361</v>
+        <v>69.79259945502608</v>
       </c>
       <c r="E100" t="n">
-        <v>70.02689174070201</v>
+        <v>70.02689901128075</v>
       </c>
       <c r="F100" t="n">
         <v>114333</v>
@@ -2432,16 +2432,16 @@
         <v>43361</v>
       </c>
       <c r="B101" t="n">
-        <v>74.50790405273438</v>
+        <v>74.50789642333984</v>
       </c>
       <c r="C101" t="n">
-        <v>75.35724998338361</v>
+        <v>75.35724226701849</v>
       </c>
       <c r="D101" t="n">
-        <v>73.62927161555359</v>
+        <v>73.62926407612848</v>
       </c>
       <c r="E101" t="n">
-        <v>74.56647706579749</v>
+        <v>74.56646943040525</v>
       </c>
       <c r="F101" t="n">
         <v>194766</v>
@@ -2452,16 +2452,16 @@
         <v>43362</v>
       </c>
       <c r="B102" t="n">
-        <v>68.76752471923828</v>
+        <v>68.76753234863281</v>
       </c>
       <c r="C102" t="n">
-        <v>74.68363797116167</v>
+        <v>74.6836462569178</v>
       </c>
       <c r="D102" t="n">
-        <v>68.76752471923828</v>
+        <v>68.76753234863281</v>
       </c>
       <c r="E102" t="n">
-        <v>73.57070592274535</v>
+        <v>73.57071408502752</v>
       </c>
       <c r="F102" t="n">
         <v>510266</v>
@@ -2492,16 +2492,16 @@
         <v>43364</v>
       </c>
       <c r="B104" t="n">
-        <v>69.35326385498047</v>
+        <v>69.353271484375</v>
       </c>
       <c r="C104" t="n">
-        <v>71.16910157229026</v>
+        <v>71.16910940144096</v>
       </c>
       <c r="D104" t="n">
-        <v>67.88887907961748</v>
+        <v>67.88888654791837</v>
       </c>
       <c r="E104" t="n">
-        <v>67.94745208719324</v>
+        <v>67.94745956193762</v>
       </c>
       <c r="F104" t="n">
         <v>293166</v>
@@ -2512,16 +2512,16 @@
         <v>43367</v>
       </c>
       <c r="B105" t="n">
-        <v>65.45801544189453</v>
+        <v>65.4580078125</v>
       </c>
       <c r="C105" t="n">
-        <v>69.4997255371003</v>
+        <v>69.49971743662823</v>
       </c>
       <c r="D105" t="n">
-        <v>65.37015590307951</v>
+        <v>65.37014828392535</v>
       </c>
       <c r="E105" t="n">
-        <v>69.35328552416013</v>
+        <v>69.35327744075623</v>
       </c>
       <c r="F105" t="n">
         <v>831466</v>
@@ -2532,16 +2532,16 @@
         <v>43368</v>
       </c>
       <c r="B106" t="n">
-        <v>63.90575790405273</v>
+        <v>63.9057731628418</v>
       </c>
       <c r="C106" t="n">
-        <v>67.21526727343412</v>
+        <v>67.21528332243533</v>
       </c>
       <c r="D106" t="n">
-        <v>61.62131724810718</v>
+        <v>61.62133196143994</v>
       </c>
       <c r="E106" t="n">
-        <v>64.46222388346429</v>
+        <v>64.46223927512084</v>
       </c>
       <c r="F106" t="n">
         <v>629433</v>
@@ -2552,16 +2552,16 @@
         <v>43369</v>
       </c>
       <c r="B107" t="n">
-        <v>65.01869964599609</v>
+        <v>65.01869201660156</v>
       </c>
       <c r="C107" t="n">
-        <v>66.48308480670883</v>
+        <v>66.48307700548109</v>
       </c>
       <c r="D107" t="n">
-        <v>63.14428842786333</v>
+        <v>63.1442810184151</v>
       </c>
       <c r="E107" t="n">
-        <v>63.93505403120882</v>
+        <v>63.93504652897094</v>
       </c>
       <c r="F107" t="n">
         <v>469400</v>
@@ -2572,16 +2572,16 @@
         <v>43370</v>
       </c>
       <c r="B108" t="n">
-        <v>68.591796875</v>
+        <v>68.59178924560547</v>
       </c>
       <c r="C108" t="n">
-        <v>69.85116144605384</v>
+        <v>69.85115367658149</v>
       </c>
       <c r="D108" t="n">
-        <v>65.07726684520698</v>
+        <v>65.07725960672998</v>
       </c>
       <c r="E108" t="n">
-        <v>65.48730031418111</v>
+        <v>65.48729303009652</v>
       </c>
       <c r="F108" t="n">
         <v>605400</v>
@@ -2592,16 +2592,16 @@
         <v>43371</v>
       </c>
       <c r="B109" t="n">
-        <v>70.29046630859375</v>
+        <v>70.29047393798828</v>
       </c>
       <c r="C109" t="n">
-        <v>71.34482509080165</v>
+        <v>71.3448328346373</v>
       </c>
       <c r="D109" t="n">
-        <v>67.3324103764931</v>
+        <v>67.3324176848174</v>
       </c>
       <c r="E109" t="n">
-        <v>68.59178212497824</v>
+        <v>68.59178956999595</v>
       </c>
       <c r="F109" t="n">
         <v>612400</v>
@@ -2652,16 +2652,16 @@
         <v>43376</v>
       </c>
       <c r="B112" t="n">
-        <v>70.43691253662109</v>
+        <v>70.43693542480469</v>
       </c>
       <c r="C112" t="n">
-        <v>73.59998171642307</v>
+        <v>73.60000563243293</v>
       </c>
       <c r="D112" t="n">
-        <v>69.08967371229606</v>
+        <v>69.08969616269998</v>
       </c>
       <c r="E112" t="n">
-        <v>70.58334506252905</v>
+        <v>70.58336799829529</v>
       </c>
       <c r="F112" t="n">
         <v>463466</v>
@@ -2672,16 +2672,16 @@
         <v>43377</v>
       </c>
       <c r="B113" t="n">
-        <v>70.29046630859375</v>
+        <v>70.29047393798828</v>
       </c>
       <c r="C113" t="n">
-        <v>72.13559045333467</v>
+        <v>72.13559828300075</v>
       </c>
       <c r="D113" t="n">
-        <v>67.71314980647165</v>
+        <v>67.71315715612178</v>
       </c>
       <c r="E113" t="n">
-        <v>70.55405228002282</v>
+        <v>70.55405993802722</v>
       </c>
       <c r="F113" t="n">
         <v>201700</v>
@@ -2692,16 +2692,16 @@
         <v>43378</v>
       </c>
       <c r="B114" t="n">
-        <v>68.26964569091797</v>
+        <v>68.26962280273438</v>
       </c>
       <c r="C114" t="n">
-        <v>71.60844251972628</v>
+        <v>71.60841851217266</v>
       </c>
       <c r="D114" t="n">
-        <v>67.36172647098773</v>
+        <v>67.36170388719449</v>
       </c>
       <c r="E114" t="n">
-        <v>71.60844251972628</v>
+        <v>71.60841851217266</v>
       </c>
       <c r="F114" t="n">
         <v>364566</v>
@@ -2732,16 +2732,16 @@
         <v>43382</v>
       </c>
       <c r="B116" t="n">
-        <v>68.26964569091797</v>
+        <v>68.26962280273438</v>
       </c>
       <c r="C116" t="n">
-        <v>71.7548825451826</v>
+        <v>71.75485848853327</v>
       </c>
       <c r="D116" t="n">
-        <v>68.26964569091797</v>
+        <v>68.26962280273438</v>
       </c>
       <c r="E116" t="n">
-        <v>69.96833062076357</v>
+        <v>69.96830716307632</v>
       </c>
       <c r="F116" t="n">
         <v>433600</v>
@@ -2772,16 +2772,16 @@
         <v>43384</v>
       </c>
       <c r="B118" t="n">
-        <v>70.87624359130859</v>
+        <v>70.876220703125</v>
       </c>
       <c r="C118" t="n">
-        <v>71.63772271864046</v>
+        <v>71.63769958455114</v>
       </c>
       <c r="D118" t="n">
-        <v>68.62109272217215</v>
+        <v>68.62107056224819</v>
       </c>
       <c r="E118" t="n">
-        <v>69.08969182441557</v>
+        <v>69.08966951316611</v>
       </c>
       <c r="F118" t="n">
         <v>258833</v>
@@ -2912,16 +2912,16 @@
         <v>43396</v>
       </c>
       <c r="B125" t="n">
-        <v>75.44510650634766</v>
+        <v>75.44511413574219</v>
       </c>
       <c r="C125" t="n">
-        <v>76.14801242817332</v>
+        <v>76.14802012864928</v>
       </c>
       <c r="D125" t="n">
-        <v>74.15644813241612</v>
+        <v>74.15645563149494</v>
       </c>
       <c r="E125" t="n">
-        <v>74.80078104350515</v>
+        <v>74.80078860774221</v>
       </c>
       <c r="F125" t="n">
         <v>244366</v>
@@ -2932,16 +2932,16 @@
         <v>43397</v>
       </c>
       <c r="B126" t="n">
-        <v>74.39076995849609</v>
+        <v>74.39075469970703</v>
       </c>
       <c r="C126" t="n">
-        <v>75.2694026245765</v>
+        <v>75.26938718556521</v>
       </c>
       <c r="D126" t="n">
-        <v>74.24432993944123</v>
+        <v>74.24431471068945</v>
       </c>
       <c r="E126" t="n">
-        <v>75.2694026245765</v>
+        <v>75.26938718556521</v>
       </c>
       <c r="F126" t="n">
         <v>414300</v>
@@ -2952,16 +2952,16 @@
         <v>43398</v>
       </c>
       <c r="B127" t="n">
-        <v>76.0015869140625</v>
+        <v>76.00157928466797</v>
       </c>
       <c r="C127" t="n">
-        <v>76.0015869140625</v>
+        <v>76.00157928466797</v>
       </c>
       <c r="D127" t="n">
-        <v>73.10210315896421</v>
+        <v>73.10209582063342</v>
       </c>
       <c r="E127" t="n">
-        <v>74.56648829198372</v>
+        <v>74.5664808066511</v>
       </c>
       <c r="F127" t="n">
         <v>495966</v>
@@ -2972,16 +2972,16 @@
         <v>43399</v>
       </c>
       <c r="B128" t="n">
-        <v>74.97651672363281</v>
+        <v>74.97650909423828</v>
       </c>
       <c r="C128" t="n">
-        <v>78.02244057845078</v>
+        <v>78.02243263911183</v>
       </c>
       <c r="D128" t="n">
-        <v>73.36569898473449</v>
+        <v>73.36569151925214</v>
       </c>
       <c r="E128" t="n">
-        <v>76.11874282434466</v>
+        <v>76.1187350787205</v>
       </c>
       <c r="F128" t="n">
         <v>546200</v>
@@ -3052,16 +3052,16 @@
         <v>43405</v>
       </c>
       <c r="B132" t="n">
-        <v>75.35723876953125</v>
+        <v>75.35724639892578</v>
       </c>
       <c r="C132" t="n">
-        <v>78.08098774710245</v>
+        <v>78.08099565225757</v>
       </c>
       <c r="D132" t="n">
-        <v>74.15644004269964</v>
+        <v>74.15644755052168</v>
       </c>
       <c r="E132" t="n">
-        <v>75.6501112395115</v>
+        <v>75.65011889855732</v>
       </c>
       <c r="F132" t="n">
         <v>289433</v>
@@ -3072,16 +3072,16 @@
         <v>43409</v>
       </c>
       <c r="B133" t="n">
-        <v>76.38231658935547</v>
+        <v>76.38232421875</v>
       </c>
       <c r="C133" t="n">
-        <v>76.85092304863853</v>
+        <v>76.85093072483949</v>
       </c>
       <c r="D133" t="n">
-        <v>73.98072617511639</v>
+        <v>73.98073356462973</v>
       </c>
       <c r="E133" t="n">
-        <v>75.82585060859577</v>
+        <v>75.82585818240808</v>
       </c>
       <c r="F133" t="n">
         <v>315933</v>
@@ -3092,16 +3092,16 @@
         <v>43410</v>
       </c>
       <c r="B134" t="n">
-        <v>75.12295532226562</v>
+        <v>75.12294769287109</v>
       </c>
       <c r="C134" t="n">
-        <v>76.96808001802316</v>
+        <v>76.96807220124005</v>
       </c>
       <c r="D134" t="n">
-        <v>74.12717669608222</v>
+        <v>74.12716916781773</v>
       </c>
       <c r="E134" t="n">
-        <v>76.1773144193408</v>
+        <v>76.17730668286687</v>
       </c>
       <c r="F134" t="n">
         <v>244033</v>
@@ -3112,16 +3112,16 @@
         <v>43411</v>
       </c>
       <c r="B135" t="n">
-        <v>77.31951904296875</v>
+        <v>77.31953430175781</v>
       </c>
       <c r="C135" t="n">
-        <v>79.04749738039364</v>
+        <v>79.04751298019434</v>
       </c>
       <c r="D135" t="n">
-        <v>75.56226164777432</v>
+        <v>75.56227655977359</v>
       </c>
       <c r="E135" t="n">
-        <v>75.56226164777432</v>
+        <v>75.56227655977359</v>
       </c>
       <c r="F135" t="n">
         <v>375833</v>
@@ -3132,16 +3132,16 @@
         <v>43412</v>
       </c>
       <c r="B136" t="n">
-        <v>77.31951904296875</v>
+        <v>77.31953430175781</v>
       </c>
       <c r="C136" t="n">
-        <v>79.25251037075398</v>
+        <v>79.25252601101343</v>
       </c>
       <c r="D136" t="n">
-        <v>76.14801411283914</v>
+        <v>76.148029140435</v>
       </c>
       <c r="E136" t="n">
-        <v>77.29023253695252</v>
+        <v>77.29024778996197</v>
       </c>
       <c r="F136" t="n">
         <v>245533</v>
@@ -3152,16 +3152,16 @@
         <v>43413</v>
       </c>
       <c r="B137" t="n">
-        <v>76.73377990722656</v>
+        <v>76.73377227783203</v>
       </c>
       <c r="C137" t="n">
-        <v>79.07679762273497</v>
+        <v>79.07678976038169</v>
       </c>
       <c r="D137" t="n">
-        <v>75.21082174385769</v>
+        <v>75.21081426588603</v>
       </c>
       <c r="E137" t="n">
-        <v>77.31953247404167</v>
+        <v>77.31952478640763</v>
       </c>
       <c r="F137" t="n">
         <v>423466</v>
@@ -3172,16 +3172,16 @@
         <v>43416</v>
       </c>
       <c r="B138" t="n">
-        <v>76.79234313964844</v>
+        <v>76.79233551025391</v>
       </c>
       <c r="C138" t="n">
-        <v>77.78812907971066</v>
+        <v>77.78812135138382</v>
       </c>
       <c r="D138" t="n">
-        <v>75.79656464783326</v>
+        <v>75.7965571173703</v>
       </c>
       <c r="E138" t="n">
-        <v>77.02665009510251</v>
+        <v>77.02664244242936</v>
       </c>
       <c r="F138" t="n">
         <v>143933</v>
@@ -3192,16 +3192,16 @@
         <v>43417</v>
       </c>
       <c r="B139" t="n">
-        <v>75.26938629150391</v>
+        <v>75.26939392089844</v>
       </c>
       <c r="C139" t="n">
-        <v>77.84670325390931</v>
+        <v>77.84671114454375</v>
       </c>
       <c r="D139" t="n">
-        <v>74.91793330133525</v>
+        <v>74.91794089510609</v>
       </c>
       <c r="E139" t="n">
-        <v>77.26095075304393</v>
+        <v>77.2609585843058</v>
       </c>
       <c r="F139" t="n">
         <v>637900</v>
@@ -3212,16 +3212,16 @@
         <v>43418</v>
       </c>
       <c r="B140" t="n">
-        <v>79.36966705322266</v>
+        <v>79.36965179443359</v>
       </c>
       <c r="C140" t="n">
-        <v>80.33616657102803</v>
+        <v>80.33615112642978</v>
       </c>
       <c r="D140" t="n">
-        <v>71.02267654659238</v>
+        <v>71.02266289250915</v>
       </c>
       <c r="E140" t="n">
-        <v>75.0350922710638</v>
+        <v>75.03507784559514</v>
       </c>
       <c r="F140" t="n">
         <v>1608700</v>
@@ -3232,16 +3232,16 @@
         <v>43420</v>
       </c>
       <c r="B141" t="n">
-        <v>81.09762573242188</v>
+        <v>81.09764099121094</v>
       </c>
       <c r="C141" t="n">
-        <v>83.46992928367727</v>
+        <v>83.46994498882317</v>
       </c>
       <c r="D141" t="n">
-        <v>78.81318168946497</v>
+        <v>78.81319651842826</v>
       </c>
       <c r="E141" t="n">
-        <v>78.81318168946497</v>
+        <v>78.81319651842826</v>
       </c>
       <c r="F141" t="n">
         <v>652300</v>
@@ -3252,16 +3252,16 @@
         <v>43423</v>
       </c>
       <c r="B142" t="n">
-        <v>80.24829864501953</v>
+        <v>80.24828338623047</v>
       </c>
       <c r="C142" t="n">
-        <v>81.53695720529036</v>
+        <v>81.5369417014697</v>
       </c>
       <c r="D142" t="n">
-        <v>79.77969959487429</v>
+        <v>79.77968442518686</v>
       </c>
       <c r="E142" t="n">
-        <v>80.65833212420613</v>
+        <v>80.65831678745137</v>
       </c>
       <c r="F142" t="n">
         <v>158533</v>
@@ -3292,16 +3292,16 @@
         <v>43426</v>
       </c>
       <c r="B144" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C144" t="n">
-        <v>80.24829487452415</v>
+        <v>80.24828713210185</v>
       </c>
       <c r="D144" t="n">
-        <v>77.78813135623429</v>
+        <v>77.78812385117061</v>
       </c>
       <c r="E144" t="n">
-        <v>79.54538888408497</v>
+        <v>79.54538120947963</v>
       </c>
       <c r="F144" t="n">
         <v>203833</v>
@@ -3312,16 +3312,16 @@
         <v>43427</v>
       </c>
       <c r="B145" t="n">
-        <v>79.51610565185547</v>
+        <v>79.51609039306641</v>
       </c>
       <c r="C145" t="n">
-        <v>79.51610565185547</v>
+        <v>79.51609039306641</v>
       </c>
       <c r="D145" t="n">
-        <v>77.31952806535949</v>
+        <v>77.31951322808395</v>
       </c>
       <c r="E145" t="n">
-        <v>78.63747312760756</v>
+        <v>78.6374580374242</v>
       </c>
       <c r="F145" t="n">
         <v>372100</v>
@@ -3332,16 +3332,16 @@
         <v>43430</v>
       </c>
       <c r="B146" t="n">
-        <v>78.75463104248047</v>
+        <v>78.75461578369141</v>
       </c>
       <c r="C146" t="n">
-        <v>80.33616967506701</v>
+        <v>80.33615410985325</v>
       </c>
       <c r="D146" t="n">
-        <v>76.23588681407345</v>
+        <v>76.23587204329363</v>
       </c>
       <c r="E146" t="n">
-        <v>80.27758920465774</v>
+        <v>80.27757365079401</v>
       </c>
       <c r="F146" t="n">
         <v>252366</v>
@@ -3352,16 +3352,16 @@
         <v>43431</v>
       </c>
       <c r="B147" t="n">
-        <v>81.59555816650391</v>
+        <v>81.59552001953125</v>
       </c>
       <c r="C147" t="n">
-        <v>82.59133698435073</v>
+        <v>82.59129837183868</v>
       </c>
       <c r="D147" t="n">
-        <v>76.32376911468376</v>
+        <v>76.32373343234028</v>
       </c>
       <c r="E147" t="n">
-        <v>78.28604768166809</v>
+        <v>78.28601108193415</v>
       </c>
       <c r="F147" t="n">
         <v>436400</v>
@@ -3412,16 +3412,16 @@
         <v>43434</v>
       </c>
       <c r="B150" t="n">
-        <v>82.91347503662109</v>
+        <v>82.91348266601562</v>
       </c>
       <c r="C150" t="n">
-        <v>84.26070649088619</v>
+        <v>84.26071424424802</v>
       </c>
       <c r="D150" t="n">
-        <v>82.32772255425571</v>
+        <v>82.32773012975143</v>
       </c>
       <c r="E150" t="n">
-        <v>84.23141998400496</v>
+        <v>84.23142773467195</v>
       </c>
       <c r="F150" t="n">
         <v>464600</v>
@@ -3472,16 +3472,16 @@
         <v>43439</v>
       </c>
       <c r="B153" t="n">
-        <v>86.1058349609375</v>
+        <v>86.10584259033203</v>
       </c>
       <c r="C153" t="n">
-        <v>86.39871494003313</v>
+        <v>86.39872259537825</v>
       </c>
       <c r="D153" t="n">
-        <v>83.11849194645005</v>
+        <v>83.11849931115151</v>
       </c>
       <c r="E153" t="n">
-        <v>83.82139793768175</v>
+        <v>83.82140536466409</v>
       </c>
       <c r="F153" t="n">
         <v>198233</v>
@@ -3492,16 +3492,16 @@
         <v>43440</v>
       </c>
       <c r="B154" t="n">
-        <v>84.93434906005859</v>
+        <v>84.93433380126953</v>
       </c>
       <c r="C154" t="n">
-        <v>85.46152867215227</v>
+        <v>85.46151331865333</v>
       </c>
       <c r="D154" t="n">
-        <v>83.87998983587121</v>
+        <v>83.87997476650193</v>
       </c>
       <c r="E154" t="n">
-        <v>85.25651561993512</v>
+        <v>85.25650030326756</v>
       </c>
       <c r="F154" t="n">
         <v>270866</v>
@@ -3512,16 +3512,16 @@
         <v>43441</v>
       </c>
       <c r="B155" t="n">
-        <v>84.26071929931641</v>
+        <v>84.26071166992188</v>
       </c>
       <c r="C155" t="n">
-        <v>86.10584399577968</v>
+        <v>86.10583619931816</v>
       </c>
       <c r="D155" t="n">
-        <v>82.1812950639406</v>
+        <v>82.18128762282772</v>
       </c>
       <c r="E155" t="n">
-        <v>85.57866444704045</v>
+        <v>85.57865669831246</v>
       </c>
       <c r="F155" t="n">
         <v>485833</v>
@@ -3552,16 +3552,16 @@
         <v>43445</v>
       </c>
       <c r="B157" t="n">
-        <v>83.87995910644531</v>
+        <v>83.87997436523438</v>
       </c>
       <c r="C157" t="n">
-        <v>84.37785202128332</v>
+        <v>84.37786737064518</v>
       </c>
       <c r="D157" t="n">
-        <v>83.14776671037318</v>
+        <v>83.14778183596749</v>
       </c>
       <c r="E157" t="n">
-        <v>83.46993315222402</v>
+        <v>83.46994833642434</v>
       </c>
       <c r="F157" t="n">
         <v>276533</v>
@@ -3592,16 +3592,16 @@
         <v>43447</v>
       </c>
       <c r="B159" t="n">
-        <v>86.77944183349609</v>
+        <v>86.77945709228516</v>
       </c>
       <c r="C159" t="n">
-        <v>88.77100603649799</v>
+        <v>88.77102164547205</v>
       </c>
       <c r="D159" t="n">
-        <v>84.99289060677064</v>
+        <v>84.99290555142299</v>
       </c>
       <c r="E159" t="n">
-        <v>85.78366345611825</v>
+        <v>85.78367853981547</v>
       </c>
       <c r="F159" t="n">
         <v>486800</v>
@@ -3632,16 +3632,16 @@
         <v>43451</v>
       </c>
       <c r="B161" t="n">
-        <v>84.9378662109375</v>
+        <v>84.93785858154297</v>
       </c>
       <c r="C161" t="n">
-        <v>86.47039992970112</v>
+        <v>86.47039216264943</v>
       </c>
       <c r="D161" t="n">
-        <v>84.28948194833528</v>
+        <v>84.28947437718072</v>
       </c>
       <c r="E161" t="n">
-        <v>86.44092928050621</v>
+        <v>86.44092151610168</v>
       </c>
       <c r="F161" t="n">
         <v>205700</v>
@@ -3692,16 +3692,16 @@
         <v>43454</v>
       </c>
       <c r="B164" t="n">
-        <v>89.00496673583984</v>
+        <v>89.00497436523438</v>
       </c>
       <c r="C164" t="n">
-        <v>93.07208057875353</v>
+        <v>93.07208855677598</v>
       </c>
       <c r="D164" t="n">
-        <v>87.20718246605232</v>
+        <v>87.20718994134303</v>
       </c>
       <c r="E164" t="n">
-        <v>89.2702175271606</v>
+        <v>89.27022517929211</v>
       </c>
       <c r="F164" t="n">
         <v>975500</v>
@@ -3712,16 +3712,16 @@
         <v>43455</v>
       </c>
       <c r="B165" t="n">
-        <v>88.0029296875</v>
+        <v>88.00292205810547</v>
       </c>
       <c r="C165" t="n">
-        <v>90.18383988988073</v>
+        <v>90.18383207141265</v>
       </c>
       <c r="D165" t="n">
-        <v>86.08725529334548</v>
+        <v>86.08724783002991</v>
       </c>
       <c r="E165" t="n">
-        <v>90.18383988988073</v>
+        <v>90.18383207141265</v>
       </c>
       <c r="F165" t="n">
         <v>2053700</v>
@@ -3732,16 +3732,16 @@
         <v>43460</v>
       </c>
       <c r="B166" t="n">
-        <v>90.59645843505859</v>
+        <v>90.59646606445312</v>
       </c>
       <c r="C166" t="n">
-        <v>92.68895686361802</v>
+        <v>92.68896466922801</v>
       </c>
       <c r="D166" t="n">
-        <v>86.38198343521785</v>
+        <v>86.38199070969904</v>
       </c>
       <c r="E166" t="n">
-        <v>87.88504642566966</v>
+        <v>87.88505382672821</v>
       </c>
       <c r="F166" t="n">
         <v>396300</v>
@@ -3752,16 +3752,16 @@
         <v>43461</v>
       </c>
       <c r="B167" t="n">
-        <v>90.62593078613281</v>
+        <v>90.62592315673828</v>
       </c>
       <c r="C167" t="n">
-        <v>91.36272697138592</v>
+        <v>91.3627192799638</v>
       </c>
       <c r="D167" t="n">
-        <v>89.35864044808805</v>
+        <v>89.35863292538107</v>
       </c>
       <c r="E167" t="n">
-        <v>91.36272697138592</v>
+        <v>91.3627192799638</v>
       </c>
       <c r="F167" t="n">
         <v>343866</v>
@@ -3772,16 +3772,16 @@
         <v>43462</v>
       </c>
       <c r="B168" t="n">
-        <v>91.95216369628906</v>
+        <v>91.95215606689453</v>
       </c>
       <c r="C168" t="n">
-        <v>92.0995244343998</v>
+        <v>92.09951679277854</v>
       </c>
       <c r="D168" t="n">
-        <v>89.97754779379356</v>
+        <v>89.97754032823556</v>
       </c>
       <c r="E168" t="n">
-        <v>91.33325759031815</v>
+        <v>91.33325001227509</v>
       </c>
       <c r="F168" t="n">
         <v>582800</v>
@@ -3852,16 +3852,16 @@
         <v>43472</v>
       </c>
       <c r="B172" t="n">
-        <v>91.24484252929688</v>
+        <v>91.24482727050781</v>
       </c>
       <c r="C172" t="n">
-        <v>91.65744661974971</v>
+        <v>91.65743129196125</v>
       </c>
       <c r="D172" t="n">
-        <v>89.88914016277521</v>
+        <v>89.88912513069897</v>
       </c>
       <c r="E172" t="n">
-        <v>89.88914016277521</v>
+        <v>89.88912513069897</v>
       </c>
       <c r="F172" t="n">
         <v>470133</v>
@@ -3912,16 +3912,16 @@
         <v>43475</v>
       </c>
       <c r="B175" t="n">
-        <v>93.39627838134766</v>
+        <v>93.39627075195312</v>
       </c>
       <c r="C175" t="n">
-        <v>94.84040001456971</v>
+        <v>94.84039226720716</v>
       </c>
       <c r="D175" t="n">
-        <v>91.0974705277286</v>
+        <v>91.09746308612006</v>
       </c>
       <c r="E175" t="n">
-        <v>91.0974705277286</v>
+        <v>91.09746308612006</v>
       </c>
       <c r="F175" t="n">
         <v>243466</v>
@@ -3932,16 +3932,16 @@
         <v>43476</v>
       </c>
       <c r="B176" t="n">
-        <v>92.36476898193359</v>
+        <v>92.36474609375</v>
       </c>
       <c r="C176" t="n">
-        <v>93.04262388911262</v>
+        <v>93.04260083295516</v>
       </c>
       <c r="D176" t="n">
-        <v>90.86170592260495</v>
+        <v>90.86168340688354</v>
       </c>
       <c r="E176" t="n">
-        <v>92.39423963092771</v>
+        <v>92.39421673544123</v>
       </c>
       <c r="F176" t="n">
         <v>283133</v>
@@ -3952,16 +3952,16 @@
         <v>43479</v>
       </c>
       <c r="B177" t="n">
-        <v>94.63410186767578</v>
+        <v>94.63409423828125</v>
       </c>
       <c r="C177" t="n">
-        <v>96.40240817851779</v>
+        <v>96.40240040656253</v>
       </c>
       <c r="D177" t="n">
-        <v>92.74789797633478</v>
+        <v>92.74789049900588</v>
       </c>
       <c r="E177" t="n">
-        <v>92.95420749959067</v>
+        <v>92.9542000056291</v>
       </c>
       <c r="F177" t="n">
         <v>478500</v>
@@ -3972,16 +3972,16 @@
         <v>43480</v>
       </c>
       <c r="B178" t="n">
-        <v>93.42575836181641</v>
+        <v>93.42575073242188</v>
       </c>
       <c r="C178" t="n">
-        <v>99.26118677047653</v>
+        <v>99.26117866454547</v>
       </c>
       <c r="D178" t="n">
-        <v>92.74790344705082</v>
+        <v>92.7478958730117</v>
       </c>
       <c r="E178" t="n">
-        <v>94.69304874829707</v>
+        <v>94.69304101541225</v>
       </c>
       <c r="F178" t="n">
         <v>736266</v>
@@ -3992,16 +3992,16 @@
         <v>43481</v>
       </c>
       <c r="B179" t="n">
-        <v>98.43596649169922</v>
+        <v>98.43595886230469</v>
       </c>
       <c r="C179" t="n">
-        <v>100.0569195841087</v>
+        <v>100.0569118290803</v>
       </c>
       <c r="D179" t="n">
-        <v>93.74994609226806</v>
+        <v>93.74993882606901</v>
       </c>
       <c r="E179" t="n">
-        <v>93.8973068270468</v>
+        <v>93.89729954942638</v>
       </c>
       <c r="F179" t="n">
         <v>1131666</v>
@@ -4012,16 +4012,16 @@
         <v>43482</v>
       </c>
       <c r="B180" t="n">
-        <v>99.26116943359375</v>
+        <v>99.26117706298828</v>
       </c>
       <c r="C180" t="n">
-        <v>100.0274361624956</v>
+        <v>100.0274438507868</v>
       </c>
       <c r="D180" t="n">
-        <v>97.90545984084979</v>
+        <v>97.90546736604202</v>
       </c>
       <c r="E180" t="n">
-        <v>98.78961664153556</v>
+        <v>98.78962423468569</v>
       </c>
       <c r="F180" t="n">
         <v>313600</v>
@@ -4092,16 +4092,16 @@
         <v>43488</v>
       </c>
       <c r="B184" t="n">
-        <v>99.23169708251953</v>
+        <v>99.23170471191406</v>
       </c>
       <c r="C184" t="n">
-        <v>101.0589519408135</v>
+        <v>101.0589597106958</v>
       </c>
       <c r="D184" t="n">
-        <v>98.17070893994681</v>
+        <v>98.17071648776765</v>
       </c>
       <c r="E184" t="n">
-        <v>99.58535979671043</v>
+        <v>99.5853674532962</v>
       </c>
       <c r="F184" t="n">
         <v>240366</v>
@@ -4132,16 +4132,16 @@
         <v>43493</v>
       </c>
       <c r="B186" t="n">
-        <v>97.25707244873047</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C186" t="n">
-        <v>98.05280973397741</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="D186" t="n">
-        <v>95.96031178255046</v>
+        <v>95.96032683788904</v>
       </c>
       <c r="E186" t="n">
-        <v>98.05280973397741</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="F186" t="n">
         <v>263933</v>
@@ -4152,16 +4152,16 @@
         <v>43494</v>
       </c>
       <c r="B187" t="n">
-        <v>97.3160400390625</v>
+        <v>97.31603240966797</v>
       </c>
       <c r="C187" t="n">
-        <v>97.99389494386627</v>
+        <v>97.99388726132918</v>
       </c>
       <c r="D187" t="n">
-        <v>96.72660457600985</v>
+        <v>96.72659699282595</v>
       </c>
       <c r="E187" t="n">
-        <v>97.49287142748615</v>
+        <v>97.49286378422838</v>
       </c>
       <c r="F187" t="n">
         <v>185333</v>
@@ -4172,16 +4172,16 @@
         <v>43495</v>
       </c>
       <c r="B188" t="n">
-        <v>98.73067474365234</v>
+        <v>98.73069763183594</v>
       </c>
       <c r="C188" t="n">
-        <v>98.73067474365234</v>
+        <v>98.73069763183594</v>
       </c>
       <c r="D188" t="n">
-        <v>96.49081585912812</v>
+        <v>96.49083822805768</v>
       </c>
       <c r="E188" t="n">
-        <v>97.28655322729401</v>
+        <v>97.28657578069495</v>
       </c>
       <c r="F188" t="n">
         <v>447533</v>
@@ -4212,16 +4212,16 @@
         <v>43497</v>
       </c>
       <c r="B190" t="n">
-        <v>100.2042770385742</v>
+        <v>100.2042617797852</v>
       </c>
       <c r="C190" t="n">
-        <v>101.5599792649856</v>
+        <v>101.5599637997546</v>
       </c>
       <c r="D190" t="n">
-        <v>98.84857481216278</v>
+        <v>98.84855975981576</v>
       </c>
       <c r="E190" t="n">
-        <v>101.2063165111256</v>
+        <v>101.2063010997492</v>
       </c>
       <c r="F190" t="n">
         <v>150066</v>
@@ -4252,16 +4252,16 @@
         <v>43501</v>
       </c>
       <c r="B192" t="n">
-        <v>98.73067474365234</v>
+        <v>98.73069763183594</v>
       </c>
       <c r="C192" t="n">
-        <v>101.8546904234038</v>
+        <v>101.8547140358106</v>
       </c>
       <c r="D192" t="n">
-        <v>93.86781611744098</v>
+        <v>93.86783787829509</v>
       </c>
       <c r="E192" t="n">
-        <v>100.2632081919947</v>
+        <v>100.263231435457</v>
       </c>
       <c r="F192" t="n">
         <v>970333</v>
@@ -4272,16 +4272,16 @@
         <v>43502</v>
       </c>
       <c r="B193" t="n">
-        <v>97.46340942382812</v>
+        <v>97.46339416503906</v>
       </c>
       <c r="C193" t="n">
-        <v>99.5559081265521</v>
+        <v>99.5558925401632</v>
       </c>
       <c r="D193" t="n">
-        <v>96.07822884246099</v>
+        <v>96.07821380053463</v>
       </c>
       <c r="E193" t="n">
-        <v>98.43597839888808</v>
+        <v>98.43596298783444</v>
       </c>
       <c r="F193" t="n">
         <v>594200</v>
@@ -4292,16 +4292,16 @@
         <v>43503</v>
       </c>
       <c r="B194" t="n">
-        <v>97.10972595214844</v>
+        <v>97.10974884033203</v>
       </c>
       <c r="C194" t="n">
-        <v>98.61278881970669</v>
+        <v>98.61281206215324</v>
       </c>
       <c r="D194" t="n">
-        <v>95.3119416420943</v>
+        <v>95.31196410655085</v>
       </c>
       <c r="E194" t="n">
-        <v>97.19814538292826</v>
+        <v>97.19816829195179</v>
       </c>
       <c r="F194" t="n">
         <v>496333</v>
@@ -4312,16 +4312,16 @@
         <v>43504</v>
       </c>
       <c r="B195" t="n">
-        <v>97.16867065429688</v>
+        <v>97.16866302490234</v>
       </c>
       <c r="C195" t="n">
-        <v>98.524380343285</v>
+        <v>98.52437260744419</v>
       </c>
       <c r="D195" t="n">
-        <v>95.78349781411782</v>
+        <v>95.78349029348294</v>
       </c>
       <c r="E195" t="n">
-        <v>96.84448605026213</v>
+        <v>96.84447844632162</v>
       </c>
       <c r="F195" t="n">
         <v>210500</v>
@@ -4332,16 +4332,16 @@
         <v>43507</v>
       </c>
       <c r="B196" t="n">
-        <v>98.1412353515625</v>
+        <v>98.14124298095703</v>
       </c>
       <c r="C196" t="n">
-        <v>98.67172940693146</v>
+        <v>98.67173707756602</v>
       </c>
       <c r="D196" t="n">
-        <v>96.10767855352002</v>
+        <v>96.10768602482801</v>
       </c>
       <c r="E196" t="n">
-        <v>97.10971788361003</v>
+        <v>97.10972543281549</v>
       </c>
       <c r="F196" t="n">
         <v>401966</v>
@@ -4372,16 +4372,16 @@
         <v>43509</v>
       </c>
       <c r="B198" t="n">
-        <v>98.73067474365234</v>
+        <v>98.73069763183594</v>
       </c>
       <c r="C198" t="n">
-        <v>99.88007482990913</v>
+        <v>99.88009798455177</v>
       </c>
       <c r="D198" t="n">
-        <v>96.28451385608797</v>
+        <v>96.28453617719168</v>
       </c>
       <c r="E198" t="n">
-        <v>97.25708258329932</v>
+        <v>97.25710512986824</v>
       </c>
       <c r="F198" t="n">
         <v>448033</v>
@@ -4392,16 +4392,16 @@
         <v>43510</v>
       </c>
       <c r="B199" t="n">
-        <v>97.64023590087891</v>
+        <v>97.64021301269531</v>
       </c>
       <c r="C199" t="n">
-        <v>99.02540891726912</v>
+        <v>99.02538570438236</v>
       </c>
       <c r="D199" t="n">
-        <v>96.54977687974589</v>
+        <v>96.54975424718056</v>
       </c>
       <c r="E199" t="n">
-        <v>98.40650278165802</v>
+        <v>98.40647971385117</v>
       </c>
       <c r="F199" t="n">
         <v>462433</v>
@@ -4432,16 +4432,16 @@
         <v>43514</v>
       </c>
       <c r="B201" t="n">
-        <v>100.2042770385742</v>
+        <v>100.2042617797852</v>
       </c>
       <c r="C201" t="n">
-        <v>100.2042770385742</v>
+        <v>100.2042617797852</v>
       </c>
       <c r="D201" t="n">
-        <v>97.64022582062798</v>
+        <v>97.64021095228451</v>
       </c>
       <c r="E201" t="n">
-        <v>98.34755132834806</v>
+        <v>98.34753635229529</v>
       </c>
       <c r="F201" t="n">
         <v>154800</v>
@@ -4452,16 +4452,16 @@
         <v>43515</v>
       </c>
       <c r="B202" t="n">
-        <v>98.43596649169922</v>
+        <v>98.43595886230469</v>
       </c>
       <c r="C202" t="n">
-        <v>101.0000177935829</v>
+        <v>101.0000099654586</v>
       </c>
       <c r="D202" t="n">
-        <v>98.2591351089804</v>
+        <v>98.2591274932914</v>
       </c>
       <c r="E202" t="n">
-        <v>100.2337509668275</v>
+        <v>100.2337431980935</v>
       </c>
       <c r="F202" t="n">
         <v>215600</v>
@@ -4472,16 +4472,16 @@
         <v>43516</v>
       </c>
       <c r="B203" t="n">
-        <v>97.25707244873047</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C203" t="n">
-        <v>99.17273905953849</v>
+        <v>99.17275461887898</v>
       </c>
       <c r="D203" t="n">
-        <v>95.51822968346485</v>
+        <v>95.5182446694446</v>
       </c>
       <c r="E203" t="n">
-        <v>98.87802515522462</v>
+        <v>98.87804066832706</v>
       </c>
       <c r="F203" t="n">
         <v>616733</v>
@@ -4532,16 +4532,16 @@
         <v>43521</v>
       </c>
       <c r="B206" t="n">
-        <v>95.40036010742188</v>
+        <v>95.40036773681641</v>
       </c>
       <c r="C206" t="n">
-        <v>97.10972496939742</v>
+        <v>97.10973273549394</v>
       </c>
       <c r="D206" t="n">
-        <v>92.24687368297073</v>
+        <v>92.24688106017342</v>
       </c>
       <c r="E206" t="n">
-        <v>93.66151710543296</v>
+        <v>93.66152459576807</v>
       </c>
       <c r="F206" t="n">
         <v>404566</v>
@@ -4552,16 +4552,16 @@
         <v>43522</v>
       </c>
       <c r="B207" t="n">
-        <v>95.13510894775391</v>
+        <v>95.13511657714844</v>
       </c>
       <c r="C207" t="n">
-        <v>97.25708531592029</v>
+        <v>97.25709311548748</v>
       </c>
       <c r="D207" t="n">
-        <v>93.36680280269279</v>
+        <v>93.36681029027736</v>
       </c>
       <c r="E207" t="n">
-        <v>95.57719110532733</v>
+        <v>95.5771987701748</v>
       </c>
       <c r="F207" t="n">
         <v>332133</v>
@@ -4592,16 +4592,16 @@
         <v>43524</v>
       </c>
       <c r="B209" t="n">
-        <v>96.04875183105469</v>
+        <v>96.04874420166016</v>
       </c>
       <c r="C209" t="n">
-        <v>96.46136341004065</v>
+        <v>96.46135574787134</v>
       </c>
       <c r="D209" t="n">
-        <v>94.75199078514714</v>
+        <v>94.75198325875762</v>
       </c>
       <c r="E209" t="n">
-        <v>95.69508904625457</v>
+        <v>95.69508144495236</v>
       </c>
       <c r="F209" t="n">
         <v>596166</v>
@@ -4612,16 +4612,16 @@
         <v>43525</v>
       </c>
       <c r="B210" t="n">
-        <v>95.42982482910156</v>
+        <v>95.42983245849609</v>
       </c>
       <c r="C210" t="n">
-        <v>96.66764430511837</v>
+        <v>96.66765203347371</v>
       </c>
       <c r="D210" t="n">
-        <v>94.60460934673134</v>
+        <v>94.60461691015179</v>
       </c>
       <c r="E210" t="n">
-        <v>95.28246411849148</v>
+        <v>95.28247173610485</v>
       </c>
       <c r="F210" t="n">
         <v>326633</v>
@@ -4652,16 +4652,16 @@
         <v>43531</v>
       </c>
       <c r="B212" t="n">
-        <v>96.10769653320312</v>
+        <v>96.10768127441406</v>
       </c>
       <c r="C212" t="n">
-        <v>96.22557912639819</v>
+        <v>96.22556384889319</v>
       </c>
       <c r="D212" t="n">
-        <v>94.89934748740488</v>
+        <v>94.89933242046251</v>
       </c>
       <c r="E212" t="n">
-        <v>95.72456311516235</v>
+        <v>95.72454791720247</v>
       </c>
       <c r="F212" t="n">
         <v>372100</v>
@@ -4672,16 +4672,16 @@
         <v>43532</v>
       </c>
       <c r="B213" t="n">
-        <v>96.63817596435547</v>
+        <v>96.63819122314453</v>
       </c>
       <c r="C213" t="n">
-        <v>96.75605853959034</v>
+        <v>96.75607381699261</v>
       </c>
       <c r="D213" t="n">
-        <v>95.63612910439541</v>
+        <v>95.63614420496521</v>
       </c>
       <c r="E213" t="n">
-        <v>95.69507039201285</v>
+        <v>95.69508550188925</v>
       </c>
       <c r="F213" t="n">
         <v>212466</v>
@@ -4692,16 +4692,16 @@
         <v>43535</v>
       </c>
       <c r="B214" t="n">
-        <v>97.3160400390625</v>
+        <v>97.31603240966797</v>
       </c>
       <c r="C214" t="n">
-        <v>97.522342076377</v>
+        <v>97.52233443080878</v>
       </c>
       <c r="D214" t="n">
-        <v>96.19611041073888</v>
+        <v>96.19610286914474</v>
       </c>
       <c r="E214" t="n">
-        <v>97.2570987412808</v>
+        <v>97.25709111650715</v>
       </c>
       <c r="F214" t="n">
         <v>533833</v>
@@ -4712,16 +4712,16 @@
         <v>43536</v>
       </c>
       <c r="B215" t="n">
-        <v>97.25707244873047</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C215" t="n">
-        <v>98.49489183306302</v>
+        <v>98.49490728605517</v>
       </c>
       <c r="D215" t="n">
-        <v>95.34139834284592</v>
+        <v>95.34141330108237</v>
       </c>
       <c r="E215" t="n">
-        <v>96.84446848564514</v>
+        <v>96.84448367970022</v>
       </c>
       <c r="F215" t="n">
         <v>275666</v>
@@ -4752,16 +4752,16 @@
         <v>43538</v>
       </c>
       <c r="B217" t="n">
-        <v>91.06800842285156</v>
+        <v>91.06800079345703</v>
       </c>
       <c r="C217" t="n">
-        <v>94.86987955903906</v>
+        <v>94.86987161113559</v>
       </c>
       <c r="D217" t="n">
-        <v>90.62593369553892</v>
+        <v>90.62592610318003</v>
       </c>
       <c r="E217" t="n">
-        <v>94.86987955903906</v>
+        <v>94.86987161113559</v>
       </c>
       <c r="F217" t="n">
         <v>2325333</v>
@@ -4852,16 +4852,16 @@
         <v>43545</v>
       </c>
       <c r="B222" t="n">
-        <v>88.38607025146484</v>
+        <v>88.38607788085938</v>
       </c>
       <c r="C222" t="n">
-        <v>89.27022715947268</v>
+        <v>89.27023486518674</v>
       </c>
       <c r="D222" t="n">
-        <v>87.6198034295508</v>
+        <v>87.61981099280197</v>
       </c>
       <c r="E222" t="n">
-        <v>89.27022715947268</v>
+        <v>89.27023486518674</v>
       </c>
       <c r="F222" t="n">
         <v>454533</v>
@@ -4872,16 +4872,16 @@
         <v>43546</v>
       </c>
       <c r="B223" t="n">
-        <v>87.82608795166016</v>
+        <v>87.82610321044922</v>
       </c>
       <c r="C223" t="n">
-        <v>87.94397051917699</v>
+        <v>87.94398579844682</v>
       </c>
       <c r="D223" t="n">
-        <v>86.55879788531681</v>
+        <v>86.55881292392856</v>
       </c>
       <c r="E223" t="n">
-        <v>87.94397051917699</v>
+        <v>87.94398579844682</v>
       </c>
       <c r="F223" t="n">
         <v>257266</v>
@@ -4972,16 +4972,16 @@
         <v>43553</v>
       </c>
       <c r="B228" t="n">
-        <v>90.65540313720703</v>
+        <v>90.65538787841797</v>
       </c>
       <c r="C228" t="n">
-        <v>91.80480340897347</v>
+        <v>91.80478795672153</v>
       </c>
       <c r="D228" t="n">
-        <v>88.68078722501544</v>
+        <v>88.68077229858658</v>
       </c>
       <c r="E228" t="n">
-        <v>90.7732932272902</v>
+        <v>90.7732779486583</v>
       </c>
       <c r="F228" t="n">
         <v>379666</v>
@@ -5012,16 +5012,16 @@
         <v>43557</v>
       </c>
       <c r="B230" t="n">
-        <v>91.6868896484375</v>
+        <v>91.68689727783203</v>
       </c>
       <c r="C230" t="n">
-        <v>91.92266225338324</v>
+        <v>91.92266990239673</v>
       </c>
       <c r="D230" t="n">
-        <v>89.88910573492085</v>
+        <v>89.88911321471926</v>
       </c>
       <c r="E230" t="n">
-        <v>91.65741151462781</v>
+        <v>91.65741914156942</v>
       </c>
       <c r="F230" t="n">
         <v>264800</v>
@@ -5032,16 +5032,16 @@
         <v>43558</v>
       </c>
       <c r="B231" t="n">
-        <v>88.88706970214844</v>
+        <v>88.88707733154297</v>
       </c>
       <c r="C231" t="n">
-        <v>92.77735937298839</v>
+        <v>92.777367336296</v>
       </c>
       <c r="D231" t="n">
-        <v>88.88706970214844</v>
+        <v>88.88707733154297</v>
       </c>
       <c r="E231" t="n">
-        <v>92.71841059337896</v>
+        <v>92.71841855162685</v>
       </c>
       <c r="F231" t="n">
         <v>371500</v>
@@ -5072,16 +5072,16 @@
         <v>43560</v>
       </c>
       <c r="B233" t="n">
-        <v>84.73155212402344</v>
+        <v>84.73154449462891</v>
       </c>
       <c r="C233" t="n">
-        <v>87.94397984584793</v>
+        <v>87.94397192720014</v>
       </c>
       <c r="D233" t="n">
-        <v>84.4368306838219</v>
+        <v>84.43682308096466</v>
       </c>
       <c r="E233" t="n">
-        <v>87.08930116040308</v>
+        <v>87.08929331871222</v>
       </c>
       <c r="F233" t="n">
         <v>673866</v>
@@ -5092,16 +5092,16 @@
         <v>43563</v>
       </c>
       <c r="B234" t="n">
-        <v>82.52116394042969</v>
+        <v>82.52117919921875</v>
       </c>
       <c r="C234" t="n">
-        <v>85.88095238775713</v>
+        <v>85.88096826779656</v>
       </c>
       <c r="D234" t="n">
-        <v>82.25591314480629</v>
+        <v>82.25592835454846</v>
       </c>
       <c r="E234" t="n">
-        <v>85.02626620586047</v>
+        <v>85.02628192786193</v>
       </c>
       <c r="F234" t="n">
         <v>619400</v>
@@ -5112,16 +5112,16 @@
         <v>43564</v>
       </c>
       <c r="B235" t="n">
-        <v>82.81588745117188</v>
+        <v>82.81586456298828</v>
       </c>
       <c r="C235" t="n">
-        <v>84.05370715186686</v>
+        <v>84.05368392158171</v>
       </c>
       <c r="D235" t="n">
-        <v>80.90022035075691</v>
+        <v>80.90019799201448</v>
       </c>
       <c r="E235" t="n">
-        <v>82.22645199681945</v>
+        <v>82.22642927154068</v>
       </c>
       <c r="F235" t="n">
         <v>535633</v>
@@ -5152,16 +5152,16 @@
         <v>43566</v>
       </c>
       <c r="B237" t="n">
-        <v>84.34842681884766</v>
+        <v>84.34841918945312</v>
       </c>
       <c r="C237" t="n">
-        <v>84.61367014434416</v>
+        <v>84.61366249095812</v>
       </c>
       <c r="D237" t="n">
-        <v>82.40328161658626</v>
+        <v>82.40327416313194</v>
       </c>
       <c r="E237" t="n">
-        <v>83.78846202495211</v>
+        <v>83.78845444620694</v>
       </c>
       <c r="F237" t="n">
         <v>403133</v>
@@ -5172,16 +5172,16 @@
         <v>43567</v>
       </c>
       <c r="B238" t="n">
-        <v>82.72746276855469</v>
+        <v>82.72747802734375</v>
       </c>
       <c r="C238" t="n">
-        <v>84.73154900085372</v>
+        <v>84.73156462928944</v>
       </c>
       <c r="D238" t="n">
-        <v>82.34432940746136</v>
+        <v>82.34434459558283</v>
       </c>
       <c r="E238" t="n">
-        <v>84.34841563976039</v>
+        <v>84.3484311975285</v>
       </c>
       <c r="F238" t="n">
         <v>343366</v>
@@ -5192,16 +5192,16 @@
         <v>43570</v>
       </c>
       <c r="B239" t="n">
-        <v>83.96529388427734</v>
+        <v>83.96527862548828</v>
       </c>
       <c r="C239" t="n">
-        <v>84.37789794631881</v>
+        <v>84.37788261254832</v>
       </c>
       <c r="D239" t="n">
-        <v>82.58011346803741</v>
+        <v>82.5800984609735</v>
       </c>
       <c r="E239" t="n">
-        <v>82.81588614704992</v>
+        <v>82.81587109713966</v>
       </c>
       <c r="F239" t="n">
         <v>210900</v>
@@ -5212,16 +5212,16 @@
         <v>43571</v>
       </c>
       <c r="B240" t="n">
-        <v>83.58214569091797</v>
+        <v>83.5821533203125</v>
       </c>
       <c r="C240" t="n">
-        <v>84.40735366908453</v>
+        <v>84.40736137380419</v>
       </c>
       <c r="D240" t="n">
-        <v>82.58009886591343</v>
+        <v>82.58010640384093</v>
       </c>
       <c r="E240" t="n">
-        <v>83.11059292119636</v>
+        <v>83.11060050754746</v>
       </c>
       <c r="F240" t="n">
         <v>215300</v>
@@ -5232,16 +5232,16 @@
         <v>43572</v>
       </c>
       <c r="B241" t="n">
-        <v>82.66852569580078</v>
+        <v>82.66853332519531</v>
       </c>
       <c r="C241" t="n">
-        <v>84.23052986373555</v>
+        <v>84.23053763728586</v>
       </c>
       <c r="D241" t="n">
-        <v>81.46017676799576</v>
+        <v>81.460184285873</v>
       </c>
       <c r="E241" t="n">
-        <v>84.20105921831454</v>
+        <v>84.20106698914505</v>
       </c>
       <c r="F241" t="n">
         <v>289766</v>
@@ -5272,16 +5272,16 @@
         <v>43577</v>
       </c>
       <c r="B243" t="n">
-        <v>84.58419036865234</v>
+        <v>84.58419799804688</v>
       </c>
       <c r="C243" t="n">
-        <v>86.26408456905386</v>
+        <v>86.26409234997288</v>
       </c>
       <c r="D243" t="n">
-        <v>82.3148607901397</v>
+        <v>82.31486821484337</v>
       </c>
       <c r="E243" t="n">
-        <v>83.49373154636193</v>
+        <v>83.49373907739835</v>
       </c>
       <c r="F243" t="n">
         <v>461666</v>
@@ -5312,16 +5312,16 @@
         <v>43579</v>
       </c>
       <c r="B245" t="n">
-        <v>86.51290893554688</v>
+        <v>86.51292419433594</v>
       </c>
       <c r="C245" t="n">
-        <v>87.07525732554228</v>
+        <v>87.07527268351602</v>
       </c>
       <c r="D245" t="n">
-        <v>85.06264005424757</v>
+        <v>85.0626550572442</v>
       </c>
       <c r="E245" t="n">
-        <v>86.27612511987749</v>
+        <v>86.27614033690361</v>
       </c>
       <c r="F245" t="n">
         <v>361900</v>
@@ -5332,16 +5332,16 @@
         <v>43580</v>
       </c>
       <c r="B246" t="n">
-        <v>87.90398406982422</v>
+        <v>87.90399932861328</v>
       </c>
       <c r="C246" t="n">
-        <v>88.5551283166666</v>
+        <v>88.55514368848435</v>
       </c>
       <c r="D246" t="n">
-        <v>84.88506172132999</v>
+        <v>84.88507645608024</v>
       </c>
       <c r="E246" t="n">
-        <v>87.01606351821326</v>
+        <v>87.01607862287288</v>
       </c>
       <c r="F246" t="n">
         <v>486633</v>
@@ -5472,16 +5472,16 @@
         <v>43592</v>
       </c>
       <c r="B253" t="n">
-        <v>96.93116760253906</v>
+        <v>96.93115997314453</v>
       </c>
       <c r="C253" t="n">
-        <v>97.64150408089029</v>
+        <v>97.64149639558559</v>
       </c>
       <c r="D253" t="n">
-        <v>89.47264963381808</v>
+        <v>89.47264259147906</v>
       </c>
       <c r="E253" t="n">
-        <v>90.8341228660023</v>
+        <v>90.83411571650254</v>
       </c>
       <c r="F253" t="n">
         <v>3210933</v>
@@ -5492,16 +5492,16 @@
         <v>43593</v>
       </c>
       <c r="B254" t="n">
-        <v>102.3474655151367</v>
+        <v>102.3474731445312</v>
       </c>
       <c r="C254" t="n">
-        <v>104.4488787191065</v>
+        <v>104.4488865051489</v>
       </c>
       <c r="D254" t="n">
-        <v>98.88457916470847</v>
+        <v>98.88458653596543</v>
       </c>
       <c r="E254" t="n">
-        <v>100.630824151866</v>
+        <v>100.6308316532951</v>
       </c>
       <c r="F254" t="n">
         <v>1898166</v>
@@ -5512,16 +5512,16 @@
         <v>43594</v>
       </c>
       <c r="B255" t="n">
-        <v>105.2184219360352</v>
+        <v>105.2184143066406</v>
       </c>
       <c r="C255" t="n">
-        <v>106.3727150372369</v>
+        <v>106.3727073241445</v>
       </c>
       <c r="D255" t="n">
-        <v>99.7725135411105</v>
+        <v>99.77250630659914</v>
       </c>
       <c r="E255" t="n">
-        <v>101.4891626693933</v>
+        <v>101.4891553104076</v>
       </c>
       <c r="F255" t="n">
         <v>781533</v>
@@ -5532,16 +5532,16 @@
         <v>43595</v>
       </c>
       <c r="B256" t="n">
-        <v>103.5905456542969</v>
+        <v>103.5905609130859</v>
       </c>
       <c r="C256" t="n">
-        <v>105.2183985914037</v>
+        <v>105.218414089974</v>
       </c>
       <c r="D256" t="n">
-        <v>101.3411521529779</v>
+        <v>101.3411670804334</v>
       </c>
       <c r="E256" t="n">
-        <v>105.2183985914037</v>
+        <v>105.218414089974</v>
       </c>
       <c r="F256" t="n">
         <v>440400</v>
@@ -5592,16 +5592,16 @@
         <v>43600</v>
       </c>
       <c r="B259" t="n">
-        <v>103.5905456542969</v>
+        <v>103.5905609130859</v>
       </c>
       <c r="C259" t="n">
-        <v>104.3304781232561</v>
+        <v>104.3304934910366</v>
       </c>
       <c r="D259" t="n">
-        <v>100.9267842498542</v>
+        <v>100.9267991162737</v>
       </c>
       <c r="E259" t="n">
-        <v>101.607524529931</v>
+        <v>101.6075394966229</v>
       </c>
       <c r="F259" t="n">
         <v>328866</v>
@@ -5612,16 +5612,16 @@
         <v>43601</v>
       </c>
       <c r="B260" t="n">
-        <v>102.5842437744141</v>
+        <v>102.5842361450195</v>
       </c>
       <c r="C260" t="n">
-        <v>103.6793445426467</v>
+        <v>103.6793368318073</v>
       </c>
       <c r="D260" t="n">
-        <v>102.5842437744141</v>
+        <v>102.5842361450195</v>
       </c>
       <c r="E260" t="n">
-        <v>103.5905562502412</v>
+        <v>103.5905485460052</v>
       </c>
       <c r="F260" t="n">
         <v>583833</v>
@@ -5672,16 +5672,16 @@
         <v>43606</v>
       </c>
       <c r="B263" t="n">
-        <v>108.3557281494141</v>
+        <v>108.3557205200195</v>
       </c>
       <c r="C263" t="n">
-        <v>109.8355933002327</v>
+        <v>109.8355855666399</v>
       </c>
       <c r="D263" t="n">
-        <v>105.8103582835301</v>
+        <v>105.8103508333566</v>
       </c>
       <c r="E263" t="n">
-        <v>105.8103582835301</v>
+        <v>105.8103508333566</v>
       </c>
       <c r="F263" t="n">
         <v>554800</v>
@@ -5732,16 +5732,16 @@
         <v>43609</v>
       </c>
       <c r="B266" t="n">
-        <v>110.3979263305664</v>
+        <v>110.39794921875</v>
       </c>
       <c r="C266" t="n">
-        <v>111.9073873691671</v>
+        <v>111.9074105702988</v>
       </c>
       <c r="D266" t="n">
-        <v>109.9539623311659</v>
+        <v>109.9539851273049</v>
       </c>
       <c r="E266" t="n">
-        <v>111.1970509917121</v>
+        <v>111.1970740455737</v>
       </c>
       <c r="F266" t="n">
         <v>294000</v>
@@ -5752,16 +5752,16 @@
         <v>43612</v>
       </c>
       <c r="B267" t="n">
-        <v>109.953971862793</v>
+        <v>109.9539794921875</v>
       </c>
       <c r="C267" t="n">
-        <v>111.7298129603736</v>
+        <v>111.7298207129887</v>
       </c>
       <c r="D267" t="n">
-        <v>109.6875994616474</v>
+        <v>109.6876070725591</v>
       </c>
       <c r="E267" t="n">
-        <v>110.0427676811635</v>
+        <v>110.0427753167193</v>
       </c>
       <c r="F267" t="n">
         <v>77066</v>
@@ -5772,16 +5772,16 @@
         <v>43613</v>
       </c>
       <c r="B268" t="n">
-        <v>109.3028335571289</v>
+        <v>109.3028411865234</v>
       </c>
       <c r="C268" t="n">
-        <v>111.0786671019285</v>
+        <v>111.0786748552771</v>
       </c>
       <c r="D268" t="n">
-        <v>107.0830359808923</v>
+        <v>107.0830434553438</v>
       </c>
       <c r="E268" t="n">
-        <v>110.5755184040759</v>
+        <v>110.5755261223044</v>
       </c>
       <c r="F268" t="n">
         <v>402233</v>
@@ -5792,16 +5792,16 @@
         <v>43614</v>
       </c>
       <c r="B269" t="n">
-        <v>109.9243774414062</v>
+        <v>109.9243698120117</v>
       </c>
       <c r="C269" t="n">
-        <v>110.1019615538715</v>
+        <v>110.1019539121516</v>
       </c>
       <c r="D269" t="n">
-        <v>108.3557240537826</v>
+        <v>108.3557165332617</v>
       </c>
       <c r="E269" t="n">
-        <v>109.2732407136891</v>
+        <v>109.2732331294873</v>
       </c>
       <c r="F269" t="n">
         <v>725533</v>
@@ -5812,16 +5812,16 @@
         <v>43615</v>
       </c>
       <c r="B270" t="n">
-        <v>107.7045822143555</v>
+        <v>107.7045745849609</v>
       </c>
       <c r="C270" t="n">
-        <v>111.6410213474626</v>
+        <v>111.6410134392252</v>
       </c>
       <c r="D270" t="n">
-        <v>107.7045822143555</v>
+        <v>107.7045745849609</v>
       </c>
       <c r="E270" t="n">
-        <v>109.9243799064583</v>
+        <v>109.9243721198215</v>
       </c>
       <c r="F270" t="n">
         <v>452966</v>
@@ -5832,16 +5832,16 @@
         <v>43616</v>
       </c>
       <c r="B271" t="n">
-        <v>108.8588790893555</v>
+        <v>108.8588714599609</v>
       </c>
       <c r="C271" t="n">
-        <v>110.4275400950732</v>
+        <v>110.4275323557388</v>
       </c>
       <c r="D271" t="n">
-        <v>106.8462615401803</v>
+        <v>106.8462540518404</v>
       </c>
       <c r="E271" t="n">
-        <v>107.4086175348022</v>
+        <v>107.4086100070495</v>
       </c>
       <c r="F271" t="n">
         <v>504400</v>
@@ -5852,16 +5852,16 @@
         <v>43619</v>
       </c>
       <c r="B272" t="n">
-        <v>109.8651733398438</v>
+        <v>109.8651809692383</v>
       </c>
       <c r="C272" t="n">
-        <v>110.7530938059435</v>
+        <v>110.7531014969981</v>
       </c>
       <c r="D272" t="n">
-        <v>108.6220846873041</v>
+        <v>108.6220922303745</v>
       </c>
       <c r="E272" t="n">
-        <v>108.7996687805241</v>
+        <v>108.7996763359265</v>
       </c>
       <c r="F272" t="n">
         <v>294000</v>
@@ -5872,16 +5872,16 @@
         <v>43620</v>
       </c>
       <c r="B273" t="n">
-        <v>107.1718292236328</v>
+        <v>107.1718368530273</v>
       </c>
       <c r="C273" t="n">
-        <v>110.9898839409142</v>
+        <v>110.9898918421101</v>
       </c>
       <c r="D273" t="n">
-        <v>107.1718292236328</v>
+        <v>107.1718368530273</v>
       </c>
       <c r="E273" t="n">
-        <v>109.5988071159028</v>
+        <v>109.5988149180701</v>
       </c>
       <c r="F273" t="n">
         <v>283866</v>
@@ -5892,16 +5892,16 @@
         <v>43621</v>
       </c>
       <c r="B274" t="n">
-        <v>108.8884735107422</v>
+        <v>108.8884658813477</v>
       </c>
       <c r="C274" t="n">
-        <v>109.835586243175</v>
+        <v>109.83557854742</v>
       </c>
       <c r="D274" t="n">
-        <v>106.4022960019959</v>
+        <v>106.4022885467982</v>
       </c>
       <c r="E274" t="n">
-        <v>106.6390723033584</v>
+        <v>106.6390648315707</v>
       </c>
       <c r="F274" t="n">
         <v>231033</v>
@@ -5932,16 +5932,16 @@
         <v>43623</v>
       </c>
       <c r="B276" t="n">
-        <v>110.6051254272461</v>
+        <v>110.6051177978516</v>
       </c>
       <c r="C276" t="n">
-        <v>110.664317626492</v>
+        <v>110.6643099930145</v>
       </c>
       <c r="D276" t="n">
-        <v>108.9180800058842</v>
+        <v>108.9180724928598</v>
       </c>
       <c r="E276" t="n">
-        <v>109.2140485290975</v>
+        <v>109.2140409956576</v>
       </c>
       <c r="F276" t="n">
         <v>204266</v>
@@ -5952,16 +5952,16 @@
         <v>43626</v>
       </c>
       <c r="B277" t="n">
-        <v>114.3935775756836</v>
+        <v>114.3935699462891</v>
       </c>
       <c r="C277" t="n">
-        <v>119.3955216779974</v>
+        <v>119.395513715002</v>
       </c>
       <c r="D277" t="n">
-        <v>111.8778112380962</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="E277" t="n">
-        <v>111.8778112380962</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="F277" t="n">
         <v>585833</v>
@@ -6012,16 +6012,16 @@
         <v>43629</v>
       </c>
       <c r="B280" t="n">
-        <v>113.8608093261719</v>
+        <v>113.8608169555664</v>
       </c>
       <c r="C280" t="n">
-        <v>114.9855061253982</v>
+        <v>114.9855138301545</v>
       </c>
       <c r="D280" t="n">
-        <v>108.9180656395131</v>
+        <v>108.9180729377125</v>
       </c>
       <c r="E280" t="n">
-        <v>108.9180656395131</v>
+        <v>108.9180729377125</v>
       </c>
       <c r="F280" t="n">
         <v>845300</v>
@@ -6032,16 +6032,16 @@
         <v>43630</v>
       </c>
       <c r="B281" t="n">
-        <v>111.9369964599609</v>
+        <v>111.9369888305664</v>
       </c>
       <c r="C281" t="n">
-        <v>114.156794133742</v>
+        <v>114.1567863530506</v>
       </c>
       <c r="D281" t="n">
-        <v>110.753107378071</v>
+        <v>110.7530998293679</v>
       </c>
       <c r="E281" t="n">
-        <v>113.3576693798154</v>
+        <v>113.3576616535908</v>
       </c>
       <c r="F281" t="n">
         <v>560666</v>
@@ -6072,16 +6072,16 @@
         <v>43634</v>
       </c>
       <c r="B283" t="n">
-        <v>112.4697494506836</v>
+        <v>112.4697570800781</v>
       </c>
       <c r="C283" t="n">
-        <v>113.1800859146894</v>
+        <v>113.1800935922697</v>
       </c>
       <c r="D283" t="n">
-        <v>110.0131754518161</v>
+        <v>110.0131829145687</v>
       </c>
       <c r="E283" t="n">
-        <v>110.9602882281628</v>
+        <v>110.9602957551629</v>
       </c>
       <c r="F283" t="n">
         <v>583133</v>
@@ -6112,16 +6112,16 @@
         <v>43637</v>
       </c>
       <c r="B285" t="n">
-        <v>116.4653778076172</v>
+        <v>116.4653701782227</v>
       </c>
       <c r="C285" t="n">
-        <v>116.4949814320171</v>
+        <v>116.4949738006833</v>
       </c>
       <c r="D285" t="n">
-        <v>114.5415562056919</v>
+        <v>114.5415487023227</v>
       </c>
       <c r="E285" t="n">
-        <v>115.3998806656956</v>
+        <v>115.3998731060995</v>
       </c>
       <c r="F285" t="n">
         <v>285566</v>
@@ -6132,16 +6132,16 @@
         <v>43640</v>
       </c>
       <c r="B286" t="n">
-        <v>116.5245742797852</v>
+        <v>116.5245666503906</v>
       </c>
       <c r="C286" t="n">
-        <v>117.5012831022177</v>
+        <v>117.5012754088736</v>
       </c>
       <c r="D286" t="n">
-        <v>115.0447092343492</v>
+        <v>115.0447017018482</v>
       </c>
       <c r="E286" t="n">
-        <v>116.6133625695595</v>
+        <v>116.6133549343516</v>
       </c>
       <c r="F286" t="n">
         <v>315633</v>
@@ -6152,16 +6152,16 @@
         <v>43641</v>
       </c>
       <c r="B287" t="n">
-        <v>114.4823760986328</v>
+        <v>114.4823684692383</v>
       </c>
       <c r="C287" t="n">
-        <v>117.1165344246257</v>
+        <v>117.1165266196842</v>
       </c>
       <c r="D287" t="n">
-        <v>113.8312317787781</v>
+        <v>113.8312241927775</v>
       </c>
       <c r="E287" t="n">
-        <v>116.583782033922</v>
+        <v>116.5837742644845</v>
       </c>
       <c r="F287" t="n">
         <v>481433</v>
@@ -6172,16 +6172,16 @@
         <v>43642</v>
       </c>
       <c r="B288" t="n">
-        <v>113.1208877563477</v>
+        <v>113.1208724975586</v>
       </c>
       <c r="C288" t="n">
-        <v>115.72544980908</v>
+        <v>115.7254341989635</v>
       </c>
       <c r="D288" t="n">
-        <v>112.6769312236937</v>
+        <v>112.6769160247896</v>
       </c>
       <c r="E288" t="n">
-        <v>115.72544980908</v>
+        <v>115.7254341989635</v>
       </c>
       <c r="F288" t="n">
         <v>335833</v>
@@ -6232,16 +6232,16 @@
         <v>43647</v>
       </c>
       <c r="B291" t="n">
-        <v>114.068000793457</v>
+        <v>114.0679931640625</v>
       </c>
       <c r="C291" t="n">
-        <v>117.0573269909192</v>
+        <v>117.0573191615848</v>
       </c>
       <c r="D291" t="n">
-        <v>114.068000793457</v>
+        <v>114.0679931640625</v>
       </c>
       <c r="E291" t="n">
-        <v>117.0573269909192</v>
+        <v>117.0573191615848</v>
       </c>
       <c r="F291" t="n">
         <v>436066</v>
@@ -6272,16 +6272,16 @@
         <v>43649</v>
       </c>
       <c r="B293" t="n">
-        <v>109.9691619873047</v>
+        <v>109.9691543579102</v>
       </c>
       <c r="C293" t="n">
-        <v>110.8608053529641</v>
+        <v>110.8607976617096</v>
       </c>
       <c r="D293" t="n">
-        <v>107.323959634633</v>
+        <v>107.3239521887562</v>
       </c>
       <c r="E293" t="n">
-        <v>110.7121968655973</v>
+        <v>110.7121891846528</v>
       </c>
       <c r="F293" t="n">
         <v>1690900</v>
@@ -6352,16 +6352,16 @@
         <v>43656</v>
       </c>
       <c r="B297" t="n">
-        <v>128.0398101806641</v>
+        <v>128.039794921875</v>
       </c>
       <c r="C297" t="n">
-        <v>128.0398101806641</v>
+        <v>128.039794921875</v>
       </c>
       <c r="D297" t="n">
-        <v>121.9171932723939</v>
+        <v>121.9171787432507</v>
       </c>
       <c r="E297" t="n">
-        <v>121.9171932723939</v>
+        <v>121.9171787432507</v>
       </c>
       <c r="F297" t="n">
         <v>529166</v>
@@ -6372,16 +6372,16 @@
         <v>43657</v>
       </c>
       <c r="B298" t="n">
-        <v>123.1654586791992</v>
+        <v>123.1654510498047</v>
       </c>
       <c r="C298" t="n">
-        <v>130.1797020465908</v>
+        <v>130.1796939827041</v>
       </c>
       <c r="D298" t="n">
-        <v>123.1060183088487</v>
+        <v>123.1060106831362</v>
       </c>
       <c r="E298" t="n">
-        <v>130.1797020465908</v>
+        <v>130.1796939827041</v>
       </c>
       <c r="F298" t="n">
         <v>660700</v>
@@ -6392,16 +6392,16 @@
         <v>43658</v>
       </c>
       <c r="B299" t="n">
-        <v>124.8001327514648</v>
+        <v>124.8001403808594</v>
       </c>
       <c r="C299" t="n">
-        <v>125.8700971749934</v>
+        <v>125.8701048697979</v>
       </c>
       <c r="D299" t="n">
-        <v>122.7196367142455</v>
+        <v>122.7196442164533</v>
       </c>
       <c r="E299" t="n">
-        <v>124.2057063920509</v>
+        <v>124.2057139851064</v>
       </c>
       <c r="F299" t="n">
         <v>362933</v>
@@ -6412,16 +6412,16 @@
         <v>43661</v>
       </c>
       <c r="B300" t="n">
-        <v>121.5605010986328</v>
+        <v>121.5605087280273</v>
       </c>
       <c r="C300" t="n">
-        <v>126.7320249772505</v>
+        <v>126.7320329312208</v>
       </c>
       <c r="D300" t="n">
-        <v>118.5289212629776</v>
+        <v>118.5289287021037</v>
       </c>
       <c r="E300" t="n">
-        <v>124.9784660186075</v>
+        <v>124.9784738625208</v>
       </c>
       <c r="F300" t="n">
         <v>1110366</v>
@@ -6432,16 +6432,16 @@
         <v>43662</v>
       </c>
       <c r="B301" t="n">
-        <v>124.1462783813477</v>
+        <v>124.1462631225586</v>
       </c>
       <c r="C301" t="n">
-        <v>124.2354465067623</v>
+        <v>124.2354312370136</v>
       </c>
       <c r="D301" t="n">
-        <v>120.4608237797831</v>
+        <v>120.4608089739724</v>
       </c>
       <c r="E301" t="n">
-        <v>121.560516122461</v>
+        <v>121.5605011814873</v>
       </c>
       <c r="F301" t="n">
         <v>378300</v>
@@ -6452,16 +6452,16 @@
         <v>43663</v>
       </c>
       <c r="B302" t="n">
-        <v>126.6131362915039</v>
+        <v>126.6131286621094</v>
       </c>
       <c r="C302" t="n">
-        <v>127.9505975350065</v>
+        <v>127.9505898250198</v>
       </c>
       <c r="D302" t="n">
-        <v>122.7493610455057</v>
+        <v>122.7493536489327</v>
       </c>
       <c r="E302" t="n">
-        <v>123.9679339896924</v>
+        <v>123.9679265196912</v>
       </c>
       <c r="F302" t="n">
         <v>443966</v>
@@ -6492,16 +6492,16 @@
         <v>43665</v>
       </c>
       <c r="B304" t="n">
-        <v>126.9995193481445</v>
+        <v>126.9995269775391</v>
       </c>
       <c r="C304" t="n">
-        <v>132.379084421508</v>
+        <v>132.3790923740756</v>
       </c>
       <c r="D304" t="n">
-        <v>126.9995193481445</v>
+        <v>126.9995269775391</v>
       </c>
       <c r="E304" t="n">
-        <v>129.9419385720236</v>
+        <v>129.9419463781816</v>
       </c>
       <c r="F304" t="n">
         <v>683033</v>
@@ -6512,16 +6512,16 @@
         <v>43668</v>
       </c>
       <c r="B305" t="n">
-        <v>127.4453582763672</v>
+        <v>127.4453506469727</v>
       </c>
       <c r="C305" t="n">
-        <v>129.0800291741361</v>
+        <v>129.0800214468836</v>
       </c>
       <c r="D305" t="n">
-        <v>126.0781766437745</v>
+        <v>126.078169096225</v>
       </c>
       <c r="E305" t="n">
-        <v>126.3456659089508</v>
+        <v>126.3456583453883</v>
       </c>
       <c r="F305" t="n">
         <v>163233</v>
@@ -6532,16 +6532,16 @@
         <v>43669</v>
       </c>
       <c r="B306" t="n">
-        <v>125.0676422119141</v>
+        <v>125.067626953125</v>
       </c>
       <c r="C306" t="n">
-        <v>127.8020129780693</v>
+        <v>127.8019973856753</v>
       </c>
       <c r="D306" t="n">
-        <v>123.6410126715648</v>
+        <v>123.6409975868307</v>
       </c>
       <c r="E306" t="n">
-        <v>127.4750757819822</v>
+        <v>127.4750602294759</v>
       </c>
       <c r="F306" t="n">
         <v>528700</v>
@@ -6552,16 +6552,16 @@
         <v>43670</v>
       </c>
       <c r="B307" t="n">
-        <v>128.8719787597656</v>
+        <v>128.8719940185547</v>
       </c>
       <c r="C307" t="n">
-        <v>131.8441184494731</v>
+        <v>131.8441340601715</v>
       </c>
       <c r="D307" t="n">
-        <v>124.9487552763768</v>
+        <v>124.9487700706457</v>
       </c>
       <c r="E307" t="n">
-        <v>124.9487552763768</v>
+        <v>124.9487700706457</v>
       </c>
       <c r="F307" t="n">
         <v>788600</v>
@@ -6572,16 +6572,16 @@
         <v>43671</v>
       </c>
       <c r="B308" t="n">
-        <v>126.4645462036133</v>
+        <v>126.4645538330078</v>
       </c>
       <c r="C308" t="n">
-        <v>131.3388459566314</v>
+        <v>131.3388538800843</v>
       </c>
       <c r="D308" t="n">
-        <v>126.0484408996179</v>
+        <v>126.0484485039095</v>
       </c>
       <c r="E308" t="n">
-        <v>129.3177976048466</v>
+        <v>129.3178054063731</v>
       </c>
       <c r="F308" t="n">
         <v>3248566</v>
@@ -6592,16 +6592,16 @@
         <v>43672</v>
       </c>
       <c r="B309" t="n">
-        <v>125.6620635986328</v>
+        <v>125.6620712280273</v>
       </c>
       <c r="C309" t="n">
-        <v>127.9208885740418</v>
+        <v>127.9208963405777</v>
       </c>
       <c r="D309" t="n">
-        <v>125.0676371669792</v>
+        <v>125.067644760284</v>
       </c>
       <c r="E309" t="n">
-        <v>127.2075738326406</v>
+        <v>127.2075815558686</v>
       </c>
       <c r="F309" t="n">
         <v>1585266</v>
@@ -6632,16 +6632,16 @@
         <v>43676</v>
       </c>
       <c r="B311" t="n">
-        <v>124.384033203125</v>
+        <v>124.3840484619141</v>
       </c>
       <c r="C311" t="n">
-        <v>126.3753687791254</v>
+        <v>126.3753842822012</v>
       </c>
       <c r="D311" t="n">
-        <v>124.2948726464664</v>
+        <v>124.2948878943177</v>
       </c>
       <c r="E311" t="n">
-        <v>126.2267602928194</v>
+        <v>126.2267757776647</v>
       </c>
       <c r="F311" t="n">
         <v>1065500</v>
@@ -6652,16 +6652,16 @@
         <v>43677</v>
       </c>
       <c r="B312" t="n">
-        <v>124.2354354858398</v>
+        <v>124.2354278564453</v>
       </c>
       <c r="C312" t="n">
-        <v>126.1673231821166</v>
+        <v>126.1673154340833</v>
       </c>
       <c r="D312" t="n">
-        <v>121.1444076132553</v>
+        <v>121.1444001736832</v>
       </c>
       <c r="E312" t="n">
-        <v>125.5728967800731</v>
+        <v>125.572889068544</v>
       </c>
       <c r="F312" t="n">
         <v>1188566</v>
@@ -6692,16 +6692,16 @@
         <v>43679</v>
       </c>
       <c r="B314" t="n">
-        <v>124.0868225097656</v>
+        <v>124.0868301391602</v>
       </c>
       <c r="C314" t="n">
-        <v>124.8001371898471</v>
+        <v>124.8001448630993</v>
       </c>
       <c r="D314" t="n">
-        <v>122.4521442943359</v>
+        <v>122.4521518232233</v>
       </c>
       <c r="E314" t="n">
-        <v>122.6601931496027</v>
+        <v>122.6602006912819</v>
       </c>
       <c r="F314" t="n">
         <v>454366</v>
@@ -6712,16 +6712,16 @@
         <v>43682</v>
       </c>
       <c r="B315" t="n">
-        <v>123.4032363891602</v>
+        <v>123.4032440185547</v>
       </c>
       <c r="C315" t="n">
-        <v>124.3543201742961</v>
+        <v>124.3543278624913</v>
       </c>
       <c r="D315" t="n">
-        <v>121.8577261831319</v>
+        <v>121.8577337169754</v>
       </c>
       <c r="E315" t="n">
-        <v>124.057110743121</v>
+        <v>124.0571184129413</v>
       </c>
       <c r="F315" t="n">
         <v>384500</v>
@@ -6732,16 +6732,16 @@
         <v>43683</v>
       </c>
       <c r="B316" t="n">
-        <v>126.6131362915039</v>
+        <v>126.6131286621094</v>
       </c>
       <c r="C316" t="n">
-        <v>127.1778424858068</v>
+        <v>127.1778348223845</v>
       </c>
       <c r="D316" t="n">
-        <v>123.1357385701055</v>
+        <v>123.1357311502504</v>
       </c>
       <c r="E316" t="n">
-        <v>123.1951789404927</v>
+        <v>123.1951715170559</v>
       </c>
       <c r="F316" t="n">
         <v>466533</v>
@@ -6752,16 +6752,16 @@
         <v>43684</v>
       </c>
       <c r="B317" t="n">
-        <v>128.5153198242188</v>
+        <v>128.5153350830078</v>
       </c>
       <c r="C317" t="n">
-        <v>129.2583547375794</v>
+        <v>129.2583700845899</v>
       </c>
       <c r="D317" t="n">
-        <v>124.7406973245383</v>
+        <v>124.7407121351615</v>
       </c>
       <c r="E317" t="n">
-        <v>126.6131447015237</v>
+        <v>126.613159734465</v>
       </c>
       <c r="F317" t="n">
         <v>506366</v>
@@ -6772,16 +6772,16 @@
         <v>43685</v>
       </c>
       <c r="B318" t="n">
-        <v>131.9035491943359</v>
+        <v>131.903564453125</v>
       </c>
       <c r="C318" t="n">
-        <v>133.5679400428555</v>
+        <v>133.5679554941837</v>
       </c>
       <c r="D318" t="n">
-        <v>129.2880670630315</v>
+        <v>129.2880820192579</v>
       </c>
       <c r="E318" t="n">
-        <v>129.2880670630315</v>
+        <v>129.2880820192579</v>
       </c>
       <c r="F318" t="n">
         <v>971500</v>
@@ -6792,16 +6792,16 @@
         <v>43686</v>
       </c>
       <c r="B319" t="n">
-        <v>131.5171966552734</v>
+        <v>131.5171813964844</v>
       </c>
       <c r="C319" t="n">
-        <v>134.8757142928603</v>
+        <v>134.8756986444118</v>
       </c>
       <c r="D319" t="n">
-        <v>129.4069723912467</v>
+        <v>129.4069573772885</v>
       </c>
       <c r="E319" t="n">
-        <v>134.8757142928603</v>
+        <v>134.8756986444118</v>
       </c>
       <c r="F319" t="n">
         <v>371566</v>
@@ -6832,16 +6832,16 @@
         <v>43690</v>
       </c>
       <c r="B321" t="n">
-        <v>131.0713806152344</v>
+        <v>131.0713500976562</v>
       </c>
       <c r="C321" t="n">
-        <v>133.7760238565671</v>
+        <v>133.7759927092622</v>
       </c>
       <c r="D321" t="n">
-        <v>128.8125553627015</v>
+        <v>128.8125253710496</v>
       </c>
       <c r="E321" t="n">
-        <v>133.6571430907768</v>
+        <v>133.6571119711511</v>
       </c>
       <c r="F321" t="n">
         <v>614133</v>
@@ -6852,16 +6852,16 @@
         <v>43691</v>
       </c>
       <c r="B322" t="n">
-        <v>137.0156707763672</v>
+        <v>137.0156555175781</v>
       </c>
       <c r="C322" t="n">
-        <v>140.9686076982084</v>
+        <v>140.9685919991994</v>
       </c>
       <c r="D322" t="n">
-        <v>135.2323835739525</v>
+        <v>135.2323685137598</v>
       </c>
       <c r="E322" t="n">
-        <v>139.6905940214455</v>
+        <v>139.6905784647628</v>
       </c>
       <c r="F322" t="n">
         <v>1453733</v>
@@ -6892,16 +6892,16 @@
         <v>43693</v>
       </c>
       <c r="B324" t="n">
-        <v>145.6348571777344</v>
+        <v>145.6348419189453</v>
       </c>
       <c r="C324" t="n">
-        <v>145.6348571777344</v>
+        <v>145.6348419189453</v>
       </c>
       <c r="D324" t="n">
-        <v>137.2236956985838</v>
+        <v>137.2236813210683</v>
       </c>
       <c r="E324" t="n">
-        <v>141.8305216795594</v>
+        <v>141.8305068193669</v>
       </c>
       <c r="F324" t="n">
         <v>930266</v>
@@ -6912,16 +6912,16 @@
         <v>43696</v>
       </c>
       <c r="B325" t="n">
-        <v>141.8899383544922</v>
+        <v>141.8899688720703</v>
       </c>
       <c r="C325" t="n">
-        <v>147.0911823847387</v>
+        <v>147.0912140209964</v>
       </c>
       <c r="D325" t="n">
-        <v>140.7308057846586</v>
+        <v>140.7308360529314</v>
       </c>
       <c r="E325" t="n">
-        <v>147.0911823847387</v>
+        <v>147.0912140209964</v>
       </c>
       <c r="F325" t="n">
         <v>598666</v>
@@ -6952,16 +6952,16 @@
         <v>43698</v>
       </c>
       <c r="B327" t="n">
-        <v>148.5772857666016</v>
+        <v>148.5772705078125</v>
       </c>
       <c r="C327" t="n">
-        <v>148.7258867257254</v>
+        <v>148.7258714516751</v>
       </c>
       <c r="D327" t="n">
-        <v>143.4057607498814</v>
+        <v>143.4057460222045</v>
       </c>
       <c r="E327" t="n">
-        <v>146.8237188635079</v>
+        <v>146.8237037848091</v>
       </c>
       <c r="F327" t="n">
         <v>558733</v>
@@ -6972,16 +6972,16 @@
         <v>43699</v>
       </c>
       <c r="B328" t="n">
-        <v>148.5475158691406</v>
+        <v>148.5475311279297</v>
       </c>
       <c r="C328" t="n">
-        <v>151.3115986035568</v>
+        <v>151.3116141462722</v>
       </c>
       <c r="D328" t="n">
-        <v>146.8236697346897</v>
+        <v>146.8236848164054</v>
       </c>
       <c r="E328" t="n">
-        <v>148.5772360510207</v>
+        <v>148.5772513128626</v>
       </c>
       <c r="F328" t="n">
         <v>509000</v>
@@ -7012,16 +7012,16 @@
         <v>43703</v>
       </c>
       <c r="B330" t="n">
-        <v>143.5543212890625</v>
+        <v>143.5543365478516</v>
       </c>
       <c r="C330" t="n">
-        <v>146.2292587368132</v>
+        <v>146.2292742799288</v>
       </c>
       <c r="D330" t="n">
-        <v>141.2063360934986</v>
+        <v>141.2063511027138</v>
       </c>
       <c r="E330" t="n">
-        <v>143.3165598214097</v>
+        <v>143.3165750549265</v>
       </c>
       <c r="F330" t="n">
         <v>278200</v>
@@ -7032,16 +7032,16 @@
         <v>43704</v>
       </c>
       <c r="B331" t="n">
-        <v>145.4862365722656</v>
+        <v>145.4862213134766</v>
       </c>
       <c r="C331" t="n">
-        <v>146.4670329458183</v>
+        <v>146.467017584162</v>
       </c>
       <c r="D331" t="n">
-        <v>141.7710621461821</v>
+        <v>141.7710472770454</v>
       </c>
       <c r="E331" t="n">
-        <v>143.4057328468255</v>
+        <v>143.4057178062424</v>
       </c>
       <c r="F331" t="n">
         <v>495866</v>
@@ -7052,16 +7052,16 @@
         <v>43705</v>
       </c>
       <c r="B332" t="n">
-        <v>145.6348571777344</v>
+        <v>145.6348419189453</v>
       </c>
       <c r="C332" t="n">
-        <v>146.5859334937354</v>
+        <v>146.585918135298</v>
       </c>
       <c r="D332" t="n">
-        <v>143.9704509491044</v>
+        <v>143.9704358647023</v>
       </c>
       <c r="E332" t="n">
-        <v>145.6942975578488</v>
+        <v>145.6942822928319</v>
       </c>
       <c r="F332" t="n">
         <v>446600</v>
@@ -7072,16 +7072,16 @@
         <v>43706</v>
       </c>
       <c r="B333" t="n">
-        <v>150.0930328369141</v>
+        <v>150.0930480957031</v>
       </c>
       <c r="C333" t="n">
-        <v>151.1035644194901</v>
+        <v>151.1035797810121</v>
       </c>
       <c r="D333" t="n">
-        <v>145.9617610738686</v>
+        <v>145.9617759126635</v>
       </c>
       <c r="E333" t="n">
-        <v>146.5264596731645</v>
+        <v>146.5264745693678</v>
       </c>
       <c r="F333" t="n">
         <v>1067466</v>
@@ -7092,16 +7092,16 @@
         <v>43707</v>
       </c>
       <c r="B334" t="n">
-        <v>153.6893463134766</v>
+        <v>153.6893310546875</v>
       </c>
       <c r="C334" t="n">
-        <v>153.6893463134766</v>
+        <v>153.6893310546875</v>
       </c>
       <c r="D334" t="n">
-        <v>149.884996068173</v>
+        <v>149.8849811870925</v>
       </c>
       <c r="E334" t="n">
-        <v>150.984688344605</v>
+        <v>150.9846733543434</v>
       </c>
       <c r="F334" t="n">
         <v>973933</v>
@@ -7132,16 +7132,16 @@
         <v>43711</v>
       </c>
       <c r="B336" t="n">
-        <v>154.5512542724609</v>
+        <v>154.55126953125</v>
       </c>
       <c r="C336" t="n">
-        <v>157.107296061017</v>
+        <v>157.1073115721632</v>
       </c>
       <c r="D336" t="n">
-        <v>153.2137854482698</v>
+        <v>153.213800575011</v>
       </c>
       <c r="E336" t="n">
-        <v>154.2540372985203</v>
+        <v>154.2540525279653</v>
       </c>
       <c r="F336" t="n">
         <v>578066</v>
@@ -7152,16 +7152,16 @@
         <v>43712</v>
       </c>
       <c r="B337" t="n">
-        <v>149.4689178466797</v>
+        <v>149.4688873291016</v>
       </c>
       <c r="C337" t="n">
-        <v>156.185953130973</v>
+        <v>156.1859212419549</v>
       </c>
       <c r="D337" t="n">
-        <v>147.9828478259584</v>
+        <v>147.9828176117963</v>
       </c>
       <c r="E337" t="n">
-        <v>155.9779117936402</v>
+        <v>155.9778799470986</v>
       </c>
       <c r="F337" t="n">
         <v>865766</v>
@@ -7212,16 +7212,16 @@
         <v>43717</v>
       </c>
       <c r="B340" t="n">
-        <v>142.9004974365234</v>
+        <v>142.9004821777344</v>
       </c>
       <c r="C340" t="n">
-        <v>146.7345532203692</v>
+        <v>146.734537552183</v>
       </c>
       <c r="D340" t="n">
-        <v>139.7203009673272</v>
+        <v>139.7202860481167</v>
       </c>
       <c r="E340" t="n">
-        <v>146.7345532203692</v>
+        <v>146.734537552183</v>
       </c>
       <c r="F340" t="n">
         <v>1841333</v>
@@ -7332,16 +7332,16 @@
         <v>43725</v>
       </c>
       <c r="B346" t="n">
-        <v>153.0652008056641</v>
+        <v>153.065185546875</v>
       </c>
       <c r="C346" t="n">
-        <v>153.0652008056641</v>
+        <v>153.065185546875</v>
       </c>
       <c r="D346" t="n">
-        <v>149.0825292121116</v>
+        <v>149.0825143503477</v>
       </c>
       <c r="E346" t="n">
-        <v>150.3902779897587</v>
+        <v>150.3902629976278</v>
       </c>
       <c r="F346" t="n">
         <v>1122433</v>
@@ -7352,16 +7352,16 @@
         <v>43726</v>
       </c>
       <c r="B347" t="n">
-        <v>152.4707641601562</v>
+        <v>152.4707489013672</v>
       </c>
       <c r="C347" t="n">
-        <v>153.2137991026854</v>
+        <v>153.2137837695358</v>
       </c>
       <c r="D347" t="n">
-        <v>151.4007920288641</v>
+        <v>151.4007768771544</v>
       </c>
       <c r="E347" t="n">
-        <v>151.4305273342831</v>
+        <v>151.4305121795976</v>
       </c>
       <c r="F347" t="n">
         <v>459166</v>
@@ -7372,16 +7372,16 @@
         <v>43727</v>
       </c>
       <c r="B348" t="n">
-        <v>153.0354461669922</v>
+        <v>153.0354614257812</v>
       </c>
       <c r="C348" t="n">
-        <v>155.3834312599305</v>
+        <v>155.3834467528314</v>
       </c>
       <c r="D348" t="n">
-        <v>151.5493765907869</v>
+        <v>151.5493917014036</v>
       </c>
       <c r="E348" t="n">
-        <v>154.4026350145672</v>
+        <v>154.4026504096753</v>
       </c>
       <c r="F348" t="n">
         <v>446666</v>
@@ -7392,16 +7392,16 @@
         <v>43728</v>
       </c>
       <c r="B349" t="n">
-        <v>153.7190551757812</v>
+        <v>153.7190399169922</v>
       </c>
       <c r="C349" t="n">
-        <v>155.056508851016</v>
+        <v>155.0564934594657</v>
       </c>
       <c r="D349" t="n">
-        <v>150.984677221191</v>
+        <v>150.9846622338277</v>
       </c>
       <c r="E349" t="n">
-        <v>153.0651808721112</v>
+        <v>153.0651656782284</v>
       </c>
       <c r="F349" t="n">
         <v>555866</v>
@@ -7412,16 +7412,16 @@
         <v>43731</v>
       </c>
       <c r="B350" t="n">
-        <v>157.9394989013672</v>
+        <v>157.9395141601562</v>
       </c>
       <c r="C350" t="n">
-        <v>159.0986315487212</v>
+        <v>159.0986469194959</v>
       </c>
       <c r="D350" t="n">
-        <v>153.6893458610692</v>
+        <v>153.6893607092441</v>
       </c>
       <c r="E350" t="n">
-        <v>154.5512615205438</v>
+        <v>154.5512764519898</v>
       </c>
       <c r="F350" t="n">
         <v>685766</v>
@@ -7472,16 +7472,16 @@
         <v>43734</v>
       </c>
       <c r="B353" t="n">
-        <v>157.3747863769531</v>
+        <v>157.3748016357422</v>
       </c>
       <c r="C353" t="n">
-        <v>159.4255546903437</v>
+        <v>159.4255701479717</v>
       </c>
       <c r="D353" t="n">
-        <v>154.9970658002995</v>
+        <v>154.9970808285488</v>
       </c>
       <c r="E353" t="n">
-        <v>155.4726038687971</v>
+        <v>155.4726189431538</v>
       </c>
       <c r="F353" t="n">
         <v>815966</v>
@@ -7512,16 +7512,16 @@
         <v>43738</v>
       </c>
       <c r="B355" t="n">
-        <v>160.0497283935547</v>
+        <v>160.0497131347656</v>
       </c>
       <c r="C355" t="n">
-        <v>161.5655184551029</v>
+        <v>161.5655030518017</v>
       </c>
       <c r="D355" t="n">
-        <v>157.5234065852795</v>
+        <v>157.5233915673444</v>
       </c>
       <c r="E355" t="n">
-        <v>158.3853222744112</v>
+        <v>158.385307174303</v>
       </c>
       <c r="F355" t="n">
         <v>546766</v>
@@ -7552,16 +7552,16 @@
         <v>43740</v>
       </c>
       <c r="B357" t="n">
-        <v>156.0373382568359</v>
+        <v>156.0373229980469</v>
       </c>
       <c r="C357" t="n">
-        <v>159.0689184099495</v>
+        <v>159.0689028547042</v>
       </c>
       <c r="D357" t="n">
-        <v>154.4323876150899</v>
+        <v>154.4323725132479</v>
       </c>
       <c r="E357" t="n">
-        <v>156.5723167650564</v>
+        <v>156.5723014539522</v>
       </c>
       <c r="F357" t="n">
         <v>1285800</v>
@@ -7612,16 +7612,16 @@
         <v>43745</v>
       </c>
       <c r="B360" t="n">
-        <v>161.4168853759766</v>
+        <v>161.4169006347656</v>
       </c>
       <c r="C360" t="n">
-        <v>163.7054454381041</v>
+        <v>163.7054609132314</v>
       </c>
       <c r="D360" t="n">
-        <v>159.6336138095562</v>
+        <v>159.6336288997721</v>
       </c>
       <c r="E360" t="n">
-        <v>161.6249417878365</v>
+        <v>161.6249570662932</v>
       </c>
       <c r="F360" t="n">
         <v>812666</v>
@@ -7632,16 +7632,16 @@
         <v>43746</v>
       </c>
       <c r="B361" t="n">
-        <v>160.6441497802734</v>
+        <v>160.6441345214844</v>
       </c>
       <c r="C361" t="n">
-        <v>163.7351854449085</v>
+        <v>163.7351698925173</v>
       </c>
       <c r="D361" t="n">
-        <v>158.2664439924785</v>
+        <v>158.2664289595359</v>
       </c>
       <c r="E361" t="n">
-        <v>161.416904917161</v>
+        <v>161.4168895849718</v>
       </c>
       <c r="F361" t="n">
         <v>478600</v>
@@ -7652,16 +7652,16 @@
         <v>43747</v>
       </c>
       <c r="B362" t="n">
-        <v>162.27880859375</v>
+        <v>162.2788238525391</v>
       </c>
       <c r="C362" t="n">
-        <v>162.9029475663277</v>
+        <v>162.9029628838034</v>
       </c>
       <c r="D362" t="n">
-        <v>159.9605284537628</v>
+        <v>159.960543494568</v>
       </c>
       <c r="E362" t="n">
-        <v>161.9815916407176</v>
+        <v>161.9816068715598</v>
       </c>
       <c r="F362" t="n">
         <v>623966</v>
@@ -7672,16 +7672,16 @@
         <v>43748</v>
       </c>
       <c r="B363" t="n">
-        <v>163.1704559326172</v>
+        <v>163.1704711914062</v>
       </c>
       <c r="C363" t="n">
-        <v>163.7648898809297</v>
+        <v>163.7649051953069</v>
       </c>
       <c r="D363" t="n">
-        <v>161.387169204763</v>
+        <v>161.3871842967891</v>
       </c>
       <c r="E363" t="n">
-        <v>162.2193797558171</v>
+        <v>162.2193949256669</v>
       </c>
       <c r="F363" t="n">
         <v>538133</v>
@@ -7692,16 +7692,16 @@
         <v>43749</v>
       </c>
       <c r="B364" t="n">
-        <v>167.2422790527344</v>
+        <v>167.2422943115234</v>
       </c>
       <c r="C364" t="n">
-        <v>168.282530850187</v>
+        <v>168.2825462038862</v>
       </c>
       <c r="D364" t="n">
-        <v>163.764881450249</v>
+        <v>163.7648963917685</v>
       </c>
       <c r="E364" t="n">
-        <v>163.764881450249</v>
+        <v>163.7648963917685</v>
       </c>
       <c r="F364" t="n">
         <v>518100</v>
@@ -7732,16 +7732,16 @@
         <v>43753</v>
       </c>
       <c r="B366" t="n">
-        <v>167.3314514160156</v>
+        <v>167.3314361572266</v>
       </c>
       <c r="C366" t="n">
-        <v>169.2038987367602</v>
+        <v>169.2038833072246</v>
       </c>
       <c r="D366" t="n">
-        <v>167.1828504846405</v>
+        <v>167.1828352394022</v>
       </c>
       <c r="E366" t="n">
-        <v>167.3017312297406</v>
+        <v>167.3017159736617</v>
       </c>
       <c r="F366" t="n">
         <v>550533</v>
@@ -7772,16 +7772,16 @@
         <v>43755</v>
       </c>
       <c r="B368" t="n">
-        <v>169.7686309814453</v>
+        <v>169.7686157226562</v>
       </c>
       <c r="C368" t="n">
-        <v>172.9785475021482</v>
+        <v>172.9785319548521</v>
       </c>
       <c r="D368" t="n">
-        <v>168.8769799449297</v>
+        <v>168.8769647662821</v>
       </c>
       <c r="E368" t="n">
-        <v>171.2547009252195</v>
+        <v>171.2546855328626</v>
       </c>
       <c r="F368" t="n">
         <v>460533</v>
@@ -7812,16 +7812,16 @@
         <v>43759</v>
       </c>
       <c r="B370" t="n">
-        <v>168.5203247070312</v>
+        <v>168.5203399658203</v>
       </c>
       <c r="C370" t="n">
-        <v>171.7302258637203</v>
+        <v>171.7302414131521</v>
       </c>
       <c r="D370" t="n">
-        <v>167.9853311028604</v>
+        <v>167.9853463132081</v>
       </c>
       <c r="E370" t="n">
-        <v>171.314128125523</v>
+        <v>171.3141436372789</v>
       </c>
       <c r="F370" t="n">
         <v>853400</v>
@@ -7832,16 +7832,16 @@
         <v>43760</v>
       </c>
       <c r="B371" t="n">
-        <v>166.8856201171875</v>
+        <v>166.8856048583984</v>
       </c>
       <c r="C371" t="n">
-        <v>169.8874796268238</v>
+        <v>169.8874640935668</v>
       </c>
       <c r="D371" t="n">
-        <v>165.3401100865331</v>
+        <v>165.340094969054</v>
       </c>
       <c r="E371" t="n">
-        <v>169.6497181556968</v>
+        <v>169.6497026441791</v>
       </c>
       <c r="F371" t="n">
         <v>630100</v>
@@ -7852,16 +7852,16 @@
         <v>43761</v>
       </c>
       <c r="B372" t="n">
-        <v>165.8453826904297</v>
+        <v>165.8453979492188</v>
       </c>
       <c r="C372" t="n">
-        <v>168.758081900606</v>
+        <v>168.7580974273812</v>
       </c>
       <c r="D372" t="n">
-        <v>164.9537468623316</v>
+        <v>164.9537620390848</v>
       </c>
       <c r="E372" t="n">
-        <v>167.2422919225891</v>
+        <v>167.2423073099024</v>
       </c>
       <c r="F372" t="n">
         <v>595766</v>
@@ -7912,16 +7912,16 @@
         <v>43766</v>
       </c>
       <c r="B375" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0063781738281</v>
       </c>
       <c r="C375" t="n">
-        <v>170.5710921032597</v>
+        <v>170.5710767937866</v>
       </c>
       <c r="D375" t="n">
-        <v>167.6881130247363</v>
+        <v>167.6880979740227</v>
       </c>
       <c r="E375" t="n">
-        <v>169.3525190838025</v>
+        <v>169.3525038837014</v>
       </c>
       <c r="F375" t="n">
         <v>598700</v>
@@ -7952,16 +7952,16 @@
         <v>43768</v>
       </c>
       <c r="B377" t="n">
-        <v>167.628662109375</v>
+        <v>167.6286926269531</v>
       </c>
       <c r="C377" t="n">
-        <v>169.4713891747379</v>
+        <v>169.4714200277931</v>
       </c>
       <c r="D377" t="n">
-        <v>166.3209286110662</v>
+        <v>166.3209588905653</v>
       </c>
       <c r="E377" t="n">
-        <v>169.1147318357295</v>
+        <v>169.1147626238536</v>
       </c>
       <c r="F377" t="n">
         <v>545966</v>
@@ -7972,16 +7972,16 @@
         <v>43769</v>
       </c>
       <c r="B378" t="n">
-        <v>167.3314514160156</v>
+        <v>167.3314361572266</v>
       </c>
       <c r="C378" t="n">
-        <v>168.520319335351</v>
+        <v>168.5203039681503</v>
       </c>
       <c r="D378" t="n">
-        <v>166.1425986137638</v>
+        <v>166.142583463385</v>
       </c>
       <c r="E378" t="n">
-        <v>167.5989482095744</v>
+        <v>167.5989329263926</v>
       </c>
       <c r="F378" t="n">
         <v>595400</v>
@@ -7992,16 +7992,16 @@
         <v>43770</v>
       </c>
       <c r="B379" t="n">
-        <v>168.6689453125</v>
+        <v>168.6689147949219</v>
       </c>
       <c r="C379" t="n">
-        <v>168.8769866473174</v>
+        <v>168.876956092098</v>
       </c>
       <c r="D379" t="n">
-        <v>166.9748188578435</v>
+        <v>166.9747886467867</v>
       </c>
       <c r="E379" t="n">
-        <v>167.3314762631877</v>
+        <v>167.3314459876003</v>
       </c>
       <c r="F379" t="n">
         <v>1063666</v>
@@ -8052,16 +8052,16 @@
         <v>43775</v>
       </c>
       <c r="B382" t="n">
-        <v>163.4973754882812</v>
+        <v>163.4974060058594</v>
       </c>
       <c r="C382" t="n">
-        <v>164.5970675922943</v>
+        <v>164.5970983151352</v>
       </c>
       <c r="D382" t="n">
-        <v>160.1388588112277</v>
+        <v>160.1388887019224</v>
       </c>
       <c r="E382" t="n">
-        <v>161.9221453470707</v>
+        <v>161.9221755706244</v>
       </c>
       <c r="F382" t="n">
         <v>1813233</v>
@@ -8072,16 +8072,16 @@
         <v>43776</v>
       </c>
       <c r="B383" t="n">
-        <v>164.4782257080078</v>
+        <v>164.4782104492188</v>
       </c>
       <c r="C383" t="n">
-        <v>166.5884347498103</v>
+        <v>166.5884192952553</v>
       </c>
       <c r="D383" t="n">
-        <v>162.6354983719431</v>
+        <v>162.6354832841055</v>
       </c>
       <c r="E383" t="n">
-        <v>164.3296096432904</v>
+        <v>164.3295943982886</v>
       </c>
       <c r="F383" t="n">
         <v>718100</v>
@@ -8192,16 +8192,16 @@
         <v>43787</v>
       </c>
       <c r="B389" t="n">
-        <v>161.6249694824219</v>
+        <v>161.6249389648438</v>
       </c>
       <c r="C389" t="n">
-        <v>163.021878883618</v>
+        <v>163.0218481022793</v>
       </c>
       <c r="D389" t="n">
-        <v>158.8311506800296</v>
+        <v>158.8311206899726</v>
       </c>
       <c r="E389" t="n">
-        <v>161.5952492923612</v>
+        <v>161.5952187803947</v>
       </c>
       <c r="F389" t="n">
         <v>1204133</v>
@@ -8212,16 +8212,16 @@
         <v>43788</v>
       </c>
       <c r="B390" t="n">
-        <v>159.5741882324219</v>
+        <v>159.5741577148438</v>
       </c>
       <c r="C390" t="n">
-        <v>162.7841048643803</v>
+        <v>162.7840737329255</v>
       </c>
       <c r="D390" t="n">
-        <v>158.5339513293935</v>
+        <v>158.5339210107543</v>
       </c>
       <c r="E390" t="n">
-        <v>162.6355039116865</v>
+        <v>162.6354728086507</v>
       </c>
       <c r="F390" t="n">
         <v>1296633</v>
@@ -8232,16 +8232,16 @@
         <v>43790</v>
       </c>
       <c r="B391" t="n">
-        <v>165.0429077148438</v>
+        <v>165.0429229736328</v>
       </c>
       <c r="C391" t="n">
-        <v>165.4590054431674</v>
+        <v>165.4590207404262</v>
       </c>
       <c r="D391" t="n">
-        <v>159.4552858933658</v>
+        <v>159.4553006355599</v>
       </c>
       <c r="E391" t="n">
-        <v>159.9011038082066</v>
+        <v>159.9011185916181</v>
       </c>
       <c r="F391" t="n">
         <v>1440266</v>
@@ -8252,16 +8252,16 @@
         <v>43791</v>
       </c>
       <c r="B392" t="n">
-        <v>169.9766387939453</v>
+        <v>169.9766540527344</v>
       </c>
       <c r="C392" t="n">
-        <v>169.9766387939453</v>
+        <v>169.9766540527344</v>
       </c>
       <c r="D392" t="n">
-        <v>164.2404165934975</v>
+        <v>164.2404313373464</v>
       </c>
       <c r="E392" t="n">
-        <v>165.1023321534766</v>
+        <v>165.1023469746995</v>
       </c>
       <c r="F392" t="n">
         <v>1134300</v>
@@ -8292,16 +8292,16 @@
         <v>43795</v>
       </c>
       <c r="B394" t="n">
-        <v>169.4119720458984</v>
+        <v>169.4119567871094</v>
       </c>
       <c r="C394" t="n">
-        <v>172.5029926633038</v>
+        <v>172.5029771261092</v>
       </c>
       <c r="D394" t="n">
-        <v>167.4800841600201</v>
+        <v>167.4800690752345</v>
       </c>
       <c r="E394" t="n">
-        <v>170.9574823546011</v>
+        <v>170.9574669566093</v>
       </c>
       <c r="F394" t="n">
         <v>9961800</v>
@@ -8352,16 +8352,16 @@
         <v>43798</v>
       </c>
       <c r="B397" t="n">
-        <v>165.5481567382812</v>
+        <v>165.5481872558594</v>
       </c>
       <c r="C397" t="n">
-        <v>166.0831351338832</v>
+        <v>166.0831657500806</v>
       </c>
       <c r="D397" t="n">
-        <v>161.0899480122997</v>
+        <v>161.08997770804</v>
       </c>
       <c r="E397" t="n">
-        <v>163.6459743788308</v>
+        <v>163.6460045457557</v>
       </c>
       <c r="F397" t="n">
         <v>703133</v>
@@ -8372,16 +8372,16 @@
         <v>43801</v>
       </c>
       <c r="B398" t="n">
-        <v>167.182861328125</v>
+        <v>167.1828460693359</v>
       </c>
       <c r="C398" t="n">
-        <v>167.3017420809357</v>
+        <v>167.3017268112964</v>
       </c>
       <c r="D398" t="n">
-        <v>162.9624283154143</v>
+        <v>162.9624134418244</v>
       </c>
       <c r="E398" t="n">
-        <v>165.6373510732474</v>
+        <v>165.6373359555172</v>
       </c>
       <c r="F398" t="n">
         <v>805633</v>
@@ -8412,16 +8412,16 @@
         <v>43803</v>
       </c>
       <c r="B400" t="n">
-        <v>172.4435577392578</v>
+        <v>172.4435272216797</v>
       </c>
       <c r="C400" t="n">
-        <v>173.7215863852452</v>
+        <v>173.7215556414925</v>
       </c>
       <c r="D400" t="n">
-        <v>170.8980473816703</v>
+        <v>170.8980171376033</v>
       </c>
       <c r="E400" t="n">
-        <v>170.8980473816703</v>
+        <v>170.8980171376033</v>
       </c>
       <c r="F400" t="n">
         <v>662400</v>
@@ -8432,16 +8432,16 @@
         <v>43804</v>
       </c>
       <c r="B401" t="n">
-        <v>172.3543853759766</v>
+        <v>172.3543548583984</v>
       </c>
       <c r="C401" t="n">
-        <v>174.7618113181715</v>
+        <v>174.7617803743274</v>
       </c>
       <c r="D401" t="n">
-        <v>169.1147488144879</v>
+        <v>169.1147188705294</v>
       </c>
       <c r="E401" t="n">
-        <v>172.7110427507926</v>
+        <v>172.7110121700637</v>
       </c>
       <c r="F401" t="n">
         <v>632400</v>
@@ -8452,16 +8452,16 @@
         <v>43805</v>
       </c>
       <c r="B402" t="n">
-        <v>171.7302093505859</v>
+        <v>171.7302398681641</v>
       </c>
       <c r="C402" t="n">
-        <v>173.4243354447788</v>
+        <v>173.4243662634142</v>
       </c>
       <c r="D402" t="n">
-        <v>167.9555947654609</v>
+        <v>167.9556246122654</v>
       </c>
       <c r="E402" t="n">
-        <v>173.4243354447788</v>
+        <v>173.4243662634142</v>
       </c>
       <c r="F402" t="n">
         <v>837700</v>
@@ -8472,16 +8472,16 @@
         <v>43808</v>
       </c>
       <c r="B403" t="n">
-        <v>165.8453826904297</v>
+        <v>165.8453979492188</v>
       </c>
       <c r="C403" t="n">
-        <v>172.6218724288928</v>
+        <v>172.6218883111604</v>
       </c>
       <c r="D403" t="n">
-        <v>165.5779010122505</v>
+        <v>165.5779162464296</v>
       </c>
       <c r="E403" t="n">
-        <v>172.3840958200943</v>
+        <v>172.3841116804849</v>
       </c>
       <c r="F403" t="n">
         <v>793900</v>
@@ -8492,16 +8492,16 @@
         <v>43809</v>
       </c>
       <c r="B404" t="n">
-        <v>162.3382568359375</v>
+        <v>162.3382720947266</v>
       </c>
       <c r="C404" t="n">
-        <v>167.2720040741151</v>
+        <v>167.2720197966458</v>
       </c>
       <c r="D404" t="n">
-        <v>162.3382568359375</v>
+        <v>162.3382720947266</v>
       </c>
       <c r="E404" t="n">
-        <v>166.5884095841042</v>
+        <v>166.5884252423812</v>
       </c>
       <c r="F404" t="n">
         <v>1232166</v>
@@ -8512,16 +8512,16 @@
         <v>43810</v>
       </c>
       <c r="B405" t="n">
-        <v>167.0936889648438</v>
+        <v>167.0936737060547</v>
       </c>
       <c r="C405" t="n">
-        <v>167.0936889648438</v>
+        <v>167.0936737060547</v>
       </c>
       <c r="D405" t="n">
-        <v>161.981605315769</v>
+        <v>161.9815905238091</v>
       </c>
       <c r="E405" t="n">
-        <v>162.7840805747468</v>
+        <v>162.7840657095058</v>
       </c>
       <c r="F405" t="n">
         <v>789933</v>
@@ -8532,16 +8532,16 @@
         <v>43811</v>
       </c>
       <c r="B406" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0063781738281</v>
       </c>
       <c r="C406" t="n">
-        <v>170.214434741823</v>
+        <v>170.2144194643613</v>
       </c>
       <c r="D406" t="n">
-        <v>167.1234143540938</v>
+        <v>167.1233993540642</v>
       </c>
       <c r="E406" t="n">
-        <v>169.085022283454</v>
+        <v>169.0850071073618</v>
       </c>
       <c r="F406" t="n">
         <v>578333</v>
@@ -8612,16 +8612,16 @@
         <v>43817</v>
       </c>
       <c r="B410" t="n">
-        <v>180.4683380126953</v>
+        <v>180.4683227539062</v>
       </c>
       <c r="C410" t="n">
-        <v>180.4683380126953</v>
+        <v>180.4683227539062</v>
       </c>
       <c r="D410" t="n">
-        <v>171.6410788983919</v>
+        <v>171.6410643859569</v>
       </c>
       <c r="E410" t="n">
-        <v>171.6410788983919</v>
+        <v>171.6410643859569</v>
       </c>
       <c r="F410" t="n">
         <v>804400</v>
@@ -8632,16 +8632,16 @@
         <v>43818</v>
       </c>
       <c r="B411" t="n">
-        <v>184.7481842041016</v>
+        <v>184.7481994628906</v>
       </c>
       <c r="C411" t="n">
-        <v>185.7587158511149</v>
+        <v>185.7587311933661</v>
       </c>
       <c r="D411" t="n">
-        <v>178.922801154627</v>
+        <v>178.922815932284</v>
       </c>
       <c r="E411" t="n">
-        <v>181.3005066706881</v>
+        <v>181.3005216447253</v>
       </c>
       <c r="F411" t="n">
         <v>904966</v>
@@ -8672,16 +8672,16 @@
         <v>43822</v>
       </c>
       <c r="B413" t="n">
-        <v>187.8392333984375</v>
+        <v>187.8392486572266</v>
       </c>
       <c r="C413" t="n">
-        <v>190.4547157062448</v>
+        <v>190.454731177498</v>
       </c>
       <c r="D413" t="n">
-        <v>186.1748273205142</v>
+        <v>186.1748424440982</v>
       </c>
       <c r="E413" t="n">
-        <v>190.2169390902317</v>
+        <v>190.2169545421696</v>
       </c>
       <c r="F413" t="n">
         <v>629966</v>
@@ -8692,16 +8692,16 @@
         <v>43825</v>
       </c>
       <c r="B414" t="n">
-        <v>191.4057922363281</v>
+        <v>191.4057769775391</v>
       </c>
       <c r="C414" t="n">
-        <v>191.6435688527141</v>
+        <v>191.6435535749696</v>
       </c>
       <c r="D414" t="n">
-        <v>187.363680460271</v>
+        <v>187.3636655237174</v>
       </c>
       <c r="E414" t="n">
-        <v>188.7903099244187</v>
+        <v>188.7902948741348</v>
       </c>
       <c r="F414" t="n">
         <v>400133</v>
@@ -8732,16 +8732,16 @@
         <v>43829</v>
       </c>
       <c r="B416" t="n">
-        <v>189.9197082519531</v>
+        <v>189.9197235107422</v>
       </c>
       <c r="C416" t="n">
-        <v>193.3376656036019</v>
+        <v>193.3376811370011</v>
       </c>
       <c r="D416" t="n">
-        <v>188.047260998992</v>
+        <v>188.0472761073423</v>
       </c>
       <c r="E416" t="n">
-        <v>190.6627431160977</v>
+        <v>190.6627584345848</v>
       </c>
       <c r="F416" t="n">
         <v>1069533</v>
@@ -8792,16 +8792,16 @@
         <v>43836</v>
       </c>
       <c r="B419" t="n">
-        <v>199.4744415283203</v>
+        <v>199.4744567871094</v>
       </c>
       <c r="C419" t="n">
-        <v>205.1941331826866</v>
+        <v>205.1941488790033</v>
       </c>
       <c r="D419" t="n">
-        <v>196.3464730805705</v>
+        <v>196.3464881000858</v>
       </c>
       <c r="E419" t="n">
-        <v>203.4663025595861</v>
+        <v>203.4663181237324</v>
       </c>
       <c r="F419" t="n">
         <v>735666</v>
@@ -8812,16 +8812,16 @@
         <v>43837</v>
       </c>
       <c r="B420" t="n">
-        <v>193.9930877685547</v>
+        <v>193.9930725097656</v>
       </c>
       <c r="C420" t="n">
-        <v>200.1894326166796</v>
+        <v>200.1894168705087</v>
       </c>
       <c r="D420" t="n">
-        <v>193.9335100064037</v>
+        <v>193.9334947523008</v>
       </c>
       <c r="E420" t="n">
-        <v>198.4020239920258</v>
+        <v>198.4020083864459</v>
       </c>
       <c r="F420" t="n">
         <v>612400</v>
@@ -8832,16 +8832,16 @@
         <v>43838</v>
       </c>
       <c r="B421" t="n">
-        <v>190.001220703125</v>
+        <v>190.0012054443359</v>
       </c>
       <c r="C421" t="n">
-        <v>196.0188174190645</v>
+        <v>196.0188016770089</v>
       </c>
       <c r="D421" t="n">
-        <v>188.005289809351</v>
+        <v>188.0052747108529</v>
       </c>
       <c r="E421" t="n">
-        <v>193.9037309949236</v>
+        <v>193.9037154227282</v>
       </c>
       <c r="F421" t="n">
         <v>832966</v>
@@ -8872,16 +8872,16 @@
         <v>43840</v>
       </c>
       <c r="B423" t="n">
-        <v>184.8475189208984</v>
+        <v>184.8475036621094</v>
       </c>
       <c r="C423" t="n">
-        <v>190.6268041707359</v>
+        <v>190.6267884348786</v>
       </c>
       <c r="D423" t="n">
-        <v>182.3153731660564</v>
+        <v>182.3153581162909</v>
       </c>
       <c r="E423" t="n">
-        <v>190.6268041707359</v>
+        <v>190.6267884348786</v>
       </c>
       <c r="F423" t="n">
         <v>656333</v>
@@ -8892,16 +8892,16 @@
         <v>43843</v>
       </c>
       <c r="B424" t="n">
-        <v>185.8603668212891</v>
+        <v>185.8603820800781</v>
       </c>
       <c r="C424" t="n">
-        <v>186.6944856919212</v>
+        <v>186.6945010191898</v>
       </c>
       <c r="D424" t="n">
-        <v>183.6558989831735</v>
+        <v>183.6559140609799</v>
       </c>
       <c r="E424" t="n">
-        <v>184.6985551474751</v>
+        <v>184.6985703108816</v>
       </c>
       <c r="F424" t="n">
         <v>736233</v>
@@ -8912,16 +8912,16 @@
         <v>43844</v>
       </c>
       <c r="B425" t="n">
-        <v>186.1880645751953</v>
+        <v>186.1880798339844</v>
       </c>
       <c r="C425" t="n">
-        <v>186.5157573870905</v>
+        <v>186.5157726727352</v>
       </c>
       <c r="D425" t="n">
-        <v>180.40877977781</v>
+        <v>180.4087945629656</v>
       </c>
       <c r="E425" t="n">
-        <v>185.3241568042139</v>
+        <v>185.3241719922026</v>
       </c>
       <c r="F425" t="n">
         <v>863500</v>
@@ -8952,16 +8952,16 @@
         <v>43846</v>
       </c>
       <c r="B427" t="n">
-        <v>187.8563232421875</v>
+        <v>187.8562927246094</v>
       </c>
       <c r="C427" t="n">
-        <v>187.9159161571754</v>
+        <v>187.9158856299163</v>
       </c>
       <c r="D427" t="n">
-        <v>181.481245020747</v>
+        <v>181.4812155388111</v>
       </c>
       <c r="E427" t="n">
-        <v>181.7195712246231</v>
+        <v>181.7195417039707</v>
       </c>
       <c r="F427" t="n">
         <v>911900</v>
@@ -8972,16 +8972,16 @@
         <v>43847</v>
       </c>
       <c r="B428" t="n">
-        <v>187.6775665283203</v>
+        <v>187.6775817871094</v>
       </c>
       <c r="C428" t="n">
-        <v>191.5800610355412</v>
+        <v>191.5800766116156</v>
       </c>
       <c r="D428" t="n">
-        <v>185.3539431506457</v>
+        <v>185.3539582205168</v>
       </c>
       <c r="E428" t="n">
-        <v>189.1968599023401</v>
+        <v>189.1968752846526</v>
       </c>
       <c r="F428" t="n">
         <v>852600</v>
@@ -9012,16 +9012,16 @@
         <v>43851</v>
       </c>
       <c r="B430" t="n">
-        <v>190.0607757568359</v>
+        <v>190.060791015625</v>
       </c>
       <c r="C430" t="n">
-        <v>192.682303175826</v>
+        <v>192.682318645081</v>
       </c>
       <c r="D430" t="n">
-        <v>187.6775745221264</v>
+        <v>187.6775895895832</v>
       </c>
       <c r="E430" t="n">
-        <v>188.1542117386635</v>
+        <v>188.1542268443865</v>
       </c>
       <c r="F430" t="n">
         <v>1218200</v>
@@ -9092,16 +9092,16 @@
         <v>43857</v>
       </c>
       <c r="B434" t="n">
-        <v>182.4047393798828</v>
+        <v>182.4047088623047</v>
       </c>
       <c r="C434" t="n">
-        <v>189.7628958871874</v>
+        <v>189.7628641385387</v>
       </c>
       <c r="D434" t="n">
-        <v>180.5279641525161</v>
+        <v>180.5279339489355</v>
       </c>
       <c r="E434" t="n">
-        <v>189.7628958871874</v>
+        <v>189.7628641385387</v>
       </c>
       <c r="F434" t="n">
         <v>939566</v>
@@ -9112,16 +9112,16 @@
         <v>43858</v>
       </c>
       <c r="B435" t="n">
-        <v>186.1880645751953</v>
+        <v>186.1880798339844</v>
       </c>
       <c r="C435" t="n">
-        <v>186.7540684124517</v>
+        <v>186.7540837176268</v>
       </c>
       <c r="D435" t="n">
-        <v>182.4047255273511</v>
+        <v>182.4047404760818</v>
       </c>
       <c r="E435" t="n">
-        <v>184.4006561248688</v>
+        <v>184.4006712371732</v>
       </c>
       <c r="F435" t="n">
         <v>417866</v>
@@ -9132,16 +9132,16 @@
         <v>43859</v>
       </c>
       <c r="B436" t="n">
-        <v>182.6132354736328</v>
+        <v>182.6132507324219</v>
       </c>
       <c r="C436" t="n">
-        <v>187.5286121716265</v>
+        <v>187.5286278411344</v>
       </c>
       <c r="D436" t="n">
-        <v>181.1237310565493</v>
+        <v>181.1237461908784</v>
       </c>
       <c r="E436" t="n">
-        <v>186.9328043439841</v>
+        <v>186.9328199637075</v>
       </c>
       <c r="F436" t="n">
         <v>838300</v>
@@ -9192,16 +9192,16 @@
         <v>43864</v>
       </c>
       <c r="B439" t="n">
-        <v>184.1027526855469</v>
+        <v>184.1027374267578</v>
       </c>
       <c r="C439" t="n">
-        <v>186.1582761969483</v>
+        <v>186.1582607677936</v>
       </c>
       <c r="D439" t="n">
-        <v>178.7405424721906</v>
+        <v>178.7405276578318</v>
       </c>
       <c r="E439" t="n">
-        <v>179.0384464067156</v>
+        <v>179.038431567666</v>
       </c>
       <c r="F439" t="n">
         <v>700100</v>
@@ -9212,16 +9212,16 @@
         <v>43865</v>
       </c>
       <c r="B440" t="n">
-        <v>182.7621917724609</v>
+        <v>182.76220703125</v>
       </c>
       <c r="C440" t="n">
-        <v>186.5753193762337</v>
+        <v>186.5753349533802</v>
       </c>
       <c r="D440" t="n">
-        <v>182.5238656152168</v>
+        <v>182.5238808541081</v>
       </c>
       <c r="E440" t="n">
-        <v>186.3667820946423</v>
+        <v>186.3667976543781</v>
       </c>
       <c r="F440" t="n">
         <v>732700</v>
@@ -9232,16 +9232,16 @@
         <v>43866</v>
       </c>
       <c r="B441" t="n">
-        <v>173.9145660400391</v>
+        <v>173.91455078125</v>
       </c>
       <c r="C441" t="n">
-        <v>185.2050066793799</v>
+        <v>185.2049904299985</v>
       </c>
       <c r="D441" t="n">
-        <v>171.859042306193</v>
+        <v>171.85902722775</v>
       </c>
       <c r="E441" t="n">
-        <v>184.6985805422995</v>
+        <v>184.6985643373504</v>
       </c>
       <c r="F441" t="n">
         <v>2347200</v>
@@ -9252,16 +9252,16 @@
         <v>43867</v>
       </c>
       <c r="B442" t="n">
-        <v>174.8678283691406</v>
+        <v>174.8678436279297</v>
       </c>
       <c r="C442" t="n">
-        <v>179.3363417160315</v>
+        <v>179.3363573647385</v>
       </c>
       <c r="D442" t="n">
-        <v>174.0634832390011</v>
+        <v>174.0634984276038</v>
       </c>
       <c r="E442" t="n">
-        <v>174.8678283691406</v>
+        <v>174.8678436279297</v>
       </c>
       <c r="F442" t="n">
         <v>1198833</v>
@@ -9272,16 +9272,16 @@
         <v>43868</v>
       </c>
       <c r="B443" t="n">
-        <v>171.6802978515625</v>
+        <v>171.6803131103516</v>
       </c>
       <c r="C443" t="n">
-        <v>180.8556515493858</v>
+        <v>180.855667623672</v>
       </c>
       <c r="D443" t="n">
-        <v>171.4419716632469</v>
+        <v>171.4419869008538</v>
       </c>
       <c r="E443" t="n">
-        <v>172.9612651277013</v>
+        <v>172.9612805003416</v>
       </c>
       <c r="F443" t="n">
         <v>1239533</v>
@@ -9292,16 +9292,16 @@
         <v>43871</v>
       </c>
       <c r="B444" t="n">
-        <v>166.1095733642578</v>
+        <v>166.1095581054688</v>
       </c>
       <c r="C444" t="n">
-        <v>172.752767167804</v>
+        <v>172.7527512987726</v>
       </c>
       <c r="D444" t="n">
-        <v>164.0838535119248</v>
+        <v>164.0838384392179</v>
       </c>
       <c r="E444" t="n">
-        <v>171.6505330144978</v>
+        <v>171.6505172467174</v>
       </c>
       <c r="F444" t="n">
         <v>872966</v>
@@ -9332,16 +9332,16 @@
         <v>43873</v>
       </c>
       <c r="B446" t="n">
-        <v>174.9572143554688</v>
+        <v>174.9571990966797</v>
       </c>
       <c r="C446" t="n">
-        <v>176.3275482967427</v>
+        <v>176.3275329184407</v>
       </c>
       <c r="D446" t="n">
-        <v>171.4121861017706</v>
+        <v>171.412171152159</v>
       </c>
       <c r="E446" t="n">
-        <v>173.4974986218312</v>
+        <v>173.4974834903504</v>
       </c>
       <c r="F446" t="n">
         <v>872333</v>
@@ -9352,16 +9352,16 @@
         <v>43874</v>
       </c>
       <c r="B447" t="n">
-        <v>174.8678283691406</v>
+        <v>174.8678436279297</v>
       </c>
       <c r="C447" t="n">
-        <v>175.9700471154318</v>
+        <v>175.9700624703994</v>
       </c>
       <c r="D447" t="n">
-        <v>171.7696488119207</v>
+        <v>171.7696638003658</v>
       </c>
       <c r="E447" t="n">
-        <v>174.2720205287461</v>
+        <v>174.2720357355455</v>
       </c>
       <c r="F447" t="n">
         <v>404433</v>
@@ -9392,16 +9392,16 @@
         <v>43878</v>
       </c>
       <c r="B449" t="n">
-        <v>178.3532867431641</v>
+        <v>178.353271484375</v>
       </c>
       <c r="C449" t="n">
-        <v>178.3532867431641</v>
+        <v>178.353271484375</v>
       </c>
       <c r="D449" t="n">
-        <v>173.4677133273196</v>
+        <v>173.4676984865096</v>
       </c>
       <c r="E449" t="n">
-        <v>173.9741394517339</v>
+        <v>173.9741245675972</v>
       </c>
       <c r="F449" t="n">
         <v>278100</v>
@@ -9452,16 +9452,16 @@
         <v>43881</v>
       </c>
       <c r="B452" t="n">
-        <v>172.1569213867188</v>
+        <v>172.1569366455078</v>
       </c>
       <c r="C452" t="n">
-        <v>177.072283095687</v>
+        <v>177.0722987901394</v>
       </c>
       <c r="D452" t="n">
-        <v>171.3228025219774</v>
+        <v>171.3228177068359</v>
       </c>
       <c r="E452" t="n">
-        <v>175.7019492899041</v>
+        <v>175.7019648628997</v>
       </c>
       <c r="F452" t="n">
         <v>757533</v>
@@ -9472,16 +9472,16 @@
         <v>43882</v>
       </c>
       <c r="B453" t="n">
-        <v>166.8245086669922</v>
+        <v>166.8245239257812</v>
       </c>
       <c r="C453" t="n">
-        <v>171.2334445346579</v>
+        <v>171.2334601967152</v>
       </c>
       <c r="D453" t="n">
-        <v>165.543526276023</v>
+        <v>165.5435414176457</v>
       </c>
       <c r="E453" t="n">
-        <v>169.8333066290028</v>
+        <v>169.8333221629949</v>
       </c>
       <c r="F453" t="n">
         <v>990066</v>
@@ -9532,16 +9532,16 @@
         <v>43889</v>
       </c>
       <c r="B456" t="n">
-        <v>164.4413146972656</v>
+        <v>164.4412841796875</v>
       </c>
       <c r="C456" t="n">
-        <v>165.0073185689544</v>
+        <v>165.0072879463353</v>
       </c>
       <c r="D456" t="n">
-        <v>155.0574235501962</v>
+        <v>155.0573947741125</v>
       </c>
       <c r="E456" t="n">
-        <v>158.6322406683202</v>
+        <v>158.6322112288098</v>
       </c>
       <c r="F456" t="n">
         <v>1340833</v>
@@ -9552,16 +9552,16 @@
         <v>43892</v>
       </c>
       <c r="B457" t="n">
-        <v>162.5347290039062</v>
+        <v>162.5347442626953</v>
       </c>
       <c r="C457" t="n">
-        <v>165.9308127071088</v>
+        <v>165.9308282847228</v>
       </c>
       <c r="D457" t="n">
-        <v>159.0790826951317</v>
+        <v>159.079097629504</v>
       </c>
       <c r="E457" t="n">
-        <v>164.7391969470962</v>
+        <v>164.7392124128411</v>
       </c>
       <c r="F457" t="n">
         <v>1544166</v>
@@ -9592,16 +9592,16 @@
         <v>43894</v>
       </c>
       <c r="B459" t="n">
-        <v>159.4663391113281</v>
+        <v>159.4663543701172</v>
       </c>
       <c r="C459" t="n">
-        <v>169.7439256406586</v>
+        <v>169.7439418828748</v>
       </c>
       <c r="D459" t="n">
-        <v>159.0790685693198</v>
+        <v>159.0790837910523</v>
       </c>
       <c r="E459" t="n">
-        <v>167.5692467693725</v>
+        <v>167.5692628035011</v>
       </c>
       <c r="F459" t="n">
         <v>1186600</v>
@@ -9632,16 +9632,16 @@
         <v>43896</v>
       </c>
       <c r="B461" t="n">
-        <v>148.9802703857422</v>
+        <v>148.980224609375</v>
       </c>
       <c r="C461" t="n">
-        <v>152.8231879598351</v>
+        <v>152.8231410026753</v>
       </c>
       <c r="D461" t="n">
-        <v>147.8780362165492</v>
+        <v>147.8779907788596</v>
       </c>
       <c r="E461" t="n">
-        <v>151.9294911316361</v>
+        <v>151.9294444490777</v>
       </c>
       <c r="F461" t="n">
         <v>1046833</v>
@@ -9652,16 +9652,16 @@
         <v>43899</v>
       </c>
       <c r="B462" t="n">
-        <v>134.4128875732422</v>
+        <v>134.4129028320312</v>
       </c>
       <c r="C462" t="n">
-        <v>142.4562028351162</v>
+        <v>142.4562190069967</v>
       </c>
       <c r="D462" t="n">
-        <v>134.4128875732422</v>
+        <v>134.4129028320312</v>
       </c>
       <c r="E462" t="n">
-        <v>137.8089560374144</v>
+        <v>137.8089716817311</v>
       </c>
       <c r="F462" t="n">
         <v>2156300</v>
@@ -9672,16 +9672,16 @@
         <v>43900</v>
       </c>
       <c r="B463" t="n">
-        <v>145.6437530517578</v>
+        <v>145.6437683105469</v>
       </c>
       <c r="C463" t="n">
-        <v>147.3715837841424</v>
+        <v>147.3715992239526</v>
       </c>
       <c r="D463" t="n">
-        <v>136.9152630573862</v>
+        <v>136.9152774017098</v>
       </c>
       <c r="E463" t="n">
-        <v>142.456206648502</v>
+        <v>142.4562215733386</v>
       </c>
       <c r="F463" t="n">
         <v>1718533</v>
@@ -9692,16 +9692,16 @@
         <v>43901</v>
       </c>
       <c r="B464" t="n">
-        <v>134.0256195068359</v>
+        <v>134.025634765625</v>
       </c>
       <c r="C464" t="n">
-        <v>144.2436139679902</v>
+        <v>144.2436303900958</v>
       </c>
       <c r="D464" t="n">
-        <v>122.020208994126</v>
+        <v>122.0202228861016</v>
       </c>
       <c r="E464" t="n">
-        <v>142.0391460401569</v>
+        <v>142.0391622112843</v>
       </c>
       <c r="F464" t="n">
         <v>1332366</v>
@@ -9732,16 +9732,16 @@
         <v>43903</v>
       </c>
       <c r="B466" t="n">
-        <v>129.9145660400391</v>
+        <v>129.9145812988281</v>
       </c>
       <c r="C466" t="n">
-        <v>137.0343947306269</v>
+        <v>137.0344108256576</v>
       </c>
       <c r="D466" t="n">
-        <v>118.713487411252</v>
+        <v>118.7135013544465</v>
       </c>
       <c r="E466" t="n">
-        <v>136.945028109679</v>
+        <v>136.9450441942133</v>
       </c>
       <c r="F466" t="n">
         <v>2459466</v>
@@ -9752,16 +9752,16 @@
         <v>43906</v>
       </c>
       <c r="B467" t="n">
-        <v>110.2233352661133</v>
+        <v>110.2233428955078</v>
       </c>
       <c r="C467" t="n">
-        <v>120.6796558589259</v>
+        <v>120.6796642120818</v>
       </c>
       <c r="D467" t="n">
-        <v>106.3208330928401</v>
+        <v>106.3208404521129</v>
       </c>
       <c r="E467" t="n">
-        <v>109.7466904828687</v>
+        <v>109.746698079271</v>
       </c>
       <c r="F467" t="n">
         <v>2066566</v>
@@ -9772,16 +9772,16 @@
         <v>43907</v>
       </c>
       <c r="B468" t="n">
-        <v>111.9511642456055</v>
+        <v>111.9511566162109</v>
       </c>
       <c r="C468" t="n">
-        <v>113.5598319500353</v>
+        <v>113.5598242110112</v>
       </c>
       <c r="D468" t="n">
-        <v>105.5165085799105</v>
+        <v>105.5165013890333</v>
       </c>
       <c r="E468" t="n">
-        <v>111.7128456295459</v>
+        <v>111.7128380163926</v>
       </c>
       <c r="F468" t="n">
         <v>2266766</v>
@@ -9792,16 +9792,16 @@
         <v>43908</v>
       </c>
       <c r="B469" t="n">
-        <v>94.49417877197266</v>
+        <v>94.49416351318359</v>
       </c>
       <c r="C469" t="n">
-        <v>104.861134406764</v>
+        <v>104.8611174739333</v>
       </c>
       <c r="D469" t="n">
-        <v>85.43799460917843</v>
+        <v>85.43798081276944</v>
       </c>
       <c r="E469" t="n">
-        <v>103.6695336198741</v>
+        <v>103.6695168794615</v>
       </c>
       <c r="F469" t="n">
         <v>1809666</v>
@@ -9832,16 +9832,16 @@
         <v>43910</v>
       </c>
       <c r="B471" t="n">
-        <v>116.1813507080078</v>
+        <v>116.1813583374023</v>
       </c>
       <c r="C471" t="n">
-        <v>120.9477605504217</v>
+        <v>120.9477684928167</v>
       </c>
       <c r="D471" t="n">
-        <v>108.1976056989515</v>
+        <v>108.1976128040696</v>
       </c>
       <c r="E471" t="n">
-        <v>113.947093963623</v>
+        <v>113.9471014462984</v>
       </c>
       <c r="F471" t="n">
         <v>2114800</v>
@@ -9852,16 +9852,16 @@
         <v>43913</v>
       </c>
       <c r="B472" t="n">
-        <v>113.7981414794922</v>
+        <v>113.7981491088867</v>
       </c>
       <c r="C472" t="n">
-        <v>119.6072074731813</v>
+        <v>119.6072154920344</v>
       </c>
       <c r="D472" t="n">
-        <v>108.4657126798635</v>
+        <v>108.4657199517548</v>
       </c>
       <c r="E472" t="n">
-        <v>118.9518294373453</v>
+        <v>118.9518374122596</v>
       </c>
       <c r="F472" t="n">
         <v>1372400</v>
@@ -9932,16 +9932,16 @@
         <v>43917</v>
       </c>
       <c r="B476" t="n">
-        <v>135.5449066162109</v>
+        <v>135.544921875</v>
       </c>
       <c r="C476" t="n">
-        <v>143.9457033323465</v>
+        <v>143.9457195368442</v>
       </c>
       <c r="D476" t="n">
-        <v>133.72770934663</v>
+        <v>133.7277244008504</v>
       </c>
       <c r="E476" t="n">
-        <v>141.3837689806335</v>
+        <v>141.3837848967248</v>
       </c>
       <c r="F476" t="n">
         <v>773066</v>
@@ -9952,16 +9952,16 @@
         <v>43920</v>
       </c>
       <c r="B477" t="n">
-        <v>134.1447601318359</v>
+        <v>134.1447906494141</v>
       </c>
       <c r="C477" t="n">
-        <v>138.7324287498381</v>
+        <v>138.7324603110987</v>
       </c>
       <c r="D477" t="n">
-        <v>128.6931838265533</v>
+        <v>128.6932131039123</v>
       </c>
       <c r="E477" t="n">
-        <v>134.6512013157082</v>
+        <v>134.6512319485003</v>
       </c>
       <c r="F477" t="n">
         <v>909700</v>
@@ -9972,16 +9972,16 @@
         <v>43921</v>
       </c>
       <c r="B478" t="n">
-        <v>126.3099822998047</v>
+        <v>126.3099899291992</v>
       </c>
       <c r="C478" t="n">
-        <v>138.5239225909137</v>
+        <v>138.5239309580564</v>
       </c>
       <c r="D478" t="n">
-        <v>125.1183816950188</v>
+        <v>125.1183892524381</v>
       </c>
       <c r="E478" t="n">
-        <v>134.1447755951023</v>
+        <v>134.1447836977352</v>
       </c>
       <c r="F478" t="n">
         <v>993633</v>
@@ -9992,16 +9992,16 @@
         <v>43922</v>
       </c>
       <c r="B479" t="n">
-        <v>119.3986968994141</v>
+        <v>119.398681640625</v>
       </c>
       <c r="C479" t="n">
-        <v>125.6248309062841</v>
+        <v>125.6248148518141</v>
       </c>
       <c r="D479" t="n">
-        <v>115.7345128434667</v>
+        <v>115.7344980529492</v>
       </c>
       <c r="E479" t="n">
-        <v>120.6498829924714</v>
+        <v>120.6498675737846</v>
       </c>
       <c r="F479" t="n">
         <v>1115733</v>
@@ -10092,16 +10092,16 @@
         <v>43929</v>
       </c>
       <c r="B484" t="n">
-        <v>148.9206848144531</v>
+        <v>148.9206390380859</v>
       </c>
       <c r="C484" t="n">
-        <v>152.5252911265695</v>
+        <v>152.5252442421911</v>
       </c>
       <c r="D484" t="n">
-        <v>142.0987579677773</v>
+        <v>142.0987142883857</v>
       </c>
       <c r="E484" t="n">
-        <v>144.3330150732328</v>
+        <v>144.3329707070583</v>
       </c>
       <c r="F484" t="n">
         <v>859700</v>
@@ -10112,16 +10112,16 @@
         <v>43930</v>
       </c>
       <c r="B485" t="n">
-        <v>145.5543823242188</v>
+        <v>145.5544128417969</v>
       </c>
       <c r="C485" t="n">
-        <v>153.0912714973958</v>
+        <v>153.0913035951916</v>
       </c>
       <c r="D485" t="n">
-        <v>144.4223595043424</v>
+        <v>144.4223897845756</v>
       </c>
       <c r="E485" t="n">
-        <v>150.4995330476759</v>
+        <v>150.4995646020763</v>
       </c>
       <c r="F485" t="n">
         <v>918500</v>
@@ -10172,16 +10172,16 @@
         <v>43936</v>
       </c>
       <c r="B488" t="n">
-        <v>155.0574188232422</v>
+        <v>155.0574340820312</v>
       </c>
       <c r="C488" t="n">
-        <v>160.8069149169485</v>
+        <v>160.8069307415302</v>
       </c>
       <c r="D488" t="n">
-        <v>148.0865483834452</v>
+        <v>148.0865629562494</v>
       </c>
       <c r="E488" t="n">
-        <v>154.610570485105</v>
+        <v>154.6105856999209</v>
       </c>
       <c r="F488" t="n">
         <v>821233</v>
@@ -10192,16 +10192,16 @@
         <v>43937</v>
       </c>
       <c r="B489" t="n">
-        <v>154.789306640625</v>
+        <v>154.7893371582031</v>
       </c>
       <c r="C489" t="n">
-        <v>158.4832788732266</v>
+        <v>158.4833101190921</v>
       </c>
       <c r="D489" t="n">
-        <v>151.5719715874492</v>
+        <v>151.5720014707118</v>
       </c>
       <c r="E489" t="n">
-        <v>155.5638477392006</v>
+        <v>155.5638784094838</v>
       </c>
       <c r="F489" t="n">
         <v>851733</v>
@@ -10292,16 +10292,16 @@
         <v>43945</v>
       </c>
       <c r="B494" t="n">
-        <v>148.950439453125</v>
+        <v>148.9504699707031</v>
       </c>
       <c r="C494" t="n">
-        <v>152.018814869374</v>
+        <v>152.0188460156135</v>
       </c>
       <c r="D494" t="n">
-        <v>136.1109036932141</v>
+        <v>136.1109315801753</v>
       </c>
       <c r="E494" t="n">
-        <v>146.9545090191811</v>
+        <v>146.9545391278248</v>
       </c>
       <c r="F494" t="n">
         <v>1301233</v>
@@ -10332,16 +10332,16 @@
         <v>43949</v>
       </c>
       <c r="B496" t="n">
-        <v>159.1386413574219</v>
+        <v>159.1386566162109</v>
       </c>
       <c r="C496" t="n">
-        <v>166.1988926738134</v>
+        <v>166.1989086095649</v>
       </c>
       <c r="D496" t="n">
-        <v>157.8874631419682</v>
+        <v>157.8874782807897</v>
       </c>
       <c r="E496" t="n">
-        <v>157.8874631419682</v>
+        <v>157.8874782807897</v>
       </c>
       <c r="F496" t="n">
         <v>787066</v>
@@ -10372,16 +10372,16 @@
         <v>43951</v>
       </c>
       <c r="B498" t="n">
-        <v>156.2674560546875</v>
+        <v>156.2674407958984</v>
       </c>
       <c r="C498" t="n">
-        <v>162.108121265528</v>
+        <v>162.1081054364251</v>
       </c>
       <c r="D498" t="n">
-        <v>155.4926757908048</v>
+        <v>155.4926606076694</v>
       </c>
       <c r="E498" t="n">
-        <v>159.0983944350523</v>
+        <v>159.0983788998354</v>
       </c>
       <c r="F498" t="n">
         <v>826166</v>
@@ -10412,16 +10412,16 @@
         <v>43956</v>
       </c>
       <c r="B500" t="n">
-        <v>154.6582946777344</v>
+        <v>154.6582794189453</v>
       </c>
       <c r="C500" t="n">
-        <v>157.6382233426491</v>
+        <v>157.6382077898564</v>
       </c>
       <c r="D500" t="n">
-        <v>151.4101681891011</v>
+        <v>151.4101532507764</v>
       </c>
       <c r="E500" t="n">
-        <v>153.615316613674</v>
+        <v>153.6153014577865</v>
       </c>
       <c r="F500" t="n">
         <v>670733</v>
@@ -10492,16 +10492,16 @@
         <v>43962</v>
       </c>
       <c r="B504" t="n">
-        <v>146.9700622558594</v>
+        <v>146.9700775146484</v>
       </c>
       <c r="C504" t="n">
-        <v>152.6915345641711</v>
+        <v>152.6915504169773</v>
       </c>
       <c r="D504" t="n">
-        <v>146.5826721647091</v>
+        <v>146.5826873832784</v>
       </c>
       <c r="E504" t="n">
-        <v>149.9499906975384</v>
+        <v>149.9500062657109</v>
       </c>
       <c r="F504" t="n">
         <v>466500</v>
@@ -10532,16 +10532,16 @@
         <v>43964</v>
       </c>
       <c r="B506" t="n">
-        <v>145.7781066894531</v>
+        <v>145.7780914306641</v>
       </c>
       <c r="C506" t="n">
-        <v>153.9431125479351</v>
+        <v>153.943096434504</v>
       </c>
       <c r="D506" t="n">
-        <v>145.7781066894531</v>
+        <v>145.7780914306641</v>
       </c>
       <c r="E506" t="n">
-        <v>152.3041578240206</v>
+        <v>152.304141882141</v>
       </c>
       <c r="F506" t="n">
         <v>632666</v>
@@ -10572,16 +10572,16 @@
         <v>43966</v>
       </c>
       <c r="B508" t="n">
-        <v>139.7586517333984</v>
+        <v>139.7586364746094</v>
       </c>
       <c r="C508" t="n">
-        <v>143.5431587230644</v>
+        <v>143.5431430510845</v>
       </c>
       <c r="D508" t="n">
-        <v>134.9907628252228</v>
+        <v>134.9907480869898</v>
       </c>
       <c r="E508" t="n">
-        <v>140.3248454564891</v>
+        <v>140.3248301358833</v>
       </c>
       <c r="F508" t="n">
         <v>930266</v>
@@ -10632,16 +10632,16 @@
         <v>43971</v>
       </c>
       <c r="B511" t="n">
-        <v>151.6783599853516</v>
+        <v>151.6783752441406</v>
       </c>
       <c r="C511" t="n">
-        <v>154.181504208285</v>
+        <v>154.1815197188895</v>
       </c>
       <c r="D511" t="n">
-        <v>149.3540193566921</v>
+        <v>149.3540343816533</v>
       </c>
       <c r="E511" t="n">
-        <v>150.7545894111537</v>
+        <v>150.7546045770118</v>
       </c>
       <c r="F511" t="n">
         <v>544933</v>
@@ -10732,16 +10732,16 @@
         <v>43978</v>
       </c>
       <c r="B516" t="n">
-        <v>163.8960571289062</v>
+        <v>163.8960723876953</v>
       </c>
       <c r="C516" t="n">
-        <v>165.9820130095902</v>
+        <v>165.9820284625826</v>
       </c>
       <c r="D516" t="n">
-        <v>160.320137092505</v>
+        <v>160.3201520183744</v>
       </c>
       <c r="E516" t="n">
-        <v>165.5350116375157</v>
+        <v>165.535027048892</v>
       </c>
       <c r="F516" t="n">
         <v>627900</v>
@@ -10772,16 +10772,16 @@
         <v>43980</v>
       </c>
       <c r="B518" t="n">
-        <v>163.4789123535156</v>
+        <v>163.4788818359375</v>
       </c>
       <c r="C518" t="n">
-        <v>165.0582711399571</v>
+        <v>165.0582403275507</v>
       </c>
       <c r="D518" t="n">
-        <v>157.9958385619926</v>
+        <v>157.9958090679723</v>
       </c>
       <c r="E518" t="n">
-        <v>163.9556967659558</v>
+        <v>163.9556661593735</v>
       </c>
       <c r="F518" t="n">
         <v>1761600</v>
@@ -10792,16 +10792,16 @@
         <v>43983</v>
       </c>
       <c r="B519" t="n">
-        <v>162.4061126708984</v>
+        <v>162.4061279296875</v>
       </c>
       <c r="C519" t="n">
-        <v>164.7304533981214</v>
+        <v>164.7304688752928</v>
       </c>
       <c r="D519" t="n">
-        <v>160.4095659164942</v>
+        <v>160.4095809876987</v>
       </c>
       <c r="E519" t="n">
-        <v>161.8995302529245</v>
+        <v>161.8995454641179</v>
       </c>
       <c r="F519" t="n">
         <v>557733</v>
@@ -10812,16 +10812,16 @@
         <v>43984</v>
       </c>
       <c r="B520" t="n">
-        <v>162.5848999023438</v>
+        <v>162.5849151611328</v>
       </c>
       <c r="C520" t="n">
-        <v>164.1642736062624</v>
+        <v>164.1642890132777</v>
       </c>
       <c r="D520" t="n">
-        <v>159.7241787043098</v>
+        <v>159.7241936946168</v>
       </c>
       <c r="E520" t="n">
-        <v>163.8662777098608</v>
+        <v>163.8662930889087</v>
       </c>
       <c r="F520" t="n">
         <v>917300</v>
@@ -10852,16 +10852,16 @@
         <v>43986</v>
       </c>
       <c r="B522" t="n">
-        <v>174.8026123046875</v>
+        <v>174.8025970458984</v>
       </c>
       <c r="C522" t="n">
-        <v>176.9779626683967</v>
+        <v>176.977947219718</v>
       </c>
       <c r="D522" t="n">
-        <v>169.7963387860876</v>
+        <v>169.7963239643039</v>
       </c>
       <c r="E522" t="n">
-        <v>174.6238238589201</v>
+        <v>174.6238086157378</v>
       </c>
       <c r="F522" t="n">
         <v>1106633</v>
@@ -10892,16 +10892,16 @@
         <v>43990</v>
       </c>
       <c r="B524" t="n">
-        <v>181.9842224121094</v>
+        <v>181.9842376708984</v>
       </c>
       <c r="C524" t="n">
-        <v>184.1893706831995</v>
+        <v>184.1893861268831</v>
       </c>
       <c r="D524" t="n">
-        <v>176.3521594462279</v>
+        <v>176.3521742327868</v>
       </c>
       <c r="E524" t="n">
-        <v>178.2891250689665</v>
+        <v>178.2891400179336</v>
       </c>
       <c r="F524" t="n">
         <v>540433</v>
@@ -10912,16 +10912,16 @@
         <v>43991</v>
       </c>
       <c r="B525" t="n">
-        <v>179.0639190673828</v>
+        <v>179.0639038085938</v>
       </c>
       <c r="C525" t="n">
-        <v>181.8352460776798</v>
+        <v>181.8352305827343</v>
       </c>
       <c r="D525" t="n">
-        <v>173.7000383361128</v>
+        <v>173.7000235344026</v>
       </c>
       <c r="E525" t="n">
-        <v>178.1699313671539</v>
+        <v>178.1699161845453</v>
       </c>
       <c r="F525" t="n">
         <v>591500</v>
@@ -10952,16 +10952,16 @@
         <v>43994</v>
       </c>
       <c r="B527" t="n">
-        <v>177.9315338134766</v>
+        <v>177.9315490722656</v>
       </c>
       <c r="C527" t="n">
-        <v>180.2260763105577</v>
+        <v>180.2260917661188</v>
       </c>
       <c r="D527" t="n">
-        <v>171.763075210948</v>
+        <v>171.7630899407515</v>
       </c>
       <c r="E527" t="n">
-        <v>174.0874157801964</v>
+        <v>174.0874307093273</v>
       </c>
       <c r="F527" t="n">
         <v>1048900</v>
@@ -10972,16 +10972,16 @@
         <v>43997</v>
       </c>
       <c r="B528" t="n">
-        <v>180.3750915527344</v>
+        <v>180.3750762939453</v>
       </c>
       <c r="C528" t="n">
-        <v>182.8782360569759</v>
+        <v>182.8782205864339</v>
       </c>
       <c r="D528" t="n">
-        <v>173.5212611882256</v>
+        <v>173.5212465092347</v>
       </c>
       <c r="E528" t="n">
-        <v>175.7860059255433</v>
+        <v>175.785991054967</v>
       </c>
       <c r="F528" t="n">
         <v>826966</v>
@@ -10992,16 +10992,16 @@
         <v>43998</v>
       </c>
       <c r="B529" t="n">
-        <v>179.8386840820312</v>
+        <v>179.8386993408203</v>
       </c>
       <c r="C529" t="n">
-        <v>186.6627153479782</v>
+        <v>186.6627311857664</v>
       </c>
       <c r="D529" t="n">
-        <v>177.1269382933809</v>
+        <v>177.1269533220862</v>
       </c>
       <c r="E529" t="n">
-        <v>183.5933926975627</v>
+        <v>183.5934082749279</v>
       </c>
       <c r="F529" t="n">
         <v>733633</v>
@@ -11012,16 +11012,16 @@
         <v>43999</v>
       </c>
       <c r="B530" t="n">
-        <v>181.2392425537109</v>
+        <v>181.2392730712891</v>
       </c>
       <c r="C530" t="n">
-        <v>186.066727321228</v>
+        <v>186.0667586516717</v>
       </c>
       <c r="D530" t="n">
-        <v>180.6134678764014</v>
+        <v>180.6134982886098</v>
       </c>
       <c r="E530" t="n">
-        <v>182.0438359788805</v>
+        <v>182.0438666319384</v>
       </c>
       <c r="F530" t="n">
         <v>934766</v>
@@ -11032,16 +11032,16 @@
         <v>44000</v>
       </c>
       <c r="B531" t="n">
-        <v>179.6896820068359</v>
+        <v>179.689697265625</v>
       </c>
       <c r="C531" t="n">
-        <v>182.9080102346423</v>
+        <v>182.9080257667236</v>
       </c>
       <c r="D531" t="n">
-        <v>178.4381174965946</v>
+        <v>178.438132649104</v>
       </c>
       <c r="E531" t="n">
-        <v>181.7756380139382</v>
+        <v>181.7756534498614</v>
       </c>
       <c r="F531" t="n">
         <v>656233</v>
@@ -11052,16 +11052,16 @@
         <v>44001</v>
       </c>
       <c r="B532" t="n">
-        <v>187.1692962646484</v>
+        <v>187.1693115234375</v>
       </c>
       <c r="C532" t="n">
-        <v>190.119426604783</v>
+        <v>190.1194421040784</v>
       </c>
       <c r="D532" t="n">
-        <v>181.0306510117299</v>
+        <v>181.0306657700721</v>
       </c>
       <c r="E532" t="n">
-        <v>181.7756331146588</v>
+        <v>181.7756479337349</v>
       </c>
       <c r="F532" t="n">
         <v>2381566</v>
@@ -11092,16 +11092,16 @@
         <v>44005</v>
       </c>
       <c r="B534" t="n">
-        <v>185.9475402832031</v>
+        <v>185.9475708007812</v>
       </c>
       <c r="C534" t="n">
-        <v>188.8380746422072</v>
+        <v>188.8381056341778</v>
       </c>
       <c r="D534" t="n">
-        <v>179.6002930167151</v>
+        <v>179.6003224925875</v>
       </c>
       <c r="E534" t="n">
-        <v>182.6696158152284</v>
+        <v>182.6696457948359</v>
       </c>
       <c r="F534" t="n">
         <v>796833</v>
@@ -11152,16 +11152,16 @@
         <v>44008</v>
       </c>
       <c r="B537" t="n">
-        <v>182.7292175292969</v>
+        <v>182.7292327880859</v>
       </c>
       <c r="C537" t="n">
-        <v>187.1693124594684</v>
+        <v>187.1693280890272</v>
       </c>
       <c r="D537" t="n">
-        <v>182.669621380978</v>
+        <v>182.6696366347904</v>
       </c>
       <c r="E537" t="n">
-        <v>182.6994194551374</v>
+        <v>182.6994347114382</v>
       </c>
       <c r="F537" t="n">
         <v>565500</v>
@@ -11232,16 +11232,16 @@
         <v>44014</v>
       </c>
       <c r="B541" t="n">
-        <v>180.9710540771484</v>
+        <v>180.9710693359375</v>
       </c>
       <c r="C541" t="n">
-        <v>190.5366139303682</v>
+        <v>190.5366299956888</v>
       </c>
       <c r="D541" t="n">
-        <v>179.9876722491709</v>
+        <v>179.9876874250449</v>
       </c>
       <c r="E541" t="n">
-        <v>190.1492238448073</v>
+        <v>190.1492398774646</v>
       </c>
       <c r="F541" t="n">
         <v>782133</v>
@@ -11252,16 +11252,16 @@
         <v>44015</v>
       </c>
       <c r="B542" t="n">
-        <v>181.5074462890625</v>
+        <v>181.5074615478516</v>
       </c>
       <c r="C542" t="n">
-        <v>184.4575768075846</v>
+        <v>184.4575923143823</v>
       </c>
       <c r="D542" t="n">
-        <v>178.0805314397118</v>
+        <v>178.0805464104103</v>
       </c>
       <c r="E542" t="n">
-        <v>179.3917072953663</v>
+        <v>179.3917223762915</v>
       </c>
       <c r="F542" t="n">
         <v>277066</v>
@@ -11312,16 +11312,16 @@
         <v>44020</v>
       </c>
       <c r="B545" t="n">
-        <v>180.9412994384766</v>
+        <v>180.9412841796875</v>
       </c>
       <c r="C545" t="n">
-        <v>183.5040402953038</v>
+        <v>183.5040248203987</v>
       </c>
       <c r="D545" t="n">
-        <v>177.1567918887944</v>
+        <v>177.1567769491531</v>
       </c>
       <c r="E545" t="n">
-        <v>180.4347017888099</v>
+        <v>180.4346865727422</v>
       </c>
       <c r="F545" t="n">
         <v>677066</v>
@@ -11372,16 +11372,16 @@
         <v>44025</v>
       </c>
       <c r="B548" t="n">
-        <v>175.6966094970703</v>
+        <v>175.6965942382812</v>
       </c>
       <c r="C548" t="n">
-        <v>181.269077041767</v>
+        <v>181.2690612990238</v>
       </c>
       <c r="D548" t="n">
-        <v>175.6369981885591</v>
+        <v>175.6369829349472</v>
       </c>
       <c r="E548" t="n">
-        <v>180.1367046872849</v>
+        <v>180.1366890428852</v>
       </c>
       <c r="F548" t="n">
         <v>495033</v>
@@ -11392,16 +11392,16 @@
         <v>44026</v>
       </c>
       <c r="B549" t="n">
-        <v>178.4679107666016</v>
+        <v>178.4679260253906</v>
       </c>
       <c r="C549" t="n">
-        <v>179.2128928695628</v>
+        <v>179.212908192047</v>
       </c>
       <c r="D549" t="n">
-        <v>173.282834117455</v>
+        <v>173.2828489329264</v>
       </c>
       <c r="E549" t="n">
-        <v>175.0707941959021</v>
+        <v>175.0708091642418</v>
       </c>
       <c r="F549" t="n">
         <v>493066</v>
@@ -11412,16 +11412,16 @@
         <v>44027</v>
       </c>
       <c r="B550" t="n">
-        <v>180.6730804443359</v>
+        <v>180.673095703125</v>
       </c>
       <c r="C550" t="n">
-        <v>184.7257853841829</v>
+        <v>184.7258009852441</v>
       </c>
       <c r="D550" t="n">
-        <v>178.9745143790679</v>
+        <v>178.9745294944042</v>
       </c>
       <c r="E550" t="n">
-        <v>180.5836862189801</v>
+        <v>180.5837014702194</v>
       </c>
       <c r="F550" t="n">
         <v>693400</v>
@@ -11452,16 +11452,16 @@
         <v>44029</v>
       </c>
       <c r="B552" t="n">
-        <v>190.1492614746094</v>
+        <v>190.1492462158203</v>
       </c>
       <c r="C552" t="n">
-        <v>190.1492614746094</v>
+        <v>190.1492462158203</v>
       </c>
       <c r="D552" t="n">
-        <v>181.3882781301977</v>
+        <v>181.3882635744458</v>
       </c>
       <c r="E552" t="n">
-        <v>181.3882781301977</v>
+        <v>181.3882635744458</v>
       </c>
       <c r="F552" t="n">
         <v>595900</v>
@@ -11472,16 +11472,16 @@
         <v>44032</v>
       </c>
       <c r="B553" t="n">
-        <v>196.0196990966797</v>
+        <v>196.0197143554688</v>
       </c>
       <c r="C553" t="n">
-        <v>197.7778612094101</v>
+        <v>197.77787660506</v>
       </c>
       <c r="D553" t="n">
-        <v>189.1956674727965</v>
+        <v>189.1956822003815</v>
       </c>
       <c r="E553" t="n">
-        <v>190.7154298418124</v>
+        <v>190.7154446877005</v>
       </c>
       <c r="F553" t="n">
         <v>643066</v>
@@ -11492,16 +11492,16 @@
         <v>44033</v>
       </c>
       <c r="B554" t="n">
-        <v>195.1853332519531</v>
+        <v>195.1853179931641</v>
       </c>
       <c r="C554" t="n">
-        <v>198.5824502103585</v>
+        <v>198.5824346859968</v>
       </c>
       <c r="D554" t="n">
-        <v>190.5068384424615</v>
+        <v>190.506823549418</v>
       </c>
       <c r="E554" t="n">
-        <v>196.0495077398707</v>
+        <v>196.0494924135241</v>
       </c>
       <c r="F554" t="n">
         <v>627900</v>
@@ -11512,16 +11512,16 @@
         <v>44034</v>
       </c>
       <c r="B555" t="n">
-        <v>193.9933624267578</v>
+        <v>193.9933471679688</v>
       </c>
       <c r="C555" t="n">
-        <v>197.926859843797</v>
+        <v>197.9268442756138</v>
       </c>
       <c r="D555" t="n">
-        <v>191.4306219124074</v>
+        <v>191.4306068551939</v>
       </c>
       <c r="E555" t="n">
-        <v>195.2151289563396</v>
+        <v>195.2151136014509</v>
       </c>
       <c r="F555" t="n">
         <v>664000</v>
@@ -11552,16 +11552,16 @@
         <v>44036</v>
       </c>
       <c r="B557" t="n">
-        <v>195.7514953613281</v>
+        <v>195.7515258789062</v>
       </c>
       <c r="C557" t="n">
-        <v>196.0792893152624</v>
+        <v>196.0793198839435</v>
       </c>
       <c r="D557" t="n">
-        <v>188.0334914560843</v>
+        <v>188.0335207704287</v>
       </c>
       <c r="E557" t="n">
-        <v>192.7119707151919</v>
+        <v>192.7120007589094</v>
       </c>
       <c r="F557" t="n">
         <v>615366</v>
@@ -11572,16 +11572,16 @@
         <v>44039</v>
       </c>
       <c r="B558" t="n">
-        <v>192.56298828125</v>
+        <v>192.5629730224609</v>
       </c>
       <c r="C558" t="n">
-        <v>201.8603661940167</v>
+        <v>201.8603501984987</v>
       </c>
       <c r="D558" t="n">
-        <v>192.1160020190085</v>
+        <v>192.1159867956388</v>
       </c>
       <c r="E558" t="n">
-        <v>196.8838756918523</v>
+        <v>196.8838600906739</v>
       </c>
       <c r="F558" t="n">
         <v>595333</v>
@@ -11592,16 +11592,16 @@
         <v>44040</v>
       </c>
       <c r="B559" t="n">
-        <v>194.2317657470703</v>
+        <v>194.2317504882812</v>
       </c>
       <c r="C559" t="n">
-        <v>195.9005338702399</v>
+        <v>195.9005184803528</v>
       </c>
       <c r="D559" t="n">
-        <v>188.7189092168689</v>
+        <v>188.7188943911681</v>
       </c>
       <c r="E559" t="n">
-        <v>190.7154561924708</v>
+        <v>190.715441209922</v>
       </c>
       <c r="F559" t="n">
         <v>415300</v>
@@ -11612,16 +11612,16 @@
         <v>44041</v>
       </c>
       <c r="B560" t="n">
-        <v>195.1853332519531</v>
+        <v>195.1853179931641</v>
       </c>
       <c r="C560" t="n">
-        <v>196.6752976279222</v>
+        <v>196.6752822526539</v>
       </c>
       <c r="D560" t="n">
-        <v>193.3973729694499</v>
+        <v>193.3973578504363</v>
       </c>
       <c r="E560" t="n">
-        <v>195.4535310835039</v>
+        <v>195.4535158037483</v>
       </c>
       <c r="F560" t="n">
         <v>374733</v>
@@ -11632,16 +11632,16 @@
         <v>44042</v>
       </c>
       <c r="B561" t="n">
-        <v>197.2712860107422</v>
+        <v>197.2712707519531</v>
       </c>
       <c r="C561" t="n">
-        <v>200.0724111073721</v>
+        <v>200.072395631918</v>
       </c>
       <c r="D561" t="n">
-        <v>193.0993737052108</v>
+        <v>193.0993587691161</v>
       </c>
       <c r="E561" t="n">
-        <v>194.8873339566241</v>
+        <v>194.887318882232</v>
       </c>
       <c r="F561" t="n">
         <v>388133</v>
@@ -11652,16 +11652,16 @@
         <v>44043</v>
       </c>
       <c r="B562" t="n">
-        <v>194.1125640869141</v>
+        <v>194.112548828125</v>
       </c>
       <c r="C562" t="n">
-        <v>199.8936333494981</v>
+        <v>199.8936176362711</v>
       </c>
       <c r="D562" t="n">
-        <v>191.8180212901964</v>
+        <v>191.8180062117766</v>
       </c>
       <c r="E562" t="n">
-        <v>197.5692773200199</v>
+        <v>197.5692617895057</v>
       </c>
       <c r="F562" t="n">
         <v>964966</v>
@@ -11712,16 +11712,16 @@
         <v>44048</v>
       </c>
       <c r="B565" t="n">
-        <v>194.4999694824219</v>
+        <v>194.4999542236328</v>
       </c>
       <c r="C565" t="n">
-        <v>198.0758904568389</v>
+        <v>198.0758749175139</v>
       </c>
       <c r="D565" t="n">
-        <v>193.09939917105</v>
+        <v>193.0993840221375</v>
       </c>
       <c r="E565" t="n">
-        <v>193.367597033307</v>
+        <v>193.3675818633541</v>
       </c>
       <c r="F565" t="n">
         <v>503800</v>
@@ -11792,16 +11792,16 @@
         <v>44054</v>
       </c>
       <c r="B569" t="n">
-        <v>186.9309234619141</v>
+        <v>186.9309387207031</v>
       </c>
       <c r="C569" t="n">
-        <v>193.5463685900656</v>
+        <v>193.54638438886</v>
       </c>
       <c r="D569" t="n">
-        <v>186.4243258997372</v>
+        <v>186.4243411171737</v>
       </c>
       <c r="E569" t="n">
-        <v>193.0099729544314</v>
+        <v>193.0099887094408</v>
       </c>
       <c r="F569" t="n">
         <v>865000</v>
@@ -11832,16 +11832,16 @@
         <v>44056</v>
       </c>
       <c r="B571" t="n">
-        <v>186.5733489990234</v>
+        <v>186.5733337402344</v>
       </c>
       <c r="C571" t="n">
-        <v>190.9240348573458</v>
+        <v>190.9240192427385</v>
       </c>
       <c r="D571" t="n">
-        <v>184.6363982583284</v>
+        <v>184.6363831579516</v>
       </c>
       <c r="E571" t="n">
-        <v>184.844984792179</v>
+        <v>184.8449696747432</v>
       </c>
       <c r="F571" t="n">
         <v>646800</v>
@@ -11912,16 +11912,16 @@
         <v>44062</v>
       </c>
       <c r="B575" t="n">
-        <v>184.6959991455078</v>
+        <v>184.6959838867188</v>
       </c>
       <c r="C575" t="n">
-        <v>188.3613141870071</v>
+        <v>188.3612986254054</v>
       </c>
       <c r="D575" t="n">
-        <v>183.7722132875247</v>
+        <v>183.7721981050549</v>
       </c>
       <c r="E575" t="n">
-        <v>187.7355242560089</v>
+        <v>187.7355087461073</v>
       </c>
       <c r="F575" t="n">
         <v>275166</v>
@@ -11952,16 +11952,16 @@
         <v>44064</v>
       </c>
       <c r="B577" t="n">
-        <v>186.5733489990234</v>
+        <v>186.5733337402344</v>
       </c>
       <c r="C577" t="n">
-        <v>188.1229095915795</v>
+        <v>188.1228942060606</v>
       </c>
       <c r="D577" t="n">
-        <v>182.908034051484</v>
+        <v>182.9080190924604</v>
       </c>
       <c r="E577" t="n">
-        <v>184.7555905633859</v>
+        <v>184.7555754532611</v>
       </c>
       <c r="F577" t="n">
         <v>431666</v>
@@ -12012,16 +12012,16 @@
         <v>44069</v>
       </c>
       <c r="B580" t="n">
-        <v>186.0369415283203</v>
+        <v>186.0369567871094</v>
       </c>
       <c r="C580" t="n">
-        <v>191.0134321430643</v>
+        <v>191.0134478100261</v>
       </c>
       <c r="D580" t="n">
-        <v>182.520632341546</v>
+        <v>182.5206473119266</v>
       </c>
       <c r="E580" t="n">
-        <v>186.6627314036357</v>
+        <v>186.6627467137522</v>
       </c>
       <c r="F580" t="n">
         <v>788933</v>
@@ -12052,16 +12052,16 @@
         <v>44071</v>
       </c>
       <c r="B582" t="n">
-        <v>192.1457977294922</v>
+        <v>192.1458129882812</v>
       </c>
       <c r="C582" t="n">
-        <v>192.1457977294922</v>
+        <v>192.1458129882812</v>
       </c>
       <c r="D582" t="n">
-        <v>187.1991053618704</v>
+        <v>187.1991202278299</v>
       </c>
       <c r="E582" t="n">
-        <v>188.9274693988745</v>
+        <v>188.9274844020878</v>
       </c>
       <c r="F582" t="n">
         <v>688066</v>
@@ -12112,16 +12112,16 @@
         <v>44076</v>
       </c>
       <c r="B585" t="n">
-        <v>202.0689544677734</v>
+        <v>202.0689392089844</v>
       </c>
       <c r="C585" t="n">
-        <v>206.4792512945507</v>
+        <v>206.4792357027279</v>
       </c>
       <c r="D585" t="n">
-        <v>199.7148156845751</v>
+        <v>199.7148006035536</v>
       </c>
       <c r="E585" t="n">
-        <v>205.3766770878564</v>
+        <v>205.376661579292</v>
       </c>
       <c r="F585" t="n">
         <v>581366</v>
@@ -12212,16 +12212,16 @@
         <v>44084</v>
       </c>
       <c r="B590" t="n">
-        <v>195.1853332519531</v>
+        <v>195.1853179931641</v>
       </c>
       <c r="C590" t="n">
-        <v>205.7938723336365</v>
+        <v>205.7938562455153</v>
       </c>
       <c r="D590" t="n">
-        <v>193.7549650259506</v>
+        <v>193.7549498789818</v>
       </c>
       <c r="E590" t="n">
-        <v>205.6746800337034</v>
+        <v>205.6746639549002</v>
       </c>
       <c r="F590" t="n">
         <v>559966</v>
@@ -12292,16 +12292,16 @@
         <v>44090</v>
       </c>
       <c r="B594" t="n">
-        <v>197.8408050537109</v>
+        <v>197.8407745361328</v>
       </c>
       <c r="C594" t="n">
-        <v>202.7689017487487</v>
+        <v>202.7688704709959</v>
       </c>
       <c r="D594" t="n">
-        <v>196.7954475265745</v>
+        <v>196.7954171702461</v>
       </c>
       <c r="E594" t="n">
-        <v>198.9458946924643</v>
+        <v>198.9458640044226</v>
       </c>
       <c r="F594" t="n">
         <v>602300</v>
@@ -12332,16 +12332,16 @@
         <v>44092</v>
       </c>
       <c r="B596" t="n">
-        <v>187.3872528076172</v>
+        <v>187.3872375488281</v>
       </c>
       <c r="C596" t="n">
-        <v>192.9724328937132</v>
+        <v>192.9724171801275</v>
       </c>
       <c r="D596" t="n">
-        <v>185.4757493545254</v>
+        <v>185.4757342513885</v>
       </c>
       <c r="E596" t="n">
-        <v>192.225751145258</v>
+        <v>192.225735492474</v>
       </c>
       <c r="F596" t="n">
         <v>571800</v>
@@ -12412,16 +12412,16 @@
         <v>44098</v>
       </c>
       <c r="B600" t="n">
-        <v>187.2677917480469</v>
+        <v>187.2677764892578</v>
       </c>
       <c r="C600" t="n">
-        <v>190.7921229760437</v>
+        <v>190.7921074300882</v>
       </c>
       <c r="D600" t="n">
-        <v>185.5354845935485</v>
+        <v>185.5354694759098</v>
       </c>
       <c r="E600" t="n">
-        <v>187.6560656561421</v>
+        <v>187.6560503657161</v>
       </c>
       <c r="F600" t="n">
         <v>378566</v>
@@ -12432,16 +12432,16 @@
         <v>44099</v>
       </c>
       <c r="B601" t="n">
-        <v>187.8352661132812</v>
+        <v>187.8352508544922</v>
       </c>
       <c r="C601" t="n">
-        <v>188.1339418625186</v>
+        <v>188.1339265794667</v>
       </c>
       <c r="D601" t="n">
-        <v>182.9967675877305</v>
+        <v>182.9967527219967</v>
       </c>
       <c r="E601" t="n">
-        <v>186.6704443634071</v>
+        <v>186.6704291992423</v>
       </c>
       <c r="F601" t="n">
         <v>316200</v>
@@ -12452,16 +12452,16 @@
         <v>44102</v>
       </c>
       <c r="B602" t="n">
-        <v>180.6372375488281</v>
+        <v>180.6372222900391</v>
       </c>
       <c r="C602" t="n">
-        <v>189.5078197050047</v>
+        <v>189.5078036968999</v>
       </c>
       <c r="D602" t="n">
-        <v>179.3529365301246</v>
+        <v>179.352921379823</v>
       </c>
       <c r="E602" t="n">
-        <v>188.9403343266758</v>
+        <v>188.9403183665075</v>
       </c>
       <c r="F602" t="n">
         <v>595500</v>
@@ -12472,16 +12472,16 @@
         <v>44103</v>
       </c>
       <c r="B603" t="n">
-        <v>180.9359130859375</v>
+        <v>180.9359283447266</v>
       </c>
       <c r="C603" t="n">
-        <v>183.5044847382582</v>
+        <v>183.5045002136614</v>
       </c>
       <c r="D603" t="n">
-        <v>178.6062546613765</v>
+        <v>178.6062697236995</v>
       </c>
       <c r="E603" t="n">
-        <v>181.2644396621141</v>
+        <v>181.2644549486086</v>
       </c>
       <c r="F603" t="n">
         <v>676133</v>
@@ -12512,16 +12512,16 @@
         <v>44105</v>
       </c>
       <c r="B605" t="n">
-        <v>188.1637878417969</v>
+        <v>188.1638031005859</v>
       </c>
       <c r="C605" t="n">
-        <v>191.1803806855457</v>
+        <v>191.1803961889597</v>
       </c>
       <c r="D605" t="n">
-        <v>183.2954237798904</v>
+        <v>183.2954386438886</v>
       </c>
       <c r="E605" t="n">
-        <v>185.9237427484422</v>
+        <v>185.923757825579</v>
       </c>
       <c r="F605" t="n">
         <v>698566</v>
@@ -12592,16 +12592,16 @@
         <v>44111</v>
       </c>
       <c r="B609" t="n">
-        <v>187.4170989990234</v>
+        <v>187.4171142578125</v>
       </c>
       <c r="C609" t="n">
-        <v>190.1648820732568</v>
+        <v>190.1648975557599</v>
       </c>
       <c r="D609" t="n">
-        <v>183.6836906524294</v>
+        <v>183.6837056072585</v>
       </c>
       <c r="E609" t="n">
-        <v>186.7600154841163</v>
+        <v>186.7600306894081</v>
       </c>
       <c r="F609" t="n">
         <v>573633</v>
@@ -12612,16 +12612,16 @@
         <v>44112</v>
       </c>
       <c r="B610" t="n">
-        <v>194.2268524169922</v>
+        <v>194.2268371582031</v>
       </c>
       <c r="C610" t="n">
-        <v>195.4812874745856</v>
+        <v>195.481272117246</v>
       </c>
       <c r="D610" t="n">
-        <v>187.4469845836759</v>
+        <v>187.4469698575246</v>
       </c>
       <c r="E610" t="n">
-        <v>188.1638002762209</v>
+        <v>188.1637854937555</v>
       </c>
       <c r="F610" t="n">
         <v>582633</v>
@@ -12632,16 +12632,16 @@
         <v>44113</v>
       </c>
       <c r="B611" t="n">
-        <v>192.8230895996094</v>
+        <v>192.8230743408203</v>
       </c>
       <c r="C611" t="n">
-        <v>196.5564983839074</v>
+        <v>196.5564828296802</v>
       </c>
       <c r="D611" t="n">
-        <v>190.4337140541703</v>
+        <v>190.4336989844612</v>
       </c>
       <c r="E611" t="n">
-        <v>194.1372567834963</v>
+        <v>194.1372414207124</v>
       </c>
       <c r="F611" t="n">
         <v>718800</v>
@@ -12652,16 +12652,16 @@
         <v>44117</v>
       </c>
       <c r="B612" t="n">
-        <v>196.9447479248047</v>
+        <v>196.9447631835938</v>
       </c>
       <c r="C612" t="n">
-        <v>198.467992496327</v>
+        <v>198.4680078731332</v>
       </c>
       <c r="D612" t="n">
-        <v>190.2843602382814</v>
+        <v>190.2843749810402</v>
       </c>
       <c r="E612" t="n">
-        <v>193.5398813577115</v>
+        <v>193.5398963526999</v>
       </c>
       <c r="F612" t="n">
         <v>922633</v>
@@ -12672,16 +12672,16 @@
         <v>44118</v>
       </c>
       <c r="B613" t="n">
-        <v>201.2157897949219</v>
+        <v>201.2157745361328</v>
       </c>
       <c r="C613" t="n">
-        <v>201.8430072986919</v>
+        <v>201.842991992339</v>
       </c>
       <c r="D613" t="n">
-        <v>196.2578274453795</v>
+        <v>196.2578125625674</v>
       </c>
       <c r="E613" t="n">
-        <v>197.5122472616411</v>
+        <v>197.5122322837026</v>
       </c>
       <c r="F613" t="n">
         <v>663866</v>
@@ -12692,16 +12692,16 @@
         <v>44119</v>
       </c>
       <c r="B614" t="n">
-        <v>198.4978790283203</v>
+        <v>198.4978637695312</v>
       </c>
       <c r="C614" t="n">
-        <v>201.4547399400632</v>
+        <v>201.4547244539764</v>
       </c>
       <c r="D614" t="n">
-        <v>196.9149021909145</v>
+        <v>196.9148870538109</v>
       </c>
       <c r="E614" t="n">
-        <v>199.6029686134291</v>
+        <v>199.6029532696903</v>
       </c>
       <c r="F614" t="n">
         <v>599566</v>
@@ -12712,16 +12712,16 @@
         <v>44120</v>
       </c>
       <c r="B615" t="n">
-        <v>193.1814880371094</v>
+        <v>193.1814727783203</v>
       </c>
       <c r="C615" t="n">
-        <v>198.8562812657416</v>
+        <v>198.8562655587187</v>
       </c>
       <c r="D615" t="n">
-        <v>190.0155648341094</v>
+        <v>190.0155498253865</v>
       </c>
       <c r="E615" t="n">
-        <v>198.6770697533628</v>
+        <v>198.6770540604953</v>
       </c>
       <c r="F615" t="n">
         <v>665566</v>
@@ -12732,16 +12732,16 @@
         <v>44123</v>
       </c>
       <c r="B616" t="n">
-        <v>192.3153381347656</v>
+        <v>192.3153533935547</v>
       </c>
       <c r="C616" t="n">
-        <v>196.6759641535809</v>
+        <v>196.6759797583532</v>
       </c>
       <c r="D616" t="n">
-        <v>189.1494149970842</v>
+        <v>189.1494300046808</v>
       </c>
       <c r="E616" t="n">
-        <v>195.1228686376407</v>
+        <v>195.1228841191864</v>
       </c>
       <c r="F616" t="n">
         <v>597800</v>
@@ -12752,16 +12752,16 @@
         <v>44124</v>
       </c>
       <c r="B617" t="n">
-        <v>194.2268524169922</v>
+        <v>194.2268371582031</v>
       </c>
       <c r="C617" t="n">
-        <v>195.8396801295791</v>
+        <v>195.8396647440835</v>
       </c>
       <c r="D617" t="n">
-        <v>190.612907899684</v>
+        <v>190.6128929248125</v>
       </c>
       <c r="E617" t="n">
-        <v>193.0321646598434</v>
+        <v>193.032149494911</v>
       </c>
       <c r="F617" t="n">
         <v>555666</v>
@@ -12772,16 +12772,16 @@
         <v>44125</v>
       </c>
       <c r="B618" t="n">
-        <v>192.70361328125</v>
+        <v>192.7036285400391</v>
       </c>
       <c r="C618" t="n">
-        <v>197.9901173573098</v>
+        <v>197.9901330346984</v>
       </c>
       <c r="D618" t="n">
-        <v>192.70361328125</v>
+        <v>192.7036285400391</v>
       </c>
       <c r="E618" t="n">
-        <v>193.6892386072849</v>
+        <v>193.6892539441184</v>
       </c>
       <c r="F618" t="n">
         <v>378600</v>
@@ -12812,16 +12812,16 @@
         <v>44127</v>
       </c>
       <c r="B620" t="n">
-        <v>190.3440856933594</v>
+        <v>190.3441162109375</v>
       </c>
       <c r="C620" t="n">
-        <v>195.2423154183572</v>
+        <v>195.242346721261</v>
       </c>
       <c r="D620" t="n">
-        <v>188.9403205672475</v>
+        <v>188.940350859762</v>
       </c>
       <c r="E620" t="n">
-        <v>194.1670920360976</v>
+        <v>194.1671231666126</v>
       </c>
       <c r="F620" t="n">
         <v>403166</v>
@@ -12852,16 +12852,16 @@
         <v>44131</v>
       </c>
       <c r="B622" t="n">
-        <v>198.3186645507812</v>
+        <v>198.3186492919922</v>
       </c>
       <c r="C622" t="n">
-        <v>204.7102583398841</v>
+        <v>204.710242589321</v>
       </c>
       <c r="D622" t="n">
-        <v>195.7500775753192</v>
+        <v>195.7500625141592</v>
       </c>
       <c r="E622" t="n">
-        <v>196.2876969283092</v>
+        <v>196.2876818257843</v>
       </c>
       <c r="F622" t="n">
         <v>606666</v>
@@ -12892,16 +12892,16 @@
         <v>44133</v>
       </c>
       <c r="B624" t="n">
-        <v>199.2744140625</v>
+        <v>199.2743988037109</v>
       </c>
       <c r="C624" t="n">
-        <v>199.871750302699</v>
+        <v>199.8717349981709</v>
       </c>
       <c r="D624" t="n">
-        <v>189.5376859918596</v>
+        <v>189.5376714786287</v>
       </c>
       <c r="E624" t="n">
-        <v>192.8529393435952</v>
+        <v>192.8529245765097</v>
       </c>
       <c r="F624" t="n">
         <v>707700</v>
@@ -12912,16 +12912,16 @@
         <v>44134</v>
       </c>
       <c r="B625" t="n">
-        <v>192.255615234375</v>
+        <v>192.2555999755859</v>
       </c>
       <c r="C625" t="n">
-        <v>199.8120308055818</v>
+        <v>199.8120149470612</v>
       </c>
       <c r="D625" t="n">
-        <v>192.255615234375</v>
+        <v>192.2555999755859</v>
       </c>
       <c r="E625" t="n">
-        <v>198.6472091128537</v>
+        <v>198.6471933467818</v>
       </c>
       <c r="F625" t="n">
         <v>632900</v>
@@ -12952,16 +12952,16 @@
         <v>44139</v>
       </c>
       <c r="B627" t="n">
-        <v>205.3076171875</v>
+        <v>205.3076019287109</v>
       </c>
       <c r="C627" t="n">
-        <v>208.0554005853026</v>
+        <v>208.0553851222939</v>
       </c>
       <c r="D627" t="n">
-        <v>195.9591621944386</v>
+        <v>195.9591476304417</v>
       </c>
       <c r="E627" t="n">
-        <v>196.5564984854674</v>
+        <v>196.5564838770755</v>
       </c>
       <c r="F627" t="n">
         <v>937700</v>
@@ -12972,16 +12972,16 @@
         <v>44140</v>
       </c>
       <c r="B628" t="n">
-        <v>207.9956512451172</v>
+        <v>207.9956359863281</v>
       </c>
       <c r="C628" t="n">
-        <v>214.894998009993</v>
+        <v>214.8949822450603</v>
       </c>
       <c r="D628" t="n">
-        <v>206.4425557493087</v>
+        <v>206.4425406044565</v>
       </c>
       <c r="E628" t="n">
-        <v>206.9801598858278</v>
+        <v>206.9801447015363</v>
       </c>
       <c r="F628" t="n">
         <v>801700</v>
@@ -12992,16 +12992,16 @@
         <v>44141</v>
       </c>
       <c r="B629" t="n">
-        <v>213.5509643554688</v>
+        <v>213.5509490966797</v>
       </c>
       <c r="C629" t="n">
-        <v>214.2379139441398</v>
+        <v>214.2378986362663</v>
       </c>
       <c r="D629" t="n">
-        <v>205.1881354642133</v>
+        <v>205.1881208029708</v>
       </c>
       <c r="E629" t="n">
-        <v>206.8308291135134</v>
+        <v>206.8308143348961</v>
       </c>
       <c r="F629" t="n">
         <v>849833</v>
@@ -13012,16 +13012,16 @@
         <v>44144</v>
       </c>
       <c r="B630" t="n">
-        <v>208.5332489013672</v>
+        <v>208.5332641601562</v>
       </c>
       <c r="C630" t="n">
-        <v>226.0653351719772</v>
+        <v>226.0653517136236</v>
       </c>
       <c r="D630" t="n">
-        <v>207.7865672291798</v>
+        <v>207.7865824333327</v>
       </c>
       <c r="E630" t="n">
-        <v>221.0177749674551</v>
+        <v>221.0177911397615</v>
       </c>
       <c r="F630" t="n">
         <v>887833</v>
@@ -13052,16 +13052,16 @@
         <v>44146</v>
       </c>
       <c r="B632" t="n">
-        <v>204.5908050537109</v>
+        <v>204.5907897949219</v>
       </c>
       <c r="C632" t="n">
-        <v>206.5620406736629</v>
+        <v>206.5620252678551</v>
       </c>
       <c r="D632" t="n">
-        <v>200.7379319803322</v>
+        <v>200.7379170088981</v>
       </c>
       <c r="E632" t="n">
-        <v>202.9779772911393</v>
+        <v>202.9779621526382</v>
       </c>
       <c r="F632" t="n">
         <v>574366</v>
@@ -13092,16 +13092,16 @@
         <v>44148</v>
       </c>
       <c r="B634" t="n">
-        <v>218.8972015380859</v>
+        <v>218.897216796875</v>
       </c>
       <c r="C634" t="n">
-        <v>220.6593745974234</v>
+        <v>220.6593899790492</v>
       </c>
       <c r="D634" t="n">
-        <v>209.9370211697153</v>
+        <v>209.9370358039121</v>
       </c>
       <c r="E634" t="n">
-        <v>209.9370211697153</v>
+        <v>209.9370358039121</v>
       </c>
       <c r="F634" t="n">
         <v>872100</v>
@@ -13112,16 +13112,16 @@
         <v>44151</v>
       </c>
       <c r="B635" t="n">
-        <v>218.0908050537109</v>
+        <v>218.0907897949219</v>
       </c>
       <c r="C635" t="n">
-        <v>221.5852702060042</v>
+        <v>221.5852547027238</v>
       </c>
       <c r="D635" t="n">
-        <v>215.0742119721199</v>
+        <v>215.0741969243876</v>
       </c>
       <c r="E635" t="n">
-        <v>221.0177999704102</v>
+        <v>221.0177845068331</v>
       </c>
       <c r="F635" t="n">
         <v>540700</v>
@@ -13132,16 +13132,16 @@
         <v>44152</v>
       </c>
       <c r="B636" t="n">
-        <v>215.7611541748047</v>
+        <v>215.7611389160156</v>
       </c>
       <c r="C636" t="n">
-        <v>220.390574829844</v>
+        <v>220.3905592436589</v>
       </c>
       <c r="D636" t="n">
-        <v>215.7611541748047</v>
+        <v>215.7611389160156</v>
       </c>
       <c r="E636" t="n">
-        <v>219.793238559895</v>
+        <v>219.7932230159539</v>
       </c>
       <c r="F636" t="n">
         <v>945033</v>
@@ -13152,16 +13152,16 @@
         <v>44153</v>
       </c>
       <c r="B637" t="n">
-        <v>213.1029663085938</v>
+        <v>213.1029357910156</v>
       </c>
       <c r="C637" t="n">
-        <v>217.4337111775966</v>
+        <v>217.4336800398308</v>
       </c>
       <c r="D637" t="n">
-        <v>213.1029663085938</v>
+        <v>213.1029357910156</v>
       </c>
       <c r="E637" t="n">
-        <v>216.8662409688433</v>
+        <v>216.8662099123425</v>
       </c>
       <c r="F637" t="n">
         <v>504433</v>
@@ -13172,16 +13172,16 @@
         <v>44154</v>
       </c>
       <c r="B638" t="n">
-        <v>213.1627044677734</v>
+        <v>213.1626892089844</v>
       </c>
       <c r="C638" t="n">
-        <v>215.4326157497906</v>
+        <v>215.4326003285149</v>
       </c>
       <c r="D638" t="n">
-        <v>209.9668999255425</v>
+        <v>209.9668848955181</v>
       </c>
       <c r="E638" t="n">
-        <v>213.819788047115</v>
+        <v>213.81977274129</v>
       </c>
       <c r="F638" t="n">
         <v>672366</v>
@@ -13192,16 +13192,16 @@
         <v>44158</v>
       </c>
       <c r="B639" t="n">
-        <v>215.3429870605469</v>
+        <v>215.343017578125</v>
       </c>
       <c r="C639" t="n">
-        <v>217.9115737137244</v>
+        <v>217.9116045953127</v>
       </c>
       <c r="D639" t="n">
-        <v>212.3263944636089</v>
+        <v>212.3264245536871</v>
       </c>
       <c r="E639" t="n">
-        <v>213.5509480942281</v>
+        <v>213.5509783578453</v>
       </c>
       <c r="F639" t="n">
         <v>541300</v>
@@ -13232,16 +13232,16 @@
         <v>44160</v>
       </c>
       <c r="B641" t="n">
-        <v>216.8363647460938</v>
+        <v>216.8363800048828</v>
       </c>
       <c r="C641" t="n">
-        <v>220.4204277256715</v>
+        <v>220.4204432366713</v>
       </c>
       <c r="D641" t="n">
-        <v>214.7456499478817</v>
+        <v>214.745665059547</v>
       </c>
       <c r="E641" t="n">
-        <v>215.044325660666</v>
+        <v>215.0443407933491</v>
       </c>
       <c r="F641" t="n">
         <v>311466</v>
@@ -13252,16 +13252,16 @@
         <v>44161</v>
       </c>
       <c r="B642" t="n">
-        <v>212.8043060302734</v>
+        <v>212.8042755126953</v>
       </c>
       <c r="C642" t="n">
-        <v>218.6284299560349</v>
+        <v>218.6283986032379</v>
       </c>
       <c r="D642" t="n">
-        <v>210.2655849551651</v>
+        <v>210.2655548016568</v>
       </c>
       <c r="E642" t="n">
-        <v>216.3883846294004</v>
+        <v>216.3883535978412</v>
       </c>
       <c r="F642" t="n">
         <v>253146</v>
@@ -13272,16 +13272,16 @@
         <v>44162</v>
       </c>
       <c r="B643" t="n">
-        <v>214.2976531982422</v>
+        <v>214.2976684570312</v>
       </c>
       <c r="C643" t="n">
-        <v>216.3883680864437</v>
+        <v>216.3883834940995</v>
       </c>
       <c r="D643" t="n">
-        <v>207.5775177320952</v>
+        <v>207.5775325123857</v>
       </c>
       <c r="E643" t="n">
-        <v>212.6549594941399</v>
+        <v>212.654974635963</v>
       </c>
       <c r="F643" t="n">
         <v>618080</v>
@@ -13292,16 +13292,16 @@
         <v>44165</v>
       </c>
       <c r="B644" t="n">
-        <v>215.3429870605469</v>
+        <v>215.343017578125</v>
       </c>
       <c r="C644" t="n">
-        <v>217.5830319706262</v>
+        <v>217.5830628056549</v>
       </c>
       <c r="D644" t="n">
-        <v>209.9668701615904</v>
+        <v>209.966899917286</v>
       </c>
       <c r="E644" t="n">
-        <v>214.2976297309212</v>
+        <v>214.2976601003553</v>
       </c>
       <c r="F644" t="n">
         <v>990433</v>
@@ -13312,16 +13312,16 @@
         <v>44166</v>
       </c>
       <c r="B645" t="n">
-        <v>215.3429870605469</v>
+        <v>215.343017578125</v>
       </c>
       <c r="C645" t="n">
-        <v>219.8230768807055</v>
+        <v>219.8231080331847</v>
       </c>
       <c r="D645" t="n">
-        <v>212.804266457535</v>
+        <v>212.8042966153354</v>
       </c>
       <c r="E645" t="n">
-        <v>216.2389989480679</v>
+        <v>216.2390295926254</v>
       </c>
       <c r="F645" t="n">
         <v>896293</v>
@@ -13372,16 +13372,16 @@
         <v>44169</v>
       </c>
       <c r="B648" t="n">
-        <v>228.9326171875</v>
+        <v>228.9326324462891</v>
       </c>
       <c r="C648" t="n">
-        <v>230.2766503886246</v>
+        <v>230.276665736996</v>
       </c>
       <c r="D648" t="n">
-        <v>224.6018722340697</v>
+        <v>224.6018872042065</v>
       </c>
       <c r="E648" t="n">
-        <v>226.9912477124258</v>
+        <v>226.9912628418189</v>
       </c>
       <c r="F648" t="n">
         <v>265620</v>
@@ -13412,16 +13412,16 @@
         <v>44173</v>
       </c>
       <c r="B650" t="n">
-        <v>228.6339263916016</v>
+        <v>228.6339416503906</v>
       </c>
       <c r="C650" t="n">
-        <v>230.7246411908779</v>
+        <v>230.7246565891991</v>
       </c>
       <c r="D650" t="n">
-        <v>221.7644609504555</v>
+        <v>221.7644757507836</v>
       </c>
       <c r="E650" t="n">
-        <v>223.8551757497318</v>
+        <v>223.8551906895921</v>
       </c>
       <c r="F650" t="n">
         <v>500300</v>
@@ -13432,16 +13432,16 @@
         <v>44174</v>
       </c>
       <c r="B651" t="n">
-        <v>225.4978790283203</v>
+        <v>225.4978637695312</v>
       </c>
       <c r="C651" t="n">
-        <v>232.0686842288357</v>
+        <v>232.0686685254193</v>
       </c>
       <c r="D651" t="n">
-        <v>222.660482420989</v>
+        <v>222.6604673541984</v>
       </c>
       <c r="E651" t="n">
-        <v>229.9779693401412</v>
+        <v>229.9779537781974</v>
       </c>
       <c r="F651" t="n">
         <v>560820</v>
@@ -13452,16 +13452,16 @@
         <v>44175</v>
       </c>
       <c r="B652" t="n">
-        <v>227.8872528076172</v>
+        <v>227.8872680664062</v>
       </c>
       <c r="C652" t="n">
-        <v>233.4127005239284</v>
+        <v>233.4127161526883</v>
       </c>
       <c r="D652" t="n">
-        <v>225.6472076678649</v>
+        <v>225.6472227766659</v>
       </c>
       <c r="E652" t="n">
-        <v>226.6925651046716</v>
+        <v>226.6925802834673</v>
       </c>
       <c r="F652" t="n">
         <v>713620</v>
@@ -13472,16 +13472,16 @@
         <v>44176</v>
       </c>
       <c r="B653" t="n">
-        <v>226.5432434082031</v>
+        <v>226.5432281494141</v>
       </c>
       <c r="C653" t="n">
-        <v>231.172664128968</v>
+        <v>231.172648558365</v>
       </c>
       <c r="D653" t="n">
-        <v>224.7512041903565</v>
+        <v>224.75118905227</v>
       </c>
       <c r="E653" t="n">
-        <v>228.4846128978375</v>
+        <v>228.4845975082877</v>
       </c>
       <c r="F653" t="n">
         <v>373833</v>
@@ -13512,16 +13512,16 @@
         <v>44180</v>
       </c>
       <c r="B655" t="n">
-        <v>226.6925659179688</v>
+        <v>226.6925506591797</v>
       </c>
       <c r="C655" t="n">
-        <v>228.1859293498279</v>
+        <v>228.1859139905198</v>
       </c>
       <c r="D655" t="n">
-        <v>223.1085027962737</v>
+        <v>223.1084877787297</v>
       </c>
       <c r="E655" t="n">
-        <v>226.0952296599921</v>
+        <v>226.09521444141</v>
       </c>
       <c r="F655" t="n">
         <v>364800</v>
@@ -13532,16 +13532,16 @@
         <v>44181</v>
       </c>
       <c r="B656" t="n">
-        <v>230.4259796142578</v>
+        <v>230.4259643554688</v>
       </c>
       <c r="C656" t="n">
-        <v>232.9647005430468</v>
+        <v>232.9646851161438</v>
       </c>
       <c r="D656" t="n">
-        <v>225.1992074866895</v>
+        <v>225.1991925740168</v>
       </c>
       <c r="E656" t="n">
-        <v>227.2899224142283</v>
+        <v>227.2899073631087</v>
       </c>
       <c r="F656" t="n">
         <v>398466</v>
@@ -13572,16 +13572,16 @@
         <v>44183</v>
       </c>
       <c r="B658" t="n">
-        <v>226.9912414550781</v>
+        <v>226.9912261962891</v>
       </c>
       <c r="C658" t="n">
-        <v>233.8607071594441</v>
+        <v>233.8606914388764</v>
       </c>
       <c r="D658" t="n">
-        <v>224.7511963091399</v>
+        <v>224.7511812009309</v>
       </c>
       <c r="E658" t="n">
-        <v>230.1272985828803</v>
+        <v>230.1272831132795</v>
       </c>
       <c r="F658" t="n">
         <v>323473</v>
@@ -13672,16 +13672,16 @@
         <v>44194</v>
       </c>
       <c r="B663" t="n">
-        <v>231.7700042724609</v>
+        <v>231.7699890136719</v>
       </c>
       <c r="C663" t="n">
-        <v>234.1593796519724</v>
+        <v>234.1593642358766</v>
       </c>
       <c r="D663" t="n">
-        <v>225.3485446476555</v>
+        <v>225.348529811629</v>
       </c>
       <c r="E663" t="n">
-        <v>227.5885897626768</v>
+        <v>227.588574779175</v>
       </c>
       <c r="F663" t="n">
         <v>293840</v>
@@ -13692,16 +13692,16 @@
         <v>44195</v>
       </c>
       <c r="B664" t="n">
-        <v>227.8872528076172</v>
+        <v>227.8872680664062</v>
       </c>
       <c r="C664" t="n">
-        <v>235.6527456636806</v>
+        <v>235.6527614424286</v>
       </c>
       <c r="D664" t="n">
-        <v>225.9458833914209</v>
+        <v>225.9458985202205</v>
       </c>
       <c r="E664" t="n">
-        <v>234.1593822371791</v>
+        <v>234.1593979159351</v>
       </c>
       <c r="F664" t="n">
         <v>659613</v>
@@ -13712,16 +13712,16 @@
         <v>44200</v>
       </c>
       <c r="B665" t="n">
-        <v>224.6018676757812</v>
+        <v>224.6018524169922</v>
       </c>
       <c r="C665" t="n">
-        <v>231.6206636977356</v>
+        <v>231.6206479621102</v>
       </c>
       <c r="D665" t="n">
-        <v>220.4204378866018</v>
+        <v>220.4204229118868</v>
       </c>
       <c r="E665" t="n">
-        <v>230.1273002562511</v>
+        <v>230.1272846220805</v>
       </c>
       <c r="F665" t="n">
         <v>564553</v>
@@ -13732,16 +13732,16 @@
         <v>44201</v>
       </c>
       <c r="B666" t="n">
-        <v>218.7777252197266</v>
+        <v>218.7777404785156</v>
       </c>
       <c r="C666" t="n">
-        <v>225.6471903787839</v>
+        <v>225.6472061166881</v>
       </c>
       <c r="D666" t="n">
-        <v>218.1803738183837</v>
+        <v>218.1803890355101</v>
       </c>
       <c r="E666" t="n">
-        <v>224.9005087227439</v>
+        <v>224.9005244085703</v>
       </c>
       <c r="F666" t="n">
         <v>585466</v>
@@ -13752,16 +13752,16 @@
         <v>44202</v>
       </c>
       <c r="B667" t="n">
-        <v>210.7135620117188</v>
+        <v>210.7135772705078</v>
       </c>
       <c r="C667" t="n">
-        <v>220.5697692085711</v>
+        <v>220.5697851810959</v>
       </c>
       <c r="D667" t="n">
-        <v>210.4149014955867</v>
+        <v>210.4149167327483</v>
       </c>
       <c r="E667" t="n">
-        <v>220.5697692085711</v>
+        <v>220.5697851810959</v>
       </c>
       <c r="F667" t="n">
         <v>989980</v>
@@ -13772,16 +13772,16 @@
         <v>44203</v>
       </c>
       <c r="B668" t="n">
-        <v>213.2523040771484</v>
+        <v>213.2522888183594</v>
       </c>
       <c r="C668" t="n">
-        <v>217.2843885524602</v>
+        <v>217.2843730051644</v>
       </c>
       <c r="D668" t="n">
-        <v>207.1295198233158</v>
+        <v>207.1295050026288</v>
       </c>
       <c r="E668" t="n">
-        <v>211.4602648446455</v>
+        <v>211.4602497140818</v>
       </c>
       <c r="F668" t="n">
         <v>485820</v>
@@ -13812,16 +13812,16 @@
         <v>44207</v>
       </c>
       <c r="B670" t="n">
-        <v>272.2713012695312</v>
+        <v>272.2713317871094</v>
       </c>
       <c r="C670" t="n">
-        <v>276.4601026942797</v>
+        <v>276.4601336813603</v>
       </c>
       <c r="D670" t="n">
-        <v>249.9809523860654</v>
+        <v>249.9809804052258</v>
       </c>
       <c r="E670" t="n">
-        <v>250.7289504664762</v>
+        <v>250.7289785694761</v>
       </c>
       <c r="F670" t="n">
         <v>3239386</v>
@@ -13932,16 +13932,16 @@
         <v>44215</v>
       </c>
       <c r="B676" t="n">
-        <v>259.8544921875</v>
+        <v>259.8545227050781</v>
       </c>
       <c r="C676" t="n">
-        <v>273.7672671170767</v>
+        <v>273.7672992685854</v>
       </c>
       <c r="D676" t="n">
-        <v>255.3665042019742</v>
+        <v>255.3665341924784</v>
       </c>
       <c r="E676" t="n">
-        <v>269.8776836168443</v>
+        <v>269.8777153115562</v>
       </c>
       <c r="F676" t="n">
         <v>761093</v>
@@ -13952,16 +13952,16 @@
         <v>44216</v>
       </c>
       <c r="B677" t="n">
-        <v>259.8544921875</v>
+        <v>259.8545227050781</v>
       </c>
       <c r="C677" t="n">
-        <v>264.4921041214365</v>
+        <v>264.4921351836605</v>
       </c>
       <c r="D677" t="n">
-        <v>256.8625001971495</v>
+        <v>256.8625303633449</v>
       </c>
       <c r="E677" t="n">
-        <v>259.4057116506173</v>
+        <v>259.4057421154902</v>
       </c>
       <c r="F677" t="n">
         <v>662453</v>
@@ -14012,16 +14012,16 @@
         <v>44222</v>
       </c>
       <c r="B680" t="n">
-        <v>267.7833557128906</v>
+        <v>267.7833251953125</v>
       </c>
       <c r="C680" t="n">
-        <v>276.1609294691975</v>
+        <v>276.1608979968802</v>
       </c>
       <c r="D680" t="n">
-        <v>261.5001830046917</v>
+        <v>261.5001532031671</v>
       </c>
       <c r="E680" t="n">
-        <v>263.4449600638367</v>
+        <v>263.4449300406782</v>
       </c>
       <c r="F680" t="n">
         <v>884853</v>
@@ -14092,16 +14092,16 @@
         <v>44228</v>
       </c>
       <c r="B684" t="n">
-        <v>261.9489440917969</v>
+        <v>261.9489135742188</v>
       </c>
       <c r="C684" t="n">
-        <v>264.6417495861901</v>
+        <v>264.6417187548947</v>
       </c>
       <c r="D684" t="n">
-        <v>256.7129570807941</v>
+        <v>256.712927173219</v>
       </c>
       <c r="E684" t="n">
-        <v>264.6417495861901</v>
+        <v>264.6417187548947</v>
       </c>
       <c r="F684" t="n">
         <v>678393</v>
@@ -14112,16 +14112,16 @@
         <v>44229</v>
       </c>
       <c r="B685" t="n">
-        <v>265.6889038085938</v>
+        <v>265.6888732910156</v>
       </c>
       <c r="C685" t="n">
-        <v>271.5232947415027</v>
+        <v>271.5232635537744</v>
       </c>
       <c r="D685" t="n">
-        <v>260.7521348931468</v>
+        <v>260.7521049426162</v>
       </c>
       <c r="E685" t="n">
-        <v>266.5864953899369</v>
+        <v>266.5864647692596</v>
       </c>
       <c r="F685" t="n">
         <v>627486</v>
@@ -14132,16 +14132,16 @@
         <v>44230</v>
       </c>
       <c r="B686" t="n">
-        <v>264.6417541503906</v>
+        <v>264.6417236328125</v>
       </c>
       <c r="C686" t="n">
-        <v>267.7833403239498</v>
+        <v>267.7833094440948</v>
       </c>
       <c r="D686" t="n">
-        <v>260.3033587506551</v>
+        <v>260.3033287333658</v>
       </c>
       <c r="E686" t="n">
-        <v>267.1849357108616</v>
+        <v>267.1849049000126</v>
       </c>
       <c r="F686" t="n">
         <v>630753</v>
@@ -14172,16 +14172,16 @@
         <v>44232</v>
       </c>
       <c r="B688" t="n">
-        <v>267.0353393554688</v>
+        <v>267.0353088378906</v>
       </c>
       <c r="C688" t="n">
-        <v>273.7673227005646</v>
+        <v>273.7672914136357</v>
       </c>
       <c r="D688" t="n">
-        <v>264.94093844977</v>
+        <v>264.9409081715461</v>
       </c>
       <c r="E688" t="n">
-        <v>265.3897495138921</v>
+        <v>265.3897191843768</v>
       </c>
       <c r="F688" t="n">
         <v>358426</v>
@@ -14212,16 +14212,16 @@
         <v>44236</v>
       </c>
       <c r="B690" t="n">
-        <v>264.7913208007812</v>
+        <v>264.7912902832031</v>
       </c>
       <c r="C690" t="n">
-        <v>270.1769008993359</v>
+        <v>270.1768697610619</v>
       </c>
       <c r="D690" t="n">
-        <v>264.1929162484707</v>
+        <v>264.1928857998596</v>
       </c>
       <c r="E690" t="n">
-        <v>269.4289028179777</v>
+        <v>269.4288717659117</v>
       </c>
       <c r="F690" t="n">
         <v>477180</v>
@@ -14372,16 +14372,16 @@
         <v>44250</v>
       </c>
       <c r="B698" t="n">
-        <v>243.8473815917969</v>
+        <v>243.8473968505859</v>
       </c>
       <c r="C698" t="n">
-        <v>250.7289580525621</v>
+        <v>250.7289737419669</v>
       </c>
       <c r="D698" t="n">
-        <v>241.4537937492856</v>
+        <v>241.4538088582955</v>
       </c>
       <c r="E698" t="n">
-        <v>247.7369656403928</v>
+        <v>247.7369811425732</v>
       </c>
       <c r="F698" t="n">
         <v>535220</v>
@@ -14472,16 +14472,16 @@
         <v>44257</v>
       </c>
       <c r="B703" t="n">
-        <v>245.3433685302734</v>
+        <v>245.3433837890625</v>
       </c>
       <c r="C703" t="n">
-        <v>246.5401624063213</v>
+        <v>246.5401777395433</v>
       </c>
       <c r="D703" t="n">
-        <v>231.8794031840999</v>
+        <v>231.8794176055164</v>
       </c>
       <c r="E703" t="n">
-        <v>242.6505785046507</v>
+        <v>242.6505935959654</v>
       </c>
       <c r="F703" t="n">
         <v>816593</v>
@@ -14492,16 +14492,16 @@
         <v>44258</v>
       </c>
       <c r="B704" t="n">
-        <v>241.6033782958984</v>
+        <v>241.6033935546875</v>
       </c>
       <c r="C704" t="n">
-        <v>245.9417732193955</v>
+        <v>245.9417887521817</v>
       </c>
       <c r="D704" t="n">
-        <v>231.1314052428255</v>
+        <v>231.1314198402428</v>
       </c>
       <c r="E704" t="n">
-        <v>242.9497809185175</v>
+        <v>242.9497962623404</v>
       </c>
       <c r="F704" t="n">
         <v>976053</v>
@@ -14552,16 +14552,16 @@
         <v>44263</v>
       </c>
       <c r="B707" t="n">
-        <v>224.5490264892578</v>
+        <v>224.5490417480469</v>
       </c>
       <c r="C707" t="n">
-        <v>232.0290075877416</v>
+        <v>232.0290233548181</v>
       </c>
       <c r="D707" t="n">
-        <v>221.7066428026703</v>
+        <v>221.7066578683107</v>
       </c>
       <c r="E707" t="n">
-        <v>225.7458356394636</v>
+        <v>225.7458509795795</v>
       </c>
       <c r="F707" t="n">
         <v>1054193</v>
@@ -14592,16 +14592,16 @@
         <v>44265</v>
       </c>
       <c r="B709" t="n">
-        <v>227.2418212890625</v>
+        <v>227.2418365478516</v>
       </c>
       <c r="C709" t="n">
-        <v>229.4858155142288</v>
+        <v>229.4858309236971</v>
       </c>
       <c r="D709" t="n">
-        <v>217.9666421147633</v>
+        <v>217.9666567507444</v>
       </c>
       <c r="E709" t="n">
-        <v>228.7378174391734</v>
+        <v>228.7378327984153</v>
       </c>
       <c r="F709" t="n">
         <v>667500</v>
@@ -14632,16 +14632,16 @@
         <v>44267</v>
       </c>
       <c r="B711" t="n">
-        <v>228.8874359130859</v>
+        <v>228.8874206542969</v>
       </c>
       <c r="C711" t="n">
-        <v>231.8794285394008</v>
+        <v>231.8794130811504</v>
       </c>
       <c r="D711" t="n">
-        <v>225.8954432867711</v>
+        <v>225.8954282274433</v>
       </c>
       <c r="E711" t="n">
-        <v>227.8402354502634</v>
+        <v>227.840220261286</v>
       </c>
       <c r="F711" t="n">
         <v>268453</v>
@@ -14652,16 +14652,16 @@
         <v>44270</v>
       </c>
       <c r="B712" t="n">
-        <v>231.5802307128906</v>
+        <v>231.5802154541016</v>
       </c>
       <c r="C712" t="n">
-        <v>232.3282288839388</v>
+        <v>232.3282135758642</v>
       </c>
       <c r="D712" t="n">
-        <v>225.5962453445055</v>
+        <v>225.5962304800004</v>
       </c>
       <c r="E712" t="n">
-        <v>228.8874403407297</v>
+        <v>228.8874252593682</v>
       </c>
       <c r="F712" t="n">
         <v>221460</v>
@@ -14852,16 +14852,16 @@
         <v>44284</v>
       </c>
       <c r="B722" t="n">
-        <v>223.8010101318359</v>
+        <v>223.801025390625</v>
       </c>
       <c r="C722" t="n">
-        <v>226.0450042784174</v>
+        <v>226.0450196902024</v>
       </c>
       <c r="D722" t="n">
-        <v>219.7618328424367</v>
+        <v>219.761847825834</v>
       </c>
       <c r="E722" t="n">
-        <v>226.0450042784174</v>
+        <v>226.0450196902024</v>
       </c>
       <c r="F722" t="n">
         <v>788160</v>
@@ -14952,16 +14952,16 @@
         <v>44292</v>
       </c>
       <c r="B727" t="n">
-        <v>219.1634368896484</v>
+        <v>219.1634521484375</v>
       </c>
       <c r="C727" t="n">
-        <v>222.9034272802568</v>
+        <v>222.9034427994347</v>
       </c>
       <c r="D727" t="n">
-        <v>215.4234464990401</v>
+        <v>215.4234614974403</v>
       </c>
       <c r="E727" t="n">
-        <v>221.1082288491528</v>
+        <v>221.1082442433439</v>
       </c>
       <c r="F727" t="n">
         <v>964873</v>
@@ -14972,16 +14972,16 @@
         <v>44293</v>
       </c>
       <c r="B728" t="n">
-        <v>227.6906127929688</v>
+        <v>227.6906280517578</v>
       </c>
       <c r="C728" t="n">
-        <v>230.3834027687316</v>
+        <v>230.3834182079792</v>
       </c>
       <c r="D728" t="n">
-        <v>219.16343185467</v>
+        <v>219.1634465420062</v>
       </c>
       <c r="E728" t="n">
-        <v>219.3130253796337</v>
+        <v>219.313040076995</v>
       </c>
       <c r="F728" t="n">
         <v>1567580</v>
@@ -15052,16 +15052,16 @@
         <v>44299</v>
       </c>
       <c r="B732" t="n">
-        <v>227.2418212890625</v>
+        <v>227.2418365478516</v>
       </c>
       <c r="C732" t="n">
-        <v>227.9898193641179</v>
+        <v>227.9898346731334</v>
       </c>
       <c r="D732" t="n">
-        <v>219.9114340662954</v>
+        <v>219.9114488328651</v>
       </c>
       <c r="E732" t="n">
-        <v>220.6594321413508</v>
+        <v>220.6594469581469</v>
       </c>
       <c r="F732" t="n">
         <v>596393</v>
@@ -15192,16 +15192,16 @@
         <v>44309</v>
       </c>
       <c r="B739" t="n">
-        <v>220.3602447509766</v>
+        <v>220.3602294921875</v>
       </c>
       <c r="C739" t="n">
-        <v>223.6514395471216</v>
+        <v>223.6514240604346</v>
       </c>
       <c r="D739" t="n">
-        <v>218.2658591302012</v>
+        <v>218.2658440164373</v>
       </c>
       <c r="E739" t="n">
-        <v>222.3050368338611</v>
+        <v>222.3050214404054</v>
       </c>
       <c r="F739" t="n">
         <v>863700</v>
@@ -15452,16 +15452,16 @@
         <v>44328</v>
       </c>
       <c r="B752" t="n">
-        <v>212.4675750732422</v>
+        <v>212.4675598144531</v>
       </c>
       <c r="C752" t="n">
-        <v>218.9014493024574</v>
+        <v>218.9014335816066</v>
       </c>
       <c r="D752" t="n">
-        <v>211.2705776944238</v>
+        <v>211.2705625215996</v>
       </c>
       <c r="E752" t="n">
-        <v>218.4525771879814</v>
+        <v>218.4525614993673</v>
       </c>
       <c r="F752" t="n">
         <v>1381546</v>
@@ -15472,16 +15472,16 @@
         <v>44329</v>
       </c>
       <c r="B753" t="n">
-        <v>218.4525604248047</v>
+        <v>218.4525756835938</v>
       </c>
       <c r="C753" t="n">
-        <v>221.7443143794447</v>
+        <v>221.7443298681609</v>
       </c>
       <c r="D753" t="n">
-        <v>214.4126812632304</v>
+        <v>214.4126962398362</v>
       </c>
       <c r="E753" t="n">
-        <v>214.7119343901334</v>
+        <v>214.7119493876418</v>
       </c>
       <c r="F753" t="n">
         <v>807133</v>
@@ -15512,16 +15512,16 @@
         <v>44333</v>
       </c>
       <c r="B755" t="n">
-        <v>218.6021881103516</v>
+        <v>218.6022033691406</v>
       </c>
       <c r="C755" t="n">
-        <v>222.9413205721625</v>
+        <v>222.9413361338301</v>
       </c>
       <c r="D755" t="n">
-        <v>217.8540628735322</v>
+        <v>217.8540780801009</v>
       </c>
       <c r="E755" t="n">
-        <v>219.2006943880658</v>
+        <v>219.2007096886316</v>
       </c>
       <c r="F755" t="n">
         <v>603380</v>
@@ -15532,16 +15532,16 @@
         <v>44334</v>
       </c>
       <c r="B756" t="n">
-        <v>219.7991943359375</v>
+        <v>219.7992095947266</v>
       </c>
       <c r="C756" t="n">
-        <v>223.2405672820714</v>
+        <v>223.2405827797657</v>
       </c>
       <c r="D756" t="n">
-        <v>215.6096809538825</v>
+        <v>215.6096959218293</v>
       </c>
       <c r="E756" t="n">
-        <v>218.7518159904238</v>
+        <v>218.7518311765023</v>
       </c>
       <c r="F756" t="n">
         <v>1363900</v>
@@ -15552,16 +15552,16 @@
         <v>44335</v>
       </c>
       <c r="B757" t="n">
-        <v>217.8540649414062</v>
+        <v>217.8540802001953</v>
       </c>
       <c r="C757" t="n">
-        <v>221.7443253421814</v>
+        <v>221.7443408734494</v>
       </c>
       <c r="D757" t="n">
-        <v>216.9563207369604</v>
+        <v>216.9563359328703</v>
       </c>
       <c r="E757" t="n">
-        <v>219.0510775081968</v>
+        <v>219.0510928508262</v>
       </c>
       <c r="F757" t="n">
         <v>577806</v>
@@ -15572,16 +15572,16 @@
         <v>44336</v>
       </c>
       <c r="B758" t="n">
-        <v>223.0909271240234</v>
+        <v>223.0909423828125</v>
       </c>
       <c r="C758" t="n">
-        <v>224.4375585636639</v>
+        <v>224.4375739145587</v>
       </c>
       <c r="D758" t="n">
-        <v>217.2555597337558</v>
+        <v>217.2555745934222</v>
       </c>
       <c r="E758" t="n">
-        <v>219.2006821971784</v>
+        <v>219.2006971898857</v>
       </c>
       <c r="F758" t="n">
         <v>585933</v>
@@ -15932,16 +15932,16 @@
         <v>44363</v>
       </c>
       <c r="B776" t="n">
-        <v>228.9263305664062</v>
+        <v>228.9263153076172</v>
       </c>
       <c r="C776" t="n">
-        <v>230.8714532068279</v>
+        <v>230.8714378183892</v>
       </c>
       <c r="D776" t="n">
-        <v>225.7842105488518</v>
+        <v>225.7841954994967</v>
       </c>
       <c r="E776" t="n">
-        <v>226.3827016270945</v>
+        <v>226.3826865378477</v>
       </c>
       <c r="F776" t="n">
         <v>725393</v>
@@ -16132,16 +16132,16 @@
         <v>44377</v>
       </c>
       <c r="B786" t="n">
-        <v>230.5721893310547</v>
+        <v>230.5721740722656</v>
       </c>
       <c r="C786" t="n">
-        <v>232.5173271016351</v>
+        <v>232.5173117141208</v>
       </c>
       <c r="D786" t="n">
-        <v>227.7293225951968</v>
+        <v>227.7293075245428</v>
       </c>
       <c r="E786" t="n">
-        <v>231.3203145595405</v>
+        <v>231.320299251242</v>
       </c>
       <c r="F786" t="n">
         <v>609766</v>
@@ -42112,19 +42112,39 @@
         <v>46280</v>
       </c>
       <c r="B2085" t="n">
-        <v>6.63</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="C2085" t="n">
         <v>6.75</v>
       </c>
       <c r="D2085" t="n">
-        <v>6.47</v>
+        <v>6.46999979019165</v>
       </c>
       <c r="E2085" t="n">
         <v>6.75</v>
       </c>
       <c r="F2085" t="n">
         <v>8419600</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B2086" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>9166800</v>
       </c>
     </row>
   </sheetData>

--- a/database/HAPV3.xlsx
+++ b/database/HAPV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2088"/>
+  <dimension ref="A1:F2089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>43217</v>
       </c>
       <c r="B3" t="n">
-        <v>82.00556182861328</v>
+        <v>82.00555419921875</v>
       </c>
       <c r="C3" t="n">
-        <v>83.90925939176427</v>
+        <v>83.90925158525906</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54117679595947</v>
+        <v>80.54116930280414</v>
       </c>
       <c r="E3" t="n">
-        <v>81.9762753196798</v>
+        <v>81.97626769300994</v>
       </c>
       <c r="F3" t="n">
         <v>932166</v>
@@ -492,16 +492,16 @@
         <v>43220</v>
       </c>
       <c r="B4" t="n">
-        <v>80.98048400878906</v>
+        <v>80.98049926757812</v>
       </c>
       <c r="C4" t="n">
-        <v>82.00555644363325</v>
+        <v>82.00557189557212</v>
       </c>
       <c r="D4" t="n">
-        <v>80.68761149043854</v>
+        <v>80.68762669404295</v>
       </c>
       <c r="E4" t="n">
-        <v>81.56623649373705</v>
+        <v>81.56625186289682</v>
       </c>
       <c r="F4" t="n">
         <v>370366</v>
@@ -552,16 +552,16 @@
         <v>43224</v>
       </c>
       <c r="B7" t="n">
-        <v>78.34458160400391</v>
+        <v>78.34458923339844</v>
       </c>
       <c r="C7" t="n">
-        <v>81.0390515428093</v>
+        <v>81.03905943459817</v>
       </c>
       <c r="D7" t="n">
-        <v>77.3195093326906</v>
+        <v>77.31951686226098</v>
       </c>
       <c r="E7" t="n">
-        <v>81.0390515428093</v>
+        <v>81.03905943459817</v>
       </c>
       <c r="F7" t="n">
         <v>632800</v>
@@ -572,16 +572,16 @@
         <v>43227</v>
       </c>
       <c r="B8" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C8" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="D8" t="n">
-        <v>77.90527738914264</v>
+        <v>77.90528490550868</v>
       </c>
       <c r="E8" t="n">
-        <v>78.05171737852535</v>
+        <v>78.05172490902004</v>
       </c>
       <c r="F8" t="n">
         <v>375200</v>
@@ -592,16 +592,16 @@
         <v>43228</v>
       </c>
       <c r="B9" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C9" t="n">
-        <v>79.95542234400601</v>
+        <v>79.95543005817173</v>
       </c>
       <c r="D9" t="n">
-        <v>78.49103734667347</v>
+        <v>78.49104491955411</v>
       </c>
       <c r="E9" t="n">
-        <v>79.51610237585788</v>
+        <v>79.51611004763765</v>
       </c>
       <c r="F9" t="n">
         <v>315733</v>
@@ -652,16 +652,16 @@
         <v>43231</v>
       </c>
       <c r="B12" t="n">
-        <v>80.83404541015625</v>
+        <v>80.83405303955078</v>
       </c>
       <c r="C12" t="n">
-        <v>82.59131034334867</v>
+        <v>82.59131813859989</v>
       </c>
       <c r="D12" t="n">
-        <v>80.48259987176485</v>
+        <v>80.48260746798874</v>
       </c>
       <c r="E12" t="n">
-        <v>80.51188637927687</v>
+        <v>80.51189397826494</v>
       </c>
       <c r="F12" t="n">
         <v>586000</v>
@@ -672,16 +672,16 @@
         <v>43234</v>
       </c>
       <c r="B13" t="n">
-        <v>80.01400756835938</v>
+        <v>80.01399230957031</v>
       </c>
       <c r="C13" t="n">
-        <v>81.82984583795763</v>
+        <v>81.82983023288553</v>
       </c>
       <c r="D13" t="n">
-        <v>80.01400756835938</v>
+        <v>80.01399230957031</v>
       </c>
       <c r="E13" t="n">
-        <v>81.68340582623227</v>
+        <v>81.6833902490865</v>
       </c>
       <c r="F13" t="n">
         <v>350433</v>
@@ -692,16 +692,16 @@
         <v>43235</v>
       </c>
       <c r="B14" t="n">
-        <v>84.78789520263672</v>
+        <v>84.78788757324219</v>
       </c>
       <c r="C14" t="n">
-        <v>85.22720775024067</v>
+        <v>85.22720008131586</v>
       </c>
       <c r="D14" t="n">
-        <v>82.00556502190037</v>
+        <v>82.0055576428658</v>
       </c>
       <c r="E14" t="n">
-        <v>82.29843757088707</v>
+        <v>82.29843016549923</v>
       </c>
       <c r="F14" t="n">
         <v>900866</v>
@@ -712,16 +712,16 @@
         <v>43236</v>
       </c>
       <c r="B15" t="n">
-        <v>87.30662536621094</v>
+        <v>87.306640625</v>
       </c>
       <c r="C15" t="n">
-        <v>87.30662536621094</v>
+        <v>87.306640625</v>
       </c>
       <c r="D15" t="n">
-        <v>83.61637672277325</v>
+        <v>83.61639133660867</v>
       </c>
       <c r="E15" t="n">
-        <v>84.7878816276515</v>
+        <v>84.78789644623366</v>
       </c>
       <c r="F15" t="n">
         <v>589600</v>
@@ -732,16 +732,16 @@
         <v>43237</v>
       </c>
       <c r="B16" t="n">
-        <v>88.74173736572266</v>
+        <v>88.74172973632812</v>
       </c>
       <c r="C16" t="n">
-        <v>90.7333019689424</v>
+        <v>90.73329416832706</v>
       </c>
       <c r="D16" t="n">
-        <v>87.86310482779517</v>
+        <v>87.86309727393932</v>
       </c>
       <c r="E16" t="n">
-        <v>87.86310482779517</v>
+        <v>87.86309727393932</v>
       </c>
       <c r="F16" t="n">
         <v>520533</v>
@@ -752,16 +752,16 @@
         <v>43238</v>
       </c>
       <c r="B17" t="n">
-        <v>86.69158935546875</v>
+        <v>86.69159698486328</v>
       </c>
       <c r="C17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74174216703163</v>
       </c>
       <c r="D17" t="n">
-        <v>85.60795128505117</v>
+        <v>85.60795881907887</v>
       </c>
       <c r="E17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74174216703163</v>
       </c>
       <c r="F17" t="n">
         <v>980066</v>
@@ -772,16 +772,16 @@
         <v>43241</v>
       </c>
       <c r="B18" t="n">
-        <v>90.20611572265625</v>
+        <v>90.20612335205078</v>
       </c>
       <c r="C18" t="n">
-        <v>91.05545423914081</v>
+        <v>91.05546194037015</v>
       </c>
       <c r="D18" t="n">
-        <v>84.93432833627266</v>
+        <v>84.93433551979336</v>
       </c>
       <c r="E18" t="n">
-        <v>86.9844658064643</v>
+        <v>86.9844731633802</v>
       </c>
       <c r="F18" t="n">
         <v>633933</v>
@@ -792,16 +792,16 @@
         <v>43242</v>
       </c>
       <c r="B19" t="n">
-        <v>95.91722106933594</v>
+        <v>95.91720581054688</v>
       </c>
       <c r="C19" t="n">
-        <v>96.06366106443481</v>
+        <v>96.06364578234965</v>
       </c>
       <c r="D19" t="n">
-        <v>90.2061208464601</v>
+        <v>90.20610649620939</v>
       </c>
       <c r="E19" t="n">
-        <v>90.2061208464601</v>
+        <v>90.20610649620939</v>
       </c>
       <c r="F19" t="n">
         <v>462766</v>
@@ -832,16 +832,16 @@
         <v>43244</v>
       </c>
       <c r="B21" t="n">
-        <v>89.32747650146484</v>
+        <v>89.32748413085938</v>
       </c>
       <c r="C21" t="n">
-        <v>93.77920409449239</v>
+        <v>93.77921210410572</v>
       </c>
       <c r="D21" t="n">
-        <v>89.09317700926512</v>
+        <v>89.09318461864831</v>
       </c>
       <c r="E21" t="n">
-        <v>93.13487862888151</v>
+        <v>93.13488658346348</v>
       </c>
       <c r="F21" t="n">
         <v>822100</v>
@@ -852,16 +852,16 @@
         <v>43245</v>
       </c>
       <c r="B22" t="n">
-        <v>90.76258087158203</v>
+        <v>90.7625732421875</v>
       </c>
       <c r="C22" t="n">
-        <v>90.879726901322</v>
+        <v>90.87971926208031</v>
       </c>
       <c r="D22" t="n">
-        <v>87.95095698586984</v>
+        <v>87.95094959281705</v>
       </c>
       <c r="E22" t="n">
-        <v>88.77101643528491</v>
+        <v>88.77100897329892</v>
       </c>
       <c r="F22" t="n">
         <v>562433</v>
@@ -872,16 +872,16 @@
         <v>43248</v>
       </c>
       <c r="B23" t="n">
-        <v>86.39871978759766</v>
+        <v>86.39871215820312</v>
       </c>
       <c r="C23" t="n">
-        <v>90.76258852113153</v>
+        <v>90.76258050638783</v>
       </c>
       <c r="D23" t="n">
-        <v>85.02219423616178</v>
+        <v>85.02218672832065</v>
       </c>
       <c r="E23" t="n">
-        <v>90.76258852113153</v>
+        <v>90.76258050638783</v>
       </c>
       <c r="F23" t="n">
         <v>427433</v>
@@ -912,16 +912,16 @@
         <v>43250</v>
       </c>
       <c r="B25" t="n">
-        <v>87.86309814453125</v>
+        <v>87.86309051513672</v>
       </c>
       <c r="C25" t="n">
-        <v>90.05967559814454</v>
+        <v>90.05966777801514</v>
       </c>
       <c r="D25" t="n">
-        <v>85.49079419669903</v>
+        <v>85.49078677329817</v>
       </c>
       <c r="E25" t="n">
-        <v>88.15597066939809</v>
+        <v>88.15596301457262</v>
       </c>
       <c r="F25" t="n">
         <v>493866</v>
@@ -952,16 +952,16 @@
         <v>43255</v>
       </c>
       <c r="B27" t="n">
-        <v>88.74173736572266</v>
+        <v>88.74172973632812</v>
       </c>
       <c r="C27" t="n">
-        <v>90.2061224461859</v>
+        <v>90.20611469089378</v>
       </c>
       <c r="D27" t="n">
-        <v>86.72088625261327</v>
+        <v>86.72087879695741</v>
       </c>
       <c r="E27" t="n">
-        <v>88.44885737033093</v>
+        <v>88.44884976611618</v>
       </c>
       <c r="F27" t="n">
         <v>304000</v>
@@ -972,16 +972,16 @@
         <v>43256</v>
       </c>
       <c r="B28" t="n">
-        <v>85.72509002685547</v>
+        <v>85.72509765625</v>
       </c>
       <c r="C28" t="n">
-        <v>88.15596688567655</v>
+        <v>88.15597473141518</v>
       </c>
       <c r="D28" t="n">
-        <v>84.34857208809417</v>
+        <v>84.34857959498085</v>
       </c>
       <c r="E28" t="n">
-        <v>88.15596688567655</v>
+        <v>88.15597473141518</v>
       </c>
       <c r="F28" t="n">
         <v>239700</v>
@@ -1012,16 +1012,16 @@
         <v>43258</v>
       </c>
       <c r="B30" t="n">
-        <v>80.83404541015625</v>
+        <v>80.83405303955078</v>
       </c>
       <c r="C30" t="n">
-        <v>83.41136979492082</v>
+        <v>83.41137766757205</v>
       </c>
       <c r="D30" t="n">
-        <v>78.63746796778928</v>
+        <v>78.6374753898633</v>
       </c>
       <c r="E30" t="n">
-        <v>83.41136979492082</v>
+        <v>83.41137766757205</v>
       </c>
       <c r="F30" t="n">
         <v>547066</v>
@@ -1032,16 +1032,16 @@
         <v>43259</v>
       </c>
       <c r="B31" t="n">
-        <v>80.98048400878906</v>
+        <v>80.98049926757812</v>
       </c>
       <c r="C31" t="n">
-        <v>83.14777490651888</v>
+        <v>83.14779057368084</v>
       </c>
       <c r="D31" t="n">
-        <v>79.07678657064635</v>
+        <v>79.07680147073026</v>
       </c>
       <c r="E31" t="n">
-        <v>79.75040602487236</v>
+        <v>79.75042105188336</v>
       </c>
       <c r="F31" t="n">
         <v>443000</v>
@@ -1052,16 +1052,16 @@
         <v>43262</v>
       </c>
       <c r="B32" t="n">
-        <v>81.41980743408203</v>
+        <v>81.4197998046875</v>
       </c>
       <c r="C32" t="n">
-        <v>82.73775244353311</v>
+        <v>82.73774469064132</v>
       </c>
       <c r="D32" t="n">
-        <v>78.93034995648213</v>
+        <v>78.93034256036073</v>
       </c>
       <c r="E32" t="n">
-        <v>81.47838045060293</v>
+        <v>81.47837281571985</v>
       </c>
       <c r="F32" t="n">
         <v>202266</v>
@@ -1072,16 +1072,16 @@
         <v>43263</v>
       </c>
       <c r="B33" t="n">
-        <v>82.23986053466797</v>
+        <v>82.2398681640625</v>
       </c>
       <c r="C33" t="n">
-        <v>83.38207906125773</v>
+        <v>83.38208679661591</v>
       </c>
       <c r="D33" t="n">
-        <v>80.07256951606338</v>
+        <v>80.07257694439825</v>
       </c>
       <c r="E33" t="n">
-        <v>81.419808499654</v>
+        <v>81.41981605297228</v>
       </c>
       <c r="F33" t="n">
         <v>203566</v>
@@ -1112,16 +1112,16 @@
         <v>43265</v>
       </c>
       <c r="B35" t="n">
-        <v>79.13536834716797</v>
+        <v>79.13536071777344</v>
       </c>
       <c r="C35" t="n">
-        <v>80.21901391602279</v>
+        <v>80.21900618215462</v>
       </c>
       <c r="D35" t="n">
-        <v>77.90528277879942</v>
+        <v>77.90527526799671</v>
       </c>
       <c r="E35" t="n">
-        <v>78.19816277782689</v>
+        <v>78.19815523878781</v>
       </c>
       <c r="F35" t="n">
         <v>536566</v>
@@ -1132,16 +1132,16 @@
         <v>43266</v>
       </c>
       <c r="B36" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C36" t="n">
-        <v>79.22322984533973</v>
+        <v>79.22323748886292</v>
       </c>
       <c r="D36" t="n">
-        <v>75.12294738386028</v>
+        <v>75.12295463178479</v>
       </c>
       <c r="E36" t="n">
-        <v>79.13536287241121</v>
+        <v>79.13537050745691</v>
       </c>
       <c r="F36" t="n">
         <v>389566</v>
@@ -1152,16 +1152,16 @@
         <v>43269</v>
       </c>
       <c r="B37" t="n">
-        <v>77.26095581054688</v>
+        <v>77.26094818115234</v>
       </c>
       <c r="C37" t="n">
-        <v>79.07679389586734</v>
+        <v>79.07678608716174</v>
       </c>
       <c r="D37" t="n">
-        <v>76.7337762907847</v>
+        <v>76.7337687134483</v>
       </c>
       <c r="E37" t="n">
-        <v>79.07679389586734</v>
+        <v>79.07678608716174</v>
       </c>
       <c r="F37" t="n">
         <v>465333</v>
@@ -1172,16 +1172,16 @@
         <v>43270</v>
       </c>
       <c r="B38" t="n">
-        <v>81.56623840332031</v>
+        <v>81.56624603271484</v>
       </c>
       <c r="C38" t="n">
-        <v>83.14777685312824</v>
+        <v>83.14778463045384</v>
       </c>
       <c r="D38" t="n">
-        <v>77.02665095250988</v>
+        <v>77.02665815728874</v>
       </c>
       <c r="E38" t="n">
-        <v>77.84670296098628</v>
+        <v>77.84671024246967</v>
       </c>
       <c r="F38" t="n">
         <v>159600</v>
@@ -1192,16 +1192,16 @@
         <v>43271</v>
       </c>
       <c r="B39" t="n">
-        <v>84.34858703613281</v>
+        <v>84.34857177734375</v>
       </c>
       <c r="C39" t="n">
-        <v>85.52009218942361</v>
+        <v>85.52007671870746</v>
       </c>
       <c r="D39" t="n">
-        <v>81.71268926885634</v>
+        <v>81.71267448690524</v>
       </c>
       <c r="E39" t="n">
-        <v>82.03485579289816</v>
+        <v>82.03484095266663</v>
       </c>
       <c r="F39" t="n">
         <v>141600</v>
@@ -1252,16 +1252,16 @@
         <v>43276</v>
       </c>
       <c r="B42" t="n">
-        <v>86.39871978759766</v>
+        <v>86.39871215820312</v>
       </c>
       <c r="C42" t="n">
-        <v>86.39871978759766</v>
+        <v>86.39871215820312</v>
       </c>
       <c r="D42" t="n">
-        <v>84.34858216364319</v>
+        <v>84.348574715285</v>
       </c>
       <c r="E42" t="n">
-        <v>85.87154026459547</v>
+        <v>85.87153268175327</v>
       </c>
       <c r="F42" t="n">
         <v>909166</v>
@@ -1292,16 +1292,16 @@
         <v>43278</v>
       </c>
       <c r="B44" t="n">
-        <v>87.86309814453125</v>
+        <v>87.86309051513672</v>
       </c>
       <c r="C44" t="n">
-        <v>88.59529062906901</v>
+        <v>88.59528293609618</v>
       </c>
       <c r="D44" t="n">
-        <v>85.25649468715613</v>
+        <v>85.25648728410015</v>
       </c>
       <c r="E44" t="n">
-        <v>86.98446567343652</v>
+        <v>86.98445812033606</v>
       </c>
       <c r="F44" t="n">
         <v>117966</v>
@@ -1312,16 +1312,16 @@
         <v>43279</v>
       </c>
       <c r="B45" t="n">
-        <v>88.68314361572266</v>
+        <v>88.68315887451172</v>
       </c>
       <c r="C45" t="n">
-        <v>88.68314361572266</v>
+        <v>88.68315887451172</v>
       </c>
       <c r="D45" t="n">
-        <v>85.37363442539693</v>
+        <v>85.37364911475306</v>
       </c>
       <c r="E45" t="n">
-        <v>87.86309166864037</v>
+        <v>87.8631067863316</v>
       </c>
       <c r="F45" t="n">
         <v>922066</v>
@@ -1352,16 +1352,16 @@
         <v>43283</v>
       </c>
       <c r="B47" t="n">
-        <v>86.10585021972656</v>
+        <v>86.10582733154297</v>
       </c>
       <c r="C47" t="n">
-        <v>86.95519635101843</v>
+        <v>86.9551732370663</v>
       </c>
       <c r="D47" t="n">
-        <v>85.87155066387828</v>
+        <v>85.8715278379749</v>
       </c>
       <c r="E47" t="n">
-        <v>86.04727719282664</v>
+        <v>86.0472543202126</v>
       </c>
       <c r="F47" t="n">
         <v>88033</v>
@@ -1372,16 +1372,16 @@
         <v>43284</v>
       </c>
       <c r="B48" t="n">
-        <v>85.52007293701172</v>
+        <v>85.52008819580078</v>
       </c>
       <c r="C48" t="n">
-        <v>87.21875726134735</v>
+        <v>87.21877282322158</v>
       </c>
       <c r="D48" t="n">
-        <v>83.9385346326842</v>
+        <v>83.93854960928969</v>
       </c>
       <c r="E48" t="n">
-        <v>86.72087177981997</v>
+        <v>86.72088725285975</v>
       </c>
       <c r="F48" t="n">
         <v>142500</v>
@@ -1392,16 +1392,16 @@
         <v>43285</v>
       </c>
       <c r="B49" t="n">
-        <v>85.78367614746094</v>
+        <v>85.78366851806641</v>
       </c>
       <c r="C49" t="n">
-        <v>87.07233465202611</v>
+        <v>87.07232690802138</v>
       </c>
       <c r="D49" t="n">
-        <v>84.14356464635551</v>
+        <v>84.14355716282856</v>
       </c>
       <c r="E49" t="n">
-        <v>86.66230119056429</v>
+        <v>86.66229348302694</v>
       </c>
       <c r="F49" t="n">
         <v>320933</v>
@@ -1412,16 +1412,16 @@
         <v>43286</v>
       </c>
       <c r="B50" t="n">
-        <v>85.52007293701172</v>
+        <v>85.52008819580078</v>
       </c>
       <c r="C50" t="n">
-        <v>86.31083836505225</v>
+        <v>86.31085376493245</v>
       </c>
       <c r="D50" t="n">
-        <v>84.28998758920142</v>
+        <v>84.29000262851439</v>
       </c>
       <c r="E50" t="n">
-        <v>85.78366637852285</v>
+        <v>85.78368168434318</v>
       </c>
       <c r="F50" t="n">
         <v>391100</v>
@@ -1432,16 +1432,16 @@
         <v>43287</v>
       </c>
       <c r="B51" t="n">
-        <v>83.61637878417969</v>
+        <v>83.61639404296875</v>
       </c>
       <c r="C51" t="n">
-        <v>85.57864917581456</v>
+        <v>85.57866479268981</v>
       </c>
       <c r="D51" t="n">
-        <v>83.61637878417969</v>
+        <v>83.61639404296875</v>
       </c>
       <c r="E51" t="n">
-        <v>85.52007616360061</v>
+        <v>85.52009176978711</v>
       </c>
       <c r="F51" t="n">
         <v>769100</v>
@@ -1452,16 +1452,16 @@
         <v>43291</v>
       </c>
       <c r="B52" t="n">
-        <v>84.23141479492188</v>
+        <v>84.23142242431641</v>
       </c>
       <c r="C52" t="n">
-        <v>86.07653909723963</v>
+        <v>86.07654689375923</v>
       </c>
       <c r="D52" t="n">
-        <v>83.17705592266988</v>
+        <v>83.17706345656418</v>
       </c>
       <c r="E52" t="n">
-        <v>84.14355527969077</v>
+        <v>84.14356290112728</v>
       </c>
       <c r="F52" t="n">
         <v>281266</v>
@@ -1472,16 +1472,16 @@
         <v>43292</v>
       </c>
       <c r="B53" t="n">
-        <v>84.08499145507812</v>
+        <v>84.08497619628906</v>
       </c>
       <c r="C53" t="n">
-        <v>86.25228263847217</v>
+        <v>86.25226698638772</v>
       </c>
       <c r="D53" t="n">
-        <v>82.64989283643895</v>
+        <v>82.64987783807528</v>
       </c>
       <c r="E53" t="n">
-        <v>83.79211889812494</v>
+        <v>83.79210369248307</v>
       </c>
       <c r="F53" t="n">
         <v>271833</v>
@@ -1492,16 +1492,16 @@
         <v>43293</v>
       </c>
       <c r="B54" t="n">
-        <v>87.07234191894531</v>
+        <v>87.07231903076172</v>
       </c>
       <c r="C54" t="n">
-        <v>87.13091494050801</v>
+        <v>87.13089203692768</v>
       </c>
       <c r="D54" t="n">
-        <v>82.35702002870303</v>
+        <v>82.35699838000778</v>
       </c>
       <c r="E54" t="n">
-        <v>83.90926468609763</v>
+        <v>83.90924262937314</v>
       </c>
       <c r="F54" t="n">
         <v>235333</v>
@@ -1512,16 +1512,16 @@
         <v>43294</v>
       </c>
       <c r="B55" t="n">
-        <v>84.40715026855469</v>
+        <v>84.40715789794922</v>
       </c>
       <c r="C55" t="n">
-        <v>87.57021977413956</v>
+        <v>87.57022768943764</v>
       </c>
       <c r="D55" t="n">
-        <v>83.96783774909052</v>
+        <v>83.96784533877647</v>
       </c>
       <c r="E55" t="n">
-        <v>87.10162074647741</v>
+        <v>87.10162861941977</v>
       </c>
       <c r="F55" t="n">
         <v>222900</v>
@@ -1552,16 +1552,16 @@
         <v>43298</v>
       </c>
       <c r="B57" t="n">
-        <v>83.08921051025391</v>
+        <v>83.08920288085938</v>
       </c>
       <c r="C57" t="n">
-        <v>84.58288210867671</v>
+        <v>84.58287434213068</v>
       </c>
       <c r="D57" t="n">
-        <v>82.35701796606644</v>
+        <v>82.35701040390309</v>
       </c>
       <c r="E57" t="n">
-        <v>84.11427560316773</v>
+        <v>84.11426787964996</v>
       </c>
       <c r="F57" t="n">
         <v>152666</v>
@@ -1592,16 +1592,16 @@
         <v>43300</v>
       </c>
       <c r="B59" t="n">
-        <v>85.19792938232422</v>
+        <v>85.19791412353516</v>
       </c>
       <c r="C59" t="n">
-        <v>86.54516856045777</v>
+        <v>86.5451530603807</v>
       </c>
       <c r="D59" t="n">
-        <v>83.61639810120876</v>
+        <v>83.61638312566897</v>
       </c>
       <c r="E59" t="n">
-        <v>85.52009592042123</v>
+        <v>85.52008060393275</v>
       </c>
       <c r="F59" t="n">
         <v>169366</v>
@@ -1612,16 +1612,16 @@
         <v>43301</v>
       </c>
       <c r="B60" t="n">
-        <v>87.86309814453125</v>
+        <v>87.86309051513672</v>
       </c>
       <c r="C60" t="n">
-        <v>88.77101712328796</v>
+        <v>88.77100941505633</v>
       </c>
       <c r="D60" t="n">
-        <v>85.54936721202297</v>
+        <v>85.54935978353605</v>
       </c>
       <c r="E60" t="n">
-        <v>86.39871317545573</v>
+        <v>86.39870567321778</v>
       </c>
       <c r="F60" t="n">
         <v>356866</v>
@@ -1632,16 +1632,16 @@
         <v>43304</v>
       </c>
       <c r="B61" t="n">
-        <v>87.65808868408203</v>
+        <v>87.65809631347656</v>
       </c>
       <c r="C61" t="n">
-        <v>89.26891370479268</v>
+        <v>89.2689214743867</v>
       </c>
       <c r="D61" t="n">
-        <v>86.72088315979977</v>
+        <v>86.72089070762384</v>
       </c>
       <c r="E61" t="n">
-        <v>89.00532022869139</v>
+        <v>89.00532797534333</v>
       </c>
       <c r="F61" t="n">
         <v>145300</v>
@@ -1652,16 +1652,16 @@
         <v>43305</v>
       </c>
       <c r="B62" t="n">
-        <v>88.15596771240234</v>
+        <v>88.15597534179688</v>
       </c>
       <c r="C62" t="n">
-        <v>88.71244113230262</v>
+        <v>88.71244880985672</v>
       </c>
       <c r="D62" t="n">
-        <v>87.10161623070165</v>
+        <v>87.1016237688481</v>
       </c>
       <c r="E62" t="n">
-        <v>88.18526166732883</v>
+        <v>88.18526929925858</v>
       </c>
       <c r="F62" t="n">
         <v>140566</v>
@@ -1672,16 +1672,16 @@
         <v>43306</v>
       </c>
       <c r="B63" t="n">
-        <v>83.99711608886719</v>
+        <v>83.99713134765625</v>
       </c>
       <c r="C63" t="n">
-        <v>89.91322851344979</v>
+        <v>89.9132448469509</v>
       </c>
       <c r="D63" t="n">
-        <v>83.99711608886719</v>
+        <v>83.99713134765625</v>
       </c>
       <c r="E63" t="n">
-        <v>88.77101011532184</v>
+        <v>88.77102624132928</v>
       </c>
       <c r="F63" t="n">
         <v>653300</v>
@@ -1692,16 +1692,16 @@
         <v>43307</v>
       </c>
       <c r="B64" t="n">
-        <v>80.57046508789062</v>
+        <v>80.57045745849609</v>
       </c>
       <c r="C64" t="n">
-        <v>84.84646679649717</v>
+        <v>84.84645876219862</v>
       </c>
       <c r="D64" t="n">
-        <v>79.9554260419345</v>
+        <v>79.95541847077936</v>
       </c>
       <c r="E64" t="n">
-        <v>84.14356822179629</v>
+        <v>84.14356025405675</v>
       </c>
       <c r="F64" t="n">
         <v>454233</v>
@@ -1732,16 +1732,16 @@
         <v>43311</v>
       </c>
       <c r="B66" t="n">
-        <v>80.39473724365234</v>
+        <v>80.39472198486328</v>
       </c>
       <c r="C66" t="n">
-        <v>82.59131480467153</v>
+        <v>82.59129912897563</v>
       </c>
       <c r="D66" t="n">
-        <v>79.80898471703006</v>
+        <v>79.80896956941586</v>
       </c>
       <c r="E66" t="n">
-        <v>82.53274178648354</v>
+        <v>82.53272612190472</v>
       </c>
       <c r="F66" t="n">
         <v>306800</v>
@@ -1752,16 +1752,16 @@
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>82.47415924072266</v>
+        <v>82.47415161132812</v>
       </c>
       <c r="C67" t="n">
-        <v>82.56202621403682</v>
+        <v>82.56201857651402</v>
       </c>
       <c r="D67" t="n">
-        <v>79.3696627348224</v>
+        <v>79.36965539261392</v>
       </c>
       <c r="E67" t="n">
-        <v>81.24408120030263</v>
+        <v>81.24407368469829</v>
       </c>
       <c r="F67" t="n">
         <v>430700</v>
@@ -1772,16 +1772,16 @@
         <v>43313</v>
       </c>
       <c r="B68" t="n">
-        <v>84.02640533447266</v>
+        <v>84.02639770507812</v>
       </c>
       <c r="C68" t="n">
-        <v>84.02640533447266</v>
+        <v>84.02639770507812</v>
       </c>
       <c r="D68" t="n">
-        <v>81.41980199786791</v>
+        <v>81.41979460514666</v>
       </c>
       <c r="E68" t="n">
-        <v>81.44908850417296</v>
+        <v>81.44908110879257</v>
       </c>
       <c r="F68" t="n">
         <v>89600</v>
@@ -1812,16 +1812,16 @@
         <v>43315</v>
       </c>
       <c r="B70" t="n">
-        <v>83.90927124023438</v>
+        <v>83.90924072265625</v>
       </c>
       <c r="C70" t="n">
-        <v>84.7586173604752</v>
+        <v>84.75858653399216</v>
       </c>
       <c r="D70" t="n">
-        <v>83.52853167384157</v>
+        <v>83.52850129473741</v>
       </c>
       <c r="E70" t="n">
-        <v>84.7586173604752</v>
+        <v>84.75858653399216</v>
       </c>
       <c r="F70" t="n">
         <v>171233</v>
@@ -1852,16 +1852,16 @@
         <v>43319</v>
       </c>
       <c r="B72" t="n">
-        <v>79.13536834716797</v>
+        <v>79.13536071777344</v>
       </c>
       <c r="C72" t="n">
-        <v>81.41981297413815</v>
+        <v>81.41980512450165</v>
       </c>
       <c r="D72" t="n">
-        <v>79.13536834716797</v>
+        <v>79.13536071777344</v>
       </c>
       <c r="E72" t="n">
-        <v>81.27337297462441</v>
+        <v>81.2733651391061</v>
       </c>
       <c r="F72" t="n">
         <v>212866</v>
@@ -1892,16 +1892,16 @@
         <v>43321</v>
       </c>
       <c r="B74" t="n">
-        <v>78.95964050292969</v>
+        <v>78.95962524414062</v>
       </c>
       <c r="C74" t="n">
-        <v>79.13536700972674</v>
+        <v>79.13535171697887</v>
       </c>
       <c r="D74" t="n">
-        <v>76.85092986961286</v>
+        <v>76.85091501832781</v>
       </c>
       <c r="E74" t="n">
-        <v>78.19816145622507</v>
+        <v>78.19814634459027</v>
       </c>
       <c r="F74" t="n">
         <v>546266</v>
@@ -1912,16 +1912,16 @@
         <v>43322</v>
       </c>
       <c r="B75" t="n">
-        <v>78.87176513671875</v>
+        <v>78.87178039550781</v>
       </c>
       <c r="C75" t="n">
-        <v>80.36543642045031</v>
+        <v>80.36545196820988</v>
       </c>
       <c r="D75" t="n">
-        <v>78.16885925066951</v>
+        <v>78.16887437347211</v>
       </c>
       <c r="E75" t="n">
-        <v>79.13535111986414</v>
+        <v>79.13536642964741</v>
       </c>
       <c r="F75" t="n">
         <v>176700</v>
@@ -1932,16 +1932,16 @@
         <v>43325</v>
       </c>
       <c r="B76" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C76" t="n">
-        <v>80.10185488514145</v>
+        <v>80.10186261343512</v>
       </c>
       <c r="D76" t="n">
-        <v>77.7588448480072</v>
+        <v>77.75885235024531</v>
       </c>
       <c r="E76" t="n">
-        <v>78.93034986657432</v>
+        <v>78.9303574818402</v>
       </c>
       <c r="F76" t="n">
         <v>160400</v>
@@ -2012,16 +2012,16 @@
         <v>43329</v>
       </c>
       <c r="B80" t="n">
-        <v>71.46197509765625</v>
+        <v>71.46198272705078</v>
       </c>
       <c r="C80" t="n">
-        <v>72.95564639852894</v>
+        <v>72.95565418739019</v>
       </c>
       <c r="D80" t="n">
-        <v>70.29047023962762</v>
+        <v>70.29047774395042</v>
       </c>
       <c r="E80" t="n">
-        <v>72.95564639852894</v>
+        <v>72.95565418739019</v>
       </c>
       <c r="F80" t="n">
         <v>2138466</v>
@@ -2032,16 +2032,16 @@
         <v>43332</v>
       </c>
       <c r="B81" t="n">
-        <v>72.34060668945312</v>
+        <v>72.34061431884766</v>
       </c>
       <c r="C81" t="n">
-        <v>73.0142260721305</v>
+        <v>73.01423377256823</v>
       </c>
       <c r="D81" t="n">
-        <v>71.75485426672097</v>
+        <v>71.75486183433918</v>
       </c>
       <c r="E81" t="n">
-        <v>71.95986724226492</v>
+        <v>71.95987483150479</v>
       </c>
       <c r="F81" t="n">
         <v>425766</v>
@@ -2052,16 +2052,16 @@
         <v>43333</v>
       </c>
       <c r="B82" t="n">
-        <v>71.60842895507812</v>
+        <v>71.60842132568359</v>
       </c>
       <c r="C82" t="n">
-        <v>72.5749210228105</v>
+        <v>72.57491329044277</v>
       </c>
       <c r="D82" t="n">
-        <v>70.31977038201907</v>
+        <v>70.31976288992242</v>
       </c>
       <c r="E82" t="n">
-        <v>71.63771546497189</v>
+        <v>71.63770783245707</v>
       </c>
       <c r="F82" t="n">
         <v>1384333</v>
@@ -2112,16 +2112,16 @@
         <v>43336</v>
       </c>
       <c r="B85" t="n">
-        <v>75.29866790771484</v>
+        <v>75.29867553710938</v>
       </c>
       <c r="C85" t="n">
-        <v>75.5622613573412</v>
+        <v>75.56226901344348</v>
       </c>
       <c r="D85" t="n">
-        <v>73.21924405784095</v>
+        <v>73.21925147654457</v>
       </c>
       <c r="E85" t="n">
-        <v>74.09787647618438</v>
+        <v>74.0978839839126</v>
       </c>
       <c r="F85" t="n">
         <v>164200</v>
@@ -2132,16 +2132,16 @@
         <v>43339</v>
       </c>
       <c r="B86" t="n">
-        <v>76.03086853027344</v>
+        <v>76.03086090087891</v>
       </c>
       <c r="C86" t="n">
-        <v>76.44089455354266</v>
+        <v>76.44088688300364</v>
       </c>
       <c r="D86" t="n">
-        <v>73.65856446957658</v>
+        <v>73.6585570782333</v>
       </c>
       <c r="E86" t="n">
-        <v>75.29867601090092</v>
+        <v>75.29866845497898</v>
       </c>
       <c r="F86" t="n">
         <v>318500</v>
@@ -2152,16 +2152,16 @@
         <v>43340</v>
       </c>
       <c r="B87" t="n">
-        <v>75.24009704589844</v>
+        <v>75.2401123046875</v>
       </c>
       <c r="C87" t="n">
-        <v>76.14801599608937</v>
+        <v>76.14803143900558</v>
       </c>
       <c r="D87" t="n">
-        <v>73.89286559810573</v>
+        <v>73.89288058367451</v>
       </c>
       <c r="E87" t="n">
-        <v>75.91371649391823</v>
+        <v>75.91373188931819</v>
       </c>
       <c r="F87" t="n">
         <v>298400</v>
@@ -2172,16 +2172,16 @@
         <v>43341</v>
       </c>
       <c r="B88" t="n">
-        <v>74.42002868652344</v>
+        <v>74.4200439453125</v>
       </c>
       <c r="C88" t="n">
-        <v>76.14800685934951</v>
+        <v>76.14802247243639</v>
       </c>
       <c r="D88" t="n">
-        <v>73.45353683881748</v>
+        <v>73.45355189944088</v>
       </c>
       <c r="E88" t="n">
-        <v>75.67940046298681</v>
+        <v>75.6794159799925</v>
       </c>
       <c r="F88" t="n">
         <v>162200</v>
@@ -2192,16 +2192,16 @@
         <v>43342</v>
       </c>
       <c r="B89" t="n">
-        <v>75.85513305664062</v>
+        <v>75.85514831542969</v>
       </c>
       <c r="C89" t="n">
-        <v>75.85513305664062</v>
+        <v>75.85514831542969</v>
       </c>
       <c r="D89" t="n">
-        <v>73.39496975973056</v>
+        <v>73.39498452364062</v>
       </c>
       <c r="E89" t="n">
-        <v>74.18573520369333</v>
+        <v>74.18575012667137</v>
       </c>
       <c r="F89" t="n">
         <v>206466</v>
@@ -2212,16 +2212,16 @@
         <v>43343</v>
       </c>
       <c r="B90" t="n">
-        <v>75.82587432861328</v>
+        <v>75.82586669921875</v>
       </c>
       <c r="C90" t="n">
-        <v>76.49949399697869</v>
+        <v>76.49948629980636</v>
       </c>
       <c r="D90" t="n">
-        <v>74.91795508143572</v>
+        <v>74.91794754339358</v>
       </c>
       <c r="E90" t="n">
-        <v>76.11875438831545</v>
+        <v>76.11874672945213</v>
       </c>
       <c r="F90" t="n">
         <v>295200</v>
@@ -2232,16 +2232,16 @@
         <v>43346</v>
       </c>
       <c r="B91" t="n">
-        <v>74.65433502197266</v>
+        <v>74.65434265136719</v>
       </c>
       <c r="C91" t="n">
-        <v>76.06013930351777</v>
+        <v>76.06014707658026</v>
       </c>
       <c r="D91" t="n">
-        <v>73.98071566007346</v>
+        <v>73.9807232206266</v>
       </c>
       <c r="E91" t="n">
-        <v>75.7672668253086</v>
+        <v>75.76727456844061</v>
       </c>
       <c r="F91" t="n">
         <v>159200</v>
@@ -2252,16 +2252,16 @@
         <v>43347</v>
       </c>
       <c r="B92" t="n">
-        <v>73.04351806640625</v>
+        <v>73.04353332519531</v>
       </c>
       <c r="C92" t="n">
-        <v>74.42003599088163</v>
+        <v>74.42005153722525</v>
       </c>
       <c r="D92" t="n">
-        <v>71.87201313288479</v>
+        <v>71.8720281469465</v>
       </c>
       <c r="E92" t="n">
-        <v>74.3907494847806</v>
+        <v>74.39076502500627</v>
       </c>
       <c r="F92" t="n">
         <v>196200</v>
@@ -2272,16 +2272,16 @@
         <v>43348</v>
       </c>
       <c r="B93" t="n">
-        <v>73.24854278564453</v>
+        <v>73.24855041503906</v>
       </c>
       <c r="C93" t="n">
-        <v>75.65013349767</v>
+        <v>75.65014137720853</v>
       </c>
       <c r="D93" t="n">
-        <v>72.80923022729456</v>
+        <v>72.80923781093135</v>
       </c>
       <c r="E93" t="n">
-        <v>72.89708975966539</v>
+        <v>72.89709735245341</v>
       </c>
       <c r="F93" t="n">
         <v>95400</v>
@@ -2292,16 +2292,16 @@
         <v>43349</v>
       </c>
       <c r="B94" t="n">
-        <v>74.21503448486328</v>
+        <v>74.21502685546875</v>
       </c>
       <c r="C94" t="n">
-        <v>76.52876565210674</v>
+        <v>76.52875778485787</v>
       </c>
       <c r="D94" t="n">
-        <v>71.4619907616264</v>
+        <v>71.46198341524806</v>
       </c>
       <c r="E94" t="n">
-        <v>74.15646146359693</v>
+        <v>74.15645384022376</v>
       </c>
       <c r="F94" t="n">
         <v>139100</v>
@@ -2312,16 +2312,16 @@
         <v>43353</v>
       </c>
       <c r="B95" t="n">
-        <v>75.50370025634766</v>
+        <v>75.50368499755859</v>
       </c>
       <c r="C95" t="n">
-        <v>76.73378595742098</v>
+        <v>76.7337704500399</v>
       </c>
       <c r="D95" t="n">
-        <v>74.42005457058639</v>
+        <v>74.42003953079482</v>
       </c>
       <c r="E95" t="n">
-        <v>75.65014027165972</v>
+        <v>75.65012498327611</v>
       </c>
       <c r="F95" t="n">
         <v>157400</v>
@@ -2372,16 +2372,16 @@
         <v>43356</v>
       </c>
       <c r="B98" t="n">
-        <v>71.60842895507812</v>
+        <v>71.60842132568359</v>
       </c>
       <c r="C98" t="n">
-        <v>73.86357959586955</v>
+        <v>73.86357172620396</v>
       </c>
       <c r="D98" t="n">
-        <v>70.43692386984178</v>
+        <v>70.4369163652632</v>
       </c>
       <c r="E98" t="n">
-        <v>73.77572006618828</v>
+        <v>73.77571220588352</v>
       </c>
       <c r="F98" t="n">
         <v>250366</v>
@@ -2412,16 +2412,16 @@
         <v>43360</v>
       </c>
       <c r="B100" t="n">
-        <v>73.48284912109375</v>
+        <v>73.48283386230469</v>
       </c>
       <c r="C100" t="n">
-        <v>74.06860918410334</v>
+        <v>74.0685938036806</v>
       </c>
       <c r="D100" t="n">
-        <v>69.79259945502608</v>
+        <v>69.79258496252115</v>
       </c>
       <c r="E100" t="n">
-        <v>70.02689901128075</v>
+        <v>70.02688447012328</v>
       </c>
       <c r="F100" t="n">
         <v>114333</v>
@@ -2452,16 +2452,16 @@
         <v>43362</v>
       </c>
       <c r="B102" t="n">
-        <v>68.76751708984375</v>
+        <v>68.76752471923828</v>
       </c>
       <c r="C102" t="n">
-        <v>74.68362968540555</v>
+        <v>74.68363797116167</v>
       </c>
       <c r="D102" t="n">
-        <v>68.76751708984375</v>
+        <v>68.76752471923828</v>
       </c>
       <c r="E102" t="n">
-        <v>73.57069776046316</v>
+        <v>73.57070592274535</v>
       </c>
       <c r="F102" t="n">
         <v>510266</v>
@@ -2492,16 +2492,16 @@
         <v>43364</v>
       </c>
       <c r="B104" t="n">
-        <v>69.35327911376953</v>
+        <v>69.353271484375</v>
       </c>
       <c r="C104" t="n">
-        <v>71.16911723059167</v>
+        <v>71.16910940144096</v>
       </c>
       <c r="D104" t="n">
-        <v>67.88889401621928</v>
+        <v>67.88888654791837</v>
       </c>
       <c r="E104" t="n">
-        <v>67.94746703668201</v>
+        <v>67.94745956193762</v>
       </c>
       <c r="F104" t="n">
         <v>293166</v>
@@ -2512,16 +2512,16 @@
         <v>43367</v>
       </c>
       <c r="B105" t="n">
-        <v>65.4580078125</v>
+        <v>65.45802307128906</v>
       </c>
       <c r="C105" t="n">
-        <v>69.49971743662823</v>
+        <v>69.49973363757238</v>
       </c>
       <c r="D105" t="n">
-        <v>65.37014828392535</v>
+        <v>65.37016352223365</v>
       </c>
       <c r="E105" t="n">
-        <v>69.35327744075623</v>
+        <v>69.35329360756403</v>
       </c>
       <c r="F105" t="n">
         <v>831466</v>
@@ -2532,16 +2532,16 @@
         <v>43368</v>
       </c>
       <c r="B106" t="n">
-        <v>63.90576171875</v>
+        <v>63.90575408935547</v>
       </c>
       <c r="C106" t="n">
-        <v>67.21527128568442</v>
+        <v>67.21526326118382</v>
       </c>
       <c r="D106" t="n">
-        <v>61.62132092644037</v>
+        <v>61.62131356977399</v>
       </c>
       <c r="E106" t="n">
-        <v>64.46222773137842</v>
+        <v>64.46222003555015</v>
       </c>
       <c r="F106" t="n">
         <v>629433</v>
@@ -2552,16 +2552,16 @@
         <v>43369</v>
       </c>
       <c r="B107" t="n">
-        <v>65.01868438720703</v>
+        <v>65.01869201660156</v>
       </c>
       <c r="C107" t="n">
-        <v>66.48306920425335</v>
+        <v>66.48307700548109</v>
       </c>
       <c r="D107" t="n">
-        <v>63.14427360896688</v>
+        <v>63.1442810184151</v>
       </c>
       <c r="E107" t="n">
-        <v>63.93503902673306</v>
+        <v>63.93504652897094</v>
       </c>
       <c r="F107" t="n">
         <v>469400</v>
@@ -2572,16 +2572,16 @@
         <v>43370</v>
       </c>
       <c r="B108" t="n">
-        <v>68.59178924560547</v>
+        <v>68.591796875</v>
       </c>
       <c r="C108" t="n">
-        <v>69.85115367658149</v>
+        <v>69.85116144605384</v>
       </c>
       <c r="D108" t="n">
-        <v>65.07725960672998</v>
+        <v>65.07726684520698</v>
       </c>
       <c r="E108" t="n">
-        <v>65.48729303009652</v>
+        <v>65.48730031418111</v>
       </c>
       <c r="F108" t="n">
         <v>605400</v>
@@ -2592,16 +2592,16 @@
         <v>43371</v>
       </c>
       <c r="B109" t="n">
-        <v>70.29048919677734</v>
+        <v>70.29046630859375</v>
       </c>
       <c r="C109" t="n">
-        <v>71.34484832230859</v>
+        <v>71.34482509080165</v>
       </c>
       <c r="D109" t="n">
-        <v>67.33243230146601</v>
+        <v>67.3324103764931</v>
       </c>
       <c r="E109" t="n">
-        <v>68.5918044600314</v>
+        <v>68.59178212497824</v>
       </c>
       <c r="F109" t="n">
         <v>612400</v>
@@ -2612,16 +2612,16 @@
         <v>43374</v>
       </c>
       <c r="B110" t="n">
-        <v>69.11896514892578</v>
+        <v>69.11897277832031</v>
       </c>
       <c r="C110" t="n">
-        <v>70.20261060743866</v>
+        <v>70.20261835644665</v>
       </c>
       <c r="D110" t="n">
-        <v>68.41606662967828</v>
+        <v>68.41607418148644</v>
       </c>
       <c r="E110" t="n">
-        <v>70.20261060743866</v>
+        <v>70.20261835644665</v>
       </c>
       <c r="F110" t="n">
         <v>385466</v>
@@ -2632,16 +2632,16 @@
         <v>43375</v>
       </c>
       <c r="B111" t="n">
-        <v>69.14826965332031</v>
+        <v>69.14826202392578</v>
       </c>
       <c r="C111" t="n">
-        <v>70.26120178888704</v>
+        <v>70.26119403669841</v>
       </c>
       <c r="D111" t="n">
-        <v>67.97675704602766</v>
+        <v>67.97674954589061</v>
       </c>
       <c r="E111" t="n">
-        <v>69.20684267679809</v>
+        <v>69.20683504094097</v>
       </c>
       <c r="F111" t="n">
         <v>391400</v>
@@ -2652,16 +2652,16 @@
         <v>43376</v>
       </c>
       <c r="B112" t="n">
-        <v>70.43692779541016</v>
+        <v>70.43691253662109</v>
       </c>
       <c r="C112" t="n">
-        <v>73.59999766042965</v>
+        <v>73.59998171642307</v>
       </c>
       <c r="D112" t="n">
-        <v>69.08968867923201</v>
+        <v>69.08967371229606</v>
       </c>
       <c r="E112" t="n">
-        <v>70.58336035303988</v>
+        <v>70.58334506252905</v>
       </c>
       <c r="F112" t="n">
         <v>463466</v>
@@ -2672,16 +2672,16 @@
         <v>43377</v>
       </c>
       <c r="B113" t="n">
-        <v>70.29048919677734</v>
+        <v>70.29046630859375</v>
       </c>
       <c r="C113" t="n">
-        <v>72.1356139423329</v>
+        <v>72.13559045333467</v>
       </c>
       <c r="D113" t="n">
-        <v>67.71317185542203</v>
+        <v>67.71314980647165</v>
       </c>
       <c r="E113" t="n">
-        <v>70.55407525403604</v>
+        <v>70.55405228002282</v>
       </c>
       <c r="F113" t="n">
         <v>201700</v>
@@ -2692,16 +2692,16 @@
         <v>43378</v>
       </c>
       <c r="B114" t="n">
-        <v>68.26963806152344</v>
+        <v>68.26962280273438</v>
       </c>
       <c r="C114" t="n">
-        <v>71.60843451720841</v>
+        <v>71.60841851217266</v>
       </c>
       <c r="D114" t="n">
-        <v>67.36171894305666</v>
+        <v>67.36170388719449</v>
       </c>
       <c r="E114" t="n">
-        <v>71.60843451720841</v>
+        <v>71.60841851217266</v>
       </c>
       <c r="F114" t="n">
         <v>364566</v>
@@ -2712,16 +2712,16 @@
         <v>43381</v>
       </c>
       <c r="B115" t="n">
-        <v>69.55828857421875</v>
+        <v>69.55829620361328</v>
       </c>
       <c r="C115" t="n">
-        <v>70.90552011365561</v>
+        <v>70.90552789081917</v>
       </c>
       <c r="D115" t="n">
-        <v>68.8553825716439</v>
+        <v>68.85539012394126</v>
       </c>
       <c r="E115" t="n">
-        <v>68.8553825716439</v>
+        <v>68.85539012394126</v>
       </c>
       <c r="F115" t="n">
         <v>697200</v>
@@ -2732,16 +2732,16 @@
         <v>43382</v>
       </c>
       <c r="B116" t="n">
-        <v>68.26963806152344</v>
+        <v>68.26962280273438</v>
       </c>
       <c r="C116" t="n">
-        <v>71.75487452629949</v>
+        <v>71.75485848853327</v>
       </c>
       <c r="D116" t="n">
-        <v>68.26963806152344</v>
+        <v>68.26962280273438</v>
       </c>
       <c r="E116" t="n">
-        <v>69.96832280153448</v>
+        <v>69.96830716307632</v>
       </c>
       <c r="F116" t="n">
         <v>433600</v>
@@ -2752,16 +2752,16 @@
         <v>43383</v>
       </c>
       <c r="B117" t="n">
-        <v>69.14826965332031</v>
+        <v>69.14826202392578</v>
       </c>
       <c r="C117" t="n">
-        <v>71.72558696181675</v>
+        <v>71.72557904805687</v>
       </c>
       <c r="D117" t="n">
-        <v>67.24456445956281</v>
+        <v>67.24455704021138</v>
       </c>
       <c r="E117" t="n">
-        <v>67.36171795476652</v>
+        <v>67.3617105224891</v>
       </c>
       <c r="F117" t="n">
         <v>149833</v>
@@ -2772,16 +2772,16 @@
         <v>43384</v>
       </c>
       <c r="B118" t="n">
-        <v>70.87622833251953</v>
+        <v>70.87623596191406</v>
       </c>
       <c r="C118" t="n">
-        <v>71.63770729591425</v>
+        <v>71.63771500727735</v>
       </c>
       <c r="D118" t="n">
-        <v>68.62107794888951</v>
+        <v>68.62108533553082</v>
       </c>
       <c r="E118" t="n">
-        <v>69.08967695024926</v>
+        <v>69.08968438733241</v>
       </c>
       <c r="F118" t="n">
         <v>258833</v>
@@ -2792,16 +2792,16 @@
         <v>43388</v>
       </c>
       <c r="B119" t="n">
-        <v>72.04773712158203</v>
+        <v>72.0477294921875</v>
       </c>
       <c r="C119" t="n">
-        <v>72.89708309812396</v>
+        <v>72.89707537878911</v>
       </c>
       <c r="D119" t="n">
-        <v>66.77595711014101</v>
+        <v>66.77595003899427</v>
       </c>
       <c r="E119" t="n">
-        <v>71.5791380952637</v>
+        <v>71.5791305154908</v>
       </c>
       <c r="F119" t="n">
         <v>520433</v>
@@ -2812,16 +2812,16 @@
         <v>43389</v>
       </c>
       <c r="B120" t="n">
-        <v>73.83428192138672</v>
+        <v>73.83428955078125</v>
       </c>
       <c r="C120" t="n">
-        <v>75.85513272920463</v>
+        <v>75.85514056741636</v>
       </c>
       <c r="D120" t="n">
-        <v>71.34483212963087</v>
+        <v>71.34483950178725</v>
       </c>
       <c r="E120" t="n">
-        <v>71.98915759460718</v>
+        <v>71.98916503334256</v>
       </c>
       <c r="F120" t="n">
         <v>484533</v>
@@ -2832,16 +2832,16 @@
         <v>43390</v>
       </c>
       <c r="B121" t="n">
-        <v>74.91793060302734</v>
+        <v>74.91792297363281</v>
       </c>
       <c r="C121" t="n">
-        <v>75.88442256705758</v>
+        <v>75.8844148392387</v>
       </c>
       <c r="D121" t="n">
-        <v>73.27781919072763</v>
+        <v>73.27781172835662</v>
       </c>
       <c r="E121" t="n">
-        <v>73.27781919072763</v>
+        <v>73.27781172835662</v>
       </c>
       <c r="F121" t="n">
         <v>520600</v>
@@ -2872,16 +2872,16 @@
         <v>43392</v>
       </c>
       <c r="B123" t="n">
-        <v>73.95143890380859</v>
+        <v>73.95144653320312</v>
       </c>
       <c r="C123" t="n">
-        <v>76.41160230694427</v>
+        <v>76.41161019014804</v>
       </c>
       <c r="D123" t="n">
-        <v>72.75063998497356</v>
+        <v>72.75064749048451</v>
       </c>
       <c r="E123" t="n">
-        <v>75.62083682883761</v>
+        <v>75.62084463045997</v>
       </c>
       <c r="F123" t="n">
         <v>198200</v>
@@ -2892,16 +2892,16 @@
         <v>43395</v>
       </c>
       <c r="B124" t="n">
-        <v>74.65433502197266</v>
+        <v>74.65434265136719</v>
       </c>
       <c r="C124" t="n">
-        <v>76.55803219919309</v>
+        <v>76.55804002313839</v>
       </c>
       <c r="D124" t="n">
-        <v>74.39074159851387</v>
+        <v>74.39074920097013</v>
       </c>
       <c r="E124" t="n">
-        <v>74.53718156174142</v>
+        <v>74.53718917916331</v>
       </c>
       <c r="F124" t="n">
         <v>312766</v>
@@ -2912,16 +2912,16 @@
         <v>43396</v>
       </c>
       <c r="B125" t="n">
-        <v>75.44511413574219</v>
+        <v>75.44510650634766</v>
       </c>
       <c r="C125" t="n">
-        <v>76.14802012864928</v>
+        <v>76.14801242817332</v>
       </c>
       <c r="D125" t="n">
-        <v>74.15645563149494</v>
+        <v>74.15644813241612</v>
       </c>
       <c r="E125" t="n">
-        <v>74.80078860774221</v>
+        <v>74.80078104350515</v>
       </c>
       <c r="F125" t="n">
         <v>244366</v>
@@ -2972,16 +2972,16 @@
         <v>43399</v>
       </c>
       <c r="B128" t="n">
-        <v>74.97653198242188</v>
+        <v>74.97650909423828</v>
       </c>
       <c r="C128" t="n">
-        <v>78.02245645712874</v>
+        <v>78.02243263911183</v>
       </c>
       <c r="D128" t="n">
-        <v>73.3657139156992</v>
+        <v>73.36569151925214</v>
       </c>
       <c r="E128" t="n">
-        <v>76.11875831559301</v>
+        <v>76.1187350787205</v>
       </c>
       <c r="F128" t="n">
         <v>546200</v>
@@ -2992,16 +2992,16 @@
         <v>43402</v>
       </c>
       <c r="B129" t="n">
-        <v>75.50370025634766</v>
+        <v>75.50368499755859</v>
       </c>
       <c r="C129" t="n">
-        <v>76.44090592679686</v>
+        <v>76.44089047860484</v>
       </c>
       <c r="D129" t="n">
-        <v>75.18154116055941</v>
+        <v>75.18152596687653</v>
       </c>
       <c r="E129" t="n">
-        <v>76.38233289997146</v>
+        <v>76.38231746361667</v>
       </c>
       <c r="F129" t="n">
         <v>188000</v>
@@ -3012,16 +3012,16 @@
         <v>43403</v>
       </c>
       <c r="B130" t="n">
-        <v>74.56649017333984</v>
+        <v>74.56647491455078</v>
       </c>
       <c r="C130" t="n">
-        <v>76.14802883827332</v>
+        <v>76.14801325584872</v>
       </c>
       <c r="D130" t="n">
-        <v>73.6585710700305</v>
+        <v>73.65855599703195</v>
       </c>
       <c r="E130" t="n">
-        <v>75.65013579497513</v>
+        <v>75.65012031443605</v>
       </c>
       <c r="F130" t="n">
         <v>1306966</v>
@@ -3072,16 +3072,16 @@
         <v>43409</v>
       </c>
       <c r="B133" t="n">
-        <v>76.38232421875</v>
+        <v>76.38231658935547</v>
       </c>
       <c r="C133" t="n">
-        <v>76.85093072483949</v>
+        <v>76.85092304863853</v>
       </c>
       <c r="D133" t="n">
-        <v>73.98073356462973</v>
+        <v>73.98072617511639</v>
       </c>
       <c r="E133" t="n">
-        <v>75.82585818240808</v>
+        <v>75.82585060859577</v>
       </c>
       <c r="F133" t="n">
         <v>315933</v>
@@ -3152,16 +3152,16 @@
         <v>43413</v>
       </c>
       <c r="B137" t="n">
-        <v>76.73377990722656</v>
+        <v>76.73377227783203</v>
       </c>
       <c r="C137" t="n">
-        <v>79.07679762273497</v>
+        <v>79.07678976038169</v>
       </c>
       <c r="D137" t="n">
-        <v>75.21082174385769</v>
+        <v>75.21081426588603</v>
       </c>
       <c r="E137" t="n">
-        <v>77.31953247404167</v>
+        <v>77.31952478640763</v>
       </c>
       <c r="F137" t="n">
         <v>423466</v>
@@ -3172,16 +3172,16 @@
         <v>43416</v>
       </c>
       <c r="B138" t="n">
-        <v>76.79234313964844</v>
+        <v>76.7923583984375</v>
       </c>
       <c r="C138" t="n">
-        <v>77.78812907971066</v>
+        <v>77.78814453636434</v>
       </c>
       <c r="D138" t="n">
-        <v>75.79656464783326</v>
+        <v>75.79657970875918</v>
       </c>
       <c r="E138" t="n">
-        <v>77.02665009510251</v>
+        <v>77.02666540044883</v>
       </c>
       <c r="F138" t="n">
         <v>143933</v>
@@ -3212,16 +3212,16 @@
         <v>43418</v>
       </c>
       <c r="B140" t="n">
-        <v>79.36966705322266</v>
+        <v>79.36965942382812</v>
       </c>
       <c r="C140" t="n">
-        <v>80.33616657102803</v>
+        <v>80.33615884872891</v>
       </c>
       <c r="D140" t="n">
-        <v>71.02267654659238</v>
+        <v>71.02266971955076</v>
       </c>
       <c r="E140" t="n">
-        <v>75.0350922710638</v>
+        <v>75.03508505832947</v>
       </c>
       <c r="F140" t="n">
         <v>1608700</v>
@@ -3252,16 +3252,16 @@
         <v>43423</v>
       </c>
       <c r="B142" t="n">
-        <v>80.24828338623047</v>
+        <v>80.248291015625</v>
       </c>
       <c r="C142" t="n">
-        <v>81.5369417014697</v>
+        <v>81.53694945338003</v>
       </c>
       <c r="D142" t="n">
-        <v>79.77968442518686</v>
+        <v>79.77969201003057</v>
       </c>
       <c r="E142" t="n">
-        <v>80.65831678745137</v>
+        <v>80.65832445582875</v>
       </c>
       <c r="F142" t="n">
         <v>158533</v>
@@ -3272,16 +3272,16 @@
         <v>43425</v>
       </c>
       <c r="B143" t="n">
-        <v>79.80897521972656</v>
+        <v>79.80899047851562</v>
       </c>
       <c r="C143" t="n">
-        <v>81.59552654433449</v>
+        <v>81.59554214469678</v>
       </c>
       <c r="D143" t="n">
-        <v>78.13957736580078</v>
+        <v>78.13959230541533</v>
       </c>
       <c r="E143" t="n">
-        <v>79.04749628090917</v>
+        <v>79.04751139411002</v>
       </c>
       <c r="F143" t="n">
         <v>918800</v>
@@ -3292,16 +3292,16 @@
         <v>43426</v>
       </c>
       <c r="B144" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C144" t="n">
-        <v>80.24829487452415</v>
+        <v>80.24830261694648</v>
       </c>
       <c r="D144" t="n">
-        <v>77.78813135623429</v>
+        <v>77.78813886129798</v>
       </c>
       <c r="E144" t="n">
-        <v>79.54538888408497</v>
+        <v>79.54539655869033</v>
       </c>
       <c r="F144" t="n">
         <v>203833</v>
@@ -3312,16 +3312,16 @@
         <v>43427</v>
       </c>
       <c r="B145" t="n">
-        <v>79.51611328125</v>
+        <v>79.51610565185547</v>
       </c>
       <c r="C145" t="n">
-        <v>79.51611328125</v>
+        <v>79.51610565185547</v>
       </c>
       <c r="D145" t="n">
-        <v>77.31953548399726</v>
+        <v>77.31952806535949</v>
       </c>
       <c r="E145" t="n">
-        <v>78.63748067269924</v>
+        <v>78.63747312760756</v>
       </c>
       <c r="F145" t="n">
         <v>372100</v>
@@ -3332,16 +3332,16 @@
         <v>43430</v>
       </c>
       <c r="B146" t="n">
-        <v>78.75461578369141</v>
+        <v>78.75462341308594</v>
       </c>
       <c r="C146" t="n">
-        <v>80.33615410985325</v>
+        <v>80.33616189246013</v>
       </c>
       <c r="D146" t="n">
-        <v>76.23587204329363</v>
+        <v>76.23587942868353</v>
       </c>
       <c r="E146" t="n">
-        <v>80.27757365079401</v>
+        <v>80.27758142772588</v>
       </c>
       <c r="F146" t="n">
         <v>252366</v>
@@ -3352,16 +3352,16 @@
         <v>43431</v>
       </c>
       <c r="B147" t="n">
-        <v>81.59553527832031</v>
+        <v>81.59554290771484</v>
       </c>
       <c r="C147" t="n">
-        <v>82.5913138168435</v>
+        <v>82.59132153934591</v>
       </c>
       <c r="D147" t="n">
-        <v>76.32374770527765</v>
+        <v>76.32375484174636</v>
       </c>
       <c r="E147" t="n">
-        <v>78.28602572182773</v>
+        <v>78.28603304177452</v>
       </c>
       <c r="F147" t="n">
         <v>436400</v>
@@ -3372,16 +3372,16 @@
         <v>43432</v>
       </c>
       <c r="B148" t="n">
-        <v>84.5242919921875</v>
+        <v>84.52429962158203</v>
       </c>
       <c r="C148" t="n">
-        <v>86.22297626560693</v>
+        <v>86.22298404832937</v>
       </c>
       <c r="D148" t="n">
-        <v>80.54116356987981</v>
+        <v>80.54117083974624</v>
       </c>
       <c r="E148" t="n">
-        <v>81.18548900535082</v>
+        <v>81.18549633337582</v>
       </c>
       <c r="F148" t="n">
         <v>429500</v>
@@ -3452,16 +3452,16 @@
         <v>43438</v>
       </c>
       <c r="B152" t="n">
-        <v>83.82139587402344</v>
+        <v>83.82140350341797</v>
       </c>
       <c r="C152" t="n">
-        <v>86.60372581394269</v>
+        <v>86.60373369658394</v>
       </c>
       <c r="D152" t="n">
-        <v>82.59131041965232</v>
+        <v>82.5913179370849</v>
       </c>
       <c r="E152" t="n">
-        <v>84.64144787810613</v>
+        <v>84.64145558214152</v>
       </c>
       <c r="F152" t="n">
         <v>207933</v>
@@ -3472,16 +3472,16 @@
         <v>43439</v>
       </c>
       <c r="B153" t="n">
-        <v>86.10585021972656</v>
+        <v>86.10582733154297</v>
       </c>
       <c r="C153" t="n">
-        <v>86.39873025072337</v>
+        <v>86.39870728468802</v>
       </c>
       <c r="D153" t="n">
-        <v>83.11850667585297</v>
+        <v>83.1184845817486</v>
       </c>
       <c r="E153" t="n">
-        <v>83.82141279164642</v>
+        <v>83.82139051069942</v>
       </c>
       <c r="F153" t="n">
         <v>198233</v>
@@ -3512,16 +3512,16 @@
         <v>43441</v>
       </c>
       <c r="B155" t="n">
-        <v>84.26070404052734</v>
+        <v>84.26071166992188</v>
       </c>
       <c r="C155" t="n">
-        <v>86.10582840285664</v>
+        <v>86.10583619931816</v>
       </c>
       <c r="D155" t="n">
-        <v>82.18128018171485</v>
+        <v>82.18128762282772</v>
       </c>
       <c r="E155" t="n">
-        <v>85.57864894958446</v>
+        <v>85.57865669831246</v>
       </c>
       <c r="F155" t="n">
         <v>485833</v>
@@ -3552,16 +3552,16 @@
         <v>43445</v>
       </c>
       <c r="B157" t="n">
-        <v>83.87997436523438</v>
+        <v>83.87995910644531</v>
       </c>
       <c r="C157" t="n">
-        <v>84.37786737064518</v>
+        <v>84.37785202128332</v>
       </c>
       <c r="D157" t="n">
-        <v>83.14778183596749</v>
+        <v>83.14776671037318</v>
       </c>
       <c r="E157" t="n">
-        <v>83.46994833642434</v>
+        <v>83.46993315222402</v>
       </c>
       <c r="F157" t="n">
         <v>276533</v>
@@ -3572,16 +3572,16 @@
         <v>43446</v>
       </c>
       <c r="B158" t="n">
-        <v>85.60794830322266</v>
+        <v>85.60794067382812</v>
       </c>
       <c r="C158" t="n">
-        <v>86.2815603291279</v>
+        <v>86.28155263970095</v>
       </c>
       <c r="D158" t="n">
-        <v>84.37786283467175</v>
+        <v>84.37785531490263</v>
       </c>
       <c r="E158" t="n">
-        <v>84.55358933017901</v>
+        <v>84.55358179474914</v>
       </c>
       <c r="F158" t="n">
         <v>243466</v>
@@ -3612,16 +3612,16 @@
         <v>43448</v>
       </c>
       <c r="B160" t="n">
-        <v>86.39871978759766</v>
+        <v>86.39871215820312</v>
       </c>
       <c r="C160" t="n">
-        <v>88.30241741378802</v>
+        <v>88.30240961628846</v>
       </c>
       <c r="D160" t="n">
-        <v>85.81296724478891</v>
+        <v>85.81295966711896</v>
       </c>
       <c r="E160" t="n">
-        <v>86.77945931283573</v>
+        <v>86.77945164982019</v>
       </c>
       <c r="F160" t="n">
         <v>286966</v>
@@ -3632,16 +3632,16 @@
         <v>43451</v>
       </c>
       <c r="B161" t="n">
-        <v>84.93785858154297</v>
+        <v>84.9378662109375</v>
       </c>
       <c r="C161" t="n">
-        <v>86.47039216264943</v>
+        <v>86.47039992970112</v>
       </c>
       <c r="D161" t="n">
-        <v>84.28947437718072</v>
+        <v>84.28948194833528</v>
       </c>
       <c r="E161" t="n">
-        <v>86.44092151610168</v>
+        <v>86.44092928050621</v>
       </c>
       <c r="F161" t="n">
         <v>205700</v>
@@ -3652,16 +3652,16 @@
         <v>43452</v>
       </c>
       <c r="B162" t="n">
-        <v>86.35250854492188</v>
+        <v>86.35250091552734</v>
       </c>
       <c r="C162" t="n">
-        <v>87.14824597251724</v>
+        <v>87.14823827281793</v>
       </c>
       <c r="D162" t="n">
-        <v>84.67261425606614</v>
+        <v>84.67260677509321</v>
       </c>
       <c r="E162" t="n">
-        <v>84.96732821310101</v>
+        <v>84.96732070608958</v>
       </c>
       <c r="F162" t="n">
         <v>387133</v>
@@ -3672,16 +3672,16 @@
         <v>43453</v>
       </c>
       <c r="B163" t="n">
-        <v>89.68282318115234</v>
+        <v>89.68283081054688</v>
       </c>
       <c r="C163" t="n">
-        <v>90.56698000992543</v>
+        <v>90.56698771453594</v>
       </c>
       <c r="D163" t="n">
-        <v>86.29355658670175</v>
+        <v>86.29356392776849</v>
       </c>
       <c r="E163" t="n">
-        <v>86.52933673775965</v>
+        <v>86.52934409888439</v>
       </c>
       <c r="F163" t="n">
         <v>384866</v>
@@ -3712,16 +3712,16 @@
         <v>43455</v>
       </c>
       <c r="B165" t="n">
-        <v>88.00294494628906</v>
+        <v>88.0029296875</v>
       </c>
       <c r="C165" t="n">
-        <v>90.18385552681684</v>
+        <v>90.18383988988073</v>
       </c>
       <c r="D165" t="n">
-        <v>86.08727021997659</v>
+        <v>86.08725529334548</v>
       </c>
       <c r="E165" t="n">
-        <v>90.18385552681684</v>
+        <v>90.18383988988073</v>
       </c>
       <c r="F165" t="n">
         <v>2053700</v>
@@ -3732,16 +3732,16 @@
         <v>43460</v>
       </c>
       <c r="B166" t="n">
-        <v>90.59644317626953</v>
+        <v>90.59646606445312</v>
       </c>
       <c r="C166" t="n">
-        <v>92.68894125239805</v>
+        <v>92.68896466922801</v>
       </c>
       <c r="D166" t="n">
-        <v>86.38196888625549</v>
+        <v>86.38199070969904</v>
       </c>
       <c r="E166" t="n">
-        <v>87.88503162355258</v>
+        <v>87.88505382672821</v>
       </c>
       <c r="F166" t="n">
         <v>396300</v>
@@ -3752,16 +3752,16 @@
         <v>43461</v>
       </c>
       <c r="B167" t="n">
-        <v>90.62591552734375</v>
+        <v>90.62593078613281</v>
       </c>
       <c r="C167" t="n">
-        <v>91.36271158854166</v>
+        <v>91.36272697138592</v>
       </c>
       <c r="D167" t="n">
-        <v>89.35862540267408</v>
+        <v>89.35864044808805</v>
       </c>
       <c r="E167" t="n">
-        <v>91.36271158854166</v>
+        <v>91.36272697138592</v>
       </c>
       <c r="F167" t="n">
         <v>343866</v>
@@ -3792,16 +3792,16 @@
         <v>43467</v>
       </c>
       <c r="B169" t="n">
-        <v>91.65743255615234</v>
+        <v>91.65744018554688</v>
       </c>
       <c r="C169" t="n">
-        <v>94.192013000172</v>
+        <v>94.19202084054029</v>
       </c>
       <c r="D169" t="n">
-        <v>90.3017303976449</v>
+        <v>90.3017379141933</v>
       </c>
       <c r="E169" t="n">
-        <v>92.21740480094809</v>
+        <v>92.21741247695367</v>
       </c>
       <c r="F169" t="n">
         <v>431033</v>
@@ -3812,16 +3812,16 @@
         <v>43468</v>
       </c>
       <c r="B170" t="n">
-        <v>89.56494903564453</v>
+        <v>89.56494140625</v>
       </c>
       <c r="C170" t="n">
-        <v>91.53956505526335</v>
+        <v>91.53955725766548</v>
       </c>
       <c r="D170" t="n">
-        <v>89.56494903564453</v>
+        <v>89.56494140625</v>
       </c>
       <c r="E170" t="n">
-        <v>91.53956505526335</v>
+        <v>91.53955725766548</v>
       </c>
       <c r="F170" t="n">
         <v>308333</v>
@@ -3892,16 +3892,16 @@
         <v>43474</v>
       </c>
       <c r="B174" t="n">
-        <v>91.36273193359375</v>
+        <v>91.36272430419922</v>
       </c>
       <c r="C174" t="n">
-        <v>91.92269676499649</v>
+        <v>91.92268908884118</v>
       </c>
       <c r="D174" t="n">
-        <v>89.71230808918374</v>
+        <v>89.71230059761056</v>
       </c>
       <c r="E174" t="n">
-        <v>89.71230808918374</v>
+        <v>89.71230059761056</v>
       </c>
       <c r="F174" t="n">
         <v>225833</v>
@@ -3912,16 +3912,16 @@
         <v>43475</v>
       </c>
       <c r="B175" t="n">
-        <v>93.39627838134766</v>
+        <v>93.39626312255859</v>
       </c>
       <c r="C175" t="n">
-        <v>94.84040001456971</v>
+        <v>94.84038451984462</v>
       </c>
       <c r="D175" t="n">
-        <v>91.0974705277286</v>
+        <v>91.09745564451151</v>
       </c>
       <c r="E175" t="n">
-        <v>91.0974705277286</v>
+        <v>91.09745564451151</v>
       </c>
       <c r="F175" t="n">
         <v>243466</v>
@@ -3952,16 +3952,16 @@
         <v>43479</v>
       </c>
       <c r="B177" t="n">
-        <v>94.63409423828125</v>
+        <v>94.63408660888672</v>
       </c>
       <c r="C177" t="n">
-        <v>96.40240040656253</v>
+        <v>96.40239263460728</v>
       </c>
       <c r="D177" t="n">
-        <v>92.74789049900588</v>
+        <v>92.74788302167697</v>
       </c>
       <c r="E177" t="n">
-        <v>92.9542000056291</v>
+        <v>92.95419251166753</v>
       </c>
       <c r="F177" t="n">
         <v>478500</v>
@@ -3972,16 +3972,16 @@
         <v>43480</v>
       </c>
       <c r="B178" t="n">
-        <v>93.42575073242188</v>
+        <v>93.42575836181641</v>
       </c>
       <c r="C178" t="n">
-        <v>99.26117866454547</v>
+        <v>99.26118677047653</v>
       </c>
       <c r="D178" t="n">
-        <v>92.7478958730117</v>
+        <v>92.74790344705082</v>
       </c>
       <c r="E178" t="n">
-        <v>94.69304101541225</v>
+        <v>94.69304874829707</v>
       </c>
       <c r="F178" t="n">
         <v>736266</v>
@@ -3992,16 +3992,16 @@
         <v>43481</v>
       </c>
       <c r="B179" t="n">
-        <v>98.43595123291016</v>
+        <v>98.43596649169922</v>
       </c>
       <c r="C179" t="n">
-        <v>100.0569040740519</v>
+        <v>100.0569195841087</v>
       </c>
       <c r="D179" t="n">
-        <v>93.74993155986996</v>
+        <v>93.74994609226806</v>
       </c>
       <c r="E179" t="n">
-        <v>93.89729227180597</v>
+        <v>93.8973068270468</v>
       </c>
       <c r="F179" t="n">
         <v>1131666</v>
@@ -4032,16 +4032,16 @@
         <v>43483</v>
       </c>
       <c r="B181" t="n">
-        <v>100.7937164306641</v>
+        <v>100.7937088012695</v>
       </c>
       <c r="C181" t="n">
-        <v>102.267308798057</v>
+        <v>102.2673010571217</v>
       </c>
       <c r="D181" t="n">
-        <v>98.73068861532957</v>
+        <v>98.73068114209212</v>
       </c>
       <c r="E181" t="n">
-        <v>99.67378683105167</v>
+        <v>99.67377928642814</v>
       </c>
       <c r="F181" t="n">
         <v>475600</v>
@@ -4052,16 +4052,16 @@
         <v>43486</v>
       </c>
       <c r="B182" t="n">
-        <v>101.3831329345703</v>
+        <v>101.3831481933594</v>
       </c>
       <c r="C182" t="n">
-        <v>102.3557091117745</v>
+        <v>102.3557245169423</v>
       </c>
       <c r="D182" t="n">
-        <v>98.22964675700621</v>
+        <v>98.22966154117607</v>
       </c>
       <c r="E182" t="n">
-        <v>100.7936975967683</v>
+        <v>100.7937127668437</v>
       </c>
       <c r="F182" t="n">
         <v>260300</v>
@@ -4072,16 +4072,16 @@
         <v>43487</v>
       </c>
       <c r="B183" t="n">
-        <v>100.2632141113281</v>
+        <v>100.2632217407227</v>
       </c>
       <c r="C183" t="n">
-        <v>101.7662770044136</v>
+        <v>101.7662847481816</v>
       </c>
       <c r="D183" t="n">
-        <v>99.17275524868226</v>
+        <v>99.17276279509979</v>
       </c>
       <c r="E183" t="n">
-        <v>101.7662770044136</v>
+        <v>101.7662847481816</v>
       </c>
       <c r="F183" t="n">
         <v>236233</v>
@@ -4092,16 +4092,16 @@
         <v>43488</v>
       </c>
       <c r="B184" t="n">
-        <v>99.23170471191406</v>
+        <v>99.23171234130859</v>
       </c>
       <c r="C184" t="n">
-        <v>101.0589597106958</v>
+        <v>101.0589674805782</v>
       </c>
       <c r="D184" t="n">
-        <v>98.17071648776765</v>
+        <v>98.17072403558848</v>
       </c>
       <c r="E184" t="n">
-        <v>99.5853674532962</v>
+        <v>99.58537510988198</v>
       </c>
       <c r="F184" t="n">
         <v>240366</v>
@@ -4112,16 +4112,16 @@
         <v>43489</v>
       </c>
       <c r="B185" t="n">
-        <v>98.22966003417969</v>
+        <v>98.22965240478516</v>
       </c>
       <c r="C185" t="n">
-        <v>100.9705425952604</v>
+        <v>100.9705347529844</v>
       </c>
       <c r="D185" t="n">
-        <v>97.05078919923396</v>
+        <v>97.05078166140109</v>
       </c>
       <c r="E185" t="n">
-        <v>99.23170698945374</v>
+        <v>99.23169928223126</v>
       </c>
       <c r="F185" t="n">
         <v>372266</v>
@@ -4132,16 +4132,16 @@
         <v>43493</v>
       </c>
       <c r="B186" t="n">
-        <v>97.25709533691406</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C186" t="n">
-        <v>98.0528328094274</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="D186" t="n">
-        <v>95.96033436555834</v>
+        <v>95.96032683788904</v>
       </c>
       <c r="E186" t="n">
-        <v>98.0528328094274</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="F186" t="n">
         <v>263933</v>
@@ -4152,16 +4152,16 @@
         <v>43494</v>
       </c>
       <c r="B187" t="n">
-        <v>97.31602478027344</v>
+        <v>97.3160400390625</v>
       </c>
       <c r="C187" t="n">
-        <v>97.9938795787921</v>
+        <v>97.99389494386627</v>
       </c>
       <c r="D187" t="n">
-        <v>96.72658940964205</v>
+        <v>96.72660457600985</v>
       </c>
       <c r="E187" t="n">
-        <v>97.4928561409706</v>
+        <v>97.49287142748615</v>
       </c>
       <c r="F187" t="n">
         <v>185333</v>
@@ -4192,16 +4192,16 @@
         <v>43496</v>
       </c>
       <c r="B189" t="n">
-        <v>100.9115982055664</v>
+        <v>100.9115905761719</v>
       </c>
       <c r="C189" t="n">
-        <v>104.5661081748688</v>
+        <v>104.566100269176</v>
       </c>
       <c r="D189" t="n">
-        <v>99.20222580374578</v>
+        <v>99.2022183035879</v>
       </c>
       <c r="E189" t="n">
-        <v>99.79166869820958</v>
+        <v>99.79166115348703</v>
       </c>
       <c r="F189" t="n">
         <v>504800</v>
@@ -4212,16 +4212,16 @@
         <v>43497</v>
       </c>
       <c r="B190" t="n">
-        <v>100.2042922973633</v>
+        <v>100.2042770385742</v>
       </c>
       <c r="C190" t="n">
-        <v>101.5599947302167</v>
+        <v>101.5599792649856</v>
       </c>
       <c r="D190" t="n">
-        <v>98.84858986450983</v>
+        <v>98.84857481216278</v>
       </c>
       <c r="E190" t="n">
-        <v>101.2063319225021</v>
+        <v>101.2063165111256</v>
       </c>
       <c r="F190" t="n">
         <v>150066</v>
@@ -4232,16 +4232,16 @@
         <v>43500</v>
       </c>
       <c r="B191" t="n">
-        <v>100.2632141113281</v>
+        <v>100.2632217407227</v>
       </c>
       <c r="C191" t="n">
-        <v>102.2673004671346</v>
+        <v>102.2673082490274</v>
       </c>
       <c r="D191" t="n">
-        <v>99.55588863338727</v>
+        <v>99.55589620895881</v>
       </c>
       <c r="E191" t="n">
-        <v>100.7347669283146</v>
+        <v>100.7347745935913</v>
       </c>
       <c r="F191" t="n">
         <v>316266</v>
@@ -4272,16 +4272,16 @@
         <v>43502</v>
       </c>
       <c r="B193" t="n">
-        <v>97.46339416503906</v>
+        <v>97.46338653564453</v>
       </c>
       <c r="C193" t="n">
-        <v>99.5558925401632</v>
+        <v>99.55588474696876</v>
       </c>
       <c r="D193" t="n">
-        <v>96.07821380053463</v>
+        <v>96.07820627957145</v>
       </c>
       <c r="E193" t="n">
-        <v>98.43596298783444</v>
+        <v>98.43595528230763</v>
       </c>
       <c r="F193" t="n">
         <v>594200</v>
@@ -4292,16 +4292,16 @@
         <v>43503</v>
       </c>
       <c r="B194" t="n">
-        <v>97.10973358154297</v>
+        <v>97.10971832275391</v>
       </c>
       <c r="C194" t="n">
-        <v>98.61279656718887</v>
+        <v>98.61278107222451</v>
       </c>
       <c r="D194" t="n">
-        <v>95.31194913024648</v>
+        <v>95.31193415394212</v>
       </c>
       <c r="E194" t="n">
-        <v>97.19815301926943</v>
+        <v>97.19813774658708</v>
       </c>
       <c r="F194" t="n">
         <v>496333</v>
@@ -4332,16 +4332,16 @@
         <v>43507</v>
       </c>
       <c r="B196" t="n">
-        <v>98.14125061035156</v>
+        <v>98.14124298095703</v>
       </c>
       <c r="C196" t="n">
-        <v>98.6717447482006</v>
+        <v>98.67173707756602</v>
       </c>
       <c r="D196" t="n">
-        <v>96.10769349613602</v>
+        <v>96.10768602482801</v>
       </c>
       <c r="E196" t="n">
-        <v>97.10973298202097</v>
+        <v>97.10972543281549</v>
       </c>
       <c r="F196" t="n">
         <v>401966</v>
@@ -4352,16 +4352,16 @@
         <v>43508</v>
       </c>
       <c r="B197" t="n">
-        <v>97.55181121826172</v>
+        <v>97.55179595947266</v>
       </c>
       <c r="C197" t="n">
-        <v>99.64431719812912</v>
+        <v>99.64430161203596</v>
       </c>
       <c r="D197" t="n">
-        <v>96.7855443786229</v>
+        <v>96.78552923969121</v>
       </c>
       <c r="E197" t="n">
-        <v>98.20019546415823</v>
+        <v>98.20018010395066</v>
       </c>
       <c r="F197" t="n">
         <v>301900</v>
@@ -4392,16 +4392,16 @@
         <v>43510</v>
       </c>
       <c r="B199" t="n">
-        <v>97.64022064208984</v>
+        <v>97.64021301269531</v>
       </c>
       <c r="C199" t="n">
-        <v>99.02539344201128</v>
+        <v>99.02538570438236</v>
       </c>
       <c r="D199" t="n">
-        <v>96.54976179136901</v>
+        <v>96.54975424718056</v>
       </c>
       <c r="E199" t="n">
-        <v>98.40648740312012</v>
+        <v>98.40647971385117</v>
       </c>
       <c r="F199" t="n">
         <v>462433</v>
@@ -4412,16 +4412,16 @@
         <v>43511</v>
       </c>
       <c r="B200" t="n">
-        <v>99.40852355957031</v>
+        <v>99.40853881835938</v>
       </c>
       <c r="C200" t="n">
-        <v>100.0863708159291</v>
+        <v>100.0863861787649</v>
       </c>
       <c r="D200" t="n">
-        <v>97.61073943320076</v>
+        <v>97.61075441603754</v>
       </c>
       <c r="E200" t="n">
-        <v>97.61073943320076</v>
+        <v>97.61075441603754</v>
       </c>
       <c r="F200" t="n">
         <v>157766</v>
@@ -4432,16 +4432,16 @@
         <v>43514</v>
       </c>
       <c r="B201" t="n">
-        <v>100.2042922973633</v>
+        <v>100.2042770385742</v>
       </c>
       <c r="C201" t="n">
-        <v>100.2042922973633</v>
+        <v>100.2042770385742</v>
       </c>
       <c r="D201" t="n">
-        <v>97.64024068897147</v>
+        <v>97.64022582062798</v>
       </c>
       <c r="E201" t="n">
-        <v>98.34756630440083</v>
+        <v>98.34755132834806</v>
       </c>
       <c r="F201" t="n">
         <v>154800</v>
@@ -4452,16 +4452,16 @@
         <v>43515</v>
       </c>
       <c r="B202" t="n">
-        <v>98.43595123291016</v>
+        <v>98.43596649169922</v>
       </c>
       <c r="C202" t="n">
-        <v>101.0000021373343</v>
+        <v>101.0000177935829</v>
       </c>
       <c r="D202" t="n">
-        <v>98.25911987760239</v>
+        <v>98.2591351089804</v>
       </c>
       <c r="E202" t="n">
-        <v>100.2337354293596</v>
+        <v>100.2337509668275</v>
       </c>
       <c r="F202" t="n">
         <v>215600</v>
@@ -4472,16 +4472,16 @@
         <v>43516</v>
       </c>
       <c r="B203" t="n">
-        <v>97.25709533691406</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C203" t="n">
-        <v>99.17276239854924</v>
+        <v>99.17275461887898</v>
       </c>
       <c r="D203" t="n">
-        <v>95.51825216243448</v>
+        <v>95.5182446694446</v>
       </c>
       <c r="E203" t="n">
-        <v>98.87804842487829</v>
+        <v>98.87804066832706</v>
       </c>
       <c r="F203" t="n">
         <v>616733</v>
@@ -4492,16 +4492,16 @@
         <v>43517</v>
       </c>
       <c r="B204" t="n">
-        <v>95.78350830078125</v>
+        <v>95.78349304199219</v>
       </c>
       <c r="C204" t="n">
-        <v>97.61076352027936</v>
+        <v>97.61074797039947</v>
       </c>
       <c r="D204" t="n">
-        <v>95.04671208308292</v>
+        <v>95.04669694166917</v>
       </c>
       <c r="E204" t="n">
-        <v>97.28657138567321</v>
+        <v>97.28655588743874</v>
       </c>
       <c r="F204" t="n">
         <v>542100</v>
@@ -4512,16 +4512,16 @@
         <v>43518</v>
       </c>
       <c r="B205" t="n">
-        <v>92.86577606201172</v>
+        <v>92.86578369140625</v>
       </c>
       <c r="C205" t="n">
-        <v>95.87190164855839</v>
+        <v>95.87190952492139</v>
       </c>
       <c r="D205" t="n">
-        <v>92.86577606201172</v>
+        <v>92.86578369140625</v>
       </c>
       <c r="E205" t="n">
-        <v>95.84243100478083</v>
+        <v>95.84243887872267</v>
       </c>
       <c r="F205" t="n">
         <v>514866</v>
@@ -4532,16 +4532,16 @@
         <v>43521</v>
       </c>
       <c r="B206" t="n">
-        <v>95.40035247802734</v>
+        <v>95.40036010742188</v>
       </c>
       <c r="C206" t="n">
-        <v>97.10971720330089</v>
+        <v>97.10972496939742</v>
       </c>
       <c r="D206" t="n">
-        <v>92.24686630576804</v>
+        <v>92.24687368297073</v>
       </c>
       <c r="E206" t="n">
-        <v>93.66150961509786</v>
+        <v>93.66151710543296</v>
       </c>
       <c r="F206" t="n">
         <v>404566</v>
@@ -4552,16 +4552,16 @@
         <v>43522</v>
       </c>
       <c r="B207" t="n">
-        <v>95.13511657714844</v>
+        <v>95.13510894775391</v>
       </c>
       <c r="C207" t="n">
-        <v>97.25709311548748</v>
+        <v>97.25708531592029</v>
       </c>
       <c r="D207" t="n">
-        <v>93.36681029027736</v>
+        <v>93.36680280269279</v>
       </c>
       <c r="E207" t="n">
-        <v>95.5771987701748</v>
+        <v>95.57719110532733</v>
       </c>
       <c r="F207" t="n">
         <v>332133</v>
@@ -4592,16 +4592,16 @@
         <v>43524</v>
       </c>
       <c r="B209" t="n">
-        <v>96.04873657226562</v>
+        <v>96.04872894287109</v>
       </c>
       <c r="C209" t="n">
-        <v>96.46134808570203</v>
+        <v>96.46134042353272</v>
       </c>
       <c r="D209" t="n">
-        <v>94.75197573236808</v>
+        <v>94.75196820597856</v>
       </c>
       <c r="E209" t="n">
-        <v>95.69507384365015</v>
+        <v>95.69506624234795</v>
       </c>
       <c r="F209" t="n">
         <v>596166</v>
@@ -4612,16 +4612,16 @@
         <v>43525</v>
       </c>
       <c r="B210" t="n">
-        <v>95.42983245849609</v>
+        <v>95.42984008789062</v>
       </c>
       <c r="C210" t="n">
-        <v>96.66765203347371</v>
+        <v>96.66765976182906</v>
       </c>
       <c r="D210" t="n">
-        <v>94.60461691015179</v>
+        <v>94.60462447357224</v>
       </c>
       <c r="E210" t="n">
-        <v>95.28247173610485</v>
+        <v>95.28247935371824</v>
       </c>
       <c r="F210" t="n">
         <v>326633</v>
@@ -4632,16 +4632,16 @@
         <v>43530</v>
       </c>
       <c r="B211" t="n">
-        <v>95.75403594970703</v>
+        <v>95.75402069091797</v>
       </c>
       <c r="C211" t="n">
-        <v>96.6087147501988</v>
+        <v>96.60869935521325</v>
       </c>
       <c r="D211" t="n">
-        <v>93.95625141165144</v>
+        <v>93.95623643934654</v>
       </c>
       <c r="E211" t="n">
-        <v>95.10565169201672</v>
+        <v>95.10563653655028</v>
       </c>
       <c r="F211" t="n">
         <v>247200</v>
@@ -4652,16 +4652,16 @@
         <v>43531</v>
       </c>
       <c r="B212" t="n">
-        <v>96.10768127441406</v>
+        <v>96.10769653320312</v>
       </c>
       <c r="C212" t="n">
-        <v>96.22556384889319</v>
+        <v>96.22557912639819</v>
       </c>
       <c r="D212" t="n">
-        <v>94.89933242046251</v>
+        <v>94.89934748740488</v>
       </c>
       <c r="E212" t="n">
-        <v>95.72454791720247</v>
+        <v>95.72456311516235</v>
       </c>
       <c r="F212" t="n">
         <v>372100</v>
@@ -4672,16 +4672,16 @@
         <v>43532</v>
       </c>
       <c r="B213" t="n">
-        <v>96.63817596435547</v>
+        <v>96.63818359375</v>
       </c>
       <c r="C213" t="n">
-        <v>96.75605853959034</v>
+        <v>96.75606617829148</v>
       </c>
       <c r="D213" t="n">
-        <v>95.63612910439541</v>
+        <v>95.63613665468031</v>
       </c>
       <c r="E213" t="n">
-        <v>95.69507039201285</v>
+        <v>95.69507794695105</v>
       </c>
       <c r="F213" t="n">
         <v>212466</v>
@@ -4692,16 +4692,16 @@
         <v>43535</v>
       </c>
       <c r="B214" t="n">
-        <v>97.31602478027344</v>
+        <v>97.3160400390625</v>
       </c>
       <c r="C214" t="n">
-        <v>97.52232678524055</v>
+        <v>97.522342076377</v>
       </c>
       <c r="D214" t="n">
-        <v>96.19609532755058</v>
+        <v>96.19611041073888</v>
       </c>
       <c r="E214" t="n">
-        <v>97.25708349173351</v>
+        <v>97.2570987412808</v>
       </c>
       <c r="F214" t="n">
         <v>533833</v>
@@ -4712,16 +4712,16 @@
         <v>43536</v>
       </c>
       <c r="B215" t="n">
-        <v>97.25709533691406</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C215" t="n">
-        <v>98.49491501255126</v>
+        <v>98.49490728605517</v>
       </c>
       <c r="D215" t="n">
-        <v>95.34142078020059</v>
+        <v>95.34141330108237</v>
       </c>
       <c r="E215" t="n">
-        <v>96.84449127672777</v>
+        <v>96.84448367970022</v>
       </c>
       <c r="F215" t="n">
         <v>275666</v>
@@ -4732,16 +4732,16 @@
         <v>43537</v>
       </c>
       <c r="B216" t="n">
-        <v>95.78350830078125</v>
+        <v>95.78349304199219</v>
       </c>
       <c r="C216" t="n">
-        <v>97.58129287078403</v>
+        <v>97.58127732559895</v>
       </c>
       <c r="D216" t="n">
-        <v>95.40037486718441</v>
+        <v>95.40035966943042</v>
       </c>
       <c r="E216" t="n">
-        <v>97.43393212822862</v>
+        <v>97.43391660651884</v>
       </c>
       <c r="F216" t="n">
         <v>425833</v>
@@ -4772,16 +4772,16 @@
         <v>43539</v>
       </c>
       <c r="B218" t="n">
-        <v>89.29969787597656</v>
+        <v>89.29969024658203</v>
       </c>
       <c r="C218" t="n">
-        <v>92.15846313647816</v>
+        <v>92.15845526284264</v>
       </c>
       <c r="D218" t="n">
-        <v>88.91656446472457</v>
+        <v>88.91655686806337</v>
       </c>
       <c r="E218" t="n">
-        <v>91.06800419827536</v>
+        <v>91.0679964178041</v>
       </c>
       <c r="F218" t="n">
         <v>927800</v>
@@ -4792,16 +4792,16 @@
         <v>43542</v>
       </c>
       <c r="B219" t="n">
-        <v>86.64723968505859</v>
+        <v>86.647216796875</v>
       </c>
       <c r="C219" t="n">
-        <v>89.32918144689393</v>
+        <v>89.32915785026566</v>
       </c>
       <c r="D219" t="n">
-        <v>83.84741531506305</v>
+        <v>83.84739316646325</v>
       </c>
       <c r="E219" t="n">
-        <v>89.29971079485388</v>
+        <v>89.29968720601039</v>
       </c>
       <c r="F219" t="n">
         <v>2555666</v>
@@ -4852,16 +4852,16 @@
         <v>43545</v>
       </c>
       <c r="B222" t="n">
-        <v>88.38606262207031</v>
+        <v>88.38607788085938</v>
       </c>
       <c r="C222" t="n">
-        <v>89.27021945375864</v>
+        <v>89.27023486518674</v>
       </c>
       <c r="D222" t="n">
-        <v>87.61979586629964</v>
+        <v>87.61981099280197</v>
       </c>
       <c r="E222" t="n">
-        <v>89.27021945375864</v>
+        <v>89.27023486518674</v>
       </c>
       <c r="F222" t="n">
         <v>454533</v>
@@ -4872,16 +4872,16 @@
         <v>43546</v>
       </c>
       <c r="B223" t="n">
-        <v>87.82609558105469</v>
+        <v>87.82610321044922</v>
       </c>
       <c r="C223" t="n">
-        <v>87.9439781588119</v>
+        <v>87.94398579844682</v>
       </c>
       <c r="D223" t="n">
-        <v>86.55880540462269</v>
+        <v>86.55881292392856</v>
       </c>
       <c r="E223" t="n">
-        <v>87.9439781588119</v>
+        <v>87.94398579844682</v>
       </c>
       <c r="F223" t="n">
         <v>257266</v>
@@ -4912,16 +4912,16 @@
         <v>43550</v>
       </c>
       <c r="B225" t="n">
-        <v>89.56494903564453</v>
+        <v>89.56494140625</v>
       </c>
       <c r="C225" t="n">
-        <v>89.62389033635351</v>
+        <v>89.62388270193819</v>
       </c>
       <c r="D225" t="n">
-        <v>86.76512482578435</v>
+        <v>86.76511743488673</v>
       </c>
       <c r="E225" t="n">
-        <v>88.20924665378564</v>
+        <v>88.20923913987366</v>
       </c>
       <c r="F225" t="n">
         <v>883933</v>
@@ -4932,16 +4932,16 @@
         <v>43551</v>
       </c>
       <c r="B226" t="n">
-        <v>86.88300323486328</v>
+        <v>86.88299560546875</v>
       </c>
       <c r="C226" t="n">
-        <v>89.29969367486639</v>
+        <v>89.29968583325677</v>
       </c>
       <c r="D226" t="n">
-        <v>86.4998623465579</v>
+        <v>86.49985475080786</v>
       </c>
       <c r="E226" t="n">
-        <v>89.29969367486639</v>
+        <v>89.29968583325677</v>
       </c>
       <c r="F226" t="n">
         <v>691333</v>
@@ -4992,16 +4992,16 @@
         <v>43556</v>
       </c>
       <c r="B229" t="n">
-        <v>90.89115905761719</v>
+        <v>90.89116668701172</v>
       </c>
       <c r="C229" t="n">
-        <v>91.62795512080989</v>
+        <v>91.62796281205101</v>
       </c>
       <c r="D229" t="n">
-        <v>89.91859035282442</v>
+        <v>89.91859790058164</v>
       </c>
       <c r="E229" t="n">
-        <v>91.12693919429439</v>
+        <v>91.12694684348028</v>
       </c>
       <c r="F229" t="n">
         <v>342733</v>
@@ -5012,16 +5012,16 @@
         <v>43557</v>
       </c>
       <c r="B230" t="n">
-        <v>91.68690490722656</v>
+        <v>91.68692016601562</v>
       </c>
       <c r="C230" t="n">
-        <v>91.92267755141023</v>
+        <v>91.92269284943723</v>
       </c>
       <c r="D230" t="n">
-        <v>89.88912069451767</v>
+        <v>89.8891356541145</v>
       </c>
       <c r="E230" t="n">
-        <v>91.65742676851103</v>
+        <v>91.65744202239426</v>
       </c>
       <c r="F230" t="n">
         <v>264800</v>
@@ -5032,16 +5032,16 @@
         <v>43558</v>
       </c>
       <c r="B231" t="n">
-        <v>88.88709259033203</v>
+        <v>88.8870849609375</v>
       </c>
       <c r="C231" t="n">
-        <v>92.77738326291121</v>
+        <v>92.77737529960361</v>
       </c>
       <c r="D231" t="n">
-        <v>88.88709259033203</v>
+        <v>88.8870849609375</v>
       </c>
       <c r="E231" t="n">
-        <v>92.71843446812262</v>
+        <v>92.71842650987473</v>
       </c>
       <c r="F231" t="n">
         <v>371500</v>
@@ -5052,16 +5052,16 @@
         <v>43559</v>
       </c>
       <c r="B232" t="n">
-        <v>86.35250854492188</v>
+        <v>86.35250091552734</v>
       </c>
       <c r="C232" t="n">
-        <v>90.06595986713747</v>
+        <v>90.06595190965305</v>
       </c>
       <c r="D232" t="n">
-        <v>85.52729297605292</v>
+        <v>85.52728541956763</v>
       </c>
       <c r="E232" t="n">
-        <v>89.59440704277266</v>
+        <v>89.59439912695075</v>
       </c>
       <c r="F232" t="n">
         <v>777800</v>
@@ -5092,16 +5092,16 @@
         <v>43563</v>
       </c>
       <c r="B234" t="n">
-        <v>82.52117156982422</v>
+        <v>82.52115631103516</v>
       </c>
       <c r="C234" t="n">
-        <v>85.88096032777685</v>
+        <v>85.88094444773742</v>
       </c>
       <c r="D234" t="n">
-        <v>82.25592074967739</v>
+        <v>82.2559055399352</v>
       </c>
       <c r="E234" t="n">
-        <v>85.02627406686121</v>
+        <v>85.02625834485973</v>
       </c>
       <c r="F234" t="n">
         <v>619400</v>
@@ -5112,16 +5112,16 @@
         <v>43564</v>
       </c>
       <c r="B235" t="n">
-        <v>82.81587982177734</v>
+        <v>82.81586456298828</v>
       </c>
       <c r="C235" t="n">
-        <v>84.05369940843848</v>
+        <v>84.05368392158171</v>
       </c>
       <c r="D235" t="n">
-        <v>80.90021289784276</v>
+        <v>80.90019799201448</v>
       </c>
       <c r="E235" t="n">
-        <v>82.22644442172653</v>
+        <v>82.22642927154068</v>
       </c>
       <c r="F235" t="n">
         <v>535633</v>
@@ -5132,16 +5132,16 @@
         <v>43565</v>
       </c>
       <c r="B236" t="n">
-        <v>83.40531921386719</v>
+        <v>83.40532684326172</v>
       </c>
       <c r="C236" t="n">
-        <v>84.23052724026388</v>
+        <v>84.23053494514326</v>
       </c>
       <c r="D236" t="n">
-        <v>81.60753494840338</v>
+        <v>81.6075424133479</v>
       </c>
       <c r="E236" t="n">
-        <v>83.64109186496947</v>
+        <v>83.64109951593099</v>
       </c>
       <c r="F236" t="n">
         <v>456233</v>
@@ -5192,16 +5192,16 @@
         <v>43570</v>
       </c>
       <c r="B239" t="n">
-        <v>83.96527099609375</v>
+        <v>83.96529388427734</v>
       </c>
       <c r="C239" t="n">
-        <v>84.37787494566307</v>
+        <v>84.37789794631881</v>
       </c>
       <c r="D239" t="n">
-        <v>82.58009095744153</v>
+        <v>82.58011346803741</v>
       </c>
       <c r="E239" t="n">
-        <v>82.81586357218453</v>
+        <v>82.81588614704992</v>
       </c>
       <c r="F239" t="n">
         <v>210900</v>
@@ -5212,16 +5212,16 @@
         <v>43571</v>
       </c>
       <c r="B240" t="n">
-        <v>83.58216857910156</v>
+        <v>83.5821533203125</v>
       </c>
       <c r="C240" t="n">
-        <v>84.40737678324356</v>
+        <v>84.40736137380419</v>
       </c>
       <c r="D240" t="n">
-        <v>82.58012147969593</v>
+        <v>82.58010640384093</v>
       </c>
       <c r="E240" t="n">
-        <v>83.11061568024967</v>
+        <v>83.11060050754746</v>
       </c>
       <c r="F240" t="n">
         <v>215300</v>
@@ -5232,16 +5232,16 @@
         <v>43572</v>
       </c>
       <c r="B241" t="n">
-        <v>82.66852569580078</v>
+        <v>82.66851806640625</v>
       </c>
       <c r="C241" t="n">
-        <v>84.23052986373555</v>
+        <v>84.23052209018523</v>
       </c>
       <c r="D241" t="n">
-        <v>81.46017676799576</v>
+        <v>81.46016925011853</v>
       </c>
       <c r="E241" t="n">
-        <v>84.20105921831454</v>
+        <v>84.20105144748405</v>
       </c>
       <c r="F241" t="n">
         <v>289766</v>
@@ -5252,16 +5252,16 @@
         <v>43573</v>
       </c>
       <c r="B242" t="n">
-        <v>83.99475860595703</v>
+        <v>83.99476623535156</v>
       </c>
       <c r="C242" t="n">
-        <v>84.43683328479936</v>
+        <v>84.43684095434833</v>
       </c>
       <c r="D242" t="n">
-        <v>81.6959507887746</v>
+        <v>81.69595820936428</v>
       </c>
       <c r="E242" t="n">
-        <v>82.19697425451963</v>
+        <v>82.19698172061818</v>
       </c>
       <c r="F242" t="n">
         <v>318766</v>
@@ -5272,16 +5272,16 @@
         <v>43577</v>
       </c>
       <c r="B243" t="n">
-        <v>84.58420562744141</v>
+        <v>84.58418273925781</v>
       </c>
       <c r="C243" t="n">
-        <v>86.2641001308919</v>
+        <v>86.26407678813486</v>
       </c>
       <c r="D243" t="n">
-        <v>82.31487563954705</v>
+        <v>82.31485336543604</v>
       </c>
       <c r="E243" t="n">
-        <v>83.49374660843478</v>
+        <v>83.4937240153255</v>
       </c>
       <c r="F243" t="n">
         <v>461666</v>
@@ -5292,16 +5292,16 @@
         <v>43578</v>
       </c>
       <c r="B244" t="n">
-        <v>86.27613067626953</v>
+        <v>86.27611541748047</v>
       </c>
       <c r="C244" t="n">
-        <v>86.77928690824331</v>
+        <v>86.77927156046609</v>
       </c>
       <c r="D244" t="n">
-        <v>84.23391717823827</v>
+        <v>84.23390228063492</v>
       </c>
       <c r="E244" t="n">
-        <v>85.24022964218584</v>
+        <v>85.24021456660616</v>
       </c>
       <c r="F244" t="n">
         <v>437600</v>
@@ -5332,16 +5332,16 @@
         <v>43580</v>
       </c>
       <c r="B246" t="n">
-        <v>87.90397644042969</v>
+        <v>87.90399169921875</v>
       </c>
       <c r="C246" t="n">
-        <v>88.55512063075771</v>
+        <v>88.55513600257547</v>
       </c>
       <c r="D246" t="n">
-        <v>84.88505435395487</v>
+        <v>84.88506908870511</v>
       </c>
       <c r="E246" t="n">
-        <v>87.01605596588345</v>
+        <v>87.01607107054306</v>
       </c>
       <c r="F246" t="n">
         <v>486633</v>
@@ -5372,16 +5372,16 @@
         <v>43584</v>
       </c>
       <c r="B248" t="n">
-        <v>87.60800170898438</v>
+        <v>87.60800933837891</v>
       </c>
       <c r="C248" t="n">
-        <v>88.910290108505</v>
+        <v>88.91029785131008</v>
       </c>
       <c r="D248" t="n">
-        <v>86.66088903140958</v>
+        <v>86.66089657832424</v>
       </c>
       <c r="E248" t="n">
-        <v>87.87438161869812</v>
+        <v>87.87438927129051</v>
       </c>
       <c r="F248" t="n">
         <v>356166</v>
@@ -5392,16 +5392,16 @@
         <v>43585</v>
       </c>
       <c r="B249" t="n">
-        <v>89.56143188476562</v>
+        <v>89.56144714355469</v>
       </c>
       <c r="C249" t="n">
-        <v>90.27176831516947</v>
+        <v>90.27178369498019</v>
       </c>
       <c r="D249" t="n">
-        <v>86.77928588367251</v>
+        <v>86.77930066846089</v>
       </c>
       <c r="E249" t="n">
-        <v>86.77928588367251</v>
+        <v>86.77930066846089</v>
       </c>
       <c r="F249" t="n">
         <v>318366</v>
@@ -5412,16 +5412,16 @@
         <v>43587</v>
       </c>
       <c r="B250" t="n">
-        <v>89.82780456542969</v>
+        <v>89.82781219482422</v>
       </c>
       <c r="C250" t="n">
-        <v>90.41975661061814</v>
+        <v>90.41976429028925</v>
       </c>
       <c r="D250" t="n">
-        <v>88.64391552901864</v>
+        <v>88.64392305786127</v>
       </c>
       <c r="E250" t="n">
-        <v>88.64391552901864</v>
+        <v>88.64392305786127</v>
       </c>
       <c r="F250" t="n">
         <v>415166</v>
@@ -5432,16 +5432,16 @@
         <v>43588</v>
       </c>
       <c r="B251" t="n">
-        <v>90.21257781982422</v>
+        <v>90.21255493164062</v>
       </c>
       <c r="C251" t="n">
-        <v>90.89331063928984</v>
+        <v>90.89328757839488</v>
       </c>
       <c r="D251" t="n">
-        <v>88.91029684856353</v>
+        <v>88.9102742907867</v>
       </c>
       <c r="E251" t="n">
-        <v>88.91029684856353</v>
+        <v>88.9102742907867</v>
       </c>
       <c r="F251" t="n">
         <v>248400</v>
@@ -5472,16 +5472,16 @@
         <v>43592</v>
       </c>
       <c r="B253" t="n">
-        <v>96.93117523193359</v>
+        <v>96.93115234375</v>
       </c>
       <c r="C253" t="n">
-        <v>97.64151176619497</v>
+        <v>97.6414887102809</v>
       </c>
       <c r="D253" t="n">
-        <v>89.47265667615709</v>
+        <v>89.47263554914004</v>
       </c>
       <c r="E253" t="n">
-        <v>90.83413001550207</v>
+        <v>90.83410856700277</v>
       </c>
       <c r="F253" t="n">
         <v>3210933</v>
@@ -5512,16 +5512,16 @@
         <v>43594</v>
       </c>
       <c r="B255" t="n">
-        <v>105.2184143066406</v>
+        <v>105.2183990478516</v>
       </c>
       <c r="C255" t="n">
-        <v>106.3727073241445</v>
+        <v>106.3726918979597</v>
       </c>
       <c r="D255" t="n">
-        <v>99.77250630659914</v>
+        <v>99.7724918375764</v>
       </c>
       <c r="E255" t="n">
-        <v>101.4891553104076</v>
+        <v>101.4891405924361</v>
       </c>
       <c r="F255" t="n">
         <v>781533</v>
@@ -5572,16 +5572,16 @@
         <v>43599</v>
       </c>
       <c r="B258" t="n">
-        <v>103.0282135009766</v>
+        <v>103.028205871582</v>
       </c>
       <c r="C258" t="n">
-        <v>104.419282847616</v>
+        <v>104.4192751152107</v>
       </c>
       <c r="D258" t="n">
-        <v>101.8147207489442</v>
+        <v>101.8147132094106</v>
       </c>
       <c r="E258" t="n">
-        <v>102.6730452577955</v>
+        <v>102.6730376547018</v>
       </c>
       <c r="F258" t="n">
         <v>522566</v>
@@ -5612,16 +5612,16 @@
         <v>43601</v>
       </c>
       <c r="B260" t="n">
-        <v>102.5842361450195</v>
+        <v>102.5842437744141</v>
       </c>
       <c r="C260" t="n">
-        <v>103.6793368318073</v>
+        <v>103.6793445426467</v>
       </c>
       <c r="D260" t="n">
-        <v>102.5842361450195</v>
+        <v>102.5842437744141</v>
       </c>
       <c r="E260" t="n">
-        <v>103.5905485460052</v>
+        <v>103.5905562502412</v>
       </c>
       <c r="F260" t="n">
         <v>583833</v>
@@ -5632,16 +5632,16 @@
         <v>43602</v>
       </c>
       <c r="B261" t="n">
-        <v>102.9690170288086</v>
+        <v>102.9690093994141</v>
       </c>
       <c r="C261" t="n">
-        <v>103.5609615672124</v>
+        <v>103.5609538939583</v>
       </c>
       <c r="D261" t="n">
-        <v>101.5483441150528</v>
+        <v>101.5483365909217</v>
       </c>
       <c r="E261" t="n">
-        <v>102.9394134039527</v>
+        <v>102.9394057767516</v>
       </c>
       <c r="F261" t="n">
         <v>361233</v>
@@ -5652,16 +5652,16 @@
         <v>43605</v>
       </c>
       <c r="B262" t="n">
-        <v>105.0704193115234</v>
+        <v>105.0704116821289</v>
       </c>
       <c r="C262" t="n">
-        <v>105.899140132578</v>
+        <v>105.8991324430082</v>
       </c>
       <c r="D262" t="n">
-        <v>103.5905542507978</v>
+        <v>103.5905467288595</v>
       </c>
       <c r="E262" t="n">
-        <v>103.5905542507978</v>
+        <v>103.5905467288595</v>
       </c>
       <c r="F262" t="n">
         <v>597600</v>
@@ -5672,16 +5672,16 @@
         <v>43606</v>
       </c>
       <c r="B263" t="n">
-        <v>108.3557357788086</v>
+        <v>108.3557205200195</v>
       </c>
       <c r="C263" t="n">
-        <v>109.8356010338254</v>
+        <v>109.8355855666399</v>
       </c>
       <c r="D263" t="n">
-        <v>105.8103657337035</v>
+        <v>105.8103508333566</v>
       </c>
       <c r="E263" t="n">
-        <v>105.8103657337035</v>
+        <v>105.8103508333566</v>
       </c>
       <c r="F263" t="n">
         <v>554800</v>
@@ -5692,16 +5692,16 @@
         <v>43607</v>
       </c>
       <c r="B264" t="n">
-        <v>109.4508209228516</v>
+        <v>109.4508285522461</v>
       </c>
       <c r="C264" t="n">
-        <v>110.3091378300045</v>
+        <v>110.309145519229</v>
       </c>
       <c r="D264" t="n">
-        <v>107.8821600641873</v>
+        <v>107.8821675842365</v>
       </c>
       <c r="E264" t="n">
-        <v>108.3261165660262</v>
+        <v>108.3261241170219</v>
       </c>
       <c r="F264" t="n">
         <v>582066</v>
@@ -5712,16 +5712,16 @@
         <v>43608</v>
       </c>
       <c r="B265" t="n">
-        <v>110.989875793457</v>
+        <v>110.9898910522461</v>
       </c>
       <c r="C265" t="n">
-        <v>112.4697408040365</v>
+        <v>112.469756266276</v>
       </c>
       <c r="D265" t="n">
-        <v>109.1844386740743</v>
+        <v>109.1844536846535</v>
       </c>
       <c r="E265" t="n">
-        <v>109.3324266805288</v>
+        <v>109.3324417114532</v>
       </c>
       <c r="F265" t="n">
         <v>449966</v>
@@ -5732,16 +5732,16 @@
         <v>43609</v>
       </c>
       <c r="B266" t="n">
-        <v>110.3979415893555</v>
+        <v>110.39794921875</v>
       </c>
       <c r="C266" t="n">
-        <v>111.9074028365882</v>
+        <v>111.9074105702988</v>
       </c>
       <c r="D266" t="n">
-        <v>109.9539775285919</v>
+        <v>109.9539851273049</v>
       </c>
       <c r="E266" t="n">
-        <v>111.1970663609532</v>
+        <v>111.1970740455737</v>
       </c>
       <c r="F266" t="n">
         <v>294000</v>
@@ -5772,16 +5772,16 @@
         <v>43613</v>
       </c>
       <c r="B268" t="n">
-        <v>109.3028259277344</v>
+        <v>109.3028411865234</v>
       </c>
       <c r="C268" t="n">
-        <v>111.0786593485798</v>
+        <v>111.0786748552771</v>
       </c>
       <c r="D268" t="n">
-        <v>107.0830285064408</v>
+        <v>107.0830434553438</v>
       </c>
       <c r="E268" t="n">
-        <v>110.5755106858472</v>
+        <v>110.5755261223044</v>
       </c>
       <c r="F268" t="n">
         <v>402233</v>
@@ -5792,16 +5792,16 @@
         <v>43614</v>
       </c>
       <c r="B269" t="n">
-        <v>109.9243850708008</v>
+        <v>109.9243774414062</v>
       </c>
       <c r="C269" t="n">
-        <v>110.1019691955914</v>
+        <v>110.1019615538715</v>
       </c>
       <c r="D269" t="n">
-        <v>108.3557315743034</v>
+        <v>108.3557240537826</v>
       </c>
       <c r="E269" t="n">
-        <v>109.2732482978909</v>
+        <v>109.2732407136891</v>
       </c>
       <c r="F269" t="n">
         <v>725533</v>
@@ -5852,16 +5852,16 @@
         <v>43619</v>
       </c>
       <c r="B272" t="n">
-        <v>109.8651885986328</v>
+        <v>109.8651809692383</v>
       </c>
       <c r="C272" t="n">
-        <v>110.7531091880527</v>
+        <v>110.7531014969981</v>
       </c>
       <c r="D272" t="n">
-        <v>108.622099773445</v>
+        <v>108.6220922303745</v>
       </c>
       <c r="E272" t="n">
-        <v>108.7996838913289</v>
+        <v>108.7996763359265</v>
       </c>
       <c r="F272" t="n">
         <v>294000</v>
@@ -5872,16 +5872,16 @@
         <v>43620</v>
       </c>
       <c r="B273" t="n">
-        <v>107.1718292236328</v>
+        <v>107.1718215942383</v>
       </c>
       <c r="C273" t="n">
-        <v>110.9898839409142</v>
+        <v>110.9898760397184</v>
       </c>
       <c r="D273" t="n">
-        <v>107.1718292236328</v>
+        <v>107.1718215942383</v>
       </c>
       <c r="E273" t="n">
-        <v>109.5988071159028</v>
+        <v>109.5987993137355</v>
       </c>
       <c r="F273" t="n">
         <v>283866</v>
@@ -5892,16 +5892,16 @@
         <v>43621</v>
       </c>
       <c r="B274" t="n">
-        <v>108.8884811401367</v>
+        <v>108.8884735107422</v>
       </c>
       <c r="C274" t="n">
-        <v>109.8355939389301</v>
+        <v>109.835586243175</v>
       </c>
       <c r="D274" t="n">
-        <v>106.4023034571936</v>
+        <v>106.4022960019959</v>
       </c>
       <c r="E274" t="n">
-        <v>106.6390797751461</v>
+        <v>106.6390723033584</v>
       </c>
       <c r="F274" t="n">
         <v>231033</v>
@@ -5912,16 +5912,16 @@
         <v>43622</v>
       </c>
       <c r="B275" t="n">
-        <v>108.7404861450195</v>
+        <v>108.7404937744141</v>
       </c>
       <c r="C275" t="n">
-        <v>109.6875988830724</v>
+        <v>109.6876065789178</v>
       </c>
       <c r="D275" t="n">
-        <v>108.0597458067072</v>
+        <v>108.05975338834</v>
       </c>
       <c r="E275" t="n">
-        <v>109.510014774251</v>
+        <v>109.5100224576369</v>
       </c>
       <c r="F275" t="n">
         <v>227300</v>
@@ -5932,16 +5932,16 @@
         <v>43623</v>
       </c>
       <c r="B276" t="n">
-        <v>110.6051254272461</v>
+        <v>110.6051177978516</v>
       </c>
       <c r="C276" t="n">
-        <v>110.664317626492</v>
+        <v>110.6643099930145</v>
       </c>
       <c r="D276" t="n">
-        <v>108.9180800058842</v>
+        <v>108.9180724928598</v>
       </c>
       <c r="E276" t="n">
-        <v>109.2140485290975</v>
+        <v>109.2140409956576</v>
       </c>
       <c r="F276" t="n">
         <v>204266</v>
@@ -5972,16 +5972,16 @@
         <v>43627</v>
       </c>
       <c r="B278" t="n">
-        <v>110.989875793457</v>
+        <v>110.9898910522461</v>
       </c>
       <c r="C278" t="n">
-        <v>116.6725595416372</v>
+        <v>116.6725755816765</v>
       </c>
       <c r="D278" t="n">
-        <v>110.989875793457</v>
+        <v>110.9898910522461</v>
       </c>
       <c r="E278" t="n">
-        <v>116.4653718164113</v>
+        <v>116.4653878279667</v>
       </c>
       <c r="F278" t="n">
         <v>422033</v>
@@ -6012,16 +6012,16 @@
         <v>43629</v>
       </c>
       <c r="B280" t="n">
-        <v>113.8608093261719</v>
+        <v>113.8608016967773</v>
       </c>
       <c r="C280" t="n">
-        <v>114.9855061253982</v>
+        <v>114.9854984206418</v>
       </c>
       <c r="D280" t="n">
-        <v>108.9180656395131</v>
+        <v>108.9180583413137</v>
       </c>
       <c r="E280" t="n">
-        <v>108.9180656395131</v>
+        <v>108.9180583413137</v>
       </c>
       <c r="F280" t="n">
         <v>845300</v>
@@ -6032,16 +6032,16 @@
         <v>43630</v>
       </c>
       <c r="B281" t="n">
-        <v>111.9369888305664</v>
+        <v>111.9369964599609</v>
       </c>
       <c r="C281" t="n">
-        <v>114.1567863530506</v>
+        <v>114.156794133742</v>
       </c>
       <c r="D281" t="n">
-        <v>110.7530998293679</v>
+        <v>110.753107378071</v>
       </c>
       <c r="E281" t="n">
-        <v>113.3576616535908</v>
+        <v>113.3576693798154</v>
       </c>
       <c r="F281" t="n">
         <v>560666</v>
@@ -6052,16 +6052,16 @@
         <v>43633</v>
       </c>
       <c r="B282" t="n">
-        <v>110.0723648071289</v>
+        <v>110.0723724365234</v>
       </c>
       <c r="C282" t="n">
-        <v>113.1504868960452</v>
+        <v>113.1504947387922</v>
       </c>
       <c r="D282" t="n">
-        <v>109.066052333433</v>
+        <v>109.0660598930775</v>
       </c>
       <c r="E282" t="n">
-        <v>113.1504868960452</v>
+        <v>113.1504947387922</v>
       </c>
       <c r="F282" t="n">
         <v>481366</v>
@@ -6072,16 +6072,16 @@
         <v>43634</v>
       </c>
       <c r="B283" t="n">
-        <v>112.4697418212891</v>
+        <v>112.4697494506836</v>
       </c>
       <c r="C283" t="n">
-        <v>113.1800782371092</v>
+        <v>113.1800859146894</v>
       </c>
       <c r="D283" t="n">
-        <v>110.0131679890634</v>
+        <v>110.0131754518161</v>
       </c>
       <c r="E283" t="n">
-        <v>110.9602807011627</v>
+        <v>110.9602882281628</v>
       </c>
       <c r="F283" t="n">
         <v>583133</v>
@@ -6112,16 +6112,16 @@
         <v>43637</v>
       </c>
       <c r="B285" t="n">
-        <v>116.4653701782227</v>
+        <v>116.4653778076172</v>
       </c>
       <c r="C285" t="n">
-        <v>116.4949738006833</v>
+        <v>116.4949814320171</v>
       </c>
       <c r="D285" t="n">
-        <v>114.5415487023227</v>
+        <v>114.5415562056919</v>
       </c>
       <c r="E285" t="n">
-        <v>115.3998731060995</v>
+        <v>115.3998806656956</v>
       </c>
       <c r="F285" t="n">
         <v>285566</v>
@@ -6132,16 +6132,16 @@
         <v>43640</v>
       </c>
       <c r="B286" t="n">
-        <v>116.5245819091797</v>
+        <v>116.5245742797852</v>
       </c>
       <c r="C286" t="n">
-        <v>117.5012907955618</v>
+        <v>117.5012831022177</v>
       </c>
       <c r="D286" t="n">
-        <v>115.0447167668502</v>
+        <v>115.0447092343492</v>
       </c>
       <c r="E286" t="n">
-        <v>116.6133702047674</v>
+        <v>116.6133625695595</v>
       </c>
       <c r="F286" t="n">
         <v>315633</v>
@@ -6152,16 +6152,16 @@
         <v>43641</v>
       </c>
       <c r="B287" t="n">
-        <v>114.4823684692383</v>
+        <v>114.4823608398438</v>
       </c>
       <c r="C287" t="n">
-        <v>117.1165266196842</v>
+        <v>117.1165188147427</v>
       </c>
       <c r="D287" t="n">
-        <v>113.8312241927775</v>
+        <v>113.8312166067768</v>
       </c>
       <c r="E287" t="n">
-        <v>116.5837742644845</v>
+        <v>116.5837664950469</v>
       </c>
       <c r="F287" t="n">
         <v>481433</v>
@@ -6172,16 +6172,16 @@
         <v>43642</v>
       </c>
       <c r="B288" t="n">
-        <v>113.1208877563477</v>
+        <v>113.1208801269531</v>
       </c>
       <c r="C288" t="n">
-        <v>115.72544980908</v>
+        <v>115.7254420040218</v>
       </c>
       <c r="D288" t="n">
-        <v>112.6769312236937</v>
+        <v>112.6769236242416</v>
       </c>
       <c r="E288" t="n">
-        <v>115.72544980908</v>
+        <v>115.7254420040218</v>
       </c>
       <c r="F288" t="n">
         <v>335833</v>
@@ -6192,16 +6192,16 @@
         <v>43643</v>
       </c>
       <c r="B289" t="n">
-        <v>115.2815017700195</v>
+        <v>115.281494140625</v>
       </c>
       <c r="C289" t="n">
-        <v>115.2815017700195</v>
+        <v>115.281494140625</v>
       </c>
       <c r="D289" t="n">
-        <v>112.9137158584524</v>
+        <v>112.9137083857593</v>
       </c>
       <c r="E289" t="n">
-        <v>113.3872760515594</v>
+        <v>113.3872685475258</v>
       </c>
       <c r="F289" t="n">
         <v>276700</v>
@@ -6232,16 +6232,16 @@
         <v>43647</v>
       </c>
       <c r="B291" t="n">
-        <v>114.0680084228516</v>
+        <v>114.068000793457</v>
       </c>
       <c r="C291" t="n">
-        <v>117.0573348202537</v>
+        <v>117.0573269909192</v>
       </c>
       <c r="D291" t="n">
-        <v>114.0680084228516</v>
+        <v>114.068000793457</v>
       </c>
       <c r="E291" t="n">
-        <v>117.0573348202537</v>
+        <v>117.0573269909192</v>
       </c>
       <c r="F291" t="n">
         <v>436066</v>
@@ -6292,16 +6292,16 @@
         <v>43650</v>
       </c>
       <c r="B294" t="n">
-        <v>114.1004333496094</v>
+        <v>114.1004409790039</v>
       </c>
       <c r="C294" t="n">
-        <v>114.1004333496094</v>
+        <v>114.1004409790039</v>
       </c>
       <c r="D294" t="n">
-        <v>109.4044550659338</v>
+        <v>109.4044623813289</v>
       </c>
       <c r="E294" t="n">
-        <v>109.9691612673977</v>
+        <v>109.9691686205522</v>
       </c>
       <c r="F294" t="n">
         <v>412866</v>
@@ -6312,16 +6312,16 @@
         <v>43651</v>
       </c>
       <c r="B295" t="n">
-        <v>117.5183944702148</v>
+        <v>117.5184020996094</v>
       </c>
       <c r="C295" t="n">
-        <v>117.5183944702148</v>
+        <v>117.5184020996094</v>
       </c>
       <c r="D295" t="n">
-        <v>112.9115768934796</v>
+        <v>112.9115842237956</v>
       </c>
       <c r="E295" t="n">
-        <v>114.0707094441784</v>
+        <v>114.0707168497463</v>
       </c>
       <c r="F295" t="n">
         <v>288866</v>
@@ -6332,16 +6332,16 @@
         <v>43654</v>
       </c>
       <c r="B296" t="n">
-        <v>121.9171676635742</v>
+        <v>121.9171600341797</v>
       </c>
       <c r="C296" t="n">
-        <v>122.8682514573375</v>
+        <v>122.8682437684256</v>
       </c>
       <c r="D296" t="n">
-        <v>115.4081820448956</v>
+        <v>115.4081748228237</v>
       </c>
       <c r="E296" t="n">
-        <v>117.4886783161617</v>
+        <v>117.4886709638954</v>
       </c>
       <c r="F296" t="n">
         <v>420600</v>
@@ -6352,16 +6352,16 @@
         <v>43656</v>
       </c>
       <c r="B297" t="n">
-        <v>128.0397644042969</v>
+        <v>128.0397796630859</v>
       </c>
       <c r="C297" t="n">
-        <v>128.0397644042969</v>
+        <v>128.0397796630859</v>
       </c>
       <c r="D297" t="n">
-        <v>121.9171496849643</v>
+        <v>121.9171642141075</v>
       </c>
       <c r="E297" t="n">
-        <v>121.9171496849643</v>
+        <v>121.9171642141075</v>
       </c>
       <c r="F297" t="n">
         <v>529166</v>
@@ -6372,16 +6372,16 @@
         <v>43657</v>
       </c>
       <c r="B298" t="n">
-        <v>123.1654663085938</v>
+        <v>123.1654586791992</v>
       </c>
       <c r="C298" t="n">
-        <v>130.1797101104775</v>
+        <v>130.1797020465908</v>
       </c>
       <c r="D298" t="n">
-        <v>123.1060259345613</v>
+        <v>123.1060183088487</v>
       </c>
       <c r="E298" t="n">
-        <v>130.1797101104775</v>
+        <v>130.1797020465908</v>
       </c>
       <c r="F298" t="n">
         <v>660700</v>
@@ -6412,16 +6412,16 @@
         <v>43661</v>
       </c>
       <c r="B300" t="n">
-        <v>121.5605010986328</v>
+        <v>121.5605087280273</v>
       </c>
       <c r="C300" t="n">
-        <v>126.7320249772505</v>
+        <v>126.7320329312208</v>
       </c>
       <c r="D300" t="n">
-        <v>118.5289212629776</v>
+        <v>118.5289287021037</v>
       </c>
       <c r="E300" t="n">
-        <v>124.9784660186075</v>
+        <v>124.9784738625208</v>
       </c>
       <c r="F300" t="n">
         <v>1110366</v>
@@ -6452,16 +6452,16 @@
         <v>43663</v>
       </c>
       <c r="B302" t="n">
-        <v>126.6131362915039</v>
+        <v>126.6131439208984</v>
       </c>
       <c r="C302" t="n">
-        <v>127.9505975350065</v>
+        <v>127.9506052449931</v>
       </c>
       <c r="D302" t="n">
-        <v>122.7493610455057</v>
+        <v>122.7493684420787</v>
       </c>
       <c r="E302" t="n">
-        <v>123.9679339896924</v>
+        <v>123.9679414596935</v>
       </c>
       <c r="F302" t="n">
         <v>443966</v>
@@ -6472,16 +6472,16 @@
         <v>43664</v>
       </c>
       <c r="B303" t="n">
-        <v>129.8825225830078</v>
+        <v>129.8825073242188</v>
       </c>
       <c r="C303" t="n">
-        <v>129.8825225830078</v>
+        <v>129.8825073242188</v>
       </c>
       <c r="D303" t="n">
-        <v>127.5048015395542</v>
+        <v>127.5047865601033</v>
       </c>
       <c r="E303" t="n">
-        <v>127.7722983693234</v>
+        <v>127.7722833584466</v>
       </c>
       <c r="F303" t="n">
         <v>405966</v>
@@ -6492,16 +6492,16 @@
         <v>43665</v>
       </c>
       <c r="B304" t="n">
-        <v>126.9995346069336</v>
+        <v>126.9995193481445</v>
       </c>
       <c r="C304" t="n">
-        <v>132.3791003266432</v>
+        <v>132.379084421508</v>
       </c>
       <c r="D304" t="n">
-        <v>126.9995346069336</v>
+        <v>126.9995193481445</v>
       </c>
       <c r="E304" t="n">
-        <v>129.9419541843396</v>
+        <v>129.9419385720236</v>
       </c>
       <c r="F304" t="n">
         <v>683033</v>
@@ -6532,16 +6532,16 @@
         <v>43669</v>
       </c>
       <c r="B306" t="n">
-        <v>125.067626953125</v>
+        <v>125.0676345825195</v>
       </c>
       <c r="C306" t="n">
-        <v>127.8019973856753</v>
+        <v>127.8020051818723</v>
       </c>
       <c r="D306" t="n">
-        <v>123.6409975868307</v>
+        <v>123.6410051291977</v>
       </c>
       <c r="E306" t="n">
-        <v>127.4750602294759</v>
+        <v>127.475068005729</v>
       </c>
       <c r="F306" t="n">
         <v>528700</v>
@@ -6552,16 +6552,16 @@
         <v>43670</v>
       </c>
       <c r="B307" t="n">
-        <v>128.8719787597656</v>
+        <v>128.8719940185547</v>
       </c>
       <c r="C307" t="n">
-        <v>131.8441184494731</v>
+        <v>131.8441340601715</v>
       </c>
       <c r="D307" t="n">
-        <v>124.9487552763768</v>
+        <v>124.9487700706457</v>
       </c>
       <c r="E307" t="n">
-        <v>124.9487552763768</v>
+        <v>124.9487700706457</v>
       </c>
       <c r="F307" t="n">
         <v>788600</v>
@@ -6612,16 +6612,16 @@
         <v>43675</v>
       </c>
       <c r="B310" t="n">
-        <v>126.0187149047852</v>
+        <v>126.0187225341797</v>
       </c>
       <c r="C310" t="n">
-        <v>126.8806305437141</v>
+        <v>126.8806382252905</v>
       </c>
       <c r="D310" t="n">
-        <v>125.0081907754589</v>
+        <v>125.0081983436745</v>
       </c>
       <c r="E310" t="n">
-        <v>126.6131413078325</v>
+        <v>126.6131489732146</v>
       </c>
       <c r="F310" t="n">
         <v>708133</v>
@@ -6632,16 +6632,16 @@
         <v>43676</v>
       </c>
       <c r="B311" t="n">
-        <v>124.384033203125</v>
+        <v>124.3840408325195</v>
       </c>
       <c r="C311" t="n">
-        <v>126.3753687791254</v>
+        <v>126.3753765306633</v>
       </c>
       <c r="D311" t="n">
-        <v>124.2948726464664</v>
+        <v>124.294880270392</v>
       </c>
       <c r="E311" t="n">
-        <v>126.2267602928194</v>
+        <v>126.2267680352421</v>
       </c>
       <c r="F311" t="n">
         <v>1065500</v>
@@ -6692,16 +6692,16 @@
         <v>43679</v>
       </c>
       <c r="B314" t="n">
-        <v>124.0868377685547</v>
+        <v>124.0868301391602</v>
       </c>
       <c r="C314" t="n">
-        <v>124.8001525363515</v>
+        <v>124.8001448630993</v>
       </c>
       <c r="D314" t="n">
-        <v>122.4521593521107</v>
+        <v>122.4521518232233</v>
       </c>
       <c r="E314" t="n">
-        <v>122.6602082329611</v>
+        <v>122.6602006912819</v>
       </c>
       <c r="F314" t="n">
         <v>454366</v>
@@ -6712,16 +6712,16 @@
         <v>43682</v>
       </c>
       <c r="B315" t="n">
-        <v>123.4032363891602</v>
+        <v>123.4032287597656</v>
       </c>
       <c r="C315" t="n">
-        <v>124.3543201742961</v>
+        <v>124.3543124861009</v>
       </c>
       <c r="D315" t="n">
-        <v>121.8577261831319</v>
+        <v>121.8577186492884</v>
       </c>
       <c r="E315" t="n">
-        <v>124.057110743121</v>
+        <v>124.0571030733008</v>
       </c>
       <c r="F315" t="n">
         <v>384500</v>
@@ -6732,16 +6732,16 @@
         <v>43683</v>
       </c>
       <c r="B316" t="n">
-        <v>126.6131362915039</v>
+        <v>126.6131439208984</v>
       </c>
       <c r="C316" t="n">
-        <v>127.1778424858068</v>
+        <v>127.1778501492292</v>
       </c>
       <c r="D316" t="n">
-        <v>123.1357385701055</v>
+        <v>123.1357459899607</v>
       </c>
       <c r="E316" t="n">
-        <v>123.1951789404927</v>
+        <v>123.1951863639296</v>
       </c>
       <c r="F316" t="n">
         <v>466533</v>
@@ -6752,16 +6752,16 @@
         <v>43684</v>
       </c>
       <c r="B317" t="n">
-        <v>128.5153198242188</v>
+        <v>128.5153350830078</v>
       </c>
       <c r="C317" t="n">
-        <v>129.2583547375794</v>
+        <v>129.2583700845899</v>
       </c>
       <c r="D317" t="n">
-        <v>124.7406973245383</v>
+        <v>124.7407121351615</v>
       </c>
       <c r="E317" t="n">
-        <v>126.6131447015237</v>
+        <v>126.613159734465</v>
       </c>
       <c r="F317" t="n">
         <v>506366</v>
@@ -6812,16 +6812,16 @@
         <v>43689</v>
       </c>
       <c r="B320" t="n">
-        <v>131.1902313232422</v>
+        <v>131.1902465820312</v>
       </c>
       <c r="C320" t="n">
-        <v>131.487448286707</v>
+        <v>131.4874635800655</v>
       </c>
       <c r="D320" t="n">
-        <v>128.8422460343276</v>
+        <v>128.8422610200215</v>
       </c>
       <c r="E320" t="n">
-        <v>131.487448286707</v>
+        <v>131.4874635800655</v>
       </c>
       <c r="F320" t="n">
         <v>372500</v>
@@ -6832,16 +6832,16 @@
         <v>43690</v>
       </c>
       <c r="B321" t="n">
-        <v>131.0713653564453</v>
+        <v>131.0713500976562</v>
       </c>
       <c r="C321" t="n">
-        <v>133.7760082829146</v>
+        <v>133.7759927092622</v>
       </c>
       <c r="D321" t="n">
-        <v>128.8125403668755</v>
+        <v>128.8125253710496</v>
       </c>
       <c r="E321" t="n">
-        <v>133.6571275309639</v>
+        <v>133.6571119711511</v>
       </c>
       <c r="F321" t="n">
         <v>614133</v>
@@ -6912,16 +6912,16 @@
         <v>43696</v>
       </c>
       <c r="B325" t="n">
-        <v>141.8899841308594</v>
+        <v>141.8899383544922</v>
       </c>
       <c r="C325" t="n">
-        <v>147.0912298391252</v>
+        <v>147.0911823847387</v>
       </c>
       <c r="D325" t="n">
-        <v>140.7308511870678</v>
+        <v>140.7308057846586</v>
       </c>
       <c r="E325" t="n">
-        <v>147.0912298391252</v>
+        <v>147.0911823847387</v>
       </c>
       <c r="F325" t="n">
         <v>598666</v>
@@ -6932,16 +6932,16 @@
         <v>43697</v>
       </c>
       <c r="B326" t="n">
-        <v>145.0106964111328</v>
+        <v>145.0106811523438</v>
       </c>
       <c r="C326" t="n">
-        <v>146.7048227534003</v>
+        <v>146.7048073163463</v>
       </c>
       <c r="D326" t="n">
-        <v>140.4633261324826</v>
+        <v>140.4633113521918</v>
       </c>
       <c r="E326" t="n">
-        <v>143.0490883704163</v>
+        <v>143.049073318038</v>
       </c>
       <c r="F326" t="n">
         <v>506533</v>
@@ -6992,16 +6992,16 @@
         <v>43700</v>
       </c>
       <c r="B329" t="n">
-        <v>143.2868499755859</v>
+        <v>143.2868347167969</v>
       </c>
       <c r="C329" t="n">
-        <v>148.3691982354048</v>
+        <v>148.3691824353904</v>
       </c>
       <c r="D329" t="n">
-        <v>142.3654788707114</v>
+        <v>142.3654637100403</v>
       </c>
       <c r="E329" t="n">
-        <v>147.9531005199104</v>
+        <v>147.9530847642067</v>
       </c>
       <c r="F329" t="n">
         <v>586733</v>
@@ -7012,16 +7012,16 @@
         <v>43703</v>
       </c>
       <c r="B330" t="n">
-        <v>143.5543518066406</v>
+        <v>143.5543365478516</v>
       </c>
       <c r="C330" t="n">
-        <v>146.2292898230444</v>
+        <v>146.2292742799288</v>
       </c>
       <c r="D330" t="n">
-        <v>141.2063661119289</v>
+        <v>141.2063511027138</v>
       </c>
       <c r="E330" t="n">
-        <v>143.3165902884432</v>
+        <v>143.3165750549265</v>
       </c>
       <c r="F330" t="n">
         <v>278200</v>
@@ -7072,16 +7072,16 @@
         <v>43706</v>
       </c>
       <c r="B333" t="n">
-        <v>150.0930480957031</v>
+        <v>150.0930633544922</v>
       </c>
       <c r="C333" t="n">
-        <v>151.1035797810121</v>
+        <v>151.103595142534</v>
       </c>
       <c r="D333" t="n">
-        <v>145.9617759126635</v>
+        <v>145.9617907514584</v>
       </c>
       <c r="E333" t="n">
-        <v>146.5264745693678</v>
+        <v>146.5264894655712</v>
       </c>
       <c r="F333" t="n">
         <v>1067466</v>
@@ -7092,16 +7092,16 @@
         <v>43707</v>
       </c>
       <c r="B334" t="n">
-        <v>153.6893463134766</v>
+        <v>153.6893615722656</v>
       </c>
       <c r="C334" t="n">
-        <v>153.6893463134766</v>
+        <v>153.6893615722656</v>
       </c>
       <c r="D334" t="n">
-        <v>149.884996068173</v>
+        <v>149.8850109492535</v>
       </c>
       <c r="E334" t="n">
-        <v>150.984688344605</v>
+        <v>150.9847033348667</v>
       </c>
       <c r="F334" t="n">
         <v>973933</v>
@@ -7132,16 +7132,16 @@
         <v>43711</v>
       </c>
       <c r="B336" t="n">
-        <v>154.5512542724609</v>
+        <v>154.55126953125</v>
       </c>
       <c r="C336" t="n">
-        <v>157.107296061017</v>
+        <v>157.1073115721632</v>
       </c>
       <c r="D336" t="n">
-        <v>153.2137854482698</v>
+        <v>153.213800575011</v>
       </c>
       <c r="E336" t="n">
-        <v>154.2540372985203</v>
+        <v>154.2540525279653</v>
       </c>
       <c r="F336" t="n">
         <v>578066</v>
@@ -7172,16 +7172,16 @@
         <v>43713</v>
       </c>
       <c r="B338" t="n">
-        <v>149.2608184814453</v>
+        <v>149.2608489990234</v>
       </c>
       <c r="C338" t="n">
-        <v>150.2118944593904</v>
+        <v>150.2119251714237</v>
       </c>
       <c r="D338" t="n">
-        <v>145.5159246944912</v>
+        <v>145.5159544463956</v>
       </c>
       <c r="E338" t="n">
-        <v>150.2118944593904</v>
+        <v>150.2119251714237</v>
       </c>
       <c r="F338" t="n">
         <v>845300</v>
@@ -7192,16 +7192,16 @@
         <v>43714</v>
       </c>
       <c r="B339" t="n">
-        <v>146.2292633056641</v>
+        <v>146.2292785644531</v>
       </c>
       <c r="C339" t="n">
-        <v>150.5091361450396</v>
+        <v>150.5091518504265</v>
       </c>
       <c r="D339" t="n">
-        <v>145.4862284618692</v>
+        <v>145.4862436431238</v>
       </c>
       <c r="E339" t="n">
-        <v>150.0633182621792</v>
+        <v>150.0633339210457</v>
       </c>
       <c r="F339" t="n">
         <v>678033</v>
@@ -7212,16 +7212,16 @@
         <v>43717</v>
       </c>
       <c r="B340" t="n">
-        <v>142.9004974365234</v>
+        <v>142.9004516601562</v>
       </c>
       <c r="C340" t="n">
-        <v>146.7345532203692</v>
+        <v>146.7345062158107</v>
       </c>
       <c r="D340" t="n">
-        <v>139.7203009673272</v>
+        <v>139.7202562096958</v>
       </c>
       <c r="E340" t="n">
-        <v>146.7345532203692</v>
+        <v>146.7345062158107</v>
       </c>
       <c r="F340" t="n">
         <v>1841333</v>
@@ -7232,16 +7232,16 @@
         <v>43718</v>
       </c>
       <c r="B341" t="n">
-        <v>146.4075927734375</v>
+        <v>146.4076080322266</v>
       </c>
       <c r="C341" t="n">
-        <v>146.4967533316851</v>
+        <v>146.4967685997666</v>
       </c>
       <c r="D341" t="n">
-        <v>140.6416348000909</v>
+        <v>140.6416494579443</v>
       </c>
       <c r="E341" t="n">
-        <v>142.0385440143037</v>
+        <v>142.0385588177449</v>
       </c>
       <c r="F341" t="n">
         <v>1022600</v>
@@ -7252,16 +7252,16 @@
         <v>43719</v>
       </c>
       <c r="B342" t="n">
-        <v>152.5301971435547</v>
+        <v>152.5301818847656</v>
       </c>
       <c r="C342" t="n">
-        <v>152.5301971435547</v>
+        <v>152.5301818847656</v>
       </c>
       <c r="D342" t="n">
-        <v>146.7048137561047</v>
+        <v>146.7047990800743</v>
       </c>
       <c r="E342" t="n">
-        <v>148.5772611158358</v>
+        <v>148.5772462524898</v>
       </c>
       <c r="F342" t="n">
         <v>523500</v>
@@ -7272,16 +7272,16 @@
         <v>43720</v>
       </c>
       <c r="B343" t="n">
-        <v>148.3691864013672</v>
+        <v>148.3692016601562</v>
       </c>
       <c r="C343" t="n">
-        <v>154.4918011372027</v>
+        <v>154.4918170256621</v>
       </c>
       <c r="D343" t="n">
-        <v>148.3394662181369</v>
+        <v>148.3394814738694</v>
       </c>
       <c r="E343" t="n">
-        <v>153.9568076048933</v>
+        <v>153.9568234383322</v>
       </c>
       <c r="F343" t="n">
         <v>700866</v>
@@ -7312,16 +7312,16 @@
         <v>43724</v>
       </c>
       <c r="B345" t="n">
-        <v>149.9444580078125</v>
+        <v>149.9444274902344</v>
       </c>
       <c r="C345" t="n">
-        <v>151.2521916506516</v>
+        <v>151.2521608669158</v>
       </c>
       <c r="D345" t="n">
-        <v>146.5264851657776</v>
+        <v>146.5264553438454</v>
       </c>
       <c r="E345" t="n">
-        <v>149.4986249469664</v>
+        <v>149.4985945201269</v>
       </c>
       <c r="F345" t="n">
         <v>541366</v>
@@ -7352,16 +7352,16 @@
         <v>43726</v>
       </c>
       <c r="B347" t="n">
-        <v>152.4707794189453</v>
+        <v>152.4707489013672</v>
       </c>
       <c r="C347" t="n">
-        <v>153.2138144358351</v>
+        <v>153.2137837695358</v>
       </c>
       <c r="D347" t="n">
-        <v>151.4008071805737</v>
+        <v>151.4007768771544</v>
       </c>
       <c r="E347" t="n">
-        <v>151.4305424889685</v>
+        <v>151.4305121795976</v>
       </c>
       <c r="F347" t="n">
         <v>459166</v>
@@ -7372,16 +7372,16 @@
         <v>43727</v>
       </c>
       <c r="B348" t="n">
-        <v>153.0354614257812</v>
+        <v>153.0354766845703</v>
       </c>
       <c r="C348" t="n">
-        <v>155.3834467528314</v>
+        <v>155.3834622457323</v>
       </c>
       <c r="D348" t="n">
-        <v>151.5493917014036</v>
+        <v>151.5494068120203</v>
       </c>
       <c r="E348" t="n">
-        <v>154.4026504096753</v>
+        <v>154.4026658047834</v>
       </c>
       <c r="F348" t="n">
         <v>446666</v>
@@ -7392,16 +7392,16 @@
         <v>43728</v>
       </c>
       <c r="B349" t="n">
-        <v>153.7190704345703</v>
+        <v>153.7190551757812</v>
       </c>
       <c r="C349" t="n">
-        <v>155.0565242425662</v>
+        <v>155.056508851016</v>
       </c>
       <c r="D349" t="n">
-        <v>150.9846922085545</v>
+        <v>150.984677221191</v>
       </c>
       <c r="E349" t="n">
-        <v>153.065196065994</v>
+        <v>153.0651808721112</v>
       </c>
       <c r="F349" t="n">
         <v>555866</v>
@@ -7412,16 +7412,16 @@
         <v>43731</v>
       </c>
       <c r="B350" t="n">
-        <v>157.9395141601562</v>
+        <v>157.9394836425781</v>
       </c>
       <c r="C350" t="n">
-        <v>159.0986469194959</v>
+        <v>159.0986161779464</v>
       </c>
       <c r="D350" t="n">
-        <v>153.6893607092441</v>
+        <v>153.6893310128942</v>
       </c>
       <c r="E350" t="n">
-        <v>154.5512764519898</v>
+        <v>154.5512465890978</v>
       </c>
       <c r="F350" t="n">
         <v>685766</v>
@@ -7472,16 +7472,16 @@
         <v>43734</v>
       </c>
       <c r="B353" t="n">
-        <v>157.3748016357422</v>
+        <v>157.3747711181641</v>
       </c>
       <c r="C353" t="n">
-        <v>159.4255701479717</v>
+        <v>159.4255392327156</v>
       </c>
       <c r="D353" t="n">
-        <v>154.9970808285488</v>
+        <v>154.9970507720501</v>
       </c>
       <c r="E353" t="n">
-        <v>155.4726189431538</v>
+        <v>155.4725887944404</v>
       </c>
       <c r="F353" t="n">
         <v>815966</v>
@@ -7512,16 +7512,16 @@
         <v>43738</v>
       </c>
       <c r="B355" t="n">
-        <v>160.0496978759766</v>
+        <v>160.0497283935547</v>
       </c>
       <c r="C355" t="n">
-        <v>161.5654876485006</v>
+        <v>161.5655184551029</v>
       </c>
       <c r="D355" t="n">
-        <v>157.5233765494093</v>
+        <v>157.5234065852795</v>
       </c>
       <c r="E355" t="n">
-        <v>158.3852920741947</v>
+        <v>158.3853222744112</v>
       </c>
       <c r="F355" t="n">
         <v>546766</v>
@@ -7552,16 +7552,16 @@
         <v>43740</v>
       </c>
       <c r="B357" t="n">
-        <v>156.0373229980469</v>
+        <v>156.0373382568359</v>
       </c>
       <c r="C357" t="n">
-        <v>159.0689028547042</v>
+        <v>159.0689184099495</v>
       </c>
       <c r="D357" t="n">
-        <v>154.4323725132479</v>
+        <v>154.4323876150899</v>
       </c>
       <c r="E357" t="n">
-        <v>156.5723014539522</v>
+        <v>156.5723167650564</v>
       </c>
       <c r="F357" t="n">
         <v>1285800</v>
@@ -7572,16 +7572,16 @@
         <v>43741</v>
       </c>
       <c r="B358" t="n">
-        <v>160.4955291748047</v>
+        <v>160.4955444335938</v>
       </c>
       <c r="C358" t="n">
-        <v>160.4955291748047</v>
+        <v>160.4955444335938</v>
       </c>
       <c r="D358" t="n">
-        <v>154.2243131652207</v>
+        <v>154.2243278277865</v>
       </c>
       <c r="E358" t="n">
-        <v>155.7401030647272</v>
+        <v>155.7401178714037</v>
       </c>
       <c r="F358" t="n">
         <v>638566</v>
@@ -7592,16 +7592,16 @@
         <v>43742</v>
       </c>
       <c r="B359" t="n">
-        <v>160.4955291748047</v>
+        <v>160.4955444335938</v>
       </c>
       <c r="C359" t="n">
-        <v>161.6249415532033</v>
+        <v>161.624956919369</v>
       </c>
       <c r="D359" t="n">
-        <v>158.2961447878574</v>
+        <v>158.2961598375444</v>
       </c>
       <c r="E359" t="n">
-        <v>160.3766484351047</v>
+        <v>160.3766636825914</v>
       </c>
       <c r="F359" t="n">
         <v>752266</v>
@@ -7612,16 +7612,16 @@
         <v>43745</v>
       </c>
       <c r="B360" t="n">
-        <v>161.4168853759766</v>
+        <v>161.4169006347656</v>
       </c>
       <c r="C360" t="n">
-        <v>163.7054454381041</v>
+        <v>163.7054609132314</v>
       </c>
       <c r="D360" t="n">
-        <v>159.6336138095562</v>
+        <v>159.6336288997721</v>
       </c>
       <c r="E360" t="n">
-        <v>161.6249417878365</v>
+        <v>161.6249570662932</v>
       </c>
       <c r="F360" t="n">
         <v>812666</v>
@@ -7652,16 +7652,16 @@
         <v>43747</v>
       </c>
       <c r="B362" t="n">
-        <v>162.2788238525391</v>
+        <v>162.2788391113281</v>
       </c>
       <c r="C362" t="n">
-        <v>162.9029628838034</v>
+        <v>162.9029782012792</v>
       </c>
       <c r="D362" t="n">
-        <v>159.960543494568</v>
+        <v>159.9605585353733</v>
       </c>
       <c r="E362" t="n">
-        <v>161.9816068715598</v>
+        <v>161.9816221024021</v>
       </c>
       <c r="F362" t="n">
         <v>623966</v>
@@ -7672,16 +7672,16 @@
         <v>43748</v>
       </c>
       <c r="B363" t="n">
-        <v>163.1704559326172</v>
+        <v>163.1704711914062</v>
       </c>
       <c r="C363" t="n">
-        <v>163.7648898809297</v>
+        <v>163.7649051953069</v>
       </c>
       <c r="D363" t="n">
-        <v>161.387169204763</v>
+        <v>161.3871842967891</v>
       </c>
       <c r="E363" t="n">
-        <v>162.2193797558171</v>
+        <v>162.2193949256669</v>
       </c>
       <c r="F363" t="n">
         <v>538133</v>
@@ -7712,16 +7712,16 @@
         <v>43752</v>
       </c>
       <c r="B365" t="n">
-        <v>167.9258880615234</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C365" t="n">
-        <v>169.5902789878799</v>
+        <v>169.590263577854</v>
       </c>
       <c r="D365" t="n">
-        <v>166.3803778821685</v>
+        <v>166.3803627638141</v>
       </c>
       <c r="E365" t="n">
-        <v>167.2125733453467</v>
+        <v>167.2125581513739</v>
       </c>
       <c r="F365" t="n">
         <v>323333</v>
@@ -7732,16 +7732,16 @@
         <v>43753</v>
       </c>
       <c r="B366" t="n">
-        <v>167.3314361572266</v>
+        <v>167.3314514160156</v>
       </c>
       <c r="C366" t="n">
-        <v>169.2038833072246</v>
+        <v>169.2038987367602</v>
       </c>
       <c r="D366" t="n">
-        <v>167.1828352394022</v>
+        <v>167.1828504846405</v>
       </c>
       <c r="E366" t="n">
-        <v>167.3017159736617</v>
+        <v>167.3017312297406</v>
       </c>
       <c r="F366" t="n">
         <v>550533</v>
@@ -7772,16 +7772,16 @@
         <v>43755</v>
       </c>
       <c r="B368" t="n">
-        <v>169.7686157226562</v>
+        <v>169.7686004638672</v>
       </c>
       <c r="C368" t="n">
-        <v>172.9785319548521</v>
+        <v>172.9785164075561</v>
       </c>
       <c r="D368" t="n">
-        <v>168.8769647662821</v>
+        <v>168.8769495876346</v>
       </c>
       <c r="E368" t="n">
-        <v>171.2546855328626</v>
+        <v>171.2546701405057</v>
       </c>
       <c r="F368" t="n">
         <v>460533</v>
@@ -7792,16 +7792,16 @@
         <v>43756</v>
       </c>
       <c r="B369" t="n">
-        <v>170.9574584960938</v>
+        <v>170.9574737548828</v>
       </c>
       <c r="C369" t="n">
-        <v>171.0466190513639</v>
+        <v>171.046634318111</v>
       </c>
       <c r="D369" t="n">
-        <v>169.1444516201863</v>
+        <v>169.1444667171556</v>
       </c>
       <c r="E369" t="n">
-        <v>170.3333043750369</v>
+        <v>170.3333195781172</v>
       </c>
       <c r="F369" t="n">
         <v>657533</v>
@@ -7812,16 +7812,16 @@
         <v>43759</v>
       </c>
       <c r="B370" t="n">
-        <v>168.5203247070312</v>
+        <v>168.5203094482422</v>
       </c>
       <c r="C370" t="n">
-        <v>171.7302258637203</v>
+        <v>171.7302103142885</v>
       </c>
       <c r="D370" t="n">
-        <v>167.9853311028604</v>
+        <v>167.9853158925127</v>
       </c>
       <c r="E370" t="n">
-        <v>171.314128125523</v>
+        <v>171.314112613767</v>
       </c>
       <c r="F370" t="n">
         <v>853400</v>
@@ -7852,16 +7852,16 @@
         <v>43761</v>
       </c>
       <c r="B372" t="n">
-        <v>165.8453979492188</v>
+        <v>165.8453826904297</v>
       </c>
       <c r="C372" t="n">
-        <v>168.7580974273812</v>
+        <v>168.758081900606</v>
       </c>
       <c r="D372" t="n">
-        <v>164.9537620390848</v>
+        <v>164.9537468623316</v>
       </c>
       <c r="E372" t="n">
-        <v>167.2423073099024</v>
+        <v>167.2422919225891</v>
       </c>
       <c r="F372" t="n">
         <v>595766</v>
@@ -7872,16 +7872,16 @@
         <v>43762</v>
       </c>
       <c r="B373" t="n">
-        <v>169.1147308349609</v>
+        <v>169.1147155761719</v>
       </c>
       <c r="C373" t="n">
-        <v>169.6497243988491</v>
+        <v>169.6497090917889</v>
       </c>
       <c r="D373" t="n">
-        <v>165.3698363560753</v>
+        <v>165.3698214351784</v>
       </c>
       <c r="E373" t="n">
-        <v>165.9048148028805</v>
+        <v>165.904799833714</v>
       </c>
       <c r="F373" t="n">
         <v>606500</v>
@@ -7932,16 +7932,16 @@
         <v>43767</v>
       </c>
       <c r="B376" t="n">
-        <v>169.1147308349609</v>
+        <v>169.1147155761719</v>
       </c>
       <c r="C376" t="n">
-        <v>170.89801751945</v>
+        <v>170.8980020997596</v>
       </c>
       <c r="D376" t="n">
-        <v>168.5203120181865</v>
+        <v>168.5202968130303</v>
       </c>
       <c r="E376" t="n">
-        <v>170.3630239555619</v>
+        <v>170.3630085841425</v>
       </c>
       <c r="F376" t="n">
         <v>290500</v>
@@ -7952,16 +7952,16 @@
         <v>43768</v>
       </c>
       <c r="B377" t="n">
-        <v>167.628662109375</v>
+        <v>167.6286773681641</v>
       </c>
       <c r="C377" t="n">
-        <v>169.4713891747379</v>
+        <v>169.4714046012655</v>
       </c>
       <c r="D377" t="n">
-        <v>166.3209286110662</v>
+        <v>166.3209437508157</v>
       </c>
       <c r="E377" t="n">
-        <v>169.1147318357295</v>
+        <v>169.1147472297916</v>
       </c>
       <c r="F377" t="n">
         <v>545966</v>
@@ -7972,16 +7972,16 @@
         <v>43769</v>
       </c>
       <c r="B378" t="n">
-        <v>167.3314361572266</v>
+        <v>167.3314514160156</v>
       </c>
       <c r="C378" t="n">
-        <v>168.5203039681503</v>
+        <v>168.520319335351</v>
       </c>
       <c r="D378" t="n">
-        <v>166.142583463385</v>
+        <v>166.1425986137638</v>
       </c>
       <c r="E378" t="n">
-        <v>167.5989329263926</v>
+        <v>167.5989482095744</v>
       </c>
       <c r="F378" t="n">
         <v>595400</v>
@@ -7992,16 +7992,16 @@
         <v>43770</v>
       </c>
       <c r="B379" t="n">
-        <v>168.6689300537109</v>
+        <v>168.6688995361328</v>
       </c>
       <c r="C379" t="n">
-        <v>168.8769713697077</v>
+        <v>168.8769408144883</v>
       </c>
       <c r="D379" t="n">
-        <v>166.9748037523151</v>
+        <v>166.9747735412583</v>
       </c>
       <c r="E379" t="n">
-        <v>167.331461125394</v>
+        <v>167.3314308498066</v>
       </c>
       <c r="F379" t="n">
         <v>1063666</v>
@@ -8012,16 +8012,16 @@
         <v>43773</v>
       </c>
       <c r="B380" t="n">
-        <v>165.9940032958984</v>
+        <v>165.9939880371094</v>
       </c>
       <c r="C380" t="n">
-        <v>168.5203250342948</v>
+        <v>168.5203095432768</v>
       </c>
       <c r="D380" t="n">
-        <v>163.9729398583477</v>
+        <v>163.9729247853423</v>
       </c>
       <c r="E380" t="n">
-        <v>168.5203250342948</v>
+        <v>168.5203095432768</v>
       </c>
       <c r="F380" t="n">
         <v>963600</v>
@@ -8052,16 +8052,16 @@
         <v>43775</v>
       </c>
       <c r="B382" t="n">
-        <v>163.4974212646484</v>
+        <v>163.4973907470703</v>
       </c>
       <c r="C382" t="n">
-        <v>164.5971136765558</v>
+        <v>164.5970829537148</v>
       </c>
       <c r="D382" t="n">
-        <v>160.1389036472698</v>
+        <v>160.1388737565751</v>
       </c>
       <c r="E382" t="n">
-        <v>161.9221906824013</v>
+        <v>161.9221604588475</v>
       </c>
       <c r="F382" t="n">
         <v>1813233</v>
@@ -8092,16 +8092,16 @@
         <v>43777</v>
       </c>
       <c r="B384" t="n">
-        <v>165.5184326171875</v>
+        <v>165.5184631347656</v>
       </c>
       <c r="C384" t="n">
-        <v>169.203886622259</v>
+        <v>169.2039178193453</v>
       </c>
       <c r="D384" t="n">
-        <v>163.4082239573274</v>
+        <v>163.4082540858343</v>
       </c>
       <c r="E384" t="n">
-        <v>164.6862372269023</v>
+        <v>164.6862675910438</v>
       </c>
       <c r="F384" t="n">
         <v>1517366</v>
@@ -8132,16 +8132,16 @@
         <v>43781</v>
       </c>
       <c r="B386" t="n">
-        <v>167.9258880615234</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C386" t="n">
-        <v>171.6410625761589</v>
+        <v>171.641046979786</v>
       </c>
       <c r="D386" t="n">
-        <v>166.8856361740087</v>
+        <v>166.8856210097434</v>
       </c>
       <c r="E386" t="n">
-        <v>170.8980276732318</v>
+        <v>170.8980121443757</v>
       </c>
       <c r="F386" t="n">
         <v>771166</v>
@@ -8212,16 +8212,16 @@
         <v>43788</v>
       </c>
       <c r="B390" t="n">
-        <v>159.5741882324219</v>
+        <v>159.5741577148438</v>
       </c>
       <c r="C390" t="n">
-        <v>162.7841048643803</v>
+        <v>162.7840737329255</v>
       </c>
       <c r="D390" t="n">
-        <v>158.5339513293935</v>
+        <v>158.5339210107543</v>
       </c>
       <c r="E390" t="n">
-        <v>162.6355039116865</v>
+        <v>162.6354728086507</v>
       </c>
       <c r="F390" t="n">
         <v>1296633</v>
@@ -8232,16 +8232,16 @@
         <v>43790</v>
       </c>
       <c r="B391" t="n">
-        <v>165.0429077148438</v>
+        <v>165.0428924560547</v>
       </c>
       <c r="C391" t="n">
-        <v>165.4590054431674</v>
+        <v>165.4589901459087</v>
       </c>
       <c r="D391" t="n">
-        <v>159.4552858933658</v>
+        <v>159.4552711511718</v>
       </c>
       <c r="E391" t="n">
-        <v>159.9011038082066</v>
+        <v>159.9010890247952</v>
       </c>
       <c r="F391" t="n">
         <v>1440266</v>
@@ -8252,16 +8252,16 @@
         <v>43791</v>
       </c>
       <c r="B392" t="n">
-        <v>169.9766235351562</v>
+        <v>169.9766540527344</v>
       </c>
       <c r="C392" t="n">
-        <v>169.9766235351562</v>
+        <v>169.9766540527344</v>
       </c>
       <c r="D392" t="n">
-        <v>164.2404018496487</v>
+        <v>164.2404313373464</v>
       </c>
       <c r="E392" t="n">
-        <v>165.1023173322536</v>
+        <v>165.1023469746995</v>
       </c>
       <c r="F392" t="n">
         <v>1134300</v>
@@ -8292,16 +8292,16 @@
         <v>43795</v>
       </c>
       <c r="B394" t="n">
-        <v>169.4119567871094</v>
+        <v>169.4119415283203</v>
       </c>
       <c r="C394" t="n">
-        <v>172.5029771261092</v>
+        <v>172.5029615889146</v>
       </c>
       <c r="D394" t="n">
-        <v>167.4800690752345</v>
+        <v>167.4800539904489</v>
       </c>
       <c r="E394" t="n">
-        <v>170.9574669566093</v>
+        <v>170.9574515586174</v>
       </c>
       <c r="F394" t="n">
         <v>9961800</v>
@@ -8312,16 +8312,16 @@
         <v>43796</v>
       </c>
       <c r="B395" t="n">
-        <v>167.9555969238281</v>
+        <v>167.9556121826172</v>
       </c>
       <c r="C395" t="n">
-        <v>170.3927578926197</v>
+        <v>170.3927733728252</v>
       </c>
       <c r="D395" t="n">
-        <v>165.2509542923181</v>
+        <v>165.25096930539</v>
       </c>
       <c r="E395" t="n">
-        <v>169.7686037787779</v>
+        <v>169.7686192022788</v>
       </c>
       <c r="F395" t="n">
         <v>429100</v>
@@ -8332,16 +8332,16 @@
         <v>43797</v>
       </c>
       <c r="B396" t="n">
-        <v>163.6162872314453</v>
+        <v>163.6162719726562</v>
       </c>
       <c r="C396" t="n">
-        <v>168.49059460861</v>
+        <v>168.490578895245</v>
       </c>
       <c r="D396" t="n">
-        <v>163.2893500448137</v>
+        <v>163.2893348165146</v>
       </c>
       <c r="E396" t="n">
-        <v>166.4695462296235</v>
+        <v>166.4695307047406</v>
       </c>
       <c r="F396" t="n">
         <v>574533</v>
@@ -8352,16 +8352,16 @@
         <v>43798</v>
       </c>
       <c r="B397" t="n">
-        <v>165.5481719970703</v>
+        <v>165.5481872558594</v>
       </c>
       <c r="C397" t="n">
-        <v>166.0831504419819</v>
+        <v>166.0831657500806</v>
       </c>
       <c r="D397" t="n">
-        <v>161.0899628601699</v>
+        <v>161.08997770804</v>
       </c>
       <c r="E397" t="n">
-        <v>163.6459894622932</v>
+        <v>163.6460045457557</v>
       </c>
       <c r="F397" t="n">
         <v>703133</v>
@@ -8372,16 +8372,16 @@
         <v>43801</v>
       </c>
       <c r="B398" t="n">
-        <v>167.182861328125</v>
+        <v>167.1828460693359</v>
       </c>
       <c r="C398" t="n">
-        <v>167.3017420809357</v>
+        <v>167.3017268112964</v>
       </c>
       <c r="D398" t="n">
-        <v>162.9624283154143</v>
+        <v>162.9624134418244</v>
       </c>
       <c r="E398" t="n">
-        <v>165.6373510732474</v>
+        <v>165.6373359555172</v>
       </c>
       <c r="F398" t="n">
         <v>805633</v>
@@ -8452,16 +8452,16 @@
         <v>43805</v>
       </c>
       <c r="B402" t="n">
-        <v>171.730224609375</v>
+        <v>171.7302093505859</v>
       </c>
       <c r="C402" t="n">
-        <v>173.4243508540965</v>
+        <v>173.4243354447788</v>
       </c>
       <c r="D402" t="n">
-        <v>167.9556096888631</v>
+        <v>167.9555947654609</v>
       </c>
       <c r="E402" t="n">
-        <v>173.4243508540965</v>
+        <v>173.4243354447788</v>
       </c>
       <c r="F402" t="n">
         <v>837700</v>
@@ -8472,16 +8472,16 @@
         <v>43808</v>
       </c>
       <c r="B403" t="n">
-        <v>165.8453979492188</v>
+        <v>165.8453826904297</v>
       </c>
       <c r="C403" t="n">
-        <v>172.6218883111604</v>
+        <v>172.6218724288928</v>
       </c>
       <c r="D403" t="n">
-        <v>165.5779162464296</v>
+        <v>165.5779010122505</v>
       </c>
       <c r="E403" t="n">
-        <v>172.3841116804849</v>
+        <v>172.3840958200943</v>
       </c>
       <c r="F403" t="n">
         <v>793900</v>
@@ -8492,16 +8492,16 @@
         <v>43809</v>
       </c>
       <c r="B404" t="n">
-        <v>162.3382568359375</v>
+        <v>162.3382873535156</v>
       </c>
       <c r="C404" t="n">
-        <v>167.2720040741151</v>
+        <v>167.2720355191765</v>
       </c>
       <c r="D404" t="n">
-        <v>162.3382568359375</v>
+        <v>162.3382873535156</v>
       </c>
       <c r="E404" t="n">
-        <v>166.5884095841042</v>
+        <v>166.5884409006583</v>
       </c>
       <c r="F404" t="n">
         <v>1232166</v>
@@ -8512,16 +8512,16 @@
         <v>43810</v>
       </c>
       <c r="B405" t="n">
-        <v>167.0936737060547</v>
+        <v>167.0936889648438</v>
       </c>
       <c r="C405" t="n">
-        <v>167.0936737060547</v>
+        <v>167.0936889648438</v>
       </c>
       <c r="D405" t="n">
-        <v>161.9815905238091</v>
+        <v>161.981605315769</v>
       </c>
       <c r="E405" t="n">
-        <v>162.7840657095058</v>
+        <v>162.7840805747468</v>
       </c>
       <c r="F405" t="n">
         <v>789933</v>
@@ -8572,16 +8572,16 @@
         <v>43815</v>
       </c>
       <c r="B408" t="n">
-        <v>171.9085693359375</v>
+        <v>171.9085540771484</v>
       </c>
       <c r="C408" t="n">
-        <v>175.8317853851723</v>
+        <v>175.8317697781544</v>
       </c>
       <c r="D408" t="n">
-        <v>167.0342619043242</v>
+        <v>167.0342470781839</v>
       </c>
       <c r="E408" t="n">
-        <v>167.1828628466874</v>
+        <v>167.1828480073571</v>
       </c>
       <c r="F408" t="n">
         <v>666133</v>
@@ -8592,16 +8592,16 @@
         <v>43816</v>
       </c>
       <c r="B409" t="n">
-        <v>173.1568298339844</v>
+        <v>173.1568450927734</v>
       </c>
       <c r="C409" t="n">
-        <v>175.2373333358522</v>
+        <v>175.2373487779778</v>
       </c>
       <c r="D409" t="n">
-        <v>171.403263460529</v>
+        <v>171.4032785647917</v>
       </c>
       <c r="E409" t="n">
-        <v>173.4243265967004</v>
+        <v>173.4243418790616</v>
       </c>
       <c r="F409" t="n">
         <v>614666</v>
@@ -8632,16 +8632,16 @@
         <v>43818</v>
       </c>
       <c r="B411" t="n">
-        <v>184.7481842041016</v>
+        <v>184.7482147216797</v>
       </c>
       <c r="C411" t="n">
-        <v>185.7587158511149</v>
+        <v>185.7587465356174</v>
       </c>
       <c r="D411" t="n">
-        <v>178.922801154627</v>
+        <v>178.9228307099409</v>
       </c>
       <c r="E411" t="n">
-        <v>181.3005066706881</v>
+        <v>181.3005366187626</v>
       </c>
       <c r="F411" t="n">
         <v>904966</v>
@@ -8652,16 +8652,16 @@
         <v>43819</v>
       </c>
       <c r="B412" t="n">
-        <v>190.0683441162109</v>
+        <v>190.0683135986328</v>
       </c>
       <c r="C412" t="n">
-        <v>190.0683441162109</v>
+        <v>190.0683135986328</v>
       </c>
       <c r="D412" t="n">
-        <v>182.9351965828794</v>
+        <v>182.9351672106071</v>
       </c>
       <c r="E412" t="n">
-        <v>185.847895972809</v>
+        <v>185.8478661328706</v>
       </c>
       <c r="F412" t="n">
         <v>984100</v>
@@ -8672,16 +8672,16 @@
         <v>43822</v>
       </c>
       <c r="B413" t="n">
-        <v>187.8392486572266</v>
+        <v>187.8392028808594</v>
       </c>
       <c r="C413" t="n">
-        <v>190.454731177498</v>
+        <v>190.4546847637385</v>
       </c>
       <c r="D413" t="n">
-        <v>186.1748424440982</v>
+        <v>186.1747970733463</v>
       </c>
       <c r="E413" t="n">
-        <v>190.2169545421696</v>
+        <v>190.2169081863562</v>
       </c>
       <c r="F413" t="n">
         <v>629966</v>
@@ -8692,16 +8692,16 @@
         <v>43825</v>
       </c>
       <c r="B414" t="n">
-        <v>191.40576171875</v>
+        <v>191.4057922363281</v>
       </c>
       <c r="C414" t="n">
-        <v>191.6435382972251</v>
+        <v>191.6435688527141</v>
       </c>
       <c r="D414" t="n">
-        <v>187.3636505871638</v>
+        <v>187.363680460271</v>
       </c>
       <c r="E414" t="n">
-        <v>188.7902798238509</v>
+        <v>188.7903099244187</v>
       </c>
       <c r="F414" t="n">
         <v>400133</v>
@@ -8712,16 +8712,16 @@
         <v>43826</v>
       </c>
       <c r="B415" t="n">
-        <v>189.6225128173828</v>
+        <v>189.6224670410156</v>
       </c>
       <c r="C415" t="n">
-        <v>194.9723735170316</v>
+        <v>194.9723264491659</v>
       </c>
       <c r="D415" t="n">
-        <v>184.9265416176233</v>
+        <v>184.9264969749005</v>
       </c>
       <c r="E415" t="n">
-        <v>194.9723735170316</v>
+        <v>194.9723264491659</v>
       </c>
       <c r="F415" t="n">
         <v>651400</v>
@@ -8732,16 +8732,16 @@
         <v>43829</v>
       </c>
       <c r="B416" t="n">
-        <v>189.9197387695312</v>
+        <v>189.9197082519531</v>
       </c>
       <c r="C416" t="n">
-        <v>193.3376966704004</v>
+        <v>193.3376656036019</v>
       </c>
       <c r="D416" t="n">
-        <v>188.0472912156926</v>
+        <v>188.047260998992</v>
       </c>
       <c r="E416" t="n">
-        <v>190.6627737530717</v>
+        <v>190.6627431160977</v>
       </c>
       <c r="F416" t="n">
         <v>1069533</v>
@@ -8752,16 +8752,16 @@
         <v>43832</v>
       </c>
       <c r="B417" t="n">
-        <v>197.4689178466797</v>
+        <v>197.4689636230469</v>
       </c>
       <c r="C417" t="n">
-        <v>199.3711002113134</v>
+        <v>199.3711464286361</v>
       </c>
       <c r="D417" t="n">
-        <v>191.4651991647313</v>
+        <v>191.4652435493431</v>
       </c>
       <c r="E417" t="n">
-        <v>193.7834791975407</v>
+        <v>193.7835241195659</v>
       </c>
       <c r="F417" t="n">
         <v>866733</v>
@@ -8772,16 +8772,16 @@
         <v>43833</v>
       </c>
       <c r="B418" t="n">
-        <v>205.8206634521484</v>
+        <v>205.8206481933594</v>
       </c>
       <c r="C418" t="n">
-        <v>205.8206634521484</v>
+        <v>205.8206481933594</v>
       </c>
       <c r="D418" t="n">
-        <v>194.3779231826556</v>
+        <v>194.3779087721894</v>
       </c>
       <c r="E418" t="n">
-        <v>195.4181750466247</v>
+        <v>195.418160559038</v>
       </c>
       <c r="F418" t="n">
         <v>3123966</v>
@@ -8792,16 +8792,16 @@
         <v>43836</v>
       </c>
       <c r="B419" t="n">
-        <v>199.4744567871094</v>
+        <v>199.4744720458984</v>
       </c>
       <c r="C419" t="n">
-        <v>205.1941488790033</v>
+        <v>205.1941645753199</v>
       </c>
       <c r="D419" t="n">
-        <v>196.3464881000858</v>
+        <v>196.346503119601</v>
       </c>
       <c r="E419" t="n">
-        <v>203.4663181237324</v>
+        <v>203.4663336878787</v>
       </c>
       <c r="F419" t="n">
         <v>735666</v>
@@ -8832,16 +8832,16 @@
         <v>43838</v>
       </c>
       <c r="B421" t="n">
-        <v>190.0012054443359</v>
+        <v>190.0011901855469</v>
       </c>
       <c r="C421" t="n">
-        <v>196.0188016770089</v>
+        <v>196.0187859349532</v>
       </c>
       <c r="D421" t="n">
-        <v>188.0052747108529</v>
+        <v>188.0052596123549</v>
       </c>
       <c r="E421" t="n">
-        <v>193.9037154227282</v>
+        <v>193.9036998505329</v>
       </c>
       <c r="F421" t="n">
         <v>832966</v>
@@ -8852,16 +8852,16 @@
         <v>43839</v>
       </c>
       <c r="B422" t="n">
-        <v>188.8691864013672</v>
+        <v>188.8691558837891</v>
       </c>
       <c r="C422" t="n">
-        <v>191.5205028574819</v>
+        <v>191.5204719115027</v>
       </c>
       <c r="D422" t="n">
-        <v>187.2009484680017</v>
+        <v>187.2009182199783</v>
       </c>
       <c r="E422" t="n">
-        <v>190.001209328158</v>
+        <v>190.0011786276671</v>
       </c>
       <c r="F422" t="n">
         <v>950500</v>
@@ -8892,16 +8892,16 @@
         <v>43843</v>
       </c>
       <c r="B424" t="n">
-        <v>185.8603973388672</v>
+        <v>185.8603668212891</v>
       </c>
       <c r="C424" t="n">
-        <v>186.6945163464585</v>
+        <v>186.6944856919212</v>
       </c>
       <c r="D424" t="n">
-        <v>183.6559291387862</v>
+        <v>183.6558989831735</v>
       </c>
       <c r="E424" t="n">
-        <v>184.6985854742881</v>
+        <v>184.6985551474751</v>
       </c>
       <c r="F424" t="n">
         <v>736233</v>
@@ -8932,16 +8932,16 @@
         <v>43845</v>
       </c>
       <c r="B426" t="n">
-        <v>181.7493591308594</v>
+        <v>181.7493286132812</v>
       </c>
       <c r="C426" t="n">
-        <v>188.0350706741274</v>
+        <v>188.0350391011139</v>
       </c>
       <c r="D426" t="n">
-        <v>179.3363688316654</v>
+        <v>179.3363387192531</v>
       </c>
       <c r="E426" t="n">
-        <v>187.677588946244</v>
+        <v>187.6775574332554</v>
       </c>
       <c r="F426" t="n">
         <v>1526633</v>
@@ -8952,16 +8952,16 @@
         <v>43846</v>
       </c>
       <c r="B427" t="n">
-        <v>187.8563079833984</v>
+        <v>187.8563232421875</v>
       </c>
       <c r="C427" t="n">
-        <v>187.9159008935459</v>
+        <v>187.9159161571754</v>
       </c>
       <c r="D427" t="n">
-        <v>181.4812302797791</v>
+        <v>181.481245020747</v>
       </c>
       <c r="E427" t="n">
-        <v>181.7195564642969</v>
+        <v>181.7195712246231</v>
       </c>
       <c r="F427" t="n">
         <v>911900</v>
@@ -8972,16 +8972,16 @@
         <v>43847</v>
       </c>
       <c r="B428" t="n">
-        <v>187.6775970458984</v>
+        <v>187.6775665283203</v>
       </c>
       <c r="C428" t="n">
-        <v>191.58009218769</v>
+        <v>191.5800610355412</v>
       </c>
       <c r="D428" t="n">
-        <v>185.3539732903878</v>
+        <v>185.3539431506457</v>
       </c>
       <c r="E428" t="n">
-        <v>189.1968906669651</v>
+        <v>189.1968599023401</v>
       </c>
       <c r="F428" t="n">
         <v>852600</v>
@@ -8992,16 +8992,16 @@
         <v>43850</v>
       </c>
       <c r="B429" t="n">
-        <v>188.1244354248047</v>
+        <v>188.1244201660156</v>
       </c>
       <c r="C429" t="n">
-        <v>189.4947845599039</v>
+        <v>189.4947691899657</v>
       </c>
       <c r="D429" t="n">
-        <v>185.9497561980689</v>
+        <v>185.9497411156683</v>
       </c>
       <c r="E429" t="n">
-        <v>189.4649956788822</v>
+        <v>189.4649803113602</v>
       </c>
       <c r="F429" t="n">
         <v>883800</v>
@@ -9032,16 +9032,16 @@
         <v>43852</v>
       </c>
       <c r="B431" t="n">
-        <v>190.5671997070312</v>
+        <v>190.5672149658203</v>
       </c>
       <c r="C431" t="n">
-        <v>193.2780935170552</v>
+        <v>193.2781089929065</v>
       </c>
       <c r="D431" t="n">
-        <v>189.4947547031485</v>
+        <v>189.4947698760664</v>
       </c>
       <c r="E431" t="n">
-        <v>191.4013185482659</v>
+        <v>191.4013338738432</v>
       </c>
       <c r="F431" t="n">
         <v>460300</v>
@@ -9072,16 +9072,16 @@
         <v>43854</v>
       </c>
       <c r="B433" t="n">
-        <v>192.1461029052734</v>
+        <v>192.1460876464844</v>
       </c>
       <c r="C433" t="n">
-        <v>193.1887592072574</v>
+        <v>193.1887438656685</v>
       </c>
       <c r="D433" t="n">
-        <v>190.0607903013054</v>
+        <v>190.0607752081161</v>
       </c>
       <c r="E433" t="n">
-        <v>191.8481989401316</v>
+        <v>191.8481837049998</v>
       </c>
       <c r="F433" t="n">
         <v>639666</v>
@@ -9092,16 +9092,16 @@
         <v>43857</v>
       </c>
       <c r="B434" t="n">
-        <v>182.4047088623047</v>
+        <v>182.4047393798828</v>
       </c>
       <c r="C434" t="n">
-        <v>189.7628641385387</v>
+        <v>189.7628958871874</v>
       </c>
       <c r="D434" t="n">
-        <v>180.5279339489355</v>
+        <v>180.5279641525161</v>
       </c>
       <c r="E434" t="n">
-        <v>189.7628641385387</v>
+        <v>189.7628958871874</v>
       </c>
       <c r="F434" t="n">
         <v>939566</v>
@@ -9152,16 +9152,16 @@
         <v>43860</v>
       </c>
       <c r="B437" t="n">
-        <v>179.0682373046875</v>
+        <v>179.0682525634766</v>
       </c>
       <c r="C437" t="n">
-        <v>182.523883588893</v>
+        <v>182.5238991421452</v>
       </c>
       <c r="D437" t="n">
-        <v>174.8678387517811</v>
+        <v>174.8678536526452</v>
       </c>
       <c r="E437" t="n">
-        <v>182.523883588893</v>
+        <v>182.5238991421452</v>
       </c>
       <c r="F437" t="n">
         <v>937800</v>
@@ -9192,16 +9192,16 @@
         <v>43864</v>
       </c>
       <c r="B439" t="n">
-        <v>184.1027526855469</v>
+        <v>184.1027374267578</v>
       </c>
       <c r="C439" t="n">
-        <v>186.1582761969483</v>
+        <v>186.1582607677936</v>
       </c>
       <c r="D439" t="n">
-        <v>178.7405424721906</v>
+        <v>178.7405276578318</v>
       </c>
       <c r="E439" t="n">
-        <v>179.0384464067156</v>
+        <v>179.038431567666</v>
       </c>
       <c r="F439" t="n">
         <v>700100</v>
@@ -9212,16 +9212,16 @@
         <v>43865</v>
       </c>
       <c r="B440" t="n">
-        <v>182.7622222900391</v>
+        <v>182.76220703125</v>
       </c>
       <c r="C440" t="n">
-        <v>186.5753505305267</v>
+        <v>186.5753349533802</v>
       </c>
       <c r="D440" t="n">
-        <v>182.5238960929993</v>
+        <v>182.5238808541081</v>
       </c>
       <c r="E440" t="n">
-        <v>186.3668132141139</v>
+        <v>186.3667976543781</v>
       </c>
       <c r="F440" t="n">
         <v>732700</v>
@@ -9232,16 +9232,16 @@
         <v>43866</v>
       </c>
       <c r="B441" t="n">
-        <v>173.91455078125</v>
+        <v>173.9145660400391</v>
       </c>
       <c r="C441" t="n">
-        <v>185.2049904299985</v>
+        <v>185.2050066793799</v>
       </c>
       <c r="D441" t="n">
-        <v>171.85902722775</v>
+        <v>171.859042306193</v>
       </c>
       <c r="E441" t="n">
-        <v>184.6985643373504</v>
+        <v>184.6985805422995</v>
       </c>
       <c r="F441" t="n">
         <v>2347200</v>
@@ -9272,16 +9272,16 @@
         <v>43868</v>
       </c>
       <c r="B443" t="n">
-        <v>171.6802825927734</v>
+        <v>171.6803131103516</v>
       </c>
       <c r="C443" t="n">
-        <v>180.8556354750996</v>
+        <v>180.855667623672</v>
       </c>
       <c r="D443" t="n">
-        <v>171.4419564256401</v>
+        <v>171.4419869008538</v>
       </c>
       <c r="E443" t="n">
-        <v>172.961249755061</v>
+        <v>172.9612805003416</v>
       </c>
       <c r="F443" t="n">
         <v>1239533</v>
@@ -9312,16 +9312,16 @@
         <v>43872</v>
       </c>
       <c r="B445" t="n">
-        <v>172.8123321533203</v>
+        <v>172.8123168945312</v>
       </c>
       <c r="C445" t="n">
-        <v>174.4209923627202</v>
+        <v>174.4209769618915</v>
       </c>
       <c r="D445" t="n">
-        <v>167.3905284389344</v>
+        <v>167.3905136588736</v>
       </c>
       <c r="E445" t="n">
-        <v>168.6119331887622</v>
+        <v>168.6119183008553</v>
       </c>
       <c r="F445" t="n">
         <v>924566</v>
@@ -9332,16 +9332,16 @@
         <v>43873</v>
       </c>
       <c r="B446" t="n">
-        <v>174.9571838378906</v>
+        <v>174.9572143554688</v>
       </c>
       <c r="C446" t="n">
-        <v>176.3275175401388</v>
+        <v>176.3275482967427</v>
       </c>
       <c r="D446" t="n">
-        <v>171.4121562025475</v>
+        <v>171.4121861017706</v>
       </c>
       <c r="E446" t="n">
-        <v>173.4974683588696</v>
+        <v>173.4974986218312</v>
       </c>
       <c r="F446" t="n">
         <v>872333</v>
@@ -9392,16 +9392,16 @@
         <v>43878</v>
       </c>
       <c r="B449" t="n">
-        <v>178.3532562255859</v>
+        <v>178.353271484375</v>
       </c>
       <c r="C449" t="n">
-        <v>178.3532562255859</v>
+        <v>178.353271484375</v>
       </c>
       <c r="D449" t="n">
-        <v>173.4676836456995</v>
+        <v>173.4676984865096</v>
       </c>
       <c r="E449" t="n">
-        <v>173.9741096834605</v>
+        <v>173.9741245675972</v>
       </c>
       <c r="F449" t="n">
         <v>278100</v>
@@ -9412,16 +9412,16 @@
         <v>43879</v>
       </c>
       <c r="B450" t="n">
-        <v>175.7019805908203</v>
+        <v>175.7019653320312</v>
       </c>
       <c r="C450" t="n">
-        <v>177.5191781818942</v>
+        <v>177.5191627652912</v>
       </c>
       <c r="D450" t="n">
-        <v>172.7825488921122</v>
+        <v>172.7825338868604</v>
       </c>
       <c r="E450" t="n">
-        <v>177.5191781818942</v>
+        <v>177.5191627652912</v>
       </c>
       <c r="F450" t="n">
         <v>669733</v>
@@ -9432,16 +9432,16 @@
         <v>43880</v>
       </c>
       <c r="B451" t="n">
-        <v>177.3701934814453</v>
+        <v>177.3701782226562</v>
       </c>
       <c r="C451" t="n">
-        <v>178.3234830416113</v>
+        <v>178.3234677008127</v>
       </c>
       <c r="D451" t="n">
-        <v>173.1995838537692</v>
+        <v>173.199568953769</v>
       </c>
       <c r="E451" t="n">
-        <v>174.9869923090657</v>
+        <v>174.9869772552985</v>
       </c>
       <c r="F451" t="n">
         <v>740433</v>
@@ -9452,16 +9452,16 @@
         <v>43881</v>
       </c>
       <c r="B452" t="n">
-        <v>172.1569366455078</v>
+        <v>172.1569213867188</v>
       </c>
       <c r="C452" t="n">
-        <v>177.0722987901394</v>
+        <v>177.072283095687</v>
       </c>
       <c r="D452" t="n">
-        <v>171.3228177068359</v>
+        <v>171.3228025219774</v>
       </c>
       <c r="E452" t="n">
-        <v>175.7019648628997</v>
+        <v>175.7019492899041</v>
       </c>
       <c r="F452" t="n">
         <v>757533</v>
@@ -9472,16 +9472,16 @@
         <v>43882</v>
       </c>
       <c r="B453" t="n">
-        <v>166.8245086669922</v>
+        <v>166.8244934082031</v>
       </c>
       <c r="C453" t="n">
-        <v>171.2334445346579</v>
+        <v>171.2334288726006</v>
       </c>
       <c r="D453" t="n">
-        <v>165.543526276023</v>
+        <v>165.5435111344005</v>
       </c>
       <c r="E453" t="n">
-        <v>169.8333066290028</v>
+        <v>169.8332910950107</v>
       </c>
       <c r="F453" t="n">
         <v>990066</v>
@@ -9492,16 +9492,16 @@
         <v>43887</v>
       </c>
       <c r="B454" t="n">
-        <v>156.4575653076172</v>
+        <v>156.4575500488281</v>
       </c>
       <c r="C454" t="n">
-        <v>160.5685975170366</v>
+        <v>160.5685818573121</v>
       </c>
       <c r="D454" t="n">
-        <v>154.1637305812634</v>
+        <v>154.1637155461845</v>
       </c>
       <c r="E454" t="n">
-        <v>159.5259412363235</v>
+        <v>159.5259256782859</v>
       </c>
       <c r="F454" t="n">
         <v>1832133</v>
@@ -9532,16 +9532,16 @@
         <v>43889</v>
       </c>
       <c r="B456" t="n">
-        <v>164.4413146972656</v>
+        <v>164.4413299560547</v>
       </c>
       <c r="C456" t="n">
-        <v>165.0073185689544</v>
+        <v>165.0073338802639</v>
       </c>
       <c r="D456" t="n">
-        <v>155.0574235501962</v>
+        <v>155.057437938238</v>
       </c>
       <c r="E456" t="n">
-        <v>158.6322406683202</v>
+        <v>158.6322553880754</v>
       </c>
       <c r="F456" t="n">
         <v>1340833</v>
@@ -9592,16 +9592,16 @@
         <v>43894</v>
       </c>
       <c r="B459" t="n">
-        <v>159.4663543701172</v>
+        <v>159.4663696289062</v>
       </c>
       <c r="C459" t="n">
-        <v>169.7439418828748</v>
+        <v>169.743958125091</v>
       </c>
       <c r="D459" t="n">
-        <v>159.0790837910523</v>
+        <v>159.0790990127847</v>
       </c>
       <c r="E459" t="n">
-        <v>167.5692628035011</v>
+        <v>167.5692788376297</v>
       </c>
       <c r="F459" t="n">
         <v>1186600</v>
@@ -9612,16 +9612,16 @@
         <v>43895</v>
       </c>
       <c r="B460" t="n">
-        <v>152.8231811523438</v>
+        <v>152.8231506347656</v>
       </c>
       <c r="C460" t="n">
-        <v>161.7602096443411</v>
+        <v>161.7601773421092</v>
       </c>
       <c r="D460" t="n">
-        <v>151.6911581494385</v>
+        <v>151.6911278579163</v>
       </c>
       <c r="E460" t="n">
-        <v>156.397998609953</v>
+        <v>156.3979673785122</v>
       </c>
       <c r="F460" t="n">
         <v>1000500</v>
@@ -9632,16 +9632,16 @@
         <v>43896</v>
       </c>
       <c r="B461" t="n">
-        <v>148.9802703857422</v>
+        <v>148.9802398681641</v>
       </c>
       <c r="C461" t="n">
-        <v>152.8231879598351</v>
+        <v>152.8231566550619</v>
       </c>
       <c r="D461" t="n">
-        <v>147.8780362165492</v>
+        <v>147.8780059247562</v>
       </c>
       <c r="E461" t="n">
-        <v>151.9294911316361</v>
+        <v>151.9294600099305</v>
       </c>
       <c r="F461" t="n">
         <v>1046833</v>
@@ -9672,16 +9672,16 @@
         <v>43900</v>
       </c>
       <c r="B463" t="n">
-        <v>145.6437835693359</v>
+        <v>145.6437530517578</v>
       </c>
       <c r="C463" t="n">
-        <v>147.3716146637628</v>
+        <v>147.3715837841424</v>
       </c>
       <c r="D463" t="n">
-        <v>136.9152917460333</v>
+        <v>136.9152630573862</v>
       </c>
       <c r="E463" t="n">
-        <v>142.4562364981751</v>
+        <v>142.456206648502</v>
       </c>
       <c r="F463" t="n">
         <v>1718533</v>
@@ -9712,16 +9712,16 @@
         <v>43902</v>
       </c>
       <c r="B465" t="n">
-        <v>116.0621948242188</v>
+        <v>116.0621871948242</v>
       </c>
       <c r="C465" t="n">
-        <v>124.8204815027402</v>
+        <v>124.8204732976162</v>
       </c>
       <c r="D465" t="n">
-        <v>107.3634934809335</v>
+        <v>107.3634864233516</v>
       </c>
       <c r="E465" t="n">
-        <v>111.2064104711344</v>
+        <v>111.2064031609368</v>
       </c>
       <c r="F465" t="n">
         <v>1010966</v>
@@ -9752,16 +9752,16 @@
         <v>43906</v>
       </c>
       <c r="B467" t="n">
-        <v>110.2233505249023</v>
+        <v>110.2233352661133</v>
       </c>
       <c r="C467" t="n">
-        <v>120.6796725652378</v>
+        <v>120.6796558589259</v>
       </c>
       <c r="D467" t="n">
-        <v>106.3208478113856</v>
+        <v>106.3208330928401</v>
       </c>
       <c r="E467" t="n">
-        <v>109.7467056756733</v>
+        <v>109.7466904828687</v>
       </c>
       <c r="F467" t="n">
         <v>2066566</v>
@@ -9772,16 +9772,16 @@
         <v>43907</v>
       </c>
       <c r="B468" t="n">
-        <v>111.9511642456055</v>
+        <v>111.951171875</v>
       </c>
       <c r="C468" t="n">
-        <v>113.5598319500353</v>
+        <v>113.5598396890594</v>
       </c>
       <c r="D468" t="n">
-        <v>105.5165085799105</v>
+        <v>105.5165157707877</v>
       </c>
       <c r="E468" t="n">
-        <v>111.7128456295459</v>
+        <v>111.7128532426991</v>
       </c>
       <c r="F468" t="n">
         <v>2266766</v>
@@ -9812,16 +9812,16 @@
         <v>43909</v>
       </c>
       <c r="B470" t="n">
-        <v>107.5422134399414</v>
+        <v>107.5422210693359</v>
       </c>
       <c r="C470" t="n">
-        <v>109.0615142961074</v>
+        <v>109.0615220332861</v>
       </c>
       <c r="D470" t="n">
-        <v>84.36552854657734</v>
+        <v>84.36553453174244</v>
       </c>
       <c r="E470" t="n">
-        <v>90.85976865815006</v>
+        <v>90.85977510403768</v>
       </c>
       <c r="F470" t="n">
         <v>2314466</v>
@@ -9832,16 +9832,16 @@
         <v>43910</v>
       </c>
       <c r="B471" t="n">
-        <v>116.1813659667969</v>
+        <v>116.1813583374023</v>
       </c>
       <c r="C471" t="n">
-        <v>120.9477764352117</v>
+        <v>120.9477684928167</v>
       </c>
       <c r="D471" t="n">
-        <v>108.1976199091878</v>
+        <v>108.1976128040696</v>
       </c>
       <c r="E471" t="n">
-        <v>113.9471089289739</v>
+        <v>113.9471014462984</v>
       </c>
       <c r="F471" t="n">
         <v>2114800</v>
@@ -9852,16 +9852,16 @@
         <v>43913</v>
       </c>
       <c r="B472" t="n">
-        <v>113.7981414794922</v>
+        <v>113.7981491088867</v>
       </c>
       <c r="C472" t="n">
-        <v>119.6072074731813</v>
+        <v>119.6072154920344</v>
       </c>
       <c r="D472" t="n">
-        <v>108.4657126798635</v>
+        <v>108.4657199517548</v>
       </c>
       <c r="E472" t="n">
-        <v>118.9518294373453</v>
+        <v>118.9518374122596</v>
       </c>
       <c r="F472" t="n">
         <v>1372400</v>
@@ -9892,16 +9892,16 @@
         <v>43915</v>
       </c>
       <c r="B474" t="n">
-        <v>135.2470397949219</v>
+        <v>135.2470092773438</v>
       </c>
       <c r="C474" t="n">
-        <v>138.3750091276931</v>
+        <v>138.3749779043099</v>
       </c>
       <c r="D474" t="n">
-        <v>119.845564822186</v>
+        <v>119.8455377798463</v>
       </c>
       <c r="E474" t="n">
-        <v>123.8970123296677</v>
+        <v>123.8969843731464</v>
       </c>
       <c r="F474" t="n">
         <v>1102933</v>
@@ -9932,16 +9932,16 @@
         <v>43917</v>
       </c>
       <c r="B476" t="n">
-        <v>135.5449371337891</v>
+        <v>135.5449066162109</v>
       </c>
       <c r="C476" t="n">
-        <v>143.9457357413418</v>
+        <v>143.9457033323465</v>
       </c>
       <c r="D476" t="n">
-        <v>133.7277394550709</v>
+        <v>133.72770934663</v>
       </c>
       <c r="E476" t="n">
-        <v>141.3838008128161</v>
+        <v>141.3837689806335</v>
       </c>
       <c r="F476" t="n">
         <v>773066</v>
@@ -9952,16 +9952,16 @@
         <v>43920</v>
       </c>
       <c r="B477" t="n">
-        <v>134.1447601318359</v>
+        <v>134.144775390625</v>
       </c>
       <c r="C477" t="n">
-        <v>138.7324287498381</v>
+        <v>138.7324445304684</v>
       </c>
       <c r="D477" t="n">
-        <v>128.6931838265533</v>
+        <v>128.6931984652328</v>
       </c>
       <c r="E477" t="n">
-        <v>134.6512013157082</v>
+        <v>134.6512166321043</v>
       </c>
       <c r="F477" t="n">
         <v>909700</v>
@@ -10032,16 +10032,16 @@
         <v>43924</v>
       </c>
       <c r="B481" t="n">
-        <v>112.4575881958008</v>
+        <v>112.4575958251953</v>
       </c>
       <c r="C481" t="n">
-        <v>121.3946150722883</v>
+        <v>121.3946233079923</v>
       </c>
       <c r="D481" t="n">
-        <v>109.1508864332576</v>
+        <v>109.1508938383175</v>
       </c>
       <c r="E481" t="n">
-        <v>121.2456631091445</v>
+        <v>121.2456713347432</v>
       </c>
       <c r="F481" t="n">
         <v>1289233</v>
@@ -10072,16 +10072,16 @@
         <v>43928</v>
       </c>
       <c r="B483" t="n">
-        <v>143.8861541748047</v>
+        <v>143.8861236572266</v>
       </c>
       <c r="C483" t="n">
-        <v>154.9084954917595</v>
+        <v>154.9084626363945</v>
       </c>
       <c r="D483" t="n">
-        <v>138.0175169188297</v>
+        <v>138.017487645962</v>
       </c>
       <c r="E483" t="n">
-        <v>145.1969256403997</v>
+        <v>145.1968948448132</v>
       </c>
       <c r="F483" t="n">
         <v>1844300</v>
@@ -10112,16 +10112,16 @@
         <v>43930</v>
       </c>
       <c r="B485" t="n">
-        <v>145.5544128417969</v>
+        <v>145.5543975830078</v>
       </c>
       <c r="C485" t="n">
-        <v>153.0913035951916</v>
+        <v>153.0912875462937</v>
       </c>
       <c r="D485" t="n">
-        <v>144.4223897845756</v>
+        <v>144.422374644459</v>
       </c>
       <c r="E485" t="n">
-        <v>150.4995646020763</v>
+        <v>150.4995488248761</v>
       </c>
       <c r="F485" t="n">
         <v>918500</v>
@@ -10132,16 +10132,16 @@
         <v>43934</v>
       </c>
       <c r="B486" t="n">
-        <v>146.2395629882812</v>
+        <v>146.2395782470703</v>
       </c>
       <c r="C486" t="n">
-        <v>151.3038694372525</v>
+        <v>151.3038852244566</v>
       </c>
       <c r="D486" t="n">
-        <v>140.6390264087451</v>
+        <v>140.6390410831683</v>
       </c>
       <c r="E486" t="n">
-        <v>142.6647459579288</v>
+        <v>142.6647608437177</v>
       </c>
       <c r="F486" t="n">
         <v>651233</v>
@@ -10172,16 +10172,16 @@
         <v>43936</v>
       </c>
       <c r="B488" t="n">
-        <v>155.0574035644531</v>
+        <v>155.0574188232422</v>
       </c>
       <c r="C488" t="n">
-        <v>160.8068990923668</v>
+        <v>160.8069149169485</v>
       </c>
       <c r="D488" t="n">
-        <v>148.086533810641</v>
+        <v>148.0865483834452</v>
       </c>
       <c r="E488" t="n">
-        <v>154.6105552702891</v>
+        <v>154.610570485105</v>
       </c>
       <c r="F488" t="n">
         <v>821233</v>
@@ -10232,16 +10232,16 @@
         <v>43941</v>
       </c>
       <c r="B491" t="n">
-        <v>161.0750122070312</v>
+        <v>161.0750274658203</v>
       </c>
       <c r="C491" t="n">
-        <v>165.9308115454324</v>
+        <v>165.930827264216</v>
       </c>
       <c r="D491" t="n">
-        <v>150.7378622318755</v>
+        <v>150.7378765114165</v>
       </c>
       <c r="E491" t="n">
-        <v>151.9294628315219</v>
+        <v>151.9294772239444</v>
       </c>
       <c r="F491" t="n">
         <v>652266</v>
@@ -10252,16 +10252,16 @@
         <v>43943</v>
       </c>
       <c r="B492" t="n">
-        <v>158.8109741210938</v>
+        <v>158.8109588623047</v>
       </c>
       <c r="C492" t="n">
-        <v>166.8245161896017</v>
+        <v>166.8245001608599</v>
       </c>
       <c r="D492" t="n">
-        <v>157.6193734644301</v>
+        <v>157.6193583201317</v>
       </c>
       <c r="E492" t="n">
-        <v>166.8245161896017</v>
+        <v>166.8245001608599</v>
       </c>
       <c r="F492" t="n">
         <v>2119233</v>
@@ -10272,16 +10272,16 @@
         <v>43944</v>
       </c>
       <c r="B493" t="n">
-        <v>151.8401031494141</v>
+        <v>151.840087890625</v>
       </c>
       <c r="C493" t="n">
-        <v>160.8664974239381</v>
+        <v>160.8664812580642</v>
       </c>
       <c r="D493" t="n">
-        <v>144.8096395919027</v>
+        <v>144.8096250396224</v>
       </c>
       <c r="E493" t="n">
-        <v>159.8238411694891</v>
+        <v>159.8238251083944</v>
       </c>
       <c r="F493" t="n">
         <v>1242300</v>
@@ -10312,16 +10312,16 @@
         <v>43948</v>
       </c>
       <c r="B495" t="n">
-        <v>156.9639892578125</v>
+        <v>156.9639739990234</v>
       </c>
       <c r="C495" t="n">
-        <v>157.9172788832115</v>
+        <v>157.9172635317512</v>
       </c>
       <c r="D495" t="n">
-        <v>152.8231682250355</v>
+        <v>152.8231533687841</v>
       </c>
       <c r="E495" t="n">
-        <v>153.8658244913087</v>
+        <v>153.8658095336986</v>
       </c>
       <c r="F495" t="n">
         <v>935633</v>
@@ -10332,16 +10332,16 @@
         <v>43949</v>
       </c>
       <c r="B496" t="n">
-        <v>159.138671875</v>
+        <v>159.1386871337891</v>
       </c>
       <c r="C496" t="n">
-        <v>166.1989245453164</v>
+        <v>166.198940481068</v>
       </c>
       <c r="D496" t="n">
-        <v>157.8874934196113</v>
+        <v>157.8875085584328</v>
       </c>
       <c r="E496" t="n">
-        <v>157.8874934196113</v>
+        <v>157.8875085584328</v>
       </c>
       <c r="F496" t="n">
         <v>787066</v>
@@ -10352,16 +10352,16 @@
         <v>43950</v>
       </c>
       <c r="B497" t="n">
-        <v>161.9591369628906</v>
+        <v>161.9591217041016</v>
       </c>
       <c r="C497" t="n">
-        <v>164.790060292696</v>
+        <v>164.7900447671948</v>
       </c>
       <c r="D497" t="n">
-        <v>159.7241903125012</v>
+        <v>159.724175264275</v>
       </c>
       <c r="E497" t="n">
-        <v>161.3631451267727</v>
+        <v>161.3631299241343</v>
       </c>
       <c r="F497" t="n">
         <v>594666</v>
@@ -10392,16 +10392,16 @@
         <v>43955</v>
       </c>
       <c r="B499" t="n">
-        <v>152.4531402587891</v>
+        <v>152.4531707763672</v>
       </c>
       <c r="C499" t="n">
-        <v>152.8107322907865</v>
+        <v>152.8107628799463</v>
       </c>
       <c r="D499" t="n">
-        <v>147.5660592592903</v>
+        <v>147.5660887985883</v>
       </c>
       <c r="E499" t="n">
-        <v>148.5494411364585</v>
+        <v>148.5494708726067</v>
       </c>
       <c r="F499" t="n">
         <v>865433</v>
@@ -10412,16 +10412,16 @@
         <v>43956</v>
       </c>
       <c r="B500" t="n">
-        <v>154.6582946777344</v>
+        <v>154.6583099365234</v>
       </c>
       <c r="C500" t="n">
-        <v>157.6382233426491</v>
+        <v>157.6382388954418</v>
       </c>
       <c r="D500" t="n">
-        <v>151.4101681891011</v>
+        <v>151.4101831274257</v>
       </c>
       <c r="E500" t="n">
-        <v>153.615316613674</v>
+        <v>153.6153317695615</v>
       </c>
       <c r="F500" t="n">
         <v>670733</v>
@@ -10432,16 +10432,16 @@
         <v>43957</v>
       </c>
       <c r="B501" t="n">
-        <v>155.5820617675781</v>
+        <v>155.5820770263672</v>
       </c>
       <c r="C501" t="n">
-        <v>160.2009445810146</v>
+        <v>160.2009602928029</v>
       </c>
       <c r="D501" t="n">
-        <v>150.3075759322569</v>
+        <v>150.3075906737481</v>
       </c>
       <c r="E501" t="n">
-        <v>155.2840659055211</v>
+        <v>155.2840811350841</v>
       </c>
       <c r="F501" t="n">
         <v>746233</v>
@@ -10452,16 +10452,16 @@
         <v>43958</v>
       </c>
       <c r="B502" t="n">
-        <v>158.7109832763672</v>
+        <v>158.7110137939453</v>
       </c>
       <c r="C502" t="n">
-        <v>165.0880281493818</v>
+        <v>165.0880598931634</v>
       </c>
       <c r="D502" t="n">
-        <v>156.9826193707709</v>
+        <v>156.9826495560124</v>
       </c>
       <c r="E502" t="n">
-        <v>157.9660011862015</v>
+        <v>157.9660315605315</v>
       </c>
       <c r="F502" t="n">
         <v>1272300</v>
@@ -10532,16 +10532,16 @@
         <v>43964</v>
       </c>
       <c r="B506" t="n">
-        <v>145.7780914306641</v>
+        <v>145.7781066894531</v>
       </c>
       <c r="C506" t="n">
-        <v>153.943096434504</v>
+        <v>153.9431125479351</v>
       </c>
       <c r="D506" t="n">
-        <v>145.7780914306641</v>
+        <v>145.7781066894531</v>
       </c>
       <c r="E506" t="n">
-        <v>152.304141882141</v>
+        <v>152.3041578240206</v>
       </c>
       <c r="F506" t="n">
         <v>632666</v>
@@ -10552,16 +10552,16 @@
         <v>43965</v>
       </c>
       <c r="B507" t="n">
-        <v>141.2784118652344</v>
+        <v>141.2784271240234</v>
       </c>
       <c r="C507" t="n">
-        <v>147.5064669352663</v>
+        <v>147.5064828667171</v>
       </c>
       <c r="D507" t="n">
-        <v>138.3580793877065</v>
+        <v>138.3580943310847</v>
       </c>
       <c r="E507" t="n">
-        <v>145.6589105815262</v>
+        <v>145.6589263134315</v>
       </c>
       <c r="F507" t="n">
         <v>844800</v>
@@ -10572,16 +10572,16 @@
         <v>43966</v>
       </c>
       <c r="B508" t="n">
-        <v>139.7586364746094</v>
+        <v>139.7586669921875</v>
       </c>
       <c r="C508" t="n">
-        <v>143.5431430510845</v>
+        <v>143.5431743950443</v>
       </c>
       <c r="D508" t="n">
-        <v>134.9907480869898</v>
+        <v>134.9907775634558</v>
       </c>
       <c r="E508" t="n">
-        <v>140.3248301358833</v>
+        <v>140.324860777095</v>
       </c>
       <c r="F508" t="n">
         <v>930266</v>
@@ -10592,16 +10592,16 @@
         <v>43969</v>
       </c>
       <c r="B509" t="n">
-        <v>147.6256713867188</v>
+        <v>147.6256561279297</v>
       </c>
       <c r="C509" t="n">
-        <v>148.3408555281376</v>
+        <v>148.3408401954261</v>
       </c>
       <c r="D509" t="n">
-        <v>142.4405939397833</v>
+        <v>142.4405792169308</v>
       </c>
       <c r="E509" t="n">
-        <v>144.4967521355379</v>
+        <v>144.4967372001582</v>
       </c>
       <c r="F509" t="n">
         <v>822866</v>
@@ -10632,16 +10632,16 @@
         <v>43971</v>
       </c>
       <c r="B511" t="n">
-        <v>151.6783752441406</v>
+        <v>151.6783599853516</v>
       </c>
       <c r="C511" t="n">
-        <v>154.1815197188895</v>
+        <v>154.181504208285</v>
       </c>
       <c r="D511" t="n">
-        <v>149.3540343816533</v>
+        <v>149.3540193566921</v>
       </c>
       <c r="E511" t="n">
-        <v>150.7546045770118</v>
+        <v>150.7545894111537</v>
       </c>
       <c r="F511" t="n">
         <v>544933</v>
@@ -10652,16 +10652,16 @@
         <v>43972</v>
       </c>
       <c r="B512" t="n">
-        <v>156.1780548095703</v>
+        <v>156.1780395507812</v>
       </c>
       <c r="C512" t="n">
-        <v>158.6811990955166</v>
+        <v>158.6811835921673</v>
       </c>
       <c r="D512" t="n">
-        <v>146.1952908961648</v>
+        <v>146.1952766127041</v>
       </c>
       <c r="E512" t="n">
-        <v>152.1253500655098</v>
+        <v>152.125335202675</v>
       </c>
       <c r="F512" t="n">
         <v>1784500</v>
@@ -10672,16 +10672,16 @@
         <v>43973</v>
       </c>
       <c r="B513" t="n">
-        <v>155.5522766113281</v>
+        <v>155.5522918701172</v>
       </c>
       <c r="C513" t="n">
-        <v>156.9528315128846</v>
+        <v>156.95284690906</v>
       </c>
       <c r="D513" t="n">
-        <v>153.4067244144283</v>
+        <v>153.406739462751</v>
       </c>
       <c r="E513" t="n">
-        <v>156.4462491150195</v>
+        <v>156.4462644615022</v>
       </c>
       <c r="F513" t="n">
         <v>725600</v>
@@ -10692,16 +10692,16 @@
         <v>43976</v>
       </c>
       <c r="B514" t="n">
-        <v>161.6313629150391</v>
+        <v>161.6313171386719</v>
       </c>
       <c r="C514" t="n">
-        <v>162.6147298622749</v>
+        <v>162.6146838074038</v>
       </c>
       <c r="D514" t="n">
-        <v>157.4296669376675</v>
+        <v>157.4296223512821</v>
       </c>
       <c r="E514" t="n">
-        <v>157.9660475310048</v>
+        <v>157.9660027927086</v>
       </c>
       <c r="F514" t="n">
         <v>561666</v>
@@ -10712,16 +10712,16 @@
         <v>43977</v>
       </c>
       <c r="B515" t="n">
-        <v>163.3298797607422</v>
+        <v>163.3298950195312</v>
       </c>
       <c r="C515" t="n">
-        <v>164.9092534423791</v>
+        <v>164.9092688487182</v>
       </c>
       <c r="D515" t="n">
-        <v>160.945942936563</v>
+        <v>160.9459579726372</v>
       </c>
       <c r="E515" t="n">
-        <v>164.9092534423791</v>
+        <v>164.9092688487182</v>
       </c>
       <c r="F515" t="n">
         <v>734300</v>
@@ -10752,16 +10752,16 @@
         <v>43979</v>
       </c>
       <c r="B517" t="n">
-        <v>163.9258728027344</v>
+        <v>163.9258575439453</v>
       </c>
       <c r="C517" t="n">
-        <v>168.0679717816257</v>
+        <v>168.0679561372757</v>
       </c>
       <c r="D517" t="n">
-        <v>161.3333342871174</v>
+        <v>161.3333192696508</v>
       </c>
       <c r="E517" t="n">
-        <v>163.4490884655809</v>
+        <v>163.4490732511726</v>
       </c>
       <c r="F517" t="n">
         <v>560100</v>
@@ -10832,16 +10832,16 @@
         <v>43985</v>
       </c>
       <c r="B521" t="n">
-        <v>172.98486328125</v>
+        <v>172.9848480224609</v>
       </c>
       <c r="C521" t="n">
-        <v>173.7298454920335</v>
+        <v>173.7298301675305</v>
       </c>
       <c r="D521" t="n">
-        <v>163.3000945410644</v>
+        <v>163.3000801365573</v>
       </c>
       <c r="E521" t="n">
-        <v>163.8960863723719</v>
+        <v>163.8960719152931</v>
       </c>
       <c r="F521" t="n">
         <v>1327400</v>
@@ -10852,16 +10852,16 @@
         <v>43986</v>
       </c>
       <c r="B522" t="n">
-        <v>174.8026275634766</v>
+        <v>174.8026123046875</v>
       </c>
       <c r="C522" t="n">
-        <v>176.9779781170755</v>
+        <v>176.9779626683967</v>
       </c>
       <c r="D522" t="n">
-        <v>169.7963536078713</v>
+        <v>169.7963387860876</v>
       </c>
       <c r="E522" t="n">
-        <v>174.6238391021025</v>
+        <v>174.6238238589201</v>
       </c>
       <c r="F522" t="n">
         <v>1106633</v>
@@ -10872,16 +10872,16 @@
         <v>43987</v>
       </c>
       <c r="B523" t="n">
-        <v>177.4547271728516</v>
+        <v>177.4547576904297</v>
       </c>
       <c r="C523" t="n">
-        <v>182.371621075518</v>
+        <v>182.3716524386734</v>
       </c>
       <c r="D523" t="n">
-        <v>175.1005886265878</v>
+        <v>175.1006187393156</v>
       </c>
       <c r="E523" t="n">
-        <v>178.7957009929787</v>
+        <v>178.7957317411692</v>
       </c>
       <c r="F523" t="n">
         <v>929700</v>
@@ -10892,16 +10892,16 @@
         <v>43990</v>
       </c>
       <c r="B524" t="n">
-        <v>181.9842224121094</v>
+        <v>181.9842376708984</v>
       </c>
       <c r="C524" t="n">
-        <v>184.1893706831995</v>
+        <v>184.1893861268831</v>
       </c>
       <c r="D524" t="n">
-        <v>176.3521594462279</v>
+        <v>176.3521742327868</v>
       </c>
       <c r="E524" t="n">
-        <v>178.2891250689665</v>
+        <v>178.2891400179336</v>
       </c>
       <c r="F524" t="n">
         <v>540433</v>
@@ -10932,16 +10932,16 @@
         <v>43992</v>
       </c>
       <c r="B526" t="n">
-        <v>180.8518829345703</v>
+        <v>180.8518676757812</v>
       </c>
       <c r="C526" t="n">
-        <v>183.5636292344882</v>
+        <v>183.5636137469044</v>
       </c>
       <c r="D526" t="n">
-        <v>178.4977438772397</v>
+        <v>178.4977288170735</v>
       </c>
       <c r="E526" t="n">
-        <v>181.4180767191804</v>
+        <v>181.4180614126206</v>
       </c>
       <c r="F526" t="n">
         <v>715466</v>
@@ -10992,16 +10992,16 @@
         <v>43998</v>
       </c>
       <c r="B529" t="n">
-        <v>179.8386993408203</v>
+        <v>179.8387145996094</v>
       </c>
       <c r="C529" t="n">
-        <v>186.6627311857664</v>
+        <v>186.6627470235547</v>
       </c>
       <c r="D529" t="n">
-        <v>177.1269533220862</v>
+        <v>177.1269683507915</v>
       </c>
       <c r="E529" t="n">
-        <v>183.5934082749279</v>
+        <v>183.5934238522931</v>
       </c>
       <c r="F529" t="n">
         <v>733633</v>
@@ -11012,16 +11012,16 @@
         <v>43999</v>
       </c>
       <c r="B530" t="n">
-        <v>181.2392425537109</v>
+        <v>181.2392730712891</v>
       </c>
       <c r="C530" t="n">
-        <v>186.066727321228</v>
+        <v>186.0667586516717</v>
       </c>
       <c r="D530" t="n">
-        <v>180.6134678764014</v>
+        <v>180.6134982886098</v>
       </c>
       <c r="E530" t="n">
-        <v>182.0438359788805</v>
+        <v>182.0438666319384</v>
       </c>
       <c r="F530" t="n">
         <v>934766</v>
@@ -11052,16 +11052,16 @@
         <v>44001</v>
       </c>
       <c r="B532" t="n">
-        <v>187.1693115234375</v>
+        <v>187.1693267822266</v>
       </c>
       <c r="C532" t="n">
-        <v>190.1194421040784</v>
+        <v>190.1194576033739</v>
       </c>
       <c r="D532" t="n">
-        <v>181.0306657700721</v>
+        <v>181.0306805284143</v>
       </c>
       <c r="E532" t="n">
-        <v>181.7756479337349</v>
+        <v>181.775662752811</v>
       </c>
       <c r="F532" t="n">
         <v>2381566</v>
@@ -11112,16 +11112,16 @@
         <v>44006</v>
       </c>
       <c r="B535" t="n">
-        <v>180.9114837646484</v>
+        <v>180.9114685058594</v>
       </c>
       <c r="C535" t="n">
-        <v>188.569892354976</v>
+        <v>188.5698764502466</v>
       </c>
       <c r="D535" t="n">
-        <v>180.9114837646484</v>
+        <v>180.9114685058594</v>
       </c>
       <c r="E535" t="n">
-        <v>185.1131791628317</v>
+        <v>185.1131635496551</v>
       </c>
       <c r="F535" t="n">
         <v>509333</v>
@@ -11132,16 +11132,16 @@
         <v>44007</v>
       </c>
       <c r="B536" t="n">
-        <v>184.9939880371094</v>
+        <v>184.9939727783203</v>
       </c>
       <c r="C536" t="n">
-        <v>185.7687683237836</v>
+        <v>185.7687530010886</v>
       </c>
       <c r="D536" t="n">
-        <v>180.017497168815</v>
+        <v>180.0174823204999</v>
       </c>
       <c r="E536" t="n">
-        <v>182.0736553457825</v>
+        <v>182.0736403278702</v>
       </c>
       <c r="F536" t="n">
         <v>496966</v>
@@ -11192,16 +11192,16 @@
         <v>44012</v>
       </c>
       <c r="B539" t="n">
-        <v>185.2621612548828</v>
+        <v>185.2621765136719</v>
       </c>
       <c r="C539" t="n">
-        <v>190.7154362155846</v>
+        <v>190.7154519235229</v>
       </c>
       <c r="D539" t="n">
-        <v>184.3979867846753</v>
+        <v>184.3980019722882</v>
       </c>
       <c r="E539" t="n">
-        <v>186.9309292032538</v>
+        <v>186.9309445994879</v>
       </c>
       <c r="F539" t="n">
         <v>688100</v>
@@ -11212,16 +11212,16 @@
         <v>44013</v>
       </c>
       <c r="B540" t="n">
-        <v>187.7057037353516</v>
+        <v>187.7057189941406</v>
       </c>
       <c r="C540" t="n">
-        <v>189.9108521119912</v>
+        <v>189.910867550039</v>
       </c>
       <c r="D540" t="n">
-        <v>185.2323575408232</v>
+        <v>185.2323725985514</v>
       </c>
       <c r="E540" t="n">
-        <v>185.7985512500661</v>
+        <v>185.7985663538207</v>
       </c>
       <c r="F540" t="n">
         <v>601100</v>
@@ -11232,16 +11232,16 @@
         <v>44014</v>
       </c>
       <c r="B541" t="n">
-        <v>180.9710693359375</v>
+        <v>180.9710845947266</v>
       </c>
       <c r="C541" t="n">
-        <v>190.5366299956888</v>
+        <v>190.5366460610093</v>
       </c>
       <c r="D541" t="n">
-        <v>179.9876874250449</v>
+        <v>179.987702600919</v>
       </c>
       <c r="E541" t="n">
-        <v>190.1492398774646</v>
+        <v>190.1492559101219</v>
       </c>
       <c r="F541" t="n">
         <v>782133</v>
@@ -11252,16 +11252,16 @@
         <v>44015</v>
       </c>
       <c r="B542" t="n">
-        <v>181.5074462890625</v>
+        <v>181.5074615478516</v>
       </c>
       <c r="C542" t="n">
-        <v>184.4575768075846</v>
+        <v>184.4575923143823</v>
       </c>
       <c r="D542" t="n">
-        <v>178.0805314397118</v>
+        <v>178.0805464104103</v>
       </c>
       <c r="E542" t="n">
-        <v>179.3917072953663</v>
+        <v>179.3917223762915</v>
       </c>
       <c r="F542" t="n">
         <v>277066</v>
@@ -11292,16 +11292,16 @@
         <v>44019</v>
       </c>
       <c r="B544" t="n">
-        <v>178.646728515625</v>
+        <v>178.6467437744141</v>
       </c>
       <c r="C544" t="n">
-        <v>182.8186255916096</v>
+        <v>182.8186412067338</v>
       </c>
       <c r="D544" t="n">
-        <v>177.8421350490122</v>
+        <v>177.8421502390783</v>
       </c>
       <c r="E544" t="n">
-        <v>178.7957188853491</v>
+        <v>178.7957341568639</v>
       </c>
       <c r="F544" t="n">
         <v>1026966</v>
@@ -11332,16 +11332,16 @@
         <v>44021</v>
       </c>
       <c r="B546" t="n">
-        <v>178.5871276855469</v>
+        <v>178.5871124267578</v>
       </c>
       <c r="C546" t="n">
-        <v>182.7888382386164</v>
+        <v>182.788822620826</v>
       </c>
       <c r="D546" t="n">
-        <v>178.5871276855469</v>
+        <v>178.5871124267578</v>
       </c>
       <c r="E546" t="n">
-        <v>179.510913502121</v>
+        <v>179.5108981644021</v>
       </c>
       <c r="F546" t="n">
         <v>527966</v>
@@ -11352,16 +11352,16 @@
         <v>44022</v>
       </c>
       <c r="B547" t="n">
-        <v>180.1963043212891</v>
+        <v>180.1962890625</v>
       </c>
       <c r="C547" t="n">
-        <v>181.0604788526272</v>
+        <v>181.060463520661</v>
       </c>
       <c r="D547" t="n">
-        <v>177.9315595685599</v>
+        <v>177.9315445015465</v>
       </c>
       <c r="E547" t="n">
-        <v>178.8255321763785</v>
+        <v>178.8255170336646</v>
       </c>
       <c r="F547" t="n">
         <v>618666</v>
@@ -11392,16 +11392,16 @@
         <v>44026</v>
       </c>
       <c r="B549" t="n">
-        <v>178.4679260253906</v>
+        <v>178.4679412841797</v>
       </c>
       <c r="C549" t="n">
-        <v>179.212908192047</v>
+        <v>179.2129235145311</v>
       </c>
       <c r="D549" t="n">
-        <v>173.2828489329264</v>
+        <v>173.2828637483977</v>
       </c>
       <c r="E549" t="n">
-        <v>175.0708091642418</v>
+        <v>175.0708241325815</v>
       </c>
       <c r="F549" t="n">
         <v>493066</v>
@@ -11412,16 +11412,16 @@
         <v>44027</v>
       </c>
       <c r="B550" t="n">
-        <v>180.6730651855469</v>
+        <v>180.6730804443359</v>
       </c>
       <c r="C550" t="n">
-        <v>184.7257697831216</v>
+        <v>184.7257853841829</v>
       </c>
       <c r="D550" t="n">
-        <v>178.9744992637316</v>
+        <v>178.9745143790679</v>
       </c>
       <c r="E550" t="n">
-        <v>180.5836709677409</v>
+        <v>180.5836862189801</v>
       </c>
       <c r="F550" t="n">
         <v>693400</v>
@@ -11432,16 +11432,16 @@
         <v>44028</v>
       </c>
       <c r="B551" t="n">
-        <v>181.3882446289062</v>
+        <v>181.3882751464844</v>
       </c>
       <c r="C551" t="n">
-        <v>183.1166085793732</v>
+        <v>183.1166393877391</v>
       </c>
       <c r="D551" t="n">
-        <v>178.3487200471918</v>
+        <v>178.3487500533865</v>
       </c>
       <c r="E551" t="n">
-        <v>181.8054327914259</v>
+        <v>181.8054633791936</v>
       </c>
       <c r="F551" t="n">
         <v>439600</v>
@@ -11452,16 +11452,16 @@
         <v>44029</v>
       </c>
       <c r="B552" t="n">
-        <v>190.1492462158203</v>
+        <v>190.1492309570312</v>
       </c>
       <c r="C552" t="n">
-        <v>190.1492462158203</v>
+        <v>190.1492309570312</v>
       </c>
       <c r="D552" t="n">
-        <v>181.3882635744458</v>
+        <v>181.3882490186939</v>
       </c>
       <c r="E552" t="n">
-        <v>181.3882635744458</v>
+        <v>181.3882490186939</v>
       </c>
       <c r="F552" t="n">
         <v>595900</v>
@@ -11472,16 +11472,16 @@
         <v>44032</v>
       </c>
       <c r="B553" t="n">
-        <v>196.0196990966797</v>
+        <v>196.0197143554688</v>
       </c>
       <c r="C553" t="n">
-        <v>197.7778612094101</v>
+        <v>197.77787660506</v>
       </c>
       <c r="D553" t="n">
-        <v>189.1956674727965</v>
+        <v>189.1956822003815</v>
       </c>
       <c r="E553" t="n">
-        <v>190.7154298418124</v>
+        <v>190.7154446877005</v>
       </c>
       <c r="F553" t="n">
         <v>643066</v>
@@ -11512,16 +11512,16 @@
         <v>44034</v>
       </c>
       <c r="B555" t="n">
-        <v>193.9933624267578</v>
+        <v>193.9933471679688</v>
       </c>
       <c r="C555" t="n">
-        <v>197.926859843797</v>
+        <v>197.9268442756138</v>
       </c>
       <c r="D555" t="n">
-        <v>191.4306219124074</v>
+        <v>191.4306068551939</v>
       </c>
       <c r="E555" t="n">
-        <v>195.2151289563396</v>
+        <v>195.2151136014509</v>
       </c>
       <c r="F555" t="n">
         <v>664000</v>
@@ -11532,16 +11532,16 @@
         <v>44035</v>
       </c>
       <c r="B556" t="n">
-        <v>191.6392059326172</v>
+        <v>191.6392211914062</v>
       </c>
       <c r="C556" t="n">
-        <v>196.6752926716999</v>
+        <v>196.6753083314747</v>
       </c>
       <c r="D556" t="n">
-        <v>190.0002512230334</v>
+        <v>190.0002663513249</v>
       </c>
       <c r="E556" t="n">
-        <v>194.8277362857887</v>
+        <v>194.8277517984564</v>
       </c>
       <c r="F556" t="n">
         <v>517766</v>
@@ -11552,16 +11552,16 @@
         <v>44036</v>
       </c>
       <c r="B557" t="n">
-        <v>195.7515258789062</v>
+        <v>195.7515106201172</v>
       </c>
       <c r="C557" t="n">
-        <v>196.0793198839435</v>
+        <v>196.079304599603</v>
       </c>
       <c r="D557" t="n">
-        <v>188.0335207704287</v>
+        <v>188.0335061132565</v>
       </c>
       <c r="E557" t="n">
-        <v>192.7120007589094</v>
+        <v>192.7119857370506</v>
       </c>
       <c r="F557" t="n">
         <v>615366</v>
@@ -11592,16 +11592,16 @@
         <v>44040</v>
       </c>
       <c r="B559" t="n">
-        <v>194.2317504882812</v>
+        <v>194.2317657470703</v>
       </c>
       <c r="C559" t="n">
-        <v>195.9005184803528</v>
+        <v>195.9005338702399</v>
       </c>
       <c r="D559" t="n">
-        <v>188.7188943911681</v>
+        <v>188.7189092168689</v>
       </c>
       <c r="E559" t="n">
-        <v>190.715441209922</v>
+        <v>190.7154561924708</v>
       </c>
       <c r="F559" t="n">
         <v>415300</v>
@@ -11632,16 +11632,16 @@
         <v>44042</v>
       </c>
       <c r="B561" t="n">
-        <v>197.2712860107422</v>
+        <v>197.2712707519531</v>
       </c>
       <c r="C561" t="n">
-        <v>200.0724111073721</v>
+        <v>200.072395631918</v>
       </c>
       <c r="D561" t="n">
-        <v>193.0993737052108</v>
+        <v>193.0993587691161</v>
       </c>
       <c r="E561" t="n">
-        <v>194.8873339566241</v>
+        <v>194.887318882232</v>
       </c>
       <c r="F561" t="n">
         <v>388133</v>
@@ -11652,16 +11652,16 @@
         <v>44043</v>
       </c>
       <c r="B562" t="n">
-        <v>194.112548828125</v>
+        <v>194.1125335693359</v>
       </c>
       <c r="C562" t="n">
-        <v>199.8936176362711</v>
+        <v>199.8936019230441</v>
       </c>
       <c r="D562" t="n">
-        <v>191.8180062117766</v>
+        <v>191.8179911333568</v>
       </c>
       <c r="E562" t="n">
-        <v>197.5692617895057</v>
+        <v>197.5692462589916</v>
       </c>
       <c r="F562" t="n">
         <v>964966</v>
@@ -11692,16 +11692,16 @@
         <v>44047</v>
       </c>
       <c r="B564" t="n">
-        <v>191.1922149658203</v>
+        <v>191.1922454833984</v>
       </c>
       <c r="C564" t="n">
-        <v>194.7979334263718</v>
+        <v>194.7979645194849</v>
       </c>
       <c r="D564" t="n">
-        <v>188.8976723660878</v>
+        <v>188.8977025174173</v>
       </c>
       <c r="E564" t="n">
-        <v>193.4271614185521</v>
+        <v>193.4271922928663</v>
       </c>
       <c r="F564" t="n">
         <v>411633</v>
@@ -11712,16 +11712,16 @@
         <v>44048</v>
       </c>
       <c r="B565" t="n">
-        <v>194.4999542236328</v>
+        <v>194.4999389648438</v>
       </c>
       <c r="C565" t="n">
-        <v>198.0758749175139</v>
+        <v>198.075859378189</v>
       </c>
       <c r="D565" t="n">
-        <v>193.0993840221375</v>
+        <v>193.0993688732251</v>
       </c>
       <c r="E565" t="n">
-        <v>193.3675818633541</v>
+        <v>193.3675666934012</v>
       </c>
       <c r="F565" t="n">
         <v>503800</v>
@@ -11732,16 +11732,16 @@
         <v>44049</v>
       </c>
       <c r="B566" t="n">
-        <v>197.4202728271484</v>
+        <v>197.4202880859375</v>
       </c>
       <c r="C566" t="n">
-        <v>198.6122412543873</v>
+        <v>198.6122566053047</v>
       </c>
       <c r="D566" t="n">
-        <v>194.7979362245427</v>
+        <v>194.797951280649</v>
       </c>
       <c r="E566" t="n">
-        <v>194.7979362245427</v>
+        <v>194.797951280649</v>
       </c>
       <c r="F566" t="n">
         <v>434133</v>
@@ -11772,16 +11772,16 @@
         <v>44053</v>
       </c>
       <c r="B568" t="n">
-        <v>191.9073944091797</v>
+        <v>191.9074096679688</v>
       </c>
       <c r="C568" t="n">
-        <v>197.0030770485053</v>
+        <v>197.0030927124582</v>
       </c>
       <c r="D568" t="n">
-        <v>191.0432199851351</v>
+        <v>191.0432351752126</v>
       </c>
       <c r="E568" t="n">
-        <v>195.3641072620583</v>
+        <v>195.3641227956948</v>
       </c>
       <c r="F568" t="n">
         <v>446333</v>
@@ -11792,16 +11792,16 @@
         <v>44054</v>
       </c>
       <c r="B569" t="n">
-        <v>186.9309387207031</v>
+        <v>186.9309234619141</v>
       </c>
       <c r="C569" t="n">
-        <v>193.54638438886</v>
+        <v>193.5463685900656</v>
       </c>
       <c r="D569" t="n">
-        <v>186.4243411171737</v>
+        <v>186.4243258997372</v>
       </c>
       <c r="E569" t="n">
-        <v>193.0099887094408</v>
+        <v>193.0099729544314</v>
       </c>
       <c r="F569" t="n">
         <v>865000</v>
@@ -11812,16 +11812,16 @@
         <v>44055</v>
       </c>
       <c r="B570" t="n">
-        <v>182.6994171142578</v>
+        <v>182.6994018554688</v>
       </c>
       <c r="C570" t="n">
-        <v>189.2552661659586</v>
+        <v>189.2552503596345</v>
       </c>
       <c r="D570" t="n">
-        <v>179.2427041457414</v>
+        <v>179.242689175652</v>
       </c>
       <c r="E570" t="n">
-        <v>186.7521218717291</v>
+        <v>186.752106274464</v>
       </c>
       <c r="F570" t="n">
         <v>1065533</v>
@@ -11832,16 +11832,16 @@
         <v>44056</v>
       </c>
       <c r="B571" t="n">
-        <v>186.5733489990234</v>
+        <v>186.5733184814453</v>
       </c>
       <c r="C571" t="n">
-        <v>190.9240348573458</v>
+        <v>190.9240036281312</v>
       </c>
       <c r="D571" t="n">
-        <v>184.6363982583284</v>
+        <v>184.6363680575749</v>
       </c>
       <c r="E571" t="n">
-        <v>184.844984792179</v>
+        <v>184.8449545573073</v>
       </c>
       <c r="F571" t="n">
         <v>646800</v>
@@ -11852,16 +11852,16 @@
         <v>44057</v>
       </c>
       <c r="B572" t="n">
-        <v>191.0730133056641</v>
+        <v>191.0730438232422</v>
       </c>
       <c r="C572" t="n">
-        <v>193.0993579878638</v>
+        <v>193.0993888290833</v>
       </c>
       <c r="D572" t="n">
-        <v>187.0799049286441</v>
+        <v>187.0799348084556</v>
       </c>
       <c r="E572" t="n">
-        <v>188.7784708184071</v>
+        <v>188.7785009695081</v>
       </c>
       <c r="F572" t="n">
         <v>670600</v>
@@ -11892,16 +11892,16 @@
         <v>44061</v>
       </c>
       <c r="B574" t="n">
-        <v>187.5268859863281</v>
+        <v>187.5269012451172</v>
       </c>
       <c r="C574" t="n">
-        <v>190.3876220767241</v>
+        <v>190.3876375682871</v>
       </c>
       <c r="D574" t="n">
-        <v>186.0965330978296</v>
+        <v>186.096548240233</v>
       </c>
       <c r="E574" t="n">
-        <v>187.9738873679771</v>
+        <v>187.973902663138</v>
       </c>
       <c r="F574" t="n">
         <v>544533</v>
@@ -11952,16 +11952,16 @@
         <v>44064</v>
       </c>
       <c r="B577" t="n">
-        <v>186.5733489990234</v>
+        <v>186.5733184814453</v>
       </c>
       <c r="C577" t="n">
-        <v>188.1229095915795</v>
+        <v>188.1228788205416</v>
       </c>
       <c r="D577" t="n">
-        <v>182.908034051484</v>
+        <v>182.9080041334369</v>
       </c>
       <c r="E577" t="n">
-        <v>184.7555905633859</v>
+        <v>184.7555603431363</v>
       </c>
       <c r="F577" t="n">
         <v>431666</v>
@@ -11972,16 +11972,16 @@
         <v>44067</v>
       </c>
       <c r="B578" t="n">
-        <v>185.2323760986328</v>
+        <v>185.2323608398438</v>
       </c>
       <c r="C578" t="n">
-        <v>187.8547129232111</v>
+        <v>187.8546974484032</v>
       </c>
       <c r="D578" t="n">
-        <v>182.8186409659118</v>
+        <v>182.8186259059577</v>
       </c>
       <c r="E578" t="n">
-        <v>186.8415480104824</v>
+        <v>186.8415326191354</v>
       </c>
       <c r="F578" t="n">
         <v>597533</v>
@@ -11992,16 +11992,16 @@
         <v>44068</v>
       </c>
       <c r="B579" t="n">
-        <v>186.2455291748047</v>
+        <v>186.2455444335938</v>
       </c>
       <c r="C579" t="n">
-        <v>189.0466540521098</v>
+        <v>189.0466695403904</v>
       </c>
       <c r="D579" t="n">
-        <v>184.4575690633866</v>
+        <v>184.457584175691</v>
       </c>
       <c r="E579" t="n">
-        <v>186.5137269806924</v>
+        <v>186.5137422614545</v>
       </c>
       <c r="F579" t="n">
         <v>543433</v>
@@ -12072,16 +12072,16 @@
         <v>44074</v>
       </c>
       <c r="B583" t="n">
-        <v>192.8907623291016</v>
+        <v>192.8907928466797</v>
       </c>
       <c r="C583" t="n">
-        <v>194.8873088445066</v>
+        <v>194.8873396779618</v>
       </c>
       <c r="D583" t="n">
-        <v>189.0466444947198</v>
+        <v>189.0466744041134</v>
       </c>
       <c r="E583" t="n">
-        <v>191.9967747402387</v>
+        <v>191.9968051163775</v>
       </c>
       <c r="F583" t="n">
         <v>944966</v>
@@ -12092,16 +12092,16 @@
         <v>44075</v>
       </c>
       <c r="B584" t="n">
-        <v>205.5852661132812</v>
+        <v>205.5852966308594</v>
       </c>
       <c r="C584" t="n">
-        <v>207.2838168514087</v>
+        <v>207.2838476211239</v>
       </c>
       <c r="D584" t="n">
-        <v>193.5463599589462</v>
+        <v>193.5463886894397</v>
       </c>
       <c r="E584" t="n">
-        <v>195.1853145528165</v>
+        <v>195.1853435266005</v>
       </c>
       <c r="F584" t="n">
         <v>1357600</v>
@@ -12132,16 +12132,16 @@
         <v>44077</v>
       </c>
       <c r="B586" t="n">
-        <v>199.3572082519531</v>
+        <v>199.3572387695312</v>
       </c>
       <c r="C586" t="n">
-        <v>204.6018810582302</v>
+        <v>204.6019123786623</v>
       </c>
       <c r="D586" t="n">
-        <v>196.5858814905054</v>
+        <v>196.5859115838492</v>
       </c>
       <c r="E586" t="n">
-        <v>202.0391407984153</v>
+        <v>202.0391717265434</v>
       </c>
       <c r="F586" t="n">
         <v>527733</v>
@@ -12152,16 +12152,16 @@
         <v>44078</v>
       </c>
       <c r="B587" t="n">
-        <v>197.8970642089844</v>
+        <v>197.8970794677734</v>
       </c>
       <c r="C587" t="n">
-        <v>203.1417376008307</v>
+        <v>203.1417532640086</v>
       </c>
       <c r="D587" t="n">
-        <v>194.6489376248939</v>
+        <v>194.6489526332372</v>
       </c>
       <c r="E587" t="n">
-        <v>200.2512182300084</v>
+        <v>200.2512336703138</v>
       </c>
       <c r="F587" t="n">
         <v>642700</v>
@@ -12192,16 +12192,16 @@
         <v>44083</v>
       </c>
       <c r="B589" t="n">
-        <v>203.4993133544922</v>
+        <v>203.4992980957031</v>
       </c>
       <c r="C589" t="n">
-        <v>204.6614836560544</v>
+        <v>204.6614683101234</v>
       </c>
       <c r="D589" t="n">
-        <v>196.7050799807286</v>
+        <v>196.7050652313848</v>
       </c>
       <c r="E589" t="n">
-        <v>202.3669411255316</v>
+        <v>202.3669259516501</v>
       </c>
       <c r="F589" t="n">
         <v>801100</v>
@@ -12232,16 +12232,16 @@
         <v>44085</v>
       </c>
       <c r="B591" t="n">
-        <v>189.7766265869141</v>
+        <v>189.776611328125</v>
       </c>
       <c r="C591" t="n">
-        <v>197.9303936359225</v>
+        <v>197.9303777215384</v>
       </c>
       <c r="D591" t="n">
-        <v>187.8053910426163</v>
+        <v>187.8053759423223</v>
       </c>
       <c r="E591" t="n">
-        <v>194.5852588258493</v>
+        <v>194.5852431804272</v>
       </c>
       <c r="F591" t="n">
         <v>1048366</v>
@@ -12252,16 +12252,16 @@
         <v>44088</v>
       </c>
       <c r="B592" t="n">
-        <v>197.1837158203125</v>
+        <v>197.1837005615234</v>
       </c>
       <c r="C592" t="n">
-        <v>199.1250853489015</v>
+        <v>199.1250699398823</v>
       </c>
       <c r="D592" t="n">
-        <v>190.0753061062856</v>
+        <v>190.075291397571</v>
       </c>
       <c r="E592" t="n">
-        <v>190.3441157921762</v>
+        <v>190.3441010626601</v>
       </c>
       <c r="F592" t="n">
         <v>434033</v>
@@ -12272,16 +12272,16 @@
         <v>44089</v>
       </c>
       <c r="B593" t="n">
-        <v>197.2733154296875</v>
+        <v>197.2733001708984</v>
       </c>
       <c r="C593" t="n">
-        <v>199.0653546966144</v>
+        <v>199.0653392992138</v>
       </c>
       <c r="D593" t="n">
-        <v>191.8076146546597</v>
+        <v>191.8075998186343</v>
       </c>
       <c r="E593" t="n">
-        <v>199.0056225862634</v>
+        <v>199.005607193483</v>
       </c>
       <c r="F593" t="n">
         <v>591666</v>
@@ -12372,16 +12372,16 @@
         <v>44096</v>
       </c>
       <c r="B598" t="n">
-        <v>187.7456665039062</v>
+        <v>187.7456359863281</v>
       </c>
       <c r="C598" t="n">
-        <v>189.0299524670994</v>
+        <v>189.0299217407639</v>
       </c>
       <c r="D598" t="n">
-        <v>185.147213330674</v>
+        <v>185.1471832354677</v>
       </c>
       <c r="E598" t="n">
-        <v>188.1339404175488</v>
+        <v>188.1339098368577</v>
       </c>
       <c r="F598" t="n">
         <v>344333</v>
@@ -12392,16 +12392,16 @@
         <v>44097</v>
       </c>
       <c r="B599" t="n">
-        <v>187.0885772705078</v>
+        <v>187.0885620117188</v>
       </c>
       <c r="C599" t="n">
-        <v>189.8961079395225</v>
+        <v>189.8960924517536</v>
       </c>
       <c r="D599" t="n">
-        <v>185.1770738153672</v>
+        <v>185.1770587124788</v>
       </c>
       <c r="E599" t="n">
-        <v>185.8640234552869</v>
+        <v>185.8640082963715</v>
       </c>
       <c r="F599" t="n">
         <v>596200</v>
@@ -12412,16 +12412,16 @@
         <v>44098</v>
       </c>
       <c r="B600" t="n">
-        <v>187.2677917480469</v>
+        <v>187.2677764892578</v>
       </c>
       <c r="C600" t="n">
-        <v>190.7921229760437</v>
+        <v>190.7921074300882</v>
       </c>
       <c r="D600" t="n">
-        <v>185.5354845935485</v>
+        <v>185.5354694759098</v>
       </c>
       <c r="E600" t="n">
-        <v>187.6560656561421</v>
+        <v>187.6560503657161</v>
       </c>
       <c r="F600" t="n">
         <v>378566</v>
@@ -12452,16 +12452,16 @@
         <v>44102</v>
       </c>
       <c r="B602" t="n">
-        <v>180.6372222900391</v>
+        <v>180.6372375488281</v>
       </c>
       <c r="C602" t="n">
-        <v>189.5078036968999</v>
+        <v>189.5078197050047</v>
       </c>
       <c r="D602" t="n">
-        <v>179.352921379823</v>
+        <v>179.3529365301246</v>
       </c>
       <c r="E602" t="n">
-        <v>188.9403183665075</v>
+        <v>188.9403343266758</v>
       </c>
       <c r="F602" t="n">
         <v>595500</v>
@@ -12472,16 +12472,16 @@
         <v>44103</v>
       </c>
       <c r="B603" t="n">
-        <v>180.9359283447266</v>
+        <v>180.9359130859375</v>
       </c>
       <c r="C603" t="n">
-        <v>183.5045002136614</v>
+        <v>183.5044847382582</v>
       </c>
       <c r="D603" t="n">
-        <v>178.6062697236995</v>
+        <v>178.6062546613765</v>
       </c>
       <c r="E603" t="n">
-        <v>181.2644549486086</v>
+        <v>181.2644396621141</v>
       </c>
       <c r="F603" t="n">
         <v>676133</v>
@@ -12492,16 +12492,16 @@
         <v>44104</v>
       </c>
       <c r="B604" t="n">
-        <v>185.59521484375</v>
+        <v>185.5951995849609</v>
       </c>
       <c r="C604" t="n">
-        <v>186.9691141315233</v>
+        <v>186.9690987597785</v>
       </c>
       <c r="D604" t="n">
-        <v>180.3983086236188</v>
+        <v>180.3982937920956</v>
       </c>
       <c r="E604" t="n">
-        <v>181.5929963910708</v>
+        <v>181.5929814613258</v>
       </c>
       <c r="F604" t="n">
         <v>757400</v>
@@ -12532,16 +12532,16 @@
         <v>44106</v>
       </c>
       <c r="B606" t="n">
-        <v>184.5797119140625</v>
+        <v>184.5796966552734</v>
       </c>
       <c r="C606" t="n">
-        <v>189.1195342625142</v>
+        <v>189.1195186284282</v>
       </c>
       <c r="D606" t="n">
-        <v>183.1162145528803</v>
+        <v>183.1161994150752</v>
       </c>
       <c r="E606" t="n">
-        <v>187.6261708483509</v>
+        <v>187.626155337718</v>
       </c>
       <c r="F606" t="n">
         <v>606133</v>
@@ -12672,16 +12672,16 @@
         <v>44118</v>
       </c>
       <c r="B613" t="n">
-        <v>201.2157897949219</v>
+        <v>201.2158050537109</v>
       </c>
       <c r="C613" t="n">
-        <v>201.8430072986919</v>
+        <v>201.8430226050447</v>
       </c>
       <c r="D613" t="n">
-        <v>196.2578274453795</v>
+        <v>196.2578423281916</v>
       </c>
       <c r="E613" t="n">
-        <v>197.5122472616411</v>
+        <v>197.5122622395795</v>
       </c>
       <c r="F613" t="n">
         <v>663866</v>
@@ -12692,16 +12692,16 @@
         <v>44119</v>
       </c>
       <c r="B614" t="n">
-        <v>198.4978485107422</v>
+        <v>198.4978790283203</v>
       </c>
       <c r="C614" t="n">
-        <v>201.4547089678896</v>
+        <v>201.4547399400632</v>
       </c>
       <c r="D614" t="n">
-        <v>196.9148719167073</v>
+        <v>196.9149021909145</v>
       </c>
       <c r="E614" t="n">
-        <v>199.6029379259516</v>
+        <v>199.6029686134291</v>
       </c>
       <c r="F614" t="n">
         <v>599566</v>
@@ -12812,16 +12812,16 @@
         <v>44127</v>
       </c>
       <c r="B620" t="n">
-        <v>190.3441009521484</v>
+        <v>190.3440856933594</v>
       </c>
       <c r="C620" t="n">
-        <v>195.2423310698091</v>
+        <v>195.2423154183572</v>
       </c>
       <c r="D620" t="n">
-        <v>188.9403357135048</v>
+        <v>188.9403205672475</v>
       </c>
       <c r="E620" t="n">
-        <v>194.1671076013551</v>
+        <v>194.1670920360976</v>
       </c>
       <c r="F620" t="n">
         <v>403166</v>
@@ -12832,16 +12832,16 @@
         <v>44130</v>
       </c>
       <c r="B621" t="n">
-        <v>196.2279510498047</v>
+        <v>196.2279357910156</v>
       </c>
       <c r="C621" t="n">
-        <v>198.4978621355634</v>
+        <v>198.4978467002649</v>
       </c>
       <c r="D621" t="n">
-        <v>188.5819227678193</v>
+        <v>188.5819081035894</v>
       </c>
       <c r="E621" t="n">
-        <v>190.4038278850452</v>
+        <v>190.403813079143</v>
       </c>
       <c r="F621" t="n">
         <v>609466</v>
@@ -12852,16 +12852,16 @@
         <v>44131</v>
       </c>
       <c r="B622" t="n">
-        <v>198.3186492919922</v>
+        <v>198.3186645507812</v>
       </c>
       <c r="C622" t="n">
-        <v>204.710242589321</v>
+        <v>204.7102583398841</v>
       </c>
       <c r="D622" t="n">
-        <v>195.7500625141592</v>
+        <v>195.7500775753192</v>
       </c>
       <c r="E622" t="n">
-        <v>196.2876818257843</v>
+        <v>196.2876969283092</v>
       </c>
       <c r="F622" t="n">
         <v>606666</v>
@@ -12872,16 +12872,16 @@
         <v>44132</v>
       </c>
       <c r="B623" t="n">
-        <v>192.9425506591797</v>
+        <v>192.9425659179688</v>
       </c>
       <c r="C623" t="n">
-        <v>196.4370154800485</v>
+        <v>196.437031015196</v>
       </c>
       <c r="D623" t="n">
-        <v>192.9425506591797</v>
+        <v>192.9425659179688</v>
       </c>
       <c r="E623" t="n">
-        <v>195.6007356378149</v>
+        <v>195.6007511068256</v>
       </c>
       <c r="F623" t="n">
         <v>477733</v>
@@ -12972,16 +12972,16 @@
         <v>44140</v>
       </c>
       <c r="B628" t="n">
-        <v>207.9956359863281</v>
+        <v>207.9956512451172</v>
       </c>
       <c r="C628" t="n">
-        <v>214.8949822450603</v>
+        <v>214.894998009993</v>
       </c>
       <c r="D628" t="n">
-        <v>206.4425406044565</v>
+        <v>206.4425557493087</v>
       </c>
       <c r="E628" t="n">
-        <v>206.9801447015363</v>
+        <v>206.9801598858278</v>
       </c>
       <c r="F628" t="n">
         <v>801700</v>
@@ -12992,16 +12992,16 @@
         <v>44141</v>
       </c>
       <c r="B629" t="n">
-        <v>213.5509643554688</v>
+        <v>213.5509490966797</v>
       </c>
       <c r="C629" t="n">
-        <v>214.2379139441398</v>
+        <v>214.2378986362663</v>
       </c>
       <c r="D629" t="n">
-        <v>205.1881354642133</v>
+        <v>205.1881208029708</v>
       </c>
       <c r="E629" t="n">
-        <v>206.8308291135134</v>
+        <v>206.8308143348961</v>
       </c>
       <c r="F629" t="n">
         <v>849833</v>
@@ -13052,16 +13052,16 @@
         <v>44146</v>
       </c>
       <c r="B632" t="n">
-        <v>204.5907897949219</v>
+        <v>204.5908050537109</v>
       </c>
       <c r="C632" t="n">
-        <v>206.5620252678551</v>
+        <v>206.5620406736629</v>
       </c>
       <c r="D632" t="n">
-        <v>200.7379170088981</v>
+        <v>200.7379319803322</v>
       </c>
       <c r="E632" t="n">
-        <v>202.9779621526382</v>
+        <v>202.9779772911393</v>
       </c>
       <c r="F632" t="n">
         <v>574366</v>
@@ -13092,16 +13092,16 @@
         <v>44148</v>
       </c>
       <c r="B634" t="n">
-        <v>218.897216796875</v>
+        <v>218.8972015380859</v>
       </c>
       <c r="C634" t="n">
-        <v>220.6593899790492</v>
+        <v>220.6593745974234</v>
       </c>
       <c r="D634" t="n">
-        <v>209.9370358039121</v>
+        <v>209.9370211697153</v>
       </c>
       <c r="E634" t="n">
-        <v>209.9370358039121</v>
+        <v>209.9370211697153</v>
       </c>
       <c r="F634" t="n">
         <v>872100</v>
@@ -13132,16 +13132,16 @@
         <v>44152</v>
       </c>
       <c r="B636" t="n">
-        <v>215.7611541748047</v>
+        <v>215.7611389160156</v>
       </c>
       <c r="C636" t="n">
-        <v>220.390574829844</v>
+        <v>220.3905592436589</v>
       </c>
       <c r="D636" t="n">
-        <v>215.7611541748047</v>
+        <v>215.7611389160156</v>
       </c>
       <c r="E636" t="n">
-        <v>219.793238559895</v>
+        <v>219.7932230159539</v>
       </c>
       <c r="F636" t="n">
         <v>945033</v>
@@ -13152,16 +13152,16 @@
         <v>44153</v>
       </c>
       <c r="B637" t="n">
-        <v>213.1029663085938</v>
+        <v>213.1029510498047</v>
       </c>
       <c r="C637" t="n">
-        <v>217.4337111775966</v>
+        <v>217.4336956087137</v>
       </c>
       <c r="D637" t="n">
-        <v>213.1029663085938</v>
+        <v>213.1029510498047</v>
       </c>
       <c r="E637" t="n">
-        <v>216.8662409688433</v>
+        <v>216.8662254405929</v>
       </c>
       <c r="F637" t="n">
         <v>504433</v>
@@ -13172,16 +13172,16 @@
         <v>44154</v>
       </c>
       <c r="B638" t="n">
-        <v>213.1627044677734</v>
+        <v>213.1626892089844</v>
       </c>
       <c r="C638" t="n">
-        <v>215.4326157497906</v>
+        <v>215.4326003285149</v>
       </c>
       <c r="D638" t="n">
-        <v>209.9668999255425</v>
+        <v>209.9668848955181</v>
       </c>
       <c r="E638" t="n">
-        <v>213.819788047115</v>
+        <v>213.81977274129</v>
       </c>
       <c r="F638" t="n">
         <v>672366</v>
@@ -13232,16 +13232,16 @@
         <v>44160</v>
       </c>
       <c r="B641" t="n">
-        <v>216.8363800048828</v>
+        <v>216.8363494873047</v>
       </c>
       <c r="C641" t="n">
-        <v>220.4204432366713</v>
+        <v>220.4204122146717</v>
       </c>
       <c r="D641" t="n">
-        <v>214.745665059547</v>
+        <v>214.7456348362164</v>
       </c>
       <c r="E641" t="n">
-        <v>215.0443407933491</v>
+        <v>215.0443105279828</v>
       </c>
       <c r="F641" t="n">
         <v>311466</v>
@@ -13252,16 +13252,16 @@
         <v>44161</v>
       </c>
       <c r="B642" t="n">
-        <v>212.8042907714844</v>
+        <v>212.8042755126953</v>
       </c>
       <c r="C642" t="n">
-        <v>218.6284142796364</v>
+        <v>218.6283986032379</v>
       </c>
       <c r="D642" t="n">
-        <v>210.265569878411</v>
+        <v>210.2655548016568</v>
       </c>
       <c r="E642" t="n">
-        <v>216.3883691136208</v>
+        <v>216.3883535978412</v>
       </c>
       <c r="F642" t="n">
         <v>253146</v>
@@ -13272,16 +13272,16 @@
         <v>44162</v>
       </c>
       <c r="B643" t="n">
-        <v>214.2976531982422</v>
+        <v>214.2976379394531</v>
       </c>
       <c r="C643" t="n">
-        <v>216.3883680864437</v>
+        <v>216.388352678788</v>
       </c>
       <c r="D643" t="n">
-        <v>207.5775177320952</v>
+        <v>207.5775029518047</v>
       </c>
       <c r="E643" t="n">
-        <v>212.6549594941399</v>
+        <v>212.6549443523167</v>
       </c>
       <c r="F643" t="n">
         <v>618080</v>
@@ -13332,16 +13332,16 @@
         <v>44167</v>
       </c>
       <c r="B646" t="n">
-        <v>220.7190856933594</v>
+        <v>220.7191009521484</v>
       </c>
       <c r="C646" t="n">
-        <v>221.4657673196504</v>
+        <v>221.4657826300592</v>
       </c>
       <c r="D646" t="n">
-        <v>213.5509451192212</v>
+        <v>213.5509598824612</v>
       </c>
       <c r="E646" t="n">
-        <v>214.1482964967647</v>
+        <v>214.1483113013008</v>
       </c>
       <c r="F646" t="n">
         <v>812640</v>
@@ -13372,16 +13372,16 @@
         <v>44169</v>
       </c>
       <c r="B648" t="n">
-        <v>228.9326171875</v>
+        <v>228.9326019287109</v>
       </c>
       <c r="C648" t="n">
-        <v>230.2766503886246</v>
+        <v>230.2766350402532</v>
       </c>
       <c r="D648" t="n">
-        <v>224.6018722340697</v>
+        <v>224.6018572639329</v>
       </c>
       <c r="E648" t="n">
-        <v>226.9912477124258</v>
+        <v>226.9912325830327</v>
       </c>
       <c r="F648" t="n">
         <v>265620</v>
@@ -13392,16 +13392,16 @@
         <v>44172</v>
       </c>
       <c r="B649" t="n">
-        <v>224.4525146484375</v>
+        <v>224.4525299072266</v>
       </c>
       <c r="C649" t="n">
-        <v>234.4580524072576</v>
+        <v>234.4580683462457</v>
       </c>
       <c r="D649" t="n">
-        <v>220.4204304541335</v>
+        <v>220.4204454388124</v>
       </c>
       <c r="E649" t="n">
-        <v>229.3806108009077</v>
+        <v>229.3806263947199</v>
       </c>
       <c r="F649" t="n">
         <v>556173</v>
@@ -13432,16 +13432,16 @@
         <v>44174</v>
       </c>
       <c r="B651" t="n">
-        <v>225.4978637695312</v>
+        <v>225.4978790283203</v>
       </c>
       <c r="C651" t="n">
-        <v>232.0686685254193</v>
+        <v>232.0686842288357</v>
       </c>
       <c r="D651" t="n">
-        <v>222.6604673541984</v>
+        <v>222.660482420989</v>
       </c>
       <c r="E651" t="n">
-        <v>229.9779537781974</v>
+        <v>229.9779693401412</v>
       </c>
       <c r="F651" t="n">
         <v>560820</v>
@@ -13452,16 +13452,16 @@
         <v>44175</v>
       </c>
       <c r="B652" t="n">
-        <v>227.8872680664062</v>
+        <v>227.8872375488281</v>
       </c>
       <c r="C652" t="n">
-        <v>233.4127161526883</v>
+        <v>233.4126848951685</v>
       </c>
       <c r="D652" t="n">
-        <v>225.6472227766659</v>
+        <v>225.647192559064</v>
       </c>
       <c r="E652" t="n">
-        <v>226.6925802834673</v>
+        <v>226.6925499258761</v>
       </c>
       <c r="F652" t="n">
         <v>713620</v>
@@ -13472,16 +13472,16 @@
         <v>44176</v>
       </c>
       <c r="B653" t="n">
-        <v>226.5432434082031</v>
+        <v>226.5432281494141</v>
       </c>
       <c r="C653" t="n">
-        <v>231.172664128968</v>
+        <v>231.172648558365</v>
       </c>
       <c r="D653" t="n">
-        <v>224.7512041903565</v>
+        <v>224.75118905227</v>
       </c>
       <c r="E653" t="n">
-        <v>228.4846128978375</v>
+        <v>228.4845975082877</v>
       </c>
       <c r="F653" t="n">
         <v>373833</v>
@@ -13532,16 +13532,16 @@
         <v>44181</v>
       </c>
       <c r="B656" t="n">
-        <v>230.4259643554688</v>
+        <v>230.4259796142578</v>
       </c>
       <c r="C656" t="n">
-        <v>232.9646851161438</v>
+        <v>232.9647005430468</v>
       </c>
       <c r="D656" t="n">
-        <v>225.1991925740168</v>
+        <v>225.1992074866895</v>
       </c>
       <c r="E656" t="n">
-        <v>227.2899073631087</v>
+        <v>227.2899224142283</v>
       </c>
       <c r="F656" t="n">
         <v>398466</v>
@@ -13592,16 +13592,16 @@
         <v>44186</v>
       </c>
       <c r="B659" t="n">
-        <v>224.7512054443359</v>
+        <v>224.7511901855469</v>
       </c>
       <c r="C659" t="n">
-        <v>228.3352839000263</v>
+        <v>228.3352683979073</v>
       </c>
       <c r="D659" t="n">
-        <v>219.0764272155587</v>
+        <v>219.0764123420412</v>
       </c>
       <c r="E659" t="n">
-        <v>223.8551934260528</v>
+        <v>223.8551782280958</v>
       </c>
       <c r="F659" t="n">
         <v>304586</v>
@@ -13632,16 +13632,16 @@
         <v>44188</v>
       </c>
       <c r="B661" t="n">
-        <v>224.4525146484375</v>
+        <v>224.4525299072266</v>
       </c>
       <c r="C661" t="n">
-        <v>229.8286319712688</v>
+        <v>229.8286475955385</v>
       </c>
       <c r="D661" t="n">
-        <v>224.0045086693544</v>
+        <v>224.004523897687</v>
       </c>
       <c r="E661" t="n">
-        <v>228.4845988427415</v>
+        <v>228.4846143756407</v>
       </c>
       <c r="F661" t="n">
         <v>316873</v>
@@ -13692,16 +13692,16 @@
         <v>44195</v>
       </c>
       <c r="B664" t="n">
-        <v>227.8872680664062</v>
+        <v>227.8872375488281</v>
       </c>
       <c r="C664" t="n">
-        <v>235.6527614424286</v>
+        <v>235.6527298849326</v>
       </c>
       <c r="D664" t="n">
-        <v>225.9458985202205</v>
+        <v>225.9458682626213</v>
       </c>
       <c r="E664" t="n">
-        <v>234.1593979159351</v>
+        <v>234.1593665584232</v>
       </c>
       <c r="F664" t="n">
         <v>659613</v>
@@ -13712,16 +13712,16 @@
         <v>44200</v>
       </c>
       <c r="B665" t="n">
-        <v>224.6018676757812</v>
+        <v>224.6018829345703</v>
       </c>
       <c r="C665" t="n">
-        <v>231.6206636977356</v>
+        <v>231.620679433361</v>
       </c>
       <c r="D665" t="n">
-        <v>220.4204378866018</v>
+        <v>220.4204528613169</v>
       </c>
       <c r="E665" t="n">
-        <v>230.1273002562511</v>
+        <v>230.1273158904218</v>
       </c>
       <c r="F665" t="n">
         <v>564553</v>
@@ -13732,16 +13732,16 @@
         <v>44201</v>
       </c>
       <c r="B666" t="n">
-        <v>218.7777404785156</v>
+        <v>218.7777557373047</v>
       </c>
       <c r="C666" t="n">
-        <v>225.6472061166881</v>
+        <v>225.6472218545923</v>
       </c>
       <c r="D666" t="n">
-        <v>218.1803890355101</v>
+        <v>218.1804042526365</v>
       </c>
       <c r="E666" t="n">
-        <v>224.9005244085703</v>
+        <v>224.9005400943967</v>
       </c>
       <c r="F666" t="n">
         <v>585466</v>
@@ -13812,16 +13812,16 @@
         <v>44207</v>
       </c>
       <c r="B670" t="n">
-        <v>272.2713012695312</v>
+        <v>272.2713317871094</v>
       </c>
       <c r="C670" t="n">
-        <v>276.4601026942797</v>
+        <v>276.4601336813603</v>
       </c>
       <c r="D670" t="n">
-        <v>249.9809523860654</v>
+        <v>249.9809804052258</v>
       </c>
       <c r="E670" t="n">
-        <v>250.7289504664762</v>
+        <v>250.7289785694761</v>
       </c>
       <c r="F670" t="n">
         <v>3239386</v>
@@ -13932,16 +13932,16 @@
         <v>44215</v>
       </c>
       <c r="B676" t="n">
-        <v>259.8544921875</v>
+        <v>259.8545227050781</v>
       </c>
       <c r="C676" t="n">
-        <v>273.7672671170767</v>
+        <v>273.7672992685854</v>
       </c>
       <c r="D676" t="n">
-        <v>255.3665042019742</v>
+        <v>255.3665341924784</v>
       </c>
       <c r="E676" t="n">
-        <v>269.8776836168443</v>
+        <v>269.8777153115562</v>
       </c>
       <c r="F676" t="n">
         <v>761093</v>
@@ -13952,16 +13952,16 @@
         <v>44216</v>
       </c>
       <c r="B677" t="n">
-        <v>259.8544921875</v>
+        <v>259.8545227050781</v>
       </c>
       <c r="C677" t="n">
-        <v>264.4921041214365</v>
+        <v>264.4921351836605</v>
       </c>
       <c r="D677" t="n">
-        <v>256.8625001971495</v>
+        <v>256.8625303633449</v>
       </c>
       <c r="E677" t="n">
-        <v>259.4057116506173</v>
+        <v>259.4057421154902</v>
       </c>
       <c r="F677" t="n">
         <v>662453</v>
@@ -14012,16 +14012,16 @@
         <v>44222</v>
       </c>
       <c r="B680" t="n">
-        <v>267.7833557128906</v>
+        <v>267.7833251953125</v>
       </c>
       <c r="C680" t="n">
-        <v>276.1609294691975</v>
+        <v>276.1608979968802</v>
       </c>
       <c r="D680" t="n">
-        <v>261.5001830046917</v>
+        <v>261.5001532031671</v>
       </c>
       <c r="E680" t="n">
-        <v>263.4449600638367</v>
+        <v>263.4449300406782</v>
       </c>
       <c r="F680" t="n">
         <v>884853</v>
@@ -14092,16 +14092,16 @@
         <v>44228</v>
       </c>
       <c r="B684" t="n">
-        <v>261.9489440917969</v>
+        <v>261.9489135742188</v>
       </c>
       <c r="C684" t="n">
-        <v>264.6417495861901</v>
+        <v>264.6417187548947</v>
       </c>
       <c r="D684" t="n">
-        <v>256.7129570807941</v>
+        <v>256.712927173219</v>
       </c>
       <c r="E684" t="n">
-        <v>264.6417495861901</v>
+        <v>264.6417187548947</v>
       </c>
       <c r="F684" t="n">
         <v>678393</v>
@@ -14112,16 +14112,16 @@
         <v>44229</v>
       </c>
       <c r="B685" t="n">
-        <v>265.6889038085938</v>
+        <v>265.6888732910156</v>
       </c>
       <c r="C685" t="n">
-        <v>271.5232947415027</v>
+        <v>271.5232635537744</v>
       </c>
       <c r="D685" t="n">
-        <v>260.7521348931468</v>
+        <v>260.7521049426162</v>
       </c>
       <c r="E685" t="n">
-        <v>266.5864953899369</v>
+        <v>266.5864647692596</v>
       </c>
       <c r="F685" t="n">
         <v>627486</v>
@@ -14132,16 +14132,16 @@
         <v>44230</v>
       </c>
       <c r="B686" t="n">
-        <v>264.6417541503906</v>
+        <v>264.6417236328125</v>
       </c>
       <c r="C686" t="n">
-        <v>267.7833403239498</v>
+        <v>267.7833094440948</v>
       </c>
       <c r="D686" t="n">
-        <v>260.3033587506551</v>
+        <v>260.3033287333658</v>
       </c>
       <c r="E686" t="n">
-        <v>267.1849357108616</v>
+        <v>267.1849049000126</v>
       </c>
       <c r="F686" t="n">
         <v>630753</v>
@@ -14172,16 +14172,16 @@
         <v>44232</v>
       </c>
       <c r="B688" t="n">
-        <v>267.0353393554688</v>
+        <v>267.0353088378906</v>
       </c>
       <c r="C688" t="n">
-        <v>273.7673227005646</v>
+        <v>273.7672914136357</v>
       </c>
       <c r="D688" t="n">
-        <v>264.94093844977</v>
+        <v>264.9409081715461</v>
       </c>
       <c r="E688" t="n">
-        <v>265.3897495138921</v>
+        <v>265.3897191843768</v>
       </c>
       <c r="F688" t="n">
         <v>358426</v>
@@ -14212,16 +14212,16 @@
         <v>44236</v>
       </c>
       <c r="B690" t="n">
-        <v>264.7913208007812</v>
+        <v>264.7912902832031</v>
       </c>
       <c r="C690" t="n">
-        <v>270.1769008993359</v>
+        <v>270.1768697610619</v>
       </c>
       <c r="D690" t="n">
-        <v>264.1929162484707</v>
+        <v>264.1928857998596</v>
       </c>
       <c r="E690" t="n">
-        <v>269.4289028179777</v>
+        <v>269.4288717659117</v>
       </c>
       <c r="F690" t="n">
         <v>477180</v>
@@ -14372,16 +14372,16 @@
         <v>44250</v>
       </c>
       <c r="B698" t="n">
-        <v>243.8473815917969</v>
+        <v>243.8473968505859</v>
       </c>
       <c r="C698" t="n">
-        <v>250.7289580525621</v>
+        <v>250.7289737419669</v>
       </c>
       <c r="D698" t="n">
-        <v>241.4537937492856</v>
+        <v>241.4538088582955</v>
       </c>
       <c r="E698" t="n">
-        <v>247.7369656403928</v>
+        <v>247.7369811425732</v>
       </c>
       <c r="F698" t="n">
         <v>535220</v>
@@ -14472,16 +14472,16 @@
         <v>44257</v>
       </c>
       <c r="B703" t="n">
-        <v>245.3433685302734</v>
+        <v>245.3433837890625</v>
       </c>
       <c r="C703" t="n">
-        <v>246.5401624063213</v>
+        <v>246.5401777395433</v>
       </c>
       <c r="D703" t="n">
-        <v>231.8794031840999</v>
+        <v>231.8794176055164</v>
       </c>
       <c r="E703" t="n">
-        <v>242.6505785046507</v>
+        <v>242.6505935959654</v>
       </c>
       <c r="F703" t="n">
         <v>816593</v>
@@ -14492,16 +14492,16 @@
         <v>44258</v>
       </c>
       <c r="B704" t="n">
-        <v>241.6033782958984</v>
+        <v>241.6033935546875</v>
       </c>
       <c r="C704" t="n">
-        <v>245.9417732193955</v>
+        <v>245.9417887521817</v>
       </c>
       <c r="D704" t="n">
-        <v>231.1314052428255</v>
+        <v>231.1314198402428</v>
       </c>
       <c r="E704" t="n">
-        <v>242.9497809185175</v>
+        <v>242.9497962623404</v>
       </c>
       <c r="F704" t="n">
         <v>976053</v>
@@ -14552,16 +14552,16 @@
         <v>44263</v>
       </c>
       <c r="B707" t="n">
-        <v>224.5490264892578</v>
+        <v>224.5490417480469</v>
       </c>
       <c r="C707" t="n">
-        <v>232.0290075877416</v>
+        <v>232.0290233548181</v>
       </c>
       <c r="D707" t="n">
-        <v>221.7066428026703</v>
+        <v>221.7066578683107</v>
       </c>
       <c r="E707" t="n">
-        <v>225.7458356394636</v>
+        <v>225.7458509795795</v>
       </c>
       <c r="F707" t="n">
         <v>1054193</v>
@@ -14592,16 +14592,16 @@
         <v>44265</v>
       </c>
       <c r="B709" t="n">
-        <v>227.2418212890625</v>
+        <v>227.2418365478516</v>
       </c>
       <c r="C709" t="n">
-        <v>229.4858155142288</v>
+        <v>229.4858309236971</v>
       </c>
       <c r="D709" t="n">
-        <v>217.9666421147633</v>
+        <v>217.9666567507444</v>
       </c>
       <c r="E709" t="n">
-        <v>228.7378174391734</v>
+        <v>228.7378327984153</v>
       </c>
       <c r="F709" t="n">
         <v>667500</v>
@@ -14632,16 +14632,16 @@
         <v>44267</v>
       </c>
       <c r="B711" t="n">
-        <v>228.8874359130859</v>
+        <v>228.8874206542969</v>
       </c>
       <c r="C711" t="n">
-        <v>231.8794285394008</v>
+        <v>231.8794130811504</v>
       </c>
       <c r="D711" t="n">
-        <v>225.8954432867711</v>
+        <v>225.8954282274433</v>
       </c>
       <c r="E711" t="n">
-        <v>227.8402354502634</v>
+        <v>227.840220261286</v>
       </c>
       <c r="F711" t="n">
         <v>268453</v>
@@ -14652,16 +14652,16 @@
         <v>44270</v>
       </c>
       <c r="B712" t="n">
-        <v>231.5802307128906</v>
+        <v>231.5802154541016</v>
       </c>
       <c r="C712" t="n">
-        <v>232.3282288839388</v>
+        <v>232.3282135758642</v>
       </c>
       <c r="D712" t="n">
-        <v>225.5962453445055</v>
+        <v>225.5962304800004</v>
       </c>
       <c r="E712" t="n">
-        <v>228.8874403407297</v>
+        <v>228.8874252593682</v>
       </c>
       <c r="F712" t="n">
         <v>221460</v>
@@ -14852,16 +14852,16 @@
         <v>44284</v>
       </c>
       <c r="B722" t="n">
-        <v>223.8010101318359</v>
+        <v>223.801025390625</v>
       </c>
       <c r="C722" t="n">
-        <v>226.0450042784174</v>
+        <v>226.0450196902024</v>
       </c>
       <c r="D722" t="n">
-        <v>219.7618328424367</v>
+        <v>219.761847825834</v>
       </c>
       <c r="E722" t="n">
-        <v>226.0450042784174</v>
+        <v>226.0450196902024</v>
       </c>
       <c r="F722" t="n">
         <v>788160</v>
@@ -14952,16 +14952,16 @@
         <v>44292</v>
       </c>
       <c r="B727" t="n">
-        <v>219.1634368896484</v>
+        <v>219.1634521484375</v>
       </c>
       <c r="C727" t="n">
-        <v>222.9034272802568</v>
+        <v>222.9034427994347</v>
       </c>
       <c r="D727" t="n">
-        <v>215.4234464990401</v>
+        <v>215.4234614974403</v>
       </c>
       <c r="E727" t="n">
-        <v>221.1082288491528</v>
+        <v>221.1082442433439</v>
       </c>
       <c r="F727" t="n">
         <v>964873</v>
@@ -14972,16 +14972,16 @@
         <v>44293</v>
       </c>
       <c r="B728" t="n">
-        <v>227.6906127929688</v>
+        <v>227.6906280517578</v>
       </c>
       <c r="C728" t="n">
-        <v>230.3834027687316</v>
+        <v>230.3834182079792</v>
       </c>
       <c r="D728" t="n">
-        <v>219.16343185467</v>
+        <v>219.1634465420062</v>
       </c>
       <c r="E728" t="n">
-        <v>219.3130253796337</v>
+        <v>219.313040076995</v>
       </c>
       <c r="F728" t="n">
         <v>1567580</v>
@@ -15052,16 +15052,16 @@
         <v>44299</v>
       </c>
       <c r="B732" t="n">
-        <v>227.2418212890625</v>
+        <v>227.2418365478516</v>
       </c>
       <c r="C732" t="n">
-        <v>227.9898193641179</v>
+        <v>227.9898346731334</v>
       </c>
       <c r="D732" t="n">
-        <v>219.9114340662954</v>
+        <v>219.9114488328651</v>
       </c>
       <c r="E732" t="n">
-        <v>220.6594321413508</v>
+        <v>220.6594469581469</v>
       </c>
       <c r="F732" t="n">
         <v>596393</v>
@@ -15192,16 +15192,16 @@
         <v>44309</v>
       </c>
       <c r="B739" t="n">
-        <v>220.3602447509766</v>
+        <v>220.3602294921875</v>
       </c>
       <c r="C739" t="n">
-        <v>223.6514395471216</v>
+        <v>223.6514240604346</v>
       </c>
       <c r="D739" t="n">
-        <v>218.2658591302012</v>
+        <v>218.2658440164373</v>
       </c>
       <c r="E739" t="n">
-        <v>222.3050368338611</v>
+        <v>222.3050214404054</v>
       </c>
       <c r="F739" t="n">
         <v>863700</v>
@@ -15452,16 +15452,16 @@
         <v>44328</v>
       </c>
       <c r="B752" t="n">
-        <v>212.4675750732422</v>
+        <v>212.4675598144531</v>
       </c>
       <c r="C752" t="n">
-        <v>218.9014493024574</v>
+        <v>218.9014335816066</v>
       </c>
       <c r="D752" t="n">
-        <v>211.2705776944238</v>
+        <v>211.2705625215996</v>
       </c>
       <c r="E752" t="n">
-        <v>218.4525771879814</v>
+        <v>218.4525614993673</v>
       </c>
       <c r="F752" t="n">
         <v>1381546</v>
@@ -15472,16 +15472,16 @@
         <v>44329</v>
       </c>
       <c r="B753" t="n">
-        <v>218.4525604248047</v>
+        <v>218.4525756835938</v>
       </c>
       <c r="C753" t="n">
-        <v>221.7443143794447</v>
+        <v>221.7443298681609</v>
       </c>
       <c r="D753" t="n">
-        <v>214.4126812632304</v>
+        <v>214.4126962398362</v>
       </c>
       <c r="E753" t="n">
-        <v>214.7119343901334</v>
+        <v>214.7119493876418</v>
       </c>
       <c r="F753" t="n">
         <v>807133</v>
@@ -15512,16 +15512,16 @@
         <v>44333</v>
       </c>
       <c r="B755" t="n">
-        <v>218.6021881103516</v>
+        <v>218.6022033691406</v>
       </c>
       <c r="C755" t="n">
-        <v>222.9413205721625</v>
+        <v>222.9413361338301</v>
       </c>
       <c r="D755" t="n">
-        <v>217.8540628735322</v>
+        <v>217.8540780801009</v>
       </c>
       <c r="E755" t="n">
-        <v>219.2006943880658</v>
+        <v>219.2007096886316</v>
       </c>
       <c r="F755" t="n">
         <v>603380</v>
@@ -15532,16 +15532,16 @@
         <v>44334</v>
       </c>
       <c r="B756" t="n">
-        <v>219.7991943359375</v>
+        <v>219.7992095947266</v>
       </c>
       <c r="C756" t="n">
-        <v>223.2405672820714</v>
+        <v>223.2405827797657</v>
       </c>
       <c r="D756" t="n">
-        <v>215.6096809538825</v>
+        <v>215.6096959218293</v>
       </c>
       <c r="E756" t="n">
-        <v>218.7518159904238</v>
+        <v>218.7518311765023</v>
       </c>
       <c r="F756" t="n">
         <v>1363900</v>
@@ -15552,16 +15552,16 @@
         <v>44335</v>
       </c>
       <c r="B757" t="n">
-        <v>217.8540649414062</v>
+        <v>217.8540802001953</v>
       </c>
       <c r="C757" t="n">
-        <v>221.7443253421814</v>
+        <v>221.7443408734494</v>
       </c>
       <c r="D757" t="n">
-        <v>216.9563207369604</v>
+        <v>216.9563359328703</v>
       </c>
       <c r="E757" t="n">
-        <v>219.0510775081968</v>
+        <v>219.0510928508262</v>
       </c>
       <c r="F757" t="n">
         <v>577806</v>
@@ -15572,16 +15572,16 @@
         <v>44336</v>
       </c>
       <c r="B758" t="n">
-        <v>223.0909271240234</v>
+        <v>223.0909423828125</v>
       </c>
       <c r="C758" t="n">
-        <v>224.4375585636639</v>
+        <v>224.4375739145587</v>
       </c>
       <c r="D758" t="n">
-        <v>217.2555597337558</v>
+        <v>217.2555745934222</v>
       </c>
       <c r="E758" t="n">
-        <v>219.2006821971784</v>
+        <v>219.2006971898857</v>
       </c>
       <c r="F758" t="n">
         <v>585933</v>
@@ -15932,16 +15932,16 @@
         <v>44363</v>
       </c>
       <c r="B776" t="n">
-        <v>228.9263305664062</v>
+        <v>228.9263153076172</v>
       </c>
       <c r="C776" t="n">
-        <v>230.8714532068279</v>
+        <v>230.8714378183892</v>
       </c>
       <c r="D776" t="n">
-        <v>225.7842105488518</v>
+        <v>225.7841954994967</v>
       </c>
       <c r="E776" t="n">
-        <v>226.3827016270945</v>
+        <v>226.3826865378477</v>
       </c>
       <c r="F776" t="n">
         <v>725393</v>
@@ -16132,16 +16132,16 @@
         <v>44377</v>
       </c>
       <c r="B786" t="n">
-        <v>230.5721893310547</v>
+        <v>230.5721740722656</v>
       </c>
       <c r="C786" t="n">
-        <v>232.5173271016351</v>
+        <v>232.5173117141208</v>
       </c>
       <c r="D786" t="n">
-        <v>227.7293225951968</v>
+        <v>227.7293075245428</v>
       </c>
       <c r="E786" t="n">
-        <v>231.3203145595405</v>
+        <v>231.320299251242</v>
       </c>
       <c r="F786" t="n">
         <v>609766</v>
@@ -42151,12 +42151,20 @@
       <c r="A2087" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B2087" t="inlineStr"/>
-      <c r="C2087" t="inlineStr"/>
-      <c r="D2087" t="inlineStr"/>
-      <c r="E2087" t="inlineStr"/>
+      <c r="B2087" t="n">
+        <v>6.389999866485596</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>6.599999904632568</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>6.349999904632568</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>6.570000171661377</v>
+      </c>
       <c r="F2087" t="n">
-        <v>9530800</v>
+        <v>8663600</v>
       </c>
     </row>
     <row r="2088">
@@ -42164,19 +42172,39 @@
         <v>46283</v>
       </c>
       <c r="B2088" t="n">
-        <v>6.21</v>
+        <v>6.210000038146973</v>
       </c>
       <c r="C2088" t="n">
-        <v>6.36</v>
+        <v>6.360000133514404</v>
       </c>
       <c r="D2088" t="n">
-        <v>6.16</v>
+        <v>6.159999847412109</v>
       </c>
       <c r="E2088" t="n">
-        <v>6.36</v>
+        <v>6.360000133514404</v>
       </c>
       <c r="F2088" t="n">
         <v>9556600</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>9954800</v>
       </c>
     </row>
   </sheetData>

--- a/database/HAPV3.xlsx
+++ b/database/HAPV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2093"/>
+  <dimension ref="A1:F2094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>43217</v>
       </c>
       <c r="B3" t="n">
-        <v>82.00556182861328</v>
+        <v>82.00556945800781</v>
       </c>
       <c r="C3" t="n">
-        <v>83.90925939176427</v>
+        <v>83.90926719826945</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54117679595947</v>
+        <v>80.54118428911481</v>
       </c>
       <c r="E3" t="n">
-        <v>81.9762753196798</v>
+        <v>81.97628294634966</v>
       </c>
       <c r="F3" t="n">
         <v>932166</v>
@@ -512,16 +512,16 @@
         <v>43222</v>
       </c>
       <c r="B5" t="n">
-        <v>79.98471069335938</v>
+        <v>79.98469543457031</v>
       </c>
       <c r="C5" t="n">
-        <v>81.85912174551177</v>
+        <v>81.85910612913884</v>
       </c>
       <c r="D5" t="n">
-        <v>79.0767916761844</v>
+        <v>79.07677659060025</v>
       </c>
       <c r="E5" t="n">
-        <v>79.0767916761844</v>
+        <v>79.07677659060025</v>
       </c>
       <c r="F5" t="n">
         <v>428333</v>
@@ -532,16 +532,16 @@
         <v>43223</v>
       </c>
       <c r="B6" t="n">
-        <v>80.51188659667969</v>
+        <v>80.51190185546875</v>
       </c>
       <c r="C6" t="n">
-        <v>81.71267809739771</v>
+        <v>81.71269358376341</v>
       </c>
       <c r="D6" t="n">
-        <v>78.49103564217513</v>
+        <v>78.49105051796811</v>
       </c>
       <c r="E6" t="n">
-        <v>79.39895461873498</v>
+        <v>79.39896966659875</v>
       </c>
       <c r="F6" t="n">
         <v>790600</v>
@@ -552,16 +552,16 @@
         <v>43224</v>
       </c>
       <c r="B7" t="n">
-        <v>78.34458923339844</v>
+        <v>78.3446044921875</v>
       </c>
       <c r="C7" t="n">
-        <v>81.03905943459817</v>
+        <v>81.0390752181759</v>
       </c>
       <c r="D7" t="n">
-        <v>77.31951686226098</v>
+        <v>77.31953192140176</v>
       </c>
       <c r="E7" t="n">
-        <v>81.03905943459817</v>
+        <v>81.0390752181759</v>
       </c>
       <c r="F7" t="n">
         <v>632800</v>
@@ -572,16 +572,16 @@
         <v>43227</v>
       </c>
       <c r="B8" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C8" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="D8" t="n">
-        <v>77.90527738914264</v>
+        <v>77.90528490550868</v>
       </c>
       <c r="E8" t="n">
-        <v>78.05171737852535</v>
+        <v>78.05172490902004</v>
       </c>
       <c r="F8" t="n">
         <v>375200</v>
@@ -592,16 +592,16 @@
         <v>43228</v>
       </c>
       <c r="B9" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C9" t="n">
-        <v>79.95542234400601</v>
+        <v>79.95543005817173</v>
       </c>
       <c r="D9" t="n">
-        <v>78.49103734667347</v>
+        <v>78.49104491955411</v>
       </c>
       <c r="E9" t="n">
-        <v>79.51610237585788</v>
+        <v>79.51611004763765</v>
       </c>
       <c r="F9" t="n">
         <v>315733</v>
@@ -612,16 +612,16 @@
         <v>43229</v>
       </c>
       <c r="B10" t="n">
-        <v>78.78391265869141</v>
+        <v>78.78389739990234</v>
       </c>
       <c r="C10" t="n">
-        <v>79.34037867939415</v>
+        <v>79.34036331282931</v>
       </c>
       <c r="D10" t="n">
-        <v>77.81742061183874</v>
+        <v>77.81740554023889</v>
       </c>
       <c r="E10" t="n">
-        <v>79.07679264779708</v>
+        <v>79.0767773322833</v>
       </c>
       <c r="F10" t="n">
         <v>333066</v>
@@ -652,16 +652,16 @@
         <v>43231</v>
       </c>
       <c r="B12" t="n">
-        <v>80.83405303955078</v>
+        <v>80.83404541015625</v>
       </c>
       <c r="C12" t="n">
-        <v>82.59131813859989</v>
+        <v>82.59131034334867</v>
       </c>
       <c r="D12" t="n">
-        <v>80.48260746798874</v>
+        <v>80.48259987176485</v>
       </c>
       <c r="E12" t="n">
-        <v>80.51189397826494</v>
+        <v>80.51188637927687</v>
       </c>
       <c r="F12" t="n">
         <v>586000</v>
@@ -672,16 +672,16 @@
         <v>43234</v>
       </c>
       <c r="B13" t="n">
-        <v>80.01399230957031</v>
+        <v>80.01399993896484</v>
       </c>
       <c r="C13" t="n">
-        <v>81.82983023288553</v>
+        <v>81.82983803542157</v>
       </c>
       <c r="D13" t="n">
-        <v>80.01399230957031</v>
+        <v>80.01399993896484</v>
       </c>
       <c r="E13" t="n">
-        <v>81.6833902490865</v>
+        <v>81.68339803765939</v>
       </c>
       <c r="F13" t="n">
         <v>350433</v>
@@ -692,16 +692,16 @@
         <v>43235</v>
       </c>
       <c r="B14" t="n">
-        <v>84.78788757324219</v>
+        <v>84.78789520263672</v>
       </c>
       <c r="C14" t="n">
-        <v>85.22720008131586</v>
+        <v>85.22720775024067</v>
       </c>
       <c r="D14" t="n">
-        <v>82.0055576428658</v>
+        <v>82.00556502190037</v>
       </c>
       <c r="E14" t="n">
-        <v>82.29843016549923</v>
+        <v>82.29843757088707</v>
       </c>
       <c r="F14" t="n">
         <v>900866</v>
@@ -732,16 +732,16 @@
         <v>43237</v>
       </c>
       <c r="B16" t="n">
-        <v>88.74172210693359</v>
+        <v>88.74171447753906</v>
       </c>
       <c r="C16" t="n">
-        <v>90.73328636771173</v>
+        <v>90.73327856709638</v>
       </c>
       <c r="D16" t="n">
-        <v>87.86308972008348</v>
+        <v>87.86308216622763</v>
       </c>
       <c r="E16" t="n">
-        <v>87.86308972008348</v>
+        <v>87.86308216622763</v>
       </c>
       <c r="F16" t="n">
         <v>520533</v>
@@ -752,16 +752,16 @@
         <v>43238</v>
       </c>
       <c r="B17" t="n">
-        <v>86.69157409667969</v>
+        <v>86.69158935546875</v>
       </c>
       <c r="C17" t="n">
-        <v>88.74171873757183</v>
+        <v>88.7417343572117</v>
       </c>
       <c r="D17" t="n">
-        <v>85.60793621699578</v>
+        <v>85.60795128505117</v>
       </c>
       <c r="E17" t="n">
-        <v>88.74171873757183</v>
+        <v>88.7417343572117</v>
       </c>
       <c r="F17" t="n">
         <v>980066</v>
@@ -772,16 +772,16 @@
         <v>43241</v>
       </c>
       <c r="B18" t="n">
-        <v>90.20610809326172</v>
+        <v>90.20611572265625</v>
       </c>
       <c r="C18" t="n">
-        <v>91.05544653791148</v>
+        <v>91.05545423914081</v>
       </c>
       <c r="D18" t="n">
-        <v>84.93432115275195</v>
+        <v>84.93432833627266</v>
       </c>
       <c r="E18" t="n">
-        <v>86.98445844954838</v>
+        <v>86.9844658064643</v>
       </c>
       <c r="F18" t="n">
         <v>633933</v>
@@ -792,16 +792,16 @@
         <v>43242</v>
       </c>
       <c r="B19" t="n">
-        <v>95.91722869873047</v>
+        <v>95.91722106933594</v>
       </c>
       <c r="C19" t="n">
-        <v>96.0636687054774</v>
+        <v>96.06366106443481</v>
       </c>
       <c r="D19" t="n">
-        <v>90.20612802158546</v>
+        <v>90.2061208464601</v>
       </c>
       <c r="E19" t="n">
-        <v>90.20612802158546</v>
+        <v>90.2061208464601</v>
       </c>
       <c r="F19" t="n">
         <v>462766</v>
@@ -832,16 +832,16 @@
         <v>43244</v>
       </c>
       <c r="B21" t="n">
-        <v>89.32748413085938</v>
+        <v>89.32749176025391</v>
       </c>
       <c r="C21" t="n">
-        <v>93.77921210410572</v>
+        <v>93.77922011371906</v>
       </c>
       <c r="D21" t="n">
-        <v>89.09318461864831</v>
+        <v>89.0931922280315</v>
       </c>
       <c r="E21" t="n">
-        <v>93.13488658346348</v>
+        <v>93.13489453804544</v>
       </c>
       <c r="F21" t="n">
         <v>822100</v>
@@ -852,16 +852,16 @@
         <v>43245</v>
       </c>
       <c r="B22" t="n">
-        <v>90.76258087158203</v>
+        <v>90.76258850097656</v>
       </c>
       <c r="C22" t="n">
-        <v>90.879726901322</v>
+        <v>90.87973454056369</v>
       </c>
       <c r="D22" t="n">
-        <v>87.95095698586984</v>
+        <v>87.95096437892261</v>
       </c>
       <c r="E22" t="n">
-        <v>88.77101643528491</v>
+        <v>88.77102389727091</v>
       </c>
       <c r="F22" t="n">
         <v>562433</v>
@@ -872,16 +872,16 @@
         <v>43248</v>
       </c>
       <c r="B23" t="n">
-        <v>86.39871215820312</v>
+        <v>86.39869689941406</v>
       </c>
       <c r="C23" t="n">
-        <v>90.76258050638783</v>
+        <v>90.76256447690039</v>
       </c>
       <c r="D23" t="n">
-        <v>85.02218672832065</v>
+        <v>85.02217171263833</v>
       </c>
       <c r="E23" t="n">
-        <v>90.76258050638783</v>
+        <v>90.76256447690039</v>
       </c>
       <c r="F23" t="n">
         <v>427433</v>
@@ -892,16 +892,16 @@
         <v>43249</v>
       </c>
       <c r="B24" t="n">
-        <v>87.16019439697266</v>
+        <v>87.16020202636719</v>
       </c>
       <c r="C24" t="n">
-        <v>88.88816542744976</v>
+        <v>88.88817320809881</v>
       </c>
       <c r="D24" t="n">
-        <v>84.49501040785843</v>
+        <v>84.49501780396137</v>
       </c>
       <c r="E24" t="n">
-        <v>87.27734787886412</v>
+        <v>87.27735551851345</v>
       </c>
       <c r="F24" t="n">
         <v>175300</v>
@@ -932,16 +932,16 @@
         <v>43252</v>
       </c>
       <c r="B26" t="n">
-        <v>87.54093170166016</v>
+        <v>87.54091644287109</v>
       </c>
       <c r="C26" t="n">
-        <v>90.76258161432011</v>
+        <v>90.76256579398257</v>
       </c>
       <c r="D26" t="n">
-        <v>84.90504173548175</v>
+        <v>84.90502693614047</v>
       </c>
       <c r="E26" t="n">
-        <v>89.70822264854989</v>
+        <v>89.708207011992</v>
       </c>
       <c r="F26" t="n">
         <v>391033</v>
@@ -952,16 +952,16 @@
         <v>43255</v>
       </c>
       <c r="B27" t="n">
-        <v>88.74172210693359</v>
+        <v>88.74171447753906</v>
       </c>
       <c r="C27" t="n">
-        <v>90.20610693560165</v>
+        <v>90.20609918030952</v>
       </c>
       <c r="D27" t="n">
-        <v>86.72087134130153</v>
+        <v>86.72086388564566</v>
       </c>
       <c r="E27" t="n">
-        <v>88.44884216190142</v>
+        <v>88.44883455768667</v>
       </c>
       <c r="F27" t="n">
         <v>304000</v>
@@ -992,16 +992,16 @@
         <v>43257</v>
       </c>
       <c r="B29" t="n">
-        <v>83.41136932373047</v>
+        <v>83.411376953125</v>
       </c>
       <c r="C29" t="n">
-        <v>85.46150676870901</v>
+        <v>85.46151458562363</v>
       </c>
       <c r="D29" t="n">
-        <v>81.71267741515801</v>
+        <v>81.71268488917815</v>
       </c>
       <c r="E29" t="n">
-        <v>84.9929003064225</v>
+        <v>84.99290808047505</v>
       </c>
       <c r="F29" t="n">
         <v>443766</v>
@@ -1012,16 +1012,16 @@
         <v>43258</v>
       </c>
       <c r="B30" t="n">
-        <v>80.83405303955078</v>
+        <v>80.83404541015625</v>
       </c>
       <c r="C30" t="n">
-        <v>83.41137766757205</v>
+        <v>83.41136979492082</v>
       </c>
       <c r="D30" t="n">
-        <v>78.6374753898633</v>
+        <v>78.63746796778928</v>
       </c>
       <c r="E30" t="n">
-        <v>83.41137766757205</v>
+        <v>83.41136979492082</v>
       </c>
       <c r="F30" t="n">
         <v>547066</v>
@@ -1052,16 +1052,16 @@
         <v>43262</v>
       </c>
       <c r="B32" t="n">
-        <v>81.41981506347656</v>
+        <v>81.41980743408203</v>
       </c>
       <c r="C32" t="n">
-        <v>82.73776019642489</v>
+        <v>82.73775244353311</v>
       </c>
       <c r="D32" t="n">
-        <v>78.93035735260352</v>
+        <v>78.93034995648213</v>
       </c>
       <c r="E32" t="n">
-        <v>81.478388085486</v>
+        <v>81.47838045060293</v>
       </c>
       <c r="F32" t="n">
         <v>202266</v>
@@ -1072,16 +1072,16 @@
         <v>43263</v>
       </c>
       <c r="B33" t="n">
-        <v>82.2398681640625</v>
+        <v>82.23986053466797</v>
       </c>
       <c r="C33" t="n">
-        <v>83.38208679661591</v>
+        <v>83.38207906125773</v>
       </c>
       <c r="D33" t="n">
-        <v>80.07257694439825</v>
+        <v>80.07256951606338</v>
       </c>
       <c r="E33" t="n">
-        <v>81.41981605297228</v>
+        <v>81.419808499654</v>
       </c>
       <c r="F33" t="n">
         <v>203566</v>
@@ -1092,16 +1092,16 @@
         <v>43264</v>
       </c>
       <c r="B34" t="n">
-        <v>78.3153076171875</v>
+        <v>78.31529998779297</v>
       </c>
       <c r="C34" t="n">
-        <v>82.32772294015612</v>
+        <v>82.32771491987633</v>
       </c>
       <c r="D34" t="n">
-        <v>77.70026117681101</v>
+        <v>77.70025360733365</v>
       </c>
       <c r="E34" t="n">
-        <v>82.32772294015612</v>
+        <v>82.32771491987633</v>
       </c>
       <c r="F34" t="n">
         <v>786033</v>
@@ -1112,16 +1112,16 @@
         <v>43265</v>
       </c>
       <c r="B35" t="n">
-        <v>79.13536834716797</v>
+        <v>79.13536071777344</v>
       </c>
       <c r="C35" t="n">
-        <v>80.21901391602279</v>
+        <v>80.21900618215462</v>
       </c>
       <c r="D35" t="n">
-        <v>77.90528277879942</v>
+        <v>77.90527526799671</v>
       </c>
       <c r="E35" t="n">
-        <v>78.19816277782689</v>
+        <v>78.19815523878781</v>
       </c>
       <c r="F35" t="n">
         <v>536566</v>
@@ -1132,16 +1132,16 @@
         <v>43266</v>
       </c>
       <c r="B36" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C36" t="n">
-        <v>79.22322984533973</v>
+        <v>79.22323748886292</v>
       </c>
       <c r="D36" t="n">
-        <v>75.12294738386028</v>
+        <v>75.12295463178479</v>
       </c>
       <c r="E36" t="n">
-        <v>79.13536287241121</v>
+        <v>79.13537050745691</v>
       </c>
       <c r="F36" t="n">
         <v>389566</v>
@@ -1152,16 +1152,16 @@
         <v>43269</v>
       </c>
       <c r="B37" t="n">
-        <v>77.26095581054688</v>
+        <v>77.26094055175781</v>
       </c>
       <c r="C37" t="n">
-        <v>79.07679389586734</v>
+        <v>79.07677827845613</v>
       </c>
       <c r="D37" t="n">
-        <v>76.7337762907847</v>
+        <v>76.73376113611189</v>
       </c>
       <c r="E37" t="n">
-        <v>79.07679389586734</v>
+        <v>79.07677827845613</v>
       </c>
       <c r="F37" t="n">
         <v>465333</v>
@@ -1192,16 +1192,16 @@
         <v>43271</v>
       </c>
       <c r="B39" t="n">
-        <v>84.34858703613281</v>
+        <v>84.34857177734375</v>
       </c>
       <c r="C39" t="n">
-        <v>85.52009218942361</v>
+        <v>85.52007671870746</v>
       </c>
       <c r="D39" t="n">
-        <v>81.71268926885634</v>
+        <v>81.71267448690524</v>
       </c>
       <c r="E39" t="n">
-        <v>82.03485579289816</v>
+        <v>82.03484095266663</v>
       </c>
       <c r="F39" t="n">
         <v>141600</v>
@@ -1212,16 +1212,16 @@
         <v>43272</v>
       </c>
       <c r="B40" t="n">
-        <v>82.62059783935547</v>
+        <v>82.62060546875</v>
       </c>
       <c r="C40" t="n">
-        <v>85.46150827396475</v>
+        <v>85.46151616569612</v>
       </c>
       <c r="D40" t="n">
-        <v>80.10185388772712</v>
+        <v>80.10186128453448</v>
       </c>
       <c r="E40" t="n">
-        <v>83.46994380860144</v>
+        <v>83.46995151642673</v>
       </c>
       <c r="F40" t="n">
         <v>246900</v>
@@ -1232,16 +1232,16 @@
         <v>43273</v>
       </c>
       <c r="B41" t="n">
-        <v>84.934326171875</v>
+        <v>84.93434143066406</v>
       </c>
       <c r="C41" t="n">
-        <v>85.52007865582475</v>
+        <v>85.52009401984657</v>
       </c>
       <c r="D41" t="n">
-        <v>81.21479082295949</v>
+        <v>81.21480541351926</v>
       </c>
       <c r="E41" t="n">
-        <v>82.03484281083975</v>
+        <v>82.03485754872511</v>
       </c>
       <c r="F41" t="n">
         <v>298800</v>
@@ -1252,16 +1252,16 @@
         <v>43276</v>
       </c>
       <c r="B42" t="n">
-        <v>86.39871215820312</v>
+        <v>86.39869689941406</v>
       </c>
       <c r="C42" t="n">
-        <v>86.39871215820312</v>
+        <v>86.39869689941406</v>
       </c>
       <c r="D42" t="n">
-        <v>84.348574715285</v>
+        <v>84.34855981856863</v>
       </c>
       <c r="E42" t="n">
-        <v>85.87153268175327</v>
+        <v>85.87151751606882</v>
       </c>
       <c r="F42" t="n">
         <v>909166</v>
@@ -1272,16 +1272,16 @@
         <v>43277</v>
       </c>
       <c r="B43" t="n">
-        <v>86.75016784667969</v>
+        <v>86.75018310546875</v>
       </c>
       <c r="C43" t="n">
-        <v>87.86309984890605</v>
+        <v>87.86311530345259</v>
       </c>
       <c r="D43" t="n">
-        <v>85.08076984334015</v>
+        <v>85.08078480849298</v>
       </c>
       <c r="E43" t="n">
-        <v>86.60372785728207</v>
+        <v>86.60374309031327</v>
       </c>
       <c r="F43" t="n">
         <v>153233</v>
@@ -1312,16 +1312,16 @@
         <v>43279</v>
       </c>
       <c r="B45" t="n">
-        <v>88.68315124511719</v>
+        <v>88.68315887451172</v>
       </c>
       <c r="C45" t="n">
-        <v>88.68315124511719</v>
+        <v>88.68315887451172</v>
       </c>
       <c r="D45" t="n">
-        <v>85.373641770075</v>
+        <v>85.37364911475306</v>
       </c>
       <c r="E45" t="n">
-        <v>87.86309922748598</v>
+        <v>87.8631067863316</v>
       </c>
       <c r="F45" t="n">
         <v>922066</v>
@@ -1332,16 +1332,16 @@
         <v>43280</v>
       </c>
       <c r="B46" t="n">
-        <v>87.54093170166016</v>
+        <v>87.54091644287109</v>
       </c>
       <c r="C46" t="n">
-        <v>89.41534267530913</v>
+        <v>89.41532708980156</v>
       </c>
       <c r="D46" t="n">
-        <v>85.37364075477042</v>
+        <v>85.37362587375019</v>
       </c>
       <c r="E46" t="n">
-        <v>87.45307217863621</v>
+        <v>87.45305693516146</v>
       </c>
       <c r="F46" t="n">
         <v>492266</v>
@@ -1372,16 +1372,16 @@
         <v>43284</v>
       </c>
       <c r="B48" t="n">
-        <v>85.52008056640625</v>
+        <v>85.52009582519531</v>
       </c>
       <c r="C48" t="n">
-        <v>87.21876504228447</v>
+        <v>87.2187806041587</v>
       </c>
       <c r="D48" t="n">
-        <v>83.93854212098695</v>
+        <v>83.93855709759244</v>
       </c>
       <c r="E48" t="n">
-        <v>86.72087951633988</v>
+        <v>86.72089498937964</v>
       </c>
       <c r="F48" t="n">
         <v>142500</v>
@@ -1392,16 +1392,16 @@
         <v>43285</v>
       </c>
       <c r="B49" t="n">
-        <v>85.78366851806641</v>
+        <v>85.78367614746094</v>
       </c>
       <c r="C49" t="n">
-        <v>87.07232690802138</v>
+        <v>87.07233465202611</v>
       </c>
       <c r="D49" t="n">
-        <v>84.14355716282856</v>
+        <v>84.14356464635551</v>
       </c>
       <c r="E49" t="n">
-        <v>86.66229348302694</v>
+        <v>86.66230119056429</v>
       </c>
       <c r="F49" t="n">
         <v>320933</v>
@@ -1412,16 +1412,16 @@
         <v>43286</v>
       </c>
       <c r="B50" t="n">
-        <v>85.52008056640625</v>
+        <v>85.52009582519531</v>
       </c>
       <c r="C50" t="n">
-        <v>86.31084606499235</v>
+        <v>86.31086146487253</v>
       </c>
       <c r="D50" t="n">
-        <v>84.28999510885791</v>
+        <v>84.29001014817086</v>
       </c>
       <c r="E50" t="n">
-        <v>85.78367403143302</v>
+        <v>85.78368933725334</v>
       </c>
       <c r="F50" t="n">
         <v>391100</v>
@@ -1432,16 +1432,16 @@
         <v>43287</v>
       </c>
       <c r="B51" t="n">
-        <v>83.61638641357422</v>
+        <v>83.61637878417969</v>
       </c>
       <c r="C51" t="n">
-        <v>85.57865698425219</v>
+        <v>85.57864917581456</v>
       </c>
       <c r="D51" t="n">
-        <v>83.61638641357422</v>
+        <v>83.61637878417969</v>
       </c>
       <c r="E51" t="n">
-        <v>85.52008396669386</v>
+        <v>85.52007616360061</v>
       </c>
       <c r="F51" t="n">
         <v>769100</v>
@@ -1452,16 +1452,16 @@
         <v>43291</v>
       </c>
       <c r="B52" t="n">
-        <v>84.23142242431641</v>
+        <v>84.23143005371094</v>
       </c>
       <c r="C52" t="n">
-        <v>86.07654689375923</v>
+        <v>86.07655469027884</v>
       </c>
       <c r="D52" t="n">
-        <v>83.17706345656418</v>
+        <v>83.17707099045847</v>
       </c>
       <c r="E52" t="n">
-        <v>84.14356290112728</v>
+        <v>84.14357052256381</v>
       </c>
       <c r="F52" t="n">
         <v>281266</v>
@@ -1492,16 +1492,16 @@
         <v>43293</v>
       </c>
       <c r="B54" t="n">
-        <v>87.07233428955078</v>
+        <v>87.07231903076172</v>
       </c>
       <c r="C54" t="n">
-        <v>87.13090730598122</v>
+        <v>87.13089203692768</v>
       </c>
       <c r="D54" t="n">
-        <v>82.35701281247128</v>
+        <v>82.35699838000778</v>
       </c>
       <c r="E54" t="n">
-        <v>83.90925733385612</v>
+        <v>83.90924262937314</v>
       </c>
       <c r="F54" t="n">
         <v>235333</v>
@@ -1552,16 +1552,16 @@
         <v>43298</v>
       </c>
       <c r="B57" t="n">
-        <v>83.08919525146484</v>
+        <v>83.08920288085938</v>
       </c>
       <c r="C57" t="n">
-        <v>84.58286657558465</v>
+        <v>84.58287434213068</v>
       </c>
       <c r="D57" t="n">
-        <v>82.35700284173974</v>
+        <v>82.35701040390309</v>
       </c>
       <c r="E57" t="n">
-        <v>84.11426015613218</v>
+        <v>84.11426787964996</v>
       </c>
       <c r="F57" t="n">
         <v>152666</v>
@@ -1572,16 +1572,16 @@
         <v>43299</v>
       </c>
       <c r="B58" t="n">
-        <v>85.90081787109375</v>
+        <v>85.90081024169922</v>
       </c>
       <c r="C58" t="n">
-        <v>85.90081787109375</v>
+        <v>85.90081024169922</v>
       </c>
       <c r="D58" t="n">
-        <v>82.73774850917258</v>
+        <v>82.73774116071021</v>
       </c>
       <c r="E58" t="n">
-        <v>82.91347499862636</v>
+        <v>82.91346763455662</v>
       </c>
       <c r="F58" t="n">
         <v>444433</v>
@@ -1592,16 +1592,16 @@
         <v>43300</v>
       </c>
       <c r="B59" t="n">
-        <v>85.19792938232422</v>
+        <v>85.19790649414062</v>
       </c>
       <c r="C59" t="n">
-        <v>86.54516856045777</v>
+        <v>86.54514531034216</v>
       </c>
       <c r="D59" t="n">
-        <v>83.61639810120876</v>
+        <v>83.6163756378991</v>
       </c>
       <c r="E59" t="n">
-        <v>85.52009592042123</v>
+        <v>85.52007294568851</v>
       </c>
       <c r="F59" t="n">
         <v>169366</v>
@@ -1632,16 +1632,16 @@
         <v>43304</v>
       </c>
       <c r="B61" t="n">
-        <v>87.6580810546875</v>
+        <v>87.65808868408203</v>
       </c>
       <c r="C61" t="n">
-        <v>89.26890593519866</v>
+        <v>89.26891370479268</v>
       </c>
       <c r="D61" t="n">
-        <v>86.7208756119757</v>
+        <v>86.72088315979977</v>
       </c>
       <c r="E61" t="n">
-        <v>89.00531248203944</v>
+        <v>89.00532022869139</v>
       </c>
       <c r="F61" t="n">
         <v>145300</v>
@@ -1672,16 +1672,16 @@
         <v>43306</v>
       </c>
       <c r="B63" t="n">
-        <v>83.99712371826172</v>
+        <v>83.99711608886719</v>
       </c>
       <c r="C63" t="n">
-        <v>89.91323668020036</v>
+        <v>89.91322851344979</v>
       </c>
       <c r="D63" t="n">
-        <v>83.99712371826172</v>
+        <v>83.99711608886719</v>
       </c>
       <c r="E63" t="n">
-        <v>88.77101817832556</v>
+        <v>88.77101011532184</v>
       </c>
       <c r="F63" t="n">
         <v>653300</v>
@@ -1692,16 +1692,16 @@
         <v>43307</v>
       </c>
       <c r="B64" t="n">
-        <v>80.57046508789062</v>
+        <v>80.57045745849609</v>
       </c>
       <c r="C64" t="n">
-        <v>84.84646679649717</v>
+        <v>84.84645876219862</v>
       </c>
       <c r="D64" t="n">
-        <v>79.9554260419345</v>
+        <v>79.95541847077936</v>
       </c>
       <c r="E64" t="n">
-        <v>84.14356822179629</v>
+        <v>84.14356025405675</v>
       </c>
       <c r="F64" t="n">
         <v>454233</v>
@@ -1712,16 +1712,16 @@
         <v>43308</v>
       </c>
       <c r="B65" t="n">
-        <v>82.62059783935547</v>
+        <v>82.62060546875</v>
       </c>
       <c r="C65" t="n">
-        <v>82.62059783935547</v>
+        <v>82.62060546875</v>
       </c>
       <c r="D65" t="n">
-        <v>80.04328087200228</v>
+        <v>80.04328826340087</v>
       </c>
       <c r="E65" t="n">
-        <v>81.24407983209161</v>
+        <v>81.24408733437501</v>
       </c>
       <c r="F65" t="n">
         <v>199833</v>
@@ -1752,16 +1752,16 @@
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>82.47415924072266</v>
+        <v>82.47415161132812</v>
       </c>
       <c r="C67" t="n">
-        <v>82.56202621403682</v>
+        <v>82.56201857651402</v>
       </c>
       <c r="D67" t="n">
-        <v>79.3696627348224</v>
+        <v>79.36965539261392</v>
       </c>
       <c r="E67" t="n">
-        <v>81.24408120030263</v>
+        <v>81.24407368469829</v>
       </c>
       <c r="F67" t="n">
         <v>430700</v>
@@ -1772,16 +1772,16 @@
         <v>43313</v>
       </c>
       <c r="B68" t="n">
-        <v>84.02640533447266</v>
+        <v>84.02641296386719</v>
       </c>
       <c r="C68" t="n">
-        <v>84.02640533447266</v>
+        <v>84.02641296386719</v>
       </c>
       <c r="D68" t="n">
-        <v>81.41980199786791</v>
+        <v>81.41980939058915</v>
       </c>
       <c r="E68" t="n">
-        <v>81.44908850417296</v>
+        <v>81.44909589955336</v>
       </c>
       <c r="F68" t="n">
         <v>89600</v>
@@ -1832,16 +1832,16 @@
         <v>43318</v>
       </c>
       <c r="B71" t="n">
-        <v>81.33193969726562</v>
+        <v>81.33193206787109</v>
       </c>
       <c r="C71" t="n">
-        <v>83.55780368312388</v>
+        <v>83.55779584493075</v>
       </c>
       <c r="D71" t="n">
-        <v>81.1269266931205</v>
+        <v>81.12691908295734</v>
       </c>
       <c r="E71" t="n">
-        <v>83.38207718696417</v>
+        <v>83.38206936525518</v>
       </c>
       <c r="F71" t="n">
         <v>242633</v>
@@ -1852,16 +1852,16 @@
         <v>43319</v>
       </c>
       <c r="B72" t="n">
-        <v>79.13536834716797</v>
+        <v>79.13536071777344</v>
       </c>
       <c r="C72" t="n">
-        <v>81.41981297413815</v>
+        <v>81.41980512450165</v>
       </c>
       <c r="D72" t="n">
-        <v>79.13536834716797</v>
+        <v>79.13536071777344</v>
       </c>
       <c r="E72" t="n">
-        <v>81.27337297462441</v>
+        <v>81.2733651391061</v>
       </c>
       <c r="F72" t="n">
         <v>212866</v>
@@ -1872,16 +1872,16 @@
         <v>43320</v>
       </c>
       <c r="B73" t="n">
-        <v>78.78391265869141</v>
+        <v>78.78389739990234</v>
       </c>
       <c r="C73" t="n">
-        <v>80.24829770772469</v>
+        <v>80.24828216531499</v>
       </c>
       <c r="D73" t="n">
-        <v>77.11451459658318</v>
+        <v>77.11449966112144</v>
       </c>
       <c r="E73" t="n">
-        <v>79.77969866305264</v>
+        <v>79.77968321140075</v>
       </c>
       <c r="F73" t="n">
         <v>270133</v>
@@ -1892,16 +1892,16 @@
         <v>43321</v>
       </c>
       <c r="B74" t="n">
-        <v>78.95964050292969</v>
+        <v>78.95962524414062</v>
       </c>
       <c r="C74" t="n">
-        <v>79.13536700972674</v>
+        <v>79.13535171697887</v>
       </c>
       <c r="D74" t="n">
-        <v>76.85092986961286</v>
+        <v>76.85091501832781</v>
       </c>
       <c r="E74" t="n">
-        <v>78.19816145622507</v>
+        <v>78.19814634459027</v>
       </c>
       <c r="F74" t="n">
         <v>546266</v>
@@ -1912,16 +1912,16 @@
         <v>43322</v>
       </c>
       <c r="B75" t="n">
-        <v>78.87177276611328</v>
+        <v>78.87178802490234</v>
       </c>
       <c r="C75" t="n">
-        <v>80.3654441943301</v>
+        <v>80.36545974208968</v>
       </c>
       <c r="D75" t="n">
-        <v>78.1688668120708</v>
+        <v>78.16888193487341</v>
       </c>
       <c r="E75" t="n">
-        <v>79.13535877475577</v>
+        <v>79.13537408453904</v>
       </c>
       <c r="F75" t="n">
         <v>176700</v>
@@ -1932,16 +1932,16 @@
         <v>43325</v>
       </c>
       <c r="B76" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C76" t="n">
-        <v>80.10185488514145</v>
+        <v>80.10186261343512</v>
       </c>
       <c r="D76" t="n">
-        <v>77.7588448480072</v>
+        <v>77.75885235024531</v>
       </c>
       <c r="E76" t="n">
-        <v>78.93034986657432</v>
+        <v>78.9303574818402</v>
       </c>
       <c r="F76" t="n">
         <v>160400</v>
@@ -1952,16 +1952,16 @@
         <v>43326</v>
       </c>
       <c r="B77" t="n">
-        <v>77.46595764160156</v>
+        <v>77.46597290039062</v>
       </c>
       <c r="C77" t="n">
-        <v>78.46174351789847</v>
+        <v>78.46175897283159</v>
       </c>
       <c r="D77" t="n">
-        <v>74.44932840370932</v>
+        <v>74.44934306830048</v>
       </c>
       <c r="E77" t="n">
-        <v>78.46174351789847</v>
+        <v>78.46175897283159</v>
       </c>
       <c r="F77" t="n">
         <v>524933</v>
@@ -1972,16 +1972,16 @@
         <v>43327</v>
       </c>
       <c r="B78" t="n">
-        <v>76.14801788330078</v>
+        <v>76.14802551269531</v>
       </c>
       <c r="C78" t="n">
-        <v>77.67097585752774</v>
+        <v>77.67098363950991</v>
       </c>
       <c r="D78" t="n">
-        <v>76.14801788330078</v>
+        <v>76.14802551269531</v>
       </c>
       <c r="E78" t="n">
-        <v>77.02665034852674</v>
+        <v>77.0266580659529</v>
       </c>
       <c r="F78" t="n">
         <v>702366</v>
@@ -2052,16 +2052,16 @@
         <v>43333</v>
       </c>
       <c r="B82" t="n">
-        <v>71.60843658447266</v>
+        <v>71.60842132568359</v>
       </c>
       <c r="C82" t="n">
-        <v>72.57492875517822</v>
+        <v>72.57491329044277</v>
       </c>
       <c r="D82" t="n">
-        <v>70.31977787411573</v>
+        <v>70.31976288992242</v>
       </c>
       <c r="E82" t="n">
-        <v>71.63772309748668</v>
+        <v>71.63770783245707</v>
       </c>
       <c r="F82" t="n">
         <v>1384333</v>
@@ -2092,16 +2092,16 @@
         <v>43335</v>
       </c>
       <c r="B84" t="n">
-        <v>73.36569213867188</v>
+        <v>73.36568450927734</v>
       </c>
       <c r="C84" t="n">
-        <v>74.33218418147305</v>
+        <v>74.33217645157174</v>
       </c>
       <c r="D84" t="n">
-        <v>71.90130709577721</v>
+        <v>71.901299618666</v>
       </c>
       <c r="E84" t="n">
-        <v>72.57491915070047</v>
+        <v>72.57491160353946</v>
       </c>
       <c r="F84" t="n">
         <v>126566</v>
@@ -2112,16 +2112,16 @@
         <v>43336</v>
       </c>
       <c r="B85" t="n">
-        <v>75.29866027832031</v>
+        <v>75.29867553710938</v>
       </c>
       <c r="C85" t="n">
-        <v>75.56225370123892</v>
+        <v>75.56226901344348</v>
       </c>
       <c r="D85" t="n">
-        <v>73.21923663913734</v>
+        <v>73.21925147654457</v>
       </c>
       <c r="E85" t="n">
-        <v>74.09786896845617</v>
+        <v>74.0978839839126</v>
       </c>
       <c r="F85" t="n">
         <v>164200</v>
@@ -2132,16 +2132,16 @@
         <v>43339</v>
       </c>
       <c r="B86" t="n">
-        <v>76.03086853027344</v>
+        <v>76.03086090087891</v>
       </c>
       <c r="C86" t="n">
-        <v>76.44089455354266</v>
+        <v>76.44088688300364</v>
       </c>
       <c r="D86" t="n">
-        <v>73.65856446957658</v>
+        <v>73.6585570782333</v>
       </c>
       <c r="E86" t="n">
-        <v>75.29867601090092</v>
+        <v>75.29866845497898</v>
       </c>
       <c r="F86" t="n">
         <v>318500</v>
@@ -2152,16 +2152,16 @@
         <v>43340</v>
       </c>
       <c r="B87" t="n">
-        <v>75.2401123046875</v>
+        <v>75.24010467529297</v>
       </c>
       <c r="C87" t="n">
-        <v>76.14803143900558</v>
+        <v>76.14802371754747</v>
       </c>
       <c r="D87" t="n">
-        <v>73.89288058367451</v>
+        <v>73.89287309089012</v>
       </c>
       <c r="E87" t="n">
-        <v>75.91373188931819</v>
+        <v>75.91372419161821</v>
       </c>
       <c r="F87" t="n">
         <v>298400</v>
@@ -2172,16 +2172,16 @@
         <v>43341</v>
       </c>
       <c r="B88" t="n">
-        <v>74.42002868652344</v>
+        <v>74.4200439453125</v>
       </c>
       <c r="C88" t="n">
-        <v>76.14800685934951</v>
+        <v>76.14802247243639</v>
       </c>
       <c r="D88" t="n">
-        <v>73.45353683881748</v>
+        <v>73.45355189944088</v>
       </c>
       <c r="E88" t="n">
-        <v>75.67940046298681</v>
+        <v>75.6794159799925</v>
       </c>
       <c r="F88" t="n">
         <v>162200</v>
@@ -2192,16 +2192,16 @@
         <v>43342</v>
       </c>
       <c r="B89" t="n">
-        <v>75.85515594482422</v>
+        <v>75.85514831542969</v>
       </c>
       <c r="C89" t="n">
-        <v>75.85515594482422</v>
+        <v>75.85514831542969</v>
       </c>
       <c r="D89" t="n">
-        <v>73.39499190559565</v>
+        <v>73.39498452364062</v>
       </c>
       <c r="E89" t="n">
-        <v>74.1857575881604</v>
+        <v>74.18575012667137</v>
       </c>
       <c r="F89" t="n">
         <v>206466</v>
@@ -2212,16 +2212,16 @@
         <v>43343</v>
       </c>
       <c r="B90" t="n">
-        <v>75.82585906982422</v>
+        <v>75.82585144042969</v>
       </c>
       <c r="C90" t="n">
-        <v>76.49947860263404</v>
+        <v>76.49947090546172</v>
       </c>
       <c r="D90" t="n">
-        <v>74.91794000535143</v>
+        <v>74.91793246730929</v>
       </c>
       <c r="E90" t="n">
-        <v>76.11873907058879</v>
+        <v>76.11873141172546</v>
       </c>
       <c r="F90" t="n">
         <v>295200</v>
@@ -2232,16 +2232,16 @@
         <v>43346</v>
       </c>
       <c r="B91" t="n">
-        <v>74.65435028076172</v>
+        <v>74.65434265136719</v>
       </c>
       <c r="C91" t="n">
-        <v>76.06015484964274</v>
+        <v>76.06014707658026</v>
       </c>
       <c r="D91" t="n">
-        <v>73.98073078117974</v>
+        <v>73.9807232206266</v>
       </c>
       <c r="E91" t="n">
-        <v>75.76728231157261</v>
+        <v>75.76727456844061</v>
       </c>
       <c r="F91" t="n">
         <v>159200</v>
@@ -2252,16 +2252,16 @@
         <v>43347</v>
       </c>
       <c r="B92" t="n">
-        <v>73.04354095458984</v>
+        <v>73.04353332519531</v>
       </c>
       <c r="C92" t="n">
-        <v>74.42005931039705</v>
+        <v>74.42005153722525</v>
       </c>
       <c r="D92" t="n">
-        <v>71.87203565397735</v>
+        <v>71.8720281469465</v>
       </c>
       <c r="E92" t="n">
-        <v>74.3907727951191</v>
+        <v>74.39076502500627</v>
       </c>
       <c r="F92" t="n">
         <v>196200</v>
@@ -2272,16 +2272,16 @@
         <v>43348</v>
       </c>
       <c r="B93" t="n">
-        <v>73.24852752685547</v>
+        <v>73.24854278564453</v>
       </c>
       <c r="C93" t="n">
-        <v>75.65011773859295</v>
+        <v>75.65013349767</v>
       </c>
       <c r="D93" t="n">
-        <v>72.80921506002102</v>
+        <v>72.80923022729456</v>
       </c>
       <c r="E93" t="n">
-        <v>72.89707457408937</v>
+        <v>72.89708975966539</v>
       </c>
       <c r="F93" t="n">
         <v>95400</v>
@@ -2292,16 +2292,16 @@
         <v>43349</v>
       </c>
       <c r="B94" t="n">
-        <v>74.21502685546875</v>
+        <v>74.21503448486328</v>
       </c>
       <c r="C94" t="n">
-        <v>76.52875778485787</v>
+        <v>76.52876565210674</v>
       </c>
       <c r="D94" t="n">
-        <v>71.46198341524806</v>
+        <v>71.4619907616264</v>
       </c>
       <c r="E94" t="n">
-        <v>74.15645384022376</v>
+        <v>74.15646146359693</v>
       </c>
       <c r="F94" t="n">
         <v>139100</v>
@@ -2312,16 +2312,16 @@
         <v>43353</v>
       </c>
       <c r="B95" t="n">
-        <v>75.50367736816406</v>
+        <v>75.50370788574219</v>
       </c>
       <c r="C95" t="n">
-        <v>76.73376269634934</v>
+        <v>76.73379371111153</v>
       </c>
       <c r="D95" t="n">
-        <v>74.42003201089904</v>
+        <v>74.42006209048218</v>
       </c>
       <c r="E95" t="n">
-        <v>75.65011733908432</v>
+        <v>75.65014791585152</v>
       </c>
       <c r="F95" t="n">
         <v>157400</v>
@@ -2332,16 +2332,16 @@
         <v>43354</v>
       </c>
       <c r="B96" t="n">
-        <v>73.45353698730469</v>
+        <v>73.45355224609375</v>
       </c>
       <c r="C96" t="n">
-        <v>75.18151516362389</v>
+        <v>75.18153078137257</v>
       </c>
       <c r="D96" t="n">
-        <v>73.45353698730469</v>
+        <v>73.45355224609375</v>
       </c>
       <c r="E96" t="n">
-        <v>74.44932278849616</v>
+        <v>74.44933825414368</v>
       </c>
       <c r="F96" t="n">
         <v>250666</v>
@@ -2372,16 +2372,16 @@
         <v>43356</v>
       </c>
       <c r="B98" t="n">
-        <v>71.60843658447266</v>
+        <v>71.60842132568359</v>
       </c>
       <c r="C98" t="n">
-        <v>73.86358746553515</v>
+        <v>73.86357172620396</v>
       </c>
       <c r="D98" t="n">
-        <v>70.43693137442035</v>
+        <v>70.4369163652632</v>
       </c>
       <c r="E98" t="n">
-        <v>73.77572792649305</v>
+        <v>73.77571220588352</v>
       </c>
       <c r="F98" t="n">
         <v>250366</v>
@@ -2412,16 +2412,16 @@
         <v>43360</v>
       </c>
       <c r="B100" t="n">
-        <v>73.48284149169922</v>
+        <v>73.48281860351562</v>
       </c>
       <c r="C100" t="n">
-        <v>74.06860149389196</v>
+        <v>74.06857842325786</v>
       </c>
       <c r="D100" t="n">
-        <v>69.79259220877361</v>
+        <v>69.79257047001622</v>
       </c>
       <c r="E100" t="n">
-        <v>70.02689174070201</v>
+        <v>70.02686992896581</v>
       </c>
       <c r="F100" t="n">
         <v>114333</v>
@@ -2492,16 +2492,16 @@
         <v>43364</v>
       </c>
       <c r="B104" t="n">
-        <v>69.353271484375</v>
+        <v>69.35326385498047</v>
       </c>
       <c r="C104" t="n">
-        <v>71.16910940144096</v>
+        <v>71.16910157229026</v>
       </c>
       <c r="D104" t="n">
-        <v>67.88888654791837</v>
+        <v>67.88887907961748</v>
       </c>
       <c r="E104" t="n">
-        <v>67.94745956193762</v>
+        <v>67.94745208719324</v>
       </c>
       <c r="F104" t="n">
         <v>293166</v>
@@ -2512,16 +2512,16 @@
         <v>43367</v>
       </c>
       <c r="B105" t="n">
-        <v>65.4580078125</v>
+        <v>65.45800018310547</v>
       </c>
       <c r="C105" t="n">
-        <v>69.49971743662823</v>
+        <v>69.49970933615616</v>
       </c>
       <c r="D105" t="n">
-        <v>65.37014828392535</v>
+        <v>65.37014066477121</v>
       </c>
       <c r="E105" t="n">
-        <v>69.35327744075623</v>
+        <v>69.35326935735233</v>
       </c>
       <c r="F105" t="n">
         <v>831466</v>
@@ -2532,16 +2532,16 @@
         <v>43368</v>
       </c>
       <c r="B106" t="n">
-        <v>63.90575408935547</v>
+        <v>63.90575790405273</v>
       </c>
       <c r="C106" t="n">
-        <v>67.21526326118382</v>
+        <v>67.21526727343412</v>
       </c>
       <c r="D106" t="n">
-        <v>61.62131356977399</v>
+        <v>61.62131724810718</v>
       </c>
       <c r="E106" t="n">
-        <v>64.46222003555015</v>
+        <v>64.46222388346429</v>
       </c>
       <c r="F106" t="n">
         <v>629433</v>
@@ -2572,16 +2572,16 @@
         <v>43370</v>
       </c>
       <c r="B108" t="n">
-        <v>68.59178924560547</v>
+        <v>68.591796875</v>
       </c>
       <c r="C108" t="n">
-        <v>69.85115367658149</v>
+        <v>69.85116144605384</v>
       </c>
       <c r="D108" t="n">
-        <v>65.07725960672998</v>
+        <v>65.07726684520698</v>
       </c>
       <c r="E108" t="n">
-        <v>65.48729303009652</v>
+        <v>65.48730031418111</v>
       </c>
       <c r="F108" t="n">
         <v>605400</v>
@@ -2592,16 +2592,16 @@
         <v>43371</v>
       </c>
       <c r="B109" t="n">
-        <v>70.29046630859375</v>
+        <v>70.29048156738281</v>
       </c>
       <c r="C109" t="n">
-        <v>71.34482509080165</v>
+        <v>71.34484057847294</v>
       </c>
       <c r="D109" t="n">
-        <v>67.3324103764931</v>
+        <v>67.33242499314171</v>
       </c>
       <c r="E109" t="n">
-        <v>68.59178212497824</v>
+        <v>68.59179701501368</v>
       </c>
       <c r="F109" t="n">
         <v>612400</v>
@@ -2612,16 +2612,16 @@
         <v>43374</v>
       </c>
       <c r="B110" t="n">
-        <v>69.11896514892578</v>
+        <v>69.11897277832031</v>
       </c>
       <c r="C110" t="n">
-        <v>70.20261060743866</v>
+        <v>70.20261835644665</v>
       </c>
       <c r="D110" t="n">
-        <v>68.41606662967828</v>
+        <v>68.41607418148644</v>
       </c>
       <c r="E110" t="n">
-        <v>70.20261060743866</v>
+        <v>70.20261835644665</v>
       </c>
       <c r="F110" t="n">
         <v>385466</v>
@@ -2632,16 +2632,16 @@
         <v>43375</v>
       </c>
       <c r="B111" t="n">
-        <v>69.14826202392578</v>
+        <v>69.14825439453125</v>
       </c>
       <c r="C111" t="n">
-        <v>70.26119403669841</v>
+        <v>70.2611862845098</v>
       </c>
       <c r="D111" t="n">
-        <v>67.97674954589061</v>
+        <v>67.97674204575357</v>
       </c>
       <c r="E111" t="n">
-        <v>69.20683504094097</v>
+        <v>69.20682740508386</v>
       </c>
       <c r="F111" t="n">
         <v>391400</v>
@@ -2652,16 +2652,16 @@
         <v>43376</v>
       </c>
       <c r="B112" t="n">
-        <v>70.43692016601562</v>
+        <v>70.43691253662109</v>
       </c>
       <c r="C112" t="n">
-        <v>73.59998968842636</v>
+        <v>73.59998171642307</v>
       </c>
       <c r="D112" t="n">
-        <v>69.08968119576403</v>
+        <v>69.08967371229606</v>
       </c>
       <c r="E112" t="n">
-        <v>70.58335270778446</v>
+        <v>70.58334506252905</v>
       </c>
       <c r="F112" t="n">
         <v>463466</v>
@@ -2672,16 +2672,16 @@
         <v>43377</v>
       </c>
       <c r="B113" t="n">
-        <v>70.29046630859375</v>
+        <v>70.29048156738281</v>
       </c>
       <c r="C113" t="n">
-        <v>72.13559045333467</v>
+        <v>72.13560611266682</v>
       </c>
       <c r="D113" t="n">
-        <v>67.71314980647165</v>
+        <v>67.71316450577191</v>
       </c>
       <c r="E113" t="n">
-        <v>70.55405228002282</v>
+        <v>70.55406759603163</v>
       </c>
       <c r="F113" t="n">
         <v>201700</v>
@@ -2692,16 +2692,16 @@
         <v>43378</v>
       </c>
       <c r="B114" t="n">
-        <v>68.26962280273438</v>
+        <v>68.26961517333984</v>
       </c>
       <c r="C114" t="n">
-        <v>71.60841851217266</v>
+        <v>71.60841050965479</v>
       </c>
       <c r="D114" t="n">
-        <v>67.36170388719449</v>
+        <v>67.36169635926342</v>
       </c>
       <c r="E114" t="n">
-        <v>71.60841851217266</v>
+        <v>71.60841050965479</v>
       </c>
       <c r="F114" t="n">
         <v>364566</v>
@@ -2712,16 +2712,16 @@
         <v>43381</v>
       </c>
       <c r="B115" t="n">
-        <v>69.55828857421875</v>
+        <v>69.55829620361328</v>
       </c>
       <c r="C115" t="n">
-        <v>70.90552011365561</v>
+        <v>70.90552789081917</v>
       </c>
       <c r="D115" t="n">
-        <v>68.8553825716439</v>
+        <v>68.85539012394126</v>
       </c>
       <c r="E115" t="n">
-        <v>68.8553825716439</v>
+        <v>68.85539012394126</v>
       </c>
       <c r="F115" t="n">
         <v>697200</v>
@@ -2732,16 +2732,16 @@
         <v>43382</v>
       </c>
       <c r="B116" t="n">
-        <v>68.26962280273438</v>
+        <v>68.26961517333984</v>
       </c>
       <c r="C116" t="n">
-        <v>71.75485848853327</v>
+        <v>71.75485046965017</v>
       </c>
       <c r="D116" t="n">
-        <v>68.26962280273438</v>
+        <v>68.26961517333984</v>
       </c>
       <c r="E116" t="n">
-        <v>69.96830716307632</v>
+        <v>69.96829934384724</v>
       </c>
       <c r="F116" t="n">
         <v>433600</v>
@@ -2752,16 +2752,16 @@
         <v>43383</v>
       </c>
       <c r="B117" t="n">
-        <v>69.14826202392578</v>
+        <v>69.14825439453125</v>
       </c>
       <c r="C117" t="n">
-        <v>71.72557904805687</v>
+        <v>71.72557113429701</v>
       </c>
       <c r="D117" t="n">
-        <v>67.24455704021138</v>
+        <v>67.24454962085997</v>
       </c>
       <c r="E117" t="n">
-        <v>67.3617105224891</v>
+        <v>67.36170309021169</v>
       </c>
       <c r="F117" t="n">
         <v>149833</v>
@@ -2792,16 +2792,16 @@
         <v>43388</v>
       </c>
       <c r="B119" t="n">
-        <v>72.04773712158203</v>
+        <v>72.0477294921875</v>
       </c>
       <c r="C119" t="n">
-        <v>72.89708309812396</v>
+        <v>72.89707537878911</v>
       </c>
       <c r="D119" t="n">
-        <v>66.77595711014101</v>
+        <v>66.77595003899427</v>
       </c>
       <c r="E119" t="n">
-        <v>71.5791380952637</v>
+        <v>71.5791305154908</v>
       </c>
       <c r="F119" t="n">
         <v>520433</v>
@@ -2852,16 +2852,16 @@
         <v>43391</v>
       </c>
       <c r="B122" t="n">
-        <v>75.56226348876953</v>
+        <v>75.562255859375</v>
       </c>
       <c r="C122" t="n">
-        <v>76.79234146090117</v>
+        <v>76.79233370730775</v>
       </c>
       <c r="D122" t="n">
-        <v>74.88864404099729</v>
+        <v>74.88863647961698</v>
       </c>
       <c r="E122" t="n">
-        <v>74.91793054772705</v>
+        <v>74.91792298338974</v>
       </c>
       <c r="F122" t="n">
         <v>252733</v>
@@ -2892,16 +2892,16 @@
         <v>43395</v>
       </c>
       <c r="B124" t="n">
-        <v>74.65435028076172</v>
+        <v>74.65434265136719</v>
       </c>
       <c r="C124" t="n">
-        <v>76.55804784708366</v>
+        <v>76.55804002313839</v>
       </c>
       <c r="D124" t="n">
-        <v>74.3907568034264</v>
+        <v>74.39074920097013</v>
       </c>
       <c r="E124" t="n">
-        <v>74.53719679658519</v>
+        <v>74.53718917916331</v>
       </c>
       <c r="F124" t="n">
         <v>312766</v>
@@ -2912,16 +2912,16 @@
         <v>43396</v>
       </c>
       <c r="B125" t="n">
-        <v>75.44510650634766</v>
+        <v>75.44511413574219</v>
       </c>
       <c r="C125" t="n">
-        <v>76.14801242817332</v>
+        <v>76.14802012864928</v>
       </c>
       <c r="D125" t="n">
-        <v>74.15644813241612</v>
+        <v>74.15645563149494</v>
       </c>
       <c r="E125" t="n">
-        <v>74.80078104350515</v>
+        <v>74.80078860774221</v>
       </c>
       <c r="F125" t="n">
         <v>244366</v>
@@ -2952,16 +2952,16 @@
         <v>43398</v>
       </c>
       <c r="B127" t="n">
-        <v>76.00157928466797</v>
+        <v>76.0015869140625</v>
       </c>
       <c r="C127" t="n">
-        <v>76.00157928466797</v>
+        <v>76.0015869140625</v>
       </c>
       <c r="D127" t="n">
-        <v>73.10209582063342</v>
+        <v>73.10210315896421</v>
       </c>
       <c r="E127" t="n">
-        <v>74.5664808066511</v>
+        <v>74.56648829198372</v>
       </c>
       <c r="F127" t="n">
         <v>495966</v>
@@ -2972,16 +2972,16 @@
         <v>43399</v>
       </c>
       <c r="B128" t="n">
-        <v>74.97650909423828</v>
+        <v>74.97649383544922</v>
       </c>
       <c r="C128" t="n">
-        <v>78.02243263911183</v>
+        <v>78.02241676043387</v>
       </c>
       <c r="D128" t="n">
-        <v>73.36569151925214</v>
+        <v>73.36567658828743</v>
       </c>
       <c r="E128" t="n">
-        <v>76.1187350787205</v>
+        <v>76.11871958747216</v>
       </c>
       <c r="F128" t="n">
         <v>546200</v>
@@ -2992,16 +2992,16 @@
         <v>43402</v>
       </c>
       <c r="B129" t="n">
-        <v>75.50367736816406</v>
+        <v>75.50370788574219</v>
       </c>
       <c r="C129" t="n">
-        <v>76.44088275450883</v>
+        <v>76.44091365089287</v>
       </c>
       <c r="D129" t="n">
-        <v>75.18151837003508</v>
+        <v>75.18154875740085</v>
       </c>
       <c r="E129" t="n">
-        <v>76.38230974543926</v>
+        <v>76.38234061814886</v>
       </c>
       <c r="F129" t="n">
         <v>188000</v>
@@ -3012,16 +3012,16 @@
         <v>43403</v>
       </c>
       <c r="B130" t="n">
-        <v>74.56646728515625</v>
+        <v>74.56648254394531</v>
       </c>
       <c r="C130" t="n">
-        <v>76.14800546463644</v>
+        <v>76.14802104706102</v>
       </c>
       <c r="D130" t="n">
-        <v>73.65854846053267</v>
+        <v>73.65856353353124</v>
       </c>
       <c r="E130" t="n">
-        <v>75.65011257416651</v>
+        <v>75.65012805470559</v>
       </c>
       <c r="F130" t="n">
         <v>1306966</v>
@@ -3032,16 +3032,16 @@
         <v>43404</v>
       </c>
       <c r="B131" t="n">
-        <v>74.62508392333984</v>
+        <v>74.62506103515625</v>
       </c>
       <c r="C131" t="n">
-        <v>76.61664155440354</v>
+        <v>76.61661805539134</v>
       </c>
       <c r="D131" t="n">
-        <v>73.86359724293376</v>
+        <v>73.86357458830497</v>
       </c>
       <c r="E131" t="n">
-        <v>75.67943577265314</v>
+        <v>75.67941256109036</v>
       </c>
       <c r="F131" t="n">
         <v>863500</v>
@@ -3052,16 +3052,16 @@
         <v>43405</v>
       </c>
       <c r="B132" t="n">
-        <v>75.35725402832031</v>
+        <v>75.35724639892578</v>
       </c>
       <c r="C132" t="n">
-        <v>78.08100355741267</v>
+        <v>78.08099565225757</v>
       </c>
       <c r="D132" t="n">
-        <v>74.15645505834372</v>
+        <v>74.15644755052168</v>
       </c>
       <c r="E132" t="n">
-        <v>75.65012655760316</v>
+        <v>75.65011889855732</v>
       </c>
       <c r="F132" t="n">
         <v>289433</v>
@@ -3112,16 +3112,16 @@
         <v>43411</v>
       </c>
       <c r="B135" t="n">
-        <v>77.31951141357422</v>
+        <v>77.31952667236328</v>
       </c>
       <c r="C135" t="n">
-        <v>79.04748958049328</v>
+        <v>79.047505180294</v>
       </c>
       <c r="D135" t="n">
-        <v>75.5622541917747</v>
+        <v>75.56226910377396</v>
       </c>
       <c r="E135" t="n">
-        <v>75.5622541917747</v>
+        <v>75.56226910377396</v>
       </c>
       <c r="F135" t="n">
         <v>375833</v>
@@ -3132,16 +3132,16 @@
         <v>43412</v>
       </c>
       <c r="B136" t="n">
-        <v>77.31951141357422</v>
+        <v>77.31952667236328</v>
       </c>
       <c r="C136" t="n">
-        <v>79.25250255062426</v>
+        <v>79.25251819088371</v>
       </c>
       <c r="D136" t="n">
-        <v>76.14800659904121</v>
+        <v>76.14802162663706</v>
       </c>
       <c r="E136" t="n">
-        <v>77.29022491044779</v>
+        <v>77.29024016345724</v>
       </c>
       <c r="F136" t="n">
         <v>245533</v>
@@ -3192,16 +3192,16 @@
         <v>43417</v>
       </c>
       <c r="B139" t="n">
-        <v>75.26938629150391</v>
+        <v>75.26939392089844</v>
       </c>
       <c r="C139" t="n">
-        <v>77.84670325390931</v>
+        <v>77.84671114454375</v>
       </c>
       <c r="D139" t="n">
-        <v>74.91793330133525</v>
+        <v>74.91794089510609</v>
       </c>
       <c r="E139" t="n">
-        <v>77.26095075304393</v>
+        <v>77.2609585843058</v>
       </c>
       <c r="F139" t="n">
         <v>637900</v>
@@ -3232,16 +3232,16 @@
         <v>43420</v>
       </c>
       <c r="B141" t="n">
-        <v>81.09762573242188</v>
+        <v>81.09764099121094</v>
       </c>
       <c r="C141" t="n">
-        <v>83.46992928367727</v>
+        <v>83.46994498882317</v>
       </c>
       <c r="D141" t="n">
-        <v>78.81318168946497</v>
+        <v>78.81319651842826</v>
       </c>
       <c r="E141" t="n">
-        <v>78.81318168946497</v>
+        <v>78.81319651842826</v>
       </c>
       <c r="F141" t="n">
         <v>652300</v>
@@ -3272,16 +3272,16 @@
         <v>43425</v>
       </c>
       <c r="B143" t="n">
-        <v>79.80898284912109</v>
+        <v>79.80897521972656</v>
       </c>
       <c r="C143" t="n">
-        <v>81.59553434451564</v>
+        <v>81.59552654433449</v>
       </c>
       <c r="D143" t="n">
-        <v>78.13958483560805</v>
+        <v>78.13957736580078</v>
       </c>
       <c r="E143" t="n">
-        <v>79.04750383750959</v>
+        <v>79.04749628090917</v>
       </c>
       <c r="F143" t="n">
         <v>918800</v>
@@ -3292,16 +3292,16 @@
         <v>43426</v>
       </c>
       <c r="B144" t="n">
-        <v>79.07678985595703</v>
+        <v>79.07679748535156</v>
       </c>
       <c r="C144" t="n">
-        <v>80.24829487452415</v>
+        <v>80.24830261694648</v>
       </c>
       <c r="D144" t="n">
-        <v>77.78813135623429</v>
+        <v>77.78813886129798</v>
       </c>
       <c r="E144" t="n">
-        <v>79.54538888408497</v>
+        <v>79.54539655869033</v>
       </c>
       <c r="F144" t="n">
         <v>203833</v>
@@ -3332,16 +3332,16 @@
         <v>43430</v>
       </c>
       <c r="B146" t="n">
-        <v>78.75462341308594</v>
+        <v>78.75461578369141</v>
       </c>
       <c r="C146" t="n">
-        <v>80.33616189246013</v>
+        <v>80.33615410985325</v>
       </c>
       <c r="D146" t="n">
-        <v>76.23587942868353</v>
+        <v>76.23587204329363</v>
       </c>
       <c r="E146" t="n">
-        <v>80.27758142772588</v>
+        <v>80.27757365079401</v>
       </c>
       <c r="F146" t="n">
         <v>252366</v>
@@ -3352,16 +3352,16 @@
         <v>43431</v>
       </c>
       <c r="B147" t="n">
-        <v>81.59552764892578</v>
+        <v>81.59554290771484</v>
       </c>
       <c r="C147" t="n">
-        <v>82.59130609434109</v>
+        <v>82.59132153934591</v>
       </c>
       <c r="D147" t="n">
-        <v>76.32374056880897</v>
+        <v>76.32375484174636</v>
       </c>
       <c r="E147" t="n">
-        <v>78.28601840188094</v>
+        <v>78.28603304177452</v>
       </c>
       <c r="F147" t="n">
         <v>436400</v>
@@ -3372,16 +3372,16 @@
         <v>43432</v>
       </c>
       <c r="B148" t="n">
-        <v>84.52429962158203</v>
+        <v>84.5242919921875</v>
       </c>
       <c r="C148" t="n">
-        <v>86.22298404832937</v>
+        <v>86.22297626560693</v>
       </c>
       <c r="D148" t="n">
-        <v>80.54117083974624</v>
+        <v>80.54116356987981</v>
       </c>
       <c r="E148" t="n">
-        <v>81.18549633337582</v>
+        <v>81.18548900535082</v>
       </c>
       <c r="F148" t="n">
         <v>429500</v>
@@ -3392,16 +3392,16 @@
         <v>43433</v>
       </c>
       <c r="B149" t="n">
-        <v>84.17285919189453</v>
+        <v>84.17284393310547</v>
       </c>
       <c r="C149" t="n">
-        <v>85.69581735682299</v>
+        <v>85.69580182195328</v>
       </c>
       <c r="D149" t="n">
-        <v>83.29422661664812</v>
+        <v>83.29421151713687</v>
       </c>
       <c r="E149" t="n">
-        <v>84.31929919581027</v>
+        <v>84.31928391047468</v>
       </c>
       <c r="F149" t="n">
         <v>232033</v>
@@ -3432,16 +3432,16 @@
         <v>43437</v>
       </c>
       <c r="B151" t="n">
-        <v>84.49500274658203</v>
+        <v>84.49501800537109</v>
       </c>
       <c r="C151" t="n">
-        <v>85.2857756432162</v>
+        <v>85.2857910448094</v>
       </c>
       <c r="D151" t="n">
-        <v>82.79631837853798</v>
+        <v>82.79633333056491</v>
       </c>
       <c r="E151" t="n">
-        <v>83.29421132112294</v>
+        <v>83.2942263630634</v>
       </c>
       <c r="F151" t="n">
         <v>313866</v>
@@ -3452,16 +3452,16 @@
         <v>43438</v>
       </c>
       <c r="B152" t="n">
-        <v>83.82139587402344</v>
+        <v>83.82140350341797</v>
       </c>
       <c r="C152" t="n">
-        <v>86.60372581394269</v>
+        <v>86.60373369658394</v>
       </c>
       <c r="D152" t="n">
-        <v>82.59131041965232</v>
+        <v>82.5913179370849</v>
       </c>
       <c r="E152" t="n">
-        <v>84.64144787810613</v>
+        <v>84.64145558214152</v>
       </c>
       <c r="F152" t="n">
         <v>207933</v>
@@ -3492,16 +3492,16 @@
         <v>43440</v>
       </c>
       <c r="B154" t="n">
-        <v>84.934326171875</v>
+        <v>84.93434143066406</v>
       </c>
       <c r="C154" t="n">
-        <v>85.46150564190386</v>
+        <v>85.46152099540281</v>
       </c>
       <c r="D154" t="n">
-        <v>83.87996723181728</v>
+        <v>83.87998230118657</v>
       </c>
       <c r="E154" t="n">
-        <v>85.25649264493379</v>
+        <v>85.25650796160134</v>
       </c>
       <c r="F154" t="n">
         <v>270866</v>
@@ -3512,16 +3512,16 @@
         <v>43441</v>
       </c>
       <c r="B155" t="n">
-        <v>84.26070404052734</v>
+        <v>84.26071166992188</v>
       </c>
       <c r="C155" t="n">
-        <v>86.10582840285664</v>
+        <v>86.10583619931816</v>
       </c>
       <c r="D155" t="n">
-        <v>82.18128018171485</v>
+        <v>82.18128762282772</v>
       </c>
       <c r="E155" t="n">
-        <v>85.57864894958446</v>
+        <v>85.57865669831246</v>
       </c>
       <c r="F155" t="n">
         <v>485833</v>
@@ -3552,16 +3552,16 @@
         <v>43445</v>
       </c>
       <c r="B157" t="n">
-        <v>83.87995910644531</v>
+        <v>83.87998962402344</v>
       </c>
       <c r="C157" t="n">
-        <v>84.37785202128332</v>
+        <v>84.37788272000704</v>
       </c>
       <c r="D157" t="n">
-        <v>83.14776671037318</v>
+        <v>83.14779696156181</v>
       </c>
       <c r="E157" t="n">
-        <v>83.46993315222402</v>
+        <v>83.46996352062467</v>
       </c>
       <c r="F157" t="n">
         <v>276533</v>
@@ -3572,16 +3572,16 @@
         <v>43446</v>
       </c>
       <c r="B158" t="n">
-        <v>85.60794830322266</v>
+        <v>85.60795593261719</v>
       </c>
       <c r="C158" t="n">
-        <v>86.2815603291279</v>
+        <v>86.28156801855484</v>
       </c>
       <c r="D158" t="n">
-        <v>84.37786283467175</v>
+        <v>84.37787035444086</v>
       </c>
       <c r="E158" t="n">
-        <v>84.55358933017901</v>
+        <v>84.5535968656089</v>
       </c>
       <c r="F158" t="n">
         <v>243466</v>
@@ -3592,16 +3592,16 @@
         <v>43447</v>
       </c>
       <c r="B159" t="n">
-        <v>86.77945709228516</v>
+        <v>86.77944946289062</v>
       </c>
       <c r="C159" t="n">
-        <v>88.77102164547205</v>
+        <v>88.77101384098502</v>
       </c>
       <c r="D159" t="n">
-        <v>84.99290555142299</v>
+        <v>84.99289807909682</v>
       </c>
       <c r="E159" t="n">
-        <v>85.78367853981547</v>
+        <v>85.78367099796685</v>
       </c>
       <c r="F159" t="n">
         <v>486800</v>
@@ -3612,16 +3612,16 @@
         <v>43448</v>
       </c>
       <c r="B160" t="n">
-        <v>86.39871215820312</v>
+        <v>86.39869689941406</v>
       </c>
       <c r="C160" t="n">
-        <v>88.30240961628846</v>
+        <v>88.3023940212893</v>
       </c>
       <c r="D160" t="n">
-        <v>85.81295966711896</v>
+        <v>85.81294451177904</v>
       </c>
       <c r="E160" t="n">
-        <v>86.77945164982019</v>
+        <v>86.77943632378911</v>
       </c>
       <c r="F160" t="n">
         <v>286966</v>
@@ -3632,16 +3632,16 @@
         <v>43451</v>
       </c>
       <c r="B161" t="n">
-        <v>84.9378662109375</v>
+        <v>84.93785095214844</v>
       </c>
       <c r="C161" t="n">
-        <v>86.47039992970112</v>
+        <v>86.47038439559775</v>
       </c>
       <c r="D161" t="n">
-        <v>84.28948194833528</v>
+        <v>84.28946680602617</v>
       </c>
       <c r="E161" t="n">
-        <v>86.44092928050621</v>
+        <v>86.44091375169715</v>
       </c>
       <c r="F161" t="n">
         <v>205700</v>
@@ -3672,16 +3672,16 @@
         <v>43453</v>
       </c>
       <c r="B163" t="n">
-        <v>89.68281555175781</v>
+        <v>89.68282318115234</v>
       </c>
       <c r="C163" t="n">
-        <v>90.56697230531492</v>
+        <v>90.56698000992543</v>
       </c>
       <c r="D163" t="n">
-        <v>86.29354924563503</v>
+        <v>86.29355658670175</v>
       </c>
       <c r="E163" t="n">
-        <v>86.52932937663491</v>
+        <v>86.52933673775965</v>
       </c>
       <c r="F163" t="n">
         <v>384866</v>
@@ -3692,16 +3692,16 @@
         <v>43454</v>
       </c>
       <c r="B164" t="n">
-        <v>89.00497436523438</v>
+        <v>89.00496673583984</v>
       </c>
       <c r="C164" t="n">
-        <v>93.07208855677598</v>
+        <v>93.07208057875353</v>
       </c>
       <c r="D164" t="n">
-        <v>87.20718994134303</v>
+        <v>87.20718246605232</v>
       </c>
       <c r="E164" t="n">
-        <v>89.27022517929211</v>
+        <v>89.2702175271606</v>
       </c>
       <c r="F164" t="n">
         <v>975500</v>
@@ -3712,16 +3712,16 @@
         <v>43455</v>
       </c>
       <c r="B165" t="n">
-        <v>88.0029296875</v>
+        <v>88.00294494628906</v>
       </c>
       <c r="C165" t="n">
-        <v>90.18383988988073</v>
+        <v>90.18385552681684</v>
       </c>
       <c r="D165" t="n">
-        <v>86.08725529334548</v>
+        <v>86.08727021997659</v>
       </c>
       <c r="E165" t="n">
-        <v>90.18383988988073</v>
+        <v>90.18385552681684</v>
       </c>
       <c r="F165" t="n">
         <v>2053700</v>
@@ -3752,16 +3752,16 @@
         <v>43461</v>
       </c>
       <c r="B167" t="n">
-        <v>90.62591552734375</v>
+        <v>90.62593078613281</v>
       </c>
       <c r="C167" t="n">
-        <v>91.36271158854166</v>
+        <v>91.36272697138592</v>
       </c>
       <c r="D167" t="n">
-        <v>89.35862540267408</v>
+        <v>89.35864044808805</v>
       </c>
       <c r="E167" t="n">
-        <v>91.36271158854166</v>
+        <v>91.36272697138592</v>
       </c>
       <c r="F167" t="n">
         <v>343866</v>
@@ -3772,16 +3772,16 @@
         <v>43462</v>
       </c>
       <c r="B168" t="n">
-        <v>91.95215606689453</v>
+        <v>91.95216369628906</v>
       </c>
       <c r="C168" t="n">
-        <v>92.09951679277854</v>
+        <v>92.0995244343998</v>
       </c>
       <c r="D168" t="n">
-        <v>89.97754032823556</v>
+        <v>89.97754779379356</v>
       </c>
       <c r="E168" t="n">
-        <v>91.33325001227509</v>
+        <v>91.33325759031815</v>
       </c>
       <c r="F168" t="n">
         <v>582800</v>
@@ -3812,16 +3812,16 @@
         <v>43468</v>
       </c>
       <c r="B170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494903564453</v>
       </c>
       <c r="C170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.53956505526335</v>
       </c>
       <c r="D170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494903564453</v>
       </c>
       <c r="E170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.53956505526335</v>
       </c>
       <c r="F170" t="n">
         <v>308333</v>
@@ -3832,16 +3832,16 @@
         <v>43469</v>
       </c>
       <c r="B171" t="n">
-        <v>89.88913726806641</v>
+        <v>89.88912200927734</v>
       </c>
       <c r="C171" t="n">
-        <v>91.362729682297</v>
+        <v>91.36271417336386</v>
       </c>
       <c r="D171" t="n">
-        <v>88.68078819056272</v>
+        <v>88.68077313689237</v>
       </c>
       <c r="E171" t="n">
-        <v>89.83019596992233</v>
+        <v>89.83018072113863</v>
       </c>
       <c r="F171" t="n">
         <v>585300</v>
@@ -3852,16 +3852,16 @@
         <v>43472</v>
       </c>
       <c r="B172" t="n">
-        <v>91.24482727050781</v>
+        <v>91.24484252929688</v>
       </c>
       <c r="C172" t="n">
-        <v>91.65743129196125</v>
+        <v>91.65744661974971</v>
       </c>
       <c r="D172" t="n">
-        <v>89.88912513069897</v>
+        <v>89.88914016277521</v>
       </c>
       <c r="E172" t="n">
-        <v>89.88912513069897</v>
+        <v>89.88914016277521</v>
       </c>
       <c r="F172" t="n">
         <v>470133</v>
@@ -3872,16 +3872,16 @@
         <v>43473</v>
       </c>
       <c r="B173" t="n">
-        <v>89.88913726806641</v>
+        <v>89.88912200927734</v>
       </c>
       <c r="C173" t="n">
-        <v>91.21536894185822</v>
+        <v>91.21535345793974</v>
       </c>
       <c r="D173" t="n">
-        <v>89.35864309953395</v>
+        <v>89.35862793079691</v>
       </c>
       <c r="E173" t="n">
-        <v>91.21536894185822</v>
+        <v>91.21535345793974</v>
       </c>
       <c r="F173" t="n">
         <v>273633</v>
@@ -3892,16 +3892,16 @@
         <v>43474</v>
       </c>
       <c r="B174" t="n">
-        <v>91.36272430419922</v>
+        <v>91.36271667480469</v>
       </c>
       <c r="C174" t="n">
-        <v>91.92268908884118</v>
+        <v>91.92268141268588</v>
       </c>
       <c r="D174" t="n">
-        <v>89.71230059761056</v>
+        <v>89.71229310603738</v>
       </c>
       <c r="E174" t="n">
-        <v>89.71230059761056</v>
+        <v>89.71229310603738</v>
       </c>
       <c r="F174" t="n">
         <v>225833</v>
@@ -4012,16 +4012,16 @@
         <v>43482</v>
       </c>
       <c r="B180" t="n">
-        <v>99.26119232177734</v>
+        <v>99.26117706298828</v>
       </c>
       <c r="C180" t="n">
-        <v>100.0274592273692</v>
+        <v>100.0274438507868</v>
       </c>
       <c r="D180" t="n">
-        <v>97.90548241642645</v>
+        <v>97.90546736604202</v>
       </c>
       <c r="E180" t="n">
-        <v>98.78963942098594</v>
+        <v>98.78962423468569</v>
       </c>
       <c r="F180" t="n">
         <v>313600</v>
@@ -4032,16 +4032,16 @@
         <v>43483</v>
       </c>
       <c r="B181" t="n">
-        <v>100.7937088012695</v>
+        <v>100.793701171875</v>
       </c>
       <c r="C181" t="n">
-        <v>102.2673010571217</v>
+        <v>102.2672933161863</v>
       </c>
       <c r="D181" t="n">
-        <v>98.73068114209212</v>
+        <v>98.73067366885468</v>
       </c>
       <c r="E181" t="n">
-        <v>99.67377928642814</v>
+        <v>99.67377174180463</v>
       </c>
       <c r="F181" t="n">
         <v>475600</v>
@@ -4052,16 +4052,16 @@
         <v>43486</v>
       </c>
       <c r="B182" t="n">
-        <v>101.3831558227539</v>
+        <v>101.3831405639648</v>
       </c>
       <c r="C182" t="n">
-        <v>102.3557322195262</v>
+        <v>102.3557168143584</v>
       </c>
       <c r="D182" t="n">
-        <v>98.22966893326101</v>
+        <v>98.22965414909113</v>
       </c>
       <c r="E182" t="n">
-        <v>100.7937203518813</v>
+        <v>100.793705181806</v>
       </c>
       <c r="F182" t="n">
         <v>260300</v>
@@ -4092,16 +4092,16 @@
         <v>43488</v>
       </c>
       <c r="B184" t="n">
-        <v>99.23171997070312</v>
+        <v>99.23170471191406</v>
       </c>
       <c r="C184" t="n">
-        <v>101.0589752504606</v>
+        <v>101.0589597106958</v>
       </c>
       <c r="D184" t="n">
-        <v>98.17073158340929</v>
+        <v>98.17071648776765</v>
       </c>
       <c r="E184" t="n">
-        <v>99.58538276646773</v>
+        <v>99.5853674532962</v>
       </c>
       <c r="F184" t="n">
         <v>240366</v>
@@ -4112,16 +4112,16 @@
         <v>43489</v>
       </c>
       <c r="B185" t="n">
-        <v>98.22966003417969</v>
+        <v>98.22964477539062</v>
       </c>
       <c r="C185" t="n">
-        <v>100.9705425952604</v>
+        <v>100.9705269107084</v>
       </c>
       <c r="D185" t="n">
-        <v>97.05078919923396</v>
+        <v>97.05077412356822</v>
       </c>
       <c r="E185" t="n">
-        <v>99.23170698945374</v>
+        <v>99.23169157500881</v>
       </c>
       <c r="F185" t="n">
         <v>372266</v>
@@ -4152,16 +4152,16 @@
         <v>43494</v>
       </c>
       <c r="B187" t="n">
-        <v>97.3160400390625</v>
+        <v>97.31603240966797</v>
       </c>
       <c r="C187" t="n">
-        <v>97.99389494386627</v>
+        <v>97.99388726132918</v>
       </c>
       <c r="D187" t="n">
-        <v>96.72660457600985</v>
+        <v>96.72659699282595</v>
       </c>
       <c r="E187" t="n">
-        <v>97.49287142748615</v>
+        <v>97.49286378422838</v>
       </c>
       <c r="F187" t="n">
         <v>185333</v>
@@ -4172,16 +4172,16 @@
         <v>43495</v>
       </c>
       <c r="B188" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73068237304688</v>
       </c>
       <c r="C188" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73068237304688</v>
       </c>
       <c r="D188" t="n">
-        <v>96.49083077174782</v>
+        <v>96.49082331543798</v>
       </c>
       <c r="E188" t="n">
-        <v>97.28656826289463</v>
+        <v>97.28656074509432</v>
       </c>
       <c r="F188" t="n">
         <v>447533</v>
@@ -4192,16 +4192,16 @@
         <v>43496</v>
       </c>
       <c r="B189" t="n">
-        <v>100.9115905761719</v>
+        <v>100.9115982055664</v>
       </c>
       <c r="C189" t="n">
-        <v>104.566100269176</v>
+        <v>104.5661081748688</v>
       </c>
       <c r="D189" t="n">
-        <v>99.2022183035879</v>
+        <v>99.20222580374578</v>
       </c>
       <c r="E189" t="n">
-        <v>99.79166115348703</v>
+        <v>99.79166869820958</v>
       </c>
       <c r="F189" t="n">
         <v>504800</v>
@@ -4252,16 +4252,16 @@
         <v>43501</v>
       </c>
       <c r="B192" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73068237304688</v>
       </c>
       <c r="C192" t="n">
-        <v>101.8547061650084</v>
+        <v>101.8546982942061</v>
       </c>
       <c r="D192" t="n">
-        <v>93.86783062467705</v>
+        <v>93.86782337105902</v>
       </c>
       <c r="E192" t="n">
-        <v>100.2632236876363</v>
+        <v>100.2632159398155</v>
       </c>
       <c r="F192" t="n">
         <v>970333</v>
@@ -4272,16 +4272,16 @@
         <v>43502</v>
       </c>
       <c r="B193" t="n">
-        <v>97.46339416503906</v>
+        <v>97.46338653564453</v>
       </c>
       <c r="C193" t="n">
-        <v>99.5558925401632</v>
+        <v>99.55588474696876</v>
       </c>
       <c r="D193" t="n">
-        <v>96.07821380053463</v>
+        <v>96.07820627957145</v>
       </c>
       <c r="E193" t="n">
-        <v>98.43596298783444</v>
+        <v>98.43595528230763</v>
       </c>
       <c r="F193" t="n">
         <v>594200</v>
@@ -4332,16 +4332,16 @@
         <v>43507</v>
       </c>
       <c r="B196" t="n">
-        <v>98.14125061035156</v>
+        <v>98.14124298095703</v>
       </c>
       <c r="C196" t="n">
-        <v>98.6717447482006</v>
+        <v>98.67173707756602</v>
       </c>
       <c r="D196" t="n">
-        <v>96.10769349613602</v>
+        <v>96.10768602482801</v>
       </c>
       <c r="E196" t="n">
-        <v>97.10973298202097</v>
+        <v>97.10972543281549</v>
       </c>
       <c r="F196" t="n">
         <v>401966</v>
@@ -4372,16 +4372,16 @@
         <v>43509</v>
       </c>
       <c r="B198" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73068237304688</v>
       </c>
       <c r="C198" t="n">
-        <v>99.88009026633756</v>
+        <v>99.88008254812335</v>
       </c>
       <c r="D198" t="n">
-        <v>96.28452873682379</v>
+        <v>96.28452129645588</v>
       </c>
       <c r="E198" t="n">
-        <v>97.25709761434527</v>
+        <v>97.25709009882229</v>
       </c>
       <c r="F198" t="n">
         <v>448033</v>
@@ -4392,16 +4392,16 @@
         <v>43510</v>
       </c>
       <c r="B199" t="n">
-        <v>97.64022064208984</v>
+        <v>97.64021301269531</v>
       </c>
       <c r="C199" t="n">
-        <v>99.02539344201128</v>
+        <v>99.02538570438236</v>
       </c>
       <c r="D199" t="n">
-        <v>96.54976179136901</v>
+        <v>96.54975424718056</v>
       </c>
       <c r="E199" t="n">
-        <v>98.40648740312012</v>
+        <v>98.40647971385117</v>
       </c>
       <c r="F199" t="n">
         <v>462433</v>
@@ -4412,16 +4412,16 @@
         <v>43511</v>
       </c>
       <c r="B200" t="n">
-        <v>99.40854644775391</v>
+        <v>99.40853881835938</v>
       </c>
       <c r="C200" t="n">
-        <v>100.0863938601828</v>
+        <v>100.0863861787649</v>
       </c>
       <c r="D200" t="n">
-        <v>97.61076190745592</v>
+        <v>97.61075441603754</v>
       </c>
       <c r="E200" t="n">
-        <v>97.61076190745592</v>
+        <v>97.61075441603754</v>
       </c>
       <c r="F200" t="n">
         <v>157766</v>
@@ -4492,16 +4492,16 @@
         <v>43517</v>
       </c>
       <c r="B204" t="n">
-        <v>95.78349304199219</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C204" t="n">
-        <v>97.61074797039947</v>
+        <v>97.61076352027936</v>
       </c>
       <c r="D204" t="n">
-        <v>95.04669694166917</v>
+        <v>95.04671208308292</v>
       </c>
       <c r="E204" t="n">
-        <v>97.28655588743874</v>
+        <v>97.28657138567321</v>
       </c>
       <c r="F204" t="n">
         <v>542100</v>
@@ -4512,16 +4512,16 @@
         <v>43518</v>
       </c>
       <c r="B205" t="n">
-        <v>92.86577606201172</v>
+        <v>92.86576843261719</v>
       </c>
       <c r="C205" t="n">
-        <v>95.87190164855839</v>
+        <v>95.87189377219539</v>
       </c>
       <c r="D205" t="n">
-        <v>92.86577606201172</v>
+        <v>92.86576843261719</v>
       </c>
       <c r="E205" t="n">
-        <v>95.84243100478083</v>
+        <v>95.84242313083899</v>
       </c>
       <c r="F205" t="n">
         <v>514866</v>
@@ -4532,16 +4532,16 @@
         <v>43521</v>
       </c>
       <c r="B206" t="n">
-        <v>95.40037536621094</v>
+        <v>95.40036773681641</v>
       </c>
       <c r="C206" t="n">
-        <v>97.10974050159045</v>
+        <v>97.10973273549394</v>
       </c>
       <c r="D206" t="n">
-        <v>92.24688843737613</v>
+        <v>92.24688106017342</v>
       </c>
       <c r="E206" t="n">
-        <v>93.66153208610318</v>
+        <v>93.66152459576807</v>
       </c>
       <c r="F206" t="n">
         <v>404566</v>
@@ -4552,16 +4552,16 @@
         <v>43522</v>
       </c>
       <c r="B207" t="n">
-        <v>95.13510131835938</v>
+        <v>95.13511657714844</v>
       </c>
       <c r="C207" t="n">
-        <v>97.25707751635309</v>
+        <v>97.25709311548748</v>
       </c>
       <c r="D207" t="n">
-        <v>93.36679531510821</v>
+        <v>93.36681029027736</v>
       </c>
       <c r="E207" t="n">
-        <v>95.57718344047986</v>
+        <v>95.5771987701748</v>
       </c>
       <c r="F207" t="n">
         <v>332133</v>
@@ -4572,16 +4572,16 @@
         <v>43523</v>
       </c>
       <c r="B208" t="n">
-        <v>95.69508361816406</v>
+        <v>95.69509124755859</v>
       </c>
       <c r="C208" t="n">
-        <v>96.63818932085464</v>
+        <v>96.6381970254393</v>
       </c>
       <c r="D208" t="n">
-        <v>94.45727143665449</v>
+        <v>94.45727896736311</v>
       </c>
       <c r="E208" t="n">
-        <v>95.13511882317307</v>
+        <v>95.13512640792381</v>
       </c>
       <c r="F208" t="n">
         <v>447266</v>
@@ -4592,16 +4592,16 @@
         <v>43524</v>
       </c>
       <c r="B209" t="n">
-        <v>96.04874420166016</v>
+        <v>96.04872894287109</v>
       </c>
       <c r="C209" t="n">
-        <v>96.46135574787134</v>
+        <v>96.46134042353272</v>
       </c>
       <c r="D209" t="n">
-        <v>94.75198325875762</v>
+        <v>94.75196820597856</v>
       </c>
       <c r="E209" t="n">
-        <v>95.69508144495236</v>
+        <v>95.69506624234795</v>
       </c>
       <c r="F209" t="n">
         <v>596166</v>
@@ -4612,16 +4612,16 @@
         <v>43525</v>
       </c>
       <c r="B210" t="n">
-        <v>95.42983245849609</v>
+        <v>95.42982482910156</v>
       </c>
       <c r="C210" t="n">
-        <v>96.66765203347371</v>
+        <v>96.66764430511837</v>
       </c>
       <c r="D210" t="n">
-        <v>94.60461691015179</v>
+        <v>94.60460934673134</v>
       </c>
       <c r="E210" t="n">
-        <v>95.28247173610485</v>
+        <v>95.28246411849148</v>
       </c>
       <c r="F210" t="n">
         <v>326633</v>
@@ -4632,16 +4632,16 @@
         <v>43530</v>
       </c>
       <c r="B211" t="n">
-        <v>95.75402069091797</v>
+        <v>95.7540283203125</v>
       </c>
       <c r="C211" t="n">
-        <v>96.60869935521325</v>
+        <v>96.60870705270602</v>
       </c>
       <c r="D211" t="n">
-        <v>93.95623643934654</v>
+        <v>93.95624392549898</v>
       </c>
       <c r="E211" t="n">
-        <v>95.10563653655028</v>
+        <v>95.10564411428351</v>
       </c>
       <c r="F211" t="n">
         <v>247200</v>
@@ -4692,16 +4692,16 @@
         <v>43535</v>
       </c>
       <c r="B214" t="n">
-        <v>97.3160400390625</v>
+        <v>97.31603240966797</v>
       </c>
       <c r="C214" t="n">
-        <v>97.522342076377</v>
+        <v>97.52233443080878</v>
       </c>
       <c r="D214" t="n">
-        <v>96.19611041073888</v>
+        <v>96.19610286914474</v>
       </c>
       <c r="E214" t="n">
-        <v>97.2570987412808</v>
+        <v>97.25709111650715</v>
       </c>
       <c r="F214" t="n">
         <v>533833</v>
@@ -4732,16 +4732,16 @@
         <v>43537</v>
       </c>
       <c r="B216" t="n">
-        <v>95.78349304199219</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C216" t="n">
-        <v>97.58127732559895</v>
+        <v>97.58129287078403</v>
       </c>
       <c r="D216" t="n">
-        <v>95.40035966943042</v>
+        <v>95.40037486718441</v>
       </c>
       <c r="E216" t="n">
-        <v>97.43391660651884</v>
+        <v>97.43393212822862</v>
       </c>
       <c r="F216" t="n">
         <v>425833</v>
@@ -4792,16 +4792,16 @@
         <v>43542</v>
       </c>
       <c r="B219" t="n">
-        <v>86.64722442626953</v>
+        <v>86.64723205566406</v>
       </c>
       <c r="C219" t="n">
-        <v>89.32916571580841</v>
+        <v>89.32917358135117</v>
       </c>
       <c r="D219" t="n">
-        <v>83.84740054932983</v>
+        <v>83.84740793219645</v>
       </c>
       <c r="E219" t="n">
-        <v>89.29969506895821</v>
+        <v>89.29970293190605</v>
       </c>
       <c r="F219" t="n">
         <v>2555666</v>
@@ -4832,16 +4832,16 @@
         <v>43544</v>
       </c>
       <c r="B221" t="n">
-        <v>88.65131378173828</v>
+        <v>88.65130615234375</v>
       </c>
       <c r="C221" t="n">
-        <v>89.94807475146169</v>
+        <v>89.948067010467</v>
       </c>
       <c r="D221" t="n">
-        <v>87.88504695804876</v>
+        <v>87.88503939459969</v>
       </c>
       <c r="E221" t="n">
-        <v>89.94807475146169</v>
+        <v>89.948067010467</v>
       </c>
       <c r="F221" t="n">
         <v>1179966</v>
@@ -4872,16 +4872,16 @@
         <v>43546</v>
       </c>
       <c r="B223" t="n">
-        <v>87.82609558105469</v>
+        <v>87.82611083984375</v>
       </c>
       <c r="C223" t="n">
-        <v>87.9439781588119</v>
+        <v>87.94399343808172</v>
       </c>
       <c r="D223" t="n">
-        <v>86.55880540462269</v>
+        <v>86.55882044323444</v>
       </c>
       <c r="E223" t="n">
-        <v>87.9439781588119</v>
+        <v>87.94399343808172</v>
       </c>
       <c r="F223" t="n">
         <v>257266</v>
@@ -4912,16 +4912,16 @@
         <v>43550</v>
       </c>
       <c r="B225" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494903564453</v>
       </c>
       <c r="C225" t="n">
-        <v>89.62387506752287</v>
+        <v>89.62389033635351</v>
       </c>
       <c r="D225" t="n">
-        <v>86.76511004398911</v>
+        <v>86.76512482578435</v>
       </c>
       <c r="E225" t="n">
-        <v>88.20923162596166</v>
+        <v>88.20924665378564</v>
       </c>
       <c r="F225" t="n">
         <v>883933</v>
@@ -4932,16 +4932,16 @@
         <v>43551</v>
       </c>
       <c r="B226" t="n">
-        <v>86.88300323486328</v>
+        <v>86.88301086425781</v>
       </c>
       <c r="C226" t="n">
-        <v>89.29969367486639</v>
+        <v>89.29970151647602</v>
       </c>
       <c r="D226" t="n">
-        <v>86.4998623465579</v>
+        <v>86.49986994230797</v>
       </c>
       <c r="E226" t="n">
-        <v>89.29969367486639</v>
+        <v>89.29970151647602</v>
       </c>
       <c r="F226" t="n">
         <v>691333</v>
@@ -4972,16 +4972,16 @@
         <v>43553</v>
       </c>
       <c r="B228" t="n">
-        <v>90.6553955078125</v>
+        <v>90.65540313720703</v>
       </c>
       <c r="C228" t="n">
-        <v>91.8047956828475</v>
+        <v>91.80480340897347</v>
       </c>
       <c r="D228" t="n">
-        <v>88.68077976180101</v>
+        <v>88.68078722501544</v>
       </c>
       <c r="E228" t="n">
-        <v>90.77328558797426</v>
+        <v>90.7732932272902</v>
       </c>
       <c r="F228" t="n">
         <v>379666</v>
@@ -4992,16 +4992,16 @@
         <v>43556</v>
       </c>
       <c r="B229" t="n">
-        <v>90.89117431640625</v>
+        <v>90.89116668701172</v>
       </c>
       <c r="C229" t="n">
-        <v>91.62797050329212</v>
+        <v>91.62796281205101</v>
       </c>
       <c r="D229" t="n">
-        <v>89.91860544833887</v>
+        <v>89.91859790058164</v>
       </c>
       <c r="E229" t="n">
-        <v>91.12695449266617</v>
+        <v>91.12694684348028</v>
       </c>
       <c r="F229" t="n">
         <v>342733</v>
@@ -5012,16 +5012,16 @@
         <v>43557</v>
       </c>
       <c r="B230" t="n">
-        <v>91.68691253662109</v>
+        <v>91.68689727783203</v>
       </c>
       <c r="C230" t="n">
-        <v>91.92268520042373</v>
+        <v>91.92266990239673</v>
       </c>
       <c r="D230" t="n">
-        <v>89.88912817431608</v>
+        <v>89.88911321471926</v>
       </c>
       <c r="E230" t="n">
-        <v>91.65743439545264</v>
+        <v>91.65741914156942</v>
       </c>
       <c r="F230" t="n">
         <v>264800</v>
@@ -5032,16 +5032,16 @@
         <v>43558</v>
       </c>
       <c r="B231" t="n">
-        <v>88.88707733154297</v>
+        <v>88.8870849609375</v>
       </c>
       <c r="C231" t="n">
-        <v>92.777367336296</v>
+        <v>92.77737529960361</v>
       </c>
       <c r="D231" t="n">
-        <v>88.88707733154297</v>
+        <v>88.8870849609375</v>
       </c>
       <c r="E231" t="n">
-        <v>92.71841855162685</v>
+        <v>92.71842650987473</v>
       </c>
       <c r="F231" t="n">
         <v>371500</v>
@@ -5092,16 +5092,16 @@
         <v>43563</v>
       </c>
       <c r="B234" t="n">
-        <v>82.52117156982422</v>
+        <v>82.52116394042969</v>
       </c>
       <c r="C234" t="n">
-        <v>85.88096032777685</v>
+        <v>85.88095238775713</v>
       </c>
       <c r="D234" t="n">
-        <v>82.25592074967739</v>
+        <v>82.25591314480629</v>
       </c>
       <c r="E234" t="n">
-        <v>85.02627406686121</v>
+        <v>85.02626620586047</v>
       </c>
       <c r="F234" t="n">
         <v>619400</v>
@@ -5132,16 +5132,16 @@
         <v>43565</v>
       </c>
       <c r="B236" t="n">
-        <v>83.40532684326172</v>
+        <v>83.40531921386719</v>
       </c>
       <c r="C236" t="n">
-        <v>84.23053494514326</v>
+        <v>84.23052724026388</v>
       </c>
       <c r="D236" t="n">
-        <v>81.6075424133479</v>
+        <v>81.60753494840338</v>
       </c>
       <c r="E236" t="n">
-        <v>83.64109951593099</v>
+        <v>83.64109186496947</v>
       </c>
       <c r="F236" t="n">
         <v>456233</v>
@@ -5172,16 +5172,16 @@
         <v>43567</v>
       </c>
       <c r="B238" t="n">
-        <v>82.72745513916016</v>
+        <v>82.72747039794922</v>
       </c>
       <c r="C238" t="n">
-        <v>84.73154118663587</v>
+        <v>84.73155681507157</v>
       </c>
       <c r="D238" t="n">
-        <v>82.34432181340063</v>
+        <v>82.34433700152209</v>
       </c>
       <c r="E238" t="n">
-        <v>84.34840786087634</v>
+        <v>84.34842341864444</v>
       </c>
       <c r="F238" t="n">
         <v>343366</v>
@@ -5192,16 +5192,16 @@
         <v>43570</v>
       </c>
       <c r="B239" t="n">
-        <v>83.96528625488281</v>
+        <v>83.96529388427734</v>
       </c>
       <c r="C239" t="n">
-        <v>84.37789027943356</v>
+        <v>84.37789794631881</v>
       </c>
       <c r="D239" t="n">
-        <v>82.58010596450545</v>
+        <v>82.58011346803741</v>
       </c>
       <c r="E239" t="n">
-        <v>82.81587862209479</v>
+        <v>82.81588614704992</v>
       </c>
       <c r="F239" t="n">
         <v>210900</v>
@@ -5212,16 +5212,16 @@
         <v>43571</v>
       </c>
       <c r="B240" t="n">
-        <v>83.5821533203125</v>
+        <v>83.58216094970703</v>
       </c>
       <c r="C240" t="n">
-        <v>84.40736137380419</v>
+        <v>84.40736907852389</v>
       </c>
       <c r="D240" t="n">
-        <v>82.58010640384093</v>
+        <v>82.58011394176843</v>
       </c>
       <c r="E240" t="n">
-        <v>83.11060050754746</v>
+        <v>83.11060809389856</v>
       </c>
       <c r="F240" t="n">
         <v>215300</v>
@@ -5232,16 +5232,16 @@
         <v>43572</v>
       </c>
       <c r="B241" t="n">
-        <v>82.66854095458984</v>
+        <v>82.66852569580078</v>
       </c>
       <c r="C241" t="n">
-        <v>84.23054541083619</v>
+        <v>84.23052986373555</v>
       </c>
       <c r="D241" t="n">
-        <v>81.46019180375023</v>
+        <v>81.46017676799576</v>
       </c>
       <c r="E241" t="n">
-        <v>84.20107475997554</v>
+        <v>84.20105921831454</v>
       </c>
       <c r="F241" t="n">
         <v>289766</v>
@@ -5272,16 +5272,16 @@
         <v>43577</v>
       </c>
       <c r="B243" t="n">
-        <v>84.58419799804688</v>
+        <v>84.58419036865234</v>
       </c>
       <c r="C243" t="n">
-        <v>86.26409234997288</v>
+        <v>86.26408456905386</v>
       </c>
       <c r="D243" t="n">
-        <v>82.31486821484337</v>
+        <v>82.3148607901397</v>
       </c>
       <c r="E243" t="n">
-        <v>83.49373907739835</v>
+        <v>83.49373154636193</v>
       </c>
       <c r="F243" t="n">
         <v>461666</v>
@@ -5292,16 +5292,16 @@
         <v>43578</v>
       </c>
       <c r="B244" t="n">
-        <v>86.276123046875</v>
+        <v>86.27613067626953</v>
       </c>
       <c r="C244" t="n">
-        <v>86.7792792343547</v>
+        <v>86.77928690824331</v>
       </c>
       <c r="D244" t="n">
-        <v>84.2339097294366</v>
+        <v>84.23391717823827</v>
       </c>
       <c r="E244" t="n">
-        <v>85.240222104396</v>
+        <v>85.24022964218584</v>
       </c>
       <c r="F244" t="n">
         <v>437600</v>
@@ -5332,16 +5332,16 @@
         <v>43580</v>
       </c>
       <c r="B246" t="n">
-        <v>87.90397644042969</v>
+        <v>87.90398406982422</v>
       </c>
       <c r="C246" t="n">
-        <v>88.55512063075771</v>
+        <v>88.5551283166666</v>
       </c>
       <c r="D246" t="n">
-        <v>84.88505435395487</v>
+        <v>84.88506172132999</v>
       </c>
       <c r="E246" t="n">
-        <v>87.01605596588345</v>
+        <v>87.01606351821326</v>
       </c>
       <c r="F246" t="n">
         <v>486633</v>
@@ -5352,16 +5352,16 @@
         <v>43581</v>
       </c>
       <c r="B247" t="n">
-        <v>87.46002197265625</v>
+        <v>87.46004486083984</v>
       </c>
       <c r="C247" t="n">
-        <v>87.66720216697192</v>
+        <v>87.66722510937433</v>
       </c>
       <c r="D247" t="n">
-        <v>86.15774108911307</v>
+        <v>86.15776363649131</v>
       </c>
       <c r="E247" t="n">
-        <v>87.43042587732295</v>
+        <v>87.43044875776127</v>
       </c>
       <c r="F247" t="n">
         <v>187233</v>
@@ -5372,16 +5372,16 @@
         <v>43584</v>
       </c>
       <c r="B248" t="n">
-        <v>87.60799407958984</v>
+        <v>87.60801696777344</v>
       </c>
       <c r="C248" t="n">
-        <v>88.91028236569991</v>
+        <v>88.91030559411517</v>
       </c>
       <c r="D248" t="n">
-        <v>86.66088148449491</v>
+        <v>86.66090412523891</v>
       </c>
       <c r="E248" t="n">
-        <v>87.87437396610575</v>
+        <v>87.8743969238829</v>
       </c>
       <c r="F248" t="n">
         <v>356166</v>
@@ -5392,16 +5392,16 @@
         <v>43585</v>
       </c>
       <c r="B249" t="n">
-        <v>89.56142425537109</v>
+        <v>89.56143951416016</v>
       </c>
       <c r="C249" t="n">
-        <v>90.27176062526411</v>
+        <v>90.27177600507484</v>
       </c>
       <c r="D249" t="n">
-        <v>86.77927849127832</v>
+        <v>86.77929327606671</v>
       </c>
       <c r="E249" t="n">
-        <v>86.77927849127832</v>
+        <v>86.77929327606671</v>
       </c>
       <c r="F249" t="n">
         <v>318366</v>
@@ -5412,16 +5412,16 @@
         <v>43587</v>
       </c>
       <c r="B250" t="n">
-        <v>89.82779693603516</v>
+        <v>89.82781219482422</v>
       </c>
       <c r="C250" t="n">
-        <v>90.41974893094701</v>
+        <v>90.41976429028925</v>
       </c>
       <c r="D250" t="n">
-        <v>88.64390800017603</v>
+        <v>88.64392305786127</v>
       </c>
       <c r="E250" t="n">
-        <v>88.64390800017603</v>
+        <v>88.64392305786127</v>
       </c>
       <c r="F250" t="n">
         <v>415166</v>
@@ -5452,16 +5452,16 @@
         <v>43591</v>
       </c>
       <c r="B252" t="n">
-        <v>90.53815460205078</v>
+        <v>90.53814697265625</v>
       </c>
       <c r="C252" t="n">
-        <v>91.10050310789021</v>
+        <v>91.10049543110814</v>
       </c>
       <c r="D252" t="n">
-        <v>88.19997227476354</v>
+        <v>88.19996484240103</v>
       </c>
       <c r="E252" t="n">
-        <v>88.64392884837949</v>
+        <v>88.64392137860601</v>
       </c>
       <c r="F252" t="n">
         <v>206566</v>
@@ -5492,16 +5492,16 @@
         <v>43593</v>
       </c>
       <c r="B254" t="n">
-        <v>102.3474655151367</v>
+        <v>102.3474731445312</v>
       </c>
       <c r="C254" t="n">
-        <v>104.4488787191065</v>
+        <v>104.4488865051489</v>
       </c>
       <c r="D254" t="n">
-        <v>98.88457916470847</v>
+        <v>98.88458653596543</v>
       </c>
       <c r="E254" t="n">
-        <v>100.630824151866</v>
+        <v>100.6308316532951</v>
       </c>
       <c r="F254" t="n">
         <v>1898166</v>
@@ -5512,16 +5512,16 @@
         <v>43594</v>
       </c>
       <c r="B255" t="n">
-        <v>105.2184143066406</v>
+        <v>105.2183990478516</v>
       </c>
       <c r="C255" t="n">
-        <v>106.3727073241445</v>
+        <v>106.3726918979597</v>
       </c>
       <c r="D255" t="n">
-        <v>99.77250630659914</v>
+        <v>99.7724918375764</v>
       </c>
       <c r="E255" t="n">
-        <v>101.4891553104076</v>
+        <v>101.4891405924361</v>
       </c>
       <c r="F255" t="n">
         <v>781533</v>
@@ -5532,16 +5532,16 @@
         <v>43595</v>
       </c>
       <c r="B256" t="n">
-        <v>103.5905609130859</v>
+        <v>103.5905685424805</v>
       </c>
       <c r="C256" t="n">
-        <v>105.218414089974</v>
+        <v>105.2184218392591</v>
       </c>
       <c r="D256" t="n">
-        <v>101.3411670804334</v>
+        <v>101.3411745441612</v>
       </c>
       <c r="E256" t="n">
-        <v>105.218414089974</v>
+        <v>105.2184218392591</v>
       </c>
       <c r="F256" t="n">
         <v>440400</v>
@@ -5592,16 +5592,16 @@
         <v>43600</v>
       </c>
       <c r="B259" t="n">
-        <v>103.5905609130859</v>
+        <v>103.5905685424805</v>
       </c>
       <c r="C259" t="n">
-        <v>104.3304934910366</v>
+        <v>104.3305011749268</v>
       </c>
       <c r="D259" t="n">
-        <v>100.9267991162737</v>
+        <v>100.9268065494834</v>
       </c>
       <c r="E259" t="n">
-        <v>101.6075394966229</v>
+        <v>101.6075469799689</v>
       </c>
       <c r="F259" t="n">
         <v>328866</v>
@@ -5632,16 +5632,16 @@
         <v>43602</v>
       </c>
       <c r="B261" t="n">
-        <v>102.9690170288086</v>
+        <v>102.9690322875977</v>
       </c>
       <c r="C261" t="n">
-        <v>103.5609615672124</v>
+        <v>103.5609769137207</v>
       </c>
       <c r="D261" t="n">
-        <v>101.5483441150528</v>
+        <v>101.548359163315</v>
       </c>
       <c r="E261" t="n">
-        <v>102.9394134039527</v>
+        <v>102.9394286583549</v>
       </c>
       <c r="F261" t="n">
         <v>361233</v>
@@ -5652,16 +5652,16 @@
         <v>43605</v>
       </c>
       <c r="B262" t="n">
-        <v>105.0704193115234</v>
+        <v>105.0704116821289</v>
       </c>
       <c r="C262" t="n">
-        <v>105.899140132578</v>
+        <v>105.8991324430082</v>
       </c>
       <c r="D262" t="n">
-        <v>103.5905542507978</v>
+        <v>103.5905467288595</v>
       </c>
       <c r="E262" t="n">
-        <v>103.5905542507978</v>
+        <v>103.5905467288595</v>
       </c>
       <c r="F262" t="n">
         <v>597600</v>
@@ -5672,16 +5672,16 @@
         <v>43606</v>
       </c>
       <c r="B263" t="n">
-        <v>108.3557205200195</v>
+        <v>108.3557357788086</v>
       </c>
       <c r="C263" t="n">
-        <v>109.8355855666399</v>
+        <v>109.8356010338254</v>
       </c>
       <c r="D263" t="n">
-        <v>105.8103508333566</v>
+        <v>105.8103657337035</v>
       </c>
       <c r="E263" t="n">
-        <v>105.8103508333566</v>
+        <v>105.8103657337035</v>
       </c>
       <c r="F263" t="n">
         <v>554800</v>
@@ -5712,16 +5712,16 @@
         <v>43608</v>
       </c>
       <c r="B265" t="n">
-        <v>110.9898834228516</v>
+        <v>110.989875793457</v>
       </c>
       <c r="C265" t="n">
-        <v>112.4697485351563</v>
+        <v>112.4697408040365</v>
       </c>
       <c r="D265" t="n">
-        <v>109.1844461793639</v>
+        <v>109.1844386740743</v>
       </c>
       <c r="E265" t="n">
-        <v>109.332434195991</v>
+        <v>109.3324266805288</v>
       </c>
       <c r="F265" t="n">
         <v>449966</v>
@@ -5772,16 +5772,16 @@
         <v>43613</v>
       </c>
       <c r="B268" t="n">
-        <v>109.3028335571289</v>
+        <v>109.3028411865234</v>
       </c>
       <c r="C268" t="n">
-        <v>111.0786671019285</v>
+        <v>111.0786748552771</v>
       </c>
       <c r="D268" t="n">
-        <v>107.0830359808923</v>
+        <v>107.0830434553438</v>
       </c>
       <c r="E268" t="n">
-        <v>110.5755184040759</v>
+        <v>110.5755261223044</v>
       </c>
       <c r="F268" t="n">
         <v>402233</v>
@@ -5812,16 +5812,16 @@
         <v>43615</v>
       </c>
       <c r="B270" t="n">
-        <v>107.70458984375</v>
+        <v>107.7045745849609</v>
       </c>
       <c r="C270" t="n">
-        <v>111.6410292556999</v>
+        <v>111.6410134392252</v>
       </c>
       <c r="D270" t="n">
-        <v>107.70458984375</v>
+        <v>107.7045745849609</v>
       </c>
       <c r="E270" t="n">
-        <v>109.9243876930951</v>
+        <v>109.9243721198215</v>
       </c>
       <c r="F270" t="n">
         <v>452966</v>
@@ -5832,16 +5832,16 @@
         <v>43616</v>
       </c>
       <c r="B271" t="n">
-        <v>108.8588638305664</v>
+        <v>108.8588790893555</v>
       </c>
       <c r="C271" t="n">
-        <v>110.4275246164044</v>
+        <v>110.4275400950732</v>
       </c>
       <c r="D271" t="n">
-        <v>106.8462465635006</v>
+        <v>106.8462615401803</v>
       </c>
       <c r="E271" t="n">
-        <v>107.4086024792968</v>
+        <v>107.4086175348022</v>
       </c>
       <c r="F271" t="n">
         <v>504400</v>
@@ -5852,16 +5852,16 @@
         <v>43619</v>
       </c>
       <c r="B272" t="n">
-        <v>109.8651733398438</v>
+        <v>109.8651885986328</v>
       </c>
       <c r="C272" t="n">
-        <v>110.7530938059435</v>
+        <v>110.7531091880527</v>
       </c>
       <c r="D272" t="n">
-        <v>108.6220846873041</v>
+        <v>108.622099773445</v>
       </c>
       <c r="E272" t="n">
-        <v>108.7996687805241</v>
+        <v>108.7996838913289</v>
       </c>
       <c r="F272" t="n">
         <v>294000</v>
@@ -5872,16 +5872,16 @@
         <v>43620</v>
       </c>
       <c r="B273" t="n">
-        <v>107.1718139648438</v>
+        <v>107.1718215942383</v>
       </c>
       <c r="C273" t="n">
-        <v>110.9898681385225</v>
+        <v>110.9898760397184</v>
       </c>
       <c r="D273" t="n">
-        <v>107.1718139648438</v>
+        <v>107.1718215942383</v>
       </c>
       <c r="E273" t="n">
-        <v>109.5987915115683</v>
+        <v>109.5987993137355</v>
       </c>
       <c r="F273" t="n">
         <v>283866</v>
@@ -5892,16 +5892,16 @@
         <v>43621</v>
       </c>
       <c r="B274" t="n">
-        <v>108.8884887695312</v>
+        <v>108.8884811401367</v>
       </c>
       <c r="C274" t="n">
-        <v>109.8356016346852</v>
+        <v>109.8355939389301</v>
       </c>
       <c r="D274" t="n">
-        <v>106.4023109123912</v>
+        <v>106.4023034571936</v>
       </c>
       <c r="E274" t="n">
-        <v>106.6390872469337</v>
+        <v>106.6390797751461</v>
       </c>
       <c r="F274" t="n">
         <v>231033</v>
@@ -5912,16 +5912,16 @@
         <v>43622</v>
       </c>
       <c r="B275" t="n">
-        <v>108.7404861450195</v>
+        <v>108.7404937744141</v>
       </c>
       <c r="C275" t="n">
-        <v>109.6875988830724</v>
+        <v>109.6876065789178</v>
       </c>
       <c r="D275" t="n">
-        <v>108.0597458067072</v>
+        <v>108.05975338834</v>
       </c>
       <c r="E275" t="n">
-        <v>109.510014774251</v>
+        <v>109.5100224576369</v>
       </c>
       <c r="F275" t="n">
         <v>227300</v>
@@ -5952,16 +5952,16 @@
         <v>43626</v>
       </c>
       <c r="B277" t="n">
-        <v>114.3935699462891</v>
+        <v>114.3935623168945</v>
       </c>
       <c r="C277" t="n">
-        <v>119.395513715002</v>
+        <v>119.3955057520065</v>
       </c>
       <c r="D277" t="n">
-        <v>111.8778037764888</v>
+        <v>111.8777963148814</v>
       </c>
       <c r="E277" t="n">
-        <v>111.8778037764888</v>
+        <v>111.8777963148814</v>
       </c>
       <c r="F277" t="n">
         <v>585833</v>
@@ -5972,16 +5972,16 @@
         <v>43627</v>
       </c>
       <c r="B278" t="n">
-        <v>110.9898834228516</v>
+        <v>110.989875793457</v>
       </c>
       <c r="C278" t="n">
-        <v>116.6725675616569</v>
+        <v>116.6725595416372</v>
       </c>
       <c r="D278" t="n">
-        <v>110.9898834228516</v>
+        <v>110.989875793457</v>
       </c>
       <c r="E278" t="n">
-        <v>116.465379822189</v>
+        <v>116.4653718164113</v>
       </c>
       <c r="F278" t="n">
         <v>422033</v>
@@ -5992,16 +5992,16 @@
         <v>43628</v>
       </c>
       <c r="B279" t="n">
-        <v>108.9180755615234</v>
+        <v>108.9180679321289</v>
       </c>
       <c r="C279" t="n">
-        <v>111.7594139141432</v>
+        <v>111.7594060857212</v>
       </c>
       <c r="D279" t="n">
-        <v>108.7996836408789</v>
+        <v>108.7996760197774</v>
       </c>
       <c r="E279" t="n">
-        <v>111.7594139141432</v>
+        <v>111.7594060857212</v>
       </c>
       <c r="F279" t="n">
         <v>382266</v>
@@ -6012,16 +6012,16 @@
         <v>43629</v>
       </c>
       <c r="B280" t="n">
-        <v>113.8608016967773</v>
+        <v>113.8608169555664</v>
       </c>
       <c r="C280" t="n">
-        <v>114.9854984206418</v>
+        <v>114.9855138301545</v>
       </c>
       <c r="D280" t="n">
-        <v>108.9180583413137</v>
+        <v>108.9180729377125</v>
       </c>
       <c r="E280" t="n">
-        <v>108.9180583413137</v>
+        <v>108.9180729377125</v>
       </c>
       <c r="F280" t="n">
         <v>845300</v>
@@ -6032,16 +6032,16 @@
         <v>43630</v>
       </c>
       <c r="B281" t="n">
-        <v>111.9370040893555</v>
+        <v>111.9369888305664</v>
       </c>
       <c r="C281" t="n">
-        <v>114.1568019144333</v>
+        <v>114.1567863530506</v>
       </c>
       <c r="D281" t="n">
-        <v>110.7531149267741</v>
+        <v>110.7530998293679</v>
       </c>
       <c r="E281" t="n">
-        <v>113.3576771060401</v>
+        <v>113.3576616535908</v>
       </c>
       <c r="F281" t="n">
         <v>560666</v>
@@ -6052,16 +6052,16 @@
         <v>43633</v>
       </c>
       <c r="B282" t="n">
-        <v>110.0723571777344</v>
+        <v>110.0723648071289</v>
       </c>
       <c r="C282" t="n">
-        <v>113.1504790532982</v>
+        <v>113.1504868960452</v>
       </c>
       <c r="D282" t="n">
-        <v>109.0660447737885</v>
+        <v>109.066052333433</v>
       </c>
       <c r="E282" t="n">
-        <v>113.1504790532982</v>
+        <v>113.1504868960452</v>
       </c>
       <c r="F282" t="n">
         <v>481366</v>
@@ -6092,16 +6092,16 @@
         <v>43635</v>
       </c>
       <c r="B284" t="n">
-        <v>115.3702850341797</v>
+        <v>115.3702926635742</v>
       </c>
       <c r="C284" t="n">
-        <v>115.3702850341797</v>
+        <v>115.3702926635742</v>
       </c>
       <c r="D284" t="n">
-        <v>111.6114225804171</v>
+        <v>111.6114299612394</v>
       </c>
       <c r="E284" t="n">
-        <v>112.3513551267584</v>
+        <v>112.3513625565122</v>
       </c>
       <c r="F284" t="n">
         <v>441733</v>
@@ -6112,16 +6112,16 @@
         <v>43637</v>
       </c>
       <c r="B285" t="n">
-        <v>116.4653854370117</v>
+        <v>116.4653701782227</v>
       </c>
       <c r="C285" t="n">
-        <v>116.4949890633509</v>
+        <v>116.4949738006833</v>
       </c>
       <c r="D285" t="n">
-        <v>114.541563709061</v>
+        <v>114.5415487023227</v>
       </c>
       <c r="E285" t="n">
-        <v>115.3998882252917</v>
+        <v>115.3998731060995</v>
       </c>
       <c r="F285" t="n">
         <v>285566</v>
@@ -6132,16 +6132,16 @@
         <v>43640</v>
       </c>
       <c r="B286" t="n">
-        <v>116.5245742797852</v>
+        <v>116.5245819091797</v>
       </c>
       <c r="C286" t="n">
-        <v>117.5012831022177</v>
+        <v>117.5012907955618</v>
       </c>
       <c r="D286" t="n">
-        <v>115.0447092343492</v>
+        <v>115.0447167668502</v>
       </c>
       <c r="E286" t="n">
-        <v>116.6133625695595</v>
+        <v>116.6133702047674</v>
       </c>
       <c r="F286" t="n">
         <v>315633</v>
@@ -6212,16 +6212,16 @@
         <v>43644</v>
       </c>
       <c r="B290" t="n">
-        <v>116.7021560668945</v>
+        <v>116.7021484375</v>
       </c>
       <c r="C290" t="n">
-        <v>117.649268773912</v>
+        <v>117.6492610826</v>
       </c>
       <c r="D290" t="n">
-        <v>114.1271903368541</v>
+        <v>114.1271828757977</v>
       </c>
       <c r="E290" t="n">
-        <v>115.0743030438715</v>
+        <v>115.0742955208978</v>
       </c>
       <c r="F290" t="n">
         <v>617600</v>
@@ -6232,16 +6232,16 @@
         <v>43647</v>
       </c>
       <c r="B291" t="n">
-        <v>114.0679931640625</v>
+        <v>114.0680084228516</v>
       </c>
       <c r="C291" t="n">
-        <v>117.0573191615848</v>
+        <v>117.0573348202537</v>
       </c>
       <c r="D291" t="n">
-        <v>114.0679931640625</v>
+        <v>114.0680084228516</v>
       </c>
       <c r="E291" t="n">
-        <v>117.0573191615848</v>
+        <v>117.0573348202537</v>
       </c>
       <c r="F291" t="n">
         <v>436066</v>
@@ -6292,16 +6292,16 @@
         <v>43650</v>
       </c>
       <c r="B294" t="n">
-        <v>114.1004333496094</v>
+        <v>114.1004409790039</v>
       </c>
       <c r="C294" t="n">
-        <v>114.1004333496094</v>
+        <v>114.1004409790039</v>
       </c>
       <c r="D294" t="n">
-        <v>109.4044550659338</v>
+        <v>109.4044623813289</v>
       </c>
       <c r="E294" t="n">
-        <v>109.9691612673977</v>
+        <v>109.9691686205522</v>
       </c>
       <c r="F294" t="n">
         <v>412866</v>
@@ -6312,16 +6312,16 @@
         <v>43651</v>
       </c>
       <c r="B295" t="n">
-        <v>117.5184020996094</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="C295" t="n">
-        <v>117.5184020996094</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="D295" t="n">
-        <v>112.9115842237956</v>
+        <v>112.9115768934796</v>
       </c>
       <c r="E295" t="n">
-        <v>114.0707168497463</v>
+        <v>114.0707094441784</v>
       </c>
       <c r="F295" t="n">
         <v>288866</v>
@@ -6332,16 +6332,16 @@
         <v>43654</v>
       </c>
       <c r="B296" t="n">
-        <v>121.9171752929688</v>
+        <v>121.9171600341797</v>
       </c>
       <c r="C296" t="n">
-        <v>122.8682591462495</v>
+        <v>122.8682437684256</v>
       </c>
       <c r="D296" t="n">
-        <v>115.4081892669675</v>
+        <v>115.4081748228237</v>
       </c>
       <c r="E296" t="n">
-        <v>117.488685668428</v>
+        <v>117.4886709638954</v>
       </c>
       <c r="F296" t="n">
         <v>420600</v>
@@ -6352,16 +6352,16 @@
         <v>43656</v>
       </c>
       <c r="B297" t="n">
-        <v>128.0397644042969</v>
+        <v>128.039794921875</v>
       </c>
       <c r="C297" t="n">
-        <v>128.0397644042969</v>
+        <v>128.039794921875</v>
       </c>
       <c r="D297" t="n">
-        <v>121.9171496849643</v>
+        <v>121.9171787432507</v>
       </c>
       <c r="E297" t="n">
-        <v>121.9171496849643</v>
+        <v>121.9171787432507</v>
       </c>
       <c r="F297" t="n">
         <v>529166</v>
@@ -6372,16 +6372,16 @@
         <v>43657</v>
       </c>
       <c r="B298" t="n">
-        <v>123.1654663085938</v>
+        <v>123.1654510498047</v>
       </c>
       <c r="C298" t="n">
-        <v>130.1797101104775</v>
+        <v>130.1796939827041</v>
       </c>
       <c r="D298" t="n">
-        <v>123.1060259345613</v>
+        <v>123.1060106831362</v>
       </c>
       <c r="E298" t="n">
-        <v>130.1797101104775</v>
+        <v>130.1796939827041</v>
       </c>
       <c r="F298" t="n">
         <v>660700</v>
@@ -6392,16 +6392,16 @@
         <v>43658</v>
       </c>
       <c r="B299" t="n">
-        <v>124.8001327514648</v>
+        <v>124.8001556396484</v>
       </c>
       <c r="C299" t="n">
-        <v>125.8700971749934</v>
+        <v>125.8701202594071</v>
       </c>
       <c r="D299" t="n">
-        <v>122.7196367142455</v>
+        <v>122.7196592208688</v>
       </c>
       <c r="E299" t="n">
-        <v>124.2057063920509</v>
+        <v>124.2057291712175</v>
       </c>
       <c r="F299" t="n">
         <v>362933</v>
@@ -6412,16 +6412,16 @@
         <v>43661</v>
       </c>
       <c r="B300" t="n">
-        <v>121.5605010986328</v>
+        <v>121.5605087280273</v>
       </c>
       <c r="C300" t="n">
-        <v>126.7320249772505</v>
+        <v>126.7320329312208</v>
       </c>
       <c r="D300" t="n">
-        <v>118.5289212629776</v>
+        <v>118.5289287021037</v>
       </c>
       <c r="E300" t="n">
-        <v>124.9784660186075</v>
+        <v>124.9784738625208</v>
       </c>
       <c r="F300" t="n">
         <v>1110366</v>
@@ -6432,16 +6432,16 @@
         <v>43662</v>
       </c>
       <c r="B301" t="n">
-        <v>124.1462631225586</v>
+        <v>124.1462707519531</v>
       </c>
       <c r="C301" t="n">
-        <v>124.2354312370136</v>
+        <v>124.2354388718879</v>
       </c>
       <c r="D301" t="n">
-        <v>120.4608089739724</v>
+        <v>120.4608163768777</v>
       </c>
       <c r="E301" t="n">
-        <v>121.5605011814873</v>
+        <v>121.5605086519742</v>
       </c>
       <c r="F301" t="n">
         <v>378300</v>
@@ -6452,16 +6452,16 @@
         <v>43663</v>
       </c>
       <c r="B302" t="n">
-        <v>126.6131286621094</v>
+        <v>126.6131362915039</v>
       </c>
       <c r="C302" t="n">
-        <v>127.9505898250198</v>
+        <v>127.9505975350065</v>
       </c>
       <c r="D302" t="n">
-        <v>122.7493536489327</v>
+        <v>122.7493610455057</v>
       </c>
       <c r="E302" t="n">
-        <v>123.9679265196912</v>
+        <v>123.9679339896924</v>
       </c>
       <c r="F302" t="n">
         <v>443966</v>
@@ -6512,16 +6512,16 @@
         <v>43668</v>
       </c>
       <c r="B305" t="n">
-        <v>127.4453430175781</v>
+        <v>127.4453506469727</v>
       </c>
       <c r="C305" t="n">
-        <v>129.080013719631</v>
+        <v>129.0800214468836</v>
       </c>
       <c r="D305" t="n">
-        <v>126.0781615486755</v>
+        <v>126.078169096225</v>
       </c>
       <c r="E305" t="n">
-        <v>126.3456507818258</v>
+        <v>126.3456583453883</v>
       </c>
       <c r="F305" t="n">
         <v>163233</v>
@@ -6532,16 +6532,16 @@
         <v>43669</v>
       </c>
       <c r="B306" t="n">
-        <v>125.067626953125</v>
+        <v>125.0676345825195</v>
       </c>
       <c r="C306" t="n">
-        <v>127.8019973856753</v>
+        <v>127.8020051818723</v>
       </c>
       <c r="D306" t="n">
-        <v>123.6409975868307</v>
+        <v>123.6410051291977</v>
       </c>
       <c r="E306" t="n">
-        <v>127.4750602294759</v>
+        <v>127.475068005729</v>
       </c>
       <c r="F306" t="n">
         <v>528700</v>
@@ -6552,16 +6552,16 @@
         <v>43670</v>
       </c>
       <c r="B307" t="n">
-        <v>128.8719635009766</v>
+        <v>128.8719482421875</v>
       </c>
       <c r="C307" t="n">
-        <v>131.8441028387747</v>
+        <v>131.8440872280763</v>
       </c>
       <c r="D307" t="n">
-        <v>124.948740482108</v>
+        <v>124.9487256878391</v>
       </c>
       <c r="E307" t="n">
-        <v>124.948740482108</v>
+        <v>124.9487256878391</v>
       </c>
       <c r="F307" t="n">
         <v>788600</v>
@@ -6572,16 +6572,16 @@
         <v>43671</v>
       </c>
       <c r="B308" t="n">
-        <v>126.4645538330078</v>
+        <v>126.4645385742188</v>
       </c>
       <c r="C308" t="n">
-        <v>131.3388538800843</v>
+        <v>131.3388380331786</v>
       </c>
       <c r="D308" t="n">
-        <v>126.0484485039095</v>
+        <v>126.0484332953263</v>
       </c>
       <c r="E308" t="n">
-        <v>129.3178054063731</v>
+        <v>129.3177898033202</v>
       </c>
       <c r="F308" t="n">
         <v>3248566</v>
@@ -6612,16 +6612,16 @@
         <v>43675</v>
       </c>
       <c r="B310" t="n">
-        <v>126.0187225341797</v>
+        <v>126.0187149047852</v>
       </c>
       <c r="C310" t="n">
-        <v>126.8806382252905</v>
+        <v>126.8806305437141</v>
       </c>
       <c r="D310" t="n">
-        <v>125.0081983436745</v>
+        <v>125.0081907754589</v>
       </c>
       <c r="E310" t="n">
-        <v>126.6131489732146</v>
+        <v>126.6131413078325</v>
       </c>
       <c r="F310" t="n">
         <v>708133</v>
@@ -6632,16 +6632,16 @@
         <v>43676</v>
       </c>
       <c r="B311" t="n">
-        <v>124.3840408325195</v>
+        <v>124.3840484619141</v>
       </c>
       <c r="C311" t="n">
-        <v>126.3753765306633</v>
+        <v>126.3753842822012</v>
       </c>
       <c r="D311" t="n">
-        <v>124.294880270392</v>
+        <v>124.2948878943177</v>
       </c>
       <c r="E311" t="n">
-        <v>126.2267680352421</v>
+        <v>126.2267757776647</v>
       </c>
       <c r="F311" t="n">
         <v>1065500</v>
@@ -6692,16 +6692,16 @@
         <v>43679</v>
       </c>
       <c r="B314" t="n">
-        <v>124.0868225097656</v>
+        <v>124.0868301391602</v>
       </c>
       <c r="C314" t="n">
-        <v>124.8001371898471</v>
+        <v>124.8001448630993</v>
       </c>
       <c r="D314" t="n">
-        <v>122.4521442943359</v>
+        <v>122.4521518232233</v>
       </c>
       <c r="E314" t="n">
-        <v>122.6601931496027</v>
+        <v>122.6602006912819</v>
       </c>
       <c r="F314" t="n">
         <v>454366</v>
@@ -6712,16 +6712,16 @@
         <v>43682</v>
       </c>
       <c r="B315" t="n">
-        <v>123.4032440185547</v>
+        <v>123.4032211303711</v>
       </c>
       <c r="C315" t="n">
-        <v>124.3543278624913</v>
+        <v>124.3543047979057</v>
       </c>
       <c r="D315" t="n">
-        <v>121.8577337169754</v>
+        <v>121.8577111154449</v>
       </c>
       <c r="E315" t="n">
-        <v>124.0571184129413</v>
+        <v>124.0570954034805</v>
       </c>
       <c r="F315" t="n">
         <v>384500</v>
@@ -6732,16 +6732,16 @@
         <v>43683</v>
       </c>
       <c r="B316" t="n">
-        <v>126.6131286621094</v>
+        <v>126.6131362915039</v>
       </c>
       <c r="C316" t="n">
-        <v>127.1778348223845</v>
+        <v>127.1778424858068</v>
       </c>
       <c r="D316" t="n">
-        <v>123.1357311502504</v>
+        <v>123.1357385701055</v>
       </c>
       <c r="E316" t="n">
-        <v>123.1951715170559</v>
+        <v>123.1951789404927</v>
       </c>
       <c r="F316" t="n">
         <v>466533</v>
@@ -6752,16 +6752,16 @@
         <v>43684</v>
       </c>
       <c r="B317" t="n">
-        <v>128.5153045654297</v>
+        <v>128.5153198242188</v>
       </c>
       <c r="C317" t="n">
-        <v>129.2583393905688</v>
+        <v>129.2583547375794</v>
       </c>
       <c r="D317" t="n">
-        <v>124.740682513915</v>
+        <v>124.7406973245383</v>
       </c>
       <c r="E317" t="n">
-        <v>126.6131296685823</v>
+        <v>126.6131447015237</v>
       </c>
       <c r="F317" t="n">
         <v>506366</v>
@@ -6792,16 +6792,16 @@
         <v>43686</v>
       </c>
       <c r="B319" t="n">
-        <v>131.5171966552734</v>
+        <v>131.5171508789062</v>
       </c>
       <c r="C319" t="n">
-        <v>134.8757142928603</v>
+        <v>134.8756673475149</v>
       </c>
       <c r="D319" t="n">
-        <v>129.4069723912467</v>
+        <v>129.4069273493721</v>
       </c>
       <c r="E319" t="n">
-        <v>134.8757142928603</v>
+        <v>134.8756673475149</v>
       </c>
       <c r="F319" t="n">
         <v>371566</v>
@@ -6812,16 +6812,16 @@
         <v>43689</v>
       </c>
       <c r="B320" t="n">
-        <v>131.1902008056641</v>
+        <v>131.1902313232422</v>
       </c>
       <c r="C320" t="n">
-        <v>131.48741769999</v>
+        <v>131.487448286707</v>
       </c>
       <c r="D320" t="n">
-        <v>128.8422160629397</v>
+        <v>128.8422460343276</v>
       </c>
       <c r="E320" t="n">
-        <v>131.48741769999</v>
+        <v>131.487448286707</v>
       </c>
       <c r="F320" t="n">
         <v>372500</v>
@@ -6832,16 +6832,16 @@
         <v>43690</v>
       </c>
       <c r="B321" t="n">
-        <v>131.0713653564453</v>
+        <v>131.0713500976562</v>
       </c>
       <c r="C321" t="n">
-        <v>133.7760082829146</v>
+        <v>133.7759927092622</v>
       </c>
       <c r="D321" t="n">
-        <v>128.8125403668755</v>
+        <v>128.8125253710496</v>
       </c>
       <c r="E321" t="n">
-        <v>133.6571275309639</v>
+        <v>133.6571119711511</v>
       </c>
       <c r="F321" t="n">
         <v>614133</v>
@@ -6852,16 +6852,16 @@
         <v>43691</v>
       </c>
       <c r="B322" t="n">
-        <v>137.0156555175781</v>
+        <v>137.015625</v>
       </c>
       <c r="C322" t="n">
-        <v>140.9685919991994</v>
+        <v>140.9685606011814</v>
       </c>
       <c r="D322" t="n">
-        <v>135.2323685137598</v>
+        <v>135.2323383933742</v>
       </c>
       <c r="E322" t="n">
-        <v>139.6905784647628</v>
+        <v>139.6905473513976</v>
       </c>
       <c r="F322" t="n">
         <v>1453733</v>
@@ -6872,16 +6872,16 @@
         <v>43692</v>
       </c>
       <c r="B323" t="n">
-        <v>140.1660919189453</v>
+        <v>140.1661224365234</v>
       </c>
       <c r="C323" t="n">
-        <v>142.0088189785496</v>
+        <v>142.0088498973343</v>
       </c>
       <c r="D323" t="n">
-        <v>136.3023166893313</v>
+        <v>136.3023463656713</v>
       </c>
       <c r="E323" t="n">
-        <v>139.5122176132928</v>
+        <v>139.5122479885065</v>
       </c>
       <c r="F323" t="n">
         <v>846233</v>
@@ -6892,16 +6892,16 @@
         <v>43693</v>
       </c>
       <c r="B324" t="n">
-        <v>145.6348419189453</v>
+        <v>145.6348571777344</v>
       </c>
       <c r="C324" t="n">
-        <v>145.6348419189453</v>
+        <v>145.6348571777344</v>
       </c>
       <c r="D324" t="n">
-        <v>137.2236813210683</v>
+        <v>137.2236956985838</v>
       </c>
       <c r="E324" t="n">
-        <v>141.8305068193669</v>
+        <v>141.8305216795594</v>
       </c>
       <c r="F324" t="n">
         <v>930266</v>
@@ -6932,16 +6932,16 @@
         <v>43697</v>
       </c>
       <c r="B326" t="n">
-        <v>145.0106811523438</v>
+        <v>145.0106658935547</v>
       </c>
       <c r="C326" t="n">
-        <v>146.7048073163463</v>
+        <v>146.7047918792924</v>
       </c>
       <c r="D326" t="n">
-        <v>140.4633113521918</v>
+        <v>140.463296571901</v>
       </c>
       <c r="E326" t="n">
-        <v>143.049073318038</v>
+        <v>143.0490582656597</v>
       </c>
       <c r="F326" t="n">
         <v>506533</v>
@@ -6952,16 +6952,16 @@
         <v>43698</v>
       </c>
       <c r="B327" t="n">
-        <v>148.5772399902344</v>
+        <v>148.5772552490234</v>
       </c>
       <c r="C327" t="n">
-        <v>148.7258409035746</v>
+        <v>148.7258561776249</v>
       </c>
       <c r="D327" t="n">
-        <v>143.4057165668508</v>
+        <v>143.4057312945277</v>
       </c>
       <c r="E327" t="n">
-        <v>146.8236736274112</v>
+        <v>146.8236887061101</v>
       </c>
       <c r="F327" t="n">
         <v>558733</v>
@@ -6972,16 +6972,16 @@
         <v>43699</v>
       </c>
       <c r="B328" t="n">
-        <v>148.5475311279297</v>
+        <v>148.5475463867188</v>
       </c>
       <c r="C328" t="n">
-        <v>151.3116141462722</v>
+        <v>151.3116296889876</v>
       </c>
       <c r="D328" t="n">
-        <v>146.8236848164054</v>
+        <v>146.8236998981212</v>
       </c>
       <c r="E328" t="n">
-        <v>148.5772513128626</v>
+        <v>148.5772665747045</v>
       </c>
       <c r="F328" t="n">
         <v>509000</v>
@@ -7012,16 +7012,16 @@
         <v>43703</v>
       </c>
       <c r="B330" t="n">
-        <v>143.5543212890625</v>
+        <v>143.5543365478516</v>
       </c>
       <c r="C330" t="n">
-        <v>146.2292587368132</v>
+        <v>146.2292742799288</v>
       </c>
       <c r="D330" t="n">
-        <v>141.2063360934986</v>
+        <v>141.2063511027138</v>
       </c>
       <c r="E330" t="n">
-        <v>143.3165598214097</v>
+        <v>143.3165750549265</v>
       </c>
       <c r="F330" t="n">
         <v>278200</v>
@@ -7032,16 +7032,16 @@
         <v>43704</v>
       </c>
       <c r="B331" t="n">
-        <v>145.4862518310547</v>
+        <v>145.4862365722656</v>
       </c>
       <c r="C331" t="n">
-        <v>146.4670483074746</v>
+        <v>146.4670329458183</v>
       </c>
       <c r="D331" t="n">
-        <v>141.7710770153187</v>
+        <v>141.7710621461821</v>
       </c>
       <c r="E331" t="n">
-        <v>143.4057478874085</v>
+        <v>143.4057328468255</v>
       </c>
       <c r="F331" t="n">
         <v>495866</v>
@@ -7052,16 +7052,16 @@
         <v>43705</v>
       </c>
       <c r="B332" t="n">
-        <v>145.6348419189453</v>
+        <v>145.6348571777344</v>
       </c>
       <c r="C332" t="n">
-        <v>146.585918135298</v>
+        <v>146.5859334937354</v>
       </c>
       <c r="D332" t="n">
-        <v>143.9704358647023</v>
+        <v>143.9704509491044</v>
       </c>
       <c r="E332" t="n">
-        <v>145.6942822928319</v>
+        <v>145.6942975578488</v>
       </c>
       <c r="F332" t="n">
         <v>446600</v>
@@ -7092,16 +7092,16 @@
         <v>43707</v>
       </c>
       <c r="B334" t="n">
-        <v>153.6893615722656</v>
+        <v>153.6893463134766</v>
       </c>
       <c r="C334" t="n">
-        <v>153.6893615722656</v>
+        <v>153.6893463134766</v>
       </c>
       <c r="D334" t="n">
-        <v>149.8850109492535</v>
+        <v>149.884996068173</v>
       </c>
       <c r="E334" t="n">
-        <v>150.9847033348667</v>
+        <v>150.984688344605</v>
       </c>
       <c r="F334" t="n">
         <v>973933</v>
@@ -7112,16 +7112,16 @@
         <v>43710</v>
       </c>
       <c r="B335" t="n">
-        <v>155.1456909179688</v>
+        <v>155.1456756591797</v>
       </c>
       <c r="C335" t="n">
-        <v>155.8887258071983</v>
+        <v>155.8887104753308</v>
       </c>
       <c r="D335" t="n">
-        <v>152.1140958715619</v>
+        <v>152.1140809109343</v>
       </c>
       <c r="E335" t="n">
-        <v>153.6596211395096</v>
+        <v>153.6596060268775</v>
       </c>
       <c r="F335" t="n">
         <v>734566</v>
@@ -7172,16 +7172,16 @@
         <v>43713</v>
       </c>
       <c r="B338" t="n">
-        <v>149.2608642578125</v>
+        <v>149.2608337402344</v>
       </c>
       <c r="C338" t="n">
-        <v>150.2119405274403</v>
+        <v>150.2119098154071</v>
       </c>
       <c r="D338" t="n">
-        <v>145.5159693223478</v>
+        <v>145.5159395704434</v>
       </c>
       <c r="E338" t="n">
-        <v>150.2119405274403</v>
+        <v>150.2119098154071</v>
       </c>
       <c r="F338" t="n">
         <v>845300</v>
@@ -7192,16 +7192,16 @@
         <v>43714</v>
       </c>
       <c r="B339" t="n">
-        <v>146.2292633056641</v>
+        <v>146.2292785644531</v>
       </c>
       <c r="C339" t="n">
-        <v>150.5091361450396</v>
+        <v>150.5091518504265</v>
       </c>
       <c r="D339" t="n">
-        <v>145.4862284618692</v>
+        <v>145.4862436431238</v>
       </c>
       <c r="E339" t="n">
-        <v>150.0633182621792</v>
+        <v>150.0633339210457</v>
       </c>
       <c r="F339" t="n">
         <v>678033</v>
@@ -7232,16 +7232,16 @@
         <v>43718</v>
       </c>
       <c r="B341" t="n">
-        <v>146.4075775146484</v>
+        <v>146.4075927734375</v>
       </c>
       <c r="C341" t="n">
-        <v>146.4967380636036</v>
+        <v>146.4967533316851</v>
       </c>
       <c r="D341" t="n">
-        <v>140.6416201422374</v>
+        <v>140.6416348000909</v>
       </c>
       <c r="E341" t="n">
-        <v>142.0385292108626</v>
+        <v>142.0385440143037</v>
       </c>
       <c r="F341" t="n">
         <v>1022600</v>
@@ -7252,16 +7252,16 @@
         <v>43719</v>
       </c>
       <c r="B342" t="n">
-        <v>152.5301818847656</v>
+        <v>152.5301971435547</v>
       </c>
       <c r="C342" t="n">
-        <v>152.5301818847656</v>
+        <v>152.5301971435547</v>
       </c>
       <c r="D342" t="n">
-        <v>146.7047990800743</v>
+        <v>146.7048137561047</v>
       </c>
       <c r="E342" t="n">
-        <v>148.5772462524898</v>
+        <v>148.5772611158358</v>
       </c>
       <c r="F342" t="n">
         <v>523500</v>
@@ -7272,16 +7272,16 @@
         <v>43720</v>
       </c>
       <c r="B343" t="n">
-        <v>148.3691864013672</v>
+        <v>148.3692016601562</v>
       </c>
       <c r="C343" t="n">
-        <v>154.4918011372027</v>
+        <v>154.4918170256621</v>
       </c>
       <c r="D343" t="n">
-        <v>148.3394662181369</v>
+        <v>148.3394814738694</v>
       </c>
       <c r="E343" t="n">
-        <v>153.9568076048933</v>
+        <v>153.9568234383322</v>
       </c>
       <c r="F343" t="n">
         <v>700866</v>
@@ -7332,16 +7332,16 @@
         <v>43725</v>
       </c>
       <c r="B346" t="n">
-        <v>153.065185546875</v>
+        <v>153.0652160644531</v>
       </c>
       <c r="C346" t="n">
-        <v>153.065185546875</v>
+        <v>153.0652160644531</v>
       </c>
       <c r="D346" t="n">
-        <v>149.0825143503477</v>
+        <v>149.0825440738754</v>
       </c>
       <c r="E346" t="n">
-        <v>150.3902629976278</v>
+        <v>150.3902929818897</v>
       </c>
       <c r="F346" t="n">
         <v>1122433</v>
@@ -7372,16 +7372,16 @@
         <v>43727</v>
       </c>
       <c r="B348" t="n">
-        <v>153.0354614257812</v>
+        <v>153.0354766845703</v>
       </c>
       <c r="C348" t="n">
-        <v>155.3834467528314</v>
+        <v>155.3834622457323</v>
       </c>
       <c r="D348" t="n">
-        <v>151.5493917014036</v>
+        <v>151.5494068120203</v>
       </c>
       <c r="E348" t="n">
-        <v>154.4026504096753</v>
+        <v>154.4026658047834</v>
       </c>
       <c r="F348" t="n">
         <v>446666</v>
@@ -7412,16 +7412,16 @@
         <v>43731</v>
       </c>
       <c r="B350" t="n">
-        <v>157.9395141601562</v>
+        <v>157.9394989013672</v>
       </c>
       <c r="C350" t="n">
-        <v>159.0986469194959</v>
+        <v>159.0986315487212</v>
       </c>
       <c r="D350" t="n">
-        <v>153.6893607092441</v>
+        <v>153.6893458610692</v>
       </c>
       <c r="E350" t="n">
-        <v>154.5512764519898</v>
+        <v>154.5512615205438</v>
       </c>
       <c r="F350" t="n">
         <v>685766</v>
@@ -7432,16 +7432,16 @@
         <v>43732</v>
       </c>
       <c r="B351" t="n">
-        <v>155.1456909179688</v>
+        <v>155.1456756591797</v>
       </c>
       <c r="C351" t="n">
-        <v>158.9203057365216</v>
+        <v>158.9202901064941</v>
       </c>
       <c r="D351" t="n">
-        <v>154.6998578907642</v>
+        <v>154.6998426758234</v>
       </c>
       <c r="E351" t="n">
-        <v>158.6825291298181</v>
+        <v>158.6825135231762</v>
       </c>
       <c r="F351" t="n">
         <v>630466</v>
@@ -7452,16 +7452,16 @@
         <v>43733</v>
       </c>
       <c r="B352" t="n">
-        <v>155.1456909179688</v>
+        <v>155.1456756591797</v>
       </c>
       <c r="C352" t="n">
-        <v>156.0373267382109</v>
+        <v>156.0373113917282</v>
       </c>
       <c r="D352" t="n">
-        <v>152.708529829779</v>
+        <v>152.708514810688</v>
       </c>
       <c r="E352" t="n">
-        <v>155.4726129661963</v>
+        <v>155.472597675254</v>
       </c>
       <c r="F352" t="n">
         <v>976666</v>
@@ -7472,16 +7472,16 @@
         <v>43734</v>
       </c>
       <c r="B353" t="n">
-        <v>157.3747863769531</v>
+        <v>157.3748016357422</v>
       </c>
       <c r="C353" t="n">
-        <v>159.4255546903437</v>
+        <v>159.4255701479717</v>
       </c>
       <c r="D353" t="n">
-        <v>154.9970658002995</v>
+        <v>154.9970808285488</v>
       </c>
       <c r="E353" t="n">
-        <v>155.4726038687971</v>
+        <v>155.4726189431538</v>
       </c>
       <c r="F353" t="n">
         <v>815966</v>
@@ -7492,16 +7492,16 @@
         <v>43735</v>
       </c>
       <c r="B354" t="n">
-        <v>158.1178436279297</v>
+        <v>158.1178283691406</v>
       </c>
       <c r="C354" t="n">
-        <v>158.8014230845343</v>
+        <v>158.8014077597781</v>
       </c>
       <c r="D354" t="n">
-        <v>156.2453810389101</v>
+        <v>156.2453659608186</v>
       </c>
       <c r="E354" t="n">
-        <v>157.3748086768907</v>
+        <v>157.3747934898065</v>
       </c>
       <c r="F354" t="n">
         <v>505200</v>
@@ -7512,16 +7512,16 @@
         <v>43738</v>
       </c>
       <c r="B355" t="n">
-        <v>160.0497283935547</v>
+        <v>160.0497131347656</v>
       </c>
       <c r="C355" t="n">
-        <v>161.5655184551029</v>
+        <v>161.5655030518017</v>
       </c>
       <c r="D355" t="n">
-        <v>157.5234065852795</v>
+        <v>157.5233915673444</v>
       </c>
       <c r="E355" t="n">
-        <v>158.3853222744112</v>
+        <v>158.385307174303</v>
       </c>
       <c r="F355" t="n">
         <v>546766</v>
@@ -7532,16 +7532,16 @@
         <v>43739</v>
       </c>
       <c r="B356" t="n">
-        <v>158.1178436279297</v>
+        <v>158.1178283691406</v>
       </c>
       <c r="C356" t="n">
-        <v>159.4850176582238</v>
+        <v>159.4850022674988</v>
       </c>
       <c r="D356" t="n">
-        <v>156.8992554239247</v>
+        <v>156.8992402827326</v>
       </c>
       <c r="E356" t="n">
-        <v>159.3066965261751</v>
+        <v>159.3066811526586</v>
       </c>
       <c r="F356" t="n">
         <v>759100</v>
@@ -7572,16 +7572,16 @@
         <v>43741</v>
       </c>
       <c r="B358" t="n">
-        <v>160.4955444335938</v>
+        <v>160.4955291748047</v>
       </c>
       <c r="C358" t="n">
-        <v>160.4955444335938</v>
+        <v>160.4955291748047</v>
       </c>
       <c r="D358" t="n">
-        <v>154.2243278277865</v>
+        <v>154.2243131652207</v>
       </c>
       <c r="E358" t="n">
-        <v>155.7401178714037</v>
+        <v>155.7401030647272</v>
       </c>
       <c r="F358" t="n">
         <v>638566</v>
@@ -7592,16 +7592,16 @@
         <v>43742</v>
       </c>
       <c r="B359" t="n">
-        <v>160.4955444335938</v>
+        <v>160.4955291748047</v>
       </c>
       <c r="C359" t="n">
-        <v>161.624956919369</v>
+        <v>161.6249415532033</v>
       </c>
       <c r="D359" t="n">
-        <v>158.2961598375444</v>
+        <v>158.2961447878574</v>
       </c>
       <c r="E359" t="n">
-        <v>160.3766636825914</v>
+        <v>160.3766484351047</v>
       </c>
       <c r="F359" t="n">
         <v>752266</v>
@@ -7632,16 +7632,16 @@
         <v>43746</v>
       </c>
       <c r="B361" t="n">
-        <v>160.6441345214844</v>
+        <v>160.6441192626953</v>
       </c>
       <c r="C361" t="n">
-        <v>163.7351698925173</v>
+        <v>163.7351543401261</v>
       </c>
       <c r="D361" t="n">
-        <v>158.2664289595359</v>
+        <v>158.2664139265933</v>
       </c>
       <c r="E361" t="n">
-        <v>161.4168895849718</v>
+        <v>161.4168742527825</v>
       </c>
       <c r="F361" t="n">
         <v>478600</v>
@@ -7692,16 +7692,16 @@
         <v>43749</v>
       </c>
       <c r="B364" t="n">
-        <v>167.2422943115234</v>
+        <v>167.2422790527344</v>
       </c>
       <c r="C364" t="n">
-        <v>168.2825462038862</v>
+        <v>168.282530850187</v>
       </c>
       <c r="D364" t="n">
-        <v>163.7648963917685</v>
+        <v>163.764881450249</v>
       </c>
       <c r="E364" t="n">
-        <v>163.7648963917685</v>
+        <v>163.764881450249</v>
       </c>
       <c r="F364" t="n">
         <v>518100</v>
@@ -7712,16 +7712,16 @@
         <v>43752</v>
       </c>
       <c r="B365" t="n">
-        <v>167.9259033203125</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C365" t="n">
-        <v>169.5902943979059</v>
+        <v>169.590263577854</v>
       </c>
       <c r="D365" t="n">
-        <v>166.3803930005229</v>
+        <v>166.3803627638141</v>
       </c>
       <c r="E365" t="n">
-        <v>167.2125885393196</v>
+        <v>167.2125581513739</v>
       </c>
       <c r="F365" t="n">
         <v>323333</v>
@@ -7732,16 +7732,16 @@
         <v>43753</v>
       </c>
       <c r="B366" t="n">
-        <v>167.3314666748047</v>
+        <v>167.3314819335938</v>
       </c>
       <c r="C366" t="n">
-        <v>169.2039141662959</v>
+        <v>169.2039295958316</v>
       </c>
       <c r="D366" t="n">
-        <v>167.1828657298788</v>
+        <v>167.1828809751171</v>
       </c>
       <c r="E366" t="n">
-        <v>167.3017464858195</v>
+        <v>167.3017617418984</v>
       </c>
       <c r="F366" t="n">
         <v>550533</v>
@@ -7752,16 +7752,16 @@
         <v>43754</v>
       </c>
       <c r="B367" t="n">
-        <v>170.7791290283203</v>
+        <v>170.7791595458984</v>
       </c>
       <c r="C367" t="n">
-        <v>172.8001771009563</v>
+        <v>172.800207979688</v>
       </c>
       <c r="D367" t="n">
-        <v>167.301716372126</v>
+        <v>167.3017462683037</v>
       </c>
       <c r="E367" t="n">
-        <v>168.7580658386021</v>
+        <v>168.758095995024</v>
       </c>
       <c r="F367" t="n">
         <v>599666</v>
@@ -7772,16 +7772,16 @@
         <v>43755</v>
       </c>
       <c r="B368" t="n">
-        <v>169.7686309814453</v>
+        <v>169.7686157226562</v>
       </c>
       <c r="C368" t="n">
-        <v>172.9785475021482</v>
+        <v>172.9785319548521</v>
       </c>
       <c r="D368" t="n">
-        <v>168.8769799449297</v>
+        <v>168.8769647662821</v>
       </c>
       <c r="E368" t="n">
-        <v>171.2547009252195</v>
+        <v>171.2546855328626</v>
       </c>
       <c r="F368" t="n">
         <v>460533</v>
@@ -7812,16 +7812,16 @@
         <v>43759</v>
       </c>
       <c r="B370" t="n">
-        <v>168.5203247070312</v>
+        <v>168.5203399658203</v>
       </c>
       <c r="C370" t="n">
-        <v>171.7302258637203</v>
+        <v>171.7302414131521</v>
       </c>
       <c r="D370" t="n">
-        <v>167.9853311028604</v>
+        <v>167.9853463132081</v>
       </c>
       <c r="E370" t="n">
-        <v>171.314128125523</v>
+        <v>171.3141436372789</v>
       </c>
       <c r="F370" t="n">
         <v>853400</v>
@@ -7872,16 +7872,16 @@
         <v>43762</v>
       </c>
       <c r="B373" t="n">
-        <v>169.1147613525391</v>
+        <v>169.1147308349609</v>
       </c>
       <c r="C373" t="n">
-        <v>169.6497550129695</v>
+        <v>169.6497243988491</v>
       </c>
       <c r="D373" t="n">
-        <v>165.3698661978689</v>
+        <v>165.3698363560753</v>
       </c>
       <c r="E373" t="n">
-        <v>165.9048447412137</v>
+        <v>165.9048148028805</v>
       </c>
       <c r="F373" t="n">
         <v>606500</v>
@@ -7892,16 +7892,16 @@
         <v>43763</v>
       </c>
       <c r="B374" t="n">
-        <v>168.3717041015625</v>
+        <v>168.3716888427734</v>
       </c>
       <c r="C374" t="n">
-        <v>169.6497325859067</v>
+        <v>169.6497172112956</v>
       </c>
       <c r="D374" t="n">
-        <v>166.8559141258676</v>
+        <v>166.8558990044479</v>
       </c>
       <c r="E374" t="n">
-        <v>169.6497325859067</v>
+        <v>169.6497172112956</v>
       </c>
       <c r="F374" t="n">
         <v>471566</v>
@@ -7912,16 +7912,16 @@
         <v>43766</v>
       </c>
       <c r="B375" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0063781738281</v>
       </c>
       <c r="C375" t="n">
-        <v>170.5710921032597</v>
+        <v>170.5710767937866</v>
       </c>
       <c r="D375" t="n">
-        <v>167.6881130247363</v>
+        <v>167.6880979740227</v>
       </c>
       <c r="E375" t="n">
-        <v>169.3525190838025</v>
+        <v>169.3525038837014</v>
       </c>
       <c r="F375" t="n">
         <v>598700</v>
@@ -7932,16 +7932,16 @@
         <v>43767</v>
       </c>
       <c r="B376" t="n">
-        <v>169.1147613525391</v>
+        <v>169.1147308349609</v>
       </c>
       <c r="C376" t="n">
-        <v>170.8980483588309</v>
+        <v>170.89801751945</v>
       </c>
       <c r="D376" t="n">
-        <v>168.5203424284989</v>
+        <v>168.5203120181865</v>
       </c>
       <c r="E376" t="n">
-        <v>170.3630546984006</v>
+        <v>170.3630239555619</v>
       </c>
       <c r="F376" t="n">
         <v>290500</v>
@@ -7972,16 +7972,16 @@
         <v>43769</v>
       </c>
       <c r="B378" t="n">
-        <v>167.3314666748047</v>
+        <v>167.3314819335938</v>
       </c>
       <c r="C378" t="n">
-        <v>168.5203347025518</v>
+        <v>168.5203500697525</v>
       </c>
       <c r="D378" t="n">
-        <v>166.1426137641425</v>
+        <v>166.1426289145213</v>
       </c>
       <c r="E378" t="n">
-        <v>167.5989634927563</v>
+        <v>167.5989787759381</v>
       </c>
       <c r="F378" t="n">
         <v>595400</v>
@@ -8012,16 +8012,16 @@
         <v>43773</v>
       </c>
       <c r="B380" t="n">
-        <v>165.9939880371094</v>
+        <v>165.9940032958984</v>
       </c>
       <c r="C380" t="n">
-        <v>168.5203095432768</v>
+        <v>168.5203250342948</v>
       </c>
       <c r="D380" t="n">
-        <v>163.9729247853423</v>
+        <v>163.9729398583477</v>
       </c>
       <c r="E380" t="n">
-        <v>168.5203095432768</v>
+        <v>168.5203250342948</v>
       </c>
       <c r="F380" t="n">
         <v>963600</v>
@@ -8032,16 +8032,16 @@
         <v>43774</v>
       </c>
       <c r="B381" t="n">
-        <v>161.5357666015625</v>
+        <v>161.5357971191406</v>
       </c>
       <c r="C381" t="n">
-        <v>166.8856110504182</v>
+        <v>166.885642578697</v>
       </c>
       <c r="D381" t="n">
-        <v>160.9710529041518</v>
+        <v>160.9710833150434</v>
       </c>
       <c r="E381" t="n">
-        <v>166.8856110504182</v>
+        <v>166.885642578697</v>
       </c>
       <c r="F381" t="n">
         <v>956400</v>
@@ -8092,16 +8092,16 @@
         <v>43777</v>
       </c>
       <c r="B384" t="n">
-        <v>165.5184173583984</v>
+        <v>165.5184326171875</v>
       </c>
       <c r="C384" t="n">
-        <v>169.2038710237159</v>
+        <v>169.203886622259</v>
       </c>
       <c r="D384" t="n">
-        <v>163.4082088930739</v>
+        <v>163.4082239573274</v>
       </c>
       <c r="E384" t="n">
-        <v>164.6862220448316</v>
+        <v>164.6862372269023</v>
       </c>
       <c r="F384" t="n">
         <v>1517366</v>
@@ -8112,16 +8112,16 @@
         <v>43780</v>
       </c>
       <c r="B385" t="n">
-        <v>170.8385772705078</v>
+        <v>170.8385620117188</v>
       </c>
       <c r="C385" t="n">
-        <v>170.8385772705078</v>
+        <v>170.8385620117188</v>
       </c>
       <c r="D385" t="n">
-        <v>164.9834589510719</v>
+        <v>164.9834442152444</v>
       </c>
       <c r="E385" t="n">
-        <v>165.9642704075064</v>
+        <v>165.9642555840758</v>
       </c>
       <c r="F385" t="n">
         <v>906700</v>
@@ -8132,16 +8132,16 @@
         <v>43781</v>
       </c>
       <c r="B386" t="n">
-        <v>167.9259033203125</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C386" t="n">
-        <v>171.6410781725318</v>
+        <v>171.641046979786</v>
       </c>
       <c r="D386" t="n">
-        <v>166.8856513382741</v>
+        <v>166.8856210097434</v>
       </c>
       <c r="E386" t="n">
-        <v>170.8980432020879</v>
+        <v>170.8980121443757</v>
       </c>
       <c r="F386" t="n">
         <v>771166</v>
@@ -8172,16 +8172,16 @@
         <v>43783</v>
       </c>
       <c r="B388" t="n">
-        <v>161.5060577392578</v>
+        <v>161.5060882568359</v>
       </c>
       <c r="C388" t="n">
-        <v>167.4800566687947</v>
+        <v>167.4800883151972</v>
       </c>
       <c r="D388" t="n">
-        <v>160.9710641866256</v>
+        <v>160.9710946031133</v>
       </c>
       <c r="E388" t="n">
-        <v>165.1023361004741</v>
+        <v>165.1023672975915</v>
       </c>
       <c r="F388" t="n">
         <v>1805133</v>
@@ -8252,16 +8252,16 @@
         <v>43791</v>
       </c>
       <c r="B392" t="n">
-        <v>169.9766235351562</v>
+        <v>169.9766693115234</v>
       </c>
       <c r="C392" t="n">
-        <v>169.9766235351562</v>
+        <v>169.9766693115234</v>
       </c>
       <c r="D392" t="n">
-        <v>164.2404018496487</v>
+        <v>164.2404460811953</v>
       </c>
       <c r="E392" t="n">
-        <v>165.1023173322536</v>
+        <v>165.1023617959225</v>
       </c>
       <c r="F392" t="n">
         <v>1134300</v>
@@ -8272,16 +8272,16 @@
         <v>43794</v>
       </c>
       <c r="B393" t="n">
-        <v>171.7599334716797</v>
+        <v>171.7599639892578</v>
       </c>
       <c r="C393" t="n">
-        <v>172.2652068516232</v>
+        <v>172.2652374589762</v>
       </c>
       <c r="D393" t="n">
-        <v>167.9555986149949</v>
+        <v>167.9556284566349</v>
       </c>
       <c r="E393" t="n">
-        <v>169.203891738165</v>
+        <v>169.2039218015965</v>
       </c>
       <c r="F393" t="n">
         <v>1287433</v>
@@ -8292,16 +8292,16 @@
         <v>43795</v>
       </c>
       <c r="B394" t="n">
-        <v>169.4119720458984</v>
+        <v>169.4119415283203</v>
       </c>
       <c r="C394" t="n">
-        <v>172.5029926633038</v>
+        <v>172.5029615889146</v>
       </c>
       <c r="D394" t="n">
-        <v>167.4800841600201</v>
+        <v>167.4800539904489</v>
       </c>
       <c r="E394" t="n">
-        <v>170.9574823546011</v>
+        <v>170.9574515586174</v>
       </c>
       <c r="F394" t="n">
         <v>9961800</v>
@@ -8332,16 +8332,16 @@
         <v>43797</v>
       </c>
       <c r="B396" t="n">
-        <v>163.6162719726562</v>
+        <v>163.6162872314453</v>
       </c>
       <c r="C396" t="n">
-        <v>168.490578895245</v>
+        <v>168.49059460861</v>
       </c>
       <c r="D396" t="n">
-        <v>163.2893348165146</v>
+        <v>163.2893500448137</v>
       </c>
       <c r="E396" t="n">
-        <v>166.4695307047406</v>
+        <v>166.4695462296235</v>
       </c>
       <c r="F396" t="n">
         <v>574533</v>
@@ -8352,16 +8352,16 @@
         <v>43798</v>
       </c>
       <c r="B397" t="n">
-        <v>165.5481872558594</v>
+        <v>165.5481719970703</v>
       </c>
       <c r="C397" t="n">
-        <v>166.0831657500806</v>
+        <v>166.0831504419819</v>
       </c>
       <c r="D397" t="n">
-        <v>161.08997770804</v>
+        <v>161.0899628601699</v>
       </c>
       <c r="E397" t="n">
-        <v>163.6460045457557</v>
+        <v>163.6459894622932</v>
       </c>
       <c r="F397" t="n">
         <v>703133</v>
@@ -8372,16 +8372,16 @@
         <v>43801</v>
       </c>
       <c r="B398" t="n">
-        <v>167.1828765869141</v>
+        <v>167.182861328125</v>
       </c>
       <c r="C398" t="n">
-        <v>167.301757350575</v>
+        <v>167.3017420809357</v>
       </c>
       <c r="D398" t="n">
-        <v>162.9624431890042</v>
+        <v>162.9624283154143</v>
       </c>
       <c r="E398" t="n">
-        <v>165.6373661909777</v>
+        <v>165.6373510732474</v>
       </c>
       <c r="F398" t="n">
         <v>805633</v>
@@ -8392,16 +8392,16 @@
         <v>43802</v>
       </c>
       <c r="B399" t="n">
-        <v>169.8280487060547</v>
+        <v>169.8280639648438</v>
       </c>
       <c r="C399" t="n">
-        <v>170.4522028366473</v>
+        <v>170.4522181515157</v>
       </c>
       <c r="D399" t="n">
-        <v>165.845377555229</v>
+        <v>165.8453924561812</v>
       </c>
       <c r="E399" t="n">
-        <v>167.3314473007672</v>
+        <v>167.3314623352405</v>
       </c>
       <c r="F399" t="n">
         <v>915133</v>
@@ -8412,16 +8412,16 @@
         <v>43803</v>
       </c>
       <c r="B400" t="n">
-        <v>172.4435577392578</v>
+        <v>172.4435424804688</v>
       </c>
       <c r="C400" t="n">
-        <v>173.7215863852452</v>
+        <v>173.7215710133688</v>
       </c>
       <c r="D400" t="n">
-        <v>170.8980473816703</v>
+        <v>170.8980322596368</v>
       </c>
       <c r="E400" t="n">
-        <v>170.8980473816703</v>
+        <v>170.8980322596368</v>
       </c>
       <c r="F400" t="n">
         <v>662400</v>
@@ -8432,16 +8432,16 @@
         <v>43804</v>
       </c>
       <c r="B401" t="n">
-        <v>172.3543853759766</v>
+        <v>172.3543701171875</v>
       </c>
       <c r="C401" t="n">
-        <v>174.7618113181715</v>
+        <v>174.7617958462494</v>
       </c>
       <c r="D401" t="n">
-        <v>169.1147488144879</v>
+        <v>169.1147338425086</v>
       </c>
       <c r="E401" t="n">
-        <v>172.7110427507926</v>
+        <v>172.7110274604281</v>
       </c>
       <c r="F401" t="n">
         <v>632400</v>
@@ -8452,16 +8452,16 @@
         <v>43805</v>
       </c>
       <c r="B402" t="n">
-        <v>171.7302398681641</v>
+        <v>171.730224609375</v>
       </c>
       <c r="C402" t="n">
-        <v>173.4243662634142</v>
+        <v>173.4243508540965</v>
       </c>
       <c r="D402" t="n">
-        <v>167.9556246122654</v>
+        <v>167.9556096888631</v>
       </c>
       <c r="E402" t="n">
-        <v>173.4243662634142</v>
+        <v>173.4243508540965</v>
       </c>
       <c r="F402" t="n">
         <v>837700</v>
@@ -8492,16 +8492,16 @@
         <v>43809</v>
       </c>
       <c r="B404" t="n">
-        <v>162.3382720947266</v>
+        <v>162.3382568359375</v>
       </c>
       <c r="C404" t="n">
-        <v>167.2720197966458</v>
+        <v>167.2720040741151</v>
       </c>
       <c r="D404" t="n">
-        <v>162.3382720947266</v>
+        <v>162.3382568359375</v>
       </c>
       <c r="E404" t="n">
-        <v>166.5884252423812</v>
+        <v>166.5884095841042</v>
       </c>
       <c r="F404" t="n">
         <v>1232166</v>
@@ -8512,16 +8512,16 @@
         <v>43810</v>
       </c>
       <c r="B405" t="n">
-        <v>167.0936889648438</v>
+        <v>167.0936737060547</v>
       </c>
       <c r="C405" t="n">
-        <v>167.0936889648438</v>
+        <v>167.0936737060547</v>
       </c>
       <c r="D405" t="n">
-        <v>161.981605315769</v>
+        <v>161.9815905238091</v>
       </c>
       <c r="E405" t="n">
-        <v>162.7840805747468</v>
+        <v>162.7840657095058</v>
       </c>
       <c r="F405" t="n">
         <v>789933</v>
@@ -8532,16 +8532,16 @@
         <v>43811</v>
       </c>
       <c r="B406" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0063781738281</v>
       </c>
       <c r="C406" t="n">
-        <v>170.214434741823</v>
+        <v>170.2144194643613</v>
       </c>
       <c r="D406" t="n">
-        <v>167.1234143540938</v>
+        <v>167.1233993540642</v>
       </c>
       <c r="E406" t="n">
-        <v>169.085022283454</v>
+        <v>169.0850071073618</v>
       </c>
       <c r="F406" t="n">
         <v>578333</v>
@@ -8572,16 +8572,16 @@
         <v>43815</v>
       </c>
       <c r="B408" t="n">
-        <v>171.9085845947266</v>
+        <v>171.9085693359375</v>
       </c>
       <c r="C408" t="n">
-        <v>175.8318009921903</v>
+        <v>175.8317853851723</v>
       </c>
       <c r="D408" t="n">
-        <v>167.0342767304645</v>
+        <v>167.0342619043242</v>
       </c>
       <c r="E408" t="n">
-        <v>167.1828776860177</v>
+        <v>167.1828628466874</v>
       </c>
       <c r="F408" t="n">
         <v>666133</v>
@@ -8592,16 +8592,16 @@
         <v>43816</v>
       </c>
       <c r="B409" t="n">
-        <v>173.1568603515625</v>
+        <v>173.1568450927734</v>
       </c>
       <c r="C409" t="n">
-        <v>175.2373642201033</v>
+        <v>175.2373487779778</v>
       </c>
       <c r="D409" t="n">
-        <v>171.4032936690544</v>
+        <v>171.4032785647917</v>
       </c>
       <c r="E409" t="n">
-        <v>173.4243571614228</v>
+        <v>173.4243418790616</v>
       </c>
       <c r="F409" t="n">
         <v>614666</v>
@@ -8632,16 +8632,16 @@
         <v>43818</v>
       </c>
       <c r="B411" t="n">
-        <v>184.7481689453125</v>
+        <v>184.7481842041016</v>
       </c>
       <c r="C411" t="n">
-        <v>185.7587005088636</v>
+        <v>185.7587158511149</v>
       </c>
       <c r="D411" t="n">
-        <v>178.9227863769701</v>
+        <v>178.922801154627</v>
       </c>
       <c r="E411" t="n">
-        <v>181.3004916966509</v>
+        <v>181.3005066706881</v>
       </c>
       <c r="F411" t="n">
         <v>904966</v>
@@ -8652,16 +8652,16 @@
         <v>43819</v>
       </c>
       <c r="B412" t="n">
-        <v>190.0683135986328</v>
+        <v>190.0683441162109</v>
       </c>
       <c r="C412" t="n">
-        <v>190.0683135986328</v>
+        <v>190.0683441162109</v>
       </c>
       <c r="D412" t="n">
-        <v>182.9351672106071</v>
+        <v>182.9351965828794</v>
       </c>
       <c r="E412" t="n">
-        <v>185.8478661328706</v>
+        <v>185.847895972809</v>
       </c>
       <c r="F412" t="n">
         <v>984100</v>
@@ -8672,16 +8672,16 @@
         <v>43822</v>
       </c>
       <c r="B413" t="n">
-        <v>187.8392333984375</v>
+        <v>187.8392486572266</v>
       </c>
       <c r="C413" t="n">
-        <v>190.4547157062448</v>
+        <v>190.454731177498</v>
       </c>
       <c r="D413" t="n">
-        <v>186.1748273205142</v>
+        <v>186.1748424440982</v>
       </c>
       <c r="E413" t="n">
-        <v>190.2169390902317</v>
+        <v>190.2169545421696</v>
       </c>
       <c r="F413" t="n">
         <v>629966</v>
@@ -8732,16 +8732,16 @@
         <v>43829</v>
       </c>
       <c r="B416" t="n">
-        <v>189.9197235107422</v>
+        <v>189.9196929931641</v>
       </c>
       <c r="C416" t="n">
-        <v>193.3376811370011</v>
+        <v>193.3376500702026</v>
       </c>
       <c r="D416" t="n">
-        <v>188.0472761073423</v>
+        <v>188.0472458906416</v>
       </c>
       <c r="E416" t="n">
-        <v>190.6627584345848</v>
+        <v>190.6627277976108</v>
       </c>
       <c r="F416" t="n">
         <v>1069533</v>
@@ -8752,16 +8752,16 @@
         <v>43832</v>
       </c>
       <c r="B417" t="n">
-        <v>197.4689483642578</v>
+        <v>197.4689331054688</v>
       </c>
       <c r="C417" t="n">
-        <v>199.3711310228619</v>
+        <v>199.3711156170877</v>
       </c>
       <c r="D417" t="n">
-        <v>191.4652287544725</v>
+        <v>191.4652139596019</v>
       </c>
       <c r="E417" t="n">
-        <v>193.7835091455575</v>
+        <v>193.7834941715491</v>
       </c>
       <c r="F417" t="n">
         <v>866733</v>
@@ -8772,16 +8772,16 @@
         <v>43833</v>
       </c>
       <c r="B418" t="n">
-        <v>205.8206634521484</v>
+        <v>205.8206787109375</v>
       </c>
       <c r="C418" t="n">
-        <v>205.8206634521484</v>
+        <v>205.8206787109375</v>
       </c>
       <c r="D418" t="n">
-        <v>194.3779231826556</v>
+        <v>194.3779375931219</v>
       </c>
       <c r="E418" t="n">
-        <v>195.4181750466247</v>
+        <v>195.4181895342114</v>
       </c>
       <c r="F418" t="n">
         <v>3123966</v>
@@ -8792,16 +8792,16 @@
         <v>43836</v>
       </c>
       <c r="B419" t="n">
-        <v>199.4744720458984</v>
+        <v>199.4744567871094</v>
       </c>
       <c r="C419" t="n">
-        <v>205.1941645753199</v>
+        <v>205.1941488790033</v>
       </c>
       <c r="D419" t="n">
-        <v>196.346503119601</v>
+        <v>196.3464881000858</v>
       </c>
       <c r="E419" t="n">
-        <v>203.4663336878787</v>
+        <v>203.4663181237324</v>
       </c>
       <c r="F419" t="n">
         <v>735666</v>
@@ -8812,16 +8812,16 @@
         <v>43837</v>
       </c>
       <c r="B420" t="n">
-        <v>193.9930572509766</v>
+        <v>193.9930877685547</v>
       </c>
       <c r="C420" t="n">
-        <v>200.1894011243377</v>
+        <v>200.1894326166796</v>
       </c>
       <c r="D420" t="n">
-        <v>193.9334794981979</v>
+        <v>193.9335100064037</v>
       </c>
       <c r="E420" t="n">
-        <v>198.401992780866</v>
+        <v>198.4020239920258</v>
       </c>
       <c r="F420" t="n">
         <v>612400</v>
@@ -8832,16 +8832,16 @@
         <v>43838</v>
       </c>
       <c r="B421" t="n">
-        <v>190.0011749267578</v>
+        <v>190.0012054443359</v>
       </c>
       <c r="C421" t="n">
-        <v>196.0187701928976</v>
+        <v>196.0188016770089</v>
       </c>
       <c r="D421" t="n">
-        <v>188.0052445138568</v>
+        <v>188.0052747108529</v>
       </c>
       <c r="E421" t="n">
-        <v>193.9036842783375</v>
+        <v>193.9037154227282</v>
       </c>
       <c r="F421" t="n">
         <v>832966</v>
@@ -8852,16 +8852,16 @@
         <v>43839</v>
       </c>
       <c r="B422" t="n">
-        <v>188.8691864013672</v>
+        <v>188.8691711425781</v>
       </c>
       <c r="C422" t="n">
-        <v>191.5205028574819</v>
+        <v>191.5204873844923</v>
       </c>
       <c r="D422" t="n">
-        <v>187.2009484680017</v>
+        <v>187.20093334399</v>
       </c>
       <c r="E422" t="n">
-        <v>190.001209328158</v>
+        <v>190.0011939779125</v>
       </c>
       <c r="F422" t="n">
         <v>950500</v>
@@ -8892,16 +8892,16 @@
         <v>43843</v>
       </c>
       <c r="B424" t="n">
-        <v>185.8603973388672</v>
+        <v>185.8603668212891</v>
       </c>
       <c r="C424" t="n">
-        <v>186.6945163464585</v>
+        <v>186.6944856919212</v>
       </c>
       <c r="D424" t="n">
-        <v>183.6559291387862</v>
+        <v>183.6558989831735</v>
       </c>
       <c r="E424" t="n">
-        <v>184.6985854742881</v>
+        <v>184.6985551474751</v>
       </c>
       <c r="F424" t="n">
         <v>736233</v>
@@ -8932,16 +8932,16 @@
         <v>43845</v>
       </c>
       <c r="B426" t="n">
-        <v>181.7493591308594</v>
+        <v>181.7493438720703</v>
       </c>
       <c r="C426" t="n">
-        <v>188.0350706741274</v>
+        <v>188.0350548876207</v>
       </c>
       <c r="D426" t="n">
-        <v>179.3363688316654</v>
+        <v>179.3363537754593</v>
       </c>
       <c r="E426" t="n">
-        <v>187.677588946244</v>
+        <v>187.6775731897497</v>
       </c>
       <c r="F426" t="n">
         <v>1526633</v>
@@ -8952,16 +8952,16 @@
         <v>43846</v>
       </c>
       <c r="B427" t="n">
-        <v>187.8562927246094</v>
+        <v>187.8562774658203</v>
       </c>
       <c r="C427" t="n">
-        <v>187.9158856299163</v>
+        <v>187.9158703662868</v>
       </c>
       <c r="D427" t="n">
-        <v>181.4812155388111</v>
+        <v>181.4812007978432</v>
       </c>
       <c r="E427" t="n">
-        <v>181.7195417039707</v>
+        <v>181.7195269436446</v>
       </c>
       <c r="F427" t="n">
         <v>911900</v>
@@ -8972,16 +8972,16 @@
         <v>43847</v>
       </c>
       <c r="B428" t="n">
-        <v>187.6775817871094</v>
+        <v>187.6775665283203</v>
       </c>
       <c r="C428" t="n">
-        <v>191.5800766116156</v>
+        <v>191.5800610355412</v>
       </c>
       <c r="D428" t="n">
-        <v>185.3539582205168</v>
+        <v>185.3539431506457</v>
       </c>
       <c r="E428" t="n">
-        <v>189.1968752846526</v>
+        <v>189.1968599023401</v>
       </c>
       <c r="F428" t="n">
         <v>852600</v>
@@ -8992,16 +8992,16 @@
         <v>43850</v>
       </c>
       <c r="B429" t="n">
-        <v>188.1244354248047</v>
+        <v>188.1244201660156</v>
       </c>
       <c r="C429" t="n">
-        <v>189.4947845599039</v>
+        <v>189.4947691899657</v>
       </c>
       <c r="D429" t="n">
-        <v>185.9497561980689</v>
+        <v>185.9497411156683</v>
       </c>
       <c r="E429" t="n">
-        <v>189.4649956788822</v>
+        <v>189.4649803113602</v>
       </c>
       <c r="F429" t="n">
         <v>883800</v>
@@ -9012,16 +9012,16 @@
         <v>43851</v>
       </c>
       <c r="B430" t="n">
-        <v>190.0607757568359</v>
+        <v>190.0607604980469</v>
       </c>
       <c r="C430" t="n">
-        <v>192.682303175826</v>
+        <v>192.6822877065709</v>
       </c>
       <c r="D430" t="n">
-        <v>187.6775745221264</v>
+        <v>187.6775594546697</v>
       </c>
       <c r="E430" t="n">
-        <v>188.1542117386635</v>
+        <v>188.1541966329406</v>
       </c>
       <c r="F430" t="n">
         <v>1218200</v>
@@ -9032,16 +9032,16 @@
         <v>43852</v>
       </c>
       <c r="B431" t="n">
-        <v>190.5672302246094</v>
+        <v>190.5671997070312</v>
       </c>
       <c r="C431" t="n">
-        <v>193.2781244687579</v>
+        <v>193.2780935170552</v>
       </c>
       <c r="D431" t="n">
-        <v>189.4947850489844</v>
+        <v>189.4947547031485</v>
       </c>
       <c r="E431" t="n">
-        <v>191.4013491994205</v>
+        <v>191.4013185482659</v>
       </c>
       <c r="F431" t="n">
         <v>460300</v>
@@ -9052,16 +9052,16 @@
         <v>43853</v>
       </c>
       <c r="B432" t="n">
-        <v>191.5502777099609</v>
+        <v>191.5502624511719</v>
       </c>
       <c r="C432" t="n">
-        <v>191.5502777099609</v>
+        <v>191.5502624511719</v>
       </c>
       <c r="D432" t="n">
-        <v>186.515760245738</v>
+        <v>186.5157453879958</v>
       </c>
       <c r="E432" t="n">
-        <v>189.8224621415167</v>
+        <v>189.8224470203644</v>
       </c>
       <c r="F432" t="n">
         <v>1068366</v>
@@ -9092,16 +9092,16 @@
         <v>43857</v>
       </c>
       <c r="B434" t="n">
-        <v>182.4047241210938</v>
+        <v>182.4047088623047</v>
       </c>
       <c r="C434" t="n">
-        <v>189.7628800128631</v>
+        <v>189.7628641385387</v>
       </c>
       <c r="D434" t="n">
-        <v>180.5279490507258</v>
+        <v>180.5279339489355</v>
       </c>
       <c r="E434" t="n">
-        <v>189.7628800128631</v>
+        <v>189.7628641385387</v>
       </c>
       <c r="F434" t="n">
         <v>939566</v>
@@ -9172,16 +9172,16 @@
         <v>43861</v>
       </c>
       <c r="B438" t="n">
-        <v>178.9490661621094</v>
+        <v>178.9490509033203</v>
       </c>
       <c r="C438" t="n">
-        <v>179.8725668518933</v>
+        <v>179.8725515143583</v>
       </c>
       <c r="D438" t="n">
-        <v>175.3742643730724</v>
+        <v>175.3742494191027</v>
       </c>
       <c r="E438" t="n">
-        <v>177.3701949931508</v>
+        <v>177.3701798689903</v>
       </c>
       <c r="F438" t="n">
         <v>886766</v>
@@ -9192,16 +9192,16 @@
         <v>43864</v>
       </c>
       <c r="B439" t="n">
-        <v>184.1027679443359</v>
+        <v>184.1027526855469</v>
       </c>
       <c r="C439" t="n">
-        <v>186.1582916261031</v>
+        <v>186.1582761969483</v>
       </c>
       <c r="D439" t="n">
-        <v>178.7405572865494</v>
+        <v>178.7405424721906</v>
       </c>
       <c r="E439" t="n">
-        <v>179.0384612457652</v>
+        <v>179.0384464067156</v>
       </c>
       <c r="F439" t="n">
         <v>700100</v>
@@ -9212,16 +9212,16 @@
         <v>43865</v>
       </c>
       <c r="B440" t="n">
-        <v>182.76220703125</v>
+        <v>182.7622222900391</v>
       </c>
       <c r="C440" t="n">
-        <v>186.5753349533802</v>
+        <v>186.5753505305267</v>
       </c>
       <c r="D440" t="n">
-        <v>182.5238808541081</v>
+        <v>182.5238960929993</v>
       </c>
       <c r="E440" t="n">
-        <v>186.3667976543781</v>
+        <v>186.3668132141139</v>
       </c>
       <c r="F440" t="n">
         <v>732700</v>
@@ -9272,16 +9272,16 @@
         <v>43868</v>
       </c>
       <c r="B443" t="n">
-        <v>171.6802978515625</v>
+        <v>171.6802673339844</v>
       </c>
       <c r="C443" t="n">
-        <v>180.8556515493858</v>
+        <v>180.8556194008135</v>
       </c>
       <c r="D443" t="n">
-        <v>171.4419716632469</v>
+        <v>171.4419411880332</v>
       </c>
       <c r="E443" t="n">
-        <v>172.9612651277013</v>
+        <v>172.9612343824207</v>
       </c>
       <c r="F443" t="n">
         <v>1239533</v>
@@ -9292,16 +9292,16 @@
         <v>43871</v>
       </c>
       <c r="B444" t="n">
-        <v>166.1095581054688</v>
+        <v>166.1095428466797</v>
       </c>
       <c r="C444" t="n">
-        <v>172.7527512987726</v>
+        <v>172.7527354297412</v>
       </c>
       <c r="D444" t="n">
-        <v>164.0838384392179</v>
+        <v>164.083823366511</v>
       </c>
       <c r="E444" t="n">
-        <v>171.6505172467174</v>
+        <v>171.6505014789369</v>
       </c>
       <c r="F444" t="n">
         <v>872966</v>
@@ -9312,16 +9312,16 @@
         <v>43872</v>
       </c>
       <c r="B445" t="n">
-        <v>172.8123168945312</v>
+        <v>172.8123016357422</v>
       </c>
       <c r="C445" t="n">
-        <v>174.4209769618915</v>
+        <v>174.4209615610627</v>
       </c>
       <c r="D445" t="n">
-        <v>167.3905136588736</v>
+        <v>167.3904988788129</v>
       </c>
       <c r="E445" t="n">
-        <v>168.6119183008553</v>
+        <v>168.6119034129483</v>
       </c>
       <c r="F445" t="n">
         <v>924566</v>
@@ -9332,16 +9332,16 @@
         <v>43873</v>
       </c>
       <c r="B446" t="n">
-        <v>174.9572143554688</v>
+        <v>174.9571990966797</v>
       </c>
       <c r="C446" t="n">
-        <v>176.3275482967427</v>
+        <v>176.3275329184407</v>
       </c>
       <c r="D446" t="n">
-        <v>171.4121861017706</v>
+        <v>171.412171152159</v>
       </c>
       <c r="E446" t="n">
-        <v>173.4974986218312</v>
+        <v>173.4974834903504</v>
       </c>
       <c r="F446" t="n">
         <v>872333</v>
@@ -9372,16 +9372,16 @@
         <v>43875</v>
       </c>
       <c r="B448" t="n">
-        <v>174.2422485351562</v>
+        <v>174.2422180175781</v>
       </c>
       <c r="C448" t="n">
-        <v>175.9998681978045</v>
+        <v>175.9998373723889</v>
       </c>
       <c r="D448" t="n">
-        <v>172.9910549794976</v>
+        <v>172.9910246810592</v>
       </c>
       <c r="E448" t="n">
-        <v>175.7913308878533</v>
+        <v>175.7913000989619</v>
       </c>
       <c r="F448" t="n">
         <v>468100</v>
@@ -9392,16 +9392,16 @@
         <v>43878</v>
       </c>
       <c r="B449" t="n">
-        <v>178.3532867431641</v>
+        <v>178.3532562255859</v>
       </c>
       <c r="C449" t="n">
-        <v>178.3532867431641</v>
+        <v>178.3532562255859</v>
       </c>
       <c r="D449" t="n">
-        <v>173.4677133273196</v>
+        <v>173.4676836456995</v>
       </c>
       <c r="E449" t="n">
-        <v>173.9741394517339</v>
+        <v>173.9741096834605</v>
       </c>
       <c r="F449" t="n">
         <v>278100</v>
@@ -9432,16 +9432,16 @@
         <v>43880</v>
       </c>
       <c r="B451" t="n">
-        <v>177.3702087402344</v>
+        <v>177.3701934814453</v>
       </c>
       <c r="C451" t="n">
-        <v>178.3234983824099</v>
+        <v>178.3234830416113</v>
       </c>
       <c r="D451" t="n">
-        <v>173.1995987537694</v>
+        <v>173.1995838537692</v>
       </c>
       <c r="E451" t="n">
-        <v>174.9870073628329</v>
+        <v>174.9869923090657</v>
       </c>
       <c r="F451" t="n">
         <v>740433</v>
@@ -9452,16 +9452,16 @@
         <v>43881</v>
       </c>
       <c r="B452" t="n">
-        <v>172.1569366455078</v>
+        <v>172.1569519042969</v>
       </c>
       <c r="C452" t="n">
-        <v>177.0722987901394</v>
+        <v>177.0723144845919</v>
       </c>
       <c r="D452" t="n">
-        <v>171.3228177068359</v>
+        <v>171.3228328916945</v>
       </c>
       <c r="E452" t="n">
-        <v>175.7019648628997</v>
+        <v>175.7019804358953</v>
       </c>
       <c r="F452" t="n">
         <v>757533</v>
@@ -9472,16 +9472,16 @@
         <v>43882</v>
       </c>
       <c r="B453" t="n">
-        <v>166.8245239257812</v>
+        <v>166.8245086669922</v>
       </c>
       <c r="C453" t="n">
-        <v>171.2334601967152</v>
+        <v>171.2334445346579</v>
       </c>
       <c r="D453" t="n">
-        <v>165.5435414176457</v>
+        <v>165.543526276023</v>
       </c>
       <c r="E453" t="n">
-        <v>169.8333221629949</v>
+        <v>169.8333066290028</v>
       </c>
       <c r="F453" t="n">
         <v>990066</v>
@@ -9492,16 +9492,16 @@
         <v>43887</v>
       </c>
       <c r="B454" t="n">
-        <v>156.4575500488281</v>
+        <v>156.4575653076172</v>
       </c>
       <c r="C454" t="n">
-        <v>160.5685818573121</v>
+        <v>160.5685975170366</v>
       </c>
       <c r="D454" t="n">
-        <v>154.1637155461845</v>
+        <v>154.1637305812634</v>
       </c>
       <c r="E454" t="n">
-        <v>159.5259256782859</v>
+        <v>159.5259412363235</v>
       </c>
       <c r="F454" t="n">
         <v>1832133</v>
@@ -9512,16 +9512,16 @@
         <v>43888</v>
       </c>
       <c r="B455" t="n">
-        <v>158.6322326660156</v>
+        <v>158.6322174072266</v>
       </c>
       <c r="C455" t="n">
-        <v>163.4582279560204</v>
+        <v>163.4582122330202</v>
       </c>
       <c r="D455" t="n">
-        <v>151.1549211271597</v>
+        <v>151.1549065876111</v>
       </c>
       <c r="E455" t="n">
-        <v>152.4954661148132</v>
+        <v>152.495451446318</v>
       </c>
       <c r="F455" t="n">
         <v>1732266</v>
@@ -9612,16 +9612,16 @@
         <v>43895</v>
       </c>
       <c r="B460" t="n">
-        <v>152.8231506347656</v>
+        <v>152.8231658935547</v>
       </c>
       <c r="C460" t="n">
-        <v>161.7601773421092</v>
+        <v>161.7601934932251</v>
       </c>
       <c r="D460" t="n">
-        <v>151.6911278579163</v>
+        <v>151.6911430036774</v>
       </c>
       <c r="E460" t="n">
-        <v>156.3979673785122</v>
+        <v>156.3979829942326</v>
       </c>
       <c r="F460" t="n">
         <v>1000500</v>
@@ -9652,16 +9652,16 @@
         <v>43899</v>
       </c>
       <c r="B462" t="n">
-        <v>134.4129180908203</v>
+        <v>134.4129028320312</v>
       </c>
       <c r="C462" t="n">
-        <v>142.4562351788772</v>
+        <v>142.4562190069967</v>
       </c>
       <c r="D462" t="n">
-        <v>134.4129180908203</v>
+        <v>134.4129028320312</v>
       </c>
       <c r="E462" t="n">
-        <v>137.8089873260479</v>
+        <v>137.8089716817311</v>
       </c>
       <c r="F462" t="n">
         <v>2156300</v>
@@ -9672,16 +9672,16 @@
         <v>43900</v>
       </c>
       <c r="B463" t="n">
-        <v>145.6437530517578</v>
+        <v>145.6437377929688</v>
       </c>
       <c r="C463" t="n">
-        <v>147.3715837841424</v>
+        <v>147.3715683443321</v>
       </c>
       <c r="D463" t="n">
-        <v>136.9152630573862</v>
+        <v>136.9152487130627</v>
       </c>
       <c r="E463" t="n">
-        <v>142.456206648502</v>
+        <v>142.4561917236655</v>
       </c>
       <c r="F463" t="n">
         <v>1718533</v>
@@ -9692,16 +9692,16 @@
         <v>43901</v>
       </c>
       <c r="B464" t="n">
-        <v>134.0256195068359</v>
+        <v>134.0256042480469</v>
       </c>
       <c r="C464" t="n">
-        <v>144.2436139679902</v>
+        <v>144.2435975458846</v>
       </c>
       <c r="D464" t="n">
-        <v>122.020208994126</v>
+        <v>122.0201951021505</v>
       </c>
       <c r="E464" t="n">
-        <v>142.0391460401569</v>
+        <v>142.0391298690295</v>
       </c>
       <c r="F464" t="n">
         <v>1332366</v>
@@ -9712,16 +9712,16 @@
         <v>43902</v>
       </c>
       <c r="B465" t="n">
-        <v>116.0622024536133</v>
+        <v>116.0621795654297</v>
       </c>
       <c r="C465" t="n">
-        <v>124.8204897078642</v>
+        <v>124.8204650924923</v>
       </c>
       <c r="D465" t="n">
-        <v>107.3635005385155</v>
+        <v>107.3634793657697</v>
       </c>
       <c r="E465" t="n">
-        <v>111.206417781332</v>
+        <v>111.2063958507392</v>
       </c>
       <c r="F465" t="n">
         <v>1010966</v>
@@ -9732,16 +9732,16 @@
         <v>43903</v>
       </c>
       <c r="B466" t="n">
-        <v>129.9145812988281</v>
+        <v>129.9145965576172</v>
       </c>
       <c r="C466" t="n">
-        <v>137.0344108256576</v>
+        <v>137.0344269206882</v>
       </c>
       <c r="D466" t="n">
-        <v>118.7135013544465</v>
+        <v>118.713515297641</v>
       </c>
       <c r="E466" t="n">
-        <v>136.9450441942133</v>
+        <v>136.9450602787476</v>
       </c>
       <c r="F466" t="n">
         <v>2459466</v>
@@ -9752,16 +9752,16 @@
         <v>43906</v>
       </c>
       <c r="B467" t="n">
-        <v>110.2233428955078</v>
+        <v>110.2233352661133</v>
       </c>
       <c r="C467" t="n">
-        <v>120.6796642120818</v>
+        <v>120.6796558589259</v>
       </c>
       <c r="D467" t="n">
-        <v>106.3208404521129</v>
+        <v>106.3208330928401</v>
       </c>
       <c r="E467" t="n">
-        <v>109.746698079271</v>
+        <v>109.7466904828687</v>
       </c>
       <c r="F467" t="n">
         <v>2066566</v>
@@ -9792,16 +9792,16 @@
         <v>43908</v>
       </c>
       <c r="B469" t="n">
-        <v>94.49414825439453</v>
+        <v>94.49417114257812</v>
       </c>
       <c r="C469" t="n">
-        <v>104.8611005411026</v>
+        <v>104.8611259403486</v>
       </c>
       <c r="D469" t="n">
-        <v>85.43796701636045</v>
+        <v>85.43798771097393</v>
       </c>
       <c r="E469" t="n">
-        <v>103.6695001390488</v>
+        <v>103.6695252496678</v>
       </c>
       <c r="F469" t="n">
         <v>1809666</v>
@@ -9812,16 +9812,16 @@
         <v>43909</v>
       </c>
       <c r="B470" t="n">
-        <v>107.5422134399414</v>
+        <v>107.5422210693359</v>
       </c>
       <c r="C470" t="n">
-        <v>109.0615142961074</v>
+        <v>109.0615220332861</v>
       </c>
       <c r="D470" t="n">
-        <v>84.36552854657734</v>
+        <v>84.36553453174244</v>
       </c>
       <c r="E470" t="n">
-        <v>90.85976865815006</v>
+        <v>90.85977510403768</v>
       </c>
       <c r="F470" t="n">
         <v>2314466</v>
@@ -9832,16 +9832,16 @@
         <v>43910</v>
       </c>
       <c r="B471" t="n">
-        <v>116.1813507080078</v>
+        <v>116.1813659667969</v>
       </c>
       <c r="C471" t="n">
-        <v>120.9477605504217</v>
+        <v>120.9477764352117</v>
       </c>
       <c r="D471" t="n">
-        <v>108.1976056989515</v>
+        <v>108.1976199091878</v>
       </c>
       <c r="E471" t="n">
-        <v>113.947093963623</v>
+        <v>113.9471089289739</v>
       </c>
       <c r="F471" t="n">
         <v>2114800</v>
@@ -9852,16 +9852,16 @@
         <v>43913</v>
       </c>
       <c r="B472" t="n">
-        <v>113.7981414794922</v>
+        <v>113.7981567382812</v>
       </c>
       <c r="C472" t="n">
-        <v>119.6072074731813</v>
+        <v>119.6072235108875</v>
       </c>
       <c r="D472" t="n">
-        <v>108.4657126798635</v>
+        <v>108.4657272236461</v>
       </c>
       <c r="E472" t="n">
-        <v>118.9518294373453</v>
+        <v>118.951845387174</v>
       </c>
       <c r="F472" t="n">
         <v>1372400</v>
@@ -9872,16 +9872,16 @@
         <v>43914</v>
       </c>
       <c r="B473" t="n">
-        <v>126.012092590332</v>
+        <v>126.0120849609375</v>
       </c>
       <c r="C473" t="n">
-        <v>131.076406792097</v>
+        <v>131.0763988560838</v>
       </c>
       <c r="D473" t="n">
-        <v>118.8624658560648</v>
+        <v>118.862458659544</v>
       </c>
       <c r="E473" t="n">
-        <v>120.3519704787023</v>
+        <v>120.3519631919995</v>
       </c>
       <c r="F473" t="n">
         <v>1251533</v>
@@ -9912,16 +9912,16 @@
         <v>43916</v>
       </c>
       <c r="B475" t="n">
-        <v>150.1122436523438</v>
+        <v>150.1122589111328</v>
       </c>
       <c r="C475" t="n">
-        <v>158.9301140813228</v>
+        <v>158.9301302364413</v>
       </c>
       <c r="D475" t="n">
-        <v>132.8935773380452</v>
+        <v>132.8935908465707</v>
       </c>
       <c r="E475" t="n">
-        <v>135.2469893165816</v>
+        <v>135.2470030643295</v>
       </c>
       <c r="F475" t="n">
         <v>1421366</v>
@@ -9932,16 +9932,16 @@
         <v>43917</v>
       </c>
       <c r="B476" t="n">
-        <v>135.544921875</v>
+        <v>135.5449066162109</v>
       </c>
       <c r="C476" t="n">
-        <v>143.9457195368442</v>
+        <v>143.9457033323465</v>
       </c>
       <c r="D476" t="n">
-        <v>133.7277244008504</v>
+        <v>133.72770934663</v>
       </c>
       <c r="E476" t="n">
-        <v>141.3837848967248</v>
+        <v>141.3837689806335</v>
       </c>
       <c r="F476" t="n">
         <v>773066</v>
@@ -9952,16 +9952,16 @@
         <v>43920</v>
       </c>
       <c r="B477" t="n">
-        <v>134.1447906494141</v>
+        <v>134.144775390625</v>
       </c>
       <c r="C477" t="n">
-        <v>138.7324603110987</v>
+        <v>138.7324445304684</v>
       </c>
       <c r="D477" t="n">
-        <v>128.6932131039123</v>
+        <v>128.6931984652328</v>
       </c>
       <c r="E477" t="n">
-        <v>134.6512319485003</v>
+        <v>134.6512166321043</v>
       </c>
       <c r="F477" t="n">
         <v>909700</v>
@@ -9972,16 +9972,16 @@
         <v>43921</v>
       </c>
       <c r="B478" t="n">
-        <v>126.3099822998047</v>
+        <v>126.3099899291992</v>
       </c>
       <c r="C478" t="n">
-        <v>138.5239225909137</v>
+        <v>138.5239309580564</v>
       </c>
       <c r="D478" t="n">
-        <v>125.1183816950188</v>
+        <v>125.1183892524381</v>
       </c>
       <c r="E478" t="n">
-        <v>134.1447755951023</v>
+        <v>134.1447836977352</v>
       </c>
       <c r="F478" t="n">
         <v>993633</v>
@@ -10012,16 +10012,16 @@
         <v>43923</v>
       </c>
       <c r="B480" t="n">
-        <v>121.5733642578125</v>
+        <v>121.573356628418</v>
       </c>
       <c r="C480" t="n">
-        <v>124.3438436888143</v>
+        <v>124.343835885557</v>
       </c>
       <c r="D480" t="n">
-        <v>116.4792537399009</v>
+        <v>116.4792464301897</v>
       </c>
       <c r="E480" t="n">
-        <v>118.415614241661</v>
+        <v>118.4156068104326</v>
       </c>
       <c r="F480" t="n">
         <v>765700</v>
@@ -10052,16 +10052,16 @@
         <v>43927</v>
       </c>
       <c r="B482" t="n">
-        <v>128.0973968505859</v>
+        <v>128.0973815917969</v>
       </c>
       <c r="C482" t="n">
-        <v>135.6342865636811</v>
+        <v>135.6342704071079</v>
       </c>
       <c r="D482" t="n">
-        <v>118.2368759992794</v>
+        <v>118.2368619150623</v>
       </c>
       <c r="E482" t="n">
-        <v>119.1603691633358</v>
+        <v>119.1603549691134</v>
       </c>
       <c r="F482" t="n">
         <v>1479633</v>
@@ -10072,16 +10072,16 @@
         <v>43928</v>
       </c>
       <c r="B483" t="n">
-        <v>143.8861236572266</v>
+        <v>143.8861389160156</v>
       </c>
       <c r="C483" t="n">
-        <v>154.9084626363945</v>
+        <v>154.908479064077</v>
       </c>
       <c r="D483" t="n">
-        <v>138.017487645962</v>
+        <v>138.0175022823959</v>
       </c>
       <c r="E483" t="n">
-        <v>145.1968948448132</v>
+        <v>145.1969102426065</v>
       </c>
       <c r="F483" t="n">
         <v>1844300</v>
@@ -10092,16 +10092,16 @@
         <v>43929</v>
       </c>
       <c r="B484" t="n">
-        <v>148.9206695556641</v>
+        <v>148.920654296875</v>
       </c>
       <c r="C484" t="n">
-        <v>152.5252754984434</v>
+        <v>152.5252598703173</v>
       </c>
       <c r="D484" t="n">
-        <v>142.0987434079801</v>
+        <v>142.0987288481829</v>
       </c>
       <c r="E484" t="n">
-        <v>144.333000284508</v>
+        <v>144.3329854957831</v>
       </c>
       <c r="F484" t="n">
         <v>859700</v>
@@ -10112,16 +10112,16 @@
         <v>43930</v>
       </c>
       <c r="B485" t="n">
-        <v>145.5543823242188</v>
+        <v>145.5543670654297</v>
       </c>
       <c r="C485" t="n">
-        <v>153.0912714973958</v>
+        <v>153.0912554484979</v>
       </c>
       <c r="D485" t="n">
-        <v>144.4223595043424</v>
+        <v>144.4223443642259</v>
       </c>
       <c r="E485" t="n">
-        <v>150.4995330476759</v>
+        <v>150.4995172704758</v>
       </c>
       <c r="F485" t="n">
         <v>918500</v>
@@ -10152,16 +10152,16 @@
         <v>43935</v>
       </c>
       <c r="B487" t="n">
-        <v>157.8576965332031</v>
+        <v>157.8577117919922</v>
       </c>
       <c r="C487" t="n">
-        <v>161.5814579816142</v>
+        <v>161.5814736003482</v>
       </c>
       <c r="D487" t="n">
-        <v>150.082480810678</v>
+        <v>150.0824953179016</v>
       </c>
       <c r="E487" t="n">
-        <v>150.171847448954</v>
+        <v>150.1718619648161</v>
       </c>
       <c r="F487" t="n">
         <v>964366</v>
@@ -10172,16 +10172,16 @@
         <v>43936</v>
       </c>
       <c r="B488" t="n">
-        <v>155.0574340820312</v>
+        <v>155.0574035644531</v>
       </c>
       <c r="C488" t="n">
-        <v>160.8069307415302</v>
+        <v>160.8068990923668</v>
       </c>
       <c r="D488" t="n">
-        <v>148.0865629562494</v>
+        <v>148.086533810641</v>
       </c>
       <c r="E488" t="n">
-        <v>154.6105856999209</v>
+        <v>154.6105552702891</v>
       </c>
       <c r="F488" t="n">
         <v>821233</v>
@@ -10212,16 +10212,16 @@
         <v>43938</v>
       </c>
       <c r="B490" t="n">
-        <v>156.1000671386719</v>
+        <v>156.10009765625</v>
       </c>
       <c r="C490" t="n">
-        <v>159.6450950891468</v>
+        <v>159.6451262997783</v>
       </c>
       <c r="D490" t="n">
-        <v>151.8400909746121</v>
+        <v>151.8401206593645</v>
       </c>
       <c r="E490" t="n">
-        <v>159.6450950891468</v>
+        <v>159.6451262997783</v>
       </c>
       <c r="F490" t="n">
         <v>607466</v>
@@ -10232,16 +10232,16 @@
         <v>43941</v>
       </c>
       <c r="B491" t="n">
-        <v>161.0750274658203</v>
+        <v>161.0749969482422</v>
       </c>
       <c r="C491" t="n">
-        <v>165.930827264216</v>
+        <v>165.9307958266489</v>
       </c>
       <c r="D491" t="n">
-        <v>150.7378765114165</v>
+        <v>150.7378479523345</v>
       </c>
       <c r="E491" t="n">
-        <v>151.9294772239444</v>
+        <v>151.9294484390994</v>
       </c>
       <c r="F491" t="n">
         <v>652266</v>
@@ -10252,16 +10252,16 @@
         <v>43943</v>
       </c>
       <c r="B492" t="n">
-        <v>158.8109741210938</v>
+        <v>158.8109893798828</v>
       </c>
       <c r="C492" t="n">
-        <v>166.8245161896017</v>
+        <v>166.8245322183435</v>
       </c>
       <c r="D492" t="n">
-        <v>157.6193734644301</v>
+        <v>157.6193886087284</v>
       </c>
       <c r="E492" t="n">
-        <v>166.8245161896017</v>
+        <v>166.8245322183435</v>
       </c>
       <c r="F492" t="n">
         <v>2119233</v>
@@ -10272,16 +10272,16 @@
         <v>43944</v>
       </c>
       <c r="B493" t="n">
-        <v>151.8401184082031</v>
+        <v>151.840087890625</v>
       </c>
       <c r="C493" t="n">
-        <v>160.8665135898119</v>
+        <v>160.8664812580642</v>
       </c>
       <c r="D493" t="n">
-        <v>144.809654144183</v>
+        <v>144.8096250396224</v>
       </c>
       <c r="E493" t="n">
-        <v>159.8238572305839</v>
+        <v>159.8238251083944</v>
       </c>
       <c r="F493" t="n">
         <v>1242300</v>
@@ -10292,16 +10292,16 @@
         <v>43945</v>
       </c>
       <c r="B494" t="n">
-        <v>148.9504699707031</v>
+        <v>148.950439453125</v>
       </c>
       <c r="C494" t="n">
-        <v>152.0188460156135</v>
+        <v>152.018814869374</v>
       </c>
       <c r="D494" t="n">
-        <v>136.1109315801753</v>
+        <v>136.1109036932141</v>
       </c>
       <c r="E494" t="n">
-        <v>146.9545391278248</v>
+        <v>146.9545090191811</v>
       </c>
       <c r="F494" t="n">
         <v>1301233</v>
@@ -10312,16 +10312,16 @@
         <v>43948</v>
       </c>
       <c r="B495" t="n">
-        <v>156.9639892578125</v>
+        <v>156.9639739990234</v>
       </c>
       <c r="C495" t="n">
-        <v>157.9172788832115</v>
+        <v>157.9172635317512</v>
       </c>
       <c r="D495" t="n">
-        <v>152.8231682250355</v>
+        <v>152.8231533687841</v>
       </c>
       <c r="E495" t="n">
-        <v>153.8658244913087</v>
+        <v>153.8658095336986</v>
       </c>
       <c r="F495" t="n">
         <v>935633</v>
@@ -10352,16 +10352,16 @@
         <v>43950</v>
       </c>
       <c r="B497" t="n">
-        <v>161.9591064453125</v>
+        <v>161.9591369628906</v>
       </c>
       <c r="C497" t="n">
-        <v>164.7900292416936</v>
+        <v>164.790060292696</v>
       </c>
       <c r="D497" t="n">
-        <v>159.7241602160489</v>
+        <v>159.7241903125012</v>
       </c>
       <c r="E497" t="n">
-        <v>161.3631147214959</v>
+        <v>161.3631451267727</v>
       </c>
       <c r="F497" t="n">
         <v>594666</v>
@@ -10372,16 +10372,16 @@
         <v>43951</v>
       </c>
       <c r="B498" t="n">
-        <v>156.2674713134766</v>
+        <v>156.2674407958984</v>
       </c>
       <c r="C498" t="n">
-        <v>162.1081370946308</v>
+        <v>162.1081054364251</v>
       </c>
       <c r="D498" t="n">
-        <v>155.4926909739401</v>
+        <v>155.4926606076694</v>
       </c>
       <c r="E498" t="n">
-        <v>159.0984099702694</v>
+        <v>159.0983788998354</v>
       </c>
       <c r="F498" t="n">
         <v>826166</v>
@@ -10392,16 +10392,16 @@
         <v>43955</v>
       </c>
       <c r="B499" t="n">
-        <v>152.4531555175781</v>
+        <v>152.4531402587891</v>
       </c>
       <c r="C499" t="n">
-        <v>152.8107475853664</v>
+        <v>152.8107322907865</v>
       </c>
       <c r="D499" t="n">
-        <v>147.5660740289393</v>
+        <v>147.5660592592903</v>
       </c>
       <c r="E499" t="n">
-        <v>148.5494560045326</v>
+        <v>148.5494411364585</v>
       </c>
       <c r="F499" t="n">
         <v>865433</v>
@@ -10412,16 +10412,16 @@
         <v>43956</v>
       </c>
       <c r="B500" t="n">
-        <v>154.6583099365234</v>
+        <v>154.6582946777344</v>
       </c>
       <c r="C500" t="n">
-        <v>157.6382388954418</v>
+        <v>157.6382233426491</v>
       </c>
       <c r="D500" t="n">
-        <v>151.4101831274257</v>
+        <v>151.4101681891011</v>
       </c>
       <c r="E500" t="n">
-        <v>153.6153317695615</v>
+        <v>153.615316613674</v>
       </c>
       <c r="F500" t="n">
         <v>670733</v>
@@ -10432,16 +10432,16 @@
         <v>43957</v>
       </c>
       <c r="B501" t="n">
-        <v>155.5820770263672</v>
+        <v>155.5820922851562</v>
       </c>
       <c r="C501" t="n">
-        <v>160.2009602928029</v>
+        <v>160.2009760045912</v>
       </c>
       <c r="D501" t="n">
-        <v>150.3075906737481</v>
+        <v>150.3076054152394</v>
       </c>
       <c r="E501" t="n">
-        <v>155.2840811350841</v>
+        <v>155.2840963646471</v>
       </c>
       <c r="F501" t="n">
         <v>746233</v>
@@ -10452,16 +10452,16 @@
         <v>43958</v>
       </c>
       <c r="B502" t="n">
-        <v>158.7110137939453</v>
+        <v>158.7109985351562</v>
       </c>
       <c r="C502" t="n">
-        <v>165.0880598931634</v>
+        <v>165.0880440212726</v>
       </c>
       <c r="D502" t="n">
-        <v>156.9826495560124</v>
+        <v>156.9826344633917</v>
       </c>
       <c r="E502" t="n">
-        <v>157.9660315605315</v>
+        <v>157.9660163733665</v>
       </c>
       <c r="F502" t="n">
         <v>1272300</v>
@@ -10492,16 +10492,16 @@
         <v>43962</v>
       </c>
       <c r="B504" t="n">
-        <v>146.9700622558594</v>
+        <v>146.9700775146484</v>
       </c>
       <c r="C504" t="n">
-        <v>152.6915345641711</v>
+        <v>152.6915504169773</v>
       </c>
       <c r="D504" t="n">
-        <v>146.5826721647091</v>
+        <v>146.5826873832784</v>
       </c>
       <c r="E504" t="n">
-        <v>149.9499906975384</v>
+        <v>149.9500062657109</v>
       </c>
       <c r="F504" t="n">
         <v>466500</v>
@@ -10572,16 +10572,16 @@
         <v>43966</v>
       </c>
       <c r="B508" t="n">
-        <v>139.7586364746094</v>
+        <v>139.7586517333984</v>
       </c>
       <c r="C508" t="n">
-        <v>143.5431430510845</v>
+        <v>143.5431587230644</v>
       </c>
       <c r="D508" t="n">
-        <v>134.9907480869898</v>
+        <v>134.9907628252228</v>
       </c>
       <c r="E508" t="n">
-        <v>140.3248301358833</v>
+        <v>140.3248454564891</v>
       </c>
       <c r="F508" t="n">
         <v>930266</v>
@@ -10592,16 +10592,16 @@
         <v>43969</v>
       </c>
       <c r="B509" t="n">
-        <v>147.6256561279297</v>
+        <v>147.6256866455078</v>
       </c>
       <c r="C509" t="n">
-        <v>148.3408401954261</v>
+        <v>148.340870860849</v>
       </c>
       <c r="D509" t="n">
-        <v>142.4405792169308</v>
+        <v>142.4406086626357</v>
       </c>
       <c r="E509" t="n">
-        <v>144.4967372001582</v>
+        <v>144.4967670709176</v>
       </c>
       <c r="F509" t="n">
         <v>822866</v>
@@ -10632,16 +10632,16 @@
         <v>43971</v>
       </c>
       <c r="B511" t="n">
-        <v>151.6783599853516</v>
+        <v>151.6783905029297</v>
       </c>
       <c r="C511" t="n">
-        <v>154.181504208285</v>
+        <v>154.181535229494</v>
       </c>
       <c r="D511" t="n">
-        <v>149.3540193566921</v>
+        <v>149.3540494066145</v>
       </c>
       <c r="E511" t="n">
-        <v>150.7545894111537</v>
+        <v>150.7546197428698</v>
       </c>
       <c r="F511" t="n">
         <v>544933</v>
@@ -10672,16 +10672,16 @@
         <v>43973</v>
       </c>
       <c r="B513" t="n">
-        <v>155.5522918701172</v>
+        <v>155.5522766113281</v>
       </c>
       <c r="C513" t="n">
-        <v>156.95284690906</v>
+        <v>156.9528315128846</v>
       </c>
       <c r="D513" t="n">
-        <v>153.406739462751</v>
+        <v>153.4067244144283</v>
       </c>
       <c r="E513" t="n">
-        <v>156.4462644615022</v>
+        <v>156.4462491150195</v>
       </c>
       <c r="F513" t="n">
         <v>725600</v>
@@ -10712,16 +10712,16 @@
         <v>43977</v>
       </c>
       <c r="B515" t="n">
-        <v>163.3298950195312</v>
+        <v>163.3298797607422</v>
       </c>
       <c r="C515" t="n">
-        <v>164.9092688487182</v>
+        <v>164.9092534423791</v>
       </c>
       <c r="D515" t="n">
-        <v>160.9459579726372</v>
+        <v>160.945942936563</v>
       </c>
       <c r="E515" t="n">
-        <v>164.9092688487182</v>
+        <v>164.9092534423791</v>
       </c>
       <c r="F515" t="n">
         <v>734300</v>
@@ -10732,16 +10732,16 @@
         <v>43978</v>
       </c>
       <c r="B516" t="n">
-        <v>163.8960723876953</v>
+        <v>163.8960571289062</v>
       </c>
       <c r="C516" t="n">
-        <v>165.9820284625826</v>
+        <v>165.9820130095902</v>
       </c>
       <c r="D516" t="n">
-        <v>160.3201520183744</v>
+        <v>160.320137092505</v>
       </c>
       <c r="E516" t="n">
-        <v>165.535027048892</v>
+        <v>165.5350116375157</v>
       </c>
       <c r="F516" t="n">
         <v>627900</v>
@@ -10792,16 +10792,16 @@
         <v>43983</v>
       </c>
       <c r="B519" t="n">
-        <v>162.4061126708984</v>
+        <v>162.4061279296875</v>
       </c>
       <c r="C519" t="n">
-        <v>164.7304533981214</v>
+        <v>164.7304688752928</v>
       </c>
       <c r="D519" t="n">
-        <v>160.4095659164942</v>
+        <v>160.4095809876987</v>
       </c>
       <c r="E519" t="n">
-        <v>161.8995302529245</v>
+        <v>161.8995454641179</v>
       </c>
       <c r="F519" t="n">
         <v>557733</v>
@@ -10832,16 +10832,16 @@
         <v>43985</v>
       </c>
       <c r="B521" t="n">
-        <v>172.98486328125</v>
+        <v>172.9848480224609</v>
       </c>
       <c r="C521" t="n">
-        <v>173.7298454920335</v>
+        <v>173.7298301675305</v>
       </c>
       <c r="D521" t="n">
-        <v>163.3000945410644</v>
+        <v>163.3000801365573</v>
       </c>
       <c r="E521" t="n">
-        <v>163.8960863723719</v>
+        <v>163.8960719152931</v>
       </c>
       <c r="F521" t="n">
         <v>1327400</v>
@@ -10852,16 +10852,16 @@
         <v>43986</v>
       </c>
       <c r="B522" t="n">
-        <v>174.8025817871094</v>
+        <v>174.8026123046875</v>
       </c>
       <c r="C522" t="n">
-        <v>176.9779317710393</v>
+        <v>176.9779626683967</v>
       </c>
       <c r="D522" t="n">
-        <v>169.7963091425201</v>
+        <v>169.7963387860876</v>
       </c>
       <c r="E522" t="n">
-        <v>174.6237933725555</v>
+        <v>174.6238238589201</v>
       </c>
       <c r="F522" t="n">
         <v>1106633</v>
@@ -10872,16 +10872,16 @@
         <v>43987</v>
       </c>
       <c r="B523" t="n">
-        <v>177.4547271728516</v>
+        <v>177.4547424316406</v>
       </c>
       <c r="C523" t="n">
-        <v>182.371621075518</v>
+        <v>182.3716367570957</v>
       </c>
       <c r="D523" t="n">
-        <v>175.1005886265878</v>
+        <v>175.1006036829517</v>
       </c>
       <c r="E523" t="n">
-        <v>178.7957009929787</v>
+        <v>178.7957163670739</v>
       </c>
       <c r="F523" t="n">
         <v>929700</v>
@@ -10892,16 +10892,16 @@
         <v>43990</v>
       </c>
       <c r="B524" t="n">
-        <v>181.9842376708984</v>
+        <v>181.9842529296875</v>
       </c>
       <c r="C524" t="n">
-        <v>184.1893861268831</v>
+        <v>184.1894015705667</v>
       </c>
       <c r="D524" t="n">
-        <v>176.3521742327868</v>
+        <v>176.3521890193455</v>
       </c>
       <c r="E524" t="n">
-        <v>178.2891400179336</v>
+        <v>178.2891549669007</v>
       </c>
       <c r="F524" t="n">
         <v>540433</v>
@@ -10972,16 +10972,16 @@
         <v>43997</v>
       </c>
       <c r="B528" t="n">
-        <v>180.3750915527344</v>
+        <v>180.3750762939453</v>
       </c>
       <c r="C528" t="n">
-        <v>182.8782360569759</v>
+        <v>182.8782205864339</v>
       </c>
       <c r="D528" t="n">
-        <v>173.5212611882256</v>
+        <v>173.5212465092347</v>
       </c>
       <c r="E528" t="n">
-        <v>175.7860059255433</v>
+        <v>175.785991054967</v>
       </c>
       <c r="F528" t="n">
         <v>826966</v>
@@ -11012,16 +11012,16 @@
         <v>43999</v>
       </c>
       <c r="B530" t="n">
-        <v>181.2392425537109</v>
+        <v>181.2392578125</v>
       </c>
       <c r="C530" t="n">
-        <v>186.066727321228</v>
+        <v>186.0667429864499</v>
       </c>
       <c r="D530" t="n">
-        <v>180.6134678764014</v>
+        <v>180.6134830825056</v>
       </c>
       <c r="E530" t="n">
-        <v>182.0438359788805</v>
+        <v>182.0438513054095</v>
       </c>
       <c r="F530" t="n">
         <v>934766</v>
@@ -11052,16 +11052,16 @@
         <v>44001</v>
       </c>
       <c r="B532" t="n">
-        <v>187.1693115234375</v>
+        <v>187.1692962646484</v>
       </c>
       <c r="C532" t="n">
-        <v>190.1194421040784</v>
+        <v>190.119426604783</v>
       </c>
       <c r="D532" t="n">
-        <v>181.0306657700721</v>
+        <v>181.0306510117299</v>
       </c>
       <c r="E532" t="n">
-        <v>181.7756479337349</v>
+        <v>181.7756331146588</v>
       </c>
       <c r="F532" t="n">
         <v>2381566</v>
@@ -11072,16 +11072,16 @@
         <v>44004</v>
       </c>
       <c r="B533" t="n">
-        <v>180.8220825195312</v>
+        <v>180.8220367431641</v>
       </c>
       <c r="C533" t="n">
-        <v>188.7189063843374</v>
+        <v>188.7188586088344</v>
       </c>
       <c r="D533" t="n">
-        <v>180.8220825195312</v>
+        <v>180.8220367431641</v>
       </c>
       <c r="E533" t="n">
-        <v>186.6031519738132</v>
+        <v>186.6031047339281</v>
       </c>
       <c r="F533" t="n">
         <v>629766</v>
@@ -11112,16 +11112,16 @@
         <v>44006</v>
       </c>
       <c r="B535" t="n">
-        <v>180.9114990234375</v>
+        <v>180.9114685058594</v>
       </c>
       <c r="C535" t="n">
-        <v>188.5699082597056</v>
+        <v>188.5698764502466</v>
       </c>
       <c r="D535" t="n">
-        <v>180.9114990234375</v>
+        <v>180.9114685058594</v>
       </c>
       <c r="E535" t="n">
-        <v>185.1131947760084</v>
+        <v>185.1131635496551</v>
       </c>
       <c r="F535" t="n">
         <v>509333</v>
@@ -11152,16 +11152,16 @@
         <v>44008</v>
       </c>
       <c r="B537" t="n">
-        <v>182.7292022705078</v>
+        <v>182.7292175292969</v>
       </c>
       <c r="C537" t="n">
-        <v>187.1692968299095</v>
+        <v>187.1693124594684</v>
       </c>
       <c r="D537" t="n">
-        <v>182.6696061271655</v>
+        <v>182.669621380978</v>
       </c>
       <c r="E537" t="n">
-        <v>182.6994041988366</v>
+        <v>182.6994194551374</v>
       </c>
       <c r="F537" t="n">
         <v>565500</v>
@@ -11172,16 +11172,16 @@
         <v>44011</v>
       </c>
       <c r="B538" t="n">
-        <v>188.0335083007812</v>
+        <v>188.0334930419922</v>
       </c>
       <c r="C538" t="n">
-        <v>188.0335083007812</v>
+        <v>188.0334930419922</v>
       </c>
       <c r="D538" t="n">
-        <v>182.0736507645074</v>
+        <v>182.0736359893566</v>
       </c>
       <c r="E538" t="n">
-        <v>184.1297937330371</v>
+        <v>184.1297787910318</v>
       </c>
       <c r="F538" t="n">
         <v>392600</v>
@@ -11212,16 +11212,16 @@
         <v>44013</v>
       </c>
       <c r="B540" t="n">
-        <v>187.7057037353516</v>
+        <v>187.7057189941406</v>
       </c>
       <c r="C540" t="n">
-        <v>189.9108521119912</v>
+        <v>189.910867550039</v>
       </c>
       <c r="D540" t="n">
-        <v>185.2323575408232</v>
+        <v>185.2323725985514</v>
       </c>
       <c r="E540" t="n">
-        <v>185.7985512500661</v>
+        <v>185.7985663538207</v>
       </c>
       <c r="F540" t="n">
         <v>601100</v>
@@ -11232,16 +11232,16 @@
         <v>44014</v>
       </c>
       <c r="B541" t="n">
-        <v>180.9710845947266</v>
+        <v>180.9710693359375</v>
       </c>
       <c r="C541" t="n">
-        <v>190.5366460610093</v>
+        <v>190.5366299956888</v>
       </c>
       <c r="D541" t="n">
-        <v>179.987702600919</v>
+        <v>179.9876874250449</v>
       </c>
       <c r="E541" t="n">
-        <v>190.1492559101219</v>
+        <v>190.1492398774646</v>
       </c>
       <c r="F541" t="n">
         <v>782133</v>
@@ -11252,16 +11252,16 @@
         <v>44015</v>
       </c>
       <c r="B542" t="n">
-        <v>181.5074462890625</v>
+        <v>181.5074615478516</v>
       </c>
       <c r="C542" t="n">
-        <v>184.4575768075846</v>
+        <v>184.4575923143823</v>
       </c>
       <c r="D542" t="n">
-        <v>178.0805314397118</v>
+        <v>178.0805464104103</v>
       </c>
       <c r="E542" t="n">
-        <v>179.3917072953663</v>
+        <v>179.3917223762915</v>
       </c>
       <c r="F542" t="n">
         <v>277066</v>
@@ -11272,16 +11272,16 @@
         <v>44018</v>
       </c>
       <c r="B543" t="n">
-        <v>181.775634765625</v>
+        <v>181.7756652832031</v>
       </c>
       <c r="C543" t="n">
-        <v>185.2919436544383</v>
+        <v>185.2919747623554</v>
       </c>
       <c r="D543" t="n">
-        <v>180.0770688865721</v>
+        <v>180.0770991189848</v>
       </c>
       <c r="E543" t="n">
-        <v>182.1034287126949</v>
+        <v>182.103459285305</v>
       </c>
       <c r="F543" t="n">
         <v>817833</v>
@@ -11312,16 +11312,16 @@
         <v>44020</v>
       </c>
       <c r="B545" t="n">
-        <v>180.9412536621094</v>
+        <v>180.9412689208984</v>
       </c>
       <c r="C545" t="n">
-        <v>183.5039938705884</v>
+        <v>183.5040093454935</v>
       </c>
       <c r="D545" t="n">
-        <v>177.1567470698704</v>
+        <v>177.1567620095117</v>
       </c>
       <c r="E545" t="n">
-        <v>180.4346561406069</v>
+        <v>180.4346713566746</v>
       </c>
       <c r="F545" t="n">
         <v>677066</v>
@@ -11372,16 +11372,16 @@
         <v>44025</v>
       </c>
       <c r="B548" t="n">
-        <v>175.6966094970703</v>
+        <v>175.6965942382812</v>
       </c>
       <c r="C548" t="n">
-        <v>181.269077041767</v>
+        <v>181.2690612990238</v>
       </c>
       <c r="D548" t="n">
-        <v>175.6369981885591</v>
+        <v>175.6369829349472</v>
       </c>
       <c r="E548" t="n">
-        <v>180.1367046872849</v>
+        <v>180.1366890428852</v>
       </c>
       <c r="F548" t="n">
         <v>495033</v>
@@ -11452,16 +11452,16 @@
         <v>44029</v>
       </c>
       <c r="B552" t="n">
-        <v>190.1492156982422</v>
+        <v>190.1492309570312</v>
       </c>
       <c r="C552" t="n">
-        <v>190.1492156982422</v>
+        <v>190.1492309570312</v>
       </c>
       <c r="D552" t="n">
-        <v>181.388234462942</v>
+        <v>181.3882490186939</v>
       </c>
       <c r="E552" t="n">
-        <v>181.388234462942</v>
+        <v>181.3882490186939</v>
       </c>
       <c r="F552" t="n">
         <v>595900</v>
@@ -11472,16 +11472,16 @@
         <v>44032</v>
       </c>
       <c r="B553" t="n">
-        <v>196.0196838378906</v>
+        <v>196.0197143554688</v>
       </c>
       <c r="C553" t="n">
-        <v>197.7778458137601</v>
+        <v>197.77787660506</v>
       </c>
       <c r="D553" t="n">
-        <v>189.1956527452115</v>
+        <v>189.1956822003815</v>
       </c>
       <c r="E553" t="n">
-        <v>190.7154149959243</v>
+        <v>190.7154446877005</v>
       </c>
       <c r="F553" t="n">
         <v>643066</v>
@@ -11532,16 +11532,16 @@
         <v>44035</v>
       </c>
       <c r="B556" t="n">
-        <v>191.6391906738281</v>
+        <v>191.6392211914062</v>
       </c>
       <c r="C556" t="n">
-        <v>196.6752770119251</v>
+        <v>196.6753083314747</v>
       </c>
       <c r="D556" t="n">
-        <v>190.000236094742</v>
+        <v>190.0002663513249</v>
       </c>
       <c r="E556" t="n">
-        <v>194.8277207731209</v>
+        <v>194.8277517984564</v>
       </c>
       <c r="F556" t="n">
         <v>517766</v>
@@ -11552,16 +11552,16 @@
         <v>44036</v>
       </c>
       <c r="B557" t="n">
-        <v>195.7514953613281</v>
+        <v>195.7515106201172</v>
       </c>
       <c r="C557" t="n">
-        <v>196.0792893152624</v>
+        <v>196.079304599603</v>
       </c>
       <c r="D557" t="n">
-        <v>188.0334914560843</v>
+        <v>188.0335061132565</v>
       </c>
       <c r="E557" t="n">
-        <v>192.7119707151919</v>
+        <v>192.7119857370506</v>
       </c>
       <c r="F557" t="n">
         <v>615366</v>
@@ -11632,16 +11632,16 @@
         <v>44042</v>
       </c>
       <c r="B561" t="n">
-        <v>197.2712707519531</v>
+        <v>197.2712860107422</v>
       </c>
       <c r="C561" t="n">
-        <v>200.072395631918</v>
+        <v>200.0724111073721</v>
       </c>
       <c r="D561" t="n">
-        <v>193.0993587691161</v>
+        <v>193.0993737052108</v>
       </c>
       <c r="E561" t="n">
-        <v>194.887318882232</v>
+        <v>194.8873339566241</v>
       </c>
       <c r="F561" t="n">
         <v>388133</v>
@@ -11652,16 +11652,16 @@
         <v>44043</v>
       </c>
       <c r="B562" t="n">
-        <v>194.112548828125</v>
+        <v>194.1125640869141</v>
       </c>
       <c r="C562" t="n">
-        <v>199.8936176362711</v>
+        <v>199.8936333494981</v>
       </c>
       <c r="D562" t="n">
-        <v>191.8180062117766</v>
+        <v>191.8180212901964</v>
       </c>
       <c r="E562" t="n">
-        <v>197.5692617895057</v>
+        <v>197.5692773200199</v>
       </c>
       <c r="F562" t="n">
         <v>964966</v>
@@ -11752,16 +11752,16 @@
         <v>44050</v>
       </c>
       <c r="B567" t="n">
-        <v>195.2449340820312</v>
+        <v>195.2449493408203</v>
       </c>
       <c r="C567" t="n">
-        <v>198.9996431869394</v>
+        <v>198.9996587391666</v>
       </c>
       <c r="D567" t="n">
-        <v>193.6953735189519</v>
+        <v>193.6953886566397</v>
       </c>
       <c r="E567" t="n">
-        <v>196.9732982559976</v>
+        <v>196.9733136498618</v>
       </c>
       <c r="F567" t="n">
         <v>600933</v>
@@ -11772,16 +11772,16 @@
         <v>44053</v>
       </c>
       <c r="B568" t="n">
-        <v>191.9074096679688</v>
+        <v>191.9074249267578</v>
       </c>
       <c r="C568" t="n">
-        <v>197.0030927124582</v>
+        <v>197.0031083764112</v>
       </c>
       <c r="D568" t="n">
-        <v>191.0432351752126</v>
+        <v>191.0432503652901</v>
       </c>
       <c r="E568" t="n">
-        <v>195.3641227956948</v>
+        <v>195.3641383293313</v>
       </c>
       <c r="F568" t="n">
         <v>446333</v>
@@ -11812,16 +11812,16 @@
         <v>44055</v>
       </c>
       <c r="B570" t="n">
-        <v>182.6994323730469</v>
+        <v>182.6994476318359</v>
       </c>
       <c r="C570" t="n">
-        <v>189.2552819722826</v>
+        <v>189.2552977786066</v>
       </c>
       <c r="D570" t="n">
-        <v>179.2427191158309</v>
+        <v>179.2427340859203</v>
       </c>
       <c r="E570" t="n">
-        <v>186.7521374689941</v>
+        <v>186.7521530662592</v>
       </c>
       <c r="F570" t="n">
         <v>1065533</v>
@@ -11832,16 +11832,16 @@
         <v>44056</v>
       </c>
       <c r="B571" t="n">
-        <v>186.5733337402344</v>
+        <v>186.5733184814453</v>
       </c>
       <c r="C571" t="n">
-        <v>190.9240192427385</v>
+        <v>190.9240036281312</v>
       </c>
       <c r="D571" t="n">
-        <v>184.6363831579516</v>
+        <v>184.6363680575749</v>
       </c>
       <c r="E571" t="n">
-        <v>184.8449696747432</v>
+        <v>184.8449545573073</v>
       </c>
       <c r="F571" t="n">
         <v>646800</v>
@@ -11852,16 +11852,16 @@
         <v>44057</v>
       </c>
       <c r="B572" t="n">
-        <v>191.0730590820312</v>
+        <v>191.0730133056641</v>
       </c>
       <c r="C572" t="n">
-        <v>193.099404249693</v>
+        <v>193.0993579878638</v>
       </c>
       <c r="D572" t="n">
-        <v>187.0799497483613</v>
+        <v>187.0799049286441</v>
       </c>
       <c r="E572" t="n">
-        <v>188.7785160450586</v>
+        <v>188.7784708184071</v>
       </c>
       <c r="F572" t="n">
         <v>670600</v>
@@ -11872,16 +11872,16 @@
         <v>44060</v>
       </c>
       <c r="B573" t="n">
-        <v>186.0965728759766</v>
+        <v>186.0965576171875</v>
       </c>
       <c r="C573" t="n">
-        <v>193.0397977741653</v>
+        <v>193.0397819460739</v>
       </c>
       <c r="D573" t="n">
-        <v>183.0272344742933</v>
+        <v>183.0272194671714</v>
       </c>
       <c r="E573" t="n">
-        <v>191.8776272782028</v>
+        <v>191.8776115454024</v>
       </c>
       <c r="F573" t="n">
         <v>389400</v>
@@ -11952,16 +11952,16 @@
         <v>44064</v>
       </c>
       <c r="B577" t="n">
-        <v>186.5733337402344</v>
+        <v>186.5733184814453</v>
       </c>
       <c r="C577" t="n">
-        <v>188.1228942060606</v>
+        <v>188.1228788205416</v>
       </c>
       <c r="D577" t="n">
-        <v>182.9080190924604</v>
+        <v>182.9080041334369</v>
       </c>
       <c r="E577" t="n">
-        <v>184.7555754532611</v>
+        <v>184.7555603431363</v>
       </c>
       <c r="F577" t="n">
         <v>431666</v>
@@ -11972,16 +11972,16 @@
         <v>44067</v>
       </c>
       <c r="B578" t="n">
-        <v>185.2323455810547</v>
+        <v>185.2323608398438</v>
       </c>
       <c r="C578" t="n">
-        <v>187.8546819735952</v>
+        <v>187.8546974484032</v>
       </c>
       <c r="D578" t="n">
-        <v>182.8186108460036</v>
+        <v>182.8186259059577</v>
       </c>
       <c r="E578" t="n">
-        <v>186.8415172277884</v>
+        <v>186.8415326191354</v>
       </c>
       <c r="F578" t="n">
         <v>597533</v>
@@ -12012,16 +12012,16 @@
         <v>44069</v>
       </c>
       <c r="B580" t="n">
-        <v>186.0369415283203</v>
+        <v>186.0369262695312</v>
       </c>
       <c r="C580" t="n">
-        <v>191.0134321430643</v>
+        <v>191.0134164761023</v>
       </c>
       <c r="D580" t="n">
-        <v>182.520632341546</v>
+        <v>182.5206173711653</v>
       </c>
       <c r="E580" t="n">
-        <v>186.6627314036357</v>
+        <v>186.6627160935192</v>
       </c>
       <c r="F580" t="n">
         <v>788933</v>
@@ -12052,16 +12052,16 @@
         <v>44071</v>
       </c>
       <c r="B582" t="n">
-        <v>192.1458129882812</v>
+        <v>192.1457977294922</v>
       </c>
       <c r="C582" t="n">
-        <v>192.1458129882812</v>
+        <v>192.1457977294922</v>
       </c>
       <c r="D582" t="n">
-        <v>187.1991202278299</v>
+        <v>187.1991053618704</v>
       </c>
       <c r="E582" t="n">
-        <v>188.9274844020878</v>
+        <v>188.9274693988745</v>
       </c>
       <c r="F582" t="n">
         <v>688066</v>
@@ -12072,16 +12072,16 @@
         <v>44074</v>
       </c>
       <c r="B583" t="n">
-        <v>192.8907775878906</v>
+        <v>192.8907928466797</v>
       </c>
       <c r="C583" t="n">
-        <v>194.8873242612342</v>
+        <v>194.8873396779618</v>
       </c>
       <c r="D583" t="n">
-        <v>189.0466594494166</v>
+        <v>189.0466744041134</v>
       </c>
       <c r="E583" t="n">
-        <v>191.9967899283081</v>
+        <v>191.9968051163775</v>
       </c>
       <c r="F583" t="n">
         <v>944966</v>
@@ -12092,16 +12092,16 @@
         <v>44075</v>
       </c>
       <c r="B584" t="n">
-        <v>205.5852813720703</v>
+        <v>205.5852966308594</v>
       </c>
       <c r="C584" t="n">
-        <v>207.2838322362663</v>
+        <v>207.2838476211239</v>
       </c>
       <c r="D584" t="n">
-        <v>193.5463743241929</v>
+        <v>193.5463886894397</v>
       </c>
       <c r="E584" t="n">
-        <v>195.1853290397085</v>
+        <v>195.1853435266005</v>
       </c>
       <c r="F584" t="n">
         <v>1357600</v>
@@ -12112,16 +12112,16 @@
         <v>44076</v>
       </c>
       <c r="B585" t="n">
-        <v>202.0689392089844</v>
+        <v>202.0689697265625</v>
       </c>
       <c r="C585" t="n">
-        <v>206.4792357027279</v>
+        <v>206.4792668863736</v>
       </c>
       <c r="D585" t="n">
-        <v>199.7148006035536</v>
+        <v>199.7148307655966</v>
       </c>
       <c r="E585" t="n">
-        <v>205.376661579292</v>
+        <v>205.3766925964208</v>
       </c>
       <c r="F585" t="n">
         <v>581366</v>
@@ -12132,16 +12132,16 @@
         <v>44077</v>
       </c>
       <c r="B586" t="n">
-        <v>199.3572082519531</v>
+        <v>199.3572387695312</v>
       </c>
       <c r="C586" t="n">
-        <v>204.6018810582302</v>
+        <v>204.6019123786623</v>
       </c>
       <c r="D586" t="n">
-        <v>196.5858814905054</v>
+        <v>196.5859115838492</v>
       </c>
       <c r="E586" t="n">
-        <v>202.0391407984153</v>
+        <v>202.0391717265434</v>
       </c>
       <c r="F586" t="n">
         <v>527733</v>
@@ -12152,16 +12152,16 @@
         <v>44078</v>
       </c>
       <c r="B587" t="n">
-        <v>197.8970642089844</v>
+        <v>197.8970489501953</v>
       </c>
       <c r="C587" t="n">
-        <v>203.1417376008307</v>
+        <v>203.1417219376528</v>
       </c>
       <c r="D587" t="n">
-        <v>194.6489376248939</v>
+        <v>194.6489226165506</v>
       </c>
       <c r="E587" t="n">
-        <v>200.2512182300084</v>
+        <v>200.2512027897031</v>
       </c>
       <c r="F587" t="n">
         <v>642700</v>
@@ -12192,16 +12192,16 @@
         <v>44083</v>
       </c>
       <c r="B589" t="n">
-        <v>203.4993286132812</v>
+        <v>203.4993133544922</v>
       </c>
       <c r="C589" t="n">
-        <v>204.6614990019853</v>
+        <v>204.6614836560544</v>
       </c>
       <c r="D589" t="n">
-        <v>196.7050947300723</v>
+        <v>196.7050799807286</v>
       </c>
       <c r="E589" t="n">
-        <v>202.3669562994131</v>
+        <v>202.3669411255316</v>
       </c>
       <c r="F589" t="n">
         <v>801100</v>
@@ -12232,16 +12232,16 @@
         <v>44085</v>
       </c>
       <c r="B591" t="n">
-        <v>189.776611328125</v>
+        <v>189.7766265869141</v>
       </c>
       <c r="C591" t="n">
-        <v>197.9303777215384</v>
+        <v>197.9303936359225</v>
       </c>
       <c r="D591" t="n">
-        <v>187.8053759423223</v>
+        <v>187.8053910426163</v>
       </c>
       <c r="E591" t="n">
-        <v>194.5852431804272</v>
+        <v>194.5852588258493</v>
       </c>
       <c r="F591" t="n">
         <v>1048366</v>
@@ -12252,16 +12252,16 @@
         <v>44088</v>
       </c>
       <c r="B592" t="n">
-        <v>197.1837158203125</v>
+        <v>197.1837005615234</v>
       </c>
       <c r="C592" t="n">
-        <v>199.1250853489015</v>
+        <v>199.1250699398823</v>
       </c>
       <c r="D592" t="n">
-        <v>190.0753061062856</v>
+        <v>190.075291397571</v>
       </c>
       <c r="E592" t="n">
-        <v>190.3441157921762</v>
+        <v>190.3441010626601</v>
       </c>
       <c r="F592" t="n">
         <v>434033</v>
@@ -12272,16 +12272,16 @@
         <v>44089</v>
       </c>
       <c r="B593" t="n">
-        <v>197.2733001708984</v>
+        <v>197.2733154296875</v>
       </c>
       <c r="C593" t="n">
-        <v>199.0653392992138</v>
+        <v>199.0653546966144</v>
       </c>
       <c r="D593" t="n">
-        <v>191.8075998186343</v>
+        <v>191.8076146546597</v>
       </c>
       <c r="E593" t="n">
-        <v>199.005607193483</v>
+        <v>199.0056225862634</v>
       </c>
       <c r="F593" t="n">
         <v>591666</v>
@@ -12292,16 +12292,16 @@
         <v>44090</v>
       </c>
       <c r="B594" t="n">
-        <v>197.8408050537109</v>
+        <v>197.8407897949219</v>
       </c>
       <c r="C594" t="n">
-        <v>202.7689017487487</v>
+        <v>202.7688861098723</v>
       </c>
       <c r="D594" t="n">
-        <v>196.7954475265745</v>
+        <v>196.7954323484103</v>
       </c>
       <c r="E594" t="n">
-        <v>198.9458946924643</v>
+        <v>198.9458793484435</v>
       </c>
       <c r="F594" t="n">
         <v>602300</v>
@@ -12312,16 +12312,16 @@
         <v>44091</v>
       </c>
       <c r="B595" t="n">
-        <v>191.3297119140625</v>
+        <v>191.3297271728516</v>
       </c>
       <c r="C595" t="n">
-        <v>195.7799360706191</v>
+        <v>195.7799516843192</v>
       </c>
       <c r="D595" t="n">
-        <v>190.8817059313864</v>
+        <v>190.8817211544465</v>
       </c>
       <c r="E595" t="n">
-        <v>195.6306058068198</v>
+        <v>195.6306214086107</v>
       </c>
       <c r="F595" t="n">
         <v>482133</v>
@@ -12392,16 +12392,16 @@
         <v>44097</v>
       </c>
       <c r="B599" t="n">
-        <v>187.0885620117188</v>
+        <v>187.0885772705078</v>
       </c>
       <c r="C599" t="n">
-        <v>189.8960924517536</v>
+        <v>189.8961079395225</v>
       </c>
       <c r="D599" t="n">
-        <v>185.1770587124788</v>
+        <v>185.1770738153672</v>
       </c>
       <c r="E599" t="n">
-        <v>185.8640082963715</v>
+        <v>185.8640234552869</v>
       </c>
       <c r="F599" t="n">
         <v>596200</v>
@@ -12412,16 +12412,16 @@
         <v>44098</v>
       </c>
       <c r="B600" t="n">
-        <v>187.2677764892578</v>
+        <v>187.2677917480469</v>
       </c>
       <c r="C600" t="n">
-        <v>190.7921074300882</v>
+        <v>190.7921229760437</v>
       </c>
       <c r="D600" t="n">
-        <v>185.5354694759098</v>
+        <v>185.5354845935485</v>
       </c>
       <c r="E600" t="n">
-        <v>187.6560503657161</v>
+        <v>187.6560656561421</v>
       </c>
       <c r="F600" t="n">
         <v>378566</v>
@@ -12492,16 +12492,16 @@
         <v>44104</v>
       </c>
       <c r="B604" t="n">
-        <v>185.5951995849609</v>
+        <v>185.59521484375</v>
       </c>
       <c r="C604" t="n">
-        <v>186.9690987597785</v>
+        <v>186.9691141315233</v>
       </c>
       <c r="D604" t="n">
-        <v>180.3982937920956</v>
+        <v>180.3983086236188</v>
       </c>
       <c r="E604" t="n">
-        <v>181.5929814613258</v>
+        <v>181.5929963910708</v>
       </c>
       <c r="F604" t="n">
         <v>757400</v>
@@ -12532,16 +12532,16 @@
         <v>44106</v>
       </c>
       <c r="B606" t="n">
-        <v>184.5797271728516</v>
+        <v>184.5797119140625</v>
       </c>
       <c r="C606" t="n">
-        <v>189.1195498966001</v>
+        <v>189.1195342625142</v>
       </c>
       <c r="D606" t="n">
-        <v>183.1162296906853</v>
+        <v>183.1162145528803</v>
       </c>
       <c r="E606" t="n">
-        <v>187.6261863589839</v>
+        <v>187.6261708483509</v>
       </c>
       <c r="F606" t="n">
         <v>606133</v>
@@ -12552,16 +12552,16 @@
         <v>44109</v>
       </c>
       <c r="B607" t="n">
-        <v>189.2688903808594</v>
+        <v>189.2688598632812</v>
       </c>
       <c r="C607" t="n">
-        <v>191.4492035189667</v>
+        <v>191.4491726498364</v>
       </c>
       <c r="D607" t="n">
-        <v>183.1162248684416</v>
+        <v>183.1161953429148</v>
       </c>
       <c r="E607" t="n">
-        <v>183.5343800162883</v>
+        <v>183.5343504233384</v>
       </c>
       <c r="F607" t="n">
         <v>384366</v>
@@ -12612,16 +12612,16 @@
         <v>44112</v>
       </c>
       <c r="B610" t="n">
-        <v>194.2268218994141</v>
+        <v>194.2268371582031</v>
       </c>
       <c r="C610" t="n">
-        <v>195.4812567599064</v>
+        <v>195.481272117246</v>
       </c>
       <c r="D610" t="n">
-        <v>187.4469551313734</v>
+        <v>187.4469698575246</v>
       </c>
       <c r="E610" t="n">
-        <v>188.16377071129</v>
+        <v>188.1637854937555</v>
       </c>
       <c r="F610" t="n">
         <v>582633</v>
@@ -12632,16 +12632,16 @@
         <v>44113</v>
       </c>
       <c r="B611" t="n">
-        <v>192.8230590820312</v>
+        <v>192.8230895996094</v>
       </c>
       <c r="C611" t="n">
-        <v>196.5564672754529</v>
+        <v>196.5564983839074</v>
       </c>
       <c r="D611" t="n">
-        <v>190.4336839147521</v>
+        <v>190.4337140541703</v>
       </c>
       <c r="E611" t="n">
-        <v>194.1372260579286</v>
+        <v>194.1372567834963</v>
       </c>
       <c r="F611" t="n">
         <v>718800</v>
@@ -12652,16 +12652,16 @@
         <v>44117</v>
       </c>
       <c r="B612" t="n">
-        <v>196.9447479248047</v>
+        <v>196.9447631835938</v>
       </c>
       <c r="C612" t="n">
-        <v>198.467992496327</v>
+        <v>198.4680078731332</v>
       </c>
       <c r="D612" t="n">
-        <v>190.2843602382814</v>
+        <v>190.2843749810402</v>
       </c>
       <c r="E612" t="n">
-        <v>193.5398813577115</v>
+        <v>193.5398963526999</v>
       </c>
       <c r="F612" t="n">
         <v>922633</v>
@@ -12672,16 +12672,16 @@
         <v>44118</v>
       </c>
       <c r="B613" t="n">
-        <v>201.2157745361328</v>
+        <v>201.2157897949219</v>
       </c>
       <c r="C613" t="n">
-        <v>201.842991992339</v>
+        <v>201.8430072986919</v>
       </c>
       <c r="D613" t="n">
-        <v>196.2578125625674</v>
+        <v>196.2578274453795</v>
       </c>
       <c r="E613" t="n">
-        <v>197.5122322837026</v>
+        <v>197.5122472616411</v>
       </c>
       <c r="F613" t="n">
         <v>663866</v>
@@ -12692,16 +12692,16 @@
         <v>44119</v>
       </c>
       <c r="B614" t="n">
-        <v>198.4978942871094</v>
+        <v>198.4978637695312</v>
       </c>
       <c r="C614" t="n">
-        <v>201.45475542615</v>
+        <v>201.4547244539764</v>
       </c>
       <c r="D614" t="n">
-        <v>196.9149173280181</v>
+        <v>196.9148870538109</v>
       </c>
       <c r="E614" t="n">
-        <v>199.6029839571678</v>
+        <v>199.6029532696903</v>
       </c>
       <c r="F614" t="n">
         <v>599566</v>
@@ -12732,16 +12732,16 @@
         <v>44123</v>
       </c>
       <c r="B616" t="n">
-        <v>192.3153533935547</v>
+        <v>192.3153381347656</v>
       </c>
       <c r="C616" t="n">
-        <v>196.6759797583532</v>
+        <v>196.6759641535809</v>
       </c>
       <c r="D616" t="n">
-        <v>189.1494300046808</v>
+        <v>189.1494149970842</v>
       </c>
       <c r="E616" t="n">
-        <v>195.1228841191864</v>
+        <v>195.1228686376407</v>
       </c>
       <c r="F616" t="n">
         <v>597800</v>
@@ -12752,16 +12752,16 @@
         <v>44124</v>
       </c>
       <c r="B617" t="n">
-        <v>194.2268218994141</v>
+        <v>194.2268371582031</v>
       </c>
       <c r="C617" t="n">
-        <v>195.839649358588</v>
+        <v>195.8396647440835</v>
       </c>
       <c r="D617" t="n">
-        <v>190.6128779499411</v>
+        <v>190.6128929248125</v>
       </c>
       <c r="E617" t="n">
-        <v>193.0321343299786</v>
+        <v>193.032149494911</v>
       </c>
       <c r="F617" t="n">
         <v>555666</v>
@@ -12792,16 +12792,16 @@
         <v>44126</v>
       </c>
       <c r="B619" t="n">
-        <v>195.2721862792969</v>
+        <v>195.2722015380859</v>
       </c>
       <c r="C619" t="n">
-        <v>197.1239573958178</v>
+        <v>197.1239727993063</v>
       </c>
       <c r="D619" t="n">
-        <v>191.2401022943088</v>
+        <v>191.2401172380263</v>
       </c>
       <c r="E619" t="n">
-        <v>193.3009509588963</v>
+        <v>193.3009660636508</v>
       </c>
       <c r="F619" t="n">
         <v>380966</v>
@@ -12832,16 +12832,16 @@
         <v>44130</v>
       </c>
       <c r="B621" t="n">
-        <v>196.2279510498047</v>
+        <v>196.2279663085938</v>
       </c>
       <c r="C621" t="n">
-        <v>198.4978621355634</v>
+        <v>198.497877570862</v>
       </c>
       <c r="D621" t="n">
-        <v>188.5819227678193</v>
+        <v>188.5819374320492</v>
       </c>
       <c r="E621" t="n">
-        <v>190.4038278850452</v>
+        <v>190.4038426909474</v>
       </c>
       <c r="F621" t="n">
         <v>609466</v>
@@ -12852,16 +12852,16 @@
         <v>44131</v>
       </c>
       <c r="B622" t="n">
-        <v>198.3186492919922</v>
+        <v>198.3186645507812</v>
       </c>
       <c r="C622" t="n">
-        <v>204.710242589321</v>
+        <v>204.7102583398841</v>
       </c>
       <c r="D622" t="n">
-        <v>195.7500625141592</v>
+        <v>195.7500775753192</v>
       </c>
       <c r="E622" t="n">
-        <v>196.2876818257843</v>
+        <v>196.2876969283092</v>
       </c>
       <c r="F622" t="n">
         <v>606666</v>
@@ -12872,16 +12872,16 @@
         <v>44132</v>
       </c>
       <c r="B623" t="n">
-        <v>192.9425659179688</v>
+        <v>192.9425506591797</v>
       </c>
       <c r="C623" t="n">
-        <v>196.437031015196</v>
+        <v>196.4370154800485</v>
       </c>
       <c r="D623" t="n">
-        <v>192.9425659179688</v>
+        <v>192.9425506591797</v>
       </c>
       <c r="E623" t="n">
-        <v>195.6007511068256</v>
+        <v>195.6007356378149</v>
       </c>
       <c r="F623" t="n">
         <v>477733</v>
@@ -12932,16 +12932,16 @@
         <v>44138</v>
       </c>
       <c r="B626" t="n">
-        <v>195.1228637695312</v>
+        <v>195.1228790283203</v>
       </c>
       <c r="C626" t="n">
-        <v>197.0045010117106</v>
+        <v>197.0045164176454</v>
       </c>
       <c r="D626" t="n">
-        <v>192.0465236760246</v>
+        <v>192.0465386942411</v>
       </c>
       <c r="E626" t="n">
-        <v>194.6151105003338</v>
+        <v>194.6151257194161</v>
       </c>
       <c r="F626" t="n">
         <v>792500</v>
@@ -12952,16 +12952,16 @@
         <v>44139</v>
       </c>
       <c r="B627" t="n">
-        <v>205.3076019287109</v>
+        <v>205.3076171875</v>
       </c>
       <c r="C627" t="n">
-        <v>208.0553851222939</v>
+        <v>208.0554005853026</v>
       </c>
       <c r="D627" t="n">
-        <v>195.9591476304417</v>
+        <v>195.9591621944386</v>
       </c>
       <c r="E627" t="n">
-        <v>196.5564838770755</v>
+        <v>196.5564984854674</v>
       </c>
       <c r="F627" t="n">
         <v>937700</v>
@@ -12992,16 +12992,16 @@
         <v>44141</v>
       </c>
       <c r="B629" t="n">
-        <v>213.5509490966797</v>
+        <v>213.5509643554688</v>
       </c>
       <c r="C629" t="n">
-        <v>214.2378986362663</v>
+        <v>214.2379139441398</v>
       </c>
       <c r="D629" t="n">
-        <v>205.1881208029708</v>
+        <v>205.1881354642133</v>
       </c>
       <c r="E629" t="n">
-        <v>206.8308143348961</v>
+        <v>206.8308291135134</v>
       </c>
       <c r="F629" t="n">
         <v>849833</v>
@@ -13072,16 +13072,16 @@
         <v>44147</v>
       </c>
       <c r="B633" t="n">
-        <v>208.6228637695312</v>
+        <v>208.6228790283203</v>
       </c>
       <c r="C633" t="n">
-        <v>209.7578193118856</v>
+        <v>209.757834653686</v>
       </c>
       <c r="D633" t="n">
-        <v>203.6350204405104</v>
+        <v>203.6350353344859</v>
       </c>
       <c r="E633" t="n">
-        <v>206.084143027316</v>
+        <v>206.0841581004217</v>
       </c>
       <c r="F633" t="n">
         <v>897733</v>
@@ -13092,16 +13092,16 @@
         <v>44148</v>
       </c>
       <c r="B634" t="n">
-        <v>218.8972015380859</v>
+        <v>218.897216796875</v>
       </c>
       <c r="C634" t="n">
-        <v>220.6593745974234</v>
+        <v>220.6593899790492</v>
       </c>
       <c r="D634" t="n">
-        <v>209.9370211697153</v>
+        <v>209.9370358039121</v>
       </c>
       <c r="E634" t="n">
-        <v>209.9370211697153</v>
+        <v>209.9370358039121</v>
       </c>
       <c r="F634" t="n">
         <v>872100</v>
@@ -13112,16 +13112,16 @@
         <v>44151</v>
       </c>
       <c r="B635" t="n">
-        <v>218.0907745361328</v>
+        <v>218.0907897949219</v>
       </c>
       <c r="C635" t="n">
-        <v>221.5852391994435</v>
+        <v>221.5852547027238</v>
       </c>
       <c r="D635" t="n">
-        <v>215.0741818766554</v>
+        <v>215.0741969243876</v>
       </c>
       <c r="E635" t="n">
-        <v>221.017769043256</v>
+        <v>221.0177845068331</v>
       </c>
       <c r="F635" t="n">
         <v>540700</v>
@@ -13132,16 +13132,16 @@
         <v>44152</v>
       </c>
       <c r="B636" t="n">
-        <v>215.7611236572266</v>
+        <v>215.7611541748047</v>
       </c>
       <c r="C636" t="n">
-        <v>220.3905436574737</v>
+        <v>220.390574829844</v>
       </c>
       <c r="D636" t="n">
-        <v>215.7611236572266</v>
+        <v>215.7611541748047</v>
       </c>
       <c r="E636" t="n">
-        <v>219.7932074720129</v>
+        <v>219.793238559895</v>
       </c>
       <c r="F636" t="n">
         <v>945033</v>
@@ -13172,16 +13172,16 @@
         <v>44154</v>
       </c>
       <c r="B638" t="n">
-        <v>213.1626892089844</v>
+        <v>213.1627044677734</v>
       </c>
       <c r="C638" t="n">
-        <v>215.4326003285149</v>
+        <v>215.4326157497906</v>
       </c>
       <c r="D638" t="n">
-        <v>209.9668848955181</v>
+        <v>209.9668999255425</v>
       </c>
       <c r="E638" t="n">
-        <v>213.81977274129</v>
+        <v>213.819788047115</v>
       </c>
       <c r="F638" t="n">
         <v>672366</v>
@@ -13212,16 +13212,16 @@
         <v>44159</v>
       </c>
       <c r="B640" t="n">
-        <v>214.8053894042969</v>
+        <v>214.8053741455078</v>
       </c>
       <c r="C640" t="n">
-        <v>216.477964338369</v>
+        <v>216.4779489607679</v>
       </c>
       <c r="D640" t="n">
-        <v>212.2965497901061</v>
+        <v>212.2965347095335</v>
       </c>
       <c r="E640" t="n">
-        <v>214.2379192027341</v>
+        <v>214.2379039842555</v>
       </c>
       <c r="F640" t="n">
         <v>404100</v>
@@ -13252,16 +13252,16 @@
         <v>44161</v>
       </c>
       <c r="B642" t="n">
-        <v>212.8042907714844</v>
+        <v>212.8042755126953</v>
       </c>
       <c r="C642" t="n">
-        <v>218.6284142796364</v>
+        <v>218.6283986032379</v>
       </c>
       <c r="D642" t="n">
-        <v>210.265569878411</v>
+        <v>210.2655548016568</v>
       </c>
       <c r="E642" t="n">
-        <v>216.3883691136208</v>
+        <v>216.3883535978412</v>
       </c>
       <c r="F642" t="n">
         <v>253146</v>
@@ -13352,16 +13352,16 @@
         <v>44168</v>
       </c>
       <c r="B647" t="n">
-        <v>226.3938903808594</v>
+        <v>226.3938751220703</v>
       </c>
       <c r="C647" t="n">
-        <v>229.8286384300032</v>
+        <v>229.8286229397145</v>
       </c>
       <c r="D647" t="n">
-        <v>219.9724306568018</v>
+        <v>219.9724158308146</v>
       </c>
       <c r="E647" t="n">
-        <v>219.9724306568018</v>
+        <v>219.9724158308146</v>
       </c>
       <c r="F647" t="n">
         <v>476626</v>
@@ -13372,16 +13372,16 @@
         <v>44169</v>
       </c>
       <c r="B648" t="n">
-        <v>228.9326019287109</v>
+        <v>228.9326171875</v>
       </c>
       <c r="C648" t="n">
-        <v>230.2766350402532</v>
+        <v>230.2766503886246</v>
       </c>
       <c r="D648" t="n">
-        <v>224.6018572639329</v>
+        <v>224.6018722340697</v>
       </c>
       <c r="E648" t="n">
-        <v>226.9912325830327</v>
+        <v>226.9912477124258</v>
       </c>
       <c r="F648" t="n">
         <v>265620</v>
@@ -13392,16 +13392,16 @@
         <v>44172</v>
       </c>
       <c r="B649" t="n">
-        <v>224.4525146484375</v>
+        <v>224.4525299072266</v>
       </c>
       <c r="C649" t="n">
-        <v>234.4580524072576</v>
+        <v>234.4580683462457</v>
       </c>
       <c r="D649" t="n">
-        <v>220.4204304541335</v>
+        <v>220.4204454388124</v>
       </c>
       <c r="E649" t="n">
-        <v>229.3806108009077</v>
+        <v>229.3806263947199</v>
       </c>
       <c r="F649" t="n">
         <v>556173</v>
@@ -13412,16 +13412,16 @@
         <v>44173</v>
       </c>
       <c r="B650" t="n">
-        <v>228.6339263916016</v>
+        <v>228.6339416503906</v>
       </c>
       <c r="C650" t="n">
-        <v>230.7246411908779</v>
+        <v>230.7246565891991</v>
       </c>
       <c r="D650" t="n">
-        <v>221.7644609504555</v>
+        <v>221.7644757507836</v>
       </c>
       <c r="E650" t="n">
-        <v>223.8551757497318</v>
+        <v>223.8551906895921</v>
       </c>
       <c r="F650" t="n">
         <v>500300</v>
@@ -13452,16 +13452,16 @@
         <v>44175</v>
       </c>
       <c r="B652" t="n">
-        <v>227.8872375488281</v>
+        <v>227.8872528076172</v>
       </c>
       <c r="C652" t="n">
-        <v>233.4126848951685</v>
+        <v>233.4127005239284</v>
       </c>
       <c r="D652" t="n">
-        <v>225.647192559064</v>
+        <v>225.6472076678649</v>
       </c>
       <c r="E652" t="n">
-        <v>226.6925499258761</v>
+        <v>226.6925651046716</v>
       </c>
       <c r="F652" t="n">
         <v>713620</v>
@@ -13512,16 +13512,16 @@
         <v>44180</v>
       </c>
       <c r="B655" t="n">
-        <v>226.6925506591797</v>
+        <v>226.6925659179688</v>
       </c>
       <c r="C655" t="n">
-        <v>228.1859139905198</v>
+        <v>228.1859293498279</v>
       </c>
       <c r="D655" t="n">
-        <v>223.1084877787297</v>
+        <v>223.1085027962737</v>
       </c>
       <c r="E655" t="n">
-        <v>226.09521444141</v>
+        <v>226.0952296599921</v>
       </c>
       <c r="F655" t="n">
         <v>364800</v>
@@ -13612,16 +13612,16 @@
         <v>44187</v>
       </c>
       <c r="B660" t="n">
-        <v>227.1405487060547</v>
+        <v>227.1405944824219</v>
       </c>
       <c r="C660" t="n">
-        <v>230.5752964014818</v>
+        <v>230.5753428700648</v>
       </c>
       <c r="D660" t="n">
-        <v>224.9005037870945</v>
+        <v>224.9005491120182</v>
       </c>
       <c r="E660" t="n">
-        <v>225.6471854267479</v>
+        <v>225.6472309021528</v>
       </c>
       <c r="F660" t="n">
         <v>374633</v>
@@ -13632,16 +13632,16 @@
         <v>44188</v>
       </c>
       <c r="B661" t="n">
-        <v>224.4525146484375</v>
+        <v>224.4525299072266</v>
       </c>
       <c r="C661" t="n">
-        <v>229.8286319712688</v>
+        <v>229.8286475955385</v>
       </c>
       <c r="D661" t="n">
-        <v>224.0045086693544</v>
+        <v>224.004523897687</v>
       </c>
       <c r="E661" t="n">
-        <v>228.4845988427415</v>
+        <v>228.4846143756407</v>
       </c>
       <c r="F661" t="n">
         <v>316873</v>
@@ -13652,16 +13652,16 @@
         <v>44193</v>
       </c>
       <c r="B662" t="n">
-        <v>226.3938903808594</v>
+        <v>226.3938751220703</v>
       </c>
       <c r="C662" t="n">
-        <v>227.588593280359</v>
+        <v>227.5885779410478</v>
       </c>
       <c r="D662" t="n">
-        <v>222.8098272561957</v>
+        <v>222.80981223897</v>
       </c>
       <c r="E662" t="n">
-        <v>225.3485481307148</v>
+        <v>225.3485329423811</v>
       </c>
       <c r="F662" t="n">
         <v>229633</v>
@@ -13672,16 +13672,16 @@
         <v>44194</v>
       </c>
       <c r="B663" t="n">
-        <v>231.7699890136719</v>
+        <v>231.7700042724609</v>
       </c>
       <c r="C663" t="n">
-        <v>234.1593642358766</v>
+        <v>234.1593796519724</v>
       </c>
       <c r="D663" t="n">
-        <v>225.348529811629</v>
+        <v>225.3485446476555</v>
       </c>
       <c r="E663" t="n">
-        <v>227.588574779175</v>
+        <v>227.5885897626768</v>
       </c>
       <c r="F663" t="n">
         <v>293840</v>
@@ -13692,16 +13692,16 @@
         <v>44195</v>
       </c>
       <c r="B664" t="n">
-        <v>227.8872375488281</v>
+        <v>227.8872528076172</v>
       </c>
       <c r="C664" t="n">
-        <v>235.6527298849326</v>
+        <v>235.6527456636806</v>
       </c>
       <c r="D664" t="n">
-        <v>225.9458682626213</v>
+        <v>225.9458833914209</v>
       </c>
       <c r="E664" t="n">
-        <v>234.1593665584232</v>
+        <v>234.1593822371791</v>
       </c>
       <c r="F664" t="n">
         <v>659613</v>
@@ -13712,16 +13712,16 @@
         <v>44200</v>
       </c>
       <c r="B665" t="n">
-        <v>224.6018829345703</v>
+        <v>224.6018524169922</v>
       </c>
       <c r="C665" t="n">
-        <v>231.620679433361</v>
+        <v>231.6206479621102</v>
       </c>
       <c r="D665" t="n">
-        <v>220.4204528613169</v>
+        <v>220.4204229118868</v>
       </c>
       <c r="E665" t="n">
-        <v>230.1273158904218</v>
+        <v>230.1272846220805</v>
       </c>
       <c r="F665" t="n">
         <v>564553</v>
@@ -13752,16 +13752,16 @@
         <v>44202</v>
       </c>
       <c r="B667" t="n">
-        <v>210.7135772705078</v>
+        <v>210.7135620117188</v>
       </c>
       <c r="C667" t="n">
-        <v>220.5697851810959</v>
+        <v>220.5697692085711</v>
       </c>
       <c r="D667" t="n">
-        <v>210.4149167327483</v>
+        <v>210.4149014955867</v>
       </c>
       <c r="E667" t="n">
-        <v>220.5697851810959</v>
+        <v>220.5697692085711</v>
       </c>
       <c r="F667" t="n">
         <v>989980</v>
@@ -13772,16 +13772,16 @@
         <v>44203</v>
       </c>
       <c r="B668" t="n">
-        <v>213.2522888183594</v>
+        <v>213.2523040771484</v>
       </c>
       <c r="C668" t="n">
-        <v>217.2843730051644</v>
+        <v>217.2843885524602</v>
       </c>
       <c r="D668" t="n">
-        <v>207.1295050026288</v>
+        <v>207.1295198233158</v>
       </c>
       <c r="E668" t="n">
-        <v>211.4602497140818</v>
+        <v>211.4602648446455</v>
       </c>
       <c r="F668" t="n">
         <v>485820</v>
@@ -13832,16 +13832,16 @@
         <v>44208</v>
       </c>
       <c r="B671" t="n">
-        <v>265.0905151367188</v>
+        <v>265.0904846191406</v>
       </c>
       <c r="C671" t="n">
-        <v>275.5624885632321</v>
+        <v>275.5624568401063</v>
       </c>
       <c r="D671" t="n">
-        <v>258.9569367884137</v>
+        <v>258.9569069769413</v>
       </c>
       <c r="E671" t="n">
-        <v>275.1137079637683</v>
+        <v>275.1136762923066</v>
       </c>
       <c r="F671" t="n">
         <v>1327226</v>
@@ -13852,16 +13852,16 @@
         <v>44209</v>
       </c>
       <c r="B672" t="n">
-        <v>254.3193664550781</v>
+        <v>254.3193511962891</v>
       </c>
       <c r="C672" t="n">
-        <v>263.5945311748733</v>
+        <v>263.5945153595879</v>
       </c>
       <c r="D672" t="n">
-        <v>252.3745743434456</v>
+        <v>252.3745592013412</v>
       </c>
       <c r="E672" t="n">
-        <v>262.3977524179344</v>
+        <v>262.3977366744541</v>
       </c>
       <c r="F672" t="n">
         <v>1017226</v>
@@ -13872,16 +13872,16 @@
         <v>44210</v>
       </c>
       <c r="B673" t="n">
-        <v>257.3113403320312</v>
+        <v>257.3113708496094</v>
       </c>
       <c r="C673" t="n">
-        <v>264.6417276263887</v>
+        <v>264.6417590133636</v>
       </c>
       <c r="D673" t="n">
-        <v>253.5713499202285</v>
+        <v>253.5713799942372</v>
       </c>
       <c r="E673" t="n">
-        <v>255.5161571088139</v>
+        <v>255.5161874134801</v>
       </c>
       <c r="F673" t="n">
         <v>708060</v>
@@ -13972,16 +13972,16 @@
         <v>44217</v>
       </c>
       <c r="B678" t="n">
-        <v>263.5945129394531</v>
+        <v>263.594482421875</v>
       </c>
       <c r="C678" t="n">
-        <v>270.4761196693022</v>
+        <v>270.4760883550081</v>
       </c>
       <c r="D678" t="n">
-        <v>255.516157971578</v>
+        <v>255.5161283892691</v>
       </c>
       <c r="E678" t="n">
-        <v>259.1065244301358</v>
+        <v>259.1064944321533</v>
       </c>
       <c r="F678" t="n">
         <v>986426</v>
@@ -13992,16 +13992,16 @@
         <v>44218</v>
       </c>
       <c r="B679" t="n">
-        <v>260.0041198730469</v>
+        <v>260.004150390625</v>
       </c>
       <c r="C679" t="n">
-        <v>268.0824740142135</v>
+        <v>268.0825054799758</v>
       </c>
       <c r="D679" t="n">
-        <v>258.9569043997023</v>
+        <v>258.9569347943651</v>
       </c>
       <c r="E679" t="n">
-        <v>258.9569043997023</v>
+        <v>258.9569347943651</v>
       </c>
       <c r="F679" t="n">
         <v>377800</v>
@@ -14012,16 +14012,16 @@
         <v>44222</v>
       </c>
       <c r="B680" t="n">
-        <v>267.7833251953125</v>
+        <v>267.7832946777344</v>
       </c>
       <c r="C680" t="n">
-        <v>276.1608979968802</v>
+        <v>276.1608665245628</v>
       </c>
       <c r="D680" t="n">
-        <v>261.5001532031671</v>
+        <v>261.5001234016424</v>
       </c>
       <c r="E680" t="n">
-        <v>263.4449300406782</v>
+        <v>263.4449000175196</v>
       </c>
       <c r="F680" t="n">
         <v>884853</v>
@@ -14052,16 +14052,16 @@
         <v>44224</v>
       </c>
       <c r="B682" t="n">
-        <v>266.8857421875</v>
+        <v>266.8857116699219</v>
       </c>
       <c r="C682" t="n">
-        <v>269.7281412040435</v>
+        <v>269.7281103614457</v>
       </c>
       <c r="D682" t="n">
-        <v>257.9097645159661</v>
+        <v>257.9097350247639</v>
       </c>
       <c r="E682" t="n">
-        <v>257.9097645159661</v>
+        <v>257.9097350247639</v>
       </c>
       <c r="F682" t="n">
         <v>574346</v>
@@ -14112,16 +14112,16 @@
         <v>44229</v>
       </c>
       <c r="B685" t="n">
-        <v>265.6889343261719</v>
+        <v>265.6889038085938</v>
       </c>
       <c r="C685" t="n">
-        <v>271.5233259292311</v>
+        <v>271.5232947415027</v>
       </c>
       <c r="D685" t="n">
-        <v>260.7521648436775</v>
+        <v>260.7521348931468</v>
       </c>
       <c r="E685" t="n">
-        <v>266.5865260106143</v>
+        <v>266.5864953899369</v>
       </c>
       <c r="F685" t="n">
         <v>627486</v>
@@ -14152,16 +14152,16 @@
         <v>44231</v>
       </c>
       <c r="B687" t="n">
-        <v>266.5865173339844</v>
+        <v>266.5864868164062</v>
       </c>
       <c r="C687" t="n">
-        <v>269.129729199273</v>
+        <v>269.1296983905599</v>
       </c>
       <c r="D687" t="n">
-        <v>262.547339667396</v>
+        <v>262.5473096122041</v>
       </c>
       <c r="E687" t="n">
-        <v>265.2401450692025</v>
+        <v>265.2401147057508</v>
       </c>
       <c r="F687" t="n">
         <v>337373</v>
@@ -14172,16 +14172,16 @@
         <v>44232</v>
       </c>
       <c r="B688" t="n">
-        <v>267.0353393554688</v>
+        <v>267.0353088378906</v>
       </c>
       <c r="C688" t="n">
-        <v>273.7673227005646</v>
+        <v>273.7672914136357</v>
       </c>
       <c r="D688" t="n">
-        <v>264.94093844977</v>
+        <v>264.9409081715461</v>
       </c>
       <c r="E688" t="n">
-        <v>265.3897495138921</v>
+        <v>265.3897191843768</v>
       </c>
       <c r="F688" t="n">
         <v>358426</v>
@@ -14212,16 +14212,16 @@
         <v>44236</v>
       </c>
       <c r="B690" t="n">
-        <v>264.7913513183594</v>
+        <v>264.7913208007812</v>
       </c>
       <c r="C690" t="n">
-        <v>270.1769320376098</v>
+        <v>270.1769008993359</v>
       </c>
       <c r="D690" t="n">
-        <v>264.1929466970819</v>
+        <v>264.1929162484707</v>
       </c>
       <c r="E690" t="n">
-        <v>269.4289338700438</v>
+        <v>269.4289028179777</v>
       </c>
       <c r="F690" t="n">
         <v>477180</v>
@@ -14252,16 +14252,16 @@
         <v>44238</v>
       </c>
       <c r="B692" t="n">
-        <v>263.5945129394531</v>
+        <v>263.594482421875</v>
       </c>
       <c r="C692" t="n">
-        <v>265.2401330750988</v>
+        <v>265.2401023669995</v>
       </c>
       <c r="D692" t="n">
-        <v>256.712936645724</v>
+        <v>256.7129069248583</v>
       </c>
       <c r="E692" t="n">
-        <v>257.9097457559899</v>
+        <v>257.909715896564</v>
       </c>
       <c r="F692" t="n">
         <v>869180</v>
@@ -14272,16 +14272,16 @@
         <v>44239</v>
       </c>
       <c r="B693" t="n">
-        <v>257.3113403320312</v>
+        <v>257.3113708496094</v>
       </c>
       <c r="C693" t="n">
-        <v>262.2481398500589</v>
+        <v>262.2481709531501</v>
       </c>
       <c r="D693" t="n">
-        <v>255.8153441673101</v>
+        <v>255.8153745074605</v>
       </c>
       <c r="E693" t="n">
-        <v>262.2481398500589</v>
+        <v>262.2481709531501</v>
       </c>
       <c r="F693" t="n">
         <v>323506</v>
@@ -14292,16 +14292,16 @@
         <v>44244</v>
       </c>
       <c r="B694" t="n">
-        <v>257.3113403320312</v>
+        <v>257.3113708496094</v>
       </c>
       <c r="C694" t="n">
-        <v>260.1537391322253</v>
+        <v>260.153769986917</v>
       </c>
       <c r="D694" t="n">
-        <v>253.1225541144241</v>
+        <v>253.1225841352048</v>
       </c>
       <c r="E694" t="n">
-        <v>260.0041456029772</v>
+        <v>260.0041764399268</v>
       </c>
       <c r="F694" t="n">
         <v>745893</v>
@@ -14312,16 +14312,16 @@
         <v>44245</v>
       </c>
       <c r="B695" t="n">
-        <v>253.1225738525391</v>
+        <v>253.12255859375</v>
       </c>
       <c r="C695" t="n">
-        <v>255.8153641154048</v>
+        <v>255.8153486942884</v>
       </c>
       <c r="D695" t="n">
-        <v>242.9498021827902</v>
+        <v>242.9497875372383</v>
       </c>
       <c r="E695" t="n">
-        <v>253.720963234253</v>
+        <v>253.7209479393917</v>
       </c>
       <c r="F695" t="n">
         <v>1056680</v>
@@ -14392,16 +14392,16 @@
         <v>44251</v>
       </c>
       <c r="B699" t="n">
-        <v>240.8553771972656</v>
+        <v>240.8553924560547</v>
       </c>
       <c r="C699" t="n">
-        <v>245.9417701321336</v>
+        <v>245.9417857131583</v>
       </c>
       <c r="D699" t="n">
-        <v>235.4697972105133</v>
+        <v>235.4698121281125</v>
       </c>
       <c r="E699" t="n">
-        <v>245.1937720663036</v>
+        <v>245.1937875999407</v>
       </c>
       <c r="F699" t="n">
         <v>632986</v>
@@ -14412,16 +14412,16 @@
         <v>44252</v>
       </c>
       <c r="B700" t="n">
-        <v>236.9658203125</v>
+        <v>236.9658050537109</v>
       </c>
       <c r="C700" t="n">
-        <v>244.4458018221362</v>
+        <v>244.4457860816935</v>
       </c>
       <c r="D700" t="n">
-        <v>231.4306309517569</v>
+        <v>231.4306160493918</v>
       </c>
       <c r="E700" t="n">
-        <v>240.5562023062886</v>
+        <v>240.5561868163063</v>
       </c>
       <c r="F700" t="n">
         <v>728733</v>
@@ -14472,16 +14472,16 @@
         <v>44257</v>
       </c>
       <c r="B703" t="n">
-        <v>245.3433685302734</v>
+        <v>245.3433837890625</v>
       </c>
       <c r="C703" t="n">
-        <v>246.5401624063213</v>
+        <v>246.5401777395433</v>
       </c>
       <c r="D703" t="n">
-        <v>231.8794031840999</v>
+        <v>231.8794176055164</v>
       </c>
       <c r="E703" t="n">
-        <v>242.6505785046507</v>
+        <v>242.6505935959654</v>
       </c>
       <c r="F703" t="n">
         <v>816593</v>
@@ -14592,16 +14592,16 @@
         <v>44265</v>
       </c>
       <c r="B709" t="n">
-        <v>227.2418212890625</v>
+        <v>227.2418365478516</v>
       </c>
       <c r="C709" t="n">
-        <v>229.4858155142288</v>
+        <v>229.4858309236971</v>
       </c>
       <c r="D709" t="n">
-        <v>217.9666421147633</v>
+        <v>217.9666567507444</v>
       </c>
       <c r="E709" t="n">
-        <v>228.7378174391734</v>
+        <v>228.7378327984153</v>
       </c>
       <c r="F709" t="n">
         <v>667500</v>
@@ -14732,16 +14732,16 @@
         <v>44274</v>
       </c>
       <c r="B716" t="n">
-        <v>228.5881958007812</v>
+        <v>228.5882110595703</v>
       </c>
       <c r="C716" t="n">
-        <v>234.5721800637235</v>
+        <v>234.5721957219573</v>
       </c>
       <c r="D716" t="n">
-        <v>225.5962036693101</v>
+        <v>225.5962187283768</v>
       </c>
       <c r="E716" t="n">
-        <v>227.2418084724546</v>
+        <v>227.2418236413692</v>
       </c>
       <c r="F716" t="n">
         <v>1057946</v>
@@ -14972,16 +14972,16 @@
         <v>44293</v>
       </c>
       <c r="B728" t="n">
-        <v>227.6906127929688</v>
+        <v>227.6906280517578</v>
       </c>
       <c r="C728" t="n">
-        <v>230.3834027687316</v>
+        <v>230.3834182079792</v>
       </c>
       <c r="D728" t="n">
-        <v>219.16343185467</v>
+        <v>219.1634465420062</v>
       </c>
       <c r="E728" t="n">
-        <v>219.3130253796337</v>
+        <v>219.313040076995</v>
       </c>
       <c r="F728" t="n">
         <v>1567580</v>
@@ -15052,16 +15052,16 @@
         <v>44299</v>
       </c>
       <c r="B732" t="n">
-        <v>227.2418212890625</v>
+        <v>227.2418365478516</v>
       </c>
       <c r="C732" t="n">
-        <v>227.9898193641179</v>
+        <v>227.9898346731334</v>
       </c>
       <c r="D732" t="n">
-        <v>219.9114340662954</v>
+        <v>219.9114488328651</v>
       </c>
       <c r="E732" t="n">
-        <v>220.6594321413508</v>
+        <v>220.6594469581469</v>
       </c>
       <c r="F732" t="n">
         <v>596393</v>
@@ -15112,16 +15112,16 @@
         <v>44302</v>
       </c>
       <c r="B735" t="n">
-        <v>229.4858245849609</v>
+        <v>229.48583984375</v>
       </c>
       <c r="C735" t="n">
-        <v>229.4858245849609</v>
+        <v>229.48583984375</v>
       </c>
       <c r="D735" t="n">
-        <v>221.108236682369</v>
+        <v>221.1082513841221</v>
       </c>
       <c r="E735" t="n">
-        <v>225.8954275955558</v>
+        <v>225.895442615615</v>
       </c>
       <c r="F735" t="n">
         <v>554213</v>
@@ -15152,16 +15152,16 @@
         <v>44306</v>
       </c>
       <c r="B737" t="n">
-        <v>228.5881958007812</v>
+        <v>228.5882110595703</v>
       </c>
       <c r="C737" t="n">
-        <v>232.627388221879</v>
+        <v>232.6274037502935</v>
       </c>
       <c r="D737" t="n">
-        <v>224.3994098603335</v>
+        <v>224.3994248395114</v>
       </c>
       <c r="E737" t="n">
-        <v>224.3994098603335</v>
+        <v>224.3994248395114</v>
       </c>
       <c r="F737" t="n">
         <v>1126586</v>
@@ -42272,19 +42272,39 @@
         <v>46290</v>
       </c>
       <c r="B2093" t="n">
-        <v>6.26</v>
+        <v>6.260000228881836</v>
       </c>
       <c r="C2093" t="n">
-        <v>6.53</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="D2093" t="n">
-        <v>6.26</v>
+        <v>6.260000228881836</v>
       </c>
       <c r="E2093" t="n">
-        <v>6.47</v>
+        <v>6.46999979019165</v>
       </c>
       <c r="F2093" t="n">
         <v>7282500</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>9224000</v>
       </c>
     </row>
   </sheetData>

--- a/database/HAPV3.xlsx
+++ b/database/HAPV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2096"/>
+  <dimension ref="A1:F2097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43216</v>
       </c>
       <c r="B2" t="n">
-        <v>81.53694915771484</v>
+        <v>81.53695678710938</v>
       </c>
       <c r="C2" t="n">
-        <v>85.6665179138684</v>
+        <v>85.66652592966578</v>
       </c>
       <c r="D2" t="n">
-        <v>79.57467872550245</v>
+        <v>79.57468617128777</v>
       </c>
       <c r="E2" t="n">
-        <v>84.93432545306611</v>
+        <v>84.9343334003524</v>
       </c>
       <c r="F2" t="n">
         <v>1956933</v>
@@ -472,16 +472,16 @@
         <v>43217</v>
       </c>
       <c r="B3" t="n">
-        <v>82.00557708740234</v>
+        <v>82.00556182861328</v>
       </c>
       <c r="C3" t="n">
-        <v>83.90927500477466</v>
+        <v>83.90925939176427</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54119178227016</v>
+        <v>80.54117679595947</v>
       </c>
       <c r="E3" t="n">
-        <v>81.97629057301951</v>
+        <v>81.9762753196798</v>
       </c>
       <c r="F3" t="n">
         <v>932166</v>
@@ -492,16 +492,16 @@
         <v>43220</v>
       </c>
       <c r="B4" t="n">
-        <v>80.98049163818359</v>
+        <v>80.98048400878906</v>
       </c>
       <c r="C4" t="n">
-        <v>82.00556416960269</v>
+        <v>82.00555644363325</v>
       </c>
       <c r="D4" t="n">
-        <v>80.68761909224075</v>
+        <v>80.68761149043854</v>
       </c>
       <c r="E4" t="n">
-        <v>81.56624417831694</v>
+        <v>81.56623649373705</v>
       </c>
       <c r="F4" t="n">
         <v>370366</v>
@@ -512,16 +512,16 @@
         <v>43222</v>
       </c>
       <c r="B5" t="n">
-        <v>79.98470306396484</v>
+        <v>79.98471832275391</v>
       </c>
       <c r="C5" t="n">
-        <v>81.8591139373253</v>
+        <v>81.85912955369824</v>
       </c>
       <c r="D5" t="n">
-        <v>79.07678413339232</v>
+        <v>79.07679921897648</v>
       </c>
       <c r="E5" t="n">
-        <v>79.07678413339232</v>
+        <v>79.07679921897648</v>
       </c>
       <c r="F5" t="n">
         <v>428333</v>
@@ -552,16 +552,16 @@
         <v>43224</v>
       </c>
       <c r="B7" t="n">
-        <v>78.3446044921875</v>
+        <v>78.34458160400391</v>
       </c>
       <c r="C7" t="n">
-        <v>81.0390752181759</v>
+        <v>81.0390515428093</v>
       </c>
       <c r="D7" t="n">
-        <v>77.31953192140176</v>
+        <v>77.3195093326906</v>
       </c>
       <c r="E7" t="n">
-        <v>81.0390752181759</v>
+        <v>81.0390515428093</v>
       </c>
       <c r="F7" t="n">
         <v>632800</v>
@@ -572,16 +572,16 @@
         <v>43227</v>
       </c>
       <c r="B8" t="n">
-        <v>79.07679748535156</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C8" t="n">
-        <v>79.07679748535156</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="D8" t="n">
-        <v>77.90528490550868</v>
+        <v>77.90527738914264</v>
       </c>
       <c r="E8" t="n">
-        <v>78.05172490902004</v>
+        <v>78.05171737852535</v>
       </c>
       <c r="F8" t="n">
         <v>375200</v>
@@ -592,16 +592,16 @@
         <v>43228</v>
       </c>
       <c r="B9" t="n">
-        <v>79.07679748535156</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C9" t="n">
-        <v>79.95543005817173</v>
+        <v>79.95542234400601</v>
       </c>
       <c r="D9" t="n">
-        <v>78.49104491955411</v>
+        <v>78.49103734667347</v>
       </c>
       <c r="E9" t="n">
-        <v>79.51611004763765</v>
+        <v>79.51610237585788</v>
       </c>
       <c r="F9" t="n">
         <v>315733</v>
@@ -612,16 +612,16 @@
         <v>43229</v>
       </c>
       <c r="B10" t="n">
-        <v>78.78390502929688</v>
+        <v>78.78391265869141</v>
       </c>
       <c r="C10" t="n">
-        <v>79.34037099611173</v>
+        <v>79.34037867939415</v>
       </c>
       <c r="D10" t="n">
-        <v>77.81741307603882</v>
+        <v>77.81742061183874</v>
       </c>
       <c r="E10" t="n">
-        <v>79.07678499004018</v>
+        <v>79.07679264779708</v>
       </c>
       <c r="F10" t="n">
         <v>333066</v>
@@ -672,16 +672,16 @@
         <v>43234</v>
       </c>
       <c r="B13" t="n">
-        <v>80.01399230957031</v>
+        <v>80.01399993896484</v>
       </c>
       <c r="C13" t="n">
-        <v>81.82983023288553</v>
+        <v>81.82983803542157</v>
       </c>
       <c r="D13" t="n">
-        <v>80.01399230957031</v>
+        <v>80.01399993896484</v>
       </c>
       <c r="E13" t="n">
-        <v>81.6833902490865</v>
+        <v>81.68339803765939</v>
       </c>
       <c r="F13" t="n">
         <v>350433</v>
@@ -692,16 +692,16 @@
         <v>43235</v>
       </c>
       <c r="B14" t="n">
-        <v>84.78787994384766</v>
+        <v>84.78789520263672</v>
       </c>
       <c r="C14" t="n">
-        <v>85.22719241239105</v>
+        <v>85.22720775024067</v>
       </c>
       <c r="D14" t="n">
-        <v>82.00555026383122</v>
+        <v>82.00556502190037</v>
       </c>
       <c r="E14" t="n">
-        <v>82.29842276011136</v>
+        <v>82.29843757088707</v>
       </c>
       <c r="F14" t="n">
         <v>900866</v>
@@ -712,16 +712,16 @@
         <v>43236</v>
       </c>
       <c r="B15" t="n">
-        <v>87.306640625</v>
+        <v>87.30662536621094</v>
       </c>
       <c r="C15" t="n">
-        <v>87.306640625</v>
+        <v>87.30662536621094</v>
       </c>
       <c r="D15" t="n">
-        <v>83.61639133660867</v>
+        <v>83.61637672277325</v>
       </c>
       <c r="E15" t="n">
-        <v>84.78789644623366</v>
+        <v>84.7878816276515</v>
       </c>
       <c r="F15" t="n">
         <v>589600</v>
@@ -752,16 +752,16 @@
         <v>43238</v>
       </c>
       <c r="B17" t="n">
-        <v>86.69158935546875</v>
+        <v>86.69158172607422</v>
       </c>
       <c r="C17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74172654739176</v>
       </c>
       <c r="D17" t="n">
-        <v>85.60795128505117</v>
+        <v>85.60794375102347</v>
       </c>
       <c r="E17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74172654739176</v>
       </c>
       <c r="F17" t="n">
         <v>980066</v>
@@ -772,16 +772,16 @@
         <v>43241</v>
       </c>
       <c r="B18" t="n">
-        <v>90.20612335205078</v>
+        <v>90.20610809326172</v>
       </c>
       <c r="C18" t="n">
-        <v>91.05546194037015</v>
+        <v>91.05544653791148</v>
       </c>
       <c r="D18" t="n">
-        <v>84.93433551979336</v>
+        <v>84.93432115275195</v>
       </c>
       <c r="E18" t="n">
-        <v>86.9844731633802</v>
+        <v>86.98445844954838</v>
       </c>
       <c r="F18" t="n">
         <v>633933</v>
@@ -792,16 +792,16 @@
         <v>43242</v>
       </c>
       <c r="B19" t="n">
-        <v>95.91722106933594</v>
+        <v>95.91721343994141</v>
       </c>
       <c r="C19" t="n">
-        <v>96.06366106443481</v>
+        <v>96.06365342339224</v>
       </c>
       <c r="D19" t="n">
-        <v>90.2061208464601</v>
+        <v>90.20611367133475</v>
       </c>
       <c r="E19" t="n">
-        <v>90.2061208464601</v>
+        <v>90.20611367133475</v>
       </c>
       <c r="F19" t="n">
         <v>462766</v>
@@ -812,16 +812,16 @@
         <v>43243</v>
       </c>
       <c r="B20" t="n">
-        <v>95.74149322509766</v>
+        <v>95.74148559570312</v>
       </c>
       <c r="C20" t="n">
-        <v>95.91721972710775</v>
+        <v>95.91721208371003</v>
       </c>
       <c r="D20" t="n">
-        <v>90.79187210810198</v>
+        <v>90.79186487313009</v>
       </c>
       <c r="E20" t="n">
-        <v>95.91721972710775</v>
+        <v>95.91721208371003</v>
       </c>
       <c r="F20" t="n">
         <v>487666</v>
@@ -832,16 +832,16 @@
         <v>43244</v>
       </c>
       <c r="B21" t="n">
-        <v>89.32749176025391</v>
+        <v>89.32748413085938</v>
       </c>
       <c r="C21" t="n">
-        <v>93.77922011371906</v>
+        <v>93.77921210410572</v>
       </c>
       <c r="D21" t="n">
-        <v>89.0931922280315</v>
+        <v>89.09318461864831</v>
       </c>
       <c r="E21" t="n">
-        <v>93.13489453804544</v>
+        <v>93.13488658346348</v>
       </c>
       <c r="F21" t="n">
         <v>822100</v>
@@ -852,16 +852,16 @@
         <v>43245</v>
       </c>
       <c r="B22" t="n">
-        <v>90.76259613037109</v>
+        <v>90.76258087158203</v>
       </c>
       <c r="C22" t="n">
-        <v>90.87974217980538</v>
+        <v>90.879726901322</v>
       </c>
       <c r="D22" t="n">
-        <v>87.95097177197539</v>
+        <v>87.95095698586984</v>
       </c>
       <c r="E22" t="n">
-        <v>88.7710313592569</v>
+        <v>88.77101643528491</v>
       </c>
       <c r="F22" t="n">
         <v>562433</v>
@@ -872,16 +872,16 @@
         <v>43248</v>
       </c>
       <c r="B23" t="n">
-        <v>86.39872741699219</v>
+        <v>86.39871978759766</v>
       </c>
       <c r="C23" t="n">
-        <v>90.76259653587526</v>
+        <v>90.76258852113153</v>
       </c>
       <c r="D23" t="n">
-        <v>85.02220174400294</v>
+        <v>85.02219423616178</v>
       </c>
       <c r="E23" t="n">
-        <v>90.76259653587526</v>
+        <v>90.76258852113153</v>
       </c>
       <c r="F23" t="n">
         <v>427433</v>
@@ -932,16 +932,16 @@
         <v>43252</v>
       </c>
       <c r="B26" t="n">
-        <v>87.54093170166016</v>
+        <v>87.54093933105469</v>
       </c>
       <c r="C26" t="n">
-        <v>90.76258161432011</v>
+        <v>90.76258952448887</v>
       </c>
       <c r="D26" t="n">
-        <v>84.90504173548175</v>
+        <v>84.90504913515237</v>
       </c>
       <c r="E26" t="n">
-        <v>89.70822264854989</v>
+        <v>89.70823046682885</v>
       </c>
       <c r="F26" t="n">
         <v>391033</v>
@@ -972,16 +972,16 @@
         <v>43256</v>
       </c>
       <c r="B28" t="n">
-        <v>85.72509765625</v>
+        <v>85.72510528564453</v>
       </c>
       <c r="C28" t="n">
-        <v>88.15597473141518</v>
+        <v>88.15598257715384</v>
       </c>
       <c r="D28" t="n">
-        <v>84.34857959498085</v>
+        <v>84.34858710186751</v>
       </c>
       <c r="E28" t="n">
-        <v>88.15597473141518</v>
+        <v>88.15598257715384</v>
       </c>
       <c r="F28" t="n">
         <v>239700</v>
@@ -992,16 +992,16 @@
         <v>43257</v>
       </c>
       <c r="B29" t="n">
-        <v>83.411376953125</v>
+        <v>83.41136932373047</v>
       </c>
       <c r="C29" t="n">
-        <v>85.46151458562363</v>
+        <v>85.46150676870901</v>
       </c>
       <c r="D29" t="n">
-        <v>81.71268488917815</v>
+        <v>81.71267741515801</v>
       </c>
       <c r="E29" t="n">
-        <v>84.99290808047505</v>
+        <v>84.9929003064225</v>
       </c>
       <c r="F29" t="n">
         <v>443766</v>
@@ -1032,16 +1032,16 @@
         <v>43259</v>
       </c>
       <c r="B31" t="n">
-        <v>80.98049163818359</v>
+        <v>80.98048400878906</v>
       </c>
       <c r="C31" t="n">
-        <v>83.14778274009986</v>
+        <v>83.14777490651888</v>
       </c>
       <c r="D31" t="n">
-        <v>79.07679402068831</v>
+        <v>79.07678657064635</v>
       </c>
       <c r="E31" t="n">
-        <v>79.75041353837787</v>
+        <v>79.75040602487236</v>
       </c>
       <c r="F31" t="n">
         <v>443000</v>
@@ -1072,16 +1072,16 @@
         <v>43263</v>
       </c>
       <c r="B33" t="n">
-        <v>82.23985290527344</v>
+        <v>82.23986053466797</v>
       </c>
       <c r="C33" t="n">
-        <v>83.38207132589955</v>
+        <v>83.38207906125773</v>
       </c>
       <c r="D33" t="n">
-        <v>80.0725620877285</v>
+        <v>80.07256951606338</v>
       </c>
       <c r="E33" t="n">
-        <v>81.41980094633571</v>
+        <v>81.419808499654</v>
       </c>
       <c r="F33" t="n">
         <v>203566</v>
@@ -1092,16 +1092,16 @@
         <v>43264</v>
       </c>
       <c r="B34" t="n">
-        <v>78.31531524658203</v>
+        <v>78.3153076171875</v>
       </c>
       <c r="C34" t="n">
-        <v>82.32773096043591</v>
+        <v>82.32772294015612</v>
       </c>
       <c r="D34" t="n">
-        <v>77.70026874628836</v>
+        <v>77.70026117681101</v>
       </c>
       <c r="E34" t="n">
-        <v>82.32773096043591</v>
+        <v>82.32772294015612</v>
       </c>
       <c r="F34" t="n">
         <v>786033</v>
@@ -1112,16 +1112,16 @@
         <v>43265</v>
       </c>
       <c r="B35" t="n">
-        <v>79.13535308837891</v>
+        <v>79.13536834716797</v>
       </c>
       <c r="C35" t="n">
-        <v>80.21899844828646</v>
+        <v>80.21901391602279</v>
       </c>
       <c r="D35" t="n">
-        <v>77.90526775719401</v>
+        <v>77.90528277879942</v>
       </c>
       <c r="E35" t="n">
-        <v>78.19814769974872</v>
+        <v>78.19816277782689</v>
       </c>
       <c r="F35" t="n">
         <v>536566</v>
@@ -1132,16 +1132,16 @@
         <v>43266</v>
       </c>
       <c r="B36" t="n">
-        <v>79.07679748535156</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C36" t="n">
-        <v>79.22323748886292</v>
+        <v>79.22322984533973</v>
       </c>
       <c r="D36" t="n">
-        <v>75.12295463178479</v>
+        <v>75.12294738386028</v>
       </c>
       <c r="E36" t="n">
-        <v>79.13537050745691</v>
+        <v>79.13536287241121</v>
       </c>
       <c r="F36" t="n">
         <v>389566</v>
@@ -1192,16 +1192,16 @@
         <v>43271</v>
       </c>
       <c r="B39" t="n">
-        <v>84.34856414794922</v>
+        <v>84.34857177734375</v>
       </c>
       <c r="C39" t="n">
-        <v>85.52006898334939</v>
+        <v>85.52007671870746</v>
       </c>
       <c r="D39" t="n">
-        <v>81.71266709592969</v>
+        <v>81.71267448690524</v>
       </c>
       <c r="E39" t="n">
-        <v>82.03483353255086</v>
+        <v>82.03484095266663</v>
       </c>
       <c r="F39" t="n">
         <v>141600</v>
@@ -1232,16 +1232,16 @@
         <v>43273</v>
       </c>
       <c r="B41" t="n">
-        <v>84.934326171875</v>
+        <v>84.93433380126953</v>
       </c>
       <c r="C41" t="n">
-        <v>85.52007865582475</v>
+        <v>85.52008633783566</v>
       </c>
       <c r="D41" t="n">
-        <v>81.21479082295949</v>
+        <v>81.21479811823937</v>
       </c>
       <c r="E41" t="n">
-        <v>82.03484281083975</v>
+        <v>82.03485017978244</v>
       </c>
       <c r="F41" t="n">
         <v>298800</v>
@@ -1252,16 +1252,16 @@
         <v>43276</v>
       </c>
       <c r="B42" t="n">
-        <v>86.39872741699219</v>
+        <v>86.39871978759766</v>
       </c>
       <c r="C42" t="n">
-        <v>86.39872741699219</v>
+        <v>86.39871978759766</v>
       </c>
       <c r="D42" t="n">
-        <v>84.34858961200136</v>
+        <v>84.34858216364319</v>
       </c>
       <c r="E42" t="n">
-        <v>85.8715478474377</v>
+        <v>85.87154026459547</v>
       </c>
       <c r="F42" t="n">
         <v>909166</v>
@@ -1312,16 +1312,16 @@
         <v>43279</v>
       </c>
       <c r="B45" t="n">
-        <v>88.68315124511719</v>
+        <v>88.68315887451172</v>
       </c>
       <c r="C45" t="n">
-        <v>88.68315124511719</v>
+        <v>88.68315887451172</v>
       </c>
       <c r="D45" t="n">
-        <v>85.373641770075</v>
+        <v>85.37364911475306</v>
       </c>
       <c r="E45" t="n">
-        <v>87.86309922748598</v>
+        <v>87.8631067863316</v>
       </c>
       <c r="F45" t="n">
         <v>922066</v>
@@ -1332,16 +1332,16 @@
         <v>43280</v>
       </c>
       <c r="B46" t="n">
-        <v>87.54093170166016</v>
+        <v>87.54093933105469</v>
       </c>
       <c r="C46" t="n">
-        <v>89.41534267530913</v>
+        <v>89.41535046806291</v>
       </c>
       <c r="D46" t="n">
-        <v>85.37364075477042</v>
+        <v>85.37364819528054</v>
       </c>
       <c r="E46" t="n">
-        <v>87.45307217863621</v>
+        <v>87.45307980037357</v>
       </c>
       <c r="F46" t="n">
         <v>492266</v>
@@ -1352,16 +1352,16 @@
         <v>43283</v>
       </c>
       <c r="B47" t="n">
-        <v>86.1058349609375</v>
+        <v>86.10582733154297</v>
       </c>
       <c r="C47" t="n">
-        <v>86.95518094171702</v>
+        <v>86.9551732370663</v>
       </c>
       <c r="D47" t="n">
-        <v>85.87153544660936</v>
+        <v>85.8715278379749</v>
       </c>
       <c r="E47" t="n">
-        <v>86.04726194441729</v>
+        <v>86.0472543202126</v>
       </c>
       <c r="F47" t="n">
         <v>88033</v>
@@ -1392,16 +1392,16 @@
         <v>43285</v>
       </c>
       <c r="B49" t="n">
-        <v>85.78367614746094</v>
+        <v>85.78368377685547</v>
       </c>
       <c r="C49" t="n">
-        <v>87.07233465202611</v>
+        <v>87.07234239603083</v>
       </c>
       <c r="D49" t="n">
-        <v>84.14356464635551</v>
+        <v>84.14357212988246</v>
       </c>
       <c r="E49" t="n">
-        <v>86.66230119056429</v>
+        <v>86.66230889810163</v>
       </c>
       <c r="F49" t="n">
         <v>320933</v>
@@ -1432,16 +1432,16 @@
         <v>43287</v>
       </c>
       <c r="B51" t="n">
-        <v>83.61638641357422</v>
+        <v>83.61637115478516</v>
       </c>
       <c r="C51" t="n">
-        <v>85.57865698425219</v>
+        <v>85.57864136737695</v>
       </c>
       <c r="D51" t="n">
-        <v>83.61638641357422</v>
+        <v>83.61637115478516</v>
       </c>
       <c r="E51" t="n">
-        <v>85.52008396669386</v>
+        <v>85.52006836050735</v>
       </c>
       <c r="F51" t="n">
         <v>769100</v>
@@ -1472,16 +1472,16 @@
         <v>43292</v>
       </c>
       <c r="B53" t="n">
-        <v>84.08497619628906</v>
+        <v>84.08499145507812</v>
       </c>
       <c r="C53" t="n">
-        <v>86.25226698638772</v>
+        <v>86.25228263847217</v>
       </c>
       <c r="D53" t="n">
-        <v>82.64987783807528</v>
+        <v>82.64989283643895</v>
       </c>
       <c r="E53" t="n">
-        <v>83.79210369248307</v>
+        <v>83.79211889812494</v>
       </c>
       <c r="F53" t="n">
         <v>271833</v>
@@ -1492,16 +1492,16 @@
         <v>43293</v>
       </c>
       <c r="B54" t="n">
-        <v>87.07231903076172</v>
+        <v>87.07233428955078</v>
       </c>
       <c r="C54" t="n">
-        <v>87.13089203692768</v>
+        <v>87.13090730598122</v>
       </c>
       <c r="D54" t="n">
-        <v>82.35699838000778</v>
+        <v>82.35701281247128</v>
       </c>
       <c r="E54" t="n">
-        <v>83.90924262937314</v>
+        <v>83.90925733385612</v>
       </c>
       <c r="F54" t="n">
         <v>235333</v>
@@ -1512,16 +1512,16 @@
         <v>43294</v>
       </c>
       <c r="B55" t="n">
-        <v>84.40716552734375</v>
+        <v>84.40715026855469</v>
       </c>
       <c r="C55" t="n">
-        <v>87.57023560473576</v>
+        <v>87.57021977413956</v>
       </c>
       <c r="D55" t="n">
-        <v>83.96785292846242</v>
+        <v>83.96783774909052</v>
       </c>
       <c r="E55" t="n">
-        <v>87.10163649236213</v>
+        <v>87.10162074647741</v>
       </c>
       <c r="F55" t="n">
         <v>222900</v>
@@ -1532,16 +1532,16 @@
         <v>43297</v>
       </c>
       <c r="B56" t="n">
-        <v>83.46994781494141</v>
+        <v>83.46994018554688</v>
       </c>
       <c r="C56" t="n">
-        <v>86.017978396731</v>
+        <v>86.0179705344391</v>
       </c>
       <c r="D56" t="n">
-        <v>82.91348179410504</v>
+        <v>82.9134742155731</v>
       </c>
       <c r="E56" t="n">
-        <v>84.43643986202616</v>
+        <v>84.43643214429146</v>
       </c>
       <c r="F56" t="n">
         <v>173400</v>
@@ -1552,16 +1552,16 @@
         <v>43298</v>
       </c>
       <c r="B57" t="n">
-        <v>83.08919525146484</v>
+        <v>83.08921051025391</v>
       </c>
       <c r="C57" t="n">
-        <v>84.58286657558465</v>
+        <v>84.58288210867671</v>
       </c>
       <c r="D57" t="n">
-        <v>82.35700284173974</v>
+        <v>82.35701796606644</v>
       </c>
       <c r="E57" t="n">
-        <v>84.11426015613218</v>
+        <v>84.11427560316773</v>
       </c>
       <c r="F57" t="n">
         <v>152666</v>
@@ -1592,16 +1592,16 @@
         <v>43300</v>
       </c>
       <c r="B59" t="n">
-        <v>85.19791412353516</v>
+        <v>85.19790649414062</v>
       </c>
       <c r="C59" t="n">
-        <v>86.5451530603807</v>
+        <v>86.54514531034216</v>
       </c>
       <c r="D59" t="n">
-        <v>83.61638312566897</v>
+        <v>83.6163756378991</v>
       </c>
       <c r="E59" t="n">
-        <v>85.52008060393275</v>
+        <v>85.52007294568851</v>
       </c>
       <c r="F59" t="n">
         <v>169366</v>
@@ -1652,16 +1652,16 @@
         <v>43305</v>
       </c>
       <c r="B62" t="n">
-        <v>88.15596771240234</v>
+        <v>88.15598297119141</v>
       </c>
       <c r="C62" t="n">
-        <v>88.71244113230262</v>
+        <v>88.71245648741085</v>
       </c>
       <c r="D62" t="n">
-        <v>87.10161623070165</v>
+        <v>87.10163130699453</v>
       </c>
       <c r="E62" t="n">
-        <v>88.18526166732883</v>
+        <v>88.18527693118834</v>
       </c>
       <c r="F62" t="n">
         <v>140566</v>
@@ -1672,16 +1672,16 @@
         <v>43306</v>
       </c>
       <c r="B63" t="n">
-        <v>83.99712371826172</v>
+        <v>83.99713134765625</v>
       </c>
       <c r="C63" t="n">
-        <v>89.91323668020036</v>
+        <v>89.9132448469509</v>
       </c>
       <c r="D63" t="n">
-        <v>83.99712371826172</v>
+        <v>83.99713134765625</v>
       </c>
       <c r="E63" t="n">
-        <v>88.77101817832556</v>
+        <v>88.77102624132928</v>
       </c>
       <c r="F63" t="n">
         <v>653300</v>
@@ -1692,16 +1692,16 @@
         <v>43307</v>
       </c>
       <c r="B64" t="n">
-        <v>80.57045745849609</v>
+        <v>80.57044982910156</v>
       </c>
       <c r="C64" t="n">
-        <v>84.84645876219862</v>
+        <v>84.84645072790009</v>
       </c>
       <c r="D64" t="n">
-        <v>79.95541847077936</v>
+        <v>79.95541089962423</v>
       </c>
       <c r="E64" t="n">
-        <v>84.14356025405675</v>
+        <v>84.14355228631722</v>
       </c>
       <c r="F64" t="n">
         <v>454233</v>
@@ -1752,16 +1752,16 @@
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>82.47416687011719</v>
+        <v>82.47415924072266</v>
       </c>
       <c r="C67" t="n">
-        <v>82.56203385155962</v>
+        <v>82.56202621403682</v>
       </c>
       <c r="D67" t="n">
-        <v>79.36967007703086</v>
+        <v>79.3696627348224</v>
       </c>
       <c r="E67" t="n">
-        <v>81.24408871590697</v>
+        <v>81.24408120030263</v>
       </c>
       <c r="F67" t="n">
         <v>430700</v>
@@ -1792,16 +1792,16 @@
         <v>43314</v>
       </c>
       <c r="B69" t="n">
-        <v>84.75860595703125</v>
+        <v>84.75861358642578</v>
       </c>
       <c r="C69" t="n">
-        <v>84.75860595703125</v>
+        <v>84.75861358642578</v>
       </c>
       <c r="D69" t="n">
-        <v>83.2356478963592</v>
+        <v>83.23565538866737</v>
       </c>
       <c r="E69" t="n">
-        <v>83.2356478963592</v>
+        <v>83.23565538866737</v>
       </c>
       <c r="F69" t="n">
         <v>63600</v>
@@ -1812,16 +1812,16 @@
         <v>43315</v>
       </c>
       <c r="B70" t="n">
-        <v>83.90926361083984</v>
+        <v>83.90925598144531</v>
       </c>
       <c r="C70" t="n">
-        <v>84.75860965385445</v>
+        <v>84.75860194723369</v>
       </c>
       <c r="D70" t="n">
-        <v>83.52852407906553</v>
+        <v>83.52851648428948</v>
       </c>
       <c r="E70" t="n">
-        <v>84.75860965385445</v>
+        <v>84.75860194723369</v>
       </c>
       <c r="F70" t="n">
         <v>171233</v>
@@ -1852,16 +1852,16 @@
         <v>43319</v>
       </c>
       <c r="B72" t="n">
-        <v>79.13535308837891</v>
+        <v>79.13536834716797</v>
       </c>
       <c r="C72" t="n">
-        <v>81.41979727486515</v>
+        <v>81.41981297413815</v>
       </c>
       <c r="D72" t="n">
-        <v>79.13535308837891</v>
+        <v>79.13536834716797</v>
       </c>
       <c r="E72" t="n">
-        <v>81.27335730358779</v>
+        <v>81.27337297462441</v>
       </c>
       <c r="F72" t="n">
         <v>212866</v>
@@ -1872,16 +1872,16 @@
         <v>43320</v>
       </c>
       <c r="B73" t="n">
-        <v>78.78390502929688</v>
+        <v>78.78391265869141</v>
       </c>
       <c r="C73" t="n">
-        <v>80.24828993651984</v>
+        <v>80.24829770772469</v>
       </c>
       <c r="D73" t="n">
-        <v>77.11450712885231</v>
+        <v>77.11451459658318</v>
       </c>
       <c r="E73" t="n">
-        <v>79.7796909372267</v>
+        <v>79.77969866305264</v>
       </c>
       <c r="F73" t="n">
         <v>270133</v>
@@ -1892,16 +1892,16 @@
         <v>43321</v>
       </c>
       <c r="B74" t="n">
-        <v>78.95963287353516</v>
+        <v>78.95964813232422</v>
       </c>
       <c r="C74" t="n">
-        <v>79.1353593633528</v>
+        <v>79.13537465610065</v>
       </c>
       <c r="D74" t="n">
-        <v>76.85092244397033</v>
+        <v>76.85093729525538</v>
       </c>
       <c r="E74" t="n">
-        <v>78.19815390040766</v>
+        <v>78.19816901204246</v>
       </c>
       <c r="F74" t="n">
         <v>546266</v>
@@ -1932,16 +1932,16 @@
         <v>43325</v>
       </c>
       <c r="B76" t="n">
-        <v>79.07679748535156</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C76" t="n">
-        <v>80.10186261343512</v>
+        <v>80.10185488514145</v>
       </c>
       <c r="D76" t="n">
-        <v>77.75885235024531</v>
+        <v>77.7588448480072</v>
       </c>
       <c r="E76" t="n">
-        <v>78.9303574818402</v>
+        <v>78.93034986657432</v>
       </c>
       <c r="F76" t="n">
         <v>160400</v>
@@ -1952,16 +1952,16 @@
         <v>43326</v>
       </c>
       <c r="B77" t="n">
-        <v>77.46596527099609</v>
+        <v>77.46595764160156</v>
       </c>
       <c r="C77" t="n">
-        <v>78.46175124536504</v>
+        <v>78.46174351789847</v>
       </c>
       <c r="D77" t="n">
-        <v>74.4493357360049</v>
+        <v>74.44932840370932</v>
       </c>
       <c r="E77" t="n">
-        <v>78.46175124536504</v>
+        <v>78.46174351789847</v>
       </c>
       <c r="F77" t="n">
         <v>524933</v>
@@ -1972,16 +1972,16 @@
         <v>43327</v>
       </c>
       <c r="B78" t="n">
-        <v>76.14802551269531</v>
+        <v>76.14801025390625</v>
       </c>
       <c r="C78" t="n">
-        <v>77.67098363950991</v>
+        <v>77.67096807554556</v>
       </c>
       <c r="D78" t="n">
-        <v>76.14802551269531</v>
+        <v>76.14801025390625</v>
       </c>
       <c r="E78" t="n">
-        <v>77.0266580659529</v>
+        <v>77.02664263110059</v>
       </c>
       <c r="F78" t="n">
         <v>702366</v>
@@ -2032,16 +2032,16 @@
         <v>43332</v>
       </c>
       <c r="B81" t="n">
-        <v>72.34061431884766</v>
+        <v>72.34060668945312</v>
       </c>
       <c r="C81" t="n">
-        <v>73.01423377256823</v>
+        <v>73.0142260721305</v>
       </c>
       <c r="D81" t="n">
-        <v>71.75486183433918</v>
+        <v>71.75485426672097</v>
       </c>
       <c r="E81" t="n">
-        <v>71.95987483150479</v>
+        <v>71.95986724226492</v>
       </c>
       <c r="F81" t="n">
         <v>425766</v>
@@ -2052,16 +2052,16 @@
         <v>43333</v>
       </c>
       <c r="B82" t="n">
-        <v>71.60842132568359</v>
+        <v>71.60842895507812</v>
       </c>
       <c r="C82" t="n">
-        <v>72.57491329044277</v>
+        <v>72.5749210228105</v>
       </c>
       <c r="D82" t="n">
-        <v>70.31976288992242</v>
+        <v>70.31977038201907</v>
       </c>
       <c r="E82" t="n">
-        <v>71.63770783245707</v>
+        <v>71.63771546497189</v>
       </c>
       <c r="F82" t="n">
         <v>1384333</v>
@@ -2092,16 +2092,16 @@
         <v>43335</v>
       </c>
       <c r="B84" t="n">
-        <v>73.36569213867188</v>
+        <v>73.36568450927734</v>
       </c>
       <c r="C84" t="n">
-        <v>74.33218418147305</v>
+        <v>74.33217645157174</v>
       </c>
       <c r="D84" t="n">
-        <v>71.90130709577721</v>
+        <v>71.901299618666</v>
       </c>
       <c r="E84" t="n">
-        <v>72.57491915070047</v>
+        <v>72.57491160353946</v>
       </c>
       <c r="F84" t="n">
         <v>126566</v>
@@ -2112,16 +2112,16 @@
         <v>43336</v>
       </c>
       <c r="B85" t="n">
-        <v>75.29869079589844</v>
+        <v>75.29866790771484</v>
       </c>
       <c r="C85" t="n">
-        <v>75.56228432564806</v>
+        <v>75.5622613573412</v>
       </c>
       <c r="D85" t="n">
-        <v>73.21926631395182</v>
+        <v>73.21924405784095</v>
       </c>
       <c r="E85" t="n">
-        <v>74.09789899936904</v>
+        <v>74.09787647618438</v>
       </c>
       <c r="F85" t="n">
         <v>164200</v>
@@ -2132,16 +2132,16 @@
         <v>43339</v>
       </c>
       <c r="B86" t="n">
-        <v>76.03086090087891</v>
+        <v>76.03086853027344</v>
       </c>
       <c r="C86" t="n">
-        <v>76.44088688300364</v>
+        <v>76.44089455354266</v>
       </c>
       <c r="D86" t="n">
-        <v>73.6585570782333</v>
+        <v>73.65856446957658</v>
       </c>
       <c r="E86" t="n">
-        <v>75.29866845497898</v>
+        <v>75.29867601090092</v>
       </c>
       <c r="F86" t="n">
         <v>318500</v>
@@ -2172,16 +2172,16 @@
         <v>43341</v>
       </c>
       <c r="B88" t="n">
-        <v>74.4200439453125</v>
+        <v>74.42003631591797</v>
       </c>
       <c r="C88" t="n">
-        <v>76.14802247243639</v>
+        <v>76.14801466589296</v>
       </c>
       <c r="D88" t="n">
-        <v>73.45355189944088</v>
+        <v>73.45354436912919</v>
       </c>
       <c r="E88" t="n">
-        <v>75.6794159799925</v>
+        <v>75.67940822148965</v>
       </c>
       <c r="F88" t="n">
         <v>162200</v>
@@ -2192,16 +2192,16 @@
         <v>43342</v>
       </c>
       <c r="B89" t="n">
-        <v>75.85514068603516</v>
+        <v>75.85514831542969</v>
       </c>
       <c r="C89" t="n">
-        <v>75.85514068603516</v>
+        <v>75.85514831542969</v>
       </c>
       <c r="D89" t="n">
-        <v>73.39497714168559</v>
+        <v>73.39498452364062</v>
       </c>
       <c r="E89" t="n">
-        <v>74.18574266518235</v>
+        <v>74.18575012667137</v>
       </c>
       <c r="F89" t="n">
         <v>206466</v>
@@ -2252,16 +2252,16 @@
         <v>43347</v>
       </c>
       <c r="B92" t="n">
-        <v>73.04351806640625</v>
+        <v>73.04352569580078</v>
       </c>
       <c r="C92" t="n">
-        <v>74.42003599088163</v>
+        <v>74.42004376405343</v>
       </c>
       <c r="D92" t="n">
-        <v>71.87201313288479</v>
+        <v>71.87202063991565</v>
       </c>
       <c r="E92" t="n">
-        <v>74.3907494847806</v>
+        <v>74.39075725489343</v>
       </c>
       <c r="F92" t="n">
         <v>196200</v>
@@ -2272,16 +2272,16 @@
         <v>43348</v>
       </c>
       <c r="B93" t="n">
-        <v>73.24852752685547</v>
+        <v>73.24854278564453</v>
       </c>
       <c r="C93" t="n">
-        <v>75.65011773859295</v>
+        <v>75.65013349767</v>
       </c>
       <c r="D93" t="n">
-        <v>72.80921506002102</v>
+        <v>72.80923022729456</v>
       </c>
       <c r="E93" t="n">
-        <v>72.89707457408937</v>
+        <v>72.89708975966539</v>
       </c>
       <c r="F93" t="n">
         <v>95400</v>
@@ -2312,16 +2312,16 @@
         <v>43353</v>
       </c>
       <c r="B95" t="n">
-        <v>75.50367736816406</v>
+        <v>75.50368499755859</v>
       </c>
       <c r="C95" t="n">
-        <v>76.73376269634934</v>
+        <v>76.7337704500399</v>
       </c>
       <c r="D95" t="n">
-        <v>74.42003201089904</v>
+        <v>74.42003953079482</v>
       </c>
       <c r="E95" t="n">
-        <v>75.65011733908432</v>
+        <v>75.65012498327611</v>
       </c>
       <c r="F95" t="n">
         <v>157400</v>
@@ -2332,16 +2332,16 @@
         <v>43354</v>
       </c>
       <c r="B96" t="n">
-        <v>73.45354461669922</v>
+        <v>73.45355224609375</v>
       </c>
       <c r="C96" t="n">
-        <v>75.18152297249823</v>
+        <v>75.18153078137257</v>
       </c>
       <c r="D96" t="n">
-        <v>73.45354461669922</v>
+        <v>73.45355224609375</v>
       </c>
       <c r="E96" t="n">
-        <v>74.44933052131992</v>
+        <v>74.44933825414368</v>
       </c>
       <c r="F96" t="n">
         <v>250666</v>
@@ -2352,16 +2352,16 @@
         <v>43355</v>
       </c>
       <c r="B97" t="n">
-        <v>72.95565795898438</v>
+        <v>72.95565032958984</v>
       </c>
       <c r="C97" t="n">
-        <v>74.65434995501845</v>
+        <v>74.65434214798188</v>
       </c>
       <c r="D97" t="n">
-        <v>71.34484038600858</v>
+        <v>71.34483292506654</v>
       </c>
       <c r="E97" t="n">
-        <v>73.21925143516954</v>
+        <v>73.21924377820952</v>
       </c>
       <c r="F97" t="n">
         <v>133333</v>
@@ -2372,16 +2372,16 @@
         <v>43356</v>
       </c>
       <c r="B98" t="n">
-        <v>71.60842132568359</v>
+        <v>71.60842895507812</v>
       </c>
       <c r="C98" t="n">
-        <v>73.86357172620396</v>
+        <v>73.86357959586955</v>
       </c>
       <c r="D98" t="n">
-        <v>70.4369163652632</v>
+        <v>70.43692386984178</v>
       </c>
       <c r="E98" t="n">
-        <v>73.77571220588352</v>
+        <v>73.77572006618828</v>
       </c>
       <c r="F98" t="n">
         <v>250366</v>
@@ -2392,16 +2392,16 @@
         <v>43357</v>
       </c>
       <c r="B99" t="n">
-        <v>69.79257965087891</v>
+        <v>69.79257202148438</v>
       </c>
       <c r="C99" t="n">
-        <v>72.28203686752244</v>
+        <v>72.28202896599223</v>
       </c>
       <c r="D99" t="n">
-        <v>69.7047201353074</v>
+        <v>69.70471251551726</v>
       </c>
       <c r="E99" t="n">
-        <v>70.96409199622441</v>
+        <v>70.96408423876569</v>
       </c>
       <c r="F99" t="n">
         <v>269466</v>
@@ -2412,16 +2412,16 @@
         <v>43360</v>
       </c>
       <c r="B100" t="n">
-        <v>73.48283386230469</v>
+        <v>73.48282623291016</v>
       </c>
       <c r="C100" t="n">
-        <v>74.0685938036806</v>
+        <v>74.06858611346924</v>
       </c>
       <c r="D100" t="n">
-        <v>69.79258496252115</v>
+        <v>69.79257771626868</v>
       </c>
       <c r="E100" t="n">
-        <v>70.02688447012328</v>
+        <v>70.02687719954454</v>
       </c>
       <c r="F100" t="n">
         <v>114333</v>
@@ -2432,16 +2432,16 @@
         <v>43361</v>
       </c>
       <c r="B101" t="n">
-        <v>74.50790405273438</v>
+        <v>74.50789642333984</v>
       </c>
       <c r="C101" t="n">
-        <v>75.35724998338361</v>
+        <v>75.35724226701849</v>
       </c>
       <c r="D101" t="n">
-        <v>73.62927161555359</v>
+        <v>73.62926407612848</v>
       </c>
       <c r="E101" t="n">
-        <v>74.56647706579749</v>
+        <v>74.56646943040525</v>
       </c>
       <c r="F101" t="n">
         <v>194766</v>
@@ -2452,16 +2452,16 @@
         <v>43362</v>
       </c>
       <c r="B102" t="n">
-        <v>68.76752471923828</v>
+        <v>68.76753234863281</v>
       </c>
       <c r="C102" t="n">
-        <v>74.68363797116167</v>
+        <v>74.6836462569178</v>
       </c>
       <c r="D102" t="n">
-        <v>68.76752471923828</v>
+        <v>68.76753234863281</v>
       </c>
       <c r="E102" t="n">
-        <v>73.57070592274535</v>
+        <v>73.57071408502752</v>
       </c>
       <c r="F102" t="n">
         <v>510266</v>
@@ -2472,16 +2472,16 @@
         <v>43363</v>
       </c>
       <c r="B103" t="n">
-        <v>68.24034881591797</v>
+        <v>68.24033355712891</v>
       </c>
       <c r="C103" t="n">
-        <v>69.58758045944499</v>
+        <v>69.58756489941005</v>
       </c>
       <c r="D103" t="n">
-        <v>65.63373761360235</v>
+        <v>65.63372293766099</v>
       </c>
       <c r="E103" t="n">
-        <v>69.41185394522425</v>
+        <v>69.4118384244824</v>
       </c>
       <c r="F103" t="n">
         <v>1256966</v>
@@ -2492,16 +2492,16 @@
         <v>43364</v>
       </c>
       <c r="B104" t="n">
-        <v>69.353271484375</v>
+        <v>69.35327911376953</v>
       </c>
       <c r="C104" t="n">
-        <v>71.16910940144096</v>
+        <v>71.16911723059167</v>
       </c>
       <c r="D104" t="n">
-        <v>67.88888654791837</v>
+        <v>67.88889401621928</v>
       </c>
       <c r="E104" t="n">
-        <v>67.94745956193762</v>
+        <v>67.94746703668201</v>
       </c>
       <c r="F104" t="n">
         <v>293166</v>
@@ -2512,16 +2512,16 @@
         <v>43367</v>
       </c>
       <c r="B105" t="n">
-        <v>65.4580078125</v>
+        <v>65.45800018310547</v>
       </c>
       <c r="C105" t="n">
-        <v>69.49971743662823</v>
+        <v>69.49970933615616</v>
       </c>
       <c r="D105" t="n">
-        <v>65.37014828392535</v>
+        <v>65.37014066477121</v>
       </c>
       <c r="E105" t="n">
-        <v>69.35327744075623</v>
+        <v>69.35326935735233</v>
       </c>
       <c r="F105" t="n">
         <v>831466</v>
@@ -2592,16 +2592,16 @@
         <v>43371</v>
       </c>
       <c r="B109" t="n">
-        <v>70.29047393798828</v>
+        <v>70.29048919677734</v>
       </c>
       <c r="C109" t="n">
-        <v>71.3448328346373</v>
+        <v>71.34484832230859</v>
       </c>
       <c r="D109" t="n">
-        <v>67.3324176848174</v>
+        <v>67.33243230146601</v>
       </c>
       <c r="E109" t="n">
-        <v>68.59178956999595</v>
+        <v>68.5918044600314</v>
       </c>
       <c r="F109" t="n">
         <v>612400</v>
@@ -2612,16 +2612,16 @@
         <v>43374</v>
       </c>
       <c r="B110" t="n">
-        <v>69.11898040771484</v>
+        <v>69.11895751953125</v>
       </c>
       <c r="C110" t="n">
-        <v>70.20262610545464</v>
+        <v>70.20260285843067</v>
       </c>
       <c r="D110" t="n">
-        <v>68.41608173329459</v>
+        <v>68.41605907787013</v>
       </c>
       <c r="E110" t="n">
-        <v>70.20262610545464</v>
+        <v>70.20260285843067</v>
       </c>
       <c r="F110" t="n">
         <v>385466</v>
@@ -2632,16 +2632,16 @@
         <v>43375</v>
       </c>
       <c r="B111" t="n">
-        <v>69.14827728271484</v>
+        <v>69.14825439453125</v>
       </c>
       <c r="C111" t="n">
-        <v>70.26120954107566</v>
+        <v>70.2611862845098</v>
       </c>
       <c r="D111" t="n">
-        <v>67.9767645461647</v>
+        <v>67.97674204575357</v>
       </c>
       <c r="E111" t="n">
-        <v>69.20685031265521</v>
+        <v>69.20682740508386</v>
       </c>
       <c r="F111" t="n">
         <v>391400</v>
@@ -2652,16 +2652,16 @@
         <v>43376</v>
       </c>
       <c r="B112" t="n">
-        <v>70.43691253662109</v>
+        <v>70.43692016601562</v>
       </c>
       <c r="C112" t="n">
-        <v>73.59998171642307</v>
+        <v>73.59998968842636</v>
       </c>
       <c r="D112" t="n">
-        <v>69.08967371229606</v>
+        <v>69.08968119576403</v>
       </c>
       <c r="E112" t="n">
-        <v>70.58334506252905</v>
+        <v>70.58335270778446</v>
       </c>
       <c r="F112" t="n">
         <v>463466</v>
@@ -2672,16 +2672,16 @@
         <v>43377</v>
       </c>
       <c r="B113" t="n">
-        <v>70.29047393798828</v>
+        <v>70.29048919677734</v>
       </c>
       <c r="C113" t="n">
-        <v>72.13559828300075</v>
+        <v>72.1356139423329</v>
       </c>
       <c r="D113" t="n">
-        <v>67.71315715612178</v>
+        <v>67.71317185542203</v>
       </c>
       <c r="E113" t="n">
-        <v>70.55405993802722</v>
+        <v>70.55407525403604</v>
       </c>
       <c r="F113" t="n">
         <v>201700</v>
@@ -2692,16 +2692,16 @@
         <v>43378</v>
       </c>
       <c r="B114" t="n">
-        <v>68.26962280273438</v>
+        <v>68.26963043212891</v>
       </c>
       <c r="C114" t="n">
-        <v>71.60841851217266</v>
+        <v>71.60842651469054</v>
       </c>
       <c r="D114" t="n">
-        <v>67.36170388719449</v>
+        <v>67.36171141512558</v>
       </c>
       <c r="E114" t="n">
-        <v>71.60841851217266</v>
+        <v>71.60842651469054</v>
       </c>
       <c r="F114" t="n">
         <v>364566</v>
@@ -2732,16 +2732,16 @@
         <v>43382</v>
       </c>
       <c r="B116" t="n">
-        <v>68.26962280273438</v>
+        <v>68.26963043212891</v>
       </c>
       <c r="C116" t="n">
-        <v>71.75485848853327</v>
+        <v>71.75486650741638</v>
       </c>
       <c r="D116" t="n">
-        <v>68.26962280273438</v>
+        <v>68.26963043212891</v>
       </c>
       <c r="E116" t="n">
-        <v>69.96830716307632</v>
+        <v>69.9683149823054</v>
       </c>
       <c r="F116" t="n">
         <v>433600</v>
@@ -2752,16 +2752,16 @@
         <v>43383</v>
       </c>
       <c r="B117" t="n">
-        <v>69.14827728271484</v>
+        <v>69.14825439453125</v>
       </c>
       <c r="C117" t="n">
-        <v>71.7255948755766</v>
+        <v>71.72557113429701</v>
       </c>
       <c r="D117" t="n">
-        <v>67.24457187891421</v>
+        <v>67.24454962085997</v>
       </c>
       <c r="E117" t="n">
-        <v>67.36172538704393</v>
+        <v>67.36170309021169</v>
       </c>
       <c r="F117" t="n">
         <v>149833</v>
@@ -2772,16 +2772,16 @@
         <v>43384</v>
       </c>
       <c r="B118" t="n">
-        <v>70.876220703125</v>
+        <v>70.87623596191406</v>
       </c>
       <c r="C118" t="n">
-        <v>71.63769958455114</v>
+        <v>71.63771500727735</v>
       </c>
       <c r="D118" t="n">
-        <v>68.62107056224819</v>
+        <v>68.62108533553082</v>
       </c>
       <c r="E118" t="n">
-        <v>69.08966951316611</v>
+        <v>69.08968438733241</v>
       </c>
       <c r="F118" t="n">
         <v>258833</v>
@@ -2792,16 +2792,16 @@
         <v>43388</v>
       </c>
       <c r="B119" t="n">
-        <v>72.04774475097656</v>
+        <v>72.04775238037109</v>
       </c>
       <c r="C119" t="n">
-        <v>72.89709081745879</v>
+        <v>72.89709853679362</v>
       </c>
       <c r="D119" t="n">
-        <v>66.77596418128775</v>
+        <v>66.7759712524345</v>
       </c>
       <c r="E119" t="n">
-        <v>71.57914567503659</v>
+        <v>71.57915325480948</v>
       </c>
       <c r="F119" t="n">
         <v>520433</v>
@@ -2832,16 +2832,16 @@
         <v>43390</v>
       </c>
       <c r="B121" t="n">
-        <v>74.91793060302734</v>
+        <v>74.91793823242188</v>
       </c>
       <c r="C121" t="n">
-        <v>75.88442256705758</v>
+        <v>75.88443029487647</v>
       </c>
       <c r="D121" t="n">
-        <v>73.27781919072763</v>
+        <v>73.27782665309864</v>
       </c>
       <c r="E121" t="n">
-        <v>73.27781919072763</v>
+        <v>73.27782665309864</v>
       </c>
       <c r="F121" t="n">
         <v>520600</v>
@@ -2852,16 +2852,16 @@
         <v>43391</v>
       </c>
       <c r="B122" t="n">
-        <v>75.56227111816406</v>
+        <v>75.56227874755859</v>
       </c>
       <c r="C122" t="n">
-        <v>76.79234921449461</v>
+        <v>76.79235696808804</v>
       </c>
       <c r="D122" t="n">
-        <v>74.88865160237759</v>
+        <v>74.88865916375791</v>
       </c>
       <c r="E122" t="n">
-        <v>74.91793811206438</v>
+        <v>74.9179456764017</v>
       </c>
       <c r="F122" t="n">
         <v>252733</v>
@@ -2872,16 +2872,16 @@
         <v>43392</v>
       </c>
       <c r="B123" t="n">
-        <v>73.95143127441406</v>
+        <v>73.95145416259766</v>
       </c>
       <c r="C123" t="n">
-        <v>76.41159442374052</v>
+        <v>76.41161807335179</v>
       </c>
       <c r="D123" t="n">
-        <v>72.7506324794626</v>
+        <v>72.75065499599548</v>
       </c>
       <c r="E123" t="n">
-        <v>75.62082902721525</v>
+        <v>75.62085243208233</v>
       </c>
       <c r="F123" t="n">
         <v>198200</v>
@@ -2912,16 +2912,16 @@
         <v>43396</v>
       </c>
       <c r="B125" t="n">
-        <v>75.44512176513672</v>
+        <v>75.44511413574219</v>
       </c>
       <c r="C125" t="n">
-        <v>76.14802782912525</v>
+        <v>76.14802012864928</v>
       </c>
       <c r="D125" t="n">
-        <v>74.15646313057375</v>
+        <v>74.15645563149494</v>
       </c>
       <c r="E125" t="n">
-        <v>74.80079617197926</v>
+        <v>74.80078860774221</v>
       </c>
       <c r="F125" t="n">
         <v>244366</v>
@@ -2992,16 +2992,16 @@
         <v>43402</v>
       </c>
       <c r="B129" t="n">
-        <v>75.50367736816406</v>
+        <v>75.50368499755859</v>
       </c>
       <c r="C129" t="n">
-        <v>76.44088275450883</v>
+        <v>76.44089047860484</v>
       </c>
       <c r="D129" t="n">
-        <v>75.18151837003508</v>
+        <v>75.18152596687653</v>
       </c>
       <c r="E129" t="n">
-        <v>76.38230974543926</v>
+        <v>76.38231746361667</v>
       </c>
       <c r="F129" t="n">
         <v>188000</v>
@@ -3032,16 +3032,16 @@
         <v>43404</v>
       </c>
       <c r="B131" t="n">
-        <v>74.62504577636719</v>
+        <v>74.62506103515625</v>
       </c>
       <c r="C131" t="n">
-        <v>76.6166023893832</v>
+        <v>76.61661805539134</v>
       </c>
       <c r="D131" t="n">
-        <v>73.86355948521911</v>
+        <v>73.86357458830497</v>
       </c>
       <c r="E131" t="n">
-        <v>75.67939708671517</v>
+        <v>75.67941256109036</v>
       </c>
       <c r="F131" t="n">
         <v>863500</v>
@@ -3052,16 +3052,16 @@
         <v>43405</v>
       </c>
       <c r="B132" t="n">
-        <v>75.35725402832031</v>
+        <v>75.35723114013672</v>
       </c>
       <c r="C132" t="n">
-        <v>78.08100355741267</v>
+        <v>78.08097984194735</v>
       </c>
       <c r="D132" t="n">
-        <v>74.15645505834372</v>
+        <v>74.1564325348776</v>
       </c>
       <c r="E132" t="n">
-        <v>75.65012655760316</v>
+        <v>75.65010358046567</v>
       </c>
       <c r="F132" t="n">
         <v>289433</v>
@@ -3072,16 +3072,16 @@
         <v>43409</v>
       </c>
       <c r="B133" t="n">
-        <v>76.38232421875</v>
+        <v>76.38231658935547</v>
       </c>
       <c r="C133" t="n">
-        <v>76.85093072483949</v>
+        <v>76.85092304863853</v>
       </c>
       <c r="D133" t="n">
-        <v>73.98073356462973</v>
+        <v>73.98072617511639</v>
       </c>
       <c r="E133" t="n">
-        <v>75.82585818240808</v>
+        <v>75.82585060859577</v>
       </c>
       <c r="F133" t="n">
         <v>315933</v>
@@ -3092,16 +3092,16 @@
         <v>43410</v>
       </c>
       <c r="B134" t="n">
-        <v>75.12294769287109</v>
+        <v>75.12295532226562</v>
       </c>
       <c r="C134" t="n">
-        <v>76.96807220124005</v>
+        <v>76.96808001802316</v>
       </c>
       <c r="D134" t="n">
-        <v>74.12716916781773</v>
+        <v>74.12717669608222</v>
       </c>
       <c r="E134" t="n">
-        <v>76.17730668286687</v>
+        <v>76.1773144193408</v>
       </c>
       <c r="F134" t="n">
         <v>244033</v>
@@ -3112,16 +3112,16 @@
         <v>43411</v>
       </c>
       <c r="B135" t="n">
-        <v>77.31951904296875</v>
+        <v>77.31952667236328</v>
       </c>
       <c r="C135" t="n">
-        <v>79.04749738039364</v>
+        <v>79.047505180294</v>
       </c>
       <c r="D135" t="n">
-        <v>75.56226164777432</v>
+        <v>75.56226910377396</v>
       </c>
       <c r="E135" t="n">
-        <v>75.56226164777432</v>
+        <v>75.56226910377396</v>
       </c>
       <c r="F135" t="n">
         <v>375833</v>
@@ -3132,16 +3132,16 @@
         <v>43412</v>
       </c>
       <c r="B136" t="n">
-        <v>77.31951904296875</v>
+        <v>77.31952667236328</v>
       </c>
       <c r="C136" t="n">
-        <v>79.25251037075398</v>
+        <v>79.25251819088371</v>
       </c>
       <c r="D136" t="n">
-        <v>76.14801411283914</v>
+        <v>76.14802162663706</v>
       </c>
       <c r="E136" t="n">
-        <v>77.29023253695252</v>
+        <v>77.29024016345724</v>
       </c>
       <c r="F136" t="n">
         <v>245533</v>
@@ -3152,16 +3152,16 @@
         <v>43413</v>
       </c>
       <c r="B137" t="n">
-        <v>76.7337646484375</v>
+        <v>76.73377990722656</v>
       </c>
       <c r="C137" t="n">
-        <v>79.07678189802839</v>
+        <v>79.07679762273497</v>
       </c>
       <c r="D137" t="n">
-        <v>75.21080678791435</v>
+        <v>75.21082174385769</v>
       </c>
       <c r="E137" t="n">
-        <v>77.31951709877359</v>
+        <v>77.31953247404167</v>
       </c>
       <c r="F137" t="n">
         <v>423466</v>
@@ -3172,16 +3172,16 @@
         <v>43416</v>
       </c>
       <c r="B138" t="n">
-        <v>76.79234313964844</v>
+        <v>76.79235076904297</v>
       </c>
       <c r="C138" t="n">
-        <v>77.78812907971066</v>
+        <v>77.78813680803749</v>
       </c>
       <c r="D138" t="n">
-        <v>75.79656464783326</v>
+        <v>75.79657217829622</v>
       </c>
       <c r="E138" t="n">
-        <v>77.02665009510251</v>
+        <v>77.02665774777567</v>
       </c>
       <c r="F138" t="n">
         <v>143933</v>
@@ -3192,16 +3192,16 @@
         <v>43417</v>
       </c>
       <c r="B139" t="n">
-        <v>75.26939392089844</v>
+        <v>75.26937866210938</v>
       </c>
       <c r="C139" t="n">
-        <v>77.84671114454375</v>
+        <v>77.84669536327486</v>
       </c>
       <c r="D139" t="n">
-        <v>74.91794089510609</v>
+        <v>74.91792570756441</v>
       </c>
       <c r="E139" t="n">
-        <v>77.2609585843058</v>
+        <v>77.26094292178205</v>
       </c>
       <c r="F139" t="n">
         <v>637900</v>
@@ -3212,16 +3212,16 @@
         <v>43418</v>
       </c>
       <c r="B140" t="n">
-        <v>79.36966705322266</v>
+        <v>79.36965942382812</v>
       </c>
       <c r="C140" t="n">
-        <v>80.33616657102803</v>
+        <v>80.33615884872891</v>
       </c>
       <c r="D140" t="n">
-        <v>71.02267654659238</v>
+        <v>71.02266971955076</v>
       </c>
       <c r="E140" t="n">
-        <v>75.0350922710638</v>
+        <v>75.03508505832947</v>
       </c>
       <c r="F140" t="n">
         <v>1608700</v>
@@ -3232,16 +3232,16 @@
         <v>43420</v>
       </c>
       <c r="B141" t="n">
-        <v>81.09763336181641</v>
+        <v>81.09764862060547</v>
       </c>
       <c r="C141" t="n">
-        <v>83.46993713625022</v>
+        <v>83.46995284139612</v>
       </c>
       <c r="D141" t="n">
-        <v>78.81318910394661</v>
+        <v>78.8132039329099</v>
       </c>
       <c r="E141" t="n">
-        <v>78.81318910394661</v>
+        <v>78.8132039329099</v>
       </c>
       <c r="F141" t="n">
         <v>652300</v>
@@ -3252,16 +3252,16 @@
         <v>43423</v>
       </c>
       <c r="B142" t="n">
-        <v>80.24828338623047</v>
+        <v>80.24829864501953</v>
       </c>
       <c r="C142" t="n">
-        <v>81.5369417014697</v>
+        <v>81.53695720529036</v>
       </c>
       <c r="D142" t="n">
-        <v>79.77968442518686</v>
+        <v>79.77969959487429</v>
       </c>
       <c r="E142" t="n">
-        <v>80.65831678745137</v>
+        <v>80.65833212420613</v>
       </c>
       <c r="F142" t="n">
         <v>158533</v>
@@ -3272,16 +3272,16 @@
         <v>43425</v>
       </c>
       <c r="B143" t="n">
-        <v>79.80899047851562</v>
+        <v>79.80898284912109</v>
       </c>
       <c r="C143" t="n">
-        <v>81.59554214469678</v>
+        <v>81.59553434451564</v>
       </c>
       <c r="D143" t="n">
-        <v>78.13959230541533</v>
+        <v>78.13958483560805</v>
       </c>
       <c r="E143" t="n">
-        <v>79.04751139411002</v>
+        <v>79.04750383750959</v>
       </c>
       <c r="F143" t="n">
         <v>918800</v>
@@ -3292,16 +3292,16 @@
         <v>43426</v>
       </c>
       <c r="B144" t="n">
-        <v>79.07679748535156</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C144" t="n">
-        <v>80.24830261694648</v>
+        <v>80.24829487452415</v>
       </c>
       <c r="D144" t="n">
-        <v>77.78813886129798</v>
+        <v>77.78813135623429</v>
       </c>
       <c r="E144" t="n">
-        <v>79.54539655869033</v>
+        <v>79.54538888408497</v>
       </c>
       <c r="F144" t="n">
         <v>203833</v>
@@ -3312,16 +3312,16 @@
         <v>43427</v>
       </c>
       <c r="B145" t="n">
-        <v>79.51609039306641</v>
+        <v>79.51609802246094</v>
       </c>
       <c r="C145" t="n">
-        <v>79.51609039306641</v>
+        <v>79.51609802246094</v>
       </c>
       <c r="D145" t="n">
-        <v>77.31951322808395</v>
+        <v>77.31952064672171</v>
       </c>
       <c r="E145" t="n">
-        <v>78.6374580374242</v>
+        <v>78.63746558251587</v>
       </c>
       <c r="F145" t="n">
         <v>372100</v>
@@ -3332,16 +3332,16 @@
         <v>43430</v>
       </c>
       <c r="B146" t="n">
-        <v>78.75460815429688</v>
+        <v>78.75462341308594</v>
       </c>
       <c r="C146" t="n">
-        <v>80.33614632724637</v>
+        <v>80.33616189246013</v>
       </c>
       <c r="D146" t="n">
-        <v>76.23586465790369</v>
+        <v>76.23587942868353</v>
       </c>
       <c r="E146" t="n">
-        <v>80.27756587386213</v>
+        <v>80.27758142772588</v>
       </c>
       <c r="F146" t="n">
         <v>252366</v>
@@ -3352,16 +3352,16 @@
         <v>43431</v>
       </c>
       <c r="B147" t="n">
-        <v>81.59554290771484</v>
+        <v>81.59552764892578</v>
       </c>
       <c r="C147" t="n">
-        <v>82.59132153934591</v>
+        <v>82.59130609434109</v>
       </c>
       <c r="D147" t="n">
-        <v>76.32375484174636</v>
+        <v>76.32374056880897</v>
       </c>
       <c r="E147" t="n">
-        <v>78.28603304177452</v>
+        <v>78.28601840188094</v>
       </c>
       <c r="F147" t="n">
         <v>436400</v>
@@ -3372,16 +3372,16 @@
         <v>43432</v>
       </c>
       <c r="B148" t="n">
-        <v>84.5242919921875</v>
+        <v>84.52429962158203</v>
       </c>
       <c r="C148" t="n">
-        <v>86.22297626560693</v>
+        <v>86.22298404832937</v>
       </c>
       <c r="D148" t="n">
-        <v>80.54116356987981</v>
+        <v>80.54117083974624</v>
       </c>
       <c r="E148" t="n">
-        <v>81.18548900535082</v>
+        <v>81.18549633337582</v>
       </c>
       <c r="F148" t="n">
         <v>429500</v>
@@ -3452,16 +3452,16 @@
         <v>43438</v>
       </c>
       <c r="B152" t="n">
-        <v>83.82138824462891</v>
+        <v>83.82140350341797</v>
       </c>
       <c r="C152" t="n">
-        <v>86.60371793130145</v>
+        <v>86.60373369658394</v>
       </c>
       <c r="D152" t="n">
-        <v>82.59130290221974</v>
+        <v>82.5913179370849</v>
       </c>
       <c r="E152" t="n">
-        <v>84.64144017407074</v>
+        <v>84.64145558214152</v>
       </c>
       <c r="F152" t="n">
         <v>207933</v>
@@ -3472,16 +3472,16 @@
         <v>43439</v>
       </c>
       <c r="B153" t="n">
-        <v>86.1058349609375</v>
+        <v>86.10582733154297</v>
       </c>
       <c r="C153" t="n">
-        <v>86.39871494003313</v>
+        <v>86.39870728468802</v>
       </c>
       <c r="D153" t="n">
-        <v>83.11849194645005</v>
+        <v>83.1184845817486</v>
       </c>
       <c r="E153" t="n">
-        <v>83.82139793768175</v>
+        <v>83.82139051069942</v>
       </c>
       <c r="F153" t="n">
         <v>198233</v>
@@ -3492,16 +3492,16 @@
         <v>43440</v>
       </c>
       <c r="B154" t="n">
-        <v>84.934326171875</v>
+        <v>84.93433380126953</v>
       </c>
       <c r="C154" t="n">
-        <v>85.46150564190386</v>
+        <v>85.46151331865333</v>
       </c>
       <c r="D154" t="n">
-        <v>83.87996723181728</v>
+        <v>83.87997476650193</v>
       </c>
       <c r="E154" t="n">
-        <v>85.25649264493379</v>
+        <v>85.25650030326756</v>
       </c>
       <c r="F154" t="n">
         <v>270866</v>
@@ -3512,16 +3512,16 @@
         <v>43441</v>
       </c>
       <c r="B155" t="n">
-        <v>84.26069641113281</v>
+        <v>84.26070404052734</v>
       </c>
       <c r="C155" t="n">
-        <v>86.10582060639513</v>
+        <v>86.10582840285664</v>
       </c>
       <c r="D155" t="n">
-        <v>82.18127274060198</v>
+        <v>82.18128018171485</v>
       </c>
       <c r="E155" t="n">
-        <v>85.57864120085647</v>
+        <v>85.57864894958446</v>
       </c>
       <c r="F155" t="n">
         <v>485833</v>
@@ -3532,16 +3532,16 @@
         <v>43444</v>
       </c>
       <c r="B156" t="n">
-        <v>83.46994781494141</v>
+        <v>83.46994018554688</v>
       </c>
       <c r="C156" t="n">
-        <v>84.70003334193406</v>
+        <v>84.70002560010616</v>
       </c>
       <c r="D156" t="n">
-        <v>83.05992178869303</v>
+        <v>83.05991419677606</v>
       </c>
       <c r="E156" t="n">
-        <v>84.31929382495377</v>
+        <v>84.31928611792657</v>
       </c>
       <c r="F156" t="n">
         <v>313733</v>
@@ -3592,16 +3592,16 @@
         <v>43447</v>
       </c>
       <c r="B159" t="n">
-        <v>86.77945709228516</v>
+        <v>86.77944946289062</v>
       </c>
       <c r="C159" t="n">
-        <v>88.77102164547205</v>
+        <v>88.77101384098502</v>
       </c>
       <c r="D159" t="n">
-        <v>84.99290555142299</v>
+        <v>84.99289807909682</v>
       </c>
       <c r="E159" t="n">
-        <v>85.78367853981547</v>
+        <v>85.78367099796685</v>
       </c>
       <c r="F159" t="n">
         <v>486800</v>
@@ -3612,16 +3612,16 @@
         <v>43448</v>
       </c>
       <c r="B160" t="n">
-        <v>86.39872741699219</v>
+        <v>86.39871978759766</v>
       </c>
       <c r="C160" t="n">
-        <v>88.3024252112876</v>
+        <v>88.30241741378802</v>
       </c>
       <c r="D160" t="n">
-        <v>85.81297482245886</v>
+        <v>85.81296724478891</v>
       </c>
       <c r="E160" t="n">
-        <v>86.77946697585128</v>
+        <v>86.77945931283573</v>
       </c>
       <c r="F160" t="n">
         <v>286966</v>
@@ -3652,16 +3652,16 @@
         <v>43452</v>
       </c>
       <c r="B162" t="n">
-        <v>86.35250091552734</v>
+        <v>86.35251617431641</v>
       </c>
       <c r="C162" t="n">
-        <v>87.14823827281793</v>
+        <v>87.14825367221657</v>
       </c>
       <c r="D162" t="n">
-        <v>84.67260677509321</v>
+        <v>84.67262173703909</v>
       </c>
       <c r="E162" t="n">
-        <v>84.96732070608958</v>
+        <v>84.96733572011246</v>
       </c>
       <c r="F162" t="n">
         <v>387133</v>
@@ -3712,16 +3712,16 @@
         <v>43455</v>
       </c>
       <c r="B165" t="n">
-        <v>88.0029296875</v>
+        <v>88.00293731689453</v>
       </c>
       <c r="C165" t="n">
-        <v>90.18383988988073</v>
+        <v>90.18384770834878</v>
       </c>
       <c r="D165" t="n">
-        <v>86.08725529334548</v>
+        <v>86.08726275666103</v>
       </c>
       <c r="E165" t="n">
-        <v>90.18383988988073</v>
+        <v>90.18384770834878</v>
       </c>
       <c r="F165" t="n">
         <v>2053700</v>
@@ -3732,16 +3732,16 @@
         <v>43460</v>
       </c>
       <c r="B166" t="n">
-        <v>90.59645080566406</v>
+        <v>90.59646606445312</v>
       </c>
       <c r="C166" t="n">
-        <v>92.68894905800803</v>
+        <v>92.68896466922801</v>
       </c>
       <c r="D166" t="n">
-        <v>86.38197616073666</v>
+        <v>86.38199070969904</v>
       </c>
       <c r="E166" t="n">
-        <v>87.88503902461112</v>
+        <v>87.88505382672821</v>
       </c>
       <c r="F166" t="n">
         <v>396300</v>
@@ -3752,16 +3752,16 @@
         <v>43461</v>
       </c>
       <c r="B167" t="n">
-        <v>90.62593078613281</v>
+        <v>90.62592315673828</v>
       </c>
       <c r="C167" t="n">
-        <v>91.36272697138592</v>
+        <v>91.3627192799638</v>
       </c>
       <c r="D167" t="n">
-        <v>89.35864044808805</v>
+        <v>89.35863292538107</v>
       </c>
       <c r="E167" t="n">
-        <v>91.36272697138592</v>
+        <v>91.3627192799638</v>
       </c>
       <c r="F167" t="n">
         <v>343866</v>
@@ -3772,16 +3772,16 @@
         <v>43462</v>
       </c>
       <c r="B168" t="n">
-        <v>91.95215606689453</v>
+        <v>91.9521484375</v>
       </c>
       <c r="C168" t="n">
-        <v>92.09951679277854</v>
+        <v>92.09950915115729</v>
       </c>
       <c r="D168" t="n">
-        <v>89.97754032823556</v>
+        <v>89.97753286267756</v>
       </c>
       <c r="E168" t="n">
-        <v>91.33325001227509</v>
+        <v>91.33324243423203</v>
       </c>
       <c r="F168" t="n">
         <v>582800</v>
@@ -3792,16 +3792,16 @@
         <v>43467</v>
       </c>
       <c r="B169" t="n">
-        <v>91.65742492675781</v>
+        <v>91.65744018554688</v>
       </c>
       <c r="C169" t="n">
-        <v>94.19200515980368</v>
+        <v>94.19202084054029</v>
       </c>
       <c r="D169" t="n">
-        <v>90.3017228810965</v>
+        <v>90.3017379141933</v>
       </c>
       <c r="E169" t="n">
-        <v>92.21739712494251</v>
+        <v>92.21741247695367</v>
       </c>
       <c r="F169" t="n">
         <v>431033</v>
@@ -3812,16 +3812,16 @@
         <v>43468</v>
       </c>
       <c r="B170" t="n">
-        <v>89.56494140625</v>
+        <v>89.56493377685547</v>
       </c>
       <c r="C170" t="n">
-        <v>91.53955725766548</v>
+        <v>91.53954946006759</v>
       </c>
       <c r="D170" t="n">
-        <v>89.56494140625</v>
+        <v>89.56493377685547</v>
       </c>
       <c r="E170" t="n">
-        <v>91.53955725766548</v>
+        <v>91.53954946006759</v>
       </c>
       <c r="F170" t="n">
         <v>308333</v>
@@ -3892,16 +3892,16 @@
         <v>43474</v>
       </c>
       <c r="B174" t="n">
-        <v>91.36273193359375</v>
+        <v>91.36272430419922</v>
       </c>
       <c r="C174" t="n">
-        <v>91.92269676499649</v>
+        <v>91.92268908884118</v>
       </c>
       <c r="D174" t="n">
-        <v>89.71230808918374</v>
+        <v>89.71230059761056</v>
       </c>
       <c r="E174" t="n">
-        <v>89.71230808918374</v>
+        <v>89.71230059761056</v>
       </c>
       <c r="F174" t="n">
         <v>225833</v>
@@ -3912,16 +3912,16 @@
         <v>43475</v>
       </c>
       <c r="B175" t="n">
-        <v>93.39627075195312</v>
+        <v>93.39627838134766</v>
       </c>
       <c r="C175" t="n">
-        <v>94.84039226720716</v>
+        <v>94.84040001456971</v>
       </c>
       <c r="D175" t="n">
-        <v>91.09746308612006</v>
+        <v>91.0974705277286</v>
       </c>
       <c r="E175" t="n">
-        <v>91.09746308612006</v>
+        <v>91.0974705277286</v>
       </c>
       <c r="F175" t="n">
         <v>243466</v>
@@ -3932,16 +3932,16 @@
         <v>43476</v>
       </c>
       <c r="B176" t="n">
-        <v>92.36475372314453</v>
+        <v>92.36476135253906</v>
       </c>
       <c r="C176" t="n">
-        <v>93.04260851834098</v>
+        <v>93.04261620372681</v>
       </c>
       <c r="D176" t="n">
-        <v>90.861690912124</v>
+        <v>90.86169841736448</v>
       </c>
       <c r="E176" t="n">
-        <v>92.39422436727006</v>
+        <v>92.39423199909888</v>
       </c>
       <c r="F176" t="n">
         <v>283133</v>
@@ -3952,16 +3952,16 @@
         <v>43479</v>
       </c>
       <c r="B177" t="n">
-        <v>94.63407897949219</v>
+        <v>94.63408660888672</v>
       </c>
       <c r="C177" t="n">
-        <v>96.40238486265201</v>
+        <v>96.40239263460728</v>
       </c>
       <c r="D177" t="n">
-        <v>92.74787554434805</v>
+        <v>92.74788302167697</v>
       </c>
       <c r="E177" t="n">
-        <v>92.95418501770595</v>
+        <v>92.95419251166753</v>
       </c>
       <c r="F177" t="n">
         <v>478500</v>
@@ -3972,16 +3972,16 @@
         <v>43480</v>
       </c>
       <c r="B178" t="n">
-        <v>93.42574310302734</v>
+        <v>93.42575073242188</v>
       </c>
       <c r="C178" t="n">
-        <v>99.26117055861442</v>
+        <v>99.26117866454547</v>
       </c>
       <c r="D178" t="n">
-        <v>92.7478882989726</v>
+        <v>92.7478958730117</v>
       </c>
       <c r="E178" t="n">
-        <v>94.69303328252744</v>
+        <v>94.69304101541225</v>
       </c>
       <c r="F178" t="n">
         <v>736266</v>
@@ -4012,16 +4012,16 @@
         <v>43482</v>
       </c>
       <c r="B180" t="n">
-        <v>99.26119232177734</v>
+        <v>99.26117706298828</v>
       </c>
       <c r="C180" t="n">
-        <v>100.0274592273692</v>
+        <v>100.0274438507868</v>
       </c>
       <c r="D180" t="n">
-        <v>97.90548241642645</v>
+        <v>97.90546736604202</v>
       </c>
       <c r="E180" t="n">
-        <v>98.78963942098594</v>
+        <v>98.78962423468569</v>
       </c>
       <c r="F180" t="n">
         <v>313600</v>
@@ -4032,16 +4032,16 @@
         <v>43483</v>
       </c>
       <c r="B181" t="n">
-        <v>100.7937088012695</v>
+        <v>100.7937164306641</v>
       </c>
       <c r="C181" t="n">
-        <v>102.2673010571217</v>
+        <v>102.267308798057</v>
       </c>
       <c r="D181" t="n">
-        <v>98.73068114209212</v>
+        <v>98.73068861532957</v>
       </c>
       <c r="E181" t="n">
-        <v>99.67377928642814</v>
+        <v>99.67378683105167</v>
       </c>
       <c r="F181" t="n">
         <v>475600</v>
@@ -4112,16 +4112,16 @@
         <v>43489</v>
       </c>
       <c r="B185" t="n">
-        <v>98.22966003417969</v>
+        <v>98.22966766357422</v>
       </c>
       <c r="C185" t="n">
-        <v>100.9705425952604</v>
+        <v>100.9705504375364</v>
       </c>
       <c r="D185" t="n">
-        <v>97.05078919923396</v>
+        <v>97.05079673706683</v>
       </c>
       <c r="E185" t="n">
-        <v>99.23170698945374</v>
+        <v>99.23171469667619</v>
       </c>
       <c r="F185" t="n">
         <v>372266</v>
@@ -4132,16 +4132,16 @@
         <v>43493</v>
       </c>
       <c r="B186" t="n">
-        <v>97.25709533691406</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C186" t="n">
-        <v>98.0528328094274</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="D186" t="n">
-        <v>95.96033436555834</v>
+        <v>95.96032683788904</v>
       </c>
       <c r="E186" t="n">
-        <v>98.0528328094274</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="F186" t="n">
         <v>263933</v>
@@ -4192,16 +4192,16 @@
         <v>43496</v>
       </c>
       <c r="B189" t="n">
-        <v>100.9115905761719</v>
+        <v>100.9115982055664</v>
       </c>
       <c r="C189" t="n">
-        <v>104.566100269176</v>
+        <v>104.5661081748688</v>
       </c>
       <c r="D189" t="n">
-        <v>99.2022183035879</v>
+        <v>99.20222580374578</v>
       </c>
       <c r="E189" t="n">
-        <v>99.79166115348703</v>
+        <v>99.79166869820958</v>
       </c>
       <c r="F189" t="n">
         <v>504800</v>
@@ -4272,16 +4272,16 @@
         <v>43502</v>
       </c>
       <c r="B193" t="n">
-        <v>97.46338653564453</v>
+        <v>97.46339416503906</v>
       </c>
       <c r="C193" t="n">
-        <v>99.55588474696876</v>
+        <v>99.5558925401632</v>
       </c>
       <c r="D193" t="n">
-        <v>96.07820627957145</v>
+        <v>96.07821380053463</v>
       </c>
       <c r="E193" t="n">
-        <v>98.43595528230763</v>
+        <v>98.43596298783444</v>
       </c>
       <c r="F193" t="n">
         <v>594200</v>
@@ -4292,16 +4292,16 @@
         <v>43503</v>
       </c>
       <c r="B194" t="n">
-        <v>97.10973358154297</v>
+        <v>97.10972595214844</v>
       </c>
       <c r="C194" t="n">
-        <v>98.61279656718887</v>
+        <v>98.61278881970669</v>
       </c>
       <c r="D194" t="n">
-        <v>95.31194913024648</v>
+        <v>95.3119416420943</v>
       </c>
       <c r="E194" t="n">
-        <v>97.19815301926943</v>
+        <v>97.19814538292826</v>
       </c>
       <c r="F194" t="n">
         <v>496333</v>
@@ -4332,16 +4332,16 @@
         <v>43507</v>
       </c>
       <c r="B196" t="n">
-        <v>98.14125061035156</v>
+        <v>98.14124298095703</v>
       </c>
       <c r="C196" t="n">
-        <v>98.6717447482006</v>
+        <v>98.67173707756602</v>
       </c>
       <c r="D196" t="n">
-        <v>96.10769349613602</v>
+        <v>96.10768602482801</v>
       </c>
       <c r="E196" t="n">
-        <v>97.10973298202097</v>
+        <v>97.10972543281549</v>
       </c>
       <c r="F196" t="n">
         <v>401966</v>
@@ -4412,16 +4412,16 @@
         <v>43511</v>
       </c>
       <c r="B200" t="n">
-        <v>99.40853118896484</v>
+        <v>99.40853881835938</v>
       </c>
       <c r="C200" t="n">
-        <v>100.086378497347</v>
+        <v>100.0863861787649</v>
       </c>
       <c r="D200" t="n">
-        <v>97.61074692461915</v>
+        <v>97.61075441603754</v>
       </c>
       <c r="E200" t="n">
-        <v>97.61074692461915</v>
+        <v>97.61075441603754</v>
       </c>
       <c r="F200" t="n">
         <v>157766</v>
@@ -4472,16 +4472,16 @@
         <v>43516</v>
       </c>
       <c r="B203" t="n">
-        <v>97.25709533691406</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C203" t="n">
-        <v>99.17276239854924</v>
+        <v>99.17275461887898</v>
       </c>
       <c r="D203" t="n">
-        <v>95.51825216243448</v>
+        <v>95.5182446694446</v>
       </c>
       <c r="E203" t="n">
-        <v>98.87804842487829</v>
+        <v>98.87804066832706</v>
       </c>
       <c r="F203" t="n">
         <v>616733</v>
@@ -4532,16 +4532,16 @@
         <v>43521</v>
       </c>
       <c r="B206" t="n">
-        <v>95.40036010742188</v>
+        <v>95.40036773681641</v>
       </c>
       <c r="C206" t="n">
-        <v>97.10972496939742</v>
+        <v>97.10973273549394</v>
       </c>
       <c r="D206" t="n">
-        <v>92.24687368297073</v>
+        <v>92.24688106017342</v>
       </c>
       <c r="E206" t="n">
-        <v>93.66151710543296</v>
+        <v>93.66152459576807</v>
       </c>
       <c r="F206" t="n">
         <v>404566</v>
@@ -4552,16 +4552,16 @@
         <v>43522</v>
       </c>
       <c r="B207" t="n">
-        <v>95.13510131835938</v>
+        <v>95.13511657714844</v>
       </c>
       <c r="C207" t="n">
-        <v>97.25707751635309</v>
+        <v>97.25709311548748</v>
       </c>
       <c r="D207" t="n">
-        <v>93.36679531510821</v>
+        <v>93.36681029027736</v>
       </c>
       <c r="E207" t="n">
-        <v>95.57718344047986</v>
+        <v>95.5771987701748</v>
       </c>
       <c r="F207" t="n">
         <v>332133</v>
@@ -4572,16 +4572,16 @@
         <v>43523</v>
       </c>
       <c r="B208" t="n">
-        <v>95.69508361816406</v>
+        <v>95.69507598876953</v>
       </c>
       <c r="C208" t="n">
-        <v>96.63818932085464</v>
+        <v>96.63818161626997</v>
       </c>
       <c r="D208" t="n">
-        <v>94.45727143665449</v>
+        <v>94.45726390594589</v>
       </c>
       <c r="E208" t="n">
-        <v>95.13511882317307</v>
+        <v>95.13511123842235</v>
       </c>
       <c r="F208" t="n">
         <v>447266</v>
@@ -4592,16 +4592,16 @@
         <v>43524</v>
       </c>
       <c r="B209" t="n">
-        <v>96.04872131347656</v>
+        <v>96.04873657226562</v>
       </c>
       <c r="C209" t="n">
-        <v>96.46133276136341</v>
+        <v>96.46134808570203</v>
       </c>
       <c r="D209" t="n">
-        <v>94.75196067958903</v>
+        <v>94.75197573236808</v>
       </c>
       <c r="E209" t="n">
-        <v>95.69505864104575</v>
+        <v>95.69507384365015</v>
       </c>
       <c r="F209" t="n">
         <v>596166</v>
@@ -4652,16 +4652,16 @@
         <v>43531</v>
       </c>
       <c r="B212" t="n">
-        <v>96.10768890380859</v>
+        <v>96.10769653320312</v>
       </c>
       <c r="C212" t="n">
-        <v>96.22557148764568</v>
+        <v>96.22557912639819</v>
       </c>
       <c r="D212" t="n">
-        <v>94.89933995393369</v>
+        <v>94.89934748740488</v>
       </c>
       <c r="E212" t="n">
-        <v>95.72455551618241</v>
+        <v>95.72456311516235</v>
       </c>
       <c r="F212" t="n">
         <v>372100</v>
@@ -4672,16 +4672,16 @@
         <v>43532</v>
       </c>
       <c r="B213" t="n">
-        <v>96.63818359375</v>
+        <v>96.63816833496094</v>
       </c>
       <c r="C213" t="n">
-        <v>96.75606617829148</v>
+        <v>96.75605090088922</v>
       </c>
       <c r="D213" t="n">
-        <v>95.63613665468031</v>
+        <v>95.63612155411052</v>
       </c>
       <c r="E213" t="n">
-        <v>95.69507794695105</v>
+        <v>95.69506283707466</v>
       </c>
       <c r="F213" t="n">
         <v>212466</v>
@@ -4712,16 +4712,16 @@
         <v>43536</v>
       </c>
       <c r="B215" t="n">
-        <v>97.25709533691406</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C215" t="n">
-        <v>98.49491501255126</v>
+        <v>98.49490728605517</v>
       </c>
       <c r="D215" t="n">
-        <v>95.34142078020059</v>
+        <v>95.34141330108237</v>
       </c>
       <c r="E215" t="n">
-        <v>96.84449127672777</v>
+        <v>96.84448367970022</v>
       </c>
       <c r="F215" t="n">
         <v>275666</v>
@@ -4752,16 +4752,16 @@
         <v>43538</v>
       </c>
       <c r="B217" t="n">
-        <v>91.06800079345703</v>
+        <v>91.0679931640625</v>
       </c>
       <c r="C217" t="n">
-        <v>94.86987161113559</v>
+        <v>94.86986366323212</v>
       </c>
       <c r="D217" t="n">
-        <v>90.62592610318003</v>
+        <v>90.62591851082115</v>
       </c>
       <c r="E217" t="n">
-        <v>94.86987161113559</v>
+        <v>94.86986366323212</v>
       </c>
       <c r="F217" t="n">
         <v>2325333</v>
@@ -4772,16 +4772,16 @@
         <v>43539</v>
       </c>
       <c r="B218" t="n">
-        <v>89.29969024658203</v>
+        <v>89.29969787597656</v>
       </c>
       <c r="C218" t="n">
-        <v>92.15845526284264</v>
+        <v>92.15846313647816</v>
       </c>
       <c r="D218" t="n">
-        <v>88.91655686806337</v>
+        <v>88.91656446472457</v>
       </c>
       <c r="E218" t="n">
-        <v>91.0679964178041</v>
+        <v>91.06800419827536</v>
       </c>
       <c r="F218" t="n">
         <v>927800</v>
@@ -4792,16 +4792,16 @@
         <v>43542</v>
       </c>
       <c r="B219" t="n">
-        <v>86.64722442626953</v>
+        <v>86.647216796875</v>
       </c>
       <c r="C219" t="n">
-        <v>89.32916571580841</v>
+        <v>89.32915785026566</v>
       </c>
       <c r="D219" t="n">
-        <v>83.84740054932983</v>
+        <v>83.84739316646325</v>
       </c>
       <c r="E219" t="n">
-        <v>89.29969506895821</v>
+        <v>89.29968720601039</v>
       </c>
       <c r="F219" t="n">
         <v>2555666</v>
@@ -4812,16 +4812,16 @@
         <v>43543</v>
       </c>
       <c r="B220" t="n">
-        <v>89.41756439208984</v>
+        <v>89.41757965087891</v>
       </c>
       <c r="C220" t="n">
-        <v>89.41756439208984</v>
+        <v>89.41757965087891</v>
       </c>
       <c r="D220" t="n">
-        <v>86.35249765309462</v>
+        <v>86.35251238884096</v>
       </c>
       <c r="E220" t="n">
-        <v>86.35249765309462</v>
+        <v>86.35251238884096</v>
       </c>
       <c r="F220" t="n">
         <v>1451666</v>
@@ -4852,16 +4852,16 @@
         <v>43545</v>
       </c>
       <c r="B222" t="n">
-        <v>88.38607025146484</v>
+        <v>88.38605499267578</v>
       </c>
       <c r="C222" t="n">
-        <v>89.27022715947268</v>
+        <v>89.27021174804459</v>
       </c>
       <c r="D222" t="n">
-        <v>87.6198034295508</v>
+        <v>87.61978830304847</v>
       </c>
       <c r="E222" t="n">
-        <v>89.27022715947268</v>
+        <v>89.27021174804459</v>
       </c>
       <c r="F222" t="n">
         <v>454533</v>
@@ -4892,16 +4892,16 @@
         <v>43549</v>
       </c>
       <c r="B224" t="n">
-        <v>87.5313720703125</v>
+        <v>87.53137969970703</v>
       </c>
       <c r="C224" t="n">
-        <v>87.64926214035084</v>
+        <v>87.6492697800209</v>
       </c>
       <c r="D224" t="n">
-        <v>85.79253663394098</v>
+        <v>85.79254411177544</v>
       </c>
       <c r="E224" t="n">
-        <v>86.7945759964966</v>
+        <v>86.79458356167065</v>
       </c>
       <c r="F224" t="n">
         <v>451333</v>
@@ -4912,16 +4912,16 @@
         <v>43550</v>
       </c>
       <c r="B225" t="n">
-        <v>89.56494140625</v>
+        <v>89.56493377685547</v>
       </c>
       <c r="C225" t="n">
-        <v>89.62388270193819</v>
+        <v>89.62387506752287</v>
       </c>
       <c r="D225" t="n">
-        <v>86.76511743488673</v>
+        <v>86.76511004398911</v>
       </c>
       <c r="E225" t="n">
-        <v>88.20923913987366</v>
+        <v>88.20923162596166</v>
       </c>
       <c r="F225" t="n">
         <v>883933</v>
@@ -4932,16 +4932,16 @@
         <v>43551</v>
       </c>
       <c r="B226" t="n">
-        <v>86.88300323486328</v>
+        <v>86.88299560546875</v>
       </c>
       <c r="C226" t="n">
-        <v>89.29969367486639</v>
+        <v>89.29968583325677</v>
       </c>
       <c r="D226" t="n">
-        <v>86.4998623465579</v>
+        <v>86.49985475080786</v>
       </c>
       <c r="E226" t="n">
-        <v>89.29969367486639</v>
+        <v>89.29968583325677</v>
       </c>
       <c r="F226" t="n">
         <v>691333</v>
@@ -4972,16 +4972,16 @@
         <v>43553</v>
       </c>
       <c r="B228" t="n">
-        <v>90.65540313720703</v>
+        <v>90.6553955078125</v>
       </c>
       <c r="C228" t="n">
-        <v>91.80480340897347</v>
+        <v>91.8047956828475</v>
       </c>
       <c r="D228" t="n">
-        <v>88.68078722501544</v>
+        <v>88.68077976180101</v>
       </c>
       <c r="E228" t="n">
-        <v>90.7732932272902</v>
+        <v>90.77328558797426</v>
       </c>
       <c r="F228" t="n">
         <v>379666</v>
@@ -4992,16 +4992,16 @@
         <v>43556</v>
       </c>
       <c r="B229" t="n">
-        <v>90.89116668701172</v>
+        <v>90.89115905761719</v>
       </c>
       <c r="C229" t="n">
-        <v>91.62796281205101</v>
+        <v>91.62795512080989</v>
       </c>
       <c r="D229" t="n">
-        <v>89.91859790058164</v>
+        <v>89.91859035282442</v>
       </c>
       <c r="E229" t="n">
-        <v>91.12694684348028</v>
+        <v>91.12693919429439</v>
       </c>
       <c r="F229" t="n">
         <v>342733</v>
@@ -5012,16 +5012,16 @@
         <v>43557</v>
       </c>
       <c r="B230" t="n">
-        <v>91.68690490722656</v>
+        <v>91.68691253662109</v>
       </c>
       <c r="C230" t="n">
-        <v>91.92267755141023</v>
+        <v>91.92268520042373</v>
       </c>
       <c r="D230" t="n">
-        <v>89.88912069451767</v>
+        <v>89.88912817431608</v>
       </c>
       <c r="E230" t="n">
-        <v>91.65742676851103</v>
+        <v>91.65743439545264</v>
       </c>
       <c r="F230" t="n">
         <v>264800</v>
@@ -5032,16 +5032,16 @@
         <v>43558</v>
       </c>
       <c r="B231" t="n">
-        <v>88.8870849609375</v>
+        <v>88.88706970214844</v>
       </c>
       <c r="C231" t="n">
-        <v>92.77737529960361</v>
+        <v>92.77735937298839</v>
       </c>
       <c r="D231" t="n">
-        <v>88.8870849609375</v>
+        <v>88.88706970214844</v>
       </c>
       <c r="E231" t="n">
-        <v>92.71842650987473</v>
+        <v>92.71841059337896</v>
       </c>
       <c r="F231" t="n">
         <v>371500</v>
@@ -5052,16 +5052,16 @@
         <v>43559</v>
       </c>
       <c r="B232" t="n">
-        <v>86.35250091552734</v>
+        <v>86.35251617431641</v>
       </c>
       <c r="C232" t="n">
-        <v>90.06595190965305</v>
+        <v>90.06596782462189</v>
       </c>
       <c r="D232" t="n">
-        <v>85.52728541956763</v>
+        <v>85.52730053253822</v>
       </c>
       <c r="E232" t="n">
-        <v>89.59439912695075</v>
+        <v>89.59441495859457</v>
       </c>
       <c r="F232" t="n">
         <v>777800</v>
@@ -5092,16 +5092,16 @@
         <v>43563</v>
       </c>
       <c r="B234" t="n">
-        <v>82.52117919921875</v>
+        <v>82.52117156982422</v>
       </c>
       <c r="C234" t="n">
-        <v>85.88096826779656</v>
+        <v>85.88096032777685</v>
       </c>
       <c r="D234" t="n">
-        <v>82.25592835454846</v>
+        <v>82.25592074967739</v>
       </c>
       <c r="E234" t="n">
-        <v>85.02628192786193</v>
+        <v>85.02627406686121</v>
       </c>
       <c r="F234" t="n">
         <v>619400</v>
@@ -5112,16 +5112,16 @@
         <v>43564</v>
       </c>
       <c r="B235" t="n">
-        <v>82.81588745117188</v>
+        <v>82.81587982177734</v>
       </c>
       <c r="C235" t="n">
-        <v>84.05370715186686</v>
+        <v>84.05369940843848</v>
       </c>
       <c r="D235" t="n">
-        <v>80.90022035075691</v>
+        <v>80.90021289784276</v>
       </c>
       <c r="E235" t="n">
-        <v>82.22645199681945</v>
+        <v>82.22644442172653</v>
       </c>
       <c r="F235" t="n">
         <v>535633</v>
@@ -5152,16 +5152,16 @@
         <v>43566</v>
       </c>
       <c r="B237" t="n">
-        <v>84.34841156005859</v>
+        <v>84.34841918945312</v>
       </c>
       <c r="C237" t="n">
-        <v>84.61365483757208</v>
+        <v>84.61366249095812</v>
       </c>
       <c r="D237" t="n">
-        <v>82.40326670967762</v>
+        <v>82.40327416313194</v>
       </c>
       <c r="E237" t="n">
-        <v>83.78844686746174</v>
+        <v>83.78845444620694</v>
       </c>
       <c r="F237" t="n">
         <v>403133</v>
@@ -5172,16 +5172,16 @@
         <v>43567</v>
       </c>
       <c r="B238" t="n">
-        <v>82.72747039794922</v>
+        <v>82.72746276855469</v>
       </c>
       <c r="C238" t="n">
-        <v>84.73155681507157</v>
+        <v>84.73154900085372</v>
       </c>
       <c r="D238" t="n">
-        <v>82.34433700152209</v>
+        <v>82.34432940746136</v>
       </c>
       <c r="E238" t="n">
-        <v>84.34842341864444</v>
+        <v>84.34841563976039</v>
       </c>
       <c r="F238" t="n">
         <v>343366</v>
@@ -5232,16 +5232,16 @@
         <v>43572</v>
       </c>
       <c r="B241" t="n">
-        <v>82.66851806640625</v>
+        <v>82.66851043701172</v>
       </c>
       <c r="C241" t="n">
-        <v>84.23052209018523</v>
+        <v>84.23051431663492</v>
       </c>
       <c r="D241" t="n">
-        <v>81.46016925011853</v>
+        <v>81.4601617322413</v>
       </c>
       <c r="E241" t="n">
-        <v>84.20105144748405</v>
+        <v>84.20104367665355</v>
       </c>
       <c r="F241" t="n">
         <v>289766</v>
@@ -5272,16 +5272,16 @@
         <v>43577</v>
       </c>
       <c r="B243" t="n">
-        <v>84.58418273925781</v>
+        <v>84.58419799804688</v>
       </c>
       <c r="C243" t="n">
-        <v>86.26407678813486</v>
+        <v>86.26409234997288</v>
       </c>
       <c r="D243" t="n">
-        <v>82.31485336543604</v>
+        <v>82.31486821484337</v>
       </c>
       <c r="E243" t="n">
-        <v>83.4937240153255</v>
+        <v>83.49373907739835</v>
       </c>
       <c r="F243" t="n">
         <v>461666</v>
@@ -5292,16 +5292,16 @@
         <v>43578</v>
       </c>
       <c r="B244" t="n">
-        <v>86.27613067626953</v>
+        <v>86.27613830566406</v>
       </c>
       <c r="C244" t="n">
-        <v>86.77928690824331</v>
+        <v>86.77929458213193</v>
       </c>
       <c r="D244" t="n">
-        <v>84.23391717823827</v>
+        <v>84.23392462703995</v>
       </c>
       <c r="E244" t="n">
-        <v>85.24022964218584</v>
+        <v>85.24023717997569</v>
       </c>
       <c r="F244" t="n">
         <v>437600</v>
@@ -5312,16 +5312,16 @@
         <v>43579</v>
       </c>
       <c r="B245" t="n">
-        <v>86.51291656494141</v>
+        <v>86.51292419433594</v>
       </c>
       <c r="C245" t="n">
-        <v>87.07526500452914</v>
+        <v>87.07527268351602</v>
       </c>
       <c r="D245" t="n">
-        <v>85.06264755574588</v>
+        <v>85.0626550572442</v>
       </c>
       <c r="E245" t="n">
-        <v>86.27613272839055</v>
+        <v>86.27614033690361</v>
       </c>
       <c r="F245" t="n">
         <v>361900</v>
@@ -5332,16 +5332,16 @@
         <v>43580</v>
       </c>
       <c r="B246" t="n">
-        <v>87.90398406982422</v>
+        <v>87.90399169921875</v>
       </c>
       <c r="C246" t="n">
-        <v>88.5551283166666</v>
+        <v>88.55513600257547</v>
       </c>
       <c r="D246" t="n">
-        <v>84.88506172132999</v>
+        <v>84.88506908870511</v>
       </c>
       <c r="E246" t="n">
-        <v>87.01606351821326</v>
+        <v>87.01607107054306</v>
       </c>
       <c r="F246" t="n">
         <v>486633</v>
@@ -5392,16 +5392,16 @@
         <v>43585</v>
       </c>
       <c r="B249" t="n">
-        <v>89.56143951416016</v>
+        <v>89.56143188476562</v>
       </c>
       <c r="C249" t="n">
-        <v>90.27177600507484</v>
+        <v>90.27176831516947</v>
       </c>
       <c r="D249" t="n">
-        <v>86.77929327606671</v>
+        <v>86.77928588367251</v>
       </c>
       <c r="E249" t="n">
-        <v>86.77929327606671</v>
+        <v>86.77928588367251</v>
       </c>
       <c r="F249" t="n">
         <v>318366</v>
@@ -5432,16 +5432,16 @@
         <v>43588</v>
       </c>
       <c r="B251" t="n">
-        <v>90.21258544921875</v>
+        <v>90.21257781982422</v>
       </c>
       <c r="C251" t="n">
-        <v>90.89331832625483</v>
+        <v>90.89331063928984</v>
       </c>
       <c r="D251" t="n">
-        <v>88.91030436782248</v>
+        <v>88.91029684856353</v>
       </c>
       <c r="E251" t="n">
-        <v>88.91030436782248</v>
+        <v>88.91029684856353</v>
       </c>
       <c r="F251" t="n">
         <v>248400</v>
@@ -5452,16 +5452,16 @@
         <v>43591</v>
       </c>
       <c r="B252" t="n">
-        <v>90.53814697265625</v>
+        <v>90.53815460205078</v>
       </c>
       <c r="C252" t="n">
-        <v>91.10049543110814</v>
+        <v>91.10050310789021</v>
       </c>
       <c r="D252" t="n">
-        <v>88.19996484240103</v>
+        <v>88.19997227476354</v>
       </c>
       <c r="E252" t="n">
-        <v>88.64392137860601</v>
+        <v>88.64392884837949</v>
       </c>
       <c r="F252" t="n">
         <v>206566</v>
@@ -5472,16 +5472,16 @@
         <v>43592</v>
       </c>
       <c r="B253" t="n">
-        <v>96.93116760253906</v>
+        <v>96.93115997314453</v>
       </c>
       <c r="C253" t="n">
-        <v>97.64150408089029</v>
+        <v>97.64149639558559</v>
       </c>
       <c r="D253" t="n">
-        <v>89.47264963381808</v>
+        <v>89.47264259147906</v>
       </c>
       <c r="E253" t="n">
-        <v>90.8341228660023</v>
+        <v>90.83411571650254</v>
       </c>
       <c r="F253" t="n">
         <v>3210933</v>
@@ -5492,16 +5492,16 @@
         <v>43593</v>
       </c>
       <c r="B254" t="n">
-        <v>102.3474578857422</v>
+        <v>102.3474731445312</v>
       </c>
       <c r="C254" t="n">
-        <v>104.4488709330641</v>
+        <v>104.4488865051489</v>
       </c>
       <c r="D254" t="n">
-        <v>98.8845717934515</v>
+        <v>98.88458653596543</v>
       </c>
       <c r="E254" t="n">
-        <v>100.6308166504369</v>
+        <v>100.6308316532951</v>
       </c>
       <c r="F254" t="n">
         <v>1898166</v>
@@ -5612,16 +5612,16 @@
         <v>43601</v>
       </c>
       <c r="B260" t="n">
-        <v>102.5842437744141</v>
+        <v>102.5842514038086</v>
       </c>
       <c r="C260" t="n">
-        <v>103.6793445426467</v>
+        <v>103.679352253486</v>
       </c>
       <c r="D260" t="n">
-        <v>102.5842437744141</v>
+        <v>102.5842514038086</v>
       </c>
       <c r="E260" t="n">
-        <v>103.5905562502412</v>
+        <v>103.5905639544772</v>
       </c>
       <c r="F260" t="n">
         <v>583833</v>
@@ -5632,16 +5632,16 @@
         <v>43602</v>
       </c>
       <c r="B261" t="n">
-        <v>102.9690322875977</v>
+        <v>102.968994140625</v>
       </c>
       <c r="C261" t="n">
-        <v>103.5609769137207</v>
+        <v>103.5609385474501</v>
       </c>
       <c r="D261" t="n">
-        <v>101.548359163315</v>
+        <v>101.5483215426596</v>
       </c>
       <c r="E261" t="n">
-        <v>102.9394286583549</v>
+        <v>102.9393905223495</v>
       </c>
       <c r="F261" t="n">
         <v>361233</v>
@@ -5652,16 +5652,16 @@
         <v>43605</v>
       </c>
       <c r="B262" t="n">
-        <v>105.070426940918</v>
+        <v>105.0704193115234</v>
       </c>
       <c r="C262" t="n">
-        <v>105.8991478221478</v>
+        <v>105.899140132578</v>
       </c>
       <c r="D262" t="n">
-        <v>103.590561772736</v>
+        <v>103.5905542507978</v>
       </c>
       <c r="E262" t="n">
-        <v>103.590561772736</v>
+        <v>103.5905542507978</v>
       </c>
       <c r="F262" t="n">
         <v>597600</v>
@@ -5692,16 +5692,16 @@
         <v>43607</v>
       </c>
       <c r="B264" t="n">
-        <v>109.4508361816406</v>
+        <v>109.450813293457</v>
       </c>
       <c r="C264" t="n">
-        <v>110.3091532084535</v>
+        <v>110.30913014078</v>
       </c>
       <c r="D264" t="n">
-        <v>107.8821751042858</v>
+        <v>107.8821525441381</v>
       </c>
       <c r="E264" t="n">
-        <v>108.3261316680177</v>
+        <v>108.3261090150305</v>
       </c>
       <c r="F264" t="n">
         <v>582066</v>
@@ -5712,16 +5712,16 @@
         <v>43608</v>
       </c>
       <c r="B265" t="n">
-        <v>110.9898834228516</v>
+        <v>110.9898681640625</v>
       </c>
       <c r="C265" t="n">
-        <v>112.4697485351563</v>
+        <v>112.4697330729167</v>
       </c>
       <c r="D265" t="n">
-        <v>109.1844461793639</v>
+        <v>109.1844311687847</v>
       </c>
       <c r="E265" t="n">
-        <v>109.332434195991</v>
+        <v>109.3324191650665</v>
       </c>
       <c r="F265" t="n">
         <v>449966</v>
@@ -5732,16 +5732,16 @@
         <v>43609</v>
       </c>
       <c r="B266" t="n">
-        <v>110.3979339599609</v>
+        <v>110.39794921875</v>
       </c>
       <c r="C266" t="n">
-        <v>111.9073951028777</v>
+        <v>111.9074105702988</v>
       </c>
       <c r="D266" t="n">
-        <v>109.9539699298789</v>
+        <v>109.9539851273049</v>
       </c>
       <c r="E266" t="n">
-        <v>111.1970586763327</v>
+        <v>111.1970740455737</v>
       </c>
       <c r="F266" t="n">
         <v>294000</v>
@@ -5752,16 +5752,16 @@
         <v>43612</v>
       </c>
       <c r="B267" t="n">
-        <v>109.9539642333984</v>
+        <v>109.953987121582</v>
       </c>
       <c r="C267" t="n">
-        <v>111.7298052077584</v>
+        <v>111.7298284656038</v>
       </c>
       <c r="D267" t="n">
-        <v>109.6875918507357</v>
+        <v>109.6876146834708</v>
       </c>
       <c r="E267" t="n">
-        <v>110.0427600456077</v>
+        <v>110.0427829522751</v>
       </c>
       <c r="F267" t="n">
         <v>77066</v>
@@ -5792,16 +5792,16 @@
         <v>43614</v>
       </c>
       <c r="B269" t="n">
-        <v>109.9243774414062</v>
+        <v>109.9243850708008</v>
       </c>
       <c r="C269" t="n">
-        <v>110.1019615538715</v>
+        <v>110.1019691955914</v>
       </c>
       <c r="D269" t="n">
-        <v>108.3557240537826</v>
+        <v>108.3557315743034</v>
       </c>
       <c r="E269" t="n">
-        <v>109.2732407136891</v>
+        <v>109.2732482978909</v>
       </c>
       <c r="F269" t="n">
         <v>725533</v>
@@ -5852,16 +5852,16 @@
         <v>43619</v>
       </c>
       <c r="B272" t="n">
-        <v>109.8651885986328</v>
+        <v>109.8651733398438</v>
       </c>
       <c r="C272" t="n">
-        <v>110.7531091880527</v>
+        <v>110.7530938059435</v>
       </c>
       <c r="D272" t="n">
-        <v>108.622099773445</v>
+        <v>108.6220846873041</v>
       </c>
       <c r="E272" t="n">
-        <v>108.7996838913289</v>
+        <v>108.7996687805241</v>
       </c>
       <c r="F272" t="n">
         <v>294000</v>
@@ -5872,16 +5872,16 @@
         <v>43620</v>
       </c>
       <c r="B273" t="n">
-        <v>107.1718139648438</v>
+        <v>107.1718292236328</v>
       </c>
       <c r="C273" t="n">
-        <v>110.9898681385225</v>
+        <v>110.9898839409142</v>
       </c>
       <c r="D273" t="n">
-        <v>107.1718139648438</v>
+        <v>107.1718292236328</v>
       </c>
       <c r="E273" t="n">
-        <v>109.5987915115683</v>
+        <v>109.5988071159028</v>
       </c>
       <c r="F273" t="n">
         <v>283866</v>
@@ -5892,16 +5892,16 @@
         <v>43621</v>
       </c>
       <c r="B274" t="n">
-        <v>108.8884735107422</v>
+        <v>108.8884811401367</v>
       </c>
       <c r="C274" t="n">
-        <v>109.835586243175</v>
+        <v>109.8355939389301</v>
       </c>
       <c r="D274" t="n">
-        <v>106.4022960019959</v>
+        <v>106.4023034571936</v>
       </c>
       <c r="E274" t="n">
-        <v>106.6390723033584</v>
+        <v>106.6390797751461</v>
       </c>
       <c r="F274" t="n">
         <v>231033</v>
@@ -5912,16 +5912,16 @@
         <v>43622</v>
       </c>
       <c r="B275" t="n">
-        <v>108.7404937744141</v>
+        <v>108.740478515625</v>
       </c>
       <c r="C275" t="n">
-        <v>109.6876065789178</v>
+        <v>109.687591187227</v>
       </c>
       <c r="D275" t="n">
-        <v>108.05975338834</v>
+        <v>108.0597382250744</v>
       </c>
       <c r="E275" t="n">
-        <v>109.5100224576369</v>
+        <v>109.5100070908652</v>
       </c>
       <c r="F275" t="n">
         <v>227300</v>
@@ -5972,16 +5972,16 @@
         <v>43627</v>
       </c>
       <c r="B278" t="n">
-        <v>110.9898834228516</v>
+        <v>110.9898681640625</v>
       </c>
       <c r="C278" t="n">
-        <v>116.6725675616569</v>
+        <v>116.6725515216175</v>
       </c>
       <c r="D278" t="n">
-        <v>110.9898834228516</v>
+        <v>110.9898681640625</v>
       </c>
       <c r="E278" t="n">
-        <v>116.465379822189</v>
+        <v>116.4653638106336</v>
       </c>
       <c r="F278" t="n">
         <v>422033</v>
@@ -6032,16 +6032,16 @@
         <v>43630</v>
       </c>
       <c r="B281" t="n">
-        <v>111.9369964599609</v>
+        <v>111.9370040893555</v>
       </c>
       <c r="C281" t="n">
-        <v>114.156794133742</v>
+        <v>114.1568019144333</v>
       </c>
       <c r="D281" t="n">
-        <v>110.753107378071</v>
+        <v>110.7531149267741</v>
       </c>
       <c r="E281" t="n">
-        <v>113.3576693798154</v>
+        <v>113.3576771060401</v>
       </c>
       <c r="F281" t="n">
         <v>560666</v>
@@ -6052,16 +6052,16 @@
         <v>43633</v>
       </c>
       <c r="B282" t="n">
-        <v>110.0723724365234</v>
+        <v>110.0723648071289</v>
       </c>
       <c r="C282" t="n">
-        <v>113.1504947387922</v>
+        <v>113.1504868960452</v>
       </c>
       <c r="D282" t="n">
-        <v>109.0660598930775</v>
+        <v>109.066052333433</v>
       </c>
       <c r="E282" t="n">
-        <v>113.1504947387922</v>
+        <v>113.1504868960452</v>
       </c>
       <c r="F282" t="n">
         <v>481366</v>
@@ -6092,16 +6092,16 @@
         <v>43635</v>
       </c>
       <c r="B284" t="n">
-        <v>115.3702774047852</v>
+        <v>115.3702850341797</v>
       </c>
       <c r="C284" t="n">
-        <v>115.3702774047852</v>
+        <v>115.3702850341797</v>
       </c>
       <c r="D284" t="n">
-        <v>111.6114151995947</v>
+        <v>111.6114225804171</v>
       </c>
       <c r="E284" t="n">
-        <v>112.3513476970046</v>
+        <v>112.3513551267584</v>
       </c>
       <c r="F284" t="n">
         <v>441733</v>
@@ -6112,16 +6112,16 @@
         <v>43637</v>
       </c>
       <c r="B285" t="n">
-        <v>116.4653701782227</v>
+        <v>116.4653625488281</v>
       </c>
       <c r="C285" t="n">
-        <v>116.4949738006833</v>
+        <v>116.4949661693495</v>
       </c>
       <c r="D285" t="n">
-        <v>114.5415487023227</v>
+        <v>114.5415411989536</v>
       </c>
       <c r="E285" t="n">
-        <v>115.3998731060995</v>
+        <v>115.3998655465033</v>
       </c>
       <c r="F285" t="n">
         <v>285566</v>
@@ -6132,16 +6132,16 @@
         <v>43640</v>
       </c>
       <c r="B286" t="n">
-        <v>116.5245742797852</v>
+        <v>116.5245819091797</v>
       </c>
       <c r="C286" t="n">
-        <v>117.5012831022177</v>
+        <v>117.5012907955618</v>
       </c>
       <c r="D286" t="n">
-        <v>115.0447092343492</v>
+        <v>115.0447167668502</v>
       </c>
       <c r="E286" t="n">
-        <v>116.6133625695595</v>
+        <v>116.6133702047674</v>
       </c>
       <c r="F286" t="n">
         <v>315633</v>
@@ -6152,16 +6152,16 @@
         <v>43641</v>
       </c>
       <c r="B287" t="n">
-        <v>114.4823532104492</v>
+        <v>114.4823684692383</v>
       </c>
       <c r="C287" t="n">
-        <v>117.1165110098012</v>
+        <v>117.1165266196842</v>
       </c>
       <c r="D287" t="n">
-        <v>113.8312090207762</v>
+        <v>113.8312241927775</v>
       </c>
       <c r="E287" t="n">
-        <v>116.5837587256094</v>
+        <v>116.5837742644845</v>
       </c>
       <c r="F287" t="n">
         <v>481433</v>
@@ -6172,16 +6172,16 @@
         <v>43642</v>
       </c>
       <c r="B288" t="n">
-        <v>113.1208953857422</v>
+        <v>113.1208801269531</v>
       </c>
       <c r="C288" t="n">
-        <v>115.7254576141382</v>
+        <v>115.7254420040218</v>
       </c>
       <c r="D288" t="n">
-        <v>112.6769388231457</v>
+        <v>112.6769236242416</v>
       </c>
       <c r="E288" t="n">
-        <v>115.7254576141382</v>
+        <v>115.7254420040218</v>
       </c>
       <c r="F288" t="n">
         <v>335833</v>
@@ -6192,16 +6192,16 @@
         <v>43643</v>
       </c>
       <c r="B289" t="n">
-        <v>115.281494140625</v>
+        <v>115.2814865112305</v>
       </c>
       <c r="C289" t="n">
-        <v>115.281494140625</v>
+        <v>115.2814865112305</v>
       </c>
       <c r="D289" t="n">
-        <v>112.9137083857593</v>
+        <v>112.9137009130662</v>
       </c>
       <c r="E289" t="n">
-        <v>113.3872685475258</v>
+        <v>113.3872610434922</v>
       </c>
       <c r="F289" t="n">
         <v>276700</v>
@@ -6212,16 +6212,16 @@
         <v>43644</v>
       </c>
       <c r="B290" t="n">
-        <v>116.7021560668945</v>
+        <v>116.7021636962891</v>
       </c>
       <c r="C290" t="n">
-        <v>117.649268773912</v>
+        <v>117.6492764652239</v>
       </c>
       <c r="D290" t="n">
-        <v>114.1271903368541</v>
+        <v>114.1271977979104</v>
       </c>
       <c r="E290" t="n">
-        <v>115.0743030438715</v>
+        <v>115.0743105668453</v>
       </c>
       <c r="F290" t="n">
         <v>617600</v>
@@ -6232,16 +6232,16 @@
         <v>43647</v>
       </c>
       <c r="B291" t="n">
-        <v>114.0680160522461</v>
+        <v>114.0680084228516</v>
       </c>
       <c r="C291" t="n">
-        <v>117.0573426495882</v>
+        <v>117.0573348202537</v>
       </c>
       <c r="D291" t="n">
-        <v>114.0680160522461</v>
+        <v>114.0680084228516</v>
       </c>
       <c r="E291" t="n">
-        <v>117.0573426495882</v>
+        <v>117.0573348202537</v>
       </c>
       <c r="F291" t="n">
         <v>436066</v>
@@ -6252,16 +6252,16 @@
         <v>43648</v>
       </c>
       <c r="B292" t="n">
-        <v>110.1315536499023</v>
+        <v>110.1315689086914</v>
       </c>
       <c r="C292" t="n">
-        <v>115.1334971877844</v>
+        <v>115.1335131395955</v>
       </c>
       <c r="D292" t="n">
-        <v>110.1315536499023</v>
+        <v>110.1315689086914</v>
       </c>
       <c r="E292" t="n">
-        <v>113.9792042621922</v>
+        <v>113.9792200540755</v>
       </c>
       <c r="F292" t="n">
         <v>537533</v>
@@ -6312,16 +6312,16 @@
         <v>43651</v>
       </c>
       <c r="B295" t="n">
-        <v>117.5184020996094</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="C295" t="n">
-        <v>117.5184020996094</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="D295" t="n">
-        <v>112.9115842237956</v>
+        <v>112.9115768934796</v>
       </c>
       <c r="E295" t="n">
-        <v>114.0707168497463</v>
+        <v>114.0707094441784</v>
       </c>
       <c r="F295" t="n">
         <v>288866</v>
@@ -6352,16 +6352,16 @@
         <v>43656</v>
       </c>
       <c r="B297" t="n">
-        <v>128.0397644042969</v>
+        <v>128.0397796630859</v>
       </c>
       <c r="C297" t="n">
-        <v>128.0397644042969</v>
+        <v>128.0397796630859</v>
       </c>
       <c r="D297" t="n">
-        <v>121.9171496849643</v>
+        <v>121.9171642141075</v>
       </c>
       <c r="E297" t="n">
-        <v>121.9171496849643</v>
+        <v>121.9171642141075</v>
       </c>
       <c r="F297" t="n">
         <v>529166</v>
@@ -6372,16 +6372,16 @@
         <v>43657</v>
       </c>
       <c r="B298" t="n">
-        <v>123.1654586791992</v>
+        <v>123.1654510498047</v>
       </c>
       <c r="C298" t="n">
-        <v>130.1797020465908</v>
+        <v>130.1796939827041</v>
       </c>
       <c r="D298" t="n">
-        <v>123.1060183088487</v>
+        <v>123.1060106831362</v>
       </c>
       <c r="E298" t="n">
-        <v>130.1797020465908</v>
+        <v>130.1796939827041</v>
       </c>
       <c r="F298" t="n">
         <v>660700</v>
@@ -6412,16 +6412,16 @@
         <v>43661</v>
       </c>
       <c r="B300" t="n">
-        <v>121.5605087280273</v>
+        <v>121.5605010986328</v>
       </c>
       <c r="C300" t="n">
-        <v>126.7320329312208</v>
+        <v>126.7320249772505</v>
       </c>
       <c r="D300" t="n">
-        <v>118.5289287021037</v>
+        <v>118.5289212629776</v>
       </c>
       <c r="E300" t="n">
-        <v>124.9784738625208</v>
+        <v>124.9784660186075</v>
       </c>
       <c r="F300" t="n">
         <v>1110366</v>
@@ -6492,16 +6492,16 @@
         <v>43665</v>
       </c>
       <c r="B304" t="n">
-        <v>126.9995269775391</v>
+        <v>126.9995193481445</v>
       </c>
       <c r="C304" t="n">
-        <v>132.3790923740756</v>
+        <v>132.379084421508</v>
       </c>
       <c r="D304" t="n">
-        <v>126.9995269775391</v>
+        <v>126.9995193481445</v>
       </c>
       <c r="E304" t="n">
-        <v>129.9419463781816</v>
+        <v>129.9419385720236</v>
       </c>
       <c r="F304" t="n">
         <v>683033</v>
@@ -6512,16 +6512,16 @@
         <v>43668</v>
       </c>
       <c r="B305" t="n">
-        <v>127.4453659057617</v>
+        <v>127.4453430175781</v>
       </c>
       <c r="C305" t="n">
-        <v>129.0800369013886</v>
+        <v>129.080013719631</v>
       </c>
       <c r="D305" t="n">
-        <v>126.0781841913241</v>
+        <v>126.0781615486755</v>
       </c>
       <c r="E305" t="n">
-        <v>126.3456734725133</v>
+        <v>126.3456507818258</v>
       </c>
       <c r="F305" t="n">
         <v>163233</v>
@@ -6552,16 +6552,16 @@
         <v>43670</v>
       </c>
       <c r="B307" t="n">
-        <v>128.8719482421875</v>
+        <v>128.8719940185547</v>
       </c>
       <c r="C307" t="n">
-        <v>131.8440872280763</v>
+        <v>131.8441340601715</v>
       </c>
       <c r="D307" t="n">
-        <v>124.9487256878391</v>
+        <v>124.9487700706457</v>
       </c>
       <c r="E307" t="n">
-        <v>124.9487256878391</v>
+        <v>124.9487700706457</v>
       </c>
       <c r="F307" t="n">
         <v>788600</v>
@@ -6612,16 +6612,16 @@
         <v>43675</v>
       </c>
       <c r="B310" t="n">
-        <v>126.0187072753906</v>
+        <v>126.0187149047852</v>
       </c>
       <c r="C310" t="n">
-        <v>126.8806228621377</v>
+        <v>126.8806305437141</v>
       </c>
       <c r="D310" t="n">
-        <v>125.0081832072433</v>
+        <v>125.0081907754589</v>
       </c>
       <c r="E310" t="n">
-        <v>126.6131336424503</v>
+        <v>126.6131413078325</v>
       </c>
       <c r="F310" t="n">
         <v>708133</v>
@@ -6632,16 +6632,16 @@
         <v>43676</v>
       </c>
       <c r="B311" t="n">
-        <v>124.384033203125</v>
+        <v>124.3840408325195</v>
       </c>
       <c r="C311" t="n">
-        <v>126.3753687791254</v>
+        <v>126.3753765306633</v>
       </c>
       <c r="D311" t="n">
-        <v>124.2948726464664</v>
+        <v>124.294880270392</v>
       </c>
       <c r="E311" t="n">
-        <v>126.2267602928194</v>
+        <v>126.2267680352421</v>
       </c>
       <c r="F311" t="n">
         <v>1065500</v>
@@ -6712,16 +6712,16 @@
         <v>43682</v>
       </c>
       <c r="B315" t="n">
-        <v>123.4032211303711</v>
+        <v>123.4032363891602</v>
       </c>
       <c r="C315" t="n">
-        <v>124.3543047979057</v>
+        <v>124.3543201742961</v>
       </c>
       <c r="D315" t="n">
-        <v>121.8577111154449</v>
+        <v>121.8577261831319</v>
       </c>
       <c r="E315" t="n">
-        <v>124.0570954034805</v>
+        <v>124.057110743121</v>
       </c>
       <c r="F315" t="n">
         <v>384500</v>
@@ -6752,16 +6752,16 @@
         <v>43684</v>
       </c>
       <c r="B317" t="n">
-        <v>128.5153045654297</v>
+        <v>128.5153198242188</v>
       </c>
       <c r="C317" t="n">
-        <v>129.2583393905688</v>
+        <v>129.2583547375794</v>
       </c>
       <c r="D317" t="n">
-        <v>124.740682513915</v>
+        <v>124.7406973245383</v>
       </c>
       <c r="E317" t="n">
-        <v>126.6131296685823</v>
+        <v>126.6131447015237</v>
       </c>
       <c r="F317" t="n">
         <v>506366</v>
@@ -6772,16 +6772,16 @@
         <v>43685</v>
       </c>
       <c r="B318" t="n">
-        <v>131.9035797119141</v>
+        <v>131.9035491943359</v>
       </c>
       <c r="C318" t="n">
-        <v>133.5679709455118</v>
+        <v>133.5679400428555</v>
       </c>
       <c r="D318" t="n">
-        <v>129.2880969754843</v>
+        <v>129.2880670630315</v>
       </c>
       <c r="E318" t="n">
-        <v>129.2880969754843</v>
+        <v>129.2880670630315</v>
       </c>
       <c r="F318" t="n">
         <v>971500</v>
@@ -6792,16 +6792,16 @@
         <v>43686</v>
       </c>
       <c r="B319" t="n">
-        <v>131.5171813964844</v>
+        <v>131.5171966552734</v>
       </c>
       <c r="C319" t="n">
-        <v>134.8756986444118</v>
+        <v>134.8757142928603</v>
       </c>
       <c r="D319" t="n">
-        <v>129.4069573772885</v>
+        <v>129.4069723912467</v>
       </c>
       <c r="E319" t="n">
-        <v>134.8756986444118</v>
+        <v>134.8757142928603</v>
       </c>
       <c r="F319" t="n">
         <v>371566</v>
@@ -6812,16 +6812,16 @@
         <v>43689</v>
       </c>
       <c r="B320" t="n">
-        <v>131.1902465820312</v>
+        <v>131.1902313232422</v>
       </c>
       <c r="C320" t="n">
-        <v>131.4874635800655</v>
+        <v>131.487448286707</v>
       </c>
       <c r="D320" t="n">
-        <v>128.8422610200215</v>
+        <v>128.8422460343276</v>
       </c>
       <c r="E320" t="n">
-        <v>131.4874635800655</v>
+        <v>131.487448286707</v>
       </c>
       <c r="F320" t="n">
         <v>372500</v>
@@ -6832,16 +6832,16 @@
         <v>43690</v>
       </c>
       <c r="B321" t="n">
-        <v>131.0713500976562</v>
+        <v>131.0713653564453</v>
       </c>
       <c r="C321" t="n">
-        <v>133.7759927092622</v>
+        <v>133.7760082829146</v>
       </c>
       <c r="D321" t="n">
-        <v>128.8125253710496</v>
+        <v>128.8125403668755</v>
       </c>
       <c r="E321" t="n">
-        <v>133.6571119711511</v>
+        <v>133.6571275309639</v>
       </c>
       <c r="F321" t="n">
         <v>614133</v>
@@ -6852,16 +6852,16 @@
         <v>43691</v>
       </c>
       <c r="B322" t="n">
-        <v>137.015625</v>
+        <v>137.0156402587891</v>
       </c>
       <c r="C322" t="n">
-        <v>140.9685606011814</v>
+        <v>140.9685763001904</v>
       </c>
       <c r="D322" t="n">
-        <v>135.2323383933742</v>
+        <v>135.232353453567</v>
       </c>
       <c r="E322" t="n">
-        <v>139.6905473513976</v>
+        <v>139.6905629080802</v>
       </c>
       <c r="F322" t="n">
         <v>1453733</v>
@@ -6872,16 +6872,16 @@
         <v>43692</v>
       </c>
       <c r="B323" t="n">
-        <v>140.1661071777344</v>
+        <v>140.1660919189453</v>
       </c>
       <c r="C323" t="n">
-        <v>142.0088344379419</v>
+        <v>142.0088189785496</v>
       </c>
       <c r="D323" t="n">
-        <v>136.3023315275013</v>
+        <v>136.3023166893313</v>
       </c>
       <c r="E323" t="n">
-        <v>139.5122328008997</v>
+        <v>139.5122176132928</v>
       </c>
       <c r="F323" t="n">
         <v>846233</v>
@@ -6932,16 +6932,16 @@
         <v>43697</v>
       </c>
       <c r="B326" t="n">
-        <v>145.0106811523438</v>
+        <v>145.0106964111328</v>
       </c>
       <c r="C326" t="n">
-        <v>146.7048073163463</v>
+        <v>146.7048227534003</v>
       </c>
       <c r="D326" t="n">
-        <v>140.4633113521918</v>
+        <v>140.4633261324826</v>
       </c>
       <c r="E326" t="n">
-        <v>143.049073318038</v>
+        <v>143.0490883704163</v>
       </c>
       <c r="F326" t="n">
         <v>506533</v>
@@ -6992,16 +6992,16 @@
         <v>43700</v>
       </c>
       <c r="B329" t="n">
-        <v>143.286865234375</v>
+        <v>143.2868499755859</v>
       </c>
       <c r="C329" t="n">
-        <v>148.3692140354192</v>
+        <v>148.3691982354048</v>
       </c>
       <c r="D329" t="n">
-        <v>142.3654940313826</v>
+        <v>142.3654788707114</v>
       </c>
       <c r="E329" t="n">
-        <v>147.9531162756141</v>
+        <v>147.9531005199104</v>
       </c>
       <c r="F329" t="n">
         <v>586733</v>
@@ -7012,16 +7012,16 @@
         <v>43703</v>
       </c>
       <c r="B330" t="n">
-        <v>143.5543518066406</v>
+        <v>143.5543060302734</v>
       </c>
       <c r="C330" t="n">
-        <v>146.2292898230444</v>
+        <v>146.2292431936976</v>
       </c>
       <c r="D330" t="n">
-        <v>141.2063661119289</v>
+        <v>141.2063210842834</v>
       </c>
       <c r="E330" t="n">
-        <v>143.3165902884432</v>
+        <v>143.316544587893</v>
       </c>
       <c r="F330" t="n">
         <v>278200</v>
@@ -7032,16 +7032,16 @@
         <v>43704</v>
       </c>
       <c r="B331" t="n">
-        <v>145.4862365722656</v>
+        <v>145.4862518310547</v>
       </c>
       <c r="C331" t="n">
-        <v>146.4670329458183</v>
+        <v>146.4670483074746</v>
       </c>
       <c r="D331" t="n">
-        <v>141.7710621461821</v>
+        <v>141.7710770153187</v>
       </c>
       <c r="E331" t="n">
-        <v>143.4057328468255</v>
+        <v>143.4057478874085</v>
       </c>
       <c r="F331" t="n">
         <v>495866</v>
@@ -7072,16 +7072,16 @@
         <v>43706</v>
       </c>
       <c r="B333" t="n">
-        <v>150.0930480957031</v>
+        <v>150.0930328369141</v>
       </c>
       <c r="C333" t="n">
-        <v>151.1035797810121</v>
+        <v>151.1035644194901</v>
       </c>
       <c r="D333" t="n">
-        <v>145.9617759126635</v>
+        <v>145.9617610738686</v>
       </c>
       <c r="E333" t="n">
-        <v>146.5264745693678</v>
+        <v>146.5264596731645</v>
       </c>
       <c r="F333" t="n">
         <v>1067466</v>
@@ -7092,16 +7092,16 @@
         <v>43707</v>
       </c>
       <c r="B334" t="n">
-        <v>153.6893463134766</v>
+        <v>153.6893157958984</v>
       </c>
       <c r="C334" t="n">
-        <v>153.6893463134766</v>
+        <v>153.6893157958984</v>
       </c>
       <c r="D334" t="n">
-        <v>149.884996068173</v>
+        <v>149.8849663060119</v>
       </c>
       <c r="E334" t="n">
-        <v>150.984688344605</v>
+        <v>150.9846583640818</v>
       </c>
       <c r="F334" t="n">
         <v>973933</v>
@@ -7172,16 +7172,16 @@
         <v>43713</v>
       </c>
       <c r="B338" t="n">
-        <v>149.2608337402344</v>
+        <v>149.2608642578125</v>
       </c>
       <c r="C338" t="n">
-        <v>150.2119098154071</v>
+        <v>150.2119405274403</v>
       </c>
       <c r="D338" t="n">
-        <v>145.5159395704434</v>
+        <v>145.5159693223478</v>
       </c>
       <c r="E338" t="n">
-        <v>150.2119098154071</v>
+        <v>150.2119405274403</v>
       </c>
       <c r="F338" t="n">
         <v>845300</v>
@@ -7192,16 +7192,16 @@
         <v>43714</v>
       </c>
       <c r="B339" t="n">
-        <v>146.2292938232422</v>
+        <v>146.2292785644531</v>
       </c>
       <c r="C339" t="n">
-        <v>150.5091675558134</v>
+        <v>150.5091518504265</v>
       </c>
       <c r="D339" t="n">
-        <v>145.4862588243783</v>
+        <v>145.4862436431238</v>
       </c>
       <c r="E339" t="n">
-        <v>150.0633495799123</v>
+        <v>150.0633339210457</v>
       </c>
       <c r="F339" t="n">
         <v>678033</v>
@@ -7252,16 +7252,16 @@
         <v>43719</v>
       </c>
       <c r="B342" t="n">
-        <v>152.5301818847656</v>
+        <v>152.5301971435547</v>
       </c>
       <c r="C342" t="n">
-        <v>152.5301818847656</v>
+        <v>152.5301971435547</v>
       </c>
       <c r="D342" t="n">
-        <v>146.7047990800743</v>
+        <v>146.7048137561047</v>
       </c>
       <c r="E342" t="n">
-        <v>148.5772462524898</v>
+        <v>148.5772611158358</v>
       </c>
       <c r="F342" t="n">
         <v>523500</v>
@@ -7272,16 +7272,16 @@
         <v>43720</v>
       </c>
       <c r="B343" t="n">
-        <v>148.3691864013672</v>
+        <v>148.3692169189453</v>
       </c>
       <c r="C343" t="n">
-        <v>154.4918011372027</v>
+        <v>154.4918329141216</v>
       </c>
       <c r="D343" t="n">
-        <v>148.3394662181369</v>
+        <v>148.339496729602</v>
       </c>
       <c r="E343" t="n">
-        <v>153.9568076048933</v>
+        <v>153.9568392717711</v>
       </c>
       <c r="F343" t="n">
         <v>700866</v>
@@ -7292,16 +7292,16 @@
         <v>43721</v>
       </c>
       <c r="B344" t="n">
-        <v>149.2013854980469</v>
+        <v>149.2014007568359</v>
       </c>
       <c r="C344" t="n">
-        <v>150.4793986306752</v>
+        <v>150.4794140201663</v>
       </c>
       <c r="D344" t="n">
-        <v>145.6348126117433</v>
+        <v>145.6348275057798</v>
       </c>
       <c r="E344" t="n">
-        <v>148.606951644636</v>
+        <v>148.6069668426325</v>
       </c>
       <c r="F344" t="n">
         <v>622000</v>
@@ -7312,16 +7312,16 @@
         <v>43724</v>
       </c>
       <c r="B345" t="n">
-        <v>149.9444427490234</v>
+        <v>149.9444274902344</v>
       </c>
       <c r="C345" t="n">
-        <v>151.2521762587837</v>
+        <v>151.2521608669158</v>
       </c>
       <c r="D345" t="n">
-        <v>146.5264702548115</v>
+        <v>146.5264553438454</v>
       </c>
       <c r="E345" t="n">
-        <v>149.4986097335467</v>
+        <v>149.4985945201269</v>
       </c>
       <c r="F345" t="n">
         <v>541366</v>
@@ -7332,16 +7332,16 @@
         <v>43725</v>
       </c>
       <c r="B346" t="n">
-        <v>153.0652160644531</v>
+        <v>153.065185546875</v>
       </c>
       <c r="C346" t="n">
-        <v>153.0652160644531</v>
+        <v>153.065185546875</v>
       </c>
       <c r="D346" t="n">
-        <v>149.0825440738754</v>
+        <v>149.0825143503477</v>
       </c>
       <c r="E346" t="n">
-        <v>150.3902929818897</v>
+        <v>150.3902629976278</v>
       </c>
       <c r="F346" t="n">
         <v>1122433</v>
@@ -7352,16 +7352,16 @@
         <v>43726</v>
       </c>
       <c r="B347" t="n">
-        <v>152.4707489013672</v>
+        <v>152.4707641601562</v>
       </c>
       <c r="C347" t="n">
-        <v>153.2137837695358</v>
+        <v>153.2137991026854</v>
       </c>
       <c r="D347" t="n">
-        <v>151.4007768771544</v>
+        <v>151.4007920288641</v>
       </c>
       <c r="E347" t="n">
-        <v>151.4305121795976</v>
+        <v>151.4305273342831</v>
       </c>
       <c r="F347" t="n">
         <v>459166</v>
@@ -7372,16 +7372,16 @@
         <v>43727</v>
       </c>
       <c r="B348" t="n">
-        <v>153.0354614257812</v>
+        <v>153.0354766845703</v>
       </c>
       <c r="C348" t="n">
-        <v>155.3834467528314</v>
+        <v>155.3834622457323</v>
       </c>
       <c r="D348" t="n">
-        <v>151.5493917014036</v>
+        <v>151.5494068120203</v>
       </c>
       <c r="E348" t="n">
-        <v>154.4026504096753</v>
+        <v>154.4026658047834</v>
       </c>
       <c r="F348" t="n">
         <v>446666</v>
@@ -7392,16 +7392,16 @@
         <v>43728</v>
       </c>
       <c r="B349" t="n">
-        <v>153.7190856933594</v>
+        <v>153.7190551757812</v>
       </c>
       <c r="C349" t="n">
-        <v>155.0565396341165</v>
+        <v>155.056508851016</v>
       </c>
       <c r="D349" t="n">
-        <v>150.9847071959179</v>
+        <v>150.984677221191</v>
       </c>
       <c r="E349" t="n">
-        <v>153.0652112598768</v>
+        <v>153.0651808721112</v>
       </c>
       <c r="F349" t="n">
         <v>555866</v>
@@ -7412,16 +7412,16 @@
         <v>43731</v>
       </c>
       <c r="B350" t="n">
-        <v>157.9394836425781</v>
+        <v>157.9395141601562</v>
       </c>
       <c r="C350" t="n">
-        <v>159.0986161779464</v>
+        <v>159.0986469194959</v>
       </c>
       <c r="D350" t="n">
-        <v>153.6893310128942</v>
+        <v>153.6893607092441</v>
       </c>
       <c r="E350" t="n">
-        <v>154.5512465890978</v>
+        <v>154.5512764519898</v>
       </c>
       <c r="F350" t="n">
         <v>685766</v>
@@ -7512,16 +7512,16 @@
         <v>43738</v>
       </c>
       <c r="B355" t="n">
-        <v>160.0496978759766</v>
+        <v>160.0497131347656</v>
       </c>
       <c r="C355" t="n">
-        <v>161.5654876485006</v>
+        <v>161.5655030518017</v>
       </c>
       <c r="D355" t="n">
-        <v>157.5233765494093</v>
+        <v>157.5233915673444</v>
       </c>
       <c r="E355" t="n">
-        <v>158.3852920741947</v>
+        <v>158.385307174303</v>
       </c>
       <c r="F355" t="n">
         <v>546766</v>
@@ -7612,16 +7612,16 @@
         <v>43745</v>
       </c>
       <c r="B360" t="n">
-        <v>161.4168853759766</v>
+        <v>161.4169158935547</v>
       </c>
       <c r="C360" t="n">
-        <v>163.7054454381041</v>
+        <v>163.7054763883588</v>
       </c>
       <c r="D360" t="n">
-        <v>159.6336138095562</v>
+        <v>159.6336439899879</v>
       </c>
       <c r="E360" t="n">
-        <v>161.6249417878365</v>
+        <v>161.6249723447499</v>
       </c>
       <c r="F360" t="n">
         <v>812666</v>
@@ -7632,16 +7632,16 @@
         <v>43746</v>
       </c>
       <c r="B361" t="n">
-        <v>160.6441345214844</v>
+        <v>160.6441192626953</v>
       </c>
       <c r="C361" t="n">
-        <v>163.7351698925173</v>
+        <v>163.7351543401261</v>
       </c>
       <c r="D361" t="n">
-        <v>158.2664289595359</v>
+        <v>158.2664139265933</v>
       </c>
       <c r="E361" t="n">
-        <v>161.4168895849718</v>
+        <v>161.4168742527825</v>
       </c>
       <c r="F361" t="n">
         <v>478600</v>
@@ -7652,16 +7652,16 @@
         <v>43747</v>
       </c>
       <c r="B362" t="n">
-        <v>162.2788238525391</v>
+        <v>162.2788391113281</v>
       </c>
       <c r="C362" t="n">
-        <v>162.9029628838034</v>
+        <v>162.9029782012792</v>
       </c>
       <c r="D362" t="n">
-        <v>159.960543494568</v>
+        <v>159.9605585353733</v>
       </c>
       <c r="E362" t="n">
-        <v>161.9816068715598</v>
+        <v>161.9816221024021</v>
       </c>
       <c r="F362" t="n">
         <v>623966</v>
@@ -7672,16 +7672,16 @@
         <v>43748</v>
       </c>
       <c r="B363" t="n">
-        <v>163.1704406738281</v>
+        <v>163.1704559326172</v>
       </c>
       <c r="C363" t="n">
-        <v>163.7648745665525</v>
+        <v>163.7648898809297</v>
       </c>
       <c r="D363" t="n">
-        <v>161.387154112737</v>
+        <v>161.387169204763</v>
       </c>
       <c r="E363" t="n">
-        <v>162.2193645859674</v>
+        <v>162.2193797558171</v>
       </c>
       <c r="F363" t="n">
         <v>538133</v>
@@ -7692,16 +7692,16 @@
         <v>43749</v>
       </c>
       <c r="B364" t="n">
-        <v>167.2422790527344</v>
+        <v>167.2422943115234</v>
       </c>
       <c r="C364" t="n">
-        <v>168.282530850187</v>
+        <v>168.2825462038862</v>
       </c>
       <c r="D364" t="n">
-        <v>163.764881450249</v>
+        <v>163.7648963917685</v>
       </c>
       <c r="E364" t="n">
-        <v>163.764881450249</v>
+        <v>163.7648963917685</v>
       </c>
       <c r="F364" t="n">
         <v>518100</v>
@@ -7712,16 +7712,16 @@
         <v>43752</v>
       </c>
       <c r="B365" t="n">
-        <v>167.9258880615234</v>
+        <v>167.9259033203125</v>
       </c>
       <c r="C365" t="n">
-        <v>169.5902789878799</v>
+        <v>169.5902943979059</v>
       </c>
       <c r="D365" t="n">
-        <v>166.3803778821685</v>
+        <v>166.3803930005229</v>
       </c>
       <c r="E365" t="n">
-        <v>167.2125733453467</v>
+        <v>167.2125885393196</v>
       </c>
       <c r="F365" t="n">
         <v>323333</v>
@@ -7832,16 +7832,16 @@
         <v>43760</v>
       </c>
       <c r="B371" t="n">
-        <v>166.8856353759766</v>
+        <v>166.8856201171875</v>
       </c>
       <c r="C371" t="n">
-        <v>169.8874951600807</v>
+        <v>169.8874796268238</v>
       </c>
       <c r="D371" t="n">
-        <v>165.3401252040121</v>
+        <v>165.3401100865331</v>
       </c>
       <c r="E371" t="n">
-        <v>169.6497336672146</v>
+        <v>169.6497181556968</v>
       </c>
       <c r="F371" t="n">
         <v>630100</v>
@@ -7892,16 +7892,16 @@
         <v>43763</v>
       </c>
       <c r="B374" t="n">
-        <v>168.3716888427734</v>
+        <v>168.3717041015625</v>
       </c>
       <c r="C374" t="n">
-        <v>169.6497172112956</v>
+        <v>169.6497325859067</v>
       </c>
       <c r="D374" t="n">
-        <v>166.8558990044479</v>
+        <v>166.8559141258676</v>
       </c>
       <c r="E374" t="n">
-        <v>169.6497172112956</v>
+        <v>169.6497325859067</v>
       </c>
       <c r="F374" t="n">
         <v>471566</v>
@@ -7952,16 +7952,16 @@
         <v>43768</v>
       </c>
       <c r="B377" t="n">
-        <v>167.628662109375</v>
+        <v>167.6286926269531</v>
       </c>
       <c r="C377" t="n">
-        <v>169.4713891747379</v>
+        <v>169.4714200277931</v>
       </c>
       <c r="D377" t="n">
-        <v>166.3209286110662</v>
+        <v>166.3209588905653</v>
       </c>
       <c r="E377" t="n">
-        <v>169.1147318357295</v>
+        <v>169.1147626238536</v>
       </c>
       <c r="F377" t="n">
         <v>545966</v>
@@ -8012,16 +8012,16 @@
         <v>43773</v>
       </c>
       <c r="B380" t="n">
-        <v>165.9940338134766</v>
+        <v>165.9940185546875</v>
       </c>
       <c r="C380" t="n">
-        <v>168.5203560163308</v>
+        <v>168.5203405253128</v>
       </c>
       <c r="D380" t="n">
-        <v>163.9729700043584</v>
+        <v>163.9729549313531</v>
       </c>
       <c r="E380" t="n">
-        <v>168.5203560163308</v>
+        <v>168.5203405253128</v>
       </c>
       <c r="F380" t="n">
         <v>963600</v>
@@ -8032,16 +8032,16 @@
         <v>43774</v>
       </c>
       <c r="B381" t="n">
-        <v>161.5358123779297</v>
+        <v>161.5357971191406</v>
       </c>
       <c r="C381" t="n">
-        <v>166.8856583428364</v>
+        <v>166.885642578697</v>
       </c>
       <c r="D381" t="n">
-        <v>160.9710985204892</v>
+        <v>160.9710833150434</v>
       </c>
       <c r="E381" t="n">
-        <v>166.8856583428364</v>
+        <v>166.885642578697</v>
       </c>
       <c r="F381" t="n">
         <v>956400</v>
@@ -8052,16 +8052,16 @@
         <v>43775</v>
       </c>
       <c r="B382" t="n">
-        <v>163.4974212646484</v>
+        <v>163.4973907470703</v>
       </c>
       <c r="C382" t="n">
-        <v>164.5971136765558</v>
+        <v>164.5970829537148</v>
       </c>
       <c r="D382" t="n">
-        <v>160.1389036472698</v>
+        <v>160.1388737565751</v>
       </c>
       <c r="E382" t="n">
-        <v>161.9221906824013</v>
+        <v>161.9221604588475</v>
       </c>
       <c r="F382" t="n">
         <v>1813233</v>
@@ -8092,16 +8092,16 @@
         <v>43777</v>
       </c>
       <c r="B384" t="n">
-        <v>165.5184326171875</v>
+        <v>165.5184631347656</v>
       </c>
       <c r="C384" t="n">
-        <v>169.203886622259</v>
+        <v>169.2039178193453</v>
       </c>
       <c r="D384" t="n">
-        <v>163.4082239573274</v>
+        <v>163.4082540858343</v>
       </c>
       <c r="E384" t="n">
-        <v>164.6862372269023</v>
+        <v>164.6862675910438</v>
       </c>
       <c r="F384" t="n">
         <v>1517366</v>
@@ -8112,16 +8112,16 @@
         <v>43780</v>
       </c>
       <c r="B385" t="n">
-        <v>170.8385620117188</v>
+        <v>170.8385925292969</v>
       </c>
       <c r="C385" t="n">
-        <v>170.8385620117188</v>
+        <v>170.8385925292969</v>
       </c>
       <c r="D385" t="n">
-        <v>164.9834442152444</v>
+        <v>164.9834736868993</v>
       </c>
       <c r="E385" t="n">
-        <v>165.9642555840758</v>
+        <v>165.964285230937</v>
       </c>
       <c r="F385" t="n">
         <v>906700</v>
@@ -8132,16 +8132,16 @@
         <v>43781</v>
       </c>
       <c r="B386" t="n">
-        <v>167.9258880615234</v>
+        <v>167.9259033203125</v>
       </c>
       <c r="C386" t="n">
-        <v>171.6410625761589</v>
+        <v>171.6410781725318</v>
       </c>
       <c r="D386" t="n">
-        <v>166.8856361740087</v>
+        <v>166.8856513382741</v>
       </c>
       <c r="E386" t="n">
-        <v>170.8980276732318</v>
+        <v>170.8980432020879</v>
       </c>
       <c r="F386" t="n">
         <v>771166</v>
@@ -8152,16 +8152,16 @@
         <v>43782</v>
       </c>
       <c r="B387" t="n">
-        <v>167.8961486816406</v>
+        <v>167.8961791992188</v>
       </c>
       <c r="C387" t="n">
-        <v>170.2738540523652</v>
+        <v>170.273885002126</v>
       </c>
       <c r="D387" t="n">
-        <v>164.9834497763996</v>
+        <v>164.9834797645522</v>
       </c>
       <c r="E387" t="n">
-        <v>168.2528059989575</v>
+        <v>168.2528365813633</v>
       </c>
       <c r="F387" t="n">
         <v>1028933</v>
@@ -8172,16 +8172,16 @@
         <v>43783</v>
       </c>
       <c r="B388" t="n">
-        <v>161.5060577392578</v>
+        <v>161.5060882568359</v>
       </c>
       <c r="C388" t="n">
-        <v>167.4800566687947</v>
+        <v>167.4800883151972</v>
       </c>
       <c r="D388" t="n">
-        <v>160.9710641866256</v>
+        <v>160.9710946031133</v>
       </c>
       <c r="E388" t="n">
-        <v>165.1023361004741</v>
+        <v>165.1023672975915</v>
       </c>
       <c r="F388" t="n">
         <v>1805133</v>
@@ -8192,16 +8192,16 @@
         <v>43787</v>
       </c>
       <c r="B389" t="n">
-        <v>161.6249694824219</v>
+        <v>161.6249542236328</v>
       </c>
       <c r="C389" t="n">
-        <v>163.021878883618</v>
+        <v>163.0218634929487</v>
       </c>
       <c r="D389" t="n">
-        <v>158.8311506800296</v>
+        <v>158.8311356850011</v>
       </c>
       <c r="E389" t="n">
-        <v>161.5952492923612</v>
+        <v>161.5952340363779</v>
       </c>
       <c r="F389" t="n">
         <v>1204133</v>
@@ -8212,16 +8212,16 @@
         <v>43788</v>
       </c>
       <c r="B390" t="n">
-        <v>159.5741729736328</v>
+        <v>159.5741577148438</v>
       </c>
       <c r="C390" t="n">
-        <v>162.7840892986529</v>
+        <v>162.7840737329255</v>
       </c>
       <c r="D390" t="n">
-        <v>158.5339361700739</v>
+        <v>158.5339210107543</v>
       </c>
       <c r="E390" t="n">
-        <v>162.6354883601686</v>
+        <v>162.6354728086507</v>
       </c>
       <c r="F390" t="n">
         <v>1296633</v>
@@ -8252,16 +8252,16 @@
         <v>43791</v>
       </c>
       <c r="B392" t="n">
-        <v>169.9766540527344</v>
+        <v>169.9766387939453</v>
       </c>
       <c r="C392" t="n">
-        <v>169.9766540527344</v>
+        <v>169.9766387939453</v>
       </c>
       <c r="D392" t="n">
-        <v>164.2404313373464</v>
+        <v>164.2404165934975</v>
       </c>
       <c r="E392" t="n">
-        <v>165.1023469746995</v>
+        <v>165.1023321534766</v>
       </c>
       <c r="F392" t="n">
         <v>1134300</v>
@@ -8272,16 +8272,16 @@
         <v>43794</v>
       </c>
       <c r="B393" t="n">
-        <v>171.7599487304688</v>
+        <v>171.7599334716797</v>
       </c>
       <c r="C393" t="n">
-        <v>172.2652221552997</v>
+        <v>172.2652068516232</v>
       </c>
       <c r="D393" t="n">
-        <v>167.9556135358149</v>
+        <v>167.9555986149949</v>
       </c>
       <c r="E393" t="n">
-        <v>169.2039067698807</v>
+        <v>169.203891738165</v>
       </c>
       <c r="F393" t="n">
         <v>1287433</v>
@@ -8292,16 +8292,16 @@
         <v>43795</v>
       </c>
       <c r="B394" t="n">
-        <v>169.4119415283203</v>
+        <v>169.4119720458984</v>
       </c>
       <c r="C394" t="n">
-        <v>172.5029615889146</v>
+        <v>172.5029926633038</v>
       </c>
       <c r="D394" t="n">
-        <v>167.4800539904489</v>
+        <v>167.4800841600201</v>
       </c>
       <c r="E394" t="n">
-        <v>170.9574515586174</v>
+        <v>170.9574823546011</v>
       </c>
       <c r="F394" t="n">
         <v>9961800</v>
@@ -8372,16 +8372,16 @@
         <v>43801</v>
       </c>
       <c r="B398" t="n">
-        <v>167.1828308105469</v>
+        <v>167.182861328125</v>
       </c>
       <c r="C398" t="n">
-        <v>167.3017115416571</v>
+        <v>167.3017420809357</v>
       </c>
       <c r="D398" t="n">
-        <v>162.9623985682345</v>
+        <v>162.9624283154143</v>
       </c>
       <c r="E398" t="n">
-        <v>165.6373208377869</v>
+        <v>165.6373510732474</v>
       </c>
       <c r="F398" t="n">
         <v>805633</v>
@@ -8412,16 +8412,16 @@
         <v>43803</v>
       </c>
       <c r="B400" t="n">
-        <v>172.4435424804688</v>
+        <v>172.4435119628906</v>
       </c>
       <c r="C400" t="n">
-        <v>173.7215710133688</v>
+        <v>173.7215402696162</v>
       </c>
       <c r="D400" t="n">
-        <v>170.8980322596368</v>
+        <v>170.8980020155698</v>
       </c>
       <c r="E400" t="n">
-        <v>170.8980322596368</v>
+        <v>170.8980020155698</v>
       </c>
       <c r="F400" t="n">
         <v>662400</v>
@@ -8432,16 +8432,16 @@
         <v>43804</v>
       </c>
       <c r="B401" t="n">
-        <v>172.3543701171875</v>
+        <v>172.3543853759766</v>
       </c>
       <c r="C401" t="n">
-        <v>174.7617958462494</v>
+        <v>174.7618113181715</v>
       </c>
       <c r="D401" t="n">
-        <v>169.1147338425086</v>
+        <v>169.1147488144879</v>
       </c>
       <c r="E401" t="n">
-        <v>172.7110274604281</v>
+        <v>172.7110427507926</v>
       </c>
       <c r="F401" t="n">
         <v>632400</v>
@@ -8492,16 +8492,16 @@
         <v>43809</v>
       </c>
       <c r="B404" t="n">
-        <v>162.3382568359375</v>
+        <v>162.3382873535156</v>
       </c>
       <c r="C404" t="n">
-        <v>167.2720040741151</v>
+        <v>167.2720355191765</v>
       </c>
       <c r="D404" t="n">
-        <v>162.3382568359375</v>
+        <v>162.3382873535156</v>
       </c>
       <c r="E404" t="n">
-        <v>166.5884095841042</v>
+        <v>166.5884409006583</v>
       </c>
       <c r="F404" t="n">
         <v>1232166</v>
@@ -8512,16 +8512,16 @@
         <v>43810</v>
       </c>
       <c r="B405" t="n">
-        <v>167.0937042236328</v>
+        <v>167.0936737060547</v>
       </c>
       <c r="C405" t="n">
-        <v>167.0937042236328</v>
+        <v>167.0936737060547</v>
       </c>
       <c r="D405" t="n">
-        <v>161.9816201077289</v>
+        <v>161.9815905238091</v>
       </c>
       <c r="E405" t="n">
-        <v>162.7840954399877</v>
+        <v>162.7840657095058</v>
       </c>
       <c r="F405" t="n">
         <v>789933</v>
@@ -8572,16 +8572,16 @@
         <v>43815</v>
       </c>
       <c r="B408" t="n">
-        <v>171.9085693359375</v>
+        <v>171.9085540771484</v>
       </c>
       <c r="C408" t="n">
-        <v>175.8317853851723</v>
+        <v>175.8317697781544</v>
       </c>
       <c r="D408" t="n">
-        <v>167.0342619043242</v>
+        <v>167.0342470781839</v>
       </c>
       <c r="E408" t="n">
-        <v>167.1828628466874</v>
+        <v>167.1828480073571</v>
       </c>
       <c r="F408" t="n">
         <v>666133</v>
@@ -8592,16 +8592,16 @@
         <v>43816</v>
       </c>
       <c r="B409" t="n">
-        <v>173.1568450927734</v>
+        <v>173.1568603515625</v>
       </c>
       <c r="C409" t="n">
-        <v>175.2373487779778</v>
+        <v>175.2373642201033</v>
       </c>
       <c r="D409" t="n">
-        <v>171.4032785647917</v>
+        <v>171.4032936690544</v>
       </c>
       <c r="E409" t="n">
-        <v>173.4243418790616</v>
+        <v>173.4243571614228</v>
       </c>
       <c r="F409" t="n">
         <v>614666</v>
@@ -8712,16 +8712,16 @@
         <v>43826</v>
       </c>
       <c r="B415" t="n">
-        <v>189.6224822998047</v>
+        <v>189.6224975585938</v>
       </c>
       <c r="C415" t="n">
-        <v>194.9723421384545</v>
+        <v>194.9723578277431</v>
       </c>
       <c r="D415" t="n">
-        <v>184.9265118558081</v>
+        <v>184.9265267367157</v>
       </c>
       <c r="E415" t="n">
-        <v>194.9723421384545</v>
+        <v>194.9723578277431</v>
       </c>
       <c r="F415" t="n">
         <v>651400</v>
@@ -8752,16 +8752,16 @@
         <v>43832</v>
       </c>
       <c r="B417" t="n">
-        <v>197.4689331054688</v>
+        <v>197.4689483642578</v>
       </c>
       <c r="C417" t="n">
-        <v>199.3711156170877</v>
+        <v>199.3711310228619</v>
       </c>
       <c r="D417" t="n">
-        <v>191.4652139596019</v>
+        <v>191.4652287544725</v>
       </c>
       <c r="E417" t="n">
-        <v>193.7834941715491</v>
+        <v>193.7835091455575</v>
       </c>
       <c r="F417" t="n">
         <v>866733</v>
@@ -8772,16 +8772,16 @@
         <v>43833</v>
       </c>
       <c r="B418" t="n">
-        <v>205.8206787109375</v>
+        <v>205.8206634521484</v>
       </c>
       <c r="C418" t="n">
-        <v>205.8206787109375</v>
+        <v>205.8206634521484</v>
       </c>
       <c r="D418" t="n">
-        <v>194.3779375931219</v>
+        <v>194.3779231826556</v>
       </c>
       <c r="E418" t="n">
-        <v>195.4181895342114</v>
+        <v>195.4181750466247</v>
       </c>
       <c r="F418" t="n">
         <v>3123966</v>
@@ -8792,16 +8792,16 @@
         <v>43836</v>
       </c>
       <c r="B419" t="n">
-        <v>199.4744873046875</v>
+        <v>199.4744567871094</v>
       </c>
       <c r="C419" t="n">
-        <v>205.1941802716366</v>
+        <v>205.1941488790033</v>
       </c>
       <c r="D419" t="n">
-        <v>196.3465181391163</v>
+        <v>196.3464881000858</v>
       </c>
       <c r="E419" t="n">
-        <v>203.466349252025</v>
+        <v>203.4663181237324</v>
       </c>
       <c r="F419" t="n">
         <v>735666</v>
@@ -8812,16 +8812,16 @@
         <v>43837</v>
       </c>
       <c r="B420" t="n">
-        <v>193.9930725097656</v>
+        <v>193.9930419921875</v>
       </c>
       <c r="C420" t="n">
-        <v>200.1894168705087</v>
+        <v>200.1893853781668</v>
       </c>
       <c r="D420" t="n">
-        <v>193.9334947523008</v>
+        <v>193.933464244095</v>
       </c>
       <c r="E420" t="n">
-        <v>198.4020083864459</v>
+        <v>198.4019771752861</v>
       </c>
       <c r="F420" t="n">
         <v>612400</v>
@@ -8852,16 +8852,16 @@
         <v>43839</v>
       </c>
       <c r="B422" t="n">
-        <v>188.8691864013672</v>
+        <v>188.8691558837891</v>
       </c>
       <c r="C422" t="n">
-        <v>191.5205028574819</v>
+        <v>191.5204719115027</v>
       </c>
       <c r="D422" t="n">
-        <v>187.2009484680017</v>
+        <v>187.2009182199783</v>
       </c>
       <c r="E422" t="n">
-        <v>190.001209328158</v>
+        <v>190.0011786276671</v>
       </c>
       <c r="F422" t="n">
         <v>950500</v>
@@ -8872,16 +8872,16 @@
         <v>43840</v>
       </c>
       <c r="B423" t="n">
-        <v>184.8475341796875</v>
+        <v>184.8475036621094</v>
       </c>
       <c r="C423" t="n">
-        <v>190.6268199065933</v>
+        <v>190.6267884348786</v>
       </c>
       <c r="D423" t="n">
-        <v>182.315388215822</v>
+        <v>182.3153581162909</v>
       </c>
       <c r="E423" t="n">
-        <v>190.6268199065933</v>
+        <v>190.6267884348786</v>
       </c>
       <c r="F423" t="n">
         <v>656333</v>
@@ -8932,16 +8932,16 @@
         <v>43845</v>
       </c>
       <c r="B426" t="n">
-        <v>181.7493438720703</v>
+        <v>181.7493591308594</v>
       </c>
       <c r="C426" t="n">
-        <v>188.0350548876207</v>
+        <v>188.0350706741274</v>
       </c>
       <c r="D426" t="n">
-        <v>179.3363537754593</v>
+        <v>179.3363688316654</v>
       </c>
       <c r="E426" t="n">
-        <v>187.6775731897497</v>
+        <v>187.677588946244</v>
       </c>
       <c r="F426" t="n">
         <v>1526633</v>
@@ -8992,16 +8992,16 @@
         <v>43850</v>
       </c>
       <c r="B429" t="n">
-        <v>188.1244354248047</v>
+        <v>188.1244201660156</v>
       </c>
       <c r="C429" t="n">
-        <v>189.4947845599039</v>
+        <v>189.4947691899657</v>
       </c>
       <c r="D429" t="n">
-        <v>185.9497561980689</v>
+        <v>185.9497411156683</v>
       </c>
       <c r="E429" t="n">
-        <v>189.4649956788822</v>
+        <v>189.4649803113602</v>
       </c>
       <c r="F429" t="n">
         <v>883800</v>
@@ -9032,16 +9032,16 @@
         <v>43852</v>
       </c>
       <c r="B431" t="n">
-        <v>190.5672149658203</v>
+        <v>190.5672302246094</v>
       </c>
       <c r="C431" t="n">
-        <v>193.2781089929065</v>
+        <v>193.2781244687579</v>
       </c>
       <c r="D431" t="n">
-        <v>189.4947698760664</v>
+        <v>189.4947850489844</v>
       </c>
       <c r="E431" t="n">
-        <v>191.4013338738432</v>
+        <v>191.4013491994205</v>
       </c>
       <c r="F431" t="n">
         <v>460300</v>
@@ -9052,16 +9052,16 @@
         <v>43853</v>
       </c>
       <c r="B432" t="n">
-        <v>191.5502624511719</v>
+        <v>191.55029296875</v>
       </c>
       <c r="C432" t="n">
-        <v>191.5502624511719</v>
+        <v>191.55029296875</v>
       </c>
       <c r="D432" t="n">
-        <v>186.5157453879958</v>
+        <v>186.5157751034802</v>
       </c>
       <c r="E432" t="n">
-        <v>189.8224470203644</v>
+        <v>189.8224772626689</v>
       </c>
       <c r="F432" t="n">
         <v>1068366</v>
@@ -9092,16 +9092,16 @@
         <v>43857</v>
       </c>
       <c r="B434" t="n">
-        <v>182.4047241210938</v>
+        <v>182.4047393798828</v>
       </c>
       <c r="C434" t="n">
-        <v>189.7628800128631</v>
+        <v>189.7628958871874</v>
       </c>
       <c r="D434" t="n">
-        <v>180.5279490507258</v>
+        <v>180.5279641525161</v>
       </c>
       <c r="E434" t="n">
-        <v>189.7628800128631</v>
+        <v>189.7628958871874</v>
       </c>
       <c r="F434" t="n">
         <v>939566</v>
@@ -9232,16 +9232,16 @@
         <v>43866</v>
       </c>
       <c r="B441" t="n">
-        <v>173.9145660400391</v>
+        <v>173.91455078125</v>
       </c>
       <c r="C441" t="n">
-        <v>185.2050066793799</v>
+        <v>185.2049904299985</v>
       </c>
       <c r="D441" t="n">
-        <v>171.859042306193</v>
+        <v>171.85902722775</v>
       </c>
       <c r="E441" t="n">
-        <v>184.6985805422995</v>
+        <v>184.6985643373504</v>
       </c>
       <c r="F441" t="n">
         <v>2347200</v>
@@ -9272,16 +9272,16 @@
         <v>43868</v>
       </c>
       <c r="B443" t="n">
-        <v>171.6802978515625</v>
+        <v>171.6802825927734</v>
       </c>
       <c r="C443" t="n">
-        <v>180.8556515493858</v>
+        <v>180.8556354750996</v>
       </c>
       <c r="D443" t="n">
-        <v>171.4419716632469</v>
+        <v>171.4419564256401</v>
       </c>
       <c r="E443" t="n">
-        <v>172.9612651277013</v>
+        <v>172.961249755061</v>
       </c>
       <c r="F443" t="n">
         <v>1239533</v>
@@ -9292,16 +9292,16 @@
         <v>43871</v>
       </c>
       <c r="B444" t="n">
-        <v>166.1095733642578</v>
+        <v>166.1095428466797</v>
       </c>
       <c r="C444" t="n">
-        <v>172.752767167804</v>
+        <v>172.7527354297412</v>
       </c>
       <c r="D444" t="n">
-        <v>164.0838535119248</v>
+        <v>164.083823366511</v>
       </c>
       <c r="E444" t="n">
-        <v>171.6505330144978</v>
+        <v>171.6505014789369</v>
       </c>
       <c r="F444" t="n">
         <v>872966</v>
@@ -9312,16 +9312,16 @@
         <v>43872</v>
       </c>
       <c r="B445" t="n">
-        <v>172.8123016357422</v>
+        <v>172.8123474121094</v>
       </c>
       <c r="C445" t="n">
-        <v>174.4209615610627</v>
+        <v>174.4210077635489</v>
       </c>
       <c r="D445" t="n">
-        <v>167.3904988788129</v>
+        <v>167.3905432189951</v>
       </c>
       <c r="E445" t="n">
-        <v>168.6119034129483</v>
+        <v>168.6119480766692</v>
       </c>
       <c r="F445" t="n">
         <v>924566</v>
@@ -9332,16 +9332,16 @@
         <v>43873</v>
       </c>
       <c r="B446" t="n">
-        <v>174.9571990966797</v>
+        <v>174.9572143554688</v>
       </c>
       <c r="C446" t="n">
-        <v>176.3275329184407</v>
+        <v>176.3275482967427</v>
       </c>
       <c r="D446" t="n">
-        <v>171.412171152159</v>
+        <v>171.4121861017706</v>
       </c>
       <c r="E446" t="n">
-        <v>173.4974834903504</v>
+        <v>173.4974986218312</v>
       </c>
       <c r="F446" t="n">
         <v>872333</v>
@@ -9372,16 +9372,16 @@
         <v>43875</v>
       </c>
       <c r="B448" t="n">
-        <v>174.2422485351562</v>
+        <v>174.2422637939453</v>
       </c>
       <c r="C448" t="n">
-        <v>175.9998681978045</v>
+        <v>175.9998836105123</v>
       </c>
       <c r="D448" t="n">
-        <v>172.9910549794976</v>
+        <v>172.9910701287168</v>
       </c>
       <c r="E448" t="n">
-        <v>175.7913308878533</v>
+        <v>175.7913462822991</v>
       </c>
       <c r="F448" t="n">
         <v>468100</v>
@@ -9392,16 +9392,16 @@
         <v>43878</v>
       </c>
       <c r="B449" t="n">
-        <v>178.353271484375</v>
+        <v>178.3532867431641</v>
       </c>
       <c r="C449" t="n">
-        <v>178.353271484375</v>
+        <v>178.3532867431641</v>
       </c>
       <c r="D449" t="n">
-        <v>173.4676984865096</v>
+        <v>173.4677133273196</v>
       </c>
       <c r="E449" t="n">
-        <v>173.9741245675972</v>
+        <v>173.9741394517339</v>
       </c>
       <c r="F449" t="n">
         <v>278100</v>
@@ -9412,16 +9412,16 @@
         <v>43879</v>
       </c>
       <c r="B450" t="n">
-        <v>175.7019653320312</v>
+        <v>175.7019500732422</v>
       </c>
       <c r="C450" t="n">
-        <v>177.5191627652912</v>
+        <v>177.5191473486881</v>
       </c>
       <c r="D450" t="n">
-        <v>172.7825338868604</v>
+        <v>172.7825188816086</v>
       </c>
       <c r="E450" t="n">
-        <v>177.5191627652912</v>
+        <v>177.5191473486881</v>
       </c>
       <c r="F450" t="n">
         <v>669733</v>
@@ -9432,16 +9432,16 @@
         <v>43880</v>
       </c>
       <c r="B451" t="n">
-        <v>177.3701934814453</v>
+        <v>177.3702087402344</v>
       </c>
       <c r="C451" t="n">
-        <v>178.3234830416113</v>
+        <v>178.3234983824099</v>
       </c>
       <c r="D451" t="n">
-        <v>173.1995838537692</v>
+        <v>173.1995987537694</v>
       </c>
       <c r="E451" t="n">
-        <v>174.9869923090657</v>
+        <v>174.9870073628329</v>
       </c>
       <c r="F451" t="n">
         <v>740433</v>
@@ -9452,16 +9452,16 @@
         <v>43881</v>
       </c>
       <c r="B452" t="n">
-        <v>172.1569366455078</v>
+        <v>172.1569519042969</v>
       </c>
       <c r="C452" t="n">
-        <v>177.0722987901394</v>
+        <v>177.0723144845919</v>
       </c>
       <c r="D452" t="n">
-        <v>171.3228177068359</v>
+        <v>171.3228328916945</v>
       </c>
       <c r="E452" t="n">
-        <v>175.7019648628997</v>
+        <v>175.7019804358953</v>
       </c>
       <c r="F452" t="n">
         <v>757533</v>
@@ -9472,16 +9472,16 @@
         <v>43882</v>
       </c>
       <c r="B453" t="n">
-        <v>166.8245391845703</v>
+        <v>166.8245086669922</v>
       </c>
       <c r="C453" t="n">
-        <v>171.2334758587725</v>
+        <v>171.2334445346579</v>
       </c>
       <c r="D453" t="n">
-        <v>165.5435565592682</v>
+        <v>165.543526276023</v>
       </c>
       <c r="E453" t="n">
-        <v>169.8333376969871</v>
+        <v>169.8333066290028</v>
       </c>
       <c r="F453" t="n">
         <v>990066</v>
@@ -9492,16 +9492,16 @@
         <v>43887</v>
       </c>
       <c r="B454" t="n">
-        <v>156.4575653076172</v>
+        <v>156.4575500488281</v>
       </c>
       <c r="C454" t="n">
-        <v>160.5685975170366</v>
+        <v>160.5685818573121</v>
       </c>
       <c r="D454" t="n">
-        <v>154.1637305812634</v>
+        <v>154.1637155461845</v>
       </c>
       <c r="E454" t="n">
-        <v>159.5259412363235</v>
+        <v>159.5259256782859</v>
       </c>
       <c r="F454" t="n">
         <v>1832133</v>
@@ -9532,16 +9532,16 @@
         <v>43889</v>
       </c>
       <c r="B456" t="n">
-        <v>164.4412994384766</v>
+        <v>164.4413146972656</v>
       </c>
       <c r="C456" t="n">
-        <v>165.0073032576448</v>
+        <v>165.0073185689544</v>
       </c>
       <c r="D456" t="n">
-        <v>155.0574091621543</v>
+        <v>155.0574235501962</v>
       </c>
       <c r="E456" t="n">
-        <v>158.632225948565</v>
+        <v>158.6322406683202</v>
       </c>
       <c r="F456" t="n">
         <v>1340833</v>
@@ -9572,16 +9572,16 @@
         <v>43893</v>
       </c>
       <c r="B458" t="n">
-        <v>165.0966796875</v>
+        <v>165.0967102050781</v>
       </c>
       <c r="C458" t="n">
-        <v>168.6417078070837</v>
+        <v>168.6417389799487</v>
       </c>
       <c r="D458" t="n">
-        <v>161.0154365941427</v>
+        <v>161.0154663573165</v>
       </c>
       <c r="E458" t="n">
-        <v>161.1643961410971</v>
+        <v>161.1644259318055</v>
       </c>
       <c r="F458" t="n">
         <v>1281800</v>
@@ -9592,16 +9592,16 @@
         <v>43894</v>
       </c>
       <c r="B459" t="n">
-        <v>159.4663391113281</v>
+        <v>159.4663543701172</v>
       </c>
       <c r="C459" t="n">
-        <v>169.7439256406586</v>
+        <v>169.7439418828748</v>
       </c>
       <c r="D459" t="n">
-        <v>159.0790685693198</v>
+        <v>159.0790837910523</v>
       </c>
       <c r="E459" t="n">
-        <v>167.5692467693725</v>
+        <v>167.5692628035011</v>
       </c>
       <c r="F459" t="n">
         <v>1186600</v>
@@ -9612,16 +9612,16 @@
         <v>43895</v>
       </c>
       <c r="B460" t="n">
-        <v>152.8231658935547</v>
+        <v>152.8231811523438</v>
       </c>
       <c r="C460" t="n">
-        <v>161.7601934932251</v>
+        <v>161.7602096443411</v>
       </c>
       <c r="D460" t="n">
-        <v>151.6911430036774</v>
+        <v>151.6911581494385</v>
       </c>
       <c r="E460" t="n">
-        <v>156.3979829942326</v>
+        <v>156.397998609953</v>
       </c>
       <c r="F460" t="n">
         <v>1000500</v>
@@ -9632,16 +9632,16 @@
         <v>43896</v>
       </c>
       <c r="B461" t="n">
-        <v>148.9802551269531</v>
+        <v>148.9802398681641</v>
       </c>
       <c r="C461" t="n">
-        <v>152.8231723074485</v>
+        <v>152.8231566550619</v>
       </c>
       <c r="D461" t="n">
-        <v>147.8780210706527</v>
+        <v>147.8780059247562</v>
       </c>
       <c r="E461" t="n">
-        <v>151.9294755707833</v>
+        <v>151.9294600099305</v>
       </c>
       <c r="F461" t="n">
         <v>1046833</v>
@@ -9672,16 +9672,16 @@
         <v>43900</v>
       </c>
       <c r="B463" t="n">
-        <v>145.6437530517578</v>
+        <v>145.6437683105469</v>
       </c>
       <c r="C463" t="n">
-        <v>147.3715837841424</v>
+        <v>147.3715992239526</v>
       </c>
       <c r="D463" t="n">
-        <v>136.9152630573862</v>
+        <v>136.9152774017098</v>
       </c>
       <c r="E463" t="n">
-        <v>142.456206648502</v>
+        <v>142.4562215733386</v>
       </c>
       <c r="F463" t="n">
         <v>1718533</v>
@@ -9732,16 +9732,16 @@
         <v>43903</v>
       </c>
       <c r="B466" t="n">
-        <v>129.9145965576172</v>
+        <v>129.9146118164062</v>
       </c>
       <c r="C466" t="n">
-        <v>137.0344269206882</v>
+        <v>137.0344430157189</v>
       </c>
       <c r="D466" t="n">
-        <v>118.713515297641</v>
+        <v>118.7135292408355</v>
       </c>
       <c r="E466" t="n">
-        <v>136.9450602787476</v>
+        <v>136.945076363282</v>
       </c>
       <c r="F466" t="n">
         <v>2459466</v>
@@ -9812,16 +9812,16 @@
         <v>43909</v>
       </c>
       <c r="B470" t="n">
-        <v>107.542236328125</v>
+        <v>107.5422286987305</v>
       </c>
       <c r="C470" t="n">
-        <v>109.0615375076434</v>
+        <v>109.0615297704648</v>
       </c>
       <c r="D470" t="n">
-        <v>84.36554650207263</v>
+        <v>84.36554051690753</v>
       </c>
       <c r="E470" t="n">
-        <v>90.85978799581292</v>
+        <v>90.8597815499253</v>
       </c>
       <c r="F470" t="n">
         <v>2314466</v>
@@ -9852,16 +9852,16 @@
         <v>43913</v>
       </c>
       <c r="B472" t="n">
-        <v>113.7981414794922</v>
+        <v>113.7981491088867</v>
       </c>
       <c r="C472" t="n">
-        <v>119.6072074731813</v>
+        <v>119.6072154920344</v>
       </c>
       <c r="D472" t="n">
-        <v>108.4657126798635</v>
+        <v>108.4657199517548</v>
       </c>
       <c r="E472" t="n">
-        <v>118.9518294373453</v>
+        <v>118.9518374122596</v>
       </c>
       <c r="F472" t="n">
         <v>1372400</v>
@@ -9912,16 +9912,16 @@
         <v>43916</v>
       </c>
       <c r="B475" t="n">
-        <v>150.1122741699219</v>
+        <v>150.1122589111328</v>
       </c>
       <c r="C475" t="n">
-        <v>158.9301463915598</v>
+        <v>158.9301302364413</v>
       </c>
       <c r="D475" t="n">
-        <v>132.8936043550962</v>
+        <v>132.8935908465707</v>
       </c>
       <c r="E475" t="n">
-        <v>135.2470168120774</v>
+        <v>135.2470030643295</v>
       </c>
       <c r="F475" t="n">
         <v>1421366</v>
@@ -9992,16 +9992,16 @@
         <v>43922</v>
       </c>
       <c r="B479" t="n">
-        <v>119.3986892700195</v>
+        <v>119.398681640625</v>
       </c>
       <c r="C479" t="n">
-        <v>125.6248228790491</v>
+        <v>125.6248148518141</v>
       </c>
       <c r="D479" t="n">
-        <v>115.734505448208</v>
+        <v>115.7344980529492</v>
       </c>
       <c r="E479" t="n">
-        <v>120.649875283128</v>
+        <v>120.6498675737846</v>
       </c>
       <c r="F479" t="n">
         <v>1115733</v>
@@ -10012,16 +10012,16 @@
         <v>43923</v>
       </c>
       <c r="B480" t="n">
-        <v>121.5733642578125</v>
+        <v>121.573371887207</v>
       </c>
       <c r="C480" t="n">
-        <v>124.3438436888143</v>
+        <v>124.3438514920716</v>
       </c>
       <c r="D480" t="n">
-        <v>116.4792537399009</v>
+        <v>116.4792610496121</v>
       </c>
       <c r="E480" t="n">
-        <v>118.415614241661</v>
+        <v>118.4156216728895</v>
       </c>
       <c r="F480" t="n">
         <v>765700</v>
@@ -10052,16 +10052,16 @@
         <v>43927</v>
       </c>
       <c r="B482" t="n">
-        <v>128.0973968505859</v>
+        <v>128.0973815917969</v>
       </c>
       <c r="C482" t="n">
-        <v>135.6342865636811</v>
+        <v>135.6342704071079</v>
       </c>
       <c r="D482" t="n">
-        <v>118.2368759992794</v>
+        <v>118.2368619150623</v>
       </c>
       <c r="E482" t="n">
-        <v>119.1603691633358</v>
+        <v>119.1603549691134</v>
       </c>
       <c r="F482" t="n">
         <v>1479633</v>
@@ -10072,16 +10072,16 @@
         <v>43928</v>
       </c>
       <c r="B483" t="n">
-        <v>143.8861541748047</v>
+        <v>143.8861389160156</v>
       </c>
       <c r="C483" t="n">
-        <v>154.9084954917595</v>
+        <v>154.908479064077</v>
       </c>
       <c r="D483" t="n">
-        <v>138.0175169188297</v>
+        <v>138.0175022823959</v>
       </c>
       <c r="E483" t="n">
-        <v>145.1969256403997</v>
+        <v>145.1969102426065</v>
       </c>
       <c r="F483" t="n">
         <v>1844300</v>
@@ -10092,16 +10092,16 @@
         <v>43929</v>
       </c>
       <c r="B484" t="n">
-        <v>148.920654296875</v>
+        <v>148.9206390380859</v>
       </c>
       <c r="C484" t="n">
-        <v>152.5252598703173</v>
+        <v>152.5252442421911</v>
       </c>
       <c r="D484" t="n">
-        <v>142.0987288481829</v>
+        <v>142.0987142883857</v>
       </c>
       <c r="E484" t="n">
-        <v>144.3329854957831</v>
+        <v>144.3329707070583</v>
       </c>
       <c r="F484" t="n">
         <v>859700</v>
@@ -10112,16 +10112,16 @@
         <v>43930</v>
       </c>
       <c r="B485" t="n">
-        <v>145.5543823242188</v>
+        <v>145.5543975830078</v>
       </c>
       <c r="C485" t="n">
-        <v>153.0912714973958</v>
+        <v>153.0912875462937</v>
       </c>
       <c r="D485" t="n">
-        <v>144.4223595043424</v>
+        <v>144.422374644459</v>
       </c>
       <c r="E485" t="n">
-        <v>150.4995330476759</v>
+        <v>150.4995488248761</v>
       </c>
       <c r="F485" t="n">
         <v>918500</v>
@@ -10132,16 +10132,16 @@
         <v>43934</v>
       </c>
       <c r="B486" t="n">
-        <v>146.2395782470703</v>
+        <v>146.2395629882812</v>
       </c>
       <c r="C486" t="n">
-        <v>151.3038852244566</v>
+        <v>151.3038694372525</v>
       </c>
       <c r="D486" t="n">
-        <v>140.6390410831683</v>
+        <v>140.6390264087451</v>
       </c>
       <c r="E486" t="n">
-        <v>142.6647608437177</v>
+        <v>142.6647459579288</v>
       </c>
       <c r="F486" t="n">
         <v>651233</v>
@@ -10152,16 +10152,16 @@
         <v>43935</v>
       </c>
       <c r="B487" t="n">
-        <v>157.8576812744141</v>
+        <v>157.8576965332031</v>
       </c>
       <c r="C487" t="n">
-        <v>161.5814423628801</v>
+        <v>161.5814579816142</v>
       </c>
       <c r="D487" t="n">
-        <v>150.0824663034543</v>
+        <v>150.082480810678</v>
       </c>
       <c r="E487" t="n">
-        <v>150.171832933092</v>
+        <v>150.171847448954</v>
       </c>
       <c r="F487" t="n">
         <v>964366</v>
@@ -10192,16 +10192,16 @@
         <v>43937</v>
       </c>
       <c r="B489" t="n">
-        <v>154.7893218994141</v>
+        <v>154.7893371582031</v>
       </c>
       <c r="C489" t="n">
-        <v>158.4832944961593</v>
+        <v>158.4833101190921</v>
       </c>
       <c r="D489" t="n">
-        <v>151.5719865290805</v>
+        <v>151.5720014707118</v>
       </c>
       <c r="E489" t="n">
-        <v>155.5638630743422</v>
+        <v>155.5638784094838</v>
       </c>
       <c r="F489" t="n">
         <v>851733</v>
@@ -10252,16 +10252,16 @@
         <v>43943</v>
       </c>
       <c r="B492" t="n">
-        <v>158.8109436035156</v>
+        <v>158.8109741210938</v>
       </c>
       <c r="C492" t="n">
-        <v>166.824484132118</v>
+        <v>166.8245161896017</v>
       </c>
       <c r="D492" t="n">
-        <v>157.6193431758334</v>
+        <v>157.6193734644301</v>
       </c>
       <c r="E492" t="n">
-        <v>166.824484132118</v>
+        <v>166.8245161896017</v>
       </c>
       <c r="F492" t="n">
         <v>2119233</v>
@@ -10272,16 +10272,16 @@
         <v>43944</v>
       </c>
       <c r="B493" t="n">
-        <v>151.8401031494141</v>
+        <v>151.8401184082031</v>
       </c>
       <c r="C493" t="n">
-        <v>160.8664974239381</v>
+        <v>160.8665135898119</v>
       </c>
       <c r="D493" t="n">
-        <v>144.8096395919027</v>
+        <v>144.809654144183</v>
       </c>
       <c r="E493" t="n">
-        <v>159.8238411694891</v>
+        <v>159.8238572305839</v>
       </c>
       <c r="F493" t="n">
         <v>1242300</v>
@@ -10292,16 +10292,16 @@
         <v>43945</v>
       </c>
       <c r="B494" t="n">
-        <v>148.9504547119141</v>
+        <v>148.9504699707031</v>
       </c>
       <c r="C494" t="n">
-        <v>152.0188304424938</v>
+        <v>152.0188460156135</v>
       </c>
       <c r="D494" t="n">
-        <v>136.1109176366947</v>
+        <v>136.1109315801753</v>
       </c>
       <c r="E494" t="n">
-        <v>146.954524073503</v>
+        <v>146.9545391278248</v>
       </c>
       <c r="F494" t="n">
         <v>1301233</v>
@@ -10312,16 +10312,16 @@
         <v>43948</v>
       </c>
       <c r="B495" t="n">
-        <v>156.9639739990234</v>
+        <v>156.9639892578125</v>
       </c>
       <c r="C495" t="n">
-        <v>157.9172635317512</v>
+        <v>157.9172788832115</v>
       </c>
       <c r="D495" t="n">
-        <v>152.8231533687841</v>
+        <v>152.8231682250355</v>
       </c>
       <c r="E495" t="n">
-        <v>153.8658095336986</v>
+        <v>153.8658244913087</v>
       </c>
       <c r="F495" t="n">
         <v>935633</v>
@@ -10332,16 +10332,16 @@
         <v>43949</v>
       </c>
       <c r="B496" t="n">
-        <v>159.138671875</v>
+        <v>159.1386566162109</v>
       </c>
       <c r="C496" t="n">
-        <v>166.1989245453164</v>
+        <v>166.1989086095649</v>
       </c>
       <c r="D496" t="n">
-        <v>157.8874934196113</v>
+        <v>157.8874782807897</v>
       </c>
       <c r="E496" t="n">
-        <v>157.8874934196113</v>
+        <v>157.8874782807897</v>
       </c>
       <c r="F496" t="n">
         <v>787066</v>
@@ -10352,16 +10352,16 @@
         <v>43950</v>
       </c>
       <c r="B497" t="n">
-        <v>161.9591217041016</v>
+        <v>161.9591369628906</v>
       </c>
       <c r="C497" t="n">
-        <v>164.7900447671948</v>
+        <v>164.790060292696</v>
       </c>
       <c r="D497" t="n">
-        <v>159.724175264275</v>
+        <v>159.7241903125012</v>
       </c>
       <c r="E497" t="n">
-        <v>161.3631299241343</v>
+        <v>161.3631451267727</v>
       </c>
       <c r="F497" t="n">
         <v>594666</v>
@@ -10372,16 +10372,16 @@
         <v>43951</v>
       </c>
       <c r="B498" t="n">
-        <v>156.2674560546875</v>
+        <v>156.2674407958984</v>
       </c>
       <c r="C498" t="n">
-        <v>162.108121265528</v>
+        <v>162.1081054364251</v>
       </c>
       <c r="D498" t="n">
-        <v>155.4926757908048</v>
+        <v>155.4926606076694</v>
       </c>
       <c r="E498" t="n">
-        <v>159.0983944350523</v>
+        <v>159.0983788998354</v>
       </c>
       <c r="F498" t="n">
         <v>826166</v>
@@ -10392,16 +10392,16 @@
         <v>43955</v>
       </c>
       <c r="B499" t="n">
-        <v>152.4531402587891</v>
+        <v>152.4531555175781</v>
       </c>
       <c r="C499" t="n">
-        <v>152.8107322907865</v>
+        <v>152.8107475853664</v>
       </c>
       <c r="D499" t="n">
-        <v>147.5660592592903</v>
+        <v>147.5660740289393</v>
       </c>
       <c r="E499" t="n">
-        <v>148.5494411364585</v>
+        <v>148.5494560045326</v>
       </c>
       <c r="F499" t="n">
         <v>865433</v>
@@ -10452,16 +10452,16 @@
         <v>43958</v>
       </c>
       <c r="B502" t="n">
-        <v>158.7110137939453</v>
+        <v>158.7109985351562</v>
       </c>
       <c r="C502" t="n">
-        <v>165.0880598931634</v>
+        <v>165.0880440212726</v>
       </c>
       <c r="D502" t="n">
-        <v>156.9826495560124</v>
+        <v>156.9826344633917</v>
       </c>
       <c r="E502" t="n">
-        <v>157.9660315605315</v>
+        <v>157.9660163733665</v>
       </c>
       <c r="F502" t="n">
         <v>1272300</v>
@@ -10492,16 +10492,16 @@
         <v>43962</v>
       </c>
       <c r="B504" t="n">
-        <v>146.9700622558594</v>
+        <v>146.9700775146484</v>
       </c>
       <c r="C504" t="n">
-        <v>152.6915345641711</v>
+        <v>152.6915504169773</v>
       </c>
       <c r="D504" t="n">
-        <v>146.5826721647091</v>
+        <v>146.5826873832784</v>
       </c>
       <c r="E504" t="n">
-        <v>149.9499906975384</v>
+        <v>149.9500062657109</v>
       </c>
       <c r="F504" t="n">
         <v>466500</v>
@@ -10512,16 +10512,16 @@
         <v>43963</v>
       </c>
       <c r="B505" t="n">
-        <v>151.7081756591797</v>
+        <v>151.7081451416016</v>
       </c>
       <c r="C505" t="n">
-        <v>155.3436925452999</v>
+        <v>155.3436612964021</v>
       </c>
       <c r="D505" t="n">
-        <v>147.0594938625293</v>
+        <v>147.0594642800789</v>
       </c>
       <c r="E505" t="n">
-        <v>147.5362782414084</v>
+        <v>147.5362485630481</v>
       </c>
       <c r="F505" t="n">
         <v>973566</v>
@@ -10552,16 +10552,16 @@
         <v>43965</v>
       </c>
       <c r="B507" t="n">
-        <v>141.2784271240234</v>
+        <v>141.2784118652344</v>
       </c>
       <c r="C507" t="n">
-        <v>147.5064828667171</v>
+        <v>147.5064669352663</v>
       </c>
       <c r="D507" t="n">
-        <v>138.3580943310847</v>
+        <v>138.3580793877065</v>
       </c>
       <c r="E507" t="n">
-        <v>145.6589263134315</v>
+        <v>145.6589105815262</v>
       </c>
       <c r="F507" t="n">
         <v>844800</v>
@@ -10572,16 +10572,16 @@
         <v>43966</v>
       </c>
       <c r="B508" t="n">
-        <v>139.7586364746094</v>
+        <v>139.7586517333984</v>
       </c>
       <c r="C508" t="n">
-        <v>143.5431430510845</v>
+        <v>143.5431587230644</v>
       </c>
       <c r="D508" t="n">
-        <v>134.9907480869898</v>
+        <v>134.9907628252228</v>
       </c>
       <c r="E508" t="n">
-        <v>140.3248301358833</v>
+        <v>140.3248454564891</v>
       </c>
       <c r="F508" t="n">
         <v>930266</v>
@@ -10612,16 +10612,16 @@
         <v>43970</v>
       </c>
       <c r="B510" t="n">
-        <v>150.1585998535156</v>
+        <v>150.1586151123047</v>
       </c>
       <c r="C510" t="n">
-        <v>154.9562867029296</v>
+        <v>154.9563024492492</v>
       </c>
       <c r="D510" t="n">
-        <v>145.8078992613276</v>
+        <v>145.807914078008</v>
       </c>
       <c r="E510" t="n">
-        <v>148.2216493010691</v>
+        <v>148.2216643630295</v>
       </c>
       <c r="F510" t="n">
         <v>591566</v>
@@ -10632,16 +10632,16 @@
         <v>43971</v>
       </c>
       <c r="B511" t="n">
-        <v>151.6783599853516</v>
+        <v>151.6783752441406</v>
       </c>
       <c r="C511" t="n">
-        <v>154.181504208285</v>
+        <v>154.1815197188895</v>
       </c>
       <c r="D511" t="n">
-        <v>149.3540193566921</v>
+        <v>149.3540343816533</v>
       </c>
       <c r="E511" t="n">
-        <v>150.7545894111537</v>
+        <v>150.7546045770118</v>
       </c>
       <c r="F511" t="n">
         <v>544933</v>
@@ -10652,16 +10652,16 @@
         <v>43972</v>
       </c>
       <c r="B512" t="n">
-        <v>156.1780548095703</v>
+        <v>156.1780395507812</v>
       </c>
       <c r="C512" t="n">
-        <v>158.6811990955166</v>
+        <v>158.6811835921673</v>
       </c>
       <c r="D512" t="n">
-        <v>146.1952908961648</v>
+        <v>146.1952766127041</v>
       </c>
       <c r="E512" t="n">
-        <v>152.1253500655098</v>
+        <v>152.125335202675</v>
       </c>
       <c r="F512" t="n">
         <v>1784500</v>
@@ -10672,16 +10672,16 @@
         <v>43973</v>
       </c>
       <c r="B513" t="n">
-        <v>155.5522766113281</v>
+        <v>155.5522918701172</v>
       </c>
       <c r="C513" t="n">
-        <v>156.9528315128846</v>
+        <v>156.95284690906</v>
       </c>
       <c r="D513" t="n">
-        <v>153.4067244144283</v>
+        <v>153.406739462751</v>
       </c>
       <c r="E513" t="n">
-        <v>156.4462491150195</v>
+        <v>156.4462644615022</v>
       </c>
       <c r="F513" t="n">
         <v>725600</v>
@@ -10692,16 +10692,16 @@
         <v>43976</v>
       </c>
       <c r="B514" t="n">
-        <v>161.63134765625</v>
+        <v>161.6313323974609</v>
       </c>
       <c r="C514" t="n">
-        <v>162.6147145106512</v>
+        <v>162.6146991590275</v>
       </c>
       <c r="D514" t="n">
-        <v>157.429652075539</v>
+        <v>157.4296372134105</v>
       </c>
       <c r="E514" t="n">
-        <v>157.9660326182394</v>
+        <v>157.966017705474</v>
       </c>
       <c r="F514" t="n">
         <v>561666</v>
@@ -10712,16 +10712,16 @@
         <v>43977</v>
       </c>
       <c r="B515" t="n">
-        <v>163.3298797607422</v>
+        <v>163.3298950195312</v>
       </c>
       <c r="C515" t="n">
-        <v>164.9092534423791</v>
+        <v>164.9092688487182</v>
       </c>
       <c r="D515" t="n">
-        <v>160.945942936563</v>
+        <v>160.9459579726372</v>
       </c>
       <c r="E515" t="n">
-        <v>164.9092534423791</v>
+        <v>164.9092688487182</v>
       </c>
       <c r="F515" t="n">
         <v>734300</v>
@@ -10732,16 +10732,16 @@
         <v>43978</v>
       </c>
       <c r="B516" t="n">
-        <v>163.8960571289062</v>
+        <v>163.8960723876953</v>
       </c>
       <c r="C516" t="n">
-        <v>165.9820130095902</v>
+        <v>165.9820284625826</v>
       </c>
       <c r="D516" t="n">
-        <v>160.320137092505</v>
+        <v>160.3201520183744</v>
       </c>
       <c r="E516" t="n">
-        <v>165.5350116375157</v>
+        <v>165.535027048892</v>
       </c>
       <c r="F516" t="n">
         <v>627900</v>
@@ -10752,16 +10752,16 @@
         <v>43979</v>
       </c>
       <c r="B517" t="n">
-        <v>163.9258728027344</v>
+        <v>163.9258880615234</v>
       </c>
       <c r="C517" t="n">
-        <v>168.0679717816257</v>
+        <v>168.0679874259757</v>
       </c>
       <c r="D517" t="n">
-        <v>161.3333342871174</v>
+        <v>161.333349304584</v>
       </c>
       <c r="E517" t="n">
-        <v>163.4490884655809</v>
+        <v>163.4491036799892</v>
       </c>
       <c r="F517" t="n">
         <v>560100</v>
@@ -10772,16 +10772,16 @@
         <v>43980</v>
       </c>
       <c r="B518" t="n">
-        <v>163.4788970947266</v>
+        <v>163.4788818359375</v>
       </c>
       <c r="C518" t="n">
-        <v>165.0582557337539</v>
+        <v>165.0582403275507</v>
       </c>
       <c r="D518" t="n">
-        <v>157.9958238149825</v>
+        <v>157.9958090679723</v>
       </c>
       <c r="E518" t="n">
-        <v>163.9556814626646</v>
+        <v>163.9556661593735</v>
       </c>
       <c r="F518" t="n">
         <v>1761600</v>
@@ -10792,16 +10792,16 @@
         <v>43983</v>
       </c>
       <c r="B519" t="n">
-        <v>162.4061126708984</v>
+        <v>162.4061279296875</v>
       </c>
       <c r="C519" t="n">
-        <v>164.7304533981214</v>
+        <v>164.7304688752928</v>
       </c>
       <c r="D519" t="n">
-        <v>160.4095659164942</v>
+        <v>160.4095809876987</v>
       </c>
       <c r="E519" t="n">
-        <v>161.8995302529245</v>
+        <v>161.8995454641179</v>
       </c>
       <c r="F519" t="n">
         <v>557733</v>
@@ -10812,16 +10812,16 @@
         <v>43984</v>
       </c>
       <c r="B520" t="n">
-        <v>162.5848846435547</v>
+        <v>162.5848999023438</v>
       </c>
       <c r="C520" t="n">
-        <v>164.1642581992473</v>
+        <v>164.1642736062624</v>
       </c>
       <c r="D520" t="n">
-        <v>159.7241637140029</v>
+        <v>159.7241787043098</v>
       </c>
       <c r="E520" t="n">
-        <v>163.8662623308128</v>
+        <v>163.8662777098608</v>
       </c>
       <c r="F520" t="n">
         <v>917300</v>
@@ -10872,16 +10872,16 @@
         <v>43987</v>
       </c>
       <c r="B523" t="n">
-        <v>177.4547424316406</v>
+        <v>177.4547576904297</v>
       </c>
       <c r="C523" t="n">
-        <v>182.3716367570957</v>
+        <v>182.3716524386734</v>
       </c>
       <c r="D523" t="n">
-        <v>175.1006036829517</v>
+        <v>175.1006187393156</v>
       </c>
       <c r="E523" t="n">
-        <v>178.7957163670739</v>
+        <v>178.7957317411692</v>
       </c>
       <c r="F523" t="n">
         <v>929700</v>
@@ -10892,16 +10892,16 @@
         <v>43990</v>
       </c>
       <c r="B524" t="n">
-        <v>181.9842529296875</v>
+        <v>181.9842376708984</v>
       </c>
       <c r="C524" t="n">
-        <v>184.1894015705667</v>
+        <v>184.1893861268831</v>
       </c>
       <c r="D524" t="n">
-        <v>176.3521890193455</v>
+        <v>176.3521742327868</v>
       </c>
       <c r="E524" t="n">
-        <v>178.2891549669007</v>
+        <v>178.2891400179336</v>
       </c>
       <c r="F524" t="n">
         <v>540433</v>
@@ -10932,16 +10932,16 @@
         <v>43992</v>
       </c>
       <c r="B526" t="n">
-        <v>180.8518524169922</v>
+        <v>180.8518676757812</v>
       </c>
       <c r="C526" t="n">
-        <v>183.5635982593205</v>
+        <v>183.5636137469044</v>
       </c>
       <c r="D526" t="n">
-        <v>178.4977137569072</v>
+        <v>178.4977288170735</v>
       </c>
       <c r="E526" t="n">
-        <v>181.4180461060608</v>
+        <v>181.4180614126206</v>
       </c>
       <c r="F526" t="n">
         <v>715466</v>
@@ -10952,16 +10952,16 @@
         <v>43994</v>
       </c>
       <c r="B527" t="n">
-        <v>177.9315338134766</v>
+        <v>177.9315643310547</v>
       </c>
       <c r="C527" t="n">
-        <v>180.2260763105577</v>
+        <v>180.2261072216798</v>
       </c>
       <c r="D527" t="n">
-        <v>171.763075210948</v>
+        <v>171.763104670555</v>
       </c>
       <c r="E527" t="n">
-        <v>174.0874157801964</v>
+        <v>174.0874456384582</v>
       </c>
       <c r="F527" t="n">
         <v>1048900</v>
@@ -10972,16 +10972,16 @@
         <v>43997</v>
       </c>
       <c r="B528" t="n">
-        <v>180.3750762939453</v>
+        <v>180.3750610351562</v>
       </c>
       <c r="C528" t="n">
-        <v>182.8782205864339</v>
+        <v>182.8782051158919</v>
       </c>
       <c r="D528" t="n">
-        <v>173.5212465092347</v>
+        <v>173.5212318302438</v>
       </c>
       <c r="E528" t="n">
-        <v>175.785991054967</v>
+        <v>175.7859761843905</v>
       </c>
       <c r="F528" t="n">
         <v>826966</v>
@@ -10992,16 +10992,16 @@
         <v>43998</v>
       </c>
       <c r="B529" t="n">
-        <v>179.8387145996094</v>
+        <v>179.8386993408203</v>
       </c>
       <c r="C529" t="n">
-        <v>186.6627470235547</v>
+        <v>186.6627311857664</v>
       </c>
       <c r="D529" t="n">
-        <v>177.1269683507915</v>
+        <v>177.1269533220862</v>
       </c>
       <c r="E529" t="n">
-        <v>183.5934238522931</v>
+        <v>183.5934082749279</v>
       </c>
       <c r="F529" t="n">
         <v>733633</v>
@@ -11012,16 +11012,16 @@
         <v>43999</v>
       </c>
       <c r="B530" t="n">
-        <v>181.2392425537109</v>
+        <v>181.2392730712891</v>
       </c>
       <c r="C530" t="n">
-        <v>186.066727321228</v>
+        <v>186.0667586516717</v>
       </c>
       <c r="D530" t="n">
-        <v>180.6134678764014</v>
+        <v>180.6134982886098</v>
       </c>
       <c r="E530" t="n">
-        <v>182.0438359788805</v>
+        <v>182.0438666319384</v>
       </c>
       <c r="F530" t="n">
         <v>934766</v>
@@ -11032,16 +11032,16 @@
         <v>44000</v>
       </c>
       <c r="B531" t="n">
-        <v>179.6896820068359</v>
+        <v>179.689697265625</v>
       </c>
       <c r="C531" t="n">
-        <v>182.9080102346423</v>
+        <v>182.9080257667236</v>
       </c>
       <c r="D531" t="n">
-        <v>178.4381174965946</v>
+        <v>178.438132649104</v>
       </c>
       <c r="E531" t="n">
-        <v>181.7756380139382</v>
+        <v>181.7756534498614</v>
       </c>
       <c r="F531" t="n">
         <v>656233</v>
@@ -11052,16 +11052,16 @@
         <v>44001</v>
       </c>
       <c r="B532" t="n">
-        <v>187.1693267822266</v>
+        <v>187.1693115234375</v>
       </c>
       <c r="C532" t="n">
-        <v>190.1194576033739</v>
+        <v>190.1194421040784</v>
       </c>
       <c r="D532" t="n">
-        <v>181.0306805284143</v>
+        <v>181.0306657700721</v>
       </c>
       <c r="E532" t="n">
-        <v>181.775662752811</v>
+        <v>181.7756479337349</v>
       </c>
       <c r="F532" t="n">
         <v>2381566</v>
@@ -11092,16 +11092,16 @@
         <v>44005</v>
       </c>
       <c r="B534" t="n">
-        <v>185.9475402832031</v>
+        <v>185.9475555419922</v>
       </c>
       <c r="C534" t="n">
-        <v>188.8380746422072</v>
+        <v>188.8380901381925</v>
       </c>
       <c r="D534" t="n">
-        <v>179.6002930167151</v>
+        <v>179.6003077546513</v>
       </c>
       <c r="E534" t="n">
-        <v>182.6696158152284</v>
+        <v>182.6696308050322</v>
       </c>
       <c r="F534" t="n">
         <v>796833</v>
@@ -11132,16 +11132,16 @@
         <v>44007</v>
       </c>
       <c r="B536" t="n">
-        <v>184.9939880371094</v>
+        <v>184.9939727783203</v>
       </c>
       <c r="C536" t="n">
-        <v>185.7687683237836</v>
+        <v>185.7687530010886</v>
       </c>
       <c r="D536" t="n">
-        <v>180.017497168815</v>
+        <v>180.0174823204999</v>
       </c>
       <c r="E536" t="n">
-        <v>182.0736553457825</v>
+        <v>182.0736403278702</v>
       </c>
       <c r="F536" t="n">
         <v>496966</v>
@@ -11172,16 +11172,16 @@
         <v>44011</v>
       </c>
       <c r="B538" t="n">
-        <v>188.0334777832031</v>
+        <v>188.0334930419922</v>
       </c>
       <c r="C538" t="n">
-        <v>188.0334777832031</v>
+        <v>188.0334930419922</v>
       </c>
       <c r="D538" t="n">
-        <v>182.0736212142059</v>
+        <v>182.0736359893566</v>
       </c>
       <c r="E538" t="n">
-        <v>184.1297638490264</v>
+        <v>184.1297787910318</v>
       </c>
       <c r="F538" t="n">
         <v>392600</v>
@@ -11212,16 +11212,16 @@
         <v>44013</v>
       </c>
       <c r="B540" t="n">
-        <v>187.7056884765625</v>
+        <v>187.7057037353516</v>
       </c>
       <c r="C540" t="n">
-        <v>189.9108366739434</v>
+        <v>189.9108521119912</v>
       </c>
       <c r="D540" t="n">
-        <v>185.232342483095</v>
+        <v>185.2323575408232</v>
       </c>
       <c r="E540" t="n">
-        <v>185.7985361463114</v>
+        <v>185.7985512500661</v>
       </c>
       <c r="F540" t="n">
         <v>601100</v>
@@ -11252,16 +11252,16 @@
         <v>44015</v>
       </c>
       <c r="B542" t="n">
-        <v>181.5074462890625</v>
+        <v>181.5074615478516</v>
       </c>
       <c r="C542" t="n">
-        <v>184.4575768075846</v>
+        <v>184.4575923143823</v>
       </c>
       <c r="D542" t="n">
-        <v>178.0805314397118</v>
+        <v>178.0805464104103</v>
       </c>
       <c r="E542" t="n">
-        <v>179.3917072953663</v>
+        <v>179.3917223762915</v>
       </c>
       <c r="F542" t="n">
         <v>277066</v>
@@ -11272,16 +11272,16 @@
         <v>44018</v>
       </c>
       <c r="B543" t="n">
-        <v>181.7756500244141</v>
+        <v>181.7756652832031</v>
       </c>
       <c r="C543" t="n">
-        <v>185.2919592083969</v>
+        <v>185.2919747623554</v>
       </c>
       <c r="D543" t="n">
-        <v>180.0770840027784</v>
+        <v>180.0770991189848</v>
       </c>
       <c r="E543" t="n">
-        <v>182.1034439989999</v>
+        <v>182.103459285305</v>
       </c>
       <c r="F543" t="n">
         <v>817833</v>
@@ -11292,16 +11292,16 @@
         <v>44019</v>
       </c>
       <c r="B544" t="n">
-        <v>178.646728515625</v>
+        <v>178.6467437744141</v>
       </c>
       <c r="C544" t="n">
-        <v>182.8186255916096</v>
+        <v>182.8186412067338</v>
       </c>
       <c r="D544" t="n">
-        <v>177.8421350490122</v>
+        <v>177.8421502390783</v>
       </c>
       <c r="E544" t="n">
-        <v>178.7957188853491</v>
+        <v>178.7957341568639</v>
       </c>
       <c r="F544" t="n">
         <v>1026966</v>
@@ -11312,16 +11312,16 @@
         <v>44020</v>
       </c>
       <c r="B545" t="n">
-        <v>180.9412689208984</v>
+        <v>180.9412841796875</v>
       </c>
       <c r="C545" t="n">
-        <v>183.5040093454935</v>
+        <v>183.5040248203987</v>
       </c>
       <c r="D545" t="n">
-        <v>177.1567620095117</v>
+        <v>177.1567769491531</v>
       </c>
       <c r="E545" t="n">
-        <v>180.4346713566746</v>
+        <v>180.4346865727422</v>
       </c>
       <c r="F545" t="n">
         <v>677066</v>
@@ -11392,16 +11392,16 @@
         <v>44026</v>
       </c>
       <c r="B549" t="n">
-        <v>178.4679412841797</v>
+        <v>178.4679260253906</v>
       </c>
       <c r="C549" t="n">
-        <v>179.2129235145311</v>
+        <v>179.212908192047</v>
       </c>
       <c r="D549" t="n">
-        <v>173.2828637483977</v>
+        <v>173.2828489329264</v>
       </c>
       <c r="E549" t="n">
-        <v>175.0708241325815</v>
+        <v>175.0708091642418</v>
       </c>
       <c r="F549" t="n">
         <v>493066</v>
@@ -11412,16 +11412,16 @@
         <v>44027</v>
       </c>
       <c r="B550" t="n">
-        <v>180.6730651855469</v>
+        <v>180.673095703125</v>
       </c>
       <c r="C550" t="n">
-        <v>184.7257697831216</v>
+        <v>184.7258009852441</v>
       </c>
       <c r="D550" t="n">
-        <v>178.9744992637316</v>
+        <v>178.9745294944042</v>
       </c>
       <c r="E550" t="n">
-        <v>180.5836709677409</v>
+        <v>180.5837014702194</v>
       </c>
       <c r="F550" t="n">
         <v>693400</v>
@@ -11432,16 +11432,16 @@
         <v>44028</v>
       </c>
       <c r="B551" t="n">
-        <v>181.3882446289062</v>
+        <v>181.3882751464844</v>
       </c>
       <c r="C551" t="n">
-        <v>183.1166085793732</v>
+        <v>183.1166393877391</v>
       </c>
       <c r="D551" t="n">
-        <v>178.3487200471918</v>
+        <v>178.3487500533865</v>
       </c>
       <c r="E551" t="n">
-        <v>181.8054327914259</v>
+        <v>181.8054633791936</v>
       </c>
       <c r="F551" t="n">
         <v>439600</v>
@@ -11452,16 +11452,16 @@
         <v>44029</v>
       </c>
       <c r="B552" t="n">
-        <v>190.1492309570312</v>
+        <v>190.1492462158203</v>
       </c>
       <c r="C552" t="n">
-        <v>190.1492309570312</v>
+        <v>190.1492462158203</v>
       </c>
       <c r="D552" t="n">
-        <v>181.3882490186939</v>
+        <v>181.3882635744458</v>
       </c>
       <c r="E552" t="n">
-        <v>181.3882490186939</v>
+        <v>181.3882635744458</v>
       </c>
       <c r="F552" t="n">
         <v>595900</v>
@@ -11472,16 +11472,16 @@
         <v>44032</v>
       </c>
       <c r="B553" t="n">
-        <v>196.0196990966797</v>
+        <v>196.0197143554688</v>
       </c>
       <c r="C553" t="n">
-        <v>197.7778612094101</v>
+        <v>197.77787660506</v>
       </c>
       <c r="D553" t="n">
-        <v>189.1956674727965</v>
+        <v>189.1956822003815</v>
       </c>
       <c r="E553" t="n">
-        <v>190.7154298418124</v>
+        <v>190.7154446877005</v>
       </c>
       <c r="F553" t="n">
         <v>643066</v>
@@ -11492,16 +11492,16 @@
         <v>44033</v>
       </c>
       <c r="B554" t="n">
-        <v>195.1853332519531</v>
+        <v>195.1853179931641</v>
       </c>
       <c r="C554" t="n">
-        <v>198.5824502103585</v>
+        <v>198.5824346859968</v>
       </c>
       <c r="D554" t="n">
-        <v>190.5068384424615</v>
+        <v>190.506823549418</v>
       </c>
       <c r="E554" t="n">
-        <v>196.0495077398707</v>
+        <v>196.0494924135241</v>
       </c>
       <c r="F554" t="n">
         <v>627900</v>
@@ -11512,16 +11512,16 @@
         <v>44034</v>
       </c>
       <c r="B555" t="n">
-        <v>193.9933624267578</v>
+        <v>193.9933319091797</v>
       </c>
       <c r="C555" t="n">
-        <v>197.926859843797</v>
+        <v>197.9268287074306</v>
       </c>
       <c r="D555" t="n">
-        <v>191.4306219124074</v>
+        <v>191.4305917979804</v>
       </c>
       <c r="E555" t="n">
-        <v>195.2151289563396</v>
+        <v>195.2150982465623</v>
       </c>
       <c r="F555" t="n">
         <v>664000</v>
@@ -11572,16 +11572,16 @@
         <v>44039</v>
       </c>
       <c r="B558" t="n">
-        <v>192.56298828125</v>
+        <v>192.5629730224609</v>
       </c>
       <c r="C558" t="n">
-        <v>201.8603661940167</v>
+        <v>201.8603501984987</v>
       </c>
       <c r="D558" t="n">
-        <v>192.1160020190085</v>
+        <v>192.1159867956388</v>
       </c>
       <c r="E558" t="n">
-        <v>196.8838756918523</v>
+        <v>196.8838600906739</v>
       </c>
       <c r="F558" t="n">
         <v>595333</v>
@@ -11592,16 +11592,16 @@
         <v>44040</v>
       </c>
       <c r="B559" t="n">
-        <v>194.2317352294922</v>
+        <v>194.2317657470703</v>
       </c>
       <c r="C559" t="n">
-        <v>195.9005030904659</v>
+        <v>195.9005338702399</v>
       </c>
       <c r="D559" t="n">
-        <v>188.7188795654674</v>
+        <v>188.7189092168689</v>
       </c>
       <c r="E559" t="n">
-        <v>190.7154262273731</v>
+        <v>190.7154561924708</v>
       </c>
       <c r="F559" t="n">
         <v>415300</v>
@@ -11612,16 +11612,16 @@
         <v>44041</v>
       </c>
       <c r="B560" t="n">
-        <v>195.1853332519531</v>
+        <v>195.1853179931641</v>
       </c>
       <c r="C560" t="n">
-        <v>196.6752976279222</v>
+        <v>196.6752822526539</v>
       </c>
       <c r="D560" t="n">
-        <v>193.3973729694499</v>
+        <v>193.3973578504363</v>
       </c>
       <c r="E560" t="n">
-        <v>195.4535310835039</v>
+        <v>195.4535158037483</v>
       </c>
       <c r="F560" t="n">
         <v>374733</v>
@@ -11632,16 +11632,16 @@
         <v>44042</v>
       </c>
       <c r="B561" t="n">
-        <v>197.2712554931641</v>
+        <v>197.2712860107422</v>
       </c>
       <c r="C561" t="n">
-        <v>200.072380156464</v>
+        <v>200.0724111073721</v>
       </c>
       <c r="D561" t="n">
-        <v>193.0993438330214</v>
+        <v>193.0993737052108</v>
       </c>
       <c r="E561" t="n">
-        <v>194.8873038078398</v>
+        <v>194.8873339566241</v>
       </c>
       <c r="F561" t="n">
         <v>388133</v>
@@ -11652,16 +11652,16 @@
         <v>44043</v>
       </c>
       <c r="B562" t="n">
-        <v>194.1125640869141</v>
+        <v>194.112548828125</v>
       </c>
       <c r="C562" t="n">
-        <v>199.8936333494981</v>
+        <v>199.8936176362711</v>
       </c>
       <c r="D562" t="n">
-        <v>191.8180212901964</v>
+        <v>191.8180062117766</v>
       </c>
       <c r="E562" t="n">
-        <v>197.5692773200199</v>
+        <v>197.5692617895057</v>
       </c>
       <c r="F562" t="n">
         <v>964966</v>
@@ -11672,16 +11672,16 @@
         <v>44046</v>
       </c>
       <c r="B563" t="n">
-        <v>194.3211364746094</v>
+        <v>194.3211517333984</v>
       </c>
       <c r="C563" t="n">
-        <v>196.7646692831627</v>
+        <v>196.7646847338267</v>
       </c>
       <c r="D563" t="n">
-        <v>190.1790226466353</v>
+        <v>190.1790375801708</v>
       </c>
       <c r="E563" t="n">
-        <v>196.049485252196</v>
+        <v>196.0495006467012</v>
       </c>
       <c r="F563" t="n">
         <v>823000</v>
@@ -11692,16 +11692,16 @@
         <v>44047</v>
       </c>
       <c r="B564" t="n">
-        <v>191.1922149658203</v>
+        <v>191.1922302246094</v>
       </c>
       <c r="C564" t="n">
-        <v>194.7979334263718</v>
+        <v>194.7979489729283</v>
       </c>
       <c r="D564" t="n">
-        <v>188.8976723660878</v>
+        <v>188.8976874417525</v>
       </c>
       <c r="E564" t="n">
-        <v>193.4271614185521</v>
+        <v>193.4271768557092</v>
       </c>
       <c r="F564" t="n">
         <v>411633</v>
@@ -11732,16 +11732,16 @@
         <v>44049</v>
       </c>
       <c r="B566" t="n">
-        <v>197.4202728271484</v>
+        <v>197.4202880859375</v>
       </c>
       <c r="C566" t="n">
-        <v>198.6122412543873</v>
+        <v>198.6122566053047</v>
       </c>
       <c r="D566" t="n">
-        <v>194.7979362245427</v>
+        <v>194.797951280649</v>
       </c>
       <c r="E566" t="n">
-        <v>194.7979362245427</v>
+        <v>194.797951280649</v>
       </c>
       <c r="F566" t="n">
         <v>434133</v>
@@ -11792,16 +11792,16 @@
         <v>44054</v>
       </c>
       <c r="B569" t="n">
-        <v>186.930908203125</v>
+        <v>186.9309234619141</v>
       </c>
       <c r="C569" t="n">
-        <v>193.5463527912713</v>
+        <v>193.5463685900656</v>
       </c>
       <c r="D569" t="n">
-        <v>186.4243106823006</v>
+        <v>186.4243258997372</v>
       </c>
       <c r="E569" t="n">
-        <v>193.0099571994219</v>
+        <v>193.0099729544314</v>
       </c>
       <c r="F569" t="n">
         <v>865000</v>
@@ -11812,16 +11812,16 @@
         <v>44055</v>
       </c>
       <c r="B570" t="n">
-        <v>182.6994323730469</v>
+        <v>182.6994171142578</v>
       </c>
       <c r="C570" t="n">
-        <v>189.2552819722826</v>
+        <v>189.2552661659586</v>
       </c>
       <c r="D570" t="n">
-        <v>179.2427191158309</v>
+        <v>179.2427041457414</v>
       </c>
       <c r="E570" t="n">
-        <v>186.7521374689941</v>
+        <v>186.7521218717291</v>
       </c>
       <c r="F570" t="n">
         <v>1065533</v>
@@ -11832,16 +11832,16 @@
         <v>44056</v>
       </c>
       <c r="B571" t="n">
-        <v>186.5733489990234</v>
+        <v>186.5733337402344</v>
       </c>
       <c r="C571" t="n">
-        <v>190.9240348573458</v>
+        <v>190.9240192427385</v>
       </c>
       <c r="D571" t="n">
-        <v>184.6363982583284</v>
+        <v>184.6363831579516</v>
       </c>
       <c r="E571" t="n">
-        <v>184.844984792179</v>
+        <v>184.8449696747432</v>
       </c>
       <c r="F571" t="n">
         <v>646800</v>
@@ -11872,16 +11872,16 @@
         <v>44060</v>
       </c>
       <c r="B573" t="n">
-        <v>186.0965576171875</v>
+        <v>186.0965423583984</v>
       </c>
       <c r="C573" t="n">
-        <v>193.0397819460739</v>
+        <v>193.0397661179825</v>
       </c>
       <c r="D573" t="n">
-        <v>183.0272194671714</v>
+        <v>183.0272044600494</v>
       </c>
       <c r="E573" t="n">
-        <v>191.8776115454024</v>
+        <v>191.877595812602</v>
       </c>
       <c r="F573" t="n">
         <v>389400</v>
@@ -11892,16 +11892,16 @@
         <v>44061</v>
       </c>
       <c r="B574" t="n">
-        <v>187.5269012451172</v>
+        <v>187.5268859863281</v>
       </c>
       <c r="C574" t="n">
-        <v>190.3876375682871</v>
+        <v>190.3876220767241</v>
       </c>
       <c r="D574" t="n">
-        <v>186.096548240233</v>
+        <v>186.0965330978296</v>
       </c>
       <c r="E574" t="n">
-        <v>187.973902663138</v>
+        <v>187.9738873679771</v>
       </c>
       <c r="F574" t="n">
         <v>544533</v>
@@ -11912,16 +11912,16 @@
         <v>44062</v>
       </c>
       <c r="B575" t="n">
-        <v>184.6959533691406</v>
+        <v>184.6959686279297</v>
       </c>
       <c r="C575" t="n">
-        <v>188.3612675022022</v>
+        <v>188.3612830638038</v>
       </c>
       <c r="D575" t="n">
-        <v>183.7721677401152</v>
+        <v>183.772182922585</v>
       </c>
       <c r="E575" t="n">
-        <v>187.7354777263042</v>
+        <v>187.7354932362058</v>
       </c>
       <c r="F575" t="n">
         <v>275166</v>
@@ -11932,16 +11932,16 @@
         <v>44063</v>
       </c>
       <c r="B576" t="n">
-        <v>185.1429901123047</v>
+        <v>185.1429595947266</v>
       </c>
       <c r="C576" t="n">
-        <v>189.3744838804269</v>
+        <v>189.3744526653612</v>
       </c>
       <c r="D576" t="n">
-        <v>180.0175085407519</v>
+        <v>180.0174788680197</v>
       </c>
       <c r="E576" t="n">
-        <v>180.5241061763734</v>
+        <v>180.5240764201374</v>
       </c>
       <c r="F576" t="n">
         <v>586600</v>
@@ -11952,16 +11952,16 @@
         <v>44064</v>
       </c>
       <c r="B577" t="n">
-        <v>186.5733489990234</v>
+        <v>186.5733337402344</v>
       </c>
       <c r="C577" t="n">
-        <v>188.1229095915795</v>
+        <v>188.1228942060606</v>
       </c>
       <c r="D577" t="n">
-        <v>182.908034051484</v>
+        <v>182.9080190924604</v>
       </c>
       <c r="E577" t="n">
-        <v>184.7555905633859</v>
+        <v>184.7555754532611</v>
       </c>
       <c r="F577" t="n">
         <v>431666</v>
@@ -11992,16 +11992,16 @@
         <v>44068</v>
       </c>
       <c r="B579" t="n">
-        <v>186.2455596923828</v>
+        <v>186.2455444335938</v>
       </c>
       <c r="C579" t="n">
-        <v>189.046685028671</v>
+        <v>189.0466695403904</v>
       </c>
       <c r="D579" t="n">
-        <v>184.4575992879955</v>
+        <v>184.457584175691</v>
       </c>
       <c r="E579" t="n">
-        <v>186.5137575422165</v>
+        <v>186.5137422614545</v>
       </c>
       <c r="F579" t="n">
         <v>543433</v>
@@ -12032,16 +12032,16 @@
         <v>44070</v>
       </c>
       <c r="B581" t="n">
-        <v>187.0203247070312</v>
+        <v>187.0203094482422</v>
       </c>
       <c r="C581" t="n">
-        <v>189.6128632921078</v>
+        <v>189.6128478217963</v>
       </c>
       <c r="D581" t="n">
-        <v>184.755580098999</v>
+        <v>184.755565024988</v>
       </c>
       <c r="E581" t="n">
-        <v>184.755580098999</v>
+        <v>184.755565024988</v>
       </c>
       <c r="F581" t="n">
         <v>465466</v>
@@ -12092,16 +12092,16 @@
         <v>44075</v>
       </c>
       <c r="B584" t="n">
-        <v>205.5852966308594</v>
+        <v>205.5852813720703</v>
       </c>
       <c r="C584" t="n">
-        <v>207.2838476211239</v>
+        <v>207.2838322362663</v>
       </c>
       <c r="D584" t="n">
-        <v>193.5463886894397</v>
+        <v>193.5463743241929</v>
       </c>
       <c r="E584" t="n">
-        <v>195.1853435266005</v>
+        <v>195.1853290397085</v>
       </c>
       <c r="F584" t="n">
         <v>1357600</v>
@@ -12112,16 +12112,16 @@
         <v>44076</v>
       </c>
       <c r="B585" t="n">
-        <v>202.0689697265625</v>
+        <v>202.0689392089844</v>
       </c>
       <c r="C585" t="n">
-        <v>206.4792668863736</v>
+        <v>206.4792357027279</v>
       </c>
       <c r="D585" t="n">
-        <v>199.7148307655966</v>
+        <v>199.7148006035536</v>
       </c>
       <c r="E585" t="n">
-        <v>205.3766925964208</v>
+        <v>205.376661579292</v>
       </c>
       <c r="F585" t="n">
         <v>581366</v>
@@ -12192,16 +12192,16 @@
         <v>44083</v>
       </c>
       <c r="B589" t="n">
-        <v>203.4993133544922</v>
+        <v>203.4992980957031</v>
       </c>
       <c r="C589" t="n">
-        <v>204.6614836560544</v>
+        <v>204.6614683101234</v>
       </c>
       <c r="D589" t="n">
-        <v>196.7050799807286</v>
+        <v>196.7050652313848</v>
       </c>
       <c r="E589" t="n">
-        <v>202.3669411255316</v>
+        <v>202.3669259516501</v>
       </c>
       <c r="F589" t="n">
         <v>801100</v>
@@ -12212,16 +12212,16 @@
         <v>44084</v>
       </c>
       <c r="B590" t="n">
-        <v>195.1853332519531</v>
+        <v>195.1853179931641</v>
       </c>
       <c r="C590" t="n">
-        <v>205.7938723336365</v>
+        <v>205.7938562455153</v>
       </c>
       <c r="D590" t="n">
-        <v>193.7549650259506</v>
+        <v>193.7549498789818</v>
       </c>
       <c r="E590" t="n">
-        <v>205.6746800337034</v>
+        <v>205.6746639549002</v>
       </c>
       <c r="F590" t="n">
         <v>559966</v>
@@ -12232,16 +12232,16 @@
         <v>44085</v>
       </c>
       <c r="B591" t="n">
-        <v>189.7765960693359</v>
+        <v>189.7766265869141</v>
       </c>
       <c r="C591" t="n">
-        <v>197.9303618071543</v>
+        <v>197.9303936359225</v>
       </c>
       <c r="D591" t="n">
-        <v>187.8053608420284</v>
+        <v>187.8053910426163</v>
       </c>
       <c r="E591" t="n">
-        <v>194.5852275350051</v>
+        <v>194.5852588258493</v>
       </c>
       <c r="F591" t="n">
         <v>1048366</v>
@@ -12252,16 +12252,16 @@
         <v>44088</v>
       </c>
       <c r="B592" t="n">
-        <v>197.1836853027344</v>
+        <v>197.1837005615234</v>
       </c>
       <c r="C592" t="n">
-        <v>199.125054530863</v>
+        <v>199.1250699398823</v>
       </c>
       <c r="D592" t="n">
-        <v>190.0752766888564</v>
+        <v>190.075291397571</v>
       </c>
       <c r="E592" t="n">
-        <v>190.344086333144</v>
+        <v>190.3441010626601</v>
       </c>
       <c r="F592" t="n">
         <v>434033</v>
@@ -12272,16 +12272,16 @@
         <v>44089</v>
       </c>
       <c r="B593" t="n">
-        <v>197.2732849121094</v>
+        <v>197.2733154296875</v>
       </c>
       <c r="C593" t="n">
-        <v>199.0653239018133</v>
+        <v>199.0653546966144</v>
       </c>
       <c r="D593" t="n">
-        <v>191.8075849826088</v>
+        <v>191.8076146546597</v>
       </c>
       <c r="E593" t="n">
-        <v>199.0055918007026</v>
+        <v>199.0056225862634</v>
       </c>
       <c r="F593" t="n">
         <v>591666</v>
@@ -12312,16 +12312,16 @@
         <v>44091</v>
       </c>
       <c r="B595" t="n">
-        <v>191.3297119140625</v>
+        <v>191.3297271728516</v>
       </c>
       <c r="C595" t="n">
-        <v>195.7799360706191</v>
+        <v>195.7799516843192</v>
       </c>
       <c r="D595" t="n">
-        <v>190.8817059313864</v>
+        <v>190.8817211544465</v>
       </c>
       <c r="E595" t="n">
-        <v>195.6306058068198</v>
+        <v>195.6306214086107</v>
       </c>
       <c r="F595" t="n">
         <v>482133</v>
@@ -12352,16 +12352,16 @@
         <v>44095</v>
       </c>
       <c r="B597" t="n">
-        <v>187.8949737548828</v>
+        <v>187.8949584960938</v>
       </c>
       <c r="C597" t="n">
-        <v>188.193649465223</v>
+        <v>188.1936341821787</v>
       </c>
       <c r="D597" t="n">
-        <v>182.847413496117</v>
+        <v>182.8473986472359</v>
       </c>
       <c r="E597" t="n">
-        <v>186.043202580307</v>
+        <v>186.0431874718987</v>
       </c>
       <c r="F597" t="n">
         <v>424066</v>
@@ -12392,16 +12392,16 @@
         <v>44097</v>
       </c>
       <c r="B599" t="n">
-        <v>187.0885620117188</v>
+        <v>187.0885772705078</v>
       </c>
       <c r="C599" t="n">
-        <v>189.8960924517536</v>
+        <v>189.8961079395225</v>
       </c>
       <c r="D599" t="n">
-        <v>185.1770587124788</v>
+        <v>185.1770738153672</v>
       </c>
       <c r="E599" t="n">
-        <v>185.8640082963715</v>
+        <v>185.8640234552869</v>
       </c>
       <c r="F599" t="n">
         <v>596200</v>
@@ -12452,16 +12452,16 @@
         <v>44102</v>
       </c>
       <c r="B602" t="n">
-        <v>180.6372375488281</v>
+        <v>180.6372222900391</v>
       </c>
       <c r="C602" t="n">
-        <v>189.5078197050047</v>
+        <v>189.5078036968999</v>
       </c>
       <c r="D602" t="n">
-        <v>179.3529365301246</v>
+        <v>179.352921379823</v>
       </c>
       <c r="E602" t="n">
-        <v>188.9403343266758</v>
+        <v>188.9403183665075</v>
       </c>
       <c r="F602" t="n">
         <v>595500</v>
@@ -12472,16 +12472,16 @@
         <v>44103</v>
       </c>
       <c r="B603" t="n">
-        <v>180.9359130859375</v>
+        <v>180.9359283447266</v>
       </c>
       <c r="C603" t="n">
-        <v>183.5044847382582</v>
+        <v>183.5045002136614</v>
       </c>
       <c r="D603" t="n">
-        <v>178.6062546613765</v>
+        <v>178.6062697236995</v>
       </c>
       <c r="E603" t="n">
-        <v>181.2644396621141</v>
+        <v>181.2644549486086</v>
       </c>
       <c r="F603" t="n">
         <v>676133</v>
@@ -12492,16 +12492,16 @@
         <v>44104</v>
       </c>
       <c r="B604" t="n">
-        <v>185.5951995849609</v>
+        <v>185.5952301025391</v>
       </c>
       <c r="C604" t="n">
-        <v>186.9690987597785</v>
+        <v>186.9691295032681</v>
       </c>
       <c r="D604" t="n">
-        <v>180.3982937920956</v>
+        <v>180.398323455142</v>
       </c>
       <c r="E604" t="n">
-        <v>181.5929814613258</v>
+        <v>181.5930113208158</v>
       </c>
       <c r="F604" t="n">
         <v>757400</v>
@@ -12512,16 +12512,16 @@
         <v>44105</v>
       </c>
       <c r="B605" t="n">
-        <v>188.1637725830078</v>
+        <v>188.1637878417969</v>
       </c>
       <c r="C605" t="n">
-        <v>191.1803651821317</v>
+        <v>191.1803806855457</v>
       </c>
       <c r="D605" t="n">
-        <v>183.2954089158922</v>
+        <v>183.2954237798904</v>
       </c>
       <c r="E605" t="n">
-        <v>185.9237276713053</v>
+        <v>185.9237427484422</v>
       </c>
       <c r="F605" t="n">
         <v>698566</v>
@@ -12572,16 +12572,16 @@
         <v>44110</v>
       </c>
       <c r="B608" t="n">
-        <v>185.8939056396484</v>
+        <v>185.8938903808594</v>
       </c>
       <c r="C608" t="n">
-        <v>190.7324044023035</v>
+        <v>190.7323887463544</v>
       </c>
       <c r="D608" t="n">
-        <v>184.6693517181751</v>
+        <v>184.6693365599015</v>
       </c>
       <c r="E608" t="n">
-        <v>190.4038625811706</v>
+        <v>190.4038469521893</v>
       </c>
       <c r="F608" t="n">
         <v>724500</v>
@@ -12772,16 +12772,16 @@
         <v>44125</v>
       </c>
       <c r="B618" t="n">
-        <v>192.70361328125</v>
+        <v>192.7036285400391</v>
       </c>
       <c r="C618" t="n">
-        <v>197.9901173573098</v>
+        <v>197.9901330346984</v>
       </c>
       <c r="D618" t="n">
-        <v>192.70361328125</v>
+        <v>192.7036285400391</v>
       </c>
       <c r="E618" t="n">
-        <v>193.6892386072849</v>
+        <v>193.6892539441184</v>
       </c>
       <c r="F618" t="n">
         <v>378600</v>
@@ -12792,16 +12792,16 @@
         <v>44126</v>
       </c>
       <c r="B619" t="n">
-        <v>195.272216796875</v>
+        <v>195.2722015380859</v>
       </c>
       <c r="C619" t="n">
-        <v>197.1239882027949</v>
+        <v>197.1239727993063</v>
       </c>
       <c r="D619" t="n">
-        <v>191.2401321817437</v>
+        <v>191.2401172380263</v>
       </c>
       <c r="E619" t="n">
-        <v>193.3009811684053</v>
+        <v>193.3009660636508</v>
       </c>
       <c r="F619" t="n">
         <v>380966</v>
@@ -12832,16 +12832,16 @@
         <v>44130</v>
       </c>
       <c r="B621" t="n">
-        <v>196.2279663085938</v>
+        <v>196.2279510498047</v>
       </c>
       <c r="C621" t="n">
-        <v>198.497877570862</v>
+        <v>198.4978621355634</v>
       </c>
       <c r="D621" t="n">
-        <v>188.5819374320492</v>
+        <v>188.5819227678193</v>
       </c>
       <c r="E621" t="n">
-        <v>190.4038426909474</v>
+        <v>190.4038278850452</v>
       </c>
       <c r="F621" t="n">
         <v>609466</v>
@@ -12892,16 +12892,16 @@
         <v>44133</v>
       </c>
       <c r="B624" t="n">
-        <v>199.2744445800781</v>
+        <v>199.2743988037109</v>
       </c>
       <c r="C624" t="n">
-        <v>199.8717809117553</v>
+        <v>199.8717349981709</v>
       </c>
       <c r="D624" t="n">
-        <v>189.5377150183212</v>
+        <v>189.5376714786287</v>
       </c>
       <c r="E624" t="n">
-        <v>192.8529688777663</v>
+        <v>192.8529245765097</v>
       </c>
       <c r="F624" t="n">
         <v>707700</v>
@@ -12912,16 +12912,16 @@
         <v>44134</v>
       </c>
       <c r="B625" t="n">
-        <v>192.2555999755859</v>
+        <v>192.255615234375</v>
       </c>
       <c r="C625" t="n">
-        <v>199.8120149470612</v>
+        <v>199.8120308055818</v>
       </c>
       <c r="D625" t="n">
-        <v>192.2555999755859</v>
+        <v>192.255615234375</v>
       </c>
       <c r="E625" t="n">
-        <v>198.6471933467818</v>
+        <v>198.6472091128537</v>
       </c>
       <c r="F625" t="n">
         <v>632900</v>
@@ -12932,16 +12932,16 @@
         <v>44138</v>
       </c>
       <c r="B626" t="n">
-        <v>195.1228637695312</v>
+        <v>195.1228942871094</v>
       </c>
       <c r="C626" t="n">
-        <v>197.0045010117106</v>
+        <v>197.0045318235803</v>
       </c>
       <c r="D626" t="n">
-        <v>192.0465236760246</v>
+        <v>192.0465537124575</v>
       </c>
       <c r="E626" t="n">
-        <v>194.6151105003338</v>
+        <v>194.6151409384984</v>
       </c>
       <c r="F626" t="n">
         <v>792500</v>
@@ -12992,16 +12992,16 @@
         <v>44141</v>
       </c>
       <c r="B629" t="n">
-        <v>213.5509796142578</v>
+        <v>213.5509643554688</v>
       </c>
       <c r="C629" t="n">
-        <v>214.2379292520132</v>
+        <v>214.2379139441398</v>
       </c>
       <c r="D629" t="n">
-        <v>205.1881501254558</v>
+        <v>205.1881354642133</v>
       </c>
       <c r="E629" t="n">
-        <v>206.8308438921308</v>
+        <v>206.8308291135134</v>
       </c>
       <c r="F629" t="n">
         <v>849833</v>
@@ -13012,16 +13012,16 @@
         <v>44144</v>
       </c>
       <c r="B630" t="n">
-        <v>208.5332641601562</v>
+        <v>208.5332489013672</v>
       </c>
       <c r="C630" t="n">
-        <v>226.0653517136236</v>
+        <v>226.0653351719772</v>
       </c>
       <c r="D630" t="n">
-        <v>207.7865824333327</v>
+        <v>207.7865672291798</v>
       </c>
       <c r="E630" t="n">
-        <v>221.0177911397615</v>
+        <v>221.0177749674551</v>
       </c>
       <c r="F630" t="n">
         <v>887833</v>
@@ -13032,16 +13032,16 @@
         <v>44145</v>
       </c>
       <c r="B631" t="n">
-        <v>204.0233001708984</v>
+        <v>204.0232849121094</v>
       </c>
       <c r="C631" t="n">
-        <v>211.0122451280538</v>
+        <v>211.0122293465654</v>
       </c>
       <c r="D631" t="n">
-        <v>201.6040587576205</v>
+        <v>201.6040436797651</v>
       </c>
       <c r="E631" t="n">
-        <v>209.0708757486434</v>
+        <v>209.070860112349</v>
       </c>
       <c r="F631" t="n">
         <v>798233</v>
@@ -13052,16 +13052,16 @@
         <v>44146</v>
       </c>
       <c r="B632" t="n">
-        <v>204.5907745361328</v>
+        <v>204.5908050537109</v>
       </c>
       <c r="C632" t="n">
-        <v>206.5620098620474</v>
+        <v>206.5620406736629</v>
       </c>
       <c r="D632" t="n">
-        <v>200.737902037464</v>
+        <v>200.7379319803322</v>
       </c>
       <c r="E632" t="n">
-        <v>202.977947014137</v>
+        <v>202.9779772911393</v>
       </c>
       <c r="F632" t="n">
         <v>574366</v>
@@ -13072,16 +13072,16 @@
         <v>44147</v>
       </c>
       <c r="B633" t="n">
-        <v>208.6228790283203</v>
+        <v>208.6228637695312</v>
       </c>
       <c r="C633" t="n">
-        <v>209.757834653686</v>
+        <v>209.7578193118856</v>
       </c>
       <c r="D633" t="n">
-        <v>203.6350353344859</v>
+        <v>203.6350204405104</v>
       </c>
       <c r="E633" t="n">
-        <v>206.0841581004217</v>
+        <v>206.084143027316</v>
       </c>
       <c r="F633" t="n">
         <v>897733</v>
@@ -13092,16 +13092,16 @@
         <v>44148</v>
       </c>
       <c r="B634" t="n">
-        <v>218.8972015380859</v>
+        <v>218.897216796875</v>
       </c>
       <c r="C634" t="n">
-        <v>220.6593745974234</v>
+        <v>220.6593899790492</v>
       </c>
       <c r="D634" t="n">
-        <v>209.9370211697153</v>
+        <v>209.9370358039121</v>
       </c>
       <c r="E634" t="n">
-        <v>209.9370211697153</v>
+        <v>209.9370358039121</v>
       </c>
       <c r="F634" t="n">
         <v>872100</v>
@@ -13112,16 +13112,16 @@
         <v>44151</v>
       </c>
       <c r="B635" t="n">
-        <v>218.0908050537109</v>
+        <v>218.0907745361328</v>
       </c>
       <c r="C635" t="n">
-        <v>221.5852702060042</v>
+        <v>221.5852391994435</v>
       </c>
       <c r="D635" t="n">
-        <v>215.0742119721199</v>
+        <v>215.0741818766554</v>
       </c>
       <c r="E635" t="n">
-        <v>221.0177999704102</v>
+        <v>221.017769043256</v>
       </c>
       <c r="F635" t="n">
         <v>540700</v>
@@ -13132,16 +13132,16 @@
         <v>44152</v>
       </c>
       <c r="B636" t="n">
-        <v>215.7611389160156</v>
+        <v>215.7611541748047</v>
       </c>
       <c r="C636" t="n">
-        <v>220.3905592436589</v>
+        <v>220.390574829844</v>
       </c>
       <c r="D636" t="n">
-        <v>215.7611389160156</v>
+        <v>215.7611541748047</v>
       </c>
       <c r="E636" t="n">
-        <v>219.7932230159539</v>
+        <v>219.793238559895</v>
       </c>
       <c r="F636" t="n">
         <v>945033</v>
@@ -13152,16 +13152,16 @@
         <v>44153</v>
       </c>
       <c r="B637" t="n">
-        <v>213.1029663085938</v>
+        <v>213.1029357910156</v>
       </c>
       <c r="C637" t="n">
-        <v>217.4337111775966</v>
+        <v>217.4336800398308</v>
       </c>
       <c r="D637" t="n">
-        <v>213.1029663085938</v>
+        <v>213.1029357910156</v>
       </c>
       <c r="E637" t="n">
-        <v>216.8662409688433</v>
+        <v>216.8662099123425</v>
       </c>
       <c r="F637" t="n">
         <v>504433</v>
@@ -13172,16 +13172,16 @@
         <v>44154</v>
       </c>
       <c r="B638" t="n">
-        <v>213.1627197265625</v>
+        <v>213.1627044677734</v>
       </c>
       <c r="C638" t="n">
-        <v>215.4326311710663</v>
+        <v>215.4326157497906</v>
       </c>
       <c r="D638" t="n">
-        <v>209.9669149555668</v>
+        <v>209.9668999255425</v>
       </c>
       <c r="E638" t="n">
-        <v>213.8198033529399</v>
+        <v>213.819788047115</v>
       </c>
       <c r="F638" t="n">
         <v>672366</v>
@@ -13212,16 +13212,16 @@
         <v>44159</v>
       </c>
       <c r="B640" t="n">
-        <v>214.8053894042969</v>
+        <v>214.8053741455078</v>
       </c>
       <c r="C640" t="n">
-        <v>216.477964338369</v>
+        <v>216.4779489607679</v>
       </c>
       <c r="D640" t="n">
-        <v>212.2965497901061</v>
+        <v>212.2965347095335</v>
       </c>
       <c r="E640" t="n">
-        <v>214.2379192027341</v>
+        <v>214.2379039842555</v>
       </c>
       <c r="F640" t="n">
         <v>404100</v>
@@ -13252,16 +13252,16 @@
         <v>44161</v>
       </c>
       <c r="B642" t="n">
-        <v>212.8042907714844</v>
+        <v>212.8042755126953</v>
       </c>
       <c r="C642" t="n">
-        <v>218.6284142796364</v>
+        <v>218.6283986032379</v>
       </c>
       <c r="D642" t="n">
-        <v>210.265569878411</v>
+        <v>210.2655548016568</v>
       </c>
       <c r="E642" t="n">
-        <v>216.3883691136208</v>
+        <v>216.3883535978412</v>
       </c>
       <c r="F642" t="n">
         <v>253146</v>
@@ -13332,16 +13332,16 @@
         <v>44167</v>
       </c>
       <c r="B646" t="n">
-        <v>220.7191009521484</v>
+        <v>220.7191162109375</v>
       </c>
       <c r="C646" t="n">
-        <v>221.4657826300592</v>
+        <v>221.4657979404679</v>
       </c>
       <c r="D646" t="n">
-        <v>213.5509598824612</v>
+        <v>213.5509746457012</v>
       </c>
       <c r="E646" t="n">
-        <v>214.1483113013008</v>
+        <v>214.148326105837</v>
       </c>
       <c r="F646" t="n">
         <v>812640</v>
@@ -13352,16 +13352,16 @@
         <v>44168</v>
       </c>
       <c r="B647" t="n">
-        <v>226.3938903808594</v>
+        <v>226.3938751220703</v>
       </c>
       <c r="C647" t="n">
-        <v>229.8286384300032</v>
+        <v>229.8286229397145</v>
       </c>
       <c r="D647" t="n">
-        <v>219.9724306568018</v>
+        <v>219.9724158308146</v>
       </c>
       <c r="E647" t="n">
-        <v>219.9724306568018</v>
+        <v>219.9724158308146</v>
       </c>
       <c r="F647" t="n">
         <v>476626</v>
@@ -13372,16 +13372,16 @@
         <v>44169</v>
       </c>
       <c r="B648" t="n">
-        <v>228.9326019287109</v>
+        <v>228.9326171875</v>
       </c>
       <c r="C648" t="n">
-        <v>230.2766350402532</v>
+        <v>230.2766503886246</v>
       </c>
       <c r="D648" t="n">
-        <v>224.6018572639329</v>
+        <v>224.6018722340697</v>
       </c>
       <c r="E648" t="n">
-        <v>226.9912325830327</v>
+        <v>226.9912477124258</v>
       </c>
       <c r="F648" t="n">
         <v>265620</v>
@@ -13392,16 +13392,16 @@
         <v>44172</v>
       </c>
       <c r="B649" t="n">
-        <v>224.4525146484375</v>
+        <v>224.4525299072266</v>
       </c>
       <c r="C649" t="n">
-        <v>234.4580524072576</v>
+        <v>234.4580683462457</v>
       </c>
       <c r="D649" t="n">
-        <v>220.4204304541335</v>
+        <v>220.4204454388124</v>
       </c>
       <c r="E649" t="n">
-        <v>229.3806108009077</v>
+        <v>229.3806263947199</v>
       </c>
       <c r="F649" t="n">
         <v>556173</v>
@@ -13412,16 +13412,16 @@
         <v>44173</v>
       </c>
       <c r="B650" t="n">
-        <v>228.6339263916016</v>
+        <v>228.6339416503906</v>
       </c>
       <c r="C650" t="n">
-        <v>230.7246411908779</v>
+        <v>230.7246565891991</v>
       </c>
       <c r="D650" t="n">
-        <v>221.7644609504555</v>
+        <v>221.7644757507836</v>
       </c>
       <c r="E650" t="n">
-        <v>223.8551757497318</v>
+        <v>223.8551906895921</v>
       </c>
       <c r="F650" t="n">
         <v>500300</v>
@@ -13452,16 +13452,16 @@
         <v>44175</v>
       </c>
       <c r="B652" t="n">
-        <v>227.8872528076172</v>
+        <v>227.8872680664062</v>
       </c>
       <c r="C652" t="n">
-        <v>233.4127005239284</v>
+        <v>233.4127161526883</v>
       </c>
       <c r="D652" t="n">
-        <v>225.6472076678649</v>
+        <v>225.6472227766659</v>
       </c>
       <c r="E652" t="n">
-        <v>226.6925651046716</v>
+        <v>226.6925802834673</v>
       </c>
       <c r="F652" t="n">
         <v>713620</v>
@@ -13492,16 +13492,16 @@
         <v>44179</v>
       </c>
       <c r="B654" t="n">
-        <v>226.0952301025391</v>
+        <v>226.0952453613281</v>
       </c>
       <c r="C654" t="n">
-        <v>227.439248079076</v>
+        <v>227.4392634285706</v>
       </c>
       <c r="D654" t="n">
-        <v>221.7644700651593</v>
+        <v>221.7644850316726</v>
       </c>
       <c r="E654" t="n">
-        <v>226.6925663616849</v>
+        <v>226.6925816607872</v>
       </c>
       <c r="F654" t="n">
         <v>327060</v>
@@ -13512,16 +13512,16 @@
         <v>44180</v>
       </c>
       <c r="B655" t="n">
-        <v>226.6925659179688</v>
+        <v>226.6925506591797</v>
       </c>
       <c r="C655" t="n">
-        <v>228.1859293498279</v>
+        <v>228.1859139905198</v>
       </c>
       <c r="D655" t="n">
-        <v>223.1085027962737</v>
+        <v>223.1084877787297</v>
       </c>
       <c r="E655" t="n">
-        <v>226.0952296599921</v>
+        <v>226.09521444141</v>
       </c>
       <c r="F655" t="n">
         <v>364800</v>
@@ -13552,16 +13552,16 @@
         <v>44182</v>
       </c>
       <c r="B657" t="n">
-        <v>231.4713439941406</v>
+        <v>231.4713287353516</v>
       </c>
       <c r="C657" t="n">
-        <v>233.8607195330523</v>
+        <v>233.8607041167536</v>
       </c>
       <c r="D657" t="n">
-        <v>228.3352867004091</v>
+        <v>228.3352716483516</v>
       </c>
       <c r="E657" t="n">
-        <v>229.3806290041335</v>
+        <v>229.3806138831661</v>
       </c>
       <c r="F657" t="n">
         <v>215466</v>
@@ -13572,16 +13572,16 @@
         <v>44183</v>
       </c>
       <c r="B658" t="n">
-        <v>226.9912567138672</v>
+        <v>226.9912414550781</v>
       </c>
       <c r="C658" t="n">
-        <v>233.8607228800119</v>
+        <v>233.8607071594441</v>
       </c>
       <c r="D658" t="n">
-        <v>224.7512114173488</v>
+        <v>224.7511963091399</v>
       </c>
       <c r="E658" t="n">
-        <v>230.1273140524812</v>
+        <v>230.1272985828803</v>
       </c>
       <c r="F658" t="n">
         <v>323473</v>
@@ -13592,16 +13592,16 @@
         <v>44186</v>
       </c>
       <c r="B659" t="n">
-        <v>224.7511901855469</v>
+        <v>224.7512054443359</v>
       </c>
       <c r="C659" t="n">
-        <v>228.3352683979073</v>
+        <v>228.3352839000263</v>
       </c>
       <c r="D659" t="n">
-        <v>219.0764123420412</v>
+        <v>219.0764272155587</v>
       </c>
       <c r="E659" t="n">
-        <v>223.8551782280958</v>
+        <v>223.8551934260528</v>
       </c>
       <c r="F659" t="n">
         <v>304586</v>
@@ -13632,16 +13632,16 @@
         <v>44188</v>
       </c>
       <c r="B661" t="n">
-        <v>224.4525146484375</v>
+        <v>224.4525299072266</v>
       </c>
       <c r="C661" t="n">
-        <v>229.8286319712688</v>
+        <v>229.8286475955385</v>
       </c>
       <c r="D661" t="n">
-        <v>224.0045086693544</v>
+        <v>224.004523897687</v>
       </c>
       <c r="E661" t="n">
-        <v>228.4845988427415</v>
+        <v>228.4846143756407</v>
       </c>
       <c r="F661" t="n">
         <v>316873</v>
@@ -13652,16 +13652,16 @@
         <v>44193</v>
       </c>
       <c r="B662" t="n">
-        <v>226.3938903808594</v>
+        <v>226.3938751220703</v>
       </c>
       <c r="C662" t="n">
-        <v>227.588593280359</v>
+        <v>227.5885779410478</v>
       </c>
       <c r="D662" t="n">
-        <v>222.8098272561957</v>
+        <v>222.80981223897</v>
       </c>
       <c r="E662" t="n">
-        <v>225.3485481307148</v>
+        <v>225.3485329423811</v>
       </c>
       <c r="F662" t="n">
         <v>229633</v>
@@ -13672,16 +13672,16 @@
         <v>44194</v>
       </c>
       <c r="B663" t="n">
-        <v>231.7700042724609</v>
+        <v>231.7699890136719</v>
       </c>
       <c r="C663" t="n">
-        <v>234.1593796519724</v>
+        <v>234.1593642358766</v>
       </c>
       <c r="D663" t="n">
-        <v>225.3485446476555</v>
+        <v>225.348529811629</v>
       </c>
       <c r="E663" t="n">
-        <v>227.5885897626768</v>
+        <v>227.588574779175</v>
       </c>
       <c r="F663" t="n">
         <v>293840</v>
@@ -13692,16 +13692,16 @@
         <v>44195</v>
       </c>
       <c r="B664" t="n">
-        <v>227.8872528076172</v>
+        <v>227.8872680664062</v>
       </c>
       <c r="C664" t="n">
-        <v>235.6527456636806</v>
+        <v>235.6527614424286</v>
       </c>
       <c r="D664" t="n">
-        <v>225.9458833914209</v>
+        <v>225.9458985202205</v>
       </c>
       <c r="E664" t="n">
-        <v>234.1593822371791</v>
+        <v>234.1593979159351</v>
       </c>
       <c r="F664" t="n">
         <v>659613</v>
@@ -13732,16 +13732,16 @@
         <v>44201</v>
       </c>
       <c r="B666" t="n">
-        <v>218.7777404785156</v>
+        <v>218.7777557373047</v>
       </c>
       <c r="C666" t="n">
-        <v>225.6472061166881</v>
+        <v>225.6472218545923</v>
       </c>
       <c r="D666" t="n">
-        <v>218.1803890355101</v>
+        <v>218.1804042526365</v>
       </c>
       <c r="E666" t="n">
-        <v>224.9005244085703</v>
+        <v>224.9005400943967</v>
       </c>
       <c r="F666" t="n">
         <v>585466</v>
@@ -13752,16 +13752,16 @@
         <v>44202</v>
       </c>
       <c r="B667" t="n">
-        <v>210.7135620117188</v>
+        <v>210.7135772705078</v>
       </c>
       <c r="C667" t="n">
-        <v>220.5697692085711</v>
+        <v>220.5697851810959</v>
       </c>
       <c r="D667" t="n">
-        <v>210.4149014955867</v>
+        <v>210.4149167327483</v>
       </c>
       <c r="E667" t="n">
-        <v>220.5697692085711</v>
+        <v>220.5697851810959</v>
       </c>
       <c r="F667" t="n">
         <v>989980</v>
@@ -13772,16 +13772,16 @@
         <v>44203</v>
       </c>
       <c r="B668" t="n">
-        <v>213.2523040771484</v>
+        <v>213.2522888183594</v>
       </c>
       <c r="C668" t="n">
-        <v>217.2843885524602</v>
+        <v>217.2843730051644</v>
       </c>
       <c r="D668" t="n">
-        <v>207.1295198233158</v>
+        <v>207.1295050026288</v>
       </c>
       <c r="E668" t="n">
-        <v>211.4602648446455</v>
+        <v>211.4602497140818</v>
       </c>
       <c r="F668" t="n">
         <v>485820</v>
@@ -13792,16 +13792,16 @@
         <v>44204</v>
       </c>
       <c r="B669" t="n">
-        <v>251.0281524658203</v>
+        <v>251.0281677246094</v>
       </c>
       <c r="C669" t="n">
-        <v>271.9721139123191</v>
+        <v>271.9721304441905</v>
       </c>
       <c r="D669" t="n">
-        <v>213.0298591536313</v>
+        <v>213.0298721026877</v>
       </c>
       <c r="E669" t="n">
-        <v>213.7778572332184</v>
+        <v>213.777870227742</v>
       </c>
       <c r="F669" t="n">
         <v>2651860</v>
@@ -13812,16 +13812,16 @@
         <v>44207</v>
       </c>
       <c r="B670" t="n">
-        <v>272.2713012695312</v>
+        <v>272.2713317871094</v>
       </c>
       <c r="C670" t="n">
-        <v>276.4601026942797</v>
+        <v>276.4601336813603</v>
       </c>
       <c r="D670" t="n">
-        <v>249.9809523860654</v>
+        <v>249.9809804052258</v>
       </c>
       <c r="E670" t="n">
-        <v>250.7289504664762</v>
+        <v>250.7289785694761</v>
       </c>
       <c r="F670" t="n">
         <v>3239386</v>
@@ -13852,16 +13852,16 @@
         <v>44209</v>
       </c>
       <c r="B672" t="n">
-        <v>254.3193664550781</v>
+        <v>254.3193359375</v>
       </c>
       <c r="C672" t="n">
-        <v>263.5945311748733</v>
+        <v>263.5944995443026</v>
       </c>
       <c r="D672" t="n">
-        <v>252.3745743434456</v>
+        <v>252.3745440592369</v>
       </c>
       <c r="E672" t="n">
-        <v>262.3977524179344</v>
+        <v>262.3977209309737</v>
       </c>
       <c r="F672" t="n">
         <v>1017226</v>
@@ -13872,16 +13872,16 @@
         <v>44210</v>
       </c>
       <c r="B673" t="n">
-        <v>257.3113708496094</v>
+        <v>257.3113403320312</v>
       </c>
       <c r="C673" t="n">
-        <v>264.6417590133636</v>
+        <v>264.6417276263887</v>
       </c>
       <c r="D673" t="n">
-        <v>253.5713799942372</v>
+        <v>253.5713499202285</v>
       </c>
       <c r="E673" t="n">
-        <v>255.5161874134801</v>
+        <v>255.5161571088139</v>
       </c>
       <c r="F673" t="n">
         <v>708060</v>
@@ -13892,16 +13892,16 @@
         <v>44211</v>
       </c>
       <c r="B674" t="n">
-        <v>258.807373046875</v>
+        <v>258.8073425292969</v>
       </c>
       <c r="C674" t="n">
-        <v>263.7441732621032</v>
+        <v>263.7441421623964</v>
       </c>
       <c r="D674" t="n">
-        <v>251.7761870360931</v>
+        <v>251.7761573476056</v>
       </c>
       <c r="E674" t="n">
-        <v>257.3113766708815</v>
+        <v>257.3113463297055</v>
       </c>
       <c r="F674" t="n">
         <v>638993</v>
@@ -14012,16 +14012,16 @@
         <v>44222</v>
       </c>
       <c r="B680" t="n">
-        <v>267.7832946777344</v>
+        <v>267.7833251953125</v>
       </c>
       <c r="C680" t="n">
-        <v>276.1608665245628</v>
+        <v>276.1608979968802</v>
       </c>
       <c r="D680" t="n">
-        <v>261.5001234016424</v>
+        <v>261.5001532031671</v>
       </c>
       <c r="E680" t="n">
-        <v>263.4449000175196</v>
+        <v>263.4449300406782</v>
       </c>
       <c r="F680" t="n">
         <v>884853</v>
@@ -14032,16 +14032,16 @@
         <v>44223</v>
       </c>
       <c r="B681" t="n">
-        <v>257.4609680175781</v>
+        <v>257.4609069824219</v>
       </c>
       <c r="C681" t="n">
-        <v>270.6257481880896</v>
+        <v>270.625684032016</v>
       </c>
       <c r="D681" t="n">
-        <v>257.4609680175781</v>
+        <v>257.4609069824219</v>
       </c>
       <c r="E681" t="n">
-        <v>267.9329425599001</v>
+        <v>267.9328790421983</v>
       </c>
       <c r="F681" t="n">
         <v>863460</v>
@@ -14052,16 +14052,16 @@
         <v>44224</v>
       </c>
       <c r="B682" t="n">
-        <v>266.8857116699219</v>
+        <v>266.8857421875</v>
       </c>
       <c r="C682" t="n">
-        <v>269.7281103614457</v>
+        <v>269.7281412040435</v>
       </c>
       <c r="D682" t="n">
-        <v>257.9097350247639</v>
+        <v>257.9097645159661</v>
       </c>
       <c r="E682" t="n">
-        <v>257.9097350247639</v>
+        <v>257.9097645159661</v>
       </c>
       <c r="F682" t="n">
         <v>574346</v>
@@ -14112,16 +14112,16 @@
         <v>44229</v>
       </c>
       <c r="B685" t="n">
-        <v>265.6889343261719</v>
+        <v>265.6888732910156</v>
       </c>
       <c r="C685" t="n">
-        <v>271.5233259292311</v>
+        <v>271.5232635537744</v>
       </c>
       <c r="D685" t="n">
-        <v>260.7521648436775</v>
+        <v>260.7521049426162</v>
       </c>
       <c r="E685" t="n">
-        <v>266.5865260106143</v>
+        <v>266.5864647692596</v>
       </c>
       <c r="F685" t="n">
         <v>627486</v>
@@ -14192,16 +14192,16 @@
         <v>44235</v>
       </c>
       <c r="B689" t="n">
-        <v>270.3265075683594</v>
+        <v>270.3264770507812</v>
       </c>
       <c r="C689" t="n">
-        <v>272.8697194302689</v>
+        <v>272.8696886255836</v>
       </c>
       <c r="D689" t="n">
-        <v>262.5473393185545</v>
+        <v>262.5473096791787</v>
       </c>
       <c r="E689" t="n">
-        <v>267.6337326062521</v>
+        <v>267.6337023926656</v>
       </c>
       <c r="F689" t="n">
         <v>645166</v>
@@ -14212,16 +14212,16 @@
         <v>44236</v>
       </c>
       <c r="B690" t="n">
-        <v>264.7913513183594</v>
+        <v>264.7912902832031</v>
       </c>
       <c r="C690" t="n">
-        <v>270.1769320376098</v>
+        <v>270.1768697610619</v>
       </c>
       <c r="D690" t="n">
-        <v>264.1929466970819</v>
+        <v>264.1928857998596</v>
       </c>
       <c r="E690" t="n">
-        <v>269.4289338700438</v>
+        <v>269.4288717659117</v>
       </c>
       <c r="F690" t="n">
         <v>477180</v>
@@ -14232,16 +14232,16 @@
         <v>44237</v>
       </c>
       <c r="B691" t="n">
-        <v>257.9097900390625</v>
+        <v>257.9097595214844</v>
       </c>
       <c r="C691" t="n">
-        <v>266.1377703855538</v>
+        <v>266.1377388943871</v>
       </c>
       <c r="D691" t="n">
-        <v>256.1145760654256</v>
+        <v>256.114545760269</v>
       </c>
       <c r="E691" t="n">
-        <v>265.240178616798</v>
+        <v>265.2401472318402</v>
       </c>
       <c r="F691" t="n">
         <v>536113</v>
@@ -14272,16 +14272,16 @@
         <v>44239</v>
       </c>
       <c r="B693" t="n">
-        <v>257.3113708496094</v>
+        <v>257.3113403320312</v>
       </c>
       <c r="C693" t="n">
-        <v>262.2481709531501</v>
+        <v>262.2481398500589</v>
       </c>
       <c r="D693" t="n">
-        <v>255.8153745074605</v>
+        <v>255.8153441673101</v>
       </c>
       <c r="E693" t="n">
-        <v>262.2481709531501</v>
+        <v>262.2481398500589</v>
       </c>
       <c r="F693" t="n">
         <v>323506</v>
@@ -14292,16 +14292,16 @@
         <v>44244</v>
       </c>
       <c r="B694" t="n">
-        <v>257.3113708496094</v>
+        <v>257.3113403320312</v>
       </c>
       <c r="C694" t="n">
-        <v>260.153769986917</v>
+        <v>260.1537391322253</v>
       </c>
       <c r="D694" t="n">
-        <v>253.1225841352048</v>
+        <v>253.1225541144241</v>
       </c>
       <c r="E694" t="n">
-        <v>260.0041764399268</v>
+        <v>260.0041456029772</v>
       </c>
       <c r="F694" t="n">
         <v>745893</v>
@@ -14332,16 +14332,16 @@
         <v>44246</v>
       </c>
       <c r="B696" t="n">
-        <v>257.9097900390625</v>
+        <v>257.9097595214844</v>
       </c>
       <c r="C696" t="n">
-        <v>257.9097900390625</v>
+        <v>257.9097595214844</v>
       </c>
       <c r="D696" t="n">
-        <v>246.2410057368611</v>
+        <v>246.24097660001</v>
       </c>
       <c r="E696" t="n">
-        <v>252.3746002169013</v>
+        <v>252.3745703542831</v>
       </c>
       <c r="F696" t="n">
         <v>558933</v>
@@ -14372,16 +14372,16 @@
         <v>44250</v>
       </c>
       <c r="B698" t="n">
-        <v>243.8473815917969</v>
+        <v>243.8473968505859</v>
       </c>
       <c r="C698" t="n">
-        <v>250.7289580525621</v>
+        <v>250.7289737419669</v>
       </c>
       <c r="D698" t="n">
-        <v>241.4537937492856</v>
+        <v>241.4538088582955</v>
       </c>
       <c r="E698" t="n">
-        <v>247.7369656403928</v>
+        <v>247.7369811425732</v>
       </c>
       <c r="F698" t="n">
         <v>535220</v>
@@ -14392,16 +14392,16 @@
         <v>44251</v>
       </c>
       <c r="B699" t="n">
-        <v>240.8553771972656</v>
+        <v>240.8553924560547</v>
       </c>
       <c r="C699" t="n">
-        <v>245.9417701321336</v>
+        <v>245.9417857131583</v>
       </c>
       <c r="D699" t="n">
-        <v>235.4697972105133</v>
+        <v>235.4698121281125</v>
       </c>
       <c r="E699" t="n">
-        <v>245.1937720663036</v>
+        <v>245.1937875999407</v>
       </c>
       <c r="F699" t="n">
         <v>632986</v>
@@ -14412,16 +14412,16 @@
         <v>44252</v>
       </c>
       <c r="B700" t="n">
-        <v>236.9658203125</v>
+        <v>236.9657897949219</v>
       </c>
       <c r="C700" t="n">
-        <v>244.4458018221362</v>
+        <v>244.4457703412507</v>
       </c>
       <c r="D700" t="n">
-        <v>231.4306309517569</v>
+        <v>231.4306011470266</v>
       </c>
       <c r="E700" t="n">
-        <v>240.5562023062886</v>
+        <v>240.5561713263241</v>
       </c>
       <c r="F700" t="n">
         <v>728733</v>
@@ -14452,16 +14452,16 @@
         <v>44256</v>
       </c>
       <c r="B702" t="n">
-        <v>244.1465759277344</v>
+        <v>244.1465911865234</v>
       </c>
       <c r="C702" t="n">
-        <v>258.6577416979149</v>
+        <v>258.6577578636297</v>
       </c>
       <c r="D702" t="n">
-        <v>242.9497820454438</v>
+        <v>242.949797229435</v>
       </c>
       <c r="E702" t="n">
-        <v>257.3113390690506</v>
+        <v>257.3113551506173</v>
       </c>
       <c r="F702" t="n">
         <v>1383033</v>
@@ -14472,16 +14472,16 @@
         <v>44257</v>
       </c>
       <c r="B703" t="n">
-        <v>245.3433685302734</v>
+        <v>245.3433837890625</v>
       </c>
       <c r="C703" t="n">
-        <v>246.5401624063213</v>
+        <v>246.5401777395433</v>
       </c>
       <c r="D703" t="n">
-        <v>231.8794031840999</v>
+        <v>231.8794176055164</v>
       </c>
       <c r="E703" t="n">
-        <v>242.6505785046507</v>
+        <v>242.6505935959654</v>
       </c>
       <c r="F703" t="n">
         <v>816593</v>
@@ -14512,16 +14512,16 @@
         <v>44259</v>
       </c>
       <c r="B705" t="n">
-        <v>232.6273956298828</v>
+        <v>232.6274108886719</v>
       </c>
       <c r="C705" t="n">
-        <v>244.5953645368864</v>
+        <v>244.5953805806936</v>
       </c>
       <c r="D705" t="n">
-        <v>229.9346056694189</v>
+        <v>229.9346207515791</v>
       </c>
       <c r="E705" t="n">
-        <v>241.7529658342493</v>
+        <v>241.7529816916143</v>
       </c>
       <c r="F705" t="n">
         <v>1246706</v>
@@ -14532,16 +14532,16 @@
         <v>44260</v>
       </c>
       <c r="B706" t="n">
-        <v>233.9738006591797</v>
+        <v>233.9738159179688</v>
       </c>
       <c r="C706" t="n">
-        <v>237.7137909816214</v>
+        <v>237.713806484317</v>
       </c>
       <c r="D706" t="n">
-        <v>227.6906138738656</v>
+        <v>227.6906287228916</v>
       </c>
       <c r="E706" t="n">
-        <v>229.9346080673307</v>
+        <v>229.9346230627006</v>
       </c>
       <c r="F706" t="n">
         <v>977786</v>
@@ -14552,16 +14552,16 @@
         <v>44263</v>
       </c>
       <c r="B707" t="n">
-        <v>224.5490264892578</v>
+        <v>224.5490417480469</v>
       </c>
       <c r="C707" t="n">
-        <v>232.0290075877416</v>
+        <v>232.0290233548181</v>
       </c>
       <c r="D707" t="n">
-        <v>221.7066428026703</v>
+        <v>221.7066578683107</v>
       </c>
       <c r="E707" t="n">
-        <v>225.7458356394636</v>
+        <v>225.7458509795795</v>
       </c>
       <c r="F707" t="n">
         <v>1054193</v>
@@ -14572,16 +14572,16 @@
         <v>44264</v>
       </c>
       <c r="B708" t="n">
-        <v>226.6434173583984</v>
+        <v>226.6434326171875</v>
       </c>
       <c r="C708" t="n">
-        <v>229.1866138641178</v>
+        <v>229.1866292941278</v>
       </c>
       <c r="D708" t="n">
-        <v>219.4626388619423</v>
+        <v>219.4626536372848</v>
       </c>
       <c r="E708" t="n">
-        <v>224.3994231271272</v>
+        <v>224.3994382348391</v>
       </c>
       <c r="F708" t="n">
         <v>998826</v>
@@ -14592,16 +14592,16 @@
         <v>44265</v>
       </c>
       <c r="B709" t="n">
-        <v>227.2418060302734</v>
+        <v>227.2418365478516</v>
       </c>
       <c r="C709" t="n">
-        <v>229.4858001047604</v>
+        <v>229.4858309236971</v>
       </c>
       <c r="D709" t="n">
-        <v>217.9666274787821</v>
+        <v>217.9666567507444</v>
       </c>
       <c r="E709" t="n">
-        <v>228.7378020799314</v>
+        <v>228.7378327984153</v>
       </c>
       <c r="F709" t="n">
         <v>667500</v>
@@ -14632,16 +14632,16 @@
         <v>44267</v>
       </c>
       <c r="B711" t="n">
-        <v>228.8874359130859</v>
+        <v>228.8874206542969</v>
       </c>
       <c r="C711" t="n">
-        <v>231.8794285394008</v>
+        <v>231.8794130811504</v>
       </c>
       <c r="D711" t="n">
-        <v>225.8954432867711</v>
+        <v>225.8954282274433</v>
       </c>
       <c r="E711" t="n">
-        <v>227.8402354502634</v>
+        <v>227.840220261286</v>
       </c>
       <c r="F711" t="n">
         <v>268453</v>
@@ -14692,16 +14692,16 @@
         <v>44272</v>
       </c>
       <c r="B714" t="n">
-        <v>232.4778137207031</v>
+        <v>232.4778289794922</v>
       </c>
       <c r="C714" t="n">
-        <v>237.7138003791148</v>
+        <v>237.7138159815703</v>
       </c>
       <c r="D714" t="n">
-        <v>226.9426247810559</v>
+        <v>226.9426396765402</v>
       </c>
       <c r="E714" t="n">
-        <v>237.564191629467</v>
+        <v>237.5642072221028</v>
       </c>
       <c r="F714" t="n">
         <v>815453</v>
@@ -14752,16 +14752,16 @@
         <v>44277</v>
       </c>
       <c r="B717" t="n">
-        <v>224.8482208251953</v>
+        <v>224.8482360839844</v>
       </c>
       <c r="C717" t="n">
-        <v>228.5882112421748</v>
+        <v>228.5882267547694</v>
       </c>
       <c r="D717" t="n">
-        <v>221.5570262146414</v>
+        <v>221.5570412500813</v>
       </c>
       <c r="E717" t="n">
-        <v>227.2418238228982</v>
+        <v>227.2418392441234</v>
       </c>
       <c r="F717" t="n">
         <v>456213</v>
@@ -14772,16 +14772,16 @@
         <v>44278</v>
       </c>
       <c r="B718" t="n">
-        <v>228.2890167236328</v>
+        <v>228.2890014648438</v>
       </c>
       <c r="C718" t="n">
-        <v>231.5802114460384</v>
+        <v>231.5801959672666</v>
       </c>
       <c r="D718" t="n">
-        <v>222.9034364273768</v>
+        <v>222.9034215285587</v>
       </c>
       <c r="E718" t="n">
-        <v>224.8482284666881</v>
+        <v>224.8482134378806</v>
       </c>
       <c r="F718" t="n">
         <v>793680</v>
@@ -14812,16 +14812,16 @@
         <v>44280</v>
       </c>
       <c r="B720" t="n">
-        <v>231.1314086914062</v>
+        <v>231.1314239501953</v>
       </c>
       <c r="C720" t="n">
-        <v>232.3282025860022</v>
+        <v>232.3282179238009</v>
       </c>
       <c r="D720" t="n">
-        <v>217.3682408584031</v>
+        <v>217.3682552085779</v>
       </c>
       <c r="E720" t="n">
-        <v>219.7618438656549</v>
+        <v>219.7618583738502</v>
       </c>
       <c r="F720" t="n">
         <v>2364866</v>
@@ -14872,16 +14872,16 @@
         <v>44285</v>
       </c>
       <c r="B723" t="n">
-        <v>224.3994293212891</v>
+        <v>224.3994445800781</v>
       </c>
       <c r="C723" t="n">
-        <v>226.7930171468254</v>
+        <v>226.7930325683745</v>
       </c>
       <c r="D723" t="n">
-        <v>222.0058414957527</v>
+        <v>222.0058565917818</v>
       </c>
       <c r="E723" t="n">
-        <v>222.7538395934904</v>
+        <v>222.7538547403821</v>
       </c>
       <c r="F723" t="n">
         <v>572013</v>
@@ -14892,16 +14892,16 @@
         <v>44286</v>
       </c>
       <c r="B724" t="n">
-        <v>222.6042327880859</v>
+        <v>222.6042175292969</v>
       </c>
       <c r="C724" t="n">
-        <v>225.2970229198573</v>
+        <v>225.2970074764863</v>
       </c>
       <c r="D724" t="n">
-        <v>221.7066411501823</v>
+        <v>221.7066259529202</v>
       </c>
       <c r="E724" t="n">
-        <v>224.5490248155841</v>
+        <v>224.549009423486</v>
       </c>
       <c r="F724" t="n">
         <v>567873</v>
@@ -14952,16 +14952,16 @@
         <v>44292</v>
       </c>
       <c r="B727" t="n">
-        <v>219.1634368896484</v>
+        <v>219.1634521484375</v>
       </c>
       <c r="C727" t="n">
-        <v>222.9034272802568</v>
+        <v>222.9034427994347</v>
       </c>
       <c r="D727" t="n">
-        <v>215.4234464990401</v>
+        <v>215.4234614974403</v>
       </c>
       <c r="E727" t="n">
-        <v>221.1082288491528</v>
+        <v>221.1082442433439</v>
       </c>
       <c r="F727" t="n">
         <v>964873</v>
@@ -14972,16 +14972,16 @@
         <v>44293</v>
       </c>
       <c r="B728" t="n">
-        <v>227.6905975341797</v>
+        <v>227.6906280517578</v>
       </c>
       <c r="C728" t="n">
-        <v>230.383387329484</v>
+        <v>230.3834182079792</v>
       </c>
       <c r="D728" t="n">
-        <v>219.1634171673338</v>
+        <v>219.1634465420062</v>
       </c>
       <c r="E728" t="n">
-        <v>219.3130106822724</v>
+        <v>219.313040076995</v>
       </c>
       <c r="F728" t="n">
         <v>1567580</v>
@@ -14992,16 +14992,16 @@
         <v>44294</v>
       </c>
       <c r="B729" t="n">
-        <v>222.6042327880859</v>
+        <v>222.6042175292969</v>
       </c>
       <c r="C729" t="n">
-        <v>229.6354180118659</v>
+        <v>229.6354022711122</v>
       </c>
       <c r="D729" t="n">
-        <v>221.5570323984914</v>
+        <v>221.5570172114845</v>
       </c>
       <c r="E729" t="n">
-        <v>228.4386240886409</v>
+        <v>228.4386084299234</v>
       </c>
       <c r="F729" t="n">
         <v>729940</v>
@@ -15052,16 +15052,16 @@
         <v>44299</v>
       </c>
       <c r="B732" t="n">
-        <v>227.2418060302734</v>
+        <v>227.2418365478516</v>
       </c>
       <c r="C732" t="n">
-        <v>227.9898040551024</v>
+        <v>227.9898346731334</v>
       </c>
       <c r="D732" t="n">
-        <v>219.9114192997257</v>
+        <v>219.9114488328651</v>
       </c>
       <c r="E732" t="n">
-        <v>220.6594173245547</v>
+        <v>220.6594469581469</v>
       </c>
       <c r="F732" t="n">
         <v>596393</v>
@@ -15172,16 +15172,16 @@
         <v>44308</v>
       </c>
       <c r="B738" t="n">
-        <v>222.3050231933594</v>
+        <v>222.3050384521484</v>
       </c>
       <c r="C738" t="n">
-        <v>227.541009751112</v>
+        <v>227.5410253692938</v>
       </c>
       <c r="D738" t="n">
-        <v>218.4154392662528</v>
+        <v>218.4154542580648</v>
       </c>
       <c r="E738" t="n">
-        <v>226.6434181427212</v>
+        <v>226.6434336992933</v>
       </c>
       <c r="F738" t="n">
         <v>1262726</v>
@@ -15232,16 +15232,16 @@
         <v>44313</v>
       </c>
       <c r="B741" t="n">
-        <v>216.4706573486328</v>
+        <v>216.4706420898438</v>
       </c>
       <c r="C741" t="n">
-        <v>222.4546422637681</v>
+        <v>222.4546265831743</v>
       </c>
       <c r="D741" t="n">
-        <v>216.4706573486328</v>
+        <v>216.4706420898438</v>
       </c>
       <c r="E741" t="n">
-        <v>220.8090372812696</v>
+        <v>220.8090217166727</v>
       </c>
       <c r="F741" t="n">
         <v>462980</v>
@@ -15252,16 +15252,16 @@
         <v>44314</v>
       </c>
       <c r="B742" t="n">
-        <v>219.9114227294922</v>
+        <v>219.9114379882812</v>
       </c>
       <c r="C742" t="n">
-        <v>221.7066210606917</v>
+        <v>221.7066364440425</v>
       </c>
       <c r="D742" t="n">
-        <v>211.833037848124</v>
+        <v>211.8330525463857</v>
       </c>
       <c r="E742" t="n">
-        <v>217.0690241035881</v>
+        <v>217.0690391651543</v>
       </c>
       <c r="F742" t="n">
         <v>681606</v>
@@ -15332,16 +15332,16 @@
         <v>44320</v>
       </c>
       <c r="B746" t="n">
-        <v>222.6042327880859</v>
+        <v>222.6042175292969</v>
       </c>
       <c r="C746" t="n">
-        <v>225.1474293862268</v>
+        <v>225.14741395311</v>
       </c>
       <c r="D746" t="n">
-        <v>220.3602384752664</v>
+        <v>220.3602233702958</v>
       </c>
       <c r="E746" t="n">
-        <v>223.8010267113109</v>
+        <v>223.8010113704856</v>
       </c>
       <c r="F746" t="n">
         <v>465600</v>
@@ -15352,16 +15352,16 @@
         <v>44321</v>
       </c>
       <c r="B747" t="n">
-        <v>222.3050231933594</v>
+        <v>222.3050384521484</v>
       </c>
       <c r="C747" t="n">
-        <v>224.2498303749726</v>
+        <v>224.2498457672512</v>
       </c>
       <c r="D747" t="n">
-        <v>219.9114354256107</v>
+        <v>219.9114505201064</v>
       </c>
       <c r="E747" t="n">
-        <v>224.2498303749726</v>
+        <v>224.2498457672512</v>
       </c>
       <c r="F747" t="n">
         <v>1063686</v>
@@ -15452,16 +15452,16 @@
         <v>44328</v>
       </c>
       <c r="B752" t="n">
-        <v>212.4675750732422</v>
+        <v>212.4675598144531</v>
       </c>
       <c r="C752" t="n">
-        <v>218.9014493024574</v>
+        <v>218.9014335816066</v>
       </c>
       <c r="D752" t="n">
-        <v>211.2705776944238</v>
+        <v>211.2705625215996</v>
       </c>
       <c r="E752" t="n">
-        <v>218.4525771879814</v>
+        <v>218.4525614993673</v>
       </c>
       <c r="F752" t="n">
         <v>1381546</v>
@@ -15472,16 +15472,16 @@
         <v>44329</v>
       </c>
       <c r="B753" t="n">
-        <v>218.4525604248047</v>
+        <v>218.4525756835938</v>
       </c>
       <c r="C753" t="n">
-        <v>221.7443143794447</v>
+        <v>221.7443298681609</v>
       </c>
       <c r="D753" t="n">
-        <v>214.4126812632304</v>
+        <v>214.4126962398362</v>
       </c>
       <c r="E753" t="n">
-        <v>214.7119343901334</v>
+        <v>214.7119493876418</v>
       </c>
       <c r="F753" t="n">
         <v>807133</v>
@@ -15512,16 +15512,16 @@
         <v>44333</v>
       </c>
       <c r="B755" t="n">
-        <v>218.6021881103516</v>
+        <v>218.6022033691406</v>
       </c>
       <c r="C755" t="n">
-        <v>222.9413205721625</v>
+        <v>222.9413361338301</v>
       </c>
       <c r="D755" t="n">
-        <v>217.8540628735322</v>
+        <v>217.8540780801009</v>
       </c>
       <c r="E755" t="n">
-        <v>219.2006943880658</v>
+        <v>219.2007096886316</v>
       </c>
       <c r="F755" t="n">
         <v>603380</v>
@@ -15532,16 +15532,16 @@
         <v>44334</v>
       </c>
       <c r="B756" t="n">
-        <v>219.7991943359375</v>
+        <v>219.7992095947266</v>
       </c>
       <c r="C756" t="n">
-        <v>223.2405672820714</v>
+        <v>223.2405827797657</v>
       </c>
       <c r="D756" t="n">
-        <v>215.6096809538825</v>
+        <v>215.6096959218293</v>
       </c>
       <c r="E756" t="n">
-        <v>218.7518159904238</v>
+        <v>218.7518311765023</v>
       </c>
       <c r="F756" t="n">
         <v>1363900</v>
@@ -15552,16 +15552,16 @@
         <v>44335</v>
       </c>
       <c r="B757" t="n">
-        <v>217.8540649414062</v>
+        <v>217.8540802001953</v>
       </c>
       <c r="C757" t="n">
-        <v>221.7443253421814</v>
+        <v>221.7443408734494</v>
       </c>
       <c r="D757" t="n">
-        <v>216.9563207369604</v>
+        <v>216.9563359328703</v>
       </c>
       <c r="E757" t="n">
-        <v>219.0510775081968</v>
+        <v>219.0510928508262</v>
       </c>
       <c r="F757" t="n">
         <v>577806</v>
@@ -15572,16 +15572,16 @@
         <v>44336</v>
       </c>
       <c r="B758" t="n">
-        <v>223.0909271240234</v>
+        <v>223.0909423828125</v>
       </c>
       <c r="C758" t="n">
-        <v>224.4375585636639</v>
+        <v>224.4375739145587</v>
       </c>
       <c r="D758" t="n">
-        <v>217.2555597337558</v>
+        <v>217.2555745934222</v>
       </c>
       <c r="E758" t="n">
-        <v>219.2006821971784</v>
+        <v>219.2006971898857</v>
       </c>
       <c r="F758" t="n">
         <v>585933</v>
@@ -15932,16 +15932,16 @@
         <v>44363</v>
       </c>
       <c r="B776" t="n">
-        <v>228.9263305664062</v>
+        <v>228.9263153076172</v>
       </c>
       <c r="C776" t="n">
-        <v>230.8714532068279</v>
+        <v>230.8714378183892</v>
       </c>
       <c r="D776" t="n">
-        <v>225.7842105488518</v>
+        <v>225.7841954994967</v>
       </c>
       <c r="E776" t="n">
-        <v>226.3827016270945</v>
+        <v>226.3826865378477</v>
       </c>
       <c r="F776" t="n">
         <v>725393</v>
@@ -16132,16 +16132,16 @@
         <v>44377</v>
       </c>
       <c r="B786" t="n">
-        <v>230.5721893310547</v>
+        <v>230.5721740722656</v>
       </c>
       <c r="C786" t="n">
-        <v>232.5173271016351</v>
+        <v>232.5173117141208</v>
       </c>
       <c r="D786" t="n">
-        <v>227.7293225951968</v>
+        <v>227.7293075245428</v>
       </c>
       <c r="E786" t="n">
-        <v>231.3203145595405</v>
+        <v>231.320299251242</v>
       </c>
       <c r="F786" t="n">
         <v>609766</v>
@@ -42332,19 +42332,39 @@
         <v>46295</v>
       </c>
       <c r="B2096" t="n">
-        <v>6.67</v>
+        <v>6.670000076293945</v>
       </c>
       <c r="C2096" t="n">
-        <v>6.76</v>
+        <v>6.760000228881836</v>
       </c>
       <c r="D2096" t="n">
-        <v>6.35</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="E2096" t="n">
-        <v>6.45</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="F2096" t="n">
         <v>8698500</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2097" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>8107300</v>
       </c>
     </row>
   </sheetData>

--- a/database/HAPV3.xlsx
+++ b/database/HAPV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2097"/>
+  <dimension ref="A1:F2098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43216</v>
       </c>
       <c r="B2" t="n">
-        <v>81.53695678710938</v>
+        <v>81.53696441650391</v>
       </c>
       <c r="C2" t="n">
-        <v>85.66652592966578</v>
+        <v>85.66653394546317</v>
       </c>
       <c r="D2" t="n">
-        <v>79.57468617128777</v>
+        <v>79.57469361707308</v>
       </c>
       <c r="E2" t="n">
-        <v>84.9343334003524</v>
+        <v>84.93434134763869</v>
       </c>
       <c r="F2" t="n">
         <v>1956933</v>
@@ -492,16 +492,16 @@
         <v>43220</v>
       </c>
       <c r="B4" t="n">
-        <v>80.98048400878906</v>
+        <v>80.98049163818359</v>
       </c>
       <c r="C4" t="n">
-        <v>82.00555644363325</v>
+        <v>82.00556416960269</v>
       </c>
       <c r="D4" t="n">
-        <v>80.68761149043854</v>
+        <v>80.68761909224075</v>
       </c>
       <c r="E4" t="n">
-        <v>81.56623649373705</v>
+        <v>81.56624417831694</v>
       </c>
       <c r="F4" t="n">
         <v>370366</v>
@@ -512,16 +512,16 @@
         <v>43222</v>
       </c>
       <c r="B5" t="n">
-        <v>79.98471832275391</v>
+        <v>79.98469543457031</v>
       </c>
       <c r="C5" t="n">
-        <v>81.85912955369824</v>
+        <v>81.85910612913884</v>
       </c>
       <c r="D5" t="n">
-        <v>79.07679921897648</v>
+        <v>79.07677659060025</v>
       </c>
       <c r="E5" t="n">
-        <v>79.07679921897648</v>
+        <v>79.07677659060025</v>
       </c>
       <c r="F5" t="n">
         <v>428333</v>
@@ -532,16 +532,16 @@
         <v>43223</v>
       </c>
       <c r="B6" t="n">
-        <v>80.51189422607422</v>
+        <v>80.51187896728516</v>
       </c>
       <c r="C6" t="n">
-        <v>81.71268584058056</v>
+        <v>81.71267035421486</v>
       </c>
       <c r="D6" t="n">
-        <v>78.49104308007162</v>
+        <v>78.49102820427865</v>
       </c>
       <c r="E6" t="n">
-        <v>79.39896214266686</v>
+        <v>79.39894709480311</v>
       </c>
       <c r="F6" t="n">
         <v>790600</v>
@@ -552,16 +552,16 @@
         <v>43224</v>
       </c>
       <c r="B7" t="n">
-        <v>78.34458160400391</v>
+        <v>78.34458923339844</v>
       </c>
       <c r="C7" t="n">
-        <v>81.0390515428093</v>
+        <v>81.03905943459817</v>
       </c>
       <c r="D7" t="n">
-        <v>77.3195093326906</v>
+        <v>77.31951686226098</v>
       </c>
       <c r="E7" t="n">
-        <v>81.0390515428093</v>
+        <v>81.03905943459817</v>
       </c>
       <c r="F7" t="n">
         <v>632800</v>
@@ -612,16 +612,16 @@
         <v>43229</v>
       </c>
       <c r="B10" t="n">
-        <v>78.78391265869141</v>
+        <v>78.78392028808594</v>
       </c>
       <c r="C10" t="n">
-        <v>79.34037867939415</v>
+        <v>79.34038636267657</v>
       </c>
       <c r="D10" t="n">
-        <v>77.81742061183874</v>
+        <v>77.81742814763868</v>
       </c>
       <c r="E10" t="n">
-        <v>79.07679264779708</v>
+        <v>79.07680030555396</v>
       </c>
       <c r="F10" t="n">
         <v>333066</v>
@@ -632,16 +632,16 @@
         <v>43230</v>
       </c>
       <c r="B11" t="n">
-        <v>79.66253662109375</v>
+        <v>79.66254425048828</v>
       </c>
       <c r="C11" t="n">
-        <v>80.95119502789649</v>
+        <v>80.95120278070766</v>
       </c>
       <c r="D11" t="n">
-        <v>78.43245122652172</v>
+        <v>78.43245873810922</v>
       </c>
       <c r="E11" t="n">
-        <v>79.36965666344675</v>
+        <v>79.36966426479174</v>
       </c>
       <c r="F11" t="n">
         <v>396433</v>
@@ -672,16 +672,16 @@
         <v>43234</v>
       </c>
       <c r="B13" t="n">
-        <v>80.01399993896484</v>
+        <v>80.01398468017578</v>
       </c>
       <c r="C13" t="n">
-        <v>81.82983803542157</v>
+        <v>81.82982243034948</v>
       </c>
       <c r="D13" t="n">
-        <v>80.01399993896484</v>
+        <v>80.01398468017578</v>
       </c>
       <c r="E13" t="n">
-        <v>81.68339803765939</v>
+        <v>81.68338246051361</v>
       </c>
       <c r="F13" t="n">
         <v>350433</v>
@@ -692,16 +692,16 @@
         <v>43235</v>
       </c>
       <c r="B14" t="n">
-        <v>84.78789520263672</v>
+        <v>84.78788757324219</v>
       </c>
       <c r="C14" t="n">
-        <v>85.22720775024067</v>
+        <v>85.22720008131586</v>
       </c>
       <c r="D14" t="n">
-        <v>82.00556502190037</v>
+        <v>82.0055576428658</v>
       </c>
       <c r="E14" t="n">
-        <v>82.29843757088707</v>
+        <v>82.29843016549923</v>
       </c>
       <c r="F14" t="n">
         <v>900866</v>
@@ -712,16 +712,16 @@
         <v>43236</v>
       </c>
       <c r="B15" t="n">
-        <v>87.30662536621094</v>
+        <v>87.30663299560547</v>
       </c>
       <c r="C15" t="n">
-        <v>87.30662536621094</v>
+        <v>87.30663299560547</v>
       </c>
       <c r="D15" t="n">
-        <v>83.61637672277325</v>
+        <v>83.61638402969096</v>
       </c>
       <c r="E15" t="n">
-        <v>84.7878816276515</v>
+        <v>84.78788903694259</v>
       </c>
       <c r="F15" t="n">
         <v>589600</v>
@@ -732,16 +732,16 @@
         <v>43237</v>
       </c>
       <c r="B16" t="n">
-        <v>88.74172973632812</v>
+        <v>88.74173736572266</v>
       </c>
       <c r="C16" t="n">
-        <v>90.73329416832706</v>
+        <v>90.7333019689424</v>
       </c>
       <c r="D16" t="n">
-        <v>87.86309727393932</v>
+        <v>87.86310482779517</v>
       </c>
       <c r="E16" t="n">
-        <v>87.86309727393932</v>
+        <v>87.86310482779517</v>
       </c>
       <c r="F16" t="n">
         <v>520533</v>
@@ -752,16 +752,16 @@
         <v>43238</v>
       </c>
       <c r="B17" t="n">
-        <v>86.69158172607422</v>
+        <v>86.69157409667969</v>
       </c>
       <c r="C17" t="n">
-        <v>88.74172654739176</v>
+        <v>88.74171873757183</v>
       </c>
       <c r="D17" t="n">
-        <v>85.60794375102347</v>
+        <v>85.60793621699578</v>
       </c>
       <c r="E17" t="n">
-        <v>88.74172654739176</v>
+        <v>88.74171873757183</v>
       </c>
       <c r="F17" t="n">
         <v>980066</v>
@@ -772,16 +772,16 @@
         <v>43241</v>
       </c>
       <c r="B18" t="n">
-        <v>90.20610809326172</v>
+        <v>90.20611572265625</v>
       </c>
       <c r="C18" t="n">
-        <v>91.05544653791148</v>
+        <v>91.05545423914081</v>
       </c>
       <c r="D18" t="n">
-        <v>84.93432115275195</v>
+        <v>84.93432833627266</v>
       </c>
       <c r="E18" t="n">
-        <v>86.98445844954838</v>
+        <v>86.9844658064643</v>
       </c>
       <c r="F18" t="n">
         <v>633933</v>
@@ -792,16 +792,16 @@
         <v>43242</v>
       </c>
       <c r="B19" t="n">
-        <v>95.91721343994141</v>
+        <v>95.91722106933594</v>
       </c>
       <c r="C19" t="n">
-        <v>96.06365342339224</v>
+        <v>96.06366106443481</v>
       </c>
       <c r="D19" t="n">
-        <v>90.20611367133475</v>
+        <v>90.2061208464601</v>
       </c>
       <c r="E19" t="n">
-        <v>90.20611367133475</v>
+        <v>90.2061208464601</v>
       </c>
       <c r="F19" t="n">
         <v>462766</v>
@@ -912,16 +912,16 @@
         <v>43250</v>
       </c>
       <c r="B25" t="n">
-        <v>87.86309814453125</v>
+        <v>87.86310577392578</v>
       </c>
       <c r="C25" t="n">
-        <v>90.05967559814454</v>
+        <v>90.05968341827392</v>
       </c>
       <c r="D25" t="n">
-        <v>85.49079419669903</v>
+        <v>85.49080162009987</v>
       </c>
       <c r="E25" t="n">
-        <v>88.15597066939809</v>
+        <v>88.15597832422354</v>
       </c>
       <c r="F25" t="n">
         <v>493866</v>
@@ -952,16 +952,16 @@
         <v>43255</v>
       </c>
       <c r="B27" t="n">
-        <v>88.74172973632812</v>
+        <v>88.74173736572266</v>
       </c>
       <c r="C27" t="n">
-        <v>90.20611469089378</v>
+        <v>90.2061224461859</v>
       </c>
       <c r="D27" t="n">
-        <v>86.72087879695741</v>
+        <v>86.72088625261327</v>
       </c>
       <c r="E27" t="n">
-        <v>88.44884976611618</v>
+        <v>88.44885737033093</v>
       </c>
       <c r="F27" t="n">
         <v>304000</v>
@@ -1032,16 +1032,16 @@
         <v>43259</v>
       </c>
       <c r="B31" t="n">
-        <v>80.98048400878906</v>
+        <v>80.98049163818359</v>
       </c>
       <c r="C31" t="n">
-        <v>83.14777490651888</v>
+        <v>83.14778274009986</v>
       </c>
       <c r="D31" t="n">
-        <v>79.07678657064635</v>
+        <v>79.07679402068831</v>
       </c>
       <c r="E31" t="n">
-        <v>79.75040602487236</v>
+        <v>79.75041353837787</v>
       </c>
       <c r="F31" t="n">
         <v>443000</v>
@@ -1092,16 +1092,16 @@
         <v>43264</v>
       </c>
       <c r="B34" t="n">
-        <v>78.3153076171875</v>
+        <v>78.31529998779297</v>
       </c>
       <c r="C34" t="n">
-        <v>82.32772294015612</v>
+        <v>82.32771491987633</v>
       </c>
       <c r="D34" t="n">
-        <v>77.70026117681101</v>
+        <v>77.70025360733365</v>
       </c>
       <c r="E34" t="n">
-        <v>82.32772294015612</v>
+        <v>82.32771491987633</v>
       </c>
       <c r="F34" t="n">
         <v>786033</v>
@@ -1112,16 +1112,16 @@
         <v>43265</v>
       </c>
       <c r="B35" t="n">
-        <v>79.13536834716797</v>
+        <v>79.1353759765625</v>
       </c>
       <c r="C35" t="n">
-        <v>80.21901391602279</v>
+        <v>80.21902164989095</v>
       </c>
       <c r="D35" t="n">
-        <v>77.90528277879942</v>
+        <v>77.90529028960211</v>
       </c>
       <c r="E35" t="n">
-        <v>78.19816277782689</v>
+        <v>78.19817031686598</v>
       </c>
       <c r="F35" t="n">
         <v>536566</v>
@@ -1152,16 +1152,16 @@
         <v>43269</v>
       </c>
       <c r="B37" t="n">
-        <v>77.26094818115234</v>
+        <v>77.26095581054688</v>
       </c>
       <c r="C37" t="n">
-        <v>79.07678608716174</v>
+        <v>79.07679389586734</v>
       </c>
       <c r="D37" t="n">
-        <v>76.7337687134483</v>
+        <v>76.7337762907847</v>
       </c>
       <c r="E37" t="n">
-        <v>79.07678608716174</v>
+        <v>79.07679389586734</v>
       </c>
       <c r="F37" t="n">
         <v>465333</v>
@@ -1192,16 +1192,16 @@
         <v>43271</v>
       </c>
       <c r="B39" t="n">
-        <v>84.34857177734375</v>
+        <v>84.34857940673828</v>
       </c>
       <c r="C39" t="n">
-        <v>85.52007671870746</v>
+        <v>85.52008445406554</v>
       </c>
       <c r="D39" t="n">
-        <v>81.71267448690524</v>
+        <v>81.71268187788078</v>
       </c>
       <c r="E39" t="n">
-        <v>82.03484095266663</v>
+        <v>82.03484837278239</v>
       </c>
       <c r="F39" t="n">
         <v>141600</v>
@@ -1212,16 +1212,16 @@
         <v>43272</v>
       </c>
       <c r="B40" t="n">
-        <v>82.62060546875</v>
+        <v>82.62059783935547</v>
       </c>
       <c r="C40" t="n">
-        <v>85.46151616569612</v>
+        <v>85.46150827396475</v>
       </c>
       <c r="D40" t="n">
-        <v>80.10186128453448</v>
+        <v>80.10185388772712</v>
       </c>
       <c r="E40" t="n">
-        <v>83.46995151642673</v>
+        <v>83.46994380860144</v>
       </c>
       <c r="F40" t="n">
         <v>246900</v>
@@ -1232,16 +1232,16 @@
         <v>43273</v>
       </c>
       <c r="B41" t="n">
-        <v>84.93433380126953</v>
+        <v>84.934326171875</v>
       </c>
       <c r="C41" t="n">
-        <v>85.52008633783566</v>
+        <v>85.52007865582475</v>
       </c>
       <c r="D41" t="n">
-        <v>81.21479811823937</v>
+        <v>81.21479082295949</v>
       </c>
       <c r="E41" t="n">
-        <v>82.03485017978244</v>
+        <v>82.03484281083975</v>
       </c>
       <c r="F41" t="n">
         <v>298800</v>
@@ -1272,16 +1272,16 @@
         <v>43277</v>
       </c>
       <c r="B43" t="n">
-        <v>86.75017547607422</v>
+        <v>86.75016021728516</v>
       </c>
       <c r="C43" t="n">
-        <v>87.86310757617932</v>
+        <v>87.86309212163277</v>
       </c>
       <c r="D43" t="n">
-        <v>85.08077732591656</v>
+        <v>85.08076236076373</v>
       </c>
       <c r="E43" t="n">
-        <v>86.60373547379767</v>
+        <v>86.60372024076645</v>
       </c>
       <c r="F43" t="n">
         <v>153233</v>
@@ -1292,16 +1292,16 @@
         <v>43278</v>
       </c>
       <c r="B44" t="n">
-        <v>87.86309814453125</v>
+        <v>87.86310577392578</v>
       </c>
       <c r="C44" t="n">
-        <v>88.59529062906901</v>
+        <v>88.59529832204183</v>
       </c>
       <c r="D44" t="n">
-        <v>85.25649468715613</v>
+        <v>85.25650209021211</v>
       </c>
       <c r="E44" t="n">
-        <v>86.98446567343652</v>
+        <v>86.98447322653696</v>
       </c>
       <c r="F44" t="n">
         <v>117966</v>
@@ -1352,16 +1352,16 @@
         <v>43283</v>
       </c>
       <c r="B47" t="n">
-        <v>86.10582733154297</v>
+        <v>86.10584259033203</v>
       </c>
       <c r="C47" t="n">
-        <v>86.9551732370663</v>
+        <v>86.95518864636772</v>
       </c>
       <c r="D47" t="n">
-        <v>85.8715278379749</v>
+        <v>85.87154305524381</v>
       </c>
       <c r="E47" t="n">
-        <v>86.0472543202126</v>
+        <v>86.04726956862196</v>
       </c>
       <c r="F47" t="n">
         <v>88033</v>
@@ -1392,16 +1392,16 @@
         <v>43285</v>
       </c>
       <c r="B49" t="n">
-        <v>85.78368377685547</v>
+        <v>85.78367614746094</v>
       </c>
       <c r="C49" t="n">
-        <v>87.07234239603083</v>
+        <v>87.07233465202611</v>
       </c>
       <c r="D49" t="n">
-        <v>84.14357212988246</v>
+        <v>84.14356464635551</v>
       </c>
       <c r="E49" t="n">
-        <v>86.66230889810163</v>
+        <v>86.66230119056429</v>
       </c>
       <c r="F49" t="n">
         <v>320933</v>
@@ -1452,16 +1452,16 @@
         <v>43291</v>
       </c>
       <c r="B52" t="n">
-        <v>84.23141479492188</v>
+        <v>84.23142242431641</v>
       </c>
       <c r="C52" t="n">
-        <v>86.07653909723963</v>
+        <v>86.07654689375923</v>
       </c>
       <c r="D52" t="n">
-        <v>83.17705592266988</v>
+        <v>83.17706345656418</v>
       </c>
       <c r="E52" t="n">
-        <v>84.14355527969077</v>
+        <v>84.14356290112728</v>
       </c>
       <c r="F52" t="n">
         <v>281266</v>
@@ -1472,16 +1472,16 @@
         <v>43292</v>
       </c>
       <c r="B53" t="n">
-        <v>84.08499145507812</v>
+        <v>84.08498382568359</v>
       </c>
       <c r="C53" t="n">
-        <v>86.25228263847217</v>
+        <v>86.25227481242993</v>
       </c>
       <c r="D53" t="n">
-        <v>82.64989283643895</v>
+        <v>82.6498853372571</v>
       </c>
       <c r="E53" t="n">
-        <v>83.79211889812494</v>
+        <v>83.792111295304</v>
       </c>
       <c r="F53" t="n">
         <v>271833</v>
@@ -1532,16 +1532,16 @@
         <v>43297</v>
       </c>
       <c r="B56" t="n">
-        <v>83.46994018554688</v>
+        <v>83.46994781494141</v>
       </c>
       <c r="C56" t="n">
-        <v>86.0179705344391</v>
+        <v>86.017978396731</v>
       </c>
       <c r="D56" t="n">
-        <v>82.9134742155731</v>
+        <v>82.91348179410504</v>
       </c>
       <c r="E56" t="n">
-        <v>84.43643214429146</v>
+        <v>84.43643986202616</v>
       </c>
       <c r="F56" t="n">
         <v>173400</v>
@@ -1552,16 +1552,16 @@
         <v>43298</v>
       </c>
       <c r="B57" t="n">
-        <v>83.08921051025391</v>
+        <v>83.08920288085938</v>
       </c>
       <c r="C57" t="n">
-        <v>84.58288210867671</v>
+        <v>84.58287434213068</v>
       </c>
       <c r="D57" t="n">
-        <v>82.35701796606644</v>
+        <v>82.35701040390309</v>
       </c>
       <c r="E57" t="n">
-        <v>84.11427560316773</v>
+        <v>84.11426787964996</v>
       </c>
       <c r="F57" t="n">
         <v>152666</v>
@@ -1592,16 +1592,16 @@
         <v>43300</v>
       </c>
       <c r="B59" t="n">
-        <v>85.19790649414062</v>
+        <v>85.19792175292969</v>
       </c>
       <c r="C59" t="n">
-        <v>86.54514531034216</v>
+        <v>86.54516081041923</v>
       </c>
       <c r="D59" t="n">
-        <v>83.6163756378991</v>
+        <v>83.61639061343887</v>
       </c>
       <c r="E59" t="n">
-        <v>85.52007294568851</v>
+        <v>85.520088262177</v>
       </c>
       <c r="F59" t="n">
         <v>169366</v>
@@ -1612,16 +1612,16 @@
         <v>43301</v>
       </c>
       <c r="B60" t="n">
-        <v>87.86309814453125</v>
+        <v>87.86310577392578</v>
       </c>
       <c r="C60" t="n">
-        <v>88.77101712328796</v>
+        <v>88.77102483151958</v>
       </c>
       <c r="D60" t="n">
-        <v>85.54936721202297</v>
+        <v>85.54937464050987</v>
       </c>
       <c r="E60" t="n">
-        <v>86.39871317545573</v>
+        <v>86.39872067769367</v>
       </c>
       <c r="F60" t="n">
         <v>356866</v>
@@ -1632,16 +1632,16 @@
         <v>43304</v>
       </c>
       <c r="B61" t="n">
-        <v>87.65808868408203</v>
+        <v>87.6580810546875</v>
       </c>
       <c r="C61" t="n">
-        <v>89.26891370479268</v>
+        <v>89.26890593519866</v>
       </c>
       <c r="D61" t="n">
-        <v>86.72088315979977</v>
+        <v>86.7208756119757</v>
       </c>
       <c r="E61" t="n">
-        <v>89.00532022869139</v>
+        <v>89.00531248203944</v>
       </c>
       <c r="F61" t="n">
         <v>145300</v>
@@ -1652,16 +1652,16 @@
         <v>43305</v>
       </c>
       <c r="B62" t="n">
-        <v>88.15598297119141</v>
+        <v>88.15596771240234</v>
       </c>
       <c r="C62" t="n">
-        <v>88.71245648741085</v>
+        <v>88.71244113230262</v>
       </c>
       <c r="D62" t="n">
-        <v>87.10163130699453</v>
+        <v>87.10161623070165</v>
       </c>
       <c r="E62" t="n">
-        <v>88.18527693118834</v>
+        <v>88.18526166732883</v>
       </c>
       <c r="F62" t="n">
         <v>140566</v>
@@ -1672,16 +1672,16 @@
         <v>43306</v>
       </c>
       <c r="B63" t="n">
-        <v>83.99713134765625</v>
+        <v>83.99711608886719</v>
       </c>
       <c r="C63" t="n">
-        <v>89.9132448469509</v>
+        <v>89.91322851344979</v>
       </c>
       <c r="D63" t="n">
-        <v>83.99713134765625</v>
+        <v>83.99711608886719</v>
       </c>
       <c r="E63" t="n">
-        <v>88.77102624132928</v>
+        <v>88.77101011532184</v>
       </c>
       <c r="F63" t="n">
         <v>653300</v>
@@ -1692,16 +1692,16 @@
         <v>43307</v>
       </c>
       <c r="B64" t="n">
-        <v>80.57044982910156</v>
+        <v>80.57046508789062</v>
       </c>
       <c r="C64" t="n">
-        <v>84.84645072790009</v>
+        <v>84.84646679649717</v>
       </c>
       <c r="D64" t="n">
-        <v>79.95541089962423</v>
+        <v>79.9554260419345</v>
       </c>
       <c r="E64" t="n">
-        <v>84.14355228631722</v>
+        <v>84.14356822179629</v>
       </c>
       <c r="F64" t="n">
         <v>454233</v>
@@ -1712,16 +1712,16 @@
         <v>43308</v>
       </c>
       <c r="B65" t="n">
-        <v>82.62060546875</v>
+        <v>82.62059783935547</v>
       </c>
       <c r="C65" t="n">
-        <v>82.62060546875</v>
+        <v>82.62059783935547</v>
       </c>
       <c r="D65" t="n">
-        <v>80.04328826340087</v>
+        <v>80.04328087200228</v>
       </c>
       <c r="E65" t="n">
-        <v>81.24408733437501</v>
+        <v>81.24407983209161</v>
       </c>
       <c r="F65" t="n">
         <v>199833</v>
@@ -1732,16 +1732,16 @@
         <v>43311</v>
       </c>
       <c r="B66" t="n">
-        <v>80.39472198486328</v>
+        <v>80.39473724365234</v>
       </c>
       <c r="C66" t="n">
-        <v>82.59129912897563</v>
+        <v>82.59131480467153</v>
       </c>
       <c r="D66" t="n">
-        <v>79.80896956941586</v>
+        <v>79.80898471703006</v>
       </c>
       <c r="E66" t="n">
-        <v>82.53272612190472</v>
+        <v>82.53274178648354</v>
       </c>
       <c r="F66" t="n">
         <v>306800</v>
@@ -1772,16 +1772,16 @@
         <v>43313</v>
       </c>
       <c r="B68" t="n">
-        <v>84.02641296386719</v>
+        <v>84.02640533447266</v>
       </c>
       <c r="C68" t="n">
-        <v>84.02641296386719</v>
+        <v>84.02640533447266</v>
       </c>
       <c r="D68" t="n">
-        <v>81.41980939058915</v>
+        <v>81.41980199786791</v>
       </c>
       <c r="E68" t="n">
-        <v>81.44909589955336</v>
+        <v>81.44908850417296</v>
       </c>
       <c r="F68" t="n">
         <v>89600</v>
@@ -1832,16 +1832,16 @@
         <v>43318</v>
       </c>
       <c r="B71" t="n">
-        <v>81.33193206787109</v>
+        <v>81.33195495605469</v>
       </c>
       <c r="C71" t="n">
-        <v>83.55779584493075</v>
+        <v>83.55781935951012</v>
       </c>
       <c r="D71" t="n">
-        <v>81.12691908295734</v>
+        <v>81.1269419134468</v>
       </c>
       <c r="E71" t="n">
-        <v>83.38206936525518</v>
+        <v>83.38209283038213</v>
       </c>
       <c r="F71" t="n">
         <v>242633</v>
@@ -1852,16 +1852,16 @@
         <v>43319</v>
       </c>
       <c r="B72" t="n">
-        <v>79.13536834716797</v>
+        <v>79.1353759765625</v>
       </c>
       <c r="C72" t="n">
-        <v>81.41981297413815</v>
+        <v>81.41982082377464</v>
       </c>
       <c r="D72" t="n">
-        <v>79.13536834716797</v>
+        <v>79.1353759765625</v>
       </c>
       <c r="E72" t="n">
-        <v>81.27337297462441</v>
+        <v>81.27338081014271</v>
       </c>
       <c r="F72" t="n">
         <v>212866</v>
@@ -1872,16 +1872,16 @@
         <v>43320</v>
       </c>
       <c r="B73" t="n">
-        <v>78.78391265869141</v>
+        <v>78.78392028808594</v>
       </c>
       <c r="C73" t="n">
-        <v>80.24829770772469</v>
+        <v>80.24830547892952</v>
       </c>
       <c r="D73" t="n">
-        <v>77.11451459658318</v>
+        <v>77.11452206431403</v>
       </c>
       <c r="E73" t="n">
-        <v>79.77969866305264</v>
+        <v>79.77970638887859</v>
       </c>
       <c r="F73" t="n">
         <v>270133</v>
@@ -1892,16 +1892,16 @@
         <v>43321</v>
       </c>
       <c r="B74" t="n">
-        <v>78.95964813232422</v>
+        <v>78.95964050292969</v>
       </c>
       <c r="C74" t="n">
-        <v>79.13537465610065</v>
+        <v>79.13536700972674</v>
       </c>
       <c r="D74" t="n">
-        <v>76.85093729525538</v>
+        <v>76.85092986961286</v>
       </c>
       <c r="E74" t="n">
-        <v>78.19816901204246</v>
+        <v>78.19816145622507</v>
       </c>
       <c r="F74" t="n">
         <v>546266</v>
@@ -1912,16 +1912,16 @@
         <v>43322</v>
       </c>
       <c r="B75" t="n">
-        <v>78.87178802490234</v>
+        <v>78.87176513671875</v>
       </c>
       <c r="C75" t="n">
-        <v>80.36545974208968</v>
+        <v>80.36543642045031</v>
       </c>
       <c r="D75" t="n">
-        <v>78.16888193487341</v>
+        <v>78.16885925066951</v>
       </c>
       <c r="E75" t="n">
-        <v>79.13537408453904</v>
+        <v>79.13535111986414</v>
       </c>
       <c r="F75" t="n">
         <v>176700</v>
@@ -1952,16 +1952,16 @@
         <v>43326</v>
       </c>
       <c r="B77" t="n">
-        <v>77.46595764160156</v>
+        <v>77.46596527099609</v>
       </c>
       <c r="C77" t="n">
-        <v>78.46174351789847</v>
+        <v>78.46175124536504</v>
       </c>
       <c r="D77" t="n">
-        <v>74.44932840370932</v>
+        <v>74.4493357360049</v>
       </c>
       <c r="E77" t="n">
-        <v>78.46174351789847</v>
+        <v>78.46175124536504</v>
       </c>
       <c r="F77" t="n">
         <v>524933</v>
@@ -1972,16 +1972,16 @@
         <v>43327</v>
       </c>
       <c r="B78" t="n">
-        <v>76.14801025390625</v>
+        <v>76.14801788330078</v>
       </c>
       <c r="C78" t="n">
-        <v>77.67096807554556</v>
+        <v>77.67097585752774</v>
       </c>
       <c r="D78" t="n">
-        <v>76.14801025390625</v>
+        <v>76.14801788330078</v>
       </c>
       <c r="E78" t="n">
-        <v>77.02664263110059</v>
+        <v>77.02665034852674</v>
       </c>
       <c r="F78" t="n">
         <v>702366</v>
@@ -2012,16 +2012,16 @@
         <v>43329</v>
       </c>
       <c r="B80" t="n">
-        <v>71.46198272705078</v>
+        <v>71.46199035644531</v>
       </c>
       <c r="C80" t="n">
-        <v>72.95565418739019</v>
+        <v>72.95566197625146</v>
       </c>
       <c r="D80" t="n">
-        <v>70.29047774395042</v>
+        <v>70.29048524827323</v>
       </c>
       <c r="E80" t="n">
-        <v>72.95565418739019</v>
+        <v>72.95566197625146</v>
       </c>
       <c r="F80" t="n">
         <v>2138466</v>
@@ -2032,16 +2032,16 @@
         <v>43332</v>
       </c>
       <c r="B81" t="n">
-        <v>72.34060668945312</v>
+        <v>72.34061431884766</v>
       </c>
       <c r="C81" t="n">
-        <v>73.0142260721305</v>
+        <v>73.01423377256823</v>
       </c>
       <c r="D81" t="n">
-        <v>71.75485426672097</v>
+        <v>71.75486183433918</v>
       </c>
       <c r="E81" t="n">
-        <v>71.95986724226492</v>
+        <v>71.95987483150479</v>
       </c>
       <c r="F81" t="n">
         <v>425766</v>
@@ -2052,16 +2052,16 @@
         <v>43333</v>
       </c>
       <c r="B82" t="n">
-        <v>71.60842895507812</v>
+        <v>71.60842132568359</v>
       </c>
       <c r="C82" t="n">
-        <v>72.5749210228105</v>
+        <v>72.57491329044277</v>
       </c>
       <c r="D82" t="n">
-        <v>70.31977038201907</v>
+        <v>70.31976288992242</v>
       </c>
       <c r="E82" t="n">
-        <v>71.63771546497189</v>
+        <v>71.63770783245707</v>
       </c>
       <c r="F82" t="n">
         <v>1384333</v>
@@ -2092,16 +2092,16 @@
         <v>43335</v>
       </c>
       <c r="B84" t="n">
-        <v>73.36568450927734</v>
+        <v>73.36569213867188</v>
       </c>
       <c r="C84" t="n">
-        <v>74.33217645157174</v>
+        <v>74.33218418147305</v>
       </c>
       <c r="D84" t="n">
-        <v>71.901299618666</v>
+        <v>71.90130709577721</v>
       </c>
       <c r="E84" t="n">
-        <v>72.57491160353946</v>
+        <v>72.57491915070047</v>
       </c>
       <c r="F84" t="n">
         <v>126566</v>
@@ -2112,16 +2112,16 @@
         <v>43336</v>
       </c>
       <c r="B85" t="n">
-        <v>75.29866790771484</v>
+        <v>75.29867553710938</v>
       </c>
       <c r="C85" t="n">
-        <v>75.5622613573412</v>
+        <v>75.56226901344348</v>
       </c>
       <c r="D85" t="n">
-        <v>73.21924405784095</v>
+        <v>73.21925147654457</v>
       </c>
       <c r="E85" t="n">
-        <v>74.09787647618438</v>
+        <v>74.0978839839126</v>
       </c>
       <c r="F85" t="n">
         <v>164200</v>
@@ -2132,16 +2132,16 @@
         <v>43339</v>
       </c>
       <c r="B86" t="n">
-        <v>76.03086853027344</v>
+        <v>76.03086090087891</v>
       </c>
       <c r="C86" t="n">
-        <v>76.44089455354266</v>
+        <v>76.44088688300364</v>
       </c>
       <c r="D86" t="n">
-        <v>73.65856446957658</v>
+        <v>73.6585570782333</v>
       </c>
       <c r="E86" t="n">
-        <v>75.29867601090092</v>
+        <v>75.29866845497898</v>
       </c>
       <c r="F86" t="n">
         <v>318500</v>
@@ -2152,16 +2152,16 @@
         <v>43340</v>
       </c>
       <c r="B87" t="n">
-        <v>75.24010467529297</v>
+        <v>75.24009704589844</v>
       </c>
       <c r="C87" t="n">
-        <v>76.14802371754747</v>
+        <v>76.14801599608937</v>
       </c>
       <c r="D87" t="n">
-        <v>73.89287309089012</v>
+        <v>73.89286559810573</v>
       </c>
       <c r="E87" t="n">
-        <v>75.91372419161821</v>
+        <v>75.91371649391823</v>
       </c>
       <c r="F87" t="n">
         <v>298400</v>
@@ -2172,16 +2172,16 @@
         <v>43341</v>
       </c>
       <c r="B88" t="n">
-        <v>74.42003631591797</v>
+        <v>74.4200439453125</v>
       </c>
       <c r="C88" t="n">
-        <v>76.14801466589296</v>
+        <v>76.14802247243639</v>
       </c>
       <c r="D88" t="n">
-        <v>73.45354436912919</v>
+        <v>73.45355189944088</v>
       </c>
       <c r="E88" t="n">
-        <v>75.67940822148965</v>
+        <v>75.6794159799925</v>
       </c>
       <c r="F88" t="n">
         <v>162200</v>
@@ -2192,16 +2192,16 @@
         <v>43342</v>
       </c>
       <c r="B89" t="n">
-        <v>75.85514831542969</v>
+        <v>75.85513305664062</v>
       </c>
       <c r="C89" t="n">
-        <v>75.85514831542969</v>
+        <v>75.85513305664062</v>
       </c>
       <c r="D89" t="n">
-        <v>73.39498452364062</v>
+        <v>73.39496975973056</v>
       </c>
       <c r="E89" t="n">
-        <v>74.18575012667137</v>
+        <v>74.18573520369333</v>
       </c>
       <c r="F89" t="n">
         <v>206466</v>
@@ -2212,16 +2212,16 @@
         <v>43343</v>
       </c>
       <c r="B90" t="n">
-        <v>75.82585906982422</v>
+        <v>75.82585144042969</v>
       </c>
       <c r="C90" t="n">
-        <v>76.49947860263404</v>
+        <v>76.49947090546172</v>
       </c>
       <c r="D90" t="n">
-        <v>74.91794000535143</v>
+        <v>74.91793246730929</v>
       </c>
       <c r="E90" t="n">
-        <v>76.11873907058879</v>
+        <v>76.11873141172546</v>
       </c>
       <c r="F90" t="n">
         <v>295200</v>
@@ -2272,16 +2272,16 @@
         <v>43348</v>
       </c>
       <c r="B93" t="n">
-        <v>73.24854278564453</v>
+        <v>73.24853515625</v>
       </c>
       <c r="C93" t="n">
-        <v>75.65013349767</v>
+        <v>75.65012561813148</v>
       </c>
       <c r="D93" t="n">
-        <v>72.80923022729456</v>
+        <v>72.80922264365779</v>
       </c>
       <c r="E93" t="n">
-        <v>72.89708975966539</v>
+        <v>72.89708216687738</v>
       </c>
       <c r="F93" t="n">
         <v>95400</v>
@@ -2292,16 +2292,16 @@
         <v>43349</v>
       </c>
       <c r="B94" t="n">
-        <v>74.21501922607422</v>
+        <v>74.21502685546875</v>
       </c>
       <c r="C94" t="n">
-        <v>76.52874991760901</v>
+        <v>76.52875778485787</v>
       </c>
       <c r="D94" t="n">
-        <v>71.46197606886972</v>
+        <v>71.46198341524806</v>
       </c>
       <c r="E94" t="n">
-        <v>74.15644621685061</v>
+        <v>74.15645384022376</v>
       </c>
       <c r="F94" t="n">
         <v>139100</v>
@@ -2332,16 +2332,16 @@
         <v>43354</v>
       </c>
       <c r="B96" t="n">
-        <v>73.45355224609375</v>
+        <v>73.45353698730469</v>
       </c>
       <c r="C96" t="n">
-        <v>75.18153078137257</v>
+        <v>75.18151516362389</v>
       </c>
       <c r="D96" t="n">
-        <v>73.45355224609375</v>
+        <v>73.45353698730469</v>
       </c>
       <c r="E96" t="n">
-        <v>74.44933825414368</v>
+        <v>74.44932278849616</v>
       </c>
       <c r="F96" t="n">
         <v>250666</v>
@@ -2352,16 +2352,16 @@
         <v>43355</v>
       </c>
       <c r="B97" t="n">
-        <v>72.95565032958984</v>
+        <v>72.95566558837891</v>
       </c>
       <c r="C97" t="n">
-        <v>74.65434214798188</v>
+        <v>74.65435776205501</v>
       </c>
       <c r="D97" t="n">
-        <v>71.34483292506654</v>
+        <v>71.34484784695061</v>
       </c>
       <c r="E97" t="n">
-        <v>73.21924377820952</v>
+        <v>73.21925909212956</v>
       </c>
       <c r="F97" t="n">
         <v>133333</v>
@@ -2372,16 +2372,16 @@
         <v>43356</v>
       </c>
       <c r="B98" t="n">
-        <v>71.60842895507812</v>
+        <v>71.60842132568359</v>
       </c>
       <c r="C98" t="n">
-        <v>73.86357959586955</v>
+        <v>73.86357172620396</v>
       </c>
       <c r="D98" t="n">
-        <v>70.43692386984178</v>
+        <v>70.4369163652632</v>
       </c>
       <c r="E98" t="n">
-        <v>73.77572006618828</v>
+        <v>73.77571220588352</v>
       </c>
       <c r="F98" t="n">
         <v>250366</v>
@@ -2392,16 +2392,16 @@
         <v>43357</v>
       </c>
       <c r="B99" t="n">
-        <v>69.79257202148438</v>
+        <v>69.79258728027344</v>
       </c>
       <c r="C99" t="n">
-        <v>72.28202896599223</v>
+        <v>72.28204476905265</v>
       </c>
       <c r="D99" t="n">
-        <v>69.70471251551726</v>
+        <v>69.70472775509755</v>
       </c>
       <c r="E99" t="n">
-        <v>70.96408423876569</v>
+        <v>70.96409975368313</v>
       </c>
       <c r="F99" t="n">
         <v>269466</v>
@@ -2412,16 +2412,16 @@
         <v>43360</v>
       </c>
       <c r="B100" t="n">
-        <v>73.48282623291016</v>
+        <v>73.48284149169922</v>
       </c>
       <c r="C100" t="n">
-        <v>74.06858611346924</v>
+        <v>74.06860149389196</v>
       </c>
       <c r="D100" t="n">
-        <v>69.79257771626868</v>
+        <v>69.79259220877361</v>
       </c>
       <c r="E100" t="n">
-        <v>70.02687719954454</v>
+        <v>70.02689174070201</v>
       </c>
       <c r="F100" t="n">
         <v>114333</v>
@@ -2432,16 +2432,16 @@
         <v>43361</v>
       </c>
       <c r="B101" t="n">
-        <v>74.50789642333984</v>
+        <v>74.50790405273438</v>
       </c>
       <c r="C101" t="n">
-        <v>75.35724226701849</v>
+        <v>75.35724998338361</v>
       </c>
       <c r="D101" t="n">
-        <v>73.62926407612848</v>
+        <v>73.62927161555359</v>
       </c>
       <c r="E101" t="n">
-        <v>74.56646943040525</v>
+        <v>74.56647706579749</v>
       </c>
       <c r="F101" t="n">
         <v>194766</v>
@@ -2452,16 +2452,16 @@
         <v>43362</v>
       </c>
       <c r="B102" t="n">
-        <v>68.76753234863281</v>
+        <v>68.76752471923828</v>
       </c>
       <c r="C102" t="n">
-        <v>74.6836462569178</v>
+        <v>74.68363797116167</v>
       </c>
       <c r="D102" t="n">
-        <v>68.76753234863281</v>
+        <v>68.76752471923828</v>
       </c>
       <c r="E102" t="n">
-        <v>73.57071408502752</v>
+        <v>73.57070592274535</v>
       </c>
       <c r="F102" t="n">
         <v>510266</v>
@@ -2472,16 +2472,16 @@
         <v>43363</v>
       </c>
       <c r="B103" t="n">
-        <v>68.24033355712891</v>
+        <v>68.24034118652344</v>
       </c>
       <c r="C103" t="n">
-        <v>69.58756489941005</v>
+        <v>69.58757267942752</v>
       </c>
       <c r="D103" t="n">
-        <v>65.63372293766099</v>
+        <v>65.63373027563168</v>
       </c>
       <c r="E103" t="n">
-        <v>69.4118384244824</v>
+        <v>69.41184618485332</v>
       </c>
       <c r="F103" t="n">
         <v>1256966</v>
@@ -2492,16 +2492,16 @@
         <v>43364</v>
       </c>
       <c r="B104" t="n">
-        <v>69.35327911376953</v>
+        <v>69.353271484375</v>
       </c>
       <c r="C104" t="n">
-        <v>71.16911723059167</v>
+        <v>71.16910940144096</v>
       </c>
       <c r="D104" t="n">
-        <v>67.88889401621928</v>
+        <v>67.88888654791837</v>
       </c>
       <c r="E104" t="n">
-        <v>67.94746703668201</v>
+        <v>67.94745956193762</v>
       </c>
       <c r="F104" t="n">
         <v>293166</v>
@@ -2552,16 +2552,16 @@
         <v>43369</v>
       </c>
       <c r="B107" t="n">
-        <v>65.01869964599609</v>
+        <v>65.01868438720703</v>
       </c>
       <c r="C107" t="n">
-        <v>66.48308480670883</v>
+        <v>66.48306920425335</v>
       </c>
       <c r="D107" t="n">
-        <v>63.14428842786333</v>
+        <v>63.14427360896688</v>
       </c>
       <c r="E107" t="n">
-        <v>63.93505403120882</v>
+        <v>63.93503902673306</v>
       </c>
       <c r="F107" t="n">
         <v>469400</v>
@@ -2572,16 +2572,16 @@
         <v>43370</v>
       </c>
       <c r="B108" t="n">
-        <v>68.591796875</v>
+        <v>68.59178924560547</v>
       </c>
       <c r="C108" t="n">
-        <v>69.85116144605384</v>
+        <v>69.85115367658149</v>
       </c>
       <c r="D108" t="n">
-        <v>65.07726684520698</v>
+        <v>65.07725960672998</v>
       </c>
       <c r="E108" t="n">
-        <v>65.48730031418111</v>
+        <v>65.48729303009652</v>
       </c>
       <c r="F108" t="n">
         <v>605400</v>
@@ -2592,16 +2592,16 @@
         <v>43371</v>
       </c>
       <c r="B109" t="n">
-        <v>70.29048919677734</v>
+        <v>70.29047393798828</v>
       </c>
       <c r="C109" t="n">
-        <v>71.34484832230859</v>
+        <v>71.3448328346373</v>
       </c>
       <c r="D109" t="n">
-        <v>67.33243230146601</v>
+        <v>67.3324176848174</v>
       </c>
       <c r="E109" t="n">
-        <v>68.5918044600314</v>
+        <v>68.59178956999595</v>
       </c>
       <c r="F109" t="n">
         <v>612400</v>
@@ -2612,16 +2612,16 @@
         <v>43374</v>
       </c>
       <c r="B110" t="n">
-        <v>69.11895751953125</v>
+        <v>69.11896514892578</v>
       </c>
       <c r="C110" t="n">
-        <v>70.20260285843067</v>
+        <v>70.20261060743866</v>
       </c>
       <c r="D110" t="n">
-        <v>68.41605907787013</v>
+        <v>68.41606662967828</v>
       </c>
       <c r="E110" t="n">
-        <v>70.20260285843067</v>
+        <v>70.20261060743866</v>
       </c>
       <c r="F110" t="n">
         <v>385466</v>
@@ -2632,16 +2632,16 @@
         <v>43375</v>
       </c>
       <c r="B111" t="n">
-        <v>69.14825439453125</v>
+        <v>69.14826202392578</v>
       </c>
       <c r="C111" t="n">
-        <v>70.2611862845098</v>
+        <v>70.26119403669841</v>
       </c>
       <c r="D111" t="n">
-        <v>67.97674204575357</v>
+        <v>67.97674954589061</v>
       </c>
       <c r="E111" t="n">
-        <v>69.20682740508386</v>
+        <v>69.20683504094097</v>
       </c>
       <c r="F111" t="n">
         <v>391400</v>
@@ -2672,16 +2672,16 @@
         <v>43377</v>
       </c>
       <c r="B113" t="n">
-        <v>70.29048919677734</v>
+        <v>70.29047393798828</v>
       </c>
       <c r="C113" t="n">
-        <v>72.1356139423329</v>
+        <v>72.13559828300075</v>
       </c>
       <c r="D113" t="n">
-        <v>67.71317185542203</v>
+        <v>67.71315715612178</v>
       </c>
       <c r="E113" t="n">
-        <v>70.55407525403604</v>
+        <v>70.55405993802722</v>
       </c>
       <c r="F113" t="n">
         <v>201700</v>
@@ -2712,16 +2712,16 @@
         <v>43381</v>
       </c>
       <c r="B115" t="n">
-        <v>69.55828857421875</v>
+        <v>69.55829620361328</v>
       </c>
       <c r="C115" t="n">
-        <v>70.90552011365561</v>
+        <v>70.90552789081917</v>
       </c>
       <c r="D115" t="n">
-        <v>68.8553825716439</v>
+        <v>68.85539012394126</v>
       </c>
       <c r="E115" t="n">
-        <v>68.8553825716439</v>
+        <v>68.85539012394126</v>
       </c>
       <c r="F115" t="n">
         <v>697200</v>
@@ -2752,16 +2752,16 @@
         <v>43383</v>
       </c>
       <c r="B117" t="n">
-        <v>69.14825439453125</v>
+        <v>69.14826202392578</v>
       </c>
       <c r="C117" t="n">
-        <v>71.72557113429701</v>
+        <v>71.72557904805687</v>
       </c>
       <c r="D117" t="n">
-        <v>67.24454962085997</v>
+        <v>67.24455704021138</v>
       </c>
       <c r="E117" t="n">
-        <v>67.36170309021169</v>
+        <v>67.3617105224891</v>
       </c>
       <c r="F117" t="n">
         <v>149833</v>
@@ -2772,16 +2772,16 @@
         <v>43384</v>
       </c>
       <c r="B118" t="n">
-        <v>70.87623596191406</v>
+        <v>70.87622833251953</v>
       </c>
       <c r="C118" t="n">
-        <v>71.63771500727735</v>
+        <v>71.63770729591425</v>
       </c>
       <c r="D118" t="n">
-        <v>68.62108533553082</v>
+        <v>68.62107794888951</v>
       </c>
       <c r="E118" t="n">
-        <v>69.08968438733241</v>
+        <v>69.08967695024926</v>
       </c>
       <c r="F118" t="n">
         <v>258833</v>
@@ -2792,16 +2792,16 @@
         <v>43388</v>
       </c>
       <c r="B119" t="n">
-        <v>72.04775238037109</v>
+        <v>72.04774475097656</v>
       </c>
       <c r="C119" t="n">
-        <v>72.89709853679362</v>
+        <v>72.89709081745879</v>
       </c>
       <c r="D119" t="n">
-        <v>66.7759712524345</v>
+        <v>66.77596418128775</v>
       </c>
       <c r="E119" t="n">
-        <v>71.57915325480948</v>
+        <v>71.57914567503659</v>
       </c>
       <c r="F119" t="n">
         <v>520433</v>
@@ -2812,16 +2812,16 @@
         <v>43389</v>
       </c>
       <c r="B120" t="n">
-        <v>73.83428955078125</v>
+        <v>73.83429718017578</v>
       </c>
       <c r="C120" t="n">
-        <v>75.85514056741636</v>
+        <v>75.85514840562809</v>
       </c>
       <c r="D120" t="n">
-        <v>71.34483950178725</v>
+        <v>71.34484687394362</v>
       </c>
       <c r="E120" t="n">
-        <v>71.98916503334256</v>
+        <v>71.98917247207794</v>
       </c>
       <c r="F120" t="n">
         <v>484533</v>
@@ -2832,16 +2832,16 @@
         <v>43390</v>
       </c>
       <c r="B121" t="n">
-        <v>74.91793823242188</v>
+        <v>74.91792297363281</v>
       </c>
       <c r="C121" t="n">
-        <v>75.88443029487647</v>
+        <v>75.8844148392387</v>
       </c>
       <c r="D121" t="n">
-        <v>73.27782665309864</v>
+        <v>73.27781172835662</v>
       </c>
       <c r="E121" t="n">
-        <v>73.27782665309864</v>
+        <v>73.27781172835662</v>
       </c>
       <c r="F121" t="n">
         <v>520600</v>
@@ -2852,16 +2852,16 @@
         <v>43391</v>
       </c>
       <c r="B122" t="n">
-        <v>75.56227874755859</v>
+        <v>75.56227111816406</v>
       </c>
       <c r="C122" t="n">
-        <v>76.79235696808804</v>
+        <v>76.79234921449461</v>
       </c>
       <c r="D122" t="n">
-        <v>74.88865916375791</v>
+        <v>74.88865160237759</v>
       </c>
       <c r="E122" t="n">
-        <v>74.9179456764017</v>
+        <v>74.91793811206438</v>
       </c>
       <c r="F122" t="n">
         <v>252733</v>
@@ -2872,16 +2872,16 @@
         <v>43392</v>
       </c>
       <c r="B123" t="n">
-        <v>73.95145416259766</v>
+        <v>73.95143890380859</v>
       </c>
       <c r="C123" t="n">
-        <v>76.41161807335179</v>
+        <v>76.41160230694427</v>
       </c>
       <c r="D123" t="n">
-        <v>72.75065499599548</v>
+        <v>72.75063998497356</v>
       </c>
       <c r="E123" t="n">
-        <v>75.62085243208233</v>
+        <v>75.62083682883761</v>
       </c>
       <c r="F123" t="n">
         <v>198200</v>
@@ -2912,16 +2912,16 @@
         <v>43396</v>
       </c>
       <c r="B125" t="n">
-        <v>75.44511413574219</v>
+        <v>75.44509887695312</v>
       </c>
       <c r="C125" t="n">
-        <v>76.14802012864928</v>
+        <v>76.14800472769734</v>
       </c>
       <c r="D125" t="n">
-        <v>74.15645563149494</v>
+        <v>74.15644063333731</v>
       </c>
       <c r="E125" t="n">
-        <v>74.80078860774221</v>
+        <v>74.8007734792681</v>
       </c>
       <c r="F125" t="n">
         <v>244366</v>
@@ -2932,16 +2932,16 @@
         <v>43397</v>
       </c>
       <c r="B126" t="n">
-        <v>74.3907470703125</v>
+        <v>74.39075469970703</v>
       </c>
       <c r="C126" t="n">
-        <v>75.26937946605956</v>
+        <v>75.26938718556521</v>
       </c>
       <c r="D126" t="n">
-        <v>74.24430709631358</v>
+        <v>74.24431471068945</v>
       </c>
       <c r="E126" t="n">
-        <v>75.26937946605956</v>
+        <v>75.26938718556521</v>
       </c>
       <c r="F126" t="n">
         <v>414300</v>
@@ -2952,16 +2952,16 @@
         <v>43398</v>
       </c>
       <c r="B127" t="n">
-        <v>76.0015869140625</v>
+        <v>76.00157165527344</v>
       </c>
       <c r="C127" t="n">
-        <v>76.0015869140625</v>
+        <v>76.00157165527344</v>
       </c>
       <c r="D127" t="n">
-        <v>73.10210315896421</v>
+        <v>73.10208848230262</v>
       </c>
       <c r="E127" t="n">
-        <v>74.56648829198372</v>
+        <v>74.56647332131847</v>
       </c>
       <c r="F127" t="n">
         <v>495966</v>
@@ -3012,16 +3012,16 @@
         <v>43403</v>
       </c>
       <c r="B130" t="n">
-        <v>74.56647491455078</v>
+        <v>74.56648254394531</v>
       </c>
       <c r="C130" t="n">
-        <v>76.14801325584872</v>
+        <v>76.14802104706102</v>
       </c>
       <c r="D130" t="n">
-        <v>73.65855599703195</v>
+        <v>73.65856353353124</v>
       </c>
       <c r="E130" t="n">
-        <v>75.65012031443605</v>
+        <v>75.65012805470559</v>
       </c>
       <c r="F130" t="n">
         <v>1306966</v>
@@ -3032,16 +3032,16 @@
         <v>43404</v>
       </c>
       <c r="B131" t="n">
-        <v>74.62506103515625</v>
+        <v>74.62507629394531</v>
       </c>
       <c r="C131" t="n">
-        <v>76.61661805539134</v>
+        <v>76.61663372139948</v>
       </c>
       <c r="D131" t="n">
-        <v>73.86357458830497</v>
+        <v>73.86358969139083</v>
       </c>
       <c r="E131" t="n">
-        <v>75.67941256109036</v>
+        <v>75.67942803546555</v>
       </c>
       <c r="F131" t="n">
         <v>863500</v>
@@ -3052,16 +3052,16 @@
         <v>43405</v>
       </c>
       <c r="B132" t="n">
-        <v>75.35723114013672</v>
+        <v>75.35726928710938</v>
       </c>
       <c r="C132" t="n">
-        <v>78.08097984194735</v>
+        <v>78.08101936772289</v>
       </c>
       <c r="D132" t="n">
-        <v>74.1564325348776</v>
+        <v>74.15647007398779</v>
       </c>
       <c r="E132" t="n">
-        <v>75.65010358046567</v>
+        <v>75.6501418756948</v>
       </c>
       <c r="F132" t="n">
         <v>289433</v>
@@ -3152,16 +3152,16 @@
         <v>43413</v>
       </c>
       <c r="B137" t="n">
-        <v>76.73377990722656</v>
+        <v>76.7337646484375</v>
       </c>
       <c r="C137" t="n">
-        <v>79.07679762273497</v>
+        <v>79.07678189802839</v>
       </c>
       <c r="D137" t="n">
-        <v>75.21082174385769</v>
+        <v>75.21080678791435</v>
       </c>
       <c r="E137" t="n">
-        <v>77.31953247404167</v>
+        <v>77.31951709877359</v>
       </c>
       <c r="F137" t="n">
         <v>423466</v>
@@ -3172,16 +3172,16 @@
         <v>43416</v>
       </c>
       <c r="B138" t="n">
-        <v>76.79235076904297</v>
+        <v>76.79234313964844</v>
       </c>
       <c r="C138" t="n">
-        <v>77.78813680803749</v>
+        <v>77.78812907971066</v>
       </c>
       <c r="D138" t="n">
-        <v>75.79657217829622</v>
+        <v>75.79656464783326</v>
       </c>
       <c r="E138" t="n">
-        <v>77.02665774777567</v>
+        <v>77.02665009510251</v>
       </c>
       <c r="F138" t="n">
         <v>143933</v>
@@ -3192,16 +3192,16 @@
         <v>43417</v>
       </c>
       <c r="B139" t="n">
-        <v>75.26937866210938</v>
+        <v>75.26938629150391</v>
       </c>
       <c r="C139" t="n">
-        <v>77.84669536327486</v>
+        <v>77.84670325390931</v>
       </c>
       <c r="D139" t="n">
-        <v>74.91792570756441</v>
+        <v>74.91793330133525</v>
       </c>
       <c r="E139" t="n">
-        <v>77.26094292178205</v>
+        <v>77.26095075304393</v>
       </c>
       <c r="F139" t="n">
         <v>637900</v>
@@ -3232,16 +3232,16 @@
         <v>43420</v>
       </c>
       <c r="B141" t="n">
-        <v>81.09764862060547</v>
+        <v>81.09764099121094</v>
       </c>
       <c r="C141" t="n">
-        <v>83.46995284139612</v>
+        <v>83.46994498882317</v>
       </c>
       <c r="D141" t="n">
-        <v>78.8132039329099</v>
+        <v>78.81319651842826</v>
       </c>
       <c r="E141" t="n">
-        <v>78.8132039329099</v>
+        <v>78.81319651842826</v>
       </c>
       <c r="F141" t="n">
         <v>652300</v>
@@ -3252,16 +3252,16 @@
         <v>43423</v>
       </c>
       <c r="B142" t="n">
-        <v>80.24829864501953</v>
+        <v>80.248291015625</v>
       </c>
       <c r="C142" t="n">
-        <v>81.53695720529036</v>
+        <v>81.53694945338003</v>
       </c>
       <c r="D142" t="n">
-        <v>79.77969959487429</v>
+        <v>79.77969201003057</v>
       </c>
       <c r="E142" t="n">
-        <v>80.65833212420613</v>
+        <v>80.65832445582875</v>
       </c>
       <c r="F142" t="n">
         <v>158533</v>
@@ -3272,16 +3272,16 @@
         <v>43425</v>
       </c>
       <c r="B143" t="n">
-        <v>79.80898284912109</v>
+        <v>79.80899047851562</v>
       </c>
       <c r="C143" t="n">
-        <v>81.59553434451564</v>
+        <v>81.59554214469678</v>
       </c>
       <c r="D143" t="n">
-        <v>78.13958483560805</v>
+        <v>78.13959230541533</v>
       </c>
       <c r="E143" t="n">
-        <v>79.04750383750959</v>
+        <v>79.04751139411002</v>
       </c>
       <c r="F143" t="n">
         <v>918800</v>
@@ -3312,16 +3312,16 @@
         <v>43427</v>
       </c>
       <c r="B145" t="n">
-        <v>79.51609802246094</v>
+        <v>79.51610565185547</v>
       </c>
       <c r="C145" t="n">
-        <v>79.51609802246094</v>
+        <v>79.51610565185547</v>
       </c>
       <c r="D145" t="n">
-        <v>77.31952064672171</v>
+        <v>77.31952806535949</v>
       </c>
       <c r="E145" t="n">
-        <v>78.63746558251587</v>
+        <v>78.63747312760756</v>
       </c>
       <c r="F145" t="n">
         <v>372100</v>
@@ -3332,16 +3332,16 @@
         <v>43430</v>
       </c>
       <c r="B146" t="n">
-        <v>78.75462341308594</v>
+        <v>78.75461578369141</v>
       </c>
       <c r="C146" t="n">
-        <v>80.33616189246013</v>
+        <v>80.33615410985325</v>
       </c>
       <c r="D146" t="n">
-        <v>76.23587942868353</v>
+        <v>76.23587204329363</v>
       </c>
       <c r="E146" t="n">
-        <v>80.27758142772588</v>
+        <v>80.27757365079401</v>
       </c>
       <c r="F146" t="n">
         <v>252366</v>
@@ -3352,16 +3352,16 @@
         <v>43431</v>
       </c>
       <c r="B147" t="n">
-        <v>81.59552764892578</v>
+        <v>81.59553527832031</v>
       </c>
       <c r="C147" t="n">
-        <v>82.59130609434109</v>
+        <v>82.5913138168435</v>
       </c>
       <c r="D147" t="n">
-        <v>76.32374056880897</v>
+        <v>76.32374770527765</v>
       </c>
       <c r="E147" t="n">
-        <v>78.28601840188094</v>
+        <v>78.28602572182773</v>
       </c>
       <c r="F147" t="n">
         <v>436400</v>
@@ -3372,16 +3372,16 @@
         <v>43432</v>
       </c>
       <c r="B148" t="n">
-        <v>84.52429962158203</v>
+        <v>84.5242919921875</v>
       </c>
       <c r="C148" t="n">
-        <v>86.22298404832937</v>
+        <v>86.22297626560693</v>
       </c>
       <c r="D148" t="n">
-        <v>80.54117083974624</v>
+        <v>80.54116356987981</v>
       </c>
       <c r="E148" t="n">
-        <v>81.18549633337582</v>
+        <v>81.18548900535082</v>
       </c>
       <c r="F148" t="n">
         <v>429500</v>
@@ -3392,16 +3392,16 @@
         <v>43433</v>
       </c>
       <c r="B149" t="n">
-        <v>84.1728515625</v>
+        <v>84.17284393310547</v>
       </c>
       <c r="C149" t="n">
-        <v>85.69580958938813</v>
+        <v>85.69580182195328</v>
       </c>
       <c r="D149" t="n">
-        <v>83.2942190668925</v>
+        <v>83.29421151713687</v>
       </c>
       <c r="E149" t="n">
-        <v>84.31929155314248</v>
+        <v>84.31928391047468</v>
       </c>
       <c r="F149" t="n">
         <v>232033</v>
@@ -3412,16 +3412,16 @@
         <v>43434</v>
       </c>
       <c r="B150" t="n">
-        <v>82.91348266601562</v>
+        <v>82.91347503662109</v>
       </c>
       <c r="C150" t="n">
-        <v>84.26071424424802</v>
+        <v>84.26070649088619</v>
       </c>
       <c r="D150" t="n">
-        <v>82.32773012975143</v>
+        <v>82.32772255425571</v>
       </c>
       <c r="E150" t="n">
-        <v>84.23142773467195</v>
+        <v>84.23141998400496</v>
       </c>
       <c r="F150" t="n">
         <v>464600</v>
@@ -3452,16 +3452,16 @@
         <v>43438</v>
       </c>
       <c r="B152" t="n">
-        <v>83.82140350341797</v>
+        <v>83.82139587402344</v>
       </c>
       <c r="C152" t="n">
-        <v>86.60373369658394</v>
+        <v>86.60372581394269</v>
       </c>
       <c r="D152" t="n">
-        <v>82.5913179370849</v>
+        <v>82.59131041965232</v>
       </c>
       <c r="E152" t="n">
-        <v>84.64145558214152</v>
+        <v>84.64144787810613</v>
       </c>
       <c r="F152" t="n">
         <v>207933</v>
@@ -3472,16 +3472,16 @@
         <v>43439</v>
       </c>
       <c r="B153" t="n">
-        <v>86.10582733154297</v>
+        <v>86.10584259033203</v>
       </c>
       <c r="C153" t="n">
-        <v>86.39870728468802</v>
+        <v>86.39872259537825</v>
       </c>
       <c r="D153" t="n">
-        <v>83.1184845817486</v>
+        <v>83.11849931115151</v>
       </c>
       <c r="E153" t="n">
-        <v>83.82139051069942</v>
+        <v>83.82140536466409</v>
       </c>
       <c r="F153" t="n">
         <v>198233</v>
@@ -3492,16 +3492,16 @@
         <v>43440</v>
       </c>
       <c r="B154" t="n">
-        <v>84.93433380126953</v>
+        <v>84.934326171875</v>
       </c>
       <c r="C154" t="n">
-        <v>85.46151331865333</v>
+        <v>85.46150564190386</v>
       </c>
       <c r="D154" t="n">
-        <v>83.87997476650193</v>
+        <v>83.87996723181728</v>
       </c>
       <c r="E154" t="n">
-        <v>85.25650030326756</v>
+        <v>85.25649264493379</v>
       </c>
       <c r="F154" t="n">
         <v>270866</v>
@@ -3532,16 +3532,16 @@
         <v>43444</v>
       </c>
       <c r="B156" t="n">
-        <v>83.46994018554688</v>
+        <v>83.46994781494141</v>
       </c>
       <c r="C156" t="n">
-        <v>84.70002560010616</v>
+        <v>84.70003334193406</v>
       </c>
       <c r="D156" t="n">
-        <v>83.05991419677606</v>
+        <v>83.05992178869303</v>
       </c>
       <c r="E156" t="n">
-        <v>84.31928611792657</v>
+        <v>84.31929382495377</v>
       </c>
       <c r="F156" t="n">
         <v>313733</v>
@@ -3592,16 +3592,16 @@
         <v>43447</v>
       </c>
       <c r="B159" t="n">
-        <v>86.77944946289062</v>
+        <v>86.77945709228516</v>
       </c>
       <c r="C159" t="n">
-        <v>88.77101384098502</v>
+        <v>88.77102164547205</v>
       </c>
       <c r="D159" t="n">
-        <v>84.99289807909682</v>
+        <v>84.99290555142299</v>
       </c>
       <c r="E159" t="n">
-        <v>85.78367099796685</v>
+        <v>85.78367853981547</v>
       </c>
       <c r="F159" t="n">
         <v>486800</v>
@@ -3632,16 +3632,16 @@
         <v>43451</v>
       </c>
       <c r="B161" t="n">
-        <v>84.9378662109375</v>
+        <v>84.93785858154297</v>
       </c>
       <c r="C161" t="n">
-        <v>86.47039992970112</v>
+        <v>86.47039216264943</v>
       </c>
       <c r="D161" t="n">
-        <v>84.28948194833528</v>
+        <v>84.28947437718072</v>
       </c>
       <c r="E161" t="n">
-        <v>86.44092928050621</v>
+        <v>86.44092151610168</v>
       </c>
       <c r="F161" t="n">
         <v>205700</v>
@@ -3672,16 +3672,16 @@
         <v>43453</v>
       </c>
       <c r="B163" t="n">
-        <v>89.68283843994141</v>
+        <v>89.68282318115234</v>
       </c>
       <c r="C163" t="n">
-        <v>90.56699541914645</v>
+        <v>90.56698000992543</v>
       </c>
       <c r="D163" t="n">
-        <v>86.29357126883521</v>
+        <v>86.29355658670175</v>
       </c>
       <c r="E163" t="n">
-        <v>86.52935146000912</v>
+        <v>86.52933673775965</v>
       </c>
       <c r="F163" t="n">
         <v>384866</v>
@@ -3692,16 +3692,16 @@
         <v>43454</v>
       </c>
       <c r="B164" t="n">
-        <v>89.00496673583984</v>
+        <v>89.00497436523438</v>
       </c>
       <c r="C164" t="n">
-        <v>93.07208057875353</v>
+        <v>93.07208855677598</v>
       </c>
       <c r="D164" t="n">
-        <v>87.20718246605232</v>
+        <v>87.20718994134303</v>
       </c>
       <c r="E164" t="n">
-        <v>89.2702175271606</v>
+        <v>89.27022517929211</v>
       </c>
       <c r="F164" t="n">
         <v>975500</v>
@@ -3712,16 +3712,16 @@
         <v>43455</v>
       </c>
       <c r="B165" t="n">
-        <v>88.00293731689453</v>
+        <v>88.0029296875</v>
       </c>
       <c r="C165" t="n">
-        <v>90.18384770834878</v>
+        <v>90.18383988988073</v>
       </c>
       <c r="D165" t="n">
-        <v>86.08726275666103</v>
+        <v>86.08725529334548</v>
       </c>
       <c r="E165" t="n">
-        <v>90.18384770834878</v>
+        <v>90.18383988988073</v>
       </c>
       <c r="F165" t="n">
         <v>2053700</v>
@@ -3732,16 +3732,16 @@
         <v>43460</v>
       </c>
       <c r="B166" t="n">
-        <v>90.59646606445312</v>
+        <v>90.59645080566406</v>
       </c>
       <c r="C166" t="n">
-        <v>92.68896466922801</v>
+        <v>92.68894905800803</v>
       </c>
       <c r="D166" t="n">
-        <v>86.38199070969904</v>
+        <v>86.38197616073666</v>
       </c>
       <c r="E166" t="n">
-        <v>87.88505382672821</v>
+        <v>87.88503902461112</v>
       </c>
       <c r="F166" t="n">
         <v>396300</v>
@@ -3772,16 +3772,16 @@
         <v>43462</v>
       </c>
       <c r="B168" t="n">
-        <v>91.9521484375</v>
+        <v>91.95215606689453</v>
       </c>
       <c r="C168" t="n">
-        <v>92.09950915115729</v>
+        <v>92.09951679277854</v>
       </c>
       <c r="D168" t="n">
-        <v>89.97753286267756</v>
+        <v>89.97754032823556</v>
       </c>
       <c r="E168" t="n">
-        <v>91.33324243423203</v>
+        <v>91.33325001227509</v>
       </c>
       <c r="F168" t="n">
         <v>582800</v>
@@ -3812,16 +3812,16 @@
         <v>43468</v>
       </c>
       <c r="B170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56492614746094</v>
       </c>
       <c r="C170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.5395416624697</v>
       </c>
       <c r="D170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56492614746094</v>
       </c>
       <c r="E170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.5395416624697</v>
       </c>
       <c r="F170" t="n">
         <v>308333</v>
@@ -3852,16 +3852,16 @@
         <v>43472</v>
       </c>
       <c r="B172" t="n">
-        <v>91.24481964111328</v>
+        <v>91.24482727050781</v>
       </c>
       <c r="C172" t="n">
-        <v>91.65742362806702</v>
+        <v>91.65743129196125</v>
       </c>
       <c r="D172" t="n">
-        <v>89.88911761466086</v>
+        <v>89.88912513069897</v>
       </c>
       <c r="E172" t="n">
-        <v>89.88911761466086</v>
+        <v>89.88912513069897</v>
       </c>
       <c r="F172" t="n">
         <v>470133</v>
@@ -3932,16 +3932,16 @@
         <v>43476</v>
       </c>
       <c r="B176" t="n">
-        <v>92.36476135253906</v>
+        <v>92.36475372314453</v>
       </c>
       <c r="C176" t="n">
-        <v>93.04261620372681</v>
+        <v>93.04260851834098</v>
       </c>
       <c r="D176" t="n">
-        <v>90.86169841736448</v>
+        <v>90.861690912124</v>
       </c>
       <c r="E176" t="n">
-        <v>92.39423199909888</v>
+        <v>92.39422436727006</v>
       </c>
       <c r="F176" t="n">
         <v>283133</v>
@@ -4012,16 +4012,16 @@
         <v>43482</v>
       </c>
       <c r="B180" t="n">
-        <v>99.26117706298828</v>
+        <v>99.26116180419922</v>
       </c>
       <c r="C180" t="n">
-        <v>100.0274438507868</v>
+        <v>100.0274284742044</v>
       </c>
       <c r="D180" t="n">
-        <v>97.90546736604202</v>
+        <v>97.90545231565758</v>
       </c>
       <c r="E180" t="n">
-        <v>98.78962423468569</v>
+        <v>98.78960904838544</v>
       </c>
       <c r="F180" t="n">
         <v>313600</v>
@@ -4052,16 +4052,16 @@
         <v>43486</v>
       </c>
       <c r="B182" t="n">
-        <v>101.3831558227539</v>
+        <v>101.3831405639648</v>
       </c>
       <c r="C182" t="n">
-        <v>102.3557322195262</v>
+        <v>102.3557168143584</v>
       </c>
       <c r="D182" t="n">
-        <v>98.22966893326101</v>
+        <v>98.22965414909113</v>
       </c>
       <c r="E182" t="n">
-        <v>100.7937203518813</v>
+        <v>100.793705181806</v>
       </c>
       <c r="F182" t="n">
         <v>260300</v>
@@ -4092,16 +4092,16 @@
         <v>43488</v>
       </c>
       <c r="B184" t="n">
-        <v>99.23170471191406</v>
+        <v>99.23171234130859</v>
       </c>
       <c r="C184" t="n">
-        <v>101.0589597106958</v>
+        <v>101.0589674805782</v>
       </c>
       <c r="D184" t="n">
-        <v>98.17071648776765</v>
+        <v>98.17072403558848</v>
       </c>
       <c r="E184" t="n">
-        <v>99.5853674532962</v>
+        <v>99.58537510988198</v>
       </c>
       <c r="F184" t="n">
         <v>240366</v>
@@ -4112,16 +4112,16 @@
         <v>43489</v>
       </c>
       <c r="B185" t="n">
-        <v>98.22966766357422</v>
+        <v>98.22965240478516</v>
       </c>
       <c r="C185" t="n">
-        <v>100.9705504375364</v>
+        <v>100.9705347529844</v>
       </c>
       <c r="D185" t="n">
-        <v>97.05079673706683</v>
+        <v>97.05078166140109</v>
       </c>
       <c r="E185" t="n">
-        <v>99.23171469667619</v>
+        <v>99.23169928223126</v>
       </c>
       <c r="F185" t="n">
         <v>372266</v>
@@ -4132,16 +4132,16 @@
         <v>43493</v>
       </c>
       <c r="B186" t="n">
-        <v>97.25708770751953</v>
+        <v>97.257080078125</v>
       </c>
       <c r="C186" t="n">
-        <v>98.05282511761074</v>
+        <v>98.05281742579406</v>
       </c>
       <c r="D186" t="n">
-        <v>95.96032683788904</v>
+        <v>95.96031931021975</v>
       </c>
       <c r="E186" t="n">
-        <v>98.05282511761074</v>
+        <v>98.05281742579406</v>
       </c>
       <c r="F186" t="n">
         <v>263933</v>
@@ -4152,16 +4152,16 @@
         <v>43494</v>
       </c>
       <c r="B187" t="n">
-        <v>97.31603240966797</v>
+        <v>97.31602478027344</v>
       </c>
       <c r="C187" t="n">
-        <v>97.99388726132918</v>
+        <v>97.9938795787921</v>
       </c>
       <c r="D187" t="n">
-        <v>96.72659699282595</v>
+        <v>96.72658940964205</v>
       </c>
       <c r="E187" t="n">
-        <v>97.49286378422838</v>
+        <v>97.4928561409706</v>
       </c>
       <c r="F187" t="n">
         <v>185333</v>
@@ -4172,16 +4172,16 @@
         <v>43495</v>
       </c>
       <c r="B188" t="n">
-        <v>98.73068237304688</v>
+        <v>98.73067474365234</v>
       </c>
       <c r="C188" t="n">
-        <v>98.73068237304688</v>
+        <v>98.73067474365234</v>
       </c>
       <c r="D188" t="n">
-        <v>96.49082331543798</v>
+        <v>96.49081585912812</v>
       </c>
       <c r="E188" t="n">
-        <v>97.28656074509432</v>
+        <v>97.28655322729401</v>
       </c>
       <c r="F188" t="n">
         <v>447533</v>
@@ -4192,16 +4192,16 @@
         <v>43496</v>
       </c>
       <c r="B189" t="n">
-        <v>100.9115982055664</v>
+        <v>100.9115829467773</v>
       </c>
       <c r="C189" t="n">
-        <v>104.5661081748688</v>
+        <v>104.5660923634832</v>
       </c>
       <c r="D189" t="n">
-        <v>99.20222580374578</v>
+        <v>99.20221080343002</v>
       </c>
       <c r="E189" t="n">
-        <v>99.79166869820958</v>
+        <v>99.79165360876446</v>
       </c>
       <c r="F189" t="n">
         <v>504800</v>
@@ -4212,16 +4212,16 @@
         <v>43497</v>
       </c>
       <c r="B190" t="n">
-        <v>100.2042694091797</v>
+        <v>100.2042770385742</v>
       </c>
       <c r="C190" t="n">
-        <v>101.5599715323701</v>
+        <v>101.5599792649856</v>
       </c>
       <c r="D190" t="n">
-        <v>98.84856728598928</v>
+        <v>98.84857481216278</v>
       </c>
       <c r="E190" t="n">
-        <v>101.2063088054374</v>
+        <v>101.2063165111256</v>
       </c>
       <c r="F190" t="n">
         <v>150066</v>
@@ -4252,16 +4252,16 @@
         <v>43501</v>
       </c>
       <c r="B192" t="n">
-        <v>98.73068237304688</v>
+        <v>98.73067474365234</v>
       </c>
       <c r="C192" t="n">
-        <v>101.8546982942061</v>
+        <v>101.8546904234038</v>
       </c>
       <c r="D192" t="n">
-        <v>93.86782337105902</v>
+        <v>93.86781611744098</v>
       </c>
       <c r="E192" t="n">
-        <v>100.2632159398155</v>
+        <v>100.2632081919947</v>
       </c>
       <c r="F192" t="n">
         <v>970333</v>
@@ -4272,16 +4272,16 @@
         <v>43502</v>
       </c>
       <c r="B193" t="n">
-        <v>97.46339416503906</v>
+        <v>97.46338653564453</v>
       </c>
       <c r="C193" t="n">
-        <v>99.5558925401632</v>
+        <v>99.55588474696876</v>
       </c>
       <c r="D193" t="n">
-        <v>96.07821380053463</v>
+        <v>96.07820627957145</v>
       </c>
       <c r="E193" t="n">
-        <v>98.43596298783444</v>
+        <v>98.43595528230763</v>
       </c>
       <c r="F193" t="n">
         <v>594200</v>
@@ -4312,16 +4312,16 @@
         <v>43504</v>
       </c>
       <c r="B195" t="n">
-        <v>97.16867065429688</v>
+        <v>97.16867828369141</v>
       </c>
       <c r="C195" t="n">
-        <v>98.524380343285</v>
+        <v>98.52438807912583</v>
       </c>
       <c r="D195" t="n">
-        <v>95.78349781411782</v>
+        <v>95.78350533475272</v>
       </c>
       <c r="E195" t="n">
-        <v>96.84448605026213</v>
+        <v>96.84449365420265</v>
       </c>
       <c r="F195" t="n">
         <v>210500</v>
@@ -4332,16 +4332,16 @@
         <v>43507</v>
       </c>
       <c r="B196" t="n">
-        <v>98.14124298095703</v>
+        <v>98.14125823974609</v>
       </c>
       <c r="C196" t="n">
-        <v>98.67173707756602</v>
+        <v>98.67175241883517</v>
       </c>
       <c r="D196" t="n">
-        <v>96.10768602482801</v>
+        <v>96.10770096744402</v>
       </c>
       <c r="E196" t="n">
-        <v>97.10972543281549</v>
+        <v>97.10974053122644</v>
       </c>
       <c r="F196" t="n">
         <v>401966</v>
@@ -4352,16 +4352,16 @@
         <v>43508</v>
       </c>
       <c r="B197" t="n">
-        <v>97.55179595947266</v>
+        <v>97.55181121826172</v>
       </c>
       <c r="C197" t="n">
-        <v>99.64430161203596</v>
+        <v>99.64431719812912</v>
       </c>
       <c r="D197" t="n">
-        <v>96.78552923969121</v>
+        <v>96.7855443786229</v>
       </c>
       <c r="E197" t="n">
-        <v>98.20018010395066</v>
+        <v>98.20019546415823</v>
       </c>
       <c r="F197" t="n">
         <v>301900</v>
@@ -4372,16 +4372,16 @@
         <v>43509</v>
       </c>
       <c r="B198" t="n">
-        <v>98.73068237304688</v>
+        <v>98.73067474365234</v>
       </c>
       <c r="C198" t="n">
-        <v>99.88008254812335</v>
+        <v>99.88007482990913</v>
       </c>
       <c r="D198" t="n">
-        <v>96.28452129645588</v>
+        <v>96.28451385608797</v>
       </c>
       <c r="E198" t="n">
-        <v>97.25709009882229</v>
+        <v>97.25708258329932</v>
       </c>
       <c r="F198" t="n">
         <v>448033</v>
@@ -4432,16 +4432,16 @@
         <v>43514</v>
       </c>
       <c r="B201" t="n">
-        <v>100.2042694091797</v>
+        <v>100.2042770385742</v>
       </c>
       <c r="C201" t="n">
-        <v>100.2042694091797</v>
+        <v>100.2042770385742</v>
       </c>
       <c r="D201" t="n">
-        <v>97.64021838645624</v>
+        <v>97.64022582062798</v>
       </c>
       <c r="E201" t="n">
-        <v>98.34754384032168</v>
+        <v>98.34755132834806</v>
       </c>
       <c r="F201" t="n">
         <v>154800</v>
@@ -4472,16 +4472,16 @@
         <v>43516</v>
       </c>
       <c r="B203" t="n">
-        <v>97.25708770751953</v>
+        <v>97.257080078125</v>
       </c>
       <c r="C203" t="n">
-        <v>99.17275461887898</v>
+        <v>99.17274683920873</v>
       </c>
       <c r="D203" t="n">
-        <v>95.5182446694446</v>
+        <v>95.51823717645472</v>
       </c>
       <c r="E203" t="n">
-        <v>98.87804066832706</v>
+        <v>98.87803291177583</v>
       </c>
       <c r="F203" t="n">
         <v>616733</v>
@@ -4492,16 +4492,16 @@
         <v>43517</v>
       </c>
       <c r="B204" t="n">
-        <v>95.78349304199219</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C204" t="n">
-        <v>97.61074797039947</v>
+        <v>97.61076352027936</v>
       </c>
       <c r="D204" t="n">
-        <v>95.04669694166917</v>
+        <v>95.04671208308292</v>
       </c>
       <c r="E204" t="n">
-        <v>97.28655588743874</v>
+        <v>97.28657138567321</v>
       </c>
       <c r="F204" t="n">
         <v>542100</v>
@@ -4512,16 +4512,16 @@
         <v>43518</v>
       </c>
       <c r="B205" t="n">
-        <v>92.86577606201172</v>
+        <v>92.86579132080078</v>
       </c>
       <c r="C205" t="n">
-        <v>95.87190164855839</v>
+        <v>95.87191740128438</v>
       </c>
       <c r="D205" t="n">
-        <v>92.86577606201172</v>
+        <v>92.86579132080078</v>
       </c>
       <c r="E205" t="n">
-        <v>95.84243100478083</v>
+        <v>95.8424467526645</v>
       </c>
       <c r="F205" t="n">
         <v>514866</v>
@@ -4532,16 +4532,16 @@
         <v>43521</v>
       </c>
       <c r="B206" t="n">
-        <v>95.40036773681641</v>
+        <v>95.40036010742188</v>
       </c>
       <c r="C206" t="n">
-        <v>97.10973273549394</v>
+        <v>97.10972496939742</v>
       </c>
       <c r="D206" t="n">
-        <v>92.24688106017342</v>
+        <v>92.24687368297073</v>
       </c>
       <c r="E206" t="n">
-        <v>93.66152459576807</v>
+        <v>93.66151710543296</v>
       </c>
       <c r="F206" t="n">
         <v>404566</v>
@@ -4552,16 +4552,16 @@
         <v>43522</v>
       </c>
       <c r="B207" t="n">
-        <v>95.13511657714844</v>
+        <v>95.13510894775391</v>
       </c>
       <c r="C207" t="n">
-        <v>97.25709311548748</v>
+        <v>97.25708531592029</v>
       </c>
       <c r="D207" t="n">
-        <v>93.36681029027736</v>
+        <v>93.36680280269279</v>
       </c>
       <c r="E207" t="n">
-        <v>95.5771987701748</v>
+        <v>95.57719110532733</v>
       </c>
       <c r="F207" t="n">
         <v>332133</v>
@@ -4572,16 +4572,16 @@
         <v>43523</v>
       </c>
       <c r="B208" t="n">
-        <v>95.69507598876953</v>
+        <v>95.69508361816406</v>
       </c>
       <c r="C208" t="n">
-        <v>96.63818161626997</v>
+        <v>96.63818932085464</v>
       </c>
       <c r="D208" t="n">
-        <v>94.45726390594589</v>
+        <v>94.45727143665449</v>
       </c>
       <c r="E208" t="n">
-        <v>95.13511123842235</v>
+        <v>95.13511882317307</v>
       </c>
       <c r="F208" t="n">
         <v>447266</v>
@@ -4632,16 +4632,16 @@
         <v>43530</v>
       </c>
       <c r="B211" t="n">
-        <v>95.7540283203125</v>
+        <v>95.75402069091797</v>
       </c>
       <c r="C211" t="n">
-        <v>96.60870705270602</v>
+        <v>96.60869935521325</v>
       </c>
       <c r="D211" t="n">
-        <v>93.95624392549898</v>
+        <v>93.95623643934654</v>
       </c>
       <c r="E211" t="n">
-        <v>95.10564411428351</v>
+        <v>95.10563653655028</v>
       </c>
       <c r="F211" t="n">
         <v>247200</v>
@@ -4652,16 +4652,16 @@
         <v>43531</v>
       </c>
       <c r="B212" t="n">
-        <v>96.10769653320312</v>
+        <v>96.10768890380859</v>
       </c>
       <c r="C212" t="n">
-        <v>96.22557912639819</v>
+        <v>96.22557148764568</v>
       </c>
       <c r="D212" t="n">
-        <v>94.89934748740488</v>
+        <v>94.89933995393369</v>
       </c>
       <c r="E212" t="n">
-        <v>95.72456311516235</v>
+        <v>95.72455551618241</v>
       </c>
       <c r="F212" t="n">
         <v>372100</v>
@@ -4672,16 +4672,16 @@
         <v>43532</v>
       </c>
       <c r="B213" t="n">
-        <v>96.63816833496094</v>
+        <v>96.63818359375</v>
       </c>
       <c r="C213" t="n">
-        <v>96.75605090088922</v>
+        <v>96.75606617829148</v>
       </c>
       <c r="D213" t="n">
-        <v>95.63612155411052</v>
+        <v>95.63613665468031</v>
       </c>
       <c r="E213" t="n">
-        <v>95.69506283707466</v>
+        <v>95.69507794695105</v>
       </c>
       <c r="F213" t="n">
         <v>212466</v>
@@ -4692,16 +4692,16 @@
         <v>43535</v>
       </c>
       <c r="B214" t="n">
-        <v>97.31603240966797</v>
+        <v>97.31602478027344</v>
       </c>
       <c r="C214" t="n">
-        <v>97.52233443080878</v>
+        <v>97.52232678524055</v>
       </c>
       <c r="D214" t="n">
-        <v>96.19610286914474</v>
+        <v>96.19609532755058</v>
       </c>
       <c r="E214" t="n">
-        <v>97.25709111650715</v>
+        <v>97.25708349173351</v>
       </c>
       <c r="F214" t="n">
         <v>533833</v>
@@ -4712,16 +4712,16 @@
         <v>43536</v>
       </c>
       <c r="B215" t="n">
-        <v>97.25708770751953</v>
+        <v>97.257080078125</v>
       </c>
       <c r="C215" t="n">
-        <v>98.49490728605517</v>
+        <v>98.49489955955909</v>
       </c>
       <c r="D215" t="n">
-        <v>95.34141330108237</v>
+        <v>95.34140582196414</v>
       </c>
       <c r="E215" t="n">
-        <v>96.84448367970022</v>
+        <v>96.84447608267267</v>
       </c>
       <c r="F215" t="n">
         <v>275666</v>
@@ -4732,16 +4732,16 @@
         <v>43537</v>
       </c>
       <c r="B216" t="n">
-        <v>95.78349304199219</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C216" t="n">
-        <v>97.58127732559895</v>
+        <v>97.58129287078403</v>
       </c>
       <c r="D216" t="n">
-        <v>95.40035966943042</v>
+        <v>95.40037486718441</v>
       </c>
       <c r="E216" t="n">
-        <v>97.43391660651884</v>
+        <v>97.43393212822862</v>
       </c>
       <c r="F216" t="n">
         <v>425833</v>
@@ -4752,16 +4752,16 @@
         <v>43538</v>
       </c>
       <c r="B217" t="n">
-        <v>91.0679931640625</v>
+        <v>91.06800842285156</v>
       </c>
       <c r="C217" t="n">
-        <v>94.86986366323212</v>
+        <v>94.86987955903906</v>
       </c>
       <c r="D217" t="n">
-        <v>90.62591851082115</v>
+        <v>90.62593369553892</v>
       </c>
       <c r="E217" t="n">
-        <v>94.86986366323212</v>
+        <v>94.86987955903906</v>
       </c>
       <c r="F217" t="n">
         <v>2325333</v>
@@ -4772,16 +4772,16 @@
         <v>43539</v>
       </c>
       <c r="B218" t="n">
-        <v>89.29969787597656</v>
+        <v>89.29969024658203</v>
       </c>
       <c r="C218" t="n">
-        <v>92.15846313647816</v>
+        <v>92.15845526284264</v>
       </c>
       <c r="D218" t="n">
-        <v>88.91656446472457</v>
+        <v>88.91655686806337</v>
       </c>
       <c r="E218" t="n">
-        <v>91.06800419827536</v>
+        <v>91.0679964178041</v>
       </c>
       <c r="F218" t="n">
         <v>927800</v>
@@ -4792,16 +4792,16 @@
         <v>43542</v>
       </c>
       <c r="B219" t="n">
-        <v>86.647216796875</v>
+        <v>86.64722442626953</v>
       </c>
       <c r="C219" t="n">
-        <v>89.32915785026566</v>
+        <v>89.32916571580841</v>
       </c>
       <c r="D219" t="n">
-        <v>83.84739316646325</v>
+        <v>83.84740054932983</v>
       </c>
       <c r="E219" t="n">
-        <v>89.29968720601039</v>
+        <v>89.29969506895821</v>
       </c>
       <c r="F219" t="n">
         <v>2555666</v>
@@ -4812,16 +4812,16 @@
         <v>43543</v>
       </c>
       <c r="B220" t="n">
-        <v>89.41757965087891</v>
+        <v>89.41758728027344</v>
       </c>
       <c r="C220" t="n">
-        <v>89.41757965087891</v>
+        <v>89.41758728027344</v>
       </c>
       <c r="D220" t="n">
-        <v>86.35251238884096</v>
+        <v>86.35251975671413</v>
       </c>
       <c r="E220" t="n">
-        <v>86.35251238884096</v>
+        <v>86.35251975671413</v>
       </c>
       <c r="F220" t="n">
         <v>1451666</v>
@@ -4852,16 +4852,16 @@
         <v>43545</v>
       </c>
       <c r="B222" t="n">
-        <v>88.38605499267578</v>
+        <v>88.38607788085938</v>
       </c>
       <c r="C222" t="n">
-        <v>89.27021174804459</v>
+        <v>89.27023486518674</v>
       </c>
       <c r="D222" t="n">
-        <v>87.61978830304847</v>
+        <v>87.61981099280197</v>
       </c>
       <c r="E222" t="n">
-        <v>89.27021174804459</v>
+        <v>89.27023486518674</v>
       </c>
       <c r="F222" t="n">
         <v>454533</v>
@@ -4872,16 +4872,16 @@
         <v>43546</v>
       </c>
       <c r="B223" t="n">
-        <v>87.82610321044922</v>
+        <v>87.82608795166016</v>
       </c>
       <c r="C223" t="n">
-        <v>87.94398579844682</v>
+        <v>87.94397051917699</v>
       </c>
       <c r="D223" t="n">
-        <v>86.55881292392856</v>
+        <v>86.55879788531681</v>
       </c>
       <c r="E223" t="n">
-        <v>87.94398579844682</v>
+        <v>87.94397051917699</v>
       </c>
       <c r="F223" t="n">
         <v>257266</v>
@@ -4892,16 +4892,16 @@
         <v>43549</v>
       </c>
       <c r="B224" t="n">
-        <v>87.53137969970703</v>
+        <v>87.53138732910156</v>
       </c>
       <c r="C224" t="n">
-        <v>87.6492697800209</v>
+        <v>87.64927741969095</v>
       </c>
       <c r="D224" t="n">
-        <v>85.79254411177544</v>
+        <v>85.79255158960989</v>
       </c>
       <c r="E224" t="n">
-        <v>86.79458356167065</v>
+        <v>86.79459112684468</v>
       </c>
       <c r="F224" t="n">
         <v>451333</v>
@@ -4912,16 +4912,16 @@
         <v>43550</v>
       </c>
       <c r="B225" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56492614746094</v>
       </c>
       <c r="C225" t="n">
-        <v>89.62387506752287</v>
+        <v>89.62386743310755</v>
       </c>
       <c r="D225" t="n">
-        <v>86.76511004398911</v>
+        <v>86.76510265309149</v>
       </c>
       <c r="E225" t="n">
-        <v>88.20923162596166</v>
+        <v>88.20922411204968</v>
       </c>
       <c r="F225" t="n">
         <v>883933</v>
@@ -4952,16 +4952,16 @@
         <v>43552</v>
       </c>
       <c r="B227" t="n">
-        <v>90.03649139404297</v>
+        <v>90.03648376464844</v>
       </c>
       <c r="C227" t="n">
-        <v>90.03649139404297</v>
+        <v>90.03648376464844</v>
       </c>
       <c r="D227" t="n">
-        <v>85.58624382921319</v>
+        <v>85.58623657691791</v>
       </c>
       <c r="E227" t="n">
-        <v>86.35251062910731</v>
+        <v>86.35250331188112</v>
       </c>
       <c r="F227" t="n">
         <v>558066</v>
@@ -5012,16 +5012,16 @@
         <v>43557</v>
       </c>
       <c r="B230" t="n">
-        <v>91.68691253662109</v>
+        <v>91.68692016601562</v>
       </c>
       <c r="C230" t="n">
-        <v>91.92268520042373</v>
+        <v>91.92269284943723</v>
       </c>
       <c r="D230" t="n">
-        <v>89.88912817431608</v>
+        <v>89.8891356541145</v>
       </c>
       <c r="E230" t="n">
-        <v>91.65743439545264</v>
+        <v>91.65744202239426</v>
       </c>
       <c r="F230" t="n">
         <v>264800</v>
@@ -5032,16 +5032,16 @@
         <v>43558</v>
       </c>
       <c r="B231" t="n">
-        <v>88.88706970214844</v>
+        <v>88.88707733154297</v>
       </c>
       <c r="C231" t="n">
-        <v>92.77735937298839</v>
+        <v>92.777367336296</v>
       </c>
       <c r="D231" t="n">
-        <v>88.88706970214844</v>
+        <v>88.88707733154297</v>
       </c>
       <c r="E231" t="n">
-        <v>92.71841059337896</v>
+        <v>92.71841855162685</v>
       </c>
       <c r="F231" t="n">
         <v>371500</v>
@@ -5152,16 +5152,16 @@
         <v>43566</v>
       </c>
       <c r="B237" t="n">
-        <v>84.34841918945312</v>
+        <v>84.34841156005859</v>
       </c>
       <c r="C237" t="n">
-        <v>84.61366249095812</v>
+        <v>84.61365483757208</v>
       </c>
       <c r="D237" t="n">
-        <v>82.40327416313194</v>
+        <v>82.40326670967762</v>
       </c>
       <c r="E237" t="n">
-        <v>83.78845444620694</v>
+        <v>83.78844686746174</v>
       </c>
       <c r="F237" t="n">
         <v>403133</v>
@@ -5192,16 +5192,16 @@
         <v>43570</v>
       </c>
       <c r="B239" t="n">
-        <v>83.96529388427734</v>
+        <v>83.96528625488281</v>
       </c>
       <c r="C239" t="n">
-        <v>84.37789794631881</v>
+        <v>84.37789027943356</v>
       </c>
       <c r="D239" t="n">
-        <v>82.58011346803741</v>
+        <v>82.58010596450545</v>
       </c>
       <c r="E239" t="n">
-        <v>82.81588614704992</v>
+        <v>82.81587862209479</v>
       </c>
       <c r="F239" t="n">
         <v>210900</v>
@@ -5232,16 +5232,16 @@
         <v>43572</v>
       </c>
       <c r="B241" t="n">
-        <v>82.66851043701172</v>
+        <v>82.66853332519531</v>
       </c>
       <c r="C241" t="n">
-        <v>84.23051431663492</v>
+        <v>84.23053763728586</v>
       </c>
       <c r="D241" t="n">
-        <v>81.4601617322413</v>
+        <v>81.460184285873</v>
       </c>
       <c r="E241" t="n">
-        <v>84.20104367665355</v>
+        <v>84.20106698914505</v>
       </c>
       <c r="F241" t="n">
         <v>289766</v>
@@ -5252,16 +5252,16 @@
         <v>43573</v>
       </c>
       <c r="B242" t="n">
-        <v>83.99475860595703</v>
+        <v>83.99476623535156</v>
       </c>
       <c r="C242" t="n">
-        <v>84.43683328479936</v>
+        <v>84.43684095434833</v>
       </c>
       <c r="D242" t="n">
-        <v>81.6959507887746</v>
+        <v>81.69595820936428</v>
       </c>
       <c r="E242" t="n">
-        <v>82.19697425451963</v>
+        <v>82.19698172061818</v>
       </c>
       <c r="F242" t="n">
         <v>318766</v>
@@ -5272,16 +5272,16 @@
         <v>43577</v>
       </c>
       <c r="B243" t="n">
-        <v>84.58419799804688</v>
+        <v>84.58419036865234</v>
       </c>
       <c r="C243" t="n">
-        <v>86.26409234997288</v>
+        <v>86.26408456905386</v>
       </c>
       <c r="D243" t="n">
-        <v>82.31486821484337</v>
+        <v>82.3148607901397</v>
       </c>
       <c r="E243" t="n">
-        <v>83.49373907739835</v>
+        <v>83.49373154636193</v>
       </c>
       <c r="F243" t="n">
         <v>461666</v>
@@ -5292,16 +5292,16 @@
         <v>43578</v>
       </c>
       <c r="B244" t="n">
-        <v>86.27613830566406</v>
+        <v>86.27613067626953</v>
       </c>
       <c r="C244" t="n">
-        <v>86.77929458213193</v>
+        <v>86.77928690824331</v>
       </c>
       <c r="D244" t="n">
-        <v>84.23392462703995</v>
+        <v>84.23391717823827</v>
       </c>
       <c r="E244" t="n">
-        <v>85.24023717997569</v>
+        <v>85.24022964218584</v>
       </c>
       <c r="F244" t="n">
         <v>437600</v>
@@ -5312,16 +5312,16 @@
         <v>43579</v>
       </c>
       <c r="B245" t="n">
-        <v>86.51292419433594</v>
+        <v>86.51291656494141</v>
       </c>
       <c r="C245" t="n">
-        <v>87.07527268351602</v>
+        <v>87.07526500452914</v>
       </c>
       <c r="D245" t="n">
-        <v>85.0626550572442</v>
+        <v>85.06264755574588</v>
       </c>
       <c r="E245" t="n">
-        <v>86.27614033690361</v>
+        <v>86.27613272839055</v>
       </c>
       <c r="F245" t="n">
         <v>361900</v>
@@ -5352,16 +5352,16 @@
         <v>43581</v>
       </c>
       <c r="B247" t="n">
-        <v>87.46002960205078</v>
+        <v>87.46004486083984</v>
       </c>
       <c r="C247" t="n">
-        <v>87.66720981443939</v>
+        <v>87.66722510937433</v>
       </c>
       <c r="D247" t="n">
-        <v>86.15774860490582</v>
+        <v>86.15776363649131</v>
       </c>
       <c r="E247" t="n">
-        <v>87.43043350413572</v>
+        <v>87.43044875776127</v>
       </c>
       <c r="F247" t="n">
         <v>187233</v>
@@ -5392,16 +5392,16 @@
         <v>43585</v>
       </c>
       <c r="B249" t="n">
-        <v>89.56143188476562</v>
+        <v>89.56142425537109</v>
       </c>
       <c r="C249" t="n">
-        <v>90.27176831516947</v>
+        <v>90.27176062526411</v>
       </c>
       <c r="D249" t="n">
-        <v>86.77928588367251</v>
+        <v>86.77927849127832</v>
       </c>
       <c r="E249" t="n">
-        <v>86.77928588367251</v>
+        <v>86.77927849127832</v>
       </c>
       <c r="F249" t="n">
         <v>318366</v>
@@ -5412,16 +5412,16 @@
         <v>43587</v>
       </c>
       <c r="B250" t="n">
-        <v>89.82779693603516</v>
+        <v>89.82781219482422</v>
       </c>
       <c r="C250" t="n">
-        <v>90.41974893094701</v>
+        <v>90.41976429028925</v>
       </c>
       <c r="D250" t="n">
-        <v>88.64390800017603</v>
+        <v>88.64392305786127</v>
       </c>
       <c r="E250" t="n">
-        <v>88.64390800017603</v>
+        <v>88.64392305786127</v>
       </c>
       <c r="F250" t="n">
         <v>415166</v>
@@ -5432,16 +5432,16 @@
         <v>43588</v>
       </c>
       <c r="B251" t="n">
-        <v>90.21257781982422</v>
+        <v>90.21258544921875</v>
       </c>
       <c r="C251" t="n">
-        <v>90.89331063928984</v>
+        <v>90.89331832625483</v>
       </c>
       <c r="D251" t="n">
-        <v>88.91029684856353</v>
+        <v>88.91030436782248</v>
       </c>
       <c r="E251" t="n">
-        <v>88.91029684856353</v>
+        <v>88.91030436782248</v>
       </c>
       <c r="F251" t="n">
         <v>248400</v>
@@ -5452,16 +5452,16 @@
         <v>43591</v>
       </c>
       <c r="B252" t="n">
-        <v>90.53815460205078</v>
+        <v>90.53813934326172</v>
       </c>
       <c r="C252" t="n">
-        <v>91.10050310789021</v>
+        <v>91.1004877543261</v>
       </c>
       <c r="D252" t="n">
-        <v>88.19997227476354</v>
+        <v>88.19995741003851</v>
       </c>
       <c r="E252" t="n">
-        <v>88.64392884837949</v>
+        <v>88.64391390883252</v>
       </c>
       <c r="F252" t="n">
         <v>206566</v>
@@ -5492,16 +5492,16 @@
         <v>43593</v>
       </c>
       <c r="B254" t="n">
-        <v>102.3474731445312</v>
+        <v>102.3474578857422</v>
       </c>
       <c r="C254" t="n">
-        <v>104.4488865051489</v>
+        <v>104.4488709330641</v>
       </c>
       <c r="D254" t="n">
-        <v>98.88458653596543</v>
+        <v>98.8845717934515</v>
       </c>
       <c r="E254" t="n">
-        <v>100.6308316532951</v>
+        <v>100.6308166504369</v>
       </c>
       <c r="F254" t="n">
         <v>1898166</v>
@@ -5612,16 +5612,16 @@
         <v>43601</v>
       </c>
       <c r="B260" t="n">
-        <v>102.5842514038086</v>
+        <v>102.5842437744141</v>
       </c>
       <c r="C260" t="n">
-        <v>103.679352253486</v>
+        <v>103.6793445426467</v>
       </c>
       <c r="D260" t="n">
-        <v>102.5842514038086</v>
+        <v>102.5842437744141</v>
       </c>
       <c r="E260" t="n">
-        <v>103.5905639544772</v>
+        <v>103.5905562502412</v>
       </c>
       <c r="F260" t="n">
         <v>583833</v>
@@ -5632,16 +5632,16 @@
         <v>43602</v>
       </c>
       <c r="B261" t="n">
-        <v>102.968994140625</v>
+        <v>102.9690093994141</v>
       </c>
       <c r="C261" t="n">
-        <v>103.5609385474501</v>
+        <v>103.5609538939583</v>
       </c>
       <c r="D261" t="n">
-        <v>101.5483215426596</v>
+        <v>101.5483365909217</v>
       </c>
       <c r="E261" t="n">
-        <v>102.9393905223495</v>
+        <v>102.9394057767516</v>
       </c>
       <c r="F261" t="n">
         <v>361233</v>
@@ -5672,16 +5672,16 @@
         <v>43606</v>
       </c>
       <c r="B263" t="n">
-        <v>108.3557205200195</v>
+        <v>108.3557281494141</v>
       </c>
       <c r="C263" t="n">
-        <v>109.8355855666399</v>
+        <v>109.8355933002327</v>
       </c>
       <c r="D263" t="n">
-        <v>105.8103508333566</v>
+        <v>105.8103582835301</v>
       </c>
       <c r="E263" t="n">
-        <v>105.8103508333566</v>
+        <v>105.8103582835301</v>
       </c>
       <c r="F263" t="n">
         <v>554800</v>
@@ -5692,16 +5692,16 @@
         <v>43607</v>
       </c>
       <c r="B264" t="n">
-        <v>109.450813293457</v>
+        <v>109.4508285522461</v>
       </c>
       <c r="C264" t="n">
-        <v>110.30913014078</v>
+        <v>110.309145519229</v>
       </c>
       <c r="D264" t="n">
-        <v>107.8821525441381</v>
+        <v>107.8821675842365</v>
       </c>
       <c r="E264" t="n">
-        <v>108.3261090150305</v>
+        <v>108.3261241170219</v>
       </c>
       <c r="F264" t="n">
         <v>582066</v>
@@ -5712,16 +5712,16 @@
         <v>43608</v>
       </c>
       <c r="B265" t="n">
-        <v>110.9898681640625</v>
+        <v>110.989875793457</v>
       </c>
       <c r="C265" t="n">
-        <v>112.4697330729167</v>
+        <v>112.4697408040365</v>
       </c>
       <c r="D265" t="n">
-        <v>109.1844311687847</v>
+        <v>109.1844386740743</v>
       </c>
       <c r="E265" t="n">
-        <v>109.3324191650665</v>
+        <v>109.3324266805288</v>
       </c>
       <c r="F265" t="n">
         <v>449966</v>
@@ -5732,16 +5732,16 @@
         <v>43609</v>
       </c>
       <c r="B266" t="n">
-        <v>110.39794921875</v>
+        <v>110.3979339599609</v>
       </c>
       <c r="C266" t="n">
-        <v>111.9074105702988</v>
+        <v>111.9073951028777</v>
       </c>
       <c r="D266" t="n">
-        <v>109.9539851273049</v>
+        <v>109.9539699298789</v>
       </c>
       <c r="E266" t="n">
-        <v>111.1970740455737</v>
+        <v>111.1970586763327</v>
       </c>
       <c r="F266" t="n">
         <v>294000</v>
@@ -5752,16 +5752,16 @@
         <v>43612</v>
       </c>
       <c r="B267" t="n">
-        <v>109.953987121582</v>
+        <v>109.9539794921875</v>
       </c>
       <c r="C267" t="n">
-        <v>111.7298284656038</v>
+        <v>111.7298207129887</v>
       </c>
       <c r="D267" t="n">
-        <v>109.6876146834708</v>
+        <v>109.6876070725591</v>
       </c>
       <c r="E267" t="n">
-        <v>110.0427829522751</v>
+        <v>110.0427753167193</v>
       </c>
       <c r="F267" t="n">
         <v>77066</v>
@@ -5812,16 +5812,16 @@
         <v>43615</v>
       </c>
       <c r="B270" t="n">
-        <v>107.7045822143555</v>
+        <v>107.70458984375</v>
       </c>
       <c r="C270" t="n">
-        <v>111.6410213474626</v>
+        <v>111.6410292556999</v>
       </c>
       <c r="D270" t="n">
-        <v>107.7045822143555</v>
+        <v>107.70458984375</v>
       </c>
       <c r="E270" t="n">
-        <v>109.9243799064583</v>
+        <v>109.9243876930951</v>
       </c>
       <c r="F270" t="n">
         <v>452966</v>
@@ -5832,16 +5832,16 @@
         <v>43616</v>
       </c>
       <c r="B271" t="n">
-        <v>108.8588790893555</v>
+        <v>108.8588714599609</v>
       </c>
       <c r="C271" t="n">
-        <v>110.4275400950732</v>
+        <v>110.4275323557388</v>
       </c>
       <c r="D271" t="n">
-        <v>106.8462615401803</v>
+        <v>106.8462540518404</v>
       </c>
       <c r="E271" t="n">
-        <v>107.4086175348022</v>
+        <v>107.4086100070495</v>
       </c>
       <c r="F271" t="n">
         <v>504400</v>
@@ -5852,16 +5852,16 @@
         <v>43619</v>
       </c>
       <c r="B272" t="n">
-        <v>109.8651733398438</v>
+        <v>109.8651962280273</v>
       </c>
       <c r="C272" t="n">
-        <v>110.7530938059435</v>
+        <v>110.7531168791073</v>
       </c>
       <c r="D272" t="n">
-        <v>108.6220846873041</v>
+        <v>108.6221073165154</v>
       </c>
       <c r="E272" t="n">
-        <v>108.7996687805241</v>
+        <v>108.7996914467314</v>
       </c>
       <c r="F272" t="n">
         <v>294000</v>
@@ -5872,16 +5872,16 @@
         <v>43620</v>
       </c>
       <c r="B273" t="n">
-        <v>107.1718292236328</v>
+        <v>107.1718215942383</v>
       </c>
       <c r="C273" t="n">
-        <v>110.9898839409142</v>
+        <v>110.9898760397184</v>
       </c>
       <c r="D273" t="n">
-        <v>107.1718292236328</v>
+        <v>107.1718215942383</v>
       </c>
       <c r="E273" t="n">
-        <v>109.5988071159028</v>
+        <v>109.5987993137355</v>
       </c>
       <c r="F273" t="n">
         <v>283866</v>
@@ -5892,16 +5892,16 @@
         <v>43621</v>
       </c>
       <c r="B274" t="n">
-        <v>108.8884811401367</v>
+        <v>108.8884658813477</v>
       </c>
       <c r="C274" t="n">
-        <v>109.8355939389301</v>
+        <v>109.83557854742</v>
       </c>
       <c r="D274" t="n">
-        <v>106.4023034571936</v>
+        <v>106.4022885467982</v>
       </c>
       <c r="E274" t="n">
-        <v>106.6390797751461</v>
+        <v>106.6390648315707</v>
       </c>
       <c r="F274" t="n">
         <v>231033</v>
@@ -5932,16 +5932,16 @@
         <v>43623</v>
       </c>
       <c r="B276" t="n">
-        <v>110.6051254272461</v>
+        <v>110.6051330566406</v>
       </c>
       <c r="C276" t="n">
-        <v>110.664317626492</v>
+        <v>110.6643252599696</v>
       </c>
       <c r="D276" t="n">
-        <v>108.9180800058842</v>
+        <v>108.9180875189086</v>
       </c>
       <c r="E276" t="n">
-        <v>109.2140485290975</v>
+        <v>109.2140560625374</v>
       </c>
       <c r="F276" t="n">
         <v>204266</v>
@@ -5952,16 +5952,16 @@
         <v>43626</v>
       </c>
       <c r="B277" t="n">
-        <v>114.3935623168945</v>
+        <v>114.3935699462891</v>
       </c>
       <c r="C277" t="n">
-        <v>119.3955057520065</v>
+        <v>119.395513715002</v>
       </c>
       <c r="D277" t="n">
-        <v>111.8777963148814</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="E277" t="n">
-        <v>111.8777963148814</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="F277" t="n">
         <v>585833</v>
@@ -5972,16 +5972,16 @@
         <v>43627</v>
       </c>
       <c r="B278" t="n">
-        <v>110.9898681640625</v>
+        <v>110.989875793457</v>
       </c>
       <c r="C278" t="n">
-        <v>116.6725515216175</v>
+        <v>116.6725595416372</v>
       </c>
       <c r="D278" t="n">
-        <v>110.9898681640625</v>
+        <v>110.989875793457</v>
       </c>
       <c r="E278" t="n">
-        <v>116.4653638106336</v>
+        <v>116.4653718164113</v>
       </c>
       <c r="F278" t="n">
         <v>422033</v>
@@ -5992,16 +5992,16 @@
         <v>43628</v>
       </c>
       <c r="B279" t="n">
-        <v>108.9180755615234</v>
+        <v>108.9180679321289</v>
       </c>
       <c r="C279" t="n">
-        <v>111.7594139141432</v>
+        <v>111.7594060857212</v>
       </c>
       <c r="D279" t="n">
-        <v>108.7996836408789</v>
+        <v>108.7996760197774</v>
       </c>
       <c r="E279" t="n">
-        <v>111.7594139141432</v>
+        <v>111.7594060857212</v>
       </c>
       <c r="F279" t="n">
         <v>382266</v>
@@ -6012,16 +6012,16 @@
         <v>43629</v>
       </c>
       <c r="B280" t="n">
-        <v>113.8608169555664</v>
+        <v>113.8608093261719</v>
       </c>
       <c r="C280" t="n">
-        <v>114.9855138301545</v>
+        <v>114.9855061253982</v>
       </c>
       <c r="D280" t="n">
-        <v>108.9180729377125</v>
+        <v>108.9180656395131</v>
       </c>
       <c r="E280" t="n">
-        <v>108.9180729377125</v>
+        <v>108.9180656395131</v>
       </c>
       <c r="F280" t="n">
         <v>845300</v>
@@ -6032,16 +6032,16 @@
         <v>43630</v>
       </c>
       <c r="B281" t="n">
-        <v>111.9370040893555</v>
+        <v>111.9369964599609</v>
       </c>
       <c r="C281" t="n">
-        <v>114.1568019144333</v>
+        <v>114.156794133742</v>
       </c>
       <c r="D281" t="n">
-        <v>110.7531149267741</v>
+        <v>110.753107378071</v>
       </c>
       <c r="E281" t="n">
-        <v>113.3576771060401</v>
+        <v>113.3576693798154</v>
       </c>
       <c r="F281" t="n">
         <v>560666</v>
@@ -6052,16 +6052,16 @@
         <v>43633</v>
       </c>
       <c r="B282" t="n">
-        <v>110.0723648071289</v>
+        <v>110.072380065918</v>
       </c>
       <c r="C282" t="n">
-        <v>113.1504868960452</v>
+        <v>113.1505025815391</v>
       </c>
       <c r="D282" t="n">
-        <v>109.066052333433</v>
+        <v>109.0660674527219</v>
       </c>
       <c r="E282" t="n">
-        <v>113.1504868960452</v>
+        <v>113.1505025815391</v>
       </c>
       <c r="F282" t="n">
         <v>481366</v>
@@ -6112,16 +6112,16 @@
         <v>43637</v>
       </c>
       <c r="B285" t="n">
-        <v>116.4653625488281</v>
+        <v>116.4653701782227</v>
       </c>
       <c r="C285" t="n">
-        <v>116.4949661693495</v>
+        <v>116.4949738006833</v>
       </c>
       <c r="D285" t="n">
-        <v>114.5415411989536</v>
+        <v>114.5415487023227</v>
       </c>
       <c r="E285" t="n">
-        <v>115.3998655465033</v>
+        <v>115.3998731060995</v>
       </c>
       <c r="F285" t="n">
         <v>285566</v>
@@ -6152,16 +6152,16 @@
         <v>43641</v>
       </c>
       <c r="B287" t="n">
-        <v>114.4823684692383</v>
+        <v>114.4823760986328</v>
       </c>
       <c r="C287" t="n">
-        <v>117.1165266196842</v>
+        <v>117.1165344246257</v>
       </c>
       <c r="D287" t="n">
-        <v>113.8312241927775</v>
+        <v>113.8312317787781</v>
       </c>
       <c r="E287" t="n">
-        <v>116.5837742644845</v>
+        <v>116.583782033922</v>
       </c>
       <c r="F287" t="n">
         <v>481433</v>
@@ -6212,16 +6212,16 @@
         <v>43644</v>
       </c>
       <c r="B290" t="n">
-        <v>116.7021636962891</v>
+        <v>116.7021713256836</v>
       </c>
       <c r="C290" t="n">
-        <v>117.6492764652239</v>
+        <v>117.6492841565359</v>
       </c>
       <c r="D290" t="n">
-        <v>114.1271977979104</v>
+        <v>114.1272052589668</v>
       </c>
       <c r="E290" t="n">
-        <v>115.0743105668453</v>
+        <v>115.0743180898191</v>
       </c>
       <c r="F290" t="n">
         <v>617600</v>
@@ -6232,16 +6232,16 @@
         <v>43647</v>
       </c>
       <c r="B291" t="n">
-        <v>114.0680084228516</v>
+        <v>114.0680160522461</v>
       </c>
       <c r="C291" t="n">
-        <v>117.0573348202537</v>
+        <v>117.0573426495882</v>
       </c>
       <c r="D291" t="n">
-        <v>114.0680084228516</v>
+        <v>114.0680160522461</v>
       </c>
       <c r="E291" t="n">
-        <v>117.0573348202537</v>
+        <v>117.0573426495882</v>
       </c>
       <c r="F291" t="n">
         <v>436066</v>
@@ -6252,16 +6252,16 @@
         <v>43648</v>
       </c>
       <c r="B292" t="n">
-        <v>110.1315689086914</v>
+        <v>110.1315612792969</v>
       </c>
       <c r="C292" t="n">
-        <v>115.1335131395955</v>
+        <v>115.1335051636899</v>
       </c>
       <c r="D292" t="n">
-        <v>110.1315689086914</v>
+        <v>110.1315612792969</v>
       </c>
       <c r="E292" t="n">
-        <v>113.9792200540755</v>
+        <v>113.9792121581339</v>
       </c>
       <c r="F292" t="n">
         <v>537533</v>
@@ -6372,16 +6372,16 @@
         <v>43657</v>
       </c>
       <c r="B298" t="n">
-        <v>123.1654510498047</v>
+        <v>123.1654663085938</v>
       </c>
       <c r="C298" t="n">
-        <v>130.1796939827041</v>
+        <v>130.1797101104775</v>
       </c>
       <c r="D298" t="n">
-        <v>123.1060106831362</v>
+        <v>123.1060259345613</v>
       </c>
       <c r="E298" t="n">
-        <v>130.1796939827041</v>
+        <v>130.1797101104775</v>
       </c>
       <c r="F298" t="n">
         <v>660700</v>
@@ -6412,16 +6412,16 @@
         <v>43661</v>
       </c>
       <c r="B300" t="n">
-        <v>121.5605010986328</v>
+        <v>121.5604934692383</v>
       </c>
       <c r="C300" t="n">
-        <v>126.7320249772505</v>
+        <v>126.7320170232801</v>
       </c>
       <c r="D300" t="n">
-        <v>118.5289212629776</v>
+        <v>118.5289138238514</v>
       </c>
       <c r="E300" t="n">
-        <v>124.9784660186075</v>
+        <v>124.9784581746943</v>
       </c>
       <c r="F300" t="n">
         <v>1110366</v>
@@ -6432,16 +6432,16 @@
         <v>43662</v>
       </c>
       <c r="B301" t="n">
-        <v>124.1462707519531</v>
+        <v>124.1462631225586</v>
       </c>
       <c r="C301" t="n">
-        <v>124.2354388718879</v>
+        <v>124.2354312370136</v>
       </c>
       <c r="D301" t="n">
-        <v>120.4608163768777</v>
+        <v>120.4608089739724</v>
       </c>
       <c r="E301" t="n">
-        <v>121.5605086519742</v>
+        <v>121.5605011814873</v>
       </c>
       <c r="F301" t="n">
         <v>378300</v>
@@ -6472,16 +6472,16 @@
         <v>43664</v>
       </c>
       <c r="B303" t="n">
-        <v>129.8825073242188</v>
+        <v>129.8824920654297</v>
       </c>
       <c r="C303" t="n">
-        <v>129.8825073242188</v>
+        <v>129.8824920654297</v>
       </c>
       <c r="D303" t="n">
-        <v>127.5047865601033</v>
+        <v>127.5047715806524</v>
       </c>
       <c r="E303" t="n">
-        <v>127.7722833584466</v>
+        <v>127.7722683475697</v>
       </c>
       <c r="F303" t="n">
         <v>405966</v>
@@ -6492,16 +6492,16 @@
         <v>43665</v>
       </c>
       <c r="B304" t="n">
-        <v>126.9995193481445</v>
+        <v>126.9995346069336</v>
       </c>
       <c r="C304" t="n">
-        <v>132.379084421508</v>
+        <v>132.3791003266432</v>
       </c>
       <c r="D304" t="n">
-        <v>126.9995193481445</v>
+        <v>126.9995346069336</v>
       </c>
       <c r="E304" t="n">
-        <v>129.9419385720236</v>
+        <v>129.9419541843396</v>
       </c>
       <c r="F304" t="n">
         <v>683033</v>
@@ -6532,16 +6532,16 @@
         <v>43669</v>
       </c>
       <c r="B306" t="n">
-        <v>125.0676345825195</v>
+        <v>125.0676498413086</v>
       </c>
       <c r="C306" t="n">
-        <v>127.8020051818723</v>
+        <v>127.8020207742663</v>
       </c>
       <c r="D306" t="n">
-        <v>123.6410051291977</v>
+        <v>123.6410202139319</v>
       </c>
       <c r="E306" t="n">
-        <v>127.475068005729</v>
+        <v>127.4750835582353</v>
       </c>
       <c r="F306" t="n">
         <v>528700</v>
@@ -6552,16 +6552,16 @@
         <v>43670</v>
       </c>
       <c r="B307" t="n">
-        <v>128.8719940185547</v>
+        <v>128.8719787597656</v>
       </c>
       <c r="C307" t="n">
-        <v>131.8441340601715</v>
+        <v>131.8441184494731</v>
       </c>
       <c r="D307" t="n">
-        <v>124.9487700706457</v>
+        <v>124.9487552763768</v>
       </c>
       <c r="E307" t="n">
-        <v>124.9487700706457</v>
+        <v>124.9487552763768</v>
       </c>
       <c r="F307" t="n">
         <v>788600</v>
@@ -6572,16 +6572,16 @@
         <v>43671</v>
       </c>
       <c r="B308" t="n">
-        <v>126.4645462036133</v>
+        <v>126.4645385742188</v>
       </c>
       <c r="C308" t="n">
-        <v>131.3388459566314</v>
+        <v>131.3388380331786</v>
       </c>
       <c r="D308" t="n">
-        <v>126.0484408996179</v>
+        <v>126.0484332953263</v>
       </c>
       <c r="E308" t="n">
-        <v>129.3177976048466</v>
+        <v>129.3177898033202</v>
       </c>
       <c r="F308" t="n">
         <v>3248566</v>
@@ -6592,16 +6592,16 @@
         <v>43672</v>
       </c>
       <c r="B309" t="n">
-        <v>125.6620635986328</v>
+        <v>125.6620559692383</v>
       </c>
       <c r="C309" t="n">
-        <v>127.9208885740418</v>
+        <v>127.9208808075059</v>
       </c>
       <c r="D309" t="n">
-        <v>125.0676371669792</v>
+        <v>125.0676295736744</v>
       </c>
       <c r="E309" t="n">
-        <v>127.2075738326406</v>
+        <v>127.2075661094126</v>
       </c>
       <c r="F309" t="n">
         <v>1585266</v>
@@ -6652,16 +6652,16 @@
         <v>43677</v>
       </c>
       <c r="B312" t="n">
-        <v>124.2354431152344</v>
+        <v>124.2354354858398</v>
       </c>
       <c r="C312" t="n">
-        <v>126.1673309301498</v>
+        <v>126.1673231821166</v>
       </c>
       <c r="D312" t="n">
-        <v>121.1444150528274</v>
+        <v>121.1444076132553</v>
       </c>
       <c r="E312" t="n">
-        <v>125.5729044916022</v>
+        <v>125.5728967800731</v>
       </c>
       <c r="F312" t="n">
         <v>1188566</v>
@@ -6712,16 +6712,16 @@
         <v>43682</v>
       </c>
       <c r="B315" t="n">
-        <v>123.4032363891602</v>
+        <v>123.4032287597656</v>
       </c>
       <c r="C315" t="n">
-        <v>124.3543201742961</v>
+        <v>124.3543124861009</v>
       </c>
       <c r="D315" t="n">
-        <v>121.8577261831319</v>
+        <v>121.8577186492884</v>
       </c>
       <c r="E315" t="n">
-        <v>124.057110743121</v>
+        <v>124.0571030733008</v>
       </c>
       <c r="F315" t="n">
         <v>384500</v>
@@ -6772,16 +6772,16 @@
         <v>43685</v>
       </c>
       <c r="B318" t="n">
-        <v>131.9035491943359</v>
+        <v>131.9035797119141</v>
       </c>
       <c r="C318" t="n">
-        <v>133.5679400428555</v>
+        <v>133.5679709455118</v>
       </c>
       <c r="D318" t="n">
-        <v>129.2880670630315</v>
+        <v>129.2880969754843</v>
       </c>
       <c r="E318" t="n">
-        <v>129.2880670630315</v>
+        <v>129.2880969754843</v>
       </c>
       <c r="F318" t="n">
         <v>971500</v>
@@ -6792,16 +6792,16 @@
         <v>43686</v>
       </c>
       <c r="B319" t="n">
-        <v>131.5171966552734</v>
+        <v>131.5171661376953</v>
       </c>
       <c r="C319" t="n">
-        <v>134.8757142928603</v>
+        <v>134.8756829959633</v>
       </c>
       <c r="D319" t="n">
-        <v>129.4069723912467</v>
+        <v>129.4069423633303</v>
       </c>
       <c r="E319" t="n">
-        <v>134.8757142928603</v>
+        <v>134.8756829959633</v>
       </c>
       <c r="F319" t="n">
         <v>371566</v>
@@ -6832,16 +6832,16 @@
         <v>43690</v>
       </c>
       <c r="B321" t="n">
-        <v>131.0713653564453</v>
+        <v>131.0713500976562</v>
       </c>
       <c r="C321" t="n">
-        <v>133.7760082829146</v>
+        <v>133.7759927092622</v>
       </c>
       <c r="D321" t="n">
-        <v>128.8125403668755</v>
+        <v>128.8125253710496</v>
       </c>
       <c r="E321" t="n">
-        <v>133.6571275309639</v>
+        <v>133.6571119711511</v>
       </c>
       <c r="F321" t="n">
         <v>614133</v>
@@ -6892,16 +6892,16 @@
         <v>43693</v>
       </c>
       <c r="B324" t="n">
-        <v>145.6348419189453</v>
+        <v>145.6348114013672</v>
       </c>
       <c r="C324" t="n">
-        <v>145.6348419189453</v>
+        <v>145.6348114013672</v>
       </c>
       <c r="D324" t="n">
-        <v>137.2236813210683</v>
+        <v>137.2236525660371</v>
       </c>
       <c r="E324" t="n">
-        <v>141.8305068193669</v>
+        <v>141.8304770989819</v>
       </c>
       <c r="F324" t="n">
         <v>930266</v>
@@ -6932,16 +6932,16 @@
         <v>43697</v>
       </c>
       <c r="B326" t="n">
-        <v>145.0106964111328</v>
+        <v>145.0106811523438</v>
       </c>
       <c r="C326" t="n">
-        <v>146.7048227534003</v>
+        <v>146.7048073163463</v>
       </c>
       <c r="D326" t="n">
-        <v>140.4633261324826</v>
+        <v>140.4633113521918</v>
       </c>
       <c r="E326" t="n">
-        <v>143.0490883704163</v>
+        <v>143.049073318038</v>
       </c>
       <c r="F326" t="n">
         <v>506533</v>
@@ -6952,16 +6952,16 @@
         <v>43698</v>
       </c>
       <c r="B327" t="n">
-        <v>148.5772552490234</v>
+        <v>148.5772399902344</v>
       </c>
       <c r="C327" t="n">
-        <v>148.7258561776249</v>
+        <v>148.7258409035746</v>
       </c>
       <c r="D327" t="n">
-        <v>143.4057312945277</v>
+        <v>143.4057165668508</v>
       </c>
       <c r="E327" t="n">
-        <v>146.8236887061101</v>
+        <v>146.8236736274112</v>
       </c>
       <c r="F327" t="n">
         <v>558733</v>
@@ -6992,16 +6992,16 @@
         <v>43700</v>
       </c>
       <c r="B329" t="n">
-        <v>143.2868499755859</v>
+        <v>143.2868804931641</v>
       </c>
       <c r="C329" t="n">
-        <v>148.3691982354048</v>
+        <v>148.3692298354337</v>
       </c>
       <c r="D329" t="n">
-        <v>142.3654788707114</v>
+        <v>142.3655091920537</v>
       </c>
       <c r="E329" t="n">
-        <v>147.9531005199104</v>
+        <v>147.9531320313178</v>
       </c>
       <c r="F329" t="n">
         <v>586733</v>
@@ -7012,16 +7012,16 @@
         <v>43703</v>
       </c>
       <c r="B330" t="n">
-        <v>143.5543060302734</v>
+        <v>143.5543518066406</v>
       </c>
       <c r="C330" t="n">
-        <v>146.2292431936976</v>
+        <v>146.2292898230444</v>
       </c>
       <c r="D330" t="n">
-        <v>141.2063210842834</v>
+        <v>141.2063661119289</v>
       </c>
       <c r="E330" t="n">
-        <v>143.316544587893</v>
+        <v>143.3165902884432</v>
       </c>
       <c r="F330" t="n">
         <v>278200</v>
@@ -7032,16 +7032,16 @@
         <v>43704</v>
       </c>
       <c r="B331" t="n">
-        <v>145.4862518310547</v>
+        <v>145.4862365722656</v>
       </c>
       <c r="C331" t="n">
-        <v>146.4670483074746</v>
+        <v>146.4670329458183</v>
       </c>
       <c r="D331" t="n">
-        <v>141.7710770153187</v>
+        <v>141.7710621461821</v>
       </c>
       <c r="E331" t="n">
-        <v>143.4057478874085</v>
+        <v>143.4057328468255</v>
       </c>
       <c r="F331" t="n">
         <v>495866</v>
@@ -7052,16 +7052,16 @@
         <v>43705</v>
       </c>
       <c r="B332" t="n">
-        <v>145.6348419189453</v>
+        <v>145.6348114013672</v>
       </c>
       <c r="C332" t="n">
-        <v>146.585918135298</v>
+        <v>146.5858874184231</v>
       </c>
       <c r="D332" t="n">
-        <v>143.9704358647023</v>
+        <v>143.9704056958981</v>
       </c>
       <c r="E332" t="n">
-        <v>145.6942822928319</v>
+        <v>145.6942517627981</v>
       </c>
       <c r="F332" t="n">
         <v>446600</v>
@@ -7092,16 +7092,16 @@
         <v>43707</v>
       </c>
       <c r="B334" t="n">
-        <v>153.6893157958984</v>
+        <v>153.6893463134766</v>
       </c>
       <c r="C334" t="n">
-        <v>153.6893157958984</v>
+        <v>153.6893463134766</v>
       </c>
       <c r="D334" t="n">
-        <v>149.8849663060119</v>
+        <v>149.884996068173</v>
       </c>
       <c r="E334" t="n">
-        <v>150.9846583640818</v>
+        <v>150.984688344605</v>
       </c>
       <c r="F334" t="n">
         <v>973933</v>
@@ -7112,16 +7112,16 @@
         <v>43710</v>
       </c>
       <c r="B335" t="n">
-        <v>155.1456756591797</v>
+        <v>155.1457061767578</v>
       </c>
       <c r="C335" t="n">
-        <v>155.8887104753308</v>
+        <v>155.8887411390659</v>
       </c>
       <c r="D335" t="n">
-        <v>152.1140809109343</v>
+        <v>152.1141108321895</v>
       </c>
       <c r="E335" t="n">
-        <v>153.6596060268775</v>
+        <v>153.6596362521417</v>
       </c>
       <c r="F335" t="n">
         <v>734566</v>
@@ -7152,16 +7152,16 @@
         <v>43712</v>
       </c>
       <c r="B337" t="n">
-        <v>149.4688873291016</v>
+        <v>149.4688720703125</v>
       </c>
       <c r="C337" t="n">
-        <v>156.1859212419549</v>
+        <v>156.1859052974459</v>
       </c>
       <c r="D337" t="n">
-        <v>147.9828176117963</v>
+        <v>147.9828025047152</v>
       </c>
       <c r="E337" t="n">
-        <v>155.9778799470986</v>
+        <v>155.9778640238278</v>
       </c>
       <c r="F337" t="n">
         <v>865766</v>
@@ -7172,16 +7172,16 @@
         <v>43713</v>
       </c>
       <c r="B338" t="n">
-        <v>149.2608642578125</v>
+        <v>149.2608795166016</v>
       </c>
       <c r="C338" t="n">
-        <v>150.2119405274403</v>
+        <v>150.211955883457</v>
       </c>
       <c r="D338" t="n">
-        <v>145.5159693223478</v>
+        <v>145.5159841983</v>
       </c>
       <c r="E338" t="n">
-        <v>150.2119405274403</v>
+        <v>150.211955883457</v>
       </c>
       <c r="F338" t="n">
         <v>845300</v>
@@ -7212,16 +7212,16 @@
         <v>43717</v>
       </c>
       <c r="B340" t="n">
-        <v>142.9004821777344</v>
+        <v>142.9004669189453</v>
       </c>
       <c r="C340" t="n">
-        <v>146.734537552183</v>
+        <v>146.7345218839969</v>
       </c>
       <c r="D340" t="n">
-        <v>139.7202860481167</v>
+        <v>139.7202711289063</v>
       </c>
       <c r="E340" t="n">
-        <v>146.734537552183</v>
+        <v>146.7345218839969</v>
       </c>
       <c r="F340" t="n">
         <v>1841333</v>
@@ -7272,16 +7272,16 @@
         <v>43720</v>
       </c>
       <c r="B343" t="n">
-        <v>148.3692169189453</v>
+        <v>148.3692016601562</v>
       </c>
       <c r="C343" t="n">
-        <v>154.4918329141216</v>
+        <v>154.4918170256621</v>
       </c>
       <c r="D343" t="n">
-        <v>148.339496729602</v>
+        <v>148.3394814738694</v>
       </c>
       <c r="E343" t="n">
-        <v>153.9568392717711</v>
+        <v>153.9568234383322</v>
       </c>
       <c r="F343" t="n">
         <v>700866</v>
@@ -7312,16 +7312,16 @@
         <v>43724</v>
       </c>
       <c r="B345" t="n">
-        <v>149.9444274902344</v>
+        <v>149.9444427490234</v>
       </c>
       <c r="C345" t="n">
-        <v>151.2521608669158</v>
+        <v>151.2521762587837</v>
       </c>
       <c r="D345" t="n">
-        <v>146.5264553438454</v>
+        <v>146.5264702548115</v>
       </c>
       <c r="E345" t="n">
-        <v>149.4985945201269</v>
+        <v>149.4986097335467</v>
       </c>
       <c r="F345" t="n">
         <v>541366</v>
@@ -7352,16 +7352,16 @@
         <v>43726</v>
       </c>
       <c r="B347" t="n">
-        <v>152.4707641601562</v>
+        <v>152.4707794189453</v>
       </c>
       <c r="C347" t="n">
-        <v>153.2137991026854</v>
+        <v>153.2138144358351</v>
       </c>
       <c r="D347" t="n">
-        <v>151.4007920288641</v>
+        <v>151.4008071805737</v>
       </c>
       <c r="E347" t="n">
-        <v>151.4305273342831</v>
+        <v>151.4305424889685</v>
       </c>
       <c r="F347" t="n">
         <v>459166</v>
@@ -7372,16 +7372,16 @@
         <v>43727</v>
       </c>
       <c r="B348" t="n">
-        <v>153.0354766845703</v>
+        <v>153.0354614257812</v>
       </c>
       <c r="C348" t="n">
-        <v>155.3834622457323</v>
+        <v>155.3834467528314</v>
       </c>
       <c r="D348" t="n">
-        <v>151.5494068120203</v>
+        <v>151.5493917014036</v>
       </c>
       <c r="E348" t="n">
-        <v>154.4026658047834</v>
+        <v>154.4026504096753</v>
       </c>
       <c r="F348" t="n">
         <v>446666</v>
@@ -7412,16 +7412,16 @@
         <v>43731</v>
       </c>
       <c r="B350" t="n">
-        <v>157.9395141601562</v>
+        <v>157.9394836425781</v>
       </c>
       <c r="C350" t="n">
-        <v>159.0986469194959</v>
+        <v>159.0986161779464</v>
       </c>
       <c r="D350" t="n">
-        <v>153.6893607092441</v>
+        <v>153.6893310128942</v>
       </c>
       <c r="E350" t="n">
-        <v>154.5512764519898</v>
+        <v>154.5512465890978</v>
       </c>
       <c r="F350" t="n">
         <v>685766</v>
@@ -7432,16 +7432,16 @@
         <v>43732</v>
       </c>
       <c r="B351" t="n">
-        <v>155.1456756591797</v>
+        <v>155.1457061767578</v>
       </c>
       <c r="C351" t="n">
-        <v>158.9202901064941</v>
+        <v>158.9203213665492</v>
       </c>
       <c r="D351" t="n">
-        <v>154.6998426758234</v>
+        <v>154.699873105705</v>
       </c>
       <c r="E351" t="n">
-        <v>158.6825135231762</v>
+        <v>158.68254473646</v>
       </c>
       <c r="F351" t="n">
         <v>630466</v>
@@ -7452,16 +7452,16 @@
         <v>43733</v>
       </c>
       <c r="B352" t="n">
-        <v>155.1456756591797</v>
+        <v>155.1457061767578</v>
       </c>
       <c r="C352" t="n">
-        <v>156.0373113917282</v>
+        <v>156.0373420846935</v>
       </c>
       <c r="D352" t="n">
-        <v>152.708514810688</v>
+        <v>152.70854484887</v>
       </c>
       <c r="E352" t="n">
-        <v>155.472597675254</v>
+        <v>155.4726282571386</v>
       </c>
       <c r="F352" t="n">
         <v>976666</v>
@@ -7492,16 +7492,16 @@
         <v>43735</v>
       </c>
       <c r="B354" t="n">
-        <v>158.1178283691406</v>
+        <v>158.1178131103516</v>
       </c>
       <c r="C354" t="n">
-        <v>158.8014077597781</v>
+        <v>158.8013924350218</v>
       </c>
       <c r="D354" t="n">
-        <v>156.2453659608186</v>
+        <v>156.2453508827271</v>
       </c>
       <c r="E354" t="n">
-        <v>157.3747934898065</v>
+        <v>157.3747783027223</v>
       </c>
       <c r="F354" t="n">
         <v>505200</v>
@@ -7532,16 +7532,16 @@
         <v>43739</v>
       </c>
       <c r="B356" t="n">
-        <v>158.1178283691406</v>
+        <v>158.1178131103516</v>
       </c>
       <c r="C356" t="n">
-        <v>159.4850022674988</v>
+        <v>159.4849868767739</v>
       </c>
       <c r="D356" t="n">
-        <v>156.8992402827326</v>
+        <v>156.8992251415405</v>
       </c>
       <c r="E356" t="n">
-        <v>159.3066811526586</v>
+        <v>159.3066657791421</v>
       </c>
       <c r="F356" t="n">
         <v>759100</v>
@@ -7612,16 +7612,16 @@
         <v>43745</v>
       </c>
       <c r="B360" t="n">
-        <v>161.4169158935547</v>
+        <v>161.4168853759766</v>
       </c>
       <c r="C360" t="n">
-        <v>163.7054763883588</v>
+        <v>163.7054454381041</v>
       </c>
       <c r="D360" t="n">
-        <v>159.6336439899879</v>
+        <v>159.6336138095562</v>
       </c>
       <c r="E360" t="n">
-        <v>161.6249723447499</v>
+        <v>161.6249417878365</v>
       </c>
       <c r="F360" t="n">
         <v>812666</v>
@@ -7632,16 +7632,16 @@
         <v>43746</v>
       </c>
       <c r="B361" t="n">
-        <v>160.6441192626953</v>
+        <v>160.6441345214844</v>
       </c>
       <c r="C361" t="n">
-        <v>163.7351543401261</v>
+        <v>163.7351698925173</v>
       </c>
       <c r="D361" t="n">
-        <v>158.2664139265933</v>
+        <v>158.2664289595359</v>
       </c>
       <c r="E361" t="n">
-        <v>161.4168742527825</v>
+        <v>161.4168895849718</v>
       </c>
       <c r="F361" t="n">
         <v>478600</v>
@@ -7652,16 +7652,16 @@
         <v>43747</v>
       </c>
       <c r="B362" t="n">
-        <v>162.2788391113281</v>
+        <v>162.27880859375</v>
       </c>
       <c r="C362" t="n">
-        <v>162.9029782012792</v>
+        <v>162.9029475663277</v>
       </c>
       <c r="D362" t="n">
-        <v>159.9605585353733</v>
+        <v>159.9605284537628</v>
       </c>
       <c r="E362" t="n">
-        <v>161.9816221024021</v>
+        <v>161.9815916407176</v>
       </c>
       <c r="F362" t="n">
         <v>623966</v>
@@ -7712,16 +7712,16 @@
         <v>43752</v>
       </c>
       <c r="B365" t="n">
-        <v>167.9259033203125</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C365" t="n">
-        <v>169.5902943979059</v>
+        <v>169.590263577854</v>
       </c>
       <c r="D365" t="n">
-        <v>166.3803930005229</v>
+        <v>166.3803627638141</v>
       </c>
       <c r="E365" t="n">
-        <v>167.2125885393196</v>
+        <v>167.2125581513739</v>
       </c>
       <c r="F365" t="n">
         <v>323333</v>
@@ -7752,16 +7752,16 @@
         <v>43754</v>
       </c>
       <c r="B367" t="n">
-        <v>170.7791290283203</v>
+        <v>170.7791442871094</v>
       </c>
       <c r="C367" t="n">
-        <v>172.8001771009563</v>
+        <v>172.8001925403221</v>
       </c>
       <c r="D367" t="n">
-        <v>167.301716372126</v>
+        <v>167.3017313202149</v>
       </c>
       <c r="E367" t="n">
-        <v>168.7580658386021</v>
+        <v>168.7580809168131</v>
       </c>
       <c r="F367" t="n">
         <v>599666</v>
@@ -7772,16 +7772,16 @@
         <v>43755</v>
       </c>
       <c r="B368" t="n">
-        <v>169.7686157226562</v>
+        <v>169.7686004638672</v>
       </c>
       <c r="C368" t="n">
-        <v>172.9785319548521</v>
+        <v>172.9785164075561</v>
       </c>
       <c r="D368" t="n">
-        <v>168.8769647662821</v>
+        <v>168.8769495876346</v>
       </c>
       <c r="E368" t="n">
-        <v>171.2546855328626</v>
+        <v>171.2546701405057</v>
       </c>
       <c r="F368" t="n">
         <v>460533</v>
@@ -7812,16 +7812,16 @@
         <v>43759</v>
       </c>
       <c r="B370" t="n">
-        <v>168.5203399658203</v>
+        <v>168.5203247070312</v>
       </c>
       <c r="C370" t="n">
-        <v>171.7302414131521</v>
+        <v>171.7302258637203</v>
       </c>
       <c r="D370" t="n">
-        <v>167.9853463132081</v>
+        <v>167.9853311028604</v>
       </c>
       <c r="E370" t="n">
-        <v>171.3141436372789</v>
+        <v>171.314128125523</v>
       </c>
       <c r="F370" t="n">
         <v>853400</v>
@@ -7852,16 +7852,16 @@
         <v>43761</v>
       </c>
       <c r="B372" t="n">
-        <v>165.8453826904297</v>
+        <v>165.8453674316406</v>
       </c>
       <c r="C372" t="n">
-        <v>168.758081900606</v>
+        <v>168.7580663738308</v>
       </c>
       <c r="D372" t="n">
-        <v>164.9537468623316</v>
+        <v>164.9537316855785</v>
       </c>
       <c r="E372" t="n">
-        <v>167.2422919225891</v>
+        <v>167.2422765352759</v>
       </c>
       <c r="F372" t="n">
         <v>595766</v>
@@ -7912,16 +7912,16 @@
         <v>43766</v>
       </c>
       <c r="B375" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0064086914062</v>
       </c>
       <c r="C375" t="n">
-        <v>170.5710921032597</v>
+        <v>170.5711074127329</v>
       </c>
       <c r="D375" t="n">
-        <v>167.6881130247363</v>
+        <v>167.68812807545</v>
       </c>
       <c r="E375" t="n">
-        <v>169.3525190838025</v>
+        <v>169.3525342839036</v>
       </c>
       <c r="F375" t="n">
         <v>598700</v>
@@ -7952,16 +7952,16 @@
         <v>43768</v>
       </c>
       <c r="B377" t="n">
-        <v>167.6286926269531</v>
+        <v>167.628662109375</v>
       </c>
       <c r="C377" t="n">
-        <v>169.4714200277931</v>
+        <v>169.4713891747379</v>
       </c>
       <c r="D377" t="n">
-        <v>166.3209588905653</v>
+        <v>166.3209286110662</v>
       </c>
       <c r="E377" t="n">
-        <v>169.1147626238536</v>
+        <v>169.1147318357295</v>
       </c>
       <c r="F377" t="n">
         <v>545966</v>
@@ -8032,16 +8032,16 @@
         <v>43774</v>
       </c>
       <c r="B381" t="n">
-        <v>161.5357971191406</v>
+        <v>161.5357818603516</v>
       </c>
       <c r="C381" t="n">
-        <v>166.885642578697</v>
+        <v>166.8856268145576</v>
       </c>
       <c r="D381" t="n">
-        <v>160.9710833150434</v>
+        <v>160.9710681095976</v>
       </c>
       <c r="E381" t="n">
-        <v>166.885642578697</v>
+        <v>166.8856268145576</v>
       </c>
       <c r="F381" t="n">
         <v>956400</v>
@@ -8052,16 +8052,16 @@
         <v>43775</v>
       </c>
       <c r="B382" t="n">
-        <v>163.4973907470703</v>
+        <v>163.4974212646484</v>
       </c>
       <c r="C382" t="n">
-        <v>164.5970829537148</v>
+        <v>164.5971136765558</v>
       </c>
       <c r="D382" t="n">
-        <v>160.1388737565751</v>
+        <v>160.1389036472698</v>
       </c>
       <c r="E382" t="n">
-        <v>161.9221604588475</v>
+        <v>161.9221906824013</v>
       </c>
       <c r="F382" t="n">
         <v>1813233</v>
@@ -8092,16 +8092,16 @@
         <v>43777</v>
       </c>
       <c r="B384" t="n">
-        <v>165.5184631347656</v>
+        <v>165.5184326171875</v>
       </c>
       <c r="C384" t="n">
-        <v>169.2039178193453</v>
+        <v>169.203886622259</v>
       </c>
       <c r="D384" t="n">
-        <v>163.4082540858343</v>
+        <v>163.4082239573274</v>
       </c>
       <c r="E384" t="n">
-        <v>164.6862675910438</v>
+        <v>164.6862372269023</v>
       </c>
       <c r="F384" t="n">
         <v>1517366</v>
@@ -8112,16 +8112,16 @@
         <v>43780</v>
       </c>
       <c r="B385" t="n">
-        <v>170.8385925292969</v>
+        <v>170.8385620117188</v>
       </c>
       <c r="C385" t="n">
-        <v>170.8385925292969</v>
+        <v>170.8385620117188</v>
       </c>
       <c r="D385" t="n">
-        <v>164.9834736868993</v>
+        <v>164.9834442152444</v>
       </c>
       <c r="E385" t="n">
-        <v>165.964285230937</v>
+        <v>165.9642555840758</v>
       </c>
       <c r="F385" t="n">
         <v>906700</v>
@@ -8132,16 +8132,16 @@
         <v>43781</v>
       </c>
       <c r="B386" t="n">
-        <v>167.9259033203125</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C386" t="n">
-        <v>171.6410781725318</v>
+        <v>171.641046979786</v>
       </c>
       <c r="D386" t="n">
-        <v>166.8856513382741</v>
+        <v>166.8856210097434</v>
       </c>
       <c r="E386" t="n">
-        <v>170.8980432020879</v>
+        <v>170.8980121443757</v>
       </c>
       <c r="F386" t="n">
         <v>771166</v>
@@ -8152,16 +8152,16 @@
         <v>43782</v>
       </c>
       <c r="B387" t="n">
-        <v>167.8961791992188</v>
+        <v>167.8961639404297</v>
       </c>
       <c r="C387" t="n">
-        <v>170.273885002126</v>
+        <v>170.2738695272456</v>
       </c>
       <c r="D387" t="n">
-        <v>164.9834797645522</v>
+        <v>164.9834647704759</v>
       </c>
       <c r="E387" t="n">
-        <v>168.2528365813633</v>
+        <v>168.2528212901604</v>
       </c>
       <c r="F387" t="n">
         <v>1028933</v>
@@ -8172,16 +8172,16 @@
         <v>43783</v>
       </c>
       <c r="B388" t="n">
-        <v>161.5060882568359</v>
+        <v>161.5060577392578</v>
       </c>
       <c r="C388" t="n">
-        <v>167.4800883151972</v>
+        <v>167.4800566687947</v>
       </c>
       <c r="D388" t="n">
-        <v>160.9710946031133</v>
+        <v>160.9710641866256</v>
       </c>
       <c r="E388" t="n">
-        <v>165.1023672975915</v>
+        <v>165.1023361004741</v>
       </c>
       <c r="F388" t="n">
         <v>1805133</v>
@@ -8192,16 +8192,16 @@
         <v>43787</v>
       </c>
       <c r="B389" t="n">
-        <v>161.6249542236328</v>
+        <v>161.6249389648438</v>
       </c>
       <c r="C389" t="n">
-        <v>163.0218634929487</v>
+        <v>163.0218481022793</v>
       </c>
       <c r="D389" t="n">
-        <v>158.8311356850011</v>
+        <v>158.8311206899726</v>
       </c>
       <c r="E389" t="n">
-        <v>161.5952340363779</v>
+        <v>161.5952187803947</v>
       </c>
       <c r="F389" t="n">
         <v>1204133</v>
@@ -8212,16 +8212,16 @@
         <v>43788</v>
       </c>
       <c r="B390" t="n">
-        <v>159.5741577148438</v>
+        <v>159.5741729736328</v>
       </c>
       <c r="C390" t="n">
-        <v>162.7840737329255</v>
+        <v>162.7840892986529</v>
       </c>
       <c r="D390" t="n">
-        <v>158.5339210107543</v>
+        <v>158.5339361700739</v>
       </c>
       <c r="E390" t="n">
-        <v>162.6354728086507</v>
+        <v>162.6354883601686</v>
       </c>
       <c r="F390" t="n">
         <v>1296633</v>
@@ -8272,16 +8272,16 @@
         <v>43794</v>
       </c>
       <c r="B393" t="n">
-        <v>171.7599334716797</v>
+        <v>171.7599487304688</v>
       </c>
       <c r="C393" t="n">
-        <v>172.2652068516232</v>
+        <v>172.2652221552997</v>
       </c>
       <c r="D393" t="n">
-        <v>167.9555986149949</v>
+        <v>167.9556135358149</v>
       </c>
       <c r="E393" t="n">
-        <v>169.203891738165</v>
+        <v>169.2039067698807</v>
       </c>
       <c r="F393" t="n">
         <v>1287433</v>
@@ -8292,16 +8292,16 @@
         <v>43795</v>
       </c>
       <c r="B394" t="n">
-        <v>169.4119720458984</v>
+        <v>169.4119567871094</v>
       </c>
       <c r="C394" t="n">
-        <v>172.5029926633038</v>
+        <v>172.5029771261092</v>
       </c>
       <c r="D394" t="n">
-        <v>167.4800841600201</v>
+        <v>167.4800690752345</v>
       </c>
       <c r="E394" t="n">
-        <v>170.9574823546011</v>
+        <v>170.9574669566093</v>
       </c>
       <c r="F394" t="n">
         <v>9961800</v>
@@ -8312,16 +8312,16 @@
         <v>43796</v>
       </c>
       <c r="B395" t="n">
-        <v>167.9556121826172</v>
+        <v>167.9556427001953</v>
       </c>
       <c r="C395" t="n">
-        <v>170.3927733728252</v>
+        <v>170.3928043332361</v>
       </c>
       <c r="D395" t="n">
-        <v>165.25096930539</v>
+        <v>165.2509993315338</v>
       </c>
       <c r="E395" t="n">
-        <v>169.7686192022788</v>
+        <v>169.7686500492808</v>
       </c>
       <c r="F395" t="n">
         <v>429100</v>
@@ -8332,16 +8332,16 @@
         <v>43797</v>
       </c>
       <c r="B396" t="n">
-        <v>163.6162872314453</v>
+        <v>163.6162719726562</v>
       </c>
       <c r="C396" t="n">
-        <v>168.49059460861</v>
+        <v>168.490578895245</v>
       </c>
       <c r="D396" t="n">
-        <v>163.2893500448137</v>
+        <v>163.2893348165146</v>
       </c>
       <c r="E396" t="n">
-        <v>166.4695462296235</v>
+        <v>166.4695307047406</v>
       </c>
       <c r="F396" t="n">
         <v>574533</v>
@@ -8352,16 +8352,16 @@
         <v>43798</v>
       </c>
       <c r="B397" t="n">
-        <v>165.5481719970703</v>
+        <v>165.5482025146484</v>
       </c>
       <c r="C397" t="n">
-        <v>166.0831504419819</v>
+        <v>166.0831810581793</v>
       </c>
       <c r="D397" t="n">
-        <v>161.0899628601699</v>
+        <v>161.0899925559102</v>
       </c>
       <c r="E397" t="n">
-        <v>163.6459894622932</v>
+        <v>163.6460196292181</v>
       </c>
       <c r="F397" t="n">
         <v>703133</v>
@@ -8412,16 +8412,16 @@
         <v>43803</v>
       </c>
       <c r="B400" t="n">
-        <v>172.4435119628906</v>
+        <v>172.4435272216797</v>
       </c>
       <c r="C400" t="n">
-        <v>173.7215402696162</v>
+        <v>173.7215556414925</v>
       </c>
       <c r="D400" t="n">
-        <v>170.8980020155698</v>
+        <v>170.8980171376033</v>
       </c>
       <c r="E400" t="n">
-        <v>170.8980020155698</v>
+        <v>170.8980171376033</v>
       </c>
       <c r="F400" t="n">
         <v>662400</v>
@@ -8432,16 +8432,16 @@
         <v>43804</v>
       </c>
       <c r="B401" t="n">
-        <v>172.3543853759766</v>
+        <v>172.3543701171875</v>
       </c>
       <c r="C401" t="n">
-        <v>174.7618113181715</v>
+        <v>174.7617958462494</v>
       </c>
       <c r="D401" t="n">
-        <v>169.1147488144879</v>
+        <v>169.1147338425086</v>
       </c>
       <c r="E401" t="n">
-        <v>172.7110427507926</v>
+        <v>172.7110274604281</v>
       </c>
       <c r="F401" t="n">
         <v>632400</v>
@@ -8452,16 +8452,16 @@
         <v>43805</v>
       </c>
       <c r="B402" t="n">
-        <v>171.7302398681641</v>
+        <v>171.730224609375</v>
       </c>
       <c r="C402" t="n">
-        <v>173.4243662634142</v>
+        <v>173.4243508540965</v>
       </c>
       <c r="D402" t="n">
-        <v>167.9556246122654</v>
+        <v>167.9556096888631</v>
       </c>
       <c r="E402" t="n">
-        <v>173.4243662634142</v>
+        <v>173.4243508540965</v>
       </c>
       <c r="F402" t="n">
         <v>837700</v>
@@ -8472,16 +8472,16 @@
         <v>43808</v>
       </c>
       <c r="B403" t="n">
-        <v>165.8453826904297</v>
+        <v>165.8453674316406</v>
       </c>
       <c r="C403" t="n">
-        <v>172.6218724288928</v>
+        <v>172.6218565466253</v>
       </c>
       <c r="D403" t="n">
-        <v>165.5779010122505</v>
+        <v>165.5778857780713</v>
       </c>
       <c r="E403" t="n">
-        <v>172.3840958200943</v>
+        <v>172.3840799597037</v>
       </c>
       <c r="F403" t="n">
         <v>793900</v>
@@ -8492,16 +8492,16 @@
         <v>43809</v>
       </c>
       <c r="B404" t="n">
-        <v>162.3382873535156</v>
+        <v>162.3382415771484</v>
       </c>
       <c r="C404" t="n">
-        <v>167.2720355191765</v>
+        <v>167.2719883515844</v>
       </c>
       <c r="D404" t="n">
-        <v>162.3382873535156</v>
+        <v>162.3382415771484</v>
       </c>
       <c r="E404" t="n">
-        <v>166.5884409006583</v>
+        <v>166.5883939258271</v>
       </c>
       <c r="F404" t="n">
         <v>1232166</v>
@@ -8512,16 +8512,16 @@
         <v>43810</v>
       </c>
       <c r="B405" t="n">
-        <v>167.0936737060547</v>
+        <v>167.0936889648438</v>
       </c>
       <c r="C405" t="n">
-        <v>167.0936737060547</v>
+        <v>167.0936889648438</v>
       </c>
       <c r="D405" t="n">
-        <v>161.9815905238091</v>
+        <v>161.981605315769</v>
       </c>
       <c r="E405" t="n">
-        <v>162.7840657095058</v>
+        <v>162.7840805747468</v>
       </c>
       <c r="F405" t="n">
         <v>789933</v>
@@ -8532,16 +8532,16 @@
         <v>43811</v>
       </c>
       <c r="B406" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0064086914062</v>
       </c>
       <c r="C406" t="n">
-        <v>170.214434741823</v>
+        <v>170.2144500192846</v>
       </c>
       <c r="D406" t="n">
-        <v>167.1234143540938</v>
+        <v>167.1234293541233</v>
       </c>
       <c r="E406" t="n">
-        <v>169.085022283454</v>
+        <v>169.0850374595461</v>
       </c>
       <c r="F406" t="n">
         <v>578333</v>
@@ -8552,16 +8552,16 @@
         <v>43812</v>
       </c>
       <c r="B407" t="n">
-        <v>166.9748077392578</v>
+        <v>166.9747924804688</v>
       </c>
       <c r="C407" t="n">
-        <v>171.3141366958159</v>
+        <v>171.3141210404826</v>
       </c>
       <c r="D407" t="n">
-        <v>166.2020525986495</v>
+        <v>166.2020374104777</v>
       </c>
       <c r="E407" t="n">
-        <v>170.808878370675</v>
+        <v>170.8088627615141</v>
       </c>
       <c r="F407" t="n">
         <v>591766</v>
@@ -8572,16 +8572,16 @@
         <v>43815</v>
       </c>
       <c r="B408" t="n">
-        <v>171.9085540771484</v>
+        <v>171.9085693359375</v>
       </c>
       <c r="C408" t="n">
-        <v>175.8317697781544</v>
+        <v>175.8317853851723</v>
       </c>
       <c r="D408" t="n">
-        <v>167.0342470781839</v>
+        <v>167.0342619043242</v>
       </c>
       <c r="E408" t="n">
-        <v>167.1828480073571</v>
+        <v>167.1828628466874</v>
       </c>
       <c r="F408" t="n">
         <v>666133</v>
@@ -8592,16 +8592,16 @@
         <v>43816</v>
       </c>
       <c r="B409" t="n">
-        <v>173.1568603515625</v>
+        <v>173.1568450927734</v>
       </c>
       <c r="C409" t="n">
-        <v>175.2373642201033</v>
+        <v>175.2373487779778</v>
       </c>
       <c r="D409" t="n">
-        <v>171.4032936690544</v>
+        <v>171.4032785647917</v>
       </c>
       <c r="E409" t="n">
-        <v>173.4243571614228</v>
+        <v>173.4243418790616</v>
       </c>
       <c r="F409" t="n">
         <v>614666</v>
@@ -8612,16 +8612,16 @@
         <v>43817</v>
       </c>
       <c r="B410" t="n">
-        <v>180.4683074951172</v>
+        <v>180.4683227539062</v>
       </c>
       <c r="C410" t="n">
-        <v>180.4683074951172</v>
+        <v>180.4683227539062</v>
       </c>
       <c r="D410" t="n">
-        <v>171.6410498735219</v>
+        <v>171.6410643859569</v>
       </c>
       <c r="E410" t="n">
-        <v>171.6410498735219</v>
+        <v>171.6410643859569</v>
       </c>
       <c r="F410" t="n">
         <v>804400</v>
@@ -8672,16 +8672,16 @@
         <v>43822</v>
       </c>
       <c r="B413" t="n">
-        <v>187.8392486572266</v>
+        <v>187.8392333984375</v>
       </c>
       <c r="C413" t="n">
-        <v>190.454731177498</v>
+        <v>190.4547157062448</v>
       </c>
       <c r="D413" t="n">
-        <v>186.1748424440982</v>
+        <v>186.1748273205142</v>
       </c>
       <c r="E413" t="n">
-        <v>190.2169545421696</v>
+        <v>190.2169390902317</v>
       </c>
       <c r="F413" t="n">
         <v>629966</v>
@@ -8812,16 +8812,16 @@
         <v>43837</v>
       </c>
       <c r="B420" t="n">
-        <v>193.9930419921875</v>
+        <v>193.9930572509766</v>
       </c>
       <c r="C420" t="n">
-        <v>200.1893853781668</v>
+        <v>200.1894011243377</v>
       </c>
       <c r="D420" t="n">
-        <v>193.933464244095</v>
+        <v>193.9334794981979</v>
       </c>
       <c r="E420" t="n">
-        <v>198.4019771752861</v>
+        <v>198.401992780866</v>
       </c>
       <c r="F420" t="n">
         <v>612400</v>
@@ -8832,16 +8832,16 @@
         <v>43838</v>
       </c>
       <c r="B421" t="n">
-        <v>190.0012054443359</v>
+        <v>190.0011901855469</v>
       </c>
       <c r="C421" t="n">
-        <v>196.0188016770089</v>
+        <v>196.0187859349532</v>
       </c>
       <c r="D421" t="n">
-        <v>188.0052747108529</v>
+        <v>188.0052596123549</v>
       </c>
       <c r="E421" t="n">
-        <v>193.9037154227282</v>
+        <v>193.9036998505329</v>
       </c>
       <c r="F421" t="n">
         <v>832966</v>
@@ -8852,16 +8852,16 @@
         <v>43839</v>
       </c>
       <c r="B422" t="n">
-        <v>188.8691558837891</v>
+        <v>188.8691864013672</v>
       </c>
       <c r="C422" t="n">
-        <v>191.5204719115027</v>
+        <v>191.5205028574819</v>
       </c>
       <c r="D422" t="n">
-        <v>187.2009182199783</v>
+        <v>187.2009484680017</v>
       </c>
       <c r="E422" t="n">
-        <v>190.0011786276671</v>
+        <v>190.001209328158</v>
       </c>
       <c r="F422" t="n">
         <v>950500</v>
@@ -8872,16 +8872,16 @@
         <v>43840</v>
       </c>
       <c r="B423" t="n">
-        <v>184.8475036621094</v>
+        <v>184.8475189208984</v>
       </c>
       <c r="C423" t="n">
-        <v>190.6267884348786</v>
+        <v>190.6268041707359</v>
       </c>
       <c r="D423" t="n">
-        <v>182.3153581162909</v>
+        <v>182.3153731660564</v>
       </c>
       <c r="E423" t="n">
-        <v>190.6267884348786</v>
+        <v>190.6268041707359</v>
       </c>
       <c r="F423" t="n">
         <v>656333</v>
@@ -8892,16 +8892,16 @@
         <v>43843</v>
       </c>
       <c r="B424" t="n">
-        <v>185.8603820800781</v>
+        <v>185.8603668212891</v>
       </c>
       <c r="C424" t="n">
-        <v>186.6945010191898</v>
+        <v>186.6944856919212</v>
       </c>
       <c r="D424" t="n">
-        <v>183.6559140609799</v>
+        <v>183.6558989831735</v>
       </c>
       <c r="E424" t="n">
-        <v>184.6985703108816</v>
+        <v>184.6985551474751</v>
       </c>
       <c r="F424" t="n">
         <v>736233</v>
@@ -8912,16 +8912,16 @@
         <v>43844</v>
       </c>
       <c r="B425" t="n">
-        <v>186.1880645751953</v>
+        <v>186.1880798339844</v>
       </c>
       <c r="C425" t="n">
-        <v>186.5157573870905</v>
+        <v>186.5157726727352</v>
       </c>
       <c r="D425" t="n">
-        <v>180.40877977781</v>
+        <v>180.4087945629656</v>
       </c>
       <c r="E425" t="n">
-        <v>185.3241568042139</v>
+        <v>185.3241719922026</v>
       </c>
       <c r="F425" t="n">
         <v>863500</v>
@@ -9032,16 +9032,16 @@
         <v>43852</v>
       </c>
       <c r="B431" t="n">
-        <v>190.5672302246094</v>
+        <v>190.5671997070312</v>
       </c>
       <c r="C431" t="n">
-        <v>193.2781244687579</v>
+        <v>193.2780935170552</v>
       </c>
       <c r="D431" t="n">
-        <v>189.4947850489844</v>
+        <v>189.4947547031485</v>
       </c>
       <c r="E431" t="n">
-        <v>191.4013491994205</v>
+        <v>191.4013185482659</v>
       </c>
       <c r="F431" t="n">
         <v>460300</v>
@@ -9072,16 +9072,16 @@
         <v>43854</v>
       </c>
       <c r="B433" t="n">
-        <v>192.1461181640625</v>
+        <v>192.1461029052734</v>
       </c>
       <c r="C433" t="n">
-        <v>193.1887745488464</v>
+        <v>193.1887592072574</v>
       </c>
       <c r="D433" t="n">
-        <v>190.0608053944947</v>
+        <v>190.0607903013054</v>
       </c>
       <c r="E433" t="n">
-        <v>191.8482141752633</v>
+        <v>191.8481989401316</v>
       </c>
       <c r="F433" t="n">
         <v>639666</v>
@@ -9092,16 +9092,16 @@
         <v>43857</v>
       </c>
       <c r="B434" t="n">
-        <v>182.4047393798828</v>
+        <v>182.4047241210938</v>
       </c>
       <c r="C434" t="n">
-        <v>189.7628958871874</v>
+        <v>189.7628800128631</v>
       </c>
       <c r="D434" t="n">
-        <v>180.5279641525161</v>
+        <v>180.5279490507258</v>
       </c>
       <c r="E434" t="n">
-        <v>189.7628958871874</v>
+        <v>189.7628800128631</v>
       </c>
       <c r="F434" t="n">
         <v>939566</v>
@@ -9112,16 +9112,16 @@
         <v>43858</v>
       </c>
       <c r="B435" t="n">
-        <v>186.1880645751953</v>
+        <v>186.1880798339844</v>
       </c>
       <c r="C435" t="n">
-        <v>186.7540684124517</v>
+        <v>186.7540837176268</v>
       </c>
       <c r="D435" t="n">
-        <v>182.4047255273511</v>
+        <v>182.4047404760818</v>
       </c>
       <c r="E435" t="n">
-        <v>184.4006561248688</v>
+        <v>184.4006712371732</v>
       </c>
       <c r="F435" t="n">
         <v>417866</v>
@@ -9132,16 +9132,16 @@
         <v>43859</v>
       </c>
       <c r="B436" t="n">
-        <v>182.6132659912109</v>
+        <v>182.6132507324219</v>
       </c>
       <c r="C436" t="n">
-        <v>187.5286435106423</v>
+        <v>187.5286278411344</v>
       </c>
       <c r="D436" t="n">
-        <v>181.1237613252075</v>
+        <v>181.1237461908784</v>
       </c>
       <c r="E436" t="n">
-        <v>186.9328355834309</v>
+        <v>186.9328199637075</v>
       </c>
       <c r="F436" t="n">
         <v>838300</v>
@@ -9152,16 +9152,16 @@
         <v>43860</v>
       </c>
       <c r="B437" t="n">
-        <v>179.0682373046875</v>
+        <v>179.0682525634766</v>
       </c>
       <c r="C437" t="n">
-        <v>182.523883588893</v>
+        <v>182.5238991421452</v>
       </c>
       <c r="D437" t="n">
-        <v>174.8678387517811</v>
+        <v>174.8678536526452</v>
       </c>
       <c r="E437" t="n">
-        <v>182.523883588893</v>
+        <v>182.5238991421452</v>
       </c>
       <c r="F437" t="n">
         <v>937800</v>
@@ -9212,16 +9212,16 @@
         <v>43865</v>
       </c>
       <c r="B440" t="n">
-        <v>182.7622222900391</v>
+        <v>182.76220703125</v>
       </c>
       <c r="C440" t="n">
-        <v>186.5753505305267</v>
+        <v>186.5753349533802</v>
       </c>
       <c r="D440" t="n">
-        <v>182.5238960929993</v>
+        <v>182.5238808541081</v>
       </c>
       <c r="E440" t="n">
-        <v>186.3668132141139</v>
+        <v>186.3667976543781</v>
       </c>
       <c r="F440" t="n">
         <v>732700</v>
@@ -9312,16 +9312,16 @@
         <v>43872</v>
       </c>
       <c r="B445" t="n">
-        <v>172.8123474121094</v>
+        <v>172.8123168945312</v>
       </c>
       <c r="C445" t="n">
-        <v>174.4210077635489</v>
+        <v>174.4209769618915</v>
       </c>
       <c r="D445" t="n">
-        <v>167.3905432189951</v>
+        <v>167.3905136588736</v>
       </c>
       <c r="E445" t="n">
-        <v>168.6119480766692</v>
+        <v>168.6119183008553</v>
       </c>
       <c r="F445" t="n">
         <v>924566</v>
@@ -9372,16 +9372,16 @@
         <v>43875</v>
       </c>
       <c r="B448" t="n">
-        <v>174.2422637939453</v>
+        <v>174.2422485351562</v>
       </c>
       <c r="C448" t="n">
-        <v>175.9998836105123</v>
+        <v>175.9998681978045</v>
       </c>
       <c r="D448" t="n">
-        <v>172.9910701287168</v>
+        <v>172.9910549794976</v>
       </c>
       <c r="E448" t="n">
-        <v>175.7913462822991</v>
+        <v>175.7913308878533</v>
       </c>
       <c r="F448" t="n">
         <v>468100</v>
@@ -9392,16 +9392,16 @@
         <v>43878</v>
       </c>
       <c r="B449" t="n">
-        <v>178.3532867431641</v>
+        <v>178.353271484375</v>
       </c>
       <c r="C449" t="n">
-        <v>178.3532867431641</v>
+        <v>178.353271484375</v>
       </c>
       <c r="D449" t="n">
-        <v>173.4677133273196</v>
+        <v>173.4676984865096</v>
       </c>
       <c r="E449" t="n">
-        <v>173.9741394517339</v>
+        <v>173.9741245675972</v>
       </c>
       <c r="F449" t="n">
         <v>278100</v>
@@ -9412,16 +9412,16 @@
         <v>43879</v>
       </c>
       <c r="B450" t="n">
-        <v>175.7019500732422</v>
+        <v>175.7019805908203</v>
       </c>
       <c r="C450" t="n">
-        <v>177.5191473486881</v>
+        <v>177.5191781818942</v>
       </c>
       <c r="D450" t="n">
-        <v>172.7825188816086</v>
+        <v>172.7825488921122</v>
       </c>
       <c r="E450" t="n">
-        <v>177.5191473486881</v>
+        <v>177.5191781818942</v>
       </c>
       <c r="F450" t="n">
         <v>669733</v>
@@ -9432,16 +9432,16 @@
         <v>43880</v>
       </c>
       <c r="B451" t="n">
-        <v>177.3702087402344</v>
+        <v>177.3701934814453</v>
       </c>
       <c r="C451" t="n">
-        <v>178.3234983824099</v>
+        <v>178.3234830416113</v>
       </c>
       <c r="D451" t="n">
-        <v>173.1995987537694</v>
+        <v>173.1995838537692</v>
       </c>
       <c r="E451" t="n">
-        <v>174.9870073628329</v>
+        <v>174.9869923090657</v>
       </c>
       <c r="F451" t="n">
         <v>740433</v>
@@ -9452,16 +9452,16 @@
         <v>43881</v>
       </c>
       <c r="B452" t="n">
-        <v>172.1569519042969</v>
+        <v>172.1569366455078</v>
       </c>
       <c r="C452" t="n">
-        <v>177.0723144845919</v>
+        <v>177.0722987901394</v>
       </c>
       <c r="D452" t="n">
-        <v>171.3228328916945</v>
+        <v>171.3228177068359</v>
       </c>
       <c r="E452" t="n">
-        <v>175.7019804358953</v>
+        <v>175.7019648628997</v>
       </c>
       <c r="F452" t="n">
         <v>757533</v>
@@ -9492,16 +9492,16 @@
         <v>43887</v>
       </c>
       <c r="B454" t="n">
-        <v>156.4575500488281</v>
+        <v>156.4575653076172</v>
       </c>
       <c r="C454" t="n">
-        <v>160.5685818573121</v>
+        <v>160.5685975170366</v>
       </c>
       <c r="D454" t="n">
-        <v>154.1637155461845</v>
+        <v>154.1637305812634</v>
       </c>
       <c r="E454" t="n">
-        <v>159.5259256782859</v>
+        <v>159.5259412363235</v>
       </c>
       <c r="F454" t="n">
         <v>1832133</v>
@@ -9572,16 +9572,16 @@
         <v>43893</v>
       </c>
       <c r="B458" t="n">
-        <v>165.0967102050781</v>
+        <v>165.0966796875</v>
       </c>
       <c r="C458" t="n">
-        <v>168.6417389799487</v>
+        <v>168.6417078070837</v>
       </c>
       <c r="D458" t="n">
-        <v>161.0154663573165</v>
+        <v>161.0154365941427</v>
       </c>
       <c r="E458" t="n">
-        <v>161.1644259318055</v>
+        <v>161.1643961410971</v>
       </c>
       <c r="F458" t="n">
         <v>1281800</v>
@@ -9592,16 +9592,16 @@
         <v>43894</v>
       </c>
       <c r="B459" t="n">
-        <v>159.4663543701172</v>
+        <v>159.4663391113281</v>
       </c>
       <c r="C459" t="n">
-        <v>169.7439418828748</v>
+        <v>169.7439256406586</v>
       </c>
       <c r="D459" t="n">
-        <v>159.0790837910523</v>
+        <v>159.0790685693198</v>
       </c>
       <c r="E459" t="n">
-        <v>167.5692628035011</v>
+        <v>167.5692467693725</v>
       </c>
       <c r="F459" t="n">
         <v>1186600</v>
@@ -9612,16 +9612,16 @@
         <v>43895</v>
       </c>
       <c r="B460" t="n">
-        <v>152.8231811523438</v>
+        <v>152.8231658935547</v>
       </c>
       <c r="C460" t="n">
-        <v>161.7602096443411</v>
+        <v>161.7601934932251</v>
       </c>
       <c r="D460" t="n">
-        <v>151.6911581494385</v>
+        <v>151.6911430036774</v>
       </c>
       <c r="E460" t="n">
-        <v>156.397998609953</v>
+        <v>156.3979829942326</v>
       </c>
       <c r="F460" t="n">
         <v>1000500</v>
@@ -9632,16 +9632,16 @@
         <v>43896</v>
       </c>
       <c r="B461" t="n">
-        <v>148.9802398681641</v>
+        <v>148.9802703857422</v>
       </c>
       <c r="C461" t="n">
-        <v>152.8231566550619</v>
+        <v>152.8231879598351</v>
       </c>
       <c r="D461" t="n">
-        <v>147.8780059247562</v>
+        <v>147.8780362165492</v>
       </c>
       <c r="E461" t="n">
-        <v>151.9294600099305</v>
+        <v>151.9294911316361</v>
       </c>
       <c r="F461" t="n">
         <v>1046833</v>
@@ -9672,16 +9672,16 @@
         <v>43900</v>
       </c>
       <c r="B463" t="n">
-        <v>145.6437683105469</v>
+        <v>145.6437530517578</v>
       </c>
       <c r="C463" t="n">
-        <v>147.3715992239526</v>
+        <v>147.3715837841424</v>
       </c>
       <c r="D463" t="n">
-        <v>136.9152774017098</v>
+        <v>136.9152630573862</v>
       </c>
       <c r="E463" t="n">
-        <v>142.4562215733386</v>
+        <v>142.456206648502</v>
       </c>
       <c r="F463" t="n">
         <v>1718533</v>
@@ -9732,16 +9732,16 @@
         <v>43903</v>
       </c>
       <c r="B466" t="n">
-        <v>129.9146118164062</v>
+        <v>129.9145812988281</v>
       </c>
       <c r="C466" t="n">
-        <v>137.0344430157189</v>
+        <v>137.0344108256576</v>
       </c>
       <c r="D466" t="n">
-        <v>118.7135292408355</v>
+        <v>118.7135013544465</v>
       </c>
       <c r="E466" t="n">
-        <v>136.945076363282</v>
+        <v>136.9450441942133</v>
       </c>
       <c r="F466" t="n">
         <v>2459466</v>
@@ -9752,16 +9752,16 @@
         <v>43906</v>
       </c>
       <c r="B467" t="n">
-        <v>110.2233352661133</v>
+        <v>110.2233428955078</v>
       </c>
       <c r="C467" t="n">
-        <v>120.6796558589259</v>
+        <v>120.6796642120818</v>
       </c>
       <c r="D467" t="n">
-        <v>106.3208330928401</v>
+        <v>106.3208404521129</v>
       </c>
       <c r="E467" t="n">
-        <v>109.7466904828687</v>
+        <v>109.746698079271</v>
       </c>
       <c r="F467" t="n">
         <v>2066566</v>
@@ -9792,16 +9792,16 @@
         <v>43908</v>
       </c>
       <c r="B469" t="n">
-        <v>94.49416351318359</v>
+        <v>94.49415588378906</v>
       </c>
       <c r="C469" t="n">
-        <v>104.8611174739333</v>
+        <v>104.8611090075179</v>
       </c>
       <c r="D469" t="n">
-        <v>85.43798081276944</v>
+        <v>85.43797391456495</v>
       </c>
       <c r="E469" t="n">
-        <v>103.6695168794615</v>
+        <v>103.6695085092552</v>
       </c>
       <c r="F469" t="n">
         <v>1809666</v>
@@ -9812,16 +9812,16 @@
         <v>43909</v>
       </c>
       <c r="B470" t="n">
-        <v>107.5422286987305</v>
+        <v>107.5422210693359</v>
       </c>
       <c r="C470" t="n">
-        <v>109.0615297704648</v>
+        <v>109.0615220332861</v>
       </c>
       <c r="D470" t="n">
-        <v>84.36554051690753</v>
+        <v>84.36553453174244</v>
       </c>
       <c r="E470" t="n">
-        <v>90.8597815499253</v>
+        <v>90.85977510403768</v>
       </c>
       <c r="F470" t="n">
         <v>2314466</v>
@@ -9932,16 +9932,16 @@
         <v>43917</v>
       </c>
       <c r="B476" t="n">
-        <v>135.544921875</v>
+        <v>135.5449066162109</v>
       </c>
       <c r="C476" t="n">
-        <v>143.9457195368442</v>
+        <v>143.9457033323465</v>
       </c>
       <c r="D476" t="n">
-        <v>133.7277244008504</v>
+        <v>133.72770934663</v>
       </c>
       <c r="E476" t="n">
-        <v>141.3837848967248</v>
+        <v>141.3837689806335</v>
       </c>
       <c r="F476" t="n">
         <v>773066</v>
@@ -10012,16 +10012,16 @@
         <v>43923</v>
       </c>
       <c r="B480" t="n">
-        <v>121.573371887207</v>
+        <v>121.573356628418</v>
       </c>
       <c r="C480" t="n">
-        <v>124.3438514920716</v>
+        <v>124.343835885557</v>
       </c>
       <c r="D480" t="n">
-        <v>116.4792610496121</v>
+        <v>116.4792464301897</v>
       </c>
       <c r="E480" t="n">
-        <v>118.4156216728895</v>
+        <v>118.4156068104326</v>
       </c>
       <c r="F480" t="n">
         <v>765700</v>
@@ -10092,16 +10092,16 @@
         <v>43929</v>
       </c>
       <c r="B484" t="n">
-        <v>148.9206390380859</v>
+        <v>148.9206848144531</v>
       </c>
       <c r="C484" t="n">
-        <v>152.5252442421911</v>
+        <v>152.5252911265695</v>
       </c>
       <c r="D484" t="n">
-        <v>142.0987142883857</v>
+        <v>142.0987579677773</v>
       </c>
       <c r="E484" t="n">
-        <v>144.3329707070583</v>
+        <v>144.3330150732328</v>
       </c>
       <c r="F484" t="n">
         <v>859700</v>
@@ -10172,16 +10172,16 @@
         <v>43936</v>
       </c>
       <c r="B488" t="n">
-        <v>155.0574188232422</v>
+        <v>155.0574340820312</v>
       </c>
       <c r="C488" t="n">
-        <v>160.8069149169485</v>
+        <v>160.8069307415302</v>
       </c>
       <c r="D488" t="n">
-        <v>148.0865483834452</v>
+        <v>148.0865629562494</v>
       </c>
       <c r="E488" t="n">
-        <v>154.610570485105</v>
+        <v>154.6105856999209</v>
       </c>
       <c r="F488" t="n">
         <v>821233</v>
@@ -10232,16 +10232,16 @@
         <v>43941</v>
       </c>
       <c r="B491" t="n">
-        <v>161.0750122070312</v>
+        <v>161.0750274658203</v>
       </c>
       <c r="C491" t="n">
-        <v>165.9308115454324</v>
+        <v>165.930827264216</v>
       </c>
       <c r="D491" t="n">
-        <v>150.7378622318755</v>
+        <v>150.7378765114165</v>
       </c>
       <c r="E491" t="n">
-        <v>151.9294628315219</v>
+        <v>151.9294772239444</v>
       </c>
       <c r="F491" t="n">
         <v>652266</v>
@@ -10292,16 +10292,16 @@
         <v>43945</v>
       </c>
       <c r="B494" t="n">
-        <v>148.9504699707031</v>
+        <v>148.9504547119141</v>
       </c>
       <c r="C494" t="n">
-        <v>152.0188460156135</v>
+        <v>152.0188304424938</v>
       </c>
       <c r="D494" t="n">
-        <v>136.1109315801753</v>
+        <v>136.1109176366947</v>
       </c>
       <c r="E494" t="n">
-        <v>146.9545391278248</v>
+        <v>146.954524073503</v>
       </c>
       <c r="F494" t="n">
         <v>1301233</v>
@@ -10312,16 +10312,16 @@
         <v>43948</v>
       </c>
       <c r="B495" t="n">
-        <v>156.9639892578125</v>
+        <v>156.9639739990234</v>
       </c>
       <c r="C495" t="n">
-        <v>157.9172788832115</v>
+        <v>157.9172635317512</v>
       </c>
       <c r="D495" t="n">
-        <v>152.8231682250355</v>
+        <v>152.8231533687841</v>
       </c>
       <c r="E495" t="n">
-        <v>153.8658244913087</v>
+        <v>153.8658095336986</v>
       </c>
       <c r="F495" t="n">
         <v>935633</v>
@@ -10352,16 +10352,16 @@
         <v>43950</v>
       </c>
       <c r="B497" t="n">
-        <v>161.9591369628906</v>
+        <v>161.9591217041016</v>
       </c>
       <c r="C497" t="n">
-        <v>164.790060292696</v>
+        <v>164.7900447671948</v>
       </c>
       <c r="D497" t="n">
-        <v>159.7241903125012</v>
+        <v>159.724175264275</v>
       </c>
       <c r="E497" t="n">
-        <v>161.3631451267727</v>
+        <v>161.3631299241343</v>
       </c>
       <c r="F497" t="n">
         <v>594666</v>
@@ -10372,16 +10372,16 @@
         <v>43951</v>
       </c>
       <c r="B498" t="n">
-        <v>156.2674407958984</v>
+        <v>156.2674560546875</v>
       </c>
       <c r="C498" t="n">
-        <v>162.1081054364251</v>
+        <v>162.108121265528</v>
       </c>
       <c r="D498" t="n">
-        <v>155.4926606076694</v>
+        <v>155.4926757908048</v>
       </c>
       <c r="E498" t="n">
-        <v>159.0983788998354</v>
+        <v>159.0983944350523</v>
       </c>
       <c r="F498" t="n">
         <v>826166</v>
@@ -10452,16 +10452,16 @@
         <v>43958</v>
       </c>
       <c r="B502" t="n">
-        <v>158.7109985351562</v>
+        <v>158.7110137939453</v>
       </c>
       <c r="C502" t="n">
-        <v>165.0880440212726</v>
+        <v>165.0880598931634</v>
       </c>
       <c r="D502" t="n">
-        <v>156.9826344633917</v>
+        <v>156.9826495560124</v>
       </c>
       <c r="E502" t="n">
-        <v>157.9660163733665</v>
+        <v>157.9660315605315</v>
       </c>
       <c r="F502" t="n">
         <v>1272300</v>
@@ -10472,16 +10472,16 @@
         <v>43959</v>
       </c>
       <c r="B503" t="n">
-        <v>150.7843780517578</v>
+        <v>150.7843933105469</v>
       </c>
       <c r="C503" t="n">
-        <v>163.4490735821289</v>
+        <v>163.4490901225356</v>
       </c>
       <c r="D503" t="n">
-        <v>150.7843780517578</v>
+        <v>150.7843933105469</v>
       </c>
       <c r="E503" t="n">
-        <v>163.4490735821289</v>
+        <v>163.4490901225356</v>
       </c>
       <c r="F503" t="n">
         <v>913666</v>
@@ -10492,16 +10492,16 @@
         <v>43962</v>
       </c>
       <c r="B504" t="n">
-        <v>146.9700775146484</v>
+        <v>146.9700622558594</v>
       </c>
       <c r="C504" t="n">
-        <v>152.6915504169773</v>
+        <v>152.6915345641711</v>
       </c>
       <c r="D504" t="n">
-        <v>146.5826873832784</v>
+        <v>146.5826721647091</v>
       </c>
       <c r="E504" t="n">
-        <v>149.9500062657109</v>
+        <v>149.9499906975384</v>
       </c>
       <c r="F504" t="n">
         <v>466500</v>
@@ -10532,16 +10532,16 @@
         <v>43964</v>
       </c>
       <c r="B506" t="n">
-        <v>145.7781066894531</v>
+        <v>145.7781219482422</v>
       </c>
       <c r="C506" t="n">
-        <v>153.9431125479351</v>
+        <v>153.9431286613662</v>
       </c>
       <c r="D506" t="n">
-        <v>145.7781066894531</v>
+        <v>145.7781219482422</v>
       </c>
       <c r="E506" t="n">
-        <v>152.3041578240206</v>
+        <v>152.3041737659001</v>
       </c>
       <c r="F506" t="n">
         <v>632666</v>
@@ -10592,16 +10592,16 @@
         <v>43969</v>
       </c>
       <c r="B509" t="n">
-        <v>147.6256713867188</v>
+        <v>147.6256561279297</v>
       </c>
       <c r="C509" t="n">
-        <v>148.3408555281376</v>
+        <v>148.3408401954261</v>
       </c>
       <c r="D509" t="n">
-        <v>142.4405939397833</v>
+        <v>142.4405792169308</v>
       </c>
       <c r="E509" t="n">
-        <v>144.4967521355379</v>
+        <v>144.4967372001582</v>
       </c>
       <c r="F509" t="n">
         <v>822866</v>
@@ -10612,16 +10612,16 @@
         <v>43970</v>
       </c>
       <c r="B510" t="n">
-        <v>150.1586151123047</v>
+        <v>150.1585998535156</v>
       </c>
       <c r="C510" t="n">
-        <v>154.9563024492492</v>
+        <v>154.9562867029296</v>
       </c>
       <c r="D510" t="n">
-        <v>145.807914078008</v>
+        <v>145.8078992613276</v>
       </c>
       <c r="E510" t="n">
-        <v>148.2216643630295</v>
+        <v>148.2216493010691</v>
       </c>
       <c r="F510" t="n">
         <v>591566</v>
@@ -10632,16 +10632,16 @@
         <v>43971</v>
       </c>
       <c r="B511" t="n">
-        <v>151.6783752441406</v>
+        <v>151.6783599853516</v>
       </c>
       <c r="C511" t="n">
-        <v>154.1815197188895</v>
+        <v>154.181504208285</v>
       </c>
       <c r="D511" t="n">
-        <v>149.3540343816533</v>
+        <v>149.3540193566921</v>
       </c>
       <c r="E511" t="n">
-        <v>150.7546045770118</v>
+        <v>150.7545894111537</v>
       </c>
       <c r="F511" t="n">
         <v>544933</v>
@@ -10652,16 +10652,16 @@
         <v>43972</v>
       </c>
       <c r="B512" t="n">
-        <v>156.1780395507812</v>
+        <v>156.1780548095703</v>
       </c>
       <c r="C512" t="n">
-        <v>158.6811835921673</v>
+        <v>158.6811990955166</v>
       </c>
       <c r="D512" t="n">
-        <v>146.1952766127041</v>
+        <v>146.1952908961648</v>
       </c>
       <c r="E512" t="n">
-        <v>152.125335202675</v>
+        <v>152.1253500655098</v>
       </c>
       <c r="F512" t="n">
         <v>1784500</v>
@@ -10672,16 +10672,16 @@
         <v>43973</v>
       </c>
       <c r="B513" t="n">
-        <v>155.5522918701172</v>
+        <v>155.5522766113281</v>
       </c>
       <c r="C513" t="n">
-        <v>156.95284690906</v>
+        <v>156.9528315128846</v>
       </c>
       <c r="D513" t="n">
-        <v>153.406739462751</v>
+        <v>153.4067244144283</v>
       </c>
       <c r="E513" t="n">
-        <v>156.4462644615022</v>
+        <v>156.4462491150195</v>
       </c>
       <c r="F513" t="n">
         <v>725600</v>
@@ -10712,16 +10712,16 @@
         <v>43977</v>
       </c>
       <c r="B515" t="n">
-        <v>163.3298950195312</v>
+        <v>163.3298797607422</v>
       </c>
       <c r="C515" t="n">
-        <v>164.9092688487182</v>
+        <v>164.9092534423791</v>
       </c>
       <c r="D515" t="n">
-        <v>160.9459579726372</v>
+        <v>160.945942936563</v>
       </c>
       <c r="E515" t="n">
-        <v>164.9092688487182</v>
+        <v>164.9092534423791</v>
       </c>
       <c r="F515" t="n">
         <v>734300</v>
@@ -10772,16 +10772,16 @@
         <v>43980</v>
       </c>
       <c r="B518" t="n">
-        <v>163.4788818359375</v>
+        <v>163.4788970947266</v>
       </c>
       <c r="C518" t="n">
-        <v>165.0582403275507</v>
+        <v>165.0582557337539</v>
       </c>
       <c r="D518" t="n">
-        <v>157.9958090679723</v>
+        <v>157.9958238149825</v>
       </c>
       <c r="E518" t="n">
-        <v>163.9556661593735</v>
+        <v>163.9556814626646</v>
       </c>
       <c r="F518" t="n">
         <v>1761600</v>
@@ -10792,16 +10792,16 @@
         <v>43983</v>
       </c>
       <c r="B519" t="n">
-        <v>162.4061279296875</v>
+        <v>162.4061126708984</v>
       </c>
       <c r="C519" t="n">
-        <v>164.7304688752928</v>
+        <v>164.7304533981214</v>
       </c>
       <c r="D519" t="n">
-        <v>160.4095809876987</v>
+        <v>160.4095659164942</v>
       </c>
       <c r="E519" t="n">
-        <v>161.8995454641179</v>
+        <v>161.8995302529245</v>
       </c>
       <c r="F519" t="n">
         <v>557733</v>
@@ -10852,16 +10852,16 @@
         <v>43986</v>
       </c>
       <c r="B522" t="n">
-        <v>174.8026123046875</v>
+        <v>174.8025970458984</v>
       </c>
       <c r="C522" t="n">
-        <v>176.9779626683967</v>
+        <v>176.977947219718</v>
       </c>
       <c r="D522" t="n">
-        <v>169.7963387860876</v>
+        <v>169.7963239643039</v>
       </c>
       <c r="E522" t="n">
-        <v>174.6238238589201</v>
+        <v>174.6238086157378</v>
       </c>
       <c r="F522" t="n">
         <v>1106633</v>
@@ -10872,16 +10872,16 @@
         <v>43987</v>
       </c>
       <c r="B523" t="n">
-        <v>177.4547576904297</v>
+        <v>177.4547271728516</v>
       </c>
       <c r="C523" t="n">
-        <v>182.3716524386734</v>
+        <v>182.371621075518</v>
       </c>
       <c r="D523" t="n">
-        <v>175.1006187393156</v>
+        <v>175.1005886265878</v>
       </c>
       <c r="E523" t="n">
-        <v>178.7957317411692</v>
+        <v>178.7957009929787</v>
       </c>
       <c r="F523" t="n">
         <v>929700</v>
@@ -10912,16 +10912,16 @@
         <v>43991</v>
       </c>
       <c r="B525" t="n">
-        <v>179.0639038085938</v>
+        <v>179.0639190673828</v>
       </c>
       <c r="C525" t="n">
-        <v>181.8352305827343</v>
+        <v>181.8352460776798</v>
       </c>
       <c r="D525" t="n">
-        <v>173.7000235344026</v>
+        <v>173.7000383361128</v>
       </c>
       <c r="E525" t="n">
-        <v>178.1699161845453</v>
+        <v>178.1699313671539</v>
       </c>
       <c r="F525" t="n">
         <v>591500</v>
@@ -10952,16 +10952,16 @@
         <v>43994</v>
       </c>
       <c r="B527" t="n">
-        <v>177.9315643310547</v>
+        <v>177.9315338134766</v>
       </c>
       <c r="C527" t="n">
-        <v>180.2261072216798</v>
+        <v>180.2260763105577</v>
       </c>
       <c r="D527" t="n">
-        <v>171.763104670555</v>
+        <v>171.763075210948</v>
       </c>
       <c r="E527" t="n">
-        <v>174.0874456384582</v>
+        <v>174.0874157801964</v>
       </c>
       <c r="F527" t="n">
         <v>1048900</v>
@@ -10972,16 +10972,16 @@
         <v>43997</v>
       </c>
       <c r="B528" t="n">
-        <v>180.3750610351562</v>
+        <v>180.3750915527344</v>
       </c>
       <c r="C528" t="n">
-        <v>182.8782051158919</v>
+        <v>182.8782360569759</v>
       </c>
       <c r="D528" t="n">
-        <v>173.5212318302438</v>
+        <v>173.5212611882256</v>
       </c>
       <c r="E528" t="n">
-        <v>175.7859761843905</v>
+        <v>175.7860059255433</v>
       </c>
       <c r="F528" t="n">
         <v>826966</v>
@@ -11012,16 +11012,16 @@
         <v>43999</v>
       </c>
       <c r="B530" t="n">
-        <v>181.2392730712891</v>
+        <v>181.2392425537109</v>
       </c>
       <c r="C530" t="n">
-        <v>186.0667586516717</v>
+        <v>186.066727321228</v>
       </c>
       <c r="D530" t="n">
-        <v>180.6134982886098</v>
+        <v>180.6134678764014</v>
       </c>
       <c r="E530" t="n">
-        <v>182.0438666319384</v>
+        <v>182.0438359788805</v>
       </c>
       <c r="F530" t="n">
         <v>934766</v>
@@ -11092,16 +11092,16 @@
         <v>44005</v>
       </c>
       <c r="B534" t="n">
-        <v>185.9475555419922</v>
+        <v>185.9475402832031</v>
       </c>
       <c r="C534" t="n">
-        <v>188.8380901381925</v>
+        <v>188.8380746422072</v>
       </c>
       <c r="D534" t="n">
-        <v>179.6003077546513</v>
+        <v>179.6002930167151</v>
       </c>
       <c r="E534" t="n">
-        <v>182.6696308050322</v>
+        <v>182.6696158152284</v>
       </c>
       <c r="F534" t="n">
         <v>796833</v>
@@ -11112,16 +11112,16 @@
         <v>44006</v>
       </c>
       <c r="B535" t="n">
-        <v>180.9114685058594</v>
+        <v>180.9114990234375</v>
       </c>
       <c r="C535" t="n">
-        <v>188.5698764502466</v>
+        <v>188.5699082597056</v>
       </c>
       <c r="D535" t="n">
-        <v>180.9114685058594</v>
+        <v>180.9114990234375</v>
       </c>
       <c r="E535" t="n">
-        <v>185.1131635496551</v>
+        <v>185.1131947760084</v>
       </c>
       <c r="F535" t="n">
         <v>509333</v>
@@ -11132,16 +11132,16 @@
         <v>44007</v>
       </c>
       <c r="B536" t="n">
-        <v>184.9939727783203</v>
+        <v>184.9939880371094</v>
       </c>
       <c r="C536" t="n">
-        <v>185.7687530010886</v>
+        <v>185.7687683237836</v>
       </c>
       <c r="D536" t="n">
-        <v>180.0174823204999</v>
+        <v>180.017497168815</v>
       </c>
       <c r="E536" t="n">
-        <v>182.0736403278702</v>
+        <v>182.0736553457825</v>
       </c>
       <c r="F536" t="n">
         <v>496966</v>
@@ -11152,16 +11152,16 @@
         <v>44008</v>
       </c>
       <c r="B537" t="n">
-        <v>182.7292175292969</v>
+        <v>182.7292022705078</v>
       </c>
       <c r="C537" t="n">
-        <v>187.1693124594684</v>
+        <v>187.1692968299095</v>
       </c>
       <c r="D537" t="n">
-        <v>182.669621380978</v>
+        <v>182.6696061271655</v>
       </c>
       <c r="E537" t="n">
-        <v>182.6994194551374</v>
+        <v>182.6994041988366</v>
       </c>
       <c r="F537" t="n">
         <v>565500</v>
@@ -11172,16 +11172,16 @@
         <v>44011</v>
       </c>
       <c r="B538" t="n">
-        <v>188.0334930419922</v>
+        <v>188.0335083007812</v>
       </c>
       <c r="C538" t="n">
-        <v>188.0334930419922</v>
+        <v>188.0335083007812</v>
       </c>
       <c r="D538" t="n">
-        <v>182.0736359893566</v>
+        <v>182.0736507645074</v>
       </c>
       <c r="E538" t="n">
-        <v>184.1297787910318</v>
+        <v>184.1297937330371</v>
       </c>
       <c r="F538" t="n">
         <v>392600</v>
@@ -11212,16 +11212,16 @@
         <v>44013</v>
       </c>
       <c r="B540" t="n">
-        <v>187.7057037353516</v>
+        <v>187.7057189941406</v>
       </c>
       <c r="C540" t="n">
-        <v>189.9108521119912</v>
+        <v>189.910867550039</v>
       </c>
       <c r="D540" t="n">
-        <v>185.2323575408232</v>
+        <v>185.2323725985514</v>
       </c>
       <c r="E540" t="n">
-        <v>185.7985512500661</v>
+        <v>185.7985663538207</v>
       </c>
       <c r="F540" t="n">
         <v>601100</v>
@@ -11252,16 +11252,16 @@
         <v>44015</v>
       </c>
       <c r="B542" t="n">
-        <v>181.5074615478516</v>
+        <v>181.5074462890625</v>
       </c>
       <c r="C542" t="n">
-        <v>184.4575923143823</v>
+        <v>184.4575768075846</v>
       </c>
       <c r="D542" t="n">
-        <v>178.0805464104103</v>
+        <v>178.0805314397118</v>
       </c>
       <c r="E542" t="n">
-        <v>179.3917223762915</v>
+        <v>179.3917072953663</v>
       </c>
       <c r="F542" t="n">
         <v>277066</v>
@@ -11272,16 +11272,16 @@
         <v>44018</v>
       </c>
       <c r="B543" t="n">
-        <v>181.7756652832031</v>
+        <v>181.7756500244141</v>
       </c>
       <c r="C543" t="n">
-        <v>185.2919747623554</v>
+        <v>185.2919592083969</v>
       </c>
       <c r="D543" t="n">
-        <v>180.0770991189848</v>
+        <v>180.0770840027784</v>
       </c>
       <c r="E543" t="n">
-        <v>182.103459285305</v>
+        <v>182.1034439989999</v>
       </c>
       <c r="F543" t="n">
         <v>817833</v>
@@ -11292,16 +11292,16 @@
         <v>44019</v>
       </c>
       <c r="B544" t="n">
-        <v>178.6467437744141</v>
+        <v>178.646728515625</v>
       </c>
       <c r="C544" t="n">
-        <v>182.8186412067338</v>
+        <v>182.8186255916096</v>
       </c>
       <c r="D544" t="n">
-        <v>177.8421502390783</v>
+        <v>177.8421350490122</v>
       </c>
       <c r="E544" t="n">
-        <v>178.7957341568639</v>
+        <v>178.7957188853491</v>
       </c>
       <c r="F544" t="n">
         <v>1026966</v>
@@ -11312,16 +11312,16 @@
         <v>44020</v>
       </c>
       <c r="B545" t="n">
-        <v>180.9412841796875</v>
+        <v>180.9412689208984</v>
       </c>
       <c r="C545" t="n">
-        <v>183.5040248203987</v>
+        <v>183.5040093454935</v>
       </c>
       <c r="D545" t="n">
-        <v>177.1567769491531</v>
+        <v>177.1567620095117</v>
       </c>
       <c r="E545" t="n">
-        <v>180.4346865727422</v>
+        <v>180.4346713566746</v>
       </c>
       <c r="F545" t="n">
         <v>677066</v>
@@ -11352,16 +11352,16 @@
         <v>44022</v>
       </c>
       <c r="B547" t="n">
-        <v>180.1962890625</v>
+        <v>180.1963043212891</v>
       </c>
       <c r="C547" t="n">
-        <v>181.060463520661</v>
+        <v>181.0604788526272</v>
       </c>
       <c r="D547" t="n">
-        <v>177.9315445015465</v>
+        <v>177.9315595685599</v>
       </c>
       <c r="E547" t="n">
-        <v>178.8255170336646</v>
+        <v>178.8255321763785</v>
       </c>
       <c r="F547" t="n">
         <v>618666</v>
@@ -11372,16 +11372,16 @@
         <v>44025</v>
       </c>
       <c r="B548" t="n">
-        <v>175.6966094970703</v>
+        <v>175.6965942382812</v>
       </c>
       <c r="C548" t="n">
-        <v>181.269077041767</v>
+        <v>181.2690612990238</v>
       </c>
       <c r="D548" t="n">
-        <v>175.6369981885591</v>
+        <v>175.6369829349472</v>
       </c>
       <c r="E548" t="n">
-        <v>180.1367046872849</v>
+        <v>180.1366890428852</v>
       </c>
       <c r="F548" t="n">
         <v>495033</v>
@@ -11392,16 +11392,16 @@
         <v>44026</v>
       </c>
       <c r="B549" t="n">
-        <v>178.4679260253906</v>
+        <v>178.4679412841797</v>
       </c>
       <c r="C549" t="n">
-        <v>179.212908192047</v>
+        <v>179.2129235145311</v>
       </c>
       <c r="D549" t="n">
-        <v>173.2828489329264</v>
+        <v>173.2828637483977</v>
       </c>
       <c r="E549" t="n">
-        <v>175.0708091642418</v>
+        <v>175.0708241325815</v>
       </c>
       <c r="F549" t="n">
         <v>493066</v>
@@ -11412,16 +11412,16 @@
         <v>44027</v>
       </c>
       <c r="B550" t="n">
-        <v>180.673095703125</v>
+        <v>180.6730499267578</v>
       </c>
       <c r="C550" t="n">
-        <v>184.7258009852441</v>
+        <v>184.7257541820604</v>
       </c>
       <c r="D550" t="n">
-        <v>178.9745294944042</v>
+        <v>178.9744841483954</v>
       </c>
       <c r="E550" t="n">
-        <v>180.5837014702194</v>
+        <v>180.5836557165016</v>
       </c>
       <c r="F550" t="n">
         <v>693400</v>
@@ -11432,16 +11432,16 @@
         <v>44028</v>
       </c>
       <c r="B551" t="n">
-        <v>181.3882751464844</v>
+        <v>181.3882598876953</v>
       </c>
       <c r="C551" t="n">
-        <v>183.1166393877391</v>
+        <v>183.1166239835562</v>
       </c>
       <c r="D551" t="n">
-        <v>178.3487500533865</v>
+        <v>178.3487350502892</v>
       </c>
       <c r="E551" t="n">
-        <v>181.8054633791936</v>
+        <v>181.8054480853098</v>
       </c>
       <c r="F551" t="n">
         <v>439600</v>
@@ -11452,16 +11452,16 @@
         <v>44029</v>
       </c>
       <c r="B552" t="n">
-        <v>190.1492462158203</v>
+        <v>190.1492309570312</v>
       </c>
       <c r="C552" t="n">
-        <v>190.1492462158203</v>
+        <v>190.1492309570312</v>
       </c>
       <c r="D552" t="n">
-        <v>181.3882635744458</v>
+        <v>181.3882490186939</v>
       </c>
       <c r="E552" t="n">
-        <v>181.3882635744458</v>
+        <v>181.3882490186939</v>
       </c>
       <c r="F552" t="n">
         <v>595900</v>
@@ -11472,16 +11472,16 @@
         <v>44032</v>
       </c>
       <c r="B553" t="n">
-        <v>196.0197143554688</v>
+        <v>196.0196990966797</v>
       </c>
       <c r="C553" t="n">
-        <v>197.77787660506</v>
+        <v>197.7778612094101</v>
       </c>
       <c r="D553" t="n">
-        <v>189.1956822003815</v>
+        <v>189.1956674727965</v>
       </c>
       <c r="E553" t="n">
-        <v>190.7154446877005</v>
+        <v>190.7154298418124</v>
       </c>
       <c r="F553" t="n">
         <v>643066</v>
@@ -11512,16 +11512,16 @@
         <v>44034</v>
       </c>
       <c r="B555" t="n">
-        <v>193.9933319091797</v>
+        <v>193.9933471679688</v>
       </c>
       <c r="C555" t="n">
-        <v>197.9268287074306</v>
+        <v>197.9268442756138</v>
       </c>
       <c r="D555" t="n">
-        <v>191.4305917979804</v>
+        <v>191.4306068551939</v>
       </c>
       <c r="E555" t="n">
-        <v>195.2150982465623</v>
+        <v>195.2151136014509</v>
       </c>
       <c r="F555" t="n">
         <v>664000</v>
@@ -11532,16 +11532,16 @@
         <v>44035</v>
       </c>
       <c r="B556" t="n">
-        <v>191.6392059326172</v>
+        <v>191.6392211914062</v>
       </c>
       <c r="C556" t="n">
-        <v>196.6752926716999</v>
+        <v>196.6753083314747</v>
       </c>
       <c r="D556" t="n">
-        <v>190.0002512230334</v>
+        <v>190.0002663513249</v>
       </c>
       <c r="E556" t="n">
-        <v>194.8277362857887</v>
+        <v>194.8277517984564</v>
       </c>
       <c r="F556" t="n">
         <v>517766</v>
@@ -11552,16 +11552,16 @@
         <v>44036</v>
       </c>
       <c r="B557" t="n">
-        <v>195.7515106201172</v>
+        <v>195.7514953613281</v>
       </c>
       <c r="C557" t="n">
-        <v>196.079304599603</v>
+        <v>196.0792893152624</v>
       </c>
       <c r="D557" t="n">
-        <v>188.0335061132565</v>
+        <v>188.0334914560843</v>
       </c>
       <c r="E557" t="n">
-        <v>192.7119857370506</v>
+        <v>192.7119707151919</v>
       </c>
       <c r="F557" t="n">
         <v>615366</v>
@@ -11632,16 +11632,16 @@
         <v>44042</v>
       </c>
       <c r="B561" t="n">
-        <v>197.2712860107422</v>
+        <v>197.2712707519531</v>
       </c>
       <c r="C561" t="n">
-        <v>200.0724111073721</v>
+        <v>200.072395631918</v>
       </c>
       <c r="D561" t="n">
-        <v>193.0993737052108</v>
+        <v>193.0993587691161</v>
       </c>
       <c r="E561" t="n">
-        <v>194.8873339566241</v>
+        <v>194.887318882232</v>
       </c>
       <c r="F561" t="n">
         <v>388133</v>
@@ -11652,16 +11652,16 @@
         <v>44043</v>
       </c>
       <c r="B562" t="n">
-        <v>194.112548828125</v>
+        <v>194.1125335693359</v>
       </c>
       <c r="C562" t="n">
-        <v>199.8936176362711</v>
+        <v>199.8936019230441</v>
       </c>
       <c r="D562" t="n">
-        <v>191.8180062117766</v>
+        <v>191.8179911333568</v>
       </c>
       <c r="E562" t="n">
-        <v>197.5692617895057</v>
+        <v>197.5692462589916</v>
       </c>
       <c r="F562" t="n">
         <v>964966</v>
@@ -11692,16 +11692,16 @@
         <v>44047</v>
       </c>
       <c r="B564" t="n">
-        <v>191.1922302246094</v>
+        <v>191.1922454833984</v>
       </c>
       <c r="C564" t="n">
-        <v>194.7979489729283</v>
+        <v>194.7979645194849</v>
       </c>
       <c r="D564" t="n">
-        <v>188.8976874417525</v>
+        <v>188.8977025174173</v>
       </c>
       <c r="E564" t="n">
-        <v>193.4271768557092</v>
+        <v>193.4271922928663</v>
       </c>
       <c r="F564" t="n">
         <v>411633</v>
@@ -11712,16 +11712,16 @@
         <v>44048</v>
       </c>
       <c r="B565" t="n">
-        <v>194.4999389648438</v>
+        <v>194.4999542236328</v>
       </c>
       <c r="C565" t="n">
-        <v>198.075859378189</v>
+        <v>198.0758749175139</v>
       </c>
       <c r="D565" t="n">
-        <v>193.0993688732251</v>
+        <v>193.0993840221375</v>
       </c>
       <c r="E565" t="n">
-        <v>193.3675666934012</v>
+        <v>193.3675818633541</v>
       </c>
       <c r="F565" t="n">
         <v>503800</v>
@@ -11732,16 +11732,16 @@
         <v>44049</v>
       </c>
       <c r="B566" t="n">
-        <v>197.4202880859375</v>
+        <v>197.4202728271484</v>
       </c>
       <c r="C566" t="n">
-        <v>198.6122566053047</v>
+        <v>198.6122412543873</v>
       </c>
       <c r="D566" t="n">
-        <v>194.797951280649</v>
+        <v>194.7979362245427</v>
       </c>
       <c r="E566" t="n">
-        <v>194.797951280649</v>
+        <v>194.7979362245427</v>
       </c>
       <c r="F566" t="n">
         <v>434133</v>
@@ -11752,16 +11752,16 @@
         <v>44050</v>
       </c>
       <c r="B567" t="n">
-        <v>195.2449188232422</v>
+        <v>195.2449340820312</v>
       </c>
       <c r="C567" t="n">
-        <v>198.9996276347122</v>
+        <v>198.9996431869394</v>
       </c>
       <c r="D567" t="n">
-        <v>193.6953583812642</v>
+        <v>193.6953735189519</v>
       </c>
       <c r="E567" t="n">
-        <v>196.9732828621334</v>
+        <v>196.9732982559976</v>
       </c>
       <c r="F567" t="n">
         <v>600933</v>
@@ -11772,16 +11772,16 @@
         <v>44053</v>
       </c>
       <c r="B568" t="n">
-        <v>191.9073944091797</v>
+        <v>191.9074096679688</v>
       </c>
       <c r="C568" t="n">
-        <v>197.0030770485053</v>
+        <v>197.0030927124582</v>
       </c>
       <c r="D568" t="n">
-        <v>191.0432199851351</v>
+        <v>191.0432351752126</v>
       </c>
       <c r="E568" t="n">
-        <v>195.3641072620583</v>
+        <v>195.3641227956948</v>
       </c>
       <c r="F568" t="n">
         <v>446333</v>
@@ -11812,16 +11812,16 @@
         <v>44055</v>
       </c>
       <c r="B570" t="n">
-        <v>182.6994171142578</v>
+        <v>182.6994323730469</v>
       </c>
       <c r="C570" t="n">
-        <v>189.2552661659586</v>
+        <v>189.2552819722826</v>
       </c>
       <c r="D570" t="n">
-        <v>179.2427041457414</v>
+        <v>179.2427191158309</v>
       </c>
       <c r="E570" t="n">
-        <v>186.7521218717291</v>
+        <v>186.7521374689941</v>
       </c>
       <c r="F570" t="n">
         <v>1065533</v>
@@ -11852,16 +11852,16 @@
         <v>44057</v>
       </c>
       <c r="B572" t="n">
-        <v>191.0730285644531</v>
+        <v>191.0730438232422</v>
       </c>
       <c r="C572" t="n">
-        <v>193.0993734084735</v>
+        <v>193.0993888290833</v>
       </c>
       <c r="D572" t="n">
-        <v>187.0799198685499</v>
+        <v>187.0799348084556</v>
       </c>
       <c r="E572" t="n">
-        <v>188.7784858939576</v>
+        <v>188.7785009695081</v>
       </c>
       <c r="F572" t="n">
         <v>670600</v>
@@ -11872,16 +11872,16 @@
         <v>44060</v>
       </c>
       <c r="B573" t="n">
-        <v>186.0965423583984</v>
+        <v>186.0965728759766</v>
       </c>
       <c r="C573" t="n">
-        <v>193.0397661179825</v>
+        <v>193.0397977741653</v>
       </c>
       <c r="D573" t="n">
-        <v>183.0272044600494</v>
+        <v>183.0272344742933</v>
       </c>
       <c r="E573" t="n">
-        <v>191.877595812602</v>
+        <v>191.8776272782028</v>
       </c>
       <c r="F573" t="n">
         <v>389400</v>
@@ -11892,16 +11892,16 @@
         <v>44061</v>
       </c>
       <c r="B574" t="n">
-        <v>187.5268859863281</v>
+        <v>187.5269012451172</v>
       </c>
       <c r="C574" t="n">
-        <v>190.3876220767241</v>
+        <v>190.3876375682871</v>
       </c>
       <c r="D574" t="n">
-        <v>186.0965330978296</v>
+        <v>186.096548240233</v>
       </c>
       <c r="E574" t="n">
-        <v>187.9738873679771</v>
+        <v>187.973902663138</v>
       </c>
       <c r="F574" t="n">
         <v>544533</v>
@@ -11912,16 +11912,16 @@
         <v>44062</v>
       </c>
       <c r="B575" t="n">
-        <v>184.6959686279297</v>
+        <v>184.6959838867188</v>
       </c>
       <c r="C575" t="n">
-        <v>188.3612830638038</v>
+        <v>188.3612986254054</v>
       </c>
       <c r="D575" t="n">
-        <v>183.772182922585</v>
+        <v>183.7721981050549</v>
       </c>
       <c r="E575" t="n">
-        <v>187.7354932362058</v>
+        <v>187.7355087461073</v>
       </c>
       <c r="F575" t="n">
         <v>275166</v>
@@ -11932,16 +11932,16 @@
         <v>44063</v>
       </c>
       <c r="B576" t="n">
-        <v>185.1429595947266</v>
+        <v>185.1429748535156</v>
       </c>
       <c r="C576" t="n">
-        <v>189.3744526653612</v>
+        <v>189.374468272894</v>
       </c>
       <c r="D576" t="n">
-        <v>180.0174788680197</v>
+        <v>180.0174937043858</v>
       </c>
       <c r="E576" t="n">
-        <v>180.5240764201374</v>
+        <v>180.5240912982554</v>
       </c>
       <c r="F576" t="n">
         <v>586600</v>
@@ -11972,16 +11972,16 @@
         <v>44067</v>
       </c>
       <c r="B578" t="n">
-        <v>185.2323608398438</v>
+        <v>185.2323455810547</v>
       </c>
       <c r="C578" t="n">
-        <v>187.8546974484032</v>
+        <v>187.8546819735952</v>
       </c>
       <c r="D578" t="n">
-        <v>182.8186259059577</v>
+        <v>182.8186108460036</v>
       </c>
       <c r="E578" t="n">
-        <v>186.8415326191354</v>
+        <v>186.8415172277884</v>
       </c>
       <c r="F578" t="n">
         <v>597533</v>
@@ -12012,16 +12012,16 @@
         <v>44069</v>
       </c>
       <c r="B580" t="n">
-        <v>186.0369415283203</v>
+        <v>186.0369262695312</v>
       </c>
       <c r="C580" t="n">
-        <v>191.0134321430643</v>
+        <v>191.0134164761023</v>
       </c>
       <c r="D580" t="n">
-        <v>182.520632341546</v>
+        <v>182.5206173711653</v>
       </c>
       <c r="E580" t="n">
-        <v>186.6627314036357</v>
+        <v>186.6627160935192</v>
       </c>
       <c r="F580" t="n">
         <v>788933</v>
@@ -12032,16 +12032,16 @@
         <v>44070</v>
       </c>
       <c r="B581" t="n">
-        <v>187.0203094482422</v>
+        <v>187.0203247070312</v>
       </c>
       <c r="C581" t="n">
-        <v>189.6128478217963</v>
+        <v>189.6128632921078</v>
       </c>
       <c r="D581" t="n">
-        <v>184.755565024988</v>
+        <v>184.755580098999</v>
       </c>
       <c r="E581" t="n">
-        <v>184.755565024988</v>
+        <v>184.755580098999</v>
       </c>
       <c r="F581" t="n">
         <v>465466</v>
@@ -12052,16 +12052,16 @@
         <v>44071</v>
       </c>
       <c r="B582" t="n">
-        <v>192.1458282470703</v>
+        <v>192.1458129882812</v>
       </c>
       <c r="C582" t="n">
-        <v>192.1458282470703</v>
+        <v>192.1458129882812</v>
       </c>
       <c r="D582" t="n">
-        <v>187.1991350937895</v>
+        <v>187.1991202278299</v>
       </c>
       <c r="E582" t="n">
-        <v>188.9274994053012</v>
+        <v>188.9274844020878</v>
       </c>
       <c r="F582" t="n">
         <v>688066</v>
@@ -12092,16 +12092,16 @@
         <v>44075</v>
       </c>
       <c r="B584" t="n">
-        <v>205.5852813720703</v>
+        <v>205.5852966308594</v>
       </c>
       <c r="C584" t="n">
-        <v>207.2838322362663</v>
+        <v>207.2838476211239</v>
       </c>
       <c r="D584" t="n">
-        <v>193.5463743241929</v>
+        <v>193.5463886894397</v>
       </c>
       <c r="E584" t="n">
-        <v>195.1853290397085</v>
+        <v>195.1853435266005</v>
       </c>
       <c r="F584" t="n">
         <v>1357600</v>
@@ -12112,16 +12112,16 @@
         <v>44076</v>
       </c>
       <c r="B585" t="n">
-        <v>202.0689392089844</v>
+        <v>202.0689544677734</v>
       </c>
       <c r="C585" t="n">
-        <v>206.4792357027279</v>
+        <v>206.4792512945507</v>
       </c>
       <c r="D585" t="n">
-        <v>199.7148006035536</v>
+        <v>199.7148156845751</v>
       </c>
       <c r="E585" t="n">
-        <v>205.376661579292</v>
+        <v>205.3766770878564</v>
       </c>
       <c r="F585" t="n">
         <v>581366</v>
@@ -12132,16 +12132,16 @@
         <v>44077</v>
       </c>
       <c r="B586" t="n">
-        <v>199.3572235107422</v>
+        <v>199.3572082519531</v>
       </c>
       <c r="C586" t="n">
-        <v>204.6018967184463</v>
+        <v>204.6018810582302</v>
       </c>
       <c r="D586" t="n">
-        <v>196.5858965371773</v>
+        <v>196.5858814905054</v>
       </c>
       <c r="E586" t="n">
-        <v>202.0391562624793</v>
+        <v>202.0391407984153</v>
       </c>
       <c r="F586" t="n">
         <v>527733</v>
@@ -12152,16 +12152,16 @@
         <v>44078</v>
       </c>
       <c r="B587" t="n">
-        <v>197.8970642089844</v>
+        <v>197.8970794677734</v>
       </c>
       <c r="C587" t="n">
-        <v>203.1417376008307</v>
+        <v>203.1417532640086</v>
       </c>
       <c r="D587" t="n">
-        <v>194.6489376248939</v>
+        <v>194.6489526332372</v>
       </c>
       <c r="E587" t="n">
-        <v>200.2512182300084</v>
+        <v>200.2512336703138</v>
       </c>
       <c r="F587" t="n">
         <v>642700</v>
@@ -12172,16 +12172,16 @@
         <v>44082</v>
       </c>
       <c r="B588" t="n">
-        <v>200.6683959960938</v>
+        <v>200.6684112548828</v>
       </c>
       <c r="C588" t="n">
-        <v>207.7904235251929</v>
+        <v>207.7904393255396</v>
       </c>
       <c r="D588" t="n">
-        <v>198.3142420975526</v>
+        <v>198.3142571773322</v>
       </c>
       <c r="E588" t="n">
-        <v>198.4632476214454</v>
+        <v>198.4632627125554</v>
       </c>
       <c r="F588" t="n">
         <v>1005833</v>
@@ -12192,16 +12192,16 @@
         <v>44083</v>
       </c>
       <c r="B589" t="n">
-        <v>203.4992980957031</v>
+        <v>203.4993133544922</v>
       </c>
       <c r="C589" t="n">
-        <v>204.6614683101234</v>
+        <v>204.6614836560544</v>
       </c>
       <c r="D589" t="n">
-        <v>196.7050652313848</v>
+        <v>196.7050799807286</v>
       </c>
       <c r="E589" t="n">
-        <v>202.3669259516501</v>
+        <v>202.3669411255316</v>
       </c>
       <c r="F589" t="n">
         <v>801100</v>
@@ -12232,16 +12232,16 @@
         <v>44085</v>
       </c>
       <c r="B591" t="n">
-        <v>189.7766265869141</v>
+        <v>189.776611328125</v>
       </c>
       <c r="C591" t="n">
-        <v>197.9303936359225</v>
+        <v>197.9303777215384</v>
       </c>
       <c r="D591" t="n">
-        <v>187.8053910426163</v>
+        <v>187.8053759423223</v>
       </c>
       <c r="E591" t="n">
-        <v>194.5852588258493</v>
+        <v>194.5852431804272</v>
       </c>
       <c r="F591" t="n">
         <v>1048366</v>
@@ -12252,16 +12252,16 @@
         <v>44088</v>
       </c>
       <c r="B592" t="n">
-        <v>197.1837005615234</v>
+        <v>197.1837158203125</v>
       </c>
       <c r="C592" t="n">
-        <v>199.1250699398823</v>
+        <v>199.1250853489015</v>
       </c>
       <c r="D592" t="n">
-        <v>190.075291397571</v>
+        <v>190.0753061062856</v>
       </c>
       <c r="E592" t="n">
-        <v>190.3441010626601</v>
+        <v>190.3441157921762</v>
       </c>
       <c r="F592" t="n">
         <v>434033</v>
@@ -12272,16 +12272,16 @@
         <v>44089</v>
       </c>
       <c r="B593" t="n">
-        <v>197.2733154296875</v>
+        <v>197.2733001708984</v>
       </c>
       <c r="C593" t="n">
-        <v>199.0653546966144</v>
+        <v>199.0653392992138</v>
       </c>
       <c r="D593" t="n">
-        <v>191.8076146546597</v>
+        <v>191.8075998186343</v>
       </c>
       <c r="E593" t="n">
-        <v>199.0056225862634</v>
+        <v>199.005607193483</v>
       </c>
       <c r="F593" t="n">
         <v>591666</v>
@@ -12292,16 +12292,16 @@
         <v>44090</v>
       </c>
       <c r="B594" t="n">
-        <v>197.8407745361328</v>
+        <v>197.8408050537109</v>
       </c>
       <c r="C594" t="n">
-        <v>202.7688704709959</v>
+        <v>202.7689017487487</v>
       </c>
       <c r="D594" t="n">
-        <v>196.7954171702461</v>
+        <v>196.7954475265745</v>
       </c>
       <c r="E594" t="n">
-        <v>198.9458640044226</v>
+        <v>198.9458946924643</v>
       </c>
       <c r="F594" t="n">
         <v>602300</v>
@@ -12332,16 +12332,16 @@
         <v>44092</v>
       </c>
       <c r="B596" t="n">
-        <v>187.3872528076172</v>
+        <v>187.3872375488281</v>
       </c>
       <c r="C596" t="n">
-        <v>192.9724328937132</v>
+        <v>192.9724171801275</v>
       </c>
       <c r="D596" t="n">
-        <v>185.4757493545254</v>
+        <v>185.4757342513885</v>
       </c>
       <c r="E596" t="n">
-        <v>192.225751145258</v>
+        <v>192.225735492474</v>
       </c>
       <c r="F596" t="n">
         <v>571800</v>
@@ -12352,16 +12352,16 @@
         <v>44095</v>
       </c>
       <c r="B597" t="n">
-        <v>187.8949584960938</v>
+        <v>187.8949737548828</v>
       </c>
       <c r="C597" t="n">
-        <v>188.1936341821787</v>
+        <v>188.193649465223</v>
       </c>
       <c r="D597" t="n">
-        <v>182.8473986472359</v>
+        <v>182.847413496117</v>
       </c>
       <c r="E597" t="n">
-        <v>186.0431874718987</v>
+        <v>186.043202580307</v>
       </c>
       <c r="F597" t="n">
         <v>424066</v>
@@ -12392,16 +12392,16 @@
         <v>44097</v>
       </c>
       <c r="B599" t="n">
-        <v>187.0885772705078</v>
+        <v>187.0885620117188</v>
       </c>
       <c r="C599" t="n">
-        <v>189.8961079395225</v>
+        <v>189.8960924517536</v>
       </c>
       <c r="D599" t="n">
-        <v>185.1770738153672</v>
+        <v>185.1770587124788</v>
       </c>
       <c r="E599" t="n">
-        <v>185.8640234552869</v>
+        <v>185.8640082963715</v>
       </c>
       <c r="F599" t="n">
         <v>596200</v>
@@ -12432,16 +12432,16 @@
         <v>44099</v>
       </c>
       <c r="B601" t="n">
-        <v>187.8352508544922</v>
+        <v>187.8352661132812</v>
       </c>
       <c r="C601" t="n">
-        <v>188.1339265794667</v>
+        <v>188.1339418625186</v>
       </c>
       <c r="D601" t="n">
-        <v>182.9967527219967</v>
+        <v>182.9967675877305</v>
       </c>
       <c r="E601" t="n">
-        <v>186.6704291992423</v>
+        <v>186.6704443634071</v>
       </c>
       <c r="F601" t="n">
         <v>316200</v>
@@ -12472,16 +12472,16 @@
         <v>44103</v>
       </c>
       <c r="B603" t="n">
-        <v>180.9359283447266</v>
+        <v>180.9359130859375</v>
       </c>
       <c r="C603" t="n">
-        <v>183.5045002136614</v>
+        <v>183.5044847382582</v>
       </c>
       <c r="D603" t="n">
-        <v>178.6062697236995</v>
+        <v>178.6062546613765</v>
       </c>
       <c r="E603" t="n">
-        <v>181.2644549486086</v>
+        <v>181.2644396621141</v>
       </c>
       <c r="F603" t="n">
         <v>676133</v>
@@ -12492,16 +12492,16 @@
         <v>44104</v>
       </c>
       <c r="B604" t="n">
-        <v>185.5952301025391</v>
+        <v>185.5951995849609</v>
       </c>
       <c r="C604" t="n">
-        <v>186.9691295032681</v>
+        <v>186.9690987597785</v>
       </c>
       <c r="D604" t="n">
-        <v>180.398323455142</v>
+        <v>180.3982937920956</v>
       </c>
       <c r="E604" t="n">
-        <v>181.5930113208158</v>
+        <v>181.5929814613258</v>
       </c>
       <c r="F604" t="n">
         <v>757400</v>
@@ -12612,16 +12612,16 @@
         <v>44112</v>
       </c>
       <c r="B610" t="n">
-        <v>194.2268371582031</v>
+        <v>194.2268524169922</v>
       </c>
       <c r="C610" t="n">
-        <v>195.481272117246</v>
+        <v>195.4812874745856</v>
       </c>
       <c r="D610" t="n">
-        <v>187.4469698575246</v>
+        <v>187.4469845836759</v>
       </c>
       <c r="E610" t="n">
-        <v>188.1637854937555</v>
+        <v>188.1638002762209</v>
       </c>
       <c r="F610" t="n">
         <v>582633</v>
@@ -12652,16 +12652,16 @@
         <v>44117</v>
       </c>
       <c r="B612" t="n">
-        <v>196.9447631835938</v>
+        <v>196.9447479248047</v>
       </c>
       <c r="C612" t="n">
-        <v>198.4680078731332</v>
+        <v>198.467992496327</v>
       </c>
       <c r="D612" t="n">
-        <v>190.2843749810402</v>
+        <v>190.2843602382814</v>
       </c>
       <c r="E612" t="n">
-        <v>193.5398963526999</v>
+        <v>193.5398813577115</v>
       </c>
       <c r="F612" t="n">
         <v>922633</v>
@@ -12692,16 +12692,16 @@
         <v>44119</v>
       </c>
       <c r="B614" t="n">
-        <v>198.4978637695312</v>
+        <v>198.4978790283203</v>
       </c>
       <c r="C614" t="n">
-        <v>201.4547244539764</v>
+        <v>201.4547399400632</v>
       </c>
       <c r="D614" t="n">
-        <v>196.9148870538109</v>
+        <v>196.9149021909145</v>
       </c>
       <c r="E614" t="n">
-        <v>199.6029532696903</v>
+        <v>199.6029686134291</v>
       </c>
       <c r="F614" t="n">
         <v>599566</v>
@@ -12712,16 +12712,16 @@
         <v>44120</v>
       </c>
       <c r="B615" t="n">
-        <v>193.1814727783203</v>
+        <v>193.1814880371094</v>
       </c>
       <c r="C615" t="n">
-        <v>198.8562655587187</v>
+        <v>198.8562812657416</v>
       </c>
       <c r="D615" t="n">
-        <v>190.0155498253865</v>
+        <v>190.0155648341094</v>
       </c>
       <c r="E615" t="n">
-        <v>198.6770540604953</v>
+        <v>198.6770697533628</v>
       </c>
       <c r="F615" t="n">
         <v>665566</v>
@@ -12732,16 +12732,16 @@
         <v>44123</v>
       </c>
       <c r="B616" t="n">
-        <v>192.3153533935547</v>
+        <v>192.3153381347656</v>
       </c>
       <c r="C616" t="n">
-        <v>196.6759797583532</v>
+        <v>196.6759641535809</v>
       </c>
       <c r="D616" t="n">
-        <v>189.1494300046808</v>
+        <v>189.1494149970842</v>
       </c>
       <c r="E616" t="n">
-        <v>195.1228841191864</v>
+        <v>195.1228686376407</v>
       </c>
       <c r="F616" t="n">
         <v>597800</v>
@@ -12752,16 +12752,16 @@
         <v>44124</v>
       </c>
       <c r="B617" t="n">
-        <v>194.2268371582031</v>
+        <v>194.2268524169922</v>
       </c>
       <c r="C617" t="n">
-        <v>195.8396647440835</v>
+        <v>195.8396801295791</v>
       </c>
       <c r="D617" t="n">
-        <v>190.6128929248125</v>
+        <v>190.612907899684</v>
       </c>
       <c r="E617" t="n">
-        <v>193.032149494911</v>
+        <v>193.0321646598434</v>
       </c>
       <c r="F617" t="n">
         <v>555666</v>
@@ -12772,16 +12772,16 @@
         <v>44125</v>
       </c>
       <c r="B618" t="n">
-        <v>192.7036285400391</v>
+        <v>192.70361328125</v>
       </c>
       <c r="C618" t="n">
-        <v>197.9901330346984</v>
+        <v>197.9901173573098</v>
       </c>
       <c r="D618" t="n">
-        <v>192.7036285400391</v>
+        <v>192.70361328125</v>
       </c>
       <c r="E618" t="n">
-        <v>193.6892539441184</v>
+        <v>193.6892386072849</v>
       </c>
       <c r="F618" t="n">
         <v>378600</v>
@@ -12792,16 +12792,16 @@
         <v>44126</v>
       </c>
       <c r="B619" t="n">
-        <v>195.2722015380859</v>
+        <v>195.2721862792969</v>
       </c>
       <c r="C619" t="n">
-        <v>197.1239727993063</v>
+        <v>197.1239573958178</v>
       </c>
       <c r="D619" t="n">
-        <v>191.2401172380263</v>
+        <v>191.2401022943088</v>
       </c>
       <c r="E619" t="n">
-        <v>193.3009660636508</v>
+        <v>193.3009509588963</v>
       </c>
       <c r="F619" t="n">
         <v>380966</v>
@@ -12812,16 +12812,16 @@
         <v>44127</v>
       </c>
       <c r="B620" t="n">
-        <v>190.3441162109375</v>
+        <v>190.3440856933594</v>
       </c>
       <c r="C620" t="n">
-        <v>195.242346721261</v>
+        <v>195.2423154183572</v>
       </c>
       <c r="D620" t="n">
-        <v>188.940350859762</v>
+        <v>188.9403205672475</v>
       </c>
       <c r="E620" t="n">
-        <v>194.1671231666126</v>
+        <v>194.1670920360976</v>
       </c>
       <c r="F620" t="n">
         <v>403166</v>
@@ -12852,16 +12852,16 @@
         <v>44131</v>
       </c>
       <c r="B622" t="n">
-        <v>198.3186645507812</v>
+        <v>198.3186492919922</v>
       </c>
       <c r="C622" t="n">
-        <v>204.7102583398841</v>
+        <v>204.710242589321</v>
       </c>
       <c r="D622" t="n">
-        <v>195.7500775753192</v>
+        <v>195.7500625141592</v>
       </c>
       <c r="E622" t="n">
-        <v>196.2876969283092</v>
+        <v>196.2876818257843</v>
       </c>
       <c r="F622" t="n">
         <v>606666</v>
@@ -12872,16 +12872,16 @@
         <v>44132</v>
       </c>
       <c r="B623" t="n">
-        <v>192.9425506591797</v>
+        <v>192.9425659179688</v>
       </c>
       <c r="C623" t="n">
-        <v>196.4370154800485</v>
+        <v>196.437031015196</v>
       </c>
       <c r="D623" t="n">
-        <v>192.9425506591797</v>
+        <v>192.9425659179688</v>
       </c>
       <c r="E623" t="n">
-        <v>195.6007356378149</v>
+        <v>195.6007511068256</v>
       </c>
       <c r="F623" t="n">
         <v>477733</v>
@@ -12892,16 +12892,16 @@
         <v>44133</v>
       </c>
       <c r="B624" t="n">
-        <v>199.2743988037109</v>
+        <v>199.2744140625</v>
       </c>
       <c r="C624" t="n">
-        <v>199.8717349981709</v>
+        <v>199.871750302699</v>
       </c>
       <c r="D624" t="n">
-        <v>189.5376714786287</v>
+        <v>189.5376859918596</v>
       </c>
       <c r="E624" t="n">
-        <v>192.8529245765097</v>
+        <v>192.8529393435952</v>
       </c>
       <c r="F624" t="n">
         <v>707700</v>
@@ -12932,16 +12932,16 @@
         <v>44138</v>
       </c>
       <c r="B626" t="n">
-        <v>195.1228942871094</v>
+        <v>195.1228790283203</v>
       </c>
       <c r="C626" t="n">
-        <v>197.0045318235803</v>
+        <v>197.0045164176454</v>
       </c>
       <c r="D626" t="n">
-        <v>192.0465537124575</v>
+        <v>192.0465386942411</v>
       </c>
       <c r="E626" t="n">
-        <v>194.6151409384984</v>
+        <v>194.6151257194161</v>
       </c>
       <c r="F626" t="n">
         <v>792500</v>
@@ -13092,16 +13092,16 @@
         <v>44148</v>
       </c>
       <c r="B634" t="n">
-        <v>218.897216796875</v>
+        <v>218.8972015380859</v>
       </c>
       <c r="C634" t="n">
-        <v>220.6593899790492</v>
+        <v>220.6593745974234</v>
       </c>
       <c r="D634" t="n">
-        <v>209.9370358039121</v>
+        <v>209.9370211697153</v>
       </c>
       <c r="E634" t="n">
-        <v>209.9370358039121</v>
+        <v>209.9370211697153</v>
       </c>
       <c r="F634" t="n">
         <v>872100</v>
@@ -13112,16 +13112,16 @@
         <v>44151</v>
       </c>
       <c r="B635" t="n">
-        <v>218.0907745361328</v>
+        <v>218.0907897949219</v>
       </c>
       <c r="C635" t="n">
-        <v>221.5852391994435</v>
+        <v>221.5852547027238</v>
       </c>
       <c r="D635" t="n">
-        <v>215.0741818766554</v>
+        <v>215.0741969243876</v>
       </c>
       <c r="E635" t="n">
-        <v>221.017769043256</v>
+        <v>221.0177845068331</v>
       </c>
       <c r="F635" t="n">
         <v>540700</v>
@@ -13132,16 +13132,16 @@
         <v>44152</v>
       </c>
       <c r="B636" t="n">
-        <v>215.7611541748047</v>
+        <v>215.7611389160156</v>
       </c>
       <c r="C636" t="n">
-        <v>220.390574829844</v>
+        <v>220.3905592436589</v>
       </c>
       <c r="D636" t="n">
-        <v>215.7611541748047</v>
+        <v>215.7611389160156</v>
       </c>
       <c r="E636" t="n">
-        <v>219.793238559895</v>
+        <v>219.7932230159539</v>
       </c>
       <c r="F636" t="n">
         <v>945033</v>
@@ -13152,16 +13152,16 @@
         <v>44153</v>
       </c>
       <c r="B637" t="n">
-        <v>213.1029357910156</v>
+        <v>213.1029663085938</v>
       </c>
       <c r="C637" t="n">
-        <v>217.4336800398308</v>
+        <v>217.4337111775966</v>
       </c>
       <c r="D637" t="n">
-        <v>213.1029357910156</v>
+        <v>213.1029663085938</v>
       </c>
       <c r="E637" t="n">
-        <v>216.8662099123425</v>
+        <v>216.8662409688433</v>
       </c>
       <c r="F637" t="n">
         <v>504433</v>
@@ -13172,16 +13172,16 @@
         <v>44154</v>
       </c>
       <c r="B638" t="n">
-        <v>213.1627044677734</v>
+        <v>213.1626892089844</v>
       </c>
       <c r="C638" t="n">
-        <v>215.4326157497906</v>
+        <v>215.4326003285149</v>
       </c>
       <c r="D638" t="n">
-        <v>209.9668999255425</v>
+        <v>209.9668848955181</v>
       </c>
       <c r="E638" t="n">
-        <v>213.819788047115</v>
+        <v>213.81977274129</v>
       </c>
       <c r="F638" t="n">
         <v>672366</v>
@@ -13192,16 +13192,16 @@
         <v>44158</v>
       </c>
       <c r="B639" t="n">
-        <v>215.3430023193359</v>
+        <v>215.3429870605469</v>
       </c>
       <c r="C639" t="n">
-        <v>217.9115891545185</v>
+        <v>217.9115737137244</v>
       </c>
       <c r="D639" t="n">
-        <v>212.326409508648</v>
+        <v>212.3263944636089</v>
       </c>
       <c r="E639" t="n">
-        <v>213.5509632260367</v>
+        <v>213.5509480942281</v>
       </c>
       <c r="F639" t="n">
         <v>541300</v>
@@ -13212,16 +13212,16 @@
         <v>44159</v>
       </c>
       <c r="B640" t="n">
-        <v>214.8053741455078</v>
+        <v>214.8053894042969</v>
       </c>
       <c r="C640" t="n">
-        <v>216.4779489607679</v>
+        <v>216.477964338369</v>
       </c>
       <c r="D640" t="n">
-        <v>212.2965347095335</v>
+        <v>212.2965497901061</v>
       </c>
       <c r="E640" t="n">
-        <v>214.2379039842555</v>
+        <v>214.2379192027341</v>
       </c>
       <c r="F640" t="n">
         <v>404100</v>
@@ -13232,16 +13232,16 @@
         <v>44160</v>
       </c>
       <c r="B641" t="n">
-        <v>216.8363647460938</v>
+        <v>216.8363494873047</v>
       </c>
       <c r="C641" t="n">
-        <v>220.4204277256715</v>
+        <v>220.4204122146717</v>
       </c>
       <c r="D641" t="n">
-        <v>214.7456499478817</v>
+        <v>214.7456348362164</v>
       </c>
       <c r="E641" t="n">
-        <v>215.044325660666</v>
+        <v>215.0443105279828</v>
       </c>
       <c r="F641" t="n">
         <v>311466</v>
@@ -13252,16 +13252,16 @@
         <v>44161</v>
       </c>
       <c r="B642" t="n">
-        <v>212.8042755126953</v>
+        <v>212.8042907714844</v>
       </c>
       <c r="C642" t="n">
-        <v>218.6283986032379</v>
+        <v>218.6284142796364</v>
       </c>
       <c r="D642" t="n">
-        <v>210.2655548016568</v>
+        <v>210.265569878411</v>
       </c>
       <c r="E642" t="n">
-        <v>216.3883535978412</v>
+        <v>216.3883691136208</v>
       </c>
       <c r="F642" t="n">
         <v>253146</v>
@@ -13292,16 +13292,16 @@
         <v>44165</v>
       </c>
       <c r="B644" t="n">
-        <v>215.3430023193359</v>
+        <v>215.3429870605469</v>
       </c>
       <c r="C644" t="n">
-        <v>217.5830473881405</v>
+        <v>217.5830319706262</v>
       </c>
       <c r="D644" t="n">
-        <v>209.9668850394382</v>
+        <v>209.9668701615904</v>
       </c>
       <c r="E644" t="n">
-        <v>214.2976449156382</v>
+        <v>214.2976297309212</v>
       </c>
       <c r="F644" t="n">
         <v>990433</v>
@@ -13312,16 +13312,16 @@
         <v>44166</v>
       </c>
       <c r="B645" t="n">
-        <v>215.3430023193359</v>
+        <v>215.3429870605469</v>
       </c>
       <c r="C645" t="n">
-        <v>219.8230924569451</v>
+        <v>219.8230768807055</v>
       </c>
       <c r="D645" t="n">
-        <v>212.8042815364352</v>
+        <v>212.804266457535</v>
       </c>
       <c r="E645" t="n">
-        <v>216.2390142703466</v>
+        <v>216.2389989480679</v>
       </c>
       <c r="F645" t="n">
         <v>896293</v>
@@ -13332,16 +13332,16 @@
         <v>44167</v>
       </c>
       <c r="B646" t="n">
-        <v>220.7191162109375</v>
+        <v>220.7191009521484</v>
       </c>
       <c r="C646" t="n">
-        <v>221.4657979404679</v>
+        <v>221.4657826300592</v>
       </c>
       <c r="D646" t="n">
-        <v>213.5509746457012</v>
+        <v>213.5509598824612</v>
       </c>
       <c r="E646" t="n">
-        <v>214.148326105837</v>
+        <v>214.1483113013008</v>
       </c>
       <c r="F646" t="n">
         <v>812640</v>
@@ -13352,16 +13352,16 @@
         <v>44168</v>
       </c>
       <c r="B647" t="n">
-        <v>226.3938751220703</v>
+        <v>226.3938903808594</v>
       </c>
       <c r="C647" t="n">
-        <v>229.8286229397145</v>
+        <v>229.8286384300032</v>
       </c>
       <c r="D647" t="n">
-        <v>219.9724158308146</v>
+        <v>219.9724306568018</v>
       </c>
       <c r="E647" t="n">
-        <v>219.9724158308146</v>
+        <v>219.9724306568018</v>
       </c>
       <c r="F647" t="n">
         <v>476626</v>
@@ -13452,16 +13452,16 @@
         <v>44175</v>
       </c>
       <c r="B652" t="n">
-        <v>227.8872680664062</v>
+        <v>227.8872375488281</v>
       </c>
       <c r="C652" t="n">
-        <v>233.4127161526883</v>
+        <v>233.4126848951685</v>
       </c>
       <c r="D652" t="n">
-        <v>225.6472227766659</v>
+        <v>225.647192559064</v>
       </c>
       <c r="E652" t="n">
-        <v>226.6925802834673</v>
+        <v>226.6925499258761</v>
       </c>
       <c r="F652" t="n">
         <v>713620</v>
@@ -13472,16 +13472,16 @@
         <v>44176</v>
       </c>
       <c r="B653" t="n">
-        <v>226.5432434082031</v>
+        <v>226.5432281494141</v>
       </c>
       <c r="C653" t="n">
-        <v>231.172664128968</v>
+        <v>231.172648558365</v>
       </c>
       <c r="D653" t="n">
-        <v>224.7512041903565</v>
+        <v>224.75118905227</v>
       </c>
       <c r="E653" t="n">
-        <v>228.4846128978375</v>
+        <v>228.4845975082877</v>
       </c>
       <c r="F653" t="n">
         <v>373833</v>
@@ -13492,16 +13492,16 @@
         <v>44179</v>
       </c>
       <c r="B654" t="n">
-        <v>226.0952453613281</v>
+        <v>226.09521484375</v>
       </c>
       <c r="C654" t="n">
-        <v>227.4392634285706</v>
+        <v>227.4392327295814</v>
       </c>
       <c r="D654" t="n">
-        <v>221.7644850316726</v>
+        <v>221.764455098646</v>
       </c>
       <c r="E654" t="n">
-        <v>226.6925816607872</v>
+        <v>226.6925510625826</v>
       </c>
       <c r="F654" t="n">
         <v>327060</v>
@@ -13512,16 +13512,16 @@
         <v>44180</v>
       </c>
       <c r="B655" t="n">
-        <v>226.6925506591797</v>
+        <v>226.6925659179688</v>
       </c>
       <c r="C655" t="n">
-        <v>228.1859139905198</v>
+        <v>228.1859293498279</v>
       </c>
       <c r="D655" t="n">
-        <v>223.1084877787297</v>
+        <v>223.1085027962737</v>
       </c>
       <c r="E655" t="n">
-        <v>226.09521444141</v>
+        <v>226.0952296599921</v>
       </c>
       <c r="F655" t="n">
         <v>364800</v>
@@ -13532,16 +13532,16 @@
         <v>44181</v>
       </c>
       <c r="B656" t="n">
-        <v>230.4259643554688</v>
+        <v>230.4259948730469</v>
       </c>
       <c r="C656" t="n">
-        <v>232.9646851161438</v>
+        <v>232.9647159699497</v>
       </c>
       <c r="D656" t="n">
-        <v>225.1991925740168</v>
+        <v>225.1992223993621</v>
       </c>
       <c r="E656" t="n">
-        <v>227.2899073631087</v>
+        <v>227.2899374653479</v>
       </c>
       <c r="F656" t="n">
         <v>398466</v>
@@ -13592,16 +13592,16 @@
         <v>44186</v>
       </c>
       <c r="B659" t="n">
-        <v>224.7512054443359</v>
+        <v>224.7511901855469</v>
       </c>
       <c r="C659" t="n">
-        <v>228.3352839000263</v>
+        <v>228.3352683979073</v>
       </c>
       <c r="D659" t="n">
-        <v>219.0764272155587</v>
+        <v>219.0764123420412</v>
       </c>
       <c r="E659" t="n">
-        <v>223.8551934260528</v>
+        <v>223.8551782280958</v>
       </c>
       <c r="F659" t="n">
         <v>304586</v>
@@ -13612,16 +13612,16 @@
         <v>44187</v>
       </c>
       <c r="B660" t="n">
-        <v>227.1405792236328</v>
+        <v>227.1405639648438</v>
       </c>
       <c r="C660" t="n">
-        <v>230.5753273805371</v>
+        <v>230.5753118910095</v>
       </c>
       <c r="D660" t="n">
-        <v>224.9005340037103</v>
+        <v>224.9005188954024</v>
       </c>
       <c r="E660" t="n">
-        <v>225.6472157436845</v>
+        <v>225.6472005852162</v>
       </c>
       <c r="F660" t="n">
         <v>374633</v>
@@ -13652,16 +13652,16 @@
         <v>44193</v>
       </c>
       <c r="B662" t="n">
-        <v>226.3938751220703</v>
+        <v>226.3938903808594</v>
       </c>
       <c r="C662" t="n">
-        <v>227.5885779410478</v>
+        <v>227.588593280359</v>
       </c>
       <c r="D662" t="n">
-        <v>222.80981223897</v>
+        <v>222.8098272561957</v>
       </c>
       <c r="E662" t="n">
-        <v>225.3485329423811</v>
+        <v>225.3485481307148</v>
       </c>
       <c r="F662" t="n">
         <v>229633</v>
@@ -13672,16 +13672,16 @@
         <v>44194</v>
       </c>
       <c r="B663" t="n">
-        <v>231.7699890136719</v>
+        <v>231.7700042724609</v>
       </c>
       <c r="C663" t="n">
-        <v>234.1593642358766</v>
+        <v>234.1593796519724</v>
       </c>
       <c r="D663" t="n">
-        <v>225.348529811629</v>
+        <v>225.3485446476555</v>
       </c>
       <c r="E663" t="n">
-        <v>227.588574779175</v>
+        <v>227.5885897626768</v>
       </c>
       <c r="F663" t="n">
         <v>293840</v>
@@ -13692,16 +13692,16 @@
         <v>44195</v>
       </c>
       <c r="B664" t="n">
-        <v>227.8872680664062</v>
+        <v>227.8872375488281</v>
       </c>
       <c r="C664" t="n">
-        <v>235.6527614424286</v>
+        <v>235.6527298849326</v>
       </c>
       <c r="D664" t="n">
-        <v>225.9458985202205</v>
+        <v>225.9458682626213</v>
       </c>
       <c r="E664" t="n">
-        <v>234.1593979159351</v>
+        <v>234.1593665584232</v>
       </c>
       <c r="F664" t="n">
         <v>659613</v>
@@ -13712,16 +13712,16 @@
         <v>44200</v>
       </c>
       <c r="B665" t="n">
-        <v>224.6018524169922</v>
+        <v>224.6018829345703</v>
       </c>
       <c r="C665" t="n">
-        <v>231.6206479621102</v>
+        <v>231.620679433361</v>
       </c>
       <c r="D665" t="n">
-        <v>220.4204229118868</v>
+        <v>220.4204528613169</v>
       </c>
       <c r="E665" t="n">
-        <v>230.1272846220805</v>
+        <v>230.1273158904218</v>
       </c>
       <c r="F665" t="n">
         <v>564553</v>
@@ -13732,16 +13732,16 @@
         <v>44201</v>
       </c>
       <c r="B666" t="n">
-        <v>218.7777557373047</v>
+        <v>218.7777404785156</v>
       </c>
       <c r="C666" t="n">
-        <v>225.6472218545923</v>
+        <v>225.6472061166881</v>
       </c>
       <c r="D666" t="n">
-        <v>218.1804042526365</v>
+        <v>218.1803890355101</v>
       </c>
       <c r="E666" t="n">
-        <v>224.9005400943967</v>
+        <v>224.9005244085703</v>
       </c>
       <c r="F666" t="n">
         <v>585466</v>
@@ -13752,16 +13752,16 @@
         <v>44202</v>
       </c>
       <c r="B667" t="n">
-        <v>210.7135772705078</v>
+        <v>210.7135620117188</v>
       </c>
       <c r="C667" t="n">
-        <v>220.5697851810959</v>
+        <v>220.5697692085711</v>
       </c>
       <c r="D667" t="n">
-        <v>210.4149167327483</v>
+        <v>210.4149014955867</v>
       </c>
       <c r="E667" t="n">
-        <v>220.5697851810959</v>
+        <v>220.5697692085711</v>
       </c>
       <c r="F667" t="n">
         <v>989980</v>
@@ -13812,16 +13812,16 @@
         <v>44207</v>
       </c>
       <c r="B670" t="n">
-        <v>272.2713317871094</v>
+        <v>272.2713012695312</v>
       </c>
       <c r="C670" t="n">
-        <v>276.4601336813603</v>
+        <v>276.4601026942797</v>
       </c>
       <c r="D670" t="n">
-        <v>249.9809804052258</v>
+        <v>249.9809523860654</v>
       </c>
       <c r="E670" t="n">
-        <v>250.7289785694761</v>
+        <v>250.7289504664762</v>
       </c>
       <c r="F670" t="n">
         <v>3239386</v>
@@ -13932,16 +13932,16 @@
         <v>44215</v>
       </c>
       <c r="B676" t="n">
-        <v>259.8545227050781</v>
+        <v>259.8544921875</v>
       </c>
       <c r="C676" t="n">
-        <v>273.7672992685854</v>
+        <v>273.7672671170767</v>
       </c>
       <c r="D676" t="n">
-        <v>255.3665341924784</v>
+        <v>255.3665042019742</v>
       </c>
       <c r="E676" t="n">
-        <v>269.8777153115562</v>
+        <v>269.8776836168443</v>
       </c>
       <c r="F676" t="n">
         <v>761093</v>
@@ -13952,16 +13952,16 @@
         <v>44216</v>
       </c>
       <c r="B677" t="n">
-        <v>259.8545227050781</v>
+        <v>259.8544921875</v>
       </c>
       <c r="C677" t="n">
-        <v>264.4921351836605</v>
+        <v>264.4921041214365</v>
       </c>
       <c r="D677" t="n">
-        <v>256.8625303633449</v>
+        <v>256.8625001971495</v>
       </c>
       <c r="E677" t="n">
-        <v>259.4057421154902</v>
+        <v>259.4057116506173</v>
       </c>
       <c r="F677" t="n">
         <v>662453</v>
@@ -14012,16 +14012,16 @@
         <v>44222</v>
       </c>
       <c r="B680" t="n">
-        <v>267.7833251953125</v>
+        <v>267.7833557128906</v>
       </c>
       <c r="C680" t="n">
-        <v>276.1608979968802</v>
+        <v>276.1609294691975</v>
       </c>
       <c r="D680" t="n">
-        <v>261.5001532031671</v>
+        <v>261.5001830046917</v>
       </c>
       <c r="E680" t="n">
-        <v>263.4449300406782</v>
+        <v>263.4449600638367</v>
       </c>
       <c r="F680" t="n">
         <v>884853</v>
@@ -14092,16 +14092,16 @@
         <v>44228</v>
       </c>
       <c r="B684" t="n">
-        <v>261.9489135742188</v>
+        <v>261.9489440917969</v>
       </c>
       <c r="C684" t="n">
-        <v>264.6417187548947</v>
+        <v>264.6417495861901</v>
       </c>
       <c r="D684" t="n">
-        <v>256.712927173219</v>
+        <v>256.7129570807941</v>
       </c>
       <c r="E684" t="n">
-        <v>264.6417187548947</v>
+        <v>264.6417495861901</v>
       </c>
       <c r="F684" t="n">
         <v>678393</v>
@@ -14112,16 +14112,16 @@
         <v>44229</v>
       </c>
       <c r="B685" t="n">
-        <v>265.6888732910156</v>
+        <v>265.6889038085938</v>
       </c>
       <c r="C685" t="n">
-        <v>271.5232635537744</v>
+        <v>271.5232947415027</v>
       </c>
       <c r="D685" t="n">
-        <v>260.7521049426162</v>
+        <v>260.7521348931468</v>
       </c>
       <c r="E685" t="n">
-        <v>266.5864647692596</v>
+        <v>266.5864953899369</v>
       </c>
       <c r="F685" t="n">
         <v>627486</v>
@@ -14132,16 +14132,16 @@
         <v>44230</v>
       </c>
       <c r="B686" t="n">
-        <v>264.6417236328125</v>
+        <v>264.6417541503906</v>
       </c>
       <c r="C686" t="n">
-        <v>267.7833094440948</v>
+        <v>267.7833403239498</v>
       </c>
       <c r="D686" t="n">
-        <v>260.3033287333658</v>
+        <v>260.3033587506551</v>
       </c>
       <c r="E686" t="n">
-        <v>267.1849049000126</v>
+        <v>267.1849357108616</v>
       </c>
       <c r="F686" t="n">
         <v>630753</v>
@@ -14172,16 +14172,16 @@
         <v>44232</v>
       </c>
       <c r="B688" t="n">
-        <v>267.0353088378906</v>
+        <v>267.0353393554688</v>
       </c>
       <c r="C688" t="n">
-        <v>273.7672914136357</v>
+        <v>273.7673227005646</v>
       </c>
       <c r="D688" t="n">
-        <v>264.9409081715461</v>
+        <v>264.94093844977</v>
       </c>
       <c r="E688" t="n">
-        <v>265.3897191843768</v>
+        <v>265.3897495138921</v>
       </c>
       <c r="F688" t="n">
         <v>358426</v>
@@ -14212,16 +14212,16 @@
         <v>44236</v>
       </c>
       <c r="B690" t="n">
-        <v>264.7912902832031</v>
+        <v>264.7913208007812</v>
       </c>
       <c r="C690" t="n">
-        <v>270.1768697610619</v>
+        <v>270.1769008993359</v>
       </c>
       <c r="D690" t="n">
-        <v>264.1928857998596</v>
+        <v>264.1929162484707</v>
       </c>
       <c r="E690" t="n">
-        <v>269.4288717659117</v>
+        <v>269.4289028179777</v>
       </c>
       <c r="F690" t="n">
         <v>477180</v>
@@ -14372,16 +14372,16 @@
         <v>44250</v>
       </c>
       <c r="B698" t="n">
-        <v>243.8473968505859</v>
+        <v>243.8473815917969</v>
       </c>
       <c r="C698" t="n">
-        <v>250.7289737419669</v>
+        <v>250.7289580525621</v>
       </c>
       <c r="D698" t="n">
-        <v>241.4538088582955</v>
+        <v>241.4537937492856</v>
       </c>
       <c r="E698" t="n">
-        <v>247.7369811425732</v>
+        <v>247.7369656403928</v>
       </c>
       <c r="F698" t="n">
         <v>535220</v>
@@ -14472,16 +14472,16 @@
         <v>44257</v>
       </c>
       <c r="B703" t="n">
-        <v>245.3433837890625</v>
+        <v>245.3433685302734</v>
       </c>
       <c r="C703" t="n">
-        <v>246.5401777395433</v>
+        <v>246.5401624063213</v>
       </c>
       <c r="D703" t="n">
-        <v>231.8794176055164</v>
+        <v>231.8794031840999</v>
       </c>
       <c r="E703" t="n">
-        <v>242.6505935959654</v>
+        <v>242.6505785046507</v>
       </c>
       <c r="F703" t="n">
         <v>816593</v>
@@ -14492,16 +14492,16 @@
         <v>44258</v>
       </c>
       <c r="B704" t="n">
-        <v>241.6033935546875</v>
+        <v>241.6033782958984</v>
       </c>
       <c r="C704" t="n">
-        <v>245.9417887521817</v>
+        <v>245.9417732193955</v>
       </c>
       <c r="D704" t="n">
-        <v>231.1314198402428</v>
+        <v>231.1314052428255</v>
       </c>
       <c r="E704" t="n">
-        <v>242.9497962623404</v>
+        <v>242.9497809185175</v>
       </c>
       <c r="F704" t="n">
         <v>976053</v>
@@ -14552,16 +14552,16 @@
         <v>44263</v>
       </c>
       <c r="B707" t="n">
-        <v>224.5490417480469</v>
+        <v>224.5490264892578</v>
       </c>
       <c r="C707" t="n">
-        <v>232.0290233548181</v>
+        <v>232.0290075877416</v>
       </c>
       <c r="D707" t="n">
-        <v>221.7066578683107</v>
+        <v>221.7066428026703</v>
       </c>
       <c r="E707" t="n">
-        <v>225.7458509795795</v>
+        <v>225.7458356394636</v>
       </c>
       <c r="F707" t="n">
         <v>1054193</v>
@@ -14592,16 +14592,16 @@
         <v>44265</v>
       </c>
       <c r="B709" t="n">
-        <v>227.2418365478516</v>
+        <v>227.2418212890625</v>
       </c>
       <c r="C709" t="n">
-        <v>229.4858309236971</v>
+        <v>229.4858155142288</v>
       </c>
       <c r="D709" t="n">
-        <v>217.9666567507444</v>
+        <v>217.9666421147633</v>
       </c>
       <c r="E709" t="n">
-        <v>228.7378327984153</v>
+        <v>228.7378174391734</v>
       </c>
       <c r="F709" t="n">
         <v>667500</v>
@@ -14632,16 +14632,16 @@
         <v>44267</v>
       </c>
       <c r="B711" t="n">
-        <v>228.8874206542969</v>
+        <v>228.8874359130859</v>
       </c>
       <c r="C711" t="n">
-        <v>231.8794130811504</v>
+        <v>231.8794285394008</v>
       </c>
       <c r="D711" t="n">
-        <v>225.8954282274433</v>
+        <v>225.8954432867711</v>
       </c>
       <c r="E711" t="n">
-        <v>227.840220261286</v>
+        <v>227.8402354502634</v>
       </c>
       <c r="F711" t="n">
         <v>268453</v>
@@ -14652,16 +14652,16 @@
         <v>44270</v>
       </c>
       <c r="B712" t="n">
-        <v>231.5802154541016</v>
+        <v>231.5802307128906</v>
       </c>
       <c r="C712" t="n">
-        <v>232.3282135758642</v>
+        <v>232.3282288839388</v>
       </c>
       <c r="D712" t="n">
-        <v>225.5962304800004</v>
+        <v>225.5962453445055</v>
       </c>
       <c r="E712" t="n">
-        <v>228.8874252593682</v>
+        <v>228.8874403407297</v>
       </c>
       <c r="F712" t="n">
         <v>221460</v>
@@ -14852,16 +14852,16 @@
         <v>44284</v>
       </c>
       <c r="B722" t="n">
-        <v>223.801025390625</v>
+        <v>223.8010101318359</v>
       </c>
       <c r="C722" t="n">
-        <v>226.0450196902024</v>
+        <v>226.0450042784174</v>
       </c>
       <c r="D722" t="n">
-        <v>219.761847825834</v>
+        <v>219.7618328424367</v>
       </c>
       <c r="E722" t="n">
-        <v>226.0450196902024</v>
+        <v>226.0450042784174</v>
       </c>
       <c r="F722" t="n">
         <v>788160</v>
@@ -14952,16 +14952,16 @@
         <v>44292</v>
       </c>
       <c r="B727" t="n">
-        <v>219.1634521484375</v>
+        <v>219.1634368896484</v>
       </c>
       <c r="C727" t="n">
-        <v>222.9034427994347</v>
+        <v>222.9034272802568</v>
       </c>
       <c r="D727" t="n">
-        <v>215.4234614974403</v>
+        <v>215.4234464990401</v>
       </c>
       <c r="E727" t="n">
-        <v>221.1082442433439</v>
+        <v>221.1082288491528</v>
       </c>
       <c r="F727" t="n">
         <v>964873</v>
@@ -14972,16 +14972,16 @@
         <v>44293</v>
       </c>
       <c r="B728" t="n">
-        <v>227.6906280517578</v>
+        <v>227.6906127929688</v>
       </c>
       <c r="C728" t="n">
-        <v>230.3834182079792</v>
+        <v>230.3834027687316</v>
       </c>
       <c r="D728" t="n">
-        <v>219.1634465420062</v>
+        <v>219.16343185467</v>
       </c>
       <c r="E728" t="n">
-        <v>219.313040076995</v>
+        <v>219.3130253796337</v>
       </c>
       <c r="F728" t="n">
         <v>1567580</v>
@@ -15052,16 +15052,16 @@
         <v>44299</v>
       </c>
       <c r="B732" t="n">
-        <v>227.2418365478516</v>
+        <v>227.2418212890625</v>
       </c>
       <c r="C732" t="n">
-        <v>227.9898346731334</v>
+        <v>227.9898193641179</v>
       </c>
       <c r="D732" t="n">
-        <v>219.9114488328651</v>
+        <v>219.9114340662954</v>
       </c>
       <c r="E732" t="n">
-        <v>220.6594469581469</v>
+        <v>220.6594321413508</v>
       </c>
       <c r="F732" t="n">
         <v>596393</v>
@@ -15192,16 +15192,16 @@
         <v>44309</v>
       </c>
       <c r="B739" t="n">
-        <v>220.3602294921875</v>
+        <v>220.3602447509766</v>
       </c>
       <c r="C739" t="n">
-        <v>223.6514240604346</v>
+        <v>223.6514395471216</v>
       </c>
       <c r="D739" t="n">
-        <v>218.2658440164373</v>
+        <v>218.2658591302012</v>
       </c>
       <c r="E739" t="n">
-        <v>222.3050214404054</v>
+        <v>222.3050368338611</v>
       </c>
       <c r="F739" t="n">
         <v>863700</v>
@@ -15452,16 +15452,16 @@
         <v>44328</v>
       </c>
       <c r="B752" t="n">
-        <v>212.4675598144531</v>
+        <v>212.4675750732422</v>
       </c>
       <c r="C752" t="n">
-        <v>218.9014335816066</v>
+        <v>218.9014493024574</v>
       </c>
       <c r="D752" t="n">
-        <v>211.2705625215996</v>
+        <v>211.2705776944238</v>
       </c>
       <c r="E752" t="n">
-        <v>218.4525614993673</v>
+        <v>218.4525771879814</v>
       </c>
       <c r="F752" t="n">
         <v>1381546</v>
@@ -15472,16 +15472,16 @@
         <v>44329</v>
       </c>
       <c r="B753" t="n">
-        <v>218.4525756835938</v>
+        <v>218.4525604248047</v>
       </c>
       <c r="C753" t="n">
-        <v>221.7443298681609</v>
+        <v>221.7443143794447</v>
       </c>
       <c r="D753" t="n">
-        <v>214.4126962398362</v>
+        <v>214.4126812632304</v>
       </c>
       <c r="E753" t="n">
-        <v>214.7119493876418</v>
+        <v>214.7119343901334</v>
       </c>
       <c r="F753" t="n">
         <v>807133</v>
@@ -15512,16 +15512,16 @@
         <v>44333</v>
       </c>
       <c r="B755" t="n">
-        <v>218.6022033691406</v>
+        <v>218.6021881103516</v>
       </c>
       <c r="C755" t="n">
-        <v>222.9413361338301</v>
+        <v>222.9413205721625</v>
       </c>
       <c r="D755" t="n">
-        <v>217.8540780801009</v>
+        <v>217.8540628735322</v>
       </c>
       <c r="E755" t="n">
-        <v>219.2007096886316</v>
+        <v>219.2006943880658</v>
       </c>
       <c r="F755" t="n">
         <v>603380</v>
@@ -15532,16 +15532,16 @@
         <v>44334</v>
       </c>
       <c r="B756" t="n">
-        <v>219.7992095947266</v>
+        <v>219.7991943359375</v>
       </c>
       <c r="C756" t="n">
-        <v>223.2405827797657</v>
+        <v>223.2405672820714</v>
       </c>
       <c r="D756" t="n">
-        <v>215.6096959218293</v>
+        <v>215.6096809538825</v>
       </c>
       <c r="E756" t="n">
-        <v>218.7518311765023</v>
+        <v>218.7518159904238</v>
       </c>
       <c r="F756" t="n">
         <v>1363900</v>
@@ -15552,16 +15552,16 @@
         <v>44335</v>
       </c>
       <c r="B757" t="n">
-        <v>217.8540802001953</v>
+        <v>217.8540649414062</v>
       </c>
       <c r="C757" t="n">
-        <v>221.7443408734494</v>
+        <v>221.7443253421814</v>
       </c>
       <c r="D757" t="n">
-        <v>216.9563359328703</v>
+        <v>216.9563207369604</v>
       </c>
       <c r="E757" t="n">
-        <v>219.0510928508262</v>
+        <v>219.0510775081968</v>
       </c>
       <c r="F757" t="n">
         <v>577806</v>
@@ -15572,16 +15572,16 @@
         <v>44336</v>
       </c>
       <c r="B758" t="n">
-        <v>223.0909423828125</v>
+        <v>223.0909271240234</v>
       </c>
       <c r="C758" t="n">
-        <v>224.4375739145587</v>
+        <v>224.4375585636639</v>
       </c>
       <c r="D758" t="n">
-        <v>217.2555745934222</v>
+        <v>217.2555597337558</v>
       </c>
       <c r="E758" t="n">
-        <v>219.2006971898857</v>
+        <v>219.2006821971784</v>
       </c>
       <c r="F758" t="n">
         <v>585933</v>
@@ -15932,16 +15932,16 @@
         <v>44363</v>
       </c>
       <c r="B776" t="n">
-        <v>228.9263153076172</v>
+        <v>228.9263305664062</v>
       </c>
       <c r="C776" t="n">
-        <v>230.8714378183892</v>
+        <v>230.8714532068279</v>
       </c>
       <c r="D776" t="n">
-        <v>225.7841954994967</v>
+        <v>225.7842105488518</v>
       </c>
       <c r="E776" t="n">
-        <v>226.3826865378477</v>
+        <v>226.3827016270945</v>
       </c>
       <c r="F776" t="n">
         <v>725393</v>
@@ -16132,16 +16132,16 @@
         <v>44377</v>
       </c>
       <c r="B786" t="n">
-        <v>230.5721740722656</v>
+        <v>230.5721893310547</v>
       </c>
       <c r="C786" t="n">
-        <v>232.5173117141208</v>
+        <v>232.5173271016351</v>
       </c>
       <c r="D786" t="n">
-        <v>227.7293075245428</v>
+        <v>227.7293225951968</v>
       </c>
       <c r="E786" t="n">
-        <v>231.320299251242</v>
+        <v>231.3203145595405</v>
       </c>
       <c r="F786" t="n">
         <v>609766</v>
@@ -42352,19 +42352,39 @@
         <v>46296</v>
       </c>
       <c r="B2097" t="n">
-        <v>6.97</v>
+        <v>6.940000057220459</v>
       </c>
       <c r="C2097" t="n">
-        <v>6.97</v>
+        <v>6.960000038146973</v>
       </c>
       <c r="D2097" t="n">
-        <v>6.58</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="E2097" t="n">
-        <v>6.68</v>
+        <v>6.679999828338623</v>
       </c>
       <c r="F2097" t="n">
         <v>8107300</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>12580800</v>
       </c>
     </row>
   </sheetData>

--- a/database/HAPV3.xlsx
+++ b/database/HAPV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2106"/>
+  <dimension ref="A1:F2107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43216</v>
       </c>
       <c r="B2" t="n">
-        <v>81.53696441650391</v>
+        <v>81.53695678710938</v>
       </c>
       <c r="C2" t="n">
-        <v>85.66653394546317</v>
+        <v>85.66652592966578</v>
       </c>
       <c r="D2" t="n">
-        <v>79.57469361707308</v>
+        <v>79.57468617128777</v>
       </c>
       <c r="E2" t="n">
-        <v>84.93434134763869</v>
+        <v>84.9343334003524</v>
       </c>
       <c r="F2" t="n">
         <v>1956933</v>
@@ -472,16 +472,16 @@
         <v>43217</v>
       </c>
       <c r="B3" t="n">
-        <v>82.00556182861328</v>
+        <v>82.00557708740234</v>
       </c>
       <c r="C3" t="n">
-        <v>83.90925939176427</v>
+        <v>83.90927500477466</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54117679595947</v>
+        <v>80.54119178227016</v>
       </c>
       <c r="E3" t="n">
-        <v>81.9762753196798</v>
+        <v>81.97629057301951</v>
       </c>
       <c r="F3" t="n">
         <v>932166</v>
@@ -492,16 +492,16 @@
         <v>43220</v>
       </c>
       <c r="B4" t="n">
-        <v>80.98049163818359</v>
+        <v>80.98047637939453</v>
       </c>
       <c r="C4" t="n">
-        <v>82.00556416960269</v>
+        <v>82.00554871766383</v>
       </c>
       <c r="D4" t="n">
-        <v>80.68761909224075</v>
+        <v>80.68760388863633</v>
       </c>
       <c r="E4" t="n">
-        <v>81.56624417831694</v>
+        <v>81.56622880915717</v>
       </c>
       <c r="F4" t="n">
         <v>370366</v>
@@ -512,16 +512,16 @@
         <v>43222</v>
       </c>
       <c r="B5" t="n">
-        <v>79.98471069335938</v>
+        <v>79.98469543457031</v>
       </c>
       <c r="C5" t="n">
-        <v>81.85912174551177</v>
+        <v>81.85910612913884</v>
       </c>
       <c r="D5" t="n">
-        <v>79.0767916761844</v>
+        <v>79.07677659060025</v>
       </c>
       <c r="E5" t="n">
-        <v>79.0767916761844</v>
+        <v>79.07677659060025</v>
       </c>
       <c r="F5" t="n">
         <v>428333</v>
@@ -552,16 +552,16 @@
         <v>43224</v>
       </c>
       <c r="B7" t="n">
-        <v>78.3446044921875</v>
+        <v>78.34461212158203</v>
       </c>
       <c r="C7" t="n">
-        <v>81.0390752181759</v>
+        <v>81.03908310996475</v>
       </c>
       <c r="D7" t="n">
-        <v>77.31953192140176</v>
+        <v>77.31953945097214</v>
       </c>
       <c r="E7" t="n">
-        <v>81.0390752181759</v>
+        <v>81.03908310996475</v>
       </c>
       <c r="F7" t="n">
         <v>632800</v>
@@ -572,16 +572,16 @@
         <v>43227</v>
       </c>
       <c r="B8" t="n">
-        <v>79.07680511474609</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C8" t="n">
-        <v>79.07680511474609</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="D8" t="n">
-        <v>77.90529242187472</v>
+        <v>77.90527738914264</v>
       </c>
       <c r="E8" t="n">
-        <v>78.05173243951472</v>
+        <v>78.05171737852535</v>
       </c>
       <c r="F8" t="n">
         <v>375200</v>
@@ -592,16 +592,16 @@
         <v>43228</v>
       </c>
       <c r="B9" t="n">
-        <v>79.07680511474609</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C9" t="n">
-        <v>79.95543777233746</v>
+        <v>79.95542234400601</v>
       </c>
       <c r="D9" t="n">
-        <v>78.49105249243476</v>
+        <v>78.49103734667347</v>
       </c>
       <c r="E9" t="n">
-        <v>79.51611771941742</v>
+        <v>79.51610237585788</v>
       </c>
       <c r="F9" t="n">
         <v>315733</v>
@@ -612,16 +612,16 @@
         <v>43229</v>
       </c>
       <c r="B10" t="n">
-        <v>78.78392028808594</v>
+        <v>78.78389739990234</v>
       </c>
       <c r="C10" t="n">
-        <v>79.34038636267657</v>
+        <v>79.34036331282931</v>
       </c>
       <c r="D10" t="n">
-        <v>77.81742814763868</v>
+        <v>77.81740554023889</v>
       </c>
       <c r="E10" t="n">
-        <v>79.07680030555396</v>
+        <v>79.0767773322833</v>
       </c>
       <c r="F10" t="n">
         <v>333066</v>
@@ -632,16 +632,16 @@
         <v>43230</v>
       </c>
       <c r="B11" t="n">
-        <v>79.66255187988281</v>
+        <v>79.66253662109375</v>
       </c>
       <c r="C11" t="n">
-        <v>80.95121053351885</v>
+        <v>80.95119502789649</v>
       </c>
       <c r="D11" t="n">
-        <v>78.43246624969672</v>
+        <v>78.43245122652172</v>
       </c>
       <c r="E11" t="n">
-        <v>79.36967186613674</v>
+        <v>79.36965666344675</v>
       </c>
       <c r="F11" t="n">
         <v>396433</v>
@@ -712,16 +712,16 @@
         <v>43236</v>
       </c>
       <c r="B15" t="n">
-        <v>87.30663299560547</v>
+        <v>87.30662536621094</v>
       </c>
       <c r="C15" t="n">
-        <v>87.30663299560547</v>
+        <v>87.30662536621094</v>
       </c>
       <c r="D15" t="n">
-        <v>83.61638402969096</v>
+        <v>83.61637672277325</v>
       </c>
       <c r="E15" t="n">
-        <v>84.78788903694259</v>
+        <v>84.7878816276515</v>
       </c>
       <c r="F15" t="n">
         <v>589600</v>
@@ -732,16 +732,16 @@
         <v>43237</v>
       </c>
       <c r="B16" t="n">
-        <v>88.74172210693359</v>
+        <v>88.74173736572266</v>
       </c>
       <c r="C16" t="n">
-        <v>90.73328636771173</v>
+        <v>90.7333019689424</v>
       </c>
       <c r="D16" t="n">
-        <v>87.86308972008348</v>
+        <v>87.86310482779517</v>
       </c>
       <c r="E16" t="n">
-        <v>87.86308972008348</v>
+        <v>87.86310482779517</v>
       </c>
       <c r="F16" t="n">
         <v>520533</v>
@@ -752,16 +752,16 @@
         <v>43238</v>
       </c>
       <c r="B17" t="n">
-        <v>86.69158172607422</v>
+        <v>86.69157409667969</v>
       </c>
       <c r="C17" t="n">
-        <v>88.74172654739176</v>
+        <v>88.74171873757183</v>
       </c>
       <c r="D17" t="n">
-        <v>85.60794375102347</v>
+        <v>85.60793621699578</v>
       </c>
       <c r="E17" t="n">
-        <v>88.74172654739176</v>
+        <v>88.74171873757183</v>
       </c>
       <c r="F17" t="n">
         <v>980066</v>
@@ -772,16 +772,16 @@
         <v>43241</v>
       </c>
       <c r="B18" t="n">
-        <v>90.20612335205078</v>
+        <v>90.20611572265625</v>
       </c>
       <c r="C18" t="n">
-        <v>91.05546194037015</v>
+        <v>91.05545423914081</v>
       </c>
       <c r="D18" t="n">
-        <v>84.93433551979336</v>
+        <v>84.93432833627266</v>
       </c>
       <c r="E18" t="n">
-        <v>86.9844731633802</v>
+        <v>86.9844658064643</v>
       </c>
       <c r="F18" t="n">
         <v>633933</v>
@@ -792,16 +792,16 @@
         <v>43242</v>
       </c>
       <c r="B19" t="n">
-        <v>95.91721343994141</v>
+        <v>95.91720581054688</v>
       </c>
       <c r="C19" t="n">
-        <v>96.06365342339224</v>
+        <v>96.06364578234965</v>
       </c>
       <c r="D19" t="n">
-        <v>90.20611367133475</v>
+        <v>90.20610649620939</v>
       </c>
       <c r="E19" t="n">
-        <v>90.20611367133475</v>
+        <v>90.20610649620939</v>
       </c>
       <c r="F19" t="n">
         <v>462766</v>
@@ -812,16 +812,16 @@
         <v>43243</v>
       </c>
       <c r="B20" t="n">
-        <v>95.74150085449219</v>
+        <v>95.74148559570312</v>
       </c>
       <c r="C20" t="n">
-        <v>95.91722737050549</v>
+        <v>95.91721208371003</v>
       </c>
       <c r="D20" t="n">
-        <v>90.79187934307389</v>
+        <v>90.79186487313009</v>
       </c>
       <c r="E20" t="n">
-        <v>95.91722737050549</v>
+        <v>95.91721208371003</v>
       </c>
       <c r="F20" t="n">
         <v>487666</v>
@@ -852,16 +852,16 @@
         <v>43245</v>
       </c>
       <c r="B22" t="n">
-        <v>90.7625732421875</v>
+        <v>90.76258087158203</v>
       </c>
       <c r="C22" t="n">
-        <v>90.87971926208031</v>
+        <v>90.879726901322</v>
       </c>
       <c r="D22" t="n">
-        <v>87.95094959281705</v>
+        <v>87.95095698586984</v>
       </c>
       <c r="E22" t="n">
-        <v>88.77100897329892</v>
+        <v>88.77101643528491</v>
       </c>
       <c r="F22" t="n">
         <v>562433</v>
@@ -872,16 +872,16 @@
         <v>43248</v>
       </c>
       <c r="B23" t="n">
-        <v>86.39869689941406</v>
+        <v>86.39872741699219</v>
       </c>
       <c r="C23" t="n">
-        <v>90.76256447690039</v>
+        <v>90.76259653587526</v>
       </c>
       <c r="D23" t="n">
-        <v>85.02217171263833</v>
+        <v>85.02220174400294</v>
       </c>
       <c r="E23" t="n">
-        <v>90.76256447690039</v>
+        <v>90.76259653587526</v>
       </c>
       <c r="F23" t="n">
         <v>427433</v>
@@ -912,16 +912,16 @@
         <v>43250</v>
       </c>
       <c r="B25" t="n">
-        <v>87.86310577392578</v>
+        <v>87.86309814453125</v>
       </c>
       <c r="C25" t="n">
-        <v>90.05968341827392</v>
+        <v>90.05967559814454</v>
       </c>
       <c r="D25" t="n">
-        <v>85.49080162009987</v>
+        <v>85.49079419669903</v>
       </c>
       <c r="E25" t="n">
-        <v>88.15597832422354</v>
+        <v>88.15597066939809</v>
       </c>
       <c r="F25" t="n">
         <v>493866</v>
@@ -932,16 +932,16 @@
         <v>43252</v>
       </c>
       <c r="B26" t="n">
-        <v>87.54093170166016</v>
+        <v>87.54092407226562</v>
       </c>
       <c r="C26" t="n">
-        <v>90.76258161432011</v>
+        <v>90.76257370415134</v>
       </c>
       <c r="D26" t="n">
-        <v>84.90504173548175</v>
+        <v>84.90503433581111</v>
       </c>
       <c r="E26" t="n">
-        <v>89.70822264854989</v>
+        <v>89.70821483027095</v>
       </c>
       <c r="F26" t="n">
         <v>391033</v>
@@ -952,16 +952,16 @@
         <v>43255</v>
       </c>
       <c r="B27" t="n">
-        <v>88.74172210693359</v>
+        <v>88.74173736572266</v>
       </c>
       <c r="C27" t="n">
-        <v>90.20610693560165</v>
+        <v>90.2061224461859</v>
       </c>
       <c r="D27" t="n">
-        <v>86.72087134130153</v>
+        <v>86.72088625261327</v>
       </c>
       <c r="E27" t="n">
-        <v>88.44884216190142</v>
+        <v>88.44885737033093</v>
       </c>
       <c r="F27" t="n">
         <v>304000</v>
@@ -992,16 +992,16 @@
         <v>43257</v>
       </c>
       <c r="B29" t="n">
-        <v>83.41136932373047</v>
+        <v>83.41138458251953</v>
       </c>
       <c r="C29" t="n">
-        <v>85.46150676870901</v>
+        <v>85.46152240253825</v>
       </c>
       <c r="D29" t="n">
-        <v>81.71267741515801</v>
+        <v>81.7126923631983</v>
       </c>
       <c r="E29" t="n">
-        <v>84.9929003064225</v>
+        <v>84.99291585452761</v>
       </c>
       <c r="F29" t="n">
         <v>443766</v>
@@ -1032,16 +1032,16 @@
         <v>43259</v>
       </c>
       <c r="B31" t="n">
-        <v>80.98049163818359</v>
+        <v>80.98047637939453</v>
       </c>
       <c r="C31" t="n">
-        <v>83.14778274009986</v>
+        <v>83.1477670729379</v>
       </c>
       <c r="D31" t="n">
-        <v>79.07679402068831</v>
+        <v>79.0767791206044</v>
       </c>
       <c r="E31" t="n">
-        <v>79.75041353837787</v>
+        <v>79.75039851136687</v>
       </c>
       <c r="F31" t="n">
         <v>443000</v>
@@ -1052,16 +1052,16 @@
         <v>43262</v>
       </c>
       <c r="B32" t="n">
-        <v>81.41981506347656</v>
+        <v>81.41980743408203</v>
       </c>
       <c r="C32" t="n">
-        <v>82.73776019642489</v>
+        <v>82.73775244353311</v>
       </c>
       <c r="D32" t="n">
-        <v>78.93035735260352</v>
+        <v>78.93034995648213</v>
       </c>
       <c r="E32" t="n">
-        <v>81.478388085486</v>
+        <v>81.47838045060293</v>
       </c>
       <c r="F32" t="n">
         <v>202266</v>
@@ -1072,16 +1072,16 @@
         <v>43263</v>
       </c>
       <c r="B33" t="n">
-        <v>82.2398681640625</v>
+        <v>82.23986053466797</v>
       </c>
       <c r="C33" t="n">
-        <v>83.38208679661591</v>
+        <v>83.38207906125773</v>
       </c>
       <c r="D33" t="n">
-        <v>80.07257694439825</v>
+        <v>80.07256951606338</v>
       </c>
       <c r="E33" t="n">
-        <v>81.41981605297228</v>
+        <v>81.419808499654</v>
       </c>
       <c r="F33" t="n">
         <v>203566</v>
@@ -1092,16 +1092,16 @@
         <v>43264</v>
       </c>
       <c r="B34" t="n">
-        <v>78.3153076171875</v>
+        <v>78.31531524658203</v>
       </c>
       <c r="C34" t="n">
-        <v>82.32772294015612</v>
+        <v>82.32773096043591</v>
       </c>
       <c r="D34" t="n">
-        <v>77.70026117681101</v>
+        <v>77.70026874628836</v>
       </c>
       <c r="E34" t="n">
-        <v>82.32772294015612</v>
+        <v>82.32773096043591</v>
       </c>
       <c r="F34" t="n">
         <v>786033</v>
@@ -1132,16 +1132,16 @@
         <v>43266</v>
       </c>
       <c r="B36" t="n">
-        <v>79.07680511474609</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C36" t="n">
-        <v>79.22324513238611</v>
+        <v>79.22322984533973</v>
       </c>
       <c r="D36" t="n">
-        <v>75.12296187970931</v>
+        <v>75.12294738386028</v>
       </c>
       <c r="E36" t="n">
-        <v>79.13537814250262</v>
+        <v>79.13536287241121</v>
       </c>
       <c r="F36" t="n">
         <v>389566</v>
@@ -1172,16 +1172,16 @@
         <v>43270</v>
       </c>
       <c r="B38" t="n">
-        <v>81.56624603271484</v>
+        <v>81.56623840332031</v>
       </c>
       <c r="C38" t="n">
-        <v>83.14778463045384</v>
+        <v>83.14777685312824</v>
       </c>
       <c r="D38" t="n">
-        <v>77.02665815728874</v>
+        <v>77.02665095250988</v>
       </c>
       <c r="E38" t="n">
-        <v>77.84671024246967</v>
+        <v>77.84670296098628</v>
       </c>
       <c r="F38" t="n">
         <v>159600</v>
@@ -1212,16 +1212,16 @@
         <v>43272</v>
       </c>
       <c r="B40" t="n">
-        <v>82.62059020996094</v>
+        <v>82.62059783935547</v>
       </c>
       <c r="C40" t="n">
-        <v>85.46150038223338</v>
+        <v>85.46150827396475</v>
       </c>
       <c r="D40" t="n">
-        <v>80.10184649091977</v>
+        <v>80.10185388772712</v>
       </c>
       <c r="E40" t="n">
-        <v>83.46993610077617</v>
+        <v>83.46994380860144</v>
       </c>
       <c r="F40" t="n">
         <v>246900</v>
@@ -1252,16 +1252,16 @@
         <v>43276</v>
       </c>
       <c r="B42" t="n">
-        <v>86.39869689941406</v>
+        <v>86.39872741699219</v>
       </c>
       <c r="C42" t="n">
-        <v>86.39869689941406</v>
+        <v>86.39872741699219</v>
       </c>
       <c r="D42" t="n">
-        <v>84.34855981856863</v>
+        <v>84.34858961200136</v>
       </c>
       <c r="E42" t="n">
-        <v>85.87151751606882</v>
+        <v>85.8715478474377</v>
       </c>
       <c r="F42" t="n">
         <v>909166</v>
@@ -1272,16 +1272,16 @@
         <v>43277</v>
       </c>
       <c r="B43" t="n">
-        <v>86.75017547607422</v>
+        <v>86.75016784667969</v>
       </c>
       <c r="C43" t="n">
-        <v>87.86310757617932</v>
+        <v>87.86309984890605</v>
       </c>
       <c r="D43" t="n">
-        <v>85.08077732591656</v>
+        <v>85.08076984334015</v>
       </c>
       <c r="E43" t="n">
-        <v>86.60373547379767</v>
+        <v>86.60372785728207</v>
       </c>
       <c r="F43" t="n">
         <v>153233</v>
@@ -1292,16 +1292,16 @@
         <v>43278</v>
       </c>
       <c r="B44" t="n">
-        <v>87.86310577392578</v>
+        <v>87.86309814453125</v>
       </c>
       <c r="C44" t="n">
-        <v>88.59529832204183</v>
+        <v>88.59529062906901</v>
       </c>
       <c r="D44" t="n">
-        <v>85.25650209021211</v>
+        <v>85.25649468715613</v>
       </c>
       <c r="E44" t="n">
-        <v>86.98447322653696</v>
+        <v>86.98446567343652</v>
       </c>
       <c r="F44" t="n">
         <v>117966</v>
@@ -1312,16 +1312,16 @@
         <v>43279</v>
       </c>
       <c r="B45" t="n">
-        <v>88.68315887451172</v>
+        <v>88.68315124511719</v>
       </c>
       <c r="C45" t="n">
-        <v>88.68315887451172</v>
+        <v>88.68315124511719</v>
       </c>
       <c r="D45" t="n">
-        <v>85.37364911475306</v>
+        <v>85.373641770075</v>
       </c>
       <c r="E45" t="n">
-        <v>87.8631067863316</v>
+        <v>87.86309922748598</v>
       </c>
       <c r="F45" t="n">
         <v>922066</v>
@@ -1332,16 +1332,16 @@
         <v>43280</v>
       </c>
       <c r="B46" t="n">
-        <v>87.54093170166016</v>
+        <v>87.54092407226562</v>
       </c>
       <c r="C46" t="n">
-        <v>89.41534267530913</v>
+        <v>89.41533488255534</v>
       </c>
       <c r="D46" t="n">
-        <v>85.37364075477042</v>
+        <v>85.3736333142603</v>
       </c>
       <c r="E46" t="n">
-        <v>87.45307217863621</v>
+        <v>87.45306455689882</v>
       </c>
       <c r="F46" t="n">
         <v>492266</v>
@@ -1392,16 +1392,16 @@
         <v>43285</v>
       </c>
       <c r="B49" t="n">
-        <v>85.78366088867188</v>
+        <v>85.78367614746094</v>
       </c>
       <c r="C49" t="n">
-        <v>87.07231916401665</v>
+        <v>87.07233465202611</v>
       </c>
       <c r="D49" t="n">
-        <v>84.14354967930161</v>
+        <v>84.14356464635551</v>
       </c>
       <c r="E49" t="n">
-        <v>86.66228577548961</v>
+        <v>86.66230119056429</v>
       </c>
       <c r="F49" t="n">
         <v>320933</v>
@@ -1432,16 +1432,16 @@
         <v>43287</v>
       </c>
       <c r="B51" t="n">
-        <v>83.61637878417969</v>
+        <v>83.61638641357422</v>
       </c>
       <c r="C51" t="n">
-        <v>85.57864917581456</v>
+        <v>85.57865698425219</v>
       </c>
       <c r="D51" t="n">
-        <v>83.61637878417969</v>
+        <v>83.61638641357422</v>
       </c>
       <c r="E51" t="n">
-        <v>85.52007616360061</v>
+        <v>85.52008396669386</v>
       </c>
       <c r="F51" t="n">
         <v>769100</v>
@@ -1472,16 +1472,16 @@
         <v>43292</v>
       </c>
       <c r="B53" t="n">
-        <v>84.08497619628906</v>
+        <v>84.08498382568359</v>
       </c>
       <c r="C53" t="n">
-        <v>86.25226698638772</v>
+        <v>86.25227481242993</v>
       </c>
       <c r="D53" t="n">
-        <v>82.64987783807528</v>
+        <v>82.6498853372571</v>
       </c>
       <c r="E53" t="n">
-        <v>83.79210369248307</v>
+        <v>83.792111295304</v>
       </c>
       <c r="F53" t="n">
         <v>271833</v>
@@ -1492,16 +1492,16 @@
         <v>43293</v>
       </c>
       <c r="B54" t="n">
-        <v>87.07233428955078</v>
+        <v>87.07234191894531</v>
       </c>
       <c r="C54" t="n">
-        <v>87.13090730598122</v>
+        <v>87.13091494050801</v>
       </c>
       <c r="D54" t="n">
-        <v>82.35701281247128</v>
+        <v>82.35702002870303</v>
       </c>
       <c r="E54" t="n">
-        <v>83.90925733385612</v>
+        <v>83.90926468609763</v>
       </c>
       <c r="F54" t="n">
         <v>235333</v>
@@ -1532,16 +1532,16 @@
         <v>43297</v>
       </c>
       <c r="B56" t="n">
-        <v>83.46994018554688</v>
+        <v>83.46995544433594</v>
       </c>
       <c r="C56" t="n">
-        <v>86.0179705344391</v>
+        <v>86.01798625902289</v>
       </c>
       <c r="D56" t="n">
-        <v>82.9134742155731</v>
+        <v>82.91348937263696</v>
       </c>
       <c r="E56" t="n">
-        <v>84.43643214429146</v>
+        <v>84.43644757976085</v>
       </c>
       <c r="F56" t="n">
         <v>173400</v>
@@ -1552,16 +1552,16 @@
         <v>43298</v>
       </c>
       <c r="B57" t="n">
-        <v>83.08920288085938</v>
+        <v>83.08921051025391</v>
       </c>
       <c r="C57" t="n">
-        <v>84.58287434213068</v>
+        <v>84.58288210867671</v>
       </c>
       <c r="D57" t="n">
-        <v>82.35701040390309</v>
+        <v>82.35701796606644</v>
       </c>
       <c r="E57" t="n">
-        <v>84.11426787964996</v>
+        <v>84.11427560316773</v>
       </c>
       <c r="F57" t="n">
         <v>152666</v>
@@ -1572,16 +1572,16 @@
         <v>43299</v>
       </c>
       <c r="B58" t="n">
-        <v>85.90081787109375</v>
+        <v>85.90082550048828</v>
       </c>
       <c r="C58" t="n">
-        <v>85.90081787109375</v>
+        <v>85.90082550048828</v>
       </c>
       <c r="D58" t="n">
-        <v>82.73774850917258</v>
+        <v>82.73775585763492</v>
       </c>
       <c r="E58" t="n">
-        <v>82.91347499862636</v>
+        <v>82.91348236269609</v>
       </c>
       <c r="F58" t="n">
         <v>444433</v>
@@ -1592,16 +1592,16 @@
         <v>43300</v>
       </c>
       <c r="B59" t="n">
-        <v>85.19791412353516</v>
+        <v>85.19790649414062</v>
       </c>
       <c r="C59" t="n">
-        <v>86.5451530603807</v>
+        <v>86.54514531034216</v>
       </c>
       <c r="D59" t="n">
-        <v>83.61638312566897</v>
+        <v>83.6163756378991</v>
       </c>
       <c r="E59" t="n">
-        <v>85.52008060393275</v>
+        <v>85.52007294568851</v>
       </c>
       <c r="F59" t="n">
         <v>169366</v>
@@ -1612,16 +1612,16 @@
         <v>43301</v>
       </c>
       <c r="B60" t="n">
-        <v>87.86310577392578</v>
+        <v>87.86309814453125</v>
       </c>
       <c r="C60" t="n">
-        <v>88.77102483151958</v>
+        <v>88.77101712328796</v>
       </c>
       <c r="D60" t="n">
-        <v>85.54937464050987</v>
+        <v>85.54936721202297</v>
       </c>
       <c r="E60" t="n">
-        <v>86.39872067769367</v>
+        <v>86.39871317545573</v>
       </c>
       <c r="F60" t="n">
         <v>356866</v>
@@ -1632,16 +1632,16 @@
         <v>43304</v>
       </c>
       <c r="B61" t="n">
-        <v>87.65809631347656</v>
+        <v>87.6580810546875</v>
       </c>
       <c r="C61" t="n">
-        <v>89.2689214743867</v>
+        <v>89.26890593519866</v>
       </c>
       <c r="D61" t="n">
-        <v>86.72089070762384</v>
+        <v>86.7208756119757</v>
       </c>
       <c r="E61" t="n">
-        <v>89.00532797534333</v>
+        <v>89.00531248203944</v>
       </c>
       <c r="F61" t="n">
         <v>145300</v>
@@ -1672,16 +1672,16 @@
         <v>43306</v>
       </c>
       <c r="B63" t="n">
-        <v>83.99713897705078</v>
+        <v>83.99712371826172</v>
       </c>
       <c r="C63" t="n">
-        <v>89.91325301370145</v>
+        <v>89.91323668020036</v>
       </c>
       <c r="D63" t="n">
-        <v>83.99713897705078</v>
+        <v>83.99712371826172</v>
       </c>
       <c r="E63" t="n">
-        <v>88.77103430433299</v>
+        <v>88.77101817832556</v>
       </c>
       <c r="F63" t="n">
         <v>653300</v>
@@ -1712,16 +1712,16 @@
         <v>43308</v>
       </c>
       <c r="B65" t="n">
-        <v>82.62059020996094</v>
+        <v>82.62059783935547</v>
       </c>
       <c r="C65" t="n">
-        <v>82.62059020996094</v>
+        <v>82.62059783935547</v>
       </c>
       <c r="D65" t="n">
-        <v>80.04327348060372</v>
+        <v>80.04328087200228</v>
       </c>
       <c r="E65" t="n">
-        <v>81.24407232980825</v>
+        <v>81.24407983209161</v>
       </c>
       <c r="F65" t="n">
         <v>199833</v>
@@ -1732,16 +1732,16 @@
         <v>43311</v>
       </c>
       <c r="B66" t="n">
-        <v>80.39472961425781</v>
+        <v>80.39473724365234</v>
       </c>
       <c r="C66" t="n">
-        <v>82.59130696682358</v>
+        <v>82.59131480467153</v>
       </c>
       <c r="D66" t="n">
-        <v>79.80897714322296</v>
+        <v>79.80898471703006</v>
       </c>
       <c r="E66" t="n">
-        <v>82.53273395419413</v>
+        <v>82.53274178648354</v>
       </c>
       <c r="F66" t="n">
         <v>306800</v>
@@ -1752,16 +1752,16 @@
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>82.47415161132812</v>
+        <v>82.47415924072266</v>
       </c>
       <c r="C67" t="n">
-        <v>82.56201857651402</v>
+        <v>82.56202621403682</v>
       </c>
       <c r="D67" t="n">
-        <v>79.36965539261392</v>
+        <v>79.3696627348224</v>
       </c>
       <c r="E67" t="n">
-        <v>81.24407368469829</v>
+        <v>81.24408120030263</v>
       </c>
       <c r="F67" t="n">
         <v>430700</v>
@@ -1792,16 +1792,16 @@
         <v>43314</v>
       </c>
       <c r="B69" t="n">
-        <v>84.75859832763672</v>
+        <v>84.75860595703125</v>
       </c>
       <c r="C69" t="n">
-        <v>84.75859832763672</v>
+        <v>84.75860595703125</v>
       </c>
       <c r="D69" t="n">
-        <v>83.23564040405101</v>
+        <v>83.2356478963592</v>
       </c>
       <c r="E69" t="n">
-        <v>83.23564040405101</v>
+        <v>83.2356478963592</v>
       </c>
       <c r="F69" t="n">
         <v>63600</v>
@@ -1832,16 +1832,16 @@
         <v>43318</v>
       </c>
       <c r="B71" t="n">
-        <v>81.33192443847656</v>
+        <v>81.33194732666016</v>
       </c>
       <c r="C71" t="n">
-        <v>83.55778800673762</v>
+        <v>83.55781152131701</v>
       </c>
       <c r="D71" t="n">
-        <v>81.12691147279418</v>
+        <v>81.12693430328365</v>
       </c>
       <c r="E71" t="n">
-        <v>83.38206154354619</v>
+        <v>83.38208500867314</v>
       </c>
       <c r="F71" t="n">
         <v>242633</v>
@@ -1872,16 +1872,16 @@
         <v>43320</v>
       </c>
       <c r="B73" t="n">
-        <v>78.78392028808594</v>
+        <v>78.78389739990234</v>
       </c>
       <c r="C73" t="n">
-        <v>80.24830547892952</v>
+        <v>80.24828216531499</v>
       </c>
       <c r="D73" t="n">
-        <v>77.11452206431403</v>
+        <v>77.11449966112144</v>
       </c>
       <c r="E73" t="n">
-        <v>79.77970638887859</v>
+        <v>79.77968321140075</v>
       </c>
       <c r="F73" t="n">
         <v>270133</v>
@@ -1892,16 +1892,16 @@
         <v>43321</v>
       </c>
       <c r="B74" t="n">
-        <v>78.95962524414062</v>
+        <v>78.95964813232422</v>
       </c>
       <c r="C74" t="n">
-        <v>79.13535171697887</v>
+        <v>79.13537465610065</v>
       </c>
       <c r="D74" t="n">
-        <v>76.85091501832781</v>
+        <v>76.85093729525538</v>
       </c>
       <c r="E74" t="n">
-        <v>78.19814634459027</v>
+        <v>78.19816901204246</v>
       </c>
       <c r="F74" t="n">
         <v>546266</v>
@@ -1912,16 +1912,16 @@
         <v>43322</v>
       </c>
       <c r="B75" t="n">
-        <v>78.87178039550781</v>
+        <v>78.87176513671875</v>
       </c>
       <c r="C75" t="n">
-        <v>80.36545196820988</v>
+        <v>80.36543642045031</v>
       </c>
       <c r="D75" t="n">
-        <v>78.16887437347211</v>
+        <v>78.16885925066951</v>
       </c>
       <c r="E75" t="n">
-        <v>79.13536642964741</v>
+        <v>79.13535111986414</v>
       </c>
       <c r="F75" t="n">
         <v>176700</v>
@@ -1932,16 +1932,16 @@
         <v>43325</v>
       </c>
       <c r="B76" t="n">
-        <v>79.07680511474609</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C76" t="n">
-        <v>80.10187034172877</v>
+        <v>80.10185488514145</v>
       </c>
       <c r="D76" t="n">
-        <v>77.7588598524834</v>
+        <v>77.7588448480072</v>
       </c>
       <c r="E76" t="n">
-        <v>78.93036509710609</v>
+        <v>78.93034986657432</v>
       </c>
       <c r="F76" t="n">
         <v>160400</v>
@@ -1972,16 +1972,16 @@
         <v>43327</v>
       </c>
       <c r="B78" t="n">
-        <v>76.14801025390625</v>
+        <v>76.14802551269531</v>
       </c>
       <c r="C78" t="n">
-        <v>77.67096807554556</v>
+        <v>77.67098363950991</v>
       </c>
       <c r="D78" t="n">
-        <v>76.14801025390625</v>
+        <v>76.14802551269531</v>
       </c>
       <c r="E78" t="n">
-        <v>77.02664263110059</v>
+        <v>77.0266580659529</v>
       </c>
       <c r="F78" t="n">
         <v>702366</v>
@@ -1992,16 +1992,16 @@
         <v>43328</v>
       </c>
       <c r="B79" t="n">
-        <v>73.51214599609375</v>
+        <v>73.51211547851562</v>
       </c>
       <c r="C79" t="n">
-        <v>76.6459374508561</v>
+        <v>76.64590563232663</v>
       </c>
       <c r="D79" t="n">
-        <v>72.69209370949214</v>
+        <v>72.69206353234769</v>
       </c>
       <c r="E79" t="n">
-        <v>76.32377086044133</v>
+        <v>76.32373917565498</v>
       </c>
       <c r="F79" t="n">
         <v>1651000</v>
@@ -2032,16 +2032,16 @@
         <v>43332</v>
       </c>
       <c r="B81" t="n">
-        <v>72.34061431884766</v>
+        <v>72.34062194824219</v>
       </c>
       <c r="C81" t="n">
-        <v>73.01423377256823</v>
+        <v>73.01424147300597</v>
       </c>
       <c r="D81" t="n">
-        <v>71.75486183433918</v>
+        <v>71.75486940195739</v>
       </c>
       <c r="E81" t="n">
-        <v>71.95987483150479</v>
+        <v>71.95988242074468</v>
       </c>
       <c r="F81" t="n">
         <v>425766</v>
@@ -2052,16 +2052,16 @@
         <v>43333</v>
       </c>
       <c r="B82" t="n">
-        <v>71.60841369628906</v>
+        <v>71.60842895507812</v>
       </c>
       <c r="C82" t="n">
-        <v>72.57490555807503</v>
+        <v>72.5749210228105</v>
       </c>
       <c r="D82" t="n">
-        <v>70.31975539782574</v>
+        <v>70.31977038201907</v>
       </c>
       <c r="E82" t="n">
-        <v>71.63770019994226</v>
+        <v>71.63771546497189</v>
       </c>
       <c r="F82" t="n">
         <v>1384333</v>
@@ -2072,16 +2072,16 @@
         <v>43334</v>
       </c>
       <c r="B83" t="n">
-        <v>73.51214599609375</v>
+        <v>73.51211547851562</v>
       </c>
       <c r="C83" t="n">
-        <v>73.68787255011547</v>
+        <v>73.68784195958683</v>
       </c>
       <c r="D83" t="n">
-        <v>70.96412213515323</v>
+        <v>70.96409267535293</v>
       </c>
       <c r="E83" t="n">
-        <v>70.96412213515323</v>
+        <v>70.96409267535293</v>
       </c>
       <c r="F83" t="n">
         <v>518466</v>
@@ -2132,16 +2132,16 @@
         <v>43339</v>
       </c>
       <c r="B86" t="n">
-        <v>76.03085327148438</v>
+        <v>76.03086853027344</v>
       </c>
       <c r="C86" t="n">
-        <v>76.44087921246464</v>
+        <v>76.44089455354266</v>
       </c>
       <c r="D86" t="n">
-        <v>73.65854968689001</v>
+        <v>73.65856446957658</v>
       </c>
       <c r="E86" t="n">
-        <v>75.29866089905705</v>
+        <v>75.29867601090092</v>
       </c>
       <c r="F86" t="n">
         <v>318500</v>
@@ -2152,16 +2152,16 @@
         <v>43340</v>
       </c>
       <c r="B87" t="n">
-        <v>75.24009704589844</v>
+        <v>75.24011993408203</v>
       </c>
       <c r="C87" t="n">
-        <v>76.14801599608937</v>
+        <v>76.14803916046368</v>
       </c>
       <c r="D87" t="n">
-        <v>73.89286559810573</v>
+        <v>73.8928880764589</v>
       </c>
       <c r="E87" t="n">
-        <v>75.91371649391823</v>
+        <v>75.91373958701817</v>
       </c>
       <c r="F87" t="n">
         <v>298400</v>
@@ -2172,16 +2172,16 @@
         <v>43341</v>
       </c>
       <c r="B88" t="n">
-        <v>74.42002868652344</v>
+        <v>74.4200439453125</v>
       </c>
       <c r="C88" t="n">
-        <v>76.14800685934951</v>
+        <v>76.14802247243639</v>
       </c>
       <c r="D88" t="n">
-        <v>73.45353683881748</v>
+        <v>73.45355189944088</v>
       </c>
       <c r="E88" t="n">
-        <v>75.67940046298681</v>
+        <v>75.6794159799925</v>
       </c>
       <c r="F88" t="n">
         <v>162200</v>
@@ -2192,16 +2192,16 @@
         <v>43342</v>
       </c>
       <c r="B89" t="n">
-        <v>75.85513305664062</v>
+        <v>75.85514068603516</v>
       </c>
       <c r="C89" t="n">
-        <v>75.85513305664062</v>
+        <v>75.85514068603516</v>
       </c>
       <c r="D89" t="n">
-        <v>73.39496975973056</v>
+        <v>73.39497714168559</v>
       </c>
       <c r="E89" t="n">
-        <v>74.18573520369333</v>
+        <v>74.18574266518235</v>
       </c>
       <c r="F89" t="n">
         <v>206466</v>
@@ -2292,16 +2292,16 @@
         <v>43349</v>
       </c>
       <c r="B94" t="n">
-        <v>74.21502685546875</v>
+        <v>74.21501159667969</v>
       </c>
       <c r="C94" t="n">
-        <v>76.52875778485787</v>
+        <v>76.52874205036014</v>
       </c>
       <c r="D94" t="n">
-        <v>71.46198341524806</v>
+        <v>71.46196872249138</v>
       </c>
       <c r="E94" t="n">
-        <v>74.15645384022376</v>
+        <v>74.15643859347746</v>
       </c>
       <c r="F94" t="n">
         <v>139100</v>
@@ -2312,16 +2312,16 @@
         <v>43353</v>
       </c>
       <c r="B95" t="n">
-        <v>75.50366973876953</v>
+        <v>75.50368499755859</v>
       </c>
       <c r="C95" t="n">
-        <v>76.73375494265879</v>
+        <v>76.7337704500399</v>
       </c>
       <c r="D95" t="n">
-        <v>74.42002449100325</v>
+        <v>74.42003953079482</v>
       </c>
       <c r="E95" t="n">
-        <v>75.65010969489252</v>
+        <v>75.65012498327611</v>
       </c>
       <c r="F95" t="n">
         <v>157400</v>
@@ -2332,16 +2332,16 @@
         <v>43354</v>
       </c>
       <c r="B96" t="n">
-        <v>73.45354461669922</v>
+        <v>73.45355987548828</v>
       </c>
       <c r="C96" t="n">
-        <v>75.18152297249823</v>
+        <v>75.18153859024693</v>
       </c>
       <c r="D96" t="n">
-        <v>73.45354461669922</v>
+        <v>73.45355987548828</v>
       </c>
       <c r="E96" t="n">
-        <v>74.44933052131992</v>
+        <v>74.44934598696744</v>
       </c>
       <c r="F96" t="n">
         <v>250666</v>
@@ -2352,16 +2352,16 @@
         <v>43355</v>
       </c>
       <c r="B97" t="n">
-        <v>72.95565032958984</v>
+        <v>72.95566558837891</v>
       </c>
       <c r="C97" t="n">
-        <v>74.65434214798188</v>
+        <v>74.65435776205501</v>
       </c>
       <c r="D97" t="n">
-        <v>71.34483292506654</v>
+        <v>71.34484784695061</v>
       </c>
       <c r="E97" t="n">
-        <v>73.21924377820952</v>
+        <v>73.21925909212956</v>
       </c>
       <c r="F97" t="n">
         <v>133333</v>
@@ -2372,16 +2372,16 @@
         <v>43356</v>
       </c>
       <c r="B98" t="n">
-        <v>71.60841369628906</v>
+        <v>71.60842895507812</v>
       </c>
       <c r="C98" t="n">
-        <v>73.86356385653835</v>
+        <v>73.86357959586955</v>
       </c>
       <c r="D98" t="n">
-        <v>70.43690886068462</v>
+        <v>70.43692386984178</v>
       </c>
       <c r="E98" t="n">
-        <v>73.77570434557876</v>
+        <v>73.77572006618828</v>
       </c>
       <c r="F98" t="n">
         <v>250366</v>
@@ -2392,16 +2392,16 @@
         <v>43357</v>
       </c>
       <c r="B99" t="n">
-        <v>69.79257202148438</v>
+        <v>69.79258728027344</v>
       </c>
       <c r="C99" t="n">
-        <v>72.28202896599223</v>
+        <v>72.28204476905265</v>
       </c>
       <c r="D99" t="n">
-        <v>69.70471251551726</v>
+        <v>69.70472775509755</v>
       </c>
       <c r="E99" t="n">
-        <v>70.96408423876569</v>
+        <v>70.96409975368313</v>
       </c>
       <c r="F99" t="n">
         <v>269466</v>
@@ -2432,16 +2432,16 @@
         <v>43361</v>
       </c>
       <c r="B101" t="n">
-        <v>74.50791931152344</v>
+        <v>74.50789642333984</v>
       </c>
       <c r="C101" t="n">
-        <v>75.35726541611382</v>
+        <v>75.35724226701849</v>
       </c>
       <c r="D101" t="n">
-        <v>73.62928669440379</v>
+        <v>73.62926407612848</v>
       </c>
       <c r="E101" t="n">
-        <v>74.56649233658196</v>
+        <v>74.56646943040525</v>
       </c>
       <c r="F101" t="n">
         <v>194766</v>
@@ -2472,16 +2472,16 @@
         <v>43363</v>
       </c>
       <c r="B103" t="n">
-        <v>68.24034118652344</v>
+        <v>68.24033355712891</v>
       </c>
       <c r="C103" t="n">
-        <v>69.58757267942752</v>
+        <v>69.58756489941005</v>
       </c>
       <c r="D103" t="n">
-        <v>65.63373027563168</v>
+        <v>65.63372293766099</v>
       </c>
       <c r="E103" t="n">
-        <v>69.41184618485332</v>
+        <v>69.4118384244824</v>
       </c>
       <c r="F103" t="n">
         <v>1256966</v>
@@ -2492,16 +2492,16 @@
         <v>43364</v>
       </c>
       <c r="B104" t="n">
-        <v>69.35326385498047</v>
+        <v>69.35327911376953</v>
       </c>
       <c r="C104" t="n">
-        <v>71.16910157229026</v>
+        <v>71.16911723059167</v>
       </c>
       <c r="D104" t="n">
-        <v>67.88887907961748</v>
+        <v>67.88889401621928</v>
       </c>
       <c r="E104" t="n">
-        <v>67.94745208719324</v>
+        <v>67.94746703668201</v>
       </c>
       <c r="F104" t="n">
         <v>293166</v>
@@ -2532,16 +2532,16 @@
         <v>43368</v>
       </c>
       <c r="B106" t="n">
-        <v>63.90575790405273</v>
+        <v>63.90576553344727</v>
       </c>
       <c r="C106" t="n">
-        <v>67.21526727343412</v>
+        <v>67.21527529793472</v>
       </c>
       <c r="D106" t="n">
-        <v>61.62131724810718</v>
+        <v>61.62132460477356</v>
       </c>
       <c r="E106" t="n">
-        <v>64.46222388346429</v>
+        <v>64.46223157929256</v>
       </c>
       <c r="F106" t="n">
         <v>629433</v>
@@ -2552,16 +2552,16 @@
         <v>43369</v>
       </c>
       <c r="B107" t="n">
-        <v>65.0186767578125</v>
+        <v>65.01868438720703</v>
       </c>
       <c r="C107" t="n">
-        <v>66.4830614030256</v>
+        <v>66.48306920425335</v>
       </c>
       <c r="D107" t="n">
-        <v>63.14426619951865</v>
+        <v>63.14427360896688</v>
       </c>
       <c r="E107" t="n">
-        <v>63.93503152449517</v>
+        <v>63.93503902673306</v>
       </c>
       <c r="F107" t="n">
         <v>469400</v>
@@ -2572,16 +2572,16 @@
         <v>43370</v>
       </c>
       <c r="B108" t="n">
-        <v>68.591796875</v>
+        <v>68.59178161621094</v>
       </c>
       <c r="C108" t="n">
-        <v>69.85116144605384</v>
+        <v>69.85114590710914</v>
       </c>
       <c r="D108" t="n">
-        <v>65.07726684520698</v>
+        <v>65.07725236825299</v>
       </c>
       <c r="E108" t="n">
-        <v>65.48730031418111</v>
+        <v>65.48728574601192</v>
       </c>
       <c r="F108" t="n">
         <v>605400</v>
@@ -2592,16 +2592,16 @@
         <v>43371</v>
       </c>
       <c r="B109" t="n">
-        <v>70.29046630859375</v>
+        <v>70.29048919677734</v>
       </c>
       <c r="C109" t="n">
-        <v>71.34482509080165</v>
+        <v>71.34484832230859</v>
       </c>
       <c r="D109" t="n">
-        <v>67.3324103764931</v>
+        <v>67.33243230146601</v>
       </c>
       <c r="E109" t="n">
-        <v>68.59178212497824</v>
+        <v>68.5918044600314</v>
       </c>
       <c r="F109" t="n">
         <v>612400</v>
@@ -2612,16 +2612,16 @@
         <v>43374</v>
       </c>
       <c r="B110" t="n">
-        <v>69.11896514892578</v>
+        <v>69.11894989013672</v>
       </c>
       <c r="C110" t="n">
-        <v>70.20261060743866</v>
+        <v>70.20259510942266</v>
       </c>
       <c r="D110" t="n">
-        <v>68.41606662967828</v>
+        <v>68.41605152606198</v>
       </c>
       <c r="E110" t="n">
-        <v>70.20261060743866</v>
+        <v>70.20259510942266</v>
       </c>
       <c r="F110" t="n">
         <v>385466</v>
@@ -2632,16 +2632,16 @@
         <v>43375</v>
       </c>
       <c r="B111" t="n">
-        <v>69.14825439453125</v>
+        <v>69.14824676513672</v>
       </c>
       <c r="C111" t="n">
-        <v>70.2611862845098</v>
+        <v>70.2611785323212</v>
       </c>
       <c r="D111" t="n">
-        <v>67.97674204575357</v>
+        <v>67.97673454561654</v>
       </c>
       <c r="E111" t="n">
-        <v>69.20682740508386</v>
+        <v>69.20681976922674</v>
       </c>
       <c r="F111" t="n">
         <v>391400</v>
@@ -2672,16 +2672,16 @@
         <v>43377</v>
       </c>
       <c r="B113" t="n">
-        <v>70.29046630859375</v>
+        <v>70.29048919677734</v>
       </c>
       <c r="C113" t="n">
-        <v>72.13559045333467</v>
+        <v>72.1356139423329</v>
       </c>
       <c r="D113" t="n">
-        <v>67.71314980647165</v>
+        <v>67.71317185542203</v>
       </c>
       <c r="E113" t="n">
-        <v>70.55405228002282</v>
+        <v>70.55407525403604</v>
       </c>
       <c r="F113" t="n">
         <v>201700</v>
@@ -2712,16 +2712,16 @@
         <v>43381</v>
       </c>
       <c r="B115" t="n">
-        <v>69.55828094482422</v>
+        <v>69.55828857421875</v>
       </c>
       <c r="C115" t="n">
-        <v>70.90551233649205</v>
+        <v>70.90552011365561</v>
       </c>
       <c r="D115" t="n">
-        <v>68.85537501934654</v>
+        <v>68.8553825716439</v>
       </c>
       <c r="E115" t="n">
-        <v>68.85537501934654</v>
+        <v>68.8553825716439</v>
       </c>
       <c r="F115" t="n">
         <v>697200</v>
@@ -2752,16 +2752,16 @@
         <v>43383</v>
       </c>
       <c r="B117" t="n">
-        <v>69.14825439453125</v>
+        <v>69.14824676513672</v>
       </c>
       <c r="C117" t="n">
-        <v>71.72557113429701</v>
+        <v>71.72556322053715</v>
       </c>
       <c r="D117" t="n">
-        <v>67.24454962085997</v>
+        <v>67.24454220150855</v>
       </c>
       <c r="E117" t="n">
-        <v>67.36170309021169</v>
+        <v>67.36169565793428</v>
       </c>
       <c r="F117" t="n">
         <v>149833</v>
@@ -2772,16 +2772,16 @@
         <v>43384</v>
       </c>
       <c r="B118" t="n">
-        <v>70.87622833251953</v>
+        <v>70.87623596191406</v>
       </c>
       <c r="C118" t="n">
-        <v>71.63770729591425</v>
+        <v>71.63771500727735</v>
       </c>
       <c r="D118" t="n">
-        <v>68.62107794888951</v>
+        <v>68.62108533553082</v>
       </c>
       <c r="E118" t="n">
-        <v>69.08967695024926</v>
+        <v>69.08968438733241</v>
       </c>
       <c r="F118" t="n">
         <v>258833</v>
@@ -2792,16 +2792,16 @@
         <v>43388</v>
       </c>
       <c r="B119" t="n">
-        <v>72.0477294921875</v>
+        <v>72.04774475097656</v>
       </c>
       <c r="C119" t="n">
-        <v>72.89707537878911</v>
+        <v>72.89709081745879</v>
       </c>
       <c r="D119" t="n">
-        <v>66.77595003899427</v>
+        <v>66.77596418128775</v>
       </c>
       <c r="E119" t="n">
-        <v>71.5791305154908</v>
+        <v>71.57914567503659</v>
       </c>
       <c r="F119" t="n">
         <v>520433</v>
@@ -2812,16 +2812,16 @@
         <v>43389</v>
       </c>
       <c r="B120" t="n">
-        <v>73.83429718017578</v>
+        <v>73.83428192138672</v>
       </c>
       <c r="C120" t="n">
-        <v>75.85514840562809</v>
+        <v>75.85513272920463</v>
       </c>
       <c r="D120" t="n">
-        <v>71.34484687394362</v>
+        <v>71.34483212963087</v>
       </c>
       <c r="E120" t="n">
-        <v>71.98917247207794</v>
+        <v>71.98915759460718</v>
       </c>
       <c r="F120" t="n">
         <v>484533</v>
@@ -2832,16 +2832,16 @@
         <v>43390</v>
       </c>
       <c r="B121" t="n">
-        <v>74.91792297363281</v>
+        <v>74.91793823242188</v>
       </c>
       <c r="C121" t="n">
-        <v>75.8844148392387</v>
+        <v>75.88443029487647</v>
       </c>
       <c r="D121" t="n">
-        <v>73.27781172835662</v>
+        <v>73.27782665309864</v>
       </c>
       <c r="E121" t="n">
-        <v>73.27781172835662</v>
+        <v>73.27782665309864</v>
       </c>
       <c r="F121" t="n">
         <v>520600</v>
@@ -2852,16 +2852,16 @@
         <v>43391</v>
       </c>
       <c r="B122" t="n">
-        <v>75.56227111816406</v>
+        <v>75.56227874755859</v>
       </c>
       <c r="C122" t="n">
-        <v>76.79234921449461</v>
+        <v>76.79235696808804</v>
       </c>
       <c r="D122" t="n">
-        <v>74.88865160237759</v>
+        <v>74.88865916375791</v>
       </c>
       <c r="E122" t="n">
-        <v>74.91793811206438</v>
+        <v>74.9179456764017</v>
       </c>
       <c r="F122" t="n">
         <v>252733</v>
@@ -2912,16 +2912,16 @@
         <v>43396</v>
       </c>
       <c r="B125" t="n">
-        <v>75.44512176513672</v>
+        <v>75.44509887695312</v>
       </c>
       <c r="C125" t="n">
-        <v>76.14802782912525</v>
+        <v>76.14800472769734</v>
       </c>
       <c r="D125" t="n">
-        <v>74.15646313057375</v>
+        <v>74.15644063333731</v>
       </c>
       <c r="E125" t="n">
-        <v>74.80079617197926</v>
+        <v>74.8007734792681</v>
       </c>
       <c r="F125" t="n">
         <v>244366</v>
@@ -2932,16 +2932,16 @@
         <v>43397</v>
       </c>
       <c r="B126" t="n">
-        <v>74.3907470703125</v>
+        <v>74.39075469970703</v>
       </c>
       <c r="C126" t="n">
-        <v>75.26937946605956</v>
+        <v>75.26938718556521</v>
       </c>
       <c r="D126" t="n">
-        <v>74.24430709631358</v>
+        <v>74.24431471068945</v>
       </c>
       <c r="E126" t="n">
-        <v>75.26937946605956</v>
+        <v>75.26938718556521</v>
       </c>
       <c r="F126" t="n">
         <v>414300</v>
@@ -2952,16 +2952,16 @@
         <v>43398</v>
       </c>
       <c r="B127" t="n">
-        <v>76.00157165527344</v>
+        <v>76.0015869140625</v>
       </c>
       <c r="C127" t="n">
-        <v>76.00157165527344</v>
+        <v>76.0015869140625</v>
       </c>
       <c r="D127" t="n">
-        <v>73.10208848230262</v>
+        <v>73.10210315896421</v>
       </c>
       <c r="E127" t="n">
-        <v>74.56647332131847</v>
+        <v>74.56648829198372</v>
       </c>
       <c r="F127" t="n">
         <v>495966</v>
@@ -2972,16 +2972,16 @@
         <v>43399</v>
       </c>
       <c r="B128" t="n">
-        <v>74.97651672363281</v>
+        <v>74.97650909423828</v>
       </c>
       <c r="C128" t="n">
-        <v>78.02244057845078</v>
+        <v>78.02243263911183</v>
       </c>
       <c r="D128" t="n">
-        <v>73.36569898473449</v>
+        <v>73.36569151925214</v>
       </c>
       <c r="E128" t="n">
-        <v>76.11874282434466</v>
+        <v>76.1187350787205</v>
       </c>
       <c r="F128" t="n">
         <v>546200</v>
@@ -2992,16 +2992,16 @@
         <v>43402</v>
       </c>
       <c r="B129" t="n">
-        <v>75.50366973876953</v>
+        <v>75.50368499755859</v>
       </c>
       <c r="C129" t="n">
-        <v>76.44087503041283</v>
+        <v>76.44089047860484</v>
       </c>
       <c r="D129" t="n">
-        <v>75.18151077319365</v>
+        <v>75.18152596687653</v>
       </c>
       <c r="E129" t="n">
-        <v>76.38230202726186</v>
+        <v>76.38231746361667</v>
       </c>
       <c r="F129" t="n">
         <v>188000</v>
@@ -3012,16 +3012,16 @@
         <v>43403</v>
       </c>
       <c r="B130" t="n">
-        <v>74.56649017333984</v>
+        <v>74.56648254394531</v>
       </c>
       <c r="C130" t="n">
-        <v>76.14802883827332</v>
+        <v>76.14802104706102</v>
       </c>
       <c r="D130" t="n">
-        <v>73.6585710700305</v>
+        <v>73.65856353353124</v>
       </c>
       <c r="E130" t="n">
-        <v>75.65013579497513</v>
+        <v>75.65012805470559</v>
       </c>
       <c r="F130" t="n">
         <v>1306966</v>
@@ -3032,16 +3032,16 @@
         <v>43404</v>
       </c>
       <c r="B131" t="n">
-        <v>74.62505340576172</v>
+        <v>74.62506103515625</v>
       </c>
       <c r="C131" t="n">
-        <v>76.61661022238727</v>
+        <v>76.61661805539134</v>
       </c>
       <c r="D131" t="n">
-        <v>73.86356703676205</v>
+        <v>73.86357458830497</v>
       </c>
       <c r="E131" t="n">
-        <v>75.67940482390277</v>
+        <v>75.67941256109036</v>
       </c>
       <c r="F131" t="n">
         <v>863500</v>
@@ -3052,16 +3052,16 @@
         <v>43405</v>
       </c>
       <c r="B132" t="n">
-        <v>75.35724639892578</v>
+        <v>75.35725402832031</v>
       </c>
       <c r="C132" t="n">
-        <v>78.08099565225757</v>
+        <v>78.08100355741267</v>
       </c>
       <c r="D132" t="n">
-        <v>74.15644755052168</v>
+        <v>74.15645505834372</v>
       </c>
       <c r="E132" t="n">
-        <v>75.65011889855732</v>
+        <v>75.65012655760316</v>
       </c>
       <c r="F132" t="n">
         <v>289433</v>
@@ -3072,16 +3072,16 @@
         <v>43409</v>
       </c>
       <c r="B133" t="n">
-        <v>76.38232421875</v>
+        <v>76.38231658935547</v>
       </c>
       <c r="C133" t="n">
-        <v>76.85093072483949</v>
+        <v>76.85092304863853</v>
       </c>
       <c r="D133" t="n">
-        <v>73.98073356462973</v>
+        <v>73.98072617511639</v>
       </c>
       <c r="E133" t="n">
-        <v>75.82585818240808</v>
+        <v>75.82585060859577</v>
       </c>
       <c r="F133" t="n">
         <v>315933</v>
@@ -3092,16 +3092,16 @@
         <v>43410</v>
       </c>
       <c r="B134" t="n">
-        <v>75.12295532226562</v>
+        <v>75.12294769287109</v>
       </c>
       <c r="C134" t="n">
-        <v>76.96808001802316</v>
+        <v>76.96807220124005</v>
       </c>
       <c r="D134" t="n">
-        <v>74.12717669608222</v>
+        <v>74.12716916781773</v>
       </c>
       <c r="E134" t="n">
-        <v>76.1773144193408</v>
+        <v>76.17730668286687</v>
       </c>
       <c r="F134" t="n">
         <v>244033</v>
@@ -3112,16 +3112,16 @@
         <v>43411</v>
       </c>
       <c r="B135" t="n">
-        <v>77.31952667236328</v>
+        <v>77.31951904296875</v>
       </c>
       <c r="C135" t="n">
-        <v>79.047505180294</v>
+        <v>79.04749738039364</v>
       </c>
       <c r="D135" t="n">
-        <v>75.56226910377396</v>
+        <v>75.56226164777432</v>
       </c>
       <c r="E135" t="n">
-        <v>75.56226910377396</v>
+        <v>75.56226164777432</v>
       </c>
       <c r="F135" t="n">
         <v>375833</v>
@@ -3132,16 +3132,16 @@
         <v>43412</v>
       </c>
       <c r="B136" t="n">
-        <v>77.31952667236328</v>
+        <v>77.31951904296875</v>
       </c>
       <c r="C136" t="n">
-        <v>79.25251819088371</v>
+        <v>79.25251037075398</v>
       </c>
       <c r="D136" t="n">
-        <v>76.14802162663706</v>
+        <v>76.14801411283914</v>
       </c>
       <c r="E136" t="n">
-        <v>77.29024016345724</v>
+        <v>77.29023253695252</v>
       </c>
       <c r="F136" t="n">
         <v>245533</v>
@@ -3152,16 +3152,16 @@
         <v>43413</v>
       </c>
       <c r="B137" t="n">
-        <v>76.73377990722656</v>
+        <v>76.7337646484375</v>
       </c>
       <c r="C137" t="n">
-        <v>79.07679762273497</v>
+        <v>79.07678189802839</v>
       </c>
       <c r="D137" t="n">
-        <v>75.21082174385769</v>
+        <v>75.21080678791435</v>
       </c>
       <c r="E137" t="n">
-        <v>77.31953247404167</v>
+        <v>77.31951709877359</v>
       </c>
       <c r="F137" t="n">
         <v>423466</v>
@@ -3172,16 +3172,16 @@
         <v>43416</v>
       </c>
       <c r="B138" t="n">
-        <v>76.79235076904297</v>
+        <v>76.79234313964844</v>
       </c>
       <c r="C138" t="n">
-        <v>77.78813680803749</v>
+        <v>77.78812907971066</v>
       </c>
       <c r="D138" t="n">
-        <v>75.79657217829622</v>
+        <v>75.79656464783326</v>
       </c>
       <c r="E138" t="n">
-        <v>77.02665774777567</v>
+        <v>77.02665009510251</v>
       </c>
       <c r="F138" t="n">
         <v>143933</v>
@@ -3192,16 +3192,16 @@
         <v>43417</v>
       </c>
       <c r="B139" t="n">
-        <v>75.26938629150391</v>
+        <v>75.26939392089844</v>
       </c>
       <c r="C139" t="n">
-        <v>77.84670325390931</v>
+        <v>77.84671114454375</v>
       </c>
       <c r="D139" t="n">
-        <v>74.91793330133525</v>
+        <v>74.91794089510609</v>
       </c>
       <c r="E139" t="n">
-        <v>77.26095075304393</v>
+        <v>77.2609585843058</v>
       </c>
       <c r="F139" t="n">
         <v>637900</v>
@@ -3212,16 +3212,16 @@
         <v>43418</v>
       </c>
       <c r="B140" t="n">
-        <v>79.36966705322266</v>
+        <v>79.36965942382812</v>
       </c>
       <c r="C140" t="n">
-        <v>80.33616657102803</v>
+        <v>80.33615884872891</v>
       </c>
       <c r="D140" t="n">
-        <v>71.02267654659238</v>
+        <v>71.02266971955076</v>
       </c>
       <c r="E140" t="n">
-        <v>75.0350922710638</v>
+        <v>75.03508505832947</v>
       </c>
       <c r="F140" t="n">
         <v>1608700</v>
@@ -3232,16 +3232,16 @@
         <v>43420</v>
       </c>
       <c r="B141" t="n">
-        <v>81.09763336181641</v>
+        <v>81.09764099121094</v>
       </c>
       <c r="C141" t="n">
-        <v>83.46993713625022</v>
+        <v>83.46994498882317</v>
       </c>
       <c r="D141" t="n">
-        <v>78.81318910394661</v>
+        <v>78.81319651842826</v>
       </c>
       <c r="E141" t="n">
-        <v>78.81318910394661</v>
+        <v>78.81319651842826</v>
       </c>
       <c r="F141" t="n">
         <v>652300</v>
@@ -3252,16 +3252,16 @@
         <v>43423</v>
       </c>
       <c r="B142" t="n">
-        <v>80.248291015625</v>
+        <v>80.24829864501953</v>
       </c>
       <c r="C142" t="n">
-        <v>81.53694945338003</v>
+        <v>81.53695720529036</v>
       </c>
       <c r="D142" t="n">
-        <v>79.77969201003057</v>
+        <v>79.77969959487429</v>
       </c>
       <c r="E142" t="n">
-        <v>80.65832445582875</v>
+        <v>80.65833212420613</v>
       </c>
       <c r="F142" t="n">
         <v>158533</v>
@@ -3292,16 +3292,16 @@
         <v>43426</v>
       </c>
       <c r="B144" t="n">
-        <v>79.07680511474609</v>
+        <v>79.07678985595703</v>
       </c>
       <c r="C144" t="n">
-        <v>80.24831035936879</v>
+        <v>80.24829487452415</v>
       </c>
       <c r="D144" t="n">
-        <v>77.78814636636166</v>
+        <v>77.78813135623429</v>
       </c>
       <c r="E144" t="n">
-        <v>79.5454042332957</v>
+        <v>79.54538888408497</v>
       </c>
       <c r="F144" t="n">
         <v>203833</v>
@@ -3312,16 +3312,16 @@
         <v>43427</v>
       </c>
       <c r="B145" t="n">
-        <v>79.51611328125</v>
+        <v>79.51609802246094</v>
       </c>
       <c r="C145" t="n">
-        <v>79.51611328125</v>
+        <v>79.51609802246094</v>
       </c>
       <c r="D145" t="n">
-        <v>77.31953548399726</v>
+        <v>77.31952064672171</v>
       </c>
       <c r="E145" t="n">
-        <v>78.63748067269924</v>
+        <v>78.63746558251587</v>
       </c>
       <c r="F145" t="n">
         <v>372100</v>
@@ -3332,16 +3332,16 @@
         <v>43430</v>
       </c>
       <c r="B146" t="n">
-        <v>78.75463104248047</v>
+        <v>78.75462341308594</v>
       </c>
       <c r="C146" t="n">
-        <v>80.33616967506701</v>
+        <v>80.33616189246013</v>
       </c>
       <c r="D146" t="n">
-        <v>76.23588681407345</v>
+        <v>76.23587942868353</v>
       </c>
       <c r="E146" t="n">
-        <v>80.27758920465774</v>
+        <v>80.27758142772588</v>
       </c>
       <c r="F146" t="n">
         <v>252366</v>
@@ -3372,16 +3372,16 @@
         <v>43432</v>
       </c>
       <c r="B148" t="n">
-        <v>84.52429962158203</v>
+        <v>84.52430725097656</v>
       </c>
       <c r="C148" t="n">
-        <v>86.22298404832937</v>
+        <v>86.2229918310518</v>
       </c>
       <c r="D148" t="n">
-        <v>80.54117083974624</v>
+        <v>80.54117810961267</v>
       </c>
       <c r="E148" t="n">
-        <v>81.18549633337582</v>
+        <v>81.18550366140083</v>
       </c>
       <c r="F148" t="n">
         <v>429500</v>
@@ -3392,16 +3392,16 @@
         <v>43433</v>
       </c>
       <c r="B149" t="n">
-        <v>84.1728515625</v>
+        <v>84.17285919189453</v>
       </c>
       <c r="C149" t="n">
-        <v>85.69580958938813</v>
+        <v>85.69581735682299</v>
       </c>
       <c r="D149" t="n">
-        <v>83.2942190668925</v>
+        <v>83.29422661664812</v>
       </c>
       <c r="E149" t="n">
-        <v>84.31929155314248</v>
+        <v>84.31929919581027</v>
       </c>
       <c r="F149" t="n">
         <v>232033</v>
@@ -3412,16 +3412,16 @@
         <v>43434</v>
       </c>
       <c r="B150" t="n">
-        <v>82.91347503662109</v>
+        <v>82.91348266601562</v>
       </c>
       <c r="C150" t="n">
-        <v>84.26070649088619</v>
+        <v>84.26071424424802</v>
       </c>
       <c r="D150" t="n">
-        <v>82.32772255425571</v>
+        <v>82.32773012975143</v>
       </c>
       <c r="E150" t="n">
-        <v>84.23141998400496</v>
+        <v>84.23142773467195</v>
       </c>
       <c r="F150" t="n">
         <v>464600</v>
@@ -3432,16 +3432,16 @@
         <v>43437</v>
       </c>
       <c r="B151" t="n">
-        <v>84.49501800537109</v>
+        <v>84.49500274658203</v>
       </c>
       <c r="C151" t="n">
-        <v>85.2857910448094</v>
+        <v>85.2857756432162</v>
       </c>
       <c r="D151" t="n">
-        <v>82.79633333056491</v>
+        <v>82.79631837853798</v>
       </c>
       <c r="E151" t="n">
-        <v>83.2942263630634</v>
+        <v>83.29421132112294</v>
       </c>
       <c r="F151" t="n">
         <v>313866</v>
@@ -3452,16 +3452,16 @@
         <v>43438</v>
       </c>
       <c r="B152" t="n">
-        <v>83.82139587402344</v>
+        <v>83.82140350341797</v>
       </c>
       <c r="C152" t="n">
-        <v>86.60372581394269</v>
+        <v>86.60373369658394</v>
       </c>
       <c r="D152" t="n">
-        <v>82.59131041965232</v>
+        <v>82.5913179370849</v>
       </c>
       <c r="E152" t="n">
-        <v>84.64144787810613</v>
+        <v>84.64145558214152</v>
       </c>
       <c r="F152" t="n">
         <v>207933</v>
@@ -3512,16 +3512,16 @@
         <v>43441</v>
       </c>
       <c r="B155" t="n">
-        <v>84.26071929931641</v>
+        <v>84.26070404052734</v>
       </c>
       <c r="C155" t="n">
-        <v>86.10584399577968</v>
+        <v>86.10582840285664</v>
       </c>
       <c r="D155" t="n">
-        <v>82.1812950639406</v>
+        <v>82.18128018171485</v>
       </c>
       <c r="E155" t="n">
-        <v>85.57866444704045</v>
+        <v>85.57864894958446</v>
       </c>
       <c r="F155" t="n">
         <v>485833</v>
@@ -3532,16 +3532,16 @@
         <v>43444</v>
       </c>
       <c r="B156" t="n">
-        <v>83.46994018554688</v>
+        <v>83.46995544433594</v>
       </c>
       <c r="C156" t="n">
-        <v>84.70002560010616</v>
+        <v>84.70004108376196</v>
       </c>
       <c r="D156" t="n">
-        <v>83.05991419677606</v>
+        <v>83.05992938061</v>
       </c>
       <c r="E156" t="n">
-        <v>84.31928611792657</v>
+        <v>84.319301531981</v>
       </c>
       <c r="F156" t="n">
         <v>313733</v>
@@ -3572,16 +3572,16 @@
         <v>43446</v>
       </c>
       <c r="B158" t="n">
-        <v>85.60794067382812</v>
+        <v>85.60795593261719</v>
       </c>
       <c r="C158" t="n">
-        <v>86.28155263970095</v>
+        <v>86.28156801855484</v>
       </c>
       <c r="D158" t="n">
-        <v>84.37785531490263</v>
+        <v>84.37787035444086</v>
       </c>
       <c r="E158" t="n">
-        <v>84.55358179474914</v>
+        <v>84.5535968656089</v>
       </c>
       <c r="F158" t="n">
         <v>243466</v>
@@ -3592,16 +3592,16 @@
         <v>43447</v>
       </c>
       <c r="B159" t="n">
-        <v>86.77945709228516</v>
+        <v>86.77944946289062</v>
       </c>
       <c r="C159" t="n">
-        <v>88.77102164547205</v>
+        <v>88.77101384098502</v>
       </c>
       <c r="D159" t="n">
-        <v>84.99290555142299</v>
+        <v>84.99289807909682</v>
       </c>
       <c r="E159" t="n">
-        <v>85.78367853981547</v>
+        <v>85.78367099796685</v>
       </c>
       <c r="F159" t="n">
         <v>486800</v>
@@ -3612,16 +3612,16 @@
         <v>43448</v>
       </c>
       <c r="B160" t="n">
-        <v>86.39869689941406</v>
+        <v>86.39872741699219</v>
       </c>
       <c r="C160" t="n">
-        <v>88.3023940212893</v>
+        <v>88.3024252112876</v>
       </c>
       <c r="D160" t="n">
-        <v>85.81294451177904</v>
+        <v>85.81297482245886</v>
       </c>
       <c r="E160" t="n">
-        <v>86.77943632378911</v>
+        <v>86.77946697585128</v>
       </c>
       <c r="F160" t="n">
         <v>286966</v>
@@ -3632,16 +3632,16 @@
         <v>43451</v>
       </c>
       <c r="B161" t="n">
-        <v>84.93785095214844</v>
+        <v>84.93785858154297</v>
       </c>
       <c r="C161" t="n">
-        <v>86.47038439559775</v>
+        <v>86.47039216264943</v>
       </c>
       <c r="D161" t="n">
-        <v>84.28946680602617</v>
+        <v>84.28947437718072</v>
       </c>
       <c r="E161" t="n">
-        <v>86.44091375169715</v>
+        <v>86.44092151610168</v>
       </c>
       <c r="F161" t="n">
         <v>205700</v>
@@ -3652,16 +3652,16 @@
         <v>43452</v>
       </c>
       <c r="B162" t="n">
-        <v>86.35250091552734</v>
+        <v>86.35251617431641</v>
       </c>
       <c r="C162" t="n">
-        <v>87.14823827281793</v>
+        <v>87.14825367221657</v>
       </c>
       <c r="D162" t="n">
-        <v>84.67260677509321</v>
+        <v>84.67262173703909</v>
       </c>
       <c r="E162" t="n">
-        <v>84.96732070608958</v>
+        <v>84.96733572011246</v>
       </c>
       <c r="F162" t="n">
         <v>387133</v>
@@ -3692,16 +3692,16 @@
         <v>43454</v>
       </c>
       <c r="B164" t="n">
-        <v>89.00496673583984</v>
+        <v>89.00497436523438</v>
       </c>
       <c r="C164" t="n">
-        <v>93.07208057875353</v>
+        <v>93.07208855677598</v>
       </c>
       <c r="D164" t="n">
-        <v>87.20718246605232</v>
+        <v>87.20718994134303</v>
       </c>
       <c r="E164" t="n">
-        <v>89.2702175271606</v>
+        <v>89.27022517929211</v>
       </c>
       <c r="F164" t="n">
         <v>975500</v>
@@ -3732,16 +3732,16 @@
         <v>43460</v>
       </c>
       <c r="B166" t="n">
-        <v>90.59646606445312</v>
+        <v>90.59644317626953</v>
       </c>
       <c r="C166" t="n">
-        <v>92.68896466922801</v>
+        <v>92.68894125239805</v>
       </c>
       <c r="D166" t="n">
-        <v>86.38199070969904</v>
+        <v>86.38196888625549</v>
       </c>
       <c r="E166" t="n">
-        <v>87.88505382672821</v>
+        <v>87.88503162355258</v>
       </c>
       <c r="F166" t="n">
         <v>396300</v>
@@ -3752,16 +3752,16 @@
         <v>43461</v>
       </c>
       <c r="B167" t="n">
-        <v>90.62592315673828</v>
+        <v>90.62591552734375</v>
       </c>
       <c r="C167" t="n">
-        <v>91.3627192799638</v>
+        <v>91.36271158854166</v>
       </c>
       <c r="D167" t="n">
-        <v>89.35863292538107</v>
+        <v>89.35862540267408</v>
       </c>
       <c r="E167" t="n">
-        <v>91.3627192799638</v>
+        <v>91.36271158854166</v>
       </c>
       <c r="F167" t="n">
         <v>343866</v>
@@ -3792,16 +3792,16 @@
         <v>43467</v>
       </c>
       <c r="B169" t="n">
-        <v>91.65743255615234</v>
+        <v>91.65744018554688</v>
       </c>
       <c r="C169" t="n">
-        <v>94.192013000172</v>
+        <v>94.19202084054029</v>
       </c>
       <c r="D169" t="n">
-        <v>90.3017303976449</v>
+        <v>90.3017379141933</v>
       </c>
       <c r="E169" t="n">
-        <v>92.21740480094809</v>
+        <v>92.21741247695367</v>
       </c>
       <c r="F169" t="n">
         <v>431033</v>
@@ -3852,16 +3852,16 @@
         <v>43472</v>
       </c>
       <c r="B172" t="n">
-        <v>91.24481964111328</v>
+        <v>91.24482727050781</v>
       </c>
       <c r="C172" t="n">
-        <v>91.65742362806702</v>
+        <v>91.65743129196125</v>
       </c>
       <c r="D172" t="n">
-        <v>89.88911761466086</v>
+        <v>89.88912513069897</v>
       </c>
       <c r="E172" t="n">
-        <v>89.88911761466086</v>
+        <v>89.88912513069897</v>
       </c>
       <c r="F172" t="n">
         <v>470133</v>
@@ -3892,16 +3892,16 @@
         <v>43474</v>
       </c>
       <c r="B174" t="n">
-        <v>91.36273193359375</v>
+        <v>91.36272430419922</v>
       </c>
       <c r="C174" t="n">
-        <v>91.92269676499649</v>
+        <v>91.92268908884118</v>
       </c>
       <c r="D174" t="n">
-        <v>89.71230808918374</v>
+        <v>89.71230059761056</v>
       </c>
       <c r="E174" t="n">
-        <v>89.71230808918374</v>
+        <v>89.71230059761056</v>
       </c>
       <c r="F174" t="n">
         <v>225833</v>
@@ -3912,16 +3912,16 @@
         <v>43475</v>
       </c>
       <c r="B175" t="n">
-        <v>93.39626312255859</v>
+        <v>93.39627075195312</v>
       </c>
       <c r="C175" t="n">
-        <v>94.84038451984462</v>
+        <v>94.84039226720716</v>
       </c>
       <c r="D175" t="n">
-        <v>91.09745564451151</v>
+        <v>91.09746308612006</v>
       </c>
       <c r="E175" t="n">
-        <v>91.09745564451151</v>
+        <v>91.09746308612006</v>
       </c>
       <c r="F175" t="n">
         <v>243466</v>
@@ -3952,16 +3952,16 @@
         <v>43479</v>
       </c>
       <c r="B177" t="n">
-        <v>94.63409423828125</v>
+        <v>94.63410186767578</v>
       </c>
       <c r="C177" t="n">
-        <v>96.40240040656253</v>
+        <v>96.40240817851779</v>
       </c>
       <c r="D177" t="n">
-        <v>92.74789049900588</v>
+        <v>92.74789797633478</v>
       </c>
       <c r="E177" t="n">
-        <v>92.9542000056291</v>
+        <v>92.95420749959067</v>
       </c>
       <c r="F177" t="n">
         <v>478500</v>
@@ -3972,16 +3972,16 @@
         <v>43480</v>
       </c>
       <c r="B178" t="n">
-        <v>93.42575073242188</v>
+        <v>93.42574310302734</v>
       </c>
       <c r="C178" t="n">
-        <v>99.26117866454547</v>
+        <v>99.26117055861442</v>
       </c>
       <c r="D178" t="n">
-        <v>92.7478958730117</v>
+        <v>92.7478882989726</v>
       </c>
       <c r="E178" t="n">
-        <v>94.69304101541225</v>
+        <v>94.69303328252744</v>
       </c>
       <c r="F178" t="n">
         <v>736266</v>
@@ -3992,16 +3992,16 @@
         <v>43481</v>
       </c>
       <c r="B179" t="n">
-        <v>98.43595123291016</v>
+        <v>98.43595886230469</v>
       </c>
       <c r="C179" t="n">
-        <v>100.0569040740519</v>
+        <v>100.0569118290803</v>
       </c>
       <c r="D179" t="n">
-        <v>93.74993155986996</v>
+        <v>93.74993882606901</v>
       </c>
       <c r="E179" t="n">
-        <v>93.89729227180597</v>
+        <v>93.89729954942638</v>
       </c>
       <c r="F179" t="n">
         <v>1131666</v>
@@ -4012,16 +4012,16 @@
         <v>43482</v>
       </c>
       <c r="B180" t="n">
-        <v>99.26116180419922</v>
+        <v>99.26116943359375</v>
       </c>
       <c r="C180" t="n">
-        <v>100.0274284742044</v>
+        <v>100.0274361624956</v>
       </c>
       <c r="D180" t="n">
-        <v>97.90545231565758</v>
+        <v>97.90545984084979</v>
       </c>
       <c r="E180" t="n">
-        <v>98.78960904838544</v>
+        <v>98.78961664153556</v>
       </c>
       <c r="F180" t="n">
         <v>313600</v>
@@ -4032,16 +4032,16 @@
         <v>43483</v>
       </c>
       <c r="B181" t="n">
-        <v>100.7937088012695</v>
+        <v>100.7937164306641</v>
       </c>
       <c r="C181" t="n">
-        <v>102.2673010571217</v>
+        <v>102.267308798057</v>
       </c>
       <c r="D181" t="n">
-        <v>98.73068114209212</v>
+        <v>98.73068861532957</v>
       </c>
       <c r="E181" t="n">
-        <v>99.67377928642814</v>
+        <v>99.67378683105167</v>
       </c>
       <c r="F181" t="n">
         <v>475600</v>
@@ -4052,16 +4052,16 @@
         <v>43486</v>
       </c>
       <c r="B182" t="n">
-        <v>101.3831253051758</v>
+        <v>101.3831405639648</v>
       </c>
       <c r="C182" t="n">
-        <v>102.3557014091906</v>
+        <v>102.3557168143584</v>
       </c>
       <c r="D182" t="n">
-        <v>98.22963936492125</v>
+        <v>98.22965414909113</v>
       </c>
       <c r="E182" t="n">
-        <v>100.7936900117306</v>
+        <v>100.793705181806</v>
       </c>
       <c r="F182" t="n">
         <v>260300</v>
@@ -4072,16 +4072,16 @@
         <v>43487</v>
       </c>
       <c r="B183" t="n">
-        <v>100.2632141113281</v>
+        <v>100.2632217407227</v>
       </c>
       <c r="C183" t="n">
-        <v>101.7662770044136</v>
+        <v>101.7662847481816</v>
       </c>
       <c r="D183" t="n">
-        <v>99.17275524868226</v>
+        <v>99.17276279509979</v>
       </c>
       <c r="E183" t="n">
-        <v>101.7662770044136</v>
+        <v>101.7662847481816</v>
       </c>
       <c r="F183" t="n">
         <v>236233</v>
@@ -4132,16 +4132,16 @@
         <v>43493</v>
       </c>
       <c r="B186" t="n">
-        <v>97.25709533691406</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C186" t="n">
-        <v>98.0528328094274</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="D186" t="n">
-        <v>95.96033436555834</v>
+        <v>95.96032683788904</v>
       </c>
       <c r="E186" t="n">
-        <v>98.0528328094274</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="F186" t="n">
         <v>263933</v>
@@ -4152,16 +4152,16 @@
         <v>43494</v>
       </c>
       <c r="B187" t="n">
-        <v>97.3160400390625</v>
+        <v>97.31602478027344</v>
       </c>
       <c r="C187" t="n">
-        <v>97.99389494386627</v>
+        <v>97.9938795787921</v>
       </c>
       <c r="D187" t="n">
-        <v>96.72660457600985</v>
+        <v>96.72658940964205</v>
       </c>
       <c r="E187" t="n">
-        <v>97.49287142748615</v>
+        <v>97.4928561409706</v>
       </c>
       <c r="F187" t="n">
         <v>185333</v>
@@ -4172,16 +4172,16 @@
         <v>43495</v>
       </c>
       <c r="B188" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73066711425781</v>
       </c>
       <c r="C188" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73066711425781</v>
       </c>
       <c r="D188" t="n">
-        <v>96.49083077174782</v>
+        <v>96.49080840281826</v>
       </c>
       <c r="E188" t="n">
-        <v>97.28656826289463</v>
+        <v>97.28654570949369</v>
       </c>
       <c r="F188" t="n">
         <v>447533</v>
@@ -4192,16 +4192,16 @@
         <v>43496</v>
       </c>
       <c r="B189" t="n">
-        <v>100.9115905761719</v>
+        <v>100.9115982055664</v>
       </c>
       <c r="C189" t="n">
-        <v>104.566100269176</v>
+        <v>104.5661081748688</v>
       </c>
       <c r="D189" t="n">
-        <v>99.2022183035879</v>
+        <v>99.20222580374578</v>
       </c>
       <c r="E189" t="n">
-        <v>99.79166115348703</v>
+        <v>99.79166869820958</v>
       </c>
       <c r="F189" t="n">
         <v>504800</v>
@@ -4232,16 +4232,16 @@
         <v>43500</v>
       </c>
       <c r="B191" t="n">
-        <v>100.2632141113281</v>
+        <v>100.2632217407227</v>
       </c>
       <c r="C191" t="n">
-        <v>102.2673004671346</v>
+        <v>102.2673082490274</v>
       </c>
       <c r="D191" t="n">
-        <v>99.55588863338727</v>
+        <v>99.55589620895881</v>
       </c>
       <c r="E191" t="n">
-        <v>100.7347669283146</v>
+        <v>100.7347745935913</v>
       </c>
       <c r="F191" t="n">
         <v>316266</v>
@@ -4252,16 +4252,16 @@
         <v>43501</v>
       </c>
       <c r="B192" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73066711425781</v>
       </c>
       <c r="C192" t="n">
-        <v>101.8547061650084</v>
+        <v>101.8546825526016</v>
       </c>
       <c r="D192" t="n">
-        <v>93.86783062467705</v>
+        <v>93.86780886382294</v>
       </c>
       <c r="E192" t="n">
-        <v>100.2632236876363</v>
+        <v>100.263200444174</v>
       </c>
       <c r="F192" t="n">
         <v>970333</v>
@@ -4312,16 +4312,16 @@
         <v>43504</v>
       </c>
       <c r="B195" t="n">
-        <v>97.16867065429688</v>
+        <v>97.16869354248047</v>
       </c>
       <c r="C195" t="n">
-        <v>98.524380343285</v>
+        <v>98.52440355080746</v>
       </c>
       <c r="D195" t="n">
-        <v>95.78349781411782</v>
+        <v>95.78352037602249</v>
       </c>
       <c r="E195" t="n">
-        <v>96.84448605026213</v>
+        <v>96.8445088620837</v>
       </c>
       <c r="F195" t="n">
         <v>210500</v>
@@ -4352,16 +4352,16 @@
         <v>43508</v>
       </c>
       <c r="B197" t="n">
-        <v>97.55180358886719</v>
+        <v>97.55181121826172</v>
       </c>
       <c r="C197" t="n">
-        <v>99.64430940508254</v>
+        <v>99.64431719812912</v>
       </c>
       <c r="D197" t="n">
-        <v>96.78553680915705</v>
+        <v>96.7855443786229</v>
       </c>
       <c r="E197" t="n">
-        <v>98.20018778405444</v>
+        <v>98.20019546415823</v>
       </c>
       <c r="F197" t="n">
         <v>301900</v>
@@ -4372,16 +4372,16 @@
         <v>43509</v>
       </c>
       <c r="B198" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73066711425781</v>
       </c>
       <c r="C198" t="n">
-        <v>99.88009026633756</v>
+        <v>99.88006711169493</v>
       </c>
       <c r="D198" t="n">
-        <v>96.28452873682379</v>
+        <v>96.28450641572007</v>
       </c>
       <c r="E198" t="n">
-        <v>97.25709761434527</v>
+        <v>97.25707506777634</v>
       </c>
       <c r="F198" t="n">
         <v>448033</v>
@@ -4412,16 +4412,16 @@
         <v>43511</v>
       </c>
       <c r="B200" t="n">
-        <v>99.40853118896484</v>
+        <v>99.40853881835938</v>
       </c>
       <c r="C200" t="n">
-        <v>100.086378497347</v>
+        <v>100.0863861787649</v>
       </c>
       <c r="D200" t="n">
-        <v>97.61074692461915</v>
+        <v>97.61075441603754</v>
       </c>
       <c r="E200" t="n">
-        <v>97.61074692461915</v>
+        <v>97.61075441603754</v>
       </c>
       <c r="F200" t="n">
         <v>157766</v>
@@ -4452,16 +4452,16 @@
         <v>43515</v>
       </c>
       <c r="B202" t="n">
-        <v>98.43595123291016</v>
+        <v>98.43595886230469</v>
       </c>
       <c r="C202" t="n">
-        <v>101.0000021373343</v>
+        <v>101.0000099654586</v>
       </c>
       <c r="D202" t="n">
-        <v>98.25911987760239</v>
+        <v>98.2591274932914</v>
       </c>
       <c r="E202" t="n">
-        <v>100.2337354293596</v>
+        <v>100.2337431980935</v>
       </c>
       <c r="F202" t="n">
         <v>215600</v>
@@ -4472,16 +4472,16 @@
         <v>43516</v>
       </c>
       <c r="B203" t="n">
-        <v>97.25709533691406</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C203" t="n">
-        <v>99.17276239854924</v>
+        <v>99.17275461887898</v>
       </c>
       <c r="D203" t="n">
-        <v>95.51825216243448</v>
+        <v>95.5182446694446</v>
       </c>
       <c r="E203" t="n">
-        <v>98.87804842487829</v>
+        <v>98.87804066832706</v>
       </c>
       <c r="F203" t="n">
         <v>616733</v>
@@ -4492,16 +4492,16 @@
         <v>43517</v>
       </c>
       <c r="B204" t="n">
-        <v>95.78349304199219</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C204" t="n">
-        <v>97.61074797039947</v>
+        <v>97.61076352027936</v>
       </c>
       <c r="D204" t="n">
-        <v>95.04669694166917</v>
+        <v>95.04671208308292</v>
       </c>
       <c r="E204" t="n">
-        <v>97.28655588743874</v>
+        <v>97.28657138567321</v>
       </c>
       <c r="F204" t="n">
         <v>542100</v>
@@ -4532,16 +4532,16 @@
         <v>43521</v>
       </c>
       <c r="B206" t="n">
-        <v>95.40036010742188</v>
+        <v>95.40036773681641</v>
       </c>
       <c r="C206" t="n">
-        <v>97.10972496939742</v>
+        <v>97.10973273549394</v>
       </c>
       <c r="D206" t="n">
-        <v>92.24687368297073</v>
+        <v>92.24688106017342</v>
       </c>
       <c r="E206" t="n">
-        <v>93.66151710543296</v>
+        <v>93.66152459576807</v>
       </c>
       <c r="F206" t="n">
         <v>404566</v>
@@ -4552,16 +4552,16 @@
         <v>43522</v>
       </c>
       <c r="B207" t="n">
-        <v>95.13510894775391</v>
+        <v>95.13511657714844</v>
       </c>
       <c r="C207" t="n">
-        <v>97.25708531592029</v>
+        <v>97.25709311548748</v>
       </c>
       <c r="D207" t="n">
-        <v>93.36680280269279</v>
+        <v>93.36681029027736</v>
       </c>
       <c r="E207" t="n">
-        <v>95.57719110532733</v>
+        <v>95.5771987701748</v>
       </c>
       <c r="F207" t="n">
         <v>332133</v>
@@ -4592,16 +4592,16 @@
         <v>43524</v>
       </c>
       <c r="B209" t="n">
-        <v>96.04872894287109</v>
+        <v>96.04874420166016</v>
       </c>
       <c r="C209" t="n">
-        <v>96.46134042353272</v>
+        <v>96.46135574787134</v>
       </c>
       <c r="D209" t="n">
-        <v>94.75196820597856</v>
+        <v>94.75198325875762</v>
       </c>
       <c r="E209" t="n">
-        <v>95.69506624234795</v>
+        <v>95.69508144495236</v>
       </c>
       <c r="F209" t="n">
         <v>596166</v>
@@ -4692,16 +4692,16 @@
         <v>43535</v>
       </c>
       <c r="B214" t="n">
-        <v>97.3160400390625</v>
+        <v>97.31602478027344</v>
       </c>
       <c r="C214" t="n">
-        <v>97.522342076377</v>
+        <v>97.52232678524055</v>
       </c>
       <c r="D214" t="n">
-        <v>96.19611041073888</v>
+        <v>96.19609532755058</v>
       </c>
       <c r="E214" t="n">
-        <v>97.2570987412808</v>
+        <v>97.25708349173351</v>
       </c>
       <c r="F214" t="n">
         <v>533833</v>
@@ -4712,16 +4712,16 @@
         <v>43536</v>
       </c>
       <c r="B215" t="n">
-        <v>97.25709533691406</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C215" t="n">
-        <v>98.49491501255126</v>
+        <v>98.49490728605517</v>
       </c>
       <c r="D215" t="n">
-        <v>95.34142078020059</v>
+        <v>95.34141330108237</v>
       </c>
       <c r="E215" t="n">
-        <v>96.84449127672777</v>
+        <v>96.84448367970022</v>
       </c>
       <c r="F215" t="n">
         <v>275666</v>
@@ -4732,16 +4732,16 @@
         <v>43537</v>
       </c>
       <c r="B216" t="n">
-        <v>95.78349304199219</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C216" t="n">
-        <v>97.58127732559895</v>
+        <v>97.58129287078403</v>
       </c>
       <c r="D216" t="n">
-        <v>95.40035966943042</v>
+        <v>95.40037486718441</v>
       </c>
       <c r="E216" t="n">
-        <v>97.43391660651884</v>
+        <v>97.43393212822862</v>
       </c>
       <c r="F216" t="n">
         <v>425833</v>
@@ -4772,16 +4772,16 @@
         <v>43539</v>
       </c>
       <c r="B218" t="n">
-        <v>89.29969024658203</v>
+        <v>89.29969787597656</v>
       </c>
       <c r="C218" t="n">
-        <v>92.15845526284264</v>
+        <v>92.15846313647816</v>
       </c>
       <c r="D218" t="n">
-        <v>88.91655686806337</v>
+        <v>88.91656446472457</v>
       </c>
       <c r="E218" t="n">
-        <v>91.0679964178041</v>
+        <v>91.06800419827536</v>
       </c>
       <c r="F218" t="n">
         <v>927800</v>
@@ -4792,16 +4792,16 @@
         <v>43542</v>
       </c>
       <c r="B219" t="n">
-        <v>86.64720916748047</v>
+        <v>86.64722442626953</v>
       </c>
       <c r="C219" t="n">
-        <v>89.3291499847229</v>
+        <v>89.32916571580841</v>
       </c>
       <c r="D219" t="n">
-        <v>83.84738578359665</v>
+        <v>83.84740054932983</v>
       </c>
       <c r="E219" t="n">
-        <v>89.29967934306256</v>
+        <v>89.29969506895821</v>
       </c>
       <c r="F219" t="n">
         <v>2555666</v>
@@ -4812,16 +4812,16 @@
         <v>43543</v>
       </c>
       <c r="B220" t="n">
-        <v>89.41757202148438</v>
+        <v>89.41758728027344</v>
       </c>
       <c r="C220" t="n">
-        <v>89.41757202148438</v>
+        <v>89.41758728027344</v>
       </c>
       <c r="D220" t="n">
-        <v>86.3525050209678</v>
+        <v>86.35251975671413</v>
       </c>
       <c r="E220" t="n">
-        <v>86.3525050209678</v>
+        <v>86.35251975671413</v>
       </c>
       <c r="F220" t="n">
         <v>1451666</v>
@@ -4832,16 +4832,16 @@
         <v>43544</v>
       </c>
       <c r="B221" t="n">
-        <v>88.65131378173828</v>
+        <v>88.65130615234375</v>
       </c>
       <c r="C221" t="n">
-        <v>89.94807475146169</v>
+        <v>89.948067010467</v>
       </c>
       <c r="D221" t="n">
-        <v>87.88504695804876</v>
+        <v>87.88503939459969</v>
       </c>
       <c r="E221" t="n">
-        <v>89.94807475146169</v>
+        <v>89.948067010467</v>
       </c>
       <c r="F221" t="n">
         <v>1179966</v>
@@ -4872,16 +4872,16 @@
         <v>43546</v>
       </c>
       <c r="B223" t="n">
-        <v>87.82610321044922</v>
+        <v>87.82609558105469</v>
       </c>
       <c r="C223" t="n">
-        <v>87.94398579844682</v>
+        <v>87.9439781588119</v>
       </c>
       <c r="D223" t="n">
-        <v>86.55881292392856</v>
+        <v>86.55880540462269</v>
       </c>
       <c r="E223" t="n">
-        <v>87.94398579844682</v>
+        <v>87.9439781588119</v>
       </c>
       <c r="F223" t="n">
         <v>257266</v>
@@ -4932,16 +4932,16 @@
         <v>43551</v>
       </c>
       <c r="B226" t="n">
-        <v>86.88300323486328</v>
+        <v>86.88299560546875</v>
       </c>
       <c r="C226" t="n">
-        <v>89.29969367486639</v>
+        <v>89.29968583325677</v>
       </c>
       <c r="D226" t="n">
-        <v>86.4998623465579</v>
+        <v>86.49985475080786</v>
       </c>
       <c r="E226" t="n">
-        <v>89.29969367486639</v>
+        <v>89.29968583325677</v>
       </c>
       <c r="F226" t="n">
         <v>691333</v>
@@ -4952,16 +4952,16 @@
         <v>43552</v>
       </c>
       <c r="B227" t="n">
-        <v>90.03647613525391</v>
+        <v>90.03649139404297</v>
       </c>
       <c r="C227" t="n">
-        <v>90.03647613525391</v>
+        <v>90.03649139404297</v>
       </c>
       <c r="D227" t="n">
-        <v>85.58622932462265</v>
+        <v>85.58624382921319</v>
       </c>
       <c r="E227" t="n">
-        <v>86.35249599465494</v>
+        <v>86.35251062910731</v>
       </c>
       <c r="F227" t="n">
         <v>558066</v>
@@ -4972,16 +4972,16 @@
         <v>43553</v>
       </c>
       <c r="B228" t="n">
-        <v>90.65538787841797</v>
+        <v>90.6553955078125</v>
       </c>
       <c r="C228" t="n">
-        <v>91.80478795672153</v>
+        <v>91.8047956828475</v>
       </c>
       <c r="D228" t="n">
-        <v>88.68077229858658</v>
+        <v>88.68077976180101</v>
       </c>
       <c r="E228" t="n">
-        <v>90.7732779486583</v>
+        <v>90.77328558797426</v>
       </c>
       <c r="F228" t="n">
         <v>379666</v>
@@ -4992,16 +4992,16 @@
         <v>43556</v>
       </c>
       <c r="B229" t="n">
-        <v>90.89117431640625</v>
+        <v>90.89116668701172</v>
       </c>
       <c r="C229" t="n">
-        <v>91.62797050329212</v>
+        <v>91.62796281205101</v>
       </c>
       <c r="D229" t="n">
-        <v>89.91860544833887</v>
+        <v>89.91859790058164</v>
       </c>
       <c r="E229" t="n">
-        <v>91.12695449266617</v>
+        <v>91.12694684348028</v>
       </c>
       <c r="F229" t="n">
         <v>342733</v>
@@ -5052,16 +5052,16 @@
         <v>43559</v>
       </c>
       <c r="B232" t="n">
-        <v>86.35250091552734</v>
+        <v>86.35251617431641</v>
       </c>
       <c r="C232" t="n">
-        <v>90.06595190965305</v>
+        <v>90.06596782462189</v>
       </c>
       <c r="D232" t="n">
-        <v>85.52728541956763</v>
+        <v>85.52730053253822</v>
       </c>
       <c r="E232" t="n">
-        <v>89.59439912695075</v>
+        <v>89.59441495859457</v>
       </c>
       <c r="F232" t="n">
         <v>777800</v>
@@ -5092,16 +5092,16 @@
         <v>43563</v>
       </c>
       <c r="B234" t="n">
-        <v>82.52116394042969</v>
+        <v>82.52117919921875</v>
       </c>
       <c r="C234" t="n">
-        <v>85.88095238775713</v>
+        <v>85.88096826779656</v>
       </c>
       <c r="D234" t="n">
-        <v>82.25591314480629</v>
+        <v>82.25592835454846</v>
       </c>
       <c r="E234" t="n">
-        <v>85.02626620586047</v>
+        <v>85.02628192786193</v>
       </c>
       <c r="F234" t="n">
         <v>619400</v>
@@ -5132,16 +5132,16 @@
         <v>43565</v>
       </c>
       <c r="B236" t="n">
-        <v>83.40533447265625</v>
+        <v>83.40532684326172</v>
       </c>
       <c r="C236" t="n">
-        <v>84.23054265002264</v>
+        <v>84.23053494514326</v>
       </c>
       <c r="D236" t="n">
-        <v>81.60754987829243</v>
+        <v>81.6075424133479</v>
       </c>
       <c r="E236" t="n">
-        <v>83.64110716689252</v>
+        <v>83.64109951593099</v>
       </c>
       <c r="F236" t="n">
         <v>456233</v>
@@ -5152,16 +5152,16 @@
         <v>43566</v>
       </c>
       <c r="B237" t="n">
-        <v>84.34841918945312</v>
+        <v>84.34842681884766</v>
       </c>
       <c r="C237" t="n">
-        <v>84.61366249095812</v>
+        <v>84.61367014434416</v>
       </c>
       <c r="D237" t="n">
-        <v>82.40327416313194</v>
+        <v>82.40328161658626</v>
       </c>
       <c r="E237" t="n">
-        <v>83.78845444620694</v>
+        <v>83.78846202495211</v>
       </c>
       <c r="F237" t="n">
         <v>403133</v>
@@ -5172,16 +5172,16 @@
         <v>43567</v>
       </c>
       <c r="B238" t="n">
-        <v>82.72747039794922</v>
+        <v>82.72745513916016</v>
       </c>
       <c r="C238" t="n">
-        <v>84.73155681507157</v>
+        <v>84.73154118663587</v>
       </c>
       <c r="D238" t="n">
-        <v>82.34433700152209</v>
+        <v>82.34432181340063</v>
       </c>
       <c r="E238" t="n">
-        <v>84.34842341864444</v>
+        <v>84.34840786087634</v>
       </c>
       <c r="F238" t="n">
         <v>343366</v>
@@ -5192,16 +5192,16 @@
         <v>43570</v>
       </c>
       <c r="B239" t="n">
-        <v>83.96529388427734</v>
+        <v>83.96528625488281</v>
       </c>
       <c r="C239" t="n">
-        <v>84.37789794631881</v>
+        <v>84.37789027943356</v>
       </c>
       <c r="D239" t="n">
-        <v>82.58011346803741</v>
+        <v>82.58010596450545</v>
       </c>
       <c r="E239" t="n">
-        <v>82.81588614704992</v>
+        <v>82.81587862209479</v>
       </c>
       <c r="F239" t="n">
         <v>210900</v>
@@ -5212,16 +5212,16 @@
         <v>43571</v>
       </c>
       <c r="B240" t="n">
-        <v>83.5821533203125</v>
+        <v>83.58216094970703</v>
       </c>
       <c r="C240" t="n">
-        <v>84.40736137380419</v>
+        <v>84.40736907852389</v>
       </c>
       <c r="D240" t="n">
-        <v>82.58010640384093</v>
+        <v>82.58011394176843</v>
       </c>
       <c r="E240" t="n">
-        <v>83.11060050754746</v>
+        <v>83.11060809389856</v>
       </c>
       <c r="F240" t="n">
         <v>215300</v>
@@ -5232,16 +5232,16 @@
         <v>43572</v>
       </c>
       <c r="B241" t="n">
-        <v>82.66852569580078</v>
+        <v>82.66854095458984</v>
       </c>
       <c r="C241" t="n">
-        <v>84.23052986373555</v>
+        <v>84.23054541083619</v>
       </c>
       <c r="D241" t="n">
-        <v>81.46017676799576</v>
+        <v>81.46019180375023</v>
       </c>
       <c r="E241" t="n">
-        <v>84.20105921831454</v>
+        <v>84.20107475997554</v>
       </c>
       <c r="F241" t="n">
         <v>289766</v>
@@ -5252,16 +5252,16 @@
         <v>43573</v>
       </c>
       <c r="B242" t="n">
-        <v>83.99475860595703</v>
+        <v>83.99476623535156</v>
       </c>
       <c r="C242" t="n">
-        <v>84.43683328479936</v>
+        <v>84.43684095434833</v>
       </c>
       <c r="D242" t="n">
-        <v>81.6959507887746</v>
+        <v>81.69595820936428</v>
       </c>
       <c r="E242" t="n">
-        <v>82.19697425451963</v>
+        <v>82.19698172061818</v>
       </c>
       <c r="F242" t="n">
         <v>318766</v>
@@ -5272,16 +5272,16 @@
         <v>43577</v>
       </c>
       <c r="B243" t="n">
-        <v>84.58419799804688</v>
+        <v>84.58418273925781</v>
       </c>
       <c r="C243" t="n">
-        <v>86.26409234997288</v>
+        <v>86.26407678813486</v>
       </c>
       <c r="D243" t="n">
-        <v>82.31486821484337</v>
+        <v>82.31485336543604</v>
       </c>
       <c r="E243" t="n">
-        <v>83.49373907739835</v>
+        <v>83.4937240153255</v>
       </c>
       <c r="F243" t="n">
         <v>461666</v>
@@ -5292,16 +5292,16 @@
         <v>43578</v>
       </c>
       <c r="B244" t="n">
-        <v>86.27613067626953</v>
+        <v>86.27611541748047</v>
       </c>
       <c r="C244" t="n">
-        <v>86.77928690824331</v>
+        <v>86.77927156046609</v>
       </c>
       <c r="D244" t="n">
-        <v>84.23391717823827</v>
+        <v>84.23390228063492</v>
       </c>
       <c r="E244" t="n">
-        <v>85.24022964218584</v>
+        <v>85.24021456660616</v>
       </c>
       <c r="F244" t="n">
         <v>437600</v>
@@ -5312,16 +5312,16 @@
         <v>43579</v>
       </c>
       <c r="B245" t="n">
-        <v>86.51290893554688</v>
+        <v>86.51292419433594</v>
       </c>
       <c r="C245" t="n">
-        <v>87.07525732554228</v>
+        <v>87.07527268351602</v>
       </c>
       <c r="D245" t="n">
-        <v>85.06264005424757</v>
+        <v>85.0626550572442</v>
       </c>
       <c r="E245" t="n">
-        <v>86.27612511987749</v>
+        <v>86.27614033690361</v>
       </c>
       <c r="F245" t="n">
         <v>361900</v>
@@ -5352,16 +5352,16 @@
         <v>43581</v>
       </c>
       <c r="B247" t="n">
-        <v>87.46002960205078</v>
+        <v>87.46003723144531</v>
       </c>
       <c r="C247" t="n">
-        <v>87.66720981443939</v>
+        <v>87.66721746190686</v>
       </c>
       <c r="D247" t="n">
-        <v>86.15774860490582</v>
+        <v>86.15775612069856</v>
       </c>
       <c r="E247" t="n">
-        <v>87.43043350413572</v>
+        <v>87.43044113094849</v>
       </c>
       <c r="F247" t="n">
         <v>187233</v>
@@ -5372,16 +5372,16 @@
         <v>43584</v>
       </c>
       <c r="B248" t="n">
-        <v>87.60800933837891</v>
+        <v>87.60800170898438</v>
       </c>
       <c r="C248" t="n">
-        <v>88.91029785131008</v>
+        <v>88.910290108505</v>
       </c>
       <c r="D248" t="n">
-        <v>86.66089657832424</v>
+        <v>86.66088903140958</v>
       </c>
       <c r="E248" t="n">
-        <v>87.87438927129051</v>
+        <v>87.87438161869812</v>
       </c>
       <c r="F248" t="n">
         <v>356166</v>
@@ -5392,16 +5392,16 @@
         <v>43585</v>
       </c>
       <c r="B249" t="n">
-        <v>89.56143951416016</v>
+        <v>89.56142425537109</v>
       </c>
       <c r="C249" t="n">
-        <v>90.27177600507484</v>
+        <v>90.27176062526411</v>
       </c>
       <c r="D249" t="n">
-        <v>86.77929327606671</v>
+        <v>86.77927849127832</v>
       </c>
       <c r="E249" t="n">
-        <v>86.77929327606671</v>
+        <v>86.77927849127832</v>
       </c>
       <c r="F249" t="n">
         <v>318366</v>
@@ -5432,16 +5432,16 @@
         <v>43588</v>
       </c>
       <c r="B251" t="n">
-        <v>90.21257781982422</v>
+        <v>90.21258544921875</v>
       </c>
       <c r="C251" t="n">
-        <v>90.89331063928984</v>
+        <v>90.89331832625483</v>
       </c>
       <c r="D251" t="n">
-        <v>88.91029684856353</v>
+        <v>88.91030436782248</v>
       </c>
       <c r="E251" t="n">
-        <v>88.91029684856353</v>
+        <v>88.91030436782248</v>
       </c>
       <c r="F251" t="n">
         <v>248400</v>
@@ -5452,16 +5452,16 @@
         <v>43591</v>
       </c>
       <c r="B252" t="n">
-        <v>90.53814697265625</v>
+        <v>90.53813934326172</v>
       </c>
       <c r="C252" t="n">
-        <v>91.10049543110814</v>
+        <v>91.1004877543261</v>
       </c>
       <c r="D252" t="n">
-        <v>88.19996484240103</v>
+        <v>88.19995741003851</v>
       </c>
       <c r="E252" t="n">
-        <v>88.64392137860601</v>
+        <v>88.64391390883252</v>
       </c>
       <c r="F252" t="n">
         <v>206566</v>
@@ -5472,16 +5472,16 @@
         <v>43592</v>
       </c>
       <c r="B253" t="n">
-        <v>96.93115997314453</v>
+        <v>96.93115234375</v>
       </c>
       <c r="C253" t="n">
-        <v>97.64149639558559</v>
+        <v>97.6414887102809</v>
       </c>
       <c r="D253" t="n">
-        <v>89.47264259147906</v>
+        <v>89.47263554914004</v>
       </c>
       <c r="E253" t="n">
-        <v>90.83411571650254</v>
+        <v>90.83410856700277</v>
       </c>
       <c r="F253" t="n">
         <v>3210933</v>
@@ -5492,16 +5492,16 @@
         <v>43593</v>
       </c>
       <c r="B254" t="n">
-        <v>102.3474578857422</v>
+        <v>102.3474731445312</v>
       </c>
       <c r="C254" t="n">
-        <v>104.4488709330641</v>
+        <v>104.4488865051489</v>
       </c>
       <c r="D254" t="n">
-        <v>98.8845717934515</v>
+        <v>98.88458653596543</v>
       </c>
       <c r="E254" t="n">
-        <v>100.6308166504369</v>
+        <v>100.6308316532951</v>
       </c>
       <c r="F254" t="n">
         <v>1898166</v>
@@ -5512,16 +5512,16 @@
         <v>43594</v>
       </c>
       <c r="B255" t="n">
-        <v>105.2184066772461</v>
+        <v>105.2184143066406</v>
       </c>
       <c r="C255" t="n">
-        <v>106.3726996110521</v>
+        <v>106.3727073241445</v>
       </c>
       <c r="D255" t="n">
-        <v>99.77249907208777</v>
+        <v>99.77250630659914</v>
       </c>
       <c r="E255" t="n">
-        <v>101.4891479514219</v>
+        <v>101.4891553104076</v>
       </c>
       <c r="F255" t="n">
         <v>781533</v>
@@ -5552,16 +5552,16 @@
         <v>43598</v>
       </c>
       <c r="B257" t="n">
-        <v>102.9986114501953</v>
+        <v>102.9986190795898</v>
       </c>
       <c r="C257" t="n">
-        <v>102.9986114501953</v>
+        <v>102.9986190795898</v>
       </c>
       <c r="D257" t="n">
-        <v>100.6900180029186</v>
+        <v>100.6900254613092</v>
       </c>
       <c r="E257" t="n">
-        <v>102.3770632970524</v>
+        <v>102.3770708804071</v>
       </c>
       <c r="F257" t="n">
         <v>256966</v>
@@ -5612,16 +5612,16 @@
         <v>43601</v>
       </c>
       <c r="B260" t="n">
-        <v>102.5842437744141</v>
+        <v>102.5842361450195</v>
       </c>
       <c r="C260" t="n">
-        <v>103.6793445426467</v>
+        <v>103.6793368318073</v>
       </c>
       <c r="D260" t="n">
-        <v>102.5842437744141</v>
+        <v>102.5842361450195</v>
       </c>
       <c r="E260" t="n">
-        <v>103.5905562502412</v>
+        <v>103.5905485460052</v>
       </c>
       <c r="F260" t="n">
         <v>583833</v>
@@ -5632,16 +5632,16 @@
         <v>43602</v>
       </c>
       <c r="B261" t="n">
-        <v>102.9690093994141</v>
+        <v>102.9690170288086</v>
       </c>
       <c r="C261" t="n">
-        <v>103.5609538939583</v>
+        <v>103.5609615672124</v>
       </c>
       <c r="D261" t="n">
-        <v>101.5483365909217</v>
+        <v>101.5483441150528</v>
       </c>
       <c r="E261" t="n">
-        <v>102.9394057767516</v>
+        <v>102.9394134039527</v>
       </c>
       <c r="F261" t="n">
         <v>361233</v>
@@ -5652,16 +5652,16 @@
         <v>43605</v>
       </c>
       <c r="B262" t="n">
-        <v>105.0704345703125</v>
+        <v>105.0704193115234</v>
       </c>
       <c r="C262" t="n">
-        <v>105.8991555117176</v>
+        <v>105.899140132578</v>
       </c>
       <c r="D262" t="n">
-        <v>103.5905692946743</v>
+        <v>103.5905542507978</v>
       </c>
       <c r="E262" t="n">
-        <v>103.5905692946743</v>
+        <v>103.5905542507978</v>
       </c>
       <c r="F262" t="n">
         <v>597600</v>
@@ -5732,16 +5732,16 @@
         <v>43609</v>
       </c>
       <c r="B266" t="n">
-        <v>110.3979415893555</v>
+        <v>110.3979339599609</v>
       </c>
       <c r="C266" t="n">
-        <v>111.9074028365882</v>
+        <v>111.9073951028777</v>
       </c>
       <c r="D266" t="n">
-        <v>109.9539775285919</v>
+        <v>109.9539699298789</v>
       </c>
       <c r="E266" t="n">
-        <v>111.1970663609532</v>
+        <v>111.1970586763327</v>
       </c>
       <c r="F266" t="n">
         <v>294000</v>
@@ -5752,16 +5752,16 @@
         <v>43612</v>
       </c>
       <c r="B267" t="n">
-        <v>109.9539794921875</v>
+        <v>109.953971862793</v>
       </c>
       <c r="C267" t="n">
-        <v>111.7298207129887</v>
+        <v>111.7298129603736</v>
       </c>
       <c r="D267" t="n">
-        <v>109.6876070725591</v>
+        <v>109.6875994616474</v>
       </c>
       <c r="E267" t="n">
-        <v>110.0427753167193</v>
+        <v>110.0427676811635</v>
       </c>
       <c r="F267" t="n">
         <v>77066</v>
@@ -5772,16 +5772,16 @@
         <v>43613</v>
       </c>
       <c r="B268" t="n">
-        <v>109.3028411865234</v>
+        <v>109.3028335571289</v>
       </c>
       <c r="C268" t="n">
-        <v>111.0786748552771</v>
+        <v>111.0786671019285</v>
       </c>
       <c r="D268" t="n">
-        <v>107.0830434553438</v>
+        <v>107.0830359808923</v>
       </c>
       <c r="E268" t="n">
-        <v>110.5755261223044</v>
+        <v>110.5755184040759</v>
       </c>
       <c r="F268" t="n">
         <v>402233</v>
@@ -5792,16 +5792,16 @@
         <v>43614</v>
       </c>
       <c r="B269" t="n">
-        <v>109.9243774414062</v>
+        <v>109.9243850708008</v>
       </c>
       <c r="C269" t="n">
-        <v>110.1019615538715</v>
+        <v>110.1019691955914</v>
       </c>
       <c r="D269" t="n">
-        <v>108.3557240537826</v>
+        <v>108.3557315743034</v>
       </c>
       <c r="E269" t="n">
-        <v>109.2732407136891</v>
+        <v>109.2732482978909</v>
       </c>
       <c r="F269" t="n">
         <v>725533</v>
@@ -5832,16 +5832,16 @@
         <v>43616</v>
       </c>
       <c r="B271" t="n">
-        <v>108.8588638305664</v>
+        <v>108.8588790893555</v>
       </c>
       <c r="C271" t="n">
-        <v>110.4275246164044</v>
+        <v>110.4275400950732</v>
       </c>
       <c r="D271" t="n">
-        <v>106.8462465635006</v>
+        <v>106.8462615401803</v>
       </c>
       <c r="E271" t="n">
-        <v>107.4086024792968</v>
+        <v>107.4086175348022</v>
       </c>
       <c r="F271" t="n">
         <v>504400</v>
@@ -5852,16 +5852,16 @@
         <v>43619</v>
       </c>
       <c r="B272" t="n">
-        <v>109.8651809692383</v>
+        <v>109.8651885986328</v>
       </c>
       <c r="C272" t="n">
-        <v>110.7531014969981</v>
+        <v>110.7531091880527</v>
       </c>
       <c r="D272" t="n">
-        <v>108.6220922303745</v>
+        <v>108.622099773445</v>
       </c>
       <c r="E272" t="n">
-        <v>108.7996763359265</v>
+        <v>108.7996838913289</v>
       </c>
       <c r="F272" t="n">
         <v>294000</v>
@@ -5872,16 +5872,16 @@
         <v>43620</v>
       </c>
       <c r="B273" t="n">
-        <v>107.1718215942383</v>
+        <v>107.1718292236328</v>
       </c>
       <c r="C273" t="n">
-        <v>110.9898760397184</v>
+        <v>110.9898839409142</v>
       </c>
       <c r="D273" t="n">
-        <v>107.1718215942383</v>
+        <v>107.1718292236328</v>
       </c>
       <c r="E273" t="n">
-        <v>109.5987993137355</v>
+        <v>109.5988071159028</v>
       </c>
       <c r="F273" t="n">
         <v>283866</v>
@@ -5892,16 +5892,16 @@
         <v>43621</v>
       </c>
       <c r="B274" t="n">
-        <v>108.8884811401367</v>
+        <v>108.8884887695312</v>
       </c>
       <c r="C274" t="n">
-        <v>109.8355939389301</v>
+        <v>109.8356016346852</v>
       </c>
       <c r="D274" t="n">
-        <v>106.4023034571936</v>
+        <v>106.4023109123912</v>
       </c>
       <c r="E274" t="n">
-        <v>106.6390797751461</v>
+        <v>106.6390872469337</v>
       </c>
       <c r="F274" t="n">
         <v>231033</v>
@@ -5912,16 +5912,16 @@
         <v>43622</v>
       </c>
       <c r="B275" t="n">
-        <v>108.7404937744141</v>
+        <v>108.740478515625</v>
       </c>
       <c r="C275" t="n">
-        <v>109.6876065789178</v>
+        <v>109.687591187227</v>
       </c>
       <c r="D275" t="n">
-        <v>108.05975338834</v>
+        <v>108.0597382250744</v>
       </c>
       <c r="E275" t="n">
-        <v>109.5100224576369</v>
+        <v>109.5100070908652</v>
       </c>
       <c r="F275" t="n">
         <v>227300</v>
@@ -5932,16 +5932,16 @@
         <v>43623</v>
       </c>
       <c r="B276" t="n">
-        <v>110.605110168457</v>
+        <v>110.6051254272461</v>
       </c>
       <c r="C276" t="n">
-        <v>110.664302359537</v>
+        <v>110.664317626492</v>
       </c>
       <c r="D276" t="n">
-        <v>108.9180649798354</v>
+        <v>108.9180800058842</v>
       </c>
       <c r="E276" t="n">
-        <v>109.2140334622177</v>
+        <v>109.2140485290975</v>
       </c>
       <c r="F276" t="n">
         <v>204266</v>
@@ -5952,16 +5952,16 @@
         <v>43626</v>
       </c>
       <c r="B277" t="n">
-        <v>114.3935775756836</v>
+        <v>114.3935699462891</v>
       </c>
       <c r="C277" t="n">
-        <v>119.3955216779974</v>
+        <v>119.395513715002</v>
       </c>
       <c r="D277" t="n">
-        <v>111.8778112380962</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="E277" t="n">
-        <v>111.8778112380962</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="F277" t="n">
         <v>585833</v>
@@ -5992,16 +5992,16 @@
         <v>43628</v>
       </c>
       <c r="B279" t="n">
-        <v>108.918083190918</v>
+        <v>108.9180679321289</v>
       </c>
       <c r="C279" t="n">
-        <v>111.7594217425652</v>
+        <v>111.7594060857212</v>
       </c>
       <c r="D279" t="n">
-        <v>108.7996912619804</v>
+        <v>108.7996760197774</v>
       </c>
       <c r="E279" t="n">
-        <v>111.7594217425652</v>
+        <v>111.7594060857212</v>
       </c>
       <c r="F279" t="n">
         <v>382266</v>
@@ -6012,16 +6012,16 @@
         <v>43629</v>
       </c>
       <c r="B280" t="n">
-        <v>113.8607940673828</v>
+        <v>113.8608016967773</v>
       </c>
       <c r="C280" t="n">
-        <v>114.9854907158855</v>
+        <v>114.9854984206418</v>
       </c>
       <c r="D280" t="n">
-        <v>108.9180510431142</v>
+        <v>108.9180583413137</v>
       </c>
       <c r="E280" t="n">
-        <v>108.9180510431142</v>
+        <v>108.9180583413137</v>
       </c>
       <c r="F280" t="n">
         <v>845300</v>
@@ -6052,16 +6052,16 @@
         <v>43633</v>
       </c>
       <c r="B282" t="n">
-        <v>110.0723724365234</v>
+        <v>110.0723648071289</v>
       </c>
       <c r="C282" t="n">
-        <v>113.1504947387922</v>
+        <v>113.1504868960452</v>
       </c>
       <c r="D282" t="n">
-        <v>109.0660598930775</v>
+        <v>109.066052333433</v>
       </c>
       <c r="E282" t="n">
-        <v>113.1504947387922</v>
+        <v>113.1504868960452</v>
       </c>
       <c r="F282" t="n">
         <v>481366</v>
@@ -6092,16 +6092,16 @@
         <v>43635</v>
       </c>
       <c r="B284" t="n">
-        <v>115.3702774047852</v>
+        <v>115.3702850341797</v>
       </c>
       <c r="C284" t="n">
-        <v>115.3702774047852</v>
+        <v>115.3702850341797</v>
       </c>
       <c r="D284" t="n">
-        <v>111.6114151995947</v>
+        <v>111.6114225804171</v>
       </c>
       <c r="E284" t="n">
-        <v>112.3513476970046</v>
+        <v>112.3513551267584</v>
       </c>
       <c r="F284" t="n">
         <v>441733</v>
@@ -6112,16 +6112,16 @@
         <v>43637</v>
       </c>
       <c r="B285" t="n">
-        <v>116.4653778076172</v>
+        <v>116.4653625488281</v>
       </c>
       <c r="C285" t="n">
-        <v>116.4949814320171</v>
+        <v>116.4949661693495</v>
       </c>
       <c r="D285" t="n">
-        <v>114.5415562056919</v>
+        <v>114.5415411989536</v>
       </c>
       <c r="E285" t="n">
-        <v>115.3998806656956</v>
+        <v>115.3998655465033</v>
       </c>
       <c r="F285" t="n">
         <v>285566</v>
@@ -6132,16 +6132,16 @@
         <v>43640</v>
       </c>
       <c r="B286" t="n">
-        <v>116.5245895385742</v>
+        <v>116.5245742797852</v>
       </c>
       <c r="C286" t="n">
-        <v>117.5012984889059</v>
+        <v>117.5012831022177</v>
       </c>
       <c r="D286" t="n">
-        <v>115.0447242993513</v>
+        <v>115.0447092343492</v>
       </c>
       <c r="E286" t="n">
-        <v>116.6133778399754</v>
+        <v>116.6133625695595</v>
       </c>
       <c r="F286" t="n">
         <v>315633</v>
@@ -6172,16 +6172,16 @@
         <v>43642</v>
       </c>
       <c r="B288" t="n">
-        <v>113.1208877563477</v>
+        <v>113.1208953857422</v>
       </c>
       <c r="C288" t="n">
-        <v>115.72544980908</v>
+        <v>115.7254576141382</v>
       </c>
       <c r="D288" t="n">
-        <v>112.6769312236937</v>
+        <v>112.6769388231457</v>
       </c>
       <c r="E288" t="n">
-        <v>115.72544980908</v>
+        <v>115.7254576141382</v>
       </c>
       <c r="F288" t="n">
         <v>335833</v>
@@ -6212,16 +6212,16 @@
         <v>43644</v>
       </c>
       <c r="B290" t="n">
-        <v>116.7021484375</v>
+        <v>116.7021713256836</v>
       </c>
       <c r="C290" t="n">
-        <v>117.6492610826</v>
+        <v>117.6492841565359</v>
       </c>
       <c r="D290" t="n">
-        <v>114.1271828757977</v>
+        <v>114.1272052589668</v>
       </c>
       <c r="E290" t="n">
-        <v>115.0742955208978</v>
+        <v>115.0743180898191</v>
       </c>
       <c r="F290" t="n">
         <v>617600</v>
@@ -6232,16 +6232,16 @@
         <v>43647</v>
       </c>
       <c r="B291" t="n">
-        <v>114.068000793457</v>
+        <v>114.0680084228516</v>
       </c>
       <c r="C291" t="n">
-        <v>117.0573269909192</v>
+        <v>117.0573348202537</v>
       </c>
       <c r="D291" t="n">
-        <v>114.068000793457</v>
+        <v>114.0680084228516</v>
       </c>
       <c r="E291" t="n">
-        <v>117.0573269909192</v>
+        <v>117.0573348202537</v>
       </c>
       <c r="F291" t="n">
         <v>436066</v>
@@ -6252,16 +6252,16 @@
         <v>43648</v>
       </c>
       <c r="B292" t="n">
-        <v>110.1315612792969</v>
+        <v>110.1315536499023</v>
       </c>
       <c r="C292" t="n">
-        <v>115.1335051636899</v>
+        <v>115.1334971877844</v>
       </c>
       <c r="D292" t="n">
-        <v>110.1315612792969</v>
+        <v>110.1315536499023</v>
       </c>
       <c r="E292" t="n">
-        <v>113.9792121581339</v>
+        <v>113.9792042621922</v>
       </c>
       <c r="F292" t="n">
         <v>537533</v>
@@ -6272,16 +6272,16 @@
         <v>43649</v>
       </c>
       <c r="B293" t="n">
-        <v>109.9691772460938</v>
+        <v>109.9691696166992</v>
       </c>
       <c r="C293" t="n">
-        <v>110.8608207354733</v>
+        <v>110.8608130442187</v>
       </c>
       <c r="D293" t="n">
-        <v>107.3239745263866</v>
+        <v>107.3239670805098</v>
       </c>
       <c r="E293" t="n">
-        <v>110.7122122274863</v>
+        <v>110.7122045465418</v>
       </c>
       <c r="F293" t="n">
         <v>1690900</v>
@@ -6292,16 +6292,16 @@
         <v>43650</v>
       </c>
       <c r="B294" t="n">
-        <v>114.1004486083984</v>
+        <v>114.1004409790039</v>
       </c>
       <c r="C294" t="n">
-        <v>114.1004486083984</v>
+        <v>114.1004409790039</v>
       </c>
       <c r="D294" t="n">
-        <v>109.404469696724</v>
+        <v>109.4044623813289</v>
       </c>
       <c r="E294" t="n">
-        <v>109.9691759737067</v>
+        <v>109.9691686205522</v>
       </c>
       <c r="F294" t="n">
         <v>412866</v>
@@ -6312,16 +6312,16 @@
         <v>43651</v>
       </c>
       <c r="B295" t="n">
-        <v>117.5184020996094</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="C295" t="n">
-        <v>117.5184020996094</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="D295" t="n">
-        <v>112.9115842237956</v>
+        <v>112.9115768934796</v>
       </c>
       <c r="E295" t="n">
-        <v>114.0707168497463</v>
+        <v>114.0707094441784</v>
       </c>
       <c r="F295" t="n">
         <v>288866</v>
@@ -6352,16 +6352,16 @@
         <v>43656</v>
       </c>
       <c r="B297" t="n">
-        <v>128.0397796630859</v>
+        <v>128.0397644042969</v>
       </c>
       <c r="C297" t="n">
-        <v>128.0397796630859</v>
+        <v>128.0397644042969</v>
       </c>
       <c r="D297" t="n">
-        <v>121.9171642141075</v>
+        <v>121.9171496849643</v>
       </c>
       <c r="E297" t="n">
-        <v>121.9171642141075</v>
+        <v>121.9171496849643</v>
       </c>
       <c r="F297" t="n">
         <v>529166</v>
@@ -6372,16 +6372,16 @@
         <v>43657</v>
       </c>
       <c r="B298" t="n">
-        <v>123.1654586791992</v>
+        <v>123.1654663085938</v>
       </c>
       <c r="C298" t="n">
-        <v>130.1797020465908</v>
+        <v>130.1797101104775</v>
       </c>
       <c r="D298" t="n">
-        <v>123.1060183088487</v>
+        <v>123.1060259345613</v>
       </c>
       <c r="E298" t="n">
-        <v>130.1797020465908</v>
+        <v>130.1797101104775</v>
       </c>
       <c r="F298" t="n">
         <v>660700</v>
@@ -6412,16 +6412,16 @@
         <v>43661</v>
       </c>
       <c r="B300" t="n">
-        <v>121.5605087280273</v>
+        <v>121.5605010986328</v>
       </c>
       <c r="C300" t="n">
-        <v>126.7320329312208</v>
+        <v>126.7320249772505</v>
       </c>
       <c r="D300" t="n">
-        <v>118.5289287021037</v>
+        <v>118.5289212629776</v>
       </c>
       <c r="E300" t="n">
-        <v>124.9784738625208</v>
+        <v>124.9784660186075</v>
       </c>
       <c r="F300" t="n">
         <v>1110366</v>
@@ -6432,16 +6432,16 @@
         <v>43662</v>
       </c>
       <c r="B301" t="n">
-        <v>124.1462631225586</v>
+        <v>124.1462707519531</v>
       </c>
       <c r="C301" t="n">
-        <v>124.2354312370136</v>
+        <v>124.2354388718879</v>
       </c>
       <c r="D301" t="n">
-        <v>120.4608089739724</v>
+        <v>120.4608163768777</v>
       </c>
       <c r="E301" t="n">
-        <v>121.5605011814873</v>
+        <v>121.5605086519742</v>
       </c>
       <c r="F301" t="n">
         <v>378300</v>
@@ -6452,16 +6452,16 @@
         <v>43663</v>
       </c>
       <c r="B302" t="n">
-        <v>126.613151550293</v>
+        <v>126.6131362915039</v>
       </c>
       <c r="C302" t="n">
-        <v>127.9506129549797</v>
+        <v>127.9505975350065</v>
       </c>
       <c r="D302" t="n">
-        <v>122.7493758386517</v>
+        <v>122.7493610455057</v>
       </c>
       <c r="E302" t="n">
-        <v>123.9679489296947</v>
+        <v>123.9679339896924</v>
       </c>
       <c r="F302" t="n">
         <v>443966</v>
@@ -6492,16 +6492,16 @@
         <v>43665</v>
       </c>
       <c r="B304" t="n">
-        <v>126.9995193481445</v>
+        <v>126.9995346069336</v>
       </c>
       <c r="C304" t="n">
-        <v>132.379084421508</v>
+        <v>132.3791003266432</v>
       </c>
       <c r="D304" t="n">
-        <v>126.9995193481445</v>
+        <v>126.9995346069336</v>
       </c>
       <c r="E304" t="n">
-        <v>129.9419385720236</v>
+        <v>129.9419541843396</v>
       </c>
       <c r="F304" t="n">
         <v>683033</v>
@@ -6572,16 +6572,16 @@
         <v>43671</v>
       </c>
       <c r="B308" t="n">
-        <v>126.4645538330078</v>
+        <v>126.4645462036133</v>
       </c>
       <c r="C308" t="n">
-        <v>131.3388538800843</v>
+        <v>131.3388459566314</v>
       </c>
       <c r="D308" t="n">
-        <v>126.0484485039095</v>
+        <v>126.0484408996179</v>
       </c>
       <c r="E308" t="n">
-        <v>129.3178054063731</v>
+        <v>129.3177976048466</v>
       </c>
       <c r="F308" t="n">
         <v>3248566</v>
@@ -6592,16 +6592,16 @@
         <v>43672</v>
       </c>
       <c r="B309" t="n">
-        <v>125.6620635986328</v>
+        <v>125.6620559692383</v>
       </c>
       <c r="C309" t="n">
-        <v>127.9208885740418</v>
+        <v>127.9208808075059</v>
       </c>
       <c r="D309" t="n">
-        <v>125.0676371669792</v>
+        <v>125.0676295736744</v>
       </c>
       <c r="E309" t="n">
-        <v>127.2075738326406</v>
+        <v>127.2075661094126</v>
       </c>
       <c r="F309" t="n">
         <v>1585266</v>
@@ -6632,16 +6632,16 @@
         <v>43676</v>
       </c>
       <c r="B311" t="n">
-        <v>124.3840408325195</v>
+        <v>124.384033203125</v>
       </c>
       <c r="C311" t="n">
-        <v>126.3753765306633</v>
+        <v>126.3753687791254</v>
       </c>
       <c r="D311" t="n">
-        <v>124.294880270392</v>
+        <v>124.2948726464664</v>
       </c>
       <c r="E311" t="n">
-        <v>126.2267680352421</v>
+        <v>126.2267602928194</v>
       </c>
       <c r="F311" t="n">
         <v>1065500</v>
@@ -6652,16 +6652,16 @@
         <v>43677</v>
       </c>
       <c r="B312" t="n">
-        <v>124.2354278564453</v>
+        <v>124.2354354858398</v>
       </c>
       <c r="C312" t="n">
-        <v>126.1673154340833</v>
+        <v>126.1673231821166</v>
       </c>
       <c r="D312" t="n">
-        <v>121.1444001736832</v>
+        <v>121.1444076132553</v>
       </c>
       <c r="E312" t="n">
-        <v>125.572889068544</v>
+        <v>125.5728967800731</v>
       </c>
       <c r="F312" t="n">
         <v>1188566</v>
@@ -6672,16 +6672,16 @@
         <v>43678</v>
       </c>
       <c r="B313" t="n">
-        <v>122.6601791381836</v>
+        <v>122.6602020263672</v>
       </c>
       <c r="C313" t="n">
-        <v>126.5834018719421</v>
+        <v>126.5834254921925</v>
       </c>
       <c r="D313" t="n">
-        <v>121.798263630326</v>
+        <v>121.7982863576776</v>
       </c>
       <c r="E313" t="n">
-        <v>124.6515144661847</v>
+        <v>124.6515377259481</v>
       </c>
       <c r="F313" t="n">
         <v>895666</v>
@@ -6732,16 +6732,16 @@
         <v>43683</v>
       </c>
       <c r="B316" t="n">
-        <v>126.613151550293</v>
+        <v>126.6131362915039</v>
       </c>
       <c r="C316" t="n">
-        <v>127.1778578126515</v>
+        <v>127.1778424858068</v>
       </c>
       <c r="D316" t="n">
-        <v>123.1357534098158</v>
+        <v>123.1357385701055</v>
       </c>
       <c r="E316" t="n">
-        <v>123.1951937873665</v>
+        <v>123.1951789404927</v>
       </c>
       <c r="F316" t="n">
         <v>466533</v>
@@ -6772,16 +6772,16 @@
         <v>43685</v>
       </c>
       <c r="B318" t="n">
-        <v>131.9035339355469</v>
+        <v>131.9035491943359</v>
       </c>
       <c r="C318" t="n">
-        <v>133.5679245915274</v>
+        <v>133.5679400428555</v>
       </c>
       <c r="D318" t="n">
-        <v>129.2880521068051</v>
+        <v>129.2880670630315</v>
       </c>
       <c r="E318" t="n">
-        <v>129.2880521068051</v>
+        <v>129.2880670630315</v>
       </c>
       <c r="F318" t="n">
         <v>971500</v>
@@ -6792,16 +6792,16 @@
         <v>43686</v>
       </c>
       <c r="B319" t="n">
-        <v>131.5171813964844</v>
+        <v>131.5171661376953</v>
       </c>
       <c r="C319" t="n">
-        <v>134.8756986444118</v>
+        <v>134.8756829959633</v>
       </c>
       <c r="D319" t="n">
-        <v>129.4069573772885</v>
+        <v>129.4069423633303</v>
       </c>
       <c r="E319" t="n">
-        <v>134.8756986444118</v>
+        <v>134.8756829959633</v>
       </c>
       <c r="F319" t="n">
         <v>371566</v>
@@ -6832,16 +6832,16 @@
         <v>43690</v>
       </c>
       <c r="B321" t="n">
-        <v>131.0713806152344</v>
+        <v>131.0713653564453</v>
       </c>
       <c r="C321" t="n">
-        <v>133.7760238565671</v>
+        <v>133.7760082829146</v>
       </c>
       <c r="D321" t="n">
-        <v>128.8125553627015</v>
+        <v>128.8125403668755</v>
       </c>
       <c r="E321" t="n">
-        <v>133.6571430907768</v>
+        <v>133.6571275309639</v>
       </c>
       <c r="F321" t="n">
         <v>614133</v>
@@ -6872,16 +6872,16 @@
         <v>43692</v>
       </c>
       <c r="B323" t="n">
-        <v>140.1660919189453</v>
+        <v>140.1660766601562</v>
       </c>
       <c r="C323" t="n">
-        <v>142.0088189785496</v>
+        <v>142.0088035191572</v>
       </c>
       <c r="D323" t="n">
-        <v>136.3023166893313</v>
+        <v>136.3023018511614</v>
       </c>
       <c r="E323" t="n">
-        <v>139.5122176132928</v>
+        <v>139.5122024256859</v>
       </c>
       <c r="F323" t="n">
         <v>846233</v>
@@ -6892,16 +6892,16 @@
         <v>43693</v>
       </c>
       <c r="B324" t="n">
-        <v>145.6348571777344</v>
+        <v>145.6348114013672</v>
       </c>
       <c r="C324" t="n">
-        <v>145.6348571777344</v>
+        <v>145.6348114013672</v>
       </c>
       <c r="D324" t="n">
-        <v>137.2236956985838</v>
+        <v>137.2236525660371</v>
       </c>
       <c r="E324" t="n">
-        <v>141.8305216795594</v>
+        <v>141.8304770989819</v>
       </c>
       <c r="F324" t="n">
         <v>930266</v>
@@ -6932,16 +6932,16 @@
         <v>43697</v>
       </c>
       <c r="B326" t="n">
-        <v>145.0106964111328</v>
+        <v>145.0106811523438</v>
       </c>
       <c r="C326" t="n">
-        <v>146.7048227534003</v>
+        <v>146.7048073163463</v>
       </c>
       <c r="D326" t="n">
-        <v>140.4633261324826</v>
+        <v>140.4633113521918</v>
       </c>
       <c r="E326" t="n">
-        <v>143.0490883704163</v>
+        <v>143.049073318038</v>
       </c>
       <c r="F326" t="n">
         <v>506533</v>
@@ -6972,16 +6972,16 @@
         <v>43699</v>
       </c>
       <c r="B328" t="n">
-        <v>148.5475311279297</v>
+        <v>148.5475463867188</v>
       </c>
       <c r="C328" t="n">
-        <v>151.3116141462722</v>
+        <v>151.3116296889876</v>
       </c>
       <c r="D328" t="n">
-        <v>146.8236848164054</v>
+        <v>146.8236998981212</v>
       </c>
       <c r="E328" t="n">
-        <v>148.5772513128626</v>
+        <v>148.5772665747045</v>
       </c>
       <c r="F328" t="n">
         <v>509000</v>
@@ -6992,16 +6992,16 @@
         <v>43700</v>
       </c>
       <c r="B329" t="n">
-        <v>143.2868499755859</v>
+        <v>143.286865234375</v>
       </c>
       <c r="C329" t="n">
-        <v>148.3691982354048</v>
+        <v>148.3692140354192</v>
       </c>
       <c r="D329" t="n">
-        <v>142.3654788707114</v>
+        <v>142.3654940313826</v>
       </c>
       <c r="E329" t="n">
-        <v>147.9531005199104</v>
+        <v>147.9531162756141</v>
       </c>
       <c r="F329" t="n">
         <v>586733</v>
@@ -7012,16 +7012,16 @@
         <v>43703</v>
       </c>
       <c r="B330" t="n">
-        <v>143.5543212890625</v>
+        <v>143.5543518066406</v>
       </c>
       <c r="C330" t="n">
-        <v>146.2292587368132</v>
+        <v>146.2292898230444</v>
       </c>
       <c r="D330" t="n">
-        <v>141.2063360934986</v>
+        <v>141.2063661119289</v>
       </c>
       <c r="E330" t="n">
-        <v>143.3165598214097</v>
+        <v>143.3165902884432</v>
       </c>
       <c r="F330" t="n">
         <v>278200</v>
@@ -7032,16 +7032,16 @@
         <v>43704</v>
       </c>
       <c r="B331" t="n">
-        <v>145.4862518310547</v>
+        <v>145.4862365722656</v>
       </c>
       <c r="C331" t="n">
-        <v>146.4670483074746</v>
+        <v>146.4670329458183</v>
       </c>
       <c r="D331" t="n">
-        <v>141.7710770153187</v>
+        <v>141.7710621461821</v>
       </c>
       <c r="E331" t="n">
-        <v>143.4057478874085</v>
+        <v>143.4057328468255</v>
       </c>
       <c r="F331" t="n">
         <v>495866</v>
@@ -7052,16 +7052,16 @@
         <v>43705</v>
       </c>
       <c r="B332" t="n">
-        <v>145.6348571777344</v>
+        <v>145.6348114013672</v>
       </c>
       <c r="C332" t="n">
-        <v>146.5859334937354</v>
+        <v>146.5858874184231</v>
       </c>
       <c r="D332" t="n">
-        <v>143.9704509491044</v>
+        <v>143.9704056958981</v>
       </c>
       <c r="E332" t="n">
-        <v>145.6942975578488</v>
+        <v>145.6942517627981</v>
       </c>
       <c r="F332" t="n">
         <v>446600</v>
@@ -7072,16 +7072,16 @@
         <v>43706</v>
       </c>
       <c r="B333" t="n">
-        <v>150.0930633544922</v>
+        <v>150.0930480957031</v>
       </c>
       <c r="C333" t="n">
-        <v>151.103595142534</v>
+        <v>151.1035797810121</v>
       </c>
       <c r="D333" t="n">
-        <v>145.9617907514584</v>
+        <v>145.9617759126635</v>
       </c>
       <c r="E333" t="n">
-        <v>146.5264894655712</v>
+        <v>146.5264745693678</v>
       </c>
       <c r="F333" t="n">
         <v>1067466</v>
@@ -7092,16 +7092,16 @@
         <v>43707</v>
       </c>
       <c r="B334" t="n">
-        <v>153.6893310546875</v>
+        <v>153.6893463134766</v>
       </c>
       <c r="C334" t="n">
-        <v>153.6893310546875</v>
+        <v>153.6893463134766</v>
       </c>
       <c r="D334" t="n">
-        <v>149.8849811870925</v>
+        <v>149.884996068173</v>
       </c>
       <c r="E334" t="n">
-        <v>150.9846733543434</v>
+        <v>150.984688344605</v>
       </c>
       <c r="F334" t="n">
         <v>973933</v>
@@ -7112,16 +7112,16 @@
         <v>43710</v>
       </c>
       <c r="B335" t="n">
-        <v>155.1456909179688</v>
+        <v>155.1457061767578</v>
       </c>
       <c r="C335" t="n">
-        <v>155.8887258071983</v>
+        <v>155.8887411390659</v>
       </c>
       <c r="D335" t="n">
-        <v>152.1140958715619</v>
+        <v>152.1141108321895</v>
       </c>
       <c r="E335" t="n">
-        <v>153.6596211395096</v>
+        <v>153.6596362521417</v>
       </c>
       <c r="F335" t="n">
         <v>734566</v>
@@ -7152,16 +7152,16 @@
         <v>43712</v>
       </c>
       <c r="B337" t="n">
-        <v>149.4688873291016</v>
+        <v>149.4688720703125</v>
       </c>
       <c r="C337" t="n">
-        <v>156.1859212419549</v>
+        <v>156.1859052974459</v>
       </c>
       <c r="D337" t="n">
-        <v>147.9828176117963</v>
+        <v>147.9828025047152</v>
       </c>
       <c r="E337" t="n">
-        <v>155.9778799470986</v>
+        <v>155.9778640238278</v>
       </c>
       <c r="F337" t="n">
         <v>865766</v>
@@ -7192,16 +7192,16 @@
         <v>43714</v>
       </c>
       <c r="B339" t="n">
-        <v>146.2292633056641</v>
+        <v>146.2292938232422</v>
       </c>
       <c r="C339" t="n">
-        <v>150.5091361450396</v>
+        <v>150.5091675558134</v>
       </c>
       <c r="D339" t="n">
-        <v>145.4862284618692</v>
+        <v>145.4862588243783</v>
       </c>
       <c r="E339" t="n">
-        <v>150.0633182621792</v>
+        <v>150.0633495799123</v>
       </c>
       <c r="F339" t="n">
         <v>678033</v>
@@ -7212,16 +7212,16 @@
         <v>43717</v>
       </c>
       <c r="B340" t="n">
-        <v>142.9004821777344</v>
+        <v>142.9004516601562</v>
       </c>
       <c r="C340" t="n">
-        <v>146.734537552183</v>
+        <v>146.7345062158107</v>
       </c>
       <c r="D340" t="n">
-        <v>139.7202860481167</v>
+        <v>139.7202562096958</v>
       </c>
       <c r="E340" t="n">
-        <v>146.734537552183</v>
+        <v>146.7345062158107</v>
       </c>
       <c r="F340" t="n">
         <v>1841333</v>
@@ -7232,16 +7232,16 @@
         <v>43718</v>
       </c>
       <c r="B341" t="n">
-        <v>146.4075775146484</v>
+        <v>146.4075927734375</v>
       </c>
       <c r="C341" t="n">
-        <v>146.4967380636036</v>
+        <v>146.4967533316851</v>
       </c>
       <c r="D341" t="n">
-        <v>140.6416201422374</v>
+        <v>140.6416348000909</v>
       </c>
       <c r="E341" t="n">
-        <v>142.0385292108626</v>
+        <v>142.0385440143037</v>
       </c>
       <c r="F341" t="n">
         <v>1022600</v>
@@ -7252,16 +7252,16 @@
         <v>43719</v>
       </c>
       <c r="B342" t="n">
-        <v>152.5301666259766</v>
+        <v>152.5302124023438</v>
       </c>
       <c r="C342" t="n">
-        <v>152.5301666259766</v>
+        <v>152.5302124023438</v>
       </c>
       <c r="D342" t="n">
-        <v>146.7047844040439</v>
+        <v>146.7048284321351</v>
       </c>
       <c r="E342" t="n">
-        <v>148.5772313891439</v>
+        <v>148.5772759791817</v>
       </c>
       <c r="F342" t="n">
         <v>523500</v>
@@ -7272,16 +7272,16 @@
         <v>43720</v>
       </c>
       <c r="B343" t="n">
-        <v>148.3692016601562</v>
+        <v>148.3692169189453</v>
       </c>
       <c r="C343" t="n">
-        <v>154.4918170256621</v>
+        <v>154.4918329141216</v>
       </c>
       <c r="D343" t="n">
-        <v>148.3394814738694</v>
+        <v>148.339496729602</v>
       </c>
       <c r="E343" t="n">
-        <v>153.9568234383322</v>
+        <v>153.9568392717711</v>
       </c>
       <c r="F343" t="n">
         <v>700866</v>
@@ -7292,16 +7292,16 @@
         <v>43721</v>
       </c>
       <c r="B344" t="n">
-        <v>149.201416015625</v>
+        <v>149.2014007568359</v>
       </c>
       <c r="C344" t="n">
-        <v>150.4794294096575</v>
+        <v>150.4794140201663</v>
       </c>
       <c r="D344" t="n">
-        <v>145.6348423998163</v>
+        <v>145.6348275057798</v>
       </c>
       <c r="E344" t="n">
-        <v>148.6069820406289</v>
+        <v>148.6069668426325</v>
       </c>
       <c r="F344" t="n">
         <v>622000</v>
@@ -7332,16 +7332,16 @@
         <v>43725</v>
       </c>
       <c r="B346" t="n">
-        <v>153.065185546875</v>
+        <v>153.0652008056641</v>
       </c>
       <c r="C346" t="n">
-        <v>153.065185546875</v>
+        <v>153.0652008056641</v>
       </c>
       <c r="D346" t="n">
-        <v>149.0825143503477</v>
+        <v>149.0825292121116</v>
       </c>
       <c r="E346" t="n">
-        <v>150.3902629976278</v>
+        <v>150.3902779897587</v>
       </c>
       <c r="F346" t="n">
         <v>1122433</v>
@@ -7352,16 +7352,16 @@
         <v>43726</v>
       </c>
       <c r="B347" t="n">
-        <v>152.4707489013672</v>
+        <v>152.4707641601562</v>
       </c>
       <c r="C347" t="n">
-        <v>153.2137837695358</v>
+        <v>153.2137991026854</v>
       </c>
       <c r="D347" t="n">
-        <v>151.4007768771544</v>
+        <v>151.4007920288641</v>
       </c>
       <c r="E347" t="n">
-        <v>151.4305121795976</v>
+        <v>151.4305273342831</v>
       </c>
       <c r="F347" t="n">
         <v>459166</v>
@@ -7372,16 +7372,16 @@
         <v>43727</v>
       </c>
       <c r="B348" t="n">
-        <v>153.0354766845703</v>
+        <v>153.0354461669922</v>
       </c>
       <c r="C348" t="n">
-        <v>155.3834622457323</v>
+        <v>155.3834312599305</v>
       </c>
       <c r="D348" t="n">
-        <v>151.5494068120203</v>
+        <v>151.5493765907869</v>
       </c>
       <c r="E348" t="n">
-        <v>154.4026658047834</v>
+        <v>154.4026350145672</v>
       </c>
       <c r="F348" t="n">
         <v>446666</v>
@@ -7432,16 +7432,16 @@
         <v>43732</v>
       </c>
       <c r="B351" t="n">
-        <v>155.1456909179688</v>
+        <v>155.1457061767578</v>
       </c>
       <c r="C351" t="n">
-        <v>158.9203057365216</v>
+        <v>158.9203213665492</v>
       </c>
       <c r="D351" t="n">
-        <v>154.6998578907642</v>
+        <v>154.699873105705</v>
       </c>
       <c r="E351" t="n">
-        <v>158.6825291298181</v>
+        <v>158.68254473646</v>
       </c>
       <c r="F351" t="n">
         <v>630466</v>
@@ -7452,16 +7452,16 @@
         <v>43733</v>
       </c>
       <c r="B352" t="n">
-        <v>155.1456909179688</v>
+        <v>155.1457061767578</v>
       </c>
       <c r="C352" t="n">
-        <v>156.0373267382109</v>
+        <v>156.0373420846935</v>
       </c>
       <c r="D352" t="n">
-        <v>152.708529829779</v>
+        <v>152.70854484887</v>
       </c>
       <c r="E352" t="n">
-        <v>155.4726129661963</v>
+        <v>155.4726282571386</v>
       </c>
       <c r="F352" t="n">
         <v>976666</v>
@@ -7472,16 +7472,16 @@
         <v>43734</v>
       </c>
       <c r="B353" t="n">
-        <v>157.3747863769531</v>
+        <v>157.3748016357422</v>
       </c>
       <c r="C353" t="n">
-        <v>159.4255546903437</v>
+        <v>159.4255701479717</v>
       </c>
       <c r="D353" t="n">
-        <v>154.9970658002995</v>
+        <v>154.9970808285488</v>
       </c>
       <c r="E353" t="n">
-        <v>155.4726038687971</v>
+        <v>155.4726189431538</v>
       </c>
       <c r="F353" t="n">
         <v>815966</v>
@@ -7552,16 +7552,16 @@
         <v>43740</v>
       </c>
       <c r="B357" t="n">
-        <v>156.0373382568359</v>
+        <v>156.0373229980469</v>
       </c>
       <c r="C357" t="n">
-        <v>159.0689184099495</v>
+        <v>159.0689028547042</v>
       </c>
       <c r="D357" t="n">
-        <v>154.4323876150899</v>
+        <v>154.4323725132479</v>
       </c>
       <c r="E357" t="n">
-        <v>156.5723167650564</v>
+        <v>156.5723014539522</v>
       </c>
       <c r="F357" t="n">
         <v>1285800</v>
@@ -7612,16 +7612,16 @@
         <v>43745</v>
       </c>
       <c r="B360" t="n">
-        <v>161.4168853759766</v>
+        <v>161.4169006347656</v>
       </c>
       <c r="C360" t="n">
-        <v>163.7054454381041</v>
+        <v>163.7054609132314</v>
       </c>
       <c r="D360" t="n">
-        <v>159.6336138095562</v>
+        <v>159.6336288997721</v>
       </c>
       <c r="E360" t="n">
-        <v>161.6249417878365</v>
+        <v>161.6249570662932</v>
       </c>
       <c r="F360" t="n">
         <v>812666</v>
@@ -7632,16 +7632,16 @@
         <v>43746</v>
       </c>
       <c r="B361" t="n">
-        <v>160.6441192626953</v>
+        <v>160.6441497802734</v>
       </c>
       <c r="C361" t="n">
-        <v>163.7351543401261</v>
+        <v>163.7351854449085</v>
       </c>
       <c r="D361" t="n">
-        <v>158.2664139265933</v>
+        <v>158.2664439924785</v>
       </c>
       <c r="E361" t="n">
-        <v>161.4168742527825</v>
+        <v>161.416904917161</v>
       </c>
       <c r="F361" t="n">
         <v>478600</v>
@@ -7692,16 +7692,16 @@
         <v>43749</v>
       </c>
       <c r="B364" t="n">
-        <v>167.2423095703125</v>
+        <v>167.2422790527344</v>
       </c>
       <c r="C364" t="n">
-        <v>168.2825615575854</v>
+        <v>168.282530850187</v>
       </c>
       <c r="D364" t="n">
-        <v>163.7649113332881</v>
+        <v>163.764881450249</v>
       </c>
       <c r="E364" t="n">
-        <v>163.7649113332881</v>
+        <v>163.764881450249</v>
       </c>
       <c r="F364" t="n">
         <v>518100</v>
@@ -7712,16 +7712,16 @@
         <v>43752</v>
       </c>
       <c r="B365" t="n">
-        <v>167.9258880615234</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C365" t="n">
-        <v>169.5902789878799</v>
+        <v>169.590263577854</v>
       </c>
       <c r="D365" t="n">
-        <v>166.3803778821685</v>
+        <v>166.3803627638141</v>
       </c>
       <c r="E365" t="n">
-        <v>167.2125733453467</v>
+        <v>167.2125581513739</v>
       </c>
       <c r="F365" t="n">
         <v>323333</v>
@@ -7732,16 +7732,16 @@
         <v>43753</v>
       </c>
       <c r="B366" t="n">
-        <v>167.3314666748047</v>
+        <v>167.3314514160156</v>
       </c>
       <c r="C366" t="n">
-        <v>169.2039141662959</v>
+        <v>169.2038987367602</v>
       </c>
       <c r="D366" t="n">
-        <v>167.1828657298788</v>
+        <v>167.1828504846405</v>
       </c>
       <c r="E366" t="n">
-        <v>167.3017464858195</v>
+        <v>167.3017312297406</v>
       </c>
       <c r="F366" t="n">
         <v>550533</v>
@@ -7772,16 +7772,16 @@
         <v>43755</v>
       </c>
       <c r="B368" t="n">
-        <v>169.7686004638672</v>
+        <v>169.7686157226562</v>
       </c>
       <c r="C368" t="n">
-        <v>172.9785164075561</v>
+        <v>172.9785319548521</v>
       </c>
       <c r="D368" t="n">
-        <v>168.8769495876346</v>
+        <v>168.8769647662821</v>
       </c>
       <c r="E368" t="n">
-        <v>171.2546701405057</v>
+        <v>171.2546855328626</v>
       </c>
       <c r="F368" t="n">
         <v>460533</v>
@@ -7792,16 +7792,16 @@
         <v>43756</v>
       </c>
       <c r="B369" t="n">
-        <v>170.9574737548828</v>
+        <v>170.9574584960938</v>
       </c>
       <c r="C369" t="n">
-        <v>171.046634318111</v>
+        <v>171.0466190513639</v>
       </c>
       <c r="D369" t="n">
-        <v>169.1444667171556</v>
+        <v>169.1444516201863</v>
       </c>
       <c r="E369" t="n">
-        <v>170.3333195781172</v>
+        <v>170.3333043750369</v>
       </c>
       <c r="F369" t="n">
         <v>657533</v>
@@ -7812,16 +7812,16 @@
         <v>43759</v>
       </c>
       <c r="B370" t="n">
-        <v>168.5203247070312</v>
+        <v>168.5203399658203</v>
       </c>
       <c r="C370" t="n">
-        <v>171.7302258637203</v>
+        <v>171.7302414131521</v>
       </c>
       <c r="D370" t="n">
-        <v>167.9853311028604</v>
+        <v>167.9853463132081</v>
       </c>
       <c r="E370" t="n">
-        <v>171.314128125523</v>
+        <v>171.3141436372789</v>
       </c>
       <c r="F370" t="n">
         <v>853400</v>
@@ -7852,16 +7852,16 @@
         <v>43761</v>
       </c>
       <c r="B372" t="n">
-        <v>165.8453979492188</v>
+        <v>165.8453826904297</v>
       </c>
       <c r="C372" t="n">
-        <v>168.7580974273812</v>
+        <v>168.758081900606</v>
       </c>
       <c r="D372" t="n">
-        <v>164.9537620390848</v>
+        <v>164.9537468623316</v>
       </c>
       <c r="E372" t="n">
-        <v>167.2423073099024</v>
+        <v>167.2422919225891</v>
       </c>
       <c r="F372" t="n">
         <v>595766</v>
@@ -7872,16 +7872,16 @@
         <v>43762</v>
       </c>
       <c r="B373" t="n">
-        <v>169.1147308349609</v>
+        <v>169.11474609375</v>
       </c>
       <c r="C373" t="n">
-        <v>169.6497243988491</v>
+        <v>169.6497397059093</v>
       </c>
       <c r="D373" t="n">
-        <v>165.3698363560753</v>
+        <v>165.3698512769721</v>
       </c>
       <c r="E373" t="n">
-        <v>165.9048148028805</v>
+        <v>165.9048297720471</v>
       </c>
       <c r="F373" t="n">
         <v>606500</v>
@@ -7892,16 +7892,16 @@
         <v>43763</v>
       </c>
       <c r="B374" t="n">
-        <v>168.3716888427734</v>
+        <v>168.3717041015625</v>
       </c>
       <c r="C374" t="n">
-        <v>169.6497172112956</v>
+        <v>169.6497325859067</v>
       </c>
       <c r="D374" t="n">
-        <v>166.8558990044479</v>
+        <v>166.8559141258676</v>
       </c>
       <c r="E374" t="n">
-        <v>169.6497172112956</v>
+        <v>169.6497325859067</v>
       </c>
       <c r="F374" t="n">
         <v>471566</v>
@@ -7912,16 +7912,16 @@
         <v>43766</v>
       </c>
       <c r="B375" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0064086914062</v>
       </c>
       <c r="C375" t="n">
-        <v>170.5710921032597</v>
+        <v>170.5711074127329</v>
       </c>
       <c r="D375" t="n">
-        <v>167.6881130247363</v>
+        <v>167.68812807545</v>
       </c>
       <c r="E375" t="n">
-        <v>169.3525190838025</v>
+        <v>169.3525342839036</v>
       </c>
       <c r="F375" t="n">
         <v>598700</v>
@@ -7932,16 +7932,16 @@
         <v>43767</v>
       </c>
       <c r="B376" t="n">
-        <v>169.1147308349609</v>
+        <v>169.11474609375</v>
       </c>
       <c r="C376" t="n">
-        <v>170.89801751945</v>
+        <v>170.8980329391405</v>
       </c>
       <c r="D376" t="n">
-        <v>168.5203120181865</v>
+        <v>168.5203272233427</v>
       </c>
       <c r="E376" t="n">
-        <v>170.3630239555619</v>
+        <v>170.3630393269812</v>
       </c>
       <c r="F376" t="n">
         <v>290500</v>
@@ -7972,16 +7972,16 @@
         <v>43769</v>
       </c>
       <c r="B378" t="n">
-        <v>167.3314666748047</v>
+        <v>167.3314514160156</v>
       </c>
       <c r="C378" t="n">
-        <v>168.5203347025518</v>
+        <v>168.520319335351</v>
       </c>
       <c r="D378" t="n">
-        <v>166.1426137641425</v>
+        <v>166.1425986137638</v>
       </c>
       <c r="E378" t="n">
-        <v>167.5989634927563</v>
+        <v>167.5989482095744</v>
       </c>
       <c r="F378" t="n">
         <v>595400</v>
@@ -8012,16 +8012,16 @@
         <v>43773</v>
       </c>
       <c r="B380" t="n">
-        <v>165.9940032958984</v>
+        <v>165.9939880371094</v>
       </c>
       <c r="C380" t="n">
-        <v>168.5203250342948</v>
+        <v>168.5203095432768</v>
       </c>
       <c r="D380" t="n">
-        <v>163.9729398583477</v>
+        <v>163.9729247853423</v>
       </c>
       <c r="E380" t="n">
-        <v>168.5203250342948</v>
+        <v>168.5203095432768</v>
       </c>
       <c r="F380" t="n">
         <v>963600</v>
@@ -8032,16 +8032,16 @@
         <v>43774</v>
       </c>
       <c r="B381" t="n">
-        <v>161.5357971191406</v>
+        <v>161.5357818603516</v>
       </c>
       <c r="C381" t="n">
-        <v>166.885642578697</v>
+        <v>166.8856268145576</v>
       </c>
       <c r="D381" t="n">
-        <v>160.9710833150434</v>
+        <v>160.9710681095976</v>
       </c>
       <c r="E381" t="n">
-        <v>166.885642578697</v>
+        <v>166.8856268145576</v>
       </c>
       <c r="F381" t="n">
         <v>956400</v>
@@ -8052,16 +8052,16 @@
         <v>43775</v>
       </c>
       <c r="B382" t="n">
-        <v>163.4973907470703</v>
+        <v>163.4974212646484</v>
       </c>
       <c r="C382" t="n">
-        <v>164.5970829537148</v>
+        <v>164.5971136765558</v>
       </c>
       <c r="D382" t="n">
-        <v>160.1388737565751</v>
+        <v>160.1389036472698</v>
       </c>
       <c r="E382" t="n">
-        <v>161.9221604588475</v>
+        <v>161.9221906824013</v>
       </c>
       <c r="F382" t="n">
         <v>1813233</v>
@@ -8072,16 +8072,16 @@
         <v>43776</v>
       </c>
       <c r="B383" t="n">
-        <v>164.4782104492188</v>
+        <v>164.4782257080078</v>
       </c>
       <c r="C383" t="n">
-        <v>166.5884192952553</v>
+        <v>166.5884347498103</v>
       </c>
       <c r="D383" t="n">
-        <v>162.6354832841055</v>
+        <v>162.6354983719431</v>
       </c>
       <c r="E383" t="n">
-        <v>164.3295943982886</v>
+        <v>164.3296096432904</v>
       </c>
       <c r="F383" t="n">
         <v>718100</v>
@@ -8092,16 +8092,16 @@
         <v>43777</v>
       </c>
       <c r="B384" t="n">
-        <v>165.5184631347656</v>
+        <v>165.5184326171875</v>
       </c>
       <c r="C384" t="n">
-        <v>169.2039178193453</v>
+        <v>169.203886622259</v>
       </c>
       <c r="D384" t="n">
-        <v>163.4082540858343</v>
+        <v>163.4082239573274</v>
       </c>
       <c r="E384" t="n">
-        <v>164.6862675910438</v>
+        <v>164.6862372269023</v>
       </c>
       <c r="F384" t="n">
         <v>1517366</v>
@@ -8132,16 +8132,16 @@
         <v>43781</v>
       </c>
       <c r="B386" t="n">
-        <v>167.9258880615234</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C386" t="n">
-        <v>171.6410625761589</v>
+        <v>171.641046979786</v>
       </c>
       <c r="D386" t="n">
-        <v>166.8856361740087</v>
+        <v>166.8856210097434</v>
       </c>
       <c r="E386" t="n">
-        <v>170.8980276732318</v>
+        <v>170.8980121443757</v>
       </c>
       <c r="F386" t="n">
         <v>771166</v>
@@ -8152,16 +8152,16 @@
         <v>43782</v>
       </c>
       <c r="B387" t="n">
-        <v>167.8961791992188</v>
+        <v>167.8961639404297</v>
       </c>
       <c r="C387" t="n">
-        <v>170.273885002126</v>
+        <v>170.2738695272456</v>
       </c>
       <c r="D387" t="n">
-        <v>164.9834797645522</v>
+        <v>164.9834647704759</v>
       </c>
       <c r="E387" t="n">
-        <v>168.2528365813633</v>
+        <v>168.2528212901604</v>
       </c>
       <c r="F387" t="n">
         <v>1028933</v>
@@ -8172,16 +8172,16 @@
         <v>43783</v>
       </c>
       <c r="B388" t="n">
-        <v>161.5060424804688</v>
+        <v>161.5060577392578</v>
       </c>
       <c r="C388" t="n">
-        <v>167.4800408455934</v>
+        <v>167.4800566687947</v>
       </c>
       <c r="D388" t="n">
-        <v>160.9710489783817</v>
+        <v>160.9710641866256</v>
       </c>
       <c r="E388" t="n">
-        <v>165.1023205019154</v>
+        <v>165.1023361004741</v>
       </c>
       <c r="F388" t="n">
         <v>1805133</v>
@@ -8212,16 +8212,16 @@
         <v>43788</v>
       </c>
       <c r="B390" t="n">
-        <v>159.5741577148438</v>
+        <v>159.5741882324219</v>
       </c>
       <c r="C390" t="n">
-        <v>162.7840737329255</v>
+        <v>162.7841048643803</v>
       </c>
       <c r="D390" t="n">
-        <v>158.5339210107543</v>
+        <v>158.5339513293935</v>
       </c>
       <c r="E390" t="n">
-        <v>162.6354728086507</v>
+        <v>162.6355039116865</v>
       </c>
       <c r="F390" t="n">
         <v>1296633</v>
@@ -8232,16 +8232,16 @@
         <v>43790</v>
       </c>
       <c r="B391" t="n">
-        <v>165.0428924560547</v>
+        <v>165.0429077148438</v>
       </c>
       <c r="C391" t="n">
-        <v>165.4589901459087</v>
+        <v>165.4590054431674</v>
       </c>
       <c r="D391" t="n">
-        <v>159.4552711511718</v>
+        <v>159.4552858933658</v>
       </c>
       <c r="E391" t="n">
-        <v>159.9010890247952</v>
+        <v>159.9011038082066</v>
       </c>
       <c r="F391" t="n">
         <v>1440266</v>
@@ -8252,16 +8252,16 @@
         <v>43791</v>
       </c>
       <c r="B392" t="n">
-        <v>169.9766540527344</v>
+        <v>169.9766387939453</v>
       </c>
       <c r="C392" t="n">
-        <v>169.9766540527344</v>
+        <v>169.9766387939453</v>
       </c>
       <c r="D392" t="n">
-        <v>164.2404313373464</v>
+        <v>164.2404165934975</v>
       </c>
       <c r="E392" t="n">
-        <v>165.1023469746995</v>
+        <v>165.1023321534766</v>
       </c>
       <c r="F392" t="n">
         <v>1134300</v>
@@ -8312,16 +8312,16 @@
         <v>43796</v>
       </c>
       <c r="B395" t="n">
-        <v>167.9555969238281</v>
+        <v>167.9556121826172</v>
       </c>
       <c r="C395" t="n">
-        <v>170.3927578926197</v>
+        <v>170.3927733728252</v>
       </c>
       <c r="D395" t="n">
-        <v>165.2509542923181</v>
+        <v>165.25096930539</v>
       </c>
       <c r="E395" t="n">
-        <v>169.7686037787779</v>
+        <v>169.7686192022788</v>
       </c>
       <c r="F395" t="n">
         <v>429100</v>
@@ -8332,16 +8332,16 @@
         <v>43797</v>
       </c>
       <c r="B396" t="n">
-        <v>163.6162567138672</v>
+        <v>163.6162872314453</v>
       </c>
       <c r="C396" t="n">
-        <v>168.49056318188</v>
+        <v>168.49059460861</v>
       </c>
       <c r="D396" t="n">
-        <v>163.2893195882156</v>
+        <v>163.2893500448137</v>
       </c>
       <c r="E396" t="n">
-        <v>166.4695151798578</v>
+        <v>166.4695462296235</v>
       </c>
       <c r="F396" t="n">
         <v>574533</v>
@@ -8432,16 +8432,16 @@
         <v>43804</v>
       </c>
       <c r="B401" t="n">
-        <v>172.3543853759766</v>
+        <v>172.3543701171875</v>
       </c>
       <c r="C401" t="n">
-        <v>174.7618113181715</v>
+        <v>174.7617958462494</v>
       </c>
       <c r="D401" t="n">
-        <v>169.1147488144879</v>
+        <v>169.1147338425086</v>
       </c>
       <c r="E401" t="n">
-        <v>172.7110427507926</v>
+        <v>172.7110274604281</v>
       </c>
       <c r="F401" t="n">
         <v>632400</v>
@@ -8472,16 +8472,16 @@
         <v>43808</v>
       </c>
       <c r="B403" t="n">
-        <v>165.8453979492188</v>
+        <v>165.8453826904297</v>
       </c>
       <c r="C403" t="n">
-        <v>172.6218883111604</v>
+        <v>172.6218724288928</v>
       </c>
       <c r="D403" t="n">
-        <v>165.5779162464296</v>
+        <v>165.5779010122505</v>
       </c>
       <c r="E403" t="n">
-        <v>172.3841116804849</v>
+        <v>172.3840958200943</v>
       </c>
       <c r="F403" t="n">
         <v>793900</v>
@@ -8492,16 +8492,16 @@
         <v>43809</v>
       </c>
       <c r="B404" t="n">
-        <v>162.3382720947266</v>
+        <v>162.3382568359375</v>
       </c>
       <c r="C404" t="n">
-        <v>167.2720197966458</v>
+        <v>167.2720040741151</v>
       </c>
       <c r="D404" t="n">
-        <v>162.3382720947266</v>
+        <v>162.3382568359375</v>
       </c>
       <c r="E404" t="n">
-        <v>166.5884252423812</v>
+        <v>166.5884095841042</v>
       </c>
       <c r="F404" t="n">
         <v>1232166</v>
@@ -8512,16 +8512,16 @@
         <v>43810</v>
       </c>
       <c r="B405" t="n">
-        <v>167.0936889648438</v>
+        <v>167.0936737060547</v>
       </c>
       <c r="C405" t="n">
-        <v>167.0936889648438</v>
+        <v>167.0936737060547</v>
       </c>
       <c r="D405" t="n">
-        <v>161.981605315769</v>
+        <v>161.9815905238091</v>
       </c>
       <c r="E405" t="n">
-        <v>162.7840805747468</v>
+        <v>162.7840657095058</v>
       </c>
       <c r="F405" t="n">
         <v>789933</v>
@@ -8532,16 +8532,16 @@
         <v>43811</v>
       </c>
       <c r="B406" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0064086914062</v>
       </c>
       <c r="C406" t="n">
-        <v>170.214434741823</v>
+        <v>170.2144500192846</v>
       </c>
       <c r="D406" t="n">
-        <v>167.1234143540938</v>
+        <v>167.1234293541233</v>
       </c>
       <c r="E406" t="n">
-        <v>169.085022283454</v>
+        <v>169.0850374595461</v>
       </c>
       <c r="F406" t="n">
         <v>578333</v>
@@ -8552,16 +8552,16 @@
         <v>43812</v>
       </c>
       <c r="B407" t="n">
-        <v>166.9747772216797</v>
+        <v>166.9747924804688</v>
       </c>
       <c r="C407" t="n">
-        <v>171.3141053851492</v>
+        <v>171.3141210404826</v>
       </c>
       <c r="D407" t="n">
-        <v>166.2020222223059</v>
+        <v>166.2020374104777</v>
       </c>
       <c r="E407" t="n">
-        <v>170.8088471523532</v>
+        <v>170.8088627615141</v>
       </c>
       <c r="F407" t="n">
         <v>591766</v>
@@ -8572,16 +8572,16 @@
         <v>43815</v>
       </c>
       <c r="B408" t="n">
-        <v>171.9085388183594</v>
+        <v>171.9085540771484</v>
       </c>
       <c r="C408" t="n">
-        <v>175.8317541711365</v>
+        <v>175.8317697781544</v>
       </c>
       <c r="D408" t="n">
-        <v>167.0342322520436</v>
+        <v>167.0342470781839</v>
       </c>
       <c r="E408" t="n">
-        <v>167.1828331680269</v>
+        <v>167.1828480073571</v>
       </c>
       <c r="F408" t="n">
         <v>666133</v>
@@ -8592,16 +8592,16 @@
         <v>43816</v>
       </c>
       <c r="B409" t="n">
-        <v>173.1568603515625</v>
+        <v>173.1568450927734</v>
       </c>
       <c r="C409" t="n">
-        <v>175.2373642201033</v>
+        <v>175.2373487779778</v>
       </c>
       <c r="D409" t="n">
-        <v>171.4032936690544</v>
+        <v>171.4032785647917</v>
       </c>
       <c r="E409" t="n">
-        <v>173.4243571614228</v>
+        <v>173.4243418790616</v>
       </c>
       <c r="F409" t="n">
         <v>614666</v>
@@ -8612,16 +8612,16 @@
         <v>43817</v>
       </c>
       <c r="B410" t="n">
-        <v>180.4683227539062</v>
+        <v>180.4683380126953</v>
       </c>
       <c r="C410" t="n">
-        <v>180.4683227539062</v>
+        <v>180.4683380126953</v>
       </c>
       <c r="D410" t="n">
-        <v>171.6410643859569</v>
+        <v>171.6410788983919</v>
       </c>
       <c r="E410" t="n">
-        <v>171.6410643859569</v>
+        <v>171.6410788983919</v>
       </c>
       <c r="F410" t="n">
         <v>804400</v>
@@ -8632,16 +8632,16 @@
         <v>43818</v>
       </c>
       <c r="B411" t="n">
-        <v>184.7481842041016</v>
+        <v>184.7481994628906</v>
       </c>
       <c r="C411" t="n">
-        <v>185.7587158511149</v>
+        <v>185.7587311933661</v>
       </c>
       <c r="D411" t="n">
-        <v>178.922801154627</v>
+        <v>178.922815932284</v>
       </c>
       <c r="E411" t="n">
-        <v>181.3005066706881</v>
+        <v>181.3005216447253</v>
       </c>
       <c r="F411" t="n">
         <v>904966</v>
@@ -8652,16 +8652,16 @@
         <v>43819</v>
       </c>
       <c r="B412" t="n">
-        <v>190.0683135986328</v>
+        <v>190.0683288574219</v>
       </c>
       <c r="C412" t="n">
-        <v>190.0683135986328</v>
+        <v>190.0683288574219</v>
       </c>
       <c r="D412" t="n">
-        <v>182.9351672106071</v>
+        <v>182.9351818967433</v>
       </c>
       <c r="E412" t="n">
-        <v>185.8478661328706</v>
+        <v>185.8478810528398</v>
       </c>
       <c r="F412" t="n">
         <v>984100</v>
@@ -8672,16 +8672,16 @@
         <v>43822</v>
       </c>
       <c r="B413" t="n">
-        <v>187.8392181396484</v>
+        <v>187.8392333984375</v>
       </c>
       <c r="C413" t="n">
-        <v>190.4547002349917</v>
+        <v>190.4547157062448</v>
       </c>
       <c r="D413" t="n">
-        <v>186.1748121969302</v>
+        <v>186.1748273205142</v>
       </c>
       <c r="E413" t="n">
-        <v>190.216923638294</v>
+        <v>190.2169390902317</v>
       </c>
       <c r="F413" t="n">
         <v>629966</v>
@@ -8692,16 +8692,16 @@
         <v>43825</v>
       </c>
       <c r="B414" t="n">
-        <v>191.4057769775391</v>
+        <v>191.4057922363281</v>
       </c>
       <c r="C414" t="n">
-        <v>191.6435535749696</v>
+        <v>191.6435688527141</v>
       </c>
       <c r="D414" t="n">
-        <v>187.3636655237174</v>
+        <v>187.363680460271</v>
       </c>
       <c r="E414" t="n">
-        <v>188.7902948741348</v>
+        <v>188.7903099244187</v>
       </c>
       <c r="F414" t="n">
         <v>400133</v>
@@ -8712,16 +8712,16 @@
         <v>43826</v>
       </c>
       <c r="B415" t="n">
-        <v>189.6224822998047</v>
+        <v>189.6224975585938</v>
       </c>
       <c r="C415" t="n">
-        <v>194.9723421384545</v>
+        <v>194.9723578277431</v>
       </c>
       <c r="D415" t="n">
-        <v>184.9265118558081</v>
+        <v>184.9265267367157</v>
       </c>
       <c r="E415" t="n">
-        <v>194.9723421384545</v>
+        <v>194.9723578277431</v>
       </c>
       <c r="F415" t="n">
         <v>651400</v>
@@ -8732,16 +8732,16 @@
         <v>43829</v>
       </c>
       <c r="B416" t="n">
-        <v>189.9197235107422</v>
+        <v>189.9197082519531</v>
       </c>
       <c r="C416" t="n">
-        <v>193.3376811370011</v>
+        <v>193.3376656036019</v>
       </c>
       <c r="D416" t="n">
-        <v>188.0472761073423</v>
+        <v>188.047260998992</v>
       </c>
       <c r="E416" t="n">
-        <v>190.6627584345848</v>
+        <v>190.6627431160977</v>
       </c>
       <c r="F416" t="n">
         <v>1069533</v>
@@ -8752,16 +8752,16 @@
         <v>43832</v>
       </c>
       <c r="B417" t="n">
-        <v>197.4689331054688</v>
+        <v>197.4689483642578</v>
       </c>
       <c r="C417" t="n">
-        <v>199.3711156170877</v>
+        <v>199.3711310228619</v>
       </c>
       <c r="D417" t="n">
-        <v>191.4652139596019</v>
+        <v>191.4652287544725</v>
       </c>
       <c r="E417" t="n">
-        <v>193.7834941715491</v>
+        <v>193.7835091455575</v>
       </c>
       <c r="F417" t="n">
         <v>866733</v>
@@ -8772,16 +8772,16 @@
         <v>43833</v>
       </c>
       <c r="B418" t="n">
-        <v>205.8206634521484</v>
+        <v>205.8206481933594</v>
       </c>
       <c r="C418" t="n">
-        <v>205.8206634521484</v>
+        <v>205.8206481933594</v>
       </c>
       <c r="D418" t="n">
-        <v>194.3779231826556</v>
+        <v>194.3779087721894</v>
       </c>
       <c r="E418" t="n">
-        <v>195.4181750466247</v>
+        <v>195.418160559038</v>
       </c>
       <c r="F418" t="n">
         <v>3123966</v>
@@ -8792,16 +8792,16 @@
         <v>43836</v>
       </c>
       <c r="B419" t="n">
-        <v>199.4744567871094</v>
+        <v>199.4744873046875</v>
       </c>
       <c r="C419" t="n">
-        <v>205.1941488790033</v>
+        <v>205.1941802716366</v>
       </c>
       <c r="D419" t="n">
-        <v>196.3464881000858</v>
+        <v>196.3465181391163</v>
       </c>
       <c r="E419" t="n">
-        <v>203.4663181237324</v>
+        <v>203.466349252025</v>
       </c>
       <c r="F419" t="n">
         <v>735666</v>
@@ -8832,16 +8832,16 @@
         <v>43838</v>
       </c>
       <c r="B421" t="n">
-        <v>190.0011901855469</v>
+        <v>190.0012054443359</v>
       </c>
       <c r="C421" t="n">
-        <v>196.0187859349532</v>
+        <v>196.0188016770089</v>
       </c>
       <c r="D421" t="n">
-        <v>188.0052596123549</v>
+        <v>188.0052747108529</v>
       </c>
       <c r="E421" t="n">
-        <v>193.9036998505329</v>
+        <v>193.9037154227282</v>
       </c>
       <c r="F421" t="n">
         <v>832966</v>
@@ -8852,16 +8852,16 @@
         <v>43839</v>
       </c>
       <c r="B422" t="n">
-        <v>188.8691864013672</v>
+        <v>188.8691711425781</v>
       </c>
       <c r="C422" t="n">
-        <v>191.5205028574819</v>
+        <v>191.5204873844923</v>
       </c>
       <c r="D422" t="n">
-        <v>187.2009484680017</v>
+        <v>187.20093334399</v>
       </c>
       <c r="E422" t="n">
-        <v>190.001209328158</v>
+        <v>190.0011939779125</v>
       </c>
       <c r="F422" t="n">
         <v>950500</v>
@@ -8912,16 +8912,16 @@
         <v>43844</v>
       </c>
       <c r="B425" t="n">
-        <v>186.1880798339844</v>
+        <v>186.1880645751953</v>
       </c>
       <c r="C425" t="n">
-        <v>186.5157726727352</v>
+        <v>186.5157573870905</v>
       </c>
       <c r="D425" t="n">
-        <v>180.4087945629656</v>
+        <v>180.40877977781</v>
       </c>
       <c r="E425" t="n">
-        <v>185.3241719922026</v>
+        <v>185.3241568042139</v>
       </c>
       <c r="F425" t="n">
         <v>863500</v>
@@ -8932,16 +8932,16 @@
         <v>43845</v>
       </c>
       <c r="B426" t="n">
-        <v>181.7493438720703</v>
+        <v>181.7493591308594</v>
       </c>
       <c r="C426" t="n">
-        <v>188.0350548876207</v>
+        <v>188.0350706741274</v>
       </c>
       <c r="D426" t="n">
-        <v>179.3363537754593</v>
+        <v>179.3363688316654</v>
       </c>
       <c r="E426" t="n">
-        <v>187.6775731897497</v>
+        <v>187.677588946244</v>
       </c>
       <c r="F426" t="n">
         <v>1526633</v>
@@ -8992,16 +8992,16 @@
         <v>43850</v>
       </c>
       <c r="B429" t="n">
-        <v>188.1244201660156</v>
+        <v>188.1244354248047</v>
       </c>
       <c r="C429" t="n">
-        <v>189.4947691899657</v>
+        <v>189.4947845599039</v>
       </c>
       <c r="D429" t="n">
-        <v>185.9497411156683</v>
+        <v>185.9497561980689</v>
       </c>
       <c r="E429" t="n">
-        <v>189.4649803113602</v>
+        <v>189.4649956788822</v>
       </c>
       <c r="F429" t="n">
         <v>883800</v>
@@ -9012,16 +9012,16 @@
         <v>43851</v>
       </c>
       <c r="B430" t="n">
-        <v>190.0607757568359</v>
+        <v>190.060791015625</v>
       </c>
       <c r="C430" t="n">
-        <v>192.682303175826</v>
+        <v>192.682318645081</v>
       </c>
       <c r="D430" t="n">
-        <v>187.6775745221264</v>
+        <v>187.6775895895832</v>
       </c>
       <c r="E430" t="n">
-        <v>188.1542117386635</v>
+        <v>188.1542268443865</v>
       </c>
       <c r="F430" t="n">
         <v>1218200</v>
@@ -9032,16 +9032,16 @@
         <v>43852</v>
       </c>
       <c r="B431" t="n">
-        <v>190.5672302246094</v>
+        <v>190.5672149658203</v>
       </c>
       <c r="C431" t="n">
-        <v>193.2781244687579</v>
+        <v>193.2781089929065</v>
       </c>
       <c r="D431" t="n">
-        <v>189.4947850489844</v>
+        <v>189.4947698760664</v>
       </c>
       <c r="E431" t="n">
-        <v>191.4013491994205</v>
+        <v>191.4013338738432</v>
       </c>
       <c r="F431" t="n">
         <v>460300</v>
@@ -9052,16 +9052,16 @@
         <v>43853</v>
       </c>
       <c r="B432" t="n">
-        <v>191.5502777099609</v>
+        <v>191.5502624511719</v>
       </c>
       <c r="C432" t="n">
-        <v>191.5502777099609</v>
+        <v>191.5502624511719</v>
       </c>
       <c r="D432" t="n">
-        <v>186.515760245738</v>
+        <v>186.5157453879958</v>
       </c>
       <c r="E432" t="n">
-        <v>189.8224621415167</v>
+        <v>189.8224470203644</v>
       </c>
       <c r="F432" t="n">
         <v>1068366</v>
@@ -9072,16 +9072,16 @@
         <v>43854</v>
       </c>
       <c r="B433" t="n">
-        <v>192.1460876464844</v>
+        <v>192.1461029052734</v>
       </c>
       <c r="C433" t="n">
-        <v>193.1887438656685</v>
+        <v>193.1887592072574</v>
       </c>
       <c r="D433" t="n">
-        <v>190.0607752081161</v>
+        <v>190.0607903013054</v>
       </c>
       <c r="E433" t="n">
-        <v>191.8481837049998</v>
+        <v>191.8481989401316</v>
       </c>
       <c r="F433" t="n">
         <v>639666</v>
@@ -9092,16 +9092,16 @@
         <v>43857</v>
       </c>
       <c r="B434" t="n">
-        <v>182.4047241210938</v>
+        <v>182.4047393798828</v>
       </c>
       <c r="C434" t="n">
-        <v>189.7628800128631</v>
+        <v>189.7628958871874</v>
       </c>
       <c r="D434" t="n">
-        <v>180.5279490507258</v>
+        <v>180.5279641525161</v>
       </c>
       <c r="E434" t="n">
-        <v>189.7628800128631</v>
+        <v>189.7628958871874</v>
       </c>
       <c r="F434" t="n">
         <v>939566</v>
@@ -9112,16 +9112,16 @@
         <v>43858</v>
       </c>
       <c r="B435" t="n">
-        <v>186.1880798339844</v>
+        <v>186.1880645751953</v>
       </c>
       <c r="C435" t="n">
-        <v>186.7540837176268</v>
+        <v>186.7540684124517</v>
       </c>
       <c r="D435" t="n">
-        <v>182.4047404760818</v>
+        <v>182.4047255273511</v>
       </c>
       <c r="E435" t="n">
-        <v>184.4006712371732</v>
+        <v>184.4006561248688</v>
       </c>
       <c r="F435" t="n">
         <v>417866</v>
@@ -9132,16 +9132,16 @@
         <v>43859</v>
       </c>
       <c r="B436" t="n">
-        <v>182.6132354736328</v>
+        <v>182.6132659912109</v>
       </c>
       <c r="C436" t="n">
-        <v>187.5286121716265</v>
+        <v>187.5286435106423</v>
       </c>
       <c r="D436" t="n">
-        <v>181.1237310565493</v>
+        <v>181.1237613252075</v>
       </c>
       <c r="E436" t="n">
-        <v>186.9328043439841</v>
+        <v>186.9328355834309</v>
       </c>
       <c r="F436" t="n">
         <v>838300</v>
@@ -9152,16 +9152,16 @@
         <v>43860</v>
       </c>
       <c r="B437" t="n">
-        <v>179.0682678222656</v>
+        <v>179.0682525634766</v>
       </c>
       <c r="C437" t="n">
-        <v>182.5239146953973</v>
+        <v>182.5238991421452</v>
       </c>
       <c r="D437" t="n">
-        <v>174.8678685535092</v>
+        <v>174.8678536526452</v>
       </c>
       <c r="E437" t="n">
-        <v>182.5239146953973</v>
+        <v>182.5238991421452</v>
       </c>
       <c r="F437" t="n">
         <v>937800</v>
@@ -9172,16 +9172,16 @@
         <v>43861</v>
       </c>
       <c r="B438" t="n">
-        <v>178.9490661621094</v>
+        <v>178.9490814208984</v>
       </c>
       <c r="C438" t="n">
-        <v>179.8725668518933</v>
+        <v>179.8725821894282</v>
       </c>
       <c r="D438" t="n">
-        <v>175.3742643730724</v>
+        <v>175.374279327042</v>
       </c>
       <c r="E438" t="n">
-        <v>177.3701949931508</v>
+        <v>177.3702101173112</v>
       </c>
       <c r="F438" t="n">
         <v>886766</v>
@@ -9212,16 +9212,16 @@
         <v>43865</v>
       </c>
       <c r="B440" t="n">
-        <v>182.76220703125</v>
+        <v>182.7622222900391</v>
       </c>
       <c r="C440" t="n">
-        <v>186.5753349533802</v>
+        <v>186.5753505305267</v>
       </c>
       <c r="D440" t="n">
-        <v>182.5238808541081</v>
+        <v>182.5238960929993</v>
       </c>
       <c r="E440" t="n">
-        <v>186.3667976543781</v>
+        <v>186.3668132141139</v>
       </c>
       <c r="F440" t="n">
         <v>732700</v>
@@ -9252,16 +9252,16 @@
         <v>43867</v>
       </c>
       <c r="B442" t="n">
-        <v>174.8678588867188</v>
+        <v>174.8678436279297</v>
       </c>
       <c r="C442" t="n">
-        <v>179.3363730134456</v>
+        <v>179.3363573647385</v>
       </c>
       <c r="D442" t="n">
-        <v>174.0635136162066</v>
+        <v>174.0634984276038</v>
       </c>
       <c r="E442" t="n">
-        <v>174.8678588867188</v>
+        <v>174.8678436279297</v>
       </c>
       <c r="F442" t="n">
         <v>1198833</v>
@@ -9272,16 +9272,16 @@
         <v>43868</v>
       </c>
       <c r="B443" t="n">
-        <v>171.6802978515625</v>
+        <v>171.6803131103516</v>
       </c>
       <c r="C443" t="n">
-        <v>180.8556515493858</v>
+        <v>180.855667623672</v>
       </c>
       <c r="D443" t="n">
-        <v>171.4419716632469</v>
+        <v>171.4419869008538</v>
       </c>
       <c r="E443" t="n">
-        <v>172.9612651277013</v>
+        <v>172.9612805003416</v>
       </c>
       <c r="F443" t="n">
         <v>1239533</v>
@@ -9292,16 +9292,16 @@
         <v>43871</v>
       </c>
       <c r="B444" t="n">
-        <v>166.1095581054688</v>
+        <v>166.1095428466797</v>
       </c>
       <c r="C444" t="n">
-        <v>172.7527512987726</v>
+        <v>172.7527354297412</v>
       </c>
       <c r="D444" t="n">
-        <v>164.0838384392179</v>
+        <v>164.083823366511</v>
       </c>
       <c r="E444" t="n">
-        <v>171.6505172467174</v>
+        <v>171.6505014789369</v>
       </c>
       <c r="F444" t="n">
         <v>872966</v>
@@ -9352,16 +9352,16 @@
         <v>43874</v>
       </c>
       <c r="B447" t="n">
-        <v>174.8678588867188</v>
+        <v>174.8678436279297</v>
       </c>
       <c r="C447" t="n">
-        <v>175.9700778253669</v>
+        <v>175.9700624703994</v>
       </c>
       <c r="D447" t="n">
-        <v>171.7696787888109</v>
+        <v>171.7696638003658</v>
       </c>
       <c r="E447" t="n">
-        <v>174.272050942345</v>
+        <v>174.2720357355455</v>
       </c>
       <c r="F447" t="n">
         <v>404433</v>
@@ -9372,16 +9372,16 @@
         <v>43875</v>
       </c>
       <c r="B448" t="n">
-        <v>174.2422332763672</v>
+        <v>174.2422485351562</v>
       </c>
       <c r="C448" t="n">
-        <v>175.9998527850967</v>
+        <v>175.9998681978045</v>
       </c>
       <c r="D448" t="n">
-        <v>172.9910398302784</v>
+        <v>172.9910549794976</v>
       </c>
       <c r="E448" t="n">
-        <v>175.7913154934076</v>
+        <v>175.7913308878533</v>
       </c>
       <c r="F448" t="n">
         <v>468100</v>
@@ -9412,16 +9412,16 @@
         <v>43879</v>
       </c>
       <c r="B450" t="n">
-        <v>175.7019500732422</v>
+        <v>175.7019653320312</v>
       </c>
       <c r="C450" t="n">
-        <v>177.5191473486881</v>
+        <v>177.5191627652912</v>
       </c>
       <c r="D450" t="n">
-        <v>172.7825188816086</v>
+        <v>172.7825338868604</v>
       </c>
       <c r="E450" t="n">
-        <v>177.5191473486881</v>
+        <v>177.5191627652912</v>
       </c>
       <c r="F450" t="n">
         <v>669733</v>
@@ -9432,16 +9432,16 @@
         <v>43880</v>
       </c>
       <c r="B451" t="n">
-        <v>177.3702239990234</v>
+        <v>177.3702087402344</v>
       </c>
       <c r="C451" t="n">
-        <v>178.3235137232084</v>
+        <v>178.3234983824099</v>
       </c>
       <c r="D451" t="n">
-        <v>173.1996136537696</v>
+        <v>173.1995987537694</v>
       </c>
       <c r="E451" t="n">
-        <v>174.9870224166001</v>
+        <v>174.9870073628329</v>
       </c>
       <c r="F451" t="n">
         <v>740433</v>
@@ -9452,16 +9452,16 @@
         <v>43881</v>
       </c>
       <c r="B452" t="n">
-        <v>172.1569213867188</v>
+        <v>172.1569366455078</v>
       </c>
       <c r="C452" t="n">
-        <v>177.072283095687</v>
+        <v>177.0722987901394</v>
       </c>
       <c r="D452" t="n">
-        <v>171.3228025219774</v>
+        <v>171.3228177068359</v>
       </c>
       <c r="E452" t="n">
-        <v>175.7019492899041</v>
+        <v>175.7019648628997</v>
       </c>
       <c r="F452" t="n">
         <v>757533</v>
@@ -9472,16 +9472,16 @@
         <v>43882</v>
       </c>
       <c r="B453" t="n">
-        <v>166.8245086669922</v>
+        <v>166.8245239257812</v>
       </c>
       <c r="C453" t="n">
-        <v>171.2334445346579</v>
+        <v>171.2334601967152</v>
       </c>
       <c r="D453" t="n">
-        <v>165.543526276023</v>
+        <v>165.5435414176457</v>
       </c>
       <c r="E453" t="n">
-        <v>169.8333066290028</v>
+        <v>169.8333221629949</v>
       </c>
       <c r="F453" t="n">
         <v>990066</v>
@@ -9492,16 +9492,16 @@
         <v>43887</v>
       </c>
       <c r="B454" t="n">
-        <v>156.4575500488281</v>
+        <v>156.4575653076172</v>
       </c>
       <c r="C454" t="n">
-        <v>160.5685818573121</v>
+        <v>160.5685975170366</v>
       </c>
       <c r="D454" t="n">
-        <v>154.1637155461845</v>
+        <v>154.1637305812634</v>
       </c>
       <c r="E454" t="n">
-        <v>159.5259256782859</v>
+        <v>159.5259412363235</v>
       </c>
       <c r="F454" t="n">
         <v>1832133</v>
@@ -9512,16 +9512,16 @@
         <v>43888</v>
       </c>
       <c r="B455" t="n">
-        <v>158.6322326660156</v>
+        <v>158.6322174072266</v>
       </c>
       <c r="C455" t="n">
-        <v>163.4582279560204</v>
+        <v>163.4582122330202</v>
       </c>
       <c r="D455" t="n">
-        <v>151.1549211271597</v>
+        <v>151.1549065876111</v>
       </c>
       <c r="E455" t="n">
-        <v>152.4954661148132</v>
+        <v>152.495451446318</v>
       </c>
       <c r="F455" t="n">
         <v>1732266</v>
@@ -9552,16 +9552,16 @@
         <v>43892</v>
       </c>
       <c r="B457" t="n">
-        <v>162.5347137451172</v>
+        <v>162.5347442626953</v>
       </c>
       <c r="C457" t="n">
-        <v>165.9307971294947</v>
+        <v>165.9308282847228</v>
       </c>
       <c r="D457" t="n">
-        <v>159.0790677607593</v>
+        <v>159.079097629504</v>
       </c>
       <c r="E457" t="n">
-        <v>164.7391814813513</v>
+        <v>164.7392124128411</v>
       </c>
       <c r="F457" t="n">
         <v>1544166</v>
@@ -9572,16 +9572,16 @@
         <v>43893</v>
       </c>
       <c r="B458" t="n">
-        <v>165.0966644287109</v>
+        <v>165.0966949462891</v>
       </c>
       <c r="C458" t="n">
-        <v>168.6416922206513</v>
+        <v>168.6417233935162</v>
       </c>
       <c r="D458" t="n">
-        <v>161.0154217125558</v>
+        <v>161.0154514757296</v>
       </c>
       <c r="E458" t="n">
-        <v>161.1643812457429</v>
+        <v>161.1644110364513</v>
       </c>
       <c r="F458" t="n">
         <v>1281800</v>
@@ -9592,16 +9592,16 @@
         <v>43894</v>
       </c>
       <c r="B459" t="n">
-        <v>159.4663696289062</v>
+        <v>159.4663391113281</v>
       </c>
       <c r="C459" t="n">
-        <v>169.743958125091</v>
+        <v>169.7439256406586</v>
       </c>
       <c r="D459" t="n">
-        <v>159.0790990127847</v>
+        <v>159.0790685693198</v>
       </c>
       <c r="E459" t="n">
-        <v>167.5692788376297</v>
+        <v>167.5692467693725</v>
       </c>
       <c r="F459" t="n">
         <v>1186600</v>
@@ -9632,16 +9632,16 @@
         <v>43896</v>
       </c>
       <c r="B461" t="n">
-        <v>148.980224609375</v>
+        <v>148.9802551269531</v>
       </c>
       <c r="C461" t="n">
-        <v>152.8231410026753</v>
+        <v>152.8231723074485</v>
       </c>
       <c r="D461" t="n">
-        <v>147.8779907788596</v>
+        <v>147.8780210706527</v>
       </c>
       <c r="E461" t="n">
-        <v>151.9294444490777</v>
+        <v>151.9294755707833</v>
       </c>
       <c r="F461" t="n">
         <v>1046833</v>
@@ -9652,16 +9652,16 @@
         <v>43899</v>
       </c>
       <c r="B462" t="n">
-        <v>134.4129028320312</v>
+        <v>134.4128875732422</v>
       </c>
       <c r="C462" t="n">
-        <v>142.4562190069967</v>
+        <v>142.4562028351162</v>
       </c>
       <c r="D462" t="n">
-        <v>134.4129028320312</v>
+        <v>134.4128875732422</v>
       </c>
       <c r="E462" t="n">
-        <v>137.8089716817311</v>
+        <v>137.8089560374144</v>
       </c>
       <c r="F462" t="n">
         <v>2156300</v>
@@ -9672,16 +9672,16 @@
         <v>43900</v>
       </c>
       <c r="B463" t="n">
-        <v>145.6437683105469</v>
+        <v>145.6437377929688</v>
       </c>
       <c r="C463" t="n">
-        <v>147.3715992239526</v>
+        <v>147.3715683443321</v>
       </c>
       <c r="D463" t="n">
-        <v>136.9152774017098</v>
+        <v>136.9152487130627</v>
       </c>
       <c r="E463" t="n">
-        <v>142.4562215733386</v>
+        <v>142.4561917236655</v>
       </c>
       <c r="F463" t="n">
         <v>1718533</v>
@@ -9692,16 +9692,16 @@
         <v>43901</v>
       </c>
       <c r="B464" t="n">
-        <v>134.025634765625</v>
+        <v>134.0256195068359</v>
       </c>
       <c r="C464" t="n">
-        <v>144.2436303900958</v>
+        <v>144.2436139679902</v>
       </c>
       <c r="D464" t="n">
-        <v>122.0202228861016</v>
+        <v>122.020208994126</v>
       </c>
       <c r="E464" t="n">
-        <v>142.0391622112843</v>
+        <v>142.0391460401569</v>
       </c>
       <c r="F464" t="n">
         <v>1332366</v>
@@ -9712,16 +9712,16 @@
         <v>43902</v>
       </c>
       <c r="B465" t="n">
-        <v>116.0621948242188</v>
+        <v>116.0621871948242</v>
       </c>
       <c r="C465" t="n">
-        <v>124.8204815027402</v>
+        <v>124.8204732976162</v>
       </c>
       <c r="D465" t="n">
-        <v>107.3634934809335</v>
+        <v>107.3634864233516</v>
       </c>
       <c r="E465" t="n">
-        <v>111.2064104711344</v>
+        <v>111.2064031609368</v>
       </c>
       <c r="F465" t="n">
         <v>1010966</v>
@@ -9752,16 +9752,16 @@
         <v>43906</v>
       </c>
       <c r="B467" t="n">
-        <v>110.2233505249023</v>
+        <v>110.2233352661133</v>
       </c>
       <c r="C467" t="n">
-        <v>120.6796725652378</v>
+        <v>120.6796558589259</v>
       </c>
       <c r="D467" t="n">
-        <v>106.3208478113856</v>
+        <v>106.3208330928401</v>
       </c>
       <c r="E467" t="n">
-        <v>109.7467056756733</v>
+        <v>109.7466904828687</v>
       </c>
       <c r="F467" t="n">
         <v>2066566</v>
@@ -9792,16 +9792,16 @@
         <v>43908</v>
       </c>
       <c r="B469" t="n">
-        <v>94.49417114257812</v>
+        <v>94.49416351318359</v>
       </c>
       <c r="C469" t="n">
-        <v>104.8611259403486</v>
+        <v>104.8611174739333</v>
       </c>
       <c r="D469" t="n">
-        <v>85.43798771097393</v>
+        <v>85.43798081276944</v>
       </c>
       <c r="E469" t="n">
-        <v>103.6695252496678</v>
+        <v>103.6695168794615</v>
       </c>
       <c r="F469" t="n">
         <v>1809666</v>
@@ -9812,16 +9812,16 @@
         <v>43909</v>
       </c>
       <c r="B470" t="n">
-        <v>107.5422210693359</v>
+        <v>107.5422286987305</v>
       </c>
       <c r="C470" t="n">
-        <v>109.0615220332861</v>
+        <v>109.0615297704648</v>
       </c>
       <c r="D470" t="n">
-        <v>84.36553453174244</v>
+        <v>84.36554051690753</v>
       </c>
       <c r="E470" t="n">
-        <v>90.85977510403768</v>
+        <v>90.8597815499253</v>
       </c>
       <c r="F470" t="n">
         <v>2314466</v>
@@ -9852,16 +9852,16 @@
         <v>43913</v>
       </c>
       <c r="B472" t="n">
-        <v>113.7981414794922</v>
+        <v>113.7981491088867</v>
       </c>
       <c r="C472" t="n">
-        <v>119.6072074731813</v>
+        <v>119.6072154920344</v>
       </c>
       <c r="D472" t="n">
-        <v>108.4657126798635</v>
+        <v>108.4657199517548</v>
       </c>
       <c r="E472" t="n">
-        <v>118.9518294373453</v>
+        <v>118.9518374122596</v>
       </c>
       <c r="F472" t="n">
         <v>1372400</v>
@@ -9872,16 +9872,16 @@
         <v>43914</v>
       </c>
       <c r="B473" t="n">
-        <v>126.0121002197266</v>
+        <v>126.012077331543</v>
       </c>
       <c r="C473" t="n">
-        <v>131.0764147281101</v>
+        <v>131.0763909200707</v>
       </c>
       <c r="D473" t="n">
-        <v>118.8624730525856</v>
+        <v>118.8624514630232</v>
       </c>
       <c r="E473" t="n">
-        <v>120.3519777654051</v>
+        <v>120.3519559052967</v>
       </c>
       <c r="F473" t="n">
         <v>1251533</v>
@@ -9892,16 +9892,16 @@
         <v>43915</v>
       </c>
       <c r="B474" t="n">
-        <v>135.2469940185547</v>
+        <v>135.2470397949219</v>
       </c>
       <c r="C474" t="n">
-        <v>138.3749622926183</v>
+        <v>138.3750091276931</v>
       </c>
       <c r="D474" t="n">
-        <v>119.8455242586765</v>
+        <v>119.845564822186</v>
       </c>
       <c r="E474" t="n">
-        <v>123.8969703948857</v>
+        <v>123.8970123296677</v>
       </c>
       <c r="F474" t="n">
         <v>1102933</v>
@@ -9912,16 +9912,16 @@
         <v>43916</v>
       </c>
       <c r="B475" t="n">
-        <v>150.1122436523438</v>
+        <v>150.1122741699219</v>
       </c>
       <c r="C475" t="n">
-        <v>158.9301140813228</v>
+        <v>158.9301463915598</v>
       </c>
       <c r="D475" t="n">
-        <v>132.8935773380452</v>
+        <v>132.8936043550962</v>
       </c>
       <c r="E475" t="n">
-        <v>135.2469893165816</v>
+        <v>135.2470168120774</v>
       </c>
       <c r="F475" t="n">
         <v>1421366</v>
@@ -9932,16 +9932,16 @@
         <v>43917</v>
       </c>
       <c r="B476" t="n">
-        <v>135.5449371337891</v>
+        <v>135.5449066162109</v>
       </c>
       <c r="C476" t="n">
-        <v>143.9457357413418</v>
+        <v>143.9457033323465</v>
       </c>
       <c r="D476" t="n">
-        <v>133.7277394550709</v>
+        <v>133.72770934663</v>
       </c>
       <c r="E476" t="n">
-        <v>141.3838008128161</v>
+        <v>141.3837689806335</v>
       </c>
       <c r="F476" t="n">
         <v>773066</v>
@@ -9952,16 +9952,16 @@
         <v>43920</v>
       </c>
       <c r="B477" t="n">
-        <v>134.1447906494141</v>
+        <v>134.144775390625</v>
       </c>
       <c r="C477" t="n">
-        <v>138.7324603110987</v>
+        <v>138.7324445304684</v>
       </c>
       <c r="D477" t="n">
-        <v>128.6932131039123</v>
+        <v>128.6931984652328</v>
       </c>
       <c r="E477" t="n">
-        <v>134.6512319485003</v>
+        <v>134.6512166321043</v>
       </c>
       <c r="F477" t="n">
         <v>909700</v>
@@ -9972,16 +9972,16 @@
         <v>43921</v>
       </c>
       <c r="B478" t="n">
-        <v>126.3099899291992</v>
+        <v>126.3099822998047</v>
       </c>
       <c r="C478" t="n">
-        <v>138.5239309580564</v>
+        <v>138.5239225909137</v>
       </c>
       <c r="D478" t="n">
-        <v>125.1183892524381</v>
+        <v>125.1183816950188</v>
       </c>
       <c r="E478" t="n">
-        <v>134.1447836977352</v>
+        <v>134.1447755951023</v>
       </c>
       <c r="F478" t="n">
         <v>993633</v>
@@ -9992,16 +9992,16 @@
         <v>43922</v>
       </c>
       <c r="B479" t="n">
-        <v>119.398681640625</v>
+        <v>119.3986968994141</v>
       </c>
       <c r="C479" t="n">
-        <v>125.6248148518141</v>
+        <v>125.6248309062841</v>
       </c>
       <c r="D479" t="n">
-        <v>115.7344980529492</v>
+        <v>115.7345128434667</v>
       </c>
       <c r="E479" t="n">
-        <v>120.6498675737846</v>
+        <v>120.6498829924714</v>
       </c>
       <c r="F479" t="n">
         <v>1115733</v>
@@ -10032,16 +10032,16 @@
         <v>43924</v>
       </c>
       <c r="B481" t="n">
-        <v>112.4575958251953</v>
+        <v>112.4575881958008</v>
       </c>
       <c r="C481" t="n">
-        <v>121.3946233079923</v>
+        <v>121.3946150722883</v>
       </c>
       <c r="D481" t="n">
-        <v>109.1508938383175</v>
+        <v>109.1508864332576</v>
       </c>
       <c r="E481" t="n">
-        <v>121.2456713347432</v>
+        <v>121.2456631091445</v>
       </c>
       <c r="F481" t="n">
         <v>1289233</v>
@@ -10052,16 +10052,16 @@
         <v>43927</v>
       </c>
       <c r="B482" t="n">
-        <v>128.0973815917969</v>
+        <v>128.0973968505859</v>
       </c>
       <c r="C482" t="n">
-        <v>135.6342704071079</v>
+        <v>135.6342865636811</v>
       </c>
       <c r="D482" t="n">
-        <v>118.2368619150623</v>
+        <v>118.2368759992794</v>
       </c>
       <c r="E482" t="n">
-        <v>119.1603549691134</v>
+        <v>119.1603691633358</v>
       </c>
       <c r="F482" t="n">
         <v>1479633</v>
@@ -10072,16 +10072,16 @@
         <v>43928</v>
       </c>
       <c r="B483" t="n">
-        <v>143.8861083984375</v>
+        <v>143.8861389160156</v>
       </c>
       <c r="C483" t="n">
-        <v>154.908446208712</v>
+        <v>154.908479064077</v>
       </c>
       <c r="D483" t="n">
-        <v>138.0174730095282</v>
+        <v>138.0175022823959</v>
       </c>
       <c r="E483" t="n">
-        <v>145.1968794470199</v>
+        <v>145.1969102426065</v>
       </c>
       <c r="F483" t="n">
         <v>1844300</v>
@@ -10112,16 +10112,16 @@
         <v>43930</v>
       </c>
       <c r="B485" t="n">
-        <v>145.5544128417969</v>
+        <v>145.5543823242188</v>
       </c>
       <c r="C485" t="n">
-        <v>153.0913035951916</v>
+        <v>153.0912714973958</v>
       </c>
       <c r="D485" t="n">
-        <v>144.4223897845756</v>
+        <v>144.4223595043424</v>
       </c>
       <c r="E485" t="n">
-        <v>150.4995646020763</v>
+        <v>150.4995330476759</v>
       </c>
       <c r="F485" t="n">
         <v>918500</v>
@@ -10132,16 +10132,16 @@
         <v>43934</v>
       </c>
       <c r="B486" t="n">
-        <v>146.2395782470703</v>
+        <v>146.2395629882812</v>
       </c>
       <c r="C486" t="n">
-        <v>151.3038852244566</v>
+        <v>151.3038694372525</v>
       </c>
       <c r="D486" t="n">
-        <v>140.6390410831683</v>
+        <v>140.6390264087451</v>
       </c>
       <c r="E486" t="n">
-        <v>142.6647608437177</v>
+        <v>142.6647459579288</v>
       </c>
       <c r="F486" t="n">
         <v>651233</v>
@@ -10152,16 +10152,16 @@
         <v>43935</v>
       </c>
       <c r="B487" t="n">
-        <v>157.8577117919922</v>
+        <v>157.8576812744141</v>
       </c>
       <c r="C487" t="n">
-        <v>161.5814736003482</v>
+        <v>161.5814423628801</v>
       </c>
       <c r="D487" t="n">
-        <v>150.0824953179016</v>
+        <v>150.0824663034543</v>
       </c>
       <c r="E487" t="n">
-        <v>150.1718619648161</v>
+        <v>150.171832933092</v>
       </c>
       <c r="F487" t="n">
         <v>964366</v>
@@ -10172,16 +10172,16 @@
         <v>43936</v>
       </c>
       <c r="B488" t="n">
-        <v>155.0574035644531</v>
+        <v>155.0574188232422</v>
       </c>
       <c r="C488" t="n">
-        <v>160.8068990923668</v>
+        <v>160.8069149169485</v>
       </c>
       <c r="D488" t="n">
-        <v>148.086533810641</v>
+        <v>148.0865483834452</v>
       </c>
       <c r="E488" t="n">
-        <v>154.6105552702891</v>
+        <v>154.610570485105</v>
       </c>
       <c r="F488" t="n">
         <v>821233</v>
@@ -10212,16 +10212,16 @@
         <v>43938</v>
       </c>
       <c r="B490" t="n">
-        <v>156.1000823974609</v>
+        <v>156.1000671386719</v>
       </c>
       <c r="C490" t="n">
-        <v>159.6451106944625</v>
+        <v>159.6450950891468</v>
       </c>
       <c r="D490" t="n">
-        <v>151.8401058169883</v>
+        <v>151.8400909746121</v>
       </c>
       <c r="E490" t="n">
-        <v>159.6451106944625</v>
+        <v>159.6450950891468</v>
       </c>
       <c r="F490" t="n">
         <v>607466</v>
@@ -10252,16 +10252,16 @@
         <v>43943</v>
       </c>
       <c r="B492" t="n">
-        <v>158.8109741210938</v>
+        <v>158.8109588623047</v>
       </c>
       <c r="C492" t="n">
-        <v>166.8245161896017</v>
+        <v>166.8245001608599</v>
       </c>
       <c r="D492" t="n">
-        <v>157.6193734644301</v>
+        <v>157.6193583201317</v>
       </c>
       <c r="E492" t="n">
-        <v>166.8245161896017</v>
+        <v>166.8245001608599</v>
       </c>
       <c r="F492" t="n">
         <v>2119233</v>
@@ -10272,16 +10272,16 @@
         <v>43944</v>
       </c>
       <c r="B493" t="n">
-        <v>151.8401031494141</v>
+        <v>151.8401184082031</v>
       </c>
       <c r="C493" t="n">
-        <v>160.8664974239381</v>
+        <v>160.8665135898119</v>
       </c>
       <c r="D493" t="n">
-        <v>144.8096395919027</v>
+        <v>144.809654144183</v>
       </c>
       <c r="E493" t="n">
-        <v>159.8238411694891</v>
+        <v>159.8238572305839</v>
       </c>
       <c r="F493" t="n">
         <v>1242300</v>
@@ -10292,16 +10292,16 @@
         <v>43945</v>
       </c>
       <c r="B494" t="n">
-        <v>148.9504699707031</v>
+        <v>148.9504547119141</v>
       </c>
       <c r="C494" t="n">
-        <v>152.0188460156135</v>
+        <v>152.0188304424938</v>
       </c>
       <c r="D494" t="n">
-        <v>136.1109315801753</v>
+        <v>136.1109176366947</v>
       </c>
       <c r="E494" t="n">
-        <v>146.9545391278248</v>
+        <v>146.954524073503</v>
       </c>
       <c r="F494" t="n">
         <v>1301233</v>
@@ -10312,16 +10312,16 @@
         <v>43948</v>
       </c>
       <c r="B495" t="n">
-        <v>156.9640045166016</v>
+        <v>156.9639587402344</v>
       </c>
       <c r="C495" t="n">
-        <v>157.9172942346718</v>
+        <v>157.9172481802909</v>
       </c>
       <c r="D495" t="n">
-        <v>152.8231830812869</v>
+        <v>152.8231385125326</v>
       </c>
       <c r="E495" t="n">
-        <v>153.8658394489189</v>
+        <v>153.8657945760884</v>
       </c>
       <c r="F495" t="n">
         <v>935633</v>
@@ -10352,16 +10352,16 @@
         <v>43950</v>
       </c>
       <c r="B497" t="n">
-        <v>161.9591369628906</v>
+        <v>161.9591064453125</v>
       </c>
       <c r="C497" t="n">
-        <v>164.790060292696</v>
+        <v>164.7900292416936</v>
       </c>
       <c r="D497" t="n">
-        <v>159.7241903125012</v>
+        <v>159.7241602160489</v>
       </c>
       <c r="E497" t="n">
-        <v>161.3631451267727</v>
+        <v>161.3631147214959</v>
       </c>
       <c r="F497" t="n">
         <v>594666</v>
@@ -10372,16 +10372,16 @@
         <v>43951</v>
       </c>
       <c r="B498" t="n">
-        <v>156.2674713134766</v>
+        <v>156.2674560546875</v>
       </c>
       <c r="C498" t="n">
-        <v>162.1081370946308</v>
+        <v>162.108121265528</v>
       </c>
       <c r="D498" t="n">
-        <v>155.4926909739401</v>
+        <v>155.4926757908048</v>
       </c>
       <c r="E498" t="n">
-        <v>159.0984099702694</v>
+        <v>159.0983944350523</v>
       </c>
       <c r="F498" t="n">
         <v>826166</v>
@@ -10392,16 +10392,16 @@
         <v>43955</v>
       </c>
       <c r="B499" t="n">
-        <v>152.4531402587891</v>
+        <v>152.4531555175781</v>
       </c>
       <c r="C499" t="n">
-        <v>152.8107322907865</v>
+        <v>152.8107475853664</v>
       </c>
       <c r="D499" t="n">
-        <v>147.5660592592903</v>
+        <v>147.5660740289393</v>
       </c>
       <c r="E499" t="n">
-        <v>148.5494411364585</v>
+        <v>148.5494560045326</v>
       </c>
       <c r="F499" t="n">
         <v>865433</v>
@@ -10432,16 +10432,16 @@
         <v>43957</v>
       </c>
       <c r="B501" t="n">
-        <v>155.5820922851562</v>
+        <v>155.5821075439453</v>
       </c>
       <c r="C501" t="n">
-        <v>160.2009760045912</v>
+        <v>160.2009917163796</v>
       </c>
       <c r="D501" t="n">
-        <v>150.3076054152394</v>
+        <v>150.3076201567306</v>
       </c>
       <c r="E501" t="n">
-        <v>155.2840963646471</v>
+        <v>155.28411159421</v>
       </c>
       <c r="F501" t="n">
         <v>746233</v>
@@ -10532,16 +10532,16 @@
         <v>43964</v>
       </c>
       <c r="B506" t="n">
-        <v>145.7781066894531</v>
+        <v>145.7781219482422</v>
       </c>
       <c r="C506" t="n">
-        <v>153.9431125479351</v>
+        <v>153.9431286613662</v>
       </c>
       <c r="D506" t="n">
-        <v>145.7781066894531</v>
+        <v>145.7781219482422</v>
       </c>
       <c r="E506" t="n">
-        <v>152.3041578240206</v>
+        <v>152.3041737659001</v>
       </c>
       <c r="F506" t="n">
         <v>632666</v>
@@ -10552,16 +10552,16 @@
         <v>43965</v>
       </c>
       <c r="B507" t="n">
-        <v>141.2784118652344</v>
+        <v>141.2783966064453</v>
       </c>
       <c r="C507" t="n">
-        <v>147.5064669352663</v>
+        <v>147.5064510038155</v>
       </c>
       <c r="D507" t="n">
-        <v>138.3580793877065</v>
+        <v>138.3580644443282</v>
       </c>
       <c r="E507" t="n">
-        <v>145.6589105815262</v>
+        <v>145.658894849621</v>
       </c>
       <c r="F507" t="n">
         <v>844800</v>
@@ -10572,16 +10572,16 @@
         <v>43966</v>
       </c>
       <c r="B508" t="n">
-        <v>139.7586669921875</v>
+        <v>139.7586364746094</v>
       </c>
       <c r="C508" t="n">
-        <v>143.5431743950443</v>
+        <v>143.5431430510845</v>
       </c>
       <c r="D508" t="n">
-        <v>134.9907775634558</v>
+        <v>134.9907480869898</v>
       </c>
       <c r="E508" t="n">
-        <v>140.324860777095</v>
+        <v>140.3248301358833</v>
       </c>
       <c r="F508" t="n">
         <v>930266</v>
@@ -10592,16 +10592,16 @@
         <v>43969</v>
       </c>
       <c r="B509" t="n">
-        <v>147.6256713867188</v>
+        <v>147.6256561279297</v>
       </c>
       <c r="C509" t="n">
-        <v>148.3408555281376</v>
+        <v>148.3408401954261</v>
       </c>
       <c r="D509" t="n">
-        <v>142.4405939397833</v>
+        <v>142.4405792169308</v>
       </c>
       <c r="E509" t="n">
-        <v>144.4967521355379</v>
+        <v>144.4967372001582</v>
       </c>
       <c r="F509" t="n">
         <v>822866</v>
@@ -10612,16 +10612,16 @@
         <v>43970</v>
       </c>
       <c r="B510" t="n">
-        <v>150.1585845947266</v>
+        <v>150.1585998535156</v>
       </c>
       <c r="C510" t="n">
-        <v>154.9562709566101</v>
+        <v>154.9562867029296</v>
       </c>
       <c r="D510" t="n">
-        <v>145.8078844446473</v>
+        <v>145.8078992613276</v>
       </c>
       <c r="E510" t="n">
-        <v>148.2216342391088</v>
+        <v>148.2216493010691</v>
       </c>
       <c r="F510" t="n">
         <v>591566</v>
@@ -10652,16 +10652,16 @@
         <v>43972</v>
       </c>
       <c r="B512" t="n">
-        <v>156.1780700683594</v>
+        <v>156.1780548095703</v>
       </c>
       <c r="C512" t="n">
-        <v>158.681214598866</v>
+        <v>158.6811990955166</v>
       </c>
       <c r="D512" t="n">
-        <v>146.1953051796255</v>
+        <v>146.1952908961648</v>
       </c>
       <c r="E512" t="n">
-        <v>152.1253649283446</v>
+        <v>152.1253500655098</v>
       </c>
       <c r="F512" t="n">
         <v>1784500</v>
@@ -10732,16 +10732,16 @@
         <v>43978</v>
       </c>
       <c r="B516" t="n">
-        <v>163.8960571289062</v>
+        <v>163.8960723876953</v>
       </c>
       <c r="C516" t="n">
-        <v>165.9820130095902</v>
+        <v>165.9820284625826</v>
       </c>
       <c r="D516" t="n">
-        <v>160.320137092505</v>
+        <v>160.3201520183744</v>
       </c>
       <c r="E516" t="n">
-        <v>165.5350116375157</v>
+        <v>165.535027048892</v>
       </c>
       <c r="F516" t="n">
         <v>627900</v>
@@ -10752,16 +10752,16 @@
         <v>43979</v>
       </c>
       <c r="B517" t="n">
-        <v>163.9258728027344</v>
+        <v>163.9258575439453</v>
       </c>
       <c r="C517" t="n">
-        <v>168.0679717816257</v>
+        <v>168.0679561372757</v>
       </c>
       <c r="D517" t="n">
-        <v>161.3333342871174</v>
+        <v>161.3333192696508</v>
       </c>
       <c r="E517" t="n">
-        <v>163.4490884655809</v>
+        <v>163.4490732511726</v>
       </c>
       <c r="F517" t="n">
         <v>560100</v>
@@ -10772,16 +10772,16 @@
         <v>43980</v>
       </c>
       <c r="B518" t="n">
-        <v>163.4788970947266</v>
+        <v>163.4788818359375</v>
       </c>
       <c r="C518" t="n">
-        <v>165.0582557337539</v>
+        <v>165.0582403275507</v>
       </c>
       <c r="D518" t="n">
-        <v>157.9958238149825</v>
+        <v>157.9958090679723</v>
       </c>
       <c r="E518" t="n">
-        <v>163.9556814626646</v>
+        <v>163.9556661593735</v>
       </c>
       <c r="F518" t="n">
         <v>1761600</v>
@@ -10812,16 +10812,16 @@
         <v>43984</v>
       </c>
       <c r="B520" t="n">
-        <v>162.5848846435547</v>
+        <v>162.5848999023438</v>
       </c>
       <c r="C520" t="n">
-        <v>164.1642581992473</v>
+        <v>164.1642736062624</v>
       </c>
       <c r="D520" t="n">
-        <v>159.7241637140029</v>
+        <v>159.7241787043098</v>
       </c>
       <c r="E520" t="n">
-        <v>163.8662623308128</v>
+        <v>163.8662777098608</v>
       </c>
       <c r="F520" t="n">
         <v>917300</v>
@@ -10832,16 +10832,16 @@
         <v>43985</v>
       </c>
       <c r="B521" t="n">
-        <v>172.98486328125</v>
+        <v>172.9848480224609</v>
       </c>
       <c r="C521" t="n">
-        <v>173.7298454920335</v>
+        <v>173.7298301675305</v>
       </c>
       <c r="D521" t="n">
-        <v>163.3000945410644</v>
+        <v>163.3000801365573</v>
       </c>
       <c r="E521" t="n">
-        <v>163.8960863723719</v>
+        <v>163.8960719152931</v>
       </c>
       <c r="F521" t="n">
         <v>1327400</v>
@@ -10892,16 +10892,16 @@
         <v>43990</v>
       </c>
       <c r="B524" t="n">
-        <v>181.9842376708984</v>
+        <v>181.9842529296875</v>
       </c>
       <c r="C524" t="n">
-        <v>184.1893861268831</v>
+        <v>184.1894015705667</v>
       </c>
       <c r="D524" t="n">
-        <v>176.3521742327868</v>
+        <v>176.3521890193455</v>
       </c>
       <c r="E524" t="n">
-        <v>178.2891400179336</v>
+        <v>178.2891549669007</v>
       </c>
       <c r="F524" t="n">
         <v>540433</v>
@@ -10952,16 +10952,16 @@
         <v>43994</v>
       </c>
       <c r="B527" t="n">
-        <v>177.9315490722656</v>
+        <v>177.9315338134766</v>
       </c>
       <c r="C527" t="n">
-        <v>180.2260917661188</v>
+        <v>180.2260763105577</v>
       </c>
       <c r="D527" t="n">
-        <v>171.7630899407515</v>
+        <v>171.763075210948</v>
       </c>
       <c r="E527" t="n">
-        <v>174.0874307093273</v>
+        <v>174.0874157801964</v>
       </c>
       <c r="F527" t="n">
         <v>1048900</v>
@@ -10972,16 +10972,16 @@
         <v>43997</v>
       </c>
       <c r="B528" t="n">
-        <v>180.3750915527344</v>
+        <v>180.3751068115234</v>
       </c>
       <c r="C528" t="n">
-        <v>182.8782360569759</v>
+        <v>182.8782515275178</v>
       </c>
       <c r="D528" t="n">
-        <v>173.5212611882256</v>
+        <v>173.5212758672164</v>
       </c>
       <c r="E528" t="n">
-        <v>175.7860059255433</v>
+        <v>175.7860207961198</v>
       </c>
       <c r="F528" t="n">
         <v>826966</v>
@@ -11032,16 +11032,16 @@
         <v>44000</v>
       </c>
       <c r="B531" t="n">
-        <v>179.6896820068359</v>
+        <v>179.689697265625</v>
       </c>
       <c r="C531" t="n">
-        <v>182.9080102346423</v>
+        <v>182.9080257667236</v>
       </c>
       <c r="D531" t="n">
-        <v>178.4381174965946</v>
+        <v>178.438132649104</v>
       </c>
       <c r="E531" t="n">
-        <v>181.7756380139382</v>
+        <v>181.7756534498614</v>
       </c>
       <c r="F531" t="n">
         <v>656233</v>
@@ -11112,16 +11112,16 @@
         <v>44006</v>
       </c>
       <c r="B535" t="n">
-        <v>180.9114837646484</v>
+        <v>180.9114990234375</v>
       </c>
       <c r="C535" t="n">
-        <v>188.569892354976</v>
+        <v>188.5699082597056</v>
       </c>
       <c r="D535" t="n">
-        <v>180.9114837646484</v>
+        <v>180.9114990234375</v>
       </c>
       <c r="E535" t="n">
-        <v>185.1131791628317</v>
+        <v>185.1131947760084</v>
       </c>
       <c r="F535" t="n">
         <v>509333</v>
@@ -11152,16 +11152,16 @@
         <v>44008</v>
       </c>
       <c r="B537" t="n">
-        <v>182.7291870117188</v>
+        <v>182.7292175292969</v>
       </c>
       <c r="C537" t="n">
-        <v>187.1692812003507</v>
+        <v>187.1693124594684</v>
       </c>
       <c r="D537" t="n">
-        <v>182.669590873353</v>
+        <v>182.669621380978</v>
       </c>
       <c r="E537" t="n">
-        <v>182.6993889425358</v>
+        <v>182.6994194551374</v>
       </c>
       <c r="F537" t="n">
         <v>565500</v>
@@ -11172,16 +11172,16 @@
         <v>44011</v>
       </c>
       <c r="B538" t="n">
-        <v>188.0335083007812</v>
+        <v>188.0335235595703</v>
       </c>
       <c r="C538" t="n">
-        <v>188.0335083007812</v>
+        <v>188.0335235595703</v>
       </c>
       <c r="D538" t="n">
-        <v>182.0736507645074</v>
+        <v>182.0736655396581</v>
       </c>
       <c r="E538" t="n">
-        <v>184.1297937330371</v>
+        <v>184.1298086750424</v>
       </c>
       <c r="F538" t="n">
         <v>392600</v>
@@ -11212,16 +11212,16 @@
         <v>44013</v>
       </c>
       <c r="B540" t="n">
-        <v>187.7057037353516</v>
+        <v>187.7057189941406</v>
       </c>
       <c r="C540" t="n">
-        <v>189.9108521119912</v>
+        <v>189.910867550039</v>
       </c>
       <c r="D540" t="n">
-        <v>185.2323575408232</v>
+        <v>185.2323725985514</v>
       </c>
       <c r="E540" t="n">
-        <v>185.7985512500661</v>
+        <v>185.7985663538207</v>
       </c>
       <c r="F540" t="n">
         <v>601100</v>
@@ -11232,16 +11232,16 @@
         <v>44014</v>
       </c>
       <c r="B541" t="n">
-        <v>180.9710693359375</v>
+        <v>180.9710845947266</v>
       </c>
       <c r="C541" t="n">
-        <v>190.5366299956888</v>
+        <v>190.5366460610093</v>
       </c>
       <c r="D541" t="n">
-        <v>179.9876874250449</v>
+        <v>179.987702600919</v>
       </c>
       <c r="E541" t="n">
-        <v>190.1492398774646</v>
+        <v>190.1492559101219</v>
       </c>
       <c r="F541" t="n">
         <v>782133</v>
@@ -11252,16 +11252,16 @@
         <v>44015</v>
       </c>
       <c r="B542" t="n">
-        <v>181.5074462890625</v>
+        <v>181.5074615478516</v>
       </c>
       <c r="C542" t="n">
-        <v>184.4575768075846</v>
+        <v>184.4575923143823</v>
       </c>
       <c r="D542" t="n">
-        <v>178.0805314397118</v>
+        <v>178.0805464104103</v>
       </c>
       <c r="E542" t="n">
-        <v>179.3917072953663</v>
+        <v>179.3917223762915</v>
       </c>
       <c r="F542" t="n">
         <v>277066</v>
@@ -11332,16 +11332,16 @@
         <v>44021</v>
       </c>
       <c r="B546" t="n">
-        <v>178.5871276855469</v>
+        <v>178.5871124267578</v>
       </c>
       <c r="C546" t="n">
-        <v>182.7888382386164</v>
+        <v>182.788822620826</v>
       </c>
       <c r="D546" t="n">
-        <v>178.5871276855469</v>
+        <v>178.5871124267578</v>
       </c>
       <c r="E546" t="n">
-        <v>179.510913502121</v>
+        <v>179.5108981644021</v>
       </c>
       <c r="F546" t="n">
         <v>527966</v>
@@ -11352,16 +11352,16 @@
         <v>44022</v>
       </c>
       <c r="B547" t="n">
-        <v>180.1963043212891</v>
+        <v>180.1962890625</v>
       </c>
       <c r="C547" t="n">
-        <v>181.0604788526272</v>
+        <v>181.060463520661</v>
       </c>
       <c r="D547" t="n">
-        <v>177.9315595685599</v>
+        <v>177.9315445015465</v>
       </c>
       <c r="E547" t="n">
-        <v>178.8255321763785</v>
+        <v>178.8255170336646</v>
       </c>
       <c r="F547" t="n">
         <v>618666</v>
@@ -11372,16 +11372,16 @@
         <v>44025</v>
       </c>
       <c r="B548" t="n">
-        <v>175.6965942382812</v>
+        <v>175.6965789794922</v>
       </c>
       <c r="C548" t="n">
-        <v>181.2690612990238</v>
+        <v>181.2690455562805</v>
       </c>
       <c r="D548" t="n">
-        <v>175.6369829349472</v>
+        <v>175.6369676813352</v>
       </c>
       <c r="E548" t="n">
-        <v>180.1366890428852</v>
+        <v>180.1366733984856</v>
       </c>
       <c r="F548" t="n">
         <v>495033</v>
@@ -11412,16 +11412,16 @@
         <v>44027</v>
       </c>
       <c r="B550" t="n">
-        <v>180.6730804443359</v>
+        <v>180.6730651855469</v>
       </c>
       <c r="C550" t="n">
-        <v>184.7257853841829</v>
+        <v>184.7257697831216</v>
       </c>
       <c r="D550" t="n">
-        <v>178.9745143790679</v>
+        <v>178.9744992637316</v>
       </c>
       <c r="E550" t="n">
-        <v>180.5836862189801</v>
+        <v>180.5836709677409</v>
       </c>
       <c r="F550" t="n">
         <v>693400</v>
@@ -11472,16 +11472,16 @@
         <v>44032</v>
       </c>
       <c r="B553" t="n">
-        <v>196.0196838378906</v>
+        <v>196.0196990966797</v>
       </c>
       <c r="C553" t="n">
-        <v>197.7778458137601</v>
+        <v>197.7778612094101</v>
       </c>
       <c r="D553" t="n">
-        <v>189.1956527452115</v>
+        <v>189.1956674727965</v>
       </c>
       <c r="E553" t="n">
-        <v>190.7154149959243</v>
+        <v>190.7154298418124</v>
       </c>
       <c r="F553" t="n">
         <v>643066</v>
@@ -11572,16 +11572,16 @@
         <v>44039</v>
       </c>
       <c r="B558" t="n">
-        <v>192.56298828125</v>
+        <v>192.5629730224609</v>
       </c>
       <c r="C558" t="n">
-        <v>201.8603661940167</v>
+        <v>201.8603501984987</v>
       </c>
       <c r="D558" t="n">
-        <v>192.1160020190085</v>
+        <v>192.1159867956388</v>
       </c>
       <c r="E558" t="n">
-        <v>196.8838756918523</v>
+        <v>196.8838600906739</v>
       </c>
       <c r="F558" t="n">
         <v>595333</v>
@@ -11592,16 +11592,16 @@
         <v>44040</v>
       </c>
       <c r="B559" t="n">
-        <v>194.2317352294922</v>
+        <v>194.2317504882812</v>
       </c>
       <c r="C559" t="n">
-        <v>195.9005030904659</v>
+        <v>195.9005184803528</v>
       </c>
       <c r="D559" t="n">
-        <v>188.7188795654674</v>
+        <v>188.7188943911681</v>
       </c>
       <c r="E559" t="n">
-        <v>190.7154262273731</v>
+        <v>190.715441209922</v>
       </c>
       <c r="F559" t="n">
         <v>415300</v>
@@ -11652,16 +11652,16 @@
         <v>44043</v>
       </c>
       <c r="B562" t="n">
-        <v>194.1125640869141</v>
+        <v>194.112548828125</v>
       </c>
       <c r="C562" t="n">
-        <v>199.8936333494981</v>
+        <v>199.8936176362711</v>
       </c>
       <c r="D562" t="n">
-        <v>191.8180212901964</v>
+        <v>191.8180062117766</v>
       </c>
       <c r="E562" t="n">
-        <v>197.5692773200199</v>
+        <v>197.5692617895057</v>
       </c>
       <c r="F562" t="n">
         <v>964966</v>
@@ -11672,16 +11672,16 @@
         <v>44046</v>
       </c>
       <c r="B563" t="n">
-        <v>194.3211364746094</v>
+        <v>194.3211517333984</v>
       </c>
       <c r="C563" t="n">
-        <v>196.7646692831627</v>
+        <v>196.7646847338267</v>
       </c>
       <c r="D563" t="n">
-        <v>190.1790226466353</v>
+        <v>190.1790375801708</v>
       </c>
       <c r="E563" t="n">
-        <v>196.049485252196</v>
+        <v>196.0495006467012</v>
       </c>
       <c r="F563" t="n">
         <v>823000</v>
@@ -11692,16 +11692,16 @@
         <v>44047</v>
       </c>
       <c r="B564" t="n">
-        <v>191.1922149658203</v>
+        <v>191.1922302246094</v>
       </c>
       <c r="C564" t="n">
-        <v>194.7979334263718</v>
+        <v>194.7979489729283</v>
       </c>
       <c r="D564" t="n">
-        <v>188.8976723660878</v>
+        <v>188.8976874417525</v>
       </c>
       <c r="E564" t="n">
-        <v>193.4271614185521</v>
+        <v>193.4271768557092</v>
       </c>
       <c r="F564" t="n">
         <v>411633</v>
@@ -11712,16 +11712,16 @@
         <v>44048</v>
       </c>
       <c r="B565" t="n">
-        <v>194.4999237060547</v>
+        <v>194.4999389648438</v>
       </c>
       <c r="C565" t="n">
-        <v>198.075843838864</v>
+        <v>198.075859378189</v>
       </c>
       <c r="D565" t="n">
-        <v>193.0993537243127</v>
+        <v>193.0993688732251</v>
       </c>
       <c r="E565" t="n">
-        <v>193.3675515234483</v>
+        <v>193.3675666934012</v>
       </c>
       <c r="F565" t="n">
         <v>503800</v>
@@ -11752,16 +11752,16 @@
         <v>44050</v>
       </c>
       <c r="B567" t="n">
-        <v>195.2449035644531</v>
+        <v>195.2449188232422</v>
       </c>
       <c r="C567" t="n">
-        <v>198.999612082485</v>
+        <v>198.9996276347122</v>
       </c>
       <c r="D567" t="n">
-        <v>193.6953432435764</v>
+        <v>193.6953583812642</v>
       </c>
       <c r="E567" t="n">
-        <v>196.9732674682691</v>
+        <v>196.9732828621334</v>
       </c>
       <c r="F567" t="n">
         <v>600933</v>
@@ -11792,16 +11792,16 @@
         <v>44054</v>
       </c>
       <c r="B569" t="n">
-        <v>186.930908203125</v>
+        <v>186.9309234619141</v>
       </c>
       <c r="C569" t="n">
-        <v>193.5463527912713</v>
+        <v>193.5463685900656</v>
       </c>
       <c r="D569" t="n">
-        <v>186.4243106823006</v>
+        <v>186.4243258997372</v>
       </c>
       <c r="E569" t="n">
-        <v>193.0099571994219</v>
+        <v>193.0099729544314</v>
       </c>
       <c r="F569" t="n">
         <v>865000</v>
@@ -11812,16 +11812,16 @@
         <v>44055</v>
       </c>
       <c r="B570" t="n">
-        <v>182.6994323730469</v>
+        <v>182.6994171142578</v>
       </c>
       <c r="C570" t="n">
-        <v>189.2552819722826</v>
+        <v>189.2552661659586</v>
       </c>
       <c r="D570" t="n">
-        <v>179.2427191158309</v>
+        <v>179.2427041457414</v>
       </c>
       <c r="E570" t="n">
-        <v>186.7521374689941</v>
+        <v>186.7521218717291</v>
       </c>
       <c r="F570" t="n">
         <v>1065533</v>
@@ -11852,16 +11852,16 @@
         <v>44057</v>
       </c>
       <c r="B572" t="n">
-        <v>191.0730285644531</v>
+        <v>191.0730438232422</v>
       </c>
       <c r="C572" t="n">
-        <v>193.0993734084735</v>
+        <v>193.0993888290833</v>
       </c>
       <c r="D572" t="n">
-        <v>187.0799198685499</v>
+        <v>187.0799348084556</v>
       </c>
       <c r="E572" t="n">
-        <v>188.7784858939576</v>
+        <v>188.7785009695081</v>
       </c>
       <c r="F572" t="n">
         <v>670600</v>
@@ -11872,16 +11872,16 @@
         <v>44060</v>
       </c>
       <c r="B573" t="n">
-        <v>186.0965423583984</v>
+        <v>186.0965576171875</v>
       </c>
       <c r="C573" t="n">
-        <v>193.0397661179825</v>
+        <v>193.0397819460739</v>
       </c>
       <c r="D573" t="n">
-        <v>183.0272044600494</v>
+        <v>183.0272194671714</v>
       </c>
       <c r="E573" t="n">
-        <v>191.877595812602</v>
+        <v>191.8776115454024</v>
       </c>
       <c r="F573" t="n">
         <v>389400</v>
@@ -11932,16 +11932,16 @@
         <v>44063</v>
       </c>
       <c r="B576" t="n">
-        <v>185.1429748535156</v>
+        <v>185.1429595947266</v>
       </c>
       <c r="C576" t="n">
-        <v>189.374468272894</v>
+        <v>189.3744526653612</v>
       </c>
       <c r="D576" t="n">
-        <v>180.0174937043858</v>
+        <v>180.0174788680197</v>
       </c>
       <c r="E576" t="n">
-        <v>180.5240912982554</v>
+        <v>180.5240764201374</v>
       </c>
       <c r="F576" t="n">
         <v>586600</v>
@@ -11972,16 +11972,16 @@
         <v>44067</v>
       </c>
       <c r="B578" t="n">
-        <v>185.2323608398438</v>
+        <v>185.2323455810547</v>
       </c>
       <c r="C578" t="n">
-        <v>187.8546974484032</v>
+        <v>187.8546819735952</v>
       </c>
       <c r="D578" t="n">
-        <v>182.8186259059577</v>
+        <v>182.8186108460036</v>
       </c>
       <c r="E578" t="n">
-        <v>186.8415326191354</v>
+        <v>186.8415172277884</v>
       </c>
       <c r="F578" t="n">
         <v>597533</v>
@@ -12132,16 +12132,16 @@
         <v>44077</v>
       </c>
       <c r="B586" t="n">
-        <v>199.3572235107422</v>
+        <v>199.3572387695312</v>
       </c>
       <c r="C586" t="n">
-        <v>204.6018967184463</v>
+        <v>204.6019123786623</v>
       </c>
       <c r="D586" t="n">
-        <v>196.5858965371773</v>
+        <v>196.5859115838492</v>
       </c>
       <c r="E586" t="n">
-        <v>202.0391562624793</v>
+        <v>202.0391717265434</v>
       </c>
       <c r="F586" t="n">
         <v>527733</v>
@@ -12172,16 +12172,16 @@
         <v>44082</v>
       </c>
       <c r="B588" t="n">
-        <v>200.6683959960938</v>
+        <v>200.6684112548828</v>
       </c>
       <c r="C588" t="n">
-        <v>207.7904235251929</v>
+        <v>207.7904393255396</v>
       </c>
       <c r="D588" t="n">
-        <v>198.3142420975526</v>
+        <v>198.3142571773322</v>
       </c>
       <c r="E588" t="n">
-        <v>198.4632476214454</v>
+        <v>198.4632627125554</v>
       </c>
       <c r="F588" t="n">
         <v>1005833</v>
@@ -42532,19 +42532,39 @@
         <v>46310</v>
       </c>
       <c r="B2106" t="n">
-        <v>8.52</v>
+        <v>8.520000457763672</v>
       </c>
       <c r="C2106" t="n">
-        <v>8.98</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="D2106" t="n">
-        <v>8.24</v>
+        <v>8.239999771118164</v>
       </c>
       <c r="E2106" t="n">
-        <v>8.33</v>
+        <v>8.329999923706055</v>
       </c>
       <c r="F2106" t="n">
         <v>10639800</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>7385700</v>
       </c>
     </row>
   </sheetData>

--- a/database/HAPV3.xlsx
+++ b/database/HAPV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2109"/>
+  <dimension ref="A1:F2110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>43217</v>
       </c>
       <c r="B3" t="n">
-        <v>82.00556945800781</v>
+        <v>82.00556182861328</v>
       </c>
       <c r="C3" t="n">
-        <v>83.90926719826945</v>
+        <v>83.90925939176427</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54118428911481</v>
+        <v>80.54117679595947</v>
       </c>
       <c r="E3" t="n">
-        <v>81.97628294634966</v>
+        <v>81.9762753196798</v>
       </c>
       <c r="F3" t="n">
         <v>932166</v>
@@ -492,16 +492,16 @@
         <v>43220</v>
       </c>
       <c r="B4" t="n">
-        <v>80.98047637939453</v>
+        <v>80.98048400878906</v>
       </c>
       <c r="C4" t="n">
-        <v>82.00554871766383</v>
+        <v>82.00555644363325</v>
       </c>
       <c r="D4" t="n">
-        <v>80.68760388863633</v>
+        <v>80.68761149043854</v>
       </c>
       <c r="E4" t="n">
-        <v>81.56622880915717</v>
+        <v>81.56623649373705</v>
       </c>
       <c r="F4" t="n">
         <v>370366</v>
@@ -512,16 +512,16 @@
         <v>43222</v>
       </c>
       <c r="B5" t="n">
-        <v>79.98471069335938</v>
+        <v>79.98470306396484</v>
       </c>
       <c r="C5" t="n">
-        <v>81.85912174551177</v>
+        <v>81.8591139373253</v>
       </c>
       <c r="D5" t="n">
-        <v>79.0767916761844</v>
+        <v>79.07678413339232</v>
       </c>
       <c r="E5" t="n">
-        <v>79.0767916761844</v>
+        <v>79.07678413339232</v>
       </c>
       <c r="F5" t="n">
         <v>428333</v>
@@ -532,16 +532,16 @@
         <v>43223</v>
       </c>
       <c r="B6" t="n">
-        <v>80.51187896728516</v>
+        <v>80.51188659667969</v>
       </c>
       <c r="C6" t="n">
-        <v>81.71267035421486</v>
+        <v>81.71267809739771</v>
       </c>
       <c r="D6" t="n">
-        <v>78.49102820427865</v>
+        <v>78.49103564217513</v>
       </c>
       <c r="E6" t="n">
-        <v>79.39894709480311</v>
+        <v>79.39895461873498</v>
       </c>
       <c r="F6" t="n">
         <v>790600</v>
@@ -572,16 +572,16 @@
         <v>43227</v>
       </c>
       <c r="B8" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C8" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="D8" t="n">
-        <v>77.90527738914264</v>
+        <v>77.90526987277661</v>
       </c>
       <c r="E8" t="n">
-        <v>78.05171737852535</v>
+        <v>78.05170984803067</v>
       </c>
       <c r="F8" t="n">
         <v>375200</v>
@@ -592,16 +592,16 @@
         <v>43228</v>
       </c>
       <c r="B9" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C9" t="n">
-        <v>79.95542234400601</v>
+        <v>79.95541462984029</v>
       </c>
       <c r="D9" t="n">
-        <v>78.49103734667347</v>
+        <v>78.49102977379283</v>
       </c>
       <c r="E9" t="n">
-        <v>79.51610237585788</v>
+        <v>79.51609470407813</v>
       </c>
       <c r="F9" t="n">
         <v>315733</v>
@@ -612,16 +612,16 @@
         <v>43229</v>
       </c>
       <c r="B10" t="n">
-        <v>78.78390502929688</v>
+        <v>78.78391265869141</v>
       </c>
       <c r="C10" t="n">
-        <v>79.34037099611173</v>
+        <v>79.34037867939415</v>
       </c>
       <c r="D10" t="n">
-        <v>77.81741307603882</v>
+        <v>77.81742061183874</v>
       </c>
       <c r="E10" t="n">
-        <v>79.07678499004018</v>
+        <v>79.07679264779708</v>
       </c>
       <c r="F10" t="n">
         <v>333066</v>
@@ -632,16 +632,16 @@
         <v>43230</v>
       </c>
       <c r="B11" t="n">
-        <v>79.66255187988281</v>
+        <v>79.66254425048828</v>
       </c>
       <c r="C11" t="n">
-        <v>80.95121053351885</v>
+        <v>80.95120278070766</v>
       </c>
       <c r="D11" t="n">
-        <v>78.43246624969672</v>
+        <v>78.43245873810922</v>
       </c>
       <c r="E11" t="n">
-        <v>79.36967186613674</v>
+        <v>79.36966426479174</v>
       </c>
       <c r="F11" t="n">
         <v>396433</v>
@@ -672,16 +672,16 @@
         <v>43234</v>
       </c>
       <c r="B13" t="n">
-        <v>80.01400756835938</v>
+        <v>80.01399230957031</v>
       </c>
       <c r="C13" t="n">
-        <v>81.82984583795763</v>
+        <v>81.82983023288553</v>
       </c>
       <c r="D13" t="n">
-        <v>80.01400756835938</v>
+        <v>80.01399230957031</v>
       </c>
       <c r="E13" t="n">
-        <v>81.68340582623227</v>
+        <v>81.6833902490865</v>
       </c>
       <c r="F13" t="n">
         <v>350433</v>
@@ -692,16 +692,16 @@
         <v>43235</v>
       </c>
       <c r="B14" t="n">
-        <v>84.78788757324219</v>
+        <v>84.78789520263672</v>
       </c>
       <c r="C14" t="n">
-        <v>85.22720008131586</v>
+        <v>85.22720775024067</v>
       </c>
       <c r="D14" t="n">
-        <v>82.0055576428658</v>
+        <v>82.00556502190037</v>
       </c>
       <c r="E14" t="n">
-        <v>82.29843016549923</v>
+        <v>82.29843757088707</v>
       </c>
       <c r="F14" t="n">
         <v>900866</v>
@@ -712,16 +712,16 @@
         <v>43236</v>
       </c>
       <c r="B15" t="n">
-        <v>87.30663299560547</v>
+        <v>87.306640625</v>
       </c>
       <c r="C15" t="n">
-        <v>87.30663299560547</v>
+        <v>87.306640625</v>
       </c>
       <c r="D15" t="n">
-        <v>83.61638402969096</v>
+        <v>83.61639133660867</v>
       </c>
       <c r="E15" t="n">
-        <v>84.78788903694259</v>
+        <v>84.78789644623366</v>
       </c>
       <c r="F15" t="n">
         <v>589600</v>
@@ -732,16 +732,16 @@
         <v>43237</v>
       </c>
       <c r="B16" t="n">
-        <v>88.74173736572266</v>
+        <v>88.74172973632812</v>
       </c>
       <c r="C16" t="n">
-        <v>90.7333019689424</v>
+        <v>90.73329416832706</v>
       </c>
       <c r="D16" t="n">
-        <v>87.86310482779517</v>
+        <v>87.86309727393932</v>
       </c>
       <c r="E16" t="n">
-        <v>87.86310482779517</v>
+        <v>87.86309727393932</v>
       </c>
       <c r="F16" t="n">
         <v>520533</v>
@@ -752,16 +752,16 @@
         <v>43238</v>
       </c>
       <c r="B17" t="n">
-        <v>86.69158935546875</v>
+        <v>86.69158172607422</v>
       </c>
       <c r="C17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74172654739176</v>
       </c>
       <c r="D17" t="n">
-        <v>85.60795128505117</v>
+        <v>85.60794375102347</v>
       </c>
       <c r="E17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74172654739176</v>
       </c>
       <c r="F17" t="n">
         <v>980066</v>
@@ -832,16 +832,16 @@
         <v>43244</v>
       </c>
       <c r="B21" t="n">
-        <v>89.32747650146484</v>
+        <v>89.32749176025391</v>
       </c>
       <c r="C21" t="n">
-        <v>93.77920409449239</v>
+        <v>93.77922011371906</v>
       </c>
       <c r="D21" t="n">
-        <v>89.09317700926512</v>
+        <v>89.0931922280315</v>
       </c>
       <c r="E21" t="n">
-        <v>93.13487862888151</v>
+        <v>93.13489453804544</v>
       </c>
       <c r="F21" t="n">
         <v>822100</v>
@@ -852,16 +852,16 @@
         <v>43245</v>
       </c>
       <c r="B22" t="n">
-        <v>90.76258850097656</v>
+        <v>90.76258087158203</v>
       </c>
       <c r="C22" t="n">
-        <v>90.87973454056369</v>
+        <v>90.879726901322</v>
       </c>
       <c r="D22" t="n">
-        <v>87.95096437892261</v>
+        <v>87.95095698586984</v>
       </c>
       <c r="E22" t="n">
-        <v>88.77102389727091</v>
+        <v>88.77101643528491</v>
       </c>
       <c r="F22" t="n">
         <v>562433</v>
@@ -892,16 +892,16 @@
         <v>43249</v>
       </c>
       <c r="B24" t="n">
-        <v>87.16019439697266</v>
+        <v>87.16020202636719</v>
       </c>
       <c r="C24" t="n">
-        <v>88.88816542744976</v>
+        <v>88.88817320809881</v>
       </c>
       <c r="D24" t="n">
-        <v>84.49501040785843</v>
+        <v>84.49501780396137</v>
       </c>
       <c r="E24" t="n">
-        <v>87.27734787886412</v>
+        <v>87.27735551851345</v>
       </c>
       <c r="F24" t="n">
         <v>175300</v>
@@ -912,16 +912,16 @@
         <v>43250</v>
       </c>
       <c r="B25" t="n">
-        <v>87.86310577392578</v>
+        <v>87.86309814453125</v>
       </c>
       <c r="C25" t="n">
-        <v>90.05968341827392</v>
+        <v>90.05967559814454</v>
       </c>
       <c r="D25" t="n">
-        <v>85.49080162009987</v>
+        <v>85.49079419669903</v>
       </c>
       <c r="E25" t="n">
-        <v>88.15597832422354</v>
+        <v>88.15597066939809</v>
       </c>
       <c r="F25" t="n">
         <v>493866</v>
@@ -932,16 +932,16 @@
         <v>43252</v>
       </c>
       <c r="B26" t="n">
-        <v>87.54093933105469</v>
+        <v>87.54093170166016</v>
       </c>
       <c r="C26" t="n">
-        <v>90.76258952448887</v>
+        <v>90.76258161432011</v>
       </c>
       <c r="D26" t="n">
-        <v>84.90504913515237</v>
+        <v>84.90504173548175</v>
       </c>
       <c r="E26" t="n">
-        <v>89.70823046682885</v>
+        <v>89.70822264854989</v>
       </c>
       <c r="F26" t="n">
         <v>391033</v>
@@ -952,16 +952,16 @@
         <v>43255</v>
       </c>
       <c r="B27" t="n">
-        <v>88.74173736572266</v>
+        <v>88.74172973632812</v>
       </c>
       <c r="C27" t="n">
-        <v>90.2061224461859</v>
+        <v>90.20611469089378</v>
       </c>
       <c r="D27" t="n">
-        <v>86.72088625261327</v>
+        <v>86.72087879695741</v>
       </c>
       <c r="E27" t="n">
-        <v>88.44885737033093</v>
+        <v>88.44884976611618</v>
       </c>
       <c r="F27" t="n">
         <v>304000</v>
@@ -972,16 +972,16 @@
         <v>43256</v>
       </c>
       <c r="B28" t="n">
-        <v>85.72508239746094</v>
+        <v>85.72510528564453</v>
       </c>
       <c r="C28" t="n">
-        <v>88.1559590399379</v>
+        <v>88.15598257715384</v>
       </c>
       <c r="D28" t="n">
-        <v>84.34856458120753</v>
+        <v>84.34858710186751</v>
       </c>
       <c r="E28" t="n">
-        <v>88.1559590399379</v>
+        <v>88.15598257715384</v>
       </c>
       <c r="F28" t="n">
         <v>239700</v>
@@ -992,16 +992,16 @@
         <v>43257</v>
       </c>
       <c r="B29" t="n">
-        <v>83.411376953125</v>
+        <v>83.41138458251953</v>
       </c>
       <c r="C29" t="n">
-        <v>85.46151458562363</v>
+        <v>85.46152240253825</v>
       </c>
       <c r="D29" t="n">
-        <v>81.71268488917815</v>
+        <v>81.7126923631983</v>
       </c>
       <c r="E29" t="n">
-        <v>84.99290808047505</v>
+        <v>84.99291585452761</v>
       </c>
       <c r="F29" t="n">
         <v>443766</v>
@@ -1032,16 +1032,16 @@
         <v>43259</v>
       </c>
       <c r="B31" t="n">
-        <v>80.98047637939453</v>
+        <v>80.98048400878906</v>
       </c>
       <c r="C31" t="n">
-        <v>83.1477670729379</v>
+        <v>83.14777490651888</v>
       </c>
       <c r="D31" t="n">
-        <v>79.0767791206044</v>
+        <v>79.07678657064635</v>
       </c>
       <c r="E31" t="n">
-        <v>79.75039851136687</v>
+        <v>79.75040602487236</v>
       </c>
       <c r="F31" t="n">
         <v>443000</v>
@@ -1052,16 +1052,16 @@
         <v>43262</v>
       </c>
       <c r="B32" t="n">
-        <v>81.41980743408203</v>
+        <v>81.4197998046875</v>
       </c>
       <c r="C32" t="n">
-        <v>82.73775244353311</v>
+        <v>82.73774469064132</v>
       </c>
       <c r="D32" t="n">
-        <v>78.93034995648213</v>
+        <v>78.93034256036073</v>
       </c>
       <c r="E32" t="n">
-        <v>81.47838045060293</v>
+        <v>81.47837281571985</v>
       </c>
       <c r="F32" t="n">
         <v>202266</v>
@@ -1092,16 +1092,16 @@
         <v>43264</v>
       </c>
       <c r="B34" t="n">
-        <v>78.31531524658203</v>
+        <v>78.3153076171875</v>
       </c>
       <c r="C34" t="n">
-        <v>82.32773096043591</v>
+        <v>82.32772294015612</v>
       </c>
       <c r="D34" t="n">
-        <v>77.70026874628836</v>
+        <v>77.70026117681101</v>
       </c>
       <c r="E34" t="n">
-        <v>82.32773096043591</v>
+        <v>82.32772294015612</v>
       </c>
       <c r="F34" t="n">
         <v>786033</v>
@@ -1132,16 +1132,16 @@
         <v>43266</v>
       </c>
       <c r="B36" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C36" t="n">
-        <v>79.22322984533973</v>
+        <v>79.22322220181655</v>
       </c>
       <c r="D36" t="n">
-        <v>75.12294738386028</v>
+        <v>75.12294013593576</v>
       </c>
       <c r="E36" t="n">
-        <v>79.13536287241121</v>
+        <v>79.1353552373655</v>
       </c>
       <c r="F36" t="n">
         <v>389566</v>
@@ -1152,16 +1152,16 @@
         <v>43269</v>
       </c>
       <c r="B37" t="n">
-        <v>77.26094055175781</v>
+        <v>77.26094818115234</v>
       </c>
       <c r="C37" t="n">
-        <v>79.07677827845613</v>
+        <v>79.07678608716174</v>
       </c>
       <c r="D37" t="n">
-        <v>76.73376113611189</v>
+        <v>76.7337687134483</v>
       </c>
       <c r="E37" t="n">
-        <v>79.07677827845613</v>
+        <v>79.07678608716174</v>
       </c>
       <c r="F37" t="n">
         <v>465333</v>
@@ -1172,16 +1172,16 @@
         <v>43270</v>
       </c>
       <c r="B38" t="n">
-        <v>81.56623077392578</v>
+        <v>81.56623840332031</v>
       </c>
       <c r="C38" t="n">
-        <v>83.14776907580264</v>
+        <v>83.14777685312824</v>
       </c>
       <c r="D38" t="n">
-        <v>77.02664374773103</v>
+        <v>77.02665095250988</v>
       </c>
       <c r="E38" t="n">
-        <v>77.8466956795029</v>
+        <v>77.84670296098628</v>
       </c>
       <c r="F38" t="n">
         <v>159600</v>
@@ -1192,16 +1192,16 @@
         <v>43271</v>
       </c>
       <c r="B39" t="n">
-        <v>84.34858703613281</v>
+        <v>84.34857177734375</v>
       </c>
       <c r="C39" t="n">
-        <v>85.52009218942361</v>
+        <v>85.52007671870746</v>
       </c>
       <c r="D39" t="n">
-        <v>81.71268926885634</v>
+        <v>81.71267448690524</v>
       </c>
       <c r="E39" t="n">
-        <v>82.03485579289816</v>
+        <v>82.03484095266663</v>
       </c>
       <c r="F39" t="n">
         <v>141600</v>
@@ -1212,16 +1212,16 @@
         <v>43272</v>
       </c>
       <c r="B40" t="n">
-        <v>82.62059783935547</v>
+        <v>82.62059020996094</v>
       </c>
       <c r="C40" t="n">
-        <v>85.46150827396475</v>
+        <v>85.46150038223338</v>
       </c>
       <c r="D40" t="n">
-        <v>80.10185388772712</v>
+        <v>80.10184649091977</v>
       </c>
       <c r="E40" t="n">
-        <v>83.46994380860144</v>
+        <v>83.46993610077617</v>
       </c>
       <c r="F40" t="n">
         <v>246900</v>
@@ -1232,16 +1232,16 @@
         <v>43273</v>
       </c>
       <c r="B41" t="n">
-        <v>84.934326171875</v>
+        <v>84.93433380126953</v>
       </c>
       <c r="C41" t="n">
-        <v>85.52007865582475</v>
+        <v>85.52008633783566</v>
       </c>
       <c r="D41" t="n">
-        <v>81.21479082295949</v>
+        <v>81.21479811823937</v>
       </c>
       <c r="E41" t="n">
-        <v>82.03484281083975</v>
+        <v>82.03485017978244</v>
       </c>
       <c r="F41" t="n">
         <v>298800</v>
@@ -1292,16 +1292,16 @@
         <v>43278</v>
       </c>
       <c r="B44" t="n">
-        <v>87.86310577392578</v>
+        <v>87.86309814453125</v>
       </c>
       <c r="C44" t="n">
-        <v>88.59529832204183</v>
+        <v>88.59529062906901</v>
       </c>
       <c r="D44" t="n">
-        <v>85.25650209021211</v>
+        <v>85.25649468715613</v>
       </c>
       <c r="E44" t="n">
-        <v>86.98447322653696</v>
+        <v>86.98446567343652</v>
       </c>
       <c r="F44" t="n">
         <v>117966</v>
@@ -1312,16 +1312,16 @@
         <v>43279</v>
       </c>
       <c r="B45" t="n">
-        <v>88.68314361572266</v>
+        <v>88.68315124511719</v>
       </c>
       <c r="C45" t="n">
-        <v>88.68314361572266</v>
+        <v>88.68315124511719</v>
       </c>
       <c r="D45" t="n">
-        <v>85.37363442539693</v>
+        <v>85.373641770075</v>
       </c>
       <c r="E45" t="n">
-        <v>87.86309166864037</v>
+        <v>87.86309922748598</v>
       </c>
       <c r="F45" t="n">
         <v>922066</v>
@@ -1332,16 +1332,16 @@
         <v>43280</v>
       </c>
       <c r="B46" t="n">
-        <v>87.54093933105469</v>
+        <v>87.54093170166016</v>
       </c>
       <c r="C46" t="n">
-        <v>89.41535046806291</v>
+        <v>89.41534267530913</v>
       </c>
       <c r="D46" t="n">
-        <v>85.37364819528054</v>
+        <v>85.37364075477042</v>
       </c>
       <c r="E46" t="n">
-        <v>87.45307980037357</v>
+        <v>87.45307217863621</v>
       </c>
       <c r="F46" t="n">
         <v>492266</v>
@@ -1372,16 +1372,16 @@
         <v>43284</v>
       </c>
       <c r="B48" t="n">
-        <v>85.52008056640625</v>
+        <v>85.52007293701172</v>
       </c>
       <c r="C48" t="n">
-        <v>87.21876504228447</v>
+        <v>87.21875726134735</v>
       </c>
       <c r="D48" t="n">
-        <v>83.93854212098695</v>
+        <v>83.9385346326842</v>
       </c>
       <c r="E48" t="n">
-        <v>86.72087951633988</v>
+        <v>86.72087177981997</v>
       </c>
       <c r="F48" t="n">
         <v>142500</v>
@@ -1412,16 +1412,16 @@
         <v>43286</v>
       </c>
       <c r="B50" t="n">
-        <v>85.52008056640625</v>
+        <v>85.52007293701172</v>
       </c>
       <c r="C50" t="n">
-        <v>86.31084606499235</v>
+        <v>86.31083836505225</v>
       </c>
       <c r="D50" t="n">
-        <v>84.28999510885791</v>
+        <v>84.28998758920142</v>
       </c>
       <c r="E50" t="n">
-        <v>85.78367403143302</v>
+        <v>85.78366637852285</v>
       </c>
       <c r="F50" t="n">
         <v>391100</v>
@@ -1432,16 +1432,16 @@
         <v>43287</v>
       </c>
       <c r="B51" t="n">
-        <v>83.61638641357422</v>
+        <v>83.61637115478516</v>
       </c>
       <c r="C51" t="n">
-        <v>85.57865698425219</v>
+        <v>85.57864136737695</v>
       </c>
       <c r="D51" t="n">
-        <v>83.61638641357422</v>
+        <v>83.61637115478516</v>
       </c>
       <c r="E51" t="n">
-        <v>85.52008396669386</v>
+        <v>85.52006836050735</v>
       </c>
       <c r="F51" t="n">
         <v>769100</v>
@@ -1492,16 +1492,16 @@
         <v>43293</v>
       </c>
       <c r="B54" t="n">
-        <v>87.07233428955078</v>
+        <v>87.07232666015625</v>
       </c>
       <c r="C54" t="n">
-        <v>87.13090730598122</v>
+        <v>87.13089967145444</v>
       </c>
       <c r="D54" t="n">
-        <v>82.35701281247128</v>
+        <v>82.35700559623953</v>
       </c>
       <c r="E54" t="n">
-        <v>83.90925733385612</v>
+        <v>83.90924998161464</v>
       </c>
       <c r="F54" t="n">
         <v>235333</v>
@@ -1512,16 +1512,16 @@
         <v>43294</v>
       </c>
       <c r="B55" t="n">
-        <v>84.40715789794922</v>
+        <v>84.40713500976562</v>
       </c>
       <c r="C55" t="n">
-        <v>87.57022768943764</v>
+        <v>87.57020394354336</v>
       </c>
       <c r="D55" t="n">
-        <v>83.96784533877647</v>
+        <v>83.96782256971863</v>
       </c>
       <c r="E55" t="n">
-        <v>87.10162861941977</v>
+        <v>87.10160500059268</v>
       </c>
       <c r="F55" t="n">
         <v>222900</v>
@@ -1552,16 +1552,16 @@
         <v>43298</v>
       </c>
       <c r="B57" t="n">
-        <v>83.08920288085938</v>
+        <v>83.08921813964844</v>
       </c>
       <c r="C57" t="n">
-        <v>84.58287434213068</v>
+        <v>84.58288987522275</v>
       </c>
       <c r="D57" t="n">
-        <v>82.35701040390309</v>
+        <v>82.35702552822978</v>
       </c>
       <c r="E57" t="n">
-        <v>84.11426787964996</v>
+        <v>84.11428332668551</v>
       </c>
       <c r="F57" t="n">
         <v>152666</v>
@@ -1572,16 +1572,16 @@
         <v>43299</v>
       </c>
       <c r="B58" t="n">
-        <v>85.90082550048828</v>
+        <v>85.90081787109375</v>
       </c>
       <c r="C58" t="n">
-        <v>85.90082550048828</v>
+        <v>85.90081787109375</v>
       </c>
       <c r="D58" t="n">
-        <v>82.73775585763492</v>
+        <v>82.73774850917258</v>
       </c>
       <c r="E58" t="n">
-        <v>82.91348236269609</v>
+        <v>82.91347499862636</v>
       </c>
       <c r="F58" t="n">
         <v>444433</v>
@@ -1592,16 +1592,16 @@
         <v>43300</v>
       </c>
       <c r="B59" t="n">
-        <v>85.19791412353516</v>
+        <v>85.19790649414062</v>
       </c>
       <c r="C59" t="n">
-        <v>86.5451530603807</v>
+        <v>86.54514531034216</v>
       </c>
       <c r="D59" t="n">
-        <v>83.61638312566897</v>
+        <v>83.6163756378991</v>
       </c>
       <c r="E59" t="n">
-        <v>85.52008060393275</v>
+        <v>85.52007294568851</v>
       </c>
       <c r="F59" t="n">
         <v>169366</v>
@@ -1612,16 +1612,16 @@
         <v>43301</v>
       </c>
       <c r="B60" t="n">
-        <v>87.86310577392578</v>
+        <v>87.86309814453125</v>
       </c>
       <c r="C60" t="n">
-        <v>88.77102483151958</v>
+        <v>88.77101712328796</v>
       </c>
       <c r="D60" t="n">
-        <v>85.54937464050987</v>
+        <v>85.54936721202297</v>
       </c>
       <c r="E60" t="n">
-        <v>86.39872067769367</v>
+        <v>86.39871317545573</v>
       </c>
       <c r="F60" t="n">
         <v>356866</v>
@@ -1672,16 +1672,16 @@
         <v>43306</v>
       </c>
       <c r="B63" t="n">
-        <v>83.99712371826172</v>
+        <v>83.99713134765625</v>
       </c>
       <c r="C63" t="n">
-        <v>89.91323668020036</v>
+        <v>89.9132448469509</v>
       </c>
       <c r="D63" t="n">
-        <v>83.99712371826172</v>
+        <v>83.99713134765625</v>
       </c>
       <c r="E63" t="n">
-        <v>88.77101817832556</v>
+        <v>88.77102624132928</v>
       </c>
       <c r="F63" t="n">
         <v>653300</v>
@@ -1692,16 +1692,16 @@
         <v>43307</v>
       </c>
       <c r="B64" t="n">
-        <v>80.57046508789062</v>
+        <v>80.57045745849609</v>
       </c>
       <c r="C64" t="n">
-        <v>84.84646679649717</v>
+        <v>84.84645876219862</v>
       </c>
       <c r="D64" t="n">
-        <v>79.9554260419345</v>
+        <v>79.95541847077936</v>
       </c>
       <c r="E64" t="n">
-        <v>84.14356822179629</v>
+        <v>84.14356025405675</v>
       </c>
       <c r="F64" t="n">
         <v>454233</v>
@@ -1712,16 +1712,16 @@
         <v>43308</v>
       </c>
       <c r="B65" t="n">
-        <v>82.62059783935547</v>
+        <v>82.62059020996094</v>
       </c>
       <c r="C65" t="n">
-        <v>82.62059783935547</v>
+        <v>82.62059020996094</v>
       </c>
       <c r="D65" t="n">
-        <v>80.04328087200228</v>
+        <v>80.04327348060372</v>
       </c>
       <c r="E65" t="n">
-        <v>81.24407983209161</v>
+        <v>81.24407232980825</v>
       </c>
       <c r="F65" t="n">
         <v>199833</v>
@@ -1732,16 +1732,16 @@
         <v>43311</v>
       </c>
       <c r="B66" t="n">
-        <v>80.39472961425781</v>
+        <v>80.39473724365234</v>
       </c>
       <c r="C66" t="n">
-        <v>82.59130696682358</v>
+        <v>82.59131480467153</v>
       </c>
       <c r="D66" t="n">
-        <v>79.80897714322296</v>
+        <v>79.80898471703006</v>
       </c>
       <c r="E66" t="n">
-        <v>82.53273395419413</v>
+        <v>82.53274178648354</v>
       </c>
       <c r="F66" t="n">
         <v>306800</v>
@@ -1752,16 +1752,16 @@
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>82.47415924072266</v>
+        <v>82.47415161132812</v>
       </c>
       <c r="C67" t="n">
-        <v>82.56202621403682</v>
+        <v>82.56201857651402</v>
       </c>
       <c r="D67" t="n">
-        <v>79.3696627348224</v>
+        <v>79.36965539261392</v>
       </c>
       <c r="E67" t="n">
-        <v>81.24408120030263</v>
+        <v>81.24407368469829</v>
       </c>
       <c r="F67" t="n">
         <v>430700</v>
@@ -1772,16 +1772,16 @@
         <v>43313</v>
       </c>
       <c r="B68" t="n">
-        <v>84.02641296386719</v>
+        <v>84.02640533447266</v>
       </c>
       <c r="C68" t="n">
-        <v>84.02641296386719</v>
+        <v>84.02640533447266</v>
       </c>
       <c r="D68" t="n">
-        <v>81.41980939058915</v>
+        <v>81.41980199786791</v>
       </c>
       <c r="E68" t="n">
-        <v>81.44909589955336</v>
+        <v>81.44908850417296</v>
       </c>
       <c r="F68" t="n">
         <v>89600</v>
@@ -1812,16 +1812,16 @@
         <v>43315</v>
       </c>
       <c r="B70" t="n">
-        <v>83.90925598144531</v>
+        <v>83.90926361083984</v>
       </c>
       <c r="C70" t="n">
-        <v>84.75860194723369</v>
+        <v>84.75860965385445</v>
       </c>
       <c r="D70" t="n">
-        <v>83.52851648428948</v>
+        <v>83.52852407906553</v>
       </c>
       <c r="E70" t="n">
-        <v>84.75860194723369</v>
+        <v>84.75860965385445</v>
       </c>
       <c r="F70" t="n">
         <v>171233</v>
@@ -1832,16 +1832,16 @@
         <v>43318</v>
       </c>
       <c r="B71" t="n">
-        <v>81.33193969726562</v>
+        <v>81.33193206787109</v>
       </c>
       <c r="C71" t="n">
-        <v>83.55780368312388</v>
+        <v>83.55779584493075</v>
       </c>
       <c r="D71" t="n">
-        <v>81.1269266931205</v>
+        <v>81.12691908295734</v>
       </c>
       <c r="E71" t="n">
-        <v>83.38207718696417</v>
+        <v>83.38206936525518</v>
       </c>
       <c r="F71" t="n">
         <v>242633</v>
@@ -1872,16 +1872,16 @@
         <v>43320</v>
       </c>
       <c r="B73" t="n">
-        <v>78.78390502929688</v>
+        <v>78.78391265869141</v>
       </c>
       <c r="C73" t="n">
-        <v>80.24828993651984</v>
+        <v>80.24829770772469</v>
       </c>
       <c r="D73" t="n">
-        <v>77.11450712885231</v>
+        <v>77.11451459658318</v>
       </c>
       <c r="E73" t="n">
-        <v>79.7796909372267</v>
+        <v>79.77969866305264</v>
       </c>
       <c r="F73" t="n">
         <v>270133</v>
@@ -1892,16 +1892,16 @@
         <v>43321</v>
       </c>
       <c r="B74" t="n">
-        <v>78.95963287353516</v>
+        <v>78.95964050292969</v>
       </c>
       <c r="C74" t="n">
-        <v>79.1353593633528</v>
+        <v>79.13536700972674</v>
       </c>
       <c r="D74" t="n">
-        <v>76.85092244397033</v>
+        <v>76.85092986961286</v>
       </c>
       <c r="E74" t="n">
-        <v>78.19815390040766</v>
+        <v>78.19816145622507</v>
       </c>
       <c r="F74" t="n">
         <v>546266</v>
@@ -1932,16 +1932,16 @@
         <v>43325</v>
       </c>
       <c r="B76" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C76" t="n">
-        <v>80.10185488514145</v>
+        <v>80.1018471568478</v>
       </c>
       <c r="D76" t="n">
-        <v>77.7588448480072</v>
+        <v>77.75883734576911</v>
       </c>
       <c r="E76" t="n">
-        <v>78.93034986657432</v>
+        <v>78.93034225130845</v>
       </c>
       <c r="F76" t="n">
         <v>160400</v>
@@ -1952,16 +1952,16 @@
         <v>43326</v>
       </c>
       <c r="B77" t="n">
-        <v>77.46595001220703</v>
+        <v>77.46595764160156</v>
       </c>
       <c r="C77" t="n">
-        <v>78.46173579043192</v>
+        <v>78.46174351789847</v>
       </c>
       <c r="D77" t="n">
-        <v>74.44932107141373</v>
+        <v>74.44932840370932</v>
       </c>
       <c r="E77" t="n">
-        <v>78.46173579043192</v>
+        <v>78.46174351789847</v>
       </c>
       <c r="F77" t="n">
         <v>524933</v>
@@ -1972,16 +1972,16 @@
         <v>43327</v>
       </c>
       <c r="B78" t="n">
-        <v>76.14801788330078</v>
+        <v>76.14804077148438</v>
       </c>
       <c r="C78" t="n">
-        <v>77.67097585752774</v>
+        <v>77.67099920347428</v>
       </c>
       <c r="D78" t="n">
-        <v>76.14801788330078</v>
+        <v>76.14804077148438</v>
       </c>
       <c r="E78" t="n">
-        <v>77.02665034852674</v>
+        <v>77.02667350080522</v>
       </c>
       <c r="F78" t="n">
         <v>702366</v>
@@ -1992,16 +1992,16 @@
         <v>43328</v>
       </c>
       <c r="B79" t="n">
-        <v>73.51211547851562</v>
+        <v>73.51210784912109</v>
       </c>
       <c r="C79" t="n">
-        <v>76.64590563232663</v>
+        <v>76.64589767769425</v>
       </c>
       <c r="D79" t="n">
-        <v>72.69206353234769</v>
+        <v>72.69205598806157</v>
       </c>
       <c r="E79" t="n">
-        <v>76.32373917565498</v>
+        <v>76.32373125445839</v>
       </c>
       <c r="F79" t="n">
         <v>1651000</v>
@@ -2032,16 +2032,16 @@
         <v>43332</v>
       </c>
       <c r="B81" t="n">
-        <v>72.34062194824219</v>
+        <v>72.34061431884766</v>
       </c>
       <c r="C81" t="n">
-        <v>73.01424147300597</v>
+        <v>73.01423377256823</v>
       </c>
       <c r="D81" t="n">
-        <v>71.75486940195739</v>
+        <v>71.75486183433918</v>
       </c>
       <c r="E81" t="n">
-        <v>71.95988242074468</v>
+        <v>71.95987483150479</v>
       </c>
       <c r="F81" t="n">
         <v>425766</v>
@@ -2052,16 +2052,16 @@
         <v>43333</v>
       </c>
       <c r="B82" t="n">
-        <v>71.60842895507812</v>
+        <v>71.60842132568359</v>
       </c>
       <c r="C82" t="n">
-        <v>72.5749210228105</v>
+        <v>72.57491329044277</v>
       </c>
       <c r="D82" t="n">
-        <v>70.31977038201907</v>
+        <v>70.31976288992242</v>
       </c>
       <c r="E82" t="n">
-        <v>71.63771546497189</v>
+        <v>71.63770783245707</v>
       </c>
       <c r="F82" t="n">
         <v>1384333</v>
@@ -2072,16 +2072,16 @@
         <v>43334</v>
       </c>
       <c r="B83" t="n">
-        <v>73.51211547851562</v>
+        <v>73.51210784912109</v>
       </c>
       <c r="C83" t="n">
-        <v>73.68784195958683</v>
+        <v>73.68783431195467</v>
       </c>
       <c r="D83" t="n">
-        <v>70.96409267535293</v>
+        <v>70.96408531040285</v>
       </c>
       <c r="E83" t="n">
-        <v>70.96409267535293</v>
+        <v>70.96408531040285</v>
       </c>
       <c r="F83" t="n">
         <v>518466</v>
@@ -2092,16 +2092,16 @@
         <v>43335</v>
       </c>
       <c r="B84" t="n">
-        <v>73.36570739746094</v>
+        <v>73.36567687988281</v>
       </c>
       <c r="C84" t="n">
-        <v>74.33219964127566</v>
+        <v>74.33216872167044</v>
       </c>
       <c r="D84" t="n">
-        <v>71.90132204999964</v>
+        <v>71.90129214155479</v>
       </c>
       <c r="E84" t="n">
-        <v>72.57493424502249</v>
+        <v>72.57490405637844</v>
       </c>
       <c r="F84" t="n">
         <v>126566</v>
@@ -2112,16 +2112,16 @@
         <v>43336</v>
       </c>
       <c r="B85" t="n">
-        <v>75.29866027832031</v>
+        <v>75.29867553710938</v>
       </c>
       <c r="C85" t="n">
-        <v>75.56225370123892</v>
+        <v>75.56226901344348</v>
       </c>
       <c r="D85" t="n">
-        <v>73.21923663913734</v>
+        <v>73.21925147654457</v>
       </c>
       <c r="E85" t="n">
-        <v>74.09786896845617</v>
+        <v>74.0978839839126</v>
       </c>
       <c r="F85" t="n">
         <v>164200</v>
@@ -2132,16 +2132,16 @@
         <v>43339</v>
       </c>
       <c r="B86" t="n">
-        <v>76.03087615966797</v>
+        <v>76.03086090087891</v>
       </c>
       <c r="C86" t="n">
-        <v>76.44090222408167</v>
+        <v>76.44088688300364</v>
       </c>
       <c r="D86" t="n">
-        <v>73.65857186091985</v>
+        <v>73.6585570782333</v>
       </c>
       <c r="E86" t="n">
-        <v>75.29868356682285</v>
+        <v>75.29866845497898</v>
       </c>
       <c r="F86" t="n">
         <v>318500</v>
@@ -2152,16 +2152,16 @@
         <v>43340</v>
       </c>
       <c r="B87" t="n">
-        <v>75.24008941650391</v>
+        <v>75.24009704589844</v>
       </c>
       <c r="C87" t="n">
-        <v>76.14800827463128</v>
+        <v>76.14801599608937</v>
       </c>
       <c r="D87" t="n">
-        <v>73.89285810532134</v>
+        <v>73.89286559810573</v>
       </c>
       <c r="E87" t="n">
-        <v>75.91370879621824</v>
+        <v>75.91371649391823</v>
       </c>
       <c r="F87" t="n">
         <v>298400</v>
@@ -2172,16 +2172,16 @@
         <v>43341</v>
       </c>
       <c r="B88" t="n">
-        <v>74.4200439453125</v>
+        <v>74.42002868652344</v>
       </c>
       <c r="C88" t="n">
-        <v>76.14802247243639</v>
+        <v>76.14800685934951</v>
       </c>
       <c r="D88" t="n">
-        <v>73.45355189944088</v>
+        <v>73.45353683881748</v>
       </c>
       <c r="E88" t="n">
-        <v>75.6794159799925</v>
+        <v>75.67940046298681</v>
       </c>
       <c r="F88" t="n">
         <v>162200</v>
@@ -2192,16 +2192,16 @@
         <v>43342</v>
       </c>
       <c r="B89" t="n">
-        <v>75.85514068603516</v>
+        <v>75.85512542724609</v>
       </c>
       <c r="C89" t="n">
-        <v>75.85514068603516</v>
+        <v>75.85512542724609</v>
       </c>
       <c r="D89" t="n">
-        <v>73.39497714168559</v>
+        <v>73.39496237777553</v>
       </c>
       <c r="E89" t="n">
-        <v>74.18574266518235</v>
+        <v>74.18572774220431</v>
       </c>
       <c r="F89" t="n">
         <v>206466</v>
@@ -2232,16 +2232,16 @@
         <v>43346</v>
       </c>
       <c r="B91" t="n">
-        <v>74.65434265136719</v>
+        <v>74.65435028076172</v>
       </c>
       <c r="C91" t="n">
-        <v>76.06014707658026</v>
+        <v>76.06015484964274</v>
       </c>
       <c r="D91" t="n">
-        <v>73.9807232206266</v>
+        <v>73.98073078117974</v>
       </c>
       <c r="E91" t="n">
-        <v>75.76727456844061</v>
+        <v>75.76728231157261</v>
       </c>
       <c r="F91" t="n">
         <v>159200</v>
@@ -2252,16 +2252,16 @@
         <v>43347</v>
       </c>
       <c r="B92" t="n">
-        <v>73.04352569580078</v>
+        <v>73.04351806640625</v>
       </c>
       <c r="C92" t="n">
-        <v>74.42004376405343</v>
+        <v>74.42003599088163</v>
       </c>
       <c r="D92" t="n">
-        <v>71.87202063991565</v>
+        <v>71.87201313288479</v>
       </c>
       <c r="E92" t="n">
-        <v>74.39075725489343</v>
+        <v>74.3907494847806</v>
       </c>
       <c r="F92" t="n">
         <v>196200</v>
@@ -2292,16 +2292,16 @@
         <v>43349</v>
       </c>
       <c r="B94" t="n">
-        <v>74.21502685546875</v>
+        <v>74.21501922607422</v>
       </c>
       <c r="C94" t="n">
-        <v>76.52875778485787</v>
+        <v>76.52874991760901</v>
       </c>
       <c r="D94" t="n">
-        <v>71.46198341524806</v>
+        <v>71.46197606886972</v>
       </c>
       <c r="E94" t="n">
-        <v>74.15645384022376</v>
+        <v>74.15644621685061</v>
       </c>
       <c r="F94" t="n">
         <v>139100</v>
@@ -2312,16 +2312,16 @@
         <v>43353</v>
       </c>
       <c r="B95" t="n">
-        <v>75.50367736816406</v>
+        <v>75.50369262695312</v>
       </c>
       <c r="C95" t="n">
-        <v>76.73376269634934</v>
+        <v>76.73377820373044</v>
       </c>
       <c r="D95" t="n">
-        <v>74.42003201089904</v>
+        <v>74.4200470506906</v>
       </c>
       <c r="E95" t="n">
-        <v>75.65011733908432</v>
+        <v>75.65013262746791</v>
       </c>
       <c r="F95" t="n">
         <v>157400</v>
@@ -2332,16 +2332,16 @@
         <v>43354</v>
       </c>
       <c r="B96" t="n">
-        <v>73.45355987548828</v>
+        <v>73.45354461669922</v>
       </c>
       <c r="C96" t="n">
-        <v>75.18153859024693</v>
+        <v>75.18152297249823</v>
       </c>
       <c r="D96" t="n">
-        <v>73.45355987548828</v>
+        <v>73.45354461669922</v>
       </c>
       <c r="E96" t="n">
-        <v>74.44934598696744</v>
+        <v>74.44933052131992</v>
       </c>
       <c r="F96" t="n">
         <v>250666</v>
@@ -2352,16 +2352,16 @@
         <v>43355</v>
       </c>
       <c r="B97" t="n">
-        <v>72.95565032958984</v>
+        <v>72.95565795898438</v>
       </c>
       <c r="C97" t="n">
-        <v>74.65434214798188</v>
+        <v>74.65434995501845</v>
       </c>
       <c r="D97" t="n">
-        <v>71.34483292506654</v>
+        <v>71.34484038600858</v>
       </c>
       <c r="E97" t="n">
-        <v>73.21924377820952</v>
+        <v>73.21925143516954</v>
       </c>
       <c r="F97" t="n">
         <v>133333</v>
@@ -2372,16 +2372,16 @@
         <v>43356</v>
       </c>
       <c r="B98" t="n">
-        <v>71.60842895507812</v>
+        <v>71.60842132568359</v>
       </c>
       <c r="C98" t="n">
-        <v>73.86357959586955</v>
+        <v>73.86357172620396</v>
       </c>
       <c r="D98" t="n">
-        <v>70.43692386984178</v>
+        <v>70.4369163652632</v>
       </c>
       <c r="E98" t="n">
-        <v>73.77572006618828</v>
+        <v>73.77571220588352</v>
       </c>
       <c r="F98" t="n">
         <v>250366</v>
@@ -2392,16 +2392,16 @@
         <v>43357</v>
       </c>
       <c r="B99" t="n">
-        <v>69.79258728027344</v>
+        <v>69.79257965087891</v>
       </c>
       <c r="C99" t="n">
-        <v>72.28204476905265</v>
+        <v>72.28203686752244</v>
       </c>
       <c r="D99" t="n">
-        <v>69.70472775509755</v>
+        <v>69.7047201353074</v>
       </c>
       <c r="E99" t="n">
-        <v>70.96409975368313</v>
+        <v>70.96409199622441</v>
       </c>
       <c r="F99" t="n">
         <v>269466</v>
@@ -2412,16 +2412,16 @@
         <v>43360</v>
       </c>
       <c r="B100" t="n">
-        <v>73.48283386230469</v>
+        <v>73.48282623291016</v>
       </c>
       <c r="C100" t="n">
-        <v>74.0685938036806</v>
+        <v>74.06858611346924</v>
       </c>
       <c r="D100" t="n">
-        <v>69.79258496252115</v>
+        <v>69.79257771626868</v>
       </c>
       <c r="E100" t="n">
-        <v>70.02688447012328</v>
+        <v>70.02687719954454</v>
       </c>
       <c r="F100" t="n">
         <v>114333</v>
@@ -2432,16 +2432,16 @@
         <v>43361</v>
       </c>
       <c r="B101" t="n">
-        <v>74.50789642333984</v>
+        <v>74.50791168212891</v>
       </c>
       <c r="C101" t="n">
-        <v>75.35724226701849</v>
+        <v>75.35725769974871</v>
       </c>
       <c r="D101" t="n">
-        <v>73.62926407612848</v>
+        <v>73.6292791549787</v>
       </c>
       <c r="E101" t="n">
-        <v>74.56646943040525</v>
+        <v>74.56648470118972</v>
       </c>
       <c r="F101" t="n">
         <v>194766</v>
@@ -2472,16 +2472,16 @@
         <v>43363</v>
       </c>
       <c r="B103" t="n">
-        <v>68.24033355712891</v>
+        <v>68.24034881591797</v>
       </c>
       <c r="C103" t="n">
-        <v>69.58756489941005</v>
+        <v>69.58758045944499</v>
       </c>
       <c r="D103" t="n">
-        <v>65.63372293766099</v>
+        <v>65.63373761360235</v>
       </c>
       <c r="E103" t="n">
-        <v>69.4118384244824</v>
+        <v>69.41185394522425</v>
       </c>
       <c r="F103" t="n">
         <v>1256966</v>
@@ -2512,16 +2512,16 @@
         <v>43367</v>
       </c>
       <c r="B105" t="n">
-        <v>65.45801544189453</v>
+        <v>65.4580078125</v>
       </c>
       <c r="C105" t="n">
-        <v>69.4997255371003</v>
+        <v>69.49971743662823</v>
       </c>
       <c r="D105" t="n">
-        <v>65.37015590307951</v>
+        <v>65.37014828392535</v>
       </c>
       <c r="E105" t="n">
-        <v>69.35328552416013</v>
+        <v>69.35327744075623</v>
       </c>
       <c r="F105" t="n">
         <v>831466</v>
@@ -2532,16 +2532,16 @@
         <v>43368</v>
       </c>
       <c r="B106" t="n">
-        <v>63.90575408935547</v>
+        <v>63.90575790405273</v>
       </c>
       <c r="C106" t="n">
-        <v>67.21526326118382</v>
+        <v>67.21526727343412</v>
       </c>
       <c r="D106" t="n">
-        <v>61.62131356977399</v>
+        <v>61.62131724810718</v>
       </c>
       <c r="E106" t="n">
-        <v>64.46222003555015</v>
+        <v>64.46222388346429</v>
       </c>
       <c r="F106" t="n">
         <v>629433</v>
@@ -2552,16 +2552,16 @@
         <v>43369</v>
       </c>
       <c r="B107" t="n">
-        <v>65.01868438720703</v>
+        <v>65.01869964599609</v>
       </c>
       <c r="C107" t="n">
-        <v>66.48306920425335</v>
+        <v>66.48308480670883</v>
       </c>
       <c r="D107" t="n">
-        <v>63.14427360896688</v>
+        <v>63.14428842786333</v>
       </c>
       <c r="E107" t="n">
-        <v>63.93503902673306</v>
+        <v>63.93505403120882</v>
       </c>
       <c r="F107" t="n">
         <v>469400</v>
@@ -2572,16 +2572,16 @@
         <v>43370</v>
       </c>
       <c r="B108" t="n">
-        <v>68.59180450439453</v>
+        <v>68.59178924560547</v>
       </c>
       <c r="C108" t="n">
-        <v>69.85116921552618</v>
+        <v>69.85115367658149</v>
       </c>
       <c r="D108" t="n">
-        <v>65.07727408368397</v>
+        <v>65.07725960672998</v>
       </c>
       <c r="E108" t="n">
-        <v>65.4873075982657</v>
+        <v>65.48729303009652</v>
       </c>
       <c r="F108" t="n">
         <v>605400</v>
@@ -2612,16 +2612,16 @@
         <v>43374</v>
       </c>
       <c r="B110" t="n">
-        <v>69.11895751953125</v>
+        <v>69.11897277832031</v>
       </c>
       <c r="C110" t="n">
-        <v>70.20260285843067</v>
+        <v>70.20261835644665</v>
       </c>
       <c r="D110" t="n">
-        <v>68.41605907787013</v>
+        <v>68.41607418148644</v>
       </c>
       <c r="E110" t="n">
-        <v>70.20260285843067</v>
+        <v>70.20261835644665</v>
       </c>
       <c r="F110" t="n">
         <v>385466</v>
@@ -2632,16 +2632,16 @@
         <v>43375</v>
       </c>
       <c r="B111" t="n">
-        <v>69.14825439453125</v>
+        <v>69.14826202392578</v>
       </c>
       <c r="C111" t="n">
-        <v>70.2611862845098</v>
+        <v>70.26119403669841</v>
       </c>
       <c r="D111" t="n">
-        <v>67.97674204575357</v>
+        <v>67.97674954589061</v>
       </c>
       <c r="E111" t="n">
-        <v>69.20682740508386</v>
+        <v>69.20683504094097</v>
       </c>
       <c r="F111" t="n">
         <v>391400</v>
@@ -2652,16 +2652,16 @@
         <v>43376</v>
       </c>
       <c r="B112" t="n">
-        <v>70.43692779541016</v>
+        <v>70.43691253662109</v>
       </c>
       <c r="C112" t="n">
-        <v>73.59999766042965</v>
+        <v>73.59998171642307</v>
       </c>
       <c r="D112" t="n">
-        <v>69.08968867923201</v>
+        <v>69.08967371229606</v>
       </c>
       <c r="E112" t="n">
-        <v>70.58336035303988</v>
+        <v>70.58334506252905</v>
       </c>
       <c r="F112" t="n">
         <v>463466</v>
@@ -2712,16 +2712,16 @@
         <v>43381</v>
       </c>
       <c r="B115" t="n">
-        <v>69.55828094482422</v>
+        <v>69.55828857421875</v>
       </c>
       <c r="C115" t="n">
-        <v>70.90551233649205</v>
+        <v>70.90552011365561</v>
       </c>
       <c r="D115" t="n">
-        <v>68.85537501934654</v>
+        <v>68.8553825716439</v>
       </c>
       <c r="E115" t="n">
-        <v>68.85537501934654</v>
+        <v>68.8553825716439</v>
       </c>
       <c r="F115" t="n">
         <v>697200</v>
@@ -2752,16 +2752,16 @@
         <v>43383</v>
       </c>
       <c r="B117" t="n">
-        <v>69.14825439453125</v>
+        <v>69.14826202392578</v>
       </c>
       <c r="C117" t="n">
-        <v>71.72557113429701</v>
+        <v>71.72557904805687</v>
       </c>
       <c r="D117" t="n">
-        <v>67.24454962085997</v>
+        <v>67.24455704021138</v>
       </c>
       <c r="E117" t="n">
-        <v>67.36170309021169</v>
+        <v>67.3617105224891</v>
       </c>
       <c r="F117" t="n">
         <v>149833</v>
@@ -2772,16 +2772,16 @@
         <v>43384</v>
       </c>
       <c r="B118" t="n">
-        <v>70.87622833251953</v>
+        <v>70.87624359130859</v>
       </c>
       <c r="C118" t="n">
-        <v>71.63770729591425</v>
+        <v>71.63772271864046</v>
       </c>
       <c r="D118" t="n">
-        <v>68.62107794888951</v>
+        <v>68.62109272217215</v>
       </c>
       <c r="E118" t="n">
-        <v>69.08967695024926</v>
+        <v>69.08969182441557</v>
       </c>
       <c r="F118" t="n">
         <v>258833</v>
@@ -2792,16 +2792,16 @@
         <v>43388</v>
       </c>
       <c r="B119" t="n">
-        <v>72.04774475097656</v>
+        <v>72.04773712158203</v>
       </c>
       <c r="C119" t="n">
-        <v>72.89709081745879</v>
+        <v>72.89708309812396</v>
       </c>
       <c r="D119" t="n">
-        <v>66.77596418128775</v>
+        <v>66.77595711014101</v>
       </c>
       <c r="E119" t="n">
-        <v>71.57914567503659</v>
+        <v>71.5791380952637</v>
       </c>
       <c r="F119" t="n">
         <v>520433</v>
@@ -2812,16 +2812,16 @@
         <v>43389</v>
       </c>
       <c r="B120" t="n">
-        <v>73.83428955078125</v>
+        <v>73.83427429199219</v>
       </c>
       <c r="C120" t="n">
-        <v>75.85514056741636</v>
+        <v>75.8551248909929</v>
       </c>
       <c r="D120" t="n">
-        <v>71.34483950178725</v>
+        <v>71.34482475747451</v>
       </c>
       <c r="E120" t="n">
-        <v>71.98916503334256</v>
+        <v>71.9891501558718</v>
       </c>
       <c r="F120" t="n">
         <v>484533</v>
@@ -2832,16 +2832,16 @@
         <v>43390</v>
       </c>
       <c r="B121" t="n">
-        <v>74.91792297363281</v>
+        <v>74.91793060302734</v>
       </c>
       <c r="C121" t="n">
-        <v>75.8844148392387</v>
+        <v>75.88442256705758</v>
       </c>
       <c r="D121" t="n">
-        <v>73.27781172835662</v>
+        <v>73.27781919072763</v>
       </c>
       <c r="E121" t="n">
-        <v>73.27781172835662</v>
+        <v>73.27781919072763</v>
       </c>
       <c r="F121" t="n">
         <v>520600</v>
@@ -2852,16 +2852,16 @@
         <v>43391</v>
       </c>
       <c r="B122" t="n">
-        <v>75.56227874755859</v>
+        <v>75.56226348876953</v>
       </c>
       <c r="C122" t="n">
-        <v>76.79235696808804</v>
+        <v>76.79234146090117</v>
       </c>
       <c r="D122" t="n">
-        <v>74.88865916375791</v>
+        <v>74.88864404099729</v>
       </c>
       <c r="E122" t="n">
-        <v>74.9179456764017</v>
+        <v>74.91793054772705</v>
       </c>
       <c r="F122" t="n">
         <v>252733</v>
@@ -2872,16 +2872,16 @@
         <v>43392</v>
       </c>
       <c r="B123" t="n">
-        <v>73.95145416259766</v>
+        <v>73.95144653320312</v>
       </c>
       <c r="C123" t="n">
-        <v>76.41161807335179</v>
+        <v>76.41161019014804</v>
       </c>
       <c r="D123" t="n">
-        <v>72.75065499599548</v>
+        <v>72.75064749048451</v>
       </c>
       <c r="E123" t="n">
-        <v>75.62085243208233</v>
+        <v>75.62084463045997</v>
       </c>
       <c r="F123" t="n">
         <v>198200</v>
@@ -2892,16 +2892,16 @@
         <v>43395</v>
       </c>
       <c r="B124" t="n">
-        <v>74.65434265136719</v>
+        <v>74.65435028076172</v>
       </c>
       <c r="C124" t="n">
-        <v>76.55804002313839</v>
+        <v>76.55804784708366</v>
       </c>
       <c r="D124" t="n">
-        <v>74.39074920097013</v>
+        <v>74.3907568034264</v>
       </c>
       <c r="E124" t="n">
-        <v>74.53718917916331</v>
+        <v>74.53719679658519</v>
       </c>
       <c r="F124" t="n">
         <v>312766</v>
@@ -2932,16 +2932,16 @@
         <v>43397</v>
       </c>
       <c r="B126" t="n">
-        <v>74.39076232910156</v>
+        <v>74.3907470703125</v>
       </c>
       <c r="C126" t="n">
-        <v>75.26939490507085</v>
+        <v>75.26937946605956</v>
       </c>
       <c r="D126" t="n">
-        <v>74.24432232506534</v>
+        <v>74.24430709631358</v>
       </c>
       <c r="E126" t="n">
-        <v>75.26939490507085</v>
+        <v>75.26937946605956</v>
       </c>
       <c r="F126" t="n">
         <v>414300</v>
@@ -2952,16 +2952,16 @@
         <v>43398</v>
       </c>
       <c r="B127" t="n">
-        <v>76.0015869140625</v>
+        <v>76.00157928466797</v>
       </c>
       <c r="C127" t="n">
-        <v>76.0015869140625</v>
+        <v>76.00157928466797</v>
       </c>
       <c r="D127" t="n">
-        <v>73.10210315896421</v>
+        <v>73.10209582063342</v>
       </c>
       <c r="E127" t="n">
-        <v>74.56648829198372</v>
+        <v>74.5664808066511</v>
       </c>
       <c r="F127" t="n">
         <v>495966</v>
@@ -2972,16 +2972,16 @@
         <v>43399</v>
       </c>
       <c r="B128" t="n">
-        <v>74.97650909423828</v>
+        <v>74.97649383544922</v>
       </c>
       <c r="C128" t="n">
-        <v>78.02243263911183</v>
+        <v>78.02241676043387</v>
       </c>
       <c r="D128" t="n">
-        <v>73.36569151925214</v>
+        <v>73.36567658828743</v>
       </c>
       <c r="E128" t="n">
-        <v>76.1187350787205</v>
+        <v>76.11871958747216</v>
       </c>
       <c r="F128" t="n">
         <v>546200</v>
@@ -2992,16 +2992,16 @@
         <v>43402</v>
       </c>
       <c r="B129" t="n">
-        <v>75.50367736816406</v>
+        <v>75.50369262695312</v>
       </c>
       <c r="C129" t="n">
-        <v>76.44088275450883</v>
+        <v>76.44089820270085</v>
       </c>
       <c r="D129" t="n">
-        <v>75.18151837003508</v>
+        <v>75.18153356371796</v>
       </c>
       <c r="E129" t="n">
-        <v>76.38230974543926</v>
+        <v>76.38232518179406</v>
       </c>
       <c r="F129" t="n">
         <v>188000</v>
@@ -3032,16 +3032,16 @@
         <v>43404</v>
       </c>
       <c r="B131" t="n">
-        <v>74.62506103515625</v>
+        <v>74.62508392333984</v>
       </c>
       <c r="C131" t="n">
-        <v>76.61661805539134</v>
+        <v>76.61664155440354</v>
       </c>
       <c r="D131" t="n">
-        <v>73.86357458830497</v>
+        <v>73.86359724293376</v>
       </c>
       <c r="E131" t="n">
-        <v>75.67941256109036</v>
+        <v>75.67943577265314</v>
       </c>
       <c r="F131" t="n">
         <v>863500</v>
@@ -3052,16 +3052,16 @@
         <v>43405</v>
       </c>
       <c r="B132" t="n">
-        <v>75.35725402832031</v>
+        <v>75.35724639892578</v>
       </c>
       <c r="C132" t="n">
-        <v>78.08100355741267</v>
+        <v>78.08099565225757</v>
       </c>
       <c r="D132" t="n">
-        <v>74.15645505834372</v>
+        <v>74.15644755052168</v>
       </c>
       <c r="E132" t="n">
-        <v>75.65012655760316</v>
+        <v>75.65011889855732</v>
       </c>
       <c r="F132" t="n">
         <v>289433</v>
@@ -3072,16 +3072,16 @@
         <v>43409</v>
       </c>
       <c r="B133" t="n">
-        <v>76.38233184814453</v>
+        <v>76.38232421875</v>
       </c>
       <c r="C133" t="n">
-        <v>76.85093840104045</v>
+        <v>76.85093072483949</v>
       </c>
       <c r="D133" t="n">
-        <v>73.98074095414307</v>
+        <v>73.98073356462973</v>
       </c>
       <c r="E133" t="n">
-        <v>75.8258657562204</v>
+        <v>75.82585818240808</v>
       </c>
       <c r="F133" t="n">
         <v>315933</v>
@@ -3192,16 +3192,16 @@
         <v>43417</v>
       </c>
       <c r="B139" t="n">
-        <v>75.26937866210938</v>
+        <v>75.26938629150391</v>
       </c>
       <c r="C139" t="n">
-        <v>77.84669536327486</v>
+        <v>77.84670325390931</v>
       </c>
       <c r="D139" t="n">
-        <v>74.91792570756441</v>
+        <v>74.91793330133525</v>
       </c>
       <c r="E139" t="n">
-        <v>77.26094292178205</v>
+        <v>77.26095075304393</v>
       </c>
       <c r="F139" t="n">
         <v>637900</v>
@@ -3212,16 +3212,16 @@
         <v>43418</v>
       </c>
       <c r="B140" t="n">
-        <v>79.36966705322266</v>
+        <v>79.36967468261719</v>
       </c>
       <c r="C140" t="n">
-        <v>80.33616657102803</v>
+        <v>80.33617429332715</v>
       </c>
       <c r="D140" t="n">
-        <v>71.02267654659238</v>
+        <v>71.022683373634</v>
       </c>
       <c r="E140" t="n">
-        <v>75.0350922710638</v>
+        <v>75.03509948379813</v>
       </c>
       <c r="F140" t="n">
         <v>1608700</v>
@@ -3292,16 +3292,16 @@
         <v>43426</v>
       </c>
       <c r="B144" t="n">
-        <v>79.07678985595703</v>
+        <v>79.0767822265625</v>
       </c>
       <c r="C144" t="n">
-        <v>80.24829487452415</v>
+        <v>80.24828713210185</v>
       </c>
       <c r="D144" t="n">
-        <v>77.78813135623429</v>
+        <v>77.78812385117061</v>
       </c>
       <c r="E144" t="n">
-        <v>79.54538888408497</v>
+        <v>79.54538120947963</v>
       </c>
       <c r="F144" t="n">
         <v>203833</v>
@@ -3312,16 +3312,16 @@
         <v>43427</v>
       </c>
       <c r="B145" t="n">
-        <v>79.51611328125</v>
+        <v>79.51610565185547</v>
       </c>
       <c r="C145" t="n">
-        <v>79.51611328125</v>
+        <v>79.51610565185547</v>
       </c>
       <c r="D145" t="n">
-        <v>77.31953548399726</v>
+        <v>77.31952806535949</v>
       </c>
       <c r="E145" t="n">
-        <v>78.63748067269924</v>
+        <v>78.63747312760756</v>
       </c>
       <c r="F145" t="n">
         <v>372100</v>
@@ -3332,16 +3332,16 @@
         <v>43430</v>
       </c>
       <c r="B146" t="n">
-        <v>78.75462341308594</v>
+        <v>78.75461578369141</v>
       </c>
       <c r="C146" t="n">
-        <v>80.33616189246013</v>
+        <v>80.33615410985325</v>
       </c>
       <c r="D146" t="n">
-        <v>76.23587942868353</v>
+        <v>76.23587204329363</v>
       </c>
       <c r="E146" t="n">
-        <v>80.27758142772588</v>
+        <v>80.27757365079401</v>
       </c>
       <c r="F146" t="n">
         <v>252366</v>
@@ -3392,16 +3392,16 @@
         <v>43433</v>
       </c>
       <c r="B149" t="n">
-        <v>84.17285919189453</v>
+        <v>84.17286682128906</v>
       </c>
       <c r="C149" t="n">
-        <v>85.69581735682299</v>
+        <v>85.69582512425784</v>
       </c>
       <c r="D149" t="n">
-        <v>83.29422661664812</v>
+        <v>83.29423416640374</v>
       </c>
       <c r="E149" t="n">
-        <v>84.31929919581027</v>
+        <v>84.31930683847806</v>
       </c>
       <c r="F149" t="n">
         <v>232033</v>
@@ -3452,16 +3452,16 @@
         <v>43438</v>
       </c>
       <c r="B152" t="n">
-        <v>83.8214111328125</v>
+        <v>83.82138824462891</v>
       </c>
       <c r="C152" t="n">
-        <v>86.60374157922517</v>
+        <v>86.60371793130145</v>
       </c>
       <c r="D152" t="n">
-        <v>82.59132545451746</v>
+        <v>82.59130290221974</v>
       </c>
       <c r="E152" t="n">
-        <v>84.64146328617689</v>
+        <v>84.64144017407074</v>
       </c>
       <c r="F152" t="n">
         <v>207933</v>
@@ -3492,16 +3492,16 @@
         <v>43440</v>
       </c>
       <c r="B154" t="n">
-        <v>84.934326171875</v>
+        <v>84.93433380126953</v>
       </c>
       <c r="C154" t="n">
-        <v>85.46150564190386</v>
+        <v>85.46151331865333</v>
       </c>
       <c r="D154" t="n">
-        <v>83.87996723181728</v>
+        <v>83.87997476650193</v>
       </c>
       <c r="E154" t="n">
-        <v>85.25649264493379</v>
+        <v>85.25650030326756</v>
       </c>
       <c r="F154" t="n">
         <v>270866</v>
@@ -3552,16 +3552,16 @@
         <v>43445</v>
       </c>
       <c r="B157" t="n">
-        <v>83.87996673583984</v>
+        <v>83.87997436523438</v>
       </c>
       <c r="C157" t="n">
-        <v>84.37785969596425</v>
+        <v>84.37786737064518</v>
       </c>
       <c r="D157" t="n">
-        <v>83.14777427317034</v>
+        <v>83.14778183596749</v>
       </c>
       <c r="E157" t="n">
-        <v>83.46994074432418</v>
+        <v>83.46994833642434</v>
       </c>
       <c r="F157" t="n">
         <v>276533</v>
@@ -3572,16 +3572,16 @@
         <v>43446</v>
       </c>
       <c r="B158" t="n">
-        <v>85.60794067382812</v>
+        <v>85.60796356201172</v>
       </c>
       <c r="C158" t="n">
-        <v>86.28155263970095</v>
+        <v>86.28157570798179</v>
       </c>
       <c r="D158" t="n">
-        <v>84.37785531490263</v>
+        <v>84.37787787420997</v>
       </c>
       <c r="E158" t="n">
-        <v>84.55358179474914</v>
+        <v>84.55360440103878</v>
       </c>
       <c r="F158" t="n">
         <v>243466</v>
@@ -3632,16 +3632,16 @@
         <v>43451</v>
       </c>
       <c r="B161" t="n">
-        <v>84.93785858154297</v>
+        <v>84.9378662109375</v>
       </c>
       <c r="C161" t="n">
-        <v>86.47039216264943</v>
+        <v>86.47039992970112</v>
       </c>
       <c r="D161" t="n">
-        <v>84.28947437718072</v>
+        <v>84.28948194833528</v>
       </c>
       <c r="E161" t="n">
-        <v>86.44092151610168</v>
+        <v>86.44092928050621</v>
       </c>
       <c r="F161" t="n">
         <v>205700</v>
@@ -3672,16 +3672,16 @@
         <v>43453</v>
       </c>
       <c r="B163" t="n">
-        <v>89.68283081054688</v>
+        <v>89.68282318115234</v>
       </c>
       <c r="C163" t="n">
-        <v>90.56698771453594</v>
+        <v>90.56698000992543</v>
       </c>
       <c r="D163" t="n">
-        <v>86.29356392776849</v>
+        <v>86.29355658670175</v>
       </c>
       <c r="E163" t="n">
-        <v>86.52934409888439</v>
+        <v>86.52933673775965</v>
       </c>
       <c r="F163" t="n">
         <v>384866</v>
@@ -3692,16 +3692,16 @@
         <v>43454</v>
       </c>
       <c r="B164" t="n">
-        <v>89.00496673583984</v>
+        <v>89.00497436523438</v>
       </c>
       <c r="C164" t="n">
-        <v>93.07208057875353</v>
+        <v>93.07208855677598</v>
       </c>
       <c r="D164" t="n">
-        <v>87.20718246605232</v>
+        <v>87.20718994134303</v>
       </c>
       <c r="E164" t="n">
-        <v>89.2702175271606</v>
+        <v>89.27022517929211</v>
       </c>
       <c r="F164" t="n">
         <v>975500</v>
@@ -3752,16 +3752,16 @@
         <v>43461</v>
       </c>
       <c r="B167" t="n">
-        <v>90.62592315673828</v>
+        <v>90.62593078613281</v>
       </c>
       <c r="C167" t="n">
-        <v>91.3627192799638</v>
+        <v>91.36272697138592</v>
       </c>
       <c r="D167" t="n">
-        <v>89.35863292538107</v>
+        <v>89.35864044808805</v>
       </c>
       <c r="E167" t="n">
-        <v>91.3627192799638</v>
+        <v>91.36272697138592</v>
       </c>
       <c r="F167" t="n">
         <v>343866</v>
@@ -3772,16 +3772,16 @@
         <v>43462</v>
       </c>
       <c r="B168" t="n">
-        <v>91.9521484375</v>
+        <v>91.95215606689453</v>
       </c>
       <c r="C168" t="n">
-        <v>92.09950915115729</v>
+        <v>92.09951679277854</v>
       </c>
       <c r="D168" t="n">
-        <v>89.97753286267756</v>
+        <v>89.97754032823556</v>
       </c>
       <c r="E168" t="n">
-        <v>91.33324243423203</v>
+        <v>91.33325001227509</v>
       </c>
       <c r="F168" t="n">
         <v>582800</v>
@@ -3812,16 +3812,16 @@
         <v>43468</v>
       </c>
       <c r="B170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494140625</v>
       </c>
       <c r="C170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.53955725766548</v>
       </c>
       <c r="D170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494140625</v>
       </c>
       <c r="E170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.53955725766548</v>
       </c>
       <c r="F170" t="n">
         <v>308333</v>
@@ -3832,16 +3832,16 @@
         <v>43469</v>
       </c>
       <c r="B171" t="n">
-        <v>89.88912963867188</v>
+        <v>89.88912200927734</v>
       </c>
       <c r="C171" t="n">
-        <v>91.36272192783044</v>
+        <v>91.36271417336386</v>
       </c>
       <c r="D171" t="n">
-        <v>88.68078066372756</v>
+        <v>88.68077313689237</v>
       </c>
       <c r="E171" t="n">
-        <v>89.83018834553049</v>
+        <v>89.83018072113863</v>
       </c>
       <c r="F171" t="n">
         <v>585300</v>
@@ -3852,16 +3852,16 @@
         <v>43472</v>
       </c>
       <c r="B172" t="n">
-        <v>91.24481964111328</v>
+        <v>91.24483489990234</v>
       </c>
       <c r="C172" t="n">
-        <v>91.65742362806702</v>
+        <v>91.65743895585547</v>
       </c>
       <c r="D172" t="n">
-        <v>89.88911761466086</v>
+        <v>89.88913264673708</v>
       </c>
       <c r="E172" t="n">
-        <v>89.88911761466086</v>
+        <v>89.88913264673708</v>
       </c>
       <c r="F172" t="n">
         <v>470133</v>
@@ -3872,16 +3872,16 @@
         <v>43473</v>
       </c>
       <c r="B173" t="n">
-        <v>89.88912963867188</v>
+        <v>89.88912200927734</v>
       </c>
       <c r="C173" t="n">
-        <v>91.21536119989898</v>
+        <v>91.21535345793974</v>
       </c>
       <c r="D173" t="n">
-        <v>89.35863551516545</v>
+        <v>89.35862793079691</v>
       </c>
       <c r="E173" t="n">
-        <v>91.21536119989898</v>
+        <v>91.21535345793974</v>
       </c>
       <c r="F173" t="n">
         <v>273633</v>
@@ -3892,16 +3892,16 @@
         <v>43474</v>
       </c>
       <c r="B174" t="n">
-        <v>91.36272430419922</v>
+        <v>91.36271667480469</v>
       </c>
       <c r="C174" t="n">
-        <v>91.92268908884118</v>
+        <v>91.92268141268588</v>
       </c>
       <c r="D174" t="n">
-        <v>89.71230059761056</v>
+        <v>89.71229310603738</v>
       </c>
       <c r="E174" t="n">
-        <v>89.71230059761056</v>
+        <v>89.71229310603738</v>
       </c>
       <c r="F174" t="n">
         <v>225833</v>
@@ -3912,16 +3912,16 @@
         <v>43475</v>
       </c>
       <c r="B175" t="n">
-        <v>93.39628601074219</v>
+        <v>93.39627838134766</v>
       </c>
       <c r="C175" t="n">
-        <v>94.84040776193225</v>
+        <v>94.84040001456971</v>
       </c>
       <c r="D175" t="n">
-        <v>91.09747796933716</v>
+        <v>91.0974705277286</v>
       </c>
       <c r="E175" t="n">
-        <v>91.09747796933716</v>
+        <v>91.0974705277286</v>
       </c>
       <c r="F175" t="n">
         <v>243466</v>
@@ -3932,16 +3932,16 @@
         <v>43476</v>
       </c>
       <c r="B176" t="n">
-        <v>92.36474609375</v>
+        <v>92.36475372314453</v>
       </c>
       <c r="C176" t="n">
-        <v>93.04260083295516</v>
+        <v>93.04260851834098</v>
       </c>
       <c r="D176" t="n">
-        <v>90.86168340688354</v>
+        <v>90.861690912124</v>
       </c>
       <c r="E176" t="n">
-        <v>92.39421673544123</v>
+        <v>92.39422436727006</v>
       </c>
       <c r="F176" t="n">
         <v>283133</v>
@@ -3952,16 +3952,16 @@
         <v>43479</v>
       </c>
       <c r="B177" t="n">
-        <v>94.63410949707031</v>
+        <v>94.63408660888672</v>
       </c>
       <c r="C177" t="n">
-        <v>96.40241595047306</v>
+        <v>96.40239263460728</v>
       </c>
       <c r="D177" t="n">
-        <v>92.74790545366369</v>
+        <v>92.74788302167697</v>
       </c>
       <c r="E177" t="n">
-        <v>92.95421499355224</v>
+        <v>92.95419251166753</v>
       </c>
       <c r="F177" t="n">
         <v>478500</v>
@@ -3972,16 +3972,16 @@
         <v>43480</v>
       </c>
       <c r="B178" t="n">
-        <v>93.42575836181641</v>
+        <v>93.42574310302734</v>
       </c>
       <c r="C178" t="n">
-        <v>99.26118677047653</v>
+        <v>99.26117055861442</v>
       </c>
       <c r="D178" t="n">
-        <v>92.74790344705082</v>
+        <v>92.7478882989726</v>
       </c>
       <c r="E178" t="n">
-        <v>94.69304874829707</v>
+        <v>94.69303328252744</v>
       </c>
       <c r="F178" t="n">
         <v>736266</v>
@@ -3992,16 +3992,16 @@
         <v>43481</v>
       </c>
       <c r="B179" t="n">
-        <v>98.43595886230469</v>
+        <v>98.43596649169922</v>
       </c>
       <c r="C179" t="n">
-        <v>100.0569118290803</v>
+        <v>100.0569195841087</v>
       </c>
       <c r="D179" t="n">
-        <v>93.74993882606901</v>
+        <v>93.74994609226806</v>
       </c>
       <c r="E179" t="n">
-        <v>93.89729954942638</v>
+        <v>93.8973068270468</v>
       </c>
       <c r="F179" t="n">
         <v>1131666</v>
@@ -4012,16 +4012,16 @@
         <v>43482</v>
       </c>
       <c r="B180" t="n">
-        <v>99.26116943359375</v>
+        <v>99.26117706298828</v>
       </c>
       <c r="C180" t="n">
-        <v>100.0274361624956</v>
+        <v>100.0274438507868</v>
       </c>
       <c r="D180" t="n">
-        <v>97.90545984084979</v>
+        <v>97.90546736604202</v>
       </c>
       <c r="E180" t="n">
-        <v>98.78961664153556</v>
+        <v>98.78962423468569</v>
       </c>
       <c r="F180" t="n">
         <v>313600</v>
@@ -4032,16 +4032,16 @@
         <v>43483</v>
       </c>
       <c r="B181" t="n">
-        <v>100.793701171875</v>
+        <v>100.7937088012695</v>
       </c>
       <c r="C181" t="n">
-        <v>102.2672933161863</v>
+        <v>102.2673010571217</v>
       </c>
       <c r="D181" t="n">
-        <v>98.73067366885468</v>
+        <v>98.73068114209212</v>
       </c>
       <c r="E181" t="n">
-        <v>99.67377174180463</v>
+        <v>99.67377928642814</v>
       </c>
       <c r="F181" t="n">
         <v>475600</v>
@@ -4052,16 +4052,16 @@
         <v>43486</v>
       </c>
       <c r="B182" t="n">
-        <v>101.3831481933594</v>
+        <v>101.3831558227539</v>
       </c>
       <c r="C182" t="n">
-        <v>102.3557245169423</v>
+        <v>102.3557322195262</v>
       </c>
       <c r="D182" t="n">
-        <v>98.22966154117607</v>
+        <v>98.22966893326101</v>
       </c>
       <c r="E182" t="n">
-        <v>100.7937127668437</v>
+        <v>100.7937203518813</v>
       </c>
       <c r="F182" t="n">
         <v>260300</v>
@@ -4072,16 +4072,16 @@
         <v>43487</v>
       </c>
       <c r="B183" t="n">
-        <v>100.2632141113281</v>
+        <v>100.2632217407227</v>
       </c>
       <c r="C183" t="n">
-        <v>101.7662770044136</v>
+        <v>101.7662847481816</v>
       </c>
       <c r="D183" t="n">
-        <v>99.17275524868226</v>
+        <v>99.17276279509979</v>
       </c>
       <c r="E183" t="n">
-        <v>101.7662770044136</v>
+        <v>101.7662847481816</v>
       </c>
       <c r="F183" t="n">
         <v>236233</v>
@@ -4092,16 +4092,16 @@
         <v>43488</v>
       </c>
       <c r="B184" t="n">
-        <v>99.23171234130859</v>
+        <v>99.23170471191406</v>
       </c>
       <c r="C184" t="n">
-        <v>101.0589674805782</v>
+        <v>101.0589597106958</v>
       </c>
       <c r="D184" t="n">
-        <v>98.17072403558848</v>
+        <v>98.17071648776765</v>
       </c>
       <c r="E184" t="n">
-        <v>99.58537510988198</v>
+        <v>99.5853674532962</v>
       </c>
       <c r="F184" t="n">
         <v>240366</v>
@@ -4132,16 +4132,16 @@
         <v>43493</v>
       </c>
       <c r="B186" t="n">
-        <v>97.25708770751953</v>
+        <v>97.25709533691406</v>
       </c>
       <c r="C186" t="n">
-        <v>98.05282511761074</v>
+        <v>98.0528328094274</v>
       </c>
       <c r="D186" t="n">
-        <v>95.96032683788904</v>
+        <v>95.96033436555834</v>
       </c>
       <c r="E186" t="n">
-        <v>98.05282511761074</v>
+        <v>98.0528328094274</v>
       </c>
       <c r="F186" t="n">
         <v>263933</v>
@@ -4152,16 +4152,16 @@
         <v>43494</v>
       </c>
       <c r="B187" t="n">
-        <v>97.31602478027344</v>
+        <v>97.3160400390625</v>
       </c>
       <c r="C187" t="n">
-        <v>97.9938795787921</v>
+        <v>97.99389494386627</v>
       </c>
       <c r="D187" t="n">
-        <v>96.72658940964205</v>
+        <v>96.72660457600985</v>
       </c>
       <c r="E187" t="n">
-        <v>97.4928561409706</v>
+        <v>97.49287142748615</v>
       </c>
       <c r="F187" t="n">
         <v>185333</v>
@@ -4192,16 +4192,16 @@
         <v>43496</v>
       </c>
       <c r="B189" t="n">
-        <v>100.9116058349609</v>
+        <v>100.9115982055664</v>
       </c>
       <c r="C189" t="n">
-        <v>104.5661160805616</v>
+        <v>104.5661081748688</v>
       </c>
       <c r="D189" t="n">
-        <v>99.20223330390368</v>
+        <v>99.20222580374578</v>
       </c>
       <c r="E189" t="n">
-        <v>99.79167624293216</v>
+        <v>99.79166869820958</v>
       </c>
       <c r="F189" t="n">
         <v>504800</v>
@@ -4212,16 +4212,16 @@
         <v>43497</v>
       </c>
       <c r="B190" t="n">
-        <v>100.2042770385742</v>
+        <v>100.2042694091797</v>
       </c>
       <c r="C190" t="n">
-        <v>101.5599792649856</v>
+        <v>101.5599715323701</v>
       </c>
       <c r="D190" t="n">
-        <v>98.84857481216278</v>
+        <v>98.84856728598928</v>
       </c>
       <c r="E190" t="n">
-        <v>101.2063165111256</v>
+        <v>101.2063088054374</v>
       </c>
       <c r="F190" t="n">
         <v>150066</v>
@@ -4232,16 +4232,16 @@
         <v>43500</v>
       </c>
       <c r="B191" t="n">
-        <v>100.2632141113281</v>
+        <v>100.2632217407227</v>
       </c>
       <c r="C191" t="n">
-        <v>102.2673004671346</v>
+        <v>102.2673082490274</v>
       </c>
       <c r="D191" t="n">
-        <v>99.55588863338727</v>
+        <v>99.55589620895881</v>
       </c>
       <c r="E191" t="n">
-        <v>100.7347669283146</v>
+        <v>100.7347745935913</v>
       </c>
       <c r="F191" t="n">
         <v>316266</v>
@@ -4332,16 +4332,16 @@
         <v>43507</v>
       </c>
       <c r="B196" t="n">
-        <v>98.14125823974609</v>
+        <v>98.14124298095703</v>
       </c>
       <c r="C196" t="n">
-        <v>98.67175241883517</v>
+        <v>98.67173707756602</v>
       </c>
       <c r="D196" t="n">
-        <v>96.10770096744402</v>
+        <v>96.10768602482801</v>
       </c>
       <c r="E196" t="n">
-        <v>97.10974053122644</v>
+        <v>97.10972543281549</v>
       </c>
       <c r="F196" t="n">
         <v>401966</v>
@@ -4352,16 +4352,16 @@
         <v>43508</v>
       </c>
       <c r="B197" t="n">
-        <v>97.55180358886719</v>
+        <v>97.55181121826172</v>
       </c>
       <c r="C197" t="n">
-        <v>99.64430940508254</v>
+        <v>99.64431719812912</v>
       </c>
       <c r="D197" t="n">
-        <v>96.78553680915705</v>
+        <v>96.7855443786229</v>
       </c>
       <c r="E197" t="n">
-        <v>98.20018778405444</v>
+        <v>98.20019546415823</v>
       </c>
       <c r="F197" t="n">
         <v>301900</v>
@@ -4432,16 +4432,16 @@
         <v>43514</v>
       </c>
       <c r="B201" t="n">
-        <v>100.2042770385742</v>
+        <v>100.2042694091797</v>
       </c>
       <c r="C201" t="n">
-        <v>100.2042770385742</v>
+        <v>100.2042694091797</v>
       </c>
       <c r="D201" t="n">
-        <v>97.64022582062798</v>
+        <v>97.64021838645624</v>
       </c>
       <c r="E201" t="n">
-        <v>98.34755132834806</v>
+        <v>98.34754384032168</v>
       </c>
       <c r="F201" t="n">
         <v>154800</v>
@@ -4452,16 +4452,16 @@
         <v>43515</v>
       </c>
       <c r="B202" t="n">
-        <v>98.43595886230469</v>
+        <v>98.43596649169922</v>
       </c>
       <c r="C202" t="n">
-        <v>101.0000099654586</v>
+        <v>101.0000177935829</v>
       </c>
       <c r="D202" t="n">
-        <v>98.2591274932914</v>
+        <v>98.2591351089804</v>
       </c>
       <c r="E202" t="n">
-        <v>100.2337431980935</v>
+        <v>100.2337509668275</v>
       </c>
       <c r="F202" t="n">
         <v>215600</v>
@@ -4472,16 +4472,16 @@
         <v>43516</v>
       </c>
       <c r="B203" t="n">
-        <v>97.25708770751953</v>
+        <v>97.25709533691406</v>
       </c>
       <c r="C203" t="n">
-        <v>99.17275461887898</v>
+        <v>99.17276239854924</v>
       </c>
       <c r="D203" t="n">
-        <v>95.5182446694446</v>
+        <v>95.51825216243448</v>
       </c>
       <c r="E203" t="n">
-        <v>98.87804066832706</v>
+        <v>98.87804842487829</v>
       </c>
       <c r="F203" t="n">
         <v>616733</v>
@@ -4492,16 +4492,16 @@
         <v>43517</v>
       </c>
       <c r="B204" t="n">
-        <v>95.78350067138672</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C204" t="n">
-        <v>97.61075574533942</v>
+        <v>97.61076352027936</v>
       </c>
       <c r="D204" t="n">
-        <v>95.04670451237605</v>
+        <v>95.04671208308292</v>
       </c>
       <c r="E204" t="n">
-        <v>97.28656363655598</v>
+        <v>97.28657138567321</v>
       </c>
       <c r="F204" t="n">
         <v>542100</v>
@@ -4512,16 +4512,16 @@
         <v>43518</v>
       </c>
       <c r="B205" t="n">
-        <v>92.86579132080078</v>
+        <v>92.86578369140625</v>
       </c>
       <c r="C205" t="n">
-        <v>95.87191740128438</v>
+        <v>95.87190952492139</v>
       </c>
       <c r="D205" t="n">
-        <v>92.86579132080078</v>
+        <v>92.86578369140625</v>
       </c>
       <c r="E205" t="n">
-        <v>95.8424467526645</v>
+        <v>95.84243887872267</v>
       </c>
       <c r="F205" t="n">
         <v>514866</v>
@@ -4532,16 +4532,16 @@
         <v>43521</v>
       </c>
       <c r="B206" t="n">
-        <v>95.40036773681641</v>
+        <v>95.40035247802734</v>
       </c>
       <c r="C206" t="n">
-        <v>97.10973273549394</v>
+        <v>97.10971720330089</v>
       </c>
       <c r="D206" t="n">
-        <v>92.24688106017342</v>
+        <v>92.24686630576804</v>
       </c>
       <c r="E206" t="n">
-        <v>93.66152459576807</v>
+        <v>93.66150961509786</v>
       </c>
       <c r="F206" t="n">
         <v>404566</v>
@@ -4552,16 +4552,16 @@
         <v>43522</v>
       </c>
       <c r="B207" t="n">
-        <v>95.13511657714844</v>
+        <v>95.13510131835938</v>
       </c>
       <c r="C207" t="n">
-        <v>97.25709311548748</v>
+        <v>97.25707751635309</v>
       </c>
       <c r="D207" t="n">
-        <v>93.36681029027736</v>
+        <v>93.36679531510821</v>
       </c>
       <c r="E207" t="n">
-        <v>95.5771987701748</v>
+        <v>95.57718344047986</v>
       </c>
       <c r="F207" t="n">
         <v>332133</v>
@@ -4572,16 +4572,16 @@
         <v>43523</v>
       </c>
       <c r="B208" t="n">
-        <v>95.69507598876953</v>
+        <v>95.69508361816406</v>
       </c>
       <c r="C208" t="n">
-        <v>96.63818161626997</v>
+        <v>96.63818932085464</v>
       </c>
       <c r="D208" t="n">
-        <v>94.45726390594589</v>
+        <v>94.45727143665449</v>
       </c>
       <c r="E208" t="n">
-        <v>95.13511123842235</v>
+        <v>95.13511882317307</v>
       </c>
       <c r="F208" t="n">
         <v>447266</v>
@@ -4592,16 +4592,16 @@
         <v>43524</v>
       </c>
       <c r="B209" t="n">
-        <v>96.04874420166016</v>
+        <v>96.04875946044922</v>
       </c>
       <c r="C209" t="n">
-        <v>96.46135574787134</v>
+        <v>96.46137107220996</v>
       </c>
       <c r="D209" t="n">
-        <v>94.75198325875762</v>
+        <v>94.75199831153668</v>
       </c>
       <c r="E209" t="n">
-        <v>95.69508144495236</v>
+        <v>95.69509664755678</v>
       </c>
       <c r="F209" t="n">
         <v>596166</v>
@@ -4632,16 +4632,16 @@
         <v>43530</v>
       </c>
       <c r="B211" t="n">
-        <v>95.75402069091797</v>
+        <v>95.75403594970703</v>
       </c>
       <c r="C211" t="n">
-        <v>96.60869935521325</v>
+        <v>96.6087147501988</v>
       </c>
       <c r="D211" t="n">
-        <v>93.95623643934654</v>
+        <v>93.95625141165144</v>
       </c>
       <c r="E211" t="n">
-        <v>95.10563653655028</v>
+        <v>95.10565169201672</v>
       </c>
       <c r="F211" t="n">
         <v>247200</v>
@@ -4692,16 +4692,16 @@
         <v>43535</v>
       </c>
       <c r="B214" t="n">
-        <v>97.31602478027344</v>
+        <v>97.3160400390625</v>
       </c>
       <c r="C214" t="n">
-        <v>97.52232678524055</v>
+        <v>97.522342076377</v>
       </c>
       <c r="D214" t="n">
-        <v>96.19609532755058</v>
+        <v>96.19611041073888</v>
       </c>
       <c r="E214" t="n">
-        <v>97.25708349173351</v>
+        <v>97.2570987412808</v>
       </c>
       <c r="F214" t="n">
         <v>533833</v>
@@ -4712,16 +4712,16 @@
         <v>43536</v>
       </c>
       <c r="B215" t="n">
-        <v>97.25708770751953</v>
+        <v>97.25709533691406</v>
       </c>
       <c r="C215" t="n">
-        <v>98.49490728605517</v>
+        <v>98.49491501255126</v>
       </c>
       <c r="D215" t="n">
-        <v>95.34141330108237</v>
+        <v>95.34142078020059</v>
       </c>
       <c r="E215" t="n">
-        <v>96.84448367970022</v>
+        <v>96.84449127672777</v>
       </c>
       <c r="F215" t="n">
         <v>275666</v>
@@ -4732,16 +4732,16 @@
         <v>43537</v>
       </c>
       <c r="B216" t="n">
-        <v>95.78350067138672</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C216" t="n">
-        <v>97.58128509819149</v>
+        <v>97.58129287078403</v>
       </c>
       <c r="D216" t="n">
-        <v>95.40036726830742</v>
+        <v>95.40037486718441</v>
       </c>
       <c r="E216" t="n">
-        <v>97.43392436737373</v>
+        <v>97.43393212822862</v>
       </c>
       <c r="F216" t="n">
         <v>425833</v>
@@ -4772,16 +4772,16 @@
         <v>43539</v>
       </c>
       <c r="B218" t="n">
-        <v>89.29969787597656</v>
+        <v>89.29969024658203</v>
       </c>
       <c r="C218" t="n">
-        <v>92.15846313647816</v>
+        <v>92.15845526284264</v>
       </c>
       <c r="D218" t="n">
-        <v>88.91656446472457</v>
+        <v>88.91655686806337</v>
       </c>
       <c r="E218" t="n">
-        <v>91.06800419827536</v>
+        <v>91.0679964178041</v>
       </c>
       <c r="F218" t="n">
         <v>927800</v>
@@ -4792,16 +4792,16 @@
         <v>43542</v>
       </c>
       <c r="B219" t="n">
-        <v>86.64722442626953</v>
+        <v>86.647216796875</v>
       </c>
       <c r="C219" t="n">
-        <v>89.32916571580841</v>
+        <v>89.32915785026566</v>
       </c>
       <c r="D219" t="n">
-        <v>83.84740054932983</v>
+        <v>83.84739316646325</v>
       </c>
       <c r="E219" t="n">
-        <v>89.29969506895821</v>
+        <v>89.29968720601039</v>
       </c>
       <c r="F219" t="n">
         <v>2555666</v>
@@ -4812,16 +4812,16 @@
         <v>43543</v>
       </c>
       <c r="B220" t="n">
-        <v>89.41757202148438</v>
+        <v>89.41757965087891</v>
       </c>
       <c r="C220" t="n">
-        <v>89.41757202148438</v>
+        <v>89.41757965087891</v>
       </c>
       <c r="D220" t="n">
-        <v>86.3525050209678</v>
+        <v>86.35251238884096</v>
       </c>
       <c r="E220" t="n">
-        <v>86.3525050209678</v>
+        <v>86.35251238884096</v>
       </c>
       <c r="F220" t="n">
         <v>1451666</v>
@@ -4832,16 +4832,16 @@
         <v>43544</v>
       </c>
       <c r="B221" t="n">
-        <v>88.65132141113281</v>
+        <v>88.65130615234375</v>
       </c>
       <c r="C221" t="n">
-        <v>89.94808249245639</v>
+        <v>89.948067010467</v>
       </c>
       <c r="D221" t="n">
-        <v>87.88505452149782</v>
+        <v>87.88503939459969</v>
       </c>
       <c r="E221" t="n">
-        <v>89.94808249245639</v>
+        <v>89.948067010467</v>
       </c>
       <c r="F221" t="n">
         <v>1179966</v>
@@ -4852,16 +4852,16 @@
         <v>43545</v>
       </c>
       <c r="B222" t="n">
-        <v>88.38606262207031</v>
+        <v>88.38605499267578</v>
       </c>
       <c r="C222" t="n">
-        <v>89.27021945375864</v>
+        <v>89.27021174804459</v>
       </c>
       <c r="D222" t="n">
-        <v>87.61979586629964</v>
+        <v>87.61978830304847</v>
       </c>
       <c r="E222" t="n">
-        <v>89.27021945375864</v>
+        <v>89.27021174804459</v>
       </c>
       <c r="F222" t="n">
         <v>454533</v>
@@ -4872,16 +4872,16 @@
         <v>43546</v>
       </c>
       <c r="B223" t="n">
-        <v>87.82608795166016</v>
+        <v>87.82609558105469</v>
       </c>
       <c r="C223" t="n">
-        <v>87.94397051917699</v>
+        <v>87.9439781588119</v>
       </c>
       <c r="D223" t="n">
-        <v>86.55879788531681</v>
+        <v>86.55880540462269</v>
       </c>
       <c r="E223" t="n">
-        <v>87.94397051917699</v>
+        <v>87.9439781588119</v>
       </c>
       <c r="F223" t="n">
         <v>257266</v>
@@ -4892,16 +4892,16 @@
         <v>43549</v>
       </c>
       <c r="B224" t="n">
-        <v>87.5313720703125</v>
+        <v>87.53139495849609</v>
       </c>
       <c r="C224" t="n">
-        <v>87.64926214035084</v>
+        <v>87.64928505936099</v>
       </c>
       <c r="D224" t="n">
-        <v>85.79253663394098</v>
+        <v>85.79255906744434</v>
       </c>
       <c r="E224" t="n">
-        <v>86.7945759964966</v>
+        <v>86.79459869201872</v>
       </c>
       <c r="F224" t="n">
         <v>451333</v>
@@ -4912,16 +4912,16 @@
         <v>43550</v>
       </c>
       <c r="B225" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494140625</v>
       </c>
       <c r="C225" t="n">
-        <v>89.62387506752287</v>
+        <v>89.62388270193819</v>
       </c>
       <c r="D225" t="n">
-        <v>86.76511004398911</v>
+        <v>86.76511743488673</v>
       </c>
       <c r="E225" t="n">
-        <v>88.20923162596166</v>
+        <v>88.20923913987366</v>
       </c>
       <c r="F225" t="n">
         <v>883933</v>
@@ -4972,16 +4972,16 @@
         <v>43553</v>
       </c>
       <c r="B228" t="n">
-        <v>90.65540313720703</v>
+        <v>90.65538787841797</v>
       </c>
       <c r="C228" t="n">
-        <v>91.80480340897347</v>
+        <v>91.80478795672153</v>
       </c>
       <c r="D228" t="n">
-        <v>88.68078722501544</v>
+        <v>88.68077229858658</v>
       </c>
       <c r="E228" t="n">
-        <v>90.7732932272902</v>
+        <v>90.7732779486583</v>
       </c>
       <c r="F228" t="n">
         <v>379666</v>
@@ -4992,16 +4992,16 @@
         <v>43556</v>
       </c>
       <c r="B229" t="n">
-        <v>90.89115905761719</v>
+        <v>90.89116668701172</v>
       </c>
       <c r="C229" t="n">
-        <v>91.62795512080989</v>
+        <v>91.62796281205101</v>
       </c>
       <c r="D229" t="n">
-        <v>89.91859035282442</v>
+        <v>89.91859790058164</v>
       </c>
       <c r="E229" t="n">
-        <v>91.12693919429439</v>
+        <v>91.12694684348028</v>
       </c>
       <c r="F229" t="n">
         <v>342733</v>
@@ -5072,16 +5072,16 @@
         <v>43560</v>
       </c>
       <c r="B233" t="n">
-        <v>84.73155212402344</v>
+        <v>84.73155975341797</v>
       </c>
       <c r="C233" t="n">
-        <v>87.94397984584793</v>
+        <v>87.94398776449573</v>
       </c>
       <c r="D233" t="n">
-        <v>84.4368306838219</v>
+        <v>84.43683828667913</v>
       </c>
       <c r="E233" t="n">
-        <v>87.08930116040308</v>
+        <v>87.08930900209394</v>
       </c>
       <c r="F233" t="n">
         <v>673866</v>
@@ -5092,16 +5092,16 @@
         <v>43563</v>
       </c>
       <c r="B234" t="n">
-        <v>82.52117919921875</v>
+        <v>82.52116394042969</v>
       </c>
       <c r="C234" t="n">
-        <v>85.88096826779656</v>
+        <v>85.88095238775713</v>
       </c>
       <c r="D234" t="n">
-        <v>82.25592835454846</v>
+        <v>82.25591314480629</v>
       </c>
       <c r="E234" t="n">
-        <v>85.02628192786193</v>
+        <v>85.02626620586047</v>
       </c>
       <c r="F234" t="n">
         <v>619400</v>
@@ -5112,16 +5112,16 @@
         <v>43564</v>
       </c>
       <c r="B235" t="n">
-        <v>82.81587982177734</v>
+        <v>82.81587219238281</v>
       </c>
       <c r="C235" t="n">
-        <v>84.05369940843848</v>
+        <v>84.05369166501009</v>
       </c>
       <c r="D235" t="n">
-        <v>80.90021289784276</v>
+        <v>80.90020544492863</v>
       </c>
       <c r="E235" t="n">
-        <v>82.22644442172653</v>
+        <v>82.2264368466336</v>
       </c>
       <c r="F235" t="n">
         <v>535633</v>
@@ -5132,16 +5132,16 @@
         <v>43565</v>
       </c>
       <c r="B236" t="n">
-        <v>83.40531158447266</v>
+        <v>83.40533447265625</v>
       </c>
       <c r="C236" t="n">
-        <v>84.2305195353845</v>
+        <v>84.23054265002264</v>
       </c>
       <c r="D236" t="n">
-        <v>81.60752748345887</v>
+        <v>81.60754987829243</v>
       </c>
       <c r="E236" t="n">
-        <v>83.64108421400793</v>
+        <v>83.64110716689252</v>
       </c>
       <c r="F236" t="n">
         <v>456233</v>
@@ -5152,16 +5152,16 @@
         <v>43566</v>
       </c>
       <c r="B237" t="n">
-        <v>84.34842681884766</v>
+        <v>84.34841918945312</v>
       </c>
       <c r="C237" t="n">
-        <v>84.61367014434416</v>
+        <v>84.61366249095812</v>
       </c>
       <c r="D237" t="n">
-        <v>82.40328161658626</v>
+        <v>82.40327416313194</v>
       </c>
       <c r="E237" t="n">
-        <v>83.78846202495211</v>
+        <v>83.78845444620694</v>
       </c>
       <c r="F237" t="n">
         <v>403133</v>
@@ -5172,16 +5172,16 @@
         <v>43567</v>
       </c>
       <c r="B238" t="n">
-        <v>82.72747039794922</v>
+        <v>82.72747802734375</v>
       </c>
       <c r="C238" t="n">
-        <v>84.73155681507157</v>
+        <v>84.73156462928944</v>
       </c>
       <c r="D238" t="n">
-        <v>82.34433700152209</v>
+        <v>82.34434459558283</v>
       </c>
       <c r="E238" t="n">
-        <v>84.34842341864444</v>
+        <v>84.3484311975285</v>
       </c>
       <c r="F238" t="n">
         <v>343366</v>
@@ -5192,16 +5192,16 @@
         <v>43570</v>
       </c>
       <c r="B239" t="n">
-        <v>83.96527862548828</v>
+        <v>83.96529388427734</v>
       </c>
       <c r="C239" t="n">
-        <v>84.37788261254832</v>
+        <v>84.37789794631881</v>
       </c>
       <c r="D239" t="n">
-        <v>82.5800984609735</v>
+        <v>82.58011346803741</v>
       </c>
       <c r="E239" t="n">
-        <v>82.81587109713966</v>
+        <v>82.81588614704992</v>
       </c>
       <c r="F239" t="n">
         <v>210900</v>
@@ -5212,16 +5212,16 @@
         <v>43571</v>
       </c>
       <c r="B240" t="n">
-        <v>83.58216094970703</v>
+        <v>83.5821533203125</v>
       </c>
       <c r="C240" t="n">
-        <v>84.40736907852389</v>
+        <v>84.40736137380419</v>
       </c>
       <c r="D240" t="n">
-        <v>82.58011394176843</v>
+        <v>82.58010640384093</v>
       </c>
       <c r="E240" t="n">
-        <v>83.11060809389856</v>
+        <v>83.11060050754746</v>
       </c>
       <c r="F240" t="n">
         <v>215300</v>
@@ -5232,16 +5232,16 @@
         <v>43572</v>
       </c>
       <c r="B241" t="n">
-        <v>82.66851806640625</v>
+        <v>82.66852569580078</v>
       </c>
       <c r="C241" t="n">
-        <v>84.23052209018523</v>
+        <v>84.23052986373555</v>
       </c>
       <c r="D241" t="n">
-        <v>81.46016925011853</v>
+        <v>81.46017676799576</v>
       </c>
       <c r="E241" t="n">
-        <v>84.20105144748405</v>
+        <v>84.20105921831454</v>
       </c>
       <c r="F241" t="n">
         <v>289766</v>
@@ -5272,16 +5272,16 @@
         <v>43577</v>
       </c>
       <c r="B243" t="n">
-        <v>84.58419799804688</v>
+        <v>84.58418273925781</v>
       </c>
       <c r="C243" t="n">
-        <v>86.26409234997288</v>
+        <v>86.26407678813486</v>
       </c>
       <c r="D243" t="n">
-        <v>82.31486821484337</v>
+        <v>82.31485336543604</v>
       </c>
       <c r="E243" t="n">
-        <v>83.49373907739835</v>
+        <v>83.4937240153255</v>
       </c>
       <c r="F243" t="n">
         <v>461666</v>
@@ -5312,16 +5312,16 @@
         <v>43579</v>
       </c>
       <c r="B245" t="n">
-        <v>86.51291656494141</v>
+        <v>86.51290893554688</v>
       </c>
       <c r="C245" t="n">
-        <v>87.07526500452914</v>
+        <v>87.07525732554228</v>
       </c>
       <c r="D245" t="n">
-        <v>85.06264755574588</v>
+        <v>85.06264005424757</v>
       </c>
       <c r="E245" t="n">
-        <v>86.27613272839055</v>
+        <v>86.27612511987749</v>
       </c>
       <c r="F245" t="n">
         <v>361900</v>
@@ -5332,16 +5332,16 @@
         <v>43580</v>
       </c>
       <c r="B246" t="n">
-        <v>87.90397644042969</v>
+        <v>87.90399169921875</v>
       </c>
       <c r="C246" t="n">
-        <v>88.55512063075771</v>
+        <v>88.55513600257547</v>
       </c>
       <c r="D246" t="n">
-        <v>84.88505435395487</v>
+        <v>84.88506908870511</v>
       </c>
       <c r="E246" t="n">
-        <v>87.01605596588345</v>
+        <v>87.01607107054306</v>
       </c>
       <c r="F246" t="n">
         <v>486633</v>
@@ -5352,16 +5352,16 @@
         <v>43581</v>
       </c>
       <c r="B247" t="n">
-        <v>87.46003723144531</v>
+        <v>87.46002960205078</v>
       </c>
       <c r="C247" t="n">
-        <v>87.66721746190686</v>
+        <v>87.66720981443939</v>
       </c>
       <c r="D247" t="n">
-        <v>86.15775612069856</v>
+        <v>86.15774860490582</v>
       </c>
       <c r="E247" t="n">
-        <v>87.43044113094849</v>
+        <v>87.43043350413572</v>
       </c>
       <c r="F247" t="n">
         <v>187233</v>
@@ -5412,16 +5412,16 @@
         <v>43587</v>
       </c>
       <c r="B250" t="n">
-        <v>89.82779693603516</v>
+        <v>89.82781219482422</v>
       </c>
       <c r="C250" t="n">
-        <v>90.41974893094701</v>
+        <v>90.41976429028925</v>
       </c>
       <c r="D250" t="n">
-        <v>88.64390800017603</v>
+        <v>88.64392305786127</v>
       </c>
       <c r="E250" t="n">
-        <v>88.64390800017603</v>
+        <v>88.64392305786127</v>
       </c>
       <c r="F250" t="n">
         <v>415166</v>
@@ -5432,16 +5432,16 @@
         <v>43588</v>
       </c>
       <c r="B251" t="n">
-        <v>90.21258544921875</v>
+        <v>90.21257781982422</v>
       </c>
       <c r="C251" t="n">
-        <v>90.89331832625483</v>
+        <v>90.89331063928984</v>
       </c>
       <c r="D251" t="n">
-        <v>88.91030436782248</v>
+        <v>88.91029684856353</v>
       </c>
       <c r="E251" t="n">
-        <v>88.91030436782248</v>
+        <v>88.91029684856353</v>
       </c>
       <c r="F251" t="n">
         <v>248400</v>
@@ -5472,16 +5472,16 @@
         <v>43592</v>
       </c>
       <c r="B253" t="n">
-        <v>96.93117523193359</v>
+        <v>96.93115997314453</v>
       </c>
       <c r="C253" t="n">
-        <v>97.64151176619497</v>
+        <v>97.64149639558559</v>
       </c>
       <c r="D253" t="n">
-        <v>89.47265667615709</v>
+        <v>89.47264259147906</v>
       </c>
       <c r="E253" t="n">
-        <v>90.83413001550207</v>
+        <v>90.83411571650254</v>
       </c>
       <c r="F253" t="n">
         <v>3210933</v>
@@ -5492,16 +5492,16 @@
         <v>43593</v>
       </c>
       <c r="B254" t="n">
-        <v>102.3474731445312</v>
+        <v>102.3474655151367</v>
       </c>
       <c r="C254" t="n">
-        <v>104.4488865051489</v>
+        <v>104.4488787191065</v>
       </c>
       <c r="D254" t="n">
-        <v>98.88458653596543</v>
+        <v>98.88457916470847</v>
       </c>
       <c r="E254" t="n">
-        <v>100.6308316532951</v>
+        <v>100.630824151866</v>
       </c>
       <c r="F254" t="n">
         <v>1898166</v>
@@ -5532,16 +5532,16 @@
         <v>43595</v>
       </c>
       <c r="B256" t="n">
-        <v>103.5905609130859</v>
+        <v>103.5905456542969</v>
       </c>
       <c r="C256" t="n">
-        <v>105.218414089974</v>
+        <v>105.2183985914037</v>
       </c>
       <c r="D256" t="n">
-        <v>101.3411670804334</v>
+        <v>101.3411521529779</v>
       </c>
       <c r="E256" t="n">
-        <v>105.218414089974</v>
+        <v>105.2183985914037</v>
       </c>
       <c r="F256" t="n">
         <v>440400</v>
@@ -5572,16 +5572,16 @@
         <v>43599</v>
       </c>
       <c r="B258" t="n">
-        <v>103.028205871582</v>
+        <v>103.0282135009766</v>
       </c>
       <c r="C258" t="n">
-        <v>104.4192751152107</v>
+        <v>104.419282847616</v>
       </c>
       <c r="D258" t="n">
-        <v>101.8147132094106</v>
+        <v>101.8147207489442</v>
       </c>
       <c r="E258" t="n">
-        <v>102.6730376547018</v>
+        <v>102.6730452577955</v>
       </c>
       <c r="F258" t="n">
         <v>522566</v>
@@ -5592,16 +5592,16 @@
         <v>43600</v>
       </c>
       <c r="B259" t="n">
-        <v>103.5905609130859</v>
+        <v>103.5905456542969</v>
       </c>
       <c r="C259" t="n">
-        <v>104.3304934910366</v>
+        <v>104.3304781232561</v>
       </c>
       <c r="D259" t="n">
-        <v>100.9267991162737</v>
+        <v>100.9267842498542</v>
       </c>
       <c r="E259" t="n">
-        <v>101.6075394966229</v>
+        <v>101.607524529931</v>
       </c>
       <c r="F259" t="n">
         <v>328866</v>
@@ -5612,16 +5612,16 @@
         <v>43601</v>
       </c>
       <c r="B260" t="n">
-        <v>102.5842437744141</v>
+        <v>102.5842361450195</v>
       </c>
       <c r="C260" t="n">
-        <v>103.6793445426467</v>
+        <v>103.6793368318073</v>
       </c>
       <c r="D260" t="n">
-        <v>102.5842437744141</v>
+        <v>102.5842361450195</v>
       </c>
       <c r="E260" t="n">
-        <v>103.5905562502412</v>
+        <v>103.5905485460052</v>
       </c>
       <c r="F260" t="n">
         <v>583833</v>
@@ -5652,16 +5652,16 @@
         <v>43605</v>
       </c>
       <c r="B262" t="n">
-        <v>105.070426940918</v>
+        <v>105.0704193115234</v>
       </c>
       <c r="C262" t="n">
-        <v>105.8991478221478</v>
+        <v>105.899140132578</v>
       </c>
       <c r="D262" t="n">
-        <v>103.590561772736</v>
+        <v>103.5905542507978</v>
       </c>
       <c r="E262" t="n">
-        <v>103.590561772736</v>
+        <v>103.5905542507978</v>
       </c>
       <c r="F262" t="n">
         <v>597600</v>
@@ -5712,16 +5712,16 @@
         <v>43608</v>
       </c>
       <c r="B265" t="n">
-        <v>110.989875793457</v>
+        <v>110.9898834228516</v>
       </c>
       <c r="C265" t="n">
-        <v>112.4697408040365</v>
+        <v>112.4697485351563</v>
       </c>
       <c r="D265" t="n">
-        <v>109.1844386740743</v>
+        <v>109.1844461793639</v>
       </c>
       <c r="E265" t="n">
-        <v>109.3324266805288</v>
+        <v>109.332434195991</v>
       </c>
       <c r="F265" t="n">
         <v>449966</v>
@@ -5732,16 +5732,16 @@
         <v>43609</v>
       </c>
       <c r="B266" t="n">
-        <v>110.3979339599609</v>
+        <v>110.3979415893555</v>
       </c>
       <c r="C266" t="n">
-        <v>111.9073951028777</v>
+        <v>111.9074028365882</v>
       </c>
       <c r="D266" t="n">
-        <v>109.9539699298789</v>
+        <v>109.9539775285919</v>
       </c>
       <c r="E266" t="n">
-        <v>111.1970586763327</v>
+        <v>111.1970663609532</v>
       </c>
       <c r="F266" t="n">
         <v>294000</v>
@@ -5752,16 +5752,16 @@
         <v>43612</v>
       </c>
       <c r="B267" t="n">
-        <v>109.9539794921875</v>
+        <v>109.953987121582</v>
       </c>
       <c r="C267" t="n">
-        <v>111.7298207129887</v>
+        <v>111.7298284656038</v>
       </c>
       <c r="D267" t="n">
-        <v>109.6876070725591</v>
+        <v>109.6876146834708</v>
       </c>
       <c r="E267" t="n">
-        <v>110.0427753167193</v>
+        <v>110.0427829522751</v>
       </c>
       <c r="F267" t="n">
         <v>77066</v>
@@ -5772,16 +5772,16 @@
         <v>43613</v>
       </c>
       <c r="B268" t="n">
-        <v>109.3028335571289</v>
+        <v>109.3028411865234</v>
       </c>
       <c r="C268" t="n">
-        <v>111.0786671019285</v>
+        <v>111.0786748552771</v>
       </c>
       <c r="D268" t="n">
-        <v>107.0830359808923</v>
+        <v>107.0830434553438</v>
       </c>
       <c r="E268" t="n">
-        <v>110.5755184040759</v>
+        <v>110.5755261223044</v>
       </c>
       <c r="F268" t="n">
         <v>402233</v>
@@ -5812,16 +5812,16 @@
         <v>43615</v>
       </c>
       <c r="B270" t="n">
-        <v>107.70458984375</v>
+        <v>107.7045822143555</v>
       </c>
       <c r="C270" t="n">
-        <v>111.6410292556999</v>
+        <v>111.6410213474626</v>
       </c>
       <c r="D270" t="n">
-        <v>107.70458984375</v>
+        <v>107.7045822143555</v>
       </c>
       <c r="E270" t="n">
-        <v>109.9243876930951</v>
+        <v>109.9243799064583</v>
       </c>
       <c r="F270" t="n">
         <v>452966</v>
@@ -5852,16 +5852,16 @@
         <v>43619</v>
       </c>
       <c r="B272" t="n">
-        <v>109.8651962280273</v>
+        <v>109.8651885986328</v>
       </c>
       <c r="C272" t="n">
-        <v>110.7531168791073</v>
+        <v>110.7531091880527</v>
       </c>
       <c r="D272" t="n">
-        <v>108.6221073165154</v>
+        <v>108.622099773445</v>
       </c>
       <c r="E272" t="n">
-        <v>108.7996914467314</v>
+        <v>108.7996838913289</v>
       </c>
       <c r="F272" t="n">
         <v>294000</v>
@@ -5872,16 +5872,16 @@
         <v>43620</v>
       </c>
       <c r="B273" t="n">
-        <v>107.1718215942383</v>
+        <v>107.1718292236328</v>
       </c>
       <c r="C273" t="n">
-        <v>110.9898760397184</v>
+        <v>110.9898839409142</v>
       </c>
       <c r="D273" t="n">
-        <v>107.1718215942383</v>
+        <v>107.1718292236328</v>
       </c>
       <c r="E273" t="n">
-        <v>109.5987993137355</v>
+        <v>109.5988071159028</v>
       </c>
       <c r="F273" t="n">
         <v>283866</v>
@@ -5892,16 +5892,16 @@
         <v>43621</v>
       </c>
       <c r="B274" t="n">
-        <v>108.8884658813477</v>
+        <v>108.8884735107422</v>
       </c>
       <c r="C274" t="n">
-        <v>109.83557854742</v>
+        <v>109.835586243175</v>
       </c>
       <c r="D274" t="n">
-        <v>106.4022885467982</v>
+        <v>106.4022960019959</v>
       </c>
       <c r="E274" t="n">
-        <v>106.6390648315707</v>
+        <v>106.6390723033584</v>
       </c>
       <c r="F274" t="n">
         <v>231033</v>
@@ -5912,16 +5912,16 @@
         <v>43622</v>
       </c>
       <c r="B275" t="n">
-        <v>108.7404937744141</v>
+        <v>108.7405014038086</v>
       </c>
       <c r="C275" t="n">
-        <v>109.6876065789178</v>
+        <v>109.6876142747631</v>
       </c>
       <c r="D275" t="n">
-        <v>108.05975338834</v>
+        <v>108.0597609699728</v>
       </c>
       <c r="E275" t="n">
-        <v>109.5100224576369</v>
+        <v>109.5100301410227</v>
       </c>
       <c r="F275" t="n">
         <v>227300</v>
@@ -5932,16 +5932,16 @@
         <v>43623</v>
       </c>
       <c r="B276" t="n">
-        <v>110.6051254272461</v>
+        <v>110.605110168457</v>
       </c>
       <c r="C276" t="n">
-        <v>110.664317626492</v>
+        <v>110.664302359537</v>
       </c>
       <c r="D276" t="n">
-        <v>108.9180800058842</v>
+        <v>108.9180649798354</v>
       </c>
       <c r="E276" t="n">
-        <v>109.2140485290975</v>
+        <v>109.2140334622177</v>
       </c>
       <c r="F276" t="n">
         <v>204266</v>
@@ -5952,16 +5952,16 @@
         <v>43626</v>
       </c>
       <c r="B277" t="n">
-        <v>114.3935775756836</v>
+        <v>114.3935699462891</v>
       </c>
       <c r="C277" t="n">
-        <v>119.3955216779974</v>
+        <v>119.395513715002</v>
       </c>
       <c r="D277" t="n">
-        <v>111.8778112380962</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="E277" t="n">
-        <v>111.8778112380962</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="F277" t="n">
         <v>585833</v>
@@ -5972,16 +5972,16 @@
         <v>43627</v>
       </c>
       <c r="B278" t="n">
-        <v>110.989875793457</v>
+        <v>110.9898834228516</v>
       </c>
       <c r="C278" t="n">
-        <v>116.6725595416372</v>
+        <v>116.6725675616569</v>
       </c>
       <c r="D278" t="n">
-        <v>110.989875793457</v>
+        <v>110.9898834228516</v>
       </c>
       <c r="E278" t="n">
-        <v>116.4653718164113</v>
+        <v>116.465379822189</v>
       </c>
       <c r="F278" t="n">
         <v>422033</v>
@@ -5992,16 +5992,16 @@
         <v>43628</v>
       </c>
       <c r="B279" t="n">
-        <v>108.9180679321289</v>
+        <v>108.918083190918</v>
       </c>
       <c r="C279" t="n">
-        <v>111.7594060857212</v>
+        <v>111.7594217425652</v>
       </c>
       <c r="D279" t="n">
-        <v>108.7996760197774</v>
+        <v>108.7996912619804</v>
       </c>
       <c r="E279" t="n">
-        <v>111.7594060857212</v>
+        <v>111.7594217425652</v>
       </c>
       <c r="F279" t="n">
         <v>382266</v>
@@ -6052,16 +6052,16 @@
         <v>43633</v>
       </c>
       <c r="B282" t="n">
-        <v>110.0723648071289</v>
+        <v>110.0723724365234</v>
       </c>
       <c r="C282" t="n">
-        <v>113.1504868960452</v>
+        <v>113.1504947387922</v>
       </c>
       <c r="D282" t="n">
-        <v>109.066052333433</v>
+        <v>109.0660598930775</v>
       </c>
       <c r="E282" t="n">
-        <v>113.1504868960452</v>
+        <v>113.1504947387922</v>
       </c>
       <c r="F282" t="n">
         <v>481366</v>
@@ -6072,16 +6072,16 @@
         <v>43634</v>
       </c>
       <c r="B283" t="n">
-        <v>112.4697494506836</v>
+        <v>112.4697418212891</v>
       </c>
       <c r="C283" t="n">
-        <v>113.1800859146894</v>
+        <v>113.1800782371092</v>
       </c>
       <c r="D283" t="n">
-        <v>110.0131754518161</v>
+        <v>110.0131679890634</v>
       </c>
       <c r="E283" t="n">
-        <v>110.9602882281628</v>
+        <v>110.9602807011627</v>
       </c>
       <c r="F283" t="n">
         <v>583133</v>
@@ -6092,16 +6092,16 @@
         <v>43635</v>
       </c>
       <c r="B284" t="n">
-        <v>115.3702850341797</v>
+        <v>115.3702774047852</v>
       </c>
       <c r="C284" t="n">
-        <v>115.3702850341797</v>
+        <v>115.3702774047852</v>
       </c>
       <c r="D284" t="n">
-        <v>111.6114225804171</v>
+        <v>111.6114151995947</v>
       </c>
       <c r="E284" t="n">
-        <v>112.3513551267584</v>
+        <v>112.3513476970046</v>
       </c>
       <c r="F284" t="n">
         <v>441733</v>
@@ -6132,16 +6132,16 @@
         <v>43640</v>
       </c>
       <c r="B286" t="n">
-        <v>116.5245742797852</v>
+        <v>116.5245590209961</v>
       </c>
       <c r="C286" t="n">
-        <v>117.5012831022177</v>
+        <v>117.5012677155295</v>
       </c>
       <c r="D286" t="n">
-        <v>115.0447092343492</v>
+        <v>115.0446941693472</v>
       </c>
       <c r="E286" t="n">
-        <v>116.6133625695595</v>
+        <v>116.6133472991437</v>
       </c>
       <c r="F286" t="n">
         <v>315633</v>
@@ -6152,16 +6152,16 @@
         <v>43641</v>
       </c>
       <c r="B287" t="n">
-        <v>114.4823684692383</v>
+        <v>114.4823760986328</v>
       </c>
       <c r="C287" t="n">
-        <v>117.1165266196842</v>
+        <v>117.1165344246257</v>
       </c>
       <c r="D287" t="n">
-        <v>113.8312241927775</v>
+        <v>113.8312317787781</v>
       </c>
       <c r="E287" t="n">
-        <v>116.5837742644845</v>
+        <v>116.583782033922</v>
       </c>
       <c r="F287" t="n">
         <v>481433</v>
@@ -6192,16 +6192,16 @@
         <v>43643</v>
       </c>
       <c r="B289" t="n">
-        <v>115.281494140625</v>
+        <v>115.2814865112305</v>
       </c>
       <c r="C289" t="n">
-        <v>115.281494140625</v>
+        <v>115.2814865112305</v>
       </c>
       <c r="D289" t="n">
-        <v>112.9137083857593</v>
+        <v>112.9137009130662</v>
       </c>
       <c r="E289" t="n">
-        <v>113.3872685475258</v>
+        <v>113.3872610434922</v>
       </c>
       <c r="F289" t="n">
         <v>276700</v>
@@ -6212,16 +6212,16 @@
         <v>43644</v>
       </c>
       <c r="B290" t="n">
-        <v>116.7021636962891</v>
+        <v>116.7021560668945</v>
       </c>
       <c r="C290" t="n">
-        <v>117.6492764652239</v>
+        <v>117.649268773912</v>
       </c>
       <c r="D290" t="n">
-        <v>114.1271977979104</v>
+        <v>114.1271903368541</v>
       </c>
       <c r="E290" t="n">
-        <v>115.0743105668453</v>
+        <v>115.0743030438715</v>
       </c>
       <c r="F290" t="n">
         <v>617600</v>
@@ -6232,16 +6232,16 @@
         <v>43647</v>
       </c>
       <c r="B291" t="n">
-        <v>114.0680084228516</v>
+        <v>114.068000793457</v>
       </c>
       <c r="C291" t="n">
-        <v>117.0573348202537</v>
+        <v>117.0573269909192</v>
       </c>
       <c r="D291" t="n">
-        <v>114.0680084228516</v>
+        <v>114.068000793457</v>
       </c>
       <c r="E291" t="n">
-        <v>117.0573348202537</v>
+        <v>117.0573269909192</v>
       </c>
       <c r="F291" t="n">
         <v>436066</v>
@@ -6252,16 +6252,16 @@
         <v>43648</v>
       </c>
       <c r="B292" t="n">
-        <v>110.1315536499023</v>
+        <v>110.1315765380859</v>
       </c>
       <c r="C292" t="n">
-        <v>115.1334971877844</v>
+        <v>115.1335211155011</v>
       </c>
       <c r="D292" t="n">
-        <v>110.1315536499023</v>
+        <v>110.1315765380859</v>
       </c>
       <c r="E292" t="n">
-        <v>113.9792042621922</v>
+        <v>113.9792279500171</v>
       </c>
       <c r="F292" t="n">
         <v>537533</v>
@@ -6272,16 +6272,16 @@
         <v>43649</v>
       </c>
       <c r="B293" t="n">
-        <v>109.9691619873047</v>
+        <v>109.9691696166992</v>
       </c>
       <c r="C293" t="n">
-        <v>110.8608053529641</v>
+        <v>110.8608130442187</v>
       </c>
       <c r="D293" t="n">
-        <v>107.323959634633</v>
+        <v>107.3239670805098</v>
       </c>
       <c r="E293" t="n">
-        <v>110.7121968655973</v>
+        <v>110.7122045465418</v>
       </c>
       <c r="F293" t="n">
         <v>1690900</v>
@@ -6312,16 +6312,16 @@
         <v>43651</v>
       </c>
       <c r="B295" t="n">
-        <v>117.5183944702148</v>
+        <v>117.5184020996094</v>
       </c>
       <c r="C295" t="n">
-        <v>117.5183944702148</v>
+        <v>117.5184020996094</v>
       </c>
       <c r="D295" t="n">
-        <v>112.9115768934796</v>
+        <v>112.9115842237956</v>
       </c>
       <c r="E295" t="n">
-        <v>114.0707094441784</v>
+        <v>114.0707168497463</v>
       </c>
       <c r="F295" t="n">
         <v>288866</v>
@@ -6372,16 +6372,16 @@
         <v>43657</v>
       </c>
       <c r="B298" t="n">
-        <v>123.1654663085938</v>
+        <v>123.1654586791992</v>
       </c>
       <c r="C298" t="n">
-        <v>130.1797101104775</v>
+        <v>130.1797020465908</v>
       </c>
       <c r="D298" t="n">
-        <v>123.1060259345613</v>
+        <v>123.1060183088487</v>
       </c>
       <c r="E298" t="n">
-        <v>130.1797101104775</v>
+        <v>130.1797020465908</v>
       </c>
       <c r="F298" t="n">
         <v>660700</v>
@@ -6392,16 +6392,16 @@
         <v>43658</v>
       </c>
       <c r="B299" t="n">
-        <v>124.8001556396484</v>
+        <v>124.8001480102539</v>
       </c>
       <c r="C299" t="n">
-        <v>125.8701202594071</v>
+        <v>125.8701125646025</v>
       </c>
       <c r="D299" t="n">
-        <v>122.7196592208688</v>
+        <v>122.7196517186611</v>
       </c>
       <c r="E299" t="n">
-        <v>124.2057291712175</v>
+        <v>124.205721578162</v>
       </c>
       <c r="F299" t="n">
         <v>362933</v>
@@ -6412,16 +6412,16 @@
         <v>43661</v>
       </c>
       <c r="B300" t="n">
-        <v>121.5605010986328</v>
+        <v>121.5605163574219</v>
       </c>
       <c r="C300" t="n">
-        <v>126.7320249772505</v>
+        <v>126.7320408851911</v>
       </c>
       <c r="D300" t="n">
-        <v>118.5289212629776</v>
+        <v>118.5289361412299</v>
       </c>
       <c r="E300" t="n">
-        <v>124.9784660186075</v>
+        <v>124.978481706434</v>
       </c>
       <c r="F300" t="n">
         <v>1110366</v>
@@ -6452,16 +6452,16 @@
         <v>43663</v>
       </c>
       <c r="B302" t="n">
-        <v>126.6131362915039</v>
+        <v>126.6131439208984</v>
       </c>
       <c r="C302" t="n">
-        <v>127.9505975350065</v>
+        <v>127.9506052449931</v>
       </c>
       <c r="D302" t="n">
-        <v>122.7493610455057</v>
+        <v>122.7493684420787</v>
       </c>
       <c r="E302" t="n">
-        <v>123.9679339896924</v>
+        <v>123.9679414596935</v>
       </c>
       <c r="F302" t="n">
         <v>443966</v>
@@ -6472,16 +6472,16 @@
         <v>43664</v>
       </c>
       <c r="B303" t="n">
-        <v>129.8825073242188</v>
+        <v>129.8825225830078</v>
       </c>
       <c r="C303" t="n">
-        <v>129.8825073242188</v>
+        <v>129.8825225830078</v>
       </c>
       <c r="D303" t="n">
-        <v>127.5047865601033</v>
+        <v>127.5048015395542</v>
       </c>
       <c r="E303" t="n">
-        <v>127.7722833584466</v>
+        <v>127.7722983693234</v>
       </c>
       <c r="F303" t="n">
         <v>405966</v>
@@ -6512,16 +6512,16 @@
         <v>43668</v>
       </c>
       <c r="B305" t="n">
-        <v>127.4453582763672</v>
+        <v>127.4453430175781</v>
       </c>
       <c r="C305" t="n">
-        <v>129.0800291741361</v>
+        <v>129.080013719631</v>
       </c>
       <c r="D305" t="n">
-        <v>126.0781766437745</v>
+        <v>126.0781615486755</v>
       </c>
       <c r="E305" t="n">
-        <v>126.3456659089508</v>
+        <v>126.3456507818258</v>
       </c>
       <c r="F305" t="n">
         <v>163233</v>
@@ -6532,16 +6532,16 @@
         <v>43669</v>
       </c>
       <c r="B306" t="n">
-        <v>125.0676345825195</v>
+        <v>125.0676422119141</v>
       </c>
       <c r="C306" t="n">
-        <v>127.8020051818723</v>
+        <v>127.8020129780693</v>
       </c>
       <c r="D306" t="n">
-        <v>123.6410051291977</v>
+        <v>123.6410126715648</v>
       </c>
       <c r="E306" t="n">
-        <v>127.475068005729</v>
+        <v>127.4750757819822</v>
       </c>
       <c r="F306" t="n">
         <v>528700</v>
@@ -6592,16 +6592,16 @@
         <v>43672</v>
       </c>
       <c r="B309" t="n">
-        <v>125.6620635986328</v>
+        <v>125.6620483398438</v>
       </c>
       <c r="C309" t="n">
-        <v>127.9208885740418</v>
+        <v>127.92087304097</v>
       </c>
       <c r="D309" t="n">
-        <v>125.0676371669792</v>
+        <v>125.0676219803697</v>
       </c>
       <c r="E309" t="n">
-        <v>127.2075738326406</v>
+        <v>127.2075583861846</v>
       </c>
       <c r="F309" t="n">
         <v>1585266</v>
@@ -6612,16 +6612,16 @@
         <v>43675</v>
       </c>
       <c r="B310" t="n">
-        <v>126.0187072753906</v>
+        <v>126.0187149047852</v>
       </c>
       <c r="C310" t="n">
-        <v>126.8806228621377</v>
+        <v>126.8806305437141</v>
       </c>
       <c r="D310" t="n">
-        <v>125.0081832072433</v>
+        <v>125.0081907754589</v>
       </c>
       <c r="E310" t="n">
-        <v>126.6131336424503</v>
+        <v>126.6131413078325</v>
       </c>
       <c r="F310" t="n">
         <v>708133</v>
@@ -6632,16 +6632,16 @@
         <v>43676</v>
       </c>
       <c r="B311" t="n">
-        <v>124.384033203125</v>
+        <v>124.3840408325195</v>
       </c>
       <c r="C311" t="n">
-        <v>126.3753687791254</v>
+        <v>126.3753765306633</v>
       </c>
       <c r="D311" t="n">
-        <v>124.2948726464664</v>
+        <v>124.294880270392</v>
       </c>
       <c r="E311" t="n">
-        <v>126.2267602928194</v>
+        <v>126.2267680352421</v>
       </c>
       <c r="F311" t="n">
         <v>1065500</v>
@@ -6672,16 +6672,16 @@
         <v>43678</v>
       </c>
       <c r="B313" t="n">
-        <v>122.6601867675781</v>
+        <v>122.6601943969727</v>
       </c>
       <c r="C313" t="n">
-        <v>126.5834097453589</v>
+        <v>126.5834176187757</v>
       </c>
       <c r="D313" t="n">
-        <v>121.7982712061099</v>
+        <v>121.7982787818937</v>
       </c>
       <c r="E313" t="n">
-        <v>124.6515222194392</v>
+        <v>124.6515299726937</v>
       </c>
       <c r="F313" t="n">
         <v>895666</v>
@@ -6712,16 +6712,16 @@
         <v>43682</v>
       </c>
       <c r="B315" t="n">
-        <v>123.4032287597656</v>
+        <v>123.4032440185547</v>
       </c>
       <c r="C315" t="n">
-        <v>124.3543124861009</v>
+        <v>124.3543278624913</v>
       </c>
       <c r="D315" t="n">
-        <v>121.8577186492884</v>
+        <v>121.8577337169754</v>
       </c>
       <c r="E315" t="n">
-        <v>124.0571030733008</v>
+        <v>124.0571184129413</v>
       </c>
       <c r="F315" t="n">
         <v>384500</v>
@@ -6732,16 +6732,16 @@
         <v>43683</v>
       </c>
       <c r="B316" t="n">
-        <v>126.6131362915039</v>
+        <v>126.6131439208984</v>
       </c>
       <c r="C316" t="n">
-        <v>127.1778424858068</v>
+        <v>127.1778501492292</v>
       </c>
       <c r="D316" t="n">
-        <v>123.1357385701055</v>
+        <v>123.1357459899607</v>
       </c>
       <c r="E316" t="n">
-        <v>123.1951789404927</v>
+        <v>123.1951863639296</v>
       </c>
       <c r="F316" t="n">
         <v>466533</v>
@@ -6772,16 +6772,16 @@
         <v>43685</v>
       </c>
       <c r="B318" t="n">
-        <v>131.903564453125</v>
+        <v>131.9035491943359</v>
       </c>
       <c r="C318" t="n">
-        <v>133.5679554941837</v>
+        <v>133.5679400428555</v>
       </c>
       <c r="D318" t="n">
-        <v>129.2880820192579</v>
+        <v>129.2880670630315</v>
       </c>
       <c r="E318" t="n">
-        <v>129.2880820192579</v>
+        <v>129.2880670630315</v>
       </c>
       <c r="F318" t="n">
         <v>971500</v>
@@ -6832,16 +6832,16 @@
         <v>43690</v>
       </c>
       <c r="B321" t="n">
-        <v>131.0713806152344</v>
+        <v>131.0713348388672</v>
       </c>
       <c r="C321" t="n">
-        <v>133.7760238565671</v>
+        <v>133.7759771356097</v>
       </c>
       <c r="D321" t="n">
-        <v>128.8125553627015</v>
+        <v>128.8125103752236</v>
       </c>
       <c r="E321" t="n">
-        <v>133.6571430907768</v>
+        <v>133.6570964113382</v>
       </c>
       <c r="F321" t="n">
         <v>614133</v>
@@ -6892,16 +6892,16 @@
         <v>43693</v>
       </c>
       <c r="B324" t="n">
-        <v>145.6348266601562</v>
+        <v>145.6348419189453</v>
       </c>
       <c r="C324" t="n">
-        <v>145.6348266601562</v>
+        <v>145.6348419189453</v>
       </c>
       <c r="D324" t="n">
-        <v>137.2236669435527</v>
+        <v>137.2236813210683</v>
       </c>
       <c r="E324" t="n">
-        <v>141.8304919591744</v>
+        <v>141.8305068193669</v>
       </c>
       <c r="F324" t="n">
         <v>930266</v>
@@ -6912,16 +6912,16 @@
         <v>43696</v>
       </c>
       <c r="B325" t="n">
-        <v>141.8899536132812</v>
+        <v>141.8899230957031</v>
       </c>
       <c r="C325" t="n">
-        <v>147.0911982028676</v>
+        <v>147.0911665666099</v>
       </c>
       <c r="D325" t="n">
-        <v>140.730820918795</v>
+        <v>140.7307906505222</v>
       </c>
       <c r="E325" t="n">
-        <v>147.0911982028676</v>
+        <v>147.0911665666099</v>
       </c>
       <c r="F325" t="n">
         <v>598666</v>
@@ -6932,16 +6932,16 @@
         <v>43697</v>
       </c>
       <c r="B326" t="n">
-        <v>145.0106811523438</v>
+        <v>145.0106964111328</v>
       </c>
       <c r="C326" t="n">
-        <v>146.7048073163463</v>
+        <v>146.7048227534003</v>
       </c>
       <c r="D326" t="n">
-        <v>140.4633113521918</v>
+        <v>140.4633261324826</v>
       </c>
       <c r="E326" t="n">
-        <v>143.049073318038</v>
+        <v>143.0490883704163</v>
       </c>
       <c r="F326" t="n">
         <v>506533</v>
@@ -6972,16 +6972,16 @@
         <v>43699</v>
       </c>
       <c r="B328" t="n">
-        <v>148.5475463867188</v>
+        <v>148.5475158691406</v>
       </c>
       <c r="C328" t="n">
-        <v>151.3116296889876</v>
+        <v>151.3115986035568</v>
       </c>
       <c r="D328" t="n">
-        <v>146.8236998981212</v>
+        <v>146.8236697346897</v>
       </c>
       <c r="E328" t="n">
-        <v>148.5772665747045</v>
+        <v>148.5772360510207</v>
       </c>
       <c r="F328" t="n">
         <v>509000</v>
@@ -7012,16 +7012,16 @@
         <v>43703</v>
       </c>
       <c r="B330" t="n">
-        <v>143.5543518066406</v>
+        <v>143.5543365478516</v>
       </c>
       <c r="C330" t="n">
-        <v>146.2292898230444</v>
+        <v>146.2292742799288</v>
       </c>
       <c r="D330" t="n">
-        <v>141.2063661119289</v>
+        <v>141.2063511027138</v>
       </c>
       <c r="E330" t="n">
-        <v>143.3165902884432</v>
+        <v>143.3165750549265</v>
       </c>
       <c r="F330" t="n">
         <v>278200</v>
@@ -7032,16 +7032,16 @@
         <v>43704</v>
       </c>
       <c r="B331" t="n">
-        <v>145.4862060546875</v>
+        <v>145.4862518310547</v>
       </c>
       <c r="C331" t="n">
-        <v>146.4670022225057</v>
+        <v>146.4670483074746</v>
       </c>
       <c r="D331" t="n">
-        <v>141.7710324079088</v>
+        <v>141.7710770153187</v>
       </c>
       <c r="E331" t="n">
-        <v>143.4057027656593</v>
+        <v>143.4057478874085</v>
       </c>
       <c r="F331" t="n">
         <v>495866</v>
@@ -7052,16 +7052,16 @@
         <v>43705</v>
       </c>
       <c r="B332" t="n">
-        <v>145.6348266601562</v>
+        <v>145.6348419189453</v>
       </c>
       <c r="C332" t="n">
-        <v>146.5859027768606</v>
+        <v>146.585918135298</v>
       </c>
       <c r="D332" t="n">
-        <v>143.9704207803002</v>
+        <v>143.9704358647023</v>
       </c>
       <c r="E332" t="n">
-        <v>145.694267027815</v>
+        <v>145.6942822928319</v>
       </c>
       <c r="F332" t="n">
         <v>446600</v>
@@ -7112,16 +7112,16 @@
         <v>43710</v>
       </c>
       <c r="B335" t="n">
-        <v>155.1456756591797</v>
+        <v>155.1457061767578</v>
       </c>
       <c r="C335" t="n">
-        <v>155.8887104753308</v>
+        <v>155.8887411390659</v>
       </c>
       <c r="D335" t="n">
-        <v>152.1140809109343</v>
+        <v>152.1141108321895</v>
       </c>
       <c r="E335" t="n">
-        <v>153.6596060268775</v>
+        <v>153.6596362521417</v>
       </c>
       <c r="F335" t="n">
         <v>734566</v>
@@ -7132,16 +7132,16 @@
         <v>43711</v>
       </c>
       <c r="B336" t="n">
-        <v>154.5512542724609</v>
+        <v>154.55126953125</v>
       </c>
       <c r="C336" t="n">
-        <v>157.107296061017</v>
+        <v>157.1073115721632</v>
       </c>
       <c r="D336" t="n">
-        <v>153.2137854482698</v>
+        <v>153.213800575011</v>
       </c>
       <c r="E336" t="n">
-        <v>154.2540372985203</v>
+        <v>154.2540525279653</v>
       </c>
       <c r="F336" t="n">
         <v>578066</v>
@@ -7152,16 +7152,16 @@
         <v>43712</v>
       </c>
       <c r="B337" t="n">
-        <v>149.4688873291016</v>
+        <v>149.4689025878906</v>
       </c>
       <c r="C337" t="n">
-        <v>156.1859212419549</v>
+        <v>156.185937186464</v>
       </c>
       <c r="D337" t="n">
-        <v>147.9828176117963</v>
+        <v>147.9828327188773</v>
       </c>
       <c r="E337" t="n">
-        <v>155.9778799470986</v>
+        <v>155.9778958703694</v>
       </c>
       <c r="F337" t="n">
         <v>865766</v>
@@ -7232,16 +7232,16 @@
         <v>43718</v>
       </c>
       <c r="B341" t="n">
-        <v>146.4075775146484</v>
+        <v>146.4076080322266</v>
       </c>
       <c r="C341" t="n">
-        <v>146.4967380636036</v>
+        <v>146.4967685997666</v>
       </c>
       <c r="D341" t="n">
-        <v>140.6416201422374</v>
+        <v>140.6416494579443</v>
       </c>
       <c r="E341" t="n">
-        <v>142.0385292108626</v>
+        <v>142.0385588177449</v>
       </c>
       <c r="F341" t="n">
         <v>1022600</v>
@@ -7252,16 +7252,16 @@
         <v>43719</v>
       </c>
       <c r="B342" t="n">
-        <v>152.5302124023438</v>
+        <v>152.5301818847656</v>
       </c>
       <c r="C342" t="n">
-        <v>152.5302124023438</v>
+        <v>152.5301818847656</v>
       </c>
       <c r="D342" t="n">
-        <v>146.7048284321351</v>
+        <v>146.7047990800743</v>
       </c>
       <c r="E342" t="n">
-        <v>148.5772759791817</v>
+        <v>148.5772462524898</v>
       </c>
       <c r="F342" t="n">
         <v>523500</v>
@@ -7272,16 +7272,16 @@
         <v>43720</v>
       </c>
       <c r="B343" t="n">
-        <v>148.3691864013672</v>
+        <v>148.3691711425781</v>
       </c>
       <c r="C343" t="n">
-        <v>154.4918011372027</v>
+        <v>154.4917852487432</v>
       </c>
       <c r="D343" t="n">
-        <v>148.3394662181369</v>
+        <v>148.3394509624044</v>
       </c>
       <c r="E343" t="n">
-        <v>153.9568076048933</v>
+        <v>153.9567917714543</v>
       </c>
       <c r="F343" t="n">
         <v>700866</v>
@@ -7292,16 +7292,16 @@
         <v>43721</v>
       </c>
       <c r="B344" t="n">
-        <v>149.201416015625</v>
+        <v>149.2014007568359</v>
       </c>
       <c r="C344" t="n">
-        <v>150.4794294096575</v>
+        <v>150.4794140201663</v>
       </c>
       <c r="D344" t="n">
-        <v>145.6348423998163</v>
+        <v>145.6348275057798</v>
       </c>
       <c r="E344" t="n">
-        <v>148.6069820406289</v>
+        <v>148.6069668426325</v>
       </c>
       <c r="F344" t="n">
         <v>622000</v>
@@ -7312,16 +7312,16 @@
         <v>43724</v>
       </c>
       <c r="B345" t="n">
-        <v>149.9444427490234</v>
+        <v>149.9444580078125</v>
       </c>
       <c r="C345" t="n">
-        <v>151.2521762587837</v>
+        <v>151.2521916506516</v>
       </c>
       <c r="D345" t="n">
-        <v>146.5264702548115</v>
+        <v>146.5264851657776</v>
       </c>
       <c r="E345" t="n">
-        <v>149.4986097335467</v>
+        <v>149.4986249469664</v>
       </c>
       <c r="F345" t="n">
         <v>541366</v>
@@ -7332,16 +7332,16 @@
         <v>43725</v>
       </c>
       <c r="B346" t="n">
-        <v>153.0652160644531</v>
+        <v>153.065185546875</v>
       </c>
       <c r="C346" t="n">
-        <v>153.0652160644531</v>
+        <v>153.065185546875</v>
       </c>
       <c r="D346" t="n">
-        <v>149.0825440738754</v>
+        <v>149.0825143503477</v>
       </c>
       <c r="E346" t="n">
-        <v>150.3902929818897</v>
+        <v>150.3902629976278</v>
       </c>
       <c r="F346" t="n">
         <v>1122433</v>
@@ -7352,16 +7352,16 @@
         <v>43726</v>
       </c>
       <c r="B347" t="n">
-        <v>152.4707794189453</v>
+        <v>152.4707489013672</v>
       </c>
       <c r="C347" t="n">
-        <v>153.2138144358351</v>
+        <v>153.2137837695358</v>
       </c>
       <c r="D347" t="n">
-        <v>151.4008071805737</v>
+        <v>151.4007768771544</v>
       </c>
       <c r="E347" t="n">
-        <v>151.4305424889685</v>
+        <v>151.4305121795976</v>
       </c>
       <c r="F347" t="n">
         <v>459166</v>
@@ -7392,16 +7392,16 @@
         <v>43728</v>
       </c>
       <c r="B349" t="n">
-        <v>153.7190704345703</v>
+        <v>153.7190399169922</v>
       </c>
       <c r="C349" t="n">
-        <v>155.0565242425662</v>
+        <v>155.0564934594657</v>
       </c>
       <c r="D349" t="n">
-        <v>150.9846922085545</v>
+        <v>150.9846622338277</v>
       </c>
       <c r="E349" t="n">
-        <v>153.065196065994</v>
+        <v>153.0651656782284</v>
       </c>
       <c r="F349" t="n">
         <v>555866</v>
@@ -7412,16 +7412,16 @@
         <v>43731</v>
       </c>
       <c r="B350" t="n">
-        <v>157.9394989013672</v>
+        <v>157.9394836425781</v>
       </c>
       <c r="C350" t="n">
-        <v>159.0986315487212</v>
+        <v>159.0986161779464</v>
       </c>
       <c r="D350" t="n">
-        <v>153.6893458610692</v>
+        <v>153.6893310128942</v>
       </c>
       <c r="E350" t="n">
-        <v>154.5512615205438</v>
+        <v>154.5512465890978</v>
       </c>
       <c r="F350" t="n">
         <v>685766</v>
@@ -7432,16 +7432,16 @@
         <v>43732</v>
       </c>
       <c r="B351" t="n">
-        <v>155.1456756591797</v>
+        <v>155.1457061767578</v>
       </c>
       <c r="C351" t="n">
-        <v>158.9202901064941</v>
+        <v>158.9203213665492</v>
       </c>
       <c r="D351" t="n">
-        <v>154.6998426758234</v>
+        <v>154.699873105705</v>
       </c>
       <c r="E351" t="n">
-        <v>158.6825135231762</v>
+        <v>158.68254473646</v>
       </c>
       <c r="F351" t="n">
         <v>630466</v>
@@ -7452,16 +7452,16 @@
         <v>43733</v>
       </c>
       <c r="B352" t="n">
-        <v>155.1456756591797</v>
+        <v>155.1457061767578</v>
       </c>
       <c r="C352" t="n">
-        <v>156.0373113917282</v>
+        <v>156.0373420846935</v>
       </c>
       <c r="D352" t="n">
-        <v>152.708514810688</v>
+        <v>152.70854484887</v>
       </c>
       <c r="E352" t="n">
-        <v>155.472597675254</v>
+        <v>155.4726282571386</v>
       </c>
       <c r="F352" t="n">
         <v>976666</v>
@@ -7512,16 +7512,16 @@
         <v>43738</v>
       </c>
       <c r="B355" t="n">
-        <v>160.0497131347656</v>
+        <v>160.0497283935547</v>
       </c>
       <c r="C355" t="n">
-        <v>161.5655030518017</v>
+        <v>161.5655184551029</v>
       </c>
       <c r="D355" t="n">
-        <v>157.5233915673444</v>
+        <v>157.5234065852795</v>
       </c>
       <c r="E355" t="n">
-        <v>158.385307174303</v>
+        <v>158.3853222744112</v>
       </c>
       <c r="F355" t="n">
         <v>546766</v>
@@ -7552,16 +7552,16 @@
         <v>43740</v>
       </c>
       <c r="B357" t="n">
-        <v>156.0373229980469</v>
+        <v>156.0373382568359</v>
       </c>
       <c r="C357" t="n">
-        <v>159.0689028547042</v>
+        <v>159.0689184099495</v>
       </c>
       <c r="D357" t="n">
-        <v>154.4323725132479</v>
+        <v>154.4323876150899</v>
       </c>
       <c r="E357" t="n">
-        <v>156.5723014539522</v>
+        <v>156.5723167650564</v>
       </c>
       <c r="F357" t="n">
         <v>1285800</v>
@@ -7612,16 +7612,16 @@
         <v>43745</v>
       </c>
       <c r="B360" t="n">
-        <v>161.4168853759766</v>
+        <v>161.4169006347656</v>
       </c>
       <c r="C360" t="n">
-        <v>163.7054454381041</v>
+        <v>163.7054609132314</v>
       </c>
       <c r="D360" t="n">
-        <v>159.6336138095562</v>
+        <v>159.6336288997721</v>
       </c>
       <c r="E360" t="n">
-        <v>161.6249417878365</v>
+        <v>161.6249570662932</v>
       </c>
       <c r="F360" t="n">
         <v>812666</v>
@@ -7652,16 +7652,16 @@
         <v>43747</v>
       </c>
       <c r="B362" t="n">
-        <v>162.2788391113281</v>
+        <v>162.2788238525391</v>
       </c>
       <c r="C362" t="n">
-        <v>162.9029782012792</v>
+        <v>162.9029628838034</v>
       </c>
       <c r="D362" t="n">
-        <v>159.9605585353733</v>
+        <v>159.960543494568</v>
       </c>
       <c r="E362" t="n">
-        <v>161.9816221024021</v>
+        <v>161.9816068715598</v>
       </c>
       <c r="F362" t="n">
         <v>623966</v>
@@ -7692,16 +7692,16 @@
         <v>43749</v>
       </c>
       <c r="B364" t="n">
-        <v>167.2422790527344</v>
+        <v>167.2422943115234</v>
       </c>
       <c r="C364" t="n">
-        <v>168.282530850187</v>
+        <v>168.2825462038862</v>
       </c>
       <c r="D364" t="n">
-        <v>163.764881450249</v>
+        <v>163.7648963917685</v>
       </c>
       <c r="E364" t="n">
-        <v>163.764881450249</v>
+        <v>163.7648963917685</v>
       </c>
       <c r="F364" t="n">
         <v>518100</v>
@@ -7712,16 +7712,16 @@
         <v>43752</v>
       </c>
       <c r="B365" t="n">
-        <v>167.9259033203125</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C365" t="n">
-        <v>169.5902943979059</v>
+        <v>169.590263577854</v>
       </c>
       <c r="D365" t="n">
-        <v>166.3803930005229</v>
+        <v>166.3803627638141</v>
       </c>
       <c r="E365" t="n">
-        <v>167.2125885393196</v>
+        <v>167.2125581513739</v>
       </c>
       <c r="F365" t="n">
         <v>323333</v>
@@ -7732,16 +7732,16 @@
         <v>43753</v>
       </c>
       <c r="B366" t="n">
-        <v>167.3314208984375</v>
+        <v>167.3314514160156</v>
       </c>
       <c r="C366" t="n">
-        <v>169.2038678776889</v>
+        <v>169.2038987367602</v>
       </c>
       <c r="D366" t="n">
-        <v>167.1828199941639</v>
+        <v>167.1828504846405</v>
       </c>
       <c r="E366" t="n">
-        <v>167.3017007175828</v>
+        <v>167.3017312297406</v>
       </c>
       <c r="F366" t="n">
         <v>550533</v>
@@ -7752,16 +7752,16 @@
         <v>43754</v>
       </c>
       <c r="B367" t="n">
-        <v>170.7791442871094</v>
+        <v>170.7791595458984</v>
       </c>
       <c r="C367" t="n">
-        <v>172.8001925403221</v>
+        <v>172.800207979688</v>
       </c>
       <c r="D367" t="n">
-        <v>167.3017313202149</v>
+        <v>167.3017462683037</v>
       </c>
       <c r="E367" t="n">
-        <v>168.7580809168131</v>
+        <v>168.758095995024</v>
       </c>
       <c r="F367" t="n">
         <v>599666</v>
@@ -7772,16 +7772,16 @@
         <v>43755</v>
       </c>
       <c r="B368" t="n">
-        <v>169.7686309814453</v>
+        <v>169.7686157226562</v>
       </c>
       <c r="C368" t="n">
-        <v>172.9785475021482</v>
+        <v>172.9785319548521</v>
       </c>
       <c r="D368" t="n">
-        <v>168.8769799449297</v>
+        <v>168.8769647662821</v>
       </c>
       <c r="E368" t="n">
-        <v>171.2547009252195</v>
+        <v>171.2546855328626</v>
       </c>
       <c r="F368" t="n">
         <v>460533</v>
@@ -7812,16 +7812,16 @@
         <v>43759</v>
       </c>
       <c r="B370" t="n">
-        <v>168.5203247070312</v>
+        <v>168.5203094482422</v>
       </c>
       <c r="C370" t="n">
-        <v>171.7302258637203</v>
+        <v>171.7302103142885</v>
       </c>
       <c r="D370" t="n">
-        <v>167.9853311028604</v>
+        <v>167.9853158925127</v>
       </c>
       <c r="E370" t="n">
-        <v>171.314128125523</v>
+        <v>171.314112613767</v>
       </c>
       <c r="F370" t="n">
         <v>853400</v>
@@ -7832,16 +7832,16 @@
         <v>43760</v>
       </c>
       <c r="B371" t="n">
-        <v>166.8856201171875</v>
+        <v>166.8856353759766</v>
       </c>
       <c r="C371" t="n">
-        <v>169.8874796268238</v>
+        <v>169.8874951600807</v>
       </c>
       <c r="D371" t="n">
-        <v>165.3401100865331</v>
+        <v>165.3401252040121</v>
       </c>
       <c r="E371" t="n">
-        <v>169.6497181556968</v>
+        <v>169.6497336672146</v>
       </c>
       <c r="F371" t="n">
         <v>630100</v>
@@ -7892,16 +7892,16 @@
         <v>43763</v>
       </c>
       <c r="B374" t="n">
-        <v>168.3717346191406</v>
+        <v>168.3717193603516</v>
       </c>
       <c r="C374" t="n">
-        <v>169.6497633351291</v>
+        <v>169.6497479605179</v>
       </c>
       <c r="D374" t="n">
-        <v>166.8559443687069</v>
+        <v>166.8559292472873</v>
       </c>
       <c r="E374" t="n">
-        <v>169.6497633351291</v>
+        <v>169.6497479605179</v>
       </c>
       <c r="F374" t="n">
         <v>471566</v>
@@ -7912,16 +7912,16 @@
         <v>43766</v>
       </c>
       <c r="B375" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0063781738281</v>
       </c>
       <c r="C375" t="n">
-        <v>170.5710921032597</v>
+        <v>170.5710767937866</v>
       </c>
       <c r="D375" t="n">
-        <v>167.6881130247363</v>
+        <v>167.6880979740227</v>
       </c>
       <c r="E375" t="n">
-        <v>169.3525190838025</v>
+        <v>169.3525038837014</v>
       </c>
       <c r="F375" t="n">
         <v>598700</v>
@@ -7972,16 +7972,16 @@
         <v>43769</v>
       </c>
       <c r="B378" t="n">
-        <v>167.3314208984375</v>
+        <v>167.3314514160156</v>
       </c>
       <c r="C378" t="n">
-        <v>168.5202886009495</v>
+        <v>168.520319335351</v>
       </c>
       <c r="D378" t="n">
-        <v>166.1425683130063</v>
+        <v>166.1425986137638</v>
       </c>
       <c r="E378" t="n">
-        <v>167.5989176432108</v>
+        <v>167.5989482095744</v>
       </c>
       <c r="F378" t="n">
         <v>595400</v>
@@ -7992,16 +7992,16 @@
         <v>43770</v>
       </c>
       <c r="B379" t="n">
-        <v>168.6689300537109</v>
+        <v>168.6689147949219</v>
       </c>
       <c r="C379" t="n">
-        <v>168.8769713697077</v>
+        <v>168.876956092098</v>
       </c>
       <c r="D379" t="n">
-        <v>166.9748037523151</v>
+        <v>166.9747886467867</v>
       </c>
       <c r="E379" t="n">
-        <v>167.331461125394</v>
+        <v>167.3314459876003</v>
       </c>
       <c r="F379" t="n">
         <v>1063666</v>
@@ -8052,16 +8052,16 @@
         <v>43775</v>
       </c>
       <c r="B382" t="n">
-        <v>163.4974060058594</v>
+        <v>163.4973907470703</v>
       </c>
       <c r="C382" t="n">
-        <v>164.5970983151352</v>
+        <v>164.5970829537148</v>
       </c>
       <c r="D382" t="n">
-        <v>160.1388887019224</v>
+        <v>160.1388737565751</v>
       </c>
       <c r="E382" t="n">
-        <v>161.9221755706244</v>
+        <v>161.9221604588475</v>
       </c>
       <c r="F382" t="n">
         <v>1813233</v>
@@ -8072,16 +8072,16 @@
         <v>43776</v>
       </c>
       <c r="B383" t="n">
-        <v>164.4782257080078</v>
+        <v>164.4781951904297</v>
       </c>
       <c r="C383" t="n">
-        <v>166.5884347498103</v>
+        <v>166.5884038407003</v>
       </c>
       <c r="D383" t="n">
-        <v>162.6354983719431</v>
+        <v>162.6354681962679</v>
       </c>
       <c r="E383" t="n">
-        <v>164.3296096432904</v>
+        <v>164.3295791532868</v>
       </c>
       <c r="F383" t="n">
         <v>718100</v>
@@ -8092,16 +8092,16 @@
         <v>43777</v>
       </c>
       <c r="B384" t="n">
-        <v>165.5184326171875</v>
+        <v>165.5184478759766</v>
       </c>
       <c r="C384" t="n">
-        <v>169.203886622259</v>
+        <v>169.2039022208022</v>
       </c>
       <c r="D384" t="n">
-        <v>163.4082239573274</v>
+        <v>163.4082390215808</v>
       </c>
       <c r="E384" t="n">
-        <v>164.6862372269023</v>
+        <v>164.6862524089731</v>
       </c>
       <c r="F384" t="n">
         <v>1517366</v>
@@ -8132,16 +8132,16 @@
         <v>43781</v>
       </c>
       <c r="B386" t="n">
-        <v>167.9259033203125</v>
+        <v>167.9258728027344</v>
       </c>
       <c r="C386" t="n">
-        <v>171.6410781725318</v>
+        <v>171.641046979786</v>
       </c>
       <c r="D386" t="n">
-        <v>166.8856513382741</v>
+        <v>166.8856210097434</v>
       </c>
       <c r="E386" t="n">
-        <v>170.8980432020879</v>
+        <v>170.8980121443757</v>
       </c>
       <c r="F386" t="n">
         <v>771166</v>
@@ -8172,16 +8172,16 @@
         <v>43783</v>
       </c>
       <c r="B388" t="n">
-        <v>161.5060882568359</v>
+        <v>161.5060729980469</v>
       </c>
       <c r="C388" t="n">
-        <v>167.4800883151972</v>
+        <v>167.4800724919959</v>
       </c>
       <c r="D388" t="n">
-        <v>160.9710946031133</v>
+        <v>160.9710793948695</v>
       </c>
       <c r="E388" t="n">
-        <v>165.1023672975915</v>
+        <v>165.1023516990328</v>
       </c>
       <c r="F388" t="n">
         <v>1805133</v>
@@ -8212,16 +8212,16 @@
         <v>43788</v>
       </c>
       <c r="B390" t="n">
-        <v>159.5741882324219</v>
+        <v>159.5741424560547</v>
       </c>
       <c r="C390" t="n">
-        <v>162.7841048643803</v>
+        <v>162.7840581671981</v>
       </c>
       <c r="D390" t="n">
-        <v>158.5339513293935</v>
+        <v>158.5339058514347</v>
       </c>
       <c r="E390" t="n">
-        <v>162.6355039116865</v>
+        <v>162.6354572571327</v>
       </c>
       <c r="F390" t="n">
         <v>1296633</v>
@@ -8252,16 +8252,16 @@
         <v>43791</v>
       </c>
       <c r="B392" t="n">
-        <v>169.9766540527344</v>
+        <v>169.9766387939453</v>
       </c>
       <c r="C392" t="n">
-        <v>169.9766540527344</v>
+        <v>169.9766387939453</v>
       </c>
       <c r="D392" t="n">
-        <v>164.2404313373464</v>
+        <v>164.2404165934975</v>
       </c>
       <c r="E392" t="n">
-        <v>165.1023469746995</v>
+        <v>165.1023321534766</v>
       </c>
       <c r="F392" t="n">
         <v>1134300</v>
@@ -8272,16 +8272,16 @@
         <v>43794</v>
       </c>
       <c r="B393" t="n">
-        <v>171.7599334716797</v>
+        <v>171.7599487304688</v>
       </c>
       <c r="C393" t="n">
-        <v>172.2652068516232</v>
+        <v>172.2652221552997</v>
       </c>
       <c r="D393" t="n">
-        <v>167.9555986149949</v>
+        <v>167.9556135358149</v>
       </c>
       <c r="E393" t="n">
-        <v>169.203891738165</v>
+        <v>169.2039067698807</v>
       </c>
       <c r="F393" t="n">
         <v>1287433</v>
@@ -8312,16 +8312,16 @@
         <v>43796</v>
       </c>
       <c r="B395" t="n">
-        <v>167.9556274414062</v>
+        <v>167.9556121826172</v>
       </c>
       <c r="C395" t="n">
-        <v>170.3927888530307</v>
+        <v>170.3927733728252</v>
       </c>
       <c r="D395" t="n">
-        <v>165.2509843184619</v>
+        <v>165.25096930539</v>
       </c>
       <c r="E395" t="n">
-        <v>169.7686346257798</v>
+        <v>169.7686192022788</v>
       </c>
       <c r="F395" t="n">
         <v>429100</v>
@@ -8372,16 +8372,16 @@
         <v>43801</v>
       </c>
       <c r="B398" t="n">
-        <v>167.1828460693359</v>
+        <v>167.182861328125</v>
       </c>
       <c r="C398" t="n">
-        <v>167.3017268112964</v>
+        <v>167.3017420809357</v>
       </c>
       <c r="D398" t="n">
-        <v>162.9624134418244</v>
+        <v>162.9624283154143</v>
       </c>
       <c r="E398" t="n">
-        <v>165.6373359555172</v>
+        <v>165.6373510732474</v>
       </c>
       <c r="F398" t="n">
         <v>805633</v>
@@ -8392,16 +8392,16 @@
         <v>43802</v>
       </c>
       <c r="B399" t="n">
-        <v>169.8280334472656</v>
+        <v>169.8280487060547</v>
       </c>
       <c r="C399" t="n">
-        <v>170.452187521779</v>
+        <v>170.4522028366473</v>
       </c>
       <c r="D399" t="n">
-        <v>165.8453626542769</v>
+        <v>165.845377555229</v>
       </c>
       <c r="E399" t="n">
-        <v>167.331432266294</v>
+        <v>167.3314473007672</v>
       </c>
       <c r="F399" t="n">
         <v>915133</v>
@@ -8432,16 +8432,16 @@
         <v>43804</v>
       </c>
       <c r="B401" t="n">
-        <v>172.3543853759766</v>
+        <v>172.3543701171875</v>
       </c>
       <c r="C401" t="n">
-        <v>174.7618113181715</v>
+        <v>174.7617958462494</v>
       </c>
       <c r="D401" t="n">
-        <v>169.1147488144879</v>
+        <v>169.1147338425086</v>
       </c>
       <c r="E401" t="n">
-        <v>172.7110427507926</v>
+        <v>172.7110274604281</v>
       </c>
       <c r="F401" t="n">
         <v>632400</v>
@@ -8452,16 +8452,16 @@
         <v>43805</v>
       </c>
       <c r="B402" t="n">
-        <v>171.730224609375</v>
+        <v>171.7302398681641</v>
       </c>
       <c r="C402" t="n">
-        <v>173.4243508540965</v>
+        <v>173.4243662634142</v>
       </c>
       <c r="D402" t="n">
-        <v>167.9556096888631</v>
+        <v>167.9556246122654</v>
       </c>
       <c r="E402" t="n">
-        <v>173.4243508540965</v>
+        <v>173.4243662634142</v>
       </c>
       <c r="F402" t="n">
         <v>837700</v>
@@ -8512,16 +8512,16 @@
         <v>43810</v>
       </c>
       <c r="B405" t="n">
-        <v>167.0936737060547</v>
+        <v>167.0936889648438</v>
       </c>
       <c r="C405" t="n">
-        <v>167.0936737060547</v>
+        <v>167.0936889648438</v>
       </c>
       <c r="D405" t="n">
-        <v>161.9815905238091</v>
+        <v>161.981605315769</v>
       </c>
       <c r="E405" t="n">
-        <v>162.7840657095058</v>
+        <v>162.7840805747468</v>
       </c>
       <c r="F405" t="n">
         <v>789933</v>
@@ -8532,16 +8532,16 @@
         <v>43811</v>
       </c>
       <c r="B406" t="n">
-        <v>170.0063934326172</v>
+        <v>170.0063781738281</v>
       </c>
       <c r="C406" t="n">
-        <v>170.214434741823</v>
+        <v>170.2144194643613</v>
       </c>
       <c r="D406" t="n">
-        <v>167.1234143540938</v>
+        <v>167.1233993540642</v>
       </c>
       <c r="E406" t="n">
-        <v>169.085022283454</v>
+        <v>169.0850071073618</v>
       </c>
       <c r="F406" t="n">
         <v>578333</v>
@@ -8552,16 +8552,16 @@
         <v>43812</v>
       </c>
       <c r="B407" t="n">
-        <v>166.9747924804688</v>
+        <v>166.9747772216797</v>
       </c>
       <c r="C407" t="n">
-        <v>171.3141210404826</v>
+        <v>171.3141053851492</v>
       </c>
       <c r="D407" t="n">
-        <v>166.2020374104777</v>
+        <v>166.2020222223059</v>
       </c>
       <c r="E407" t="n">
-        <v>170.8088627615141</v>
+        <v>170.8088471523532</v>
       </c>
       <c r="F407" t="n">
         <v>591766</v>
@@ -8592,16 +8592,16 @@
         <v>43816</v>
       </c>
       <c r="B409" t="n">
-        <v>173.1568298339844</v>
+        <v>173.1568756103516</v>
       </c>
       <c r="C409" t="n">
-        <v>175.2373333358522</v>
+        <v>175.2373796622288</v>
       </c>
       <c r="D409" t="n">
-        <v>171.403263460529</v>
+        <v>171.403308773317</v>
       </c>
       <c r="E409" t="n">
-        <v>173.4243265967004</v>
+        <v>173.424372443784</v>
       </c>
       <c r="F409" t="n">
         <v>614666</v>
@@ -8632,16 +8632,16 @@
         <v>43818</v>
       </c>
       <c r="B411" t="n">
-        <v>184.7481842041016</v>
+        <v>184.7481994628906</v>
       </c>
       <c r="C411" t="n">
-        <v>185.7587158511149</v>
+        <v>185.7587311933661</v>
       </c>
       <c r="D411" t="n">
-        <v>178.922801154627</v>
+        <v>178.922815932284</v>
       </c>
       <c r="E411" t="n">
-        <v>181.3005066706881</v>
+        <v>181.3005216447253</v>
       </c>
       <c r="F411" t="n">
         <v>904966</v>
@@ -8652,16 +8652,16 @@
         <v>43819</v>
       </c>
       <c r="B412" t="n">
-        <v>190.0683441162109</v>
+        <v>190.0683288574219</v>
       </c>
       <c r="C412" t="n">
-        <v>190.0683441162109</v>
+        <v>190.0683288574219</v>
       </c>
       <c r="D412" t="n">
-        <v>182.9351965828794</v>
+        <v>182.9351818967433</v>
       </c>
       <c r="E412" t="n">
-        <v>185.847895972809</v>
+        <v>185.8478810528398</v>
       </c>
       <c r="F412" t="n">
         <v>984100</v>
@@ -8672,16 +8672,16 @@
         <v>43822</v>
       </c>
       <c r="B413" t="n">
-        <v>187.8392181396484</v>
+        <v>187.8392333984375</v>
       </c>
       <c r="C413" t="n">
-        <v>190.4547002349917</v>
+        <v>190.4547157062448</v>
       </c>
       <c r="D413" t="n">
-        <v>186.1748121969302</v>
+        <v>186.1748273205142</v>
       </c>
       <c r="E413" t="n">
-        <v>190.216923638294</v>
+        <v>190.2169390902317</v>
       </c>
       <c r="F413" t="n">
         <v>629966</v>
@@ -8692,16 +8692,16 @@
         <v>43825</v>
       </c>
       <c r="B414" t="n">
-        <v>191.4057769775391</v>
+        <v>191.40576171875</v>
       </c>
       <c r="C414" t="n">
-        <v>191.6435535749696</v>
+        <v>191.6435382972251</v>
       </c>
       <c r="D414" t="n">
-        <v>187.3636655237174</v>
+        <v>187.3636505871638</v>
       </c>
       <c r="E414" t="n">
-        <v>188.7902948741348</v>
+        <v>188.7902798238509</v>
       </c>
       <c r="F414" t="n">
         <v>400133</v>
@@ -8712,16 +8712,16 @@
         <v>43826</v>
       </c>
       <c r="B415" t="n">
-        <v>189.6225128173828</v>
+        <v>189.6224822998047</v>
       </c>
       <c r="C415" t="n">
-        <v>194.9723735170316</v>
+        <v>194.9723421384545</v>
       </c>
       <c r="D415" t="n">
-        <v>184.9265416176233</v>
+        <v>184.9265118558081</v>
       </c>
       <c r="E415" t="n">
-        <v>194.9723735170316</v>
+        <v>194.9723421384545</v>
       </c>
       <c r="F415" t="n">
         <v>651400</v>
@@ -8732,16 +8732,16 @@
         <v>43829</v>
       </c>
       <c r="B416" t="n">
-        <v>189.9197235107422</v>
+        <v>189.9196929931641</v>
       </c>
       <c r="C416" t="n">
-        <v>193.3376811370011</v>
+        <v>193.3376500702026</v>
       </c>
       <c r="D416" t="n">
-        <v>188.0472761073423</v>
+        <v>188.0472458906416</v>
       </c>
       <c r="E416" t="n">
-        <v>190.6627584345848</v>
+        <v>190.6627277976108</v>
       </c>
       <c r="F416" t="n">
         <v>1069533</v>
@@ -8752,16 +8752,16 @@
         <v>43832</v>
       </c>
       <c r="B417" t="n">
-        <v>197.4689178466797</v>
+        <v>197.4689331054688</v>
       </c>
       <c r="C417" t="n">
-        <v>199.3711002113134</v>
+        <v>199.3711156170877</v>
       </c>
       <c r="D417" t="n">
-        <v>191.4651991647313</v>
+        <v>191.4652139596019</v>
       </c>
       <c r="E417" t="n">
-        <v>193.7834791975407</v>
+        <v>193.7834941715491</v>
       </c>
       <c r="F417" t="n">
         <v>866733</v>
@@ -8772,16 +8772,16 @@
         <v>43833</v>
       </c>
       <c r="B418" t="n">
-        <v>205.8206481933594</v>
+        <v>205.8206634521484</v>
       </c>
       <c r="C418" t="n">
-        <v>205.8206481933594</v>
+        <v>205.8206634521484</v>
       </c>
       <c r="D418" t="n">
-        <v>194.3779087721894</v>
+        <v>194.3779231826556</v>
       </c>
       <c r="E418" t="n">
-        <v>195.418160559038</v>
+        <v>195.4181750466247</v>
       </c>
       <c r="F418" t="n">
         <v>3123966</v>
@@ -8832,16 +8832,16 @@
         <v>43838</v>
       </c>
       <c r="B421" t="n">
-        <v>190.0012359619141</v>
+        <v>190.0012054443359</v>
       </c>
       <c r="C421" t="n">
-        <v>196.0188331611202</v>
+        <v>196.0188016770089</v>
       </c>
       <c r="D421" t="n">
-        <v>188.005304907849</v>
+        <v>188.0052747108529</v>
       </c>
       <c r="E421" t="n">
-        <v>193.903746567119</v>
+        <v>193.9037154227282</v>
       </c>
       <c r="F421" t="n">
         <v>832966</v>
@@ -8852,16 +8852,16 @@
         <v>43839</v>
       </c>
       <c r="B422" t="n">
-        <v>188.8691711425781</v>
+        <v>188.8691864013672</v>
       </c>
       <c r="C422" t="n">
-        <v>191.5204873844923</v>
+        <v>191.5205028574819</v>
       </c>
       <c r="D422" t="n">
-        <v>187.20093334399</v>
+        <v>187.2009484680017</v>
       </c>
       <c r="E422" t="n">
-        <v>190.0011939779125</v>
+        <v>190.001209328158</v>
       </c>
       <c r="F422" t="n">
         <v>950500</v>
@@ -8872,16 +8872,16 @@
         <v>43840</v>
       </c>
       <c r="B423" t="n">
-        <v>184.8475036621094</v>
+        <v>184.8475189208984</v>
       </c>
       <c r="C423" t="n">
-        <v>190.6267884348786</v>
+        <v>190.6268041707359</v>
       </c>
       <c r="D423" t="n">
-        <v>182.3153581162909</v>
+        <v>182.3153731660564</v>
       </c>
       <c r="E423" t="n">
-        <v>190.6267884348786</v>
+        <v>190.6268041707359</v>
       </c>
       <c r="F423" t="n">
         <v>656333</v>
@@ -8892,16 +8892,16 @@
         <v>43843</v>
       </c>
       <c r="B424" t="n">
-        <v>185.8603973388672</v>
+        <v>185.8603820800781</v>
       </c>
       <c r="C424" t="n">
-        <v>186.6945163464585</v>
+        <v>186.6945010191898</v>
       </c>
       <c r="D424" t="n">
-        <v>183.6559291387862</v>
+        <v>183.6559140609799</v>
       </c>
       <c r="E424" t="n">
-        <v>184.6985854742881</v>
+        <v>184.6985703108816</v>
       </c>
       <c r="F424" t="n">
         <v>736233</v>
@@ -8912,16 +8912,16 @@
         <v>43844</v>
       </c>
       <c r="B425" t="n">
-        <v>186.1880645751953</v>
+        <v>186.1880798339844</v>
       </c>
       <c r="C425" t="n">
-        <v>186.5157573870905</v>
+        <v>186.5157726727352</v>
       </c>
       <c r="D425" t="n">
-        <v>180.40877977781</v>
+        <v>180.4087945629656</v>
       </c>
       <c r="E425" t="n">
-        <v>185.3241568042139</v>
+        <v>185.3241719922026</v>
       </c>
       <c r="F425" t="n">
         <v>863500</v>
@@ -8932,16 +8932,16 @@
         <v>43845</v>
       </c>
       <c r="B426" t="n">
-        <v>181.7493438720703</v>
+        <v>181.7493286132812</v>
       </c>
       <c r="C426" t="n">
-        <v>188.0350548876207</v>
+        <v>188.0350391011139</v>
       </c>
       <c r="D426" t="n">
-        <v>179.3363537754593</v>
+        <v>179.3363387192531</v>
       </c>
       <c r="E426" t="n">
-        <v>187.6775731897497</v>
+        <v>187.6775574332554</v>
       </c>
       <c r="F426" t="n">
         <v>1526633</v>
@@ -8992,16 +8992,16 @@
         <v>43850</v>
       </c>
       <c r="B429" t="n">
-        <v>188.1244201660156</v>
+        <v>188.1244354248047</v>
       </c>
       <c r="C429" t="n">
-        <v>189.4947691899657</v>
+        <v>189.4947845599039</v>
       </c>
       <c r="D429" t="n">
-        <v>185.9497411156683</v>
+        <v>185.9497561980689</v>
       </c>
       <c r="E429" t="n">
-        <v>189.4649803113602</v>
+        <v>189.4649956788822</v>
       </c>
       <c r="F429" t="n">
         <v>883800</v>
@@ -9012,16 +9012,16 @@
         <v>43851</v>
       </c>
       <c r="B430" t="n">
-        <v>190.060791015625</v>
+        <v>190.0607604980469</v>
       </c>
       <c r="C430" t="n">
-        <v>192.682318645081</v>
+        <v>192.6822877065709</v>
       </c>
       <c r="D430" t="n">
-        <v>187.6775895895832</v>
+        <v>187.6775594546697</v>
       </c>
       <c r="E430" t="n">
-        <v>188.1542268443865</v>
+        <v>188.1541966329406</v>
       </c>
       <c r="F430" t="n">
         <v>1218200</v>
@@ -9052,16 +9052,16 @@
         <v>43853</v>
       </c>
       <c r="B432" t="n">
-        <v>191.55029296875</v>
+        <v>191.5502777099609</v>
       </c>
       <c r="C432" t="n">
-        <v>191.55029296875</v>
+        <v>191.5502777099609</v>
       </c>
       <c r="D432" t="n">
-        <v>186.5157751034802</v>
+        <v>186.515760245738</v>
       </c>
       <c r="E432" t="n">
-        <v>189.8224772626689</v>
+        <v>189.8224621415167</v>
       </c>
       <c r="F432" t="n">
         <v>1068366</v>
@@ -9072,16 +9072,16 @@
         <v>43854</v>
       </c>
       <c r="B433" t="n">
-        <v>192.1461029052734</v>
+        <v>192.1460876464844</v>
       </c>
       <c r="C433" t="n">
-        <v>193.1887592072574</v>
+        <v>193.1887438656685</v>
       </c>
       <c r="D433" t="n">
-        <v>190.0607903013054</v>
+        <v>190.0607752081161</v>
       </c>
       <c r="E433" t="n">
-        <v>191.8481989401316</v>
+        <v>191.8481837049998</v>
       </c>
       <c r="F433" t="n">
         <v>639666</v>
@@ -9092,16 +9092,16 @@
         <v>43857</v>
       </c>
       <c r="B434" t="n">
-        <v>182.4047088623047</v>
+        <v>182.4047393798828</v>
       </c>
       <c r="C434" t="n">
-        <v>189.7628641385387</v>
+        <v>189.7628958871874</v>
       </c>
       <c r="D434" t="n">
-        <v>180.5279339489355</v>
+        <v>180.5279641525161</v>
       </c>
       <c r="E434" t="n">
-        <v>189.7628641385387</v>
+        <v>189.7628958871874</v>
       </c>
       <c r="F434" t="n">
         <v>939566</v>
@@ -9112,16 +9112,16 @@
         <v>43858</v>
       </c>
       <c r="B435" t="n">
-        <v>186.1880645751953</v>
+        <v>186.1880798339844</v>
       </c>
       <c r="C435" t="n">
-        <v>186.7540684124517</v>
+        <v>186.7540837176268</v>
       </c>
       <c r="D435" t="n">
-        <v>182.4047255273511</v>
+        <v>182.4047404760818</v>
       </c>
       <c r="E435" t="n">
-        <v>184.4006561248688</v>
+        <v>184.4006712371732</v>
       </c>
       <c r="F435" t="n">
         <v>417866</v>
@@ -9132,16 +9132,16 @@
         <v>43859</v>
       </c>
       <c r="B436" t="n">
-        <v>182.6132507324219</v>
+        <v>182.61328125</v>
       </c>
       <c r="C436" t="n">
-        <v>187.5286278411344</v>
+        <v>187.5286591801502</v>
       </c>
       <c r="D436" t="n">
-        <v>181.1237461908784</v>
+        <v>181.1237764595366</v>
       </c>
       <c r="E436" t="n">
-        <v>186.9328199637075</v>
+        <v>186.9328512031543</v>
       </c>
       <c r="F436" t="n">
         <v>838300</v>
@@ -9152,16 +9152,16 @@
         <v>43860</v>
       </c>
       <c r="B437" t="n">
-        <v>179.0682373046875</v>
+        <v>179.0682525634766</v>
       </c>
       <c r="C437" t="n">
-        <v>182.523883588893</v>
+        <v>182.5238991421452</v>
       </c>
       <c r="D437" t="n">
-        <v>174.8678387517811</v>
+        <v>174.8678536526452</v>
       </c>
       <c r="E437" t="n">
-        <v>182.523883588893</v>
+        <v>182.5238991421452</v>
       </c>
       <c r="F437" t="n">
         <v>937800</v>
@@ -9172,16 +9172,16 @@
         <v>43861</v>
       </c>
       <c r="B438" t="n">
-        <v>178.9490661621094</v>
+        <v>178.9490509033203</v>
       </c>
       <c r="C438" t="n">
-        <v>179.8725668518933</v>
+        <v>179.8725515143583</v>
       </c>
       <c r="D438" t="n">
-        <v>175.3742643730724</v>
+        <v>175.3742494191027</v>
       </c>
       <c r="E438" t="n">
-        <v>177.3701949931508</v>
+        <v>177.3701798689903</v>
       </c>
       <c r="F438" t="n">
         <v>886766</v>
@@ -9192,16 +9192,16 @@
         <v>43864</v>
       </c>
       <c r="B439" t="n">
-        <v>184.1027679443359</v>
+        <v>184.1027526855469</v>
       </c>
       <c r="C439" t="n">
-        <v>186.1582916261031</v>
+        <v>186.1582761969483</v>
       </c>
       <c r="D439" t="n">
-        <v>178.7405572865494</v>
+        <v>178.7405424721906</v>
       </c>
       <c r="E439" t="n">
-        <v>179.0384612457652</v>
+        <v>179.0384464067156</v>
       </c>
       <c r="F439" t="n">
         <v>700100</v>
@@ -9212,16 +9212,16 @@
         <v>43865</v>
       </c>
       <c r="B440" t="n">
-        <v>182.7622222900391</v>
+        <v>182.7622375488281</v>
       </c>
       <c r="C440" t="n">
-        <v>186.5753505305267</v>
+        <v>186.5753661076733</v>
       </c>
       <c r="D440" t="n">
-        <v>182.5238960929993</v>
+        <v>182.5239113318906</v>
       </c>
       <c r="E440" t="n">
-        <v>186.3668132141139</v>
+        <v>186.3668287738497</v>
       </c>
       <c r="F440" t="n">
         <v>732700</v>
@@ -9392,16 +9392,16 @@
         <v>43878</v>
       </c>
       <c r="B449" t="n">
-        <v>178.3532867431641</v>
+        <v>178.353271484375</v>
       </c>
       <c r="C449" t="n">
-        <v>178.3532867431641</v>
+        <v>178.353271484375</v>
       </c>
       <c r="D449" t="n">
-        <v>173.4677133273196</v>
+        <v>173.4676984865096</v>
       </c>
       <c r="E449" t="n">
-        <v>173.9741394517339</v>
+        <v>173.9741245675972</v>
       </c>
       <c r="F449" t="n">
         <v>278100</v>
@@ -9472,16 +9472,16 @@
         <v>43882</v>
       </c>
       <c r="B453" t="n">
-        <v>166.8245086669922</v>
+        <v>166.8245239257812</v>
       </c>
       <c r="C453" t="n">
-        <v>171.2334445346579</v>
+        <v>171.2334601967152</v>
       </c>
       <c r="D453" t="n">
-        <v>165.543526276023</v>
+        <v>165.5435414176457</v>
       </c>
       <c r="E453" t="n">
-        <v>169.8333066290028</v>
+        <v>169.8333221629949</v>
       </c>
       <c r="F453" t="n">
         <v>990066</v>
@@ -9532,16 +9532,16 @@
         <v>43889</v>
       </c>
       <c r="B456" t="n">
-        <v>164.4412841796875</v>
+        <v>164.4412994384766</v>
       </c>
       <c r="C456" t="n">
-        <v>165.0072879463353</v>
+        <v>165.0073032576448</v>
       </c>
       <c r="D456" t="n">
-        <v>155.0573947741125</v>
+        <v>155.0574091621543</v>
       </c>
       <c r="E456" t="n">
-        <v>158.6322112288098</v>
+        <v>158.632225948565</v>
       </c>
       <c r="F456" t="n">
         <v>1340833</v>
@@ -9552,16 +9552,16 @@
         <v>43892</v>
       </c>
       <c r="B457" t="n">
-        <v>162.5347442626953</v>
+        <v>162.5347137451172</v>
       </c>
       <c r="C457" t="n">
-        <v>165.9308282847228</v>
+        <v>165.9307971294947</v>
       </c>
       <c r="D457" t="n">
-        <v>159.079097629504</v>
+        <v>159.0790677607593</v>
       </c>
       <c r="E457" t="n">
-        <v>164.7392124128411</v>
+        <v>164.7391814813513</v>
       </c>
       <c r="F457" t="n">
         <v>1544166</v>
@@ -9612,16 +9612,16 @@
         <v>43895</v>
       </c>
       <c r="B460" t="n">
-        <v>152.8231811523438</v>
+        <v>152.8231658935547</v>
       </c>
       <c r="C460" t="n">
-        <v>161.7602096443411</v>
+        <v>161.7601934932251</v>
       </c>
       <c r="D460" t="n">
-        <v>151.6911581494385</v>
+        <v>151.6911430036774</v>
       </c>
       <c r="E460" t="n">
-        <v>156.397998609953</v>
+        <v>156.3979829942326</v>
       </c>
       <c r="F460" t="n">
         <v>1000500</v>
@@ -9672,16 +9672,16 @@
         <v>43900</v>
       </c>
       <c r="B463" t="n">
-        <v>145.6437530517578</v>
+        <v>145.6437683105469</v>
       </c>
       <c r="C463" t="n">
-        <v>147.3715837841424</v>
+        <v>147.3715992239526</v>
       </c>
       <c r="D463" t="n">
-        <v>136.9152630573862</v>
+        <v>136.9152774017098</v>
       </c>
       <c r="E463" t="n">
-        <v>142.456206648502</v>
+        <v>142.4562215733386</v>
       </c>
       <c r="F463" t="n">
         <v>1718533</v>
@@ -9692,16 +9692,16 @@
         <v>43901</v>
       </c>
       <c r="B464" t="n">
-        <v>134.0256195068359</v>
+        <v>134.025634765625</v>
       </c>
       <c r="C464" t="n">
-        <v>144.2436139679902</v>
+        <v>144.2436303900958</v>
       </c>
       <c r="D464" t="n">
-        <v>122.020208994126</v>
+        <v>122.0202228861016</v>
       </c>
       <c r="E464" t="n">
-        <v>142.0391460401569</v>
+        <v>142.0391622112843</v>
       </c>
       <c r="F464" t="n">
         <v>1332366</v>
@@ -9872,16 +9872,16 @@
         <v>43914</v>
       </c>
       <c r="B473" t="n">
-        <v>126.012077331543</v>
+        <v>126.0120849609375</v>
       </c>
       <c r="C473" t="n">
-        <v>131.0763909200707</v>
+        <v>131.0763988560838</v>
       </c>
       <c r="D473" t="n">
-        <v>118.8624514630232</v>
+        <v>118.862458659544</v>
       </c>
       <c r="E473" t="n">
-        <v>120.3519559052967</v>
+        <v>120.3519631919995</v>
       </c>
       <c r="F473" t="n">
         <v>1251533</v>
@@ -9892,16 +9892,16 @@
         <v>43915</v>
       </c>
       <c r="B474" t="n">
-        <v>135.2470092773438</v>
+        <v>135.2470245361328</v>
       </c>
       <c r="C474" t="n">
-        <v>138.3749779043099</v>
+        <v>138.3749935160015</v>
       </c>
       <c r="D474" t="n">
-        <v>119.8455377798463</v>
+        <v>119.8455513010161</v>
       </c>
       <c r="E474" t="n">
-        <v>123.8969843731464</v>
+        <v>123.8969983514071</v>
       </c>
       <c r="F474" t="n">
         <v>1102933</v>
@@ -9912,16 +9912,16 @@
         <v>43916</v>
       </c>
       <c r="B475" t="n">
-        <v>150.1122741699219</v>
+        <v>150.1122894287109</v>
       </c>
       <c r="C475" t="n">
-        <v>158.9301463915598</v>
+        <v>158.9301625466783</v>
       </c>
       <c r="D475" t="n">
-        <v>132.8936043550962</v>
+        <v>132.8936178636216</v>
       </c>
       <c r="E475" t="n">
-        <v>135.2470168120774</v>
+        <v>135.2470305598253</v>
       </c>
       <c r="F475" t="n">
         <v>1421366</v>
@@ -9972,16 +9972,16 @@
         <v>43921</v>
       </c>
       <c r="B478" t="n">
-        <v>126.3099746704102</v>
+        <v>126.3099899291992</v>
       </c>
       <c r="C478" t="n">
-        <v>138.5239142237709</v>
+        <v>138.5239309580564</v>
       </c>
       <c r="D478" t="n">
-        <v>125.1183741375995</v>
+        <v>125.1183892524381</v>
       </c>
       <c r="E478" t="n">
-        <v>134.1447674924694</v>
+        <v>134.1447836977352</v>
       </c>
       <c r="F478" t="n">
         <v>993633</v>
@@ -9992,16 +9992,16 @@
         <v>43922</v>
       </c>
       <c r="B479" t="n">
-        <v>119.398681640625</v>
+        <v>119.3986892700195</v>
       </c>
       <c r="C479" t="n">
-        <v>125.6248148518141</v>
+        <v>125.6248228790491</v>
       </c>
       <c r="D479" t="n">
-        <v>115.7344980529492</v>
+        <v>115.734505448208</v>
       </c>
       <c r="E479" t="n">
-        <v>120.6498675737846</v>
+        <v>120.649875283128</v>
       </c>
       <c r="F479" t="n">
         <v>1115733</v>
@@ -10032,16 +10032,16 @@
         <v>43924</v>
       </c>
       <c r="B481" t="n">
-        <v>112.4576034545898</v>
+        <v>112.4575958251953</v>
       </c>
       <c r="C481" t="n">
-        <v>121.3946315436963</v>
+        <v>121.3946233079923</v>
       </c>
       <c r="D481" t="n">
-        <v>109.1509012433774</v>
+        <v>109.1508938383175</v>
       </c>
       <c r="E481" t="n">
-        <v>121.245679560342</v>
+        <v>121.2456713347432</v>
       </c>
       <c r="F481" t="n">
         <v>1289233</v>
@@ -10052,16 +10052,16 @@
         <v>43927</v>
       </c>
       <c r="B482" t="n">
-        <v>128.0973968505859</v>
+        <v>128.0973815917969</v>
       </c>
       <c r="C482" t="n">
-        <v>135.6342865636811</v>
+        <v>135.6342704071079</v>
       </c>
       <c r="D482" t="n">
-        <v>118.2368759992794</v>
+        <v>118.2368619150623</v>
       </c>
       <c r="E482" t="n">
-        <v>119.1603691633358</v>
+        <v>119.1603549691134</v>
       </c>
       <c r="F482" t="n">
         <v>1479633</v>
@@ -10072,16 +10072,16 @@
         <v>43928</v>
       </c>
       <c r="B483" t="n">
-        <v>143.8861389160156</v>
+        <v>143.8861236572266</v>
       </c>
       <c r="C483" t="n">
-        <v>154.908479064077</v>
+        <v>154.9084626363945</v>
       </c>
       <c r="D483" t="n">
-        <v>138.0175022823959</v>
+        <v>138.017487645962</v>
       </c>
       <c r="E483" t="n">
-        <v>145.1969102426065</v>
+        <v>145.1968948448132</v>
       </c>
       <c r="F483" t="n">
         <v>1844300</v>
@@ -10112,16 +10112,16 @@
         <v>43930</v>
       </c>
       <c r="B485" t="n">
-        <v>145.5543975830078</v>
+        <v>145.5543823242188</v>
       </c>
       <c r="C485" t="n">
-        <v>153.0912875462937</v>
+        <v>153.0912714973958</v>
       </c>
       <c r="D485" t="n">
-        <v>144.422374644459</v>
+        <v>144.4223595043424</v>
       </c>
       <c r="E485" t="n">
-        <v>150.4995488248761</v>
+        <v>150.4995330476759</v>
       </c>
       <c r="F485" t="n">
         <v>918500</v>
@@ -10152,16 +10152,16 @@
         <v>43935</v>
       </c>
       <c r="B487" t="n">
-        <v>157.8576812744141</v>
+        <v>157.8576965332031</v>
       </c>
       <c r="C487" t="n">
-        <v>161.5814423628801</v>
+        <v>161.5814579816142</v>
       </c>
       <c r="D487" t="n">
-        <v>150.0824663034543</v>
+        <v>150.082480810678</v>
       </c>
       <c r="E487" t="n">
-        <v>150.171832933092</v>
+        <v>150.171847448954</v>
       </c>
       <c r="F487" t="n">
         <v>964366</v>
@@ -10172,16 +10172,16 @@
         <v>43936</v>
       </c>
       <c r="B488" t="n">
-        <v>155.0574188232422</v>
+        <v>155.0574340820312</v>
       </c>
       <c r="C488" t="n">
-        <v>160.8069149169485</v>
+        <v>160.8069307415302</v>
       </c>
       <c r="D488" t="n">
-        <v>148.0865483834452</v>
+        <v>148.0865629562494</v>
       </c>
       <c r="E488" t="n">
-        <v>154.610570485105</v>
+        <v>154.6105856999209</v>
       </c>
       <c r="F488" t="n">
         <v>821233</v>
@@ -10212,16 +10212,16 @@
         <v>43938</v>
       </c>
       <c r="B490" t="n">
-        <v>156.1000671386719</v>
+        <v>156.1000823974609</v>
       </c>
       <c r="C490" t="n">
-        <v>159.6450950891468</v>
+        <v>159.6451106944625</v>
       </c>
       <c r="D490" t="n">
-        <v>151.8400909746121</v>
+        <v>151.8401058169883</v>
       </c>
       <c r="E490" t="n">
-        <v>159.6450950891468</v>
+        <v>159.6451106944625</v>
       </c>
       <c r="F490" t="n">
         <v>607466</v>
@@ -10252,16 +10252,16 @@
         <v>43943</v>
       </c>
       <c r="B492" t="n">
-        <v>158.8109741210938</v>
+        <v>158.8109588623047</v>
       </c>
       <c r="C492" t="n">
-        <v>166.8245161896017</v>
+        <v>166.8245001608599</v>
       </c>
       <c r="D492" t="n">
-        <v>157.6193734644301</v>
+        <v>157.6193583201317</v>
       </c>
       <c r="E492" t="n">
-        <v>166.8245161896017</v>
+        <v>166.8245001608599</v>
       </c>
       <c r="F492" t="n">
         <v>2119233</v>
@@ -10272,16 +10272,16 @@
         <v>43944</v>
       </c>
       <c r="B493" t="n">
-        <v>151.8401184082031</v>
+        <v>151.8401031494141</v>
       </c>
       <c r="C493" t="n">
-        <v>160.8665135898119</v>
+        <v>160.8664974239381</v>
       </c>
       <c r="D493" t="n">
-        <v>144.809654144183</v>
+        <v>144.8096395919027</v>
       </c>
       <c r="E493" t="n">
-        <v>159.8238572305839</v>
+        <v>159.8238411694891</v>
       </c>
       <c r="F493" t="n">
         <v>1242300</v>
@@ -10292,16 +10292,16 @@
         <v>43945</v>
       </c>
       <c r="B494" t="n">
-        <v>148.9504852294922</v>
+        <v>148.9504547119141</v>
       </c>
       <c r="C494" t="n">
-        <v>152.0188615887333</v>
+        <v>152.0188304424938</v>
       </c>
       <c r="D494" t="n">
-        <v>136.110945523656</v>
+        <v>136.1109176366947</v>
       </c>
       <c r="E494" t="n">
-        <v>146.9545541821467</v>
+        <v>146.954524073503</v>
       </c>
       <c r="F494" t="n">
         <v>1301233</v>
@@ -10312,16 +10312,16 @@
         <v>43948</v>
       </c>
       <c r="B495" t="n">
-        <v>156.9639892578125</v>
+        <v>156.9640045166016</v>
       </c>
       <c r="C495" t="n">
-        <v>157.9172788832115</v>
+        <v>157.9172942346718</v>
       </c>
       <c r="D495" t="n">
-        <v>152.8231682250355</v>
+        <v>152.8231830812869</v>
       </c>
       <c r="E495" t="n">
-        <v>153.8658244913087</v>
+        <v>153.8658394489189</v>
       </c>
       <c r="F495" t="n">
         <v>935633</v>
@@ -10352,16 +10352,16 @@
         <v>43950</v>
       </c>
       <c r="B497" t="n">
-        <v>161.9591064453125</v>
+        <v>161.9591369628906</v>
       </c>
       <c r="C497" t="n">
-        <v>164.7900292416936</v>
+        <v>164.790060292696</v>
       </c>
       <c r="D497" t="n">
-        <v>159.7241602160489</v>
+        <v>159.7241903125012</v>
       </c>
       <c r="E497" t="n">
-        <v>161.3631147214959</v>
+        <v>161.3631451267727</v>
       </c>
       <c r="F497" t="n">
         <v>594666</v>
@@ -10392,16 +10392,16 @@
         <v>43955</v>
       </c>
       <c r="B499" t="n">
-        <v>152.4531402587891</v>
+        <v>152.4531555175781</v>
       </c>
       <c r="C499" t="n">
-        <v>152.8107322907865</v>
+        <v>152.8107475853664</v>
       </c>
       <c r="D499" t="n">
-        <v>147.5660592592903</v>
+        <v>147.5660740289393</v>
       </c>
       <c r="E499" t="n">
-        <v>148.5494411364585</v>
+        <v>148.5494560045326</v>
       </c>
       <c r="F499" t="n">
         <v>865433</v>
@@ -10412,16 +10412,16 @@
         <v>43956</v>
       </c>
       <c r="B500" t="n">
-        <v>154.6582946777344</v>
+        <v>154.6583099365234</v>
       </c>
       <c r="C500" t="n">
-        <v>157.6382233426491</v>
+        <v>157.6382388954418</v>
       </c>
       <c r="D500" t="n">
-        <v>151.4101681891011</v>
+        <v>151.4101831274257</v>
       </c>
       <c r="E500" t="n">
-        <v>153.615316613674</v>
+        <v>153.6153317695615</v>
       </c>
       <c r="F500" t="n">
         <v>670733</v>
@@ -10452,16 +10452,16 @@
         <v>43958</v>
       </c>
       <c r="B502" t="n">
-        <v>158.7109832763672</v>
+        <v>158.7109985351562</v>
       </c>
       <c r="C502" t="n">
-        <v>165.0880281493818</v>
+        <v>165.0880440212726</v>
       </c>
       <c r="D502" t="n">
-        <v>156.9826193707709</v>
+        <v>156.9826344633917</v>
       </c>
       <c r="E502" t="n">
-        <v>157.9660011862015</v>
+        <v>157.9660163733665</v>
       </c>
       <c r="F502" t="n">
         <v>1272300</v>
@@ -10492,16 +10492,16 @@
         <v>43962</v>
       </c>
       <c r="B504" t="n">
-        <v>146.9700622558594</v>
+        <v>146.9700775146484</v>
       </c>
       <c r="C504" t="n">
-        <v>152.6915345641711</v>
+        <v>152.6915504169773</v>
       </c>
       <c r="D504" t="n">
-        <v>146.5826721647091</v>
+        <v>146.5826873832784</v>
       </c>
       <c r="E504" t="n">
-        <v>149.9499906975384</v>
+        <v>149.9500062657109</v>
       </c>
       <c r="F504" t="n">
         <v>466500</v>
@@ -10532,16 +10532,16 @@
         <v>43964</v>
       </c>
       <c r="B506" t="n">
-        <v>145.7781066894531</v>
+        <v>145.7780914306641</v>
       </c>
       <c r="C506" t="n">
-        <v>153.9431125479351</v>
+        <v>153.943096434504</v>
       </c>
       <c r="D506" t="n">
-        <v>145.7781066894531</v>
+        <v>145.7780914306641</v>
       </c>
       <c r="E506" t="n">
-        <v>152.3041578240206</v>
+        <v>152.304141882141</v>
       </c>
       <c r="F506" t="n">
         <v>632666</v>
@@ -10552,16 +10552,16 @@
         <v>43965</v>
       </c>
       <c r="B507" t="n">
-        <v>141.2783966064453</v>
+        <v>141.2784118652344</v>
       </c>
       <c r="C507" t="n">
-        <v>147.5064510038155</v>
+        <v>147.5064669352663</v>
       </c>
       <c r="D507" t="n">
-        <v>138.3580644443282</v>
+        <v>138.3580793877065</v>
       </c>
       <c r="E507" t="n">
-        <v>145.658894849621</v>
+        <v>145.6589105815262</v>
       </c>
       <c r="F507" t="n">
         <v>844800</v>
@@ -10572,16 +10572,16 @@
         <v>43966</v>
       </c>
       <c r="B508" t="n">
-        <v>139.7586669921875</v>
+        <v>139.7586364746094</v>
       </c>
       <c r="C508" t="n">
-        <v>143.5431743950443</v>
+        <v>143.5431430510845</v>
       </c>
       <c r="D508" t="n">
-        <v>134.9907775634558</v>
+        <v>134.9907480869898</v>
       </c>
       <c r="E508" t="n">
-        <v>140.324860777095</v>
+        <v>140.3248301358833</v>
       </c>
       <c r="F508" t="n">
         <v>930266</v>
@@ -10592,16 +10592,16 @@
         <v>43969</v>
       </c>
       <c r="B509" t="n">
-        <v>147.6256713867188</v>
+        <v>147.6256866455078</v>
       </c>
       <c r="C509" t="n">
-        <v>148.3408555281376</v>
+        <v>148.340870860849</v>
       </c>
       <c r="D509" t="n">
-        <v>142.4405939397833</v>
+        <v>142.4406086626357</v>
       </c>
       <c r="E509" t="n">
-        <v>144.4967521355379</v>
+        <v>144.4967670709176</v>
       </c>
       <c r="F509" t="n">
         <v>822866</v>
@@ -10632,16 +10632,16 @@
         <v>43971</v>
       </c>
       <c r="B511" t="n">
-        <v>151.6783447265625</v>
+        <v>151.6783599853516</v>
       </c>
       <c r="C511" t="n">
-        <v>154.1814886976806</v>
+        <v>154.181504208285</v>
       </c>
       <c r="D511" t="n">
-        <v>149.3540043317309</v>
+        <v>149.3540193566921</v>
       </c>
       <c r="E511" t="n">
-        <v>150.7545742452956</v>
+        <v>150.7545894111537</v>
       </c>
       <c r="F511" t="n">
         <v>544933</v>
@@ -10732,16 +10732,16 @@
         <v>43978</v>
       </c>
       <c r="B516" t="n">
-        <v>163.8960571289062</v>
+        <v>163.8960723876953</v>
       </c>
       <c r="C516" t="n">
-        <v>165.9820130095902</v>
+        <v>165.9820284625826</v>
       </c>
       <c r="D516" t="n">
-        <v>160.320137092505</v>
+        <v>160.3201520183744</v>
       </c>
       <c r="E516" t="n">
-        <v>165.5350116375157</v>
+        <v>165.535027048892</v>
       </c>
       <c r="F516" t="n">
         <v>627900</v>
@@ -10752,16 +10752,16 @@
         <v>43979</v>
       </c>
       <c r="B517" t="n">
-        <v>163.9258728027344</v>
+        <v>163.9258880615234</v>
       </c>
       <c r="C517" t="n">
-        <v>168.0679717816257</v>
+        <v>168.0679874259757</v>
       </c>
       <c r="D517" t="n">
-        <v>161.3333342871174</v>
+        <v>161.333349304584</v>
       </c>
       <c r="E517" t="n">
-        <v>163.4490884655809</v>
+        <v>163.4491036799892</v>
       </c>
       <c r="F517" t="n">
         <v>560100</v>
@@ -10772,16 +10772,16 @@
         <v>43980</v>
       </c>
       <c r="B518" t="n">
-        <v>163.4788818359375</v>
+        <v>163.4788665771484</v>
       </c>
       <c r="C518" t="n">
-        <v>165.0582403275507</v>
+        <v>165.0582249213475</v>
       </c>
       <c r="D518" t="n">
-        <v>157.9958090679723</v>
+        <v>157.9957943209622</v>
       </c>
       <c r="E518" t="n">
-        <v>163.9556661593735</v>
+        <v>163.9556508560823</v>
       </c>
       <c r="F518" t="n">
         <v>1761600</v>
@@ -10792,16 +10792,16 @@
         <v>43983</v>
       </c>
       <c r="B519" t="n">
-        <v>162.4060974121094</v>
+        <v>162.4061126708984</v>
       </c>
       <c r="C519" t="n">
-        <v>164.73043792095</v>
+        <v>164.7304533981214</v>
       </c>
       <c r="D519" t="n">
-        <v>160.4095508452898</v>
+        <v>160.4095659164942</v>
       </c>
       <c r="E519" t="n">
-        <v>161.8995150417311</v>
+        <v>161.8995302529245</v>
       </c>
       <c r="F519" t="n">
         <v>557733</v>
@@ -10812,16 +10812,16 @@
         <v>43984</v>
       </c>
       <c r="B520" t="n">
-        <v>162.5848999023438</v>
+        <v>162.5848846435547</v>
       </c>
       <c r="C520" t="n">
-        <v>164.1642736062624</v>
+        <v>164.1642581992473</v>
       </c>
       <c r="D520" t="n">
-        <v>159.7241787043098</v>
+        <v>159.7241637140029</v>
       </c>
       <c r="E520" t="n">
-        <v>163.8662777098608</v>
+        <v>163.8662623308128</v>
       </c>
       <c r="F520" t="n">
         <v>917300</v>
@@ -10872,16 +10872,16 @@
         <v>43987</v>
       </c>
       <c r="B523" t="n">
-        <v>177.4547271728516</v>
+        <v>177.4547576904297</v>
       </c>
       <c r="C523" t="n">
-        <v>182.371621075518</v>
+        <v>182.3716524386734</v>
       </c>
       <c r="D523" t="n">
-        <v>175.1005886265878</v>
+        <v>175.1006187393156</v>
       </c>
       <c r="E523" t="n">
-        <v>178.7957009929787</v>
+        <v>178.7957317411692</v>
       </c>
       <c r="F523" t="n">
         <v>929700</v>
@@ -10932,16 +10932,16 @@
         <v>43992</v>
       </c>
       <c r="B526" t="n">
-        <v>180.8518829345703</v>
+        <v>180.8518524169922</v>
       </c>
       <c r="C526" t="n">
-        <v>183.5636292344882</v>
+        <v>183.5635982593205</v>
       </c>
       <c r="D526" t="n">
-        <v>178.4977438772397</v>
+        <v>178.4977137569072</v>
       </c>
       <c r="E526" t="n">
-        <v>181.4180767191804</v>
+        <v>181.4180461060608</v>
       </c>
       <c r="F526" t="n">
         <v>715466</v>
@@ -10952,16 +10952,16 @@
         <v>43994</v>
       </c>
       <c r="B527" t="n">
-        <v>177.9315490722656</v>
+        <v>177.9315643310547</v>
       </c>
       <c r="C527" t="n">
-        <v>180.2260917661188</v>
+        <v>180.2261072216798</v>
       </c>
       <c r="D527" t="n">
-        <v>171.7630899407515</v>
+        <v>171.763104670555</v>
       </c>
       <c r="E527" t="n">
-        <v>174.0874307093273</v>
+        <v>174.0874456384582</v>
       </c>
       <c r="F527" t="n">
         <v>1048900</v>
@@ -10972,16 +10972,16 @@
         <v>43997</v>
       </c>
       <c r="B528" t="n">
-        <v>180.3750915527344</v>
+        <v>180.3750610351562</v>
       </c>
       <c r="C528" t="n">
-        <v>182.8782360569759</v>
+        <v>182.8782051158919</v>
       </c>
       <c r="D528" t="n">
-        <v>173.5212611882256</v>
+        <v>173.5212318302438</v>
       </c>
       <c r="E528" t="n">
-        <v>175.7860059255433</v>
+        <v>175.7859761843905</v>
       </c>
       <c r="F528" t="n">
         <v>826966</v>
@@ -10992,16 +10992,16 @@
         <v>43998</v>
       </c>
       <c r="B529" t="n">
-        <v>179.8386993408203</v>
+        <v>179.8386840820312</v>
       </c>
       <c r="C529" t="n">
-        <v>186.6627311857664</v>
+        <v>186.6627153479782</v>
       </c>
       <c r="D529" t="n">
-        <v>177.1269533220862</v>
+        <v>177.1269382933809</v>
       </c>
       <c r="E529" t="n">
-        <v>183.5934082749279</v>
+        <v>183.5933926975627</v>
       </c>
       <c r="F529" t="n">
         <v>733633</v>
@@ -11032,16 +11032,16 @@
         <v>44000</v>
       </c>
       <c r="B531" t="n">
-        <v>179.6897125244141</v>
+        <v>179.689697265625</v>
       </c>
       <c r="C531" t="n">
-        <v>182.9080412988048</v>
+        <v>182.9080257667236</v>
       </c>
       <c r="D531" t="n">
-        <v>178.4381478016134</v>
+        <v>178.438132649104</v>
       </c>
       <c r="E531" t="n">
-        <v>181.7756688857845</v>
+        <v>181.7756534498614</v>
       </c>
       <c r="F531" t="n">
         <v>656233</v>
@@ -11052,16 +11052,16 @@
         <v>44001</v>
       </c>
       <c r="B532" t="n">
-        <v>187.1693115234375</v>
+        <v>187.1693267822266</v>
       </c>
       <c r="C532" t="n">
-        <v>190.1194421040784</v>
+        <v>190.1194576033739</v>
       </c>
       <c r="D532" t="n">
-        <v>181.0306657700721</v>
+        <v>181.0306805284143</v>
       </c>
       <c r="E532" t="n">
-        <v>181.7756479337349</v>
+        <v>181.775662752811</v>
       </c>
       <c r="F532" t="n">
         <v>2381566</v>
@@ -11092,16 +11092,16 @@
         <v>44005</v>
       </c>
       <c r="B534" t="n">
-        <v>185.9475555419922</v>
+        <v>185.9475402832031</v>
       </c>
       <c r="C534" t="n">
-        <v>188.8380901381925</v>
+        <v>188.8380746422072</v>
       </c>
       <c r="D534" t="n">
-        <v>179.6003077546513</v>
+        <v>179.6002930167151</v>
       </c>
       <c r="E534" t="n">
-        <v>182.6696308050322</v>
+        <v>182.6696158152284</v>
       </c>
       <c r="F534" t="n">
         <v>796833</v>
@@ -11212,16 +11212,16 @@
         <v>44013</v>
       </c>
       <c r="B540" t="n">
-        <v>187.7057037353516</v>
+        <v>187.7057189941406</v>
       </c>
       <c r="C540" t="n">
-        <v>189.9108521119912</v>
+        <v>189.910867550039</v>
       </c>
       <c r="D540" t="n">
-        <v>185.2323575408232</v>
+        <v>185.2323725985514</v>
       </c>
       <c r="E540" t="n">
-        <v>185.7985512500661</v>
+        <v>185.7985663538207</v>
       </c>
       <c r="F540" t="n">
         <v>601100</v>
@@ -11232,16 +11232,16 @@
         <v>44014</v>
       </c>
       <c r="B541" t="n">
-        <v>180.9710845947266</v>
+        <v>180.9710693359375</v>
       </c>
       <c r="C541" t="n">
-        <v>190.5366460610093</v>
+        <v>190.5366299956888</v>
       </c>
       <c r="D541" t="n">
-        <v>179.987702600919</v>
+        <v>179.9876874250449</v>
       </c>
       <c r="E541" t="n">
-        <v>190.1492559101219</v>
+        <v>190.1492398774646</v>
       </c>
       <c r="F541" t="n">
         <v>782133</v>
@@ -11252,16 +11252,16 @@
         <v>44015</v>
       </c>
       <c r="B542" t="n">
-        <v>181.5074310302734</v>
+        <v>181.5074462890625</v>
       </c>
       <c r="C542" t="n">
-        <v>184.4575613007869</v>
+        <v>184.4575768075846</v>
       </c>
       <c r="D542" t="n">
-        <v>178.0805164690132</v>
+        <v>178.0805314397118</v>
       </c>
       <c r="E542" t="n">
-        <v>179.3916922144411</v>
+        <v>179.3917072953663</v>
       </c>
       <c r="F542" t="n">
         <v>277066</v>
@@ -11272,16 +11272,16 @@
         <v>44018</v>
       </c>
       <c r="B543" t="n">
-        <v>181.775634765625</v>
+        <v>181.7756652832031</v>
       </c>
       <c r="C543" t="n">
-        <v>185.2919436544383</v>
+        <v>185.2919747623554</v>
       </c>
       <c r="D543" t="n">
-        <v>180.0770688865721</v>
+        <v>180.0770991189848</v>
       </c>
       <c r="E543" t="n">
-        <v>182.1034287126949</v>
+        <v>182.103459285305</v>
       </c>
       <c r="F543" t="n">
         <v>817833</v>
@@ -11312,16 +11312,16 @@
         <v>44020</v>
       </c>
       <c r="B545" t="n">
-        <v>180.9412689208984</v>
+        <v>180.9412536621094</v>
       </c>
       <c r="C545" t="n">
-        <v>183.5040093454935</v>
+        <v>183.5039938705884</v>
       </c>
       <c r="D545" t="n">
-        <v>177.1567620095117</v>
+        <v>177.1567470698704</v>
       </c>
       <c r="E545" t="n">
-        <v>180.4346713566746</v>
+        <v>180.4346561406069</v>
       </c>
       <c r="F545" t="n">
         <v>677066</v>
@@ -11352,16 +11352,16 @@
         <v>44022</v>
       </c>
       <c r="B547" t="n">
-        <v>180.1963043212891</v>
+        <v>180.1962890625</v>
       </c>
       <c r="C547" t="n">
-        <v>181.0604788526272</v>
+        <v>181.060463520661</v>
       </c>
       <c r="D547" t="n">
-        <v>177.9315595685599</v>
+        <v>177.9315445015465</v>
       </c>
       <c r="E547" t="n">
-        <v>178.8255321763785</v>
+        <v>178.8255170336646</v>
       </c>
       <c r="F547" t="n">
         <v>618666</v>
@@ -11372,16 +11372,16 @@
         <v>44025</v>
       </c>
       <c r="B548" t="n">
-        <v>175.6965942382812</v>
+        <v>175.6966094970703</v>
       </c>
       <c r="C548" t="n">
-        <v>181.2690612990238</v>
+        <v>181.269077041767</v>
       </c>
       <c r="D548" t="n">
-        <v>175.6369829349472</v>
+        <v>175.6369981885591</v>
       </c>
       <c r="E548" t="n">
-        <v>180.1366890428852</v>
+        <v>180.1367046872849</v>
       </c>
       <c r="F548" t="n">
         <v>495033</v>
@@ -11392,16 +11392,16 @@
         <v>44026</v>
       </c>
       <c r="B549" t="n">
-        <v>178.4679260253906</v>
+        <v>178.4679107666016</v>
       </c>
       <c r="C549" t="n">
-        <v>179.212908192047</v>
+        <v>179.2128928695628</v>
       </c>
       <c r="D549" t="n">
-        <v>173.2828489329264</v>
+        <v>173.282834117455</v>
       </c>
       <c r="E549" t="n">
-        <v>175.0708091642418</v>
+        <v>175.0707941959021</v>
       </c>
       <c r="F549" t="n">
         <v>493066</v>
@@ -11412,16 +11412,16 @@
         <v>44027</v>
       </c>
       <c r="B550" t="n">
-        <v>180.6730804443359</v>
+        <v>180.6730651855469</v>
       </c>
       <c r="C550" t="n">
-        <v>184.7257853841829</v>
+        <v>184.7257697831216</v>
       </c>
       <c r="D550" t="n">
-        <v>178.9745143790679</v>
+        <v>178.9744992637316</v>
       </c>
       <c r="E550" t="n">
-        <v>180.5836862189801</v>
+        <v>180.5836709677409</v>
       </c>
       <c r="F550" t="n">
         <v>693400</v>
@@ -11432,16 +11432,16 @@
         <v>44028</v>
       </c>
       <c r="B551" t="n">
-        <v>181.3882598876953</v>
+        <v>181.3882751464844</v>
       </c>
       <c r="C551" t="n">
-        <v>183.1166239835562</v>
+        <v>183.1166393877391</v>
       </c>
       <c r="D551" t="n">
-        <v>178.3487350502892</v>
+        <v>178.3487500533865</v>
       </c>
       <c r="E551" t="n">
-        <v>181.8054480853098</v>
+        <v>181.8054633791936</v>
       </c>
       <c r="F551" t="n">
         <v>439600</v>
@@ -11492,16 +11492,16 @@
         <v>44033</v>
       </c>
       <c r="B554" t="n">
-        <v>195.1853332519531</v>
+        <v>195.1853179931641</v>
       </c>
       <c r="C554" t="n">
-        <v>198.5824502103585</v>
+        <v>198.5824346859968</v>
       </c>
       <c r="D554" t="n">
-        <v>190.5068384424615</v>
+        <v>190.506823549418</v>
       </c>
       <c r="E554" t="n">
-        <v>196.0495077398707</v>
+        <v>196.0494924135241</v>
       </c>
       <c r="F554" t="n">
         <v>627900</v>
@@ -11532,16 +11532,16 @@
         <v>44035</v>
       </c>
       <c r="B556" t="n">
-        <v>191.6392211914062</v>
+        <v>191.6392059326172</v>
       </c>
       <c r="C556" t="n">
-        <v>196.6753083314747</v>
+        <v>196.6752926716999</v>
       </c>
       <c r="D556" t="n">
-        <v>190.0002663513249</v>
+        <v>190.0002512230334</v>
       </c>
       <c r="E556" t="n">
-        <v>194.8277517984564</v>
+        <v>194.8277362857887</v>
       </c>
       <c r="F556" t="n">
         <v>517766</v>
@@ -11552,16 +11552,16 @@
         <v>44036</v>
       </c>
       <c r="B557" t="n">
-        <v>195.7515106201172</v>
+        <v>195.7514953613281</v>
       </c>
       <c r="C557" t="n">
-        <v>196.079304599603</v>
+        <v>196.0792893152624</v>
       </c>
       <c r="D557" t="n">
-        <v>188.0335061132565</v>
+        <v>188.0334914560843</v>
       </c>
       <c r="E557" t="n">
-        <v>192.7119857370506</v>
+        <v>192.7119707151919</v>
       </c>
       <c r="F557" t="n">
         <v>615366</v>
@@ -11572,16 +11572,16 @@
         <v>44039</v>
       </c>
       <c r="B558" t="n">
-        <v>192.5629730224609</v>
+        <v>192.56298828125</v>
       </c>
       <c r="C558" t="n">
-        <v>201.8603501984987</v>
+        <v>201.8603661940167</v>
       </c>
       <c r="D558" t="n">
-        <v>192.1159867956388</v>
+        <v>192.1160020190085</v>
       </c>
       <c r="E558" t="n">
-        <v>196.8838600906739</v>
+        <v>196.8838756918523</v>
       </c>
       <c r="F558" t="n">
         <v>595333</v>
@@ -11612,16 +11612,16 @@
         <v>44041</v>
       </c>
       <c r="B560" t="n">
-        <v>195.1853332519531</v>
+        <v>195.1853179931641</v>
       </c>
       <c r="C560" t="n">
-        <v>196.6752976279222</v>
+        <v>196.6752822526539</v>
       </c>
       <c r="D560" t="n">
-        <v>193.3973729694499</v>
+        <v>193.3973578504363</v>
       </c>
       <c r="E560" t="n">
-        <v>195.4535310835039</v>
+        <v>195.4535158037483</v>
       </c>
       <c r="F560" t="n">
         <v>374733</v>
@@ -11652,16 +11652,16 @@
         <v>44043</v>
       </c>
       <c r="B562" t="n">
-        <v>194.112548828125</v>
+        <v>194.1125335693359</v>
       </c>
       <c r="C562" t="n">
-        <v>199.8936176362711</v>
+        <v>199.8936019230441</v>
       </c>
       <c r="D562" t="n">
-        <v>191.8180062117766</v>
+        <v>191.8179911333568</v>
       </c>
       <c r="E562" t="n">
-        <v>197.5692617895057</v>
+        <v>197.5692462589916</v>
       </c>
       <c r="F562" t="n">
         <v>964966</v>
@@ -11672,16 +11672,16 @@
         <v>44046</v>
       </c>
       <c r="B563" t="n">
-        <v>194.3211669921875</v>
+        <v>194.3211517333984</v>
       </c>
       <c r="C563" t="n">
-        <v>196.7647001844907</v>
+        <v>196.7646847338267</v>
       </c>
       <c r="D563" t="n">
-        <v>190.1790525137064</v>
+        <v>190.1790375801708</v>
       </c>
       <c r="E563" t="n">
-        <v>196.0495160412063</v>
+        <v>196.0495006467012</v>
       </c>
       <c r="F563" t="n">
         <v>823000</v>
@@ -11692,16 +11692,16 @@
         <v>44047</v>
       </c>
       <c r="B564" t="n">
-        <v>191.1922149658203</v>
+        <v>191.1922302246094</v>
       </c>
       <c r="C564" t="n">
-        <v>194.7979334263718</v>
+        <v>194.7979489729283</v>
       </c>
       <c r="D564" t="n">
-        <v>188.8976723660878</v>
+        <v>188.8976874417525</v>
       </c>
       <c r="E564" t="n">
-        <v>193.4271614185521</v>
+        <v>193.4271768557092</v>
       </c>
       <c r="F564" t="n">
         <v>411633</v>
@@ -11712,16 +11712,16 @@
         <v>44048</v>
       </c>
       <c r="B565" t="n">
-        <v>194.4999542236328</v>
+        <v>194.4999237060547</v>
       </c>
       <c r="C565" t="n">
-        <v>198.0758749175139</v>
+        <v>198.075843838864</v>
       </c>
       <c r="D565" t="n">
-        <v>193.0993840221375</v>
+        <v>193.0993537243127</v>
       </c>
       <c r="E565" t="n">
-        <v>193.3675818633541</v>
+        <v>193.3675515234483</v>
       </c>
       <c r="F565" t="n">
         <v>503800</v>
@@ -11732,16 +11732,16 @@
         <v>44049</v>
       </c>
       <c r="B566" t="n">
-        <v>197.4202575683594</v>
+        <v>197.4202728271484</v>
       </c>
       <c r="C566" t="n">
-        <v>198.6122259034699</v>
+        <v>198.6122412543873</v>
       </c>
       <c r="D566" t="n">
-        <v>194.7979211684363</v>
+        <v>194.7979362245427</v>
       </c>
       <c r="E566" t="n">
-        <v>194.7979211684363</v>
+        <v>194.7979362245427</v>
       </c>
       <c r="F566" t="n">
         <v>434133</v>
@@ -11752,16 +11752,16 @@
         <v>44050</v>
       </c>
       <c r="B567" t="n">
-        <v>195.2449188232422</v>
+        <v>195.2449340820312</v>
       </c>
       <c r="C567" t="n">
-        <v>198.9996276347122</v>
+        <v>198.9996431869394</v>
       </c>
       <c r="D567" t="n">
-        <v>193.6953583812642</v>
+        <v>193.6953735189519</v>
       </c>
       <c r="E567" t="n">
-        <v>196.9732828621334</v>
+        <v>196.9732982559976</v>
       </c>
       <c r="F567" t="n">
         <v>600933</v>
@@ -11772,16 +11772,16 @@
         <v>44053</v>
       </c>
       <c r="B568" t="n">
-        <v>191.9074096679688</v>
+        <v>191.9073791503906</v>
       </c>
       <c r="C568" t="n">
-        <v>197.0030927124582</v>
+        <v>197.0030613845523</v>
       </c>
       <c r="D568" t="n">
-        <v>191.0432351752126</v>
+        <v>191.0432047950576</v>
       </c>
       <c r="E568" t="n">
-        <v>195.3641227956948</v>
+        <v>195.3640917284218</v>
       </c>
       <c r="F568" t="n">
         <v>446333</v>
@@ -11812,16 +11812,16 @@
         <v>44055</v>
       </c>
       <c r="B570" t="n">
-        <v>182.6994171142578</v>
+        <v>182.6994323730469</v>
       </c>
       <c r="C570" t="n">
-        <v>189.2552661659586</v>
+        <v>189.2552819722826</v>
       </c>
       <c r="D570" t="n">
-        <v>179.2427041457414</v>
+        <v>179.2427191158309</v>
       </c>
       <c r="E570" t="n">
-        <v>186.7521218717291</v>
+        <v>186.7521374689941</v>
       </c>
       <c r="F570" t="n">
         <v>1065533</v>
@@ -11832,16 +11832,16 @@
         <v>44056</v>
       </c>
       <c r="B571" t="n">
-        <v>186.5733337402344</v>
+        <v>186.5733184814453</v>
       </c>
       <c r="C571" t="n">
-        <v>190.9240192427385</v>
+        <v>190.9240036281312</v>
       </c>
       <c r="D571" t="n">
-        <v>184.6363831579516</v>
+        <v>184.6363680575749</v>
       </c>
       <c r="E571" t="n">
-        <v>184.8449696747432</v>
+        <v>184.8449545573073</v>
       </c>
       <c r="F571" t="n">
         <v>646800</v>
@@ -11852,16 +11852,16 @@
         <v>44057</v>
       </c>
       <c r="B572" t="n">
-        <v>191.0730285644531</v>
+        <v>191.0730133056641</v>
       </c>
       <c r="C572" t="n">
-        <v>193.0993734084735</v>
+        <v>193.0993579878638</v>
       </c>
       <c r="D572" t="n">
-        <v>187.0799198685499</v>
+        <v>187.0799049286441</v>
       </c>
       <c r="E572" t="n">
-        <v>188.7784858939576</v>
+        <v>188.7784708184071</v>
       </c>
       <c r="F572" t="n">
         <v>670600</v>
@@ -11872,16 +11872,16 @@
         <v>44060</v>
       </c>
       <c r="B573" t="n">
-        <v>186.0965270996094</v>
+        <v>186.0965423583984</v>
       </c>
       <c r="C573" t="n">
-        <v>193.0397502898912</v>
+        <v>193.0397661179825</v>
       </c>
       <c r="D573" t="n">
-        <v>183.0271894529275</v>
+        <v>183.0272044600494</v>
       </c>
       <c r="E573" t="n">
-        <v>191.8775800798015</v>
+        <v>191.877595812602</v>
       </c>
       <c r="F573" t="n">
         <v>389400</v>
@@ -11892,16 +11892,16 @@
         <v>44061</v>
       </c>
       <c r="B574" t="n">
-        <v>187.5268707275391</v>
+        <v>187.5269012451172</v>
       </c>
       <c r="C574" t="n">
-        <v>190.3876065851611</v>
+        <v>190.3876375682871</v>
       </c>
       <c r="D574" t="n">
-        <v>186.0965179554263</v>
+        <v>186.096548240233</v>
       </c>
       <c r="E574" t="n">
-        <v>187.9738720728162</v>
+        <v>187.973902663138</v>
       </c>
       <c r="F574" t="n">
         <v>544533</v>
@@ -11912,16 +11912,16 @@
         <v>44062</v>
       </c>
       <c r="B575" t="n">
-        <v>184.6959838867188</v>
+        <v>184.6959686279297</v>
       </c>
       <c r="C575" t="n">
-        <v>188.3612986254054</v>
+        <v>188.3612830638038</v>
       </c>
       <c r="D575" t="n">
-        <v>183.7721981050549</v>
+        <v>183.772182922585</v>
       </c>
       <c r="E575" t="n">
-        <v>187.7355087461073</v>
+        <v>187.7354932362058</v>
       </c>
       <c r="F575" t="n">
         <v>275166</v>
@@ -11952,16 +11952,16 @@
         <v>44064</v>
       </c>
       <c r="B577" t="n">
-        <v>186.5733337402344</v>
+        <v>186.5733184814453</v>
       </c>
       <c r="C577" t="n">
-        <v>188.1228942060606</v>
+        <v>188.1228788205416</v>
       </c>
       <c r="D577" t="n">
-        <v>182.9080190924604</v>
+        <v>182.9080041334369</v>
       </c>
       <c r="E577" t="n">
-        <v>184.7555754532611</v>
+        <v>184.7555603431363</v>
       </c>
       <c r="F577" t="n">
         <v>431666</v>
@@ -12012,16 +12012,16 @@
         <v>44069</v>
       </c>
       <c r="B580" t="n">
-        <v>186.0369262695312</v>
+        <v>186.0369110107422</v>
       </c>
       <c r="C580" t="n">
-        <v>191.0134164761023</v>
+        <v>191.0134008091405</v>
       </c>
       <c r="D580" t="n">
-        <v>182.5206173711653</v>
+        <v>182.5206024007847</v>
       </c>
       <c r="E580" t="n">
-        <v>186.6627160935192</v>
+        <v>186.6627007834027</v>
       </c>
       <c r="F580" t="n">
         <v>788933</v>
@@ -12032,16 +12032,16 @@
         <v>44070</v>
       </c>
       <c r="B581" t="n">
-        <v>187.0203247070312</v>
+        <v>187.0203094482422</v>
       </c>
       <c r="C581" t="n">
-        <v>189.6128632921078</v>
+        <v>189.6128478217963</v>
       </c>
       <c r="D581" t="n">
-        <v>184.755580098999</v>
+        <v>184.755565024988</v>
       </c>
       <c r="E581" t="n">
-        <v>184.755580098999</v>
+        <v>184.755565024988</v>
       </c>
       <c r="F581" t="n">
         <v>465466</v>
@@ -12072,16 +12072,16 @@
         <v>44074</v>
       </c>
       <c r="B583" t="n">
-        <v>192.8907775878906</v>
+        <v>192.8907928466797</v>
       </c>
       <c r="C583" t="n">
-        <v>194.8873242612342</v>
+        <v>194.8873396779618</v>
       </c>
       <c r="D583" t="n">
-        <v>189.0466594494166</v>
+        <v>189.0466744041134</v>
       </c>
       <c r="E583" t="n">
-        <v>191.9967899283081</v>
+        <v>191.9968051163775</v>
       </c>
       <c r="F583" t="n">
         <v>944966</v>
@@ -12092,16 +12092,16 @@
         <v>44075</v>
       </c>
       <c r="B584" t="n">
-        <v>205.5852661132812</v>
+        <v>205.5852813720703</v>
       </c>
       <c r="C584" t="n">
-        <v>207.2838168514087</v>
+        <v>207.2838322362663</v>
       </c>
       <c r="D584" t="n">
-        <v>193.5463599589462</v>
+        <v>193.5463743241929</v>
       </c>
       <c r="E584" t="n">
-        <v>195.1853145528165</v>
+        <v>195.1853290397085</v>
       </c>
       <c r="F584" t="n">
         <v>1357600</v>
@@ -12132,16 +12132,16 @@
         <v>44077</v>
       </c>
       <c r="B586" t="n">
-        <v>199.3572235107422</v>
+        <v>199.3572387695312</v>
       </c>
       <c r="C586" t="n">
-        <v>204.6018967184463</v>
+        <v>204.6019123786623</v>
       </c>
       <c r="D586" t="n">
-        <v>196.5858965371773</v>
+        <v>196.5859115838492</v>
       </c>
       <c r="E586" t="n">
-        <v>202.0391562624793</v>
+        <v>202.0391717265434</v>
       </c>
       <c r="F586" t="n">
         <v>527733</v>
@@ -12172,16 +12172,16 @@
         <v>44082</v>
       </c>
       <c r="B588" t="n">
-        <v>200.6684265136719</v>
+        <v>200.6683959960938</v>
       </c>
       <c r="C588" t="n">
-        <v>207.7904551258864</v>
+        <v>207.7904235251929</v>
       </c>
       <c r="D588" t="n">
-        <v>198.3142722571118</v>
+        <v>198.3142420975526</v>
       </c>
       <c r="E588" t="n">
-        <v>198.4632778036654</v>
+        <v>198.4632476214454</v>
       </c>
       <c r="F588" t="n">
         <v>1005833</v>
@@ -12212,16 +12212,16 @@
         <v>44084</v>
       </c>
       <c r="B590" t="n">
-        <v>195.1853332519531</v>
+        <v>195.1853179931641</v>
       </c>
       <c r="C590" t="n">
-        <v>205.7938723336365</v>
+        <v>205.7938562455153</v>
       </c>
       <c r="D590" t="n">
-        <v>193.7549650259506</v>
+        <v>193.7549498789818</v>
       </c>
       <c r="E590" t="n">
-        <v>205.6746800337034</v>
+        <v>205.6746639549002</v>
       </c>
       <c r="F590" t="n">
         <v>559966</v>
@@ -12232,16 +12232,16 @@
         <v>44085</v>
       </c>
       <c r="B591" t="n">
-        <v>189.7766265869141</v>
+        <v>189.7766418457031</v>
       </c>
       <c r="C591" t="n">
-        <v>197.9303936359225</v>
+        <v>197.9304095503066</v>
       </c>
       <c r="D591" t="n">
-        <v>187.8053910426163</v>
+        <v>187.8054061429102</v>
       </c>
       <c r="E591" t="n">
-        <v>194.5852588258493</v>
+        <v>194.5852744712713</v>
       </c>
       <c r="F591" t="n">
         <v>1048366</v>
@@ -12252,16 +12252,16 @@
         <v>44088</v>
       </c>
       <c r="B592" t="n">
-        <v>197.1837158203125</v>
+        <v>197.1836853027344</v>
       </c>
       <c r="C592" t="n">
-        <v>199.1250853489015</v>
+        <v>199.125054530863</v>
       </c>
       <c r="D592" t="n">
-        <v>190.0753061062856</v>
+        <v>190.0752766888564</v>
       </c>
       <c r="E592" t="n">
-        <v>190.3441157921762</v>
+        <v>190.344086333144</v>
       </c>
       <c r="F592" t="n">
         <v>434033</v>
@@ -12292,16 +12292,16 @@
         <v>44090</v>
       </c>
       <c r="B594" t="n">
-        <v>197.8407897949219</v>
+        <v>197.8407745361328</v>
       </c>
       <c r="C594" t="n">
-        <v>202.7688861098723</v>
+        <v>202.7688704709959</v>
       </c>
       <c r="D594" t="n">
-        <v>196.7954323484103</v>
+        <v>196.7954171702461</v>
       </c>
       <c r="E594" t="n">
-        <v>198.9458793484435</v>
+        <v>198.9458640044226</v>
       </c>
       <c r="F594" t="n">
         <v>602300</v>
@@ -12312,16 +12312,16 @@
         <v>44091</v>
       </c>
       <c r="B595" t="n">
-        <v>191.3297271728516</v>
+        <v>191.3297119140625</v>
       </c>
       <c r="C595" t="n">
-        <v>195.7799516843192</v>
+        <v>195.7799360706191</v>
       </c>
       <c r="D595" t="n">
-        <v>190.8817211544465</v>
+        <v>190.8817059313864</v>
       </c>
       <c r="E595" t="n">
-        <v>195.6306214086107</v>
+        <v>195.6306058068198</v>
       </c>
       <c r="F595" t="n">
         <v>482133</v>
@@ -12332,16 +12332,16 @@
         <v>44092</v>
       </c>
       <c r="B596" t="n">
-        <v>187.3872375488281</v>
+        <v>187.3872528076172</v>
       </c>
       <c r="C596" t="n">
-        <v>192.9724171801275</v>
+        <v>192.9724328937132</v>
       </c>
       <c r="D596" t="n">
-        <v>185.4757342513885</v>
+        <v>185.4757493545254</v>
       </c>
       <c r="E596" t="n">
-        <v>192.225735492474</v>
+        <v>192.225751145258</v>
       </c>
       <c r="F596" t="n">
         <v>571800</v>
@@ -12392,16 +12392,16 @@
         <v>44097</v>
       </c>
       <c r="B599" t="n">
-        <v>187.0885620117188</v>
+        <v>187.0885772705078</v>
       </c>
       <c r="C599" t="n">
-        <v>189.8960924517536</v>
+        <v>189.8961079395225</v>
       </c>
       <c r="D599" t="n">
-        <v>185.1770587124788</v>
+        <v>185.1770738153672</v>
       </c>
       <c r="E599" t="n">
-        <v>185.8640082963715</v>
+        <v>185.8640234552869</v>
       </c>
       <c r="F599" t="n">
         <v>596200</v>
@@ -12412,16 +12412,16 @@
         <v>44098</v>
       </c>
       <c r="B600" t="n">
-        <v>187.2677612304688</v>
+        <v>187.2677764892578</v>
       </c>
       <c r="C600" t="n">
-        <v>190.7920918841326</v>
+        <v>190.7921074300882</v>
       </c>
       <c r="D600" t="n">
-        <v>185.535454358271</v>
+        <v>185.5354694759098</v>
       </c>
       <c r="E600" t="n">
-        <v>187.65603507529</v>
+        <v>187.6560503657161</v>
       </c>
       <c r="F600" t="n">
         <v>378566</v>
@@ -12452,16 +12452,16 @@
         <v>44102</v>
       </c>
       <c r="B602" t="n">
-        <v>180.6372528076172</v>
+        <v>180.6372375488281</v>
       </c>
       <c r="C602" t="n">
-        <v>189.5078357131096</v>
+        <v>189.5078197050047</v>
       </c>
       <c r="D602" t="n">
-        <v>179.3529516804262</v>
+        <v>179.3529365301246</v>
       </c>
       <c r="E602" t="n">
-        <v>188.940350286844</v>
+        <v>188.9403343266758</v>
       </c>
       <c r="F602" t="n">
         <v>595500</v>
@@ -12472,16 +12472,16 @@
         <v>44103</v>
       </c>
       <c r="B603" t="n">
-        <v>180.9359283447266</v>
+        <v>180.9359130859375</v>
       </c>
       <c r="C603" t="n">
-        <v>183.5045002136614</v>
+        <v>183.5044847382582</v>
       </c>
       <c r="D603" t="n">
-        <v>178.6062697236995</v>
+        <v>178.6062546613765</v>
       </c>
       <c r="E603" t="n">
-        <v>181.2644549486086</v>
+        <v>181.2644396621141</v>
       </c>
       <c r="F603" t="n">
         <v>676133</v>
@@ -12492,16 +12492,16 @@
         <v>44104</v>
       </c>
       <c r="B604" t="n">
-        <v>185.5951995849609</v>
+        <v>185.59521484375</v>
       </c>
       <c r="C604" t="n">
-        <v>186.9690987597785</v>
+        <v>186.9691141315233</v>
       </c>
       <c r="D604" t="n">
-        <v>180.3982937920956</v>
+        <v>180.3983086236188</v>
       </c>
       <c r="E604" t="n">
-        <v>181.5929814613258</v>
+        <v>181.5929963910708</v>
       </c>
       <c r="F604" t="n">
         <v>757400</v>
@@ -12512,16 +12512,16 @@
         <v>44105</v>
       </c>
       <c r="B605" t="n">
-        <v>188.1637725830078</v>
+        <v>188.1638031005859</v>
       </c>
       <c r="C605" t="n">
-        <v>191.1803651821317</v>
+        <v>191.1803961889597</v>
       </c>
       <c r="D605" t="n">
-        <v>183.2954089158922</v>
+        <v>183.2954386438886</v>
       </c>
       <c r="E605" t="n">
-        <v>185.9237276713053</v>
+        <v>185.923757825579</v>
       </c>
       <c r="F605" t="n">
         <v>698566</v>
@@ -12592,16 +12592,16 @@
         <v>44111</v>
       </c>
       <c r="B609" t="n">
-        <v>187.4170989990234</v>
+        <v>187.4171142578125</v>
       </c>
       <c r="C609" t="n">
-        <v>190.1648820732568</v>
+        <v>190.1648975557599</v>
       </c>
       <c r="D609" t="n">
-        <v>183.6836906524294</v>
+        <v>183.6837056072585</v>
       </c>
       <c r="E609" t="n">
-        <v>186.7600154841163</v>
+        <v>186.7600306894081</v>
       </c>
       <c r="F609" t="n">
         <v>573633</v>
@@ -12652,16 +12652,16 @@
         <v>44117</v>
       </c>
       <c r="B612" t="n">
-        <v>196.9447326660156</v>
+        <v>196.9447631835938</v>
       </c>
       <c r="C612" t="n">
-        <v>198.4679771195207</v>
+        <v>198.4680078731332</v>
       </c>
       <c r="D612" t="n">
-        <v>190.2843454955226</v>
+        <v>190.2843749810402</v>
       </c>
       <c r="E612" t="n">
-        <v>193.539866362723</v>
+        <v>193.5398963526999</v>
       </c>
       <c r="F612" t="n">
         <v>922633</v>
@@ -12712,16 +12712,16 @@
         <v>44120</v>
       </c>
       <c r="B615" t="n">
-        <v>193.1814880371094</v>
+        <v>193.1815032958984</v>
       </c>
       <c r="C615" t="n">
-        <v>198.8562812657416</v>
+        <v>198.8562969727645</v>
       </c>
       <c r="D615" t="n">
-        <v>190.0155648341094</v>
+        <v>190.0155798428323</v>
       </c>
       <c r="E615" t="n">
-        <v>198.6770697533628</v>
+        <v>198.6770854462303</v>
       </c>
       <c r="F615" t="n">
         <v>665566</v>
@@ -12812,16 +12812,16 @@
         <v>44127</v>
       </c>
       <c r="B620" t="n">
-        <v>190.3441162109375</v>
+        <v>190.3441009521484</v>
       </c>
       <c r="C620" t="n">
-        <v>195.242346721261</v>
+        <v>195.2423310698091</v>
       </c>
       <c r="D620" t="n">
-        <v>188.940350859762</v>
+        <v>188.9403357135048</v>
       </c>
       <c r="E620" t="n">
-        <v>194.1671231666126</v>
+        <v>194.1671076013551</v>
       </c>
       <c r="F620" t="n">
         <v>403166</v>
@@ -12872,16 +12872,16 @@
         <v>44132</v>
       </c>
       <c r="B623" t="n">
-        <v>192.9425659179688</v>
+        <v>192.9425354003906</v>
       </c>
       <c r="C623" t="n">
-        <v>196.437031015196</v>
+        <v>196.436999944901</v>
       </c>
       <c r="D623" t="n">
-        <v>192.9425659179688</v>
+        <v>192.9425354003906</v>
       </c>
       <c r="E623" t="n">
-        <v>195.6007511068256</v>
+        <v>195.6007201688043</v>
       </c>
       <c r="F623" t="n">
         <v>477733</v>
@@ -12912,16 +12912,16 @@
         <v>44134</v>
       </c>
       <c r="B625" t="n">
-        <v>192.255615234375</v>
+        <v>192.2555999755859</v>
       </c>
       <c r="C625" t="n">
-        <v>199.8120308055818</v>
+        <v>199.8120149470612</v>
       </c>
       <c r="D625" t="n">
-        <v>192.255615234375</v>
+        <v>192.2555999755859</v>
       </c>
       <c r="E625" t="n">
-        <v>198.6472091128537</v>
+        <v>198.6471933467818</v>
       </c>
       <c r="F625" t="n">
         <v>632900</v>
@@ -12952,16 +12952,16 @@
         <v>44139</v>
       </c>
       <c r="B627" t="n">
-        <v>205.3076019287109</v>
+        <v>205.3076171875</v>
       </c>
       <c r="C627" t="n">
-        <v>208.0553851222939</v>
+        <v>208.0554005853026</v>
       </c>
       <c r="D627" t="n">
-        <v>195.9591476304417</v>
+        <v>195.9591621944386</v>
       </c>
       <c r="E627" t="n">
-        <v>196.5564838770755</v>
+        <v>196.5564984854674</v>
       </c>
       <c r="F627" t="n">
         <v>937700</v>
@@ -12992,16 +12992,16 @@
         <v>44141</v>
       </c>
       <c r="B629" t="n">
-        <v>213.5509643554688</v>
+        <v>213.5509796142578</v>
       </c>
       <c r="C629" t="n">
-        <v>214.2379139441398</v>
+        <v>214.2379292520132</v>
       </c>
       <c r="D629" t="n">
-        <v>205.1881354642133</v>
+        <v>205.1881501254558</v>
       </c>
       <c r="E629" t="n">
-        <v>206.8308291135134</v>
+        <v>206.8308438921308</v>
       </c>
       <c r="F629" t="n">
         <v>849833</v>
@@ -13012,16 +13012,16 @@
         <v>44144</v>
       </c>
       <c r="B630" t="n">
-        <v>208.5332641601562</v>
+        <v>208.5332489013672</v>
       </c>
       <c r="C630" t="n">
-        <v>226.0653517136236</v>
+        <v>226.0653351719772</v>
       </c>
       <c r="D630" t="n">
-        <v>207.7865824333327</v>
+        <v>207.7865672291798</v>
       </c>
       <c r="E630" t="n">
-        <v>221.0177911397615</v>
+        <v>221.0177749674551</v>
       </c>
       <c r="F630" t="n">
         <v>887833</v>
@@ -13032,16 +13032,16 @@
         <v>44145</v>
       </c>
       <c r="B631" t="n">
-        <v>204.0233001708984</v>
+        <v>204.0232849121094</v>
       </c>
       <c r="C631" t="n">
-        <v>211.0122451280538</v>
+        <v>211.0122293465654</v>
       </c>
       <c r="D631" t="n">
-        <v>201.6040587576205</v>
+        <v>201.6040436797651</v>
       </c>
       <c r="E631" t="n">
-        <v>209.0708757486434</v>
+        <v>209.070860112349</v>
       </c>
       <c r="F631" t="n">
         <v>798233</v>
@@ -13052,16 +13052,16 @@
         <v>44146</v>
       </c>
       <c r="B632" t="n">
-        <v>204.5907897949219</v>
+        <v>204.5907745361328</v>
       </c>
       <c r="C632" t="n">
-        <v>206.5620252678551</v>
+        <v>206.5620098620474</v>
       </c>
       <c r="D632" t="n">
-        <v>200.7379170088981</v>
+        <v>200.737902037464</v>
       </c>
       <c r="E632" t="n">
-        <v>202.9779621526382</v>
+        <v>202.977947014137</v>
       </c>
       <c r="F632" t="n">
         <v>574366</v>
@@ -13132,16 +13132,16 @@
         <v>44152</v>
       </c>
       <c r="B636" t="n">
-        <v>215.7611541748047</v>
+        <v>215.7611389160156</v>
       </c>
       <c r="C636" t="n">
-        <v>220.390574829844</v>
+        <v>220.3905592436589</v>
       </c>
       <c r="D636" t="n">
-        <v>215.7611541748047</v>
+        <v>215.7611389160156</v>
       </c>
       <c r="E636" t="n">
-        <v>219.793238559895</v>
+        <v>219.7932230159539</v>
       </c>
       <c r="F636" t="n">
         <v>945033</v>
@@ -13152,16 +13152,16 @@
         <v>44153</v>
       </c>
       <c r="B637" t="n">
-        <v>213.1029663085938</v>
+        <v>213.1029510498047</v>
       </c>
       <c r="C637" t="n">
-        <v>217.4337111775966</v>
+        <v>217.4336956087137</v>
       </c>
       <c r="D637" t="n">
-        <v>213.1029663085938</v>
+        <v>213.1029510498047</v>
       </c>
       <c r="E637" t="n">
-        <v>216.8662409688433</v>
+        <v>216.8662254405929</v>
       </c>
       <c r="F637" t="n">
         <v>504433</v>
@@ -13272,16 +13272,16 @@
         <v>44162</v>
       </c>
       <c r="B643" t="n">
-        <v>214.2976531982422</v>
+        <v>214.2976379394531</v>
       </c>
       <c r="C643" t="n">
-        <v>216.3883680864437</v>
+        <v>216.388352678788</v>
       </c>
       <c r="D643" t="n">
-        <v>207.5775177320952</v>
+        <v>207.5775029518047</v>
       </c>
       <c r="E643" t="n">
-        <v>212.6549594941399</v>
+        <v>212.6549443523167</v>
       </c>
       <c r="F643" t="n">
         <v>618080</v>
@@ -13332,16 +13332,16 @@
         <v>44167</v>
       </c>
       <c r="B646" t="n">
-        <v>220.7191009521484</v>
+        <v>220.7191162109375</v>
       </c>
       <c r="C646" t="n">
-        <v>221.4657826300592</v>
+        <v>221.4657979404679</v>
       </c>
       <c r="D646" t="n">
-        <v>213.5509598824612</v>
+        <v>213.5509746457012</v>
       </c>
       <c r="E646" t="n">
-        <v>214.1483113013008</v>
+        <v>214.148326105837</v>
       </c>
       <c r="F646" t="n">
         <v>812640</v>
@@ -13412,16 +13412,16 @@
         <v>44173</v>
       </c>
       <c r="B650" t="n">
-        <v>228.6339263916016</v>
+        <v>228.6339416503906</v>
       </c>
       <c r="C650" t="n">
-        <v>230.7246411908779</v>
+        <v>230.7246565891991</v>
       </c>
       <c r="D650" t="n">
-        <v>221.7644609504555</v>
+        <v>221.7644757507836</v>
       </c>
       <c r="E650" t="n">
-        <v>223.8551757497318</v>
+        <v>223.8551906895921</v>
       </c>
       <c r="F650" t="n">
         <v>500300</v>
@@ -13452,16 +13452,16 @@
         <v>44175</v>
       </c>
       <c r="B652" t="n">
-        <v>227.8872528076172</v>
+        <v>227.8872680664062</v>
       </c>
       <c r="C652" t="n">
-        <v>233.4127005239284</v>
+        <v>233.4127161526883</v>
       </c>
       <c r="D652" t="n">
-        <v>225.6472076678649</v>
+        <v>225.6472227766659</v>
       </c>
       <c r="E652" t="n">
-        <v>226.6925651046716</v>
+        <v>226.6925802834673</v>
       </c>
       <c r="F652" t="n">
         <v>713620</v>
@@ -13512,16 +13512,16 @@
         <v>44180</v>
       </c>
       <c r="B655" t="n">
-        <v>226.6925659179688</v>
+        <v>226.6925506591797</v>
       </c>
       <c r="C655" t="n">
-        <v>228.1859293498279</v>
+        <v>228.1859139905198</v>
       </c>
       <c r="D655" t="n">
-        <v>223.1085027962737</v>
+        <v>223.1084877787297</v>
       </c>
       <c r="E655" t="n">
-        <v>226.0952296599921</v>
+        <v>226.09521444141</v>
       </c>
       <c r="F655" t="n">
         <v>364800</v>
@@ -13692,16 +13692,16 @@
         <v>44195</v>
       </c>
       <c r="B664" t="n">
-        <v>227.8872528076172</v>
+        <v>227.8872680664062</v>
       </c>
       <c r="C664" t="n">
-        <v>235.6527456636806</v>
+        <v>235.6527614424286</v>
       </c>
       <c r="D664" t="n">
-        <v>225.9458833914209</v>
+        <v>225.9458985202205</v>
       </c>
       <c r="E664" t="n">
-        <v>234.1593822371791</v>
+        <v>234.1593979159351</v>
       </c>
       <c r="F664" t="n">
         <v>659613</v>
@@ -13712,16 +13712,16 @@
         <v>44200</v>
       </c>
       <c r="B665" t="n">
-        <v>224.6018676757812</v>
+        <v>224.6018524169922</v>
       </c>
       <c r="C665" t="n">
-        <v>231.6206636977356</v>
+        <v>231.6206479621102</v>
       </c>
       <c r="D665" t="n">
-        <v>220.4204378866018</v>
+        <v>220.4204229118868</v>
       </c>
       <c r="E665" t="n">
-        <v>230.1273002562511</v>
+        <v>230.1272846220805</v>
       </c>
       <c r="F665" t="n">
         <v>564553</v>
@@ -13732,16 +13732,16 @@
         <v>44201</v>
       </c>
       <c r="B666" t="n">
-        <v>218.7777404785156</v>
+        <v>218.7777557373047</v>
       </c>
       <c r="C666" t="n">
-        <v>225.6472061166881</v>
+        <v>225.6472218545923</v>
       </c>
       <c r="D666" t="n">
-        <v>218.1803890355101</v>
+        <v>218.1804042526365</v>
       </c>
       <c r="E666" t="n">
-        <v>224.9005244085703</v>
+        <v>224.9005400943967</v>
       </c>
       <c r="F666" t="n">
         <v>585466</v>
@@ -13752,16 +13752,16 @@
         <v>44202</v>
       </c>
       <c r="B667" t="n">
-        <v>210.7135620117188</v>
+        <v>210.7135772705078</v>
       </c>
       <c r="C667" t="n">
-        <v>220.5697692085711</v>
+        <v>220.5697851810959</v>
       </c>
       <c r="D667" t="n">
-        <v>210.4149014955867</v>
+        <v>210.4149167327483</v>
       </c>
       <c r="E667" t="n">
-        <v>220.5697692085711</v>
+        <v>220.5697851810959</v>
       </c>
       <c r="F667" t="n">
         <v>989980</v>
@@ -13772,16 +13772,16 @@
         <v>44203</v>
       </c>
       <c r="B668" t="n">
-        <v>213.2523040771484</v>
+        <v>213.2522888183594</v>
       </c>
       <c r="C668" t="n">
-        <v>217.2843885524602</v>
+        <v>217.2843730051644</v>
       </c>
       <c r="D668" t="n">
-        <v>207.1295198233158</v>
+        <v>207.1295050026288</v>
       </c>
       <c r="E668" t="n">
-        <v>211.4602648446455</v>
+        <v>211.4602497140818</v>
       </c>
       <c r="F668" t="n">
         <v>485820</v>
@@ -13812,16 +13812,16 @@
         <v>44207</v>
       </c>
       <c r="B670" t="n">
-        <v>272.2713012695312</v>
+        <v>272.2713317871094</v>
       </c>
       <c r="C670" t="n">
-        <v>276.4601026942797</v>
+        <v>276.4601336813603</v>
       </c>
       <c r="D670" t="n">
-        <v>249.9809523860654</v>
+        <v>249.9809804052258</v>
       </c>
       <c r="E670" t="n">
-        <v>250.7289504664762</v>
+        <v>250.7289785694761</v>
       </c>
       <c r="F670" t="n">
         <v>3239386</v>
@@ -13832,16 +13832,16 @@
         <v>44208</v>
       </c>
       <c r="B671" t="n">
-        <v>265.0905456542969</v>
+        <v>265.0904846191406</v>
       </c>
       <c r="C671" t="n">
-        <v>275.562520286358</v>
+        <v>275.5624568401063</v>
       </c>
       <c r="D671" t="n">
-        <v>258.9569665998859</v>
+        <v>258.9569069769413</v>
       </c>
       <c r="E671" t="n">
-        <v>275.1137396352299</v>
+        <v>275.1136762923066</v>
       </c>
       <c r="F671" t="n">
         <v>1327226</v>
@@ -13852,16 +13852,16 @@
         <v>44209</v>
       </c>
       <c r="B672" t="n">
-        <v>254.3193359375</v>
+        <v>254.3193511962891</v>
       </c>
       <c r="C672" t="n">
-        <v>263.5944995443026</v>
+        <v>263.5945153595879</v>
       </c>
       <c r="D672" t="n">
-        <v>252.3745440592369</v>
+        <v>252.3745592013412</v>
       </c>
       <c r="E672" t="n">
-        <v>262.3977209309737</v>
+        <v>262.3977366744541</v>
       </c>
       <c r="F672" t="n">
         <v>1017226</v>
@@ -13932,16 +13932,16 @@
         <v>44215</v>
       </c>
       <c r="B676" t="n">
-        <v>259.8545532226562</v>
+        <v>259.8544921875</v>
       </c>
       <c r="C676" t="n">
-        <v>273.7673314200941</v>
+        <v>273.7672671170767</v>
       </c>
       <c r="D676" t="n">
-        <v>255.3665641829826</v>
+        <v>255.3665042019742</v>
       </c>
       <c r="E676" t="n">
-        <v>269.8777470062683</v>
+        <v>269.8776836168443</v>
       </c>
       <c r="F676" t="n">
         <v>761093</v>
@@ -13952,16 +13952,16 @@
         <v>44216</v>
       </c>
       <c r="B677" t="n">
-        <v>259.8545532226562</v>
+        <v>259.8544921875</v>
       </c>
       <c r="C677" t="n">
-        <v>264.4921662458846</v>
+        <v>264.4921041214365</v>
       </c>
       <c r="D677" t="n">
-        <v>256.8625605295405</v>
+        <v>256.8625001971495</v>
       </c>
       <c r="E677" t="n">
-        <v>259.405772580363</v>
+        <v>259.4057116506173</v>
       </c>
       <c r="F677" t="n">
         <v>662453</v>
@@ -13972,16 +13972,16 @@
         <v>44217</v>
       </c>
       <c r="B678" t="n">
-        <v>263.5945434570312</v>
+        <v>263.594482421875</v>
       </c>
       <c r="C678" t="n">
-        <v>270.4761509835964</v>
+        <v>270.4760883550081</v>
       </c>
       <c r="D678" t="n">
-        <v>255.516187553887</v>
+        <v>255.5161283892691</v>
       </c>
       <c r="E678" t="n">
-        <v>259.1065544281184</v>
+        <v>259.1064944321533</v>
       </c>
       <c r="F678" t="n">
         <v>986426</v>
@@ -14012,16 +14012,16 @@
         <v>44222</v>
       </c>
       <c r="B680" t="n">
-        <v>267.7833251953125</v>
+        <v>267.7832946777344</v>
       </c>
       <c r="C680" t="n">
-        <v>276.1608979968802</v>
+        <v>276.1608665245628</v>
       </c>
       <c r="D680" t="n">
-        <v>261.5001532031671</v>
+        <v>261.5001234016424</v>
       </c>
       <c r="E680" t="n">
-        <v>263.4449300406782</v>
+        <v>263.4449000175196</v>
       </c>
       <c r="F680" t="n">
         <v>884853</v>
@@ -14032,16 +14032,16 @@
         <v>44223</v>
       </c>
       <c r="B681" t="n">
-        <v>257.4609375</v>
+        <v>257.4609069824219</v>
       </c>
       <c r="C681" t="n">
-        <v>270.6257161100528</v>
+        <v>270.625684032016</v>
       </c>
       <c r="D681" t="n">
-        <v>257.4609375</v>
+        <v>257.4609069824219</v>
       </c>
       <c r="E681" t="n">
-        <v>267.9329108010492</v>
+        <v>267.9328790421983</v>
       </c>
       <c r="F681" t="n">
         <v>863460</v>
@@ -14052,16 +14052,16 @@
         <v>44224</v>
       </c>
       <c r="B682" t="n">
-        <v>266.8857421875</v>
+        <v>266.8857116699219</v>
       </c>
       <c r="C682" t="n">
-        <v>269.7281412040435</v>
+        <v>269.7281103614457</v>
       </c>
       <c r="D682" t="n">
-        <v>257.9097645159661</v>
+        <v>257.9097350247639</v>
       </c>
       <c r="E682" t="n">
-        <v>257.9097645159661</v>
+        <v>257.9097350247639</v>
       </c>
       <c r="F682" t="n">
         <v>574346</v>
@@ -14072,16 +14072,16 @@
         <v>44225</v>
       </c>
       <c r="B683" t="n">
-        <v>256.862548828125</v>
+        <v>256.8625183105469</v>
       </c>
       <c r="C683" t="n">
-        <v>265.240152336105</v>
+        <v>265.2401208231923</v>
       </c>
       <c r="D683" t="n">
-        <v>256.2641746656598</v>
+        <v>256.2641442191738</v>
       </c>
       <c r="E683" t="n">
-        <v>264.1929366795464</v>
+        <v>264.1929052910523</v>
       </c>
       <c r="F683" t="n">
         <v>726533</v>
@@ -14092,16 +14092,16 @@
         <v>44228</v>
       </c>
       <c r="B684" t="n">
-        <v>261.9489440917969</v>
+        <v>261.9489135742188</v>
       </c>
       <c r="C684" t="n">
-        <v>264.6417495861901</v>
+        <v>264.6417187548947</v>
       </c>
       <c r="D684" t="n">
-        <v>256.7129570807941</v>
+        <v>256.712927173219</v>
       </c>
       <c r="E684" t="n">
-        <v>264.6417495861901</v>
+        <v>264.6417187548947</v>
       </c>
       <c r="F684" t="n">
         <v>678393</v>
@@ -14112,16 +14112,16 @@
         <v>44229</v>
       </c>
       <c r="B685" t="n">
-        <v>265.6889343261719</v>
+        <v>265.6889038085938</v>
       </c>
       <c r="C685" t="n">
-        <v>271.5233259292311</v>
+        <v>271.5232947415027</v>
       </c>
       <c r="D685" t="n">
-        <v>260.7521648436775</v>
+        <v>260.7521348931468</v>
       </c>
       <c r="E685" t="n">
-        <v>266.5865260106143</v>
+        <v>266.5864953899369</v>
       </c>
       <c r="F685" t="n">
         <v>627486</v>
@@ -14192,16 +14192,16 @@
         <v>44235</v>
       </c>
       <c r="B689" t="n">
-        <v>270.3264770507812</v>
+        <v>270.3265380859375</v>
       </c>
       <c r="C689" t="n">
-        <v>272.8696886255836</v>
+        <v>272.8697502349542</v>
       </c>
       <c r="D689" t="n">
-        <v>262.5473096791787</v>
+        <v>262.5473689579302</v>
       </c>
       <c r="E689" t="n">
-        <v>267.6337023926656</v>
+        <v>267.6337628198388</v>
       </c>
       <c r="F689" t="n">
         <v>645166</v>
@@ -14252,16 +14252,16 @@
         <v>44238</v>
       </c>
       <c r="B692" t="n">
-        <v>263.5945434570312</v>
+        <v>263.594482421875</v>
       </c>
       <c r="C692" t="n">
-        <v>265.2401637831981</v>
+        <v>265.2401023669995</v>
       </c>
       <c r="D692" t="n">
-        <v>256.7129663665896</v>
+        <v>256.7129069248583</v>
       </c>
       <c r="E692" t="n">
-        <v>257.9097756154158</v>
+        <v>257.909715896564</v>
       </c>
       <c r="F692" t="n">
         <v>869180</v>
@@ -14372,16 +14372,16 @@
         <v>44250</v>
       </c>
       <c r="B698" t="n">
-        <v>243.8473663330078</v>
+        <v>243.8473968505859</v>
       </c>
       <c r="C698" t="n">
-        <v>250.7289423631573</v>
+        <v>250.7289737419669</v>
       </c>
       <c r="D698" t="n">
-        <v>241.4537786402757</v>
+        <v>241.4538088582955</v>
       </c>
       <c r="E698" t="n">
-        <v>247.7369501382124</v>
+        <v>247.7369811425732</v>
       </c>
       <c r="F698" t="n">
         <v>535220</v>
@@ -14392,16 +14392,16 @@
         <v>44251</v>
       </c>
       <c r="B699" t="n">
-        <v>240.8553771972656</v>
+        <v>240.8553924560547</v>
       </c>
       <c r="C699" t="n">
-        <v>245.9417701321336</v>
+        <v>245.9417857131583</v>
       </c>
       <c r="D699" t="n">
-        <v>235.4697972105133</v>
+        <v>235.4698121281125</v>
       </c>
       <c r="E699" t="n">
-        <v>245.1937720663036</v>
+        <v>245.1937875999407</v>
       </c>
       <c r="F699" t="n">
         <v>632986</v>
@@ -14412,16 +14412,16 @@
         <v>44252</v>
       </c>
       <c r="B700" t="n">
-        <v>236.9658203125</v>
+        <v>236.9657897949219</v>
       </c>
       <c r="C700" t="n">
-        <v>244.4458018221362</v>
+        <v>244.4457703412507</v>
       </c>
       <c r="D700" t="n">
-        <v>231.4306309517569</v>
+        <v>231.4306011470266</v>
       </c>
       <c r="E700" t="n">
-        <v>240.5562023062886</v>
+        <v>240.5561713263241</v>
       </c>
       <c r="F700" t="n">
         <v>728733</v>
@@ -14432,16 +14432,16 @@
         <v>44253</v>
       </c>
       <c r="B701" t="n">
-        <v>231.87939453125</v>
+        <v>231.8794097900391</v>
       </c>
       <c r="C701" t="n">
-        <v>240.5561688313882</v>
+        <v>240.5561846611511</v>
       </c>
       <c r="D701" t="n">
-        <v>227.39140625</v>
+        <v>227.3914212134577</v>
       </c>
       <c r="E701" t="n">
-        <v>236.3673828125</v>
+        <v>236.3673983666205</v>
       </c>
       <c r="F701" t="n">
         <v>875760</v>
@@ -14472,16 +14472,16 @@
         <v>44257</v>
       </c>
       <c r="B703" t="n">
-        <v>245.3433685302734</v>
+        <v>245.3433837890625</v>
       </c>
       <c r="C703" t="n">
-        <v>246.5401624063213</v>
+        <v>246.5401777395433</v>
       </c>
       <c r="D703" t="n">
-        <v>231.8794031840999</v>
+        <v>231.8794176055164</v>
       </c>
       <c r="E703" t="n">
-        <v>242.6505785046507</v>
+        <v>242.6505935959654</v>
       </c>
       <c r="F703" t="n">
         <v>816593</v>
@@ -14492,16 +14492,16 @@
         <v>44258</v>
       </c>
       <c r="B704" t="n">
-        <v>241.6033782958984</v>
+        <v>241.6033935546875</v>
       </c>
       <c r="C704" t="n">
-        <v>245.9417732193955</v>
+        <v>245.9417887521817</v>
       </c>
       <c r="D704" t="n">
-        <v>231.1314052428255</v>
+        <v>231.1314198402428</v>
       </c>
       <c r="E704" t="n">
-        <v>242.9497809185175</v>
+        <v>242.9497962623404</v>
       </c>
       <c r="F704" t="n">
         <v>976053</v>
@@ -14612,16 +14612,16 @@
         <v>44266</v>
       </c>
       <c r="B710" t="n">
-        <v>231.87939453125</v>
+        <v>231.8794097900391</v>
       </c>
       <c r="C710" t="n">
-        <v>232.7769861002763</v>
+        <v>232.7770014181312</v>
       </c>
       <c r="D710" t="n">
-        <v>225.2970056315263</v>
+        <v>225.2970204571623</v>
       </c>
       <c r="E710" t="n">
-        <v>228.4386065592368</v>
+        <v>228.4386215916054</v>
       </c>
       <c r="F710" t="n">
         <v>932126</v>
@@ -14632,16 +14632,16 @@
         <v>44267</v>
       </c>
       <c r="B711" t="n">
-        <v>228.8874206542969</v>
+        <v>228.8874053955078</v>
       </c>
       <c r="C711" t="n">
-        <v>231.8794130811504</v>
+        <v>231.8793976229001</v>
       </c>
       <c r="D711" t="n">
-        <v>225.8954282274433</v>
+        <v>225.8954131681156</v>
       </c>
       <c r="E711" t="n">
-        <v>227.840220261286</v>
+        <v>227.8402050723086</v>
       </c>
       <c r="F711" t="n">
         <v>268453</v>
@@ -14692,16 +14692,16 @@
         <v>44272</v>
       </c>
       <c r="B714" t="n">
-        <v>232.4778289794922</v>
+        <v>232.4778137207031</v>
       </c>
       <c r="C714" t="n">
-        <v>237.7138159815703</v>
+        <v>237.7138003791148</v>
       </c>
       <c r="D714" t="n">
-        <v>226.9426396765402</v>
+        <v>226.9426247810559</v>
       </c>
       <c r="E714" t="n">
-        <v>237.5642072221028</v>
+        <v>237.564191629467</v>
       </c>
       <c r="F714" t="n">
         <v>815453</v>
@@ -14812,16 +14812,16 @@
         <v>44280</v>
       </c>
       <c r="B720" t="n">
-        <v>231.1314086914062</v>
+        <v>231.1313934326172</v>
       </c>
       <c r="C720" t="n">
-        <v>232.3282025860022</v>
+        <v>232.3281872482034</v>
       </c>
       <c r="D720" t="n">
-        <v>217.3682408584031</v>
+        <v>217.3682265082282</v>
       </c>
       <c r="E720" t="n">
-        <v>219.7618438656549</v>
+        <v>219.7618293574596</v>
       </c>
       <c r="F720" t="n">
         <v>2364866</v>
@@ -14892,16 +14892,16 @@
         <v>44286</v>
       </c>
       <c r="B724" t="n">
-        <v>222.6042175292969</v>
+        <v>222.604248046875</v>
       </c>
       <c r="C724" t="n">
-        <v>225.2970074764863</v>
+        <v>225.2970383632283</v>
       </c>
       <c r="D724" t="n">
-        <v>221.7066259529202</v>
+        <v>221.7066563474444</v>
       </c>
       <c r="E724" t="n">
-        <v>224.549009423486</v>
+        <v>224.5490402076823</v>
       </c>
       <c r="F724" t="n">
         <v>567873</v>
@@ -14992,16 +14992,16 @@
         <v>44294</v>
       </c>
       <c r="B729" t="n">
-        <v>222.6042175292969</v>
+        <v>222.604248046875</v>
       </c>
       <c r="C729" t="n">
-        <v>229.6354022711122</v>
+        <v>229.6354337526196</v>
       </c>
       <c r="D729" t="n">
-        <v>221.5570172114845</v>
+        <v>221.5570475854983</v>
       </c>
       <c r="E729" t="n">
-        <v>228.4386084299234</v>
+        <v>228.4386397473583</v>
       </c>
       <c r="F729" t="n">
         <v>729940</v>
@@ -15192,16 +15192,16 @@
         <v>44309</v>
       </c>
       <c r="B739" t="n">
-        <v>220.3602294921875</v>
+        <v>220.3602447509766</v>
       </c>
       <c r="C739" t="n">
-        <v>223.6514240604346</v>
+        <v>223.6514395471216</v>
       </c>
       <c r="D739" t="n">
-        <v>218.2658440164373</v>
+        <v>218.2658591302012</v>
       </c>
       <c r="E739" t="n">
-        <v>222.3050214404054</v>
+        <v>222.3050368338611</v>
       </c>
       <c r="F739" t="n">
         <v>863700</v>
@@ -15232,16 +15232,16 @@
         <v>44313</v>
       </c>
       <c r="B741" t="n">
-        <v>216.4706573486328</v>
+        <v>216.4706420898438</v>
       </c>
       <c r="C741" t="n">
-        <v>222.4546422637681</v>
+        <v>222.4546265831743</v>
       </c>
       <c r="D741" t="n">
-        <v>216.4706573486328</v>
+        <v>216.4706420898438</v>
       </c>
       <c r="E741" t="n">
-        <v>220.8090372812696</v>
+        <v>220.8090217166727</v>
       </c>
       <c r="F741" t="n">
         <v>462980</v>
@@ -15252,16 +15252,16 @@
         <v>44314</v>
       </c>
       <c r="B742" t="n">
-        <v>219.9114379882812</v>
+        <v>219.9114532470703</v>
       </c>
       <c r="C742" t="n">
-        <v>221.7066364440425</v>
+        <v>221.7066518273933</v>
       </c>
       <c r="D742" t="n">
-        <v>211.8330525463857</v>
+        <v>211.8330672446474</v>
       </c>
       <c r="E742" t="n">
-        <v>217.0690391651543</v>
+        <v>217.0690542267205</v>
       </c>
       <c r="F742" t="n">
         <v>681606</v>
@@ -15272,16 +15272,16 @@
         <v>44315</v>
       </c>
       <c r="B743" t="n">
-        <v>220.8090209960938</v>
+        <v>220.8090362548828</v>
       </c>
       <c r="C743" t="n">
-        <v>223.6514197083738</v>
+        <v>223.651435163584</v>
       </c>
       <c r="D743" t="n">
-        <v>218.2658397691752</v>
+        <v>218.2658548522203</v>
       </c>
       <c r="E743" t="n">
-        <v>220.5098339468512</v>
+        <v>220.5098491849652</v>
       </c>
       <c r="F743" t="n">
         <v>369126</v>
@@ -15332,16 +15332,16 @@
         <v>44320</v>
       </c>
       <c r="B746" t="n">
-        <v>222.6042175292969</v>
+        <v>222.604248046875</v>
       </c>
       <c r="C746" t="n">
-        <v>225.14741395311</v>
+        <v>225.1474448193437</v>
       </c>
       <c r="D746" t="n">
-        <v>220.3602233702958</v>
+        <v>220.360253580237</v>
       </c>
       <c r="E746" t="n">
-        <v>223.8010113704856</v>
+        <v>223.8010420521363</v>
       </c>
       <c r="F746" t="n">
         <v>465600</v>
@@ -15452,16 +15452,16 @@
         <v>44328</v>
       </c>
       <c r="B752" t="n">
-        <v>212.4675750732422</v>
+        <v>212.4675598144531</v>
       </c>
       <c r="C752" t="n">
-        <v>218.9014493024574</v>
+        <v>218.9014335816066</v>
       </c>
       <c r="D752" t="n">
-        <v>211.2705776944238</v>
+        <v>211.2705625215996</v>
       </c>
       <c r="E752" t="n">
-        <v>218.4525771879814</v>
+        <v>218.4525614993673</v>
       </c>
       <c r="F752" t="n">
         <v>1381546</v>
@@ -15472,16 +15472,16 @@
         <v>44329</v>
       </c>
       <c r="B753" t="n">
-        <v>218.4525604248047</v>
+        <v>218.4525756835938</v>
       </c>
       <c r="C753" t="n">
-        <v>221.7443143794447</v>
+        <v>221.7443298681609</v>
       </c>
       <c r="D753" t="n">
-        <v>214.4126812632304</v>
+        <v>214.4126962398362</v>
       </c>
       <c r="E753" t="n">
-        <v>214.7119343901334</v>
+        <v>214.7119493876418</v>
       </c>
       <c r="F753" t="n">
         <v>807133</v>
@@ -15512,16 +15512,16 @@
         <v>44333</v>
       </c>
       <c r="B755" t="n">
-        <v>218.6021728515625</v>
+        <v>218.6021881103516</v>
       </c>
       <c r="C755" t="n">
-        <v>222.9413050104949</v>
+        <v>222.9413205721625</v>
       </c>
       <c r="D755" t="n">
-        <v>217.8540476669635</v>
+        <v>217.8540628735322</v>
       </c>
       <c r="E755" t="n">
-        <v>219.2006790875</v>
+        <v>219.2006943880658</v>
       </c>
       <c r="F755" t="n">
         <v>603380</v>
@@ -15552,16 +15552,16 @@
         <v>44335</v>
       </c>
       <c r="B757" t="n">
-        <v>217.8540496826172</v>
+        <v>217.8540649414062</v>
       </c>
       <c r="C757" t="n">
-        <v>221.7443098109133</v>
+        <v>221.7443253421814</v>
       </c>
       <c r="D757" t="n">
-        <v>216.9563055410505</v>
+        <v>216.9563207369604</v>
       </c>
       <c r="E757" t="n">
-        <v>219.0510621655674</v>
+        <v>219.0510775081968</v>
       </c>
       <c r="F757" t="n">
         <v>577806</v>
@@ -15652,16 +15652,16 @@
         <v>44342</v>
       </c>
       <c r="B762" t="n">
-        <v>235.80908203125</v>
+        <v>235.8090667724609</v>
       </c>
       <c r="C762" t="n">
-        <v>242.2429716120442</v>
+        <v>242.2429559369295</v>
       </c>
       <c r="D762" t="n">
-        <v>234.4624656604181</v>
+        <v>234.4624504887662</v>
       </c>
       <c r="E762" t="n">
-        <v>235.5098440959414</v>
+        <v>235.5098288565155</v>
       </c>
       <c r="F762" t="n">
         <v>960346</v>
@@ -15672,16 +15672,16 @@
         <v>44343</v>
       </c>
       <c r="B763" t="n">
-        <v>235.80908203125</v>
+        <v>235.8090667724609</v>
       </c>
       <c r="C763" t="n">
-        <v>237.454966778686</v>
+        <v>237.4549514133946</v>
       </c>
       <c r="D763" t="n">
-        <v>231.3203303538482</v>
+        <v>231.3203153855183</v>
       </c>
       <c r="E763" t="n">
-        <v>234.1632125044618</v>
+        <v>234.163197352174</v>
       </c>
       <c r="F763" t="n">
         <v>742060</v>
@@ -15752,16 +15752,16 @@
         <v>44349</v>
       </c>
       <c r="B767" t="n">
-        <v>236.4075775146484</v>
+        <v>236.4075622558594</v>
       </c>
       <c r="C767" t="n">
-        <v>241.7940731925462</v>
+        <v>241.7940575860889</v>
       </c>
       <c r="D767" t="n">
-        <v>232.8165702489519</v>
+        <v>232.8165552219423</v>
       </c>
       <c r="E767" t="n">
-        <v>240.2978227019471</v>
+        <v>240.2978071920645</v>
       </c>
       <c r="F767" t="n">
         <v>1207373</v>
@@ -15772,16 +15772,16 @@
         <v>44351</v>
       </c>
       <c r="B768" t="n">
-        <v>234.6120758056641</v>
+        <v>234.612060546875</v>
       </c>
       <c r="C768" t="n">
-        <v>237.1557047046701</v>
+        <v>237.1556892804475</v>
       </c>
       <c r="D768" t="n">
-        <v>230.8714495484926</v>
+        <v>230.8714345329878</v>
       </c>
       <c r="E768" t="n">
-        <v>235.8090731638295</v>
+        <v>235.8090578271896</v>
       </c>
       <c r="F768" t="n">
         <v>719633</v>
@@ -15792,16 +15792,16 @@
         <v>44354</v>
       </c>
       <c r="B769" t="n">
-        <v>236.4075775146484</v>
+        <v>236.4075622558594</v>
       </c>
       <c r="C769" t="n">
-        <v>237.6045748629983</v>
+        <v>237.6045595269497</v>
       </c>
       <c r="D769" t="n">
-        <v>234.0135828179488</v>
+        <v>234.0135677136788</v>
       </c>
       <c r="E769" t="n">
-        <v>234.7617080632483</v>
+        <v>234.761692910691</v>
       </c>
       <c r="F769" t="n">
         <v>603120</v>
@@ -15812,16 +15812,16 @@
         <v>44355</v>
       </c>
       <c r="B770" t="n">
-        <v>236.4075775146484</v>
+        <v>236.4075622558594</v>
       </c>
       <c r="C770" t="n">
-        <v>236.4075775146484</v>
+        <v>236.4075622558594</v>
       </c>
       <c r="D770" t="n">
-        <v>233.8639486365007</v>
+        <v>233.8639335418887</v>
       </c>
       <c r="E770" t="n">
-        <v>234.7617080632483</v>
+        <v>234.761692910691</v>
       </c>
       <c r="F770" t="n">
         <v>523580</v>
@@ -15972,16 +15972,16 @@
         <v>44365</v>
       </c>
       <c r="B778" t="n">
-        <v>231.9188079833984</v>
+        <v>231.9188232421875</v>
       </c>
       <c r="C778" t="n">
-        <v>237.6045563607977</v>
+        <v>237.6045719936731</v>
       </c>
       <c r="D778" t="n">
-        <v>231.1706827963552</v>
+        <v>231.1706980059224</v>
       </c>
       <c r="E778" t="n">
-        <v>234.761689782421</v>
+        <v>234.7617052282537</v>
       </c>
       <c r="F778" t="n">
         <v>1042493</v>
@@ -16012,16 +16012,16 @@
         <v>44369</v>
       </c>
       <c r="B780" t="n">
-        <v>235.9587097167969</v>
+        <v>235.9586944580078</v>
       </c>
       <c r="C780" t="n">
-        <v>235.9587097167969</v>
+        <v>235.9586944580078</v>
       </c>
       <c r="D780" t="n">
-        <v>227.130825572934</v>
+        <v>227.1308108850195</v>
       </c>
       <c r="E780" t="n">
-        <v>230.5721987199722</v>
+        <v>230.5721838095137</v>
       </c>
       <c r="F780" t="n">
         <v>510040</v>
@@ -16032,16 +16032,16 @@
         <v>44370</v>
       </c>
       <c r="B781" t="n">
-        <v>234.4624633789062</v>
+        <v>234.4624481201172</v>
       </c>
       <c r="C781" t="n">
-        <v>237.4549644680546</v>
+        <v>237.454949014514</v>
       </c>
       <c r="D781" t="n">
-        <v>233.1158318005304</v>
+        <v>233.11581662938</v>
       </c>
       <c r="E781" t="n">
-        <v>233.4150849535748</v>
+        <v>233.415069762949</v>
       </c>
       <c r="F781" t="n">
         <v>396613</v>
@@ -16052,16 +16052,16 @@
         <v>44371</v>
       </c>
       <c r="B782" t="n">
-        <v>236.1083221435547</v>
+        <v>236.1083068847656</v>
       </c>
       <c r="C782" t="n">
-        <v>241.1955798518269</v>
+        <v>241.1955642642676</v>
       </c>
       <c r="D782" t="n">
-        <v>233.1158211906056</v>
+        <v>233.1158061252106</v>
       </c>
       <c r="E782" t="n">
-        <v>236.2579563235903</v>
+        <v>236.2579410551309</v>
       </c>
       <c r="F782" t="n">
         <v>341100</v>
@@ -16292,16 +16292,16 @@
         <v>44390</v>
       </c>
       <c r="B794" t="n">
-        <v>231.8934936523438</v>
+        <v>231.8935089111328</v>
       </c>
       <c r="C794" t="n">
-        <v>231.8934936523438</v>
+        <v>231.8935089111328</v>
       </c>
       <c r="D794" t="n">
-        <v>225.7516177292607</v>
+        <v>225.7516325839092</v>
       </c>
       <c r="E794" t="n">
-        <v>227.3994336387764</v>
+        <v>227.3994486018525</v>
       </c>
       <c r="F794" t="n">
         <v>354526</v>
@@ -16432,16 +16432,16 @@
         <v>44399</v>
       </c>
       <c r="B801" t="n">
-        <v>217.9619140625</v>
+        <v>217.9619293212891</v>
       </c>
       <c r="C801" t="n">
-        <v>221.2575611716557</v>
+        <v>221.257576661162</v>
       </c>
       <c r="D801" t="n">
-        <v>216.7635010878928</v>
+        <v>216.7635162627849</v>
       </c>
       <c r="E801" t="n">
-        <v>216.7635010878928</v>
+        <v>216.7635162627849</v>
       </c>
       <c r="F801" t="n">
         <v>954046</v>
@@ -16452,16 +16452,16 @@
         <v>44400</v>
       </c>
       <c r="B802" t="n">
-        <v>218.5611267089844</v>
+        <v>218.5611419677734</v>
       </c>
       <c r="C802" t="n">
-        <v>219.4599326242732</v>
+        <v>219.4599479458122</v>
       </c>
       <c r="D802" t="n">
-        <v>216.6136884947792</v>
+        <v>216.6137036176084</v>
       </c>
       <c r="E802" t="n">
-        <v>218.5611267089844</v>
+        <v>218.5611419677734</v>
       </c>
       <c r="F802" t="n">
         <v>399593</v>
@@ -16512,16 +16512,16 @@
         <v>44405</v>
       </c>
       <c r="B805" t="n">
-        <v>218.8607177734375</v>
+        <v>218.8607330322266</v>
       </c>
       <c r="C805" t="n">
-        <v>220.6583448365173</v>
+        <v>220.6583602206354</v>
       </c>
       <c r="D805" t="n">
-        <v>213.7674588731336</v>
+        <v>213.7674737768248</v>
       </c>
       <c r="E805" t="n">
-        <v>216.1642847981416</v>
+        <v>216.1642998689376</v>
       </c>
       <c r="F805" t="n">
         <v>723426</v>
@@ -16552,16 +16552,16 @@
         <v>44407</v>
       </c>
       <c r="B807" t="n">
-        <v>213.1682586669922</v>
+        <v>213.1682434082031</v>
       </c>
       <c r="C807" t="n">
-        <v>218.2615331379264</v>
+        <v>218.2615175145558</v>
       </c>
       <c r="D807" t="n">
-        <v>212.4192486117753</v>
+        <v>212.4192334066011</v>
       </c>
       <c r="E807" t="n">
-        <v>217.5125230827095</v>
+        <v>217.5125075129538</v>
       </c>
       <c r="F807" t="n">
         <v>616053</v>
@@ -16652,16 +16652,16 @@
         <v>44414</v>
       </c>
       <c r="B812" t="n">
-        <v>213.6176605224609</v>
+        <v>213.6176452636719</v>
       </c>
       <c r="C812" t="n">
-        <v>216.1642977444576</v>
+        <v>216.1642823037613</v>
       </c>
       <c r="D812" t="n">
-        <v>212.5690586416228</v>
+        <v>212.5690434577357</v>
       </c>
       <c r="E812" t="n">
-        <v>215.5650988466427</v>
+        <v>215.5650834487474</v>
       </c>
       <c r="F812" t="n">
         <v>516400</v>
@@ -16672,16 +16672,16 @@
         <v>44417</v>
       </c>
       <c r="B813" t="n">
-        <v>211.9698486328125</v>
+        <v>211.9698333740234</v>
       </c>
       <c r="C813" t="n">
-        <v>216.3141131101459</v>
+        <v>216.3140975386321</v>
       </c>
       <c r="D813" t="n">
-        <v>211.2208385669722</v>
+        <v>211.2208233621011</v>
       </c>
       <c r="E813" t="n">
-        <v>211.9698486328125</v>
+        <v>211.9698333740234</v>
       </c>
       <c r="F813" t="n">
         <v>495180</v>
@@ -16812,16 +16812,16 @@
         <v>44426</v>
       </c>
       <c r="B820" t="n">
-        <v>218.7109222412109</v>
+        <v>218.7109375</v>
       </c>
       <c r="C820" t="n">
-        <v>221.8567581779885</v>
+        <v>221.8567736562529</v>
       </c>
       <c r="D820" t="n">
-        <v>215.2654792536337</v>
+        <v>215.2654942720448</v>
       </c>
       <c r="E820" t="n">
-        <v>220.5085493073614</v>
+        <v>220.5085646915653</v>
       </c>
       <c r="F820" t="n">
         <v>1229380</v>
@@ -17052,16 +17052,16 @@
         <v>44442</v>
       </c>
       <c r="B832" t="n">
-        <v>223.0551910400391</v>
+        <v>223.0552062988281</v>
       </c>
       <c r="C832" t="n">
-        <v>224.2536040296208</v>
+        <v>224.2536193703911</v>
       </c>
       <c r="D832" t="n">
-        <v>218.261523843064</v>
+        <v>218.2615387739272</v>
       </c>
       <c r="E832" t="n">
-        <v>221.5571709933998</v>
+        <v>221.5571861497122</v>
       </c>
       <c r="F832" t="n">
         <v>758106</v>
@@ -17092,16 +17092,16 @@
         <v>44447</v>
       </c>
       <c r="B834" t="n">
-        <v>218.2615203857422</v>
+        <v>218.2615356445312</v>
       </c>
       <c r="C834" t="n">
-        <v>226.6504264185801</v>
+        <v>226.6504422638424</v>
       </c>
       <c r="D834" t="n">
-        <v>216.1642862582089</v>
+        <v>216.1643013703791</v>
       </c>
       <c r="E834" t="n">
-        <v>225.6018093548134</v>
+        <v>225.6018251267663</v>
       </c>
       <c r="F834" t="n">
         <v>607486</v>
@@ -17252,16 +17252,16 @@
         <v>44459</v>
       </c>
       <c r="B842" t="n">
-        <v>222.9053802490234</v>
+        <v>222.9053955078125</v>
       </c>
       <c r="C842" t="n">
-        <v>229.0472715932652</v>
+        <v>229.047287272492</v>
       </c>
       <c r="D842" t="n">
-        <v>221.2575642905416</v>
+        <v>221.2575794365308</v>
       </c>
       <c r="E842" t="n">
-        <v>226.9500374291538</v>
+        <v>226.9500529648163</v>
       </c>
       <c r="F842" t="n">
         <v>721006</v>
@@ -17292,16 +17292,16 @@
         <v>44461</v>
       </c>
       <c r="B844" t="n">
-        <v>218.5611267089844</v>
+        <v>218.5611419677734</v>
       </c>
       <c r="C844" t="n">
-        <v>230.0958686559974</v>
+        <v>230.0958847200815</v>
       </c>
       <c r="D844" t="n">
-        <v>217.3626985037358</v>
+        <v>217.3627136788569</v>
       </c>
       <c r="E844" t="n">
-        <v>229.1970627407085</v>
+        <v>229.1970787420427</v>
       </c>
       <c r="F844" t="n">
         <v>1356373</v>
@@ -17312,16 +17312,16 @@
         <v>44462</v>
       </c>
       <c r="B845" t="n">
-        <v>223.0551910400391</v>
+        <v>223.0552062988281</v>
       </c>
       <c r="C845" t="n">
-        <v>223.2049869492438</v>
+        <v>223.2050022182801</v>
       </c>
       <c r="D845" t="n">
-        <v>215.565090806843</v>
+        <v>215.5651055532483</v>
       </c>
       <c r="E845" t="n">
-        <v>217.9619167860065</v>
+        <v>217.9619316963742</v>
       </c>
       <c r="F845" t="n">
         <v>1074353</v>
@@ -42592,19 +42592,39 @@
         <v>46315</v>
       </c>
       <c r="B2109" t="n">
-        <v>9.550000000000001</v>
+        <v>9.550000190734863</v>
       </c>
       <c r="C2109" t="n">
-        <v>9.609999999999999</v>
+        <v>9.609999656677246</v>
       </c>
       <c r="D2109" t="n">
-        <v>8.93</v>
+        <v>8.930000305175781</v>
       </c>
       <c r="E2109" t="n">
-        <v>9.19</v>
+        <v>9.189999580383301</v>
       </c>
       <c r="F2109" t="n">
         <v>13493700</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>13144400</v>
       </c>
     </row>
   </sheetData>

--- a/database/HAPV3.xlsx
+++ b/database/HAPV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2111"/>
+  <dimension ref="A1:F2112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>43216</v>
       </c>
       <c r="B2" t="n">
-        <v>81.53694152832031</v>
+        <v>81.53694915771484</v>
       </c>
       <c r="C2" t="n">
-        <v>85.66650989807103</v>
+        <v>85.6665179138684</v>
       </c>
       <c r="D2" t="n">
-        <v>79.57467127971712</v>
+        <v>79.57467872550245</v>
       </c>
       <c r="E2" t="n">
-        <v>84.93431750577982</v>
+        <v>84.93432545306611</v>
       </c>
       <c r="F2" t="n">
         <v>1956933</v>
@@ -472,16 +472,16 @@
         <v>43217</v>
       </c>
       <c r="B3" t="n">
-        <v>82.00556945800781</v>
+        <v>82.00555419921875</v>
       </c>
       <c r="C3" t="n">
-        <v>83.90926719826945</v>
+        <v>83.90925158525906</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54118428911481</v>
+        <v>80.54116930280414</v>
       </c>
       <c r="E3" t="n">
-        <v>81.97628294634966</v>
+        <v>81.97626769300994</v>
       </c>
       <c r="F3" t="n">
         <v>932166</v>
@@ -492,16 +492,16 @@
         <v>43220</v>
       </c>
       <c r="B4" t="n">
-        <v>80.98046875</v>
+        <v>80.98048400878906</v>
       </c>
       <c r="C4" t="n">
-        <v>82.0055409916944</v>
+        <v>82.00555644363325</v>
       </c>
       <c r="D4" t="n">
-        <v>80.68759628683414</v>
+        <v>80.68761149043854</v>
       </c>
       <c r="E4" t="n">
-        <v>81.56622112457728</v>
+        <v>81.56623649373705</v>
       </c>
       <c r="F4" t="n">
         <v>370366</v>
@@ -512,16 +512,16 @@
         <v>43222</v>
       </c>
       <c r="B5" t="n">
-        <v>79.98471832275391</v>
+        <v>79.98469543457031</v>
       </c>
       <c r="C5" t="n">
-        <v>81.85912955369824</v>
+        <v>81.85910612913884</v>
       </c>
       <c r="D5" t="n">
-        <v>79.07679921897648</v>
+        <v>79.07677659060025</v>
       </c>
       <c r="E5" t="n">
-        <v>79.07679921897648</v>
+        <v>79.07677659060025</v>
       </c>
       <c r="F5" t="n">
         <v>428333</v>
@@ -532,16 +532,16 @@
         <v>43223</v>
       </c>
       <c r="B6" t="n">
-        <v>80.51189422607422</v>
+        <v>80.51187896728516</v>
       </c>
       <c r="C6" t="n">
-        <v>81.71268584058056</v>
+        <v>81.71267035421486</v>
       </c>
       <c r="D6" t="n">
-        <v>78.49104308007162</v>
+        <v>78.49102820427865</v>
       </c>
       <c r="E6" t="n">
-        <v>79.39896214266686</v>
+        <v>79.39894709480311</v>
       </c>
       <c r="F6" t="n">
         <v>790600</v>
@@ -632,16 +632,16 @@
         <v>43230</v>
       </c>
       <c r="B11" t="n">
-        <v>79.66254425048828</v>
+        <v>79.66255187988281</v>
       </c>
       <c r="C11" t="n">
-        <v>80.95120278070766</v>
+        <v>80.95121053351885</v>
       </c>
       <c r="D11" t="n">
-        <v>78.43245873810922</v>
+        <v>78.43246624969672</v>
       </c>
       <c r="E11" t="n">
-        <v>79.36966426479174</v>
+        <v>79.36967186613674</v>
       </c>
       <c r="F11" t="n">
         <v>396433</v>
@@ -652,16 +652,16 @@
         <v>43231</v>
       </c>
       <c r="B12" t="n">
-        <v>80.83403778076172</v>
+        <v>80.83404541015625</v>
       </c>
       <c r="C12" t="n">
-        <v>82.59130254809743</v>
+        <v>82.59131034334867</v>
       </c>
       <c r="D12" t="n">
-        <v>80.48259227554095</v>
+        <v>80.48259987176485</v>
       </c>
       <c r="E12" t="n">
-        <v>80.51187878028881</v>
+        <v>80.51188637927687</v>
       </c>
       <c r="F12" t="n">
         <v>586000</v>
@@ -692,16 +692,16 @@
         <v>43235</v>
       </c>
       <c r="B14" t="n">
-        <v>84.78788757324219</v>
+        <v>84.78787994384766</v>
       </c>
       <c r="C14" t="n">
-        <v>85.22720008131586</v>
+        <v>85.22719241239105</v>
       </c>
       <c r="D14" t="n">
-        <v>82.0055576428658</v>
+        <v>82.00555026383122</v>
       </c>
       <c r="E14" t="n">
-        <v>82.29843016549923</v>
+        <v>82.29842276011136</v>
       </c>
       <c r="F14" t="n">
         <v>900866</v>
@@ -712,16 +712,16 @@
         <v>43236</v>
       </c>
       <c r="B15" t="n">
-        <v>87.306640625</v>
+        <v>87.30662536621094</v>
       </c>
       <c r="C15" t="n">
-        <v>87.306640625</v>
+        <v>87.30662536621094</v>
       </c>
       <c r="D15" t="n">
-        <v>83.61639133660867</v>
+        <v>83.61637672277325</v>
       </c>
       <c r="E15" t="n">
-        <v>84.78789644623366</v>
+        <v>84.7878816276515</v>
       </c>
       <c r="F15" t="n">
         <v>589600</v>
@@ -732,16 +732,16 @@
         <v>43237</v>
       </c>
       <c r="B16" t="n">
-        <v>88.74174499511719</v>
+        <v>88.74173736572266</v>
       </c>
       <c r="C16" t="n">
-        <v>90.73330976955775</v>
+        <v>90.7333019689424</v>
       </c>
       <c r="D16" t="n">
-        <v>87.86311238165101</v>
+        <v>87.86310482779517</v>
       </c>
       <c r="E16" t="n">
-        <v>87.86311238165101</v>
+        <v>87.86310482779517</v>
       </c>
       <c r="F16" t="n">
         <v>520533</v>
@@ -752,16 +752,16 @@
         <v>43238</v>
       </c>
       <c r="B17" t="n">
-        <v>86.69158935546875</v>
+        <v>86.69158172607422</v>
       </c>
       <c r="C17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74172654739176</v>
       </c>
       <c r="D17" t="n">
-        <v>85.60795128505117</v>
+        <v>85.60794375102347</v>
       </c>
       <c r="E17" t="n">
-        <v>88.7417343572117</v>
+        <v>88.74172654739176</v>
       </c>
       <c r="F17" t="n">
         <v>980066</v>
@@ -772,16 +772,16 @@
         <v>43241</v>
       </c>
       <c r="B18" t="n">
-        <v>90.20612335205078</v>
+        <v>90.20611572265625</v>
       </c>
       <c r="C18" t="n">
-        <v>91.05546194037015</v>
+        <v>91.05545423914081</v>
       </c>
       <c r="D18" t="n">
-        <v>84.93433551979336</v>
+        <v>84.93432833627266</v>
       </c>
       <c r="E18" t="n">
-        <v>86.9844731633802</v>
+        <v>86.9844658064643</v>
       </c>
       <c r="F18" t="n">
         <v>633933</v>
@@ -792,16 +792,16 @@
         <v>43242</v>
       </c>
       <c r="B19" t="n">
-        <v>95.91720581054688</v>
+        <v>95.91721343994141</v>
       </c>
       <c r="C19" t="n">
-        <v>96.06364578234965</v>
+        <v>96.06365342339224</v>
       </c>
       <c r="D19" t="n">
-        <v>90.20610649620939</v>
+        <v>90.20611367133475</v>
       </c>
       <c r="E19" t="n">
-        <v>90.20610649620939</v>
+        <v>90.20611367133475</v>
       </c>
       <c r="F19" t="n">
         <v>462766</v>
@@ -812,16 +812,16 @@
         <v>43243</v>
       </c>
       <c r="B20" t="n">
-        <v>95.74150085449219</v>
+        <v>95.74148559570312</v>
       </c>
       <c r="C20" t="n">
-        <v>95.91722737050549</v>
+        <v>95.91721208371003</v>
       </c>
       <c r="D20" t="n">
-        <v>90.79187934307389</v>
+        <v>90.79186487313009</v>
       </c>
       <c r="E20" t="n">
-        <v>95.91722737050549</v>
+        <v>95.91721208371003</v>
       </c>
       <c r="F20" t="n">
         <v>487666</v>
@@ -832,16 +832,16 @@
         <v>43244</v>
       </c>
       <c r="B21" t="n">
-        <v>89.32747650146484</v>
+        <v>89.32749176025391</v>
       </c>
       <c r="C21" t="n">
-        <v>93.77920409449239</v>
+        <v>93.77922011371906</v>
       </c>
       <c r="D21" t="n">
-        <v>89.09317700926512</v>
+        <v>89.0931922280315</v>
       </c>
       <c r="E21" t="n">
-        <v>93.13487862888151</v>
+        <v>93.13489453804544</v>
       </c>
       <c r="F21" t="n">
         <v>822100</v>
@@ -872,16 +872,16 @@
         <v>43248</v>
       </c>
       <c r="B23" t="n">
-        <v>86.39871978759766</v>
+        <v>86.39870452880859</v>
       </c>
       <c r="C23" t="n">
-        <v>90.76258852113153</v>
+        <v>90.76257249164411</v>
       </c>
       <c r="D23" t="n">
-        <v>85.02219423616178</v>
+        <v>85.02217922047949</v>
       </c>
       <c r="E23" t="n">
-        <v>90.76258852113153</v>
+        <v>90.76257249164411</v>
       </c>
       <c r="F23" t="n">
         <v>427433</v>
@@ -892,16 +892,16 @@
         <v>43249</v>
       </c>
       <c r="B24" t="n">
-        <v>87.16018676757812</v>
+        <v>87.16019439697266</v>
       </c>
       <c r="C24" t="n">
-        <v>88.88815764680072</v>
+        <v>88.88816542744976</v>
       </c>
       <c r="D24" t="n">
-        <v>84.49500301175549</v>
+        <v>84.49501040785843</v>
       </c>
       <c r="E24" t="n">
-        <v>87.27734023921479</v>
+        <v>87.27734787886412</v>
       </c>
       <c r="F24" t="n">
         <v>175300</v>
@@ -932,16 +932,16 @@
         <v>43252</v>
       </c>
       <c r="B26" t="n">
-        <v>87.54093933105469</v>
+        <v>87.54093170166016</v>
       </c>
       <c r="C26" t="n">
-        <v>90.76258952448887</v>
+        <v>90.76258161432011</v>
       </c>
       <c r="D26" t="n">
-        <v>84.90504913515237</v>
+        <v>84.90504173548175</v>
       </c>
       <c r="E26" t="n">
-        <v>89.70823046682885</v>
+        <v>89.70822264854989</v>
       </c>
       <c r="F26" t="n">
         <v>391033</v>
@@ -952,16 +952,16 @@
         <v>43255</v>
       </c>
       <c r="B27" t="n">
-        <v>88.74174499511719</v>
+        <v>88.74173736572266</v>
       </c>
       <c r="C27" t="n">
-        <v>90.20613020147803</v>
+        <v>90.2061224461859</v>
       </c>
       <c r="D27" t="n">
-        <v>86.72089370826914</v>
+        <v>86.72088625261327</v>
       </c>
       <c r="E27" t="n">
-        <v>88.44886497454569</v>
+        <v>88.44885737033093</v>
       </c>
       <c r="F27" t="n">
         <v>304000</v>
@@ -1012,16 +1012,16 @@
         <v>43258</v>
       </c>
       <c r="B30" t="n">
-        <v>80.83403778076172</v>
+        <v>80.83404541015625</v>
       </c>
       <c r="C30" t="n">
-        <v>83.41136192226955</v>
+        <v>83.41136979492082</v>
       </c>
       <c r="D30" t="n">
-        <v>78.63746054571526</v>
+        <v>78.63746796778928</v>
       </c>
       <c r="E30" t="n">
-        <v>83.41136192226955</v>
+        <v>83.41136979492082</v>
       </c>
       <c r="F30" t="n">
         <v>547066</v>
@@ -1032,16 +1032,16 @@
         <v>43259</v>
       </c>
       <c r="B31" t="n">
-        <v>80.98046875</v>
+        <v>80.98048400878906</v>
       </c>
       <c r="C31" t="n">
-        <v>83.14775923935693</v>
+        <v>83.14777490651888</v>
       </c>
       <c r="D31" t="n">
-        <v>79.07677167056245</v>
+        <v>79.07678657064635</v>
       </c>
       <c r="E31" t="n">
-        <v>79.75039099786137</v>
+        <v>79.75040602487236</v>
       </c>
       <c r="F31" t="n">
         <v>443000</v>
@@ -1052,16 +1052,16 @@
         <v>43262</v>
       </c>
       <c r="B32" t="n">
-        <v>81.41981506347656</v>
+        <v>81.41980743408203</v>
       </c>
       <c r="C32" t="n">
-        <v>82.73776019642489</v>
+        <v>82.73775244353311</v>
       </c>
       <c r="D32" t="n">
-        <v>78.93035735260352</v>
+        <v>78.93034995648213</v>
       </c>
       <c r="E32" t="n">
-        <v>81.478388085486</v>
+        <v>81.47838045060293</v>
       </c>
       <c r="F32" t="n">
         <v>202266</v>
@@ -1092,16 +1092,16 @@
         <v>43264</v>
       </c>
       <c r="B34" t="n">
-        <v>78.3153076171875</v>
+        <v>78.31531524658203</v>
       </c>
       <c r="C34" t="n">
-        <v>82.32772294015612</v>
+        <v>82.32773096043591</v>
       </c>
       <c r="D34" t="n">
-        <v>77.70026117681101</v>
+        <v>77.70026874628836</v>
       </c>
       <c r="E34" t="n">
-        <v>82.32772294015612</v>
+        <v>82.32773096043591</v>
       </c>
       <c r="F34" t="n">
         <v>786033</v>
@@ -1152,16 +1152,16 @@
         <v>43269</v>
       </c>
       <c r="B37" t="n">
-        <v>77.26096343994141</v>
+        <v>77.26095581054688</v>
       </c>
       <c r="C37" t="n">
-        <v>79.07680170457296</v>
+        <v>79.07679389586734</v>
       </c>
       <c r="D37" t="n">
-        <v>76.73378386812112</v>
+        <v>76.7337762907847</v>
       </c>
       <c r="E37" t="n">
-        <v>79.07680170457296</v>
+        <v>79.07679389586734</v>
       </c>
       <c r="F37" t="n">
         <v>465333</v>
@@ -1192,16 +1192,16 @@
         <v>43271</v>
       </c>
       <c r="B39" t="n">
-        <v>84.34858703613281</v>
+        <v>84.34857177734375</v>
       </c>
       <c r="C39" t="n">
-        <v>85.52009218942361</v>
+        <v>85.52007671870746</v>
       </c>
       <c r="D39" t="n">
-        <v>81.71268926885634</v>
+        <v>81.71267448690524</v>
       </c>
       <c r="E39" t="n">
-        <v>82.03485579289816</v>
+        <v>82.03484095266663</v>
       </c>
       <c r="F39" t="n">
         <v>141600</v>
@@ -1212,16 +1212,16 @@
         <v>43272</v>
       </c>
       <c r="B40" t="n">
-        <v>82.62059020996094</v>
+        <v>82.62060546875</v>
       </c>
       <c r="C40" t="n">
-        <v>85.46150038223338</v>
+        <v>85.46151616569612</v>
       </c>
       <c r="D40" t="n">
-        <v>80.10184649091977</v>
+        <v>80.10186128453448</v>
       </c>
       <c r="E40" t="n">
-        <v>83.46993610077617</v>
+        <v>83.46995151642673</v>
       </c>
       <c r="F40" t="n">
         <v>246900</v>
@@ -1232,16 +1232,16 @@
         <v>43273</v>
       </c>
       <c r="B41" t="n">
-        <v>84.93431091308594</v>
+        <v>84.93431854248047</v>
       </c>
       <c r="C41" t="n">
-        <v>85.52006329180293</v>
+        <v>85.52007097381384</v>
       </c>
       <c r="D41" t="n">
-        <v>81.21477623239973</v>
+        <v>81.21478352767961</v>
       </c>
       <c r="E41" t="n">
-        <v>82.0348280729544</v>
+        <v>82.03483544189709</v>
       </c>
       <c r="F41" t="n">
         <v>298800</v>
@@ -1252,16 +1252,16 @@
         <v>43276</v>
       </c>
       <c r="B42" t="n">
-        <v>86.39871978759766</v>
+        <v>86.39870452880859</v>
       </c>
       <c r="C42" t="n">
-        <v>86.39871978759766</v>
+        <v>86.39870452880859</v>
       </c>
       <c r="D42" t="n">
-        <v>84.34858216364319</v>
+        <v>84.34856726692682</v>
       </c>
       <c r="E42" t="n">
-        <v>85.87154026459547</v>
+        <v>85.87152509891105</v>
       </c>
       <c r="F42" t="n">
         <v>909166</v>
@@ -1272,16 +1272,16 @@
         <v>43277</v>
       </c>
       <c r="B43" t="n">
-        <v>86.75017547607422</v>
+        <v>86.75016021728516</v>
       </c>
       <c r="C43" t="n">
-        <v>87.86310757617932</v>
+        <v>87.86309212163277</v>
       </c>
       <c r="D43" t="n">
-        <v>85.08077732591656</v>
+        <v>85.08076236076373</v>
       </c>
       <c r="E43" t="n">
-        <v>86.60373547379767</v>
+        <v>86.60372024076645</v>
       </c>
       <c r="F43" t="n">
         <v>153233</v>
@@ -1312,16 +1312,16 @@
         <v>43279</v>
       </c>
       <c r="B45" t="n">
-        <v>88.68315887451172</v>
+        <v>88.68315124511719</v>
       </c>
       <c r="C45" t="n">
-        <v>88.68315887451172</v>
+        <v>88.68315124511719</v>
       </c>
       <c r="D45" t="n">
-        <v>85.37364911475306</v>
+        <v>85.373641770075</v>
       </c>
       <c r="E45" t="n">
-        <v>87.8631067863316</v>
+        <v>87.86309922748598</v>
       </c>
       <c r="F45" t="n">
         <v>922066</v>
@@ -1332,16 +1332,16 @@
         <v>43280</v>
       </c>
       <c r="B46" t="n">
-        <v>87.54093933105469</v>
+        <v>87.54093170166016</v>
       </c>
       <c r="C46" t="n">
-        <v>89.41535046806291</v>
+        <v>89.41534267530913</v>
       </c>
       <c r="D46" t="n">
-        <v>85.37364819528054</v>
+        <v>85.37364075477042</v>
       </c>
       <c r="E46" t="n">
-        <v>87.45307980037357</v>
+        <v>87.45307217863621</v>
       </c>
       <c r="F46" t="n">
         <v>492266</v>
@@ -1452,16 +1452,16 @@
         <v>43291</v>
       </c>
       <c r="B52" t="n">
-        <v>84.23142242431641</v>
+        <v>84.23143768310547</v>
       </c>
       <c r="C52" t="n">
-        <v>86.07654689375923</v>
+        <v>86.07656248679844</v>
       </c>
       <c r="D52" t="n">
-        <v>83.17706345656418</v>
+        <v>83.17707852435278</v>
       </c>
       <c r="E52" t="n">
-        <v>84.14356290112728</v>
+        <v>84.14357814400032</v>
       </c>
       <c r="F52" t="n">
         <v>281266</v>
@@ -1472,16 +1472,16 @@
         <v>43292</v>
       </c>
       <c r="B53" t="n">
-        <v>84.08498382568359</v>
+        <v>84.08499145507812</v>
       </c>
       <c r="C53" t="n">
-        <v>86.25227481242993</v>
+        <v>86.25228263847217</v>
       </c>
       <c r="D53" t="n">
-        <v>82.6498853372571</v>
+        <v>82.64989283643895</v>
       </c>
       <c r="E53" t="n">
-        <v>83.792111295304</v>
+        <v>83.79211889812494</v>
       </c>
       <c r="F53" t="n">
         <v>271833</v>
@@ -1492,16 +1492,16 @@
         <v>43293</v>
       </c>
       <c r="B54" t="n">
-        <v>87.07234191894531</v>
+        <v>87.07233428955078</v>
       </c>
       <c r="C54" t="n">
-        <v>87.13091494050801</v>
+        <v>87.13090730598122</v>
       </c>
       <c r="D54" t="n">
-        <v>82.35702002870303</v>
+        <v>82.35701281247128</v>
       </c>
       <c r="E54" t="n">
-        <v>83.90926468609763</v>
+        <v>83.90925733385612</v>
       </c>
       <c r="F54" t="n">
         <v>235333</v>
@@ -1512,16 +1512,16 @@
         <v>43294</v>
       </c>
       <c r="B55" t="n">
-        <v>84.40715026855469</v>
+        <v>84.40715789794922</v>
       </c>
       <c r="C55" t="n">
-        <v>87.57021977413956</v>
+        <v>87.57022768943764</v>
       </c>
       <c r="D55" t="n">
-        <v>83.96783774909052</v>
+        <v>83.96784533877647</v>
       </c>
       <c r="E55" t="n">
-        <v>87.10162074647741</v>
+        <v>87.10162861941977</v>
       </c>
       <c r="F55" t="n">
         <v>222900</v>
@@ -1632,16 +1632,16 @@
         <v>43304</v>
       </c>
       <c r="B61" t="n">
-        <v>87.65807342529297</v>
+        <v>87.65808868408203</v>
       </c>
       <c r="C61" t="n">
-        <v>89.26889816560464</v>
+        <v>89.26891370479268</v>
       </c>
       <c r="D61" t="n">
-        <v>86.72086806415163</v>
+        <v>86.72088315979977</v>
       </c>
       <c r="E61" t="n">
-        <v>89.0053047353875</v>
+        <v>89.00532022869139</v>
       </c>
       <c r="F61" t="n">
         <v>145300</v>
@@ -1652,16 +1652,16 @@
         <v>43305</v>
       </c>
       <c r="B62" t="n">
-        <v>88.15598297119141</v>
+        <v>88.15596771240234</v>
       </c>
       <c r="C62" t="n">
-        <v>88.71245648741085</v>
+        <v>88.71244113230262</v>
       </c>
       <c r="D62" t="n">
-        <v>87.10163130699453</v>
+        <v>87.10161623070165</v>
       </c>
       <c r="E62" t="n">
-        <v>88.18527693118834</v>
+        <v>88.18526166732883</v>
       </c>
       <c r="F62" t="n">
         <v>140566</v>
@@ -1692,16 +1692,16 @@
         <v>43307</v>
       </c>
       <c r="B64" t="n">
-        <v>80.57044982910156</v>
+        <v>80.57045745849609</v>
       </c>
       <c r="C64" t="n">
-        <v>84.84645072790009</v>
+        <v>84.84645876219862</v>
       </c>
       <c r="D64" t="n">
-        <v>79.95541089962423</v>
+        <v>79.95541847077936</v>
       </c>
       <c r="E64" t="n">
-        <v>84.14355228631722</v>
+        <v>84.14356025405675</v>
       </c>
       <c r="F64" t="n">
         <v>454233</v>
@@ -1712,16 +1712,16 @@
         <v>43308</v>
       </c>
       <c r="B65" t="n">
-        <v>82.62059020996094</v>
+        <v>82.62060546875</v>
       </c>
       <c r="C65" t="n">
-        <v>82.62059020996094</v>
+        <v>82.62060546875</v>
       </c>
       <c r="D65" t="n">
-        <v>80.04327348060372</v>
+        <v>80.04328826340087</v>
       </c>
       <c r="E65" t="n">
-        <v>81.24407232980825</v>
+        <v>81.24408733437501</v>
       </c>
       <c r="F65" t="n">
         <v>199833</v>
@@ -1732,16 +1732,16 @@
         <v>43311</v>
       </c>
       <c r="B66" t="n">
-        <v>80.39472198486328</v>
+        <v>80.39473724365234</v>
       </c>
       <c r="C66" t="n">
-        <v>82.59129912897563</v>
+        <v>82.59131480467153</v>
       </c>
       <c r="D66" t="n">
-        <v>79.80896956941586</v>
+        <v>79.80898471703006</v>
       </c>
       <c r="E66" t="n">
-        <v>82.53272612190472</v>
+        <v>82.53274178648354</v>
       </c>
       <c r="F66" t="n">
         <v>306800</v>
@@ -1752,16 +1752,16 @@
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>82.47415924072266</v>
+        <v>82.47413635253906</v>
       </c>
       <c r="C67" t="n">
-        <v>82.56202621403682</v>
+        <v>82.56200330146844</v>
       </c>
       <c r="D67" t="n">
-        <v>79.3696627348224</v>
+        <v>79.36964070819697</v>
       </c>
       <c r="E67" t="n">
-        <v>81.24408120030263</v>
+        <v>81.24405865348962</v>
       </c>
       <c r="F67" t="n">
         <v>430700</v>
@@ -1792,16 +1792,16 @@
         <v>43314</v>
       </c>
       <c r="B69" t="n">
-        <v>84.75860595703125</v>
+        <v>84.75859069824219</v>
       </c>
       <c r="C69" t="n">
-        <v>84.75860595703125</v>
+        <v>84.75859069824219</v>
       </c>
       <c r="D69" t="n">
-        <v>83.2356478963592</v>
+        <v>83.23563291174283</v>
       </c>
       <c r="E69" t="n">
-        <v>83.2356478963592</v>
+        <v>83.23563291174283</v>
       </c>
       <c r="F69" t="n">
         <v>63600</v>
@@ -1832,16 +1832,16 @@
         <v>43318</v>
       </c>
       <c r="B71" t="n">
-        <v>81.33194732666016</v>
+        <v>81.33193206787109</v>
       </c>
       <c r="C71" t="n">
-        <v>83.55781152131701</v>
+        <v>83.55779584493075</v>
       </c>
       <c r="D71" t="n">
-        <v>81.12693430328365</v>
+        <v>81.12691908295734</v>
       </c>
       <c r="E71" t="n">
-        <v>83.38208500867314</v>
+        <v>83.38206936525518</v>
       </c>
       <c r="F71" t="n">
         <v>242633</v>
@@ -1912,16 +1912,16 @@
         <v>43322</v>
       </c>
       <c r="B75" t="n">
-        <v>78.87178039550781</v>
+        <v>78.87177276611328</v>
       </c>
       <c r="C75" t="n">
-        <v>80.36545196820988</v>
+        <v>80.3654441943301</v>
       </c>
       <c r="D75" t="n">
-        <v>78.16887437347211</v>
+        <v>78.1688668120708</v>
       </c>
       <c r="E75" t="n">
-        <v>79.13536642964741</v>
+        <v>79.13535877475577</v>
       </c>
       <c r="F75" t="n">
         <v>176700</v>
@@ -1952,16 +1952,16 @@
         <v>43326</v>
       </c>
       <c r="B77" t="n">
-        <v>77.46597290039062</v>
+        <v>77.46596527099609</v>
       </c>
       <c r="C77" t="n">
-        <v>78.46175897283159</v>
+        <v>78.46175124536504</v>
       </c>
       <c r="D77" t="n">
-        <v>74.44934306830048</v>
+        <v>74.4493357360049</v>
       </c>
       <c r="E77" t="n">
-        <v>78.46175897283159</v>
+        <v>78.46175124536504</v>
       </c>
       <c r="F77" t="n">
         <v>524933</v>
@@ -1992,16 +1992,16 @@
         <v>43328</v>
       </c>
       <c r="B79" t="n">
-        <v>73.51210784912109</v>
+        <v>73.51213073730469</v>
       </c>
       <c r="C79" t="n">
-        <v>76.64589767769425</v>
+        <v>76.64592154159136</v>
       </c>
       <c r="D79" t="n">
-        <v>72.69205598806157</v>
+        <v>72.69207862091992</v>
       </c>
       <c r="E79" t="n">
-        <v>76.32373125445839</v>
+        <v>76.32375501804815</v>
       </c>
       <c r="F79" t="n">
         <v>1651000</v>
@@ -2012,16 +2012,16 @@
         <v>43329</v>
       </c>
       <c r="B80" t="n">
-        <v>71.46199798583984</v>
+        <v>71.46199035644531</v>
       </c>
       <c r="C80" t="n">
-        <v>72.95566976511273</v>
+        <v>72.95566197625146</v>
       </c>
       <c r="D80" t="n">
-        <v>70.29049275259602</v>
+        <v>70.29048524827323</v>
       </c>
       <c r="E80" t="n">
-        <v>72.95566976511273</v>
+        <v>72.95566197625146</v>
       </c>
       <c r="F80" t="n">
         <v>2138466</v>
@@ -2032,16 +2032,16 @@
         <v>43332</v>
       </c>
       <c r="B81" t="n">
-        <v>72.34062957763672</v>
+        <v>72.34061431884766</v>
       </c>
       <c r="C81" t="n">
-        <v>73.01424917344369</v>
+        <v>73.01423377256823</v>
       </c>
       <c r="D81" t="n">
-        <v>71.75487696957561</v>
+        <v>71.75486183433918</v>
       </c>
       <c r="E81" t="n">
-        <v>71.95989000998456</v>
+        <v>71.95987483150479</v>
       </c>
       <c r="F81" t="n">
         <v>425766</v>
@@ -2052,16 +2052,16 @@
         <v>43333</v>
       </c>
       <c r="B82" t="n">
-        <v>71.60840606689453</v>
+        <v>71.60843658447266</v>
       </c>
       <c r="C82" t="n">
-        <v>72.5748978257073</v>
+        <v>72.57492875517822</v>
       </c>
       <c r="D82" t="n">
-        <v>70.31974790572909</v>
+        <v>70.31977787411573</v>
       </c>
       <c r="E82" t="n">
-        <v>71.63769256742745</v>
+        <v>71.63772309748668</v>
       </c>
       <c r="F82" t="n">
         <v>1384333</v>
@@ -2072,16 +2072,16 @@
         <v>43334</v>
       </c>
       <c r="B83" t="n">
-        <v>73.51210784912109</v>
+        <v>73.51213073730469</v>
       </c>
       <c r="C83" t="n">
-        <v>73.68783431195467</v>
+        <v>73.68785725485115</v>
       </c>
       <c r="D83" t="n">
-        <v>70.96408531040285</v>
+        <v>70.96410740525307</v>
       </c>
       <c r="E83" t="n">
-        <v>70.96408531040285</v>
+        <v>70.96410740525307</v>
       </c>
       <c r="F83" t="n">
         <v>518466</v>
@@ -2112,16 +2112,16 @@
         <v>43336</v>
       </c>
       <c r="B85" t="n">
-        <v>75.29867553710938</v>
+        <v>75.29869079589844</v>
       </c>
       <c r="C85" t="n">
-        <v>75.56226901344348</v>
+        <v>75.56228432564806</v>
       </c>
       <c r="D85" t="n">
-        <v>73.21925147654457</v>
+        <v>73.21926631395182</v>
       </c>
       <c r="E85" t="n">
-        <v>74.0978839839126</v>
+        <v>74.09789899936904</v>
       </c>
       <c r="F85" t="n">
         <v>164200</v>
@@ -2132,16 +2132,16 @@
         <v>43339</v>
       </c>
       <c r="B86" t="n">
-        <v>76.03086090087891</v>
+        <v>76.03086853027344</v>
       </c>
       <c r="C86" t="n">
-        <v>76.44088688300364</v>
+        <v>76.44089455354266</v>
       </c>
       <c r="D86" t="n">
-        <v>73.6585570782333</v>
+        <v>73.65856446957658</v>
       </c>
       <c r="E86" t="n">
-        <v>75.29866845497898</v>
+        <v>75.29867601090092</v>
       </c>
       <c r="F86" t="n">
         <v>318500</v>
@@ -2152,16 +2152,16 @@
         <v>43340</v>
       </c>
       <c r="B87" t="n">
-        <v>75.24010467529297</v>
+        <v>75.2401123046875</v>
       </c>
       <c r="C87" t="n">
-        <v>76.14802371754747</v>
+        <v>76.14803143900558</v>
       </c>
       <c r="D87" t="n">
-        <v>73.89287309089012</v>
+        <v>73.89288058367451</v>
       </c>
       <c r="E87" t="n">
-        <v>75.91372419161821</v>
+        <v>75.91373188931819</v>
       </c>
       <c r="F87" t="n">
         <v>298400</v>
@@ -2192,16 +2192,16 @@
         <v>43342</v>
       </c>
       <c r="B89" t="n">
-        <v>75.85512542724609</v>
+        <v>75.85514831542969</v>
       </c>
       <c r="C89" t="n">
-        <v>75.85512542724609</v>
+        <v>75.85514831542969</v>
       </c>
       <c r="D89" t="n">
-        <v>73.39496237777553</v>
+        <v>73.39498452364062</v>
       </c>
       <c r="E89" t="n">
-        <v>74.18572774220431</v>
+        <v>74.18575012667137</v>
       </c>
       <c r="F89" t="n">
         <v>206466</v>
@@ -2212,16 +2212,16 @@
         <v>43343</v>
       </c>
       <c r="B90" t="n">
-        <v>75.82585144042969</v>
+        <v>75.82585906982422</v>
       </c>
       <c r="C90" t="n">
-        <v>76.49947090546172</v>
+        <v>76.49947860263404</v>
       </c>
       <c r="D90" t="n">
-        <v>74.91793246730929</v>
+        <v>74.91794000535143</v>
       </c>
       <c r="E90" t="n">
-        <v>76.11873141172546</v>
+        <v>76.11873907058879</v>
       </c>
       <c r="F90" t="n">
         <v>295200</v>
@@ -2232,16 +2232,16 @@
         <v>43346</v>
       </c>
       <c r="B91" t="n">
-        <v>74.65434265136719</v>
+        <v>74.65435028076172</v>
       </c>
       <c r="C91" t="n">
-        <v>76.06014707658026</v>
+        <v>76.06015484964274</v>
       </c>
       <c r="D91" t="n">
-        <v>73.9807232206266</v>
+        <v>73.98073078117974</v>
       </c>
       <c r="E91" t="n">
-        <v>75.76727456844061</v>
+        <v>75.76728231157261</v>
       </c>
       <c r="F91" t="n">
         <v>159200</v>
@@ -2252,16 +2252,16 @@
         <v>43347</v>
       </c>
       <c r="B92" t="n">
-        <v>73.04352569580078</v>
+        <v>73.04351806640625</v>
       </c>
       <c r="C92" t="n">
-        <v>74.42004376405343</v>
+        <v>74.42003599088163</v>
       </c>
       <c r="D92" t="n">
-        <v>71.87202063991565</v>
+        <v>71.87201313288479</v>
       </c>
       <c r="E92" t="n">
-        <v>74.39075725489343</v>
+        <v>74.3907494847806</v>
       </c>
       <c r="F92" t="n">
         <v>196200</v>
@@ -2272,16 +2272,16 @@
         <v>43348</v>
       </c>
       <c r="B93" t="n">
-        <v>73.24852752685547</v>
+        <v>73.24854278564453</v>
       </c>
       <c r="C93" t="n">
-        <v>75.65011773859295</v>
+        <v>75.65013349767</v>
       </c>
       <c r="D93" t="n">
-        <v>72.80921506002102</v>
+        <v>72.80923022729456</v>
       </c>
       <c r="E93" t="n">
-        <v>72.89707457408937</v>
+        <v>72.89708975966539</v>
       </c>
       <c r="F93" t="n">
         <v>95400</v>
@@ -2292,16 +2292,16 @@
         <v>43349</v>
       </c>
       <c r="B94" t="n">
-        <v>74.21502685546875</v>
+        <v>74.21501922607422</v>
       </c>
       <c r="C94" t="n">
-        <v>76.52875778485787</v>
+        <v>76.52874991760901</v>
       </c>
       <c r="D94" t="n">
-        <v>71.46198341524806</v>
+        <v>71.46197606886972</v>
       </c>
       <c r="E94" t="n">
-        <v>74.15645384022376</v>
+        <v>74.15644621685061</v>
       </c>
       <c r="F94" t="n">
         <v>139100</v>
@@ -2312,16 +2312,16 @@
         <v>43353</v>
       </c>
       <c r="B95" t="n">
-        <v>75.50368499755859</v>
+        <v>75.50369262695312</v>
       </c>
       <c r="C95" t="n">
-        <v>76.7337704500399</v>
+        <v>76.73377820373044</v>
       </c>
       <c r="D95" t="n">
-        <v>74.42003953079482</v>
+        <v>74.4200470506906</v>
       </c>
       <c r="E95" t="n">
-        <v>75.65012498327611</v>
+        <v>75.65013262746791</v>
       </c>
       <c r="F95" t="n">
         <v>157400</v>
@@ -2352,16 +2352,16 @@
         <v>43355</v>
       </c>
       <c r="B97" t="n">
-        <v>72.95565795898438</v>
+        <v>72.95567321777344</v>
       </c>
       <c r="C97" t="n">
-        <v>74.65434995501845</v>
+        <v>74.65436556909158</v>
       </c>
       <c r="D97" t="n">
-        <v>71.34484038600858</v>
+        <v>71.34485530789266</v>
       </c>
       <c r="E97" t="n">
-        <v>73.21925143516954</v>
+        <v>73.21926674908958</v>
       </c>
       <c r="F97" t="n">
         <v>133333</v>
@@ -2372,16 +2372,16 @@
         <v>43356</v>
       </c>
       <c r="B98" t="n">
-        <v>71.60840606689453</v>
+        <v>71.60843658447266</v>
       </c>
       <c r="C98" t="n">
-        <v>73.86355598687275</v>
+        <v>73.86358746553515</v>
       </c>
       <c r="D98" t="n">
-        <v>70.43690135610605</v>
+        <v>70.43693137442035</v>
       </c>
       <c r="E98" t="n">
-        <v>73.775696485274</v>
+        <v>73.77572792649305</v>
       </c>
       <c r="F98" t="n">
         <v>250366</v>
@@ -2392,16 +2392,16 @@
         <v>43357</v>
       </c>
       <c r="B99" t="n">
-        <v>69.79257965087891</v>
+        <v>69.79258728027344</v>
       </c>
       <c r="C99" t="n">
-        <v>72.28203686752244</v>
+        <v>72.28204476905265</v>
       </c>
       <c r="D99" t="n">
-        <v>69.7047201353074</v>
+        <v>69.70472775509755</v>
       </c>
       <c r="E99" t="n">
-        <v>70.96409199622441</v>
+        <v>70.96409975368313</v>
       </c>
       <c r="F99" t="n">
         <v>269466</v>
@@ -2412,16 +2412,16 @@
         <v>43360</v>
       </c>
       <c r="B100" t="n">
-        <v>73.48282623291016</v>
+        <v>73.48283386230469</v>
       </c>
       <c r="C100" t="n">
-        <v>74.06858611346924</v>
+        <v>74.0685938036806</v>
       </c>
       <c r="D100" t="n">
-        <v>69.79257771626868</v>
+        <v>69.79258496252115</v>
       </c>
       <c r="E100" t="n">
-        <v>70.02687719954454</v>
+        <v>70.02688447012328</v>
       </c>
       <c r="F100" t="n">
         <v>114333</v>
@@ -2432,16 +2432,16 @@
         <v>43361</v>
       </c>
       <c r="B101" t="n">
-        <v>74.50790405273438</v>
+        <v>74.50791168212891</v>
       </c>
       <c r="C101" t="n">
-        <v>75.35724998338361</v>
+        <v>75.35725769974871</v>
       </c>
       <c r="D101" t="n">
-        <v>73.62927161555359</v>
+        <v>73.6292791549787</v>
       </c>
       <c r="E101" t="n">
-        <v>74.56647706579749</v>
+        <v>74.56648470118972</v>
       </c>
       <c r="F101" t="n">
         <v>194766</v>
@@ -2452,16 +2452,16 @@
         <v>43362</v>
       </c>
       <c r="B102" t="n">
-        <v>68.76751708984375</v>
+        <v>68.76750183105469</v>
       </c>
       <c r="C102" t="n">
-        <v>74.68362968540555</v>
+        <v>74.6836131138933</v>
       </c>
       <c r="D102" t="n">
-        <v>68.76751708984375</v>
+        <v>68.76750183105469</v>
       </c>
       <c r="E102" t="n">
-        <v>73.57069776046316</v>
+        <v>73.57068143589881</v>
       </c>
       <c r="F102" t="n">
         <v>510266</v>
@@ -2472,16 +2472,16 @@
         <v>43363</v>
       </c>
       <c r="B103" t="n">
-        <v>68.24034118652344</v>
+        <v>68.24033355712891</v>
       </c>
       <c r="C103" t="n">
-        <v>69.58757267942752</v>
+        <v>69.58756489941005</v>
       </c>
       <c r="D103" t="n">
-        <v>65.63373027563168</v>
+        <v>65.63372293766099</v>
       </c>
       <c r="E103" t="n">
-        <v>69.41184618485332</v>
+        <v>69.4118384244824</v>
       </c>
       <c r="F103" t="n">
         <v>1256966</v>
@@ -2492,16 +2492,16 @@
         <v>43364</v>
       </c>
       <c r="B104" t="n">
-        <v>69.35327911376953</v>
+        <v>69.353271484375</v>
       </c>
       <c r="C104" t="n">
-        <v>71.16911723059167</v>
+        <v>71.16910940144096</v>
       </c>
       <c r="D104" t="n">
-        <v>67.88889401621928</v>
+        <v>67.88888654791837</v>
       </c>
       <c r="E104" t="n">
-        <v>67.94746703668201</v>
+        <v>67.94745956193762</v>
       </c>
       <c r="F104" t="n">
         <v>293166</v>
@@ -2532,16 +2532,16 @@
         <v>43368</v>
       </c>
       <c r="B106" t="n">
-        <v>63.90576171875</v>
+        <v>63.90576553344727</v>
       </c>
       <c r="C106" t="n">
-        <v>67.21527128568442</v>
+        <v>67.21527529793472</v>
       </c>
       <c r="D106" t="n">
-        <v>61.62132092644037</v>
+        <v>61.62132460477356</v>
       </c>
       <c r="E106" t="n">
-        <v>64.46222773137842</v>
+        <v>64.46223157929256</v>
       </c>
       <c r="F106" t="n">
         <v>629433</v>
@@ -2552,16 +2552,16 @@
         <v>43369</v>
       </c>
       <c r="B107" t="n">
-        <v>65.01868438720703</v>
+        <v>65.01869201660156</v>
       </c>
       <c r="C107" t="n">
-        <v>66.48306920425335</v>
+        <v>66.48307700548109</v>
       </c>
       <c r="D107" t="n">
-        <v>63.14427360896688</v>
+        <v>63.1442810184151</v>
       </c>
       <c r="E107" t="n">
-        <v>63.93503902673306</v>
+        <v>63.93504652897094</v>
       </c>
       <c r="F107" t="n">
         <v>469400</v>
@@ -2592,16 +2592,16 @@
         <v>43371</v>
       </c>
       <c r="B109" t="n">
-        <v>70.29047393798828</v>
+        <v>70.29048156738281</v>
       </c>
       <c r="C109" t="n">
-        <v>71.3448328346373</v>
+        <v>71.34484057847294</v>
       </c>
       <c r="D109" t="n">
-        <v>67.3324176848174</v>
+        <v>67.33242499314171</v>
       </c>
       <c r="E109" t="n">
-        <v>68.59178956999595</v>
+        <v>68.59179701501368</v>
       </c>
       <c r="F109" t="n">
         <v>612400</v>
@@ -2672,16 +2672,16 @@
         <v>43377</v>
       </c>
       <c r="B113" t="n">
-        <v>70.29047393798828</v>
+        <v>70.29048156738281</v>
       </c>
       <c r="C113" t="n">
-        <v>72.13559828300075</v>
+        <v>72.13560611266682</v>
       </c>
       <c r="D113" t="n">
-        <v>67.71315715612178</v>
+        <v>67.71316450577191</v>
       </c>
       <c r="E113" t="n">
-        <v>70.55405993802722</v>
+        <v>70.55406759603163</v>
       </c>
       <c r="F113" t="n">
         <v>201700</v>
@@ -2692,16 +2692,16 @@
         <v>43378</v>
       </c>
       <c r="B114" t="n">
-        <v>68.26963043212891</v>
+        <v>68.26962280273438</v>
       </c>
       <c r="C114" t="n">
-        <v>71.60842651469054</v>
+        <v>71.60841851217266</v>
       </c>
       <c r="D114" t="n">
-        <v>67.36171141512558</v>
+        <v>67.36170388719449</v>
       </c>
       <c r="E114" t="n">
-        <v>71.60842651469054</v>
+        <v>71.60841851217266</v>
       </c>
       <c r="F114" t="n">
         <v>364566</v>
@@ -2712,16 +2712,16 @@
         <v>43381</v>
       </c>
       <c r="B115" t="n">
-        <v>69.55826568603516</v>
+        <v>69.55830383300781</v>
       </c>
       <c r="C115" t="n">
-        <v>70.90549678216492</v>
+        <v>70.90553566798273</v>
       </c>
       <c r="D115" t="n">
-        <v>68.85535991475182</v>
+        <v>68.85539767623862</v>
       </c>
       <c r="E115" t="n">
-        <v>68.85535991475182</v>
+        <v>68.85539767623862</v>
       </c>
       <c r="F115" t="n">
         <v>697200</v>
@@ -2732,16 +2732,16 @@
         <v>43382</v>
       </c>
       <c r="B116" t="n">
-        <v>68.26963043212891</v>
+        <v>68.26962280273438</v>
       </c>
       <c r="C116" t="n">
-        <v>71.75486650741638</v>
+        <v>71.75485848853327</v>
       </c>
       <c r="D116" t="n">
-        <v>68.26963043212891</v>
+        <v>68.26962280273438</v>
       </c>
       <c r="E116" t="n">
-        <v>69.9683149823054</v>
+        <v>69.96830716307632</v>
       </c>
       <c r="F116" t="n">
         <v>433600</v>
@@ -2772,16 +2772,16 @@
         <v>43384</v>
       </c>
       <c r="B118" t="n">
-        <v>70.87622833251953</v>
+        <v>70.876220703125</v>
       </c>
       <c r="C118" t="n">
-        <v>71.63770729591425</v>
+        <v>71.63769958455114</v>
       </c>
       <c r="D118" t="n">
-        <v>68.62107794888951</v>
+        <v>68.62107056224819</v>
       </c>
       <c r="E118" t="n">
-        <v>69.08967695024926</v>
+        <v>69.08966951316611</v>
       </c>
       <c r="F118" t="n">
         <v>258833</v>
@@ -2792,16 +2792,16 @@
         <v>43388</v>
       </c>
       <c r="B119" t="n">
-        <v>72.04773712158203</v>
+        <v>72.04774475097656</v>
       </c>
       <c r="C119" t="n">
-        <v>72.89708309812396</v>
+        <v>72.89709081745879</v>
       </c>
       <c r="D119" t="n">
-        <v>66.77595711014101</v>
+        <v>66.77596418128775</v>
       </c>
       <c r="E119" t="n">
-        <v>71.5791380952637</v>
+        <v>71.57914567503659</v>
       </c>
       <c r="F119" t="n">
         <v>520433</v>
@@ -2832,16 +2832,16 @@
         <v>43390</v>
       </c>
       <c r="B121" t="n">
-        <v>74.91794586181641</v>
+        <v>74.91793823242188</v>
       </c>
       <c r="C121" t="n">
-        <v>75.88443802269533</v>
+        <v>75.88443029487647</v>
       </c>
       <c r="D121" t="n">
-        <v>73.27783411546963</v>
+        <v>73.27782665309864</v>
       </c>
       <c r="E121" t="n">
-        <v>73.27783411546963</v>
+        <v>73.27782665309864</v>
       </c>
       <c r="F121" t="n">
         <v>520600</v>
@@ -2852,16 +2852,16 @@
         <v>43391</v>
       </c>
       <c r="B122" t="n">
-        <v>75.56228637695312</v>
+        <v>75.56227111816406</v>
       </c>
       <c r="C122" t="n">
-        <v>76.79236472168148</v>
+        <v>76.79234921449461</v>
       </c>
       <c r="D122" t="n">
-        <v>74.88866672513822</v>
+        <v>74.88865160237759</v>
       </c>
       <c r="E122" t="n">
-        <v>74.91795324073902</v>
+        <v>74.91793811206438</v>
       </c>
       <c r="F122" t="n">
         <v>252733</v>
@@ -2872,16 +2872,16 @@
         <v>43392</v>
       </c>
       <c r="B123" t="n">
-        <v>73.95144653320312</v>
+        <v>73.95143890380859</v>
       </c>
       <c r="C123" t="n">
-        <v>76.41161019014804</v>
+        <v>76.41160230694427</v>
       </c>
       <c r="D123" t="n">
-        <v>72.75064749048451</v>
+        <v>72.75063998497356</v>
       </c>
       <c r="E123" t="n">
-        <v>75.62084463045997</v>
+        <v>75.62083682883761</v>
       </c>
       <c r="F123" t="n">
         <v>198200</v>
@@ -2892,16 +2892,16 @@
         <v>43395</v>
       </c>
       <c r="B124" t="n">
-        <v>74.65434265136719</v>
+        <v>74.65435028076172</v>
       </c>
       <c r="C124" t="n">
-        <v>76.55804002313839</v>
+        <v>76.55804784708366</v>
       </c>
       <c r="D124" t="n">
-        <v>74.39074920097013</v>
+        <v>74.3907568034264</v>
       </c>
       <c r="E124" t="n">
-        <v>74.53718917916331</v>
+        <v>74.53719679658519</v>
       </c>
       <c r="F124" t="n">
         <v>312766</v>
@@ -2932,16 +2932,16 @@
         <v>43397</v>
       </c>
       <c r="B126" t="n">
-        <v>74.39075469970703</v>
+        <v>74.39076232910156</v>
       </c>
       <c r="C126" t="n">
-        <v>75.26938718556521</v>
+        <v>75.26939490507085</v>
       </c>
       <c r="D126" t="n">
-        <v>74.24431471068945</v>
+        <v>74.24432232506534</v>
       </c>
       <c r="E126" t="n">
-        <v>75.26938718556521</v>
+        <v>75.26939490507085</v>
       </c>
       <c r="F126" t="n">
         <v>414300</v>
@@ -2952,16 +2952,16 @@
         <v>43398</v>
       </c>
       <c r="B127" t="n">
-        <v>76.00157165527344</v>
+        <v>76.0015869140625</v>
       </c>
       <c r="C127" t="n">
-        <v>76.00157165527344</v>
+        <v>76.0015869140625</v>
       </c>
       <c r="D127" t="n">
-        <v>73.10208848230262</v>
+        <v>73.10210315896421</v>
       </c>
       <c r="E127" t="n">
-        <v>74.56647332131847</v>
+        <v>74.56648829198372</v>
       </c>
       <c r="F127" t="n">
         <v>495966</v>
@@ -2992,16 +2992,16 @@
         <v>43402</v>
       </c>
       <c r="B129" t="n">
-        <v>75.50368499755859</v>
+        <v>75.50369262695312</v>
       </c>
       <c r="C129" t="n">
-        <v>76.44089047860484</v>
+        <v>76.44089820270085</v>
       </c>
       <c r="D129" t="n">
-        <v>75.18152596687653</v>
+        <v>75.18153356371796</v>
       </c>
       <c r="E129" t="n">
-        <v>76.38231746361667</v>
+        <v>76.38232518179406</v>
       </c>
       <c r="F129" t="n">
         <v>188000</v>
@@ -3012,16 +3012,16 @@
         <v>43403</v>
       </c>
       <c r="B130" t="n">
-        <v>74.56648254394531</v>
+        <v>74.56649017333984</v>
       </c>
       <c r="C130" t="n">
-        <v>76.14802104706102</v>
+        <v>76.14802883827332</v>
       </c>
       <c r="D130" t="n">
-        <v>73.65856353353124</v>
+        <v>73.6585710700305</v>
       </c>
       <c r="E130" t="n">
-        <v>75.65012805470559</v>
+        <v>75.65013579497513</v>
       </c>
       <c r="F130" t="n">
         <v>1306966</v>
@@ -3052,16 +3052,16 @@
         <v>43405</v>
       </c>
       <c r="B132" t="n">
-        <v>75.35725402832031</v>
+        <v>75.35726165771484</v>
       </c>
       <c r="C132" t="n">
-        <v>78.08100355741267</v>
+        <v>78.08101146256779</v>
       </c>
       <c r="D132" t="n">
-        <v>74.15645505834372</v>
+        <v>74.15646256616576</v>
       </c>
       <c r="E132" t="n">
-        <v>75.65012655760316</v>
+        <v>75.65013421664898</v>
       </c>
       <c r="F132" t="n">
         <v>289433</v>
@@ -3072,16 +3072,16 @@
         <v>43409</v>
       </c>
       <c r="B133" t="n">
-        <v>76.38231658935547</v>
+        <v>76.38232421875</v>
       </c>
       <c r="C133" t="n">
-        <v>76.85092304863853</v>
+        <v>76.85093072483949</v>
       </c>
       <c r="D133" t="n">
-        <v>73.98072617511639</v>
+        <v>73.98073356462973</v>
       </c>
       <c r="E133" t="n">
-        <v>75.82585060859577</v>
+        <v>75.82585818240808</v>
       </c>
       <c r="F133" t="n">
         <v>315933</v>
@@ -3152,16 +3152,16 @@
         <v>43413</v>
       </c>
       <c r="B137" t="n">
-        <v>76.73377990722656</v>
+        <v>76.73374938964844</v>
       </c>
       <c r="C137" t="n">
-        <v>79.07679762273497</v>
+        <v>79.0767661733218</v>
       </c>
       <c r="D137" t="n">
-        <v>75.21082174385769</v>
+        <v>75.21079183197102</v>
       </c>
       <c r="E137" t="n">
-        <v>77.31953247404167</v>
+        <v>77.31950172350552</v>
       </c>
       <c r="F137" t="n">
         <v>423466</v>
@@ -3172,16 +3172,16 @@
         <v>43416</v>
       </c>
       <c r="B138" t="n">
-        <v>76.79234313964844</v>
+        <v>76.79235076904297</v>
       </c>
       <c r="C138" t="n">
-        <v>77.78812907971066</v>
+        <v>77.78813680803749</v>
       </c>
       <c r="D138" t="n">
-        <v>75.79656464783326</v>
+        <v>75.79657217829622</v>
       </c>
       <c r="E138" t="n">
-        <v>77.02665009510251</v>
+        <v>77.02665774777567</v>
       </c>
       <c r="F138" t="n">
         <v>143933</v>
@@ -3192,16 +3192,16 @@
         <v>43417</v>
       </c>
       <c r="B139" t="n">
-        <v>75.26938629150391</v>
+        <v>75.26937866210938</v>
       </c>
       <c r="C139" t="n">
-        <v>77.84670325390931</v>
+        <v>77.84669536327486</v>
       </c>
       <c r="D139" t="n">
-        <v>74.91793330133525</v>
+        <v>74.91792570756441</v>
       </c>
       <c r="E139" t="n">
-        <v>77.26095075304393</v>
+        <v>77.26094292178205</v>
       </c>
       <c r="F139" t="n">
         <v>637900</v>
@@ -3252,16 +3252,16 @@
         <v>43423</v>
       </c>
       <c r="B142" t="n">
-        <v>80.24828338623047</v>
+        <v>80.248291015625</v>
       </c>
       <c r="C142" t="n">
-        <v>81.5369417014697</v>
+        <v>81.53694945338003</v>
       </c>
       <c r="D142" t="n">
-        <v>79.77968442518686</v>
+        <v>79.77969201003057</v>
       </c>
       <c r="E142" t="n">
-        <v>80.65831678745137</v>
+        <v>80.65832445582875</v>
       </c>
       <c r="F142" t="n">
         <v>158533</v>
@@ -3272,16 +3272,16 @@
         <v>43425</v>
       </c>
       <c r="B143" t="n">
-        <v>79.80899047851562</v>
+        <v>79.80897521972656</v>
       </c>
       <c r="C143" t="n">
-        <v>81.59554214469678</v>
+        <v>81.59552654433449</v>
       </c>
       <c r="D143" t="n">
-        <v>78.13959230541533</v>
+        <v>78.13957736580078</v>
       </c>
       <c r="E143" t="n">
-        <v>79.04751139411002</v>
+        <v>79.04749628090917</v>
       </c>
       <c r="F143" t="n">
         <v>918800</v>
@@ -3352,16 +3352,16 @@
         <v>43431</v>
       </c>
       <c r="B147" t="n">
-        <v>81.59552764892578</v>
+        <v>81.59553527832031</v>
       </c>
       <c r="C147" t="n">
-        <v>82.59130609434109</v>
+        <v>82.5913138168435</v>
       </c>
       <c r="D147" t="n">
-        <v>76.32374056880897</v>
+        <v>76.32374770527765</v>
       </c>
       <c r="E147" t="n">
-        <v>78.28601840188094</v>
+        <v>78.28602572182773</v>
       </c>
       <c r="F147" t="n">
         <v>436400</v>
@@ -3372,16 +3372,16 @@
         <v>43432</v>
       </c>
       <c r="B148" t="n">
-        <v>84.52429962158203</v>
+        <v>84.52430725097656</v>
       </c>
       <c r="C148" t="n">
-        <v>86.22298404832937</v>
+        <v>86.2229918310518</v>
       </c>
       <c r="D148" t="n">
-        <v>80.54117083974624</v>
+        <v>80.54117810961267</v>
       </c>
       <c r="E148" t="n">
-        <v>81.18549633337582</v>
+        <v>81.18550366140083</v>
       </c>
       <c r="F148" t="n">
         <v>429500</v>
@@ -3392,16 +3392,16 @@
         <v>43433</v>
       </c>
       <c r="B149" t="n">
-        <v>84.1728515625</v>
+        <v>84.17283630371094</v>
       </c>
       <c r="C149" t="n">
-        <v>85.69580958938813</v>
+        <v>85.69579405451842</v>
       </c>
       <c r="D149" t="n">
-        <v>83.2942190668925</v>
+        <v>83.29420396738125</v>
       </c>
       <c r="E149" t="n">
-        <v>84.31929155314248</v>
+        <v>84.31927626780688</v>
       </c>
       <c r="F149" t="n">
         <v>232033</v>
@@ -3412,16 +3412,16 @@
         <v>43434</v>
       </c>
       <c r="B150" t="n">
-        <v>82.91347503662109</v>
+        <v>82.91348266601562</v>
       </c>
       <c r="C150" t="n">
-        <v>84.26070649088619</v>
+        <v>84.26071424424802</v>
       </c>
       <c r="D150" t="n">
-        <v>82.32772255425571</v>
+        <v>82.32773012975143</v>
       </c>
       <c r="E150" t="n">
-        <v>84.23141998400496</v>
+        <v>84.23142773467195</v>
       </c>
       <c r="F150" t="n">
         <v>464600</v>
@@ -3432,16 +3432,16 @@
         <v>43437</v>
       </c>
       <c r="B151" t="n">
-        <v>84.49500274658203</v>
+        <v>84.49501800537109</v>
       </c>
       <c r="C151" t="n">
-        <v>85.2857756432162</v>
+        <v>85.2857910448094</v>
       </c>
       <c r="D151" t="n">
-        <v>82.79631837853798</v>
+        <v>82.79633333056491</v>
       </c>
       <c r="E151" t="n">
-        <v>83.29421132112294</v>
+        <v>83.2942263630634</v>
       </c>
       <c r="F151" t="n">
         <v>313866</v>
@@ -3452,16 +3452,16 @@
         <v>43438</v>
       </c>
       <c r="B152" t="n">
-        <v>83.82138824462891</v>
+        <v>83.82139587402344</v>
       </c>
       <c r="C152" t="n">
-        <v>86.60371793130145</v>
+        <v>86.60372581394269</v>
       </c>
       <c r="D152" t="n">
-        <v>82.59130290221974</v>
+        <v>82.59131041965232</v>
       </c>
       <c r="E152" t="n">
-        <v>84.64144017407074</v>
+        <v>84.64144787810613</v>
       </c>
       <c r="F152" t="n">
         <v>207933</v>
@@ -3492,16 +3492,16 @@
         <v>43440</v>
       </c>
       <c r="B154" t="n">
-        <v>84.93431091308594</v>
+        <v>84.93431854248047</v>
       </c>
       <c r="C154" t="n">
-        <v>85.46149028840492</v>
+        <v>85.46149796515439</v>
       </c>
       <c r="D154" t="n">
-        <v>83.87995216244801</v>
+        <v>83.87995969713265</v>
       </c>
       <c r="E154" t="n">
-        <v>85.25647732826624</v>
+        <v>85.25648498660001</v>
       </c>
       <c r="F154" t="n">
         <v>270866</v>
@@ -3512,16 +3512,16 @@
         <v>43441</v>
       </c>
       <c r="B155" t="n">
-        <v>84.26071166992188</v>
+        <v>84.26070404052734</v>
       </c>
       <c r="C155" t="n">
-        <v>86.10583619931816</v>
+        <v>86.10582840285664</v>
       </c>
       <c r="D155" t="n">
-        <v>82.18128762282772</v>
+        <v>82.18128018171485</v>
       </c>
       <c r="E155" t="n">
-        <v>85.57865669831246</v>
+        <v>85.57864894958446</v>
       </c>
       <c r="F155" t="n">
         <v>485833</v>
@@ -3592,16 +3592,16 @@
         <v>43447</v>
       </c>
       <c r="B159" t="n">
-        <v>86.77944946289062</v>
+        <v>86.77945709228516</v>
       </c>
       <c r="C159" t="n">
-        <v>88.77101384098502</v>
+        <v>88.77102164547205</v>
       </c>
       <c r="D159" t="n">
-        <v>84.99289807909682</v>
+        <v>84.99290555142299</v>
       </c>
       <c r="E159" t="n">
-        <v>85.78367099796685</v>
+        <v>85.78367853981547</v>
       </c>
       <c r="F159" t="n">
         <v>486800</v>
@@ -3612,16 +3612,16 @@
         <v>43448</v>
       </c>
       <c r="B160" t="n">
-        <v>86.39871978759766</v>
+        <v>86.39870452880859</v>
       </c>
       <c r="C160" t="n">
-        <v>88.30241741378802</v>
+        <v>88.30240181878888</v>
       </c>
       <c r="D160" t="n">
-        <v>85.81296724478891</v>
+        <v>85.812952089449</v>
       </c>
       <c r="E160" t="n">
-        <v>86.77945931283573</v>
+        <v>86.77944398680465</v>
       </c>
       <c r="F160" t="n">
         <v>286966</v>
@@ -3632,16 +3632,16 @@
         <v>43451</v>
       </c>
       <c r="B161" t="n">
-        <v>84.93785095214844</v>
+        <v>84.9378662109375</v>
       </c>
       <c r="C161" t="n">
-        <v>86.47038439559775</v>
+        <v>86.47039992970112</v>
       </c>
       <c r="D161" t="n">
-        <v>84.28946680602617</v>
+        <v>84.28948194833528</v>
       </c>
       <c r="E161" t="n">
-        <v>86.44091375169715</v>
+        <v>86.44092928050621</v>
       </c>
       <c r="F161" t="n">
         <v>205700</v>
@@ -3652,16 +3652,16 @@
         <v>43452</v>
       </c>
       <c r="B162" t="n">
-        <v>86.35251617431641</v>
+        <v>86.35250091552734</v>
       </c>
       <c r="C162" t="n">
-        <v>87.14825367221657</v>
+        <v>87.14823827281793</v>
       </c>
       <c r="D162" t="n">
-        <v>84.67262173703909</v>
+        <v>84.67260677509321</v>
       </c>
       <c r="E162" t="n">
-        <v>84.96733572011246</v>
+        <v>84.96732070608958</v>
       </c>
       <c r="F162" t="n">
         <v>387133</v>
@@ -3672,16 +3672,16 @@
         <v>43453</v>
       </c>
       <c r="B163" t="n">
-        <v>89.68283081054688</v>
+        <v>89.68281555175781</v>
       </c>
       <c r="C163" t="n">
-        <v>90.56698771453594</v>
+        <v>90.56697230531492</v>
       </c>
       <c r="D163" t="n">
-        <v>86.29356392776849</v>
+        <v>86.29354924563503</v>
       </c>
       <c r="E163" t="n">
-        <v>86.52934409888439</v>
+        <v>86.52932937663491</v>
       </c>
       <c r="F163" t="n">
         <v>384866</v>
@@ -3692,16 +3692,16 @@
         <v>43454</v>
       </c>
       <c r="B164" t="n">
-        <v>89.00496673583984</v>
+        <v>89.00498199462891</v>
       </c>
       <c r="C164" t="n">
-        <v>93.07208057875353</v>
+        <v>93.07209653479842</v>
       </c>
       <c r="D164" t="n">
-        <v>87.20718246605232</v>
+        <v>87.20719741663375</v>
       </c>
       <c r="E164" t="n">
-        <v>89.2702175271606</v>
+        <v>89.2702328314236</v>
       </c>
       <c r="F164" t="n">
         <v>975500</v>
@@ -3712,16 +3712,16 @@
         <v>43455</v>
       </c>
       <c r="B165" t="n">
-        <v>88.00293731689453</v>
+        <v>88.00292205810547</v>
       </c>
       <c r="C165" t="n">
-        <v>90.18384770834878</v>
+        <v>90.18383207141265</v>
       </c>
       <c r="D165" t="n">
-        <v>86.08726275666103</v>
+        <v>86.08724783002991</v>
       </c>
       <c r="E165" t="n">
-        <v>90.18384770834878</v>
+        <v>90.18383207141265</v>
       </c>
       <c r="F165" t="n">
         <v>2053700</v>
@@ -3812,16 +3812,16 @@
         <v>43468</v>
       </c>
       <c r="B170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494140625</v>
       </c>
       <c r="C170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.53955725766548</v>
       </c>
       <c r="D170" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494140625</v>
       </c>
       <c r="E170" t="n">
-        <v>91.53954946006759</v>
+        <v>91.53955725766548</v>
       </c>
       <c r="F170" t="n">
         <v>308333</v>
@@ -3832,16 +3832,16 @@
         <v>43469</v>
       </c>
       <c r="B171" t="n">
-        <v>89.88912200927734</v>
+        <v>89.88913726806641</v>
       </c>
       <c r="C171" t="n">
-        <v>91.36271417336386</v>
+        <v>91.362729682297</v>
       </c>
       <c r="D171" t="n">
-        <v>88.68077313689237</v>
+        <v>88.68078819056272</v>
       </c>
       <c r="E171" t="n">
-        <v>89.83018072113863</v>
+        <v>89.83019596992233</v>
       </c>
       <c r="F171" t="n">
         <v>585300</v>
@@ -3852,16 +3852,16 @@
         <v>43472</v>
       </c>
       <c r="B172" t="n">
-        <v>91.24482727050781</v>
+        <v>91.24481964111328</v>
       </c>
       <c r="C172" t="n">
-        <v>91.65743129196125</v>
+        <v>91.65742362806702</v>
       </c>
       <c r="D172" t="n">
-        <v>89.88912513069897</v>
+        <v>89.88911761466086</v>
       </c>
       <c r="E172" t="n">
-        <v>89.88912513069897</v>
+        <v>89.88911761466086</v>
       </c>
       <c r="F172" t="n">
         <v>470133</v>
@@ -3872,16 +3872,16 @@
         <v>43473</v>
       </c>
       <c r="B173" t="n">
-        <v>89.88912200927734</v>
+        <v>89.88913726806641</v>
       </c>
       <c r="C173" t="n">
-        <v>91.21535345793974</v>
+        <v>91.21536894185822</v>
       </c>
       <c r="D173" t="n">
-        <v>89.35862793079691</v>
+        <v>89.35864309953395</v>
       </c>
       <c r="E173" t="n">
-        <v>91.21535345793974</v>
+        <v>91.21536894185822</v>
       </c>
       <c r="F173" t="n">
         <v>273633</v>
@@ -3912,16 +3912,16 @@
         <v>43475</v>
       </c>
       <c r="B175" t="n">
-        <v>93.39627838134766</v>
+        <v>93.39628601074219</v>
       </c>
       <c r="C175" t="n">
-        <v>94.84040001456971</v>
+        <v>94.84040776193225</v>
       </c>
       <c r="D175" t="n">
-        <v>91.0974705277286</v>
+        <v>91.09747796933716</v>
       </c>
       <c r="E175" t="n">
-        <v>91.0974705277286</v>
+        <v>91.09747796933716</v>
       </c>
       <c r="F175" t="n">
         <v>243466</v>
@@ -3932,16 +3932,16 @@
         <v>43476</v>
       </c>
       <c r="B176" t="n">
-        <v>92.36476135253906</v>
+        <v>92.36476898193359</v>
       </c>
       <c r="C176" t="n">
-        <v>93.04261620372681</v>
+        <v>93.04262388911262</v>
       </c>
       <c r="D176" t="n">
-        <v>90.86169841736448</v>
+        <v>90.86170592260495</v>
       </c>
       <c r="E176" t="n">
-        <v>92.39423199909888</v>
+        <v>92.39423963092771</v>
       </c>
       <c r="F176" t="n">
         <v>283133</v>
@@ -3972,16 +3972,16 @@
         <v>43480</v>
       </c>
       <c r="B178" t="n">
-        <v>93.42575836181641</v>
+        <v>93.42575073242188</v>
       </c>
       <c r="C178" t="n">
-        <v>99.26118677047653</v>
+        <v>99.26117866454547</v>
       </c>
       <c r="D178" t="n">
-        <v>92.74790344705082</v>
+        <v>92.7478958730117</v>
       </c>
       <c r="E178" t="n">
-        <v>94.69304874829707</v>
+        <v>94.69304101541225</v>
       </c>
       <c r="F178" t="n">
         <v>736266</v>
@@ -3992,16 +3992,16 @@
         <v>43481</v>
       </c>
       <c r="B179" t="n">
-        <v>98.43595886230469</v>
+        <v>98.43595123291016</v>
       </c>
       <c r="C179" t="n">
-        <v>100.0569118290803</v>
+        <v>100.0569040740519</v>
       </c>
       <c r="D179" t="n">
-        <v>93.74993882606901</v>
+        <v>93.74993155986996</v>
       </c>
       <c r="E179" t="n">
-        <v>93.89729954942638</v>
+        <v>93.89729227180597</v>
       </c>
       <c r="F179" t="n">
         <v>1131666</v>
@@ -4012,16 +4012,16 @@
         <v>43482</v>
       </c>
       <c r="B180" t="n">
-        <v>99.26117706298828</v>
+        <v>99.26116943359375</v>
       </c>
       <c r="C180" t="n">
-        <v>100.0274438507868</v>
+        <v>100.0274361624956</v>
       </c>
       <c r="D180" t="n">
-        <v>97.90546736604202</v>
+        <v>97.90545984084979</v>
       </c>
       <c r="E180" t="n">
-        <v>98.78962423468569</v>
+        <v>98.78961664153556</v>
       </c>
       <c r="F180" t="n">
         <v>313600</v>
@@ -4032,16 +4032,16 @@
         <v>43483</v>
       </c>
       <c r="B181" t="n">
-        <v>100.7937088012695</v>
+        <v>100.7937164306641</v>
       </c>
       <c r="C181" t="n">
-        <v>102.2673010571217</v>
+        <v>102.267308798057</v>
       </c>
       <c r="D181" t="n">
-        <v>98.73068114209212</v>
+        <v>98.73068861532957</v>
       </c>
       <c r="E181" t="n">
-        <v>99.67377928642814</v>
+        <v>99.67378683105167</v>
       </c>
       <c r="F181" t="n">
         <v>475600</v>
@@ -4052,16 +4052,16 @@
         <v>43486</v>
       </c>
       <c r="B182" t="n">
-        <v>101.3831329345703</v>
+        <v>101.3831481933594</v>
       </c>
       <c r="C182" t="n">
-        <v>102.3557091117745</v>
+        <v>102.3557245169423</v>
       </c>
       <c r="D182" t="n">
-        <v>98.22964675700621</v>
+        <v>98.22966154117607</v>
       </c>
       <c r="E182" t="n">
-        <v>100.7936975967683</v>
+        <v>100.7937127668437</v>
       </c>
       <c r="F182" t="n">
         <v>260300</v>
@@ -4072,16 +4072,16 @@
         <v>43487</v>
       </c>
       <c r="B183" t="n">
-        <v>100.2632141113281</v>
+        <v>100.2632064819336</v>
       </c>
       <c r="C183" t="n">
-        <v>101.7662770044136</v>
+        <v>101.7662692606455</v>
       </c>
       <c r="D183" t="n">
-        <v>99.17275524868226</v>
+        <v>99.17274770226473</v>
       </c>
       <c r="E183" t="n">
-        <v>101.7662770044136</v>
+        <v>101.7662692606455</v>
       </c>
       <c r="F183" t="n">
         <v>236233</v>
@@ -4092,16 +4092,16 @@
         <v>43488</v>
       </c>
       <c r="B184" t="n">
-        <v>99.23171997070312</v>
+        <v>99.23170471191406</v>
       </c>
       <c r="C184" t="n">
-        <v>101.0589752504606</v>
+        <v>101.0589597106958</v>
       </c>
       <c r="D184" t="n">
-        <v>98.17073158340929</v>
+        <v>98.17071648776765</v>
       </c>
       <c r="E184" t="n">
-        <v>99.58538276646773</v>
+        <v>99.5853674532962</v>
       </c>
       <c r="F184" t="n">
         <v>240366</v>
@@ -4112,16 +4112,16 @@
         <v>43489</v>
       </c>
       <c r="B185" t="n">
-        <v>98.22964477539062</v>
+        <v>98.22966766357422</v>
       </c>
       <c r="C185" t="n">
-        <v>100.9705269107084</v>
+        <v>100.9705504375364</v>
       </c>
       <c r="D185" t="n">
-        <v>97.05077412356822</v>
+        <v>97.05079673706683</v>
       </c>
       <c r="E185" t="n">
-        <v>99.23169157500881</v>
+        <v>99.23171469667619</v>
       </c>
       <c r="F185" t="n">
         <v>372266</v>
@@ -4132,16 +4132,16 @@
         <v>43493</v>
       </c>
       <c r="B186" t="n">
-        <v>97.257080078125</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C186" t="n">
-        <v>98.05281742579406</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="D186" t="n">
-        <v>95.96031931021975</v>
+        <v>95.96032683788904</v>
       </c>
       <c r="E186" t="n">
-        <v>98.05281742579406</v>
+        <v>98.05282511761074</v>
       </c>
       <c r="F186" t="n">
         <v>263933</v>
@@ -4172,16 +4172,16 @@
         <v>43495</v>
       </c>
       <c r="B188" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73068237304688</v>
       </c>
       <c r="C188" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73068237304688</v>
       </c>
       <c r="D188" t="n">
-        <v>96.49083077174782</v>
+        <v>96.49082331543798</v>
       </c>
       <c r="E188" t="n">
-        <v>97.28656826289463</v>
+        <v>97.28656074509432</v>
       </c>
       <c r="F188" t="n">
         <v>447533</v>
@@ -4192,16 +4192,16 @@
         <v>43496</v>
       </c>
       <c r="B189" t="n">
-        <v>100.9115982055664</v>
+        <v>100.9115905761719</v>
       </c>
       <c r="C189" t="n">
-        <v>104.5661081748688</v>
+        <v>104.566100269176</v>
       </c>
       <c r="D189" t="n">
-        <v>99.20222580374578</v>
+        <v>99.2022183035879</v>
       </c>
       <c r="E189" t="n">
-        <v>99.79166869820958</v>
+        <v>99.79166115348703</v>
       </c>
       <c r="F189" t="n">
         <v>504800</v>
@@ -4212,16 +4212,16 @@
         <v>43497</v>
       </c>
       <c r="B190" t="n">
-        <v>100.2042846679688</v>
+        <v>100.2042922973633</v>
       </c>
       <c r="C190" t="n">
-        <v>101.5599869976012</v>
+        <v>101.5599947302167</v>
       </c>
       <c r="D190" t="n">
-        <v>98.84858233833631</v>
+        <v>98.84858986450983</v>
       </c>
       <c r="E190" t="n">
-        <v>101.2063242168138</v>
+        <v>101.2063319225021</v>
       </c>
       <c r="F190" t="n">
         <v>150066</v>
@@ -4232,16 +4232,16 @@
         <v>43500</v>
       </c>
       <c r="B191" t="n">
-        <v>100.2632141113281</v>
+        <v>100.2632064819336</v>
       </c>
       <c r="C191" t="n">
-        <v>102.2673004671346</v>
+        <v>102.2672926852418</v>
       </c>
       <c r="D191" t="n">
-        <v>99.55588863338727</v>
+        <v>99.55588105781572</v>
       </c>
       <c r="E191" t="n">
-        <v>100.7347669283146</v>
+        <v>100.7347592630379</v>
       </c>
       <c r="F191" t="n">
         <v>316266</v>
@@ -4252,16 +4252,16 @@
         <v>43501</v>
       </c>
       <c r="B192" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73068237304688</v>
       </c>
       <c r="C192" t="n">
-        <v>101.8547061650084</v>
+        <v>101.8546982942061</v>
       </c>
       <c r="D192" t="n">
-        <v>93.86783062467705</v>
+        <v>93.86782337105902</v>
       </c>
       <c r="E192" t="n">
-        <v>100.2632236876363</v>
+        <v>100.2632159398155</v>
       </c>
       <c r="F192" t="n">
         <v>970333</v>
@@ -4272,16 +4272,16 @@
         <v>43502</v>
       </c>
       <c r="B193" t="n">
-        <v>97.46338653564453</v>
+        <v>97.46339416503906</v>
       </c>
       <c r="C193" t="n">
-        <v>99.55588474696876</v>
+        <v>99.5558925401632</v>
       </c>
       <c r="D193" t="n">
-        <v>96.07820627957145</v>
+        <v>96.07821380053463</v>
       </c>
       <c r="E193" t="n">
-        <v>98.43595528230763</v>
+        <v>98.43596298783444</v>
       </c>
       <c r="F193" t="n">
         <v>594200</v>
@@ -4292,16 +4292,16 @@
         <v>43503</v>
       </c>
       <c r="B194" t="n">
-        <v>97.10972595214844</v>
+        <v>97.10971832275391</v>
       </c>
       <c r="C194" t="n">
-        <v>98.61278881970669</v>
+        <v>98.61278107222451</v>
       </c>
       <c r="D194" t="n">
-        <v>95.3119416420943</v>
+        <v>95.31193415394212</v>
       </c>
       <c r="E194" t="n">
-        <v>97.19814538292826</v>
+        <v>97.19813774658708</v>
       </c>
       <c r="F194" t="n">
         <v>496333</v>
@@ -4332,16 +4332,16 @@
         <v>43507</v>
       </c>
       <c r="B196" t="n">
-        <v>98.1412353515625</v>
+        <v>98.14124298095703</v>
       </c>
       <c r="C196" t="n">
-        <v>98.67172940693146</v>
+        <v>98.67173707756602</v>
       </c>
       <c r="D196" t="n">
-        <v>96.10767855352002</v>
+        <v>96.10768602482801</v>
       </c>
       <c r="E196" t="n">
-        <v>97.10971788361003</v>
+        <v>97.10972543281549</v>
       </c>
       <c r="F196" t="n">
         <v>401966</v>
@@ -4352,16 +4352,16 @@
         <v>43508</v>
       </c>
       <c r="B197" t="n">
-        <v>97.55181121826172</v>
+        <v>97.55180358886719</v>
       </c>
       <c r="C197" t="n">
-        <v>99.64431719812912</v>
+        <v>99.64430940508254</v>
       </c>
       <c r="D197" t="n">
-        <v>96.7855443786229</v>
+        <v>96.78553680915705</v>
       </c>
       <c r="E197" t="n">
-        <v>98.20019546415823</v>
+        <v>98.20018778405444</v>
       </c>
       <c r="F197" t="n">
         <v>301900</v>
@@ -4372,16 +4372,16 @@
         <v>43509</v>
       </c>
       <c r="B198" t="n">
-        <v>98.73069000244141</v>
+        <v>98.73068237304688</v>
       </c>
       <c r="C198" t="n">
-        <v>99.88009026633756</v>
+        <v>99.88008254812335</v>
       </c>
       <c r="D198" t="n">
-        <v>96.28452873682379</v>
+        <v>96.28452129645588</v>
       </c>
       <c r="E198" t="n">
-        <v>97.25709761434527</v>
+        <v>97.25709009882229</v>
       </c>
       <c r="F198" t="n">
         <v>448033</v>
@@ -4392,16 +4392,16 @@
         <v>43510</v>
       </c>
       <c r="B199" t="n">
-        <v>97.64022827148438</v>
+        <v>97.64022064208984</v>
       </c>
       <c r="C199" t="n">
-        <v>99.0254011796402</v>
+        <v>99.02539344201128</v>
       </c>
       <c r="D199" t="n">
-        <v>96.54976933555744</v>
+        <v>96.54976179136901</v>
       </c>
       <c r="E199" t="n">
-        <v>98.40649509238908</v>
+        <v>98.40648740312012</v>
       </c>
       <c r="F199" t="n">
         <v>462433</v>
@@ -4432,16 +4432,16 @@
         <v>43514</v>
       </c>
       <c r="B201" t="n">
-        <v>100.2042846679688</v>
+        <v>100.2042922973633</v>
       </c>
       <c r="C201" t="n">
-        <v>100.2042846679688</v>
+        <v>100.2042922973633</v>
       </c>
       <c r="D201" t="n">
-        <v>97.64023325479974</v>
+        <v>97.64024068897147</v>
       </c>
       <c r="E201" t="n">
-        <v>98.34755881637444</v>
+        <v>98.34756630440083</v>
       </c>
       <c r="F201" t="n">
         <v>154800</v>
@@ -4452,16 +4452,16 @@
         <v>43515</v>
       </c>
       <c r="B202" t="n">
-        <v>98.43595886230469</v>
+        <v>98.43595123291016</v>
       </c>
       <c r="C202" t="n">
-        <v>101.0000099654586</v>
+        <v>101.0000021373343</v>
       </c>
       <c r="D202" t="n">
-        <v>98.2591274932914</v>
+        <v>98.25911987760239</v>
       </c>
       <c r="E202" t="n">
-        <v>100.2337431980935</v>
+        <v>100.2337354293596</v>
       </c>
       <c r="F202" t="n">
         <v>215600</v>
@@ -4472,16 +4472,16 @@
         <v>43516</v>
       </c>
       <c r="B203" t="n">
-        <v>97.257080078125</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C203" t="n">
-        <v>99.17274683920873</v>
+        <v>99.17275461887898</v>
       </c>
       <c r="D203" t="n">
-        <v>95.51823717645472</v>
+        <v>95.5182446694446</v>
       </c>
       <c r="E203" t="n">
-        <v>98.87803291177583</v>
+        <v>98.87804066832706</v>
       </c>
       <c r="F203" t="n">
         <v>616733</v>
@@ -4492,16 +4492,16 @@
         <v>43517</v>
       </c>
       <c r="B204" t="n">
-        <v>95.78350067138672</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C204" t="n">
-        <v>97.61075574533942</v>
+        <v>97.61076352027936</v>
       </c>
       <c r="D204" t="n">
-        <v>95.04670451237605</v>
+        <v>95.04671208308292</v>
       </c>
       <c r="E204" t="n">
-        <v>97.28656363655598</v>
+        <v>97.28657138567321</v>
       </c>
       <c r="F204" t="n">
         <v>542100</v>
@@ -4512,16 +4512,16 @@
         <v>43518</v>
       </c>
       <c r="B205" t="n">
-        <v>92.86579132080078</v>
+        <v>92.86578369140625</v>
       </c>
       <c r="C205" t="n">
-        <v>95.87191740128438</v>
+        <v>95.87190952492139</v>
       </c>
       <c r="D205" t="n">
-        <v>92.86579132080078</v>
+        <v>92.86578369140625</v>
       </c>
       <c r="E205" t="n">
-        <v>95.8424467526645</v>
+        <v>95.84243887872267</v>
       </c>
       <c r="F205" t="n">
         <v>514866</v>
@@ -4532,16 +4532,16 @@
         <v>43521</v>
       </c>
       <c r="B206" t="n">
-        <v>95.40037536621094</v>
+        <v>95.40036010742188</v>
       </c>
       <c r="C206" t="n">
-        <v>97.10974050159045</v>
+        <v>97.10972496939742</v>
       </c>
       <c r="D206" t="n">
-        <v>92.24688843737613</v>
+        <v>92.24687368297073</v>
       </c>
       <c r="E206" t="n">
-        <v>93.66153208610318</v>
+        <v>93.66151710543296</v>
       </c>
       <c r="F206" t="n">
         <v>404566</v>
@@ -4552,16 +4552,16 @@
         <v>43522</v>
       </c>
       <c r="B207" t="n">
-        <v>95.13511657714844</v>
+        <v>95.13510894775391</v>
       </c>
       <c r="C207" t="n">
-        <v>97.25709311548748</v>
+        <v>97.25708531592029</v>
       </c>
       <c r="D207" t="n">
-        <v>93.36681029027736</v>
+        <v>93.36680280269279</v>
       </c>
       <c r="E207" t="n">
-        <v>95.5771987701748</v>
+        <v>95.57719110532733</v>
       </c>
       <c r="F207" t="n">
         <v>332133</v>
@@ -4572,16 +4572,16 @@
         <v>43523</v>
       </c>
       <c r="B208" t="n">
-        <v>95.69507598876953</v>
+        <v>95.69508361816406</v>
       </c>
       <c r="C208" t="n">
-        <v>96.63818161626997</v>
+        <v>96.63818932085464</v>
       </c>
       <c r="D208" t="n">
-        <v>94.45726390594589</v>
+        <v>94.45727143665449</v>
       </c>
       <c r="E208" t="n">
-        <v>95.13511123842235</v>
+        <v>95.13511882317307</v>
       </c>
       <c r="F208" t="n">
         <v>447266</v>
@@ -4612,16 +4612,16 @@
         <v>43525</v>
       </c>
       <c r="B210" t="n">
-        <v>95.42984008789062</v>
+        <v>95.42983245849609</v>
       </c>
       <c r="C210" t="n">
-        <v>96.66765976182906</v>
+        <v>96.66765203347371</v>
       </c>
       <c r="D210" t="n">
-        <v>94.60462447357224</v>
+        <v>94.60461691015179</v>
       </c>
       <c r="E210" t="n">
-        <v>95.28247935371824</v>
+        <v>95.28247173610485</v>
       </c>
       <c r="F210" t="n">
         <v>326633</v>
@@ -4712,16 +4712,16 @@
         <v>43536</v>
       </c>
       <c r="B215" t="n">
-        <v>97.257080078125</v>
+        <v>97.25708770751953</v>
       </c>
       <c r="C215" t="n">
-        <v>98.49489955955909</v>
+        <v>98.49490728605517</v>
       </c>
       <c r="D215" t="n">
-        <v>95.34140582196414</v>
+        <v>95.34141330108237</v>
       </c>
       <c r="E215" t="n">
-        <v>96.84447608267267</v>
+        <v>96.84448367970022</v>
       </c>
       <c r="F215" t="n">
         <v>275666</v>
@@ -4732,16 +4732,16 @@
         <v>43537</v>
       </c>
       <c r="B216" t="n">
-        <v>95.78350067138672</v>
+        <v>95.78350830078125</v>
       </c>
       <c r="C216" t="n">
-        <v>97.58128509819149</v>
+        <v>97.58129287078403</v>
       </c>
       <c r="D216" t="n">
-        <v>95.40036726830742</v>
+        <v>95.40037486718441</v>
       </c>
       <c r="E216" t="n">
-        <v>97.43392436737373</v>
+        <v>97.43393212822862</v>
       </c>
       <c r="F216" t="n">
         <v>425833</v>
@@ -4752,16 +4752,16 @@
         <v>43538</v>
       </c>
       <c r="B217" t="n">
-        <v>91.06800079345703</v>
+        <v>91.0679931640625</v>
       </c>
       <c r="C217" t="n">
-        <v>94.86987161113559</v>
+        <v>94.86986366323212</v>
       </c>
       <c r="D217" t="n">
-        <v>90.62592610318003</v>
+        <v>90.62591851082115</v>
       </c>
       <c r="E217" t="n">
-        <v>94.86987161113559</v>
+        <v>94.86986366323212</v>
       </c>
       <c r="F217" t="n">
         <v>2325333</v>
@@ -4772,16 +4772,16 @@
         <v>43539</v>
       </c>
       <c r="B218" t="n">
-        <v>89.29970550537109</v>
+        <v>89.29969787597656</v>
       </c>
       <c r="C218" t="n">
-        <v>92.15847101011371</v>
+        <v>92.15846313647816</v>
       </c>
       <c r="D218" t="n">
-        <v>88.91657206138578</v>
+        <v>88.91656446472457</v>
       </c>
       <c r="E218" t="n">
-        <v>91.06801197874663</v>
+        <v>91.06800419827536</v>
       </c>
       <c r="F218" t="n">
         <v>927800</v>
@@ -4812,16 +4812,16 @@
         <v>43543</v>
       </c>
       <c r="B220" t="n">
-        <v>89.41757965087891</v>
+        <v>89.41758728027344</v>
       </c>
       <c r="C220" t="n">
-        <v>89.41757965087891</v>
+        <v>89.41758728027344</v>
       </c>
       <c r="D220" t="n">
-        <v>86.35251238884096</v>
+        <v>86.35251975671413</v>
       </c>
       <c r="E220" t="n">
-        <v>86.35251238884096</v>
+        <v>86.35251975671413</v>
       </c>
       <c r="F220" t="n">
         <v>1451666</v>
@@ -4872,16 +4872,16 @@
         <v>43546</v>
       </c>
       <c r="B223" t="n">
-        <v>87.82610321044922</v>
+        <v>87.82608795166016</v>
       </c>
       <c r="C223" t="n">
-        <v>87.94398579844682</v>
+        <v>87.94397051917699</v>
       </c>
       <c r="D223" t="n">
-        <v>86.55881292392856</v>
+        <v>86.55879788531681</v>
       </c>
       <c r="E223" t="n">
-        <v>87.94398579844682</v>
+        <v>87.94397051917699</v>
       </c>
       <c r="F223" t="n">
         <v>257266</v>
@@ -4912,16 +4912,16 @@
         <v>43550</v>
       </c>
       <c r="B225" t="n">
-        <v>89.56493377685547</v>
+        <v>89.56494140625</v>
       </c>
       <c r="C225" t="n">
-        <v>89.62387506752287</v>
+        <v>89.62388270193819</v>
       </c>
       <c r="D225" t="n">
-        <v>86.76511004398911</v>
+        <v>86.76511743488673</v>
       </c>
       <c r="E225" t="n">
-        <v>88.20923162596166</v>
+        <v>88.20923913987366</v>
       </c>
       <c r="F225" t="n">
         <v>883933</v>
@@ -4932,16 +4932,16 @@
         <v>43551</v>
       </c>
       <c r="B226" t="n">
-        <v>86.88301086425781</v>
+        <v>86.88300323486328</v>
       </c>
       <c r="C226" t="n">
-        <v>89.29970151647602</v>
+        <v>89.29969367486639</v>
       </c>
       <c r="D226" t="n">
-        <v>86.49986994230797</v>
+        <v>86.4998623465579</v>
       </c>
       <c r="E226" t="n">
-        <v>89.29970151647602</v>
+        <v>89.29969367486639</v>
       </c>
       <c r="F226" t="n">
         <v>691333</v>
@@ -4952,16 +4952,16 @@
         <v>43552</v>
       </c>
       <c r="B227" t="n">
-        <v>90.03649139404297</v>
+        <v>90.03648376464844</v>
       </c>
       <c r="C227" t="n">
-        <v>90.03649139404297</v>
+        <v>90.03648376464844</v>
       </c>
       <c r="D227" t="n">
-        <v>85.58624382921319</v>
+        <v>85.58623657691791</v>
       </c>
       <c r="E227" t="n">
-        <v>86.35251062910731</v>
+        <v>86.35250331188112</v>
       </c>
       <c r="F227" t="n">
         <v>558066</v>
@@ -4972,16 +4972,16 @@
         <v>43553</v>
       </c>
       <c r="B228" t="n">
-        <v>90.6553955078125</v>
+        <v>90.65540313720703</v>
       </c>
       <c r="C228" t="n">
-        <v>91.8047956828475</v>
+        <v>91.80480340897347</v>
       </c>
       <c r="D228" t="n">
-        <v>88.68077976180101</v>
+        <v>88.68078722501544</v>
       </c>
       <c r="E228" t="n">
-        <v>90.77328558797426</v>
+        <v>90.7732932272902</v>
       </c>
       <c r="F228" t="n">
         <v>379666</v>
@@ -5012,16 +5012,16 @@
         <v>43557</v>
       </c>
       <c r="B230" t="n">
-        <v>91.68690490722656</v>
+        <v>91.68691253662109</v>
       </c>
       <c r="C230" t="n">
-        <v>91.92267755141023</v>
+        <v>91.92268520042373</v>
       </c>
       <c r="D230" t="n">
-        <v>89.88912069451767</v>
+        <v>89.88912817431608</v>
       </c>
       <c r="E230" t="n">
-        <v>91.65742676851103</v>
+        <v>91.65743439545264</v>
       </c>
       <c r="F230" t="n">
         <v>264800</v>
@@ -5032,16 +5032,16 @@
         <v>43558</v>
       </c>
       <c r="B231" t="n">
-        <v>88.88709259033203</v>
+        <v>88.88706970214844</v>
       </c>
       <c r="C231" t="n">
-        <v>92.77738326291121</v>
+        <v>92.77735937298839</v>
       </c>
       <c r="D231" t="n">
-        <v>88.88709259033203</v>
+        <v>88.88706970214844</v>
       </c>
       <c r="E231" t="n">
-        <v>92.71843446812262</v>
+        <v>92.71841059337896</v>
       </c>
       <c r="F231" t="n">
         <v>371500</v>
@@ -5052,16 +5052,16 @@
         <v>43559</v>
       </c>
       <c r="B232" t="n">
-        <v>86.35251617431641</v>
+        <v>86.35250091552734</v>
       </c>
       <c r="C232" t="n">
-        <v>90.06596782462189</v>
+        <v>90.06595190965305</v>
       </c>
       <c r="D232" t="n">
-        <v>85.52730053253822</v>
+        <v>85.52728541956763</v>
       </c>
       <c r="E232" t="n">
-        <v>89.59441495859457</v>
+        <v>89.59439912695075</v>
       </c>
       <c r="F232" t="n">
         <v>777800</v>
@@ -5072,16 +5072,16 @@
         <v>43560</v>
       </c>
       <c r="B233" t="n">
-        <v>84.73155975341797</v>
+        <v>84.73154449462891</v>
       </c>
       <c r="C233" t="n">
-        <v>87.94398776449573</v>
+        <v>87.94397192720014</v>
       </c>
       <c r="D233" t="n">
-        <v>84.43683828667913</v>
+        <v>84.43682308096466</v>
       </c>
       <c r="E233" t="n">
-        <v>87.08930900209394</v>
+        <v>87.08929331871222</v>
       </c>
       <c r="F233" t="n">
         <v>673866</v>
@@ -5092,16 +5092,16 @@
         <v>43563</v>
       </c>
       <c r="B234" t="n">
-        <v>82.52117156982422</v>
+        <v>82.52116394042969</v>
       </c>
       <c r="C234" t="n">
-        <v>85.88096032777685</v>
+        <v>85.88095238775713</v>
       </c>
       <c r="D234" t="n">
-        <v>82.25592074967739</v>
+        <v>82.25591314480629</v>
       </c>
       <c r="E234" t="n">
-        <v>85.02627406686121</v>
+        <v>85.02626620586047</v>
       </c>
       <c r="F234" t="n">
         <v>619400</v>
@@ -5112,16 +5112,16 @@
         <v>43564</v>
       </c>
       <c r="B235" t="n">
-        <v>82.81587219238281</v>
+        <v>82.81588745117188</v>
       </c>
       <c r="C235" t="n">
-        <v>84.05369166501009</v>
+        <v>84.05370715186686</v>
       </c>
       <c r="D235" t="n">
-        <v>80.90020544492863</v>
+        <v>80.90022035075691</v>
       </c>
       <c r="E235" t="n">
-        <v>82.2264368466336</v>
+        <v>82.22645199681945</v>
       </c>
       <c r="F235" t="n">
         <v>535633</v>
@@ -5132,16 +5132,16 @@
         <v>43565</v>
       </c>
       <c r="B236" t="n">
-        <v>83.40531158447266</v>
+        <v>83.40531921386719</v>
       </c>
       <c r="C236" t="n">
-        <v>84.2305195353845</v>
+        <v>84.23052724026388</v>
       </c>
       <c r="D236" t="n">
-        <v>81.60752748345887</v>
+        <v>81.60753494840338</v>
       </c>
       <c r="E236" t="n">
-        <v>83.64108421400793</v>
+        <v>83.64109186496947</v>
       </c>
       <c r="F236" t="n">
         <v>456233</v>
@@ -5152,16 +5152,16 @@
         <v>43566</v>
       </c>
       <c r="B237" t="n">
-        <v>84.34842681884766</v>
+        <v>84.34841918945312</v>
       </c>
       <c r="C237" t="n">
-        <v>84.61367014434416</v>
+        <v>84.61366249095812</v>
       </c>
       <c r="D237" t="n">
-        <v>82.40328161658626</v>
+        <v>82.40327416313194</v>
       </c>
       <c r="E237" t="n">
-        <v>83.78846202495211</v>
+        <v>83.78845444620694</v>
       </c>
       <c r="F237" t="n">
         <v>403133</v>
@@ -5272,16 +5272,16 @@
         <v>43577</v>
       </c>
       <c r="B243" t="n">
-        <v>84.58419036865234</v>
+        <v>84.58419799804688</v>
       </c>
       <c r="C243" t="n">
-        <v>86.26408456905386</v>
+        <v>86.26409234997288</v>
       </c>
       <c r="D243" t="n">
-        <v>82.3148607901397</v>
+        <v>82.31486821484337</v>
       </c>
       <c r="E243" t="n">
-        <v>83.49373154636193</v>
+        <v>83.49373907739835</v>
       </c>
       <c r="F243" t="n">
         <v>461666</v>
@@ -5292,16 +5292,16 @@
         <v>43578</v>
       </c>
       <c r="B244" t="n">
-        <v>86.27613830566406</v>
+        <v>86.27613067626953</v>
       </c>
       <c r="C244" t="n">
-        <v>86.77929458213193</v>
+        <v>86.77928690824331</v>
       </c>
       <c r="D244" t="n">
-        <v>84.23392462703995</v>
+        <v>84.23391717823827</v>
       </c>
       <c r="E244" t="n">
-        <v>85.24023717997569</v>
+        <v>85.24022964218584</v>
       </c>
       <c r="F244" t="n">
         <v>437600</v>
@@ -5312,16 +5312,16 @@
         <v>43579</v>
       </c>
       <c r="B245" t="n">
-        <v>86.51291656494141</v>
+        <v>86.51292419433594</v>
       </c>
       <c r="C245" t="n">
-        <v>87.07526500452914</v>
+        <v>87.07527268351602</v>
       </c>
       <c r="D245" t="n">
-        <v>85.06264755574588</v>
+        <v>85.0626550572442</v>
       </c>
       <c r="E245" t="n">
-        <v>86.27613272839055</v>
+        <v>86.27614033690361</v>
       </c>
       <c r="F245" t="n">
         <v>361900</v>
@@ -5332,16 +5332,16 @@
         <v>43580</v>
       </c>
       <c r="B246" t="n">
-        <v>87.90399169921875</v>
+        <v>87.90398406982422</v>
       </c>
       <c r="C246" t="n">
-        <v>88.55513600257547</v>
+        <v>88.5551283166666</v>
       </c>
       <c r="D246" t="n">
-        <v>84.88506908870511</v>
+        <v>84.88506172132999</v>
       </c>
       <c r="E246" t="n">
-        <v>87.01607107054306</v>
+        <v>87.01606351821326</v>
       </c>
       <c r="F246" t="n">
         <v>486633</v>
@@ -5372,16 +5372,16 @@
         <v>43584</v>
       </c>
       <c r="B248" t="n">
-        <v>87.60800170898438</v>
+        <v>87.60800933837891</v>
       </c>
       <c r="C248" t="n">
-        <v>88.910290108505</v>
+        <v>88.91029785131008</v>
       </c>
       <c r="D248" t="n">
-        <v>86.66088903140958</v>
+        <v>86.66089657832424</v>
       </c>
       <c r="E248" t="n">
-        <v>87.87438161869812</v>
+        <v>87.87438927129051</v>
       </c>
       <c r="F248" t="n">
         <v>356166</v>
@@ -5392,16 +5392,16 @@
         <v>43585</v>
       </c>
       <c r="B249" t="n">
-        <v>89.56142425537109</v>
+        <v>89.56143188476562</v>
       </c>
       <c r="C249" t="n">
-        <v>90.27176062526411</v>
+        <v>90.27176831516947</v>
       </c>
       <c r="D249" t="n">
-        <v>86.77927849127832</v>
+        <v>86.77928588367251</v>
       </c>
       <c r="E249" t="n">
-        <v>86.77927849127832</v>
+        <v>86.77928588367251</v>
       </c>
       <c r="F249" t="n">
         <v>318366</v>
@@ -5452,16 +5452,16 @@
         <v>43591</v>
       </c>
       <c r="B252" t="n">
-        <v>90.53813934326172</v>
+        <v>90.53815460205078</v>
       </c>
       <c r="C252" t="n">
-        <v>91.1004877543261</v>
+        <v>91.10050310789021</v>
       </c>
       <c r="D252" t="n">
-        <v>88.19995741003851</v>
+        <v>88.19997227476354</v>
       </c>
       <c r="E252" t="n">
-        <v>88.64391390883252</v>
+        <v>88.64392884837949</v>
       </c>
       <c r="F252" t="n">
         <v>206566</v>
@@ -5472,16 +5472,16 @@
         <v>43592</v>
       </c>
       <c r="B253" t="n">
-        <v>96.93115997314453</v>
+        <v>96.93115234375</v>
       </c>
       <c r="C253" t="n">
-        <v>97.64149639558559</v>
+        <v>97.6414887102809</v>
       </c>
       <c r="D253" t="n">
-        <v>89.47264259147906</v>
+        <v>89.47263554914004</v>
       </c>
       <c r="E253" t="n">
-        <v>90.83411571650254</v>
+        <v>90.83410856700277</v>
       </c>
       <c r="F253" t="n">
         <v>3210933</v>
@@ -5512,16 +5512,16 @@
         <v>43594</v>
       </c>
       <c r="B255" t="n">
-        <v>105.2183990478516</v>
+        <v>105.2184219360352</v>
       </c>
       <c r="C255" t="n">
-        <v>106.3726918979597</v>
+        <v>106.3727150372369</v>
       </c>
       <c r="D255" t="n">
-        <v>99.7724918375764</v>
+        <v>99.7725135411105</v>
       </c>
       <c r="E255" t="n">
-        <v>101.4891405924361</v>
+        <v>101.4891626693933</v>
       </c>
       <c r="F255" t="n">
         <v>781533</v>
@@ -5532,16 +5532,16 @@
         <v>43595</v>
       </c>
       <c r="B256" t="n">
-        <v>103.5905532836914</v>
+        <v>103.5905456542969</v>
       </c>
       <c r="C256" t="n">
-        <v>105.2184063406888</v>
+        <v>105.2183985914037</v>
       </c>
       <c r="D256" t="n">
-        <v>101.3411596167057</v>
+        <v>101.3411521529779</v>
       </c>
       <c r="E256" t="n">
-        <v>105.2184063406888</v>
+        <v>105.2183985914037</v>
       </c>
       <c r="F256" t="n">
         <v>440400</v>
@@ -5552,16 +5552,16 @@
         <v>43598</v>
       </c>
       <c r="B257" t="n">
-        <v>102.9986190795898</v>
+        <v>102.9986267089844</v>
       </c>
       <c r="C257" t="n">
-        <v>102.9986190795898</v>
+        <v>102.9986267089844</v>
       </c>
       <c r="D257" t="n">
-        <v>100.6900254613092</v>
+        <v>100.6900329196998</v>
       </c>
       <c r="E257" t="n">
-        <v>102.3770708804071</v>
+        <v>102.3770784637618</v>
       </c>
       <c r="F257" t="n">
         <v>256966</v>
@@ -5572,16 +5572,16 @@
         <v>43599</v>
       </c>
       <c r="B258" t="n">
-        <v>103.0281982421875</v>
+        <v>103.028205871582</v>
       </c>
       <c r="C258" t="n">
-        <v>104.4192673828053</v>
+        <v>104.4192751152107</v>
       </c>
       <c r="D258" t="n">
-        <v>101.814705669877</v>
+        <v>101.8147132094106</v>
       </c>
       <c r="E258" t="n">
-        <v>102.673030051608</v>
+        <v>102.6730376547018</v>
       </c>
       <c r="F258" t="n">
         <v>522566</v>
@@ -5592,16 +5592,16 @@
         <v>43600</v>
       </c>
       <c r="B259" t="n">
-        <v>103.5905532836914</v>
+        <v>103.5905456542969</v>
       </c>
       <c r="C259" t="n">
-        <v>104.3304858071463</v>
+        <v>104.3304781232561</v>
       </c>
       <c r="D259" t="n">
-        <v>100.9267916830639</v>
+        <v>100.9267842498542</v>
       </c>
       <c r="E259" t="n">
-        <v>101.607532013277</v>
+        <v>101.607524529931</v>
       </c>
       <c r="F259" t="n">
         <v>328866</v>
@@ -5612,16 +5612,16 @@
         <v>43601</v>
       </c>
       <c r="B260" t="n">
-        <v>102.5842361450195</v>
+        <v>102.5842437744141</v>
       </c>
       <c r="C260" t="n">
-        <v>103.6793368318073</v>
+        <v>103.6793445426467</v>
       </c>
       <c r="D260" t="n">
-        <v>102.5842361450195</v>
+        <v>102.5842437744141</v>
       </c>
       <c r="E260" t="n">
-        <v>103.5905485460052</v>
+        <v>103.5905562502412</v>
       </c>
       <c r="F260" t="n">
         <v>583833</v>
@@ -5632,16 +5632,16 @@
         <v>43602</v>
       </c>
       <c r="B261" t="n">
-        <v>102.9690246582031</v>
+        <v>102.9690170288086</v>
       </c>
       <c r="C261" t="n">
-        <v>103.5609692404666</v>
+        <v>103.5609615672124</v>
       </c>
       <c r="D261" t="n">
-        <v>101.5483516391839</v>
+        <v>101.5483441150528</v>
       </c>
       <c r="E261" t="n">
-        <v>102.9394210311538</v>
+        <v>102.9394134039527</v>
       </c>
       <c r="F261" t="n">
         <v>361233</v>
@@ -5672,16 +5672,16 @@
         <v>43606</v>
       </c>
       <c r="B263" t="n">
-        <v>108.3557281494141</v>
+        <v>108.355712890625</v>
       </c>
       <c r="C263" t="n">
-        <v>109.8355933002327</v>
+        <v>109.8355778330471</v>
       </c>
       <c r="D263" t="n">
-        <v>105.8103582835301</v>
+        <v>105.8103433831832</v>
       </c>
       <c r="E263" t="n">
-        <v>105.8103582835301</v>
+        <v>105.8103433831832</v>
       </c>
       <c r="F263" t="n">
         <v>554800</v>
@@ -5712,16 +5712,16 @@
         <v>43608</v>
       </c>
       <c r="B265" t="n">
-        <v>110.989875793457</v>
+        <v>110.9898834228516</v>
       </c>
       <c r="C265" t="n">
-        <v>112.4697408040365</v>
+        <v>112.4697485351563</v>
       </c>
       <c r="D265" t="n">
-        <v>109.1844386740743</v>
+        <v>109.1844461793639</v>
       </c>
       <c r="E265" t="n">
-        <v>109.3324266805288</v>
+        <v>109.332434195991</v>
       </c>
       <c r="F265" t="n">
         <v>449966</v>
@@ -5772,16 +5772,16 @@
         <v>43613</v>
       </c>
       <c r="B268" t="n">
-        <v>109.3028411865234</v>
+        <v>109.3028335571289</v>
       </c>
       <c r="C268" t="n">
-        <v>111.0786748552771</v>
+        <v>111.0786671019285</v>
       </c>
       <c r="D268" t="n">
-        <v>107.0830434553438</v>
+        <v>107.0830359808923</v>
       </c>
       <c r="E268" t="n">
-        <v>110.5755261223044</v>
+        <v>110.5755184040759</v>
       </c>
       <c r="F268" t="n">
         <v>402233</v>
@@ -5792,16 +5792,16 @@
         <v>43614</v>
       </c>
       <c r="B269" t="n">
-        <v>109.9243850708008</v>
+        <v>109.9243774414062</v>
       </c>
       <c r="C269" t="n">
-        <v>110.1019691955914</v>
+        <v>110.1019615538715</v>
       </c>
       <c r="D269" t="n">
-        <v>108.3557315743034</v>
+        <v>108.3557240537826</v>
       </c>
       <c r="E269" t="n">
-        <v>109.2732482978909</v>
+        <v>109.2732407136891</v>
       </c>
       <c r="F269" t="n">
         <v>725533</v>
@@ -5812,16 +5812,16 @@
         <v>43615</v>
       </c>
       <c r="B270" t="n">
-        <v>107.7045822143555</v>
+        <v>107.7045745849609</v>
       </c>
       <c r="C270" t="n">
-        <v>111.6410213474626</v>
+        <v>111.6410134392252</v>
       </c>
       <c r="D270" t="n">
-        <v>107.7045822143555</v>
+        <v>107.7045745849609</v>
       </c>
       <c r="E270" t="n">
-        <v>109.9243799064583</v>
+        <v>109.9243721198215</v>
       </c>
       <c r="F270" t="n">
         <v>452966</v>
@@ -5832,16 +5832,16 @@
         <v>43616</v>
       </c>
       <c r="B271" t="n">
-        <v>108.8588714599609</v>
+        <v>108.8588790893555</v>
       </c>
       <c r="C271" t="n">
-        <v>110.4275323557388</v>
+        <v>110.4275400950732</v>
       </c>
       <c r="D271" t="n">
-        <v>106.8462540518404</v>
+        <v>106.8462615401803</v>
       </c>
       <c r="E271" t="n">
-        <v>107.4086100070495</v>
+        <v>107.4086175348022</v>
       </c>
       <c r="F271" t="n">
         <v>504400</v>
@@ -5852,16 +5852,16 @@
         <v>43619</v>
       </c>
       <c r="B272" t="n">
-        <v>109.8651809692383</v>
+        <v>109.8651885986328</v>
       </c>
       <c r="C272" t="n">
-        <v>110.7531014969981</v>
+        <v>110.7531091880527</v>
       </c>
       <c r="D272" t="n">
-        <v>108.6220922303745</v>
+        <v>108.622099773445</v>
       </c>
       <c r="E272" t="n">
-        <v>108.7996763359265</v>
+        <v>108.7996838913289</v>
       </c>
       <c r="F272" t="n">
         <v>294000</v>
@@ -5872,16 +5872,16 @@
         <v>43620</v>
       </c>
       <c r="B273" t="n">
-        <v>107.1718139648438</v>
+        <v>107.1718215942383</v>
       </c>
       <c r="C273" t="n">
-        <v>110.9898681385225</v>
+        <v>110.9898760397184</v>
       </c>
       <c r="D273" t="n">
-        <v>107.1718139648438</v>
+        <v>107.1718215942383</v>
       </c>
       <c r="E273" t="n">
-        <v>109.5987915115683</v>
+        <v>109.5987993137355</v>
       </c>
       <c r="F273" t="n">
         <v>283866</v>
@@ -5892,16 +5892,16 @@
         <v>43621</v>
       </c>
       <c r="B274" t="n">
-        <v>108.8884658813477</v>
+        <v>108.8884811401367</v>
       </c>
       <c r="C274" t="n">
-        <v>109.83557854742</v>
+        <v>109.8355939389301</v>
       </c>
       <c r="D274" t="n">
-        <v>106.4022885467982</v>
+        <v>106.4023034571936</v>
       </c>
       <c r="E274" t="n">
-        <v>106.6390648315707</v>
+        <v>106.6390797751461</v>
       </c>
       <c r="F274" t="n">
         <v>231033</v>
@@ -5952,16 +5952,16 @@
         <v>43626</v>
       </c>
       <c r="B277" t="n">
-        <v>114.3935546875</v>
+        <v>114.3935699462891</v>
       </c>
       <c r="C277" t="n">
-        <v>119.395497789011</v>
+        <v>119.395513715002</v>
       </c>
       <c r="D277" t="n">
-        <v>111.8777888532741</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="E277" t="n">
-        <v>111.8777888532741</v>
+        <v>111.8778037764888</v>
       </c>
       <c r="F277" t="n">
         <v>585833</v>
@@ -5972,16 +5972,16 @@
         <v>43627</v>
       </c>
       <c r="B278" t="n">
-        <v>110.989875793457</v>
+        <v>110.9898834228516</v>
       </c>
       <c r="C278" t="n">
-        <v>116.6725595416372</v>
+        <v>116.6725675616569</v>
       </c>
       <c r="D278" t="n">
-        <v>110.989875793457</v>
+        <v>110.9898834228516</v>
       </c>
       <c r="E278" t="n">
-        <v>116.4653718164113</v>
+        <v>116.465379822189</v>
       </c>
       <c r="F278" t="n">
         <v>422033</v>
@@ -6012,16 +6012,16 @@
         <v>43629</v>
       </c>
       <c r="B280" t="n">
-        <v>113.8608169555664</v>
+        <v>113.8608093261719</v>
       </c>
       <c r="C280" t="n">
-        <v>114.9855138301545</v>
+        <v>114.9855061253982</v>
       </c>
       <c r="D280" t="n">
-        <v>108.9180729377125</v>
+        <v>108.9180656395131</v>
       </c>
       <c r="E280" t="n">
-        <v>108.9180729377125</v>
+        <v>108.9180656395131</v>
       </c>
       <c r="F280" t="n">
         <v>845300</v>
@@ -6032,16 +6032,16 @@
         <v>43630</v>
       </c>
       <c r="B281" t="n">
-        <v>111.9369964599609</v>
+        <v>111.9370040893555</v>
       </c>
       <c r="C281" t="n">
-        <v>114.156794133742</v>
+        <v>114.1568019144333</v>
       </c>
       <c r="D281" t="n">
-        <v>110.753107378071</v>
+        <v>110.7531149267741</v>
       </c>
       <c r="E281" t="n">
-        <v>113.3576693798154</v>
+        <v>113.3576771060401</v>
       </c>
       <c r="F281" t="n">
         <v>560666</v>
@@ -6072,16 +6072,16 @@
         <v>43634</v>
       </c>
       <c r="B283" t="n">
-        <v>112.4697418212891</v>
+        <v>112.4697570800781</v>
       </c>
       <c r="C283" t="n">
-        <v>113.1800782371092</v>
+        <v>113.1800935922697</v>
       </c>
       <c r="D283" t="n">
-        <v>110.0131679890634</v>
+        <v>110.0131829145687</v>
       </c>
       <c r="E283" t="n">
-        <v>110.9602807011627</v>
+        <v>110.9602957551629</v>
       </c>
       <c r="F283" t="n">
         <v>583133</v>
@@ -6092,16 +6092,16 @@
         <v>43635</v>
       </c>
       <c r="B284" t="n">
-        <v>115.3702774047852</v>
+        <v>115.3702850341797</v>
       </c>
       <c r="C284" t="n">
-        <v>115.3702774047852</v>
+        <v>115.3702850341797</v>
       </c>
       <c r="D284" t="n">
-        <v>111.6114151995947</v>
+        <v>111.6114225804171</v>
       </c>
       <c r="E284" t="n">
-        <v>112.3513476970046</v>
+        <v>112.3513551267584</v>
       </c>
       <c r="F284" t="n">
         <v>441733</v>
@@ -6152,16 +6152,16 @@
         <v>43641</v>
       </c>
       <c r="B287" t="n">
-        <v>114.4823608398438</v>
+        <v>114.4823684692383</v>
       </c>
       <c r="C287" t="n">
-        <v>117.1165188147427</v>
+        <v>117.1165266196842</v>
       </c>
       <c r="D287" t="n">
-        <v>113.8312166067768</v>
+        <v>113.8312241927775</v>
       </c>
       <c r="E287" t="n">
-        <v>116.5837664950469</v>
+        <v>116.5837742644845</v>
       </c>
       <c r="F287" t="n">
         <v>481433</v>
@@ -6172,16 +6172,16 @@
         <v>43642</v>
       </c>
       <c r="B288" t="n">
-        <v>113.1208877563477</v>
+        <v>113.1208801269531</v>
       </c>
       <c r="C288" t="n">
-        <v>115.72544980908</v>
+        <v>115.7254420040218</v>
       </c>
       <c r="D288" t="n">
-        <v>112.6769312236937</v>
+        <v>112.6769236242416</v>
       </c>
       <c r="E288" t="n">
-        <v>115.72544980908</v>
+        <v>115.7254420040218</v>
       </c>
       <c r="F288" t="n">
         <v>335833</v>
@@ -6192,16 +6192,16 @@
         <v>43643</v>
       </c>
       <c r="B289" t="n">
-        <v>115.2815017700195</v>
+        <v>115.281494140625</v>
       </c>
       <c r="C289" t="n">
-        <v>115.2815017700195</v>
+        <v>115.281494140625</v>
       </c>
       <c r="D289" t="n">
-        <v>112.9137158584524</v>
+        <v>112.9137083857593</v>
       </c>
       <c r="E289" t="n">
-        <v>113.3872760515594</v>
+        <v>113.3872685475258</v>
       </c>
       <c r="F289" t="n">
         <v>276700</v>
@@ -6212,16 +6212,16 @@
         <v>43644</v>
       </c>
       <c r="B290" t="n">
-        <v>116.7021560668945</v>
+        <v>116.7021636962891</v>
       </c>
       <c r="C290" t="n">
-        <v>117.649268773912</v>
+        <v>117.6492764652239</v>
       </c>
       <c r="D290" t="n">
-        <v>114.1271903368541</v>
+        <v>114.1271977979104</v>
       </c>
       <c r="E290" t="n">
-        <v>115.0743030438715</v>
+        <v>115.0743105668453</v>
       </c>
       <c r="F290" t="n">
         <v>617600</v>
@@ -6272,16 +6272,16 @@
         <v>43649</v>
       </c>
       <c r="B293" t="n">
-        <v>109.9691696166992</v>
+        <v>109.9691619873047</v>
       </c>
       <c r="C293" t="n">
-        <v>110.8608130442187</v>
+        <v>110.8608053529641</v>
       </c>
       <c r="D293" t="n">
-        <v>107.3239670805098</v>
+        <v>107.323959634633</v>
       </c>
       <c r="E293" t="n">
-        <v>110.7122045465418</v>
+        <v>110.7121968655973</v>
       </c>
       <c r="F293" t="n">
         <v>1690900</v>
@@ -6292,16 +6292,16 @@
         <v>43650</v>
       </c>
       <c r="B294" t="n">
-        <v>114.1004333496094</v>
+        <v>114.1004486083984</v>
       </c>
       <c r="C294" t="n">
-        <v>114.1004333496094</v>
+        <v>114.1004486083984</v>
       </c>
       <c r="D294" t="n">
-        <v>109.4044550659338</v>
+        <v>109.404469696724</v>
       </c>
       <c r="E294" t="n">
-        <v>109.9691612673977</v>
+        <v>109.9691759737067</v>
       </c>
       <c r="F294" t="n">
         <v>412866</v>
@@ -6312,16 +6312,16 @@
         <v>43651</v>
       </c>
       <c r="B295" t="n">
-        <v>117.5184020996094</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="C295" t="n">
-        <v>117.5184020996094</v>
+        <v>117.5183944702148</v>
       </c>
       <c r="D295" t="n">
-        <v>112.9115842237956</v>
+        <v>112.9115768934796</v>
       </c>
       <c r="E295" t="n">
-        <v>114.0707168497463</v>
+        <v>114.0707094441784</v>
       </c>
       <c r="F295" t="n">
         <v>288866</v>
@@ -6332,16 +6332,16 @@
         <v>43654</v>
       </c>
       <c r="B296" t="n">
-        <v>121.9171676635742</v>
+        <v>121.9171752929688</v>
       </c>
       <c r="C296" t="n">
-        <v>122.8682514573375</v>
+        <v>122.8682591462495</v>
       </c>
       <c r="D296" t="n">
-        <v>115.4081820448956</v>
+        <v>115.4081892669675</v>
       </c>
       <c r="E296" t="n">
-        <v>117.4886783161617</v>
+        <v>117.488685668428</v>
       </c>
       <c r="F296" t="n">
         <v>420600</v>
@@ -6352,16 +6352,16 @@
         <v>43656</v>
       </c>
       <c r="B297" t="n">
-        <v>128.0397796630859</v>
+        <v>128.0397644042969</v>
       </c>
       <c r="C297" t="n">
-        <v>128.0397796630859</v>
+        <v>128.0397644042969</v>
       </c>
       <c r="D297" t="n">
-        <v>121.9171642141075</v>
+        <v>121.9171496849643</v>
       </c>
       <c r="E297" t="n">
-        <v>121.9171642141075</v>
+        <v>121.9171496849643</v>
       </c>
       <c r="F297" t="n">
         <v>529166</v>
@@ -6372,16 +6372,16 @@
         <v>43657</v>
       </c>
       <c r="B298" t="n">
-        <v>123.1654586791992</v>
+        <v>123.1654663085938</v>
       </c>
       <c r="C298" t="n">
-        <v>130.1797020465908</v>
+        <v>130.1797101104775</v>
       </c>
       <c r="D298" t="n">
-        <v>123.1060183088487</v>
+        <v>123.1060259345613</v>
       </c>
       <c r="E298" t="n">
-        <v>130.1797020465908</v>
+        <v>130.1797101104775</v>
       </c>
       <c r="F298" t="n">
         <v>660700</v>
@@ -6412,16 +6412,16 @@
         <v>43661</v>
       </c>
       <c r="B300" t="n">
-        <v>121.5604934692383</v>
+        <v>121.5605010986328</v>
       </c>
       <c r="C300" t="n">
-        <v>126.732017023280